--- a/results/PACLock_baseline_matrix_filled.xlsx
+++ b/results/PACLock_baseline_matrix_filled.xlsx
@@ -3431,6 +3431,7 @@
     <col width="17" customWidth="1" style="220" min="4" max="4"/>
     <col width="17" customWidth="1" style="219" min="5" max="7"/>
     <col width="17" customWidth="1" style="220" min="6" max="6"/>
+    <col width="17" customWidth="1" style="220" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1" s="220">
@@ -3443,7 +3444,8 @@
       <c r="C1" s="228" t="n"/>
       <c r="D1" s="228" t="n"/>
       <c r="E1" s="228" t="n"/>
-      <c r="F1" s="229" t="n"/>
+      <c r="F1" s="228" t="n"/>
+      <c r="G1" s="229" t="n"/>
     </row>
     <row r="2" ht="22" customHeight="1" s="220">
       <c r="A2" s="267" t="inlineStr">
@@ -3451,7 +3453,7 @@
           <t>主指标：Balanced Accuracy</t>
         </is>
       </c>
-      <c r="F2" s="231" t="n"/>
+      <c r="G2" s="231" t="n"/>
     </row>
     <row r="3" ht="8" customHeight="1" s="220">
       <c r="A3" s="268" t="n"/>
@@ -3460,7 +3462,7 @@
       <c r="D3" s="268" t="n"/>
       <c r="E3" s="268" t="n"/>
       <c r="F3" s="268" t="n"/>
-      <c r="G3" s="269" t="n"/>
+      <c r="G3" s="268" t="n"/>
     </row>
     <row r="4" ht="28" customHeight="1" s="220">
       <c r="A4" s="270" t="inlineStr">
@@ -3493,6 +3495,11 @@
           <t>Weighted F1</t>
         </is>
       </c>
+      <c r="G4" s="270" t="inlineStr">
+        <is>
+          <t>ΔBalanced Acc vs PACLock</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="20" customHeight="1" s="220">
       <c r="A5" s="271" t="inlineStr">
@@ -3521,6 +3528,11 @@
       <c r="F5" s="274" t="inlineStr">
         <is>
           <t>0.6428±0.0068</t>
+        </is>
+      </c>
+      <c r="G5" s="274" t="inlineStr">
+        <is>
+          <t>+0.2852</t>
         </is>
       </c>
     </row>
@@ -3549,6 +3561,11 @@
           <t>0.4861±0.0153</t>
         </is>
       </c>
+      <c r="G6" s="279" t="inlineStr">
+        <is>
+          <t>+0.1334</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="20" customHeight="1" s="220">
       <c r="A7" s="276" t="n"/>
@@ -3563,6 +3580,7 @@
       <c r="D7" s="279" t="n"/>
       <c r="E7" s="279" t="n"/>
       <c r="F7" s="279" t="n"/>
+      <c r="G7" s="279" t="n"/>
     </row>
     <row r="8" ht="20" customHeight="1" s="220">
       <c r="A8" s="276" t="n"/>
@@ -3589,6 +3607,11 @@
           <t>0.4858±0.0093</t>
         </is>
       </c>
+      <c r="G8" s="279" t="inlineStr">
+        <is>
+          <t>+0.1303</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="20" customHeight="1" s="220">
       <c r="A9" s="276" t="n"/>
@@ -3615,6 +3638,11 @@
           <t>0.5461±0.0228</t>
         </is>
       </c>
+      <c r="G9" s="279" t="inlineStr">
+        <is>
+          <t>+0.1883</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="20" customHeight="1" s="220">
       <c r="A10" s="271" t="inlineStr">
@@ -3643,6 +3671,11 @@
       <c r="F10" s="283" t="inlineStr">
         <is>
           <t>0.4557±0.0139</t>
+        </is>
+      </c>
+      <c r="G10" s="283" t="inlineStr">
+        <is>
+          <t>+0.1074</t>
         </is>
       </c>
     </row>
@@ -3658,17 +3691,22 @@
       </c>
       <c r="D11" s="279" t="inlineStr">
         <is>
-          <t>0.3938±0.0240</t>
+          <t>0.4227±0.0246</t>
         </is>
       </c>
       <c r="E11" s="279" t="inlineStr">
         <is>
-          <t>0.1917±0.0320</t>
+          <t>0.2303±0.0329</t>
         </is>
       </c>
       <c r="F11" s="279" t="inlineStr">
         <is>
-          <t>0.3781±0.0365</t>
+          <t>0.4224±0.0240</t>
+        </is>
+      </c>
+      <c r="G11" s="279" t="inlineStr">
+        <is>
+          <t>+0.0639</t>
         </is>
       </c>
     </row>
@@ -3684,17 +3722,22 @@
       </c>
       <c r="D12" s="279" t="inlineStr">
         <is>
-          <t>0.5379±0.0019</t>
+          <t>0.5293±0.0036</t>
         </is>
       </c>
       <c r="E12" s="279" t="inlineStr">
         <is>
-          <t>0.3839±0.0026</t>
+          <t>0.3724±0.0048</t>
         </is>
       </c>
       <c r="F12" s="279" t="inlineStr">
         <is>
-          <t>0.5373±0.0009</t>
+          <t>0.5300±0.0036</t>
+        </is>
+      </c>
+      <c r="G12" s="279" t="inlineStr">
+        <is>
+          <t>+0.1705</t>
         </is>
       </c>
     </row>
@@ -3723,6 +3766,11 @@
           <t>0.3639±0.0144</t>
         </is>
       </c>
+      <c r="G13" s="279" t="inlineStr">
+        <is>
+          <t>+0.0185</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="20" customHeight="1" s="220">
       <c r="A14" s="276" t="n"/>
@@ -3749,6 +3797,11 @@
           <t>0.3364±0.0185</t>
         </is>
       </c>
+      <c r="G14" s="279" t="inlineStr">
+        <is>
+          <t>-0.0183</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="20" customHeight="1" s="220">
       <c r="A15" s="271" t="inlineStr">
@@ -3777,6 +3830,11 @@
       <c r="F15" s="287" t="inlineStr">
         <is>
           <t>0.3219±0.0057</t>
+        </is>
+      </c>
+      <c r="G15" s="287" t="inlineStr">
+        <is>
+          <t>-0.0307</t>
         </is>
       </c>
     </row>
@@ -3788,11 +3846,28 @@
         </is>
       </c>
       <c r="C16" s="278" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="D16" s="279" t="n"/>
-      <c r="E16" s="279" t="n"/>
-      <c r="F16" s="279" t="n"/>
+        <v>5.82</v>
+      </c>
+      <c r="D16" s="279" t="inlineStr">
+        <is>
+          <t>0.3147±0.0124</t>
+        </is>
+      </c>
+      <c r="E16" s="279" t="inlineStr">
+        <is>
+          <t>0.0862±0.0165</t>
+        </is>
+      </c>
+      <c r="F16" s="279" t="inlineStr">
+        <is>
+          <t>0.2972±0.0130</t>
+        </is>
+      </c>
+      <c r="G16" s="279" t="inlineStr">
+        <is>
+          <t>-0.0441</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="20" customHeight="1" s="220">
       <c r="A17" s="276" t="n"/>
@@ -3802,11 +3877,28 @@
         </is>
       </c>
       <c r="C17" s="278" t="n">
-        <v>4</v>
-      </c>
-      <c r="D17" s="279" t="n"/>
-      <c r="E17" s="279" t="n"/>
-      <c r="F17" s="279" t="n"/>
+        <v>19.13</v>
+      </c>
+      <c r="D17" s="279" t="inlineStr">
+        <is>
+          <t>0.3043±0.0083</t>
+        </is>
+      </c>
+      <c r="E17" s="279" t="inlineStr">
+        <is>
+          <t>0.0724±0.0111</t>
+        </is>
+      </c>
+      <c r="F17" s="279" t="inlineStr">
+        <is>
+          <t>0.3013±0.0114</t>
+        </is>
+      </c>
+      <c r="G17" s="279" t="inlineStr">
+        <is>
+          <t>-0.0545</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="20" customHeight="1" s="220">
       <c r="A18" s="276" t="n"/>
@@ -3816,23 +3908,24 @@
         </is>
       </c>
       <c r="C18" s="290" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="D18" s="291" t="inlineStr">
         <is>
-          <t>0.2775±0.0051</t>
+          <t>0.3588±0.0042</t>
         </is>
       </c>
       <c r="E18" s="291" t="inlineStr">
         <is>
-          <t>0.0367±0.0068</t>
+          <t>0.1451±0.0057</t>
         </is>
       </c>
       <c r="F18" s="291" t="inlineStr">
         <is>
-          <t>0.2559±0.0128</t>
-        </is>
-      </c>
+          <t>0.3446±0.0201</t>
+        </is>
+      </c>
+      <c r="G18" s="291" t="n"/>
     </row>
     <row r="19" ht="13.75" customHeight="1" s="220"/>
     <row r="20" ht="24" customHeight="1" s="220"/>
@@ -3855,8 +3948,8 @@
     <row r="37" ht="38" customHeight="1" s="220"/>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A2:G2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" scale="100" fitToHeight="1" fitToWidth="1" firstPageNumber="1" useFirstPageNumber="0" pageOrder="downThenOver"/>
@@ -3877,7 +3970,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F164"/>
+  <dimension ref="A1:F178"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4026,12 +4119,12 @@
       </c>
       <c r="E5" s="219" t="inlineStr">
         <is>
-          <t>[实测 19.13M] balanced_acc per-seed 0:0.5405, 1:0.5359, 2:0.5374</t>
+          <t>[实测 19.13M] balanced_acc per-seed 0:0.5278, 1:0.5258, 2:0.5343</t>
         </is>
       </c>
       <c r="F5" s="219" t="inlineStr">
         <is>
-          <t>lr=0.0001 batch_size=64 epochs=50 patience=10 eval_every_steps=0 loss=cross_entropy label_smoothing=0.1 multi_lr=True</t>
+          <t>lr=0.0001 batch_size=64 epochs=50 patience=0 eval_every_steps=0 loss=cross_entropy label_smoothing=0.1 grad_clip=1.0 multi_lr=True</t>
         </is>
       </c>
     </row>
@@ -4043,7 +4136,7 @@
       </c>
       <c r="B6" s="219" t="inlineStr">
         <is>
-          <t>cnn_transformer</t>
+          <t>cbramod_scratch</t>
         </is>
       </c>
       <c r="C6" s="219" t="inlineStr">
@@ -4053,12 +4146,17 @@
       </c>
       <c r="D6" s="219" t="inlineStr">
         <is>
-          <t>withheld (rule 3)</t>
+          <t>filled</t>
         </is>
       </c>
       <c r="E6" s="219" t="inlineStr">
         <is>
-          <t>mis-configured seeds [2]: {2: 'val curve is flat (model not learning)'}; measured balanced_acc 0.2614±0.0081</t>
+          <t>[实测 19.13M] balanced_acc per-seed 0:0.2975, 1:0.3160, 2:0.2994</t>
+        </is>
+      </c>
+      <c r="F6" s="219" t="inlineStr">
+        <is>
+          <t>lr=0.0001 batch_size=64 epochs=50 patience=0 eval_every_steps=0 loss=cross_entropy label_smoothing=0.1 grad_clip=1.0 multi_lr=True</t>
         </is>
       </c>
     </row>
@@ -4070,7 +4168,7 @@
       </c>
       <c r="B7" s="219" t="inlineStr">
         <is>
-          <t>contrawr</t>
+          <t>cnn_transformer</t>
         </is>
       </c>
       <c r="C7" s="219" t="inlineStr">
@@ -4080,17 +4178,12 @@
       </c>
       <c r="D7" s="219" t="inlineStr">
         <is>
-          <t>filled</t>
+          <t>withheld (rule 3)</t>
         </is>
       </c>
       <c r="E7" s="219" t="inlineStr">
         <is>
-          <t>[实测 1.58M] balanced_acc per-seed 0:0.4969, 1:0.4769, 2:0.5027</t>
-        </is>
-      </c>
-      <c r="F7" s="219" t="inlineStr">
-        <is>
-          <t>lr=0.001 batch_size=16 epochs=100 patience=20 eval_every_steps=0 loss=cross_entropy label_smoothing=0.1</t>
+          <t>mis-configured seeds [2]: {2: 'val curve is flat (model not learning)'}; measured balanced_acc 0.2614±0.0081</t>
         </is>
       </c>
     </row>
@@ -4102,7 +4195,7 @@
       </c>
       <c r="B8" s="219" t="inlineStr">
         <is>
-          <t>eegpt_pretrained</t>
+          <t>contrawr</t>
         </is>
       </c>
       <c r="C8" s="219" t="inlineStr">
@@ -4117,12 +4210,12 @@
       </c>
       <c r="E8" s="219" t="inlineStr">
         <is>
-          <t>[实测 25.69M] balanced_acc per-seed 0:0.3935, 1:0.3889, 2:0.3495</t>
+          <t>[实测 1.58M] balanced_acc per-seed 0:0.4969, 1:0.4769, 2:0.5027</t>
         </is>
       </c>
       <c r="F8" s="219" t="inlineStr">
         <is>
-          <t>lr=0.0004 batch_size=32 epochs=100 patience=10 eval_every_steps=0 loss=cross_entropy</t>
+          <t>lr=0.001 batch_size=16 epochs=100 patience=20 eval_every_steps=0 loss=cross_entropy label_smoothing=0.1</t>
         </is>
       </c>
     </row>
@@ -4134,7 +4227,7 @@
       </c>
       <c r="B9" s="219" t="inlineStr">
         <is>
-          <t>ffcl</t>
+          <t>eegpt_pretrained</t>
         </is>
       </c>
       <c r="C9" s="219" t="inlineStr">
@@ -4149,12 +4242,12 @@
       </c>
       <c r="E9" s="219" t="inlineStr">
         <is>
-          <t>[实测 2.41M] balanced_acc per-seed 0:0.4954, 1:0.4753, 2:0.4965</t>
+          <t>[实测 25.69M] balanced_acc per-seed 0:0.3935, 1:0.3889, 2:0.3495</t>
         </is>
       </c>
       <c r="F9" s="219" t="inlineStr">
         <is>
-          <t>lr=0.001 batch_size=16 epochs=100 patience=20 eval_every_steps=0 loss=cross_entropy label_smoothing=0.1</t>
+          <t>lr=0.0004 batch_size=32 epochs=100 patience=10 eval_every_steps=0 loss=cross_entropy</t>
         </is>
       </c>
     </row>
@@ -4166,7 +4259,7 @@
       </c>
       <c r="B10" s="219" t="inlineStr">
         <is>
-          <t>labram_pretrained</t>
+          <t>ffcl</t>
         </is>
       </c>
       <c r="C10" s="219" t="inlineStr">
@@ -4181,12 +4274,12 @@
       </c>
       <c r="E10" s="219" t="inlineStr">
         <is>
-          <t>[实测 5.82M] balanced_acc per-seed 0:0.4198, 1:0.3997, 2:0.3619</t>
+          <t>[实测 2.41M] balanced_acc per-seed 0:0.4954, 1:0.4753, 2:0.4965</t>
         </is>
       </c>
       <c r="F10" s="219" t="inlineStr">
         <is>
-          <t>lr=0.0005 batch_size=64 epochs=50 patience=10 eval_every_steps=0 loss=cross_entropy loader_divisor=1.0</t>
+          <t>lr=0.001 batch_size=16 epochs=100 patience=20 eval_every_steps=0 loss=cross_entropy label_smoothing=0.1</t>
         </is>
       </c>
     </row>
@@ -4198,7 +4291,7 @@
       </c>
       <c r="B11" s="219" t="inlineStr">
         <is>
-          <t>paclock_full</t>
+          <t>labram_pretrained</t>
         </is>
       </c>
       <c r="C11" s="219" t="inlineStr">
@@ -4213,12 +4306,12 @@
       </c>
       <c r="E11" s="219" t="inlineStr">
         <is>
-          <t>[实测 1.62M] balanced_acc per-seed 0:0.2762, 1:0.2720, 2:0.2843</t>
+          <t>[实测 5.82M] balanced_acc per-seed 0:0.4309, 1:0.3893, 2:0.4479</t>
         </is>
       </c>
       <c r="F11" s="219" t="inlineStr">
         <is>
-          <t>lr=0.0001 batch_size=32 epochs=638 patience=20 eval_every_steps=0 loss=cross_entropy label_smoothing=0.1 grad_clip=1.0 tokenizer_mode=pac_interaction pac_token_mode=measured interaction_mode=product band_pe=index spatial_pe=index</t>
+          <t>stopped_by=patience lr=0.0005 batch_size=64 epochs=50 patience=10 eval_every_steps=0 loss=cross_entropy label_smoothing=0.1 loader_divisor=1.0</t>
         </is>
       </c>
     </row>
@@ -4230,22 +4323,27 @@
       </c>
       <c r="B12" s="219" t="inlineStr">
         <is>
-          <t>paclock_pac</t>
+          <t>labram_scratch</t>
         </is>
       </c>
       <c r="C12" s="219" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>[0, 1, 2]</t>
         </is>
       </c>
       <c r="D12" s="219" t="inlineStr">
         <is>
-          <t>skipped</t>
+          <t>filled</t>
         </is>
       </c>
       <c r="E12" s="219" t="inlineStr">
         <is>
-          <t>the workbook has no row for this variant</t>
+          <t>[实测 5.82M] balanced_acc per-seed 0:0.2986, 1:0.3287, 2:0.3167</t>
+        </is>
+      </c>
+      <c r="F12" s="219" t="inlineStr">
+        <is>
+          <t>stopped_by=patience lr=0.0005 batch_size=64 epochs=50 patience=10 eval_every_steps=0 loss=cross_entropy label_smoothing=0.1 loader_divisor=1.0</t>
         </is>
       </c>
     </row>
@@ -4257,27 +4355,22 @@
       </c>
       <c r="B13" s="219" t="inlineStr">
         <is>
-          <t>sparcnet</t>
+          <t>paclock_pac</t>
         </is>
       </c>
       <c r="C13" s="219" t="inlineStr">
         <is>
-          <t>[0, 1, 2]</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D13" s="219" t="inlineStr">
         <is>
-          <t>filled</t>
+          <t>skipped</t>
         </is>
       </c>
       <c r="E13" s="219" t="inlineStr">
         <is>
-          <t>[实测 0.99M] balanced_acc per-seed 0:0.6539, 1:0.6397, 2:0.6385</t>
-        </is>
-      </c>
-      <c r="F13" s="219" t="inlineStr">
-        <is>
-          <t>lr=0.001 batch_size=16 epochs=100 patience=20 eval_every_steps=0 loss=cross_entropy label_smoothing=0.1</t>
+          <t>the workbook has no row for this variant</t>
         </is>
       </c>
     </row>
@@ -4289,7 +4382,7 @@
       </c>
       <c r="B14" s="219" t="inlineStr">
         <is>
-          <t>st_transformer</t>
+          <t>paclock_v2</t>
         </is>
       </c>
       <c r="C14" s="219" t="inlineStr">
@@ -4304,12 +4397,12 @@
       </c>
       <c r="E14" s="219" t="inlineStr">
         <is>
-          <t>[实测 3.43M] balanced_acc per-seed 0:0.5729, 1:0.5185, 2:0.5498</t>
+          <t>[实测 1.60M] balanced_acc per-seed 0:0.3630, 1:0.3530, 2:0.3603</t>
         </is>
       </c>
       <c r="F14" s="219" t="inlineStr">
         <is>
-          <t>lr=0.001 batch_size=16 epochs=100 patience=20 eval_every_steps=0 loss=cross_entropy label_smoothing=0.1</t>
+          <t>stopped_by=patience lr=0.0001 batch_size=32 epochs=638 patience=20 eval_every_steps=0 loss=cross_entropy label_smoothing=0.1 grad_clip=1.0 tokenizer_mode=pac_interaction pac_token_mode=measured interaction_mode=product band_pe=index spatial_pe=index</t>
         </is>
       </c>
     </row>
@@ -4321,7 +4414,7 @@
       </c>
       <c r="B15" s="219" t="inlineStr">
         <is>
-          <t>tfm_pretrained</t>
+          <t>sparcnet</t>
         </is>
       </c>
       <c r="C15" s="219" t="inlineStr">
@@ -4336,24 +4429,24 @@
       </c>
       <c r="E15" s="219" t="inlineStr">
         <is>
-          <t>[实测 1.89M] balanced_acc per-seed 0:0.3376, 1:0.3160, 2:0.3681</t>
+          <t>[实测 0.99M] balanced_acc per-seed 0:0.6539, 1:0.6397, 2:0.6385</t>
         </is>
       </c>
       <c r="F15" s="219" t="inlineStr">
         <is>
-          <t>lr=0.001 batch_size=16 epochs=50 patience=10 eval_every_steps=0 loss=cross_entropy label_smoothing=0.1</t>
+          <t>lr=0.001 batch_size=16 epochs=100 patience=20 eval_every_steps=0 loss=cross_entropy label_smoothing=0.1</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="219" t="inlineStr">
         <is>
-          <t>chbmit</t>
+          <t>bci_iv_2a</t>
         </is>
       </c>
       <c r="B16" s="219" t="inlineStr">
         <is>
-          <t>biot_prest16</t>
+          <t>st_transformer</t>
         </is>
       </c>
       <c r="C16" s="219" t="inlineStr">
@@ -4368,24 +4461,24 @@
       </c>
       <c r="E16" s="219" t="inlineStr">
         <is>
-          <t>[实测 3.19M] pr_auc per-seed 0:0.4713, 1:0.5990, 2:0.6100</t>
+          <t>[实测 3.43M] balanced_acc per-seed 0:0.5729, 1:0.5185, 2:0.5498</t>
         </is>
       </c>
       <c r="F16" s="219" t="inlineStr">
         <is>
-          <t>lr=0.001 batch_size=512 epochs=100 patience=5 eval_every_steps=0 loss=focal</t>
+          <t>lr=0.001 batch_size=16 epochs=100 patience=20 eval_every_steps=0 loss=cross_entropy label_smoothing=0.1</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="219" t="inlineStr">
         <is>
-          <t>chbmit</t>
+          <t>bci_iv_2a</t>
         </is>
       </c>
       <c r="B17" s="219" t="inlineStr">
         <is>
-          <t>biot_scratch</t>
+          <t>tfm_pretrained</t>
         </is>
       </c>
       <c r="C17" s="219" t="inlineStr">
@@ -4400,12 +4493,12 @@
       </c>
       <c r="E17" s="219" t="inlineStr">
         <is>
-          <t>[实测 3.19M] pr_auc per-seed 0:0.6491, 1:0.5180, 2:0.5313</t>
+          <t>[实测 1.89M] balanced_acc per-seed 0:0.3376, 1:0.3160, 2:0.3681</t>
         </is>
       </c>
       <c r="F17" s="219" t="inlineStr">
         <is>
-          <t>lr=0.001 batch_size=512 epochs=100 patience=5 eval_every_steps=0 loss=focal</t>
+          <t>lr=0.001 batch_size=16 epochs=50 patience=10 eval_every_steps=0 loss=cross_entropy label_smoothing=0.1</t>
         </is>
       </c>
     </row>
@@ -4417,22 +4510,27 @@
       </c>
       <c r="B18" s="219" t="inlineStr">
         <is>
-          <t>cbramod_pac</t>
+          <t>biot_prest16</t>
         </is>
       </c>
       <c r="C18" s="219" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>[0, 1, 2]</t>
         </is>
       </c>
       <c r="D18" s="219" t="inlineStr">
         <is>
-          <t>skipped</t>
+          <t>filled</t>
         </is>
       </c>
       <c r="E18" s="219" t="inlineStr">
         <is>
-          <t>the workbook has no row for this variant</t>
+          <t>[实测 3.19M] pr_auc per-seed 0:0.4713, 1:0.5990, 2:0.6100</t>
+        </is>
+      </c>
+      <c r="F18" s="219" t="inlineStr">
+        <is>
+          <t>lr=0.001 batch_size=512 epochs=100 patience=5 eval_every_steps=0 loss=focal</t>
         </is>
       </c>
     </row>
@@ -4444,7 +4542,7 @@
       </c>
       <c r="B19" s="219" t="inlineStr">
         <is>
-          <t>cbramod_pretrained</t>
+          <t>biot_scratch</t>
         </is>
       </c>
       <c r="C19" s="219" t="inlineStr">
@@ -4454,12 +4552,17 @@
       </c>
       <c r="D19" s="219" t="inlineStr">
         <is>
-          <t>withheld (rule 3)</t>
+          <t>filled</t>
         </is>
       </c>
       <c r="E19" s="219" t="inlineStr">
         <is>
-          <t>mis-configured seeds [1]: {1: 'test AUROC 0.4805 is at chance -- the model does not discriminate, whatever the val curve did'}; measured pr_auc 0.1804±0.1178</t>
+          <t>[实测 3.19M] pr_auc per-seed 0:0.6491, 1:0.5180, 2:0.5313</t>
+        </is>
+      </c>
+      <c r="F19" s="219" t="inlineStr">
+        <is>
+          <t>lr=0.001 batch_size=512 epochs=100 patience=5 eval_every_steps=0 loss=focal</t>
         </is>
       </c>
     </row>
@@ -4471,27 +4574,22 @@
       </c>
       <c r="B20" s="219" t="inlineStr">
         <is>
-          <t>cbramod_scratch</t>
+          <t>cbramod_pac</t>
         </is>
       </c>
       <c r="C20" s="219" t="inlineStr">
         <is>
-          <t>[0, 1, 2]</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D20" s="219" t="inlineStr">
         <is>
-          <t>filled</t>
+          <t>skipped</t>
         </is>
       </c>
       <c r="E20" s="219" t="inlineStr">
         <is>
-          <t>[实测 30.65M] pr_auc per-seed 0:0.4148, 1:0.4546, 2:0.0813  [seed spread 53% -- mean is a weak summary]</t>
-        </is>
-      </c>
-      <c r="F20" s="219" t="inlineStr">
-        <is>
-          <t>lr=0.0001 batch_size=64 epochs=50 patience=0 eval_every_steps=0 loss=focal grad_clip=1.0 select_metric=auroc multi_lr=True</t>
+          <t>the workbook has no row for this variant</t>
         </is>
       </c>
     </row>
@@ -4503,7 +4601,7 @@
       </c>
       <c r="B21" s="219" t="inlineStr">
         <is>
-          <t>cnn_transformer</t>
+          <t>cbramod_pretrained</t>
         </is>
       </c>
       <c r="C21" s="219" t="inlineStr">
@@ -4518,12 +4616,12 @@
       </c>
       <c r="E21" s="219" t="inlineStr">
         <is>
-          <t>[实测 3.15M] pr_auc per-seed 0:0.5439, 1:0.5528, 2:0.4202</t>
+          <t>[实测 30.65M] pr_auc per-seed 0:0.1203, 1:0.2909, 2:0.2883  [seed spread 34% -- mean is a weak summary]</t>
         </is>
       </c>
       <c r="F21" s="219" t="inlineStr">
         <is>
-          <t>lr=0.001 batch_size=512 epochs=20 patience=8 eval_every_steps=200 loss=focal</t>
+          <t>lr=0.0001 batch_size=64 epochs=50 patience=0 eval_every_steps=0 loss=focal grad_clip=1.0 select_metric=auroc multi_lr=True</t>
         </is>
       </c>
     </row>
@@ -4535,7 +4633,7 @@
       </c>
       <c r="B22" s="219" t="inlineStr">
         <is>
-          <t>contrawr</t>
+          <t>cbramod_scratch</t>
         </is>
       </c>
       <c r="C22" s="219" t="inlineStr">
@@ -4550,12 +4648,12 @@
       </c>
       <c r="E22" s="219" t="inlineStr">
         <is>
-          <t>[实测 1.57M] pr_auc per-seed 0:0.5327, 1:0.5229, 2:0.4661</t>
+          <t>[实测 30.65M] pr_auc per-seed 0:0.4148, 1:0.4546, 2:0.0813  [seed spread 53% -- mean is a weak summary]</t>
         </is>
       </c>
       <c r="F22" s="219" t="inlineStr">
         <is>
-          <t>lr=0.001 batch_size=512 epochs=20 patience=8 eval_every_steps=200 loss=focal</t>
+          <t>lr=0.0001 batch_size=64 epochs=50 patience=0 eval_every_steps=0 loss=focal grad_clip=1.0 select_metric=auroc multi_lr=True</t>
         </is>
       </c>
     </row>
@@ -4567,7 +4665,7 @@
       </c>
       <c r="B23" s="219" t="inlineStr">
         <is>
-          <t>eegpt_pretrained</t>
+          <t>cnn_transformer</t>
         </is>
       </c>
       <c r="C23" s="219" t="inlineStr">
@@ -4582,12 +4680,12 @@
       </c>
       <c r="E23" s="219" t="inlineStr">
         <is>
-          <t>[实测 25.69M] pr_auc per-seed 0:0.4041, 1:0.2986, 2:0.1407  [seed spread 38% -- mean is a weak summary]</t>
+          <t>[实测 3.15M] pr_auc per-seed 0:0.5439, 1:0.5528, 2:0.4202</t>
         </is>
       </c>
       <c r="F23" s="219" t="inlineStr">
         <is>
-          <t>lr=0.0004 batch_size=32 epochs=40 patience=10 eval_every_steps=200 loss=focal</t>
+          <t>lr=0.001 batch_size=512 epochs=20 patience=8 eval_every_steps=200 loss=focal</t>
         </is>
       </c>
     </row>
@@ -4599,7 +4697,7 @@
       </c>
       <c r="B24" s="219" t="inlineStr">
         <is>
-          <t>ffcl</t>
+          <t>contrawr</t>
         </is>
       </c>
       <c r="C24" s="219" t="inlineStr">
@@ -4614,7 +4712,7 @@
       </c>
       <c r="E24" s="219" t="inlineStr">
         <is>
-          <t>[实测 2.46M] pr_auc per-seed 0:0.5774, 1:0.4736, 2:0.5513</t>
+          <t>[实测 1.57M] pr_auc per-seed 0:0.5327, 1:0.5229, 2:0.4661</t>
         </is>
       </c>
       <c r="F24" s="219" t="inlineStr">
@@ -4631,7 +4729,7 @@
       </c>
       <c r="B25" s="219" t="inlineStr">
         <is>
-          <t>labram_pretrained</t>
+          <t>eegpt_pretrained</t>
         </is>
       </c>
       <c r="C25" s="219" t="inlineStr">
@@ -4646,12 +4744,12 @@
       </c>
       <c r="E25" s="219" t="inlineStr">
         <is>
-          <t>[实测 5.82M] pr_auc per-seed 0:0.5425, 1:0.3497, 2:0.4634  [seed spread 18% -- mean is a weak summary]</t>
+          <t>[实测 25.69M] pr_auc per-seed 0:0.4041, 1:0.2986, 2:0.1407  [seed spread 38% -- mean is a weak summary]</t>
         </is>
       </c>
       <c r="F25" s="219" t="inlineStr">
         <is>
-          <t>lr=0.0005 batch_size=64 epochs=50 patience=10 eval_every_steps=0 loss=cross_entropy loader_divisor=1.0</t>
+          <t>lr=0.0004 batch_size=32 epochs=40 patience=10 eval_every_steps=200 loss=focal</t>
         </is>
       </c>
     </row>
@@ -4663,22 +4761,27 @@
       </c>
       <c r="B26" s="219" t="inlineStr">
         <is>
-          <t>paclock_full</t>
+          <t>ffcl</t>
         </is>
       </c>
       <c r="C26" s="219" t="inlineStr">
         <is>
-          <t>[0, 2]</t>
+          <t>[0, 1, 2]</t>
         </is>
       </c>
       <c r="D26" s="219" t="inlineStr">
         <is>
-          <t>withheld (rule 4)</t>
+          <t>filled</t>
         </is>
       </c>
       <c r="E26" s="219" t="inlineStr">
         <is>
-          <t>only 2 seeds; primary pr_auc 0.4200</t>
+          <t>[实测 2.46M] pr_auc per-seed 0:0.5774, 1:0.4736, 2:0.5513</t>
+        </is>
+      </c>
+      <c r="F26" s="219" t="inlineStr">
+        <is>
+          <t>lr=0.001 batch_size=512 epochs=20 patience=8 eval_every_steps=200 loss=focal</t>
         </is>
       </c>
     </row>
@@ -4690,22 +4793,27 @@
       </c>
       <c r="B27" s="219" t="inlineStr">
         <is>
-          <t>paclock_pac</t>
+          <t>labram_pretrained</t>
         </is>
       </c>
       <c r="C27" s="219" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>[0, 1, 2]</t>
         </is>
       </c>
       <c r="D27" s="219" t="inlineStr">
         <is>
-          <t>skipped</t>
+          <t>filled</t>
         </is>
       </c>
       <c r="E27" s="219" t="inlineStr">
         <is>
-          <t>the workbook has no row for this variant</t>
+          <t>[实测 5.82M] pr_auc per-seed 0:0.5425, 1:0.3497, 2:0.4634  [seed spread 18% -- mean is a weak summary]</t>
+        </is>
+      </c>
+      <c r="F27" s="219" t="inlineStr">
+        <is>
+          <t>lr=0.0005 batch_size=64 epochs=50 patience=10 eval_every_steps=0 loss=cross_entropy loader_divisor=1.0</t>
         </is>
       </c>
     </row>
@@ -4717,7 +4825,7 @@
       </c>
       <c r="B28" s="219" t="inlineStr">
         <is>
-          <t>sparcnet</t>
+          <t>labram_scratch</t>
         </is>
       </c>
       <c r="C28" s="219" t="inlineStr">
@@ -4732,12 +4840,12 @@
       </c>
       <c r="E28" s="219" t="inlineStr">
         <is>
-          <t>[实测 1.14M] pr_auc per-seed 0:0.2337, 1:0.1153, 2:0.2438  [seed spread 30% -- mean is a weak summary]</t>
+          <t>[实测 5.82M] pr_auc per-seed 0:0.4020, 1:0.3719, 2:0.3047</t>
         </is>
       </c>
       <c r="F28" s="219" t="inlineStr">
         <is>
-          <t>lr=0.001 batch_size=512 epochs=20 patience=8 eval_every_steps=200 loss=focal</t>
+          <t>stopped_by=patience lr=0.0005 batch_size=64 epochs=50 patience=10 eval_every_steps=0 loss=cross_entropy loader_divisor=1.0</t>
         </is>
       </c>
     </row>
@@ -4749,27 +4857,22 @@
       </c>
       <c r="B29" s="219" t="inlineStr">
         <is>
-          <t>st_transformer</t>
+          <t>paclock_pac</t>
         </is>
       </c>
       <c r="C29" s="219" t="inlineStr">
         <is>
-          <t>[0, 1, 2]</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D29" s="219" t="inlineStr">
         <is>
-          <t>filled</t>
+          <t>skipped</t>
         </is>
       </c>
       <c r="E29" s="219" t="inlineStr">
         <is>
-          <t>[实测 3.43M] pr_auc per-seed 0:0.3099, 1:0.1098, 2:0.3024  [seed spread 38% -- mean is a weak summary]</t>
-        </is>
-      </c>
-      <c r="F29" s="219" t="inlineStr">
-        <is>
-          <t>lr=0.001 batch_size=512 epochs=20 patience=8 eval_every_steps=200 loss=focal</t>
+          <t>the workbook has no row for this variant</t>
         </is>
       </c>
     </row>
@@ -4781,7 +4884,7 @@
       </c>
       <c r="B30" s="219" t="inlineStr">
         <is>
-          <t>tfm_pretrained</t>
+          <t>sparcnet</t>
         </is>
       </c>
       <c r="C30" s="219" t="inlineStr">
@@ -4796,24 +4899,24 @@
       </c>
       <c r="E30" s="219" t="inlineStr">
         <is>
-          <t>[实测 1.89M] pr_auc per-seed 0:0.6366, 1:0.6457, 2:0.5984</t>
+          <t>[实测 1.14M] pr_auc per-seed 0:0.2337, 1:0.1153, 2:0.2438  [seed spread 30% -- mean is a weak summary]</t>
         </is>
       </c>
       <c r="F30" s="219" t="inlineStr">
         <is>
-          <t>lr=0.001 batch_size=512 epochs=7 patience=10 eval_every_steps=100 loss=focal label_smoothing=0.1</t>
+          <t>lr=0.001 batch_size=512 epochs=20 patience=8 eval_every_steps=200 loss=focal</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="219" t="inlineStr">
         <is>
-          <t>faced</t>
+          <t>chbmit</t>
         </is>
       </c>
       <c r="B31" s="219" t="inlineStr">
         <is>
-          <t>biot_prest16</t>
+          <t>st_transformer</t>
         </is>
       </c>
       <c r="C31" s="219" t="inlineStr">
@@ -4828,24 +4931,24 @@
       </c>
       <c r="E31" s="219" t="inlineStr">
         <is>
-          <t>[实测 3.19M] balanced_acc per-seed 0:0.2267, 1:0.2364, 2:0.1954</t>
+          <t>[实测 3.43M] pr_auc per-seed 0:0.3099, 1:0.1098, 2:0.3024  [seed spread 38% -- mean is a weak summary]</t>
         </is>
       </c>
       <c r="F31" s="219" t="inlineStr">
         <is>
-          <t>lr=0.0004 batch_size=64 epochs=100 patience=10 eval_every_steps=0 loss=cross_entropy</t>
+          <t>lr=0.001 batch_size=512 epochs=20 patience=8 eval_every_steps=200 loss=focal</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="219" t="inlineStr">
         <is>
-          <t>faced</t>
+          <t>chbmit</t>
         </is>
       </c>
       <c r="B32" s="219" t="inlineStr">
         <is>
-          <t>biot_scratch</t>
+          <t>tfm_pretrained</t>
         </is>
       </c>
       <c r="C32" s="219" t="inlineStr">
@@ -4860,12 +4963,12 @@
       </c>
       <c r="E32" s="219" t="inlineStr">
         <is>
-          <t>[实测 3.19M] balanced_acc per-seed 0:0.1959, 1:0.1795, 2:0.1808</t>
+          <t>[实测 1.89M] pr_auc per-seed 0:0.6366, 1:0.6457, 2:0.5984</t>
         </is>
       </c>
       <c r="F32" s="219" t="inlineStr">
         <is>
-          <t>lr=0.0004 batch_size=64 epochs=100 patience=10 eval_every_steps=0 loss=cross_entropy</t>
+          <t>lr=0.001 batch_size=512 epochs=7 patience=10 eval_every_steps=100 loss=focal label_smoothing=0.1</t>
         </is>
       </c>
     </row>
@@ -4877,22 +4980,27 @@
       </c>
       <c r="B33" s="219" t="inlineStr">
         <is>
-          <t>cbramod_pac</t>
+          <t>biot_prest16</t>
         </is>
       </c>
       <c r="C33" s="219" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>[0, 1, 2]</t>
         </is>
       </c>
       <c r="D33" s="219" t="inlineStr">
         <is>
-          <t>skipped</t>
+          <t>filled</t>
         </is>
       </c>
       <c r="E33" s="219" t="inlineStr">
         <is>
-          <t>the workbook has no row for this variant</t>
+          <t>[实测 3.19M] balanced_acc per-seed 0:0.2267, 1:0.2364, 2:0.1954</t>
+        </is>
+      </c>
+      <c r="F33" s="219" t="inlineStr">
+        <is>
+          <t>lr=0.0004 batch_size=64 epochs=100 patience=10 eval_every_steps=0 loss=cross_entropy</t>
         </is>
       </c>
     </row>
@@ -4904,7 +5012,7 @@
       </c>
       <c r="B34" s="219" t="inlineStr">
         <is>
-          <t>cbramod_pretrained</t>
+          <t>biot_scratch</t>
         </is>
       </c>
       <c r="C34" s="219" t="inlineStr">
@@ -4919,12 +5027,12 @@
       </c>
       <c r="E34" s="219" t="inlineStr">
         <is>
-          <t>[实测 56.25M] balanced_acc per-seed 0:0.5401, 1:0.5330, 2:0.5318</t>
+          <t>[实测 3.19M] balanced_acc per-seed 0:0.1959, 1:0.1795, 2:0.1808</t>
         </is>
       </c>
       <c r="F34" s="219" t="inlineStr">
         <is>
-          <t>lr=0.0001 batch_size=64 epochs=50 patience=10 eval_every_steps=0 loss=cross_entropy label_smoothing=0.1 multi_lr=True</t>
+          <t>lr=0.0004 batch_size=64 epochs=100 patience=10 eval_every_steps=0 loss=cross_entropy</t>
         </is>
       </c>
     </row>
@@ -4936,22 +5044,22 @@
       </c>
       <c r="B35" s="219" t="inlineStr">
         <is>
-          <t>cnn_transformer</t>
+          <t>cbramod_pac</t>
         </is>
       </c>
       <c r="C35" s="219" t="inlineStr">
         <is>
-          <t>[0, 1, 2]</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D35" s="219" t="inlineStr">
         <is>
-          <t>withheld (rule 3)</t>
+          <t>skipped</t>
         </is>
       </c>
       <c r="E35" s="219" t="inlineStr">
         <is>
-          <t>mis-configured seeds [0, 1, 2]: {0: 'val peak at first evaluation and never cleared chance (0.1111 vs 0.1111)', 1: "test Cohen's Kappa 0.0005 is at chance -- the model does not discriminate, whatever the val curve did", 2: 'val peak at first evaluation and never cleared chance (0.1111 vs 0.1111)'}; measured balanced_acc 0.1112±0.0002</t>
+          <t>the workbook has no row for this variant</t>
         </is>
       </c>
     </row>
@@ -4963,7 +5071,7 @@
       </c>
       <c r="B36" s="219" t="inlineStr">
         <is>
-          <t>contrawr</t>
+          <t>cbramod_pretrained</t>
         </is>
       </c>
       <c r="C36" s="219" t="inlineStr">
@@ -4978,12 +5086,12 @@
       </c>
       <c r="E36" s="219" t="inlineStr">
         <is>
-          <t>[实测 1.58M] balanced_acc per-seed 0:0.1758, 1:0.2012, 2:0.2272</t>
+          <t>[实测 56.25M] balanced_acc per-seed 0:0.5464, 1:0.5515, 2:0.5548</t>
         </is>
       </c>
       <c r="F36" s="219" t="inlineStr">
         <is>
-          <t>lr=0.001 batch_size=64 epochs=100 patience=20 eval_every_steps=0 loss=cross_entropy label_smoothing=0.1</t>
+          <t>lr=0.0001 batch_size=64 epochs=50 patience=0 eval_every_steps=0 loss=cross_entropy label_smoothing=0.1 grad_clip=1.0 multi_lr=True</t>
         </is>
       </c>
     </row>
@@ -4995,7 +5103,7 @@
       </c>
       <c r="B37" s="219" t="inlineStr">
         <is>
-          <t>eegpt_pretrained</t>
+          <t>cbramod_scratch</t>
         </is>
       </c>
       <c r="C37" s="219" t="inlineStr">
@@ -5005,17 +5113,12 @@
       </c>
       <c r="D37" s="219" t="inlineStr">
         <is>
-          <t>filled</t>
+          <t>withheld (rule 3)</t>
         </is>
       </c>
       <c r="E37" s="219" t="inlineStr">
         <is>
-          <t>[实测 25.69M] balanced_acc per-seed 0:0.1755, 1:0.1806, 2:0.1593</t>
-        </is>
-      </c>
-      <c r="F37" s="219" t="inlineStr">
-        <is>
-          <t>lr=0.0004 batch_size=32 epochs=100 patience=10 eval_every_steps=0 loss=cross_entropy</t>
+          <t>mis-configured seeds [1, 2]: {1: 'val peak at first evaluation and never cleared chance (0.1144 vs 0.1111)', 2: 'val curve is flat (model not learning)'}; measured balanced_acc 0.2444±0.1877</t>
         </is>
       </c>
     </row>
@@ -5027,7 +5130,7 @@
       </c>
       <c r="B38" s="219" t="inlineStr">
         <is>
-          <t>ffcl</t>
+          <t>cnn_transformer</t>
         </is>
       </c>
       <c r="C38" s="219" t="inlineStr">
@@ -5037,17 +5140,12 @@
       </c>
       <c r="D38" s="219" t="inlineStr">
         <is>
-          <t>filled</t>
+          <t>withheld (rule 3)</t>
         </is>
       </c>
       <c r="E38" s="219" t="inlineStr">
         <is>
-          <t>[实测 2.48M] balanced_acc per-seed 0:0.2205, 1:0.2547, 2:0.2424</t>
-        </is>
-      </c>
-      <c r="F38" s="219" t="inlineStr">
-        <is>
-          <t>lr=0.001 batch_size=64 epochs=100 patience=20 eval_every_steps=0 loss=cross_entropy label_smoothing=0.1</t>
+          <t>mis-configured seeds [0, 1, 2]: {0: 'val peak at first evaluation and never cleared chance (0.1111 vs 0.1111)', 1: "test Cohen's Kappa 0.0005 is at chance -- the model does not discriminate, whatever the val curve did", 2: 'val peak at first evaluation and never cleared chance (0.1111 vs 0.1111)'}; measured balanced_acc 0.1112±0.0002</t>
         </is>
       </c>
     </row>
@@ -5059,7 +5157,7 @@
       </c>
       <c r="B39" s="219" t="inlineStr">
         <is>
-          <t>labram_pretrained</t>
+          <t>contrawr</t>
         </is>
       </c>
       <c r="C39" s="219" t="inlineStr">
@@ -5074,12 +5172,12 @@
       </c>
       <c r="E39" s="219" t="inlineStr">
         <is>
-          <t>[实测 5.82M] balanced_acc per-seed 0:0.3230, 1:0.3254, 2:0.3043</t>
+          <t>[实测 1.58M] balanced_acc per-seed 0:0.1758, 1:0.2012, 2:0.2272</t>
         </is>
       </c>
       <c r="F39" s="219" t="inlineStr">
         <is>
-          <t>lr=0.0005 batch_size=64 epochs=50 patience=10 eval_every_steps=0 loss=cross_entropy loader_divisor=1.0</t>
+          <t>lr=0.001 batch_size=64 epochs=100 patience=20 eval_every_steps=0 loss=cross_entropy label_smoothing=0.1</t>
         </is>
       </c>
     </row>
@@ -5091,7 +5189,7 @@
       </c>
       <c r="B40" s="219" t="inlineStr">
         <is>
-          <t>paclock_full</t>
+          <t>eegpt_pretrained</t>
         </is>
       </c>
       <c r="C40" s="219" t="inlineStr">
@@ -5106,12 +5204,12 @@
       </c>
       <c r="E40" s="219" t="inlineStr">
         <is>
-          <t>[实测 1.62M] balanced_acc per-seed 0:0.1511, 1:0.1469, 2:0.1448</t>
+          <t>[实测 25.69M] balanced_acc per-seed 0:0.1755, 1:0.1806, 2:0.1593</t>
         </is>
       </c>
       <c r="F40" s="219" t="inlineStr">
         <is>
-          <t>lr=0.0001 batch_size=32 epochs=120 patience=20 eval_every_steps=0 loss=cross_entropy label_smoothing=0.1 grad_clip=1.0 tokenizer_mode=pac_interaction pac_token_mode=measured interaction_mode=product band_pe=index spatial_pe=index</t>
+          <t>lr=0.0004 batch_size=32 epochs=100 patience=10 eval_every_steps=0 loss=cross_entropy</t>
         </is>
       </c>
     </row>
@@ -5123,22 +5221,27 @@
       </c>
       <c r="B41" s="219" t="inlineStr">
         <is>
-          <t>paclock_pac</t>
+          <t>ffcl</t>
         </is>
       </c>
       <c r="C41" s="219" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>[0, 1, 2]</t>
         </is>
       </c>
       <c r="D41" s="219" t="inlineStr">
         <is>
-          <t>skipped</t>
+          <t>filled</t>
         </is>
       </c>
       <c r="E41" s="219" t="inlineStr">
         <is>
-          <t>the workbook has no row for this variant</t>
+          <t>[实测 2.48M] balanced_acc per-seed 0:0.2205, 1:0.2547, 2:0.2424</t>
+        </is>
+      </c>
+      <c r="F41" s="219" t="inlineStr">
+        <is>
+          <t>lr=0.001 batch_size=64 epochs=100 patience=20 eval_every_steps=0 loss=cross_entropy label_smoothing=0.1</t>
         </is>
       </c>
     </row>
@@ -5150,7 +5253,7 @@
       </c>
       <c r="B42" s="219" t="inlineStr">
         <is>
-          <t>sparcnet</t>
+          <t>labram_pretrained</t>
         </is>
       </c>
       <c r="C42" s="219" t="inlineStr">
@@ -5165,12 +5268,12 @@
       </c>
       <c r="E42" s="219" t="inlineStr">
         <is>
-          <t>[实测 1.23M] balanced_acc per-seed 0:0.2458, 1:0.2662, 2:0.2790</t>
+          <t>[实测 5.82M] balanced_acc per-seed 0:0.3273, 1:0.3253, 2:0.3290</t>
         </is>
       </c>
       <c r="F42" s="219" t="inlineStr">
         <is>
-          <t>lr=0.001 batch_size=64 epochs=100 patience=20 eval_every_steps=0 loss=cross_entropy label_smoothing=0.1</t>
+          <t>stopped_by=patience lr=0.0005 batch_size=64 epochs=50 patience=10 eval_every_steps=0 loss=cross_entropy label_smoothing=0.1 loader_divisor=1.0</t>
         </is>
       </c>
     </row>
@@ -5182,7 +5285,7 @@
       </c>
       <c r="B43" s="219" t="inlineStr">
         <is>
-          <t>st_transformer</t>
+          <t>labram_scratch</t>
         </is>
       </c>
       <c r="C43" s="219" t="inlineStr">
@@ -5197,12 +5300,12 @@
       </c>
       <c r="E43" s="219" t="inlineStr">
         <is>
-          <t>[实测 3.45M] balanced_acc per-seed 0:0.3371, 1:0.2954, 2:0.3268</t>
+          <t>[实测 5.82M] balanced_acc per-seed 0:0.1455, 1:0.1618, 2:0.1676</t>
         </is>
       </c>
       <c r="F43" s="219" t="inlineStr">
         <is>
-          <t>lr=0.001 batch_size=64 epochs=100 patience=20 eval_every_steps=0 loss=cross_entropy label_smoothing=0.1</t>
+          <t>stopped_by=patience lr=0.0005 batch_size=64 epochs=50 patience=10 eval_every_steps=0 loss=cross_entropy label_smoothing=0.1 loader_divisor=1.0</t>
         </is>
       </c>
     </row>
@@ -5214,66 +5317,61 @@
       </c>
       <c r="B44" s="219" t="inlineStr">
         <is>
-          <t>tfm_pretrained</t>
+          <t>paclock_pac</t>
         </is>
       </c>
       <c r="C44" s="219" t="inlineStr">
         <is>
-          <t>[0, 1, 2]</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D44" s="219" t="inlineStr">
         <is>
-          <t>filled</t>
+          <t>skipped</t>
         </is>
       </c>
       <c r="E44" s="219" t="inlineStr">
         <is>
-          <t>[实测 1.89M] balanced_acc per-seed 0:0.2492, 1:0.2226, 2:0.2358</t>
-        </is>
-      </c>
-      <c r="F44" s="219" t="inlineStr">
-        <is>
-          <t>lr=0.001 batch_size=64 epochs=50 patience=10 eval_every_steps=0 loss=cross_entropy label_smoothing=0.1</t>
+          <t>the workbook has no row for this variant</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="219" t="inlineStr">
         <is>
-          <t>isruc</t>
+          <t>faced</t>
         </is>
       </c>
       <c r="B45" s="219" t="inlineStr">
         <is>
-          <t>biot_hop50</t>
+          <t>paclock_v2</t>
         </is>
       </c>
       <c r="C45" s="219" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>[0, 1, 2]</t>
         </is>
       </c>
       <c r="D45" s="219" t="inlineStr">
         <is>
-          <t>skipped</t>
+          <t>withheld (rule 3)</t>
         </is>
       </c>
       <c r="E45" s="219" t="inlineStr">
         <is>
-          <t>the workbook has no row for this variant</t>
+          <t>mis-configured seeds [1, 2]: {1: 'val peak at first evaluation and never cleared chance (0.1111 vs 0.1111)', 2: 'val peak at first evaluation and never cleared chance (0.1111 vs 0.1111)'}; measured balanced_acc 0.1307±0.0276</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="219" t="inlineStr">
         <is>
-          <t>isruc</t>
+          <t>faced</t>
         </is>
       </c>
       <c r="B46" s="219" t="inlineStr">
         <is>
-          <t>biot_prest16</t>
+          <t>sparcnet</t>
         </is>
       </c>
       <c r="C46" s="219" t="inlineStr">
@@ -5288,24 +5386,24 @@
       </c>
       <c r="E46" s="219" t="inlineStr">
         <is>
-          <t>[实测 3.19M] cohen_kappa per-seed 0:0.7382, 1:0.7300, 2:0.7409</t>
+          <t>[实测 1.23M] balanced_acc per-seed 0:0.2458, 1:0.2662, 2:0.2790</t>
         </is>
       </c>
       <c r="F46" s="219" t="inlineStr">
         <is>
-          <t>lr=0.0004 batch_size=64 epochs=40 patience=10 eval_every_steps=0 loss=cross_entropy</t>
+          <t>lr=0.001 batch_size=64 epochs=100 patience=20 eval_every_steps=0 loss=cross_entropy label_smoothing=0.1</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="219" t="inlineStr">
         <is>
-          <t>isruc</t>
+          <t>faced</t>
         </is>
       </c>
       <c r="B47" s="219" t="inlineStr">
         <is>
-          <t>biot_scratch</t>
+          <t>st_transformer</t>
         </is>
       </c>
       <c r="C47" s="219" t="inlineStr">
@@ -5320,39 +5418,44 @@
       </c>
       <c r="E47" s="219" t="inlineStr">
         <is>
-          <t>[实测 3.18M] cohen_kappa per-seed 0:0.7361, 1:0.7421, 2:0.7352</t>
+          <t>[实测 3.45M] balanced_acc per-seed 0:0.3371, 1:0.2954, 2:0.3268</t>
         </is>
       </c>
       <c r="F47" s="219" t="inlineStr">
         <is>
-          <t>lr=0.0004 batch_size=64 epochs=40 patience=10 eval_every_steps=0 loss=cross_entropy</t>
+          <t>lr=0.001 batch_size=64 epochs=100 patience=20 eval_every_steps=0 loss=cross_entropy label_smoothing=0.1</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="219" t="inlineStr">
         <is>
-          <t>isruc</t>
+          <t>faced</t>
         </is>
       </c>
       <c r="B48" s="219" t="inlineStr">
         <is>
-          <t>biot_tok100</t>
+          <t>tfm_pretrained</t>
         </is>
       </c>
       <c r="C48" s="219" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>[0, 1, 2]</t>
         </is>
       </c>
       <c r="D48" s="219" t="inlineStr">
         <is>
-          <t>skipped</t>
+          <t>filled</t>
         </is>
       </c>
       <c r="E48" s="219" t="inlineStr">
         <is>
-          <t>the workbook has no row for this variant</t>
+          <t>[实测 1.89M] balanced_acc per-seed 0:0.2492, 1:0.2226, 2:0.2358</t>
+        </is>
+      </c>
+      <c r="F48" s="219" t="inlineStr">
+        <is>
+          <t>lr=0.001 batch_size=64 epochs=50 patience=10 eval_every_steps=0 loss=cross_entropy label_smoothing=0.1</t>
         </is>
       </c>
     </row>
@@ -5364,7 +5467,7 @@
       </c>
       <c r="B49" s="219" t="inlineStr">
         <is>
-          <t>cand_aug</t>
+          <t>biot_hop50</t>
         </is>
       </c>
       <c r="C49" s="219" t="inlineStr">
@@ -5391,22 +5494,27 @@
       </c>
       <c r="B50" s="219" t="inlineStr">
         <is>
-          <t>cand_aug_drop03</t>
+          <t>biot_prest16</t>
         </is>
       </c>
       <c r="C50" s="219" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>[0, 1, 2]</t>
         </is>
       </c>
       <c r="D50" s="219" t="inlineStr">
         <is>
-          <t>skipped</t>
+          <t>filled</t>
         </is>
       </c>
       <c r="E50" s="219" t="inlineStr">
         <is>
-          <t>the workbook has no row for this variant</t>
+          <t>[实测 3.19M] cohen_kappa per-seed 0:0.7382, 1:0.7300, 2:0.7409</t>
+        </is>
+      </c>
+      <c r="F50" s="219" t="inlineStr">
+        <is>
+          <t>lr=0.0004 batch_size=64 epochs=40 patience=10 eval_every_steps=0 loss=cross_entropy</t>
         </is>
       </c>
     </row>
@@ -5418,22 +5526,27 @@
       </c>
       <c r="B51" s="219" t="inlineStr">
         <is>
-          <t>cand_band_aug</t>
+          <t>biot_scratch</t>
         </is>
       </c>
       <c r="C51" s="219" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>[0, 1, 2]</t>
         </is>
       </c>
       <c r="D51" s="219" t="inlineStr">
         <is>
-          <t>skipped</t>
+          <t>filled</t>
         </is>
       </c>
       <c r="E51" s="219" t="inlineStr">
         <is>
-          <t>the workbook has no row for this variant</t>
+          <t>[实测 3.18M] cohen_kappa per-seed 0:0.7361, 1:0.7421, 2:0.7352</t>
+        </is>
+      </c>
+      <c r="F51" s="219" t="inlineStr">
+        <is>
+          <t>lr=0.0004 batch_size=64 epochs=40 patience=10 eval_every_steps=0 loss=cross_entropy</t>
         </is>
       </c>
     </row>
@@ -5445,7 +5558,7 @@
       </c>
       <c r="B52" s="219" t="inlineStr">
         <is>
-          <t>cand_base</t>
+          <t>biot_tok100</t>
         </is>
       </c>
       <c r="C52" s="219" t="inlineStr">
@@ -5472,7 +5585,7 @@
       </c>
       <c r="B53" s="219" t="inlineStr">
         <is>
-          <t>cand_drop03</t>
+          <t>cand_base</t>
         </is>
       </c>
       <c r="C53" s="219" t="inlineStr">
@@ -5499,7 +5612,7 @@
       </c>
       <c r="B54" s="219" t="inlineStr">
         <is>
-          <t>cand_head_attn</t>
+          <t>cand_e60_base</t>
         </is>
       </c>
       <c r="C54" s="219" t="inlineStr">
@@ -5526,7 +5639,7 @@
       </c>
       <c r="B55" s="219" t="inlineStr">
         <is>
-          <t>cand_head_band</t>
+          <t>cand_e60_patch100</t>
         </is>
       </c>
       <c r="C55" s="219" t="inlineStr">
@@ -5553,7 +5666,7 @@
       </c>
       <c r="B56" s="219" t="inlineStr">
         <is>
-          <t>cand_heads8</t>
+          <t>cand_e60_size_base</t>
         </is>
       </c>
       <c r="C56" s="219" t="inlineStr">
@@ -5580,7 +5693,7 @@
       </c>
       <c r="B57" s="219" t="inlineStr">
         <is>
-          <t>cand_pacwin200</t>
+          <t>cand_e60_size_large</t>
         </is>
       </c>
       <c r="C57" s="219" t="inlineStr">
@@ -5607,7 +5720,7 @@
       </c>
       <c r="B58" s="219" t="inlineStr">
         <is>
-          <t>cand_pacwin400</t>
+          <t>cand_ms</t>
         </is>
       </c>
       <c r="C58" s="219" t="inlineStr">
@@ -5634,7 +5747,7 @@
       </c>
       <c r="B59" s="219" t="inlineStr">
         <is>
-          <t>cand_patch100</t>
+          <t>cand_p100_large</t>
         </is>
       </c>
       <c r="C59" s="219" t="inlineStr">
@@ -5661,7 +5774,7 @@
       </c>
       <c r="B60" s="219" t="inlineStr">
         <is>
-          <t>cand_patch400</t>
+          <t>cand_p200_win1200</t>
         </is>
       </c>
       <c r="C60" s="219" t="inlineStr">
@@ -5688,7 +5801,7 @@
       </c>
       <c r="B61" s="219" t="inlineStr">
         <is>
-          <t>cand_size_base</t>
+          <t>cand_p200_win3000</t>
         </is>
       </c>
       <c r="C61" s="219" t="inlineStr">
@@ -5715,7 +5828,7 @@
       </c>
       <c r="B62" s="219" t="inlineStr">
         <is>
-          <t>cand_size_large</t>
+          <t>cand_p200_win400</t>
         </is>
       </c>
       <c r="C62" s="219" t="inlineStr">
@@ -5742,7 +5855,7 @@
       </c>
       <c r="B63" s="219" t="inlineStr">
         <is>
-          <t>cbramod_pac</t>
+          <t>cand_p200_win600</t>
         </is>
       </c>
       <c r="C63" s="219" t="inlineStr">
@@ -5769,27 +5882,22 @@
       </c>
       <c r="B64" s="219" t="inlineStr">
         <is>
-          <t>cbramod_pretrained</t>
+          <t>cand_p200_win6000</t>
         </is>
       </c>
       <c r="C64" s="219" t="inlineStr">
         <is>
-          <t>[0, 1, 2]</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D64" s="219" t="inlineStr">
         <is>
-          <t>filled</t>
+          <t>skipped</t>
         </is>
       </c>
       <c r="E64" s="219" t="inlineStr">
         <is>
-          <t>[实测 26.47M] cohen_kappa per-seed 0:0.7609, 1:0.7558, 2:0.7251</t>
-        </is>
-      </c>
-      <c r="F64" s="219" t="inlineStr">
-        <is>
-          <t>lr=0.0001 batch_size=64 epochs=50 patience=10 eval_every_steps=0 loss=cross_entropy label_smoothing=0.1 multi_lr=True</t>
+          <t>the workbook has no row for this variant</t>
         </is>
       </c>
     </row>
@@ -5801,27 +5909,22 @@
       </c>
       <c r="B65" s="219" t="inlineStr">
         <is>
-          <t>cnn_transformer</t>
+          <t>cand_pacwin200</t>
         </is>
       </c>
       <c r="C65" s="219" t="inlineStr">
         <is>
-          <t>[0, 1, 2]</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D65" s="219" t="inlineStr">
         <is>
-          <t>filled</t>
+          <t>skipped</t>
         </is>
       </c>
       <c r="E65" s="219" t="inlineStr">
         <is>
-          <t>[实测 3.15M] cohen_kappa per-seed 0:0.7595, 1:0.7456, 2:0.7544</t>
-        </is>
-      </c>
-      <c r="F65" s="219" t="inlineStr">
-        <is>
-          <t>lr=0.001 batch_size=512 epochs=60 patience=15 eval_every_steps=0 loss=cross_entropy label_smoothing=0.1</t>
+          <t>the workbook has no row for this variant</t>
         </is>
       </c>
     </row>
@@ -5833,27 +5936,22 @@
       </c>
       <c r="B66" s="219" t="inlineStr">
         <is>
-          <t>contrawr</t>
+          <t>cand_patch100</t>
         </is>
       </c>
       <c r="C66" s="219" t="inlineStr">
         <is>
-          <t>[0, 1, 2]</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D66" s="219" t="inlineStr">
         <is>
-          <t>filled</t>
+          <t>skipped</t>
         </is>
       </c>
       <c r="E66" s="219" t="inlineStr">
         <is>
-          <t>[实测 1.57M] cohen_kappa per-seed 0:0.7584, 1:0.7495, 2:0.7482</t>
-        </is>
-      </c>
-      <c r="F66" s="219" t="inlineStr">
-        <is>
-          <t>lr=0.001 batch_size=512 epochs=60 patience=15 eval_every_steps=0 loss=cross_entropy label_smoothing=0.1</t>
+          <t>the workbook has no row for this variant</t>
         </is>
       </c>
     </row>
@@ -5865,27 +5963,22 @@
       </c>
       <c r="B67" s="219" t="inlineStr">
         <is>
-          <t>eegpt_pretrained</t>
+          <t>cand_patch50</t>
         </is>
       </c>
       <c r="C67" s="219" t="inlineStr">
         <is>
-          <t>[0, 1, 2]</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D67" s="219" t="inlineStr">
         <is>
-          <t>filled</t>
+          <t>skipped</t>
         </is>
       </c>
       <c r="E67" s="219" t="inlineStr">
         <is>
-          <t>[实测 25.69M] cohen_kappa per-seed 0:0.7111, 1:0.7127, 2:0.6766</t>
-        </is>
-      </c>
-      <c r="F67" s="219" t="inlineStr">
-        <is>
-          <t>lr=0.0004 batch_size=32 epochs=40 patience=10 eval_every_steps=50 loss=cross_entropy</t>
+          <t>the workbook has no row for this variant</t>
         </is>
       </c>
     </row>
@@ -5897,27 +5990,22 @@
       </c>
       <c r="B68" s="219" t="inlineStr">
         <is>
-          <t>ffcl</t>
+          <t>cbramod_pac</t>
         </is>
       </c>
       <c r="C68" s="219" t="inlineStr">
         <is>
-          <t>[0, 1, 2]</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D68" s="219" t="inlineStr">
         <is>
-          <t>filled</t>
+          <t>skipped</t>
         </is>
       </c>
       <c r="E68" s="219" t="inlineStr">
         <is>
-          <t>[实测 2.67M] cohen_kappa per-seed 0:0.7252, 1:0.7243, 2:0.7516</t>
-        </is>
-      </c>
-      <c r="F68" s="219" t="inlineStr">
-        <is>
-          <t>lr=0.001 batch_size=512 epochs=60 patience=15 eval_every_steps=0 loss=cross_entropy label_smoothing=0.1</t>
+          <t>the workbook has no row for this variant</t>
         </is>
       </c>
     </row>
@@ -5929,7 +6017,7 @@
       </c>
       <c r="B69" s="219" t="inlineStr">
         <is>
-          <t>labram_pretrained</t>
+          <t>cbramod_pretrained</t>
         </is>
       </c>
       <c r="C69" s="219" t="inlineStr">
@@ -5944,12 +6032,12 @@
       </c>
       <c r="E69" s="219" t="inlineStr">
         <is>
-          <t>[实测 5.82M] cohen_kappa per-seed 0:0.7352, 1:0.7462, 2:0.7488</t>
+          <t>[实测 26.47M] cohen_kappa per-seed 0:0.7476, 1:0.7625, 2:0.7519</t>
         </is>
       </c>
       <c r="F69" s="219" t="inlineStr">
         <is>
-          <t>lr=0.0005 batch_size=64 epochs=50 patience=10 eval_every_steps=0 loss=cross_entropy loader_divisor=1.0</t>
+          <t>lr=0.0001 batch_size=64 epochs=50 patience=0 eval_every_steps=0 loss=cross_entropy label_smoothing=0.1 grad_clip=1.0 multi_lr=True</t>
         </is>
       </c>
     </row>
@@ -5961,7 +6049,7 @@
       </c>
       <c r="B70" s="219" t="inlineStr">
         <is>
-          <t>paclock_full</t>
+          <t>cbramod_scratch</t>
         </is>
       </c>
       <c r="C70" s="219" t="inlineStr">
@@ -5976,12 +6064,12 @@
       </c>
       <c r="E70" s="219" t="inlineStr">
         <is>
-          <t>[实测 1.62M] cohen_kappa per-seed 0:0.6921, 1:0.6855, 2:0.6819</t>
+          <t>[实测 26.47M] cohen_kappa per-seed 0:0.6947, 1:0.6930, 2:0.7049</t>
         </is>
       </c>
       <c r="F70" s="219" t="inlineStr">
         <is>
-          <t>lr=0.0001 batch_size=32 epochs=20 patience=20 eval_every_steps=0 loss=cross_entropy label_smoothing=0.1 grad_clip=1.0 tokenizer_mode=pac_interaction pac_token_mode=measured interaction_mode=product band_pe=index spatial_pe=index</t>
+          <t>lr=0.0001 batch_size=64 epochs=50 patience=0 eval_every_steps=0 loss=cross_entropy label_smoothing=0.1 grad_clip=1.0 multi_lr=True</t>
         </is>
       </c>
     </row>
@@ -5993,22 +6081,27 @@
       </c>
       <c r="B71" s="219" t="inlineStr">
         <is>
-          <t>paclock_pac</t>
+          <t>cnn_transformer</t>
         </is>
       </c>
       <c r="C71" s="219" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>[0, 1, 2]</t>
         </is>
       </c>
       <c r="D71" s="219" t="inlineStr">
         <is>
-          <t>skipped</t>
+          <t>filled</t>
         </is>
       </c>
       <c r="E71" s="219" t="inlineStr">
         <is>
-          <t>the workbook has no row for this variant</t>
+          <t>[实测 3.15M] cohen_kappa per-seed 0:0.7595, 1:0.7456, 2:0.7544</t>
+        </is>
+      </c>
+      <c r="F71" s="219" t="inlineStr">
+        <is>
+          <t>lr=0.001 batch_size=512 epochs=60 patience=15 eval_every_steps=0 loss=cross_entropy label_smoothing=0.1</t>
         </is>
       </c>
     </row>
@@ -6020,7 +6113,7 @@
       </c>
       <c r="B72" s="219" t="inlineStr">
         <is>
-          <t>sparcnet</t>
+          <t>contrawr</t>
         </is>
       </c>
       <c r="C72" s="219" t="inlineStr">
@@ -6035,7 +6128,7 @@
       </c>
       <c r="E72" s="219" t="inlineStr">
         <is>
-          <t>[实测 1.38M] cohen_kappa per-seed 0:0.7286, 1:0.7185, 2:0.7565</t>
+          <t>[实测 1.57M] cohen_kappa per-seed 0:0.7584, 1:0.7495, 2:0.7482</t>
         </is>
       </c>
       <c r="F72" s="219" t="inlineStr">
@@ -6052,7 +6145,7 @@
       </c>
       <c r="B73" s="219" t="inlineStr">
         <is>
-          <t>st_transformer</t>
+          <t>eegpt_pretrained</t>
         </is>
       </c>
       <c r="C73" s="219" t="inlineStr">
@@ -6067,12 +6160,12 @@
       </c>
       <c r="E73" s="219" t="inlineStr">
         <is>
-          <t>[实测 3.42M] cohen_kappa per-seed 0:0.5488, 1:0.3217, 2:0.3076  [seed spread 28% -- mean is a weak summary]</t>
+          <t>[实测 25.69M] cohen_kappa per-seed 0:0.7111, 1:0.7127, 2:0.6766</t>
         </is>
       </c>
       <c r="F73" s="219" t="inlineStr">
         <is>
-          <t>lr=0.001 batch_size=512 epochs=60 patience=15 eval_every_steps=0 loss=cross_entropy label_smoothing=0.1</t>
+          <t>lr=0.0004 batch_size=32 epochs=40 patience=10 eval_every_steps=50 loss=cross_entropy</t>
         </is>
       </c>
     </row>
@@ -6084,7 +6177,7 @@
       </c>
       <c r="B74" s="219" t="inlineStr">
         <is>
-          <t>tfm_pretrained</t>
+          <t>ffcl</t>
         </is>
       </c>
       <c r="C74" s="219" t="inlineStr">
@@ -6099,24 +6192,24 @@
       </c>
       <c r="E74" s="219" t="inlineStr">
         <is>
-          <t>[实测 1.89M] cohen_kappa per-seed 0:0.7144, 1:0.7084, 2:0.7077</t>
+          <t>[实测 2.67M] cohen_kappa per-seed 0:0.7252, 1:0.7243, 2:0.7516</t>
         </is>
       </c>
       <c r="F74" s="219" t="inlineStr">
         <is>
-          <t>lr=0.001 batch_size=512 epochs=50 patience=10 eval_every_steps=0 loss=cross_entropy label_smoothing=0.1</t>
+          <t>lr=0.001 batch_size=512 epochs=60 patience=15 eval_every_steps=0 loss=cross_entropy label_smoothing=0.1</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="219" t="inlineStr">
         <is>
-          <t>physionet_mi</t>
+          <t>isruc</t>
         </is>
       </c>
       <c r="B75" s="219" t="inlineStr">
         <is>
-          <t>biot_prest16</t>
+          <t>labram_pretrained</t>
         </is>
       </c>
       <c r="C75" s="219" t="inlineStr">
@@ -6131,24 +6224,24 @@
       </c>
       <c r="E75" s="219" t="inlineStr">
         <is>
-          <t>[实测 3.19M] balanced_acc per-seed 0:0.4950, 1:0.5034, 2:0.5126</t>
+          <t>[实测 5.82M] cohen_kappa per-seed 0:0.7376, 1:0.7538, 2:0.7183</t>
         </is>
       </c>
       <c r="F75" s="219" t="inlineStr">
         <is>
-          <t>lr=0.0004 batch_size=64 epochs=100 patience=10 eval_every_steps=0 loss=cross_entropy</t>
+          <t>stopped_by=patience lr=0.0005 batch_size=64 epochs=50 patience=10 eval_every_steps=0 loss=cross_entropy label_smoothing=0.1 loader_divisor=1.0</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="219" t="inlineStr">
         <is>
-          <t>physionet_mi</t>
+          <t>isruc</t>
         </is>
       </c>
       <c r="B76" s="219" t="inlineStr">
         <is>
-          <t>biot_scratch</t>
+          <t>labram_scratch</t>
         </is>
       </c>
       <c r="C76" s="219" t="inlineStr">
@@ -6163,24 +6256,24 @@
       </c>
       <c r="E76" s="219" t="inlineStr">
         <is>
-          <t>[实测 3.20M] balanced_acc per-seed 0:0.3337, 1:0.3273, 2:0.2687</t>
+          <t>[实测 5.82M] cohen_kappa per-seed 0:0.6301, 1:0.6084, 2:0.6322</t>
         </is>
       </c>
       <c r="F76" s="219" t="inlineStr">
         <is>
-          <t>lr=0.0004 batch_size=64 epochs=100 patience=10 eval_every_steps=0 loss=cross_entropy</t>
+          <t>stopped_by=patience lr=0.0005 batch_size=64 epochs=50 patience=10 eval_every_steps=0 loss=cross_entropy label_smoothing=0.1 loader_divisor=1.0</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="219" t="inlineStr">
         <is>
-          <t>physionet_mi</t>
+          <t>isruc</t>
         </is>
       </c>
       <c r="B77" s="219" t="inlineStr">
         <is>
-          <t>cbramod_pac</t>
+          <t>paclock_pac</t>
         </is>
       </c>
       <c r="C77" s="219" t="inlineStr">
@@ -6202,12 +6295,12 @@
     <row r="78">
       <c r="A78" s="219" t="inlineStr">
         <is>
-          <t>physionet_mi</t>
+          <t>isruc</t>
         </is>
       </c>
       <c r="B78" s="219" t="inlineStr">
         <is>
-          <t>cbramod_pretrained</t>
+          <t>sparcnet</t>
         </is>
       </c>
       <c r="C78" s="219" t="inlineStr">
@@ -6222,24 +6315,24 @@
       </c>
       <c r="E78" s="219" t="inlineStr">
         <is>
-          <t>[实测 46.01M] balanced_acc per-seed 0:0.6007, 1:0.6240, 2:0.5924</t>
+          <t>[实测 1.38M] cohen_kappa per-seed 0:0.7286, 1:0.7185, 2:0.7565</t>
         </is>
       </c>
       <c r="F78" s="219" t="inlineStr">
         <is>
-          <t>lr=0.0001 batch_size=64 epochs=50 patience=10 eval_every_steps=0 loss=cross_entropy label_smoothing=0.1 multi_lr=True</t>
+          <t>lr=0.001 batch_size=512 epochs=60 patience=15 eval_every_steps=0 loss=cross_entropy label_smoothing=0.1</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="219" t="inlineStr">
         <is>
-          <t>physionet_mi</t>
+          <t>isruc</t>
         </is>
       </c>
       <c r="B79" s="219" t="inlineStr">
         <is>
-          <t>cnn_transformer</t>
+          <t>st_transformer</t>
         </is>
       </c>
       <c r="C79" s="219" t="inlineStr">
@@ -6249,24 +6342,29 @@
       </c>
       <c r="D79" s="219" t="inlineStr">
         <is>
-          <t>withheld (rule 3)</t>
+          <t>filled</t>
         </is>
       </c>
       <c r="E79" s="219" t="inlineStr">
         <is>
-          <t>mis-configured seeds [0, 1, 2]: {0: "test Cohen's Kappa 0.0072 is at chance -- the model does not discriminate, whatever the val curve did", 1: 'val peak at first evaluation and never cleared chance (0.2500 vs 0.2500)', 2: "test Cohen's Kappa -0.0006 is at chance -- the model does not discriminate, whatever the val curve did"}; measured balanced_acc 0.2516±0.0027</t>
+          <t>[实测 3.42M] cohen_kappa per-seed 0:0.5488, 1:0.3217, 2:0.3076  [seed spread 28% -- mean is a weak summary]</t>
+        </is>
+      </c>
+      <c r="F79" s="219" t="inlineStr">
+        <is>
+          <t>lr=0.001 batch_size=512 epochs=60 patience=15 eval_every_steps=0 loss=cross_entropy label_smoothing=0.1</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="219" t="inlineStr">
         <is>
-          <t>physionet_mi</t>
+          <t>isruc</t>
         </is>
       </c>
       <c r="B80" s="219" t="inlineStr">
         <is>
-          <t>contrawr</t>
+          <t>tfm_pretrained</t>
         </is>
       </c>
       <c r="C80" s="219" t="inlineStr">
@@ -6281,12 +6379,12 @@
       </c>
       <c r="E80" s="219" t="inlineStr">
         <is>
-          <t>[实测 1.60M] balanced_acc per-seed 0:0.4898, 1:0.4965, 2:0.4810</t>
+          <t>[实测 1.89M] cohen_kappa per-seed 0:0.7144, 1:0.7084, 2:0.7077</t>
         </is>
       </c>
       <c r="F80" s="219" t="inlineStr">
         <is>
-          <t>lr=0.001 batch_size=64 epochs=100 patience=20 eval_every_steps=0 loss=cross_entropy label_smoothing=0.1</t>
+          <t>lr=0.001 batch_size=512 epochs=50 patience=10 eval_every_steps=0 loss=cross_entropy label_smoothing=0.1</t>
         </is>
       </c>
     </row>
@@ -6298,7 +6396,7 @@
       </c>
       <c r="B81" s="219" t="inlineStr">
         <is>
-          <t>eegpt_pretrained</t>
+          <t>biot_prest16</t>
         </is>
       </c>
       <c r="C81" s="219" t="inlineStr">
@@ -6313,12 +6411,12 @@
       </c>
       <c r="E81" s="219" t="inlineStr">
         <is>
-          <t>[实测 25.69M] balanced_acc per-seed 0:0.4233, 1:0.4411, 2:0.3494</t>
+          <t>[实测 3.19M] balanced_acc per-seed 0:0.4950, 1:0.5034, 2:0.5126</t>
         </is>
       </c>
       <c r="F81" s="219" t="inlineStr">
         <is>
-          <t>lr=0.0004 batch_size=32 epochs=100 patience=10 eval_every_steps=0 loss=cross_entropy</t>
+          <t>lr=0.0004 batch_size=64 epochs=100 patience=10 eval_every_steps=0 loss=cross_entropy</t>
         </is>
       </c>
     </row>
@@ -6330,7 +6428,7 @@
       </c>
       <c r="B82" s="219" t="inlineStr">
         <is>
-          <t>ffcl</t>
+          <t>biot_scratch</t>
         </is>
       </c>
       <c r="C82" s="219" t="inlineStr">
@@ -6345,12 +6443,12 @@
       </c>
       <c r="E82" s="219" t="inlineStr">
         <is>
-          <t>[实测 2.43M] balanced_acc per-seed 0:0.4760, 1:0.5004, 2:0.5041</t>
+          <t>[实测 3.20M] balanced_acc per-seed 0:0.3337, 1:0.3273, 2:0.2687</t>
         </is>
       </c>
       <c r="F82" s="219" t="inlineStr">
         <is>
-          <t>lr=0.001 batch_size=64 epochs=100 patience=20 eval_every_steps=0 loss=cross_entropy label_smoothing=0.1</t>
+          <t>lr=0.0004 batch_size=64 epochs=100 patience=10 eval_every_steps=0 loss=cross_entropy</t>
         </is>
       </c>
     </row>
@@ -6362,22 +6460,22 @@
       </c>
       <c r="B83" s="219" t="inlineStr">
         <is>
-          <t>labram_pretrained</t>
+          <t>cbramod_pac</t>
         </is>
       </c>
       <c r="C83" s="219" t="inlineStr">
         <is>
-          <t>[0, 1, 2]</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D83" s="219" t="inlineStr">
         <is>
-          <t>withheld (rule 3)</t>
+          <t>skipped</t>
         </is>
       </c>
       <c r="E83" s="219" t="inlineStr">
         <is>
-          <t>mis-configured seeds [0, 1]: {0: 'val curve is flat (model not learning)', 1: "test Cohen's Kappa -0.0007 is at chance -- the model does not discriminate, whatever the val curve did"}; measured balanced_acc 0.3587±0.1541</t>
+          <t>the workbook has no row for this variant</t>
         </is>
       </c>
     </row>
@@ -6389,7 +6487,7 @@
       </c>
       <c r="B84" s="219" t="inlineStr">
         <is>
-          <t>paclock_full</t>
+          <t>cbramod_pretrained</t>
         </is>
       </c>
       <c r="C84" s="219" t="inlineStr">
@@ -6399,12 +6497,17 @@
       </c>
       <c r="D84" s="219" t="inlineStr">
         <is>
-          <t>withheld (rule 3)</t>
+          <t>filled</t>
         </is>
       </c>
       <c r="E84" s="219" t="inlineStr">
         <is>
-          <t>mis-configured seeds [2]: {2: "test Cohen's Kappa 0.0193 is at chance -- the model does not discriminate, whatever the val curve did"}; measured balanced_acc 0.2738±0.0086</t>
+          <t>[实测 46.01M] balanced_acc per-seed 0:0.6035, 1:0.6257, 2:0.6096</t>
+        </is>
+      </c>
+      <c r="F84" s="219" t="inlineStr">
+        <is>
+          <t>lr=0.0001 batch_size=64 epochs=50 patience=0 eval_every_steps=0 loss=cross_entropy label_smoothing=0.1 grad_clip=1.0 multi_lr=True</t>
         </is>
       </c>
     </row>
@@ -6416,22 +6519,27 @@
       </c>
       <c r="B85" s="219" t="inlineStr">
         <is>
-          <t>paclock_pac</t>
+          <t>cbramod_scratch</t>
         </is>
       </c>
       <c r="C85" s="219" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>[0, 1, 2]</t>
         </is>
       </c>
       <c r="D85" s="219" t="inlineStr">
         <is>
-          <t>skipped</t>
+          <t>filled</t>
         </is>
       </c>
       <c r="E85" s="219" t="inlineStr">
         <is>
-          <t>the workbook has no row for this variant</t>
+          <t>[实测 46.01M] balanced_acc per-seed 0:0.5491, 1:0.5562, 2:0.5558</t>
+        </is>
+      </c>
+      <c r="F85" s="219" t="inlineStr">
+        <is>
+          <t>lr=0.0001 batch_size=64 epochs=50 patience=0 eval_every_steps=0 loss=cross_entropy label_smoothing=0.1 grad_clip=1.0 multi_lr=True</t>
         </is>
       </c>
     </row>
@@ -6443,7 +6551,7 @@
       </c>
       <c r="B86" s="219" t="inlineStr">
         <is>
-          <t>sparcnet</t>
+          <t>cnn_transformer</t>
         </is>
       </c>
       <c r="C86" s="219" t="inlineStr">
@@ -6453,17 +6561,12 @@
       </c>
       <c r="D86" s="219" t="inlineStr">
         <is>
-          <t>filled</t>
+          <t>withheld (rule 3)</t>
         </is>
       </c>
       <c r="E86" s="219" t="inlineStr">
         <is>
-          <t>[实测 1.27M] balanced_acc per-seed 0:0.5951, 1:0.5863, 2:0.5901</t>
-        </is>
-      </c>
-      <c r="F86" s="219" t="inlineStr">
-        <is>
-          <t>lr=0.001 batch_size=64 epochs=100 patience=20 eval_every_steps=0 loss=cross_entropy label_smoothing=0.1</t>
+          <t>mis-configured seeds [0, 1, 2]: {0: "test Cohen's Kappa 0.0072 is at chance -- the model does not discriminate, whatever the val curve did", 1: 'val peak at first evaluation and never cleared chance (0.2500 vs 0.2500)', 2: "test Cohen's Kappa -0.0006 is at chance -- the model does not discriminate, whatever the val curve did"}; measured balanced_acc 0.2516±0.0027</t>
         </is>
       </c>
     </row>
@@ -6475,7 +6578,7 @@
       </c>
       <c r="B87" s="219" t="inlineStr">
         <is>
-          <t>st_transformer</t>
+          <t>contrawr</t>
         </is>
       </c>
       <c r="C87" s="219" t="inlineStr">
@@ -6490,7 +6593,7 @@
       </c>
       <c r="E87" s="219" t="inlineStr">
         <is>
-          <t>[实测 3.48M] balanced_acc per-seed 0:0.5757, 1:0.5973, 2:0.6085</t>
+          <t>[实测 1.60M] balanced_acc per-seed 0:0.4898, 1:0.4965, 2:0.4810</t>
         </is>
       </c>
       <c r="F87" s="219" t="inlineStr">
@@ -6507,7 +6610,7 @@
       </c>
       <c r="B88" s="219" t="inlineStr">
         <is>
-          <t>tfm_pretrained</t>
+          <t>eegpt_pretrained</t>
         </is>
       </c>
       <c r="C88" s="219" t="inlineStr">
@@ -6522,24 +6625,24 @@
       </c>
       <c r="E88" s="219" t="inlineStr">
         <is>
-          <t>[实测 1.89M] balanced_acc per-seed 0:0.4524, 1:0.4217, 2:0.4226</t>
+          <t>[实测 25.69M] balanced_acc per-seed 0:0.4233, 1:0.4411, 2:0.3494</t>
         </is>
       </c>
       <c r="F88" s="219" t="inlineStr">
         <is>
-          <t>lr=0.001 batch_size=32 epochs=50 patience=10 eval_every_steps=0 loss=cross_entropy label_smoothing=0.1</t>
+          <t>lr=0.0004 batch_size=32 epochs=100 patience=10 eval_every_steps=0 loss=cross_entropy</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="219" t="inlineStr">
         <is>
-          <t>sleepedf</t>
+          <t>physionet_mi</t>
         </is>
       </c>
       <c r="B89" s="219" t="inlineStr">
         <is>
-          <t>biot_prest16</t>
+          <t>ffcl</t>
         </is>
       </c>
       <c r="C89" s="219" t="inlineStr">
@@ -6554,24 +6657,24 @@
       </c>
       <c r="E89" s="219" t="inlineStr">
         <is>
-          <t>[实测 3.19M] cohen_kappa per-seed 0:0.5804, 1:0.5861, 2:0.6156</t>
+          <t>[实测 2.43M] balanced_acc per-seed 0:0.4760, 1:0.5004, 2:0.5041</t>
         </is>
       </c>
       <c r="F89" s="219" t="inlineStr">
         <is>
-          <t>lr=0.0004 batch_size=64 epochs=40 patience=10 eval_every_steps=0 loss=cross_entropy</t>
+          <t>lr=0.001 batch_size=64 epochs=100 patience=20 eval_every_steps=0 loss=cross_entropy label_smoothing=0.1</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="219" t="inlineStr">
         <is>
-          <t>sleepedf</t>
+          <t>physionet_mi</t>
         </is>
       </c>
       <c r="B90" s="219" t="inlineStr">
         <is>
-          <t>biot_scratch</t>
+          <t>labram_pretrained</t>
         </is>
       </c>
       <c r="C90" s="219" t="inlineStr">
@@ -6586,83 +6689,83 @@
       </c>
       <c r="E90" s="219" t="inlineStr">
         <is>
-          <t>[实测 3.18M] cohen_kappa per-seed 0:0.6579, 1:0.6341, 2:0.6722</t>
+          <t>[实测 5.82M] balanced_acc per-seed 0:0.5352, 1:0.5647, 2:0.5720</t>
         </is>
       </c>
       <c r="F90" s="219" t="inlineStr">
         <is>
-          <t>lr=0.0004 batch_size=64 epochs=40 patience=10 eval_every_steps=0 loss=cross_entropy</t>
+          <t>stopped_by=patience lr=0.0005 batch_size=64 epochs=50 patience=10 eval_every_steps=0 loss=cross_entropy label_smoothing=0.1 loader_divisor=1.0</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="219" t="inlineStr">
         <is>
-          <t>sleepedf</t>
+          <t>physionet_mi</t>
         </is>
       </c>
       <c r="B91" s="219" t="inlineStr">
         <is>
-          <t>cbramod_pac</t>
+          <t>labram_scratch</t>
         </is>
       </c>
       <c r="C91" s="219" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>[0, 1, 2]</t>
         </is>
       </c>
       <c r="D91" s="219" t="inlineStr">
         <is>
-          <t>skipped</t>
+          <t>filled</t>
         </is>
       </c>
       <c r="E91" s="219" t="inlineStr">
         <is>
-          <t>the workbook has no row for this variant</t>
+          <t>[实测 5.82M] balanced_acc per-seed 0:0.3854, 1:0.3635, 2:0.3510</t>
+        </is>
+      </c>
+      <c r="F91" s="219" t="inlineStr">
+        <is>
+          <t>stopped_by=patience lr=0.0005 batch_size=64 epochs=50 patience=10 eval_every_steps=0 loss=cross_entropy label_smoothing=0.1 loader_divisor=1.0</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="219" t="inlineStr">
         <is>
-          <t>sleepedf</t>
+          <t>physionet_mi</t>
         </is>
       </c>
       <c r="B92" s="219" t="inlineStr">
         <is>
-          <t>cbramod_pretrained</t>
+          <t>paclock_pac</t>
         </is>
       </c>
       <c r="C92" s="219" t="inlineStr">
         <is>
-          <t>[0, 1, 2]</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D92" s="219" t="inlineStr">
         <is>
-          <t>filled</t>
+          <t>skipped</t>
         </is>
       </c>
       <c r="E92" s="219" t="inlineStr">
         <is>
-          <t>[实测 9.85M] cohen_kappa per-seed 0:0.6744, 1:0.6671, 2:0.6749</t>
-        </is>
-      </c>
-      <c r="F92" s="219" t="inlineStr">
-        <is>
-          <t>lr=0.0001 batch_size=64 epochs=50 patience=10 eval_every_steps=0 loss=cross_entropy label_smoothing=0.1 multi_lr=True</t>
+          <t>the workbook has no row for this variant</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="219" t="inlineStr">
         <is>
-          <t>sleepedf</t>
+          <t>physionet_mi</t>
         </is>
       </c>
       <c r="B93" s="219" t="inlineStr">
         <is>
-          <t>cbramod_scratch</t>
+          <t>paclock_v2</t>
         </is>
       </c>
       <c r="C93" s="219" t="inlineStr">
@@ -6672,29 +6775,24 @@
       </c>
       <c r="D93" s="219" t="inlineStr">
         <is>
-          <t>filled</t>
+          <t>withheld (rule 3)</t>
         </is>
       </c>
       <c r="E93" s="219" t="inlineStr">
         <is>
-          <t>[实测 9.85M] cohen_kappa per-seed 0:0.6504, 1:0.6561, 2:0.6569</t>
-        </is>
-      </c>
-      <c r="F93" s="219" t="inlineStr">
-        <is>
-          <t>lr=0.0001 batch_size=64 epochs=50 patience=0 eval_every_steps=0 loss=cross_entropy label_smoothing=0.1 grad_clip=1.0 multi_lr=True</t>
+          <t>mis-configured seeds [1, 2]: {1: "test Cohen's Kappa 0.0146 is at chance -- the model does not discriminate, whatever the val curve did", 2: 'val peak at first evaluation and never cleared chance (0.2500 vs 0.2500)'}; measured balanced_acc 0.2830±0.0392</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="219" t="inlineStr">
         <is>
-          <t>sleepedf</t>
+          <t>physionet_mi</t>
         </is>
       </c>
       <c r="B94" s="219" t="inlineStr">
         <is>
-          <t>cnn_transformer</t>
+          <t>sparcnet</t>
         </is>
       </c>
       <c r="C94" s="219" t="inlineStr">
@@ -6709,24 +6807,24 @@
       </c>
       <c r="E94" s="219" t="inlineStr">
         <is>
-          <t>[实测 3.15M] cohen_kappa per-seed 0:0.6871, 1:0.6614, 2:0.6850</t>
+          <t>[实测 1.27M] balanced_acc per-seed 0:0.5951, 1:0.5863, 2:0.5901</t>
         </is>
       </c>
       <c r="F94" s="219" t="inlineStr">
         <is>
-          <t>lr=0.001 batch_size=512 epochs=60 patience=15 eval_every_steps=0 loss=cross_entropy label_smoothing=0.1</t>
+          <t>lr=0.001 batch_size=64 epochs=100 patience=20 eval_every_steps=0 loss=cross_entropy label_smoothing=0.1</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="219" t="inlineStr">
         <is>
-          <t>sleepedf</t>
+          <t>physionet_mi</t>
         </is>
       </c>
       <c r="B95" s="219" t="inlineStr">
         <is>
-          <t>contrawr</t>
+          <t>st_transformer</t>
         </is>
       </c>
       <c r="C95" s="219" t="inlineStr">
@@ -6741,24 +6839,24 @@
       </c>
       <c r="E95" s="219" t="inlineStr">
         <is>
-          <t>[实测 1.56M] cohen_kappa per-seed 0:0.6752, 1:0.6964, 2:0.7031</t>
+          <t>[实测 3.48M] balanced_acc per-seed 0:0.5757, 1:0.5973, 2:0.6085</t>
         </is>
       </c>
       <c r="F95" s="219" t="inlineStr">
         <is>
-          <t>lr=0.001 batch_size=512 epochs=60 patience=15 eval_every_steps=0 loss=cross_entropy label_smoothing=0.1</t>
+          <t>lr=0.001 batch_size=64 epochs=100 patience=20 eval_every_steps=0 loss=cross_entropy label_smoothing=0.1</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="219" t="inlineStr">
         <is>
-          <t>sleepedf</t>
+          <t>physionet_mi</t>
         </is>
       </c>
       <c r="B96" s="219" t="inlineStr">
         <is>
-          <t>eegpt_pretrained</t>
+          <t>tfm_pretrained</t>
         </is>
       </c>
       <c r="C96" s="219" t="inlineStr">
@@ -6773,12 +6871,12 @@
       </c>
       <c r="E96" s="219" t="inlineStr">
         <is>
-          <t>[实测 25.69M] cohen_kappa per-seed 0:0.6071, 1:0.5831, 2:0.6031</t>
+          <t>[实测 1.89M] balanced_acc per-seed 0:0.4524, 1:0.4217, 2:0.4226</t>
         </is>
       </c>
       <c r="F96" s="219" t="inlineStr">
         <is>
-          <t>lr=0.0004 batch_size=32 epochs=40 patience=10 eval_every_steps=200 loss=cross_entropy</t>
+          <t>lr=0.001 batch_size=32 epochs=50 patience=10 eval_every_steps=0 loss=cross_entropy label_smoothing=0.1</t>
         </is>
       </c>
     </row>
@@ -6790,7 +6888,7 @@
       </c>
       <c r="B97" s="219" t="inlineStr">
         <is>
-          <t>ffcl</t>
+          <t>biot_prest16</t>
         </is>
       </c>
       <c r="C97" s="219" t="inlineStr">
@@ -6805,12 +6903,12 @@
       </c>
       <c r="E97" s="219" t="inlineStr">
         <is>
-          <t>[实测 2.51M] cohen_kappa per-seed 0:0.6785, 1:0.6730, 2:0.6824</t>
+          <t>[实测 3.19M] cohen_kappa per-seed 0:0.5804, 1:0.5861, 2:0.6156</t>
         </is>
       </c>
       <c r="F97" s="219" t="inlineStr">
         <is>
-          <t>lr=0.001 batch_size=512 epochs=60 patience=15 eval_every_steps=0 loss=cross_entropy label_smoothing=0.1</t>
+          <t>lr=0.0004 batch_size=64 epochs=40 patience=10 eval_every_steps=0 loss=cross_entropy</t>
         </is>
       </c>
     </row>
@@ -6822,7 +6920,7 @@
       </c>
       <c r="B98" s="219" t="inlineStr">
         <is>
-          <t>labram_pretrained</t>
+          <t>biot_scratch</t>
         </is>
       </c>
       <c r="C98" s="219" t="inlineStr">
@@ -6837,12 +6935,12 @@
       </c>
       <c r="E98" s="219" t="inlineStr">
         <is>
-          <t>[实测 5.82M] cohen_kappa per-seed 0:0.6019, 1:0.6217, 2:0.6089</t>
+          <t>[实测 3.18M] cohen_kappa per-seed 0:0.6579, 1:0.6341, 2:0.6722</t>
         </is>
       </c>
       <c r="F98" s="219" t="inlineStr">
         <is>
-          <t>lr=0.0005 batch_size=64 epochs=50 patience=10 eval_every_steps=0 loss=cross_entropy loader_divisor=1.0</t>
+          <t>lr=0.0004 batch_size=64 epochs=40 patience=10 eval_every_steps=0 loss=cross_entropy</t>
         </is>
       </c>
     </row>
@@ -6854,27 +6952,22 @@
       </c>
       <c r="B99" s="219" t="inlineStr">
         <is>
-          <t>paclock_full</t>
+          <t>cbramod_pac</t>
         </is>
       </c>
       <c r="C99" s="219" t="inlineStr">
         <is>
-          <t>[0, 1, 2]</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D99" s="219" t="inlineStr">
         <is>
-          <t>filled</t>
+          <t>skipped</t>
         </is>
       </c>
       <c r="E99" s="219" t="inlineStr">
         <is>
-          <t>[实测 1.64M] cohen_kappa per-seed 0:0.6376, 1:0.6100, 2:0.6121</t>
-        </is>
-      </c>
-      <c r="F99" s="219" t="inlineStr">
-        <is>
-          <t>lr=0.0001 batch_size=32 epochs=20 patience=20 eval_every_steps=0 loss=cross_entropy label_smoothing=0.1 grad_clip=1.0 tokenizer_mode=pac_interaction pac_token_mode=measured interaction_mode=product band_pe=index spatial_pe=xyz</t>
+          <t>the workbook has no row for this variant</t>
         </is>
       </c>
     </row>
@@ -6886,22 +6979,27 @@
       </c>
       <c r="B100" s="219" t="inlineStr">
         <is>
-          <t>paclock_pac</t>
+          <t>cbramod_pretrained</t>
         </is>
       </c>
       <c r="C100" s="219" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>[0, 1, 2]</t>
         </is>
       </c>
       <c r="D100" s="219" t="inlineStr">
         <is>
-          <t>skipped</t>
+          <t>filled</t>
         </is>
       </c>
       <c r="E100" s="219" t="inlineStr">
         <is>
-          <t>the workbook has no row for this variant</t>
+          <t>[实测 9.85M] cohen_kappa per-seed 0:0.6658, 1:0.6743, 2:0.6742</t>
+        </is>
+      </c>
+      <c r="F100" s="219" t="inlineStr">
+        <is>
+          <t>lr=0.0001 batch_size=64 epochs=50 patience=0 eval_every_steps=0 loss=cross_entropy label_smoothing=0.1 grad_clip=1.0 multi_lr=True</t>
         </is>
       </c>
     </row>
@@ -6913,7 +7011,7 @@
       </c>
       <c r="B101" s="219" t="inlineStr">
         <is>
-          <t>sparcnet</t>
+          <t>cbramod_scratch</t>
         </is>
       </c>
       <c r="C101" s="219" t="inlineStr">
@@ -6928,12 +7026,12 @@
       </c>
       <c r="E101" s="219" t="inlineStr">
         <is>
-          <t>[实测 1.23M] cohen_kappa per-seed 0:0.6662, 1:0.6848, 2:0.6632</t>
+          <t>[实测 9.85M] cohen_kappa per-seed 0:0.6504, 1:0.6561, 2:0.6569</t>
         </is>
       </c>
       <c r="F101" s="219" t="inlineStr">
         <is>
-          <t>lr=0.001 batch_size=512 epochs=60 patience=15 eval_every_steps=0 loss=cross_entropy label_smoothing=0.1</t>
+          <t>lr=0.0001 batch_size=64 epochs=50 patience=0 eval_every_steps=0 loss=cross_entropy label_smoothing=0.1 grad_clip=1.0 multi_lr=True</t>
         </is>
       </c>
     </row>
@@ -6945,7 +7043,7 @@
       </c>
       <c r="B102" s="219" t="inlineStr">
         <is>
-          <t>st_transformer</t>
+          <t>cnn_transformer</t>
         </is>
       </c>
       <c r="C102" s="219" t="inlineStr">
@@ -6960,7 +7058,7 @@
       </c>
       <c r="E102" s="219" t="inlineStr">
         <is>
-          <t>[实测 3.41M] cohen_kappa per-seed 0:0.6508, 1:0.6570, 2:0.6581</t>
+          <t>[实测 3.15M] cohen_kappa per-seed 0:0.6871, 1:0.6614, 2:0.6850</t>
         </is>
       </c>
       <c r="F102" s="219" t="inlineStr">
@@ -6977,7 +7075,7 @@
       </c>
       <c r="B103" s="219" t="inlineStr">
         <is>
-          <t>tfm_pretrained</t>
+          <t>contrawr</t>
         </is>
       </c>
       <c r="C103" s="219" t="inlineStr">
@@ -6992,24 +7090,24 @@
       </c>
       <c r="E103" s="219" t="inlineStr">
         <is>
-          <t>[实测 1.89M] cohen_kappa per-seed 0:0.6165, 1:0.6126, 2:0.6122</t>
+          <t>[实测 1.56M] cohen_kappa per-seed 0:0.6752, 1:0.6964, 2:0.7031</t>
         </is>
       </c>
       <c r="F103" s="219" t="inlineStr">
         <is>
-          <t>lr=0.001 batch_size=512 epochs=50 patience=10 eval_every_steps=0 loss=cross_entropy label_smoothing=0.1</t>
+          <t>lr=0.001 batch_size=512 epochs=60 patience=15 eval_every_steps=0 loss=cross_entropy label_smoothing=0.1</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="219" t="inlineStr">
         <is>
-          <t>tuab</t>
+          <t>sleepedf</t>
         </is>
       </c>
       <c r="B104" s="219" t="inlineStr">
         <is>
-          <t>biot_prest16</t>
+          <t>eegpt_pretrained</t>
         </is>
       </c>
       <c r="C104" s="219" t="inlineStr">
@@ -7024,24 +7122,24 @@
       </c>
       <c r="E104" s="219" t="inlineStr">
         <is>
-          <t>[实测 3.19M] auroc per-seed 0:0.8750, 1:0.8692, 2:0.8747</t>
+          <t>[实测 25.69M] cohen_kappa per-seed 0:0.6071, 1:0.5831, 2:0.6031</t>
         </is>
       </c>
       <c r="F104" s="219" t="inlineStr">
         <is>
-          <t>lr=0.001 batch_size=512 epochs=100 patience=5 eval_every_steps=0 loss=bce_with_logits</t>
+          <t>lr=0.0004 batch_size=32 epochs=40 patience=10 eval_every_steps=200 loss=cross_entropy</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="219" t="inlineStr">
         <is>
-          <t>tuab</t>
+          <t>sleepedf</t>
         </is>
       </c>
       <c r="B105" s="219" t="inlineStr">
         <is>
-          <t>biot_scratch</t>
+          <t>ffcl</t>
         </is>
       </c>
       <c r="C105" s="219" t="inlineStr">
@@ -7056,51 +7154,56 @@
       </c>
       <c r="E105" s="219" t="inlineStr">
         <is>
-          <t>[实测 3.19M] auroc per-seed 0:0.8658, 1:0.8761, 2:0.8665</t>
+          <t>[实测 2.51M] cohen_kappa per-seed 0:0.6785, 1:0.6730, 2:0.6824</t>
         </is>
       </c>
       <c r="F105" s="219" t="inlineStr">
         <is>
-          <t>lr=0.001 batch_size=512 epochs=100 patience=5 eval_every_steps=0 loss=bce_with_logits</t>
+          <t>lr=0.001 batch_size=512 epochs=60 patience=15 eval_every_steps=0 loss=cross_entropy label_smoothing=0.1</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="219" t="inlineStr">
         <is>
-          <t>tuab</t>
+          <t>sleepedf</t>
         </is>
       </c>
       <c r="B106" s="219" t="inlineStr">
         <is>
-          <t>cbramod_pac</t>
+          <t>labram_pretrained</t>
         </is>
       </c>
       <c r="C106" s="219" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>[0, 1, 2]</t>
         </is>
       </c>
       <c r="D106" s="219" t="inlineStr">
         <is>
-          <t>skipped</t>
+          <t>filled</t>
         </is>
       </c>
       <c r="E106" s="219" t="inlineStr">
         <is>
-          <t>the workbook has no row for this variant</t>
+          <t>[实测 5.82M] cohen_kappa per-seed 0:0.6082, 1:0.6032, 2:0.6188</t>
+        </is>
+      </c>
+      <c r="F106" s="219" t="inlineStr">
+        <is>
+          <t>stopped_by=patience lr=0.0005 batch_size=64 epochs=50 patience=10 eval_every_steps=0 loss=cross_entropy label_smoothing=0.1 loader_divisor=1.0</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="219" t="inlineStr">
         <is>
-          <t>tuab</t>
+          <t>sleepedf</t>
         </is>
       </c>
       <c r="B107" s="219" t="inlineStr">
         <is>
-          <t>cbramod_pretrained</t>
+          <t>labram_scratch</t>
         </is>
       </c>
       <c r="C107" s="219" t="inlineStr">
@@ -7115,56 +7218,51 @@
       </c>
       <c r="E107" s="219" t="inlineStr">
         <is>
-          <t>[实测 30.65M] auroc per-seed 0:0.8900, 1:0.8697, 2:0.8858</t>
+          <t>[实测 5.82M] cohen_kappa per-seed 0:0.6094, 1:0.5932, 2:0.5915</t>
         </is>
       </c>
       <c r="F107" s="219" t="inlineStr">
         <is>
-          <t>lr=0.0001 batch_size=64 epochs=50 patience=10 eval_every_steps=100 loss=bce_with_logits multi_lr=True</t>
+          <t>stopped_by=patience lr=0.0005 batch_size=64 epochs=50 patience=10 eval_every_steps=0 loss=cross_entropy label_smoothing=0.1 loader_divisor=1.0</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="219" t="inlineStr">
         <is>
-          <t>tuab</t>
+          <t>sleepedf</t>
         </is>
       </c>
       <c r="B108" s="219" t="inlineStr">
         <is>
-          <t>cbramod_scratch</t>
+          <t>paclock_pac</t>
         </is>
       </c>
       <c r="C108" s="219" t="inlineStr">
         <is>
-          <t>[0, 1, 2]</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D108" s="219" t="inlineStr">
         <is>
-          <t>filled</t>
+          <t>skipped</t>
         </is>
       </c>
       <c r="E108" s="219" t="inlineStr">
         <is>
-          <t>[实测 30.65M] auroc per-seed 0:0.8727, 1:0.8789, 2:0.8771</t>
-        </is>
-      </c>
-      <c r="F108" s="219" t="inlineStr">
-        <is>
-          <t>lr=0.0001 batch_size=64 epochs=50 patience=0 eval_every_steps=0 loss=bce_with_logits grad_clip=1.0 select_metric=auroc multi_lr=True</t>
+          <t>the workbook has no row for this variant</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="219" t="inlineStr">
         <is>
-          <t>tuab</t>
+          <t>sleepedf</t>
         </is>
       </c>
       <c r="B109" s="219" t="inlineStr">
         <is>
-          <t>cnn_transformer</t>
+          <t>paclock_v2</t>
         </is>
       </c>
       <c r="C109" s="219" t="inlineStr">
@@ -7179,24 +7277,24 @@
       </c>
       <c r="E109" s="219" t="inlineStr">
         <is>
-          <t>[实测 3.15M] auroc per-seed 0:0.8910, 1:0.8972, 2:0.8858</t>
+          <t>[实测 1.62M] cohen_kappa per-seed 0:0.6535, 1:0.6427, 2:0.6414</t>
         </is>
       </c>
       <c r="F109" s="219" t="inlineStr">
         <is>
-          <t>lr=0.001 batch_size=512 epochs=20 patience=8 eval_every_steps=200 loss=bce_with_logits</t>
+          <t>lr=0.0001 batch_size=32 epochs=20 patience=20 eval_every_steps=0 loss=cross_entropy label_smoothing=0.1 grad_clip=1.0 tokenizer_mode=pac_interaction pac_token_mode=measured interaction_mode=product band_pe=index spatial_pe=xyz</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="219" t="inlineStr">
         <is>
-          <t>tuab</t>
+          <t>sleepedf</t>
         </is>
       </c>
       <c r="B110" s="219" t="inlineStr">
         <is>
-          <t>contrawr</t>
+          <t>sparcnet</t>
         </is>
       </c>
       <c r="C110" s="219" t="inlineStr">
@@ -7211,24 +7309,24 @@
       </c>
       <c r="E110" s="219" t="inlineStr">
         <is>
-          <t>[实测 1.57M] auroc per-seed 0:0.8849, 1:0.8839, 2:0.8969</t>
+          <t>[实测 1.23M] cohen_kappa per-seed 0:0.6662, 1:0.6848, 2:0.6632</t>
         </is>
       </c>
       <c r="F110" s="219" t="inlineStr">
         <is>
-          <t>lr=0.001 batch_size=512 epochs=20 patience=8 eval_every_steps=200 loss=bce_with_logits</t>
+          <t>lr=0.001 batch_size=512 epochs=60 patience=15 eval_every_steps=0 loss=cross_entropy label_smoothing=0.1</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="219" t="inlineStr">
         <is>
-          <t>tuab</t>
+          <t>sleepedf</t>
         </is>
       </c>
       <c r="B111" s="219" t="inlineStr">
         <is>
-          <t>eegpt_pretrained</t>
+          <t>st_transformer</t>
         </is>
       </c>
       <c r="C111" s="219" t="inlineStr">
@@ -7243,24 +7341,24 @@
       </c>
       <c r="E111" s="219" t="inlineStr">
         <is>
-          <t>[实测 25.69M] auroc per-seed 0:0.9046, 1:0.8981, 2:0.9057</t>
+          <t>[实测 3.41M] cohen_kappa per-seed 0:0.6508, 1:0.6570, 2:0.6581</t>
         </is>
       </c>
       <c r="F111" s="219" t="inlineStr">
         <is>
-          <t>lr=0.0004 batch_size=32 epochs=40 patience=10 eval_every_steps=200 loss=bce_with_logits</t>
+          <t>lr=0.001 batch_size=512 epochs=60 patience=15 eval_every_steps=0 loss=cross_entropy label_smoothing=0.1</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="219" t="inlineStr">
         <is>
-          <t>tuab</t>
+          <t>sleepedf</t>
         </is>
       </c>
       <c r="B112" s="219" t="inlineStr">
         <is>
-          <t>ffcl</t>
+          <t>tfm_pretrained</t>
         </is>
       </c>
       <c r="C112" s="219" t="inlineStr">
@@ -7275,12 +7373,12 @@
       </c>
       <c r="E112" s="219" t="inlineStr">
         <is>
-          <t>[实测 2.46M] auroc per-seed 0:0.8896, 1:0.8929, 2:0.8769</t>
+          <t>[实测 1.89M] cohen_kappa per-seed 0:0.6165, 1:0.6126, 2:0.6122</t>
         </is>
       </c>
       <c r="F112" s="219" t="inlineStr">
         <is>
-          <t>lr=0.001 batch_size=512 epochs=20 patience=8 eval_every_steps=200 loss=bce_with_logits</t>
+          <t>lr=0.001 batch_size=512 epochs=50 patience=10 eval_every_steps=0 loss=cross_entropy label_smoothing=0.1</t>
         </is>
       </c>
     </row>
@@ -7292,7 +7390,7 @@
       </c>
       <c r="B113" s="219" t="inlineStr">
         <is>
-          <t>labram_pretrained</t>
+          <t>biot_prest16</t>
         </is>
       </c>
       <c r="C113" s="219" t="inlineStr">
@@ -7307,12 +7405,12 @@
       </c>
       <c r="E113" s="219" t="inlineStr">
         <is>
-          <t>[实测 5.82M] auroc per-seed 0:0.8750, 1:0.8748, 2:0.8811</t>
+          <t>[实测 3.19M] auroc per-seed 0:0.8750, 1:0.8692, 2:0.8747</t>
         </is>
       </c>
       <c r="F113" s="219" t="inlineStr">
         <is>
-          <t>lr=0.0005 batch_size=64 epochs=50 patience=10 eval_every_steps=0 loss=bce_with_logits</t>
+          <t>lr=0.001 batch_size=512 epochs=100 patience=5 eval_every_steps=0 loss=bce_with_logits</t>
         </is>
       </c>
     </row>
@@ -7324,7 +7422,7 @@
       </c>
       <c r="B114" s="219" t="inlineStr">
         <is>
-          <t>sparcnet</t>
+          <t>biot_scratch</t>
         </is>
       </c>
       <c r="C114" s="219" t="inlineStr">
@@ -7339,12 +7437,12 @@
       </c>
       <c r="E114" s="219" t="inlineStr">
         <is>
-          <t>[实测 1.14M] auroc per-seed 0:0.8836, 1:0.8896, 2:0.8898</t>
+          <t>[实测 3.19M] auroc per-seed 0:0.8658, 1:0.8761, 2:0.8665</t>
         </is>
       </c>
       <c r="F114" s="219" t="inlineStr">
         <is>
-          <t>lr=0.001 batch_size=512 epochs=20 patience=8 eval_every_steps=200 loss=bce_with_logits</t>
+          <t>lr=0.001 batch_size=512 epochs=100 patience=5 eval_every_steps=0 loss=bce_with_logits</t>
         </is>
       </c>
     </row>
@@ -7356,27 +7454,22 @@
       </c>
       <c r="B115" s="219" t="inlineStr">
         <is>
-          <t>st_transformer</t>
+          <t>cbramod_pac</t>
         </is>
       </c>
       <c r="C115" s="219" t="inlineStr">
         <is>
-          <t>[0, 1, 2]</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D115" s="219" t="inlineStr">
         <is>
-          <t>filled</t>
+          <t>skipped</t>
         </is>
       </c>
       <c r="E115" s="219" t="inlineStr">
         <is>
-          <t>[实测 3.43M] auroc per-seed 0:0.9017, 1:0.8992, 2:0.8908</t>
-        </is>
-      </c>
-      <c r="F115" s="219" t="inlineStr">
-        <is>
-          <t>lr=0.001 batch_size=512 epochs=20 patience=8 eval_every_steps=200 loss=bce_with_logits</t>
+          <t>the workbook has no row for this variant</t>
         </is>
       </c>
     </row>
@@ -7388,7 +7481,7 @@
       </c>
       <c r="B116" s="219" t="inlineStr">
         <is>
-          <t>tfm_pretrained</t>
+          <t>cbramod_pretrained</t>
         </is>
       </c>
       <c r="C116" s="219" t="inlineStr">
@@ -7403,51 +7496,56 @@
       </c>
       <c r="E116" s="219" t="inlineStr">
         <is>
-          <t>[实测 1.89M] auroc per-seed 0:0.8785, 1:0.8821, 2:0.8772</t>
+          <t>[实测 30.65M] auroc per-seed 0:0.8586, 1:0.8584, 2:0.8744</t>
         </is>
       </c>
       <c r="F116" s="219" t="inlineStr">
         <is>
-          <t>lr=0.001 batch_size=512 epochs=10 patience=10 eval_every_steps=100 loss=bce_with_logits label_smoothing=0.1</t>
+          <t>lr=0.0001 batch_size=64 epochs=50 patience=0 eval_every_steps=0 loss=bce_with_logits grad_clip=1.0 select_metric=auroc multi_lr=True</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="219" t="inlineStr">
         <is>
-          <t>tuev</t>
+          <t>tuab</t>
         </is>
       </c>
       <c r="B117" s="219" t="inlineStr">
         <is>
-          <t>biot_hop50</t>
+          <t>cbramod_scratch</t>
         </is>
       </c>
       <c r="C117" s="219" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>[0, 1, 2]</t>
         </is>
       </c>
       <c r="D117" s="219" t="inlineStr">
         <is>
-          <t>skipped</t>
+          <t>filled</t>
         </is>
       </c>
       <c r="E117" s="219" t="inlineStr">
         <is>
-          <t>the workbook has no row for this variant</t>
+          <t>[实测 30.65M] auroc per-seed 0:0.8727, 1:0.8789, 2:0.8771</t>
+        </is>
+      </c>
+      <c r="F117" s="219" t="inlineStr">
+        <is>
+          <t>lr=0.0001 batch_size=64 epochs=50 patience=0 eval_every_steps=0 loss=bce_with_logits grad_clip=1.0 select_metric=auroc multi_lr=True</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="219" t="inlineStr">
         <is>
-          <t>tuev</t>
+          <t>tuab</t>
         </is>
       </c>
       <c r="B118" s="219" t="inlineStr">
         <is>
-          <t>biot_prest16</t>
+          <t>cnn_transformer</t>
         </is>
       </c>
       <c r="C118" s="219" t="inlineStr">
@@ -7462,24 +7560,24 @@
       </c>
       <c r="E118" s="219" t="inlineStr">
         <is>
-          <t>[实测 3.19M] cohen_kappa per-seed 0:0.5005, 1:0.5354, 2:0.5554</t>
+          <t>[实测 3.15M] auroc per-seed 0:0.8910, 1:0.8972, 2:0.8858</t>
         </is>
       </c>
       <c r="F118" s="219" t="inlineStr">
         <is>
-          <t>lr=0.001 batch_size=128 epochs=100 patience=5 eval_every_steps=0 loss=cross_entropy label_smoothing=0.0</t>
+          <t>lr=0.001 batch_size=512 epochs=20 patience=8 eval_every_steps=200 loss=bce_with_logits</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="219" t="inlineStr">
         <is>
-          <t>tuev</t>
+          <t>tuab</t>
         </is>
       </c>
       <c r="B119" s="219" t="inlineStr">
         <is>
-          <t>biot_scratch</t>
+          <t>contrawr</t>
         </is>
       </c>
       <c r="C119" s="219" t="inlineStr">
@@ -7494,174 +7592,204 @@
       </c>
       <c r="E119" s="219" t="inlineStr">
         <is>
-          <t>[实测 3.19M] cohen_kappa per-seed 0:0.5039, 1:0.5425, 2:0.5508</t>
+          <t>[实测 1.57M] auroc per-seed 0:0.8849, 1:0.8839, 2:0.8969</t>
         </is>
       </c>
       <c r="F119" s="219" t="inlineStr">
         <is>
-          <t>lr=0.001 batch_size=128 epochs=100 patience=5 eval_every_steps=0 loss=cross_entropy label_smoothing=0.0</t>
+          <t>lr=0.001 batch_size=512 epochs=20 patience=8 eval_every_steps=200 loss=bce_with_logits</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="219" t="inlineStr">
         <is>
-          <t>tuev</t>
+          <t>tuab</t>
         </is>
       </c>
       <c r="B120" s="219" t="inlineStr">
         <is>
-          <t>biot_tok100</t>
+          <t>eegpt_pretrained</t>
         </is>
       </c>
       <c r="C120" s="219" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>[0, 1, 2]</t>
         </is>
       </c>
       <c r="D120" s="219" t="inlineStr">
         <is>
-          <t>skipped</t>
+          <t>filled</t>
         </is>
       </c>
       <c r="E120" s="219" t="inlineStr">
         <is>
-          <t>the workbook has no row for this variant</t>
+          <t>[实测 25.69M] auroc per-seed 0:0.9046, 1:0.8981, 2:0.9057</t>
+        </is>
+      </c>
+      <c r="F120" s="219" t="inlineStr">
+        <is>
+          <t>lr=0.0004 batch_size=32 epochs=40 patience=10 eval_every_steps=200 loss=bce_with_logits</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="219" t="inlineStr">
         <is>
-          <t>tuev</t>
+          <t>tuab</t>
         </is>
       </c>
       <c r="B121" s="219" t="inlineStr">
         <is>
-          <t>cand_aug</t>
+          <t>ffcl</t>
         </is>
       </c>
       <c r="C121" s="219" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>[0, 1, 2]</t>
         </is>
       </c>
       <c r="D121" s="219" t="inlineStr">
         <is>
-          <t>skipped</t>
+          <t>filled</t>
         </is>
       </c>
       <c r="E121" s="219" t="inlineStr">
         <is>
-          <t>the workbook has no row for this variant</t>
+          <t>[实测 2.46M] auroc per-seed 0:0.8896, 1:0.8929, 2:0.8769</t>
+        </is>
+      </c>
+      <c r="F121" s="219" t="inlineStr">
+        <is>
+          <t>lr=0.001 batch_size=512 epochs=20 patience=8 eval_every_steps=200 loss=bce_with_logits</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="219" t="inlineStr">
         <is>
-          <t>tuev</t>
+          <t>tuab</t>
         </is>
       </c>
       <c r="B122" s="219" t="inlineStr">
         <is>
-          <t>cand_aug_drop03</t>
+          <t>labram_pretrained</t>
         </is>
       </c>
       <c r="C122" s="219" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>[0, 1, 2]</t>
         </is>
       </c>
       <c r="D122" s="219" t="inlineStr">
         <is>
-          <t>skipped</t>
+          <t>filled</t>
         </is>
       </c>
       <c r="E122" s="219" t="inlineStr">
         <is>
-          <t>the workbook has no row for this variant</t>
+          <t>[实测 5.82M] auroc per-seed 0:0.8750, 1:0.8748, 2:0.8811</t>
+        </is>
+      </c>
+      <c r="F122" s="219" t="inlineStr">
+        <is>
+          <t>lr=0.0005 batch_size=64 epochs=50 patience=10 eval_every_steps=0 loss=bce_with_logits</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="219" t="inlineStr">
         <is>
-          <t>tuev</t>
+          <t>tuab</t>
         </is>
       </c>
       <c r="B123" s="219" t="inlineStr">
         <is>
-          <t>cand_band_aug</t>
+          <t>sparcnet</t>
         </is>
       </c>
       <c r="C123" s="219" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>[0, 1, 2]</t>
         </is>
       </c>
       <c r="D123" s="219" t="inlineStr">
         <is>
-          <t>skipped</t>
+          <t>filled</t>
         </is>
       </c>
       <c r="E123" s="219" t="inlineStr">
         <is>
-          <t>the workbook has no row for this variant</t>
+          <t>[实测 1.14M] auroc per-seed 0:0.8836, 1:0.8896, 2:0.8898</t>
+        </is>
+      </c>
+      <c r="F123" s="219" t="inlineStr">
+        <is>
+          <t>lr=0.001 batch_size=512 epochs=20 patience=8 eval_every_steps=200 loss=bce_with_logits</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="219" t="inlineStr">
         <is>
-          <t>tuev</t>
+          <t>tuab</t>
         </is>
       </c>
       <c r="B124" s="219" t="inlineStr">
         <is>
-          <t>cand_base</t>
+          <t>st_transformer</t>
         </is>
       </c>
       <c r="C124" s="219" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>[0, 1, 2]</t>
         </is>
       </c>
       <c r="D124" s="219" t="inlineStr">
         <is>
-          <t>skipped</t>
+          <t>filled</t>
         </is>
       </c>
       <c r="E124" s="219" t="inlineStr">
         <is>
-          <t>the workbook has no row for this variant</t>
+          <t>[实测 3.43M] auroc per-seed 0:0.9017, 1:0.8992, 2:0.8908</t>
+        </is>
+      </c>
+      <c r="F124" s="219" t="inlineStr">
+        <is>
+          <t>lr=0.001 batch_size=512 epochs=20 patience=8 eval_every_steps=200 loss=bce_with_logits</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="219" t="inlineStr">
         <is>
-          <t>tuev</t>
+          <t>tuab</t>
         </is>
       </c>
       <c r="B125" s="219" t="inlineStr">
         <is>
-          <t>cand_drop03</t>
+          <t>tfm_pretrained</t>
         </is>
       </c>
       <c r="C125" s="219" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>[0, 1, 2]</t>
         </is>
       </c>
       <c r="D125" s="219" t="inlineStr">
         <is>
-          <t>skipped</t>
+          <t>filled</t>
         </is>
       </c>
       <c r="E125" s="219" t="inlineStr">
         <is>
-          <t>the workbook has no row for this variant</t>
+          <t>[实测 1.89M] auroc per-seed 0:0.8785, 1:0.8821, 2:0.8772</t>
+        </is>
+      </c>
+      <c r="F125" s="219" t="inlineStr">
+        <is>
+          <t>lr=0.001 batch_size=512 epochs=10 patience=10 eval_every_steps=100 loss=bce_with_logits label_smoothing=0.1</t>
         </is>
       </c>
     </row>
@@ -7673,7 +7801,7 @@
       </c>
       <c r="B126" s="219" t="inlineStr">
         <is>
-          <t>cand_head_attn</t>
+          <t>biot_hop50</t>
         </is>
       </c>
       <c r="C126" s="219" t="inlineStr">
@@ -7700,22 +7828,27 @@
       </c>
       <c r="B127" s="219" t="inlineStr">
         <is>
-          <t>cand_head_band</t>
+          <t>biot_prest16</t>
         </is>
       </c>
       <c r="C127" s="219" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>[0, 1, 2]</t>
         </is>
       </c>
       <c r="D127" s="219" t="inlineStr">
         <is>
-          <t>skipped</t>
+          <t>filled</t>
         </is>
       </c>
       <c r="E127" s="219" t="inlineStr">
         <is>
-          <t>the workbook has no row for this variant</t>
+          <t>[实测 3.19M] cohen_kappa per-seed 0:0.5005, 1:0.5354, 2:0.5554</t>
+        </is>
+      </c>
+      <c r="F127" s="219" t="inlineStr">
+        <is>
+          <t>lr=0.001 batch_size=128 epochs=100 patience=5 eval_every_steps=0 loss=cross_entropy label_smoothing=0.0</t>
         </is>
       </c>
     </row>
@@ -7727,22 +7860,27 @@
       </c>
       <c r="B128" s="219" t="inlineStr">
         <is>
-          <t>cand_heads8</t>
+          <t>biot_scratch</t>
         </is>
       </c>
       <c r="C128" s="219" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>[0, 1, 2]</t>
         </is>
       </c>
       <c r="D128" s="219" t="inlineStr">
         <is>
-          <t>skipped</t>
+          <t>filled</t>
         </is>
       </c>
       <c r="E128" s="219" t="inlineStr">
         <is>
-          <t>the workbook has no row for this variant</t>
+          <t>[实测 3.19M] cohen_kappa per-seed 0:0.5039, 1:0.5425, 2:0.5508</t>
+        </is>
+      </c>
+      <c r="F128" s="219" t="inlineStr">
+        <is>
+          <t>lr=0.001 batch_size=128 epochs=100 patience=5 eval_every_steps=0 loss=cross_entropy label_smoothing=0.0</t>
         </is>
       </c>
     </row>
@@ -7754,7 +7892,7 @@
       </c>
       <c r="B129" s="219" t="inlineStr">
         <is>
-          <t>cand_pacwin200</t>
+          <t>biot_tok100</t>
         </is>
       </c>
       <c r="C129" s="219" t="inlineStr">
@@ -7781,7 +7919,7 @@
       </c>
       <c r="B130" s="219" t="inlineStr">
         <is>
-          <t>cand_pacwin400</t>
+          <t>cand_base</t>
         </is>
       </c>
       <c r="C130" s="219" t="inlineStr">
@@ -7808,7 +7946,7 @@
       </c>
       <c r="B131" s="219" t="inlineStr">
         <is>
-          <t>cand_patch100</t>
+          <t>cand_dense</t>
         </is>
       </c>
       <c r="C131" s="219" t="inlineStr">
@@ -7835,7 +7973,7 @@
       </c>
       <c r="B132" s="219" t="inlineStr">
         <is>
-          <t>cand_size_base</t>
+          <t>cand_dense_lr1e5</t>
         </is>
       </c>
       <c r="C132" s="219" t="inlineStr">
@@ -7862,7 +8000,7 @@
       </c>
       <c r="B133" s="219" t="inlineStr">
         <is>
-          <t>cand_size_large</t>
+          <t>cand_dense_lr3e5</t>
         </is>
       </c>
       <c r="C133" s="219" t="inlineStr">
@@ -7889,7 +8027,7 @@
       </c>
       <c r="B134" s="219" t="inlineStr">
         <is>
-          <t>cbramod_pac</t>
+          <t>cand_dense_patch100</t>
         </is>
       </c>
       <c r="C134" s="219" t="inlineStr">
@@ -7916,27 +8054,22 @@
       </c>
       <c r="B135" s="219" t="inlineStr">
         <is>
-          <t>cbramod_pretrained</t>
+          <t>cand_e60_base</t>
         </is>
       </c>
       <c r="C135" s="219" t="inlineStr">
         <is>
-          <t>[0, 1, 2]</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D135" s="219" t="inlineStr">
         <is>
-          <t>filled</t>
+          <t>skipped</t>
         </is>
       </c>
       <c r="E135" s="219" t="inlineStr">
         <is>
-          <t>[实测 17.85M] cohen_kappa per-seed 0:0.5170, 1:0.6104, 2:0.6635</t>
-        </is>
-      </c>
-      <c r="F135" s="219" t="inlineStr">
-        <is>
-          <t>lr=0.0001 batch_size=64 epochs=50 patience=10 eval_every_steps=25 loss=cross_entropy label_smoothing=0.0 multi_lr=True</t>
+          <t>the workbook has no row for this variant</t>
         </is>
       </c>
     </row>
@@ -7948,27 +8081,22 @@
       </c>
       <c r="B136" s="219" t="inlineStr">
         <is>
-          <t>cbramod_scratch</t>
+          <t>cand_e60_patch100</t>
         </is>
       </c>
       <c r="C136" s="219" t="inlineStr">
         <is>
-          <t>[0, 1, 2]</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D136" s="219" t="inlineStr">
         <is>
-          <t>filled</t>
+          <t>skipped</t>
         </is>
       </c>
       <c r="E136" s="219" t="inlineStr">
         <is>
-          <t>[实测 17.85M] cohen_kappa per-seed 0:0.5755, 1:0.5366, 2:0.5794</t>
-        </is>
-      </c>
-      <c r="F136" s="219" t="inlineStr">
-        <is>
-          <t>lr=0.0001 batch_size=64 epochs=50 patience=0 eval_every_steps=0 loss=cross_entropy label_smoothing=0.1 grad_clip=1.0 multi_lr=True</t>
+          <t>the workbook has no row for this variant</t>
         </is>
       </c>
     </row>
@@ -7980,27 +8108,22 @@
       </c>
       <c r="B137" s="219" t="inlineStr">
         <is>
-          <t>cnn_transformer</t>
+          <t>cand_e60_size_base</t>
         </is>
       </c>
       <c r="C137" s="219" t="inlineStr">
         <is>
-          <t>[0, 1, 2]</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D137" s="219" t="inlineStr">
         <is>
-          <t>filled</t>
+          <t>skipped</t>
         </is>
       </c>
       <c r="E137" s="219" t="inlineStr">
         <is>
-          <t>[实测 3.16M] cohen_kappa per-seed 0:0.4987, 1:0.2779, 2:0.4527  [seed spread 23% -- mean is a weak summary]</t>
-        </is>
-      </c>
-      <c r="F137" s="219" t="inlineStr">
-        <is>
-          <t>lr=0.001 batch_size=512 epochs=100 patience=15 eval_every_steps=0 loss=cross_entropy label_smoothing=0.1</t>
+          <t>the workbook has no row for this variant</t>
         </is>
       </c>
     </row>
@@ -8012,27 +8135,22 @@
       </c>
       <c r="B138" s="219" t="inlineStr">
         <is>
-          <t>contrawr</t>
+          <t>cand_e60_size_large</t>
         </is>
       </c>
       <c r="C138" s="219" t="inlineStr">
         <is>
-          <t>[0, 1, 2]</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D138" s="219" t="inlineStr">
         <is>
-          <t>filled</t>
+          <t>skipped</t>
         </is>
       </c>
       <c r="E138" s="219" t="inlineStr">
         <is>
-          <t>[实测 1.57M] cohen_kappa per-seed 0:0.4410, 1:0.4849, 2:0.2969  [seed spread 20% -- mean is a weak summary]</t>
-        </is>
-      </c>
-      <c r="F138" s="219" t="inlineStr">
-        <is>
-          <t>lr=0.001 batch_size=512 epochs=100 patience=15 eval_every_steps=0 loss=cross_entropy label_smoothing=0.1</t>
+          <t>the workbook has no row for this variant</t>
         </is>
       </c>
     </row>
@@ -8044,27 +8162,22 @@
       </c>
       <c r="B139" s="219" t="inlineStr">
         <is>
-          <t>eegpt_pretrained</t>
+          <t>cand_ms</t>
         </is>
       </c>
       <c r="C139" s="219" t="inlineStr">
         <is>
-          <t>[0, 1, 2]</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D139" s="219" t="inlineStr">
         <is>
-          <t>filled</t>
+          <t>skipped</t>
         </is>
       </c>
       <c r="E139" s="219" t="inlineStr">
         <is>
-          <t>[实测 25.69M] cohen_kappa per-seed 0:0.5311, 1:0.6095, 2:0.5803</t>
-        </is>
-      </c>
-      <c r="F139" s="219" t="inlineStr">
-        <is>
-          <t>lr=0.0004 batch_size=32 epochs=40 patience=10 eval_every_steps=0 loss=cross_entropy</t>
+          <t>the workbook has no row for this variant</t>
         </is>
       </c>
     </row>
@@ -8076,27 +8189,22 @@
       </c>
       <c r="B140" s="219" t="inlineStr">
         <is>
-          <t>ffcl</t>
+          <t>cand_p100_large</t>
         </is>
       </c>
       <c r="C140" s="219" t="inlineStr">
         <is>
-          <t>[0, 1, 2]</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D140" s="219" t="inlineStr">
         <is>
-          <t>filled</t>
+          <t>skipped</t>
         </is>
       </c>
       <c r="E140" s="219" t="inlineStr">
         <is>
-          <t>[实测 2.42M] cohen_kappa per-seed 0:0.5069, 1:0.4432, 2:0.4827</t>
-        </is>
-      </c>
-      <c r="F140" s="219" t="inlineStr">
-        <is>
-          <t>lr=0.001 batch_size=512 epochs=100 patience=15 eval_every_steps=0 loss=cross_entropy label_smoothing=0.1</t>
+          <t>the workbook has no row for this variant</t>
         </is>
       </c>
     </row>
@@ -8108,27 +8216,22 @@
       </c>
       <c r="B141" s="219" t="inlineStr">
         <is>
-          <t>labram_pretrained</t>
+          <t>cand_p50_win100</t>
         </is>
       </c>
       <c r="C141" s="219" t="inlineStr">
         <is>
-          <t>[0, 1, 2]</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D141" s="219" t="inlineStr">
         <is>
-          <t>filled</t>
+          <t>skipped</t>
         </is>
       </c>
       <c r="E141" s="219" t="inlineStr">
         <is>
-          <t>[实测 5.82M] cohen_kappa per-seed 0:0.5550, 1:0.6349, 2:0.6608</t>
-        </is>
-      </c>
-      <c r="F141" s="219" t="inlineStr">
-        <is>
-          <t>lr=0.0005 batch_size=64 epochs=50 patience=10 eval_every_steps=0 loss=cross_entropy label_smoothing=0.0</t>
+          <t>the workbook has no row for this variant</t>
         </is>
       </c>
     </row>
@@ -8140,7 +8243,7 @@
       </c>
       <c r="B142" s="219" t="inlineStr">
         <is>
-          <t>paclock</t>
+          <t>cand_p50_win200</t>
         </is>
       </c>
       <c r="C142" s="219" t="inlineStr">
@@ -8155,7 +8258,7 @@
       </c>
       <c r="E142" s="219" t="inlineStr">
         <is>
-          <t>no row label for 'paclock'</t>
+          <t>the workbook has no row for this variant</t>
         </is>
       </c>
     </row>
@@ -8167,27 +8270,22 @@
       </c>
       <c r="B143" s="219" t="inlineStr">
         <is>
-          <t>paclock_full</t>
+          <t>cand_pacwin200</t>
         </is>
       </c>
       <c r="C143" s="219" t="inlineStr">
         <is>
-          <t>[0, 1, 2]</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D143" s="219" t="inlineStr">
         <is>
-          <t>filled</t>
+          <t>skipped</t>
         </is>
       </c>
       <c r="E143" s="219" t="inlineStr">
         <is>
-          <t>[实测 1.64M] cohen_kappa per-seed 0:0.6207, 1:0.6386, 2:0.6222</t>
-        </is>
-      </c>
-      <c r="F143" s="219" t="inlineStr">
-        <is>
-          <t>lr=0.0001 batch_size=32 epochs=20 patience=20 eval_every_steps=0 loss=cross_entropy label_smoothing=0.1 grad_clip=1.0 tokenizer_mode=pac_interaction pac_token_mode=measured interaction_mode=product band_pe=index spatial_pe=xyz</t>
+          <t>the workbook has no row for this variant</t>
         </is>
       </c>
     </row>
@@ -8199,7 +8297,7 @@
       </c>
       <c r="B144" s="219" t="inlineStr">
         <is>
-          <t>paclock_pac</t>
+          <t>cand_patch100</t>
         </is>
       </c>
       <c r="C144" s="219" t="inlineStr">
@@ -8226,7 +8324,7 @@
       </c>
       <c r="B145" s="219" t="inlineStr">
         <is>
-          <t>paclock_pilot_frozen</t>
+          <t>cand_patch50</t>
         </is>
       </c>
       <c r="C145" s="219" t="inlineStr">
@@ -8253,7 +8351,7 @@
       </c>
       <c r="B146" s="219" t="inlineStr">
         <is>
-          <t>paclock_pilot_unfiltered</t>
+          <t>cbramod_pac</t>
         </is>
       </c>
       <c r="C146" s="219" t="inlineStr">
@@ -8280,7 +8378,7 @@
       </c>
       <c r="B147" s="219" t="inlineStr">
         <is>
-          <t>sparcnet</t>
+          <t>cbramod_pretrained</t>
         </is>
       </c>
       <c r="C147" s="219" t="inlineStr">
@@ -8295,12 +8393,12 @@
       </c>
       <c r="E147" s="219" t="inlineStr">
         <is>
-          <t>[实测 0.99M] cohen_kappa per-seed 0:0.4665, 1:0.5199, 2:0.4791</t>
+          <t>[实测 17.85M] cohen_kappa per-seed 0:0.6199, 1:0.6566, 2:0.6582</t>
         </is>
       </c>
       <c r="F147" s="219" t="inlineStr">
         <is>
-          <t>lr=0.001 batch_size=512 epochs=100 patience=15 eval_every_steps=0 loss=cross_entropy label_smoothing=0.1</t>
+          <t>lr=0.0001 batch_size=64 epochs=50 patience=0 eval_every_steps=0 loss=cross_entropy label_smoothing=0.1 grad_clip=1.0 multi_lr=True</t>
         </is>
       </c>
     </row>
@@ -8312,7 +8410,7 @@
       </c>
       <c r="B148" s="219" t="inlineStr">
         <is>
-          <t>st_transformer</t>
+          <t>cbramod_scratch</t>
         </is>
       </c>
       <c r="C148" s="219" t="inlineStr">
@@ -8327,12 +8425,12 @@
       </c>
       <c r="E148" s="219" t="inlineStr">
         <is>
-          <t>[实测 3.43M] cohen_kappa per-seed 0:0.5139, 1:0.4916, 2:0.4962</t>
+          <t>[实测 17.85M] cohen_kappa per-seed 0:0.5755, 1:0.5366, 2:0.5794</t>
         </is>
       </c>
       <c r="F148" s="219" t="inlineStr">
         <is>
-          <t>lr=0.001 batch_size=512 epochs=100 patience=15 eval_every_steps=0 loss=cross_entropy label_smoothing=0.1</t>
+          <t>lr=0.0001 batch_size=64 epochs=50 patience=0 eval_every_steps=0 loss=cross_entropy label_smoothing=0.1 grad_clip=1.0 multi_lr=True</t>
         </is>
       </c>
     </row>
@@ -8344,7 +8442,7 @@
       </c>
       <c r="B149" s="219" t="inlineStr">
         <is>
-          <t>tfm_pretrained</t>
+          <t>cnn_transformer</t>
         </is>
       </c>
       <c r="C149" s="219" t="inlineStr">
@@ -8359,24 +8457,24 @@
       </c>
       <c r="E149" s="219" t="inlineStr">
         <is>
-          <t>[实测 1.89M] cohen_kappa per-seed 0:0.6543, 1:0.6299, 2:0.6715</t>
+          <t>[实测 3.16M] cohen_kappa per-seed 0:0.4987, 1:0.2779, 2:0.4527  [seed spread 23% -- mean is a weak summary]</t>
         </is>
       </c>
       <c r="F149" s="219" t="inlineStr">
         <is>
-          <t>lr=0.001 batch_size=512 epochs=50 patience=10 eval_every_steps=100 loss=cross_entropy label_smoothing=0.1</t>
+          <t>lr=0.001 batch_size=512 epochs=100 patience=15 eval_every_steps=0 loss=cross_entropy label_smoothing=0.1</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="219" t="inlineStr">
         <is>
-          <t>tusz</t>
+          <t>tuev</t>
         </is>
       </c>
       <c r="B150" s="219" t="inlineStr">
         <is>
-          <t>biot_prest16</t>
+          <t>contrawr</t>
         </is>
       </c>
       <c r="C150" s="219" t="inlineStr">
@@ -8391,24 +8489,24 @@
       </c>
       <c r="E150" s="219" t="inlineStr">
         <is>
-          <t>[实测 3.19M] pr_auc per-seed 0:0.3673, 1:0.3513, 2:0.2951</t>
+          <t>[实测 1.57M] cohen_kappa per-seed 0:0.4410, 1:0.4849, 2:0.2969  [seed spread 20% -- mean is a weak summary]</t>
         </is>
       </c>
       <c r="F150" s="219" t="inlineStr">
         <is>
-          <t>lr=0.001 batch_size=512 epochs=100 patience=5 eval_every_steps=0 loss=bce_with_logits</t>
+          <t>lr=0.001 batch_size=512 epochs=100 patience=15 eval_every_steps=0 loss=cross_entropy label_smoothing=0.1</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="219" t="inlineStr">
         <is>
-          <t>tusz</t>
+          <t>tuev</t>
         </is>
       </c>
       <c r="B151" s="219" t="inlineStr">
         <is>
-          <t>biot_scratch</t>
+          <t>eegpt_pretrained</t>
         </is>
       </c>
       <c r="C151" s="219" t="inlineStr">
@@ -8423,51 +8521,56 @@
       </c>
       <c r="E151" s="219" t="inlineStr">
         <is>
-          <t>[实测 3.19M] pr_auc per-seed 0:0.3186, 1:0.3682, 2:0.3556</t>
+          <t>[实测 25.69M] cohen_kappa per-seed 0:0.5311, 1:0.6095, 2:0.5803</t>
         </is>
       </c>
       <c r="F151" s="219" t="inlineStr">
         <is>
-          <t>lr=0.001 batch_size=512 epochs=100 patience=5 eval_every_steps=0 loss=bce_with_logits</t>
+          <t>lr=0.0004 batch_size=32 epochs=40 patience=10 eval_every_steps=0 loss=cross_entropy</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="219" t="inlineStr">
         <is>
-          <t>tusz</t>
+          <t>tuev</t>
         </is>
       </c>
       <c r="B152" s="219" t="inlineStr">
         <is>
-          <t>cbramod_pac</t>
+          <t>ffcl</t>
         </is>
       </c>
       <c r="C152" s="219" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>[0, 1, 2]</t>
         </is>
       </c>
       <c r="D152" s="219" t="inlineStr">
         <is>
-          <t>skipped</t>
+          <t>filled</t>
         </is>
       </c>
       <c r="E152" s="219" t="inlineStr">
         <is>
-          <t>the workbook has no row for this variant</t>
+          <t>[实测 2.42M] cohen_kappa per-seed 0:0.5069, 1:0.4432, 2:0.4827</t>
+        </is>
+      </c>
+      <c r="F152" s="219" t="inlineStr">
+        <is>
+          <t>lr=0.001 batch_size=512 epochs=100 patience=15 eval_every_steps=0 loss=cross_entropy label_smoothing=0.1</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="219" t="inlineStr">
         <is>
-          <t>tusz</t>
+          <t>tuev</t>
         </is>
       </c>
       <c r="B153" s="219" t="inlineStr">
         <is>
-          <t>cbramod_pretrained</t>
+          <t>labram_pretrained</t>
         </is>
       </c>
       <c r="C153" s="219" t="inlineStr">
@@ -8482,24 +8585,24 @@
       </c>
       <c r="E153" s="219" t="inlineStr">
         <is>
-          <t>[实测 30.65M] pr_auc per-seed 0:0.3534, 1:0.3933, 2:0.4017</t>
+          <t>[实测 5.82M] cohen_kappa per-seed 0:0.6012, 1:0.5989, 2:0.5951</t>
         </is>
       </c>
       <c r="F153" s="219" t="inlineStr">
         <is>
-          <t>lr=0.0001 batch_size=64 epochs=50 patience=10 eval_every_steps=0 loss=bce_with_logits multi_lr=True</t>
+          <t>stopped_by=patience lr=0.0005 batch_size=64 epochs=50 patience=10 eval_every_steps=100 loss=cross_entropy label_smoothing=0.1</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="219" t="inlineStr">
         <is>
-          <t>tusz</t>
+          <t>tuev</t>
         </is>
       </c>
       <c r="B154" s="219" t="inlineStr">
         <is>
-          <t>cbramod_scratch</t>
+          <t>labram_scratch</t>
         </is>
       </c>
       <c r="C154" s="219" t="inlineStr">
@@ -8514,152 +8617,132 @@
       </c>
       <c r="E154" s="219" t="inlineStr">
         <is>
-          <t>[实测 30.65M] pr_auc per-seed 0:0.4662, 1:0.5401, 2:0.4392</t>
+          <t>[实测 5.82M] cohen_kappa per-seed 0:0.3624, 1:0.3727, 2:0.3801</t>
         </is>
       </c>
       <c r="F154" s="219" t="inlineStr">
         <is>
-          <t>lr=0.0001 batch_size=64 epochs=50 patience=0 eval_every_steps=0 loss=bce_with_logits grad_clip=1.0 select_metric=auroc multi_lr=True</t>
+          <t>lr=0.0005 batch_size=64 epochs=50 patience=10 eval_every_steps=0 loss=cross_entropy label_smoothing=0.1</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="219" t="inlineStr">
         <is>
-          <t>tusz</t>
+          <t>tuev</t>
         </is>
       </c>
       <c r="B155" s="219" t="inlineStr">
         <is>
-          <t>cnn_transformer</t>
+          <t>paclock</t>
         </is>
       </c>
       <c r="C155" s="219" t="inlineStr">
         <is>
-          <t>[0, 1, 2]</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D155" s="219" t="inlineStr">
         <is>
-          <t>filled</t>
+          <t>skipped</t>
         </is>
       </c>
       <c r="E155" s="219" t="inlineStr">
         <is>
-          <t>[实测 3.15M] pr_auc per-seed 0:0.1493, 1:0.4554, 2:0.5073  [seed spread 43% -- mean is a weak summary]</t>
-        </is>
-      </c>
-      <c r="F155" s="219" t="inlineStr">
-        <is>
-          <t>lr=0.001 batch_size=512 epochs=20 patience=8 eval_every_steps=200 loss=bce_with_logits</t>
+          <t>no row label for 'paclock'</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="219" t="inlineStr">
         <is>
-          <t>tusz</t>
+          <t>tuev</t>
         </is>
       </c>
       <c r="B156" s="219" t="inlineStr">
         <is>
-          <t>contrawr</t>
+          <t>paclock_pac</t>
         </is>
       </c>
       <c r="C156" s="219" t="inlineStr">
         <is>
-          <t>[0, 1, 2]</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D156" s="219" t="inlineStr">
         <is>
-          <t>filled</t>
+          <t>skipped</t>
         </is>
       </c>
       <c r="E156" s="219" t="inlineStr">
         <is>
-          <t>[实测 1.57M] pr_auc per-seed 0:0.5188, 1:0.4849, 2:0.5092</t>
-        </is>
-      </c>
-      <c r="F156" s="219" t="inlineStr">
-        <is>
-          <t>lr=0.001 batch_size=512 epochs=20 patience=8 eval_every_steps=200 loss=bce_with_logits</t>
+          <t>the workbook has no row for this variant</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="219" t="inlineStr">
         <is>
-          <t>tusz</t>
+          <t>tuev</t>
         </is>
       </c>
       <c r="B157" s="219" t="inlineStr">
         <is>
-          <t>eegpt_pretrained</t>
+          <t>paclock_pilot_frozen</t>
         </is>
       </c>
       <c r="C157" s="219" t="inlineStr">
         <is>
-          <t>[0, 1, 2]</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D157" s="219" t="inlineStr">
         <is>
-          <t>filled</t>
+          <t>skipped</t>
         </is>
       </c>
       <c r="E157" s="219" t="inlineStr">
         <is>
-          <t>[实测 25.69M] pr_auc per-seed 0:0.6257, 1:0.5102, 2:0.4980</t>
-        </is>
-      </c>
-      <c r="F157" s="219" t="inlineStr">
-        <is>
-          <t>lr=0.0004 batch_size=32 epochs=40 patience=10 eval_every_steps=500 loss=bce_with_logits</t>
+          <t>the workbook has no row for this variant</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="219" t="inlineStr">
         <is>
-          <t>tusz</t>
+          <t>tuev</t>
         </is>
       </c>
       <c r="B158" s="219" t="inlineStr">
         <is>
-          <t>ffcl</t>
+          <t>paclock_pilot_unfiltered</t>
         </is>
       </c>
       <c r="C158" s="219" t="inlineStr">
         <is>
-          <t>[0, 1, 2]</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D158" s="219" t="inlineStr">
         <is>
-          <t>filled</t>
+          <t>skipped</t>
         </is>
       </c>
       <c r="E158" s="219" t="inlineStr">
         <is>
-          <t>[实测 2.46M] pr_auc per-seed 0:0.5511, 1:0.5126, 2:0.5709</t>
-        </is>
-      </c>
-      <c r="F158" s="219" t="inlineStr">
-        <is>
-          <t>lr=0.001 batch_size=512 epochs=20 patience=8 eval_every_steps=200 loss=bce_with_logits</t>
+          <t>the workbook has no row for this variant</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="219" t="inlineStr">
         <is>
-          <t>tusz</t>
+          <t>tuev</t>
         </is>
       </c>
       <c r="B159" s="219" t="inlineStr">
         <is>
-          <t>labram_pretrained</t>
+          <t>paclock_v2</t>
         </is>
       </c>
       <c r="C159" s="219" t="inlineStr">
@@ -8674,78 +8757,88 @@
       </c>
       <c r="E159" s="219" t="inlineStr">
         <is>
-          <t>[实测 5.82M] pr_auc per-seed 0:0.4828, 1:0.5186, 2:0.4249</t>
+          <t>[实测 1.62M] cohen_kappa per-seed 0:0.7278, 1:0.7233, 2:0.6718</t>
         </is>
       </c>
       <c r="F159" s="219" t="inlineStr">
         <is>
-          <t>lr=0.0005 batch_size=64 epochs=50 patience=10 eval_every_steps=100 loss=bce_with_logits</t>
+          <t>lr=0.0001 batch_size=32 epochs=20 patience=20 eval_every_steps=0 loss=cross_entropy label_smoothing=0.1 grad_clip=1.0 tokenizer_mode=pac_interaction pac_token_mode=measured interaction_mode=product band_pe=index spatial_pe=xyz</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="219" t="inlineStr">
         <is>
-          <t>tusz</t>
+          <t>tuev</t>
         </is>
       </c>
       <c r="B160" s="219" t="inlineStr">
         <is>
-          <t>paclock_full</t>
+          <t>sparcnet</t>
         </is>
       </c>
       <c r="C160" s="219" t="inlineStr">
         <is>
-          <t>[1, 2]</t>
+          <t>[0, 1, 2]</t>
         </is>
       </c>
       <c r="D160" s="219" t="inlineStr">
         <is>
-          <t>withheld (rule 4)</t>
+          <t>filled</t>
         </is>
       </c>
       <c r="E160" s="219" t="inlineStr">
         <is>
-          <t>only 2 seeds; primary pr_auc 0.6813</t>
+          <t>[实测 0.99M] cohen_kappa per-seed 0:0.4665, 1:0.5199, 2:0.4791</t>
+        </is>
+      </c>
+      <c r="F160" s="219" t="inlineStr">
+        <is>
+          <t>lr=0.001 batch_size=512 epochs=100 patience=15 eval_every_steps=0 loss=cross_entropy label_smoothing=0.1</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="219" t="inlineStr">
         <is>
-          <t>tusz</t>
+          <t>tuev</t>
         </is>
       </c>
       <c r="B161" s="219" t="inlineStr">
         <is>
-          <t>paclock_pac</t>
+          <t>st_transformer</t>
         </is>
       </c>
       <c r="C161" s="219" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>[0, 1, 2]</t>
         </is>
       </c>
       <c r="D161" s="219" t="inlineStr">
         <is>
-          <t>skipped</t>
+          <t>filled</t>
         </is>
       </c>
       <c r="E161" s="219" t="inlineStr">
         <is>
-          <t>the workbook has no row for this variant</t>
+          <t>[实测 3.43M] cohen_kappa per-seed 0:0.5139, 1:0.4916, 2:0.4962</t>
+        </is>
+      </c>
+      <c r="F161" s="219" t="inlineStr">
+        <is>
+          <t>lr=0.001 batch_size=512 epochs=100 patience=15 eval_every_steps=0 loss=cross_entropy label_smoothing=0.1</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="219" t="inlineStr">
         <is>
-          <t>tusz</t>
+          <t>tuev</t>
         </is>
       </c>
       <c r="B162" s="219" t="inlineStr">
         <is>
-          <t>sparcnet</t>
+          <t>tfm_pretrained</t>
         </is>
       </c>
       <c r="C162" s="219" t="inlineStr">
@@ -8760,12 +8853,12 @@
       </c>
       <c r="E162" s="219" t="inlineStr">
         <is>
-          <t>[实测 1.14M] pr_auc per-seed 0:0.4795, 1:0.5046, 2:0.5218</t>
+          <t>[实测 1.89M] cohen_kappa per-seed 0:0.6543, 1:0.6299, 2:0.6715</t>
         </is>
       </c>
       <c r="F162" s="219" t="inlineStr">
         <is>
-          <t>lr=0.001 batch_size=512 epochs=20 patience=8 eval_every_steps=200 loss=bce_with_logits</t>
+          <t>lr=0.001 batch_size=512 epochs=50 patience=10 eval_every_steps=100 loss=cross_entropy label_smoothing=0.1</t>
         </is>
       </c>
     </row>
@@ -8777,7 +8870,7 @@
       </c>
       <c r="B163" s="219" t="inlineStr">
         <is>
-          <t>st_transformer</t>
+          <t>biot_prest16</t>
         </is>
       </c>
       <c r="C163" s="219" t="inlineStr">
@@ -8792,12 +8885,12 @@
       </c>
       <c r="E163" s="219" t="inlineStr">
         <is>
-          <t>[实测 3.43M] pr_auc per-seed 0:0.3318, 1:0.3515, 2:0.3933</t>
+          <t>[实测 3.19M] pr_auc per-seed 0:0.3673, 1:0.3513, 2:0.2951</t>
         </is>
       </c>
       <c r="F163" s="219" t="inlineStr">
         <is>
-          <t>lr=0.001 batch_size=512 epochs=20 patience=8 eval_every_steps=200 loss=bce_with_logits</t>
+          <t>lr=0.001 batch_size=512 epochs=100 patience=5 eval_every_steps=0 loss=bce_with_logits</t>
         </is>
       </c>
     </row>
@@ -8809,25 +8902,458 @@
       </c>
       <c r="B164" s="219" t="inlineStr">
         <is>
+          <t>biot_scratch</t>
+        </is>
+      </c>
+      <c r="C164" s="219" t="inlineStr">
+        <is>
+          <t>[0, 1, 2]</t>
+        </is>
+      </c>
+      <c r="D164" s="219" t="inlineStr">
+        <is>
+          <t>filled</t>
+        </is>
+      </c>
+      <c r="E164" s="219" t="inlineStr">
+        <is>
+          <t>[实测 3.19M] pr_auc per-seed 0:0.3186, 1:0.3682, 2:0.3556</t>
+        </is>
+      </c>
+      <c r="F164" s="219" t="inlineStr">
+        <is>
+          <t>lr=0.001 batch_size=512 epochs=100 patience=5 eval_every_steps=0 loss=bce_with_logits</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="219" t="inlineStr">
+        <is>
+          <t>tusz</t>
+        </is>
+      </c>
+      <c r="B165" s="219" t="inlineStr">
+        <is>
+          <t>cbramod_pac</t>
+        </is>
+      </c>
+      <c r="C165" s="219" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D165" s="219" t="inlineStr">
+        <is>
+          <t>skipped</t>
+        </is>
+      </c>
+      <c r="E165" s="219" t="inlineStr">
+        <is>
+          <t>the workbook has no row for this variant</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="219" t="inlineStr">
+        <is>
+          <t>tusz</t>
+        </is>
+      </c>
+      <c r="B166" s="219" t="inlineStr">
+        <is>
+          <t>cbramod_pretrained</t>
+        </is>
+      </c>
+      <c r="C166" s="219" t="inlineStr">
+        <is>
+          <t>[0, 1, 2]</t>
+        </is>
+      </c>
+      <c r="D166" s="219" t="inlineStr">
+        <is>
+          <t>filled</t>
+        </is>
+      </c>
+      <c r="E166" s="219" t="inlineStr">
+        <is>
+          <t>[实测 30.65M] pr_auc per-seed 0:0.4139, 1:0.4061, 2:0.4831</t>
+        </is>
+      </c>
+      <c r="F166" s="219" t="inlineStr">
+        <is>
+          <t>lr=0.0001 batch_size=64 epochs=50 patience=0 eval_every_steps=0 loss=bce_with_logits grad_clip=1.0 select_metric=auroc multi_lr=True</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="219" t="inlineStr">
+        <is>
+          <t>tusz</t>
+        </is>
+      </c>
+      <c r="B167" s="219" t="inlineStr">
+        <is>
+          <t>cbramod_scratch</t>
+        </is>
+      </c>
+      <c r="C167" s="219" t="inlineStr">
+        <is>
+          <t>[0, 1, 2]</t>
+        </is>
+      </c>
+      <c r="D167" s="219" t="inlineStr">
+        <is>
+          <t>filled</t>
+        </is>
+      </c>
+      <c r="E167" s="219" t="inlineStr">
+        <is>
+          <t>[实测 30.65M] pr_auc per-seed 0:0.4662, 1:0.5401, 2:0.4392</t>
+        </is>
+      </c>
+      <c r="F167" s="219" t="inlineStr">
+        <is>
+          <t>lr=0.0001 batch_size=64 epochs=50 patience=0 eval_every_steps=0 loss=bce_with_logits grad_clip=1.0 select_metric=auroc multi_lr=True</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="219" t="inlineStr">
+        <is>
+          <t>tusz</t>
+        </is>
+      </c>
+      <c r="B168" s="219" t="inlineStr">
+        <is>
+          <t>cnn_transformer</t>
+        </is>
+      </c>
+      <c r="C168" s="219" t="inlineStr">
+        <is>
+          <t>[0, 1, 2]</t>
+        </is>
+      </c>
+      <c r="D168" s="219" t="inlineStr">
+        <is>
+          <t>filled</t>
+        </is>
+      </c>
+      <c r="E168" s="219" t="inlineStr">
+        <is>
+          <t>[实测 3.15M] pr_auc per-seed 0:0.1493, 1:0.4554, 2:0.5073  [seed spread 43% -- mean is a weak summary]</t>
+        </is>
+      </c>
+      <c r="F168" s="219" t="inlineStr">
+        <is>
+          <t>lr=0.001 batch_size=512 epochs=20 patience=8 eval_every_steps=200 loss=bce_with_logits</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="219" t="inlineStr">
+        <is>
+          <t>tusz</t>
+        </is>
+      </c>
+      <c r="B169" s="219" t="inlineStr">
+        <is>
+          <t>contrawr</t>
+        </is>
+      </c>
+      <c r="C169" s="219" t="inlineStr">
+        <is>
+          <t>[0, 1, 2]</t>
+        </is>
+      </c>
+      <c r="D169" s="219" t="inlineStr">
+        <is>
+          <t>filled</t>
+        </is>
+      </c>
+      <c r="E169" s="219" t="inlineStr">
+        <is>
+          <t>[实测 1.57M] pr_auc per-seed 0:0.5188, 1:0.4849, 2:0.5092</t>
+        </is>
+      </c>
+      <c r="F169" s="219" t="inlineStr">
+        <is>
+          <t>lr=0.001 batch_size=512 epochs=20 patience=8 eval_every_steps=200 loss=bce_with_logits</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="219" t="inlineStr">
+        <is>
+          <t>tusz</t>
+        </is>
+      </c>
+      <c r="B170" s="219" t="inlineStr">
+        <is>
+          <t>eegpt_pretrained</t>
+        </is>
+      </c>
+      <c r="C170" s="219" t="inlineStr">
+        <is>
+          <t>[0, 1, 2]</t>
+        </is>
+      </c>
+      <c r="D170" s="219" t="inlineStr">
+        <is>
+          <t>filled</t>
+        </is>
+      </c>
+      <c r="E170" s="219" t="inlineStr">
+        <is>
+          <t>[实测 25.69M] pr_auc per-seed 0:0.6257, 1:0.5102, 2:0.4980</t>
+        </is>
+      </c>
+      <c r="F170" s="219" t="inlineStr">
+        <is>
+          <t>lr=0.0004 batch_size=32 epochs=40 patience=10 eval_every_steps=500 loss=bce_with_logits</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="219" t="inlineStr">
+        <is>
+          <t>tusz</t>
+        </is>
+      </c>
+      <c r="B171" s="219" t="inlineStr">
+        <is>
+          <t>ffcl</t>
+        </is>
+      </c>
+      <c r="C171" s="219" t="inlineStr">
+        <is>
+          <t>[0, 1, 2]</t>
+        </is>
+      </c>
+      <c r="D171" s="219" t="inlineStr">
+        <is>
+          <t>filled</t>
+        </is>
+      </c>
+      <c r="E171" s="219" t="inlineStr">
+        <is>
+          <t>[实测 2.46M] pr_auc per-seed 0:0.5511, 1:0.5126, 2:0.5709</t>
+        </is>
+      </c>
+      <c r="F171" s="219" t="inlineStr">
+        <is>
+          <t>lr=0.001 batch_size=512 epochs=20 patience=8 eval_every_steps=200 loss=bce_with_logits</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="219" t="inlineStr">
+        <is>
+          <t>tusz</t>
+        </is>
+      </c>
+      <c r="B172" s="219" t="inlineStr">
+        <is>
+          <t>labram_pretrained</t>
+        </is>
+      </c>
+      <c r="C172" s="219" t="inlineStr">
+        <is>
+          <t>[0, 1, 2]</t>
+        </is>
+      </c>
+      <c r="D172" s="219" t="inlineStr">
+        <is>
+          <t>filled</t>
+        </is>
+      </c>
+      <c r="E172" s="219" t="inlineStr">
+        <is>
+          <t>[实测 5.82M] pr_auc per-seed 0:0.4828, 1:0.5186, 2:0.4249</t>
+        </is>
+      </c>
+      <c r="F172" s="219" t="inlineStr">
+        <is>
+          <t>lr=0.0005 batch_size=64 epochs=50 patience=10 eval_every_steps=100 loss=bce_with_logits</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="219" t="inlineStr">
+        <is>
+          <t>tusz</t>
+        </is>
+      </c>
+      <c r="B173" s="219" t="inlineStr">
+        <is>
+          <t>labram_scratch</t>
+        </is>
+      </c>
+      <c r="C173" s="219" t="inlineStr">
+        <is>
+          <t>[0, 1, 2]</t>
+        </is>
+      </c>
+      <c r="D173" s="219" t="inlineStr">
+        <is>
+          <t>filled</t>
+        </is>
+      </c>
+      <c r="E173" s="219" t="inlineStr">
+        <is>
+          <t>[实测 5.82M] pr_auc per-seed 0:0.4201, 1:0.5036, 2:0.5020</t>
+        </is>
+      </c>
+      <c r="F173" s="219" t="inlineStr">
+        <is>
+          <t>stopped_by=patience lr=0.0005 batch_size=64 epochs=50 patience=10 eval_every_steps=0 loss=bce_with_logits</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="219" t="inlineStr">
+        <is>
+          <t>tusz</t>
+        </is>
+      </c>
+      <c r="B174" s="219" t="inlineStr">
+        <is>
+          <t>paclock_pac</t>
+        </is>
+      </c>
+      <c r="C174" s="219" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D174" s="219" t="inlineStr">
+        <is>
+          <t>skipped</t>
+        </is>
+      </c>
+      <c r="E174" s="219" t="inlineStr">
+        <is>
+          <t>the workbook has no row for this variant</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="219" t="inlineStr">
+        <is>
+          <t>tusz</t>
+        </is>
+      </c>
+      <c r="B175" s="219" t="inlineStr">
+        <is>
+          <t>paclock_v2</t>
+        </is>
+      </c>
+      <c r="C175" s="219" t="inlineStr">
+        <is>
+          <t>[0]</t>
+        </is>
+      </c>
+      <c r="D175" s="219" t="inlineStr">
+        <is>
+          <t>withheld (rule 4)</t>
+        </is>
+      </c>
+      <c r="E175" s="219" t="inlineStr">
+        <is>
+          <t>only 1 seeds; primary pr_auc 0.6248</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="219" t="inlineStr">
+        <is>
+          <t>tusz</t>
+        </is>
+      </c>
+      <c r="B176" s="219" t="inlineStr">
+        <is>
+          <t>sparcnet</t>
+        </is>
+      </c>
+      <c r="C176" s="219" t="inlineStr">
+        <is>
+          <t>[0, 1, 2]</t>
+        </is>
+      </c>
+      <c r="D176" s="219" t="inlineStr">
+        <is>
+          <t>filled</t>
+        </is>
+      </c>
+      <c r="E176" s="219" t="inlineStr">
+        <is>
+          <t>[实测 1.14M] pr_auc per-seed 0:0.4795, 1:0.5046, 2:0.5218</t>
+        </is>
+      </c>
+      <c r="F176" s="219" t="inlineStr">
+        <is>
+          <t>lr=0.001 batch_size=512 epochs=20 patience=8 eval_every_steps=200 loss=bce_with_logits</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="219" t="inlineStr">
+        <is>
+          <t>tusz</t>
+        </is>
+      </c>
+      <c r="B177" s="219" t="inlineStr">
+        <is>
+          <t>st_transformer</t>
+        </is>
+      </c>
+      <c r="C177" s="219" t="inlineStr">
+        <is>
+          <t>[0, 1, 2]</t>
+        </is>
+      </c>
+      <c r="D177" s="219" t="inlineStr">
+        <is>
+          <t>filled</t>
+        </is>
+      </c>
+      <c r="E177" s="219" t="inlineStr">
+        <is>
+          <t>[实测 3.43M] pr_auc per-seed 0:0.3318, 1:0.3515, 2:0.3933</t>
+        </is>
+      </c>
+      <c r="F177" s="219" t="inlineStr">
+        <is>
+          <t>lr=0.001 batch_size=512 epochs=20 patience=8 eval_every_steps=200 loss=bce_with_logits</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="219" t="inlineStr">
+        <is>
+          <t>tusz</t>
+        </is>
+      </c>
+      <c r="B178" s="219" t="inlineStr">
+        <is>
           <t>tfm_pretrained</t>
         </is>
       </c>
-      <c r="C164" s="219" t="inlineStr">
+      <c r="C178" s="219" t="inlineStr">
         <is>
           <t>[0, 1, 2]</t>
         </is>
       </c>
-      <c r="D164" s="219" t="inlineStr">
+      <c r="D178" s="219" t="inlineStr">
         <is>
           <t>filled</t>
         </is>
       </c>
-      <c r="E164" s="219" t="inlineStr">
+      <c r="E178" s="219" t="inlineStr">
         <is>
           <t>[实测 1.89M] pr_auc per-seed 0:0.3348, 1:0.3686, 2:0.3389</t>
         </is>
       </c>
-      <c r="F164" s="219" t="inlineStr">
+      <c r="F178" s="219" t="inlineStr">
         <is>
           <t>lr=0.001 batch_size=512 epochs=5 patience=10 eval_every_steps=100 loss=bce_with_logits label_smoothing=0.1</t>
         </is>
@@ -9118,17 +9644,17 @@
       </c>
       <c r="D12" s="279" t="inlineStr">
         <is>
-          <t>0.8031±0.0055</t>
+          <t>0.7869±0.0104</t>
         </is>
       </c>
       <c r="E12" s="280" t="inlineStr">
         <is>
-          <t>0.8856±0.0067</t>
+          <t>0.8662±0.0049</t>
         </is>
       </c>
       <c r="F12" s="280" t="inlineStr">
         <is>
-          <t>0.8818±0.0087</t>
+          <t>0.8638±0.0075</t>
         </is>
       </c>
     </row>
@@ -9339,6 +9865,7 @@
     <col width="17" customWidth="1" style="220" min="4" max="4"/>
     <col width="17" customWidth="1" style="219" min="5" max="7"/>
     <col width="17" customWidth="1" style="220" min="6" max="6"/>
+    <col width="17" customWidth="1" style="220" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1" s="220">
@@ -9351,7 +9878,8 @@
       <c r="C1" s="228" t="n"/>
       <c r="D1" s="228" t="n"/>
       <c r="E1" s="228" t="n"/>
-      <c r="F1" s="229" t="n"/>
+      <c r="F1" s="228" t="n"/>
+      <c r="G1" s="229" t="n"/>
     </row>
     <row r="2" ht="22" customHeight="1" s="220">
       <c r="A2" s="267" t="inlineStr">
@@ -9359,7 +9887,7 @@
           <t>主指标：Cohen's Kappa</t>
         </is>
       </c>
-      <c r="F2" s="231" t="n"/>
+      <c r="G2" s="231" t="n"/>
     </row>
     <row r="3" ht="8" customHeight="1" s="220">
       <c r="A3" s="268" t="n"/>
@@ -9368,7 +9896,7 @@
       <c r="D3" s="268" t="n"/>
       <c r="E3" s="268" t="n"/>
       <c r="F3" s="268" t="n"/>
-      <c r="G3" s="269" t="n"/>
+      <c r="G3" s="268" t="n"/>
     </row>
     <row r="4" ht="28" customHeight="1" s="220">
       <c r="A4" s="270" t="inlineStr">
@@ -9401,6 +9929,11 @@
           <t>Weighted F1</t>
         </is>
       </c>
+      <c r="G4" s="270" t="inlineStr">
+        <is>
+          <t>ΔCohen's Kappa vs PACLock</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="20" customHeight="1" s="220">
       <c r="A5" s="271" t="inlineStr">
@@ -9429,6 +9962,11 @@
       <c r="F5" s="275" t="inlineStr">
         <is>
           <t>0.7354±0.0119</t>
+        </is>
+      </c>
+      <c r="G5" s="275" t="inlineStr">
+        <is>
+          <t>-0.2191</t>
         </is>
       </c>
     </row>
@@ -9457,6 +9995,11 @@
           <t>0.6962±0.0371</t>
         </is>
       </c>
+      <c r="G6" s="280" t="inlineStr">
+        <is>
+          <t>-0.3000</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="20" customHeight="1" s="220">
       <c r="A7" s="276" t="n"/>
@@ -9483,6 +10026,11 @@
           <t>0.6916±0.0607</t>
         </is>
       </c>
+      <c r="G7" s="280" t="inlineStr">
+        <is>
+          <t>-0.2978</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="20" customHeight="1" s="220">
       <c r="A8" s="276" t="n"/>
@@ -9509,6 +10057,11 @@
           <t>0.7366±0.0138</t>
         </is>
       </c>
+      <c r="G8" s="280" t="inlineStr">
+        <is>
+          <t>-0.2300</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="20" customHeight="1" s="220">
       <c r="A9" s="276" t="n"/>
@@ -9535,6 +10088,11 @@
           <t>0.7411±0.0071</t>
         </is>
       </c>
+      <c r="G9" s="280" t="inlineStr">
+        <is>
+          <t>-0.2070</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="20" customHeight="1" s="220">
       <c r="A10" s="271" t="inlineStr">
@@ -9563,6 +10121,11 @@
       <c r="F10" s="284" t="inlineStr">
         <is>
           <t>0.7532±0.0129</t>
+        </is>
+      </c>
+      <c r="G10" s="284" t="inlineStr">
+        <is>
+          <t>-0.1772</t>
         </is>
       </c>
     </row>
@@ -9578,17 +10141,22 @@
       </c>
       <c r="D11" s="279" t="inlineStr">
         <is>
-          <t>0.6436±0.0400</t>
+          <t>0.6305±0.0250</t>
         </is>
       </c>
       <c r="E11" s="280" t="inlineStr">
         <is>
-          <t>0.6169±0.0450</t>
+          <t>0.5984±0.0025</t>
         </is>
       </c>
       <c r="F11" s="280" t="inlineStr">
         <is>
-          <t>0.8152±0.0219</t>
+          <t>0.8086±0.0039</t>
+        </is>
+      </c>
+      <c r="G11" s="280" t="inlineStr">
+        <is>
+          <t>-0.1092</t>
         </is>
       </c>
     </row>
@@ -9604,17 +10172,22 @@
       </c>
       <c r="D12" s="279" t="inlineStr">
         <is>
-          <t>0.5153±0.0742</t>
+          <t>0.6029±0.0088</t>
         </is>
       </c>
       <c r="E12" s="280" t="inlineStr">
         <is>
-          <t>0.5970±0.0606</t>
+          <t>0.6449±0.0177</t>
         </is>
       </c>
       <c r="F12" s="280" t="inlineStr">
         <is>
-          <t>0.7892±0.0282</t>
+          <t>0.8130±0.0095</t>
+        </is>
+      </c>
+      <c r="G12" s="280" t="inlineStr">
+        <is>
+          <t>-0.0627</t>
         </is>
       </c>
     </row>
@@ -9643,6 +10216,11 @@
           <t>0.7766±0.0163</t>
         </is>
       </c>
+      <c r="G13" s="280" t="inlineStr">
+        <is>
+          <t>-0.1340</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="20" customHeight="1" s="220">
       <c r="A14" s="276" t="n"/>
@@ -9669,6 +10247,11 @@
           <t>0.8171±0.0085</t>
         </is>
       </c>
+      <c r="G14" s="280" t="inlineStr">
+        <is>
+          <t>-0.0557</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="20" customHeight="1" s="220">
       <c r="A15" s="271" t="inlineStr">
@@ -9697,6 +10280,11 @@
       <c r="F15" s="288" t="inlineStr">
         <is>
           <t>0.7612±0.0103</t>
+        </is>
+      </c>
+      <c r="G15" s="288" t="inlineStr">
+        <is>
+          <t>-0.1752</t>
         </is>
       </c>
     </row>
@@ -9708,11 +10296,28 @@
         </is>
       </c>
       <c r="C16" s="278" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="D16" s="279" t="n"/>
-      <c r="E16" s="280" t="n"/>
-      <c r="F16" s="280" t="n"/>
+        <v>5.82</v>
+      </c>
+      <c r="D16" s="279" t="inlineStr">
+        <is>
+          <t>0.3724±0.0697</t>
+        </is>
+      </c>
+      <c r="E16" s="280" t="inlineStr">
+        <is>
+          <t>0.3717±0.0073</t>
+        </is>
+      </c>
+      <c r="F16" s="280" t="inlineStr">
+        <is>
+          <t>0.6928±0.0108</t>
+        </is>
+      </c>
+      <c r="G16" s="280" t="inlineStr">
+        <is>
+          <t>-0.3359</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="20" customHeight="1" s="220">
       <c r="A17" s="276" t="n"/>
@@ -9739,6 +10344,11 @@
           <t>0.7671±0.0034</t>
         </is>
       </c>
+      <c r="G17" s="280" t="inlineStr">
+        <is>
+          <t>-0.1438</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="20" customHeight="1" s="220">
       <c r="A18" s="276" t="n"/>
@@ -9748,23 +10358,24 @@
         </is>
       </c>
       <c r="C18" s="290" t="n">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="D18" s="291" t="inlineStr">
         <is>
-          <t>0.5499±0.0418</t>
+          <t>0.5583±0.0308</t>
         </is>
       </c>
       <c r="E18" s="292" t="inlineStr">
         <is>
-          <t>0.6272±0.0081</t>
+          <t>0.7076±0.0254</t>
         </is>
       </c>
       <c r="F18" s="292" t="inlineStr">
         <is>
-          <t>0.8054±0.0053</t>
-        </is>
-      </c>
+          <t>0.8426±0.0116</t>
+        </is>
+      </c>
+      <c r="G18" s="292" t="n"/>
     </row>
     <row r="19" ht="15" customHeight="1" s="220"/>
     <row r="20" ht="24" customHeight="1" s="220"/>
@@ -9807,8 +10418,8 @@
     <row r="57" ht="42" customHeight="1" s="220"/>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A2:G2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" scale="100" fitToHeight="1" fitToWidth="1" firstPageNumber="1" useFirstPageNumber="0" pageOrder="downThenOver"/>
@@ -10103,17 +10714,17 @@
       </c>
       <c r="D12" s="279" t="inlineStr">
         <is>
-          <t>0.5645±0.0361</t>
+          <t>0.6347±0.0279</t>
         </is>
       </c>
       <c r="E12" s="280" t="inlineStr">
         <is>
-          <t>0.3828±0.0211</t>
+          <t>0.4344±0.0346</t>
         </is>
       </c>
       <c r="F12" s="280" t="inlineStr">
         <is>
-          <t>0.8140±0.0014</t>
+          <t>0.8520±0.0041</t>
         </is>
       </c>
     </row>
@@ -10207,11 +10818,23 @@
         </is>
       </c>
       <c r="C16" s="278" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="D16" s="279" t="n"/>
-      <c r="E16" s="280" t="n"/>
-      <c r="F16" s="280" t="n"/>
+        <v>5.82</v>
+      </c>
+      <c r="D16" s="279" t="inlineStr">
+        <is>
+          <t>0.5814±0.0290</t>
+        </is>
+      </c>
+      <c r="E16" s="280" t="inlineStr">
+        <is>
+          <t>0.4752±0.0390</t>
+        </is>
+      </c>
+      <c r="F16" s="280" t="inlineStr">
+        <is>
+          <t>0.8575±0.0156</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="20" customHeight="1" s="220">
       <c r="A17" s="276" t="n"/>
@@ -10583,11 +11206,23 @@
         </is>
       </c>
       <c r="C12" s="278" t="n">
-        <v>4</v>
-      </c>
-      <c r="D12" s="279" t="n"/>
-      <c r="E12" s="280" t="n"/>
-      <c r="F12" s="280" t="n"/>
+        <v>30.65</v>
+      </c>
+      <c r="D12" s="279" t="inlineStr">
+        <is>
+          <t>0.5446±0.0162</t>
+        </is>
+      </c>
+      <c r="E12" s="280" t="inlineStr">
+        <is>
+          <t>0.2332±0.0798</t>
+        </is>
+      </c>
+      <c r="F12" s="280" t="inlineStr">
+        <is>
+          <t>0.7828±0.0387</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="20" customHeight="1" s="220">
       <c r="A13" s="276" t="n"/>
@@ -10679,11 +11314,23 @@
         </is>
       </c>
       <c r="C16" s="278" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="D16" s="279" t="n"/>
-      <c r="E16" s="280" t="n"/>
-      <c r="F16" s="280" t="n"/>
+        <v>5.82</v>
+      </c>
+      <c r="D16" s="279" t="inlineStr">
+        <is>
+          <t>0.5854±0.0530</t>
+        </is>
+      </c>
+      <c r="E16" s="280" t="inlineStr">
+        <is>
+          <t>0.3596±0.0407</t>
+        </is>
+      </c>
+      <c r="F16" s="280" t="inlineStr">
+        <is>
+          <t>0.8226±0.0243</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="20" customHeight="1" s="220">
       <c r="A17" s="276" t="n"/>
@@ -10795,6 +11442,7 @@
     <col width="17" customWidth="1" style="220" min="4" max="4"/>
     <col width="17" customWidth="1" style="219" min="5" max="7"/>
     <col width="17" customWidth="1" style="220" min="6" max="6"/>
+    <col width="17" customWidth="1" style="220" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1" s="220">
@@ -10807,7 +11455,8 @@
       <c r="C1" s="228" t="n"/>
       <c r="D1" s="228" t="n"/>
       <c r="E1" s="228" t="n"/>
-      <c r="F1" s="229" t="n"/>
+      <c r="F1" s="228" t="n"/>
+      <c r="G1" s="229" t="n"/>
     </row>
     <row r="2" ht="22" customHeight="1" s="220">
       <c r="A2" s="267" t="inlineStr">
@@ -10815,7 +11464,7 @@
           <t>主指标：Cohen's Kappa</t>
         </is>
       </c>
-      <c r="F2" s="231" t="n"/>
+      <c r="G2" s="231" t="n"/>
     </row>
     <row r="3" ht="8" customHeight="1" s="220">
       <c r="A3" s="268" t="n"/>
@@ -10824,7 +11473,7 @@
       <c r="D3" s="268" t="n"/>
       <c r="E3" s="268" t="n"/>
       <c r="F3" s="268" t="n"/>
-      <c r="G3" s="269" t="n"/>
+      <c r="G3" s="268" t="n"/>
     </row>
     <row r="4" ht="28" customHeight="1" s="220">
       <c r="A4" s="270" t="inlineStr">
@@ -10857,6 +11506,11 @@
           <t>Weighted F1</t>
         </is>
       </c>
+      <c r="G4" s="270" t="inlineStr">
+        <is>
+          <t>ΔCohen's Kappa vs PACLock</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="20" customHeight="1" s="220">
       <c r="A5" s="271" t="inlineStr">
@@ -10885,6 +11539,11 @@
       <c r="F5" s="275" t="inlineStr">
         <is>
           <t>0.7718±0.0058</t>
+        </is>
+      </c>
+      <c r="G5" s="275" t="inlineStr">
+        <is>
+          <t>+0.0255</t>
         </is>
       </c>
     </row>
@@ -10913,6 +11572,11 @@
           <t>0.7866±0.0098</t>
         </is>
       </c>
+      <c r="G6" s="280" t="inlineStr">
+        <is>
+          <t>+0.0457</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="20" customHeight="1" s="220">
       <c r="A7" s="276" t="n"/>
@@ -10939,6 +11603,11 @@
           <t>0.7771±0.0075</t>
         </is>
       </c>
+      <c r="G7" s="280" t="inlineStr">
+        <is>
+          <t>+0.0319</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="20" customHeight="1" s="220">
       <c r="A8" s="276" t="n"/>
@@ -10965,6 +11634,11 @@
           <t>0.7716±0.0066</t>
         </is>
       </c>
+      <c r="G8" s="280" t="inlineStr">
+        <is>
+          <t>+0.0321</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="20" customHeight="1" s="220">
       <c r="A9" s="276" t="n"/>
@@ -10991,6 +11665,11 @@
           <t>0.7607±0.0033</t>
         </is>
       </c>
+      <c r="G9" s="280" t="inlineStr">
+        <is>
+          <t>+0.0094</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="20" customHeight="1" s="220">
       <c r="A10" s="271" t="inlineStr">
@@ -11019,6 +11698,11 @@
       <c r="F10" s="284" t="inlineStr">
         <is>
           <t>0.7172±0.0128</t>
+        </is>
+      </c>
+      <c r="G10" s="284" t="inlineStr">
+        <is>
+          <t>-0.0519</t>
         </is>
       </c>
     </row>
@@ -11034,17 +11718,22 @@
       </c>
       <c r="D11" s="279" t="inlineStr">
         <is>
-          <t>0.6364±0.0122</t>
+          <t>0.6399±0.0144</t>
         </is>
       </c>
       <c r="E11" s="280" t="inlineStr">
         <is>
-          <t>0.6109±0.0082</t>
+          <t>0.6100±0.0065</t>
         </is>
       </c>
       <c r="F11" s="280" t="inlineStr">
         <is>
-          <t>0.7337±0.0071</t>
+          <t>0.7321±0.0069</t>
+        </is>
+      </c>
+      <c r="G11" s="280" t="inlineStr">
+        <is>
+          <t>-0.0359</t>
         </is>
       </c>
     </row>
@@ -11060,17 +11749,22 @@
       </c>
       <c r="D12" s="279" t="inlineStr">
         <is>
-          <t>0.6801±0.0104</t>
+          <t>0.6848±0.0135</t>
         </is>
       </c>
       <c r="E12" s="280" t="inlineStr">
         <is>
-          <t>0.6721±0.0036</t>
+          <t>0.6715±0.0040</t>
         </is>
       </c>
       <c r="F12" s="280" t="inlineStr">
         <is>
-          <t>0.7745±0.0037</t>
+          <t>0.7665±0.0031</t>
+        </is>
+      </c>
+      <c r="G12" s="280" t="inlineStr">
+        <is>
+          <t>+0.0256</t>
         </is>
       </c>
     </row>
@@ -11099,6 +11793,11 @@
           <t>0.7253±0.0063</t>
         </is>
       </c>
+      <c r="G13" s="280" t="inlineStr">
+        <is>
+          <t>-0.0481</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="20" customHeight="1" s="220">
       <c r="A14" s="276" t="n"/>
@@ -11125,6 +11824,11 @@
           <t>0.7266±0.0014</t>
         </is>
       </c>
+      <c r="G14" s="280" t="inlineStr">
+        <is>
+          <t>-0.0321</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="20" customHeight="1" s="220">
       <c r="A15" s="271" t="inlineStr">
@@ -11153,6 +11857,11 @@
       <c r="F15" s="288" t="inlineStr">
         <is>
           <t>0.7655±0.0068</t>
+        </is>
+      </c>
+      <c r="G15" s="288" t="inlineStr">
+        <is>
+          <t>+0.0088</t>
         </is>
       </c>
     </row>
@@ -11164,11 +11873,28 @@
         </is>
       </c>
       <c r="C16" s="278" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="D16" s="279" t="n"/>
-      <c r="E16" s="280" t="n"/>
-      <c r="F16" s="280" t="n"/>
+        <v>5.82</v>
+      </c>
+      <c r="D16" s="279" t="inlineStr">
+        <is>
+          <t>0.6138±0.0065</t>
+        </is>
+      </c>
+      <c r="E16" s="280" t="inlineStr">
+        <is>
+          <t>0.5980±0.0081</t>
+        </is>
+      </c>
+      <c r="F16" s="280" t="inlineStr">
+        <is>
+          <t>0.7150±0.0076</t>
+        </is>
+      </c>
+      <c r="G16" s="280" t="inlineStr">
+        <is>
+          <t>-0.0479</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="20" customHeight="1" s="220">
       <c r="A17" s="276" t="n"/>
@@ -11195,6 +11921,11 @@
           <t>0.7614±0.0033</t>
         </is>
       </c>
+      <c r="G17" s="280" t="inlineStr">
+        <is>
+          <t>+0.0086</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="20" customHeight="1" s="220">
       <c r="A18" s="276" t="n"/>
@@ -11204,23 +11935,24 @@
         </is>
       </c>
       <c r="C18" s="290" t="n">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="D18" s="291" t="inlineStr">
         <is>
-          <t>0.6064±0.0111</t>
+          <t>0.6284±0.0046</t>
         </is>
       </c>
       <c r="E18" s="292" t="inlineStr">
         <is>
-          <t>0.6199±0.0125</t>
+          <t>0.6459±0.0054</t>
         </is>
       </c>
       <c r="F18" s="292" t="inlineStr">
         <is>
-          <t>0.7383±0.0057</t>
-        </is>
-      </c>
+          <t>0.7563±0.0043</t>
+        </is>
+      </c>
+      <c r="G18" s="292" t="n"/>
     </row>
     <row r="19" ht="15" customHeight="1" s="220"/>
     <row r="20" ht="24" customHeight="1" s="220"/>
@@ -11264,8 +11996,8 @@
     <row r="58" ht="38" customHeight="1" s="220"/>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A2:G2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" scale="100" fitToHeight="1" fitToWidth="1" firstPageNumber="1" useFirstPageNumber="0" pageOrder="downThenOver"/>
@@ -11534,17 +12266,17 @@
       </c>
       <c r="D11" s="279" t="inlineStr">
         <is>
-          <t>0.7733±0.0056</t>
+          <t>0.7683±0.0119</t>
         </is>
       </c>
       <c r="E11" s="280" t="inlineStr">
         <is>
-          <t>0.7434±0.0059</t>
+          <t>0.7366±0.0145</t>
         </is>
       </c>
       <c r="F11" s="280" t="inlineStr">
         <is>
-          <t>0.7987±0.0052</t>
+          <t>0.7927±0.0111</t>
         </is>
       </c>
     </row>
@@ -11560,17 +12292,17 @@
       </c>
       <c r="D12" s="279" t="inlineStr">
         <is>
-          <t>0.7830±0.0114</t>
+          <t>0.7842±0.0059</t>
         </is>
       </c>
       <c r="E12" s="280" t="inlineStr">
         <is>
-          <t>0.7473±0.0158</t>
+          <t>0.7540±0.0063</t>
         </is>
       </c>
       <c r="F12" s="280" t="inlineStr">
         <is>
-          <t>0.8057±0.0109</t>
+          <t>0.8105±0.0046</t>
         </is>
       </c>
     </row>
@@ -11664,11 +12396,23 @@
         </is>
       </c>
       <c r="C16" s="278" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="D16" s="279" t="n"/>
-      <c r="E16" s="280" t="n"/>
-      <c r="F16" s="280" t="n"/>
+        <v>5.82</v>
+      </c>
+      <c r="D16" s="279" t="inlineStr">
+        <is>
+          <t>0.6660±0.0144</t>
+        </is>
+      </c>
+      <c r="E16" s="280" t="inlineStr">
+        <is>
+          <t>0.6236±0.0107</t>
+        </is>
+      </c>
+      <c r="F16" s="280" t="inlineStr">
+        <is>
+          <t>0.6979±0.0115</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="20" customHeight="1" s="220">
       <c r="A17" s="276" t="n"/>
@@ -11678,11 +12422,23 @@
         </is>
       </c>
       <c r="C17" s="278" t="n">
-        <v>4</v>
-      </c>
-      <c r="D17" s="279" t="n"/>
-      <c r="E17" s="280" t="n"/>
-      <c r="F17" s="280" t="n"/>
+        <v>26.47</v>
+      </c>
+      <c r="D17" s="279" t="inlineStr">
+        <is>
+          <t>0.7428±0.0021</t>
+        </is>
+      </c>
+      <c r="E17" s="280" t="inlineStr">
+        <is>
+          <t>0.6976±0.0052</t>
+        </is>
+      </c>
+      <c r="F17" s="280" t="inlineStr">
+        <is>
+          <t>0.7614±0.0067</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="20" customHeight="1" s="220">
       <c r="A18" s="276" t="n"/>
@@ -11692,23 +12448,11 @@
         </is>
       </c>
       <c r="C18" s="290" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="D18" s="291" t="inlineStr">
-        <is>
-          <t>0.7500±0.0073</t>
-        </is>
-      </c>
-      <c r="E18" s="292" t="inlineStr">
-        <is>
-          <t>0.6865±0.0042</t>
-        </is>
-      </c>
-      <c r="F18" s="292" t="inlineStr">
-        <is>
-          <t>0.7526±0.0047</t>
-        </is>
-      </c>
+        <v>1.64</v>
+      </c>
+      <c r="D18" s="291" t="n"/>
+      <c r="E18" s="292" t="n"/>
+      <c r="F18" s="292" t="n"/>
     </row>
     <row r="19" ht="15" customHeight="1" s="220"/>
     <row r="20" ht="24" customHeight="1" s="220"/>
@@ -12001,11 +12745,23 @@
         </is>
       </c>
       <c r="C11" s="278" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="D11" s="279" t="n"/>
-      <c r="E11" s="279" t="n"/>
-      <c r="F11" s="279" t="n"/>
+        <v>5.82</v>
+      </c>
+      <c r="D11" s="279" t="inlineStr">
+        <is>
+          <t>0.5573±0.0159</t>
+        </is>
+      </c>
+      <c r="E11" s="279" t="inlineStr">
+        <is>
+          <t>0.4096±0.0211</t>
+        </is>
+      </c>
+      <c r="F11" s="279" t="inlineStr">
+        <is>
+          <t>0.5594±0.0157</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="20" customHeight="1" s="220">
       <c r="A12" s="276" t="n"/>
@@ -12019,17 +12775,17 @@
       </c>
       <c r="D12" s="279" t="inlineStr">
         <is>
-          <t>0.6057±0.0134</t>
+          <t>0.6129±0.0094</t>
         </is>
       </c>
       <c r="E12" s="279" t="inlineStr">
         <is>
-          <t>0.4742±0.0178</t>
+          <t>0.4838±0.0125</t>
         </is>
       </c>
       <c r="F12" s="279" t="inlineStr">
         <is>
-          <t>0.6056±0.0134</t>
+          <t>0.6122±0.0094</t>
         </is>
       </c>
     </row>
@@ -12123,11 +12879,23 @@
         </is>
       </c>
       <c r="C16" s="278" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="D16" s="279" t="n"/>
-      <c r="E16" s="279" t="n"/>
-      <c r="F16" s="279" t="n"/>
+        <v>5.82</v>
+      </c>
+      <c r="D16" s="279" t="inlineStr">
+        <is>
+          <t>0.3667±0.0142</t>
+        </is>
+      </c>
+      <c r="E16" s="279" t="inlineStr">
+        <is>
+          <t>0.1555±0.0190</t>
+        </is>
+      </c>
+      <c r="F16" s="279" t="inlineStr">
+        <is>
+          <t>0.3644±0.0163</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="20" customHeight="1" s="220">
       <c r="A17" s="276" t="n"/>
@@ -12137,11 +12905,23 @@
         </is>
       </c>
       <c r="C17" s="278" t="n">
-        <v>4</v>
-      </c>
-      <c r="D17" s="279" t="n"/>
-      <c r="E17" s="279" t="n"/>
-      <c r="F17" s="279" t="n"/>
+        <v>46.01</v>
+      </c>
+      <c r="D17" s="279" t="inlineStr">
+        <is>
+          <t>0.5537±0.0033</t>
+        </is>
+      </c>
+      <c r="E17" s="279" t="inlineStr">
+        <is>
+          <t>0.4049±0.0044</t>
+        </is>
+      </c>
+      <c r="F17" s="279" t="inlineStr">
+        <is>
+          <t>0.5546±0.0044</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="20" customHeight="1" s="220">
       <c r="A18" s="276" t="n"/>
@@ -12449,17 +13229,17 @@
       </c>
       <c r="D11" s="299" t="inlineStr">
         <is>
-          <t>0.3176±0.0094</t>
+          <t>0.3272±0.0015</t>
         </is>
       </c>
       <c r="E11" s="299" t="inlineStr">
         <is>
-          <t>0.2309±0.0103</t>
+          <t>0.2409±0.0009</t>
         </is>
       </c>
       <c r="F11" s="299" t="inlineStr">
         <is>
-          <t>0.3165±0.0089</t>
+          <t>0.3240±0.0003</t>
         </is>
       </c>
     </row>
@@ -12475,17 +13255,17 @@
       </c>
       <c r="D12" s="299" t="inlineStr">
         <is>
-          <t>0.5350±0.0037</t>
+          <t>0.5509±0.0034</t>
         </is>
       </c>
       <c r="E12" s="299" t="inlineStr">
         <is>
-          <t>0.4740±0.0047</t>
+          <t>0.4923±0.0034</t>
         </is>
       </c>
       <c r="F12" s="299" t="inlineStr">
         <is>
-          <t>0.5365±0.0044</t>
+          <t>0.5557±0.0027</t>
         </is>
       </c>
     </row>
@@ -12579,11 +13359,23 @@
         </is>
       </c>
       <c r="C16" s="299" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="D16" s="299" t="n"/>
-      <c r="E16" s="299" t="n"/>
-      <c r="F16" s="299" t="n"/>
+        <v>5.82</v>
+      </c>
+      <c r="D16" s="299" t="inlineStr">
+        <is>
+          <t>0.1583±0.0094</t>
+        </is>
+      </c>
+      <c r="E16" s="299" t="inlineStr">
+        <is>
+          <t>0.0536±0.0112</t>
+        </is>
+      </c>
+      <c r="F16" s="299" t="inlineStr">
+        <is>
+          <t>0.1548±0.0103</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="20" customHeight="1" s="220">
       <c r="A17" s="297" t="n"/>
@@ -12607,23 +13399,11 @@
         </is>
       </c>
       <c r="C18" s="299" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="D18" s="299" t="inlineStr">
-        <is>
-          <t>0.1476±0.0026</t>
-        </is>
-      </c>
-      <c r="E18" s="299" t="inlineStr">
-        <is>
-          <t>0.0406±0.0032</t>
-        </is>
-      </c>
-      <c r="F18" s="299" t="inlineStr">
-        <is>
-          <t>0.1379±0.0072</t>
-        </is>
-      </c>
+        <v>1.64</v>
+      </c>
+      <c r="D18" s="299" t="n"/>
+      <c r="E18" s="299" t="n"/>
+      <c r="F18" s="299" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">

--- a/results/PACLock_baseline_matrix_filled.xlsx
+++ b/results/PACLock_baseline_matrix_filled.xlsx
@@ -1953,7 +1953,6 @@
     <xf numFmtId="1" fontId="10" fillId="0" borderId="69" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="69" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="49" fontId="36" fillId="15" borderId="68" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2023,6 +2022,7 @@
     <xf numFmtId="164" fontId="38" fillId="10" borderId="68" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="69" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="39" fillId="15" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -3465,467 +3465,467 @@
       <c r="G3" s="268" t="n"/>
     </row>
     <row r="4" ht="28" customHeight="1" s="220">
-      <c r="A4" s="270" t="inlineStr">
+      <c r="A4" s="269" t="inlineStr">
         <is>
           <t>分组</t>
         </is>
       </c>
-      <c r="B4" s="270" t="inlineStr">
+      <c r="B4" s="269" t="inlineStr">
         <is>
           <t>模型</t>
         </is>
       </c>
-      <c r="C4" s="270" t="inlineStr">
+      <c r="C4" s="269" t="inlineStr">
         <is>
           <t>参数量 (M)</t>
         </is>
       </c>
-      <c r="D4" s="270" t="inlineStr">
+      <c r="D4" s="269" t="inlineStr">
         <is>
           <t>Balanced Acc</t>
         </is>
       </c>
-      <c r="E4" s="270" t="inlineStr">
+      <c r="E4" s="269" t="inlineStr">
         <is>
           <t>Cohen's Kappa</t>
         </is>
       </c>
-      <c r="F4" s="270" t="inlineStr">
+      <c r="F4" s="269" t="inlineStr">
         <is>
           <t>Weighted F1</t>
         </is>
       </c>
-      <c r="G4" s="270" t="inlineStr">
+      <c r="G4" s="269" t="inlineStr">
         <is>
           <t>ΔBalanced Acc vs PACLock</t>
         </is>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1" s="220">
-      <c r="A5" s="271" t="inlineStr">
+      <c r="A5" s="270" t="inlineStr">
         <is>
           <t>A 轻量监督基线</t>
         </is>
       </c>
-      <c r="B5" s="272" t="inlineStr">
+      <c r="B5" s="271" t="inlineStr">
         <is>
           <t>SPaRCNet</t>
         </is>
       </c>
-      <c r="C5" s="273" t="n">
+      <c r="C5" s="272" t="n">
         <v>0.99</v>
       </c>
-      <c r="D5" s="274" t="inlineStr">
+      <c r="D5" s="273" t="inlineStr">
         <is>
           <t>0.6440±0.0070</t>
         </is>
       </c>
-      <c r="E5" s="274" t="inlineStr">
+      <c r="E5" s="273" t="inlineStr">
         <is>
           <t>0.5254±0.0094</t>
         </is>
       </c>
-      <c r="F5" s="274" t="inlineStr">
+      <c r="F5" s="273" t="inlineStr">
         <is>
           <t>0.6428±0.0068</t>
         </is>
       </c>
-      <c r="G5" s="274" t="inlineStr">
+      <c r="G5" s="273" t="inlineStr">
         <is>
           <t>+0.2852</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1" s="220">
-      <c r="A6" s="276" t="n"/>
-      <c r="B6" s="277" t="inlineStr">
+      <c r="A6" s="275" t="n"/>
+      <c r="B6" s="276" t="inlineStr">
         <is>
           <t>ContraWR</t>
         </is>
       </c>
-      <c r="C6" s="278" t="n">
+      <c r="C6" s="277" t="n">
         <v>1.58</v>
       </c>
-      <c r="D6" s="279" t="inlineStr">
+      <c r="D6" s="278" t="inlineStr">
         <is>
           <t>0.4922±0.0111</t>
         </is>
       </c>
-      <c r="E6" s="279" t="inlineStr">
+      <c r="E6" s="278" t="inlineStr">
         <is>
           <t>0.3229±0.0148</t>
         </is>
       </c>
-      <c r="F6" s="279" t="inlineStr">
+      <c r="F6" s="278" t="inlineStr">
         <is>
           <t>0.4861±0.0153</t>
         </is>
       </c>
-      <c r="G6" s="279" t="inlineStr">
+      <c r="G6" s="278" t="inlineStr">
         <is>
           <t>+0.1334</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1" s="220">
-      <c r="A7" s="276" t="n"/>
-      <c r="B7" s="277" t="inlineStr">
+      <c r="A7" s="275" t="n"/>
+      <c r="B7" s="276" t="inlineStr">
         <is>
           <t>CNN-Transformer</t>
         </is>
       </c>
-      <c r="C7" s="278" t="n">
+      <c r="C7" s="277" t="n">
         <v>3.2</v>
       </c>
-      <c r="D7" s="279" t="n"/>
-      <c r="E7" s="279" t="n"/>
-      <c r="F7" s="279" t="n"/>
-      <c r="G7" s="279" t="n"/>
+      <c r="D7" s="278" t="n"/>
+      <c r="E7" s="278" t="n"/>
+      <c r="F7" s="278" t="n"/>
+      <c r="G7" s="278" t="n"/>
     </row>
     <row r="8" ht="20" customHeight="1" s="220">
-      <c r="A8" s="276" t="n"/>
-      <c r="B8" s="277" t="inlineStr">
+      <c r="A8" s="275" t="n"/>
+      <c r="B8" s="276" t="inlineStr">
         <is>
           <t>FFCL</t>
         </is>
       </c>
-      <c r="C8" s="278" t="n">
+      <c r="C8" s="277" t="n">
         <v>2.41</v>
       </c>
-      <c r="D8" s="279" t="inlineStr">
+      <c r="D8" s="278" t="inlineStr">
         <is>
           <t>0.4891±0.0097</t>
         </is>
       </c>
-      <c r="E8" s="279" t="inlineStr">
+      <c r="E8" s="278" t="inlineStr">
         <is>
           <t>0.3188±0.0130</t>
         </is>
       </c>
-      <c r="F8" s="279" t="inlineStr">
+      <c r="F8" s="278" t="inlineStr">
         <is>
           <t>0.4858±0.0093</t>
         </is>
       </c>
-      <c r="G8" s="279" t="inlineStr">
+      <c r="G8" s="278" t="inlineStr">
         <is>
           <t>+0.1303</t>
         </is>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1" s="220">
-      <c r="A9" s="276" t="n"/>
-      <c r="B9" s="277" t="inlineStr">
+      <c r="A9" s="275" t="n"/>
+      <c r="B9" s="276" t="inlineStr">
         <is>
           <t>ST-Transformer</t>
         </is>
       </c>
-      <c r="C9" s="278" t="n">
+      <c r="C9" s="277" t="n">
         <v>3.43</v>
       </c>
-      <c r="D9" s="279" t="inlineStr">
+      <c r="D9" s="278" t="inlineStr">
         <is>
           <t>0.5471±0.0223</t>
         </is>
       </c>
-      <c r="E9" s="279" t="inlineStr">
+      <c r="E9" s="278" t="inlineStr">
         <is>
           <t>0.3961±0.0297</t>
         </is>
       </c>
-      <c r="F9" s="279" t="inlineStr">
+      <c r="F9" s="278" t="inlineStr">
         <is>
           <t>0.5461±0.0228</t>
         </is>
       </c>
-      <c r="G9" s="279" t="inlineStr">
+      <c r="G9" s="278" t="inlineStr">
         <is>
           <t>+0.1883</t>
         </is>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1" s="220">
-      <c r="A10" s="271" t="inlineStr">
+      <c r="A10" s="270" t="inlineStr">
         <is>
           <t>B FM · 官方预训练权重</t>
         </is>
       </c>
-      <c r="B10" s="281" t="inlineStr">
+      <c r="B10" s="280" t="inlineStr">
         <is>
           <t>BIOT (pretrained)</t>
         </is>
       </c>
-      <c r="C10" s="282" t="n">
+      <c r="C10" s="281" t="n">
         <v>3.19</v>
       </c>
-      <c r="D10" s="283" t="inlineStr">
+      <c r="D10" s="282" t="inlineStr">
         <is>
           <t>0.4662±0.0066</t>
         </is>
       </c>
-      <c r="E10" s="283" t="inlineStr">
+      <c r="E10" s="282" t="inlineStr">
         <is>
           <t>0.2882±0.0088</t>
         </is>
       </c>
-      <c r="F10" s="283" t="inlineStr">
+      <c r="F10" s="282" t="inlineStr">
         <is>
           <t>0.4557±0.0139</t>
         </is>
       </c>
-      <c r="G10" s="283" t="inlineStr">
+      <c r="G10" s="282" t="inlineStr">
         <is>
           <t>+0.1074</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1" s="220">
-      <c r="A11" s="276" t="n"/>
-      <c r="B11" s="277" t="inlineStr">
+      <c r="A11" s="275" t="n"/>
+      <c r="B11" s="276" t="inlineStr">
         <is>
           <t>LaBraM-Base (pretrained)</t>
         </is>
       </c>
-      <c r="C11" s="278" t="n">
+      <c r="C11" s="277" t="n">
         <v>5.82</v>
       </c>
-      <c r="D11" s="279" t="inlineStr">
+      <c r="D11" s="278" t="inlineStr">
         <is>
           <t>0.4227±0.0246</t>
         </is>
       </c>
-      <c r="E11" s="279" t="inlineStr">
+      <c r="E11" s="278" t="inlineStr">
         <is>
           <t>0.2303±0.0329</t>
         </is>
       </c>
-      <c r="F11" s="279" t="inlineStr">
+      <c r="F11" s="278" t="inlineStr">
         <is>
           <t>0.4224±0.0240</t>
         </is>
       </c>
-      <c r="G11" s="279" t="inlineStr">
+      <c r="G11" s="278" t="inlineStr">
         <is>
           <t>+0.0639</t>
         </is>
       </c>
     </row>
     <row r="12" ht="20" customHeight="1" s="220">
-      <c r="A12" s="276" t="n"/>
-      <c r="B12" s="277" t="inlineStr">
+      <c r="A12" s="275" t="n"/>
+      <c r="B12" s="276" t="inlineStr">
         <is>
           <t>CBraMod (pretrained)</t>
         </is>
       </c>
-      <c r="C12" s="278" t="n">
+      <c r="C12" s="277" t="n">
         <v>19.13</v>
       </c>
-      <c r="D12" s="279" t="inlineStr">
+      <c r="D12" s="278" t="inlineStr">
         <is>
           <t>0.5293±0.0036</t>
         </is>
       </c>
-      <c r="E12" s="279" t="inlineStr">
+      <c r="E12" s="278" t="inlineStr">
         <is>
           <t>0.3724±0.0048</t>
         </is>
       </c>
-      <c r="F12" s="279" t="inlineStr">
+      <c r="F12" s="278" t="inlineStr">
         <is>
           <t>0.5300±0.0036</t>
         </is>
       </c>
-      <c r="G12" s="279" t="inlineStr">
+      <c r="G12" s="278" t="inlineStr">
         <is>
           <t>+0.1705</t>
         </is>
       </c>
     </row>
     <row r="13" ht="20" customHeight="1" s="220">
-      <c r="A13" s="276" t="n"/>
-      <c r="B13" s="277" t="inlineStr">
+      <c r="A13" s="275" t="n"/>
+      <c r="B13" s="276" t="inlineStr">
         <is>
           <t>EEGPT</t>
         </is>
       </c>
-      <c r="C13" s="278" t="n">
+      <c r="C13" s="277" t="n">
         <v>25.69</v>
       </c>
-      <c r="D13" s="279" t="inlineStr">
+      <c r="D13" s="278" t="inlineStr">
         <is>
           <t>0.3773±0.0197</t>
         </is>
       </c>
-      <c r="E13" s="279" t="inlineStr">
+      <c r="E13" s="278" t="inlineStr">
         <is>
           <t>0.1698±0.0263</t>
         </is>
       </c>
-      <c r="F13" s="279" t="inlineStr">
+      <c r="F13" s="278" t="inlineStr">
         <is>
           <t>0.3639±0.0144</t>
         </is>
       </c>
-      <c r="G13" s="279" t="inlineStr">
+      <c r="G13" s="278" t="inlineStr">
         <is>
           <t>+0.0185</t>
         </is>
       </c>
     </row>
     <row r="14" ht="20" customHeight="1" s="220">
-      <c r="A14" s="276" t="n"/>
-      <c r="B14" s="277" t="inlineStr">
+      <c r="A14" s="275" t="n"/>
+      <c r="B14" s="276" t="inlineStr">
         <is>
           <t>TFM-Tokenizer</t>
         </is>
       </c>
-      <c r="C14" s="278" t="n">
+      <c r="C14" s="277" t="n">
         <v>1.89</v>
       </c>
-      <c r="D14" s="279" t="inlineStr">
+      <c r="D14" s="278" t="inlineStr">
         <is>
           <t>0.3405±0.0214</t>
         </is>
       </c>
-      <c r="E14" s="279" t="inlineStr">
+      <c r="E14" s="278" t="inlineStr">
         <is>
           <t>0.1207±0.0285</t>
         </is>
       </c>
-      <c r="F14" s="279" t="inlineStr">
+      <c r="F14" s="278" t="inlineStr">
         <is>
           <t>0.3364±0.0185</t>
         </is>
       </c>
-      <c r="G14" s="279" t="inlineStr">
+      <c r="G14" s="278" t="inlineStr">
         <is>
           <t>-0.0183</t>
         </is>
       </c>
     </row>
     <row r="15" ht="20" customHeight="1" s="220">
-      <c r="A15" s="271" t="inlineStr">
+      <c r="A15" s="270" t="inlineStr">
         <is>
           <t>C FM · 同 pipeline scratch</t>
         </is>
       </c>
-      <c r="B15" s="285" t="inlineStr">
+      <c r="B15" s="284" t="inlineStr">
         <is>
           <t>BIOT (scratch)</t>
         </is>
       </c>
-      <c r="C15" s="286" t="n">
+      <c r="C15" s="285" t="n">
         <v>3.19</v>
       </c>
-      <c r="D15" s="287" t="inlineStr">
+      <c r="D15" s="286" t="inlineStr">
         <is>
           <t>0.3281±0.0013</t>
         </is>
       </c>
-      <c r="E15" s="287" t="inlineStr">
+      <c r="E15" s="286" t="inlineStr">
         <is>
           <t>0.1041±0.0017</t>
         </is>
       </c>
-      <c r="F15" s="287" t="inlineStr">
+      <c r="F15" s="286" t="inlineStr">
         <is>
           <t>0.3219±0.0057</t>
         </is>
       </c>
-      <c r="G15" s="287" t="inlineStr">
+      <c r="G15" s="286" t="inlineStr">
         <is>
           <t>-0.0307</t>
         </is>
       </c>
     </row>
     <row r="16" ht="20" customHeight="1" s="220">
-      <c r="A16" s="276" t="n"/>
-      <c r="B16" s="277" t="inlineStr">
+      <c r="A16" s="275" t="n"/>
+      <c r="B16" s="276" t="inlineStr">
         <is>
           <t>LaBraM-Base (scratch)</t>
         </is>
       </c>
-      <c r="C16" s="278" t="n">
+      <c r="C16" s="277" t="n">
         <v>5.82</v>
       </c>
-      <c r="D16" s="279" t="inlineStr">
+      <c r="D16" s="278" t="inlineStr">
         <is>
           <t>0.3147±0.0124</t>
         </is>
       </c>
-      <c r="E16" s="279" t="inlineStr">
+      <c r="E16" s="278" t="inlineStr">
         <is>
           <t>0.0862±0.0165</t>
         </is>
       </c>
-      <c r="F16" s="279" t="inlineStr">
+      <c r="F16" s="278" t="inlineStr">
         <is>
           <t>0.2972±0.0130</t>
         </is>
       </c>
-      <c r="G16" s="279" t="inlineStr">
+      <c r="G16" s="278" t="inlineStr">
         <is>
           <t>-0.0441</t>
         </is>
       </c>
     </row>
     <row r="17" ht="20" customHeight="1" s="220">
-      <c r="A17" s="276" t="n"/>
-      <c r="B17" s="277" t="inlineStr">
+      <c r="A17" s="275" t="n"/>
+      <c r="B17" s="276" t="inlineStr">
         <is>
           <t>CBraMod (scratch)</t>
         </is>
       </c>
-      <c r="C17" s="278" t="n">
+      <c r="C17" s="277" t="n">
         <v>19.13</v>
       </c>
-      <c r="D17" s="279" t="inlineStr">
+      <c r="D17" s="278" t="inlineStr">
         <is>
           <t>0.3043±0.0083</t>
         </is>
       </c>
-      <c r="E17" s="279" t="inlineStr">
+      <c r="E17" s="278" t="inlineStr">
         <is>
           <t>0.0724±0.0111</t>
         </is>
       </c>
-      <c r="F17" s="279" t="inlineStr">
+      <c r="F17" s="278" t="inlineStr">
         <is>
           <t>0.3013±0.0114</t>
         </is>
       </c>
-      <c r="G17" s="279" t="inlineStr">
+      <c r="G17" s="278" t="inlineStr">
         <is>
           <t>-0.0545</t>
         </is>
       </c>
     </row>
     <row r="18" ht="20" customHeight="1" s="220">
-      <c r="A18" s="276" t="n"/>
-      <c r="B18" s="289" t="inlineStr">
+      <c r="A18" s="275" t="n"/>
+      <c r="B18" s="288" t="inlineStr">
         <is>
           <t>PACLock (from scratch, full)</t>
         </is>
       </c>
-      <c r="C18" s="290" t="n">
+      <c r="C18" s="289" t="n">
         <v>1.6</v>
       </c>
-      <c r="D18" s="291" t="inlineStr">
+      <c r="D18" s="290" t="inlineStr">
         <is>
           <t>0.3588±0.0042</t>
         </is>
       </c>
-      <c r="E18" s="291" t="inlineStr">
+      <c r="E18" s="290" t="inlineStr">
         <is>
           <t>0.1451±0.0057</t>
         </is>
       </c>
-      <c r="F18" s="291" t="inlineStr">
+      <c r="F18" s="290" t="inlineStr">
         <is>
           <t>0.3446±0.0201</t>
         </is>
       </c>
-      <c r="G18" s="291" t="n"/>
+      <c r="G18" s="290" t="n"/>
     </row>
     <row r="19" ht="13.75" customHeight="1" s="220"/>
     <row r="20" ht="24" customHeight="1" s="220"/>
@@ -3970,7 +3970,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F178"/>
+  <dimension ref="A1:F186"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4884,7 +4884,7 @@
       </c>
       <c r="B30" s="219" t="inlineStr">
         <is>
-          <t>sparcnet</t>
+          <t>paclock_v2</t>
         </is>
       </c>
       <c r="C30" s="219" t="inlineStr">
@@ -4899,12 +4899,12 @@
       </c>
       <c r="E30" s="219" t="inlineStr">
         <is>
-          <t>[实测 1.14M] pr_auc per-seed 0:0.2337, 1:0.1153, 2:0.2438  [seed spread 30% -- mean is a weak summary]</t>
+          <t>[实测 1.62M] pr_auc per-seed 0:0.5809, 1:0.5382, 2:0.5200</t>
         </is>
       </c>
       <c r="F30" s="219" t="inlineStr">
         <is>
-          <t>lr=0.001 batch_size=512 epochs=20 patience=8 eval_every_steps=200 loss=focal</t>
+          <t>stopped_by=patience lr=0.0001 batch_size=32 epochs=20 patience=20 eval_every_steps=200 loss=focal grad_clip=1.0 tokenizer_mode=pac_interaction pac_token_mode=measured interaction_mode=product band_pe=index spatial_pe=xyz</t>
         </is>
       </c>
     </row>
@@ -4916,7 +4916,7 @@
       </c>
       <c r="B31" s="219" t="inlineStr">
         <is>
-          <t>st_transformer</t>
+          <t>sparcnet</t>
         </is>
       </c>
       <c r="C31" s="219" t="inlineStr">
@@ -4931,7 +4931,7 @@
       </c>
       <c r="E31" s="219" t="inlineStr">
         <is>
-          <t>[实测 3.43M] pr_auc per-seed 0:0.3099, 1:0.1098, 2:0.3024  [seed spread 38% -- mean is a weak summary]</t>
+          <t>[实测 1.14M] pr_auc per-seed 0:0.2337, 1:0.1153, 2:0.2438  [seed spread 30% -- mean is a weak summary]</t>
         </is>
       </c>
       <c r="F31" s="219" t="inlineStr">
@@ -4948,7 +4948,7 @@
       </c>
       <c r="B32" s="219" t="inlineStr">
         <is>
-          <t>tfm_pretrained</t>
+          <t>st_transformer</t>
         </is>
       </c>
       <c r="C32" s="219" t="inlineStr">
@@ -4963,24 +4963,24 @@
       </c>
       <c r="E32" s="219" t="inlineStr">
         <is>
-          <t>[实测 1.89M] pr_auc per-seed 0:0.6366, 1:0.6457, 2:0.5984</t>
+          <t>[实测 3.43M] pr_auc per-seed 0:0.3099, 1:0.1098, 2:0.3024  [seed spread 38% -- mean is a weak summary]</t>
         </is>
       </c>
       <c r="F32" s="219" t="inlineStr">
         <is>
-          <t>lr=0.001 batch_size=512 epochs=7 patience=10 eval_every_steps=100 loss=focal label_smoothing=0.1</t>
+          <t>lr=0.001 batch_size=512 epochs=20 patience=8 eval_every_steps=200 loss=focal</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="219" t="inlineStr">
         <is>
-          <t>faced</t>
+          <t>chbmit</t>
         </is>
       </c>
       <c r="B33" s="219" t="inlineStr">
         <is>
-          <t>biot_prest16</t>
+          <t>tfm_pretrained</t>
         </is>
       </c>
       <c r="C33" s="219" t="inlineStr">
@@ -4995,12 +4995,12 @@
       </c>
       <c r="E33" s="219" t="inlineStr">
         <is>
-          <t>[实测 3.19M] balanced_acc per-seed 0:0.2267, 1:0.2364, 2:0.1954</t>
+          <t>[实测 1.89M] pr_auc per-seed 0:0.6366, 1:0.6457, 2:0.5984</t>
         </is>
       </c>
       <c r="F33" s="219" t="inlineStr">
         <is>
-          <t>lr=0.0004 batch_size=64 epochs=100 patience=10 eval_every_steps=0 loss=cross_entropy</t>
+          <t>lr=0.001 batch_size=512 epochs=7 patience=10 eval_every_steps=100 loss=focal label_smoothing=0.1</t>
         </is>
       </c>
     </row>
@@ -5012,7 +5012,7 @@
       </c>
       <c r="B34" s="219" t="inlineStr">
         <is>
-          <t>biot_scratch</t>
+          <t>biot_prest16</t>
         </is>
       </c>
       <c r="C34" s="219" t="inlineStr">
@@ -5027,7 +5027,7 @@
       </c>
       <c r="E34" s="219" t="inlineStr">
         <is>
-          <t>[实测 3.19M] balanced_acc per-seed 0:0.1959, 1:0.1795, 2:0.1808</t>
+          <t>[实测 3.19M] balanced_acc per-seed 0:0.2267, 1:0.2364, 2:0.1954</t>
         </is>
       </c>
       <c r="F34" s="219" t="inlineStr">
@@ -5044,22 +5044,27 @@
       </c>
       <c r="B35" s="219" t="inlineStr">
         <is>
-          <t>cbramod_pac</t>
+          <t>biot_scratch</t>
         </is>
       </c>
       <c r="C35" s="219" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>[0, 1, 2]</t>
         </is>
       </c>
       <c r="D35" s="219" t="inlineStr">
         <is>
-          <t>skipped</t>
+          <t>filled</t>
         </is>
       </c>
       <c r="E35" s="219" t="inlineStr">
         <is>
-          <t>the workbook has no row for this variant</t>
+          <t>[实测 3.19M] balanced_acc per-seed 0:0.1959, 1:0.1795, 2:0.1808</t>
+        </is>
+      </c>
+      <c r="F35" s="219" t="inlineStr">
+        <is>
+          <t>lr=0.0004 batch_size=64 epochs=100 patience=10 eval_every_steps=0 loss=cross_entropy</t>
         </is>
       </c>
     </row>
@@ -5071,27 +5076,22 @@
       </c>
       <c r="B36" s="219" t="inlineStr">
         <is>
-          <t>cbramod_pretrained</t>
+          <t>cbramod_pac</t>
         </is>
       </c>
       <c r="C36" s="219" t="inlineStr">
         <is>
-          <t>[0, 1, 2]</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D36" s="219" t="inlineStr">
         <is>
-          <t>filled</t>
+          <t>skipped</t>
         </is>
       </c>
       <c r="E36" s="219" t="inlineStr">
         <is>
-          <t>[实测 56.25M] balanced_acc per-seed 0:0.5464, 1:0.5515, 2:0.5548</t>
-        </is>
-      </c>
-      <c r="F36" s="219" t="inlineStr">
-        <is>
-          <t>lr=0.0001 batch_size=64 epochs=50 patience=0 eval_every_steps=0 loss=cross_entropy label_smoothing=0.1 grad_clip=1.0 multi_lr=True</t>
+          <t>the workbook has no row for this variant</t>
         </is>
       </c>
     </row>
@@ -5103,7 +5103,7 @@
       </c>
       <c r="B37" s="219" t="inlineStr">
         <is>
-          <t>cbramod_scratch</t>
+          <t>cbramod_pretrained</t>
         </is>
       </c>
       <c r="C37" s="219" t="inlineStr">
@@ -5113,12 +5113,17 @@
       </c>
       <c r="D37" s="219" t="inlineStr">
         <is>
-          <t>withheld (rule 3)</t>
+          <t>filled</t>
         </is>
       </c>
       <c r="E37" s="219" t="inlineStr">
         <is>
-          <t>mis-configured seeds [1, 2]: {1: 'val peak at first evaluation and never cleared chance (0.1144 vs 0.1111)', 2: 'val curve is flat (model not learning)'}; measured balanced_acc 0.2444±0.1877</t>
+          <t>[实测 56.25M] balanced_acc per-seed 0:0.5464, 1:0.5515, 2:0.5548</t>
+        </is>
+      </c>
+      <c r="F37" s="219" t="inlineStr">
+        <is>
+          <t>lr=0.0001 batch_size=64 epochs=50 patience=0 eval_every_steps=0 loss=cross_entropy label_smoothing=0.1 grad_clip=1.0 multi_lr=True</t>
         </is>
       </c>
     </row>
@@ -5130,7 +5135,7 @@
       </c>
       <c r="B38" s="219" t="inlineStr">
         <is>
-          <t>cnn_transformer</t>
+          <t>cbramod_scratch</t>
         </is>
       </c>
       <c r="C38" s="219" t="inlineStr">
@@ -5145,7 +5150,7 @@
       </c>
       <c r="E38" s="219" t="inlineStr">
         <is>
-          <t>mis-configured seeds [0, 1, 2]: {0: 'val peak at first evaluation and never cleared chance (0.1111 vs 0.1111)', 1: "test Cohen's Kappa 0.0005 is at chance -- the model does not discriminate, whatever the val curve did", 2: 'val peak at first evaluation and never cleared chance (0.1111 vs 0.1111)'}; measured balanced_acc 0.1112±0.0002</t>
+          <t>mis-configured seeds [1, 2]: {1: 'val peak at first evaluation and never cleared chance (0.1144 vs 0.1111)', 2: 'val curve is flat (model not learning)'}; measured balanced_acc 0.2444±0.1877</t>
         </is>
       </c>
     </row>
@@ -5157,7 +5162,7 @@
       </c>
       <c r="B39" s="219" t="inlineStr">
         <is>
-          <t>contrawr</t>
+          <t>cnn_transformer</t>
         </is>
       </c>
       <c r="C39" s="219" t="inlineStr">
@@ -5167,17 +5172,12 @@
       </c>
       <c r="D39" s="219" t="inlineStr">
         <is>
-          <t>filled</t>
+          <t>withheld (rule 3)</t>
         </is>
       </c>
       <c r="E39" s="219" t="inlineStr">
         <is>
-          <t>[实测 1.58M] balanced_acc per-seed 0:0.1758, 1:0.2012, 2:0.2272</t>
-        </is>
-      </c>
-      <c r="F39" s="219" t="inlineStr">
-        <is>
-          <t>lr=0.001 batch_size=64 epochs=100 patience=20 eval_every_steps=0 loss=cross_entropy label_smoothing=0.1</t>
+          <t>mis-configured seeds [0, 1, 2]: {0: 'val peak at first evaluation and never cleared chance (0.1111 vs 0.1111)', 1: "test Cohen's Kappa 0.0005 is at chance -- the model does not discriminate, whatever the val curve did", 2: 'val peak at first evaluation and never cleared chance (0.1111 vs 0.1111)'}; measured balanced_acc 0.1112±0.0002</t>
         </is>
       </c>
     </row>
@@ -5189,7 +5189,7 @@
       </c>
       <c r="B40" s="219" t="inlineStr">
         <is>
-          <t>eegpt_pretrained</t>
+          <t>contrawr</t>
         </is>
       </c>
       <c r="C40" s="219" t="inlineStr">
@@ -5204,12 +5204,12 @@
       </c>
       <c r="E40" s="219" t="inlineStr">
         <is>
-          <t>[实测 25.69M] balanced_acc per-seed 0:0.1755, 1:0.1806, 2:0.1593</t>
+          <t>[实测 1.58M] balanced_acc per-seed 0:0.1758, 1:0.2012, 2:0.2272</t>
         </is>
       </c>
       <c r="F40" s="219" t="inlineStr">
         <is>
-          <t>lr=0.0004 batch_size=32 epochs=100 patience=10 eval_every_steps=0 loss=cross_entropy</t>
+          <t>lr=0.001 batch_size=64 epochs=100 patience=20 eval_every_steps=0 loss=cross_entropy label_smoothing=0.1</t>
         </is>
       </c>
     </row>
@@ -5221,27 +5221,22 @@
       </c>
       <c r="B41" s="219" t="inlineStr">
         <is>
-          <t>ffcl</t>
+          <t>diag_lr3e5</t>
         </is>
       </c>
       <c r="C41" s="219" t="inlineStr">
         <is>
-          <t>[0, 1, 2]</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D41" s="219" t="inlineStr">
         <is>
-          <t>filled</t>
+          <t>skipped</t>
         </is>
       </c>
       <c r="E41" s="219" t="inlineStr">
         <is>
-          <t>[实测 2.48M] balanced_acc per-seed 0:0.2205, 1:0.2547, 2:0.2424</t>
-        </is>
-      </c>
-      <c r="F41" s="219" t="inlineStr">
-        <is>
-          <t>lr=0.001 batch_size=64 epochs=100 patience=20 eval_every_steps=0 loss=cross_entropy label_smoothing=0.1</t>
+          <t>no row label for 'diag_lr3e5'</t>
         </is>
       </c>
     </row>
@@ -5253,27 +5248,22 @@
       </c>
       <c r="B42" s="219" t="inlineStr">
         <is>
-          <t>labram_pretrained</t>
+          <t>diag_patch200</t>
         </is>
       </c>
       <c r="C42" s="219" t="inlineStr">
         <is>
-          <t>[0, 1, 2]</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D42" s="219" t="inlineStr">
         <is>
-          <t>filled</t>
+          <t>skipped</t>
         </is>
       </c>
       <c r="E42" s="219" t="inlineStr">
         <is>
-          <t>[实测 5.82M] balanced_acc per-seed 0:0.3273, 1:0.3253, 2:0.3290</t>
-        </is>
-      </c>
-      <c r="F42" s="219" t="inlineStr">
-        <is>
-          <t>stopped_by=patience lr=0.0005 batch_size=64 epochs=50 patience=10 eval_every_steps=0 loss=cross_entropy label_smoothing=0.1 loader_divisor=1.0</t>
+          <t>no row label for 'diag_patch200'</t>
         </is>
       </c>
     </row>
@@ -5285,27 +5275,22 @@
       </c>
       <c r="B43" s="219" t="inlineStr">
         <is>
-          <t>labram_scratch</t>
+          <t>diag_patch200_lr3e5</t>
         </is>
       </c>
       <c r="C43" s="219" t="inlineStr">
         <is>
-          <t>[0, 1, 2]</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D43" s="219" t="inlineStr">
         <is>
-          <t>filled</t>
+          <t>skipped</t>
         </is>
       </c>
       <c r="E43" s="219" t="inlineStr">
         <is>
-          <t>[实测 5.82M] balanced_acc per-seed 0:0.1455, 1:0.1618, 2:0.1676</t>
-        </is>
-      </c>
-      <c r="F43" s="219" t="inlineStr">
-        <is>
-          <t>stopped_by=patience lr=0.0005 batch_size=64 epochs=50 patience=10 eval_every_steps=0 loss=cross_entropy label_smoothing=0.1 loader_divisor=1.0</t>
+          <t>no row label for 'diag_patch200_lr3e5'</t>
         </is>
       </c>
     </row>
@@ -5317,22 +5302,27 @@
       </c>
       <c r="B44" s="219" t="inlineStr">
         <is>
-          <t>paclock_pac</t>
+          <t>eegpt_pretrained</t>
         </is>
       </c>
       <c r="C44" s="219" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>[0, 1, 2]</t>
         </is>
       </c>
       <c r="D44" s="219" t="inlineStr">
         <is>
-          <t>skipped</t>
+          <t>filled</t>
         </is>
       </c>
       <c r="E44" s="219" t="inlineStr">
         <is>
-          <t>the workbook has no row for this variant</t>
+          <t>[实测 25.69M] balanced_acc per-seed 0:0.1755, 1:0.1806, 2:0.1593</t>
+        </is>
+      </c>
+      <c r="F44" s="219" t="inlineStr">
+        <is>
+          <t>lr=0.0004 batch_size=32 epochs=100 patience=10 eval_every_steps=0 loss=cross_entropy</t>
         </is>
       </c>
     </row>
@@ -5344,7 +5334,7 @@
       </c>
       <c r="B45" s="219" t="inlineStr">
         <is>
-          <t>paclock_v2</t>
+          <t>ffcl</t>
         </is>
       </c>
       <c r="C45" s="219" t="inlineStr">
@@ -5354,12 +5344,17 @@
       </c>
       <c r="D45" s="219" t="inlineStr">
         <is>
-          <t>withheld (rule 3)</t>
+          <t>filled</t>
         </is>
       </c>
       <c r="E45" s="219" t="inlineStr">
         <is>
-          <t>mis-configured seeds [1, 2]: {1: 'val peak at first evaluation and never cleared chance (0.1111 vs 0.1111)', 2: 'val peak at first evaluation and never cleared chance (0.1111 vs 0.1111)'}; measured balanced_acc 0.1307±0.0276</t>
+          <t>[实测 2.48M] balanced_acc per-seed 0:0.2205, 1:0.2547, 2:0.2424</t>
+        </is>
+      </c>
+      <c r="F45" s="219" t="inlineStr">
+        <is>
+          <t>lr=0.001 batch_size=64 epochs=100 patience=20 eval_every_steps=0 loss=cross_entropy label_smoothing=0.1</t>
         </is>
       </c>
     </row>
@@ -5371,7 +5366,7 @@
       </c>
       <c r="B46" s="219" t="inlineStr">
         <is>
-          <t>sparcnet</t>
+          <t>labram_pretrained</t>
         </is>
       </c>
       <c r="C46" s="219" t="inlineStr">
@@ -5386,12 +5381,12 @@
       </c>
       <c r="E46" s="219" t="inlineStr">
         <is>
-          <t>[实测 1.23M] balanced_acc per-seed 0:0.2458, 1:0.2662, 2:0.2790</t>
+          <t>[实测 5.82M] balanced_acc per-seed 0:0.3273, 1:0.3253, 2:0.3290</t>
         </is>
       </c>
       <c r="F46" s="219" t="inlineStr">
         <is>
-          <t>lr=0.001 batch_size=64 epochs=100 patience=20 eval_every_steps=0 loss=cross_entropy label_smoothing=0.1</t>
+          <t>stopped_by=patience lr=0.0005 batch_size=64 epochs=50 patience=10 eval_every_steps=0 loss=cross_entropy label_smoothing=0.1 loader_divisor=1.0</t>
         </is>
       </c>
     </row>
@@ -5403,7 +5398,7 @@
       </c>
       <c r="B47" s="219" t="inlineStr">
         <is>
-          <t>st_transformer</t>
+          <t>labram_scratch</t>
         </is>
       </c>
       <c r="C47" s="219" t="inlineStr">
@@ -5418,12 +5413,12 @@
       </c>
       <c r="E47" s="219" t="inlineStr">
         <is>
-          <t>[实测 3.45M] balanced_acc per-seed 0:0.3371, 1:0.2954, 2:0.3268</t>
+          <t>[实测 5.82M] balanced_acc per-seed 0:0.1455, 1:0.1618, 2:0.1676</t>
         </is>
       </c>
       <c r="F47" s="219" t="inlineStr">
         <is>
-          <t>lr=0.001 batch_size=64 epochs=100 patience=20 eval_every_steps=0 loss=cross_entropy label_smoothing=0.1</t>
+          <t>stopped_by=patience lr=0.0005 batch_size=64 epochs=50 patience=10 eval_every_steps=0 loss=cross_entropy label_smoothing=0.1 loader_divisor=1.0</t>
         </is>
       </c>
     </row>
@@ -5435,66 +5430,66 @@
       </c>
       <c r="B48" s="219" t="inlineStr">
         <is>
-          <t>tfm_pretrained</t>
+          <t>paclock_pac</t>
         </is>
       </c>
       <c r="C48" s="219" t="inlineStr">
         <is>
-          <t>[0, 1, 2]</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D48" s="219" t="inlineStr">
         <is>
-          <t>filled</t>
+          <t>skipped</t>
         </is>
       </c>
       <c r="E48" s="219" t="inlineStr">
         <is>
-          <t>[实测 1.89M] balanced_acc per-seed 0:0.2492, 1:0.2226, 2:0.2358</t>
-        </is>
-      </c>
-      <c r="F48" s="219" t="inlineStr">
-        <is>
-          <t>lr=0.001 batch_size=64 epochs=50 patience=10 eval_every_steps=0 loss=cross_entropy label_smoothing=0.1</t>
+          <t>the workbook has no row for this variant</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="219" t="inlineStr">
         <is>
-          <t>isruc</t>
+          <t>faced</t>
         </is>
       </c>
       <c r="B49" s="219" t="inlineStr">
         <is>
-          <t>biot_hop50</t>
+          <t>sparcnet</t>
         </is>
       </c>
       <c r="C49" s="219" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>[0, 1, 2]</t>
         </is>
       </c>
       <c r="D49" s="219" t="inlineStr">
         <is>
-          <t>skipped</t>
+          <t>filled</t>
         </is>
       </c>
       <c r="E49" s="219" t="inlineStr">
         <is>
-          <t>the workbook has no row for this variant</t>
+          <t>[实测 1.23M] balanced_acc per-seed 0:0.2458, 1:0.2662, 2:0.2790</t>
+        </is>
+      </c>
+      <c r="F49" s="219" t="inlineStr">
+        <is>
+          <t>lr=0.001 batch_size=64 epochs=100 patience=20 eval_every_steps=0 loss=cross_entropy label_smoothing=0.1</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="219" t="inlineStr">
         <is>
-          <t>isruc</t>
+          <t>faced</t>
         </is>
       </c>
       <c r="B50" s="219" t="inlineStr">
         <is>
-          <t>biot_prest16</t>
+          <t>st_transformer</t>
         </is>
       </c>
       <c r="C50" s="219" t="inlineStr">
@@ -5509,24 +5504,24 @@
       </c>
       <c r="E50" s="219" t="inlineStr">
         <is>
-          <t>[实测 3.19M] cohen_kappa per-seed 0:0.7382, 1:0.7300, 2:0.7409</t>
+          <t>[实测 3.45M] balanced_acc per-seed 0:0.3371, 1:0.2954, 2:0.3268</t>
         </is>
       </c>
       <c r="F50" s="219" t="inlineStr">
         <is>
-          <t>lr=0.0004 batch_size=64 epochs=40 patience=10 eval_every_steps=0 loss=cross_entropy</t>
+          <t>lr=0.001 batch_size=64 epochs=100 patience=20 eval_every_steps=0 loss=cross_entropy label_smoothing=0.1</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="219" t="inlineStr">
         <is>
-          <t>isruc</t>
+          <t>faced</t>
         </is>
       </c>
       <c r="B51" s="219" t="inlineStr">
         <is>
-          <t>biot_scratch</t>
+          <t>tfm_pretrained</t>
         </is>
       </c>
       <c r="C51" s="219" t="inlineStr">
@@ -5541,12 +5536,12 @@
       </c>
       <c r="E51" s="219" t="inlineStr">
         <is>
-          <t>[实测 3.18M] cohen_kappa per-seed 0:0.7361, 1:0.7421, 2:0.7352</t>
+          <t>[实测 1.89M] balanced_acc per-seed 0:0.2492, 1:0.2226, 2:0.2358</t>
         </is>
       </c>
       <c r="F51" s="219" t="inlineStr">
         <is>
-          <t>lr=0.0004 batch_size=64 epochs=40 patience=10 eval_every_steps=0 loss=cross_entropy</t>
+          <t>lr=0.001 batch_size=64 epochs=50 patience=10 eval_every_steps=0 loss=cross_entropy label_smoothing=0.1</t>
         </is>
       </c>
     </row>
@@ -5558,7 +5553,7 @@
       </c>
       <c r="B52" s="219" t="inlineStr">
         <is>
-          <t>biot_tok100</t>
+          <t>biot_hop50</t>
         </is>
       </c>
       <c r="C52" s="219" t="inlineStr">
@@ -5585,22 +5580,27 @@
       </c>
       <c r="B53" s="219" t="inlineStr">
         <is>
-          <t>cand_base</t>
+          <t>biot_prest16</t>
         </is>
       </c>
       <c r="C53" s="219" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>[0, 1, 2]</t>
         </is>
       </c>
       <c r="D53" s="219" t="inlineStr">
         <is>
-          <t>skipped</t>
+          <t>filled</t>
         </is>
       </c>
       <c r="E53" s="219" t="inlineStr">
         <is>
-          <t>the workbook has no row for this variant</t>
+          <t>[实测 3.19M] cohen_kappa per-seed 0:0.7382, 1:0.7300, 2:0.7409</t>
+        </is>
+      </c>
+      <c r="F53" s="219" t="inlineStr">
+        <is>
+          <t>lr=0.0004 batch_size=64 epochs=40 patience=10 eval_every_steps=0 loss=cross_entropy</t>
         </is>
       </c>
     </row>
@@ -5612,22 +5612,27 @@
       </c>
       <c r="B54" s="219" t="inlineStr">
         <is>
-          <t>cand_e60_base</t>
+          <t>biot_scratch</t>
         </is>
       </c>
       <c r="C54" s="219" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>[0, 1, 2]</t>
         </is>
       </c>
       <c r="D54" s="219" t="inlineStr">
         <is>
-          <t>skipped</t>
+          <t>filled</t>
         </is>
       </c>
       <c r="E54" s="219" t="inlineStr">
         <is>
-          <t>the workbook has no row for this variant</t>
+          <t>[实测 3.18M] cohen_kappa per-seed 0:0.7361, 1:0.7421, 2:0.7352</t>
+        </is>
+      </c>
+      <c r="F54" s="219" t="inlineStr">
+        <is>
+          <t>lr=0.0004 batch_size=64 epochs=40 patience=10 eval_every_steps=0 loss=cross_entropy</t>
         </is>
       </c>
     </row>
@@ -5639,7 +5644,7 @@
       </c>
       <c r="B55" s="219" t="inlineStr">
         <is>
-          <t>cand_e60_patch100</t>
+          <t>biot_tok100</t>
         </is>
       </c>
       <c r="C55" s="219" t="inlineStr">
@@ -5666,7 +5671,7 @@
       </c>
       <c r="B56" s="219" t="inlineStr">
         <is>
-          <t>cand_e60_size_base</t>
+          <t>cand_base</t>
         </is>
       </c>
       <c r="C56" s="219" t="inlineStr">
@@ -5693,7 +5698,7 @@
       </c>
       <c r="B57" s="219" t="inlineStr">
         <is>
-          <t>cand_e60_size_large</t>
+          <t>cand_e60_base</t>
         </is>
       </c>
       <c r="C57" s="219" t="inlineStr">
@@ -5720,7 +5725,7 @@
       </c>
       <c r="B58" s="219" t="inlineStr">
         <is>
-          <t>cand_ms</t>
+          <t>cand_e60_patch100</t>
         </is>
       </c>
       <c r="C58" s="219" t="inlineStr">
@@ -5747,7 +5752,7 @@
       </c>
       <c r="B59" s="219" t="inlineStr">
         <is>
-          <t>cand_p100_large</t>
+          <t>cand_e60_size_base</t>
         </is>
       </c>
       <c r="C59" s="219" t="inlineStr">
@@ -5774,7 +5779,7 @@
       </c>
       <c r="B60" s="219" t="inlineStr">
         <is>
-          <t>cand_p200_win1200</t>
+          <t>cand_e60_size_large</t>
         </is>
       </c>
       <c r="C60" s="219" t="inlineStr">
@@ -5801,7 +5806,7 @@
       </c>
       <c r="B61" s="219" t="inlineStr">
         <is>
-          <t>cand_p200_win3000</t>
+          <t>cand_ms</t>
         </is>
       </c>
       <c r="C61" s="219" t="inlineStr">
@@ -5828,7 +5833,7 @@
       </c>
       <c r="B62" s="219" t="inlineStr">
         <is>
-          <t>cand_p200_win400</t>
+          <t>cand_p100_large</t>
         </is>
       </c>
       <c r="C62" s="219" t="inlineStr">
@@ -5855,7 +5860,7 @@
       </c>
       <c r="B63" s="219" t="inlineStr">
         <is>
-          <t>cand_p200_win600</t>
+          <t>cand_p200_win1200</t>
         </is>
       </c>
       <c r="C63" s="219" t="inlineStr">
@@ -5882,7 +5887,7 @@
       </c>
       <c r="B64" s="219" t="inlineStr">
         <is>
-          <t>cand_p200_win6000</t>
+          <t>cand_p200_win3000</t>
         </is>
       </c>
       <c r="C64" s="219" t="inlineStr">
@@ -5909,7 +5914,7 @@
       </c>
       <c r="B65" s="219" t="inlineStr">
         <is>
-          <t>cand_pacwin200</t>
+          <t>cand_p200_win400</t>
         </is>
       </c>
       <c r="C65" s="219" t="inlineStr">
@@ -5936,7 +5941,7 @@
       </c>
       <c r="B66" s="219" t="inlineStr">
         <is>
-          <t>cand_patch100</t>
+          <t>cand_p200_win600</t>
         </is>
       </c>
       <c r="C66" s="219" t="inlineStr">
@@ -5963,7 +5968,7 @@
       </c>
       <c r="B67" s="219" t="inlineStr">
         <is>
-          <t>cand_patch50</t>
+          <t>cand_p200_win6000</t>
         </is>
       </c>
       <c r="C67" s="219" t="inlineStr">
@@ -5990,7 +5995,7 @@
       </c>
       <c r="B68" s="219" t="inlineStr">
         <is>
-          <t>cbramod_pac</t>
+          <t>cand_pacwin200</t>
         </is>
       </c>
       <c r="C68" s="219" t="inlineStr">
@@ -6017,27 +6022,22 @@
       </c>
       <c r="B69" s="219" t="inlineStr">
         <is>
-          <t>cbramod_pretrained</t>
+          <t>cand_patch100</t>
         </is>
       </c>
       <c r="C69" s="219" t="inlineStr">
         <is>
-          <t>[0, 1, 2]</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D69" s="219" t="inlineStr">
         <is>
-          <t>filled</t>
+          <t>skipped</t>
         </is>
       </c>
       <c r="E69" s="219" t="inlineStr">
         <is>
-          <t>[实测 26.47M] cohen_kappa per-seed 0:0.7476, 1:0.7625, 2:0.7519</t>
-        </is>
-      </c>
-      <c r="F69" s="219" t="inlineStr">
-        <is>
-          <t>lr=0.0001 batch_size=64 epochs=50 patience=0 eval_every_steps=0 loss=cross_entropy label_smoothing=0.1 grad_clip=1.0 multi_lr=True</t>
+          <t>the workbook has no row for this variant</t>
         </is>
       </c>
     </row>
@@ -6049,27 +6049,22 @@
       </c>
       <c r="B70" s="219" t="inlineStr">
         <is>
-          <t>cbramod_scratch</t>
+          <t>cand_patch50</t>
         </is>
       </c>
       <c r="C70" s="219" t="inlineStr">
         <is>
-          <t>[0, 1, 2]</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D70" s="219" t="inlineStr">
         <is>
-          <t>filled</t>
+          <t>skipped</t>
         </is>
       </c>
       <c r="E70" s="219" t="inlineStr">
         <is>
-          <t>[实测 26.47M] cohen_kappa per-seed 0:0.6947, 1:0.6930, 2:0.7049</t>
-        </is>
-      </c>
-      <c r="F70" s="219" t="inlineStr">
-        <is>
-          <t>lr=0.0001 batch_size=64 epochs=50 patience=0 eval_every_steps=0 loss=cross_entropy label_smoothing=0.1 grad_clip=1.0 multi_lr=True</t>
+          <t>the workbook has no row for this variant</t>
         </is>
       </c>
     </row>
@@ -6081,27 +6076,22 @@
       </c>
       <c r="B71" s="219" t="inlineStr">
         <is>
-          <t>cnn_transformer</t>
+          <t>cbramod_pac</t>
         </is>
       </c>
       <c r="C71" s="219" t="inlineStr">
         <is>
-          <t>[0, 1, 2]</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D71" s="219" t="inlineStr">
         <is>
-          <t>filled</t>
+          <t>skipped</t>
         </is>
       </c>
       <c r="E71" s="219" t="inlineStr">
         <is>
-          <t>[实测 3.15M] cohen_kappa per-seed 0:0.7595, 1:0.7456, 2:0.7544</t>
-        </is>
-      </c>
-      <c r="F71" s="219" t="inlineStr">
-        <is>
-          <t>lr=0.001 batch_size=512 epochs=60 patience=15 eval_every_steps=0 loss=cross_entropy label_smoothing=0.1</t>
+          <t>the workbook has no row for this variant</t>
         </is>
       </c>
     </row>
@@ -6113,7 +6103,7 @@
       </c>
       <c r="B72" s="219" t="inlineStr">
         <is>
-          <t>contrawr</t>
+          <t>cbramod_pretrained</t>
         </is>
       </c>
       <c r="C72" s="219" t="inlineStr">
@@ -6128,12 +6118,12 @@
       </c>
       <c r="E72" s="219" t="inlineStr">
         <is>
-          <t>[实测 1.57M] cohen_kappa per-seed 0:0.7584, 1:0.7495, 2:0.7482</t>
+          <t>[实测 26.47M] cohen_kappa per-seed 0:0.7476, 1:0.7625, 2:0.7519</t>
         </is>
       </c>
       <c r="F72" s="219" t="inlineStr">
         <is>
-          <t>lr=0.001 batch_size=512 epochs=60 patience=15 eval_every_steps=0 loss=cross_entropy label_smoothing=0.1</t>
+          <t>lr=0.0001 batch_size=64 epochs=50 patience=0 eval_every_steps=0 loss=cross_entropy label_smoothing=0.1 grad_clip=1.0 multi_lr=True</t>
         </is>
       </c>
     </row>
@@ -6145,7 +6135,7 @@
       </c>
       <c r="B73" s="219" t="inlineStr">
         <is>
-          <t>eegpt_pretrained</t>
+          <t>cbramod_scratch</t>
         </is>
       </c>
       <c r="C73" s="219" t="inlineStr">
@@ -6160,12 +6150,12 @@
       </c>
       <c r="E73" s="219" t="inlineStr">
         <is>
-          <t>[实测 25.69M] cohen_kappa per-seed 0:0.7111, 1:0.7127, 2:0.6766</t>
+          <t>[实测 26.47M] cohen_kappa per-seed 0:0.6947, 1:0.6930, 2:0.7049</t>
         </is>
       </c>
       <c r="F73" s="219" t="inlineStr">
         <is>
-          <t>lr=0.0004 batch_size=32 epochs=40 patience=10 eval_every_steps=50 loss=cross_entropy</t>
+          <t>lr=0.0001 batch_size=64 epochs=50 patience=0 eval_every_steps=0 loss=cross_entropy label_smoothing=0.1 grad_clip=1.0 multi_lr=True</t>
         </is>
       </c>
     </row>
@@ -6177,7 +6167,7 @@
       </c>
       <c r="B74" s="219" t="inlineStr">
         <is>
-          <t>ffcl</t>
+          <t>cnn_transformer</t>
         </is>
       </c>
       <c r="C74" s="219" t="inlineStr">
@@ -6192,7 +6182,7 @@
       </c>
       <c r="E74" s="219" t="inlineStr">
         <is>
-          <t>[实测 2.67M] cohen_kappa per-seed 0:0.7252, 1:0.7243, 2:0.7516</t>
+          <t>[实测 3.15M] cohen_kappa per-seed 0:0.7595, 1:0.7456, 2:0.7544</t>
         </is>
       </c>
       <c r="F74" s="219" t="inlineStr">
@@ -6209,7 +6199,7 @@
       </c>
       <c r="B75" s="219" t="inlineStr">
         <is>
-          <t>labram_pretrained</t>
+          <t>contrawr</t>
         </is>
       </c>
       <c r="C75" s="219" t="inlineStr">
@@ -6224,12 +6214,12 @@
       </c>
       <c r="E75" s="219" t="inlineStr">
         <is>
-          <t>[实测 5.82M] cohen_kappa per-seed 0:0.7376, 1:0.7538, 2:0.7183</t>
+          <t>[实测 1.57M] cohen_kappa per-seed 0:0.7584, 1:0.7495, 2:0.7482</t>
         </is>
       </c>
       <c r="F75" s="219" t="inlineStr">
         <is>
-          <t>stopped_by=patience lr=0.0005 batch_size=64 epochs=50 patience=10 eval_every_steps=0 loss=cross_entropy label_smoothing=0.1 loader_divisor=1.0</t>
+          <t>lr=0.001 batch_size=512 epochs=60 patience=15 eval_every_steps=0 loss=cross_entropy label_smoothing=0.1</t>
         </is>
       </c>
     </row>
@@ -6241,7 +6231,7 @@
       </c>
       <c r="B76" s="219" t="inlineStr">
         <is>
-          <t>labram_scratch</t>
+          <t>eegpt_pretrained</t>
         </is>
       </c>
       <c r="C76" s="219" t="inlineStr">
@@ -6256,12 +6246,12 @@
       </c>
       <c r="E76" s="219" t="inlineStr">
         <is>
-          <t>[实测 5.82M] cohen_kappa per-seed 0:0.6301, 1:0.6084, 2:0.6322</t>
+          <t>[实测 25.69M] cohen_kappa per-seed 0:0.7111, 1:0.7127, 2:0.6766</t>
         </is>
       </c>
       <c r="F76" s="219" t="inlineStr">
         <is>
-          <t>stopped_by=patience lr=0.0005 batch_size=64 epochs=50 patience=10 eval_every_steps=0 loss=cross_entropy label_smoothing=0.1 loader_divisor=1.0</t>
+          <t>lr=0.0004 batch_size=32 epochs=40 patience=10 eval_every_steps=50 loss=cross_entropy</t>
         </is>
       </c>
     </row>
@@ -6273,22 +6263,27 @@
       </c>
       <c r="B77" s="219" t="inlineStr">
         <is>
-          <t>paclock_pac</t>
+          <t>ffcl</t>
         </is>
       </c>
       <c r="C77" s="219" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>[0, 1, 2]</t>
         </is>
       </c>
       <c r="D77" s="219" t="inlineStr">
         <is>
-          <t>skipped</t>
+          <t>filled</t>
         </is>
       </c>
       <c r="E77" s="219" t="inlineStr">
         <is>
-          <t>the workbook has no row for this variant</t>
+          <t>[实测 2.67M] cohen_kappa per-seed 0:0.7252, 1:0.7243, 2:0.7516</t>
+        </is>
+      </c>
+      <c r="F77" s="219" t="inlineStr">
+        <is>
+          <t>lr=0.001 batch_size=512 epochs=60 patience=15 eval_every_steps=0 loss=cross_entropy label_smoothing=0.1</t>
         </is>
       </c>
     </row>
@@ -6300,7 +6295,7 @@
       </c>
       <c r="B78" s="219" t="inlineStr">
         <is>
-          <t>sparcnet</t>
+          <t>labram_pretrained</t>
         </is>
       </c>
       <c r="C78" s="219" t="inlineStr">
@@ -6315,12 +6310,12 @@
       </c>
       <c r="E78" s="219" t="inlineStr">
         <is>
-          <t>[实测 1.38M] cohen_kappa per-seed 0:0.7286, 1:0.7185, 2:0.7565</t>
+          <t>[实测 5.82M] cohen_kappa per-seed 0:0.7376, 1:0.7538, 2:0.7183</t>
         </is>
       </c>
       <c r="F78" s="219" t="inlineStr">
         <is>
-          <t>lr=0.001 batch_size=512 epochs=60 patience=15 eval_every_steps=0 loss=cross_entropy label_smoothing=0.1</t>
+          <t>stopped_by=patience lr=0.0005 batch_size=64 epochs=50 patience=10 eval_every_steps=0 loss=cross_entropy label_smoothing=0.1 loader_divisor=1.0</t>
         </is>
       </c>
     </row>
@@ -6332,7 +6327,7 @@
       </c>
       <c r="B79" s="219" t="inlineStr">
         <is>
-          <t>st_transformer</t>
+          <t>labram_scratch</t>
         </is>
       </c>
       <c r="C79" s="219" t="inlineStr">
@@ -6347,12 +6342,12 @@
       </c>
       <c r="E79" s="219" t="inlineStr">
         <is>
-          <t>[实测 3.42M] cohen_kappa per-seed 0:0.5488, 1:0.3217, 2:0.3076  [seed spread 28% -- mean is a weak summary]</t>
+          <t>[实测 5.82M] cohen_kappa per-seed 0:0.6301, 1:0.6084, 2:0.6322</t>
         </is>
       </c>
       <c r="F79" s="219" t="inlineStr">
         <is>
-          <t>lr=0.001 batch_size=512 epochs=60 patience=15 eval_every_steps=0 loss=cross_entropy label_smoothing=0.1</t>
+          <t>stopped_by=patience lr=0.0005 batch_size=64 epochs=50 patience=10 eval_every_steps=0 loss=cross_entropy label_smoothing=0.1 loader_divisor=1.0</t>
         </is>
       </c>
     </row>
@@ -6364,39 +6359,34 @@
       </c>
       <c r="B80" s="219" t="inlineStr">
         <is>
-          <t>tfm_pretrained</t>
+          <t>paclock_pac</t>
         </is>
       </c>
       <c r="C80" s="219" t="inlineStr">
         <is>
-          <t>[0, 1, 2]</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D80" s="219" t="inlineStr">
         <is>
-          <t>filled</t>
+          <t>skipped</t>
         </is>
       </c>
       <c r="E80" s="219" t="inlineStr">
         <is>
-          <t>[实测 1.89M] cohen_kappa per-seed 0:0.7144, 1:0.7084, 2:0.7077</t>
-        </is>
-      </c>
-      <c r="F80" s="219" t="inlineStr">
-        <is>
-          <t>lr=0.001 batch_size=512 epochs=50 patience=10 eval_every_steps=0 loss=cross_entropy label_smoothing=0.1</t>
+          <t>the workbook has no row for this variant</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="219" t="inlineStr">
         <is>
-          <t>physionet_mi</t>
+          <t>isruc</t>
         </is>
       </c>
       <c r="B81" s="219" t="inlineStr">
         <is>
-          <t>biot_prest16</t>
+          <t>paclock_v2</t>
         </is>
       </c>
       <c r="C81" s="219" t="inlineStr">
@@ -6411,24 +6401,24 @@
       </c>
       <c r="E81" s="219" t="inlineStr">
         <is>
-          <t>[实测 3.19M] balanced_acc per-seed 0:0.4950, 1:0.5034, 2:0.5126</t>
+          <t>[实测 1.60M] cohen_kappa per-seed 0:0.6952, 1:0.6947, 2:0.6958</t>
         </is>
       </c>
       <c r="F81" s="219" t="inlineStr">
         <is>
-          <t>lr=0.0004 batch_size=64 epochs=100 patience=10 eval_every_steps=0 loss=cross_entropy</t>
+          <t>lr=0.0001 batch_size=32 epochs=20 patience=20 eval_every_steps=0 loss=cross_entropy label_smoothing=0.1 grad_clip=1.0 tokenizer_mode=pac_interaction pac_token_mode=measured interaction_mode=product band_pe=index spatial_pe=index</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="219" t="inlineStr">
         <is>
-          <t>physionet_mi</t>
+          <t>isruc</t>
         </is>
       </c>
       <c r="B82" s="219" t="inlineStr">
         <is>
-          <t>biot_scratch</t>
+          <t>sparcnet</t>
         </is>
       </c>
       <c r="C82" s="219" t="inlineStr">
@@ -6443,51 +6433,56 @@
       </c>
       <c r="E82" s="219" t="inlineStr">
         <is>
-          <t>[实测 3.20M] balanced_acc per-seed 0:0.3337, 1:0.3273, 2:0.2687</t>
+          <t>[实测 1.38M] cohen_kappa per-seed 0:0.7286, 1:0.7185, 2:0.7565</t>
         </is>
       </c>
       <c r="F82" s="219" t="inlineStr">
         <is>
-          <t>lr=0.0004 batch_size=64 epochs=100 patience=10 eval_every_steps=0 loss=cross_entropy</t>
+          <t>lr=0.001 batch_size=512 epochs=60 patience=15 eval_every_steps=0 loss=cross_entropy label_smoothing=0.1</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="219" t="inlineStr">
         <is>
-          <t>physionet_mi</t>
+          <t>isruc</t>
         </is>
       </c>
       <c r="B83" s="219" t="inlineStr">
         <is>
-          <t>cbramod_pac</t>
+          <t>st_transformer</t>
         </is>
       </c>
       <c r="C83" s="219" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>[0, 1, 2]</t>
         </is>
       </c>
       <c r="D83" s="219" t="inlineStr">
         <is>
-          <t>skipped</t>
+          <t>filled</t>
         </is>
       </c>
       <c r="E83" s="219" t="inlineStr">
         <is>
-          <t>the workbook has no row for this variant</t>
+          <t>[实测 3.42M] cohen_kappa per-seed 0:0.5488, 1:0.3217, 2:0.3076  [seed spread 28% -- mean is a weak summary]</t>
+        </is>
+      </c>
+      <c r="F83" s="219" t="inlineStr">
+        <is>
+          <t>lr=0.001 batch_size=512 epochs=60 patience=15 eval_every_steps=0 loss=cross_entropy label_smoothing=0.1</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="219" t="inlineStr">
         <is>
-          <t>physionet_mi</t>
+          <t>isruc</t>
         </is>
       </c>
       <c r="B84" s="219" t="inlineStr">
         <is>
-          <t>cbramod_pretrained</t>
+          <t>tfm_pretrained</t>
         </is>
       </c>
       <c r="C84" s="219" t="inlineStr">
@@ -6502,12 +6497,12 @@
       </c>
       <c r="E84" s="219" t="inlineStr">
         <is>
-          <t>[实测 46.01M] balanced_acc per-seed 0:0.6035, 1:0.6257, 2:0.6096</t>
+          <t>[实测 1.89M] cohen_kappa per-seed 0:0.7144, 1:0.7084, 2:0.7077</t>
         </is>
       </c>
       <c r="F84" s="219" t="inlineStr">
         <is>
-          <t>lr=0.0001 batch_size=64 epochs=50 patience=0 eval_every_steps=0 loss=cross_entropy label_smoothing=0.1 grad_clip=1.0 multi_lr=True</t>
+          <t>lr=0.001 batch_size=512 epochs=50 patience=10 eval_every_steps=0 loss=cross_entropy label_smoothing=0.1</t>
         </is>
       </c>
     </row>
@@ -6519,7 +6514,7 @@
       </c>
       <c r="B85" s="219" t="inlineStr">
         <is>
-          <t>cbramod_scratch</t>
+          <t>biot_prest16</t>
         </is>
       </c>
       <c r="C85" s="219" t="inlineStr">
@@ -6534,12 +6529,12 @@
       </c>
       <c r="E85" s="219" t="inlineStr">
         <is>
-          <t>[实测 46.01M] balanced_acc per-seed 0:0.5491, 1:0.5562, 2:0.5558</t>
+          <t>[实测 3.19M] balanced_acc per-seed 0:0.4950, 1:0.5034, 2:0.5126</t>
         </is>
       </c>
       <c r="F85" s="219" t="inlineStr">
         <is>
-          <t>lr=0.0001 batch_size=64 epochs=50 patience=0 eval_every_steps=0 loss=cross_entropy label_smoothing=0.1 grad_clip=1.0 multi_lr=True</t>
+          <t>lr=0.0004 batch_size=64 epochs=100 patience=10 eval_every_steps=0 loss=cross_entropy</t>
         </is>
       </c>
     </row>
@@ -6551,7 +6546,7 @@
       </c>
       <c r="B86" s="219" t="inlineStr">
         <is>
-          <t>cnn_transformer</t>
+          <t>biot_scratch</t>
         </is>
       </c>
       <c r="C86" s="219" t="inlineStr">
@@ -6561,12 +6556,17 @@
       </c>
       <c r="D86" s="219" t="inlineStr">
         <is>
-          <t>withheld (rule 3)</t>
+          <t>filled</t>
         </is>
       </c>
       <c r="E86" s="219" t="inlineStr">
         <is>
-          <t>mis-configured seeds [0, 1, 2]: {0: "test Cohen's Kappa 0.0072 is at chance -- the model does not discriminate, whatever the val curve did", 1: 'val peak at first evaluation and never cleared chance (0.2500 vs 0.2500)', 2: "test Cohen's Kappa -0.0006 is at chance -- the model does not discriminate, whatever the val curve did"}; measured balanced_acc 0.2516±0.0027</t>
+          <t>[实测 3.20M] balanced_acc per-seed 0:0.3337, 1:0.3273, 2:0.2687</t>
+        </is>
+      </c>
+      <c r="F86" s="219" t="inlineStr">
+        <is>
+          <t>lr=0.0004 batch_size=64 epochs=100 patience=10 eval_every_steps=0 loss=cross_entropy</t>
         </is>
       </c>
     </row>
@@ -6578,27 +6578,22 @@
       </c>
       <c r="B87" s="219" t="inlineStr">
         <is>
-          <t>contrawr</t>
+          <t>cbramod_pac</t>
         </is>
       </c>
       <c r="C87" s="219" t="inlineStr">
         <is>
-          <t>[0, 1, 2]</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D87" s="219" t="inlineStr">
         <is>
-          <t>filled</t>
+          <t>skipped</t>
         </is>
       </c>
       <c r="E87" s="219" t="inlineStr">
         <is>
-          <t>[实测 1.60M] balanced_acc per-seed 0:0.4898, 1:0.4965, 2:0.4810</t>
-        </is>
-      </c>
-      <c r="F87" s="219" t="inlineStr">
-        <is>
-          <t>lr=0.001 batch_size=64 epochs=100 patience=20 eval_every_steps=0 loss=cross_entropy label_smoothing=0.1</t>
+          <t>the workbook has no row for this variant</t>
         </is>
       </c>
     </row>
@@ -6610,7 +6605,7 @@
       </c>
       <c r="B88" s="219" t="inlineStr">
         <is>
-          <t>eegpt_pretrained</t>
+          <t>cbramod_pretrained</t>
         </is>
       </c>
       <c r="C88" s="219" t="inlineStr">
@@ -6625,12 +6620,12 @@
       </c>
       <c r="E88" s="219" t="inlineStr">
         <is>
-          <t>[实测 25.69M] balanced_acc per-seed 0:0.4233, 1:0.4411, 2:0.3494</t>
+          <t>[实测 46.01M] balanced_acc per-seed 0:0.6035, 1:0.6257, 2:0.6096</t>
         </is>
       </c>
       <c r="F88" s="219" t="inlineStr">
         <is>
-          <t>lr=0.0004 batch_size=32 epochs=100 patience=10 eval_every_steps=0 loss=cross_entropy</t>
+          <t>lr=0.0001 batch_size=64 epochs=50 patience=0 eval_every_steps=0 loss=cross_entropy label_smoothing=0.1 grad_clip=1.0 multi_lr=True</t>
         </is>
       </c>
     </row>
@@ -6642,7 +6637,7 @@
       </c>
       <c r="B89" s="219" t="inlineStr">
         <is>
-          <t>ffcl</t>
+          <t>cbramod_scratch</t>
         </is>
       </c>
       <c r="C89" s="219" t="inlineStr">
@@ -6657,12 +6652,12 @@
       </c>
       <c r="E89" s="219" t="inlineStr">
         <is>
-          <t>[实测 2.43M] balanced_acc per-seed 0:0.4760, 1:0.5004, 2:0.5041</t>
+          <t>[实测 46.01M] balanced_acc per-seed 0:0.5491, 1:0.5562, 2:0.5558</t>
         </is>
       </c>
       <c r="F89" s="219" t="inlineStr">
         <is>
-          <t>lr=0.001 batch_size=64 epochs=100 patience=20 eval_every_steps=0 loss=cross_entropy label_smoothing=0.1</t>
+          <t>lr=0.0001 batch_size=64 epochs=50 patience=0 eval_every_steps=0 loss=cross_entropy label_smoothing=0.1 grad_clip=1.0 multi_lr=True</t>
         </is>
       </c>
     </row>
@@ -6674,7 +6669,7 @@
       </c>
       <c r="B90" s="219" t="inlineStr">
         <is>
-          <t>labram_pretrained</t>
+          <t>cnn_transformer</t>
         </is>
       </c>
       <c r="C90" s="219" t="inlineStr">
@@ -6684,17 +6679,12 @@
       </c>
       <c r="D90" s="219" t="inlineStr">
         <is>
-          <t>filled</t>
+          <t>withheld (rule 3)</t>
         </is>
       </c>
       <c r="E90" s="219" t="inlineStr">
         <is>
-          <t>[实测 5.82M] balanced_acc per-seed 0:0.5352, 1:0.5647, 2:0.5720</t>
-        </is>
-      </c>
-      <c r="F90" s="219" t="inlineStr">
-        <is>
-          <t>stopped_by=patience lr=0.0005 batch_size=64 epochs=50 patience=10 eval_every_steps=0 loss=cross_entropy label_smoothing=0.1 loader_divisor=1.0</t>
+          <t>mis-configured seeds [0, 1, 2]: {0: "test Cohen's Kappa 0.0072 is at chance -- the model does not discriminate, whatever the val curve did", 1: 'val peak at first evaluation and never cleared chance (0.2500 vs 0.2500)', 2: "test Cohen's Kappa -0.0006 is at chance -- the model does not discriminate, whatever the val curve did"}; measured balanced_acc 0.2516±0.0027</t>
         </is>
       </c>
     </row>
@@ -6706,7 +6696,7 @@
       </c>
       <c r="B91" s="219" t="inlineStr">
         <is>
-          <t>labram_scratch</t>
+          <t>contrawr</t>
         </is>
       </c>
       <c r="C91" s="219" t="inlineStr">
@@ -6721,12 +6711,12 @@
       </c>
       <c r="E91" s="219" t="inlineStr">
         <is>
-          <t>[实测 5.82M] balanced_acc per-seed 0:0.3854, 1:0.3635, 2:0.3510</t>
+          <t>[实测 1.60M] balanced_acc per-seed 0:0.4898, 1:0.4965, 2:0.4810</t>
         </is>
       </c>
       <c r="F91" s="219" t="inlineStr">
         <is>
-          <t>stopped_by=patience lr=0.0005 batch_size=64 epochs=50 patience=10 eval_every_steps=0 loss=cross_entropy label_smoothing=0.1 loader_divisor=1.0</t>
+          <t>lr=0.001 batch_size=64 epochs=100 patience=20 eval_every_steps=0 loss=cross_entropy label_smoothing=0.1</t>
         </is>
       </c>
     </row>
@@ -6738,7 +6728,7 @@
       </c>
       <c r="B92" s="219" t="inlineStr">
         <is>
-          <t>paclock_pac</t>
+          <t>diag_lr3e5</t>
         </is>
       </c>
       <c r="C92" s="219" t="inlineStr">
@@ -6753,7 +6743,7 @@
       </c>
       <c r="E92" s="219" t="inlineStr">
         <is>
-          <t>the workbook has no row for this variant</t>
+          <t>no row label for 'diag_lr3e5'</t>
         </is>
       </c>
     </row>
@@ -6765,22 +6755,22 @@
       </c>
       <c r="B93" s="219" t="inlineStr">
         <is>
-          <t>paclock_v2</t>
+          <t>diag_patch200</t>
         </is>
       </c>
       <c r="C93" s="219" t="inlineStr">
         <is>
-          <t>[0, 1, 2]</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D93" s="219" t="inlineStr">
         <is>
-          <t>withheld (rule 3)</t>
+          <t>skipped</t>
         </is>
       </c>
       <c r="E93" s="219" t="inlineStr">
         <is>
-          <t>mis-configured seeds [1, 2]: {1: "test Cohen's Kappa 0.0146 is at chance -- the model does not discriminate, whatever the val curve did", 2: 'val peak at first evaluation and never cleared chance (0.2500 vs 0.2500)'}; measured balanced_acc 0.2830±0.0392</t>
+          <t>no row label for 'diag_patch200'</t>
         </is>
       </c>
     </row>
@@ -6792,27 +6782,22 @@
       </c>
       <c r="B94" s="219" t="inlineStr">
         <is>
-          <t>sparcnet</t>
+          <t>diag_patch200_lr3e5</t>
         </is>
       </c>
       <c r="C94" s="219" t="inlineStr">
         <is>
-          <t>[0, 1, 2]</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D94" s="219" t="inlineStr">
         <is>
-          <t>filled</t>
+          <t>skipped</t>
         </is>
       </c>
       <c r="E94" s="219" t="inlineStr">
         <is>
-          <t>[实测 1.27M] balanced_acc per-seed 0:0.5951, 1:0.5863, 2:0.5901</t>
-        </is>
-      </c>
-      <c r="F94" s="219" t="inlineStr">
-        <is>
-          <t>lr=0.001 batch_size=64 epochs=100 patience=20 eval_every_steps=0 loss=cross_entropy label_smoothing=0.1</t>
+          <t>no row label for 'diag_patch200_lr3e5'</t>
         </is>
       </c>
     </row>
@@ -6824,7 +6809,7 @@
       </c>
       <c r="B95" s="219" t="inlineStr">
         <is>
-          <t>st_transformer</t>
+          <t>eegpt_pretrained</t>
         </is>
       </c>
       <c r="C95" s="219" t="inlineStr">
@@ -6839,12 +6824,12 @@
       </c>
       <c r="E95" s="219" t="inlineStr">
         <is>
-          <t>[实测 3.48M] balanced_acc per-seed 0:0.5757, 1:0.5973, 2:0.6085</t>
+          <t>[实测 25.69M] balanced_acc per-seed 0:0.4233, 1:0.4411, 2:0.3494</t>
         </is>
       </c>
       <c r="F95" s="219" t="inlineStr">
         <is>
-          <t>lr=0.001 batch_size=64 epochs=100 patience=20 eval_every_steps=0 loss=cross_entropy label_smoothing=0.1</t>
+          <t>lr=0.0004 batch_size=32 epochs=100 patience=10 eval_every_steps=0 loss=cross_entropy</t>
         </is>
       </c>
     </row>
@@ -6856,7 +6841,7 @@
       </c>
       <c r="B96" s="219" t="inlineStr">
         <is>
-          <t>tfm_pretrained</t>
+          <t>ffcl</t>
         </is>
       </c>
       <c r="C96" s="219" t="inlineStr">
@@ -6871,24 +6856,24 @@
       </c>
       <c r="E96" s="219" t="inlineStr">
         <is>
-          <t>[实测 1.89M] balanced_acc per-seed 0:0.4524, 1:0.4217, 2:0.4226</t>
+          <t>[实测 2.43M] balanced_acc per-seed 0:0.4760, 1:0.5004, 2:0.5041</t>
         </is>
       </c>
       <c r="F96" s="219" t="inlineStr">
         <is>
-          <t>lr=0.001 batch_size=32 epochs=50 patience=10 eval_every_steps=0 loss=cross_entropy label_smoothing=0.1</t>
+          <t>lr=0.001 batch_size=64 epochs=100 patience=20 eval_every_steps=0 loss=cross_entropy label_smoothing=0.1</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="219" t="inlineStr">
         <is>
-          <t>sleepedf</t>
+          <t>physionet_mi</t>
         </is>
       </c>
       <c r="B97" s="219" t="inlineStr">
         <is>
-          <t>biot_prest16</t>
+          <t>labram_pretrained</t>
         </is>
       </c>
       <c r="C97" s="219" t="inlineStr">
@@ -6903,24 +6888,24 @@
       </c>
       <c r="E97" s="219" t="inlineStr">
         <is>
-          <t>[实测 3.19M] cohen_kappa per-seed 0:0.5804, 1:0.5861, 2:0.6156</t>
+          <t>[实测 5.82M] balanced_acc per-seed 0:0.5352, 1:0.5647, 2:0.5720</t>
         </is>
       </c>
       <c r="F97" s="219" t="inlineStr">
         <is>
-          <t>lr=0.0004 batch_size=64 epochs=40 patience=10 eval_every_steps=0 loss=cross_entropy</t>
+          <t>stopped_by=patience lr=0.0005 batch_size=64 epochs=50 patience=10 eval_every_steps=0 loss=cross_entropy label_smoothing=0.1 loader_divisor=1.0</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="219" t="inlineStr">
         <is>
-          <t>sleepedf</t>
+          <t>physionet_mi</t>
         </is>
       </c>
       <c r="B98" s="219" t="inlineStr">
         <is>
-          <t>biot_scratch</t>
+          <t>labram_scratch</t>
         </is>
       </c>
       <c r="C98" s="219" t="inlineStr">
@@ -6935,24 +6920,24 @@
       </c>
       <c r="E98" s="219" t="inlineStr">
         <is>
-          <t>[实测 3.18M] cohen_kappa per-seed 0:0.6579, 1:0.6341, 2:0.6722</t>
+          <t>[实测 5.82M] balanced_acc per-seed 0:0.3854, 1:0.3635, 2:0.3510</t>
         </is>
       </c>
       <c r="F98" s="219" t="inlineStr">
         <is>
-          <t>lr=0.0004 batch_size=64 epochs=40 patience=10 eval_every_steps=0 loss=cross_entropy</t>
+          <t>stopped_by=patience lr=0.0005 batch_size=64 epochs=50 patience=10 eval_every_steps=0 loss=cross_entropy label_smoothing=0.1 loader_divisor=1.0</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="219" t="inlineStr">
         <is>
-          <t>sleepedf</t>
+          <t>physionet_mi</t>
         </is>
       </c>
       <c r="B99" s="219" t="inlineStr">
         <is>
-          <t>cbramod_pac</t>
+          <t>paclock_pac</t>
         </is>
       </c>
       <c r="C99" s="219" t="inlineStr">
@@ -6974,12 +6959,12 @@
     <row r="100">
       <c r="A100" s="219" t="inlineStr">
         <is>
-          <t>sleepedf</t>
+          <t>physionet_mi</t>
         </is>
       </c>
       <c r="B100" s="219" t="inlineStr">
         <is>
-          <t>cbramod_pretrained</t>
+          <t>sparcnet</t>
         </is>
       </c>
       <c r="C100" s="219" t="inlineStr">
@@ -6994,24 +6979,24 @@
       </c>
       <c r="E100" s="219" t="inlineStr">
         <is>
-          <t>[实测 9.85M] cohen_kappa per-seed 0:0.6658, 1:0.6743, 2:0.6742</t>
+          <t>[实测 1.27M] balanced_acc per-seed 0:0.5951, 1:0.5863, 2:0.5901</t>
         </is>
       </c>
       <c r="F100" s="219" t="inlineStr">
         <is>
-          <t>lr=0.0001 batch_size=64 epochs=50 patience=0 eval_every_steps=0 loss=cross_entropy label_smoothing=0.1 grad_clip=1.0 multi_lr=True</t>
+          <t>lr=0.001 batch_size=64 epochs=100 patience=20 eval_every_steps=0 loss=cross_entropy label_smoothing=0.1</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="219" t="inlineStr">
         <is>
-          <t>sleepedf</t>
+          <t>physionet_mi</t>
         </is>
       </c>
       <c r="B101" s="219" t="inlineStr">
         <is>
-          <t>cbramod_scratch</t>
+          <t>st_transformer</t>
         </is>
       </c>
       <c r="C101" s="219" t="inlineStr">
@@ -7026,24 +7011,24 @@
       </c>
       <c r="E101" s="219" t="inlineStr">
         <is>
-          <t>[实测 9.85M] cohen_kappa per-seed 0:0.6504, 1:0.6561, 2:0.6569</t>
+          <t>[实测 3.48M] balanced_acc per-seed 0:0.5757, 1:0.5973, 2:0.6085</t>
         </is>
       </c>
       <c r="F101" s="219" t="inlineStr">
         <is>
-          <t>lr=0.0001 batch_size=64 epochs=50 patience=0 eval_every_steps=0 loss=cross_entropy label_smoothing=0.1 grad_clip=1.0 multi_lr=True</t>
+          <t>lr=0.001 batch_size=64 epochs=100 patience=20 eval_every_steps=0 loss=cross_entropy label_smoothing=0.1</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="219" t="inlineStr">
         <is>
-          <t>sleepedf</t>
+          <t>physionet_mi</t>
         </is>
       </c>
       <c r="B102" s="219" t="inlineStr">
         <is>
-          <t>cnn_transformer</t>
+          <t>tfm_pretrained</t>
         </is>
       </c>
       <c r="C102" s="219" t="inlineStr">
@@ -7058,12 +7043,12 @@
       </c>
       <c r="E102" s="219" t="inlineStr">
         <is>
-          <t>[实测 3.15M] cohen_kappa per-seed 0:0.6871, 1:0.6614, 2:0.6850</t>
+          <t>[实测 1.89M] balanced_acc per-seed 0:0.4524, 1:0.4217, 2:0.4226</t>
         </is>
       </c>
       <c r="F102" s="219" t="inlineStr">
         <is>
-          <t>lr=0.001 batch_size=512 epochs=60 patience=15 eval_every_steps=0 loss=cross_entropy label_smoothing=0.1</t>
+          <t>lr=0.001 batch_size=32 epochs=50 patience=10 eval_every_steps=0 loss=cross_entropy label_smoothing=0.1</t>
         </is>
       </c>
     </row>
@@ -7075,7 +7060,7 @@
       </c>
       <c r="B103" s="219" t="inlineStr">
         <is>
-          <t>contrawr</t>
+          <t>biot_prest16</t>
         </is>
       </c>
       <c r="C103" s="219" t="inlineStr">
@@ -7090,12 +7075,12 @@
       </c>
       <c r="E103" s="219" t="inlineStr">
         <is>
-          <t>[实测 1.56M] cohen_kappa per-seed 0:0.6752, 1:0.6964, 2:0.7031</t>
+          <t>[实测 3.19M] cohen_kappa per-seed 0:0.5804, 1:0.5861, 2:0.6156</t>
         </is>
       </c>
       <c r="F103" s="219" t="inlineStr">
         <is>
-          <t>lr=0.001 batch_size=512 epochs=60 patience=15 eval_every_steps=0 loss=cross_entropy label_smoothing=0.1</t>
+          <t>lr=0.0004 batch_size=64 epochs=40 patience=10 eval_every_steps=0 loss=cross_entropy</t>
         </is>
       </c>
     </row>
@@ -7107,7 +7092,7 @@
       </c>
       <c r="B104" s="219" t="inlineStr">
         <is>
-          <t>eegpt_pretrained</t>
+          <t>biot_scratch</t>
         </is>
       </c>
       <c r="C104" s="219" t="inlineStr">
@@ -7122,12 +7107,12 @@
       </c>
       <c r="E104" s="219" t="inlineStr">
         <is>
-          <t>[实测 25.69M] cohen_kappa per-seed 0:0.6071, 1:0.5831, 2:0.6031</t>
+          <t>[实测 3.18M] cohen_kappa per-seed 0:0.6579, 1:0.6341, 2:0.6722</t>
         </is>
       </c>
       <c r="F104" s="219" t="inlineStr">
         <is>
-          <t>lr=0.0004 batch_size=32 epochs=40 patience=10 eval_every_steps=200 loss=cross_entropy</t>
+          <t>lr=0.0004 batch_size=64 epochs=40 patience=10 eval_every_steps=0 loss=cross_entropy</t>
         </is>
       </c>
     </row>
@@ -7139,27 +7124,22 @@
       </c>
       <c r="B105" s="219" t="inlineStr">
         <is>
-          <t>ffcl</t>
+          <t>cbramod_pac</t>
         </is>
       </c>
       <c r="C105" s="219" t="inlineStr">
         <is>
-          <t>[0, 1, 2]</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D105" s="219" t="inlineStr">
         <is>
-          <t>filled</t>
+          <t>skipped</t>
         </is>
       </c>
       <c r="E105" s="219" t="inlineStr">
         <is>
-          <t>[实测 2.51M] cohen_kappa per-seed 0:0.6785, 1:0.6730, 2:0.6824</t>
-        </is>
-      </c>
-      <c r="F105" s="219" t="inlineStr">
-        <is>
-          <t>lr=0.001 batch_size=512 epochs=60 patience=15 eval_every_steps=0 loss=cross_entropy label_smoothing=0.1</t>
+          <t>the workbook has no row for this variant</t>
         </is>
       </c>
     </row>
@@ -7171,7 +7151,7 @@
       </c>
       <c r="B106" s="219" t="inlineStr">
         <is>
-          <t>labram_pretrained</t>
+          <t>cbramod_pretrained</t>
         </is>
       </c>
       <c r="C106" s="219" t="inlineStr">
@@ -7186,12 +7166,12 @@
       </c>
       <c r="E106" s="219" t="inlineStr">
         <is>
-          <t>[实测 5.82M] cohen_kappa per-seed 0:0.6082, 1:0.6032, 2:0.6188</t>
+          <t>[实测 9.85M] cohen_kappa per-seed 0:0.6658, 1:0.6743, 2:0.6742</t>
         </is>
       </c>
       <c r="F106" s="219" t="inlineStr">
         <is>
-          <t>stopped_by=patience lr=0.0005 batch_size=64 epochs=50 patience=10 eval_every_steps=0 loss=cross_entropy label_smoothing=0.1 loader_divisor=1.0</t>
+          <t>lr=0.0001 batch_size=64 epochs=50 patience=0 eval_every_steps=0 loss=cross_entropy label_smoothing=0.1 grad_clip=1.0 multi_lr=True</t>
         </is>
       </c>
     </row>
@@ -7203,7 +7183,7 @@
       </c>
       <c r="B107" s="219" t="inlineStr">
         <is>
-          <t>labram_scratch</t>
+          <t>cbramod_scratch</t>
         </is>
       </c>
       <c r="C107" s="219" t="inlineStr">
@@ -7218,12 +7198,12 @@
       </c>
       <c r="E107" s="219" t="inlineStr">
         <is>
-          <t>[实测 5.82M] cohen_kappa per-seed 0:0.6094, 1:0.5932, 2:0.5915</t>
+          <t>[实测 9.85M] cohen_kappa per-seed 0:0.6504, 1:0.6561, 2:0.6569</t>
         </is>
       </c>
       <c r="F107" s="219" t="inlineStr">
         <is>
-          <t>stopped_by=patience lr=0.0005 batch_size=64 epochs=50 patience=10 eval_every_steps=0 loss=cross_entropy label_smoothing=0.1 loader_divisor=1.0</t>
+          <t>lr=0.0001 batch_size=64 epochs=50 patience=0 eval_every_steps=0 loss=cross_entropy label_smoothing=0.1 grad_clip=1.0 multi_lr=True</t>
         </is>
       </c>
     </row>
@@ -7235,22 +7215,27 @@
       </c>
       <c r="B108" s="219" t="inlineStr">
         <is>
-          <t>paclock_pac</t>
+          <t>cnn_transformer</t>
         </is>
       </c>
       <c r="C108" s="219" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>[0, 1, 2]</t>
         </is>
       </c>
       <c r="D108" s="219" t="inlineStr">
         <is>
-          <t>skipped</t>
+          <t>filled</t>
         </is>
       </c>
       <c r="E108" s="219" t="inlineStr">
         <is>
-          <t>the workbook has no row for this variant</t>
+          <t>[实测 3.15M] cohen_kappa per-seed 0:0.6871, 1:0.6614, 2:0.6850</t>
+        </is>
+      </c>
+      <c r="F108" s="219" t="inlineStr">
+        <is>
+          <t>lr=0.001 batch_size=512 epochs=60 patience=15 eval_every_steps=0 loss=cross_entropy label_smoothing=0.1</t>
         </is>
       </c>
     </row>
@@ -7262,7 +7247,7 @@
       </c>
       <c r="B109" s="219" t="inlineStr">
         <is>
-          <t>paclock_v2</t>
+          <t>contrawr</t>
         </is>
       </c>
       <c r="C109" s="219" t="inlineStr">
@@ -7277,12 +7262,12 @@
       </c>
       <c r="E109" s="219" t="inlineStr">
         <is>
-          <t>[实测 1.62M] cohen_kappa per-seed 0:0.6535, 1:0.6427, 2:0.6414</t>
+          <t>[实测 1.56M] cohen_kappa per-seed 0:0.6752, 1:0.6964, 2:0.7031</t>
         </is>
       </c>
       <c r="F109" s="219" t="inlineStr">
         <is>
-          <t>lr=0.0001 batch_size=32 epochs=20 patience=20 eval_every_steps=0 loss=cross_entropy label_smoothing=0.1 grad_clip=1.0 tokenizer_mode=pac_interaction pac_token_mode=measured interaction_mode=product band_pe=index spatial_pe=xyz</t>
+          <t>lr=0.001 batch_size=512 epochs=60 patience=15 eval_every_steps=0 loss=cross_entropy label_smoothing=0.1</t>
         </is>
       </c>
     </row>
@@ -7294,7 +7279,7 @@
       </c>
       <c r="B110" s="219" t="inlineStr">
         <is>
-          <t>sparcnet</t>
+          <t>eegpt_pretrained</t>
         </is>
       </c>
       <c r="C110" s="219" t="inlineStr">
@@ -7309,12 +7294,12 @@
       </c>
       <c r="E110" s="219" t="inlineStr">
         <is>
-          <t>[实测 1.23M] cohen_kappa per-seed 0:0.6662, 1:0.6848, 2:0.6632</t>
+          <t>[实测 25.69M] cohen_kappa per-seed 0:0.6071, 1:0.5831, 2:0.6031</t>
         </is>
       </c>
       <c r="F110" s="219" t="inlineStr">
         <is>
-          <t>lr=0.001 batch_size=512 epochs=60 patience=15 eval_every_steps=0 loss=cross_entropy label_smoothing=0.1</t>
+          <t>lr=0.0004 batch_size=32 epochs=40 patience=10 eval_every_steps=200 loss=cross_entropy</t>
         </is>
       </c>
     </row>
@@ -7326,7 +7311,7 @@
       </c>
       <c r="B111" s="219" t="inlineStr">
         <is>
-          <t>st_transformer</t>
+          <t>ffcl</t>
         </is>
       </c>
       <c r="C111" s="219" t="inlineStr">
@@ -7341,7 +7326,7 @@
       </c>
       <c r="E111" s="219" t="inlineStr">
         <is>
-          <t>[实测 3.41M] cohen_kappa per-seed 0:0.6508, 1:0.6570, 2:0.6581</t>
+          <t>[实测 2.51M] cohen_kappa per-seed 0:0.6785, 1:0.6730, 2:0.6824</t>
         </is>
       </c>
       <c r="F111" s="219" t="inlineStr">
@@ -7358,7 +7343,7 @@
       </c>
       <c r="B112" s="219" t="inlineStr">
         <is>
-          <t>tfm_pretrained</t>
+          <t>labram_pretrained</t>
         </is>
       </c>
       <c r="C112" s="219" t="inlineStr">
@@ -7373,24 +7358,24 @@
       </c>
       <c r="E112" s="219" t="inlineStr">
         <is>
-          <t>[实测 1.89M] cohen_kappa per-seed 0:0.6165, 1:0.6126, 2:0.6122</t>
+          <t>[实测 5.82M] cohen_kappa per-seed 0:0.6082, 1:0.6032, 2:0.6188</t>
         </is>
       </c>
       <c r="F112" s="219" t="inlineStr">
         <is>
-          <t>lr=0.001 batch_size=512 epochs=50 patience=10 eval_every_steps=0 loss=cross_entropy label_smoothing=0.1</t>
+          <t>stopped_by=patience lr=0.0005 batch_size=64 epochs=50 patience=10 eval_every_steps=0 loss=cross_entropy label_smoothing=0.1 loader_divisor=1.0</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="219" t="inlineStr">
         <is>
-          <t>tuab</t>
+          <t>sleepedf</t>
         </is>
       </c>
       <c r="B113" s="219" t="inlineStr">
         <is>
-          <t>biot_prest16</t>
+          <t>labram_scratch</t>
         </is>
       </c>
       <c r="C113" s="219" t="inlineStr">
@@ -7405,83 +7390,83 @@
       </c>
       <c r="E113" s="219" t="inlineStr">
         <is>
-          <t>[实测 3.19M] auroc per-seed 0:0.8750, 1:0.8692, 2:0.8747</t>
+          <t>[实测 5.82M] cohen_kappa per-seed 0:0.6094, 1:0.5932, 2:0.5915</t>
         </is>
       </c>
       <c r="F113" s="219" t="inlineStr">
         <is>
-          <t>lr=0.001 batch_size=512 epochs=100 patience=5 eval_every_steps=0 loss=bce_with_logits</t>
+          <t>stopped_by=patience lr=0.0005 batch_size=64 epochs=50 patience=10 eval_every_steps=0 loss=cross_entropy label_smoothing=0.1 loader_divisor=1.0</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="219" t="inlineStr">
         <is>
-          <t>tuab</t>
+          <t>sleepedf</t>
         </is>
       </c>
       <c r="B114" s="219" t="inlineStr">
         <is>
-          <t>biot_scratch</t>
+          <t>paclock_pac</t>
         </is>
       </c>
       <c r="C114" s="219" t="inlineStr">
         <is>
-          <t>[0, 1, 2]</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D114" s="219" t="inlineStr">
         <is>
-          <t>filled</t>
+          <t>skipped</t>
         </is>
       </c>
       <c r="E114" s="219" t="inlineStr">
         <is>
-          <t>[实测 3.19M] auroc per-seed 0:0.8658, 1:0.8761, 2:0.8665</t>
-        </is>
-      </c>
-      <c r="F114" s="219" t="inlineStr">
-        <is>
-          <t>lr=0.001 batch_size=512 epochs=100 patience=5 eval_every_steps=0 loss=bce_with_logits</t>
+          <t>the workbook has no row for this variant</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="219" t="inlineStr">
         <is>
-          <t>tuab</t>
+          <t>sleepedf</t>
         </is>
       </c>
       <c r="B115" s="219" t="inlineStr">
         <is>
-          <t>cbramod_pac</t>
+          <t>paclock_v2</t>
         </is>
       </c>
       <c r="C115" s="219" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>[0, 1, 2]</t>
         </is>
       </c>
       <c r="D115" s="219" t="inlineStr">
         <is>
-          <t>skipped</t>
+          <t>filled</t>
         </is>
       </c>
       <c r="E115" s="219" t="inlineStr">
         <is>
-          <t>the workbook has no row for this variant</t>
+          <t>[实测 1.62M] cohen_kappa per-seed 0:0.6535, 1:0.6427, 2:0.6414</t>
+        </is>
+      </c>
+      <c r="F115" s="219" t="inlineStr">
+        <is>
+          <t>lr=0.0001 batch_size=32 epochs=20 patience=20 eval_every_steps=0 loss=cross_entropy label_smoothing=0.1 grad_clip=1.0 tokenizer_mode=pac_interaction pac_token_mode=measured interaction_mode=product band_pe=index spatial_pe=xyz</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="219" t="inlineStr">
         <is>
-          <t>tuab</t>
+          <t>sleepedf</t>
         </is>
       </c>
       <c r="B116" s="219" t="inlineStr">
         <is>
-          <t>cbramod_pretrained</t>
+          <t>sparcnet</t>
         </is>
       </c>
       <c r="C116" s="219" t="inlineStr">
@@ -7496,24 +7481,24 @@
       </c>
       <c r="E116" s="219" t="inlineStr">
         <is>
-          <t>[实测 30.65M] auroc per-seed 0:0.8586, 1:0.8584, 2:0.8744</t>
+          <t>[实测 1.23M] cohen_kappa per-seed 0:0.6662, 1:0.6848, 2:0.6632</t>
         </is>
       </c>
       <c r="F116" s="219" t="inlineStr">
         <is>
-          <t>lr=0.0001 batch_size=64 epochs=50 patience=0 eval_every_steps=0 loss=bce_with_logits grad_clip=1.0 select_metric=auroc multi_lr=True</t>
+          <t>lr=0.001 batch_size=512 epochs=60 patience=15 eval_every_steps=0 loss=cross_entropy label_smoothing=0.1</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="219" t="inlineStr">
         <is>
-          <t>tuab</t>
+          <t>sleepedf</t>
         </is>
       </c>
       <c r="B117" s="219" t="inlineStr">
         <is>
-          <t>cbramod_scratch</t>
+          <t>st_transformer</t>
         </is>
       </c>
       <c r="C117" s="219" t="inlineStr">
@@ -7528,24 +7513,24 @@
       </c>
       <c r="E117" s="219" t="inlineStr">
         <is>
-          <t>[实测 30.65M] auroc per-seed 0:0.8727, 1:0.8789, 2:0.8771</t>
+          <t>[实测 3.41M] cohen_kappa per-seed 0:0.6508, 1:0.6570, 2:0.6581</t>
         </is>
       </c>
       <c r="F117" s="219" t="inlineStr">
         <is>
-          <t>lr=0.0001 batch_size=64 epochs=50 patience=0 eval_every_steps=0 loss=bce_with_logits grad_clip=1.0 select_metric=auroc multi_lr=True</t>
+          <t>lr=0.001 batch_size=512 epochs=60 patience=15 eval_every_steps=0 loss=cross_entropy label_smoothing=0.1</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="219" t="inlineStr">
         <is>
-          <t>tuab</t>
+          <t>sleepedf</t>
         </is>
       </c>
       <c r="B118" s="219" t="inlineStr">
         <is>
-          <t>cnn_transformer</t>
+          <t>tfm_pretrained</t>
         </is>
       </c>
       <c r="C118" s="219" t="inlineStr">
@@ -7560,12 +7545,12 @@
       </c>
       <c r="E118" s="219" t="inlineStr">
         <is>
-          <t>[实测 3.15M] auroc per-seed 0:0.8910, 1:0.8972, 2:0.8858</t>
+          <t>[实测 1.89M] cohen_kappa per-seed 0:0.6165, 1:0.6126, 2:0.6122</t>
         </is>
       </c>
       <c r="F118" s="219" t="inlineStr">
         <is>
-          <t>lr=0.001 batch_size=512 epochs=20 patience=8 eval_every_steps=200 loss=bce_with_logits</t>
+          <t>lr=0.001 batch_size=512 epochs=50 patience=10 eval_every_steps=0 loss=cross_entropy label_smoothing=0.1</t>
         </is>
       </c>
     </row>
@@ -7577,7 +7562,7 @@
       </c>
       <c r="B119" s="219" t="inlineStr">
         <is>
-          <t>contrawr</t>
+          <t>biot_prest16</t>
         </is>
       </c>
       <c r="C119" s="219" t="inlineStr">
@@ -7592,12 +7577,12 @@
       </c>
       <c r="E119" s="219" t="inlineStr">
         <is>
-          <t>[实测 1.57M] auroc per-seed 0:0.8849, 1:0.8839, 2:0.8969</t>
+          <t>[实测 3.19M] auroc per-seed 0:0.8750, 1:0.8692, 2:0.8747</t>
         </is>
       </c>
       <c r="F119" s="219" t="inlineStr">
         <is>
-          <t>lr=0.001 batch_size=512 epochs=20 patience=8 eval_every_steps=200 loss=bce_with_logits</t>
+          <t>lr=0.001 batch_size=512 epochs=100 patience=5 eval_every_steps=0 loss=bce_with_logits</t>
         </is>
       </c>
     </row>
@@ -7609,7 +7594,7 @@
       </c>
       <c r="B120" s="219" t="inlineStr">
         <is>
-          <t>eegpt_pretrained</t>
+          <t>biot_scratch</t>
         </is>
       </c>
       <c r="C120" s="219" t="inlineStr">
@@ -7624,12 +7609,12 @@
       </c>
       <c r="E120" s="219" t="inlineStr">
         <is>
-          <t>[实测 25.69M] auroc per-seed 0:0.9046, 1:0.8981, 2:0.9057</t>
+          <t>[实测 3.19M] auroc per-seed 0:0.8658, 1:0.8761, 2:0.8665</t>
         </is>
       </c>
       <c r="F120" s="219" t="inlineStr">
         <is>
-          <t>lr=0.0004 batch_size=32 epochs=40 patience=10 eval_every_steps=200 loss=bce_with_logits</t>
+          <t>lr=0.001 batch_size=512 epochs=100 patience=5 eval_every_steps=0 loss=bce_with_logits</t>
         </is>
       </c>
     </row>
@@ -7641,27 +7626,22 @@
       </c>
       <c r="B121" s="219" t="inlineStr">
         <is>
-          <t>ffcl</t>
+          <t>cbramod_pac</t>
         </is>
       </c>
       <c r="C121" s="219" t="inlineStr">
         <is>
-          <t>[0, 1, 2]</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D121" s="219" t="inlineStr">
         <is>
-          <t>filled</t>
+          <t>skipped</t>
         </is>
       </c>
       <c r="E121" s="219" t="inlineStr">
         <is>
-          <t>[实测 2.46M] auroc per-seed 0:0.8896, 1:0.8929, 2:0.8769</t>
-        </is>
-      </c>
-      <c r="F121" s="219" t="inlineStr">
-        <is>
-          <t>lr=0.001 batch_size=512 epochs=20 patience=8 eval_every_steps=200 loss=bce_with_logits</t>
+          <t>the workbook has no row for this variant</t>
         </is>
       </c>
     </row>
@@ -7673,7 +7653,7 @@
       </c>
       <c r="B122" s="219" t="inlineStr">
         <is>
-          <t>labram_pretrained</t>
+          <t>cbramod_pretrained</t>
         </is>
       </c>
       <c r="C122" s="219" t="inlineStr">
@@ -7688,12 +7668,12 @@
       </c>
       <c r="E122" s="219" t="inlineStr">
         <is>
-          <t>[实测 5.82M] auroc per-seed 0:0.8750, 1:0.8748, 2:0.8811</t>
+          <t>[实测 30.65M] auroc per-seed 0:0.8586, 1:0.8584, 2:0.8744</t>
         </is>
       </c>
       <c r="F122" s="219" t="inlineStr">
         <is>
-          <t>lr=0.0005 batch_size=64 epochs=50 patience=10 eval_every_steps=0 loss=bce_with_logits</t>
+          <t>lr=0.0001 batch_size=64 epochs=50 patience=0 eval_every_steps=0 loss=bce_with_logits grad_clip=1.0 select_metric=auroc multi_lr=True</t>
         </is>
       </c>
     </row>
@@ -7705,7 +7685,7 @@
       </c>
       <c r="B123" s="219" t="inlineStr">
         <is>
-          <t>sparcnet</t>
+          <t>cbramod_scratch</t>
         </is>
       </c>
       <c r="C123" s="219" t="inlineStr">
@@ -7720,12 +7700,12 @@
       </c>
       <c r="E123" s="219" t="inlineStr">
         <is>
-          <t>[实测 1.14M] auroc per-seed 0:0.8836, 1:0.8896, 2:0.8898</t>
+          <t>[实测 30.65M] auroc per-seed 0:0.8727, 1:0.8789, 2:0.8771</t>
         </is>
       </c>
       <c r="F123" s="219" t="inlineStr">
         <is>
-          <t>lr=0.001 batch_size=512 epochs=20 patience=8 eval_every_steps=200 loss=bce_with_logits</t>
+          <t>lr=0.0001 batch_size=64 epochs=50 patience=0 eval_every_steps=0 loss=bce_with_logits grad_clip=1.0 select_metric=auroc multi_lr=True</t>
         </is>
       </c>
     </row>
@@ -7737,7 +7717,7 @@
       </c>
       <c r="B124" s="219" t="inlineStr">
         <is>
-          <t>st_transformer</t>
+          <t>cnn_transformer</t>
         </is>
       </c>
       <c r="C124" s="219" t="inlineStr">
@@ -7752,7 +7732,7 @@
       </c>
       <c r="E124" s="219" t="inlineStr">
         <is>
-          <t>[实测 3.43M] auroc per-seed 0:0.9017, 1:0.8992, 2:0.8908</t>
+          <t>[实测 3.15M] auroc per-seed 0:0.8910, 1:0.8972, 2:0.8858</t>
         </is>
       </c>
       <c r="F124" s="219" t="inlineStr">
@@ -7769,7 +7749,7 @@
       </c>
       <c r="B125" s="219" t="inlineStr">
         <is>
-          <t>tfm_pretrained</t>
+          <t>contrawr</t>
         </is>
       </c>
       <c r="C125" s="219" t="inlineStr">
@@ -7784,51 +7764,56 @@
       </c>
       <c r="E125" s="219" t="inlineStr">
         <is>
-          <t>[实测 1.89M] auroc per-seed 0:0.8785, 1:0.8821, 2:0.8772</t>
+          <t>[实测 1.57M] auroc per-seed 0:0.8849, 1:0.8839, 2:0.8969</t>
         </is>
       </c>
       <c r="F125" s="219" t="inlineStr">
         <is>
-          <t>lr=0.001 batch_size=512 epochs=10 patience=10 eval_every_steps=100 loss=bce_with_logits label_smoothing=0.1</t>
+          <t>lr=0.001 batch_size=512 epochs=20 patience=8 eval_every_steps=200 loss=bce_with_logits</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="219" t="inlineStr">
         <is>
-          <t>tuev</t>
+          <t>tuab</t>
         </is>
       </c>
       <c r="B126" s="219" t="inlineStr">
         <is>
-          <t>biot_hop50</t>
+          <t>eegpt_pretrained</t>
         </is>
       </c>
       <c r="C126" s="219" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>[0, 1, 2]</t>
         </is>
       </c>
       <c r="D126" s="219" t="inlineStr">
         <is>
-          <t>skipped</t>
+          <t>filled</t>
         </is>
       </c>
       <c r="E126" s="219" t="inlineStr">
         <is>
-          <t>the workbook has no row for this variant</t>
+          <t>[实测 25.69M] auroc per-seed 0:0.9046, 1:0.8981, 2:0.9057</t>
+        </is>
+      </c>
+      <c r="F126" s="219" t="inlineStr">
+        <is>
+          <t>lr=0.0004 batch_size=32 epochs=40 patience=10 eval_every_steps=200 loss=bce_with_logits</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="219" t="inlineStr">
         <is>
-          <t>tuev</t>
+          <t>tuab</t>
         </is>
       </c>
       <c r="B127" s="219" t="inlineStr">
         <is>
-          <t>biot_prest16</t>
+          <t>ffcl</t>
         </is>
       </c>
       <c r="C127" s="219" t="inlineStr">
@@ -7843,24 +7828,24 @@
       </c>
       <c r="E127" s="219" t="inlineStr">
         <is>
-          <t>[实测 3.19M] cohen_kappa per-seed 0:0.5005, 1:0.5354, 2:0.5554</t>
+          <t>[实测 2.46M] auroc per-seed 0:0.8896, 1:0.8929, 2:0.8769</t>
         </is>
       </c>
       <c r="F127" s="219" t="inlineStr">
         <is>
-          <t>lr=0.001 batch_size=128 epochs=100 patience=5 eval_every_steps=0 loss=cross_entropy label_smoothing=0.0</t>
+          <t>lr=0.001 batch_size=512 epochs=20 patience=8 eval_every_steps=200 loss=bce_with_logits</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="219" t="inlineStr">
         <is>
-          <t>tuev</t>
+          <t>tuab</t>
         </is>
       </c>
       <c r="B128" s="219" t="inlineStr">
         <is>
-          <t>biot_scratch</t>
+          <t>labram_pretrained</t>
         </is>
       </c>
       <c r="C128" s="219" t="inlineStr">
@@ -7875,120 +7860,140 @@
       </c>
       <c r="E128" s="219" t="inlineStr">
         <is>
-          <t>[实测 3.19M] cohen_kappa per-seed 0:0.5039, 1:0.5425, 2:0.5508</t>
+          <t>[实测 5.82M] auroc per-seed 0:0.8750, 1:0.8748, 2:0.8811</t>
         </is>
       </c>
       <c r="F128" s="219" t="inlineStr">
         <is>
-          <t>lr=0.001 batch_size=128 epochs=100 patience=5 eval_every_steps=0 loss=cross_entropy label_smoothing=0.0</t>
+          <t>lr=0.0005 batch_size=64 epochs=50 patience=10 eval_every_steps=0 loss=bce_with_logits</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="219" t="inlineStr">
         <is>
-          <t>tuev</t>
+          <t>tuab</t>
         </is>
       </c>
       <c r="B129" s="219" t="inlineStr">
         <is>
-          <t>biot_tok100</t>
+          <t>paclock_v2</t>
         </is>
       </c>
       <c r="C129" s="219" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>[0, 1, 2]</t>
         </is>
       </c>
       <c r="D129" s="219" t="inlineStr">
         <is>
-          <t>skipped</t>
+          <t>filled</t>
         </is>
       </c>
       <c r="E129" s="219" t="inlineStr">
         <is>
-          <t>the workbook has no row for this variant</t>
+          <t>[实测 1.62M] auroc per-seed 0:0.8874, 1:0.8818, 2:0.8795</t>
+        </is>
+      </c>
+      <c r="F129" s="219" t="inlineStr">
+        <is>
+          <t>stopped_by=patience lr=0.0001 batch_size=32 epochs=20 patience=20 eval_every_steps=200 loss=bce_with_logits grad_clip=1.0 tokenizer_mode=pac_interaction pac_token_mode=measured interaction_mode=product band_pe=index spatial_pe=xyz</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="219" t="inlineStr">
         <is>
-          <t>tuev</t>
+          <t>tuab</t>
         </is>
       </c>
       <c r="B130" s="219" t="inlineStr">
         <is>
-          <t>cand_base</t>
+          <t>sparcnet</t>
         </is>
       </c>
       <c r="C130" s="219" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>[0, 1, 2]</t>
         </is>
       </c>
       <c r="D130" s="219" t="inlineStr">
         <is>
-          <t>skipped</t>
+          <t>filled</t>
         </is>
       </c>
       <c r="E130" s="219" t="inlineStr">
         <is>
-          <t>the workbook has no row for this variant</t>
+          <t>[实测 1.14M] auroc per-seed 0:0.8836, 1:0.8896, 2:0.8898</t>
+        </is>
+      </c>
+      <c r="F130" s="219" t="inlineStr">
+        <is>
+          <t>lr=0.001 batch_size=512 epochs=20 patience=8 eval_every_steps=200 loss=bce_with_logits</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="219" t="inlineStr">
         <is>
-          <t>tuev</t>
+          <t>tuab</t>
         </is>
       </c>
       <c r="B131" s="219" t="inlineStr">
         <is>
-          <t>cand_dense</t>
+          <t>st_transformer</t>
         </is>
       </c>
       <c r="C131" s="219" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>[0, 1, 2]</t>
         </is>
       </c>
       <c r="D131" s="219" t="inlineStr">
         <is>
-          <t>skipped</t>
+          <t>filled</t>
         </is>
       </c>
       <c r="E131" s="219" t="inlineStr">
         <is>
-          <t>the workbook has no row for this variant</t>
+          <t>[实测 3.43M] auroc per-seed 0:0.9017, 1:0.8992, 2:0.8908</t>
+        </is>
+      </c>
+      <c r="F131" s="219" t="inlineStr">
+        <is>
+          <t>lr=0.001 batch_size=512 epochs=20 patience=8 eval_every_steps=200 loss=bce_with_logits</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="219" t="inlineStr">
         <is>
-          <t>tuev</t>
+          <t>tuab</t>
         </is>
       </c>
       <c r="B132" s="219" t="inlineStr">
         <is>
-          <t>cand_dense_lr1e5</t>
+          <t>tfm_pretrained</t>
         </is>
       </c>
       <c r="C132" s="219" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>[0, 1, 2]</t>
         </is>
       </c>
       <c r="D132" s="219" t="inlineStr">
         <is>
-          <t>skipped</t>
+          <t>filled</t>
         </is>
       </c>
       <c r="E132" s="219" t="inlineStr">
         <is>
-          <t>the workbook has no row for this variant</t>
+          <t>[实测 1.89M] auroc per-seed 0:0.8785, 1:0.8821, 2:0.8772</t>
+        </is>
+      </c>
+      <c r="F132" s="219" t="inlineStr">
+        <is>
+          <t>lr=0.001 batch_size=512 epochs=10 patience=10 eval_every_steps=100 loss=bce_with_logits label_smoothing=0.1</t>
         </is>
       </c>
     </row>
@@ -8000,7 +8005,7 @@
       </c>
       <c r="B133" s="219" t="inlineStr">
         <is>
-          <t>cand_dense_lr3e5</t>
+          <t>biot_hop50</t>
         </is>
       </c>
       <c r="C133" s="219" t="inlineStr">
@@ -8027,22 +8032,27 @@
       </c>
       <c r="B134" s="219" t="inlineStr">
         <is>
-          <t>cand_dense_patch100</t>
+          <t>biot_prest16</t>
         </is>
       </c>
       <c r="C134" s="219" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>[0, 1, 2]</t>
         </is>
       </c>
       <c r="D134" s="219" t="inlineStr">
         <is>
-          <t>skipped</t>
+          <t>filled</t>
         </is>
       </c>
       <c r="E134" s="219" t="inlineStr">
         <is>
-          <t>the workbook has no row for this variant</t>
+          <t>[实测 3.19M] cohen_kappa per-seed 0:0.5005, 1:0.5354, 2:0.5554</t>
+        </is>
+      </c>
+      <c r="F134" s="219" t="inlineStr">
+        <is>
+          <t>lr=0.001 batch_size=128 epochs=100 patience=5 eval_every_steps=0 loss=cross_entropy label_smoothing=0.0</t>
         </is>
       </c>
     </row>
@@ -8054,22 +8064,27 @@
       </c>
       <c r="B135" s="219" t="inlineStr">
         <is>
-          <t>cand_e60_base</t>
+          <t>biot_scratch</t>
         </is>
       </c>
       <c r="C135" s="219" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>[0, 1, 2]</t>
         </is>
       </c>
       <c r="D135" s="219" t="inlineStr">
         <is>
-          <t>skipped</t>
+          <t>filled</t>
         </is>
       </c>
       <c r="E135" s="219" t="inlineStr">
         <is>
-          <t>the workbook has no row for this variant</t>
+          <t>[实测 3.19M] cohen_kappa per-seed 0:0.5039, 1:0.5425, 2:0.5508</t>
+        </is>
+      </c>
+      <c r="F135" s="219" t="inlineStr">
+        <is>
+          <t>lr=0.001 batch_size=128 epochs=100 patience=5 eval_every_steps=0 loss=cross_entropy label_smoothing=0.0</t>
         </is>
       </c>
     </row>
@@ -8081,7 +8096,7 @@
       </c>
       <c r="B136" s="219" t="inlineStr">
         <is>
-          <t>cand_e60_patch100</t>
+          <t>biot_tok100</t>
         </is>
       </c>
       <c r="C136" s="219" t="inlineStr">
@@ -8108,7 +8123,7 @@
       </c>
       <c r="B137" s="219" t="inlineStr">
         <is>
-          <t>cand_e60_size_base</t>
+          <t>cand_base</t>
         </is>
       </c>
       <c r="C137" s="219" t="inlineStr">
@@ -8135,7 +8150,7 @@
       </c>
       <c r="B138" s="219" t="inlineStr">
         <is>
-          <t>cand_e60_size_large</t>
+          <t>cand_dense</t>
         </is>
       </c>
       <c r="C138" s="219" t="inlineStr">
@@ -8162,7 +8177,7 @@
       </c>
       <c r="B139" s="219" t="inlineStr">
         <is>
-          <t>cand_ms</t>
+          <t>cand_dense_lr1e5</t>
         </is>
       </c>
       <c r="C139" s="219" t="inlineStr">
@@ -8189,7 +8204,7 @@
       </c>
       <c r="B140" s="219" t="inlineStr">
         <is>
-          <t>cand_p100_large</t>
+          <t>cand_dense_lr3e5</t>
         </is>
       </c>
       <c r="C140" s="219" t="inlineStr">
@@ -8216,7 +8231,7 @@
       </c>
       <c r="B141" s="219" t="inlineStr">
         <is>
-          <t>cand_p50_win100</t>
+          <t>cand_dense_patch100</t>
         </is>
       </c>
       <c r="C141" s="219" t="inlineStr">
@@ -8243,7 +8258,7 @@
       </c>
       <c r="B142" s="219" t="inlineStr">
         <is>
-          <t>cand_p50_win200</t>
+          <t>cand_e60_base</t>
         </is>
       </c>
       <c r="C142" s="219" t="inlineStr">
@@ -8270,7 +8285,7 @@
       </c>
       <c r="B143" s="219" t="inlineStr">
         <is>
-          <t>cand_pacwin200</t>
+          <t>cand_e60_patch100</t>
         </is>
       </c>
       <c r="C143" s="219" t="inlineStr">
@@ -8297,7 +8312,7 @@
       </c>
       <c r="B144" s="219" t="inlineStr">
         <is>
-          <t>cand_patch100</t>
+          <t>cand_e60_size_base</t>
         </is>
       </c>
       <c r="C144" s="219" t="inlineStr">
@@ -8324,7 +8339,7 @@
       </c>
       <c r="B145" s="219" t="inlineStr">
         <is>
-          <t>cand_patch50</t>
+          <t>cand_e60_size_large</t>
         </is>
       </c>
       <c r="C145" s="219" t="inlineStr">
@@ -8351,7 +8366,7 @@
       </c>
       <c r="B146" s="219" t="inlineStr">
         <is>
-          <t>cbramod_pac</t>
+          <t>cand_ms</t>
         </is>
       </c>
       <c r="C146" s="219" t="inlineStr">
@@ -8378,27 +8393,22 @@
       </c>
       <c r="B147" s="219" t="inlineStr">
         <is>
-          <t>cbramod_pretrained</t>
+          <t>cand_p100_large</t>
         </is>
       </c>
       <c r="C147" s="219" t="inlineStr">
         <is>
-          <t>[0, 1, 2]</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D147" s="219" t="inlineStr">
         <is>
-          <t>filled</t>
+          <t>skipped</t>
         </is>
       </c>
       <c r="E147" s="219" t="inlineStr">
         <is>
-          <t>[实测 17.85M] cohen_kappa per-seed 0:0.6199, 1:0.6566, 2:0.6582</t>
-        </is>
-      </c>
-      <c r="F147" s="219" t="inlineStr">
-        <is>
-          <t>lr=0.0001 batch_size=64 epochs=50 patience=0 eval_every_steps=0 loss=cross_entropy label_smoothing=0.1 grad_clip=1.0 multi_lr=True</t>
+          <t>the workbook has no row for this variant</t>
         </is>
       </c>
     </row>
@@ -8410,27 +8420,22 @@
       </c>
       <c r="B148" s="219" t="inlineStr">
         <is>
-          <t>cbramod_scratch</t>
+          <t>cand_p50_win100</t>
         </is>
       </c>
       <c r="C148" s="219" t="inlineStr">
         <is>
-          <t>[0, 1, 2]</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D148" s="219" t="inlineStr">
         <is>
-          <t>filled</t>
+          <t>skipped</t>
         </is>
       </c>
       <c r="E148" s="219" t="inlineStr">
         <is>
-          <t>[实测 17.85M] cohen_kappa per-seed 0:0.5755, 1:0.5366, 2:0.5794</t>
-        </is>
-      </c>
-      <c r="F148" s="219" t="inlineStr">
-        <is>
-          <t>lr=0.0001 batch_size=64 epochs=50 patience=0 eval_every_steps=0 loss=cross_entropy label_smoothing=0.1 grad_clip=1.0 multi_lr=True</t>
+          <t>the workbook has no row for this variant</t>
         </is>
       </c>
     </row>
@@ -8442,27 +8447,22 @@
       </c>
       <c r="B149" s="219" t="inlineStr">
         <is>
-          <t>cnn_transformer</t>
+          <t>cand_p50_win200</t>
         </is>
       </c>
       <c r="C149" s="219" t="inlineStr">
         <is>
-          <t>[0, 1, 2]</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D149" s="219" t="inlineStr">
         <is>
-          <t>filled</t>
+          <t>skipped</t>
         </is>
       </c>
       <c r="E149" s="219" t="inlineStr">
         <is>
-          <t>[实测 3.16M] cohen_kappa per-seed 0:0.4987, 1:0.2779, 2:0.4527  [seed spread 23% -- mean is a weak summary]</t>
-        </is>
-      </c>
-      <c r="F149" s="219" t="inlineStr">
-        <is>
-          <t>lr=0.001 batch_size=512 epochs=100 patience=15 eval_every_steps=0 loss=cross_entropy label_smoothing=0.1</t>
+          <t>the workbook has no row for this variant</t>
         </is>
       </c>
     </row>
@@ -8474,27 +8474,22 @@
       </c>
       <c r="B150" s="219" t="inlineStr">
         <is>
-          <t>contrawr</t>
+          <t>cand_pacwin200</t>
         </is>
       </c>
       <c r="C150" s="219" t="inlineStr">
         <is>
-          <t>[0, 1, 2]</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D150" s="219" t="inlineStr">
         <is>
-          <t>filled</t>
+          <t>skipped</t>
         </is>
       </c>
       <c r="E150" s="219" t="inlineStr">
         <is>
-          <t>[实测 1.57M] cohen_kappa per-seed 0:0.4410, 1:0.4849, 2:0.2969  [seed spread 20% -- mean is a weak summary]</t>
-        </is>
-      </c>
-      <c r="F150" s="219" t="inlineStr">
-        <is>
-          <t>lr=0.001 batch_size=512 epochs=100 patience=15 eval_every_steps=0 loss=cross_entropy label_smoothing=0.1</t>
+          <t>the workbook has no row for this variant</t>
         </is>
       </c>
     </row>
@@ -8506,27 +8501,22 @@
       </c>
       <c r="B151" s="219" t="inlineStr">
         <is>
-          <t>eegpt_pretrained</t>
+          <t>cand_patch100</t>
         </is>
       </c>
       <c r="C151" s="219" t="inlineStr">
         <is>
-          <t>[0, 1, 2]</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D151" s="219" t="inlineStr">
         <is>
-          <t>filled</t>
+          <t>skipped</t>
         </is>
       </c>
       <c r="E151" s="219" t="inlineStr">
         <is>
-          <t>[实测 25.69M] cohen_kappa per-seed 0:0.5311, 1:0.6095, 2:0.5803</t>
-        </is>
-      </c>
-      <c r="F151" s="219" t="inlineStr">
-        <is>
-          <t>lr=0.0004 batch_size=32 epochs=40 patience=10 eval_every_steps=0 loss=cross_entropy</t>
+          <t>the workbook has no row for this variant</t>
         </is>
       </c>
     </row>
@@ -8538,27 +8528,22 @@
       </c>
       <c r="B152" s="219" t="inlineStr">
         <is>
-          <t>ffcl</t>
+          <t>cand_patch50</t>
         </is>
       </c>
       <c r="C152" s="219" t="inlineStr">
         <is>
-          <t>[0, 1, 2]</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D152" s="219" t="inlineStr">
         <is>
-          <t>filled</t>
+          <t>skipped</t>
         </is>
       </c>
       <c r="E152" s="219" t="inlineStr">
         <is>
-          <t>[实测 2.42M] cohen_kappa per-seed 0:0.5069, 1:0.4432, 2:0.4827</t>
-        </is>
-      </c>
-      <c r="F152" s="219" t="inlineStr">
-        <is>
-          <t>lr=0.001 batch_size=512 epochs=100 patience=15 eval_every_steps=0 loss=cross_entropy label_smoothing=0.1</t>
+          <t>the workbook has no row for this variant</t>
         </is>
       </c>
     </row>
@@ -8570,27 +8555,22 @@
       </c>
       <c r="B153" s="219" t="inlineStr">
         <is>
-          <t>labram_pretrained</t>
+          <t>cbramod_pac</t>
         </is>
       </c>
       <c r="C153" s="219" t="inlineStr">
         <is>
-          <t>[0, 1, 2]</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D153" s="219" t="inlineStr">
         <is>
-          <t>filled</t>
+          <t>skipped</t>
         </is>
       </c>
       <c r="E153" s="219" t="inlineStr">
         <is>
-          <t>[实测 5.82M] cohen_kappa per-seed 0:0.6012, 1:0.5989, 2:0.5951</t>
-        </is>
-      </c>
-      <c r="F153" s="219" t="inlineStr">
-        <is>
-          <t>stopped_by=patience lr=0.0005 batch_size=64 epochs=50 patience=10 eval_every_steps=100 loss=cross_entropy label_smoothing=0.1</t>
+          <t>the workbook has no row for this variant</t>
         </is>
       </c>
     </row>
@@ -8602,27 +8582,22 @@
       </c>
       <c r="B154" s="219" t="inlineStr">
         <is>
-          <t>labram_scratch</t>
+          <t>cbramod_paclockfe</t>
         </is>
       </c>
       <c r="C154" s="219" t="inlineStr">
         <is>
-          <t>[0, 1, 2]</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D154" s="219" t="inlineStr">
         <is>
-          <t>filled</t>
+          <t>skipped</t>
         </is>
       </c>
       <c r="E154" s="219" t="inlineStr">
         <is>
-          <t>[实测 5.82M] cohen_kappa per-seed 0:0.3624, 1:0.3727, 2:0.3801</t>
-        </is>
-      </c>
-      <c r="F154" s="219" t="inlineStr">
-        <is>
-          <t>lr=0.0005 batch_size=64 epochs=50 patience=10 eval_every_steps=0 loss=cross_entropy label_smoothing=0.1</t>
+          <t>no row label for 'cbramod_paclockfe'</t>
         </is>
       </c>
     </row>
@@ -8634,22 +8609,27 @@
       </c>
       <c r="B155" s="219" t="inlineStr">
         <is>
-          <t>paclock</t>
+          <t>cbramod_pretrained</t>
         </is>
       </c>
       <c r="C155" s="219" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>[0, 1, 2]</t>
         </is>
       </c>
       <c r="D155" s="219" t="inlineStr">
         <is>
-          <t>skipped</t>
+          <t>filled</t>
         </is>
       </c>
       <c r="E155" s="219" t="inlineStr">
         <is>
-          <t>no row label for 'paclock'</t>
+          <t>[实测 17.85M] cohen_kappa per-seed 0:0.6199, 1:0.6566, 2:0.6582</t>
+        </is>
+      </c>
+      <c r="F155" s="219" t="inlineStr">
+        <is>
+          <t>lr=0.0001 batch_size=64 epochs=50 patience=0 eval_every_steps=0 loss=cross_entropy label_smoothing=0.1 grad_clip=1.0 multi_lr=True</t>
         </is>
       </c>
     </row>
@@ -8661,22 +8641,27 @@
       </c>
       <c r="B156" s="219" t="inlineStr">
         <is>
-          <t>paclock_pac</t>
+          <t>cbramod_scratch</t>
         </is>
       </c>
       <c r="C156" s="219" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>[0, 1, 2]</t>
         </is>
       </c>
       <c r="D156" s="219" t="inlineStr">
         <is>
-          <t>skipped</t>
+          <t>filled</t>
         </is>
       </c>
       <c r="E156" s="219" t="inlineStr">
         <is>
-          <t>the workbook has no row for this variant</t>
+          <t>[实测 17.85M] cohen_kappa per-seed 0:0.5755, 1:0.5366, 2:0.5794</t>
+        </is>
+      </c>
+      <c r="F156" s="219" t="inlineStr">
+        <is>
+          <t>lr=0.0001 batch_size=64 epochs=50 patience=0 eval_every_steps=0 loss=cross_entropy label_smoothing=0.1 grad_clip=1.0 multi_lr=True</t>
         </is>
       </c>
     </row>
@@ -8688,22 +8673,27 @@
       </c>
       <c r="B157" s="219" t="inlineStr">
         <is>
-          <t>paclock_pilot_frozen</t>
+          <t>cnn_transformer</t>
         </is>
       </c>
       <c r="C157" s="219" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>[0, 1, 2]</t>
         </is>
       </c>
       <c r="D157" s="219" t="inlineStr">
         <is>
-          <t>skipped</t>
+          <t>filled</t>
         </is>
       </c>
       <c r="E157" s="219" t="inlineStr">
         <is>
-          <t>the workbook has no row for this variant</t>
+          <t>[实测 3.16M] cohen_kappa per-seed 0:0.4987, 1:0.2779, 2:0.4527  [seed spread 23% -- mean is a weak summary]</t>
+        </is>
+      </c>
+      <c r="F157" s="219" t="inlineStr">
+        <is>
+          <t>lr=0.001 batch_size=512 epochs=100 patience=15 eval_every_steps=0 loss=cross_entropy label_smoothing=0.1</t>
         </is>
       </c>
     </row>
@@ -8715,22 +8705,27 @@
       </c>
       <c r="B158" s="219" t="inlineStr">
         <is>
-          <t>paclock_pilot_unfiltered</t>
+          <t>contrawr</t>
         </is>
       </c>
       <c r="C158" s="219" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>[0, 1, 2]</t>
         </is>
       </c>
       <c r="D158" s="219" t="inlineStr">
         <is>
-          <t>skipped</t>
+          <t>filled</t>
         </is>
       </c>
       <c r="E158" s="219" t="inlineStr">
         <is>
-          <t>the workbook has no row for this variant</t>
+          <t>[实测 1.57M] cohen_kappa per-seed 0:0.4410, 1:0.4849, 2:0.2969  [seed spread 20% -- mean is a weak summary]</t>
+        </is>
+      </c>
+      <c r="F158" s="219" t="inlineStr">
+        <is>
+          <t>lr=0.001 batch_size=512 epochs=100 patience=15 eval_every_steps=0 loss=cross_entropy label_smoothing=0.1</t>
         </is>
       </c>
     </row>
@@ -8742,7 +8737,7 @@
       </c>
       <c r="B159" s="219" t="inlineStr">
         <is>
-          <t>paclock_v2</t>
+          <t>eegpt_pretrained</t>
         </is>
       </c>
       <c r="C159" s="219" t="inlineStr">
@@ -8757,12 +8752,12 @@
       </c>
       <c r="E159" s="219" t="inlineStr">
         <is>
-          <t>[实测 1.62M] cohen_kappa per-seed 0:0.7278, 1:0.7233, 2:0.6718</t>
+          <t>[实测 25.69M] cohen_kappa per-seed 0:0.5311, 1:0.6095, 2:0.5803</t>
         </is>
       </c>
       <c r="F159" s="219" t="inlineStr">
         <is>
-          <t>lr=0.0001 batch_size=32 epochs=20 patience=20 eval_every_steps=0 loss=cross_entropy label_smoothing=0.1 grad_clip=1.0 tokenizer_mode=pac_interaction pac_token_mode=measured interaction_mode=product band_pe=index spatial_pe=xyz</t>
+          <t>lr=0.0004 batch_size=32 epochs=40 patience=10 eval_every_steps=0 loss=cross_entropy</t>
         </is>
       </c>
     </row>
@@ -8774,7 +8769,7 @@
       </c>
       <c r="B160" s="219" t="inlineStr">
         <is>
-          <t>sparcnet</t>
+          <t>ffcl</t>
         </is>
       </c>
       <c r="C160" s="219" t="inlineStr">
@@ -8789,7 +8784,7 @@
       </c>
       <c r="E160" s="219" t="inlineStr">
         <is>
-          <t>[实测 0.99M] cohen_kappa per-seed 0:0.4665, 1:0.5199, 2:0.4791</t>
+          <t>[实测 2.42M] cohen_kappa per-seed 0:0.5069, 1:0.4432, 2:0.4827</t>
         </is>
       </c>
       <c r="F160" s="219" t="inlineStr">
@@ -8806,7 +8801,7 @@
       </c>
       <c r="B161" s="219" t="inlineStr">
         <is>
-          <t>st_transformer</t>
+          <t>labram_pretrained</t>
         </is>
       </c>
       <c r="C161" s="219" t="inlineStr">
@@ -8821,12 +8816,12 @@
       </c>
       <c r="E161" s="219" t="inlineStr">
         <is>
-          <t>[实测 3.43M] cohen_kappa per-seed 0:0.5139, 1:0.4916, 2:0.4962</t>
+          <t>[实测 5.82M] cohen_kappa per-seed 0:0.6012, 1:0.5989, 2:0.5951</t>
         </is>
       </c>
       <c r="F161" s="219" t="inlineStr">
         <is>
-          <t>lr=0.001 batch_size=512 epochs=100 patience=15 eval_every_steps=0 loss=cross_entropy label_smoothing=0.1</t>
+          <t>stopped_by=patience lr=0.0005 batch_size=64 epochs=50 patience=10 eval_every_steps=100 loss=cross_entropy label_smoothing=0.1</t>
         </is>
       </c>
     </row>
@@ -8838,7 +8833,7 @@
       </c>
       <c r="B162" s="219" t="inlineStr">
         <is>
-          <t>tfm_pretrained</t>
+          <t>labram_scratch</t>
         </is>
       </c>
       <c r="C162" s="219" t="inlineStr">
@@ -8853,88 +8848,78 @@
       </c>
       <c r="E162" s="219" t="inlineStr">
         <is>
-          <t>[实测 1.89M] cohen_kappa per-seed 0:0.6543, 1:0.6299, 2:0.6715</t>
+          <t>[实测 5.82M] cohen_kappa per-seed 0:0.3624, 1:0.3727, 2:0.3801</t>
         </is>
       </c>
       <c r="F162" s="219" t="inlineStr">
         <is>
-          <t>lr=0.001 batch_size=512 epochs=50 patience=10 eval_every_steps=100 loss=cross_entropy label_smoothing=0.1</t>
+          <t>lr=0.0005 batch_size=64 epochs=50 patience=10 eval_every_steps=0 loss=cross_entropy label_smoothing=0.1</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="219" t="inlineStr">
         <is>
-          <t>tusz</t>
+          <t>tuev</t>
         </is>
       </c>
       <c r="B163" s="219" t="inlineStr">
         <is>
-          <t>biot_prest16</t>
+          <t>paclock</t>
         </is>
       </c>
       <c r="C163" s="219" t="inlineStr">
         <is>
-          <t>[0, 1, 2]</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D163" s="219" t="inlineStr">
         <is>
-          <t>filled</t>
+          <t>skipped</t>
         </is>
       </c>
       <c r="E163" s="219" t="inlineStr">
         <is>
-          <t>[实测 3.19M] pr_auc per-seed 0:0.3673, 1:0.3513, 2:0.2951</t>
-        </is>
-      </c>
-      <c r="F163" s="219" t="inlineStr">
-        <is>
-          <t>lr=0.001 batch_size=512 epochs=100 patience=5 eval_every_steps=0 loss=bce_with_logits</t>
+          <t>no row label for 'paclock'</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="219" t="inlineStr">
         <is>
-          <t>tusz</t>
+          <t>tuev</t>
         </is>
       </c>
       <c r="B164" s="219" t="inlineStr">
         <is>
-          <t>biot_scratch</t>
+          <t>paclock_pac</t>
         </is>
       </c>
       <c r="C164" s="219" t="inlineStr">
         <is>
-          <t>[0, 1, 2]</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D164" s="219" t="inlineStr">
         <is>
-          <t>filled</t>
+          <t>skipped</t>
         </is>
       </c>
       <c r="E164" s="219" t="inlineStr">
         <is>
-          <t>[实测 3.19M] pr_auc per-seed 0:0.3186, 1:0.3682, 2:0.3556</t>
-        </is>
-      </c>
-      <c r="F164" s="219" t="inlineStr">
-        <is>
-          <t>lr=0.001 batch_size=512 epochs=100 patience=5 eval_every_steps=0 loss=bce_with_logits</t>
+          <t>the workbook has no row for this variant</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="219" t="inlineStr">
         <is>
-          <t>tusz</t>
+          <t>tuev</t>
         </is>
       </c>
       <c r="B165" s="219" t="inlineStr">
         <is>
-          <t>cbramod_pac</t>
+          <t>paclock_pilot_frozen</t>
         </is>
       </c>
       <c r="C165" s="219" t="inlineStr">
@@ -8956,44 +8941,39 @@
     <row r="166">
       <c r="A166" s="219" t="inlineStr">
         <is>
-          <t>tusz</t>
+          <t>tuev</t>
         </is>
       </c>
       <c r="B166" s="219" t="inlineStr">
         <is>
-          <t>cbramod_pretrained</t>
+          <t>paclock_pilot_unfiltered</t>
         </is>
       </c>
       <c r="C166" s="219" t="inlineStr">
         <is>
-          <t>[0, 1, 2]</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D166" s="219" t="inlineStr">
         <is>
-          <t>filled</t>
+          <t>skipped</t>
         </is>
       </c>
       <c r="E166" s="219" t="inlineStr">
         <is>
-          <t>[实测 30.65M] pr_auc per-seed 0:0.4139, 1:0.4061, 2:0.4831</t>
-        </is>
-      </c>
-      <c r="F166" s="219" t="inlineStr">
-        <is>
-          <t>lr=0.0001 batch_size=64 epochs=50 patience=0 eval_every_steps=0 loss=bce_with_logits grad_clip=1.0 select_metric=auroc multi_lr=True</t>
+          <t>the workbook has no row for this variant</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="219" t="inlineStr">
         <is>
-          <t>tusz</t>
+          <t>tuev</t>
         </is>
       </c>
       <c r="B167" s="219" t="inlineStr">
         <is>
-          <t>cbramod_scratch</t>
+          <t>paclock_v2</t>
         </is>
       </c>
       <c r="C167" s="219" t="inlineStr">
@@ -9008,24 +8988,24 @@
       </c>
       <c r="E167" s="219" t="inlineStr">
         <is>
-          <t>[实测 30.65M] pr_auc per-seed 0:0.4662, 1:0.5401, 2:0.4392</t>
+          <t>[实测 1.62M] cohen_kappa per-seed 0:0.7278, 1:0.7233, 2:0.6718</t>
         </is>
       </c>
       <c r="F167" s="219" t="inlineStr">
         <is>
-          <t>lr=0.0001 batch_size=64 epochs=50 patience=0 eval_every_steps=0 loss=bce_with_logits grad_clip=1.0 select_metric=auroc multi_lr=True</t>
+          <t>lr=0.0001 batch_size=32 epochs=20 patience=20 eval_every_steps=0 loss=cross_entropy label_smoothing=0.1 grad_clip=1.0 tokenizer_mode=pac_interaction pac_token_mode=measured interaction_mode=product band_pe=index spatial_pe=xyz</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="219" t="inlineStr">
         <is>
-          <t>tusz</t>
+          <t>tuev</t>
         </is>
       </c>
       <c r="B168" s="219" t="inlineStr">
         <is>
-          <t>cnn_transformer</t>
+          <t>sparcnet</t>
         </is>
       </c>
       <c r="C168" s="219" t="inlineStr">
@@ -9040,24 +9020,24 @@
       </c>
       <c r="E168" s="219" t="inlineStr">
         <is>
-          <t>[实测 3.15M] pr_auc per-seed 0:0.1493, 1:0.4554, 2:0.5073  [seed spread 43% -- mean is a weak summary]</t>
+          <t>[实测 0.99M] cohen_kappa per-seed 0:0.4665, 1:0.5199, 2:0.4791</t>
         </is>
       </c>
       <c r="F168" s="219" t="inlineStr">
         <is>
-          <t>lr=0.001 batch_size=512 epochs=20 patience=8 eval_every_steps=200 loss=bce_with_logits</t>
+          <t>lr=0.001 batch_size=512 epochs=100 patience=15 eval_every_steps=0 loss=cross_entropy label_smoothing=0.1</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="219" t="inlineStr">
         <is>
-          <t>tusz</t>
+          <t>tuev</t>
         </is>
       </c>
       <c r="B169" s="219" t="inlineStr">
         <is>
-          <t>contrawr</t>
+          <t>st_transformer</t>
         </is>
       </c>
       <c r="C169" s="219" t="inlineStr">
@@ -9072,24 +9052,24 @@
       </c>
       <c r="E169" s="219" t="inlineStr">
         <is>
-          <t>[实测 1.57M] pr_auc per-seed 0:0.5188, 1:0.4849, 2:0.5092</t>
+          <t>[实测 3.43M] cohen_kappa per-seed 0:0.5139, 1:0.4916, 2:0.4962</t>
         </is>
       </c>
       <c r="F169" s="219" t="inlineStr">
         <is>
-          <t>lr=0.001 batch_size=512 epochs=20 patience=8 eval_every_steps=200 loss=bce_with_logits</t>
+          <t>lr=0.001 batch_size=512 epochs=100 patience=15 eval_every_steps=0 loss=cross_entropy label_smoothing=0.1</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="219" t="inlineStr">
         <is>
-          <t>tusz</t>
+          <t>tuev</t>
         </is>
       </c>
       <c r="B170" s="219" t="inlineStr">
         <is>
-          <t>eegpt_pretrained</t>
+          <t>tfm_pretrained</t>
         </is>
       </c>
       <c r="C170" s="219" t="inlineStr">
@@ -9104,12 +9084,12 @@
       </c>
       <c r="E170" s="219" t="inlineStr">
         <is>
-          <t>[实测 25.69M] pr_auc per-seed 0:0.6257, 1:0.5102, 2:0.4980</t>
+          <t>[实测 1.89M] cohen_kappa per-seed 0:0.6543, 1:0.6299, 2:0.6715</t>
         </is>
       </c>
       <c r="F170" s="219" t="inlineStr">
         <is>
-          <t>lr=0.0004 batch_size=32 epochs=40 patience=10 eval_every_steps=500 loss=bce_with_logits</t>
+          <t>lr=0.001 batch_size=512 epochs=50 patience=10 eval_every_steps=100 loss=cross_entropy label_smoothing=0.1</t>
         </is>
       </c>
     </row>
@@ -9121,7 +9101,7 @@
       </c>
       <c r="B171" s="219" t="inlineStr">
         <is>
-          <t>ffcl</t>
+          <t>biot_prest16</t>
         </is>
       </c>
       <c r="C171" s="219" t="inlineStr">
@@ -9136,12 +9116,12 @@
       </c>
       <c r="E171" s="219" t="inlineStr">
         <is>
-          <t>[实测 2.46M] pr_auc per-seed 0:0.5511, 1:0.5126, 2:0.5709</t>
+          <t>[实测 3.19M] pr_auc per-seed 0:0.3673, 1:0.3513, 2:0.2951</t>
         </is>
       </c>
       <c r="F171" s="219" t="inlineStr">
         <is>
-          <t>lr=0.001 batch_size=512 epochs=20 patience=8 eval_every_steps=200 loss=bce_with_logits</t>
+          <t>lr=0.001 batch_size=512 epochs=100 patience=5 eval_every_steps=0 loss=bce_with_logits</t>
         </is>
       </c>
     </row>
@@ -9153,7 +9133,7 @@
       </c>
       <c r="B172" s="219" t="inlineStr">
         <is>
-          <t>labram_pretrained</t>
+          <t>biot_scratch</t>
         </is>
       </c>
       <c r="C172" s="219" t="inlineStr">
@@ -9168,12 +9148,12 @@
       </c>
       <c r="E172" s="219" t="inlineStr">
         <is>
-          <t>[实测 5.82M] pr_auc per-seed 0:0.4828, 1:0.5186, 2:0.4249</t>
+          <t>[实测 3.19M] pr_auc per-seed 0:0.3186, 1:0.3682, 2:0.3556</t>
         </is>
       </c>
       <c r="F172" s="219" t="inlineStr">
         <is>
-          <t>lr=0.0005 batch_size=64 epochs=50 patience=10 eval_every_steps=100 loss=bce_with_logits</t>
+          <t>lr=0.001 batch_size=512 epochs=100 patience=5 eval_every_steps=0 loss=bce_with_logits</t>
         </is>
       </c>
     </row>
@@ -9185,27 +9165,22 @@
       </c>
       <c r="B173" s="219" t="inlineStr">
         <is>
-          <t>labram_scratch</t>
+          <t>cbramod_pac</t>
         </is>
       </c>
       <c r="C173" s="219" t="inlineStr">
         <is>
-          <t>[0, 1, 2]</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D173" s="219" t="inlineStr">
         <is>
-          <t>filled</t>
+          <t>skipped</t>
         </is>
       </c>
       <c r="E173" s="219" t="inlineStr">
         <is>
-          <t>[实测 5.82M] pr_auc per-seed 0:0.4201, 1:0.5036, 2:0.5020</t>
-        </is>
-      </c>
-      <c r="F173" s="219" t="inlineStr">
-        <is>
-          <t>stopped_by=patience lr=0.0005 batch_size=64 epochs=50 patience=10 eval_every_steps=0 loss=bce_with_logits</t>
+          <t>the workbook has no row for this variant</t>
         </is>
       </c>
     </row>
@@ -9217,22 +9192,27 @@
       </c>
       <c r="B174" s="219" t="inlineStr">
         <is>
-          <t>paclock_pac</t>
+          <t>cbramod_pretrained</t>
         </is>
       </c>
       <c r="C174" s="219" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>[0, 1, 2]</t>
         </is>
       </c>
       <c r="D174" s="219" t="inlineStr">
         <is>
-          <t>skipped</t>
+          <t>filled</t>
         </is>
       </c>
       <c r="E174" s="219" t="inlineStr">
         <is>
-          <t>the workbook has no row for this variant</t>
+          <t>[实测 30.65M] pr_auc per-seed 0:0.4139, 1:0.4061, 2:0.4831</t>
+        </is>
+      </c>
+      <c r="F174" s="219" t="inlineStr">
+        <is>
+          <t>lr=0.0001 batch_size=64 epochs=50 patience=0 eval_every_steps=0 loss=bce_with_logits grad_clip=1.0 select_metric=auroc multi_lr=True</t>
         </is>
       </c>
     </row>
@@ -9244,22 +9224,27 @@
       </c>
       <c r="B175" s="219" t="inlineStr">
         <is>
-          <t>paclock_v2</t>
+          <t>cbramod_scratch</t>
         </is>
       </c>
       <c r="C175" s="219" t="inlineStr">
         <is>
-          <t>[0]</t>
+          <t>[0, 1, 2]</t>
         </is>
       </c>
       <c r="D175" s="219" t="inlineStr">
         <is>
-          <t>withheld (rule 4)</t>
+          <t>filled</t>
         </is>
       </c>
       <c r="E175" s="219" t="inlineStr">
         <is>
-          <t>only 1 seeds; primary pr_auc 0.6248</t>
+          <t>[实测 30.65M] pr_auc per-seed 0:0.4662, 1:0.5401, 2:0.4392</t>
+        </is>
+      </c>
+      <c r="F175" s="219" t="inlineStr">
+        <is>
+          <t>lr=0.0001 batch_size=64 epochs=50 patience=0 eval_every_steps=0 loss=bce_with_logits grad_clip=1.0 select_metric=auroc multi_lr=True</t>
         </is>
       </c>
     </row>
@@ -9271,7 +9256,7 @@
       </c>
       <c r="B176" s="219" t="inlineStr">
         <is>
-          <t>sparcnet</t>
+          <t>cnn_transformer</t>
         </is>
       </c>
       <c r="C176" s="219" t="inlineStr">
@@ -9286,7 +9271,7 @@
       </c>
       <c r="E176" s="219" t="inlineStr">
         <is>
-          <t>[实测 1.14M] pr_auc per-seed 0:0.4795, 1:0.5046, 2:0.5218</t>
+          <t>[实测 3.15M] pr_auc per-seed 0:0.1493, 1:0.4554, 2:0.5073  [seed spread 43% -- mean is a weak summary]</t>
         </is>
       </c>
       <c r="F176" s="219" t="inlineStr">
@@ -9303,7 +9288,7 @@
       </c>
       <c r="B177" s="219" t="inlineStr">
         <is>
-          <t>st_transformer</t>
+          <t>contrawr</t>
         </is>
       </c>
       <c r="C177" s="219" t="inlineStr">
@@ -9318,7 +9303,7 @@
       </c>
       <c r="E177" s="219" t="inlineStr">
         <is>
-          <t>[实测 3.43M] pr_auc per-seed 0:0.3318, 1:0.3515, 2:0.3933</t>
+          <t>[实测 1.57M] pr_auc per-seed 0:0.5188, 1:0.4849, 2:0.5092</t>
         </is>
       </c>
       <c r="F177" s="219" t="inlineStr">
@@ -9335,25 +9320,276 @@
       </c>
       <c r="B178" s="219" t="inlineStr">
         <is>
+          <t>eegpt_pretrained</t>
+        </is>
+      </c>
+      <c r="C178" s="219" t="inlineStr">
+        <is>
+          <t>[0, 1, 2]</t>
+        </is>
+      </c>
+      <c r="D178" s="219" t="inlineStr">
+        <is>
+          <t>filled</t>
+        </is>
+      </c>
+      <c r="E178" s="219" t="inlineStr">
+        <is>
+          <t>[实测 25.69M] pr_auc per-seed 0:0.6257, 1:0.5102, 2:0.4980</t>
+        </is>
+      </c>
+      <c r="F178" s="219" t="inlineStr">
+        <is>
+          <t>lr=0.0004 batch_size=32 epochs=40 patience=10 eval_every_steps=500 loss=bce_with_logits</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="219" t="inlineStr">
+        <is>
+          <t>tusz</t>
+        </is>
+      </c>
+      <c r="B179" s="219" t="inlineStr">
+        <is>
+          <t>ffcl</t>
+        </is>
+      </c>
+      <c r="C179" s="219" t="inlineStr">
+        <is>
+          <t>[0, 1, 2]</t>
+        </is>
+      </c>
+      <c r="D179" s="219" t="inlineStr">
+        <is>
+          <t>filled</t>
+        </is>
+      </c>
+      <c r="E179" s="219" t="inlineStr">
+        <is>
+          <t>[实测 2.46M] pr_auc per-seed 0:0.5511, 1:0.5126, 2:0.5709</t>
+        </is>
+      </c>
+      <c r="F179" s="219" t="inlineStr">
+        <is>
+          <t>lr=0.001 batch_size=512 epochs=20 patience=8 eval_every_steps=200 loss=bce_with_logits</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="219" t="inlineStr">
+        <is>
+          <t>tusz</t>
+        </is>
+      </c>
+      <c r="B180" s="219" t="inlineStr">
+        <is>
+          <t>labram_pretrained</t>
+        </is>
+      </c>
+      <c r="C180" s="219" t="inlineStr">
+        <is>
+          <t>[0, 1, 2]</t>
+        </is>
+      </c>
+      <c r="D180" s="219" t="inlineStr">
+        <is>
+          <t>filled</t>
+        </is>
+      </c>
+      <c r="E180" s="219" t="inlineStr">
+        <is>
+          <t>[实测 5.82M] pr_auc per-seed 0:0.4828, 1:0.5186, 2:0.4249</t>
+        </is>
+      </c>
+      <c r="F180" s="219" t="inlineStr">
+        <is>
+          <t>lr=0.0005 batch_size=64 epochs=50 patience=10 eval_every_steps=100 loss=bce_with_logits</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="219" t="inlineStr">
+        <is>
+          <t>tusz</t>
+        </is>
+      </c>
+      <c r="B181" s="219" t="inlineStr">
+        <is>
+          <t>labram_scratch</t>
+        </is>
+      </c>
+      <c r="C181" s="219" t="inlineStr">
+        <is>
+          <t>[0, 1, 2]</t>
+        </is>
+      </c>
+      <c r="D181" s="219" t="inlineStr">
+        <is>
+          <t>filled</t>
+        </is>
+      </c>
+      <c r="E181" s="219" t="inlineStr">
+        <is>
+          <t>[实测 5.82M] pr_auc per-seed 0:0.4201, 1:0.5036, 2:0.5020</t>
+        </is>
+      </c>
+      <c r="F181" s="219" t="inlineStr">
+        <is>
+          <t>stopped_by=patience lr=0.0005 batch_size=64 epochs=50 patience=10 eval_every_steps=0 loss=bce_with_logits</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="219" t="inlineStr">
+        <is>
+          <t>tusz</t>
+        </is>
+      </c>
+      <c r="B182" s="219" t="inlineStr">
+        <is>
+          <t>paclock_pac</t>
+        </is>
+      </c>
+      <c r="C182" s="219" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D182" s="219" t="inlineStr">
+        <is>
+          <t>skipped</t>
+        </is>
+      </c>
+      <c r="E182" s="219" t="inlineStr">
+        <is>
+          <t>the workbook has no row for this variant</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="219" t="inlineStr">
+        <is>
+          <t>tusz</t>
+        </is>
+      </c>
+      <c r="B183" s="219" t="inlineStr">
+        <is>
+          <t>paclock_v2</t>
+        </is>
+      </c>
+      <c r="C183" s="219" t="inlineStr">
+        <is>
+          <t>[0, 1, 2]</t>
+        </is>
+      </c>
+      <c r="D183" s="219" t="inlineStr">
+        <is>
+          <t>filled</t>
+        </is>
+      </c>
+      <c r="E183" s="219" t="inlineStr">
+        <is>
+          <t>[实测 1.62M] pr_auc per-seed 0:0.6248, 1:0.4975, 2:0.6424</t>
+        </is>
+      </c>
+      <c r="F183" s="219" t="inlineStr">
+        <is>
+          <t>stopped_by=patience lr=0.0001 batch_size=32 epochs=20 patience=20 eval_every_steps=200 loss=bce_with_logits grad_clip=1.0 tokenizer_mode=pac_interaction pac_token_mode=measured interaction_mode=product band_pe=index spatial_pe=xyz</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="219" t="inlineStr">
+        <is>
+          <t>tusz</t>
+        </is>
+      </c>
+      <c r="B184" s="219" t="inlineStr">
+        <is>
+          <t>sparcnet</t>
+        </is>
+      </c>
+      <c r="C184" s="219" t="inlineStr">
+        <is>
+          <t>[0, 1, 2]</t>
+        </is>
+      </c>
+      <c r="D184" s="219" t="inlineStr">
+        <is>
+          <t>filled</t>
+        </is>
+      </c>
+      <c r="E184" s="219" t="inlineStr">
+        <is>
+          <t>[实测 1.14M] pr_auc per-seed 0:0.4795, 1:0.5046, 2:0.5218</t>
+        </is>
+      </c>
+      <c r="F184" s="219" t="inlineStr">
+        <is>
+          <t>lr=0.001 batch_size=512 epochs=20 patience=8 eval_every_steps=200 loss=bce_with_logits</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="219" t="inlineStr">
+        <is>
+          <t>tusz</t>
+        </is>
+      </c>
+      <c r="B185" s="219" t="inlineStr">
+        <is>
+          <t>st_transformer</t>
+        </is>
+      </c>
+      <c r="C185" s="219" t="inlineStr">
+        <is>
+          <t>[0, 1, 2]</t>
+        </is>
+      </c>
+      <c r="D185" s="219" t="inlineStr">
+        <is>
+          <t>filled</t>
+        </is>
+      </c>
+      <c r="E185" s="219" t="inlineStr">
+        <is>
+          <t>[实测 3.43M] pr_auc per-seed 0:0.3318, 1:0.3515, 2:0.3933</t>
+        </is>
+      </c>
+      <c r="F185" s="219" t="inlineStr">
+        <is>
+          <t>lr=0.001 batch_size=512 epochs=20 patience=8 eval_every_steps=200 loss=bce_with_logits</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="219" t="inlineStr">
+        <is>
+          <t>tusz</t>
+        </is>
+      </c>
+      <c r="B186" s="219" t="inlineStr">
+        <is>
           <t>tfm_pretrained</t>
         </is>
       </c>
-      <c r="C178" s="219" t="inlineStr">
+      <c r="C186" s="219" t="inlineStr">
         <is>
           <t>[0, 1, 2]</t>
         </is>
       </c>
-      <c r="D178" s="219" t="inlineStr">
+      <c r="D186" s="219" t="inlineStr">
         <is>
           <t>filled</t>
         </is>
       </c>
-      <c r="E178" s="219" t="inlineStr">
+      <c r="E186" s="219" t="inlineStr">
         <is>
           <t>[实测 1.89M] pr_auc per-seed 0:0.3348, 1:0.3686, 2:0.3389</t>
         </is>
       </c>
-      <c r="F178" s="219" t="inlineStr">
+      <c r="F186" s="219" t="inlineStr">
         <is>
           <t>lr=0.001 batch_size=512 epochs=5 patience=10 eval_every_steps=100 loss=bce_with_logits label_smoothing=0.1</t>
         </is>
@@ -9379,6 +9615,7 @@
     <col width="17" customWidth="1" style="220" min="4" max="4"/>
     <col width="17" customWidth="1" style="219" min="5" max="7"/>
     <col width="17" customWidth="1" style="220" min="6" max="6"/>
+    <col width="17" customWidth="1" style="220" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1" s="220">
@@ -9391,7 +9628,8 @@
       <c r="C1" s="228" t="n"/>
       <c r="D1" s="228" t="n"/>
       <c r="E1" s="228" t="n"/>
-      <c r="F1" s="229" t="n"/>
+      <c r="F1" s="228" t="n"/>
+      <c r="G1" s="229" t="n"/>
     </row>
     <row r="2" ht="22" customHeight="1" s="220">
       <c r="A2" s="267" t="inlineStr">
@@ -9399,7 +9637,7 @@
           <t>主指标：AUROC</t>
         </is>
       </c>
-      <c r="F2" s="231" t="n"/>
+      <c r="G2" s="231" t="n"/>
     </row>
     <row r="3" ht="8" customHeight="1" s="220">
       <c r="A3" s="268" t="n"/>
@@ -9408,391 +9646,470 @@
       <c r="D3" s="268" t="n"/>
       <c r="E3" s="268" t="n"/>
       <c r="F3" s="268" t="n"/>
-      <c r="G3" s="269" t="n"/>
+      <c r="G3" s="268" t="n"/>
     </row>
     <row r="4" ht="28" customHeight="1" s="220">
-      <c r="A4" s="270" t="inlineStr">
+      <c r="A4" s="269" t="inlineStr">
         <is>
           <t>分组</t>
         </is>
       </c>
-      <c r="B4" s="270" t="inlineStr">
+      <c r="B4" s="269" t="inlineStr">
         <is>
           <t>模型</t>
         </is>
       </c>
-      <c r="C4" s="270" t="inlineStr">
+      <c r="C4" s="269" t="inlineStr">
         <is>
           <t>参数量 (M)</t>
         </is>
       </c>
-      <c r="D4" s="270" t="inlineStr">
+      <c r="D4" s="269" t="inlineStr">
         <is>
           <t>Balanced Acc</t>
         </is>
       </c>
-      <c r="E4" s="270" t="inlineStr">
+      <c r="E4" s="269" t="inlineStr">
         <is>
           <t>AUC-PR</t>
         </is>
       </c>
-      <c r="F4" s="270" t="inlineStr">
+      <c r="F4" s="269" t="inlineStr">
         <is>
           <t>AUROC</t>
         </is>
       </c>
+      <c r="G4" s="269" t="inlineStr">
+        <is>
+          <t>ΔAUROC vs PACLock</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="20" customHeight="1" s="220">
-      <c r="A5" s="271" t="inlineStr">
+      <c r="A5" s="270" t="inlineStr">
         <is>
           <t>A 轻量监督基线</t>
         </is>
       </c>
-      <c r="B5" s="272" t="inlineStr">
+      <c r="B5" s="271" t="inlineStr">
         <is>
           <t>SPaRCNet</t>
         </is>
       </c>
-      <c r="C5" s="273" t="n">
+      <c r="C5" s="272" t="n">
         <v>1.14</v>
       </c>
-      <c r="D5" s="274" t="inlineStr">
+      <c r="D5" s="273" t="inlineStr">
         <is>
           <t>0.7923±0.0093</t>
         </is>
       </c>
-      <c r="E5" s="275" t="inlineStr">
+      <c r="E5" s="274" t="inlineStr">
         <is>
           <t>0.8874±0.0025</t>
         </is>
       </c>
-      <c r="F5" s="275" t="inlineStr">
+      <c r="F5" s="274" t="inlineStr">
         <is>
           <t>0.8877±0.0029</t>
         </is>
       </c>
+      <c r="G5" s="274" t="inlineStr">
+        <is>
+          <t>+0.0048</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="20" customHeight="1" s="220">
-      <c r="A6" s="276" t="n"/>
-      <c r="B6" s="277" t="inlineStr">
+      <c r="A6" s="275" t="n"/>
+      <c r="B6" s="276" t="inlineStr">
         <is>
           <t>ContraWR</t>
         </is>
       </c>
-      <c r="C6" s="278" t="n">
+      <c r="C6" s="277" t="n">
         <v>1.57</v>
       </c>
-      <c r="D6" s="279" t="inlineStr">
+      <c r="D6" s="278" t="inlineStr">
         <is>
           <t>0.7895±0.0012</t>
         </is>
       </c>
-      <c r="E6" s="280" t="inlineStr">
+      <c r="E6" s="279" t="inlineStr">
         <is>
           <t>0.8893±0.0062</t>
         </is>
       </c>
-      <c r="F6" s="280" t="inlineStr">
+      <c r="F6" s="279" t="inlineStr">
         <is>
           <t>0.8886±0.0059</t>
         </is>
       </c>
+      <c r="G6" s="279" t="inlineStr">
+        <is>
+          <t>+0.0057</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="20" customHeight="1" s="220">
-      <c r="A7" s="276" t="n"/>
-      <c r="B7" s="277" t="inlineStr">
+      <c r="A7" s="275" t="n"/>
+      <c r="B7" s="276" t="inlineStr">
         <is>
           <t>CNN-Transformer</t>
         </is>
       </c>
-      <c r="C7" s="278" t="n">
+      <c r="C7" s="277" t="n">
         <v>3.15</v>
       </c>
-      <c r="D7" s="279" t="inlineStr">
+      <c r="D7" s="278" t="inlineStr">
         <is>
           <t>0.7816±0.0320</t>
         </is>
       </c>
-      <c r="E7" s="280" t="inlineStr">
+      <c r="E7" s="279" t="inlineStr">
         <is>
           <t>0.8876±0.0104</t>
         </is>
       </c>
-      <c r="F7" s="280" t="inlineStr">
+      <c r="F7" s="279" t="inlineStr">
         <is>
           <t>0.8913±0.0047</t>
         </is>
       </c>
+      <c r="G7" s="279" t="inlineStr">
+        <is>
+          <t>+0.0084</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="20" customHeight="1" s="220">
-      <c r="A8" s="276" t="n"/>
-      <c r="B8" s="277" t="inlineStr">
+      <c r="A8" s="275" t="n"/>
+      <c r="B8" s="276" t="inlineStr">
         <is>
           <t>FFCL</t>
         </is>
       </c>
-      <c r="C8" s="278" t="n">
+      <c r="C8" s="277" t="n">
         <v>2.46</v>
       </c>
-      <c r="D8" s="279" t="inlineStr">
+      <c r="D8" s="278" t="inlineStr">
         <is>
           <t>0.7648±0.0330</t>
         </is>
       </c>
-      <c r="E8" s="280" t="inlineStr">
+      <c r="E8" s="279" t="inlineStr">
         <is>
           <t>0.8868±0.0050</t>
         </is>
       </c>
-      <c r="F8" s="280" t="inlineStr">
+      <c r="F8" s="279" t="inlineStr">
         <is>
           <t>0.8865±0.0069</t>
         </is>
       </c>
+      <c r="G8" s="279" t="inlineStr">
+        <is>
+          <t>+0.0036</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="20" customHeight="1" s="220">
-      <c r="A9" s="276" t="n"/>
-      <c r="B9" s="277" t="inlineStr">
+      <c r="A9" s="275" t="n"/>
+      <c r="B9" s="276" t="inlineStr">
         <is>
           <t>ST-Transformer</t>
         </is>
       </c>
-      <c r="C9" s="278" t="n">
+      <c r="C9" s="277" t="n">
         <v>3.43</v>
       </c>
-      <c r="D9" s="279" t="inlineStr">
+      <c r="D9" s="278" t="inlineStr">
         <is>
           <t>0.8198±0.0036</t>
         </is>
       </c>
-      <c r="E9" s="280" t="inlineStr">
+      <c r="E9" s="279" t="inlineStr">
         <is>
           <t>0.9022±0.0029</t>
         </is>
       </c>
-      <c r="F9" s="280" t="inlineStr">
+      <c r="F9" s="279" t="inlineStr">
         <is>
           <t>0.8972±0.0046</t>
         </is>
       </c>
+      <c r="G9" s="279" t="inlineStr">
+        <is>
+          <t>+0.0143</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="20" customHeight="1" s="220">
-      <c r="A10" s="271" t="inlineStr">
+      <c r="A10" s="270" t="inlineStr">
         <is>
           <t>B FM · 官方预训练权重</t>
         </is>
       </c>
-      <c r="B10" s="281" t="inlineStr">
+      <c r="B10" s="280" t="inlineStr">
         <is>
           <t>BIOT (pretrained)</t>
         </is>
       </c>
-      <c r="C10" s="282" t="n">
+      <c r="C10" s="281" t="n">
         <v>3.19</v>
       </c>
-      <c r="D10" s="283" t="inlineStr">
+      <c r="D10" s="282" t="inlineStr">
         <is>
           <t>0.7950±0.0026</t>
         </is>
       </c>
-      <c r="E10" s="284" t="inlineStr">
+      <c r="E10" s="283" t="inlineStr">
         <is>
           <t>0.8704±0.0044</t>
         </is>
       </c>
-      <c r="F10" s="284" t="inlineStr">
+      <c r="F10" s="283" t="inlineStr">
         <is>
           <t>0.8730±0.0026</t>
         </is>
       </c>
+      <c r="G10" s="283" t="inlineStr">
+        <is>
+          <t>-0.0099</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="20" customHeight="1" s="220">
-      <c r="A11" s="276" t="n"/>
-      <c r="B11" s="277" t="inlineStr">
+      <c r="A11" s="275" t="n"/>
+      <c r="B11" s="276" t="inlineStr">
         <is>
           <t>LaBraM-Base (pretrained)</t>
         </is>
       </c>
-      <c r="C11" s="278" t="n">
+      <c r="C11" s="277" t="n">
         <v>5.82</v>
       </c>
-      <c r="D11" s="279" t="inlineStr">
+      <c r="D11" s="278" t="inlineStr">
         <is>
           <t>0.7959±0.0016</t>
         </is>
       </c>
-      <c r="E11" s="280" t="inlineStr">
+      <c r="E11" s="279" t="inlineStr">
         <is>
           <t>0.8586±0.0126</t>
         </is>
       </c>
-      <c r="F11" s="280" t="inlineStr">
+      <c r="F11" s="279" t="inlineStr">
         <is>
           <t>0.8770±0.0029</t>
         </is>
       </c>
+      <c r="G11" s="279" t="inlineStr">
+        <is>
+          <t>-0.0059</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="20" customHeight="1" s="220">
-      <c r="A12" s="276" t="n"/>
-      <c r="B12" s="277" t="inlineStr">
+      <c r="A12" s="275" t="n"/>
+      <c r="B12" s="276" t="inlineStr">
         <is>
           <t>CBraMod (pretrained)</t>
         </is>
       </c>
-      <c r="C12" s="278" t="n">
+      <c r="C12" s="277" t="n">
         <v>30.65</v>
       </c>
-      <c r="D12" s="279" t="inlineStr">
+      <c r="D12" s="278" t="inlineStr">
         <is>
           <t>0.7869±0.0104</t>
         </is>
       </c>
-      <c r="E12" s="280" t="inlineStr">
+      <c r="E12" s="279" t="inlineStr">
         <is>
           <t>0.8662±0.0049</t>
         </is>
       </c>
-      <c r="F12" s="280" t="inlineStr">
+      <c r="F12" s="279" t="inlineStr">
         <is>
           <t>0.8638±0.0075</t>
         </is>
       </c>
+      <c r="G12" s="279" t="inlineStr">
+        <is>
+          <t>-0.0191</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="20" customHeight="1" s="220">
-      <c r="A13" s="276" t="n"/>
-      <c r="B13" s="277" t="inlineStr">
+      <c r="A13" s="275" t="n"/>
+      <c r="B13" s="276" t="inlineStr">
         <is>
           <t>EEGPT</t>
         </is>
       </c>
-      <c r="C13" s="278" t="n">
+      <c r="C13" s="277" t="n">
         <v>25.69</v>
       </c>
-      <c r="D13" s="279" t="inlineStr">
+      <c r="D13" s="278" t="inlineStr">
         <is>
           <t>0.8137±0.0052</t>
         </is>
       </c>
-      <c r="E13" s="280" t="inlineStr">
+      <c r="E13" s="279" t="inlineStr">
         <is>
           <t>0.9054±0.0029</t>
         </is>
       </c>
-      <c r="F13" s="280" t="inlineStr">
+      <c r="F13" s="279" t="inlineStr">
         <is>
           <t>0.9028±0.0033</t>
         </is>
       </c>
+      <c r="G13" s="279" t="inlineStr">
+        <is>
+          <t>+0.0199</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="20" customHeight="1" s="220">
-      <c r="A14" s="276" t="n"/>
-      <c r="B14" s="277" t="inlineStr">
+      <c r="A14" s="275" t="n"/>
+      <c r="B14" s="276" t="inlineStr">
         <is>
           <t>TFM-Tokenizer</t>
         </is>
       </c>
-      <c r="C14" s="278" t="n">
+      <c r="C14" s="277" t="n">
         <v>1.89</v>
       </c>
-      <c r="D14" s="279" t="inlineStr">
+      <c r="D14" s="278" t="inlineStr">
         <is>
           <t>0.7961±0.0056</t>
         </is>
       </c>
-      <c r="E14" s="280" t="inlineStr">
+      <c r="E14" s="279" t="inlineStr">
         <is>
           <t>0.8840±0.0027</t>
         </is>
       </c>
-      <c r="F14" s="280" t="inlineStr">
+      <c r="F14" s="279" t="inlineStr">
         <is>
           <t>0.8793±0.0021</t>
         </is>
       </c>
+      <c r="G14" s="279" t="inlineStr">
+        <is>
+          <t>-0.0036</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="20" customHeight="1" s="220">
-      <c r="A15" s="271" t="inlineStr">
+      <c r="A15" s="270" t="inlineStr">
         <is>
           <t>C FM · 同 pipeline scratch</t>
         </is>
       </c>
-      <c r="B15" s="285" t="inlineStr">
+      <c r="B15" s="284" t="inlineStr">
         <is>
           <t>BIOT (scratch)</t>
         </is>
       </c>
-      <c r="C15" s="286" t="n">
+      <c r="C15" s="285" t="n">
         <v>3.19</v>
       </c>
-      <c r="D15" s="287" t="inlineStr">
+      <c r="D15" s="286" t="inlineStr">
         <is>
           <t>0.7909±0.0035</t>
         </is>
       </c>
-      <c r="E15" s="288" t="inlineStr">
+      <c r="E15" s="287" t="inlineStr">
         <is>
           <t>0.8683±0.0024</t>
         </is>
       </c>
-      <c r="F15" s="288" t="inlineStr">
+      <c r="F15" s="287" t="inlineStr">
         <is>
           <t>0.8694±0.0047</t>
         </is>
       </c>
+      <c r="G15" s="287" t="inlineStr">
+        <is>
+          <t>-0.0135</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="20" customHeight="1" s="220">
-      <c r="A16" s="276" t="n"/>
-      <c r="B16" s="277" t="inlineStr">
+      <c r="A16" s="275" t="n"/>
+      <c r="B16" s="276" t="inlineStr">
         <is>
           <t>LaBraM-Base (scratch)</t>
         </is>
       </c>
-      <c r="C16" s="278" t="n">
+      <c r="C16" s="277" t="n">
         <v>5.8</v>
       </c>
-      <c r="D16" s="279" t="n"/>
-      <c r="E16" s="280" t="n"/>
-      <c r="F16" s="280" t="n"/>
+      <c r="D16" s="278" t="n"/>
+      <c r="E16" s="279" t="n"/>
+      <c r="F16" s="279" t="n"/>
+      <c r="G16" s="279" t="n"/>
     </row>
     <row r="17" ht="20" customHeight="1" s="220">
-      <c r="A17" s="276" t="n"/>
-      <c r="B17" s="277" t="inlineStr">
+      <c r="A17" s="275" t="n"/>
+      <c r="B17" s="276" t="inlineStr">
         <is>
           <t>CBraMod (scratch)</t>
         </is>
       </c>
-      <c r="C17" s="278" t="n">
+      <c r="C17" s="277" t="n">
         <v>30.65</v>
       </c>
-      <c r="D17" s="279" t="inlineStr">
+      <c r="D17" s="278" t="inlineStr">
         <is>
           <t>0.7920±0.0064</t>
         </is>
       </c>
-      <c r="E17" s="280" t="inlineStr">
+      <c r="E17" s="279" t="inlineStr">
         <is>
           <t>0.8831±0.0030</t>
         </is>
       </c>
-      <c r="F17" s="280" t="inlineStr">
+      <c r="F17" s="279" t="inlineStr">
         <is>
           <t>0.8763±0.0026</t>
         </is>
       </c>
+      <c r="G17" s="279" t="inlineStr">
+        <is>
+          <t>-0.0066</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="20" customHeight="1" s="220">
-      <c r="A18" s="276" t="n"/>
-      <c r="B18" s="289" t="inlineStr">
+      <c r="A18" s="275" t="n"/>
+      <c r="B18" s="288" t="inlineStr">
         <is>
           <t>PACLock (from scratch, full)</t>
         </is>
       </c>
-      <c r="C18" s="290" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="D18" s="291" t="n"/>
-      <c r="E18" s="292" t="n"/>
-      <c r="F18" s="292" t="n"/>
+      <c r="C18" s="289" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="D18" s="290" t="inlineStr">
+        <is>
+          <t>0.8045±0.0059</t>
+        </is>
+      </c>
+      <c r="E18" s="291" t="inlineStr">
+        <is>
+          <t>0.8890±0.0039</t>
+        </is>
+      </c>
+      <c r="F18" s="291" t="inlineStr">
+        <is>
+          <t>0.8829±0.0033</t>
+        </is>
+      </c>
+      <c r="G18" s="291" t="n"/>
     </row>
     <row r="19" ht="15" customHeight="1" s="220"/>
     <row r="20" ht="24" customHeight="1" s="220"/>
@@ -9834,8 +10151,8 @@
     <row r="56" ht="42" customHeight="1" s="220"/>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A2:G2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" scale="100" fitToHeight="1" fitToWidth="1" firstPageNumber="1" useFirstPageNumber="0" pageOrder="downThenOver"/>
@@ -9899,483 +10216,483 @@
       <c r="G3" s="268" t="n"/>
     </row>
     <row r="4" ht="28" customHeight="1" s="220">
-      <c r="A4" s="270" t="inlineStr">
+      <c r="A4" s="269" t="inlineStr">
         <is>
           <t>分组</t>
         </is>
       </c>
-      <c r="B4" s="270" t="inlineStr">
+      <c r="B4" s="269" t="inlineStr">
         <is>
           <t>模型</t>
         </is>
       </c>
-      <c r="C4" s="270" t="inlineStr">
+      <c r="C4" s="269" t="inlineStr">
         <is>
           <t>参数量 (M)</t>
         </is>
       </c>
-      <c r="D4" s="270" t="inlineStr">
+      <c r="D4" s="269" t="inlineStr">
         <is>
           <t>Balanced Acc</t>
         </is>
       </c>
-      <c r="E4" s="270" t="inlineStr">
+      <c r="E4" s="269" t="inlineStr">
         <is>
           <t>Cohen's Kappa</t>
         </is>
       </c>
-      <c r="F4" s="270" t="inlineStr">
+      <c r="F4" s="269" t="inlineStr">
         <is>
           <t>Weighted F1</t>
         </is>
       </c>
-      <c r="G4" s="270" t="inlineStr">
+      <c r="G4" s="269" t="inlineStr">
         <is>
           <t>ΔCohen's Kappa vs PACLock</t>
         </is>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1" s="220">
-      <c r="A5" s="271" t="inlineStr">
+      <c r="A5" s="270" t="inlineStr">
         <is>
           <t>A 轻量监督基线</t>
         </is>
       </c>
-      <c r="B5" s="272" t="inlineStr">
+      <c r="B5" s="271" t="inlineStr">
         <is>
           <t>SPaRCNet</t>
         </is>
       </c>
-      <c r="C5" s="273" t="n">
+      <c r="C5" s="272" t="n">
         <v>0.99</v>
       </c>
-      <c r="D5" s="274" t="inlineStr">
+      <c r="D5" s="273" t="inlineStr">
         <is>
           <t>0.4654±0.0283</t>
         </is>
       </c>
-      <c r="E5" s="275" t="inlineStr">
+      <c r="E5" s="274" t="inlineStr">
         <is>
           <t>0.4885±0.0228</t>
         </is>
       </c>
-      <c r="F5" s="275" t="inlineStr">
+      <c r="F5" s="274" t="inlineStr">
         <is>
           <t>0.7354±0.0119</t>
         </is>
       </c>
-      <c r="G5" s="275" t="inlineStr">
+      <c r="G5" s="274" t="inlineStr">
         <is>
           <t>-0.2191</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1" s="220">
-      <c r="A6" s="276" t="n"/>
-      <c r="B6" s="277" t="inlineStr">
+      <c r="A6" s="275" t="n"/>
+      <c r="B6" s="276" t="inlineStr">
         <is>
           <t>ContraWR</t>
         </is>
       </c>
-      <c r="C6" s="278" t="n">
+      <c r="C6" s="277" t="n">
         <v>1.57</v>
       </c>
-      <c r="D6" s="279" t="inlineStr">
+      <c r="D6" s="278" t="inlineStr">
         <is>
           <t>0.4195±0.1027</t>
         </is>
       </c>
-      <c r="E6" s="280" t="inlineStr">
+      <c r="E6" s="279" t="inlineStr">
         <is>
           <t>0.4076±0.0803</t>
         </is>
       </c>
-      <c r="F6" s="280" t="inlineStr">
+      <c r="F6" s="279" t="inlineStr">
         <is>
           <t>0.6962±0.0371</t>
         </is>
       </c>
-      <c r="G6" s="280" t="inlineStr">
+      <c r="G6" s="279" t="inlineStr">
         <is>
           <t>-0.3000</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1" s="220">
-      <c r="A7" s="276" t="n"/>
-      <c r="B7" s="277" t="inlineStr">
+      <c r="A7" s="275" t="n"/>
+      <c r="B7" s="276" t="inlineStr">
         <is>
           <t>CNN-Transformer</t>
         </is>
       </c>
-      <c r="C7" s="278" t="n">
+      <c r="C7" s="277" t="n">
         <v>3.16</v>
       </c>
-      <c r="D7" s="279" t="inlineStr">
+      <c r="D7" s="278" t="inlineStr">
         <is>
           <t>0.3679±0.0838</t>
         </is>
       </c>
-      <c r="E7" s="280" t="inlineStr">
+      <c r="E7" s="279" t="inlineStr">
         <is>
           <t>0.4098±0.0951</t>
         </is>
       </c>
-      <c r="F7" s="280" t="inlineStr">
+      <c r="F7" s="279" t="inlineStr">
         <is>
           <t>0.6916±0.0607</t>
         </is>
       </c>
-      <c r="G7" s="280" t="inlineStr">
+      <c r="G7" s="279" t="inlineStr">
         <is>
           <t>-0.2978</t>
         </is>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1" s="220">
-      <c r="A8" s="276" t="n"/>
-      <c r="B8" s="277" t="inlineStr">
+      <c r="A8" s="275" t="n"/>
+      <c r="B8" s="276" t="inlineStr">
         <is>
           <t>FFCL</t>
         </is>
       </c>
-      <c r="C8" s="278" t="n">
+      <c r="C8" s="277" t="n">
         <v>2.42</v>
       </c>
-      <c r="D8" s="279" t="inlineStr">
+      <c r="D8" s="278" t="inlineStr">
         <is>
           <t>0.4376±0.0561</t>
         </is>
       </c>
-      <c r="E8" s="280" t="inlineStr">
+      <c r="E8" s="279" t="inlineStr">
         <is>
           <t>0.4776±0.0263</t>
         </is>
       </c>
-      <c r="F8" s="280" t="inlineStr">
+      <c r="F8" s="279" t="inlineStr">
         <is>
           <t>0.7366±0.0138</t>
         </is>
       </c>
-      <c r="G8" s="280" t="inlineStr">
+      <c r="G8" s="279" t="inlineStr">
         <is>
           <t>-0.2300</t>
         </is>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1" s="220">
-      <c r="A9" s="276" t="n"/>
-      <c r="B9" s="277" t="inlineStr">
+      <c r="A9" s="275" t="n"/>
+      <c r="B9" s="276" t="inlineStr">
         <is>
           <t>ST-Transformer</t>
         </is>
       </c>
-      <c r="C9" s="278" t="n">
+      <c r="C9" s="277" t="n">
         <v>3.43</v>
       </c>
-      <c r="D9" s="279" t="inlineStr">
+      <c r="D9" s="278" t="inlineStr">
         <is>
           <t>0.4731±0.0162</t>
         </is>
       </c>
-      <c r="E9" s="280" t="inlineStr">
+      <c r="E9" s="279" t="inlineStr">
         <is>
           <t>0.5006±0.0096</t>
         </is>
       </c>
-      <c r="F9" s="280" t="inlineStr">
+      <c r="F9" s="279" t="inlineStr">
         <is>
           <t>0.7411±0.0071</t>
         </is>
       </c>
-      <c r="G9" s="280" t="inlineStr">
+      <c r="G9" s="279" t="inlineStr">
         <is>
           <t>-0.2070</t>
         </is>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1" s="220">
-      <c r="A10" s="271" t="inlineStr">
+      <c r="A10" s="270" t="inlineStr">
         <is>
           <t>B FM · 官方预训练权重</t>
         </is>
       </c>
-      <c r="B10" s="281" t="inlineStr">
+      <c r="B10" s="280" t="inlineStr">
         <is>
           <t>BIOT (pretrained)</t>
         </is>
       </c>
-      <c r="C10" s="282" t="n">
+      <c r="C10" s="281" t="n">
         <v>3.19</v>
       </c>
-      <c r="D10" s="283" t="inlineStr">
+      <c r="D10" s="282" t="inlineStr">
         <is>
           <t>0.4894±0.0247</t>
         </is>
       </c>
-      <c r="E10" s="284" t="inlineStr">
+      <c r="E10" s="283" t="inlineStr">
         <is>
           <t>0.5304±0.0227</t>
         </is>
       </c>
-      <c r="F10" s="284" t="inlineStr">
+      <c r="F10" s="283" t="inlineStr">
         <is>
           <t>0.7532±0.0129</t>
         </is>
       </c>
-      <c r="G10" s="284" t="inlineStr">
+      <c r="G10" s="283" t="inlineStr">
         <is>
           <t>-0.1772</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1" s="220">
-      <c r="A11" s="276" t="n"/>
-      <c r="B11" s="277" t="inlineStr">
+      <c r="A11" s="275" t="n"/>
+      <c r="B11" s="276" t="inlineStr">
         <is>
           <t>LaBraM-Base (pretrained)</t>
         </is>
       </c>
-      <c r="C11" s="278" t="n">
+      <c r="C11" s="277" t="n">
         <v>5.82</v>
       </c>
-      <c r="D11" s="279" t="inlineStr">
+      <c r="D11" s="278" t="inlineStr">
         <is>
           <t>0.6305±0.0250</t>
         </is>
       </c>
-      <c r="E11" s="280" t="inlineStr">
+      <c r="E11" s="279" t="inlineStr">
         <is>
           <t>0.5984±0.0025</t>
         </is>
       </c>
-      <c r="F11" s="280" t="inlineStr">
+      <c r="F11" s="279" t="inlineStr">
         <is>
           <t>0.8086±0.0039</t>
         </is>
       </c>
-      <c r="G11" s="280" t="inlineStr">
+      <c r="G11" s="279" t="inlineStr">
         <is>
           <t>-0.1092</t>
         </is>
       </c>
     </row>
     <row r="12" ht="20" customHeight="1" s="220">
-      <c r="A12" s="276" t="n"/>
-      <c r="B12" s="277" t="inlineStr">
+      <c r="A12" s="275" t="n"/>
+      <c r="B12" s="276" t="inlineStr">
         <is>
           <t>CBraMod (pretrained)</t>
         </is>
       </c>
-      <c r="C12" s="278" t="n">
+      <c r="C12" s="277" t="n">
         <v>17.85</v>
       </c>
-      <c r="D12" s="279" t="inlineStr">
+      <c r="D12" s="278" t="inlineStr">
         <is>
           <t>0.6029±0.0088</t>
         </is>
       </c>
-      <c r="E12" s="280" t="inlineStr">
+      <c r="E12" s="279" t="inlineStr">
         <is>
           <t>0.6449±0.0177</t>
         </is>
       </c>
-      <c r="F12" s="280" t="inlineStr">
+      <c r="F12" s="279" t="inlineStr">
         <is>
           <t>0.8130±0.0095</t>
         </is>
       </c>
-      <c r="G12" s="280" t="inlineStr">
+      <c r="G12" s="279" t="inlineStr">
         <is>
           <t>-0.0627</t>
         </is>
       </c>
     </row>
     <row r="13" ht="20" customHeight="1" s="220">
-      <c r="A13" s="276" t="n"/>
-      <c r="B13" s="277" t="inlineStr">
+      <c r="A13" s="275" t="n"/>
+      <c r="B13" s="276" t="inlineStr">
         <is>
           <t>EEGPT</t>
         </is>
       </c>
-      <c r="C13" s="278" t="n">
+      <c r="C13" s="277" t="n">
         <v>25.69</v>
       </c>
-      <c r="D13" s="279" t="inlineStr">
+      <c r="D13" s="278" t="inlineStr">
         <is>
           <t>0.5131±0.0613</t>
         </is>
       </c>
-      <c r="E13" s="280" t="inlineStr">
+      <c r="E13" s="279" t="inlineStr">
         <is>
           <t>0.5736±0.0323</t>
         </is>
       </c>
-      <c r="F13" s="280" t="inlineStr">
+      <c r="F13" s="279" t="inlineStr">
         <is>
           <t>0.7766±0.0163</t>
         </is>
       </c>
-      <c r="G13" s="280" t="inlineStr">
+      <c r="G13" s="279" t="inlineStr">
         <is>
           <t>-0.1340</t>
         </is>
       </c>
     </row>
     <row r="14" ht="20" customHeight="1" s="220">
-      <c r="A14" s="276" t="n"/>
-      <c r="B14" s="277" t="inlineStr">
+      <c r="A14" s="275" t="n"/>
+      <c r="B14" s="276" t="inlineStr">
         <is>
           <t>TFM-Tokenizer</t>
         </is>
       </c>
-      <c r="C14" s="278" t="n">
+      <c r="C14" s="277" t="n">
         <v>1.89</v>
       </c>
-      <c r="D14" s="279" t="inlineStr">
+      <c r="D14" s="278" t="inlineStr">
         <is>
           <t>0.5959±0.0294</t>
         </is>
       </c>
-      <c r="E14" s="280" t="inlineStr">
+      <c r="E14" s="279" t="inlineStr">
         <is>
           <t>0.6519±0.0170</t>
         </is>
       </c>
-      <c r="F14" s="280" t="inlineStr">
+      <c r="F14" s="279" t="inlineStr">
         <is>
           <t>0.8171±0.0085</t>
         </is>
       </c>
-      <c r="G14" s="280" t="inlineStr">
+      <c r="G14" s="279" t="inlineStr">
         <is>
           <t>-0.0557</t>
         </is>
       </c>
     </row>
     <row r="15" ht="20" customHeight="1" s="220">
-      <c r="A15" s="271" t="inlineStr">
+      <c r="A15" s="270" t="inlineStr">
         <is>
           <t>C FM · 同 pipeline scratch</t>
         </is>
       </c>
-      <c r="B15" s="285" t="inlineStr">
+      <c r="B15" s="284" t="inlineStr">
         <is>
           <t>BIOT (scratch)</t>
         </is>
       </c>
-      <c r="C15" s="286" t="n">
+      <c r="C15" s="285" t="n">
         <v>3.19</v>
       </c>
-      <c r="D15" s="287" t="inlineStr">
+      <c r="D15" s="286" t="inlineStr">
         <is>
           <t>0.5351±0.0510</t>
         </is>
       </c>
-      <c r="E15" s="288" t="inlineStr">
+      <c r="E15" s="287" t="inlineStr">
         <is>
           <t>0.5324±0.0204</t>
         </is>
       </c>
-      <c r="F15" s="288" t="inlineStr">
+      <c r="F15" s="287" t="inlineStr">
         <is>
           <t>0.7612±0.0103</t>
         </is>
       </c>
-      <c r="G15" s="288" t="inlineStr">
+      <c r="G15" s="287" t="inlineStr">
         <is>
           <t>-0.1752</t>
         </is>
       </c>
     </row>
     <row r="16" ht="20" customHeight="1" s="220">
-      <c r="A16" s="276" t="n"/>
-      <c r="B16" s="277" t="inlineStr">
+      <c r="A16" s="275" t="n"/>
+      <c r="B16" s="276" t="inlineStr">
         <is>
           <t>LaBraM-Base (scratch)</t>
         </is>
       </c>
-      <c r="C16" s="278" t="n">
+      <c r="C16" s="277" t="n">
         <v>5.82</v>
       </c>
-      <c r="D16" s="279" t="inlineStr">
+      <c r="D16" s="278" t="inlineStr">
         <is>
           <t>0.3724±0.0697</t>
         </is>
       </c>
-      <c r="E16" s="280" t="inlineStr">
+      <c r="E16" s="279" t="inlineStr">
         <is>
           <t>0.3717±0.0073</t>
         </is>
       </c>
-      <c r="F16" s="280" t="inlineStr">
+      <c r="F16" s="279" t="inlineStr">
         <is>
           <t>0.6928±0.0108</t>
         </is>
       </c>
-      <c r="G16" s="280" t="inlineStr">
+      <c r="G16" s="279" t="inlineStr">
         <is>
           <t>-0.3359</t>
         </is>
       </c>
     </row>
     <row r="17" ht="20" customHeight="1" s="220">
-      <c r="A17" s="276" t="n"/>
-      <c r="B17" s="277" t="inlineStr">
+      <c r="A17" s="275" t="n"/>
+      <c r="B17" s="276" t="inlineStr">
         <is>
           <t>CBraMod (scratch)</t>
         </is>
       </c>
-      <c r="C17" s="278" t="n">
+      <c r="C17" s="277" t="n">
         <v>17.85</v>
       </c>
-      <c r="D17" s="279" t="inlineStr">
+      <c r="D17" s="278" t="inlineStr">
         <is>
           <t>0.5744±0.0086</t>
         </is>
       </c>
-      <c r="E17" s="280" t="inlineStr">
+      <c r="E17" s="279" t="inlineStr">
         <is>
           <t>0.5638±0.0193</t>
         </is>
       </c>
-      <c r="F17" s="280" t="inlineStr">
+      <c r="F17" s="279" t="inlineStr">
         <is>
           <t>0.7671±0.0034</t>
         </is>
       </c>
-      <c r="G17" s="280" t="inlineStr">
+      <c r="G17" s="279" t="inlineStr">
         <is>
           <t>-0.1438</t>
         </is>
       </c>
     </row>
     <row r="18" ht="20" customHeight="1" s="220">
-      <c r="A18" s="276" t="n"/>
-      <c r="B18" s="289" t="inlineStr">
+      <c r="A18" s="275" t="n"/>
+      <c r="B18" s="288" t="inlineStr">
         <is>
           <t>PACLock (from scratch, full)</t>
         </is>
       </c>
-      <c r="C18" s="290" t="n">
+      <c r="C18" s="289" t="n">
         <v>1.62</v>
       </c>
-      <c r="D18" s="291" t="inlineStr">
+      <c r="D18" s="290" t="inlineStr">
         <is>
           <t>0.5583±0.0308</t>
         </is>
       </c>
-      <c r="E18" s="292" t="inlineStr">
+      <c r="E18" s="291" t="inlineStr">
         <is>
           <t>0.7076±0.0254</t>
         </is>
       </c>
-      <c r="F18" s="292" t="inlineStr">
+      <c r="F18" s="291" t="inlineStr">
         <is>
           <t>0.8426±0.0116</t>
         </is>
       </c>
-      <c r="G18" s="292" t="n"/>
+      <c r="G18" s="291" t="n"/>
     </row>
     <row r="19" ht="15" customHeight="1" s="220"/>
     <row r="20" ht="24" customHeight="1" s="220"/>
@@ -10449,6 +10766,7 @@
     <col width="17" customWidth="1" style="220" min="4" max="4"/>
     <col width="17" customWidth="1" style="219" min="5" max="7"/>
     <col width="17" customWidth="1" style="220" min="6" max="6"/>
+    <col width="17" customWidth="1" style="220" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1" s="220">
@@ -10461,7 +10779,8 @@
       <c r="C1" s="228" t="n"/>
       <c r="D1" s="228" t="n"/>
       <c r="E1" s="228" t="n"/>
-      <c r="F1" s="229" t="n"/>
+      <c r="F1" s="228" t="n"/>
+      <c r="G1" s="229" t="n"/>
     </row>
     <row r="2" ht="22" customHeight="1" s="220">
       <c r="A2" s="267" t="inlineStr">
@@ -10469,7 +10788,7 @@
           <t>主指标：AUC-PR</t>
         </is>
       </c>
-      <c r="F2" s="231" t="n"/>
+      <c r="G2" s="231" t="n"/>
     </row>
     <row r="3" ht="8" customHeight="1" s="220">
       <c r="A3" s="268" t="n"/>
@@ -10478,403 +10797,486 @@
       <c r="D3" s="268" t="n"/>
       <c r="E3" s="268" t="n"/>
       <c r="F3" s="268" t="n"/>
-      <c r="G3" s="269" t="n"/>
+      <c r="G3" s="268" t="n"/>
     </row>
     <row r="4" ht="28" customHeight="1" s="220">
-      <c r="A4" s="270" t="inlineStr">
+      <c r="A4" s="269" t="inlineStr">
         <is>
           <t>分组</t>
         </is>
       </c>
-      <c r="B4" s="270" t="inlineStr">
+      <c r="B4" s="269" t="inlineStr">
         <is>
           <t>模型</t>
         </is>
       </c>
-      <c r="C4" s="270" t="inlineStr">
+      <c r="C4" s="269" t="inlineStr">
         <is>
           <t>参数量 (M)</t>
         </is>
       </c>
-      <c r="D4" s="270" t="inlineStr">
+      <c r="D4" s="269" t="inlineStr">
         <is>
           <t>Balanced Acc</t>
         </is>
       </c>
-      <c r="E4" s="270" t="inlineStr">
+      <c r="E4" s="269" t="inlineStr">
         <is>
           <t>AUC-PR</t>
         </is>
       </c>
-      <c r="F4" s="270" t="inlineStr">
+      <c r="F4" s="269" t="inlineStr">
         <is>
           <t>AUROC</t>
         </is>
       </c>
+      <c r="G4" s="269" t="inlineStr">
+        <is>
+          <t>ΔAUC-PR vs PACLock</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="20" customHeight="1" s="220">
-      <c r="A5" s="271" t="inlineStr">
+      <c r="A5" s="270" t="inlineStr">
         <is>
           <t>A 轻量监督基线</t>
         </is>
       </c>
-      <c r="B5" s="272" t="inlineStr">
+      <c r="B5" s="271" t="inlineStr">
         <is>
           <t>SPaRCNet</t>
         </is>
       </c>
-      <c r="C5" s="273" t="n">
+      <c r="C5" s="272" t="n">
         <v>1.14</v>
       </c>
-      <c r="D5" s="274" t="inlineStr">
+      <c r="D5" s="273" t="inlineStr">
         <is>
           <t>0.5609±0.0310</t>
         </is>
       </c>
-      <c r="E5" s="275" t="inlineStr">
+      <c r="E5" s="274" t="inlineStr">
         <is>
           <t>0.5020±0.0174</t>
         </is>
       </c>
-      <c r="F5" s="275" t="inlineStr">
+      <c r="F5" s="274" t="inlineStr">
         <is>
           <t>0.8888±0.0015</t>
         </is>
       </c>
+      <c r="G5" s="274" t="inlineStr">
+        <is>
+          <t>-0.0862</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="20" customHeight="1" s="220">
-      <c r="A6" s="276" t="n"/>
-      <c r="B6" s="277" t="inlineStr">
+      <c r="A6" s="275" t="n"/>
+      <c r="B6" s="276" t="inlineStr">
         <is>
           <t>ContraWR</t>
         </is>
       </c>
-      <c r="C6" s="278" t="n">
+      <c r="C6" s="277" t="n">
         <v>1.57</v>
       </c>
-      <c r="D6" s="279" t="inlineStr">
+      <c r="D6" s="278" t="inlineStr">
         <is>
           <t>0.5601±0.0144</t>
         </is>
       </c>
-      <c r="E6" s="280" t="inlineStr">
+      <c r="E6" s="279" t="inlineStr">
         <is>
           <t>0.5043±0.0143</t>
         </is>
       </c>
-      <c r="F6" s="280" t="inlineStr">
+      <c r="F6" s="279" t="inlineStr">
         <is>
           <t>0.8871±0.0028</t>
         </is>
       </c>
+      <c r="G6" s="279" t="inlineStr">
+        <is>
+          <t>-0.0839</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="20" customHeight="1" s="220">
-      <c r="A7" s="276" t="n"/>
-      <c r="B7" s="277" t="inlineStr">
+      <c r="A7" s="275" t="n"/>
+      <c r="B7" s="276" t="inlineStr">
         <is>
           <t>CNN-Transformer</t>
         </is>
       </c>
-      <c r="C7" s="278" t="n">
+      <c r="C7" s="277" t="n">
         <v>3.15</v>
       </c>
-      <c r="D7" s="279" t="inlineStr">
+      <c r="D7" s="278" t="inlineStr">
         <is>
           <t>0.5389±0.0447</t>
         </is>
       </c>
-      <c r="E7" s="280" t="inlineStr">
+      <c r="E7" s="279" t="inlineStr">
         <is>
           <t>0.3707±0.1579</t>
         </is>
       </c>
-      <c r="F7" s="280" t="inlineStr">
+      <c r="F7" s="279" t="inlineStr">
         <is>
           <t>0.8455±0.0343</t>
         </is>
       </c>
+      <c r="G7" s="279" t="inlineStr">
+        <is>
+          <t>-0.2175</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="20" customHeight="1" s="220">
-      <c r="A8" s="276" t="n"/>
-      <c r="B8" s="277" t="inlineStr">
+      <c r="A8" s="275" t="n"/>
+      <c r="B8" s="276" t="inlineStr">
         <is>
           <t>FFCL</t>
         </is>
       </c>
-      <c r="C8" s="278" t="n">
+      <c r="C8" s="277" t="n">
         <v>2.46</v>
       </c>
-      <c r="D8" s="279" t="inlineStr">
+      <c r="D8" s="278" t="inlineStr">
         <is>
           <t>0.5953±0.0273</t>
         </is>
       </c>
-      <c r="E8" s="280" t="inlineStr">
+      <c r="E8" s="279" t="inlineStr">
         <is>
           <t>0.5449±0.0242</t>
         </is>
       </c>
-      <c r="F8" s="280" t="inlineStr">
+      <c r="F8" s="279" t="inlineStr">
         <is>
           <t>0.8924±0.0091</t>
         </is>
       </c>
+      <c r="G8" s="279" t="inlineStr">
+        <is>
+          <t>-0.0433</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="20" customHeight="1" s="220">
-      <c r="A9" s="276" t="n"/>
-      <c r="B9" s="277" t="inlineStr">
+      <c r="A9" s="275" t="n"/>
+      <c r="B9" s="276" t="inlineStr">
         <is>
           <t>ST-Transformer</t>
         </is>
       </c>
-      <c r="C9" s="278" t="n">
+      <c r="C9" s="277" t="n">
         <v>3.43</v>
       </c>
-      <c r="D9" s="279" t="inlineStr">
+      <c r="D9" s="278" t="inlineStr">
         <is>
           <t>0.5514±0.0346</t>
         </is>
       </c>
-      <c r="E9" s="280" t="inlineStr">
+      <c r="E9" s="279" t="inlineStr">
         <is>
           <t>0.3589±0.0256</t>
         </is>
       </c>
-      <c r="F9" s="280" t="inlineStr">
+      <c r="F9" s="279" t="inlineStr">
         <is>
           <t>0.8148±0.0162</t>
         </is>
       </c>
+      <c r="G9" s="279" t="inlineStr">
+        <is>
+          <t>-0.2293</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="20" customHeight="1" s="220">
-      <c r="A10" s="271" t="inlineStr">
+      <c r="A10" s="270" t="inlineStr">
         <is>
           <t>B FM · 官方预训练权重</t>
         </is>
       </c>
-      <c r="B10" s="281" t="inlineStr">
+      <c r="B10" s="280" t="inlineStr">
         <is>
           <t>BIOT (pretrained)</t>
         </is>
       </c>
-      <c r="C10" s="282" t="n">
+      <c r="C10" s="281" t="n">
         <v>3.19</v>
       </c>
-      <c r="D10" s="283" t="inlineStr">
+      <c r="D10" s="282" t="inlineStr">
         <is>
           <t>0.5634±0.0267</t>
         </is>
       </c>
-      <c r="E10" s="284" t="inlineStr">
+      <c r="E10" s="283" t="inlineStr">
         <is>
           <t>0.3379±0.0310</t>
         </is>
       </c>
-      <c r="F10" s="284" t="inlineStr">
+      <c r="F10" s="283" t="inlineStr">
         <is>
           <t>0.8382±0.0110</t>
         </is>
       </c>
+      <c r="G10" s="283" t="inlineStr">
+        <is>
+          <t>-0.2503</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="20" customHeight="1" s="220">
-      <c r="A11" s="276" t="n"/>
-      <c r="B11" s="277" t="inlineStr">
+      <c r="A11" s="275" t="n"/>
+      <c r="B11" s="276" t="inlineStr">
         <is>
           <t>LaBraM-Base (pretrained)</t>
         </is>
       </c>
-      <c r="C11" s="278" t="n">
+      <c r="C11" s="277" t="n">
         <v>5.82</v>
       </c>
-      <c r="D11" s="279" t="inlineStr">
+      <c r="D11" s="278" t="inlineStr">
         <is>
           <t>0.6139±0.0309</t>
         </is>
       </c>
-      <c r="E11" s="280" t="inlineStr">
+      <c r="E11" s="279" t="inlineStr">
         <is>
           <t>0.4754±0.0386</t>
         </is>
       </c>
-      <c r="F11" s="280" t="inlineStr">
+      <c r="F11" s="279" t="inlineStr">
         <is>
           <t>0.8687±0.0206</t>
         </is>
       </c>
+      <c r="G11" s="279" t="inlineStr">
+        <is>
+          <t>-0.1128</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="20" customHeight="1" s="220">
-      <c r="A12" s="276" t="n"/>
-      <c r="B12" s="277" t="inlineStr">
+      <c r="A12" s="275" t="n"/>
+      <c r="B12" s="276" t="inlineStr">
         <is>
           <t>CBraMod (pretrained)</t>
         </is>
       </c>
-      <c r="C12" s="278" t="n">
+      <c r="C12" s="277" t="n">
         <v>30.65</v>
       </c>
-      <c r="D12" s="279" t="inlineStr">
+      <c r="D12" s="278" t="inlineStr">
         <is>
           <t>0.6347±0.0279</t>
         </is>
       </c>
-      <c r="E12" s="280" t="inlineStr">
+      <c r="E12" s="279" t="inlineStr">
         <is>
           <t>0.4344±0.0346</t>
         </is>
       </c>
-      <c r="F12" s="280" t="inlineStr">
+      <c r="F12" s="279" t="inlineStr">
         <is>
           <t>0.8520±0.0041</t>
         </is>
       </c>
+      <c r="G12" s="279" t="inlineStr">
+        <is>
+          <t>-0.1538</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="20" customHeight="1" s="220">
-      <c r="A13" s="276" t="n"/>
-      <c r="B13" s="277" t="inlineStr">
+      <c r="A13" s="275" t="n"/>
+      <c r="B13" s="276" t="inlineStr">
         <is>
           <t>EEGPT</t>
         </is>
       </c>
-      <c r="C13" s="278" t="n">
+      <c r="C13" s="277" t="n">
         <v>25.69</v>
       </c>
-      <c r="D13" s="279" t="inlineStr">
+      <c r="D13" s="278" t="inlineStr">
         <is>
           <t>0.6587±0.0505</t>
         </is>
       </c>
-      <c r="E13" s="280" t="inlineStr">
+      <c r="E13" s="279" t="inlineStr">
         <is>
           <t>0.5446±0.0575</t>
         </is>
       </c>
-      <c r="F13" s="280" t="inlineStr">
+      <c r="F13" s="279" t="inlineStr">
         <is>
           <t>0.8821±0.0099</t>
         </is>
       </c>
+      <c r="G13" s="279" t="inlineStr">
+        <is>
+          <t>-0.0436</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="20" customHeight="1" s="220">
-      <c r="A14" s="276" t="n"/>
-      <c r="B14" s="277" t="inlineStr">
+      <c r="A14" s="275" t="n"/>
+      <c r="B14" s="276" t="inlineStr">
         <is>
           <t>TFM-Tokenizer</t>
         </is>
       </c>
-      <c r="C14" s="278" t="n">
+      <c r="C14" s="277" t="n">
         <v>1.89</v>
       </c>
-      <c r="D14" s="279" t="inlineStr">
+      <c r="D14" s="278" t="inlineStr">
         <is>
           <t>0.5645±0.0224</t>
         </is>
       </c>
-      <c r="E14" s="280" t="inlineStr">
+      <c r="E14" s="279" t="inlineStr">
         <is>
           <t>0.3474±0.0151</t>
         </is>
       </c>
-      <c r="F14" s="280" t="inlineStr">
+      <c r="F14" s="279" t="inlineStr">
         <is>
           <t>0.8286±0.0048</t>
         </is>
       </c>
+      <c r="G14" s="279" t="inlineStr">
+        <is>
+          <t>-0.2408</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="20" customHeight="1" s="220">
-      <c r="A15" s="271" t="inlineStr">
+      <c r="A15" s="270" t="inlineStr">
         <is>
           <t>C FM · 同 pipeline scratch</t>
         </is>
       </c>
-      <c r="B15" s="285" t="inlineStr">
+      <c r="B15" s="284" t="inlineStr">
         <is>
           <t>BIOT (scratch)</t>
         </is>
       </c>
-      <c r="C15" s="286" t="n">
+      <c r="C15" s="285" t="n">
         <v>3.19</v>
       </c>
-      <c r="D15" s="287" t="inlineStr">
+      <c r="D15" s="286" t="inlineStr">
         <is>
           <t>0.6156±0.0527</t>
         </is>
       </c>
-      <c r="E15" s="288" t="inlineStr">
+      <c r="E15" s="287" t="inlineStr">
         <is>
           <t>0.3475±0.0210</t>
         </is>
       </c>
-      <c r="F15" s="288" t="inlineStr">
+      <c r="F15" s="287" t="inlineStr">
         <is>
           <t>0.8256±0.0136</t>
         </is>
       </c>
+      <c r="G15" s="287" t="inlineStr">
+        <is>
+          <t>-0.2407</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="20" customHeight="1" s="220">
-      <c r="A16" s="276" t="n"/>
-      <c r="B16" s="277" t="inlineStr">
+      <c r="A16" s="275" t="n"/>
+      <c r="B16" s="276" t="inlineStr">
         <is>
           <t>LaBraM-Base (scratch)</t>
         </is>
       </c>
-      <c r="C16" s="278" t="n">
+      <c r="C16" s="277" t="n">
         <v>5.82</v>
       </c>
-      <c r="D16" s="279" t="inlineStr">
+      <c r="D16" s="278" t="inlineStr">
         <is>
           <t>0.5814±0.0290</t>
         </is>
       </c>
-      <c r="E16" s="280" t="inlineStr">
+      <c r="E16" s="279" t="inlineStr">
         <is>
           <t>0.4752±0.0390</t>
         </is>
       </c>
-      <c r="F16" s="280" t="inlineStr">
+      <c r="F16" s="279" t="inlineStr">
         <is>
           <t>0.8575±0.0156</t>
         </is>
       </c>
+      <c r="G16" s="279" t="inlineStr">
+        <is>
+          <t>-0.1130</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="20" customHeight="1" s="220">
-      <c r="A17" s="276" t="n"/>
-      <c r="B17" s="277" t="inlineStr">
+      <c r="A17" s="275" t="n"/>
+      <c r="B17" s="276" t="inlineStr">
         <is>
           <t>CBraMod (scratch)</t>
         </is>
       </c>
-      <c r="C17" s="278" t="n">
+      <c r="C17" s="277" t="n">
         <v>30.65</v>
       </c>
-      <c r="D17" s="279" t="inlineStr">
+      <c r="D17" s="278" t="inlineStr">
         <is>
           <t>0.5761±0.0403</t>
         </is>
       </c>
-      <c r="E17" s="280" t="inlineStr">
+      <c r="E17" s="279" t="inlineStr">
         <is>
           <t>0.4818±0.0426</t>
         </is>
       </c>
-      <c r="F17" s="280" t="inlineStr">
+      <c r="F17" s="279" t="inlineStr">
         <is>
           <t>0.8753±0.0273</t>
         </is>
       </c>
+      <c r="G17" s="279" t="inlineStr">
+        <is>
+          <t>-0.1064</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="20" customHeight="1" s="220">
-      <c r="A18" s="276" t="n"/>
-      <c r="B18" s="289" t="inlineStr">
+      <c r="A18" s="275" t="n"/>
+      <c r="B18" s="288" t="inlineStr">
         <is>
           <t>PACLock (from scratch, full)</t>
         </is>
       </c>
-      <c r="C18" s="290" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="D18" s="291" t="n"/>
-      <c r="E18" s="292" t="n"/>
-      <c r="F18" s="292" t="n"/>
+      <c r="C18" s="289" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="D18" s="290" t="inlineStr">
+        <is>
+          <t>0.6121±0.0341</t>
+        </is>
+      </c>
+      <c r="E18" s="291" t="inlineStr">
+        <is>
+          <t>0.5882±0.0645</t>
+        </is>
+      </c>
+      <c r="F18" s="291" t="inlineStr">
+        <is>
+          <t>0.9226±0.0022</t>
+        </is>
+      </c>
+      <c r="G18" s="291" t="n"/>
     </row>
     <row r="19" ht="15" customHeight="1" s="220"/>
     <row r="20" ht="24" customHeight="1" s="220"/>
@@ -10914,8 +11316,8 @@
     <row r="54" ht="38" customHeight="1" s="220"/>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A2:G2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" scale="100" fitToHeight="1" fitToWidth="1" firstPageNumber="1" useFirstPageNumber="0" pageOrder="downThenOver"/>
@@ -10945,6 +11347,7 @@
     <col width="17" customWidth="1" style="220" min="4" max="4"/>
     <col width="17" customWidth="1" style="219" min="5" max="7"/>
     <col width="17" customWidth="1" style="220" min="6" max="6"/>
+    <col width="17" customWidth="1" style="220" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1" s="220">
@@ -10957,7 +11360,8 @@
       <c r="C1" s="228" t="n"/>
       <c r="D1" s="228" t="n"/>
       <c r="E1" s="228" t="n"/>
-      <c r="F1" s="229" t="n"/>
+      <c r="F1" s="228" t="n"/>
+      <c r="G1" s="229" t="n"/>
     </row>
     <row r="2" ht="22" customHeight="1" s="220">
       <c r="A2" s="267" t="inlineStr">
@@ -10965,7 +11369,7 @@
           <t>主指标：AUC-PR</t>
         </is>
       </c>
-      <c r="F2" s="231" t="n"/>
+      <c r="G2" s="231" t="n"/>
     </row>
     <row r="3" ht="8" customHeight="1" s="220">
       <c r="A3" s="268" t="n"/>
@@ -10974,403 +11378,486 @@
       <c r="D3" s="268" t="n"/>
       <c r="E3" s="268" t="n"/>
       <c r="F3" s="268" t="n"/>
-      <c r="G3" s="269" t="n"/>
+      <c r="G3" s="268" t="n"/>
     </row>
     <row r="4" ht="28" customHeight="1" s="220">
-      <c r="A4" s="270" t="inlineStr">
+      <c r="A4" s="269" t="inlineStr">
         <is>
           <t>分组</t>
         </is>
       </c>
-      <c r="B4" s="270" t="inlineStr">
+      <c r="B4" s="269" t="inlineStr">
         <is>
           <t>模型</t>
         </is>
       </c>
-      <c r="C4" s="270" t="inlineStr">
+      <c r="C4" s="269" t="inlineStr">
         <is>
           <t>参数量 (M)</t>
         </is>
       </c>
-      <c r="D4" s="270" t="inlineStr">
+      <c r="D4" s="269" t="inlineStr">
         <is>
           <t>Balanced Acc</t>
         </is>
       </c>
-      <c r="E4" s="270" t="inlineStr">
+      <c r="E4" s="269" t="inlineStr">
         <is>
           <t>AUC-PR</t>
         </is>
       </c>
-      <c r="F4" s="270" t="inlineStr">
+      <c r="F4" s="269" t="inlineStr">
         <is>
           <t>AUROC</t>
         </is>
       </c>
+      <c r="G4" s="269" t="inlineStr">
+        <is>
+          <t>ΔAUC-PR vs PACLock</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="20" customHeight="1" s="220">
-      <c r="A5" s="271" t="inlineStr">
+      <c r="A5" s="270" t="inlineStr">
         <is>
           <t>A 轻量监督基线</t>
         </is>
       </c>
-      <c r="B5" s="272" t="inlineStr">
+      <c r="B5" s="271" t="inlineStr">
         <is>
           <t>SPaRCNet</t>
         </is>
       </c>
-      <c r="C5" s="273" t="n">
+      <c r="C5" s="272" t="n">
         <v>1.14</v>
       </c>
-      <c r="D5" s="274" t="inlineStr">
+      <c r="D5" s="273" t="inlineStr">
         <is>
           <t>0.5127±0.0064</t>
         </is>
       </c>
-      <c r="E5" s="275" t="inlineStr">
+      <c r="E5" s="274" t="inlineStr">
         <is>
           <t>0.1976±0.0584</t>
         </is>
       </c>
-      <c r="F5" s="275" t="inlineStr">
+      <c r="F5" s="274" t="inlineStr">
         <is>
           <t>0.7995±0.0305</t>
         </is>
       </c>
+      <c r="G5" s="274" t="inlineStr">
+        <is>
+          <t>-0.3488</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="20" customHeight="1" s="220">
-      <c r="A6" s="276" t="n"/>
-      <c r="B6" s="277" t="inlineStr">
+      <c r="A6" s="275" t="n"/>
+      <c r="B6" s="276" t="inlineStr">
         <is>
           <t>ContraWR</t>
         </is>
       </c>
-      <c r="C6" s="278" t="n">
+      <c r="C6" s="277" t="n">
         <v>1.57</v>
       </c>
-      <c r="D6" s="279" t="inlineStr">
+      <c r="D6" s="278" t="inlineStr">
         <is>
           <t>0.6362±0.0137</t>
         </is>
       </c>
-      <c r="E6" s="280" t="inlineStr">
+      <c r="E6" s="279" t="inlineStr">
         <is>
           <t>0.5072±0.0294</t>
         </is>
       </c>
-      <c r="F6" s="280" t="inlineStr">
+      <c r="F6" s="279" t="inlineStr">
         <is>
           <t>0.8905±0.0195</t>
         </is>
       </c>
+      <c r="G6" s="279" t="inlineStr">
+        <is>
+          <t>-0.0392</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="20" customHeight="1" s="220">
-      <c r="A7" s="276" t="n"/>
-      <c r="B7" s="277" t="inlineStr">
+      <c r="A7" s="275" t="n"/>
+      <c r="B7" s="276" t="inlineStr">
         <is>
           <t>CNN-Transformer</t>
         </is>
       </c>
-      <c r="C7" s="278" t="n">
+      <c r="C7" s="277" t="n">
         <v>3.15</v>
       </c>
-      <c r="D7" s="279" t="inlineStr">
+      <c r="D7" s="278" t="inlineStr">
         <is>
           <t>0.6420±0.0476</t>
         </is>
       </c>
-      <c r="E7" s="280" t="inlineStr">
+      <c r="E7" s="279" t="inlineStr">
         <is>
           <t>0.5057±0.0605</t>
         </is>
       </c>
-      <c r="F7" s="280" t="inlineStr">
+      <c r="F7" s="279" t="inlineStr">
         <is>
           <t>0.9106±0.0068</t>
         </is>
       </c>
+      <c r="G7" s="279" t="inlineStr">
+        <is>
+          <t>-0.0407</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="20" customHeight="1" s="220">
-      <c r="A8" s="276" t="n"/>
-      <c r="B8" s="277" t="inlineStr">
+      <c r="A8" s="275" t="n"/>
+      <c r="B8" s="276" t="inlineStr">
         <is>
           <t>FFCL</t>
         </is>
       </c>
-      <c r="C8" s="278" t="n">
+      <c r="C8" s="277" t="n">
         <v>2.46</v>
       </c>
-      <c r="D8" s="279" t="inlineStr">
+      <c r="D8" s="278" t="inlineStr">
         <is>
           <t>0.6163±0.0119</t>
         </is>
       </c>
-      <c r="E8" s="280" t="inlineStr">
+      <c r="E8" s="279" t="inlineStr">
         <is>
           <t>0.5341±0.0441</t>
         </is>
       </c>
-      <c r="F8" s="280" t="inlineStr">
+      <c r="F8" s="279" t="inlineStr">
         <is>
           <t>0.9124±0.0087</t>
         </is>
       </c>
+      <c r="G8" s="279" t="inlineStr">
+        <is>
+          <t>-0.0123</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="20" customHeight="1" s="220">
-      <c r="A9" s="276" t="n"/>
-      <c r="B9" s="277" t="inlineStr">
+      <c r="A9" s="275" t="n"/>
+      <c r="B9" s="276" t="inlineStr">
         <is>
           <t>ST-Transformer</t>
         </is>
       </c>
-      <c r="C9" s="278" t="n">
+      <c r="C9" s="277" t="n">
         <v>3.43</v>
       </c>
-      <c r="D9" s="279" t="inlineStr">
+      <c r="D9" s="278" t="inlineStr">
         <is>
           <t>0.5551±0.0849</t>
         </is>
       </c>
-      <c r="E9" s="280" t="inlineStr">
+      <c r="E9" s="279" t="inlineStr">
         <is>
           <t>0.2407±0.0926</t>
         </is>
       </c>
-      <c r="F9" s="280" t="inlineStr">
+      <c r="F9" s="279" t="inlineStr">
         <is>
           <t>0.7208±0.0847</t>
         </is>
       </c>
+      <c r="G9" s="279" t="inlineStr">
+        <is>
+          <t>-0.3057</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="20" customHeight="1" s="220">
-      <c r="A10" s="271" t="inlineStr">
+      <c r="A10" s="270" t="inlineStr">
         <is>
           <t>B FM · 官方预训练权重</t>
         </is>
       </c>
-      <c r="B10" s="281" t="inlineStr">
+      <c r="B10" s="280" t="inlineStr">
         <is>
           <t>BIOT (pretrained)</t>
         </is>
       </c>
-      <c r="C10" s="282" t="n">
+      <c r="C10" s="281" t="n">
         <v>3.19</v>
       </c>
-      <c r="D10" s="283" t="inlineStr">
+      <c r="D10" s="282" t="inlineStr">
         <is>
           <t>0.6190±0.0365</t>
         </is>
       </c>
-      <c r="E10" s="284" t="inlineStr">
+      <c r="E10" s="283" t="inlineStr">
         <is>
           <t>0.5601±0.0630</t>
         </is>
       </c>
-      <c r="F10" s="284" t="inlineStr">
+      <c r="F10" s="283" t="inlineStr">
         <is>
           <t>0.8738±0.0030</t>
         </is>
       </c>
+      <c r="G10" s="283" t="inlineStr">
+        <is>
+          <t>+0.0137</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="20" customHeight="1" s="220">
-      <c r="A11" s="276" t="n"/>
-      <c r="B11" s="277" t="inlineStr">
+      <c r="A11" s="275" t="n"/>
+      <c r="B11" s="276" t="inlineStr">
         <is>
           <t>LaBraM-Base (pretrained)</t>
         </is>
       </c>
-      <c r="C11" s="278" t="n">
+      <c r="C11" s="277" t="n">
         <v>5.82</v>
       </c>
-      <c r="D11" s="279" t="inlineStr">
+      <c r="D11" s="278" t="inlineStr">
         <is>
           <t>0.5855±0.0387</t>
         </is>
       </c>
-      <c r="E11" s="280" t="inlineStr">
+      <c r="E11" s="279" t="inlineStr">
         <is>
           <t>0.4519±0.0791</t>
         </is>
       </c>
-      <c r="F11" s="280" t="inlineStr">
+      <c r="F11" s="279" t="inlineStr">
         <is>
           <t>0.8709±0.0507</t>
         </is>
       </c>
+      <c r="G11" s="279" t="inlineStr">
+        <is>
+          <t>-0.0945</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="20" customHeight="1" s="220">
-      <c r="A12" s="276" t="n"/>
-      <c r="B12" s="277" t="inlineStr">
+      <c r="A12" s="275" t="n"/>
+      <c r="B12" s="276" t="inlineStr">
         <is>
           <t>CBraMod (pretrained)</t>
         </is>
       </c>
-      <c r="C12" s="278" t="n">
+      <c r="C12" s="277" t="n">
         <v>30.65</v>
       </c>
-      <c r="D12" s="279" t="inlineStr">
+      <c r="D12" s="278" t="inlineStr">
         <is>
           <t>0.5446±0.0162</t>
         </is>
       </c>
-      <c r="E12" s="280" t="inlineStr">
+      <c r="E12" s="279" t="inlineStr">
         <is>
           <t>0.2332±0.0798</t>
         </is>
       </c>
-      <c r="F12" s="280" t="inlineStr">
+      <c r="F12" s="279" t="inlineStr">
         <is>
           <t>0.7828±0.0387</t>
         </is>
       </c>
+      <c r="G12" s="279" t="inlineStr">
+        <is>
+          <t>-0.3132</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="20" customHeight="1" s="220">
-      <c r="A13" s="276" t="n"/>
-      <c r="B13" s="277" t="inlineStr">
+      <c r="A13" s="275" t="n"/>
+      <c r="B13" s="276" t="inlineStr">
         <is>
           <t>EEGPT</t>
         </is>
       </c>
-      <c r="C13" s="278" t="n">
+      <c r="C13" s="277" t="n">
         <v>25.69</v>
       </c>
-      <c r="D13" s="279" t="inlineStr">
+      <c r="D13" s="278" t="inlineStr">
         <is>
           <t>0.5468±0.0516</t>
         </is>
       </c>
-      <c r="E13" s="280" t="inlineStr">
+      <c r="E13" s="279" t="inlineStr">
         <is>
           <t>0.2811±0.1082</t>
         </is>
       </c>
-      <c r="F13" s="280" t="inlineStr">
+      <c r="F13" s="279" t="inlineStr">
         <is>
           <t>0.8574±0.0308</t>
         </is>
       </c>
+      <c r="G13" s="279" t="inlineStr">
+        <is>
+          <t>-0.2653</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="20" customHeight="1" s="220">
-      <c r="A14" s="276" t="n"/>
-      <c r="B14" s="277" t="inlineStr">
+      <c r="A14" s="275" t="n"/>
+      <c r="B14" s="276" t="inlineStr">
         <is>
           <t>TFM-Tokenizer</t>
         </is>
       </c>
-      <c r="C14" s="278" t="n">
+      <c r="C14" s="277" t="n">
         <v>1.89</v>
       </c>
-      <c r="D14" s="279" t="inlineStr">
+      <c r="D14" s="278" t="inlineStr">
         <is>
           <t>0.6344±0.0133</t>
         </is>
       </c>
-      <c r="E14" s="280" t="inlineStr">
+      <c r="E14" s="279" t="inlineStr">
         <is>
           <t>0.6269±0.0205</t>
         </is>
       </c>
-      <c r="F14" s="280" t="inlineStr">
+      <c r="F14" s="279" t="inlineStr">
         <is>
           <t>0.9291±0.0045</t>
         </is>
       </c>
+      <c r="G14" s="279" t="inlineStr">
+        <is>
+          <t>+0.0805</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="20" customHeight="1" s="220">
-      <c r="A15" s="271" t="inlineStr">
+      <c r="A15" s="270" t="inlineStr">
         <is>
           <t>C FM · 同 pipeline scratch</t>
         </is>
       </c>
-      <c r="B15" s="285" t="inlineStr">
+      <c r="B15" s="284" t="inlineStr">
         <is>
           <t>BIOT (scratch)</t>
         </is>
       </c>
-      <c r="C15" s="286" t="n">
+      <c r="C15" s="285" t="n">
         <v>3.19</v>
       </c>
-      <c r="D15" s="287" t="inlineStr">
+      <c r="D15" s="286" t="inlineStr">
         <is>
           <t>0.6240±0.0580</t>
         </is>
       </c>
-      <c r="E15" s="288" t="inlineStr">
+      <c r="E15" s="287" t="inlineStr">
         <is>
           <t>0.5661±0.0589</t>
         </is>
       </c>
-      <c r="F15" s="288" t="inlineStr">
+      <c r="F15" s="287" t="inlineStr">
         <is>
           <t>0.8748±0.0151</t>
         </is>
       </c>
+      <c r="G15" s="287" t="inlineStr">
+        <is>
+          <t>+0.0197</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="20" customHeight="1" s="220">
-      <c r="A16" s="276" t="n"/>
-      <c r="B16" s="277" t="inlineStr">
+      <c r="A16" s="275" t="n"/>
+      <c r="B16" s="276" t="inlineStr">
         <is>
           <t>LaBraM-Base (scratch)</t>
         </is>
       </c>
-      <c r="C16" s="278" t="n">
+      <c r="C16" s="277" t="n">
         <v>5.82</v>
       </c>
-      <c r="D16" s="279" t="inlineStr">
+      <c r="D16" s="278" t="inlineStr">
         <is>
           <t>0.5854±0.0530</t>
         </is>
       </c>
-      <c r="E16" s="280" t="inlineStr">
+      <c r="E16" s="279" t="inlineStr">
         <is>
           <t>0.3596±0.0407</t>
         </is>
       </c>
-      <c r="F16" s="280" t="inlineStr">
+      <c r="F16" s="279" t="inlineStr">
         <is>
           <t>0.8226±0.0243</t>
         </is>
       </c>
+      <c r="G16" s="279" t="inlineStr">
+        <is>
+          <t>-0.1868</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="20" customHeight="1" s="220">
-      <c r="A17" s="276" t="n"/>
-      <c r="B17" s="277" t="inlineStr">
+      <c r="A17" s="275" t="n"/>
+      <c r="B17" s="276" t="inlineStr">
         <is>
           <t>CBraMod (scratch)</t>
         </is>
       </c>
-      <c r="C17" s="278" t="n">
+      <c r="C17" s="277" t="n">
         <v>30.65</v>
       </c>
-      <c r="D17" s="279" t="inlineStr">
+      <c r="D17" s="278" t="inlineStr">
         <is>
           <t>0.6018±0.0721</t>
         </is>
       </c>
-      <c r="E17" s="280" t="inlineStr">
+      <c r="E17" s="279" t="inlineStr">
         <is>
           <t>0.3169±0.1674</t>
         </is>
       </c>
-      <c r="F17" s="280" t="inlineStr">
+      <c r="F17" s="279" t="inlineStr">
         <is>
           <t>0.7802±0.1088</t>
         </is>
       </c>
+      <c r="G17" s="279" t="inlineStr">
+        <is>
+          <t>-0.2295</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="20" customHeight="1" s="220">
-      <c r="A18" s="276" t="n"/>
-      <c r="B18" s="289" t="inlineStr">
+      <c r="A18" s="275" t="n"/>
+      <c r="B18" s="288" t="inlineStr">
         <is>
           <t>PACLock (from scratch, full)</t>
         </is>
       </c>
-      <c r="C18" s="290" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="D18" s="291" t="n"/>
-      <c r="E18" s="292" t="n"/>
-      <c r="F18" s="292" t="n"/>
+      <c r="C18" s="289" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="D18" s="290" t="inlineStr">
+        <is>
+          <t>0.5223±0.0175</t>
+        </is>
+      </c>
+      <c r="E18" s="291" t="inlineStr">
+        <is>
+          <t>0.5464±0.0255</t>
+        </is>
+      </c>
+      <c r="F18" s="291" t="inlineStr">
+        <is>
+          <t>0.9035±0.0008</t>
+        </is>
+      </c>
+      <c r="G18" s="291" t="n"/>
     </row>
     <row r="19" ht="15" customHeight="1" s="220"/>
     <row r="20" ht="24" customHeight="1" s="220"/>
@@ -11411,8 +11898,8 @@
     <row r="55" ht="42" customHeight="1" s="220"/>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A2:G2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" scale="100" fitToHeight="1" fitToWidth="1" firstPageNumber="1" useFirstPageNumber="0" pageOrder="downThenOver"/>
@@ -11476,483 +11963,483 @@
       <c r="G3" s="268" t="n"/>
     </row>
     <row r="4" ht="28" customHeight="1" s="220">
-      <c r="A4" s="270" t="inlineStr">
+      <c r="A4" s="269" t="inlineStr">
         <is>
           <t>分组</t>
         </is>
       </c>
-      <c r="B4" s="270" t="inlineStr">
+      <c r="B4" s="269" t="inlineStr">
         <is>
           <t>模型</t>
         </is>
       </c>
-      <c r="C4" s="270" t="inlineStr">
+      <c r="C4" s="269" t="inlineStr">
         <is>
           <t>参数量 (M)</t>
         </is>
       </c>
-      <c r="D4" s="270" t="inlineStr">
+      <c r="D4" s="269" t="inlineStr">
         <is>
           <t>Balanced Acc</t>
         </is>
       </c>
-      <c r="E4" s="270" t="inlineStr">
+      <c r="E4" s="269" t="inlineStr">
         <is>
           <t>Cohen's Kappa</t>
         </is>
       </c>
-      <c r="F4" s="270" t="inlineStr">
+      <c r="F4" s="269" t="inlineStr">
         <is>
           <t>Weighted F1</t>
         </is>
       </c>
-      <c r="G4" s="270" t="inlineStr">
+      <c r="G4" s="269" t="inlineStr">
         <is>
           <t>ΔCohen's Kappa vs PACLock</t>
         </is>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1" s="220">
-      <c r="A5" s="271" t="inlineStr">
+      <c r="A5" s="270" t="inlineStr">
         <is>
           <t>A 轻量监督基线</t>
         </is>
       </c>
-      <c r="B5" s="272" t="inlineStr">
+      <c r="B5" s="271" t="inlineStr">
         <is>
           <t>SPaRCNet</t>
         </is>
       </c>
-      <c r="C5" s="273" t="n">
+      <c r="C5" s="272" t="n">
         <v>1.23</v>
       </c>
-      <c r="D5" s="274" t="inlineStr">
+      <c r="D5" s="273" t="inlineStr">
         <is>
           <t>0.6855±0.0018</t>
         </is>
       </c>
-      <c r="E5" s="275" t="inlineStr">
+      <c r="E5" s="274" t="inlineStr">
         <is>
           <t>0.6714±0.0095</t>
         </is>
       </c>
-      <c r="F5" s="275" t="inlineStr">
+      <c r="F5" s="274" t="inlineStr">
         <is>
           <t>0.7718±0.0058</t>
         </is>
       </c>
-      <c r="G5" s="275" t="inlineStr">
+      <c r="G5" s="274" t="inlineStr">
         <is>
           <t>+0.0255</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1" s="220">
-      <c r="A6" s="276" t="n"/>
-      <c r="B6" s="277" t="inlineStr">
+      <c r="A6" s="275" t="n"/>
+      <c r="B6" s="276" t="inlineStr">
         <is>
           <t>ContraWR</t>
         </is>
       </c>
-      <c r="C6" s="278" t="n">
+      <c r="C6" s="277" t="n">
         <v>1.56</v>
       </c>
-      <c r="D6" s="279" t="inlineStr">
+      <c r="D6" s="278" t="inlineStr">
         <is>
           <t>0.7059±0.0080</t>
         </is>
       </c>
-      <c r="E6" s="280" t="inlineStr">
+      <c r="E6" s="279" t="inlineStr">
         <is>
           <t>0.6916±0.0119</t>
         </is>
       </c>
-      <c r="F6" s="280" t="inlineStr">
+      <c r="F6" s="279" t="inlineStr">
         <is>
           <t>0.7866±0.0098</t>
         </is>
       </c>
-      <c r="G6" s="280" t="inlineStr">
+      <c r="G6" s="279" t="inlineStr">
         <is>
           <t>+0.0457</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1" s="220">
-      <c r="A7" s="276" t="n"/>
-      <c r="B7" s="277" t="inlineStr">
+      <c r="A7" s="275" t="n"/>
+      <c r="B7" s="276" t="inlineStr">
         <is>
           <t>CNN-Transformer</t>
         </is>
       </c>
-      <c r="C7" s="278" t="n">
+      <c r="C7" s="277" t="n">
         <v>3.15</v>
       </c>
-      <c r="D7" s="279" t="inlineStr">
+      <c r="D7" s="278" t="inlineStr">
         <is>
           <t>0.6989±0.0105</t>
         </is>
       </c>
-      <c r="E7" s="280" t="inlineStr">
+      <c r="E7" s="279" t="inlineStr">
         <is>
           <t>0.6778±0.0116</t>
         </is>
       </c>
-      <c r="F7" s="280" t="inlineStr">
+      <c r="F7" s="279" t="inlineStr">
         <is>
           <t>0.7771±0.0075</t>
         </is>
       </c>
-      <c r="G7" s="280" t="inlineStr">
+      <c r="G7" s="279" t="inlineStr">
         <is>
           <t>+0.0319</t>
         </is>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1" s="220">
-      <c r="A8" s="276" t="n"/>
-      <c r="B8" s="277" t="inlineStr">
+      <c r="A8" s="275" t="n"/>
+      <c r="B8" s="276" t="inlineStr">
         <is>
           <t>FFCL</t>
         </is>
       </c>
-      <c r="C8" s="278" t="n">
+      <c r="C8" s="277" t="n">
         <v>2.51</v>
       </c>
-      <c r="D8" s="279" t="inlineStr">
+      <c r="D8" s="278" t="inlineStr">
         <is>
           <t>0.6963±0.0082</t>
         </is>
       </c>
-      <c r="E8" s="280" t="inlineStr">
+      <c r="E8" s="279" t="inlineStr">
         <is>
           <t>0.6780±0.0039</t>
         </is>
       </c>
-      <c r="F8" s="280" t="inlineStr">
+      <c r="F8" s="279" t="inlineStr">
         <is>
           <t>0.7716±0.0066</t>
         </is>
       </c>
-      <c r="G8" s="280" t="inlineStr">
+      <c r="G8" s="279" t="inlineStr">
         <is>
           <t>+0.0321</t>
         </is>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1" s="220">
-      <c r="A9" s="276" t="n"/>
-      <c r="B9" s="277" t="inlineStr">
+      <c r="A9" s="275" t="n"/>
+      <c r="B9" s="276" t="inlineStr">
         <is>
           <t>ST-Transformer</t>
         </is>
       </c>
-      <c r="C9" s="278" t="n">
+      <c r="C9" s="277" t="n">
         <v>3.41</v>
       </c>
-      <c r="D9" s="279" t="inlineStr">
+      <c r="D9" s="278" t="inlineStr">
         <is>
           <t>0.6576±0.0062</t>
         </is>
       </c>
-      <c r="E9" s="280" t="inlineStr">
+      <c r="E9" s="279" t="inlineStr">
         <is>
           <t>0.6553±0.0032</t>
         </is>
       </c>
-      <c r="F9" s="280" t="inlineStr">
+      <c r="F9" s="279" t="inlineStr">
         <is>
           <t>0.7607±0.0033</t>
         </is>
       </c>
-      <c r="G9" s="280" t="inlineStr">
+      <c r="G9" s="279" t="inlineStr">
         <is>
           <t>+0.0094</t>
         </is>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1" s="220">
-      <c r="A10" s="271" t="inlineStr">
+      <c r="A10" s="270" t="inlineStr">
         <is>
           <t>B FM · 官方预训练权重</t>
         </is>
       </c>
-      <c r="B10" s="281" t="inlineStr">
+      <c r="B10" s="280" t="inlineStr">
         <is>
           <t>BIOT (pretrained)</t>
         </is>
       </c>
-      <c r="C10" s="282" t="n">
+      <c r="C10" s="281" t="n">
         <v>3.19</v>
       </c>
-      <c r="D10" s="283" t="inlineStr">
+      <c r="D10" s="282" t="inlineStr">
         <is>
           <t>0.5625±0.0302</t>
         </is>
       </c>
-      <c r="E10" s="284" t="inlineStr">
+      <c r="E10" s="283" t="inlineStr">
         <is>
           <t>0.5940±0.0154</t>
         </is>
       </c>
-      <c r="F10" s="284" t="inlineStr">
+      <c r="F10" s="283" t="inlineStr">
         <is>
           <t>0.7172±0.0128</t>
         </is>
       </c>
-      <c r="G10" s="284" t="inlineStr">
+      <c r="G10" s="283" t="inlineStr">
         <is>
           <t>-0.0519</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1" s="220">
-      <c r="A11" s="276" t="n"/>
-      <c r="B11" s="277" t="inlineStr">
+      <c r="A11" s="275" t="n"/>
+      <c r="B11" s="276" t="inlineStr">
         <is>
           <t>LaBraM-Base (pretrained)</t>
         </is>
       </c>
-      <c r="C11" s="278" t="n">
+      <c r="C11" s="277" t="n">
         <v>5.82</v>
       </c>
-      <c r="D11" s="279" t="inlineStr">
+      <c r="D11" s="278" t="inlineStr">
         <is>
           <t>0.6399±0.0144</t>
         </is>
       </c>
-      <c r="E11" s="280" t="inlineStr">
+      <c r="E11" s="279" t="inlineStr">
         <is>
           <t>0.6100±0.0065</t>
         </is>
       </c>
-      <c r="F11" s="280" t="inlineStr">
+      <c r="F11" s="279" t="inlineStr">
         <is>
           <t>0.7321±0.0069</t>
         </is>
       </c>
-      <c r="G11" s="280" t="inlineStr">
+      <c r="G11" s="279" t="inlineStr">
         <is>
           <t>-0.0359</t>
         </is>
       </c>
     </row>
     <row r="12" ht="20" customHeight="1" s="220">
-      <c r="A12" s="276" t="n"/>
-      <c r="B12" s="277" t="inlineStr">
+      <c r="A12" s="275" t="n"/>
+      <c r="B12" s="276" t="inlineStr">
         <is>
           <t>CBraMod (pretrained)</t>
         </is>
       </c>
-      <c r="C12" s="278" t="n">
+      <c r="C12" s="277" t="n">
         <v>9.85</v>
       </c>
-      <c r="D12" s="279" t="inlineStr">
+      <c r="D12" s="278" t="inlineStr">
         <is>
           <t>0.6848±0.0135</t>
         </is>
       </c>
-      <c r="E12" s="280" t="inlineStr">
+      <c r="E12" s="279" t="inlineStr">
         <is>
           <t>0.6715±0.0040</t>
         </is>
       </c>
-      <c r="F12" s="280" t="inlineStr">
+      <c r="F12" s="279" t="inlineStr">
         <is>
           <t>0.7665±0.0031</t>
         </is>
       </c>
-      <c r="G12" s="280" t="inlineStr">
+      <c r="G12" s="279" t="inlineStr">
         <is>
           <t>+0.0256</t>
         </is>
       </c>
     </row>
     <row r="13" ht="20" customHeight="1" s="220">
-      <c r="A13" s="276" t="n"/>
-      <c r="B13" s="277" t="inlineStr">
+      <c r="A13" s="275" t="n"/>
+      <c r="B13" s="276" t="inlineStr">
         <is>
           <t>EEGPT</t>
         </is>
       </c>
-      <c r="C13" s="278" t="n">
+      <c r="C13" s="277" t="n">
         <v>25.69</v>
       </c>
-      <c r="D13" s="279" t="inlineStr">
+      <c r="D13" s="278" t="inlineStr">
         <is>
           <t>0.6385±0.0099</t>
         </is>
       </c>
-      <c r="E13" s="280" t="inlineStr">
+      <c r="E13" s="279" t="inlineStr">
         <is>
           <t>0.5978±0.0105</t>
         </is>
       </c>
-      <c r="F13" s="280" t="inlineStr">
+      <c r="F13" s="279" t="inlineStr">
         <is>
           <t>0.7253±0.0063</t>
         </is>
       </c>
-      <c r="G13" s="280" t="inlineStr">
+      <c r="G13" s="279" t="inlineStr">
         <is>
           <t>-0.0481</t>
         </is>
       </c>
     </row>
     <row r="14" ht="20" customHeight="1" s="220">
-      <c r="A14" s="276" t="n"/>
-      <c r="B14" s="277" t="inlineStr">
+      <c r="A14" s="275" t="n"/>
+      <c r="B14" s="276" t="inlineStr">
         <is>
           <t>TFM-Tokenizer</t>
         </is>
       </c>
-      <c r="C14" s="278" t="n">
+      <c r="C14" s="277" t="n">
         <v>1.89</v>
       </c>
-      <c r="D14" s="279" t="inlineStr">
+      <c r="D14" s="278" t="inlineStr">
         <is>
           <t>0.5574±0.0075</t>
         </is>
       </c>
-      <c r="E14" s="280" t="inlineStr">
+      <c r="E14" s="279" t="inlineStr">
         <is>
           <t>0.6138±0.0020</t>
         </is>
       </c>
-      <c r="F14" s="280" t="inlineStr">
+      <c r="F14" s="279" t="inlineStr">
         <is>
           <t>0.7266±0.0014</t>
         </is>
       </c>
-      <c r="G14" s="280" t="inlineStr">
+      <c r="G14" s="279" t="inlineStr">
         <is>
           <t>-0.0321</t>
         </is>
       </c>
     </row>
     <row r="15" ht="20" customHeight="1" s="220">
-      <c r="A15" s="271" t="inlineStr">
+      <c r="A15" s="270" t="inlineStr">
         <is>
           <t>C FM · 同 pipeline scratch</t>
         </is>
       </c>
-      <c r="B15" s="285" t="inlineStr">
+      <c r="B15" s="284" t="inlineStr">
         <is>
           <t>BIOT (scratch)</t>
         </is>
       </c>
-      <c r="C15" s="286" t="n">
+      <c r="C15" s="285" t="n">
         <v>3.18</v>
       </c>
-      <c r="D15" s="287" t="inlineStr">
+      <c r="D15" s="286" t="inlineStr">
         <is>
           <t>0.6372±0.0118</t>
         </is>
       </c>
-      <c r="E15" s="288" t="inlineStr">
+      <c r="E15" s="287" t="inlineStr">
         <is>
           <t>0.6547±0.0157</t>
         </is>
       </c>
-      <c r="F15" s="288" t="inlineStr">
+      <c r="F15" s="287" t="inlineStr">
         <is>
           <t>0.7655±0.0068</t>
         </is>
       </c>
-      <c r="G15" s="288" t="inlineStr">
+      <c r="G15" s="287" t="inlineStr">
         <is>
           <t>+0.0088</t>
         </is>
       </c>
     </row>
     <row r="16" ht="20" customHeight="1" s="220">
-      <c r="A16" s="276" t="n"/>
-      <c r="B16" s="277" t="inlineStr">
+      <c r="A16" s="275" t="n"/>
+      <c r="B16" s="276" t="inlineStr">
         <is>
           <t>LaBraM-Base (scratch)</t>
         </is>
       </c>
-      <c r="C16" s="278" t="n">
+      <c r="C16" s="277" t="n">
         <v>5.82</v>
       </c>
-      <c r="D16" s="279" t="inlineStr">
+      <c r="D16" s="278" t="inlineStr">
         <is>
           <t>0.6138±0.0065</t>
         </is>
       </c>
-      <c r="E16" s="280" t="inlineStr">
+      <c r="E16" s="279" t="inlineStr">
         <is>
           <t>0.5980±0.0081</t>
         </is>
       </c>
-      <c r="F16" s="280" t="inlineStr">
+      <c r="F16" s="279" t="inlineStr">
         <is>
           <t>0.7150±0.0076</t>
         </is>
       </c>
-      <c r="G16" s="280" t="inlineStr">
+      <c r="G16" s="279" t="inlineStr">
         <is>
           <t>-0.0479</t>
         </is>
       </c>
     </row>
     <row r="17" ht="20" customHeight="1" s="220">
-      <c r="A17" s="276" t="n"/>
-      <c r="B17" s="277" t="inlineStr">
+      <c r="A17" s="275" t="n"/>
+      <c r="B17" s="276" t="inlineStr">
         <is>
           <t>CBraMod (scratch)</t>
         </is>
       </c>
-      <c r="C17" s="278" t="n">
+      <c r="C17" s="277" t="n">
         <v>9.85</v>
       </c>
-      <c r="D17" s="279" t="inlineStr">
+      <c r="D17" s="278" t="inlineStr">
         <is>
           <t>0.6588±0.0028</t>
         </is>
       </c>
-      <c r="E17" s="280" t="inlineStr">
+      <c r="E17" s="279" t="inlineStr">
         <is>
           <t>0.6545±0.0029</t>
         </is>
       </c>
-      <c r="F17" s="280" t="inlineStr">
+      <c r="F17" s="279" t="inlineStr">
         <is>
           <t>0.7614±0.0033</t>
         </is>
       </c>
-      <c r="G17" s="280" t="inlineStr">
+      <c r="G17" s="279" t="inlineStr">
         <is>
           <t>+0.0086</t>
         </is>
       </c>
     </row>
     <row r="18" ht="20" customHeight="1" s="220">
-      <c r="A18" s="276" t="n"/>
-      <c r="B18" s="289" t="inlineStr">
+      <c r="A18" s="275" t="n"/>
+      <c r="B18" s="288" t="inlineStr">
         <is>
           <t>PACLock (from scratch, full)</t>
         </is>
       </c>
-      <c r="C18" s="290" t="n">
+      <c r="C18" s="289" t="n">
         <v>1.62</v>
       </c>
-      <c r="D18" s="291" t="inlineStr">
+      <c r="D18" s="290" t="inlineStr">
         <is>
           <t>0.6284±0.0046</t>
         </is>
       </c>
-      <c r="E18" s="292" t="inlineStr">
+      <c r="E18" s="291" t="inlineStr">
         <is>
           <t>0.6459±0.0054</t>
         </is>
       </c>
-      <c r="F18" s="292" t="inlineStr">
+      <c r="F18" s="291" t="inlineStr">
         <is>
           <t>0.7563±0.0043</t>
         </is>
       </c>
-      <c r="G18" s="292" t="n"/>
+      <c r="G18" s="291" t="n"/>
     </row>
     <row r="19" ht="15" customHeight="1" s="220"/>
     <row r="20" ht="24" customHeight="1" s="220"/>
@@ -12027,6 +12514,7 @@
     <col width="17" customWidth="1" style="220" min="4" max="4"/>
     <col width="17" customWidth="1" style="219" min="5" max="7"/>
     <col width="17" customWidth="1" style="220" min="6" max="6"/>
+    <col width="17" customWidth="1" style="220" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1" s="220">
@@ -12039,7 +12527,8 @@
       <c r="C1" s="228" t="n"/>
       <c r="D1" s="228" t="n"/>
       <c r="E1" s="228" t="n"/>
-      <c r="F1" s="229" t="n"/>
+      <c r="F1" s="228" t="n"/>
+      <c r="G1" s="229" t="n"/>
     </row>
     <row r="2" ht="22" customHeight="1" s="220">
       <c r="A2" s="267" t="inlineStr">
@@ -12047,7 +12536,7 @@
           <t>主指标：Cohen's Kappa</t>
         </is>
       </c>
-      <c r="F2" s="231" t="n"/>
+      <c r="G2" s="231" t="n"/>
     </row>
     <row r="3" ht="8" customHeight="1" s="220">
       <c r="A3" s="268" t="n"/>
@@ -12056,403 +12545,486 @@
       <c r="D3" s="268" t="n"/>
       <c r="E3" s="268" t="n"/>
       <c r="F3" s="268" t="n"/>
-      <c r="G3" s="269" t="n"/>
+      <c r="G3" s="268" t="n"/>
     </row>
     <row r="4" ht="28" customHeight="1" s="220">
-      <c r="A4" s="270" t="inlineStr">
+      <c r="A4" s="269" t="inlineStr">
         <is>
           <t>分组</t>
         </is>
       </c>
-      <c r="B4" s="270" t="inlineStr">
+      <c r="B4" s="269" t="inlineStr">
         <is>
           <t>模型</t>
         </is>
       </c>
-      <c r="C4" s="270" t="inlineStr">
+      <c r="C4" s="269" t="inlineStr">
         <is>
           <t>参数量 (M)</t>
         </is>
       </c>
-      <c r="D4" s="270" t="inlineStr">
+      <c r="D4" s="269" t="inlineStr">
         <is>
           <t>Balanced Acc</t>
         </is>
       </c>
-      <c r="E4" s="270" t="inlineStr">
+      <c r="E4" s="269" t="inlineStr">
         <is>
           <t>Cohen's Kappa</t>
         </is>
       </c>
-      <c r="F4" s="270" t="inlineStr">
+      <c r="F4" s="269" t="inlineStr">
         <is>
           <t>Weighted F1</t>
         </is>
       </c>
+      <c r="G4" s="269" t="inlineStr">
+        <is>
+          <t>ΔCohen's Kappa vs PACLock</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="20" customHeight="1" s="220">
-      <c r="A5" s="271" t="inlineStr">
+      <c r="A5" s="270" t="inlineStr">
         <is>
           <t>A 轻量监督基线</t>
         </is>
       </c>
-      <c r="B5" s="272" t="inlineStr">
+      <c r="B5" s="271" t="inlineStr">
         <is>
           <t>SPaRCNet</t>
         </is>
       </c>
-      <c r="C5" s="273" t="n">
+      <c r="C5" s="272" t="n">
         <v>1.38</v>
       </c>
-      <c r="D5" s="274" t="inlineStr">
+      <c r="D5" s="273" t="inlineStr">
         <is>
           <t>0.7790±0.0090</t>
         </is>
       </c>
-      <c r="E5" s="275" t="inlineStr">
+      <c r="E5" s="274" t="inlineStr">
         <is>
           <t>0.7345±0.0161</t>
         </is>
       </c>
-      <c r="F5" s="275" t="inlineStr">
+      <c r="F5" s="274" t="inlineStr">
         <is>
           <t>0.7905±0.0113</t>
         </is>
       </c>
+      <c r="G5" s="274" t="inlineStr">
+        <is>
+          <t>+0.0393</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="20" customHeight="1" s="220">
-      <c r="A6" s="276" t="n"/>
-      <c r="B6" s="277" t="inlineStr">
+      <c r="A6" s="275" t="n"/>
+      <c r="B6" s="276" t="inlineStr">
         <is>
           <t>ContraWR</t>
         </is>
       </c>
-      <c r="C6" s="278" t="n">
+      <c r="C6" s="277" t="n">
         <v>1.57</v>
       </c>
-      <c r="D6" s="279" t="inlineStr">
+      <c r="D6" s="278" t="inlineStr">
         <is>
           <t>0.7947±0.0008</t>
         </is>
       </c>
-      <c r="E6" s="280" t="inlineStr">
+      <c r="E6" s="279" t="inlineStr">
         <is>
           <t>0.7520±0.0045</t>
         </is>
       </c>
-      <c r="F6" s="280" t="inlineStr">
+      <c r="F6" s="279" t="inlineStr">
         <is>
           <t>0.8063±0.0051</t>
         </is>
       </c>
+      <c r="G6" s="279" t="inlineStr">
+        <is>
+          <t>+0.0568</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="20" customHeight="1" s="220">
-      <c r="A7" s="276" t="n"/>
-      <c r="B7" s="277" t="inlineStr">
+      <c r="A7" s="275" t="n"/>
+      <c r="B7" s="276" t="inlineStr">
         <is>
           <t>CNN-Transformer</t>
         </is>
       </c>
-      <c r="C7" s="278" t="n">
+      <c r="C7" s="277" t="n">
         <v>3.15</v>
       </c>
-      <c r="D7" s="279" t="inlineStr">
+      <c r="D7" s="278" t="inlineStr">
         <is>
           <t>0.7918±0.0018</t>
         </is>
       </c>
-      <c r="E7" s="280" t="inlineStr">
+      <c r="E7" s="279" t="inlineStr">
         <is>
           <t>0.7532±0.0058</t>
         </is>
       </c>
-      <c r="F7" s="280" t="inlineStr">
+      <c r="F7" s="279" t="inlineStr">
         <is>
           <t>0.8058±0.0032</t>
         </is>
       </c>
+      <c r="G7" s="279" t="inlineStr">
+        <is>
+          <t>+0.0580</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="20" customHeight="1" s="220">
-      <c r="A8" s="276" t="n"/>
-      <c r="B8" s="277" t="inlineStr">
+      <c r="A8" s="275" t="n"/>
+      <c r="B8" s="276" t="inlineStr">
         <is>
           <t>FFCL</t>
         </is>
       </c>
-      <c r="C8" s="278" t="n">
+      <c r="C8" s="277" t="n">
         <v>2.67</v>
       </c>
-      <c r="D8" s="279" t="inlineStr">
+      <c r="D8" s="278" t="inlineStr">
         <is>
           <t>0.7723±0.0082</t>
         </is>
       </c>
-      <c r="E8" s="280" t="inlineStr">
+      <c r="E8" s="279" t="inlineStr">
         <is>
           <t>0.7337±0.0126</t>
         </is>
       </c>
-      <c r="F8" s="280" t="inlineStr">
+      <c r="F8" s="279" t="inlineStr">
         <is>
           <t>0.7890±0.0088</t>
         </is>
       </c>
+      <c r="G8" s="279" t="inlineStr">
+        <is>
+          <t>+0.0385</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="20" customHeight="1" s="220">
-      <c r="A9" s="276" t="n"/>
-      <c r="B9" s="277" t="inlineStr">
+      <c r="A9" s="275" t="n"/>
+      <c r="B9" s="276" t="inlineStr">
         <is>
           <t>ST-Transformer</t>
         </is>
       </c>
-      <c r="C9" s="278" t="n">
+      <c r="C9" s="277" t="n">
         <v>3.42</v>
       </c>
-      <c r="D9" s="279" t="inlineStr">
+      <c r="D9" s="278" t="inlineStr">
         <is>
           <t>0.5237±0.0668</t>
         </is>
       </c>
-      <c r="E9" s="280" t="inlineStr">
+      <c r="E9" s="279" t="inlineStr">
         <is>
           <t>0.3927±0.1105</t>
         </is>
       </c>
-      <c r="F9" s="280" t="inlineStr">
+      <c r="F9" s="279" t="inlineStr">
         <is>
           <t>0.4926±0.1033</t>
         </is>
       </c>
+      <c r="G9" s="279" t="inlineStr">
+        <is>
+          <t>-0.3025</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="20" customHeight="1" s="220">
-      <c r="A10" s="271" t="inlineStr">
+      <c r="A10" s="270" t="inlineStr">
         <is>
           <t>B FM · 官方预训练权重</t>
         </is>
       </c>
-      <c r="B10" s="281" t="inlineStr">
+      <c r="B10" s="280" t="inlineStr">
         <is>
           <t>BIOT (pretrained)</t>
         </is>
       </c>
-      <c r="C10" s="282" t="n">
+      <c r="C10" s="281" t="n">
         <v>3.19</v>
       </c>
-      <c r="D10" s="283" t="inlineStr">
+      <c r="D10" s="282" t="inlineStr">
         <is>
           <t>0.7711±0.0040</t>
         </is>
       </c>
-      <c r="E10" s="284" t="inlineStr">
+      <c r="E10" s="283" t="inlineStr">
         <is>
           <t>0.7364±0.0046</t>
         </is>
       </c>
-      <c r="F10" s="284" t="inlineStr">
+      <c r="F10" s="283" t="inlineStr">
         <is>
           <t>0.7866±0.0019</t>
         </is>
       </c>
+      <c r="G10" s="283" t="inlineStr">
+        <is>
+          <t>+0.0412</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="20" customHeight="1" s="220">
-      <c r="A11" s="276" t="n"/>
-      <c r="B11" s="277" t="inlineStr">
+      <c r="A11" s="275" t="n"/>
+      <c r="B11" s="276" t="inlineStr">
         <is>
           <t>LaBraM-Base (pretrained)</t>
         </is>
       </c>
-      <c r="C11" s="278" t="n">
+      <c r="C11" s="277" t="n">
         <v>5.82</v>
       </c>
-      <c r="D11" s="279" t="inlineStr">
+      <c r="D11" s="278" t="inlineStr">
         <is>
           <t>0.7683±0.0119</t>
         </is>
       </c>
-      <c r="E11" s="280" t="inlineStr">
+      <c r="E11" s="279" t="inlineStr">
         <is>
           <t>0.7366±0.0145</t>
         </is>
       </c>
-      <c r="F11" s="280" t="inlineStr">
+      <c r="F11" s="279" t="inlineStr">
         <is>
           <t>0.7927±0.0111</t>
         </is>
       </c>
+      <c r="G11" s="279" t="inlineStr">
+        <is>
+          <t>+0.0414</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="20" customHeight="1" s="220">
-      <c r="A12" s="276" t="n"/>
-      <c r="B12" s="277" t="inlineStr">
+      <c r="A12" s="275" t="n"/>
+      <c r="B12" s="276" t="inlineStr">
         <is>
           <t>CBraMod (pretrained)</t>
         </is>
       </c>
-      <c r="C12" s="278" t="n">
+      <c r="C12" s="277" t="n">
         <v>26.47</v>
       </c>
-      <c r="D12" s="279" t="inlineStr">
+      <c r="D12" s="278" t="inlineStr">
         <is>
           <t>0.7842±0.0059</t>
         </is>
       </c>
-      <c r="E12" s="280" t="inlineStr">
+      <c r="E12" s="279" t="inlineStr">
         <is>
           <t>0.7540±0.0063</t>
         </is>
       </c>
-      <c r="F12" s="280" t="inlineStr">
+      <c r="F12" s="279" t="inlineStr">
         <is>
           <t>0.8105±0.0046</t>
         </is>
       </c>
+      <c r="G12" s="279" t="inlineStr">
+        <is>
+          <t>+0.0588</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="20" customHeight="1" s="220">
-      <c r="A13" s="276" t="n"/>
-      <c r="B13" s="277" t="inlineStr">
+      <c r="A13" s="275" t="n"/>
+      <c r="B13" s="276" t="inlineStr">
         <is>
           <t>EEGPT</t>
         </is>
       </c>
-      <c r="C13" s="278" t="n">
+      <c r="C13" s="277" t="n">
         <v>25.69</v>
       </c>
-      <c r="D13" s="279" t="inlineStr">
+      <c r="D13" s="278" t="inlineStr">
         <is>
           <t>0.7387±0.0205</t>
         </is>
       </c>
-      <c r="E13" s="280" t="inlineStr">
+      <c r="E13" s="279" t="inlineStr">
         <is>
           <t>0.7001±0.0167</t>
         </is>
       </c>
-      <c r="F13" s="280" t="inlineStr">
+      <c r="F13" s="279" t="inlineStr">
         <is>
           <t>0.7589±0.0179</t>
         </is>
       </c>
+      <c r="G13" s="279" t="inlineStr">
+        <is>
+          <t>+0.0049</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="20" customHeight="1" s="220">
-      <c r="A14" s="276" t="n"/>
-      <c r="B14" s="277" t="inlineStr">
+      <c r="A14" s="275" t="n"/>
+      <c r="B14" s="276" t="inlineStr">
         <is>
           <t>TFM-Tokenizer</t>
         </is>
       </c>
-      <c r="C14" s="278" t="n">
+      <c r="C14" s="277" t="n">
         <v>1.89</v>
       </c>
-      <c r="D14" s="279" t="inlineStr">
+      <c r="D14" s="278" t="inlineStr">
         <is>
           <t>0.7400±0.0067</t>
         </is>
       </c>
-      <c r="E14" s="280" t="inlineStr">
+      <c r="E14" s="279" t="inlineStr">
         <is>
           <t>0.7102±0.0030</t>
         </is>
       </c>
-      <c r="F14" s="280" t="inlineStr">
+      <c r="F14" s="279" t="inlineStr">
         <is>
           <t>0.7736±0.0043</t>
         </is>
       </c>
+      <c r="G14" s="279" t="inlineStr">
+        <is>
+          <t>+0.0150</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="20" customHeight="1" s="220">
-      <c r="A15" s="271" t="inlineStr">
+      <c r="A15" s="270" t="inlineStr">
         <is>
           <t>C FM · 同 pipeline scratch</t>
         </is>
       </c>
-      <c r="B15" s="285" t="inlineStr">
+      <c r="B15" s="284" t="inlineStr">
         <is>
           <t>BIOT (scratch)</t>
         </is>
       </c>
-      <c r="C15" s="286" t="n">
+      <c r="C15" s="285" t="n">
         <v>3.18</v>
       </c>
-      <c r="D15" s="287" t="inlineStr">
+      <c r="D15" s="286" t="inlineStr">
         <is>
           <t>0.7642±0.0071</t>
         </is>
       </c>
-      <c r="E15" s="288" t="inlineStr">
+      <c r="E15" s="287" t="inlineStr">
         <is>
           <t>0.7378±0.0031</t>
         </is>
       </c>
-      <c r="F15" s="288" t="inlineStr">
+      <c r="F15" s="287" t="inlineStr">
         <is>
           <t>0.7943±0.0027</t>
         </is>
       </c>
+      <c r="G15" s="287" t="inlineStr">
+        <is>
+          <t>+0.0426</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="20" customHeight="1" s="220">
-      <c r="A16" s="276" t="n"/>
-      <c r="B16" s="277" t="inlineStr">
+      <c r="A16" s="275" t="n"/>
+      <c r="B16" s="276" t="inlineStr">
         <is>
           <t>LaBraM-Base (scratch)</t>
         </is>
       </c>
-      <c r="C16" s="278" t="n">
+      <c r="C16" s="277" t="n">
         <v>5.82</v>
       </c>
-      <c r="D16" s="279" t="inlineStr">
+      <c r="D16" s="278" t="inlineStr">
         <is>
           <t>0.6660±0.0144</t>
         </is>
       </c>
-      <c r="E16" s="280" t="inlineStr">
+      <c r="E16" s="279" t="inlineStr">
         <is>
           <t>0.6236±0.0107</t>
         </is>
       </c>
-      <c r="F16" s="280" t="inlineStr">
+      <c r="F16" s="279" t="inlineStr">
         <is>
           <t>0.6979±0.0115</t>
         </is>
       </c>
+      <c r="G16" s="279" t="inlineStr">
+        <is>
+          <t>-0.0716</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="20" customHeight="1" s="220">
-      <c r="A17" s="276" t="n"/>
-      <c r="B17" s="277" t="inlineStr">
+      <c r="A17" s="275" t="n"/>
+      <c r="B17" s="276" t="inlineStr">
         <is>
           <t>CBraMod (scratch)</t>
         </is>
       </c>
-      <c r="C17" s="278" t="n">
+      <c r="C17" s="277" t="n">
         <v>26.47</v>
       </c>
-      <c r="D17" s="279" t="inlineStr">
+      <c r="D17" s="278" t="inlineStr">
         <is>
           <t>0.7428±0.0021</t>
         </is>
       </c>
-      <c r="E17" s="280" t="inlineStr">
+      <c r="E17" s="279" t="inlineStr">
         <is>
           <t>0.6976±0.0052</t>
         </is>
       </c>
-      <c r="F17" s="280" t="inlineStr">
+      <c r="F17" s="279" t="inlineStr">
         <is>
           <t>0.7614±0.0067</t>
         </is>
       </c>
+      <c r="G17" s="279" t="inlineStr">
+        <is>
+          <t>+0.0024</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="20" customHeight="1" s="220">
-      <c r="A18" s="276" t="n"/>
-      <c r="B18" s="289" t="inlineStr">
+      <c r="A18" s="275" t="n"/>
+      <c r="B18" s="288" t="inlineStr">
         <is>
           <t>PACLock (from scratch, full)</t>
         </is>
       </c>
-      <c r="C18" s="290" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="D18" s="291" t="n"/>
-      <c r="E18" s="292" t="n"/>
-      <c r="F18" s="292" t="n"/>
+      <c r="C18" s="289" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="D18" s="290" t="inlineStr">
+        <is>
+          <t>0.7557±0.0064</t>
+        </is>
+      </c>
+      <c r="E18" s="291" t="inlineStr">
+        <is>
+          <t>0.6952±0.0005</t>
+        </is>
+      </c>
+      <c r="F18" s="291" t="inlineStr">
+        <is>
+          <t>0.7586±0.0008</t>
+        </is>
+      </c>
+      <c r="G18" s="291" t="n"/>
     </row>
     <row r="19" ht="15" customHeight="1" s="220"/>
     <row r="20" ht="24" customHeight="1" s="220"/>
@@ -12491,8 +13063,8 @@
     <row r="53" ht="38" customHeight="1" s="220"/>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A2:G2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" scale="100" fitToHeight="1" fitToWidth="1" firstPageNumber="1" useFirstPageNumber="0" pageOrder="downThenOver"/>
@@ -12551,391 +13123,391 @@
       <c r="D3" s="268" t="n"/>
       <c r="E3" s="268" t="n"/>
       <c r="F3" s="268" t="n"/>
-      <c r="G3" s="269" t="n"/>
+      <c r="G3" s="292" t="n"/>
     </row>
     <row r="4" ht="28" customHeight="1" s="220">
-      <c r="A4" s="270" t="inlineStr">
+      <c r="A4" s="269" t="inlineStr">
         <is>
           <t>分组</t>
         </is>
       </c>
-      <c r="B4" s="270" t="inlineStr">
+      <c r="B4" s="269" t="inlineStr">
         <is>
           <t>模型</t>
         </is>
       </c>
-      <c r="C4" s="270" t="inlineStr">
+      <c r="C4" s="269" t="inlineStr">
         <is>
           <t>参数量 (M)</t>
         </is>
       </c>
-      <c r="D4" s="270" t="inlineStr">
+      <c r="D4" s="269" t="inlineStr">
         <is>
           <t>Balanced Acc</t>
         </is>
       </c>
-      <c r="E4" s="270" t="inlineStr">
+      <c r="E4" s="269" t="inlineStr">
         <is>
           <t>Cohen's Kappa</t>
         </is>
       </c>
-      <c r="F4" s="270" t="inlineStr">
+      <c r="F4" s="269" t="inlineStr">
         <is>
           <t>Weighted F1</t>
         </is>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1" s="220">
-      <c r="A5" s="271" t="inlineStr">
+      <c r="A5" s="270" t="inlineStr">
         <is>
           <t>A 轻量监督基线</t>
         </is>
       </c>
-      <c r="B5" s="272" t="inlineStr">
+      <c r="B5" s="271" t="inlineStr">
         <is>
           <t>SPaRCNet</t>
         </is>
       </c>
-      <c r="C5" s="273" t="n">
+      <c r="C5" s="272" t="n">
         <v>1.27</v>
       </c>
-      <c r="D5" s="274" t="inlineStr">
+      <c r="D5" s="273" t="inlineStr">
         <is>
           <t>0.5905±0.0036</t>
         </is>
       </c>
-      <c r="E5" s="274" t="inlineStr">
+      <c r="E5" s="273" t="inlineStr">
         <is>
           <t>0.4540±0.0048</t>
         </is>
       </c>
-      <c r="F5" s="274" t="inlineStr">
+      <c r="F5" s="273" t="inlineStr">
         <is>
           <t>0.5916±0.0057</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1" s="220">
-      <c r="A6" s="276" t="n"/>
-      <c r="B6" s="277" t="inlineStr">
+      <c r="A6" s="275" t="n"/>
+      <c r="B6" s="276" t="inlineStr">
         <is>
           <t>ContraWR</t>
         </is>
       </c>
-      <c r="C6" s="278" t="n">
+      <c r="C6" s="277" t="n">
         <v>1.6</v>
       </c>
-      <c r="D6" s="279" t="inlineStr">
+      <c r="D6" s="278" t="inlineStr">
         <is>
           <t>0.4891±0.0063</t>
         </is>
       </c>
-      <c r="E6" s="279" t="inlineStr">
+      <c r="E6" s="278" t="inlineStr">
         <is>
           <t>0.3188±0.0085</t>
         </is>
       </c>
-      <c r="F6" s="279" t="inlineStr">
+      <c r="F6" s="278" t="inlineStr">
         <is>
           <t>0.4848±0.0026</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1" s="220">
-      <c r="A7" s="276" t="n"/>
-      <c r="B7" s="277" t="inlineStr">
+      <c r="A7" s="275" t="n"/>
+      <c r="B7" s="276" t="inlineStr">
         <is>
           <t>CNN-Transformer</t>
         </is>
       </c>
-      <c r="C7" s="278" t="n">
+      <c r="C7" s="277" t="n">
         <v>3.2</v>
       </c>
-      <c r="D7" s="279" t="n"/>
-      <c r="E7" s="279" t="n"/>
-      <c r="F7" s="279" t="n"/>
+      <c r="D7" s="278" t="n"/>
+      <c r="E7" s="278" t="n"/>
+      <c r="F7" s="278" t="n"/>
     </row>
     <row r="8" ht="20" customHeight="1" s="220">
-      <c r="A8" s="276" t="n"/>
-      <c r="B8" s="277" t="inlineStr">
+      <c r="A8" s="275" t="n"/>
+      <c r="B8" s="276" t="inlineStr">
         <is>
           <t>FFCL</t>
         </is>
       </c>
-      <c r="C8" s="278" t="n">
+      <c r="C8" s="277" t="n">
         <v>2.43</v>
       </c>
-      <c r="D8" s="279" t="inlineStr">
+      <c r="D8" s="278" t="inlineStr">
         <is>
           <t>0.4935±0.0125</t>
         </is>
       </c>
-      <c r="E8" s="279" t="inlineStr">
+      <c r="E8" s="278" t="inlineStr">
         <is>
           <t>0.3246±0.0166</t>
         </is>
       </c>
-      <c r="F8" s="279" t="inlineStr">
+      <c r="F8" s="278" t="inlineStr">
         <is>
           <t>0.4903±0.0157</t>
         </is>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1" s="220">
-      <c r="A9" s="276" t="n"/>
-      <c r="B9" s="277" t="inlineStr">
+      <c r="A9" s="275" t="n"/>
+      <c r="B9" s="276" t="inlineStr">
         <is>
           <t>ST-Transformer</t>
         </is>
       </c>
-      <c r="C9" s="278" t="n">
+      <c r="C9" s="277" t="n">
         <v>3.48</v>
       </c>
-      <c r="D9" s="279" t="inlineStr">
+      <c r="D9" s="278" t="inlineStr">
         <is>
           <t>0.5938±0.0136</t>
         </is>
       </c>
-      <c r="E9" s="279" t="inlineStr">
+      <c r="E9" s="278" t="inlineStr">
         <is>
           <t>0.4584±0.0181</t>
         </is>
       </c>
-      <c r="F9" s="279" t="inlineStr">
+      <c r="F9" s="278" t="inlineStr">
         <is>
           <t>0.5940±0.0128</t>
         </is>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1" s="220">
-      <c r="A10" s="271" t="inlineStr">
+      <c r="A10" s="270" t="inlineStr">
         <is>
           <t>B FM · 官方预训练权重</t>
         </is>
       </c>
-      <c r="B10" s="281" t="inlineStr">
+      <c r="B10" s="280" t="inlineStr">
         <is>
           <t>BIOT (pretrained)</t>
         </is>
       </c>
-      <c r="C10" s="282" t="n">
+      <c r="C10" s="281" t="n">
         <v>3.19</v>
       </c>
-      <c r="D10" s="283" t="inlineStr">
+      <c r="D10" s="282" t="inlineStr">
         <is>
           <t>0.5037±0.0072</t>
         </is>
       </c>
-      <c r="E10" s="283" t="inlineStr">
+      <c r="E10" s="282" t="inlineStr">
         <is>
           <t>0.3380±0.0096</t>
         </is>
       </c>
-      <c r="F10" s="283" t="inlineStr">
+      <c r="F10" s="282" t="inlineStr">
         <is>
           <t>0.5046±0.0049</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1" s="220">
-      <c r="A11" s="276" t="n"/>
-      <c r="B11" s="277" t="inlineStr">
+      <c r="A11" s="275" t="n"/>
+      <c r="B11" s="276" t="inlineStr">
         <is>
           <t>LaBraM-Base (pretrained)</t>
         </is>
       </c>
-      <c r="C11" s="278" t="n">
+      <c r="C11" s="277" t="n">
         <v>5.82</v>
       </c>
-      <c r="D11" s="279" t="inlineStr">
+      <c r="D11" s="278" t="inlineStr">
         <is>
           <t>0.5573±0.0159</t>
         </is>
       </c>
-      <c r="E11" s="279" t="inlineStr">
+      <c r="E11" s="278" t="inlineStr">
         <is>
           <t>0.4096±0.0211</t>
         </is>
       </c>
-      <c r="F11" s="279" t="inlineStr">
+      <c r="F11" s="278" t="inlineStr">
         <is>
           <t>0.5594±0.0157</t>
         </is>
       </c>
     </row>
     <row r="12" ht="20" customHeight="1" s="220">
-      <c r="A12" s="276" t="n"/>
-      <c r="B12" s="277" t="inlineStr">
+      <c r="A12" s="275" t="n"/>
+      <c r="B12" s="276" t="inlineStr">
         <is>
           <t>CBraMod (pretrained)</t>
         </is>
       </c>
-      <c r="C12" s="278" t="n">
+      <c r="C12" s="277" t="n">
         <v>46.01</v>
       </c>
-      <c r="D12" s="279" t="inlineStr">
+      <c r="D12" s="278" t="inlineStr">
         <is>
           <t>0.6129±0.0094</t>
         </is>
       </c>
-      <c r="E12" s="279" t="inlineStr">
+      <c r="E12" s="278" t="inlineStr">
         <is>
           <t>0.4838±0.0125</t>
         </is>
       </c>
-      <c r="F12" s="279" t="inlineStr">
+      <c r="F12" s="278" t="inlineStr">
         <is>
           <t>0.6122±0.0094</t>
         </is>
       </c>
     </row>
     <row r="13" ht="20" customHeight="1" s="220">
-      <c r="A13" s="276" t="n"/>
-      <c r="B13" s="277" t="inlineStr">
+      <c r="A13" s="275" t="n"/>
+      <c r="B13" s="276" t="inlineStr">
         <is>
           <t>EEGPT</t>
         </is>
       </c>
-      <c r="C13" s="278" t="n">
+      <c r="C13" s="277" t="n">
         <v>25.69</v>
       </c>
-      <c r="D13" s="279" t="inlineStr">
+      <c r="D13" s="278" t="inlineStr">
         <is>
           <t>0.4046±0.0397</t>
         </is>
       </c>
-      <c r="E13" s="279" t="inlineStr">
+      <c r="E13" s="278" t="inlineStr">
         <is>
           <t>0.2060±0.0528</t>
         </is>
       </c>
-      <c r="F13" s="279" t="inlineStr">
+      <c r="F13" s="278" t="inlineStr">
         <is>
           <t>0.4045±0.0409</t>
         </is>
       </c>
     </row>
     <row r="14" ht="20" customHeight="1" s="220">
-      <c r="A14" s="276" t="n"/>
-      <c r="B14" s="277" t="inlineStr">
+      <c r="A14" s="275" t="n"/>
+      <c r="B14" s="276" t="inlineStr">
         <is>
           <t>TFM-Tokenizer</t>
         </is>
       </c>
-      <c r="C14" s="278" t="n">
+      <c r="C14" s="277" t="n">
         <v>1.89</v>
       </c>
-      <c r="D14" s="279" t="inlineStr">
+      <c r="D14" s="278" t="inlineStr">
         <is>
           <t>0.4322±0.0143</t>
         </is>
       </c>
-      <c r="E14" s="279" t="inlineStr">
+      <c r="E14" s="278" t="inlineStr">
         <is>
           <t>0.2429±0.0191</t>
         </is>
       </c>
-      <c r="F14" s="279" t="inlineStr">
+      <c r="F14" s="278" t="inlineStr">
         <is>
           <t>0.4324±0.0147</t>
         </is>
       </c>
     </row>
     <row r="15" ht="20" customHeight="1" s="220">
-      <c r="A15" s="271" t="inlineStr">
+      <c r="A15" s="270" t="inlineStr">
         <is>
           <t>C FM · 同 pipeline scratch</t>
         </is>
       </c>
-      <c r="B15" s="285" t="inlineStr">
+      <c r="B15" s="284" t="inlineStr">
         <is>
           <t>BIOT (scratch)</t>
         </is>
       </c>
-      <c r="C15" s="286" t="n">
+      <c r="C15" s="285" t="n">
         <v>3.2</v>
       </c>
-      <c r="D15" s="287" t="inlineStr">
+      <c r="D15" s="286" t="inlineStr">
         <is>
           <t>0.3099±0.0292</t>
         </is>
       </c>
-      <c r="E15" s="287" t="inlineStr">
+      <c r="E15" s="286" t="inlineStr">
         <is>
           <t>0.0800±0.0390</t>
         </is>
       </c>
-      <c r="F15" s="287" t="inlineStr">
+      <c r="F15" s="286" t="inlineStr">
         <is>
           <t>0.2901±0.0544</t>
         </is>
       </c>
     </row>
     <row r="16" ht="20" customHeight="1" s="220">
-      <c r="A16" s="276" t="n"/>
-      <c r="B16" s="277" t="inlineStr">
+      <c r="A16" s="275" t="n"/>
+      <c r="B16" s="276" t="inlineStr">
         <is>
           <t>LaBraM-Base (scratch)</t>
         </is>
       </c>
-      <c r="C16" s="278" t="n">
+      <c r="C16" s="277" t="n">
         <v>5.82</v>
       </c>
-      <c r="D16" s="279" t="inlineStr">
+      <c r="D16" s="278" t="inlineStr">
         <is>
           <t>0.3667±0.0142</t>
         </is>
       </c>
-      <c r="E16" s="279" t="inlineStr">
+      <c r="E16" s="278" t="inlineStr">
         <is>
           <t>0.1555±0.0190</t>
         </is>
       </c>
-      <c r="F16" s="279" t="inlineStr">
+      <c r="F16" s="278" t="inlineStr">
         <is>
           <t>0.3644±0.0163</t>
         </is>
       </c>
     </row>
     <row r="17" ht="20" customHeight="1" s="220">
-      <c r="A17" s="276" t="n"/>
-      <c r="B17" s="277" t="inlineStr">
+      <c r="A17" s="275" t="n"/>
+      <c r="B17" s="276" t="inlineStr">
         <is>
           <t>CBraMod (scratch)</t>
         </is>
       </c>
-      <c r="C17" s="278" t="n">
+      <c r="C17" s="277" t="n">
         <v>46.01</v>
       </c>
-      <c r="D17" s="279" t="inlineStr">
+      <c r="D17" s="278" t="inlineStr">
         <is>
           <t>0.5537±0.0033</t>
         </is>
       </c>
-      <c r="E17" s="279" t="inlineStr">
+      <c r="E17" s="278" t="inlineStr">
         <is>
           <t>0.4049±0.0044</t>
         </is>
       </c>
-      <c r="F17" s="279" t="inlineStr">
+      <c r="F17" s="278" t="inlineStr">
         <is>
           <t>0.5546±0.0044</t>
         </is>
       </c>
     </row>
     <row r="18" ht="20" customHeight="1" s="220">
-      <c r="A18" s="276" t="n"/>
-      <c r="B18" s="289" t="inlineStr">
+      <c r="A18" s="275" t="n"/>
+      <c r="B18" s="288" t="inlineStr">
         <is>
           <t>PACLock (from scratch, full)</t>
         </is>
       </c>
-      <c r="C18" s="290" t="n">
+      <c r="C18" s="289" t="n">
         <v>1.64</v>
       </c>
-      <c r="D18" s="291" t="n"/>
-      <c r="E18" s="291" t="n"/>
-      <c r="F18" s="291" t="n"/>
+      <c r="D18" s="290" t="n"/>
+      <c r="E18" s="290" t="n"/>
+      <c r="F18" s="290" t="n"/>
     </row>
     <row r="19" ht="13.75" customHeight="1" s="220"/>
     <row r="20" ht="24" customHeight="1" s="220"/>
@@ -13031,7 +13603,7 @@
       <c r="D3" s="295" t="n"/>
       <c r="E3" s="295" t="n"/>
       <c r="F3" s="295" t="n"/>
-      <c r="G3" s="269" t="n"/>
+      <c r="G3" s="292" t="n"/>
     </row>
     <row r="4" ht="28" customHeight="1" s="220">
       <c r="A4" s="296" t="inlineStr">

--- a/results/PACLock_baseline_matrix_filled.xlsx
+++ b/results/PACLock_baseline_matrix_filled.xlsx
@@ -17,6 +17,7 @@
     <sheet name="FACED" sheetId="9" state="visible" r:id="rId9"/>
     <sheet name="BCI-IV-2a" sheetId="10" state="visible" r:id="rId10"/>
     <sheet name="_填写记录" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="_消融" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames/>
 </workbook>
@@ -27,7 +28,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0000"/>
   </numFmts>
-  <fonts count="42">
+  <fonts count="44">
     <font>
       <name val="Calibri"/>
       <color indexed="8"/>
@@ -251,8 +252,16 @@
       <color rgb="00808080"/>
       <sz val="9"/>
     </font>
+    <font>
+      <b val="1"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="00808080"/>
+    </font>
   </fonts>
-  <fills count="18">
+  <fills count="21">
     <fill>
       <patternFill/>
     </fill>
@@ -352,8 +361,23 @@
         <fgColor rgb="00EFEFEF"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9D9D9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EDF3FA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F2F2F2"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="70">
+  <borders count="71">
     <border>
       <left/>
       <right/>
@@ -1185,13 +1209,27 @@
       </bottom>
     </border>
     <border/>
+    <border>
+      <left style="thin">
+        <color rgb="00BFBFBF"/>
+      </left>
+      <right style="thin">
+        <color rgb="00BFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BFBFBF"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" applyAlignment="1">
       <alignment vertical="bottom"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="308">
+  <cellXfs count="315">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="bottom"/>
     </xf>
@@ -2079,6 +2117,19 @@
     </xf>
     <xf numFmtId="0" fontId="40" fillId="17" borderId="68" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="34" fillId="18" borderId="70" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="34" fillId="18" borderId="70" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="19" borderId="70" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="70" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="70" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="20" borderId="70" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -10843,6 +10894,695 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K20"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" style="220" min="1" max="1"/>
+    <col width="42" customWidth="1" style="220" min="2" max="2"/>
+    <col width="18" customWidth="1" style="220" min="3" max="3"/>
+    <col width="18" customWidth="1" style="220" min="4" max="4"/>
+    <col width="18" customWidth="1" style="220" min="5" max="5"/>
+    <col width="18" customWidth="1" style="220" min="6" max="6"/>
+    <col width="18" customWidth="1" style="220" min="7" max="7"/>
+    <col width="18" customWidth="1" style="220" min="8" max="8"/>
+    <col width="18" customWidth="1" style="220" min="9" max="9"/>
+    <col width="18" customWidth="1" style="220" min="10" max="10"/>
+    <col width="18" customWidth="1" style="220" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="308" t="inlineStr">
+        <is>
+          <t>PACLock 自身消融 —— 与冻结 baseline 主表分开,主表未改动</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="30" customHeight="1" s="220">
+      <c r="A2" s="263" t="inlineStr">
+        <is>
+          <t>每格 mean±std,括号内为 seed 数。硬规则 4:少于 3 seed 不可进论文表,此处灰底标出并保留数字,以便区分「尚未达标」与「没跑」。指标:TUAB=AUROC,TUSZ/CHB-MIT=PR-AUC,TUEV/Sleep-EDF/ISRUC=kappa,其余=balanced acc。</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="309" t="inlineStr">
+        <is>
+          <t>分组</t>
+        </is>
+      </c>
+      <c r="B4" s="309" t="inlineStr">
+        <is>
+          <t>变体</t>
+        </is>
+      </c>
+      <c r="C4" s="310" t="inlineStr">
+        <is>
+          <t>TUAB</t>
+        </is>
+      </c>
+      <c r="D4" s="310" t="inlineStr">
+        <is>
+          <t>TUEV</t>
+        </is>
+      </c>
+      <c r="E4" s="310" t="inlineStr">
+        <is>
+          <t>TUSZ</t>
+        </is>
+      </c>
+      <c r="F4" s="310" t="inlineStr">
+        <is>
+          <t>CHB-MIT</t>
+        </is>
+      </c>
+      <c r="G4" s="310" t="inlineStr">
+        <is>
+          <t>Sleep-EDF</t>
+        </is>
+      </c>
+      <c r="H4" s="310" t="inlineStr">
+        <is>
+          <t>ISRUC</t>
+        </is>
+      </c>
+      <c r="I4" s="310" t="inlineStr">
+        <is>
+          <t>PhysioNet-MI</t>
+        </is>
+      </c>
+      <c r="J4" s="310" t="inlineStr">
+        <is>
+          <t>FACED</t>
+        </is>
+      </c>
+      <c r="K4" s="310" t="inlineStr">
+        <is>
+          <t>BCI-IV-2a</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="311" t="inlineStr">
+        <is>
+          <t>参照</t>
+        </is>
+      </c>
+      <c r="B5" s="312" t="inlineStr">
+        <is>
+          <t>PACLock v2(冻结配置:pac_interaction + product)</t>
+        </is>
+      </c>
+      <c r="C5" s="313" t="inlineStr">
+        <is>
+          <t>0.8829±0.0041 (3)</t>
+        </is>
+      </c>
+      <c r="D5" s="313" t="inlineStr">
+        <is>
+          <t>0.7076±0.0311 (3)</t>
+        </is>
+      </c>
+      <c r="E5" s="313" t="inlineStr">
+        <is>
+          <t>0.5882±0.0790 (3)</t>
+        </is>
+      </c>
+      <c r="F5" s="313" t="inlineStr">
+        <is>
+          <t>0.5464±0.0313 (3)</t>
+        </is>
+      </c>
+      <c r="G5" s="313" t="inlineStr">
+        <is>
+          <t>0.6459±0.0066 (3)</t>
+        </is>
+      </c>
+      <c r="H5" s="313" t="inlineStr">
+        <is>
+          <t>0.6952±0.0006 (3)</t>
+        </is>
+      </c>
+      <c r="I5" s="313" t="inlineStr">
+        <is>
+          <t>0.2722±0.0133 (5)</t>
+        </is>
+      </c>
+      <c r="J5" s="313" t="inlineStr">
+        <is>
+          <t>0.1477±0.0040 (3)</t>
+        </is>
+      </c>
+      <c r="K5" s="313" t="inlineStr">
+        <is>
+          <t>0.3588±0.0052 (3)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="311" t="inlineStr">
+        <is>
+          <t>tokenizer 消融</t>
+        </is>
+      </c>
+      <c r="B6" s="312" t="inlineStr">
+        <is>
+          <t>└ raw tokenizer(去掉整个交互)</t>
+        </is>
+      </c>
+      <c r="C6" s="313" t="inlineStr">
+        <is>
+          <t>0.8842±0.0063 (3)</t>
+        </is>
+      </c>
+      <c r="D6" s="313" t="inlineStr">
+        <is>
+          <t>0.5359±0.0414 (3)</t>
+        </is>
+      </c>
+      <c r="E6" s="313" t="inlineStr">
+        <is>
+          <t>0.6710±0.0324 (3)</t>
+        </is>
+      </c>
+      <c r="F6" s="313" t="inlineStr">
+        <is>
+          <t>0.6672±0.0574 (3)</t>
+        </is>
+      </c>
+      <c r="G6" s="313" t="inlineStr">
+        <is>
+          <t>0.6503±0.0019 (3)</t>
+        </is>
+      </c>
+      <c r="H6" s="313" t="inlineStr">
+        <is>
+          <t>0.7013±0.0305 (3)</t>
+        </is>
+      </c>
+      <c r="I6" s="313" t="inlineStr">
+        <is>
+          <t>0.3420±0.0260 (3)</t>
+        </is>
+      </c>
+      <c r="J6" s="313" t="inlineStr">
+        <is>
+          <t>0.1528±0.0030 (3)</t>
+        </is>
+      </c>
+      <c r="K6" s="313" t="inlineStr">
+        <is>
+          <t>0.4192±0.0190 (3)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="312" t="inlineStr"/>
+      <c r="B7" s="312" t="inlineStr">
+        <is>
+          <t>└ PAC 协议预处理(0.5Hz 高通,无 notch)</t>
+        </is>
+      </c>
+      <c r="C7" s="313" t="n"/>
+      <c r="D7" s="313" t="inlineStr">
+        <is>
+          <t>0.6257±0.0085 (3)</t>
+        </is>
+      </c>
+      <c r="E7" s="313" t="inlineStr">
+        <is>
+          <t>0.6438±0.0480 (3)</t>
+        </is>
+      </c>
+      <c r="F7" s="314" t="inlineStr">
+        <is>
+          <t>0.5001±0.0000 (1)</t>
+        </is>
+      </c>
+      <c r="G7" s="313" t="inlineStr">
+        <is>
+          <t>0.6193±0.0109 (3)</t>
+        </is>
+      </c>
+      <c r="H7" s="313" t="inlineStr">
+        <is>
+          <t>0.6949±0.0057 (3)</t>
+        </is>
+      </c>
+      <c r="I7" s="313" t="inlineStr">
+        <is>
+          <t>0.2441±0.0042 (3)</t>
+        </is>
+      </c>
+      <c r="J7" s="313" t="inlineStr">
+        <is>
+          <t>0.1112±0.0005 (3)</t>
+        </is>
+      </c>
+      <c r="K7" s="313" t="inlineStr">
+        <is>
+          <t>0.2591±0.0012 (3)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="312" t="inlineStr"/>
+      <c r="B8" s="312" t="inlineStr">
+        <is>
+          <t>└ concat 融合(SleepPACNet 式)</t>
+        </is>
+      </c>
+      <c r="C8" s="313" t="n"/>
+      <c r="D8" s="313" t="n"/>
+      <c r="E8" s="313" t="n"/>
+      <c r="F8" s="313" t="n"/>
+      <c r="G8" s="313" t="n"/>
+      <c r="H8" s="313" t="n"/>
+      <c r="I8" s="314" t="inlineStr">
+        <is>
+          <t>0.2417±0.0000 (1)</t>
+        </is>
+      </c>
+      <c r="J8" s="314" t="inlineStr">
+        <is>
+          <t>0.1249±0.0000 (1)</t>
+        </is>
+      </c>
+      <c r="K8" s="314" t="inlineStr">
+        <is>
+          <t>0.3090±0.0000 (1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="312" t="inlineStr"/>
+      <c r="B9" s="312" t="inlineStr">
+        <is>
+          <t>└ uniform 耦合(去掉测得的 α 与 ∠Z)</t>
+        </is>
+      </c>
+      <c r="C9" s="313" t="n"/>
+      <c r="D9" s="313" t="n"/>
+      <c r="E9" s="313" t="n"/>
+      <c r="F9" s="313" t="n"/>
+      <c r="G9" s="313" t="n"/>
+      <c r="H9" s="313" t="n"/>
+      <c r="I9" s="313" t="n"/>
+      <c r="J9" s="313" t="n"/>
+      <c r="K9" s="314" t="inlineStr">
+        <is>
+          <t>0.2639±0.0000 (1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="311" t="inlineStr">
+        <is>
+          <t>架构改动</t>
+        </is>
+      </c>
+      <c r="B10" s="312" t="inlineStr">
+        <is>
+          <t>PACLock + rotation(耦合只旋转,不缩放)</t>
+        </is>
+      </c>
+      <c r="C10" s="313" t="n"/>
+      <c r="D10" s="313" t="inlineStr">
+        <is>
+          <t>0.7328±0.0161 (3)</t>
+        </is>
+      </c>
+      <c r="E10" s="314" t="inlineStr">
+        <is>
+          <t>0.6884±0.0000 (1)</t>
+        </is>
+      </c>
+      <c r="F10" s="313" t="n"/>
+      <c r="G10" s="314" t="inlineStr">
+        <is>
+          <t>0.6449±0.0000 (1)</t>
+        </is>
+      </c>
+      <c r="H10" s="313" t="n"/>
+      <c r="I10" s="314" t="inlineStr">
+        <is>
+          <t>0.2961±0.0000 (1)</t>
+        </is>
+      </c>
+      <c r="J10" s="314" t="inlineStr">
+        <is>
+          <t>0.1514±0.0000 (1)</t>
+        </is>
+      </c>
+      <c r="K10" s="313" t="inlineStr">
+        <is>
+          <t>0.3708±0.0092 (3)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="312" t="inlineStr"/>
+      <c r="B11" s="312" t="inlineStr">
+        <is>
+          <t>PACLock + spatial 头(保留电极身份)</t>
+        </is>
+      </c>
+      <c r="C11" s="313" t="n"/>
+      <c r="D11" s="313" t="n"/>
+      <c r="E11" s="313" t="n"/>
+      <c r="F11" s="313" t="n"/>
+      <c r="G11" s="313" t="n"/>
+      <c r="H11" s="313" t="n"/>
+      <c r="I11" s="314" t="inlineStr">
+        <is>
+          <t>0.3560±0.0000 (1)</t>
+        </is>
+      </c>
+      <c r="J11" s="314" t="inlineStr">
+        <is>
+          <t>0.1514±0.0000 (1)</t>
+        </is>
+      </c>
+      <c r="K11" s="314" t="inlineStr">
+        <is>
+          <t>0.4144±0.0000 (1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="312" t="inlineStr"/>
+      <c r="B12" s="312" t="inlineStr">
+        <is>
+          <t>PACLock + rotation + spatial 头</t>
+        </is>
+      </c>
+      <c r="C12" s="313" t="n"/>
+      <c r="D12" s="313" t="n"/>
+      <c r="E12" s="313" t="n"/>
+      <c r="F12" s="313" t="n"/>
+      <c r="G12" s="313" t="n"/>
+      <c r="H12" s="313" t="n"/>
+      <c r="I12" s="314" t="inlineStr">
+        <is>
+          <t>0.3299±0.0000 (1)</t>
+        </is>
+      </c>
+      <c r="J12" s="313" t="n"/>
+      <c r="K12" s="314" t="inlineStr">
+        <is>
+          <t>0.4344±0.0000 (1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="311" t="inlineStr">
+        <is>
+          <t>预训练</t>
+        </is>
+      </c>
+      <c r="B13" s="312" t="inlineStr">
+        <is>
+          <t>PACLock 预训练 base(60k)</t>
+        </is>
+      </c>
+      <c r="C13" s="313" t="inlineStr">
+        <is>
+          <t>0.8841±0.0043 (3)</t>
+        </is>
+      </c>
+      <c r="D13" s="313" t="inlineStr">
+        <is>
+          <t>0.6730±0.0116 (3)</t>
+        </is>
+      </c>
+      <c r="E13" s="313" t="inlineStr">
+        <is>
+          <t>0.6398±0.0615 (3)</t>
+        </is>
+      </c>
+      <c r="F13" s="313" t="inlineStr">
+        <is>
+          <t>0.6830±0.0228 (3)</t>
+        </is>
+      </c>
+      <c r="G13" s="313" t="inlineStr">
+        <is>
+          <t>0.6651±0.0109 (3)</t>
+        </is>
+      </c>
+      <c r="H13" s="313" t="inlineStr">
+        <is>
+          <t>0.6934±0.0032 (3)</t>
+        </is>
+      </c>
+      <c r="I13" s="313" t="inlineStr">
+        <is>
+          <t>0.3059±0.0262 (3)</t>
+        </is>
+      </c>
+      <c r="J13" s="313" t="inlineStr">
+        <is>
+          <t>0.1540±0.0202 (3)</t>
+        </is>
+      </c>
+      <c r="K13" s="313" t="inlineStr">
+        <is>
+          <t>0.3652±0.0083 (3)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="312" t="inlineStr"/>
+      <c r="B14" s="312" t="inlineStr">
+        <is>
+          <t>PACLock 预训练 large(60k)</t>
+        </is>
+      </c>
+      <c r="C14" s="313" t="inlineStr">
+        <is>
+          <t>0.8869±0.0069 (3)</t>
+        </is>
+      </c>
+      <c r="D14" s="313" t="inlineStr">
+        <is>
+          <t>0.6523±0.0302 (3)</t>
+        </is>
+      </c>
+      <c r="E14" s="313" t="inlineStr">
+        <is>
+          <t>0.6289±0.0297 (3)</t>
+        </is>
+      </c>
+      <c r="F14" s="313" t="inlineStr">
+        <is>
+          <t>0.6162±0.0467 (3)</t>
+        </is>
+      </c>
+      <c r="G14" s="313" t="inlineStr">
+        <is>
+          <t>0.6641±0.0044 (3)</t>
+        </is>
+      </c>
+      <c r="H14" s="313" t="inlineStr">
+        <is>
+          <t>0.6996±0.0153 (3)</t>
+        </is>
+      </c>
+      <c r="I14" s="313" t="inlineStr">
+        <is>
+          <t>0.3140±0.0094 (3)</t>
+        </is>
+      </c>
+      <c r="J14" s="313" t="inlineStr">
+        <is>
+          <t>0.1640±0.0155 (3)</t>
+        </is>
+      </c>
+      <c r="K14" s="313" t="inlineStr">
+        <is>
+          <t>0.4122±0.0166 (3)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="312" t="inlineStr"/>
+      <c r="B15" s="312" t="inlineStr">
+        <is>
+          <t>└ raw tokenizer 预训练 large(60k)</t>
+        </is>
+      </c>
+      <c r="C15" s="313" t="n"/>
+      <c r="D15" s="313" t="n"/>
+      <c r="E15" s="313" t="n"/>
+      <c r="F15" s="313" t="n"/>
+      <c r="G15" s="313" t="n"/>
+      <c r="H15" s="313" t="n"/>
+      <c r="I15" s="313" t="inlineStr">
+        <is>
+          <t>0.3633±0.0349 (3)</t>
+        </is>
+      </c>
+      <c r="J15" s="314" t="inlineStr">
+        <is>
+          <t>0.1690±0.0018 (2)</t>
+        </is>
+      </c>
+      <c r="K15" s="313" t="inlineStr">
+        <is>
+          <t>0.4483±0.0031 (3)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="312" t="inlineStr"/>
+      <c r="B16" s="312" t="inlineStr">
+        <is>
+          <t>└ 预训练池剔除 TUSZ/CHB-MIT</t>
+        </is>
+      </c>
+      <c r="C16" s="313" t="n"/>
+      <c r="D16" s="313" t="n"/>
+      <c r="E16" s="314" t="inlineStr">
+        <is>
+          <t>0.6221±0.0000 (1)</t>
+        </is>
+      </c>
+      <c r="F16" s="314" t="inlineStr">
+        <is>
+          <t>0.6410±0.0000 (1)</t>
+        </is>
+      </c>
+      <c r="G16" s="313" t="n"/>
+      <c r="H16" s="313" t="n"/>
+      <c r="I16" s="313" t="n"/>
+      <c r="J16" s="313" t="n"/>
+      <c r="K16" s="313" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="311" t="inlineStr">
+        <is>
+          <t>已否决</t>
+        </is>
+      </c>
+      <c r="B17" s="312" t="inlineStr">
+        <is>
+          <t>spatial_pe: xyz(蒙太奇坐标)</t>
+        </is>
+      </c>
+      <c r="C17" s="313" t="n"/>
+      <c r="D17" s="313" t="n"/>
+      <c r="E17" s="313" t="n"/>
+      <c r="F17" s="313" t="n"/>
+      <c r="G17" s="313" t="n"/>
+      <c r="H17" s="313" t="inlineStr">
+        <is>
+          <t>0.6954±0.0167 (3)</t>
+        </is>
+      </c>
+      <c r="I17" s="313" t="inlineStr">
+        <is>
+          <t>0.2478±0.0053 (3)</t>
+        </is>
+      </c>
+      <c r="J17" s="313" t="n"/>
+      <c r="K17" s="313" t="inlineStr">
+        <is>
+          <t>0.3338±0.0027 (3)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="312" t="inlineStr"/>
+      <c r="B18" s="312" t="inlineStr">
+        <is>
+          <t>每窗口归一化</t>
+        </is>
+      </c>
+      <c r="C18" s="313" t="n"/>
+      <c r="D18" s="313" t="n"/>
+      <c r="E18" s="313" t="n"/>
+      <c r="F18" s="313" t="n"/>
+      <c r="G18" s="313" t="n"/>
+      <c r="H18" s="313" t="n"/>
+      <c r="I18" s="313" t="inlineStr">
+        <is>
+          <t>0.2532±0.0155 (3)</t>
+        </is>
+      </c>
+      <c r="J18" s="313" t="n"/>
+      <c r="K18" s="313" t="inlineStr">
+        <is>
+          <t>0.3050±0.0438 (3)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="311" t="inlineStr">
+        <is>
+          <t>容量</t>
+        </is>
+      </c>
+      <c r="B19" s="312" t="inlineStr">
+        <is>
+          <t>raw + large 容量</t>
+        </is>
+      </c>
+      <c r="C19" s="313" t="n"/>
+      <c r="D19" s="313" t="n"/>
+      <c r="E19" s="313" t="n"/>
+      <c r="F19" s="313" t="n"/>
+      <c r="G19" s="313" t="n"/>
+      <c r="H19" s="313" t="n"/>
+      <c r="I19" s="313" t="inlineStr">
+        <is>
+          <t>0.4159±0.0529 (3)</t>
+        </is>
+      </c>
+      <c r="J19" s="313" t="n"/>
+      <c r="K19" s="313" t="inlineStr">
+        <is>
+          <t>0.4437±0.0192 (3)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="312" t="inlineStr"/>
+      <c r="B20" s="312" t="inlineStr">
+        <is>
+          <t>raw + attn 头</t>
+        </is>
+      </c>
+      <c r="C20" s="313" t="n"/>
+      <c r="D20" s="313" t="n"/>
+      <c r="E20" s="313" t="n"/>
+      <c r="F20" s="313" t="n"/>
+      <c r="G20" s="313" t="n"/>
+      <c r="H20" s="313" t="n"/>
+      <c r="I20" s="313" t="inlineStr">
+        <is>
+          <t>0.3524±0.0467 (3)</t>
+        </is>
+      </c>
+      <c r="J20" s="313" t="n"/>
+      <c r="K20" s="313" t="inlineStr">
+        <is>
+          <t>0.4545±0.0054 (3)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A2:K2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/results/PACLock_baseline_matrix_filled.xlsx
+++ b/results/PACLock_baseline_matrix_filled.xlsx
@@ -261,7 +261,7 @@
       <color rgb="00808080"/>
     </font>
   </fonts>
-  <fills count="21">
+  <fills count="22">
     <fill>
       <patternFill/>
     </fill>
@@ -374,6 +374,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00F2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF7E6"/>
       </patternFill>
     </fill>
   </fills>
@@ -1229,7 +1234,7 @@
       <alignment vertical="bottom"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="315">
+  <cellXfs count="318">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="bottom"/>
     </xf>
@@ -2131,6 +2136,11 @@
     <xf numFmtId="0" fontId="43" fillId="20" borderId="70" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="21" borderId="70" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="19" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -10900,11 +10910,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K20"/>
+  <dimension ref="A1:L46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" style="220" min="1" max="1"/>
-    <col width="42" customWidth="1" style="220" min="2" max="2"/>
+    <col width="44" customWidth="1" style="220" min="2" max="2"/>
     <col width="18" customWidth="1" style="220" min="3" max="3"/>
     <col width="18" customWidth="1" style="220" min="4" max="4"/>
     <col width="18" customWidth="1" style="220" min="5" max="5"/>
@@ -10914,19 +10924,20 @@
     <col width="18" customWidth="1" style="220" min="9" max="9"/>
     <col width="18" customWidth="1" style="220" min="10" max="10"/>
     <col width="18" customWidth="1" style="220" min="11" max="11"/>
+    <col width="18" customWidth="1" style="220" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="308" t="inlineStr">
         <is>
-          <t>PACLock 自身消融 —— 与冻结 baseline 主表分开,主表未改动</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="30" customHeight="1" s="220">
+          <t>PACLock 自身消融 —— 与冻结的 baseline 主表分开,主表未改动</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="32" customHeight="1" s="220">
       <c r="A2" s="263" t="inlineStr">
         <is>
-          <t>每格 mean±std,括号内为 seed 数。硬规则 4:少于 3 seed 不可进论文表,此处灰底标出并保留数字,以便区分「尚未达标」与「没跑」。指标:TUAB=AUROC,TUSZ/CHB-MIT=PR-AUC,TUEV/Sleep-EDF/ISRUC=kappa,其余=balanced acc。</t>
+          <t>每格 mean±std,括号内为 seed 数。淡黄底 = 只有 1-2 个 seed,数字可用但不可当作 3-seed 结论;硬规则 4 只约束论文正表,不约束本表。指标:TUAB=AUROC,TUSZ/CHB-MIT=PR-AUC,TUEV/Sleep-EDF/ISRUC/TUAR=kappa,其余=balanced acc。空格 = 未跑或在跑。</t>
         </is>
       </c>
     </row>
@@ -10986,6 +10997,11 @@
           <t>BCI-IV-2a</t>
         </is>
       </c>
+      <c r="L4" s="310" t="inlineStr">
+        <is>
+          <t>TUAR</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="311" t="inlineStr">
@@ -11043,6 +11059,7 @@
           <t>0.3588±0.0052 (3)</t>
         </is>
       </c>
+      <c r="L5" s="313" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="311" t="inlineStr">
@@ -11052,7 +11069,7 @@
       </c>
       <c r="B6" s="312" t="inlineStr">
         <is>
-          <t>└ raw tokenizer(去掉整个交互)</t>
+          <t>raw tokenizer(去掉整个交互)</t>
         </is>
       </c>
       <c r="C6" s="313" t="inlineStr">
@@ -11100,53 +11117,27 @@
           <t>0.4192±0.0190 (3)</t>
         </is>
       </c>
+      <c r="L6" s="313" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="312" t="inlineStr"/>
       <c r="B7" s="312" t="inlineStr">
         <is>
-          <t>└ PAC 协议预处理(0.5Hz 高通,无 notch)</t>
+          <t>raw tokenizer(TUAR 专跑)</t>
         </is>
       </c>
       <c r="C7" s="313" t="n"/>
-      <c r="D7" s="313" t="inlineStr">
-        <is>
-          <t>0.6257±0.0085 (3)</t>
-        </is>
-      </c>
-      <c r="E7" s="313" t="inlineStr">
-        <is>
-          <t>0.6438±0.0480 (3)</t>
-        </is>
-      </c>
-      <c r="F7" s="314" t="inlineStr">
-        <is>
-          <t>0.5001±0.0000 (1)</t>
-        </is>
-      </c>
-      <c r="G7" s="313" t="inlineStr">
-        <is>
-          <t>0.6193±0.0109 (3)</t>
-        </is>
-      </c>
-      <c r="H7" s="313" t="inlineStr">
-        <is>
-          <t>0.6949±0.0057 (3)</t>
-        </is>
-      </c>
-      <c r="I7" s="313" t="inlineStr">
-        <is>
-          <t>0.2441±0.0042 (3)</t>
-        </is>
-      </c>
-      <c r="J7" s="313" t="inlineStr">
-        <is>
-          <t>0.1112±0.0005 (3)</t>
-        </is>
-      </c>
-      <c r="K7" s="313" t="inlineStr">
-        <is>
-          <t>0.2591±0.0012 (3)</t>
+      <c r="D7" s="313" t="n"/>
+      <c r="E7" s="313" t="n"/>
+      <c r="F7" s="313" t="n"/>
+      <c r="G7" s="313" t="n"/>
+      <c r="H7" s="313" t="n"/>
+      <c r="I7" s="313" t="n"/>
+      <c r="J7" s="313" t="n"/>
+      <c r="K7" s="313" t="n"/>
+      <c r="L7" s="315" t="inlineStr">
+        <is>
+          <t>0.6289±0.0000 (1)</t>
         </is>
       </c>
     </row>
@@ -11154,7 +11145,7 @@
       <c r="A8" s="312" t="inlineStr"/>
       <c r="B8" s="312" t="inlineStr">
         <is>
-          <t>└ concat 融合(SleepPACNet 式)</t>
+          <t>concat 融合(SleepPACNet 式)</t>
         </is>
       </c>
       <c r="C8" s="313" t="n"/>
@@ -11163,27 +11154,28 @@
       <c r="F8" s="313" t="n"/>
       <c r="G8" s="313" t="n"/>
       <c r="H8" s="313" t="n"/>
-      <c r="I8" s="314" t="inlineStr">
+      <c r="I8" s="315" t="inlineStr">
         <is>
           <t>0.2417±0.0000 (1)</t>
         </is>
       </c>
-      <c r="J8" s="314" t="inlineStr">
+      <c r="J8" s="315" t="inlineStr">
         <is>
           <t>0.1249±0.0000 (1)</t>
         </is>
       </c>
-      <c r="K8" s="314" t="inlineStr">
+      <c r="K8" s="315" t="inlineStr">
         <is>
           <t>0.3090±0.0000 (1)</t>
         </is>
       </c>
+      <c r="L8" s="313" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="312" t="inlineStr"/>
       <c r="B9" s="312" t="inlineStr">
         <is>
-          <t>└ uniform 耦合(去掉测得的 α 与 ∠Z)</t>
+          <t>uniform 耦合(去掉测得的 α 与 ∠Z)</t>
         </is>
       </c>
       <c r="C9" s="313" t="n"/>
@@ -11194,91 +11186,118 @@
       <c r="H9" s="313" t="n"/>
       <c r="I9" s="313" t="n"/>
       <c r="J9" s="313" t="n"/>
-      <c r="K9" s="314" t="inlineStr">
+      <c r="K9" s="315" t="inlineStr">
         <is>
           <t>0.2639±0.0000 (1)</t>
         </is>
       </c>
+      <c r="L9" s="313" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="311" t="inlineStr">
-        <is>
-          <t>架构改动</t>
-        </is>
-      </c>
+      <c r="A10" s="312" t="inlineStr"/>
       <c r="B10" s="312" t="inlineStr">
         <is>
-          <t>PACLock + rotation(耦合只旋转,不缩放)</t>
+          <t>PAC 协议预处理(0.5Hz 高通、无 notch)</t>
         </is>
       </c>
       <c r="C10" s="313" t="n"/>
       <c r="D10" s="313" t="inlineStr">
         <is>
+          <t>0.6257±0.0085 (3)</t>
+        </is>
+      </c>
+      <c r="E10" s="313" t="inlineStr">
+        <is>
+          <t>0.6438±0.0480 (3)</t>
+        </is>
+      </c>
+      <c r="F10" s="315" t="inlineStr">
+        <is>
+          <t>0.5001±0.0000 (1)</t>
+        </is>
+      </c>
+      <c r="G10" s="313" t="inlineStr">
+        <is>
+          <t>0.6193±0.0109 (3)</t>
+        </is>
+      </c>
+      <c r="H10" s="313" t="inlineStr">
+        <is>
+          <t>0.6949±0.0057 (3)</t>
+        </is>
+      </c>
+      <c r="I10" s="313" t="inlineStr">
+        <is>
+          <t>0.2441±0.0042 (3)</t>
+        </is>
+      </c>
+      <c r="J10" s="313" t="inlineStr">
+        <is>
+          <t>0.1112±0.0005 (3)</t>
+        </is>
+      </c>
+      <c r="K10" s="313" t="inlineStr">
+        <is>
+          <t>0.2591±0.0012 (3)</t>
+        </is>
+      </c>
+      <c r="L10" s="315" t="inlineStr">
+        <is>
+          <t>0.5780±0.0000 (1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="311" t="inlineStr">
+        <is>
+          <t>架构改动</t>
+        </is>
+      </c>
+      <c r="B11" s="312" t="inlineStr">
+        <is>
+          <t>rotation(耦合只旋转不缩放)</t>
+        </is>
+      </c>
+      <c r="C11" s="313" t="n"/>
+      <c r="D11" s="313" t="inlineStr">
+        <is>
           <t>0.7328±0.0161 (3)</t>
         </is>
       </c>
-      <c r="E10" s="314" t="inlineStr">
+      <c r="E11" s="315" t="inlineStr">
         <is>
           <t>0.6884±0.0000 (1)</t>
         </is>
       </c>
-      <c r="F10" s="313" t="n"/>
-      <c r="G10" s="314" t="inlineStr">
+      <c r="F11" s="313" t="n"/>
+      <c r="G11" s="315" t="inlineStr">
         <is>
           <t>0.6449±0.0000 (1)</t>
         </is>
       </c>
-      <c r="H10" s="313" t="n"/>
-      <c r="I10" s="314" t="inlineStr">
+      <c r="H11" s="313" t="n"/>
+      <c r="I11" s="315" t="inlineStr">
         <is>
           <t>0.2961±0.0000 (1)</t>
         </is>
       </c>
-      <c r="J10" s="314" t="inlineStr">
+      <c r="J11" s="315" t="inlineStr">
         <is>
           <t>0.1514±0.0000 (1)</t>
         </is>
       </c>
-      <c r="K10" s="313" t="inlineStr">
+      <c r="K11" s="313" t="inlineStr">
         <is>
           <t>0.3708±0.0092 (3)</t>
         </is>
       </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="312" t="inlineStr"/>
-      <c r="B11" s="312" t="inlineStr">
-        <is>
-          <t>PACLock + spatial 头(保留电极身份)</t>
-        </is>
-      </c>
-      <c r="C11" s="313" t="n"/>
-      <c r="D11" s="313" t="n"/>
-      <c r="E11" s="313" t="n"/>
-      <c r="F11" s="313" t="n"/>
-      <c r="G11" s="313" t="n"/>
-      <c r="H11" s="313" t="n"/>
-      <c r="I11" s="314" t="inlineStr">
-        <is>
-          <t>0.3560±0.0000 (1)</t>
-        </is>
-      </c>
-      <c r="J11" s="314" t="inlineStr">
-        <is>
-          <t>0.1514±0.0000 (1)</t>
-        </is>
-      </c>
-      <c r="K11" s="314" t="inlineStr">
-        <is>
-          <t>0.4144±0.0000 (1)</t>
-        </is>
-      </c>
+      <c r="L11" s="313" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="312" t="inlineStr"/>
       <c r="B12" s="312" t="inlineStr">
         <is>
-          <t>PACLock + rotation + spatial 头</t>
+          <t>rotation(跑在 PAC 协议数据上,与上行不可比)</t>
         </is>
       </c>
       <c r="C12" s="313" t="n"/>
@@ -11287,191 +11306,196 @@
       <c r="F12" s="313" t="n"/>
       <c r="G12" s="313" t="n"/>
       <c r="H12" s="313" t="n"/>
-      <c r="I12" s="314" t="inlineStr">
-        <is>
-          <t>0.3299±0.0000 (1)</t>
-        </is>
-      </c>
-      <c r="J12" s="313" t="n"/>
-      <c r="K12" s="314" t="inlineStr">
-        <is>
-          <t>0.4344±0.0000 (1)</t>
+      <c r="I12" s="313" t="n"/>
+      <c r="J12" s="315" t="inlineStr">
+        <is>
+          <t>0.1098±0.0000 (1)</t>
+        </is>
+      </c>
+      <c r="K12" s="315" t="inlineStr">
+        <is>
+          <t>0.2724±0.0000 (1)</t>
+        </is>
+      </c>
+      <c r="L12" s="315" t="inlineStr">
+        <is>
+          <t>0.5568±0.0000 (1)</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="311" t="inlineStr">
-        <is>
-          <t>预训练</t>
-        </is>
-      </c>
+      <c r="A13" s="312" t="inlineStr"/>
       <c r="B13" s="312" t="inlineStr">
         <is>
-          <t>PACLock 预训练 base(60k)</t>
-        </is>
-      </c>
-      <c r="C13" s="313" t="inlineStr">
-        <is>
-          <t>0.8841±0.0043 (3)</t>
-        </is>
-      </c>
-      <c r="D13" s="313" t="inlineStr">
-        <is>
-          <t>0.6730±0.0116 (3)</t>
-        </is>
-      </c>
-      <c r="E13" s="313" t="inlineStr">
-        <is>
-          <t>0.6398±0.0615 (3)</t>
-        </is>
-      </c>
-      <c r="F13" s="313" t="inlineStr">
-        <is>
-          <t>0.6830±0.0228 (3)</t>
-        </is>
-      </c>
-      <c r="G13" s="313" t="inlineStr">
-        <is>
-          <t>0.6651±0.0109 (3)</t>
-        </is>
-      </c>
-      <c r="H13" s="313" t="inlineStr">
-        <is>
-          <t>0.6934±0.0032 (3)</t>
-        </is>
-      </c>
-      <c r="I13" s="313" t="inlineStr">
-        <is>
-          <t>0.3059±0.0262 (3)</t>
-        </is>
-      </c>
-      <c r="J13" s="313" t="inlineStr">
-        <is>
-          <t>0.1540±0.0202 (3)</t>
-        </is>
-      </c>
-      <c r="K13" s="313" t="inlineStr">
-        <is>
-          <t>0.3652±0.0083 (3)</t>
-        </is>
-      </c>
+          <t>spatial 头(保留电极身份)</t>
+        </is>
+      </c>
+      <c r="C13" s="313" t="n"/>
+      <c r="D13" s="313" t="n"/>
+      <c r="E13" s="313" t="n"/>
+      <c r="F13" s="313" t="n"/>
+      <c r="G13" s="313" t="n"/>
+      <c r="H13" s="313" t="n"/>
+      <c r="I13" s="315" t="inlineStr">
+        <is>
+          <t>0.3560±0.0000 (1)</t>
+        </is>
+      </c>
+      <c r="J13" s="315" t="inlineStr">
+        <is>
+          <t>0.1514±0.0000 (1)</t>
+        </is>
+      </c>
+      <c r="K13" s="315" t="inlineStr">
+        <is>
+          <t>0.4144±0.0000 (1)</t>
+        </is>
+      </c>
+      <c r="L13" s="313" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="312" t="inlineStr"/>
       <c r="B14" s="312" t="inlineStr">
         <is>
-          <t>PACLock 预训练 large(60k)</t>
-        </is>
-      </c>
-      <c r="C14" s="313" t="inlineStr">
-        <is>
-          <t>0.8869±0.0069 (3)</t>
-        </is>
-      </c>
-      <c r="D14" s="313" t="inlineStr">
-        <is>
-          <t>0.6523±0.0302 (3)</t>
-        </is>
-      </c>
-      <c r="E14" s="313" t="inlineStr">
-        <is>
-          <t>0.6289±0.0297 (3)</t>
-        </is>
-      </c>
-      <c r="F14" s="313" t="inlineStr">
-        <is>
-          <t>0.6162±0.0467 (3)</t>
-        </is>
-      </c>
-      <c r="G14" s="313" t="inlineStr">
-        <is>
-          <t>0.6641±0.0044 (3)</t>
-        </is>
-      </c>
-      <c r="H14" s="313" t="inlineStr">
-        <is>
-          <t>0.6996±0.0153 (3)</t>
-        </is>
-      </c>
-      <c r="I14" s="313" t="inlineStr">
-        <is>
-          <t>0.3140±0.0094 (3)</t>
-        </is>
-      </c>
-      <c r="J14" s="313" t="inlineStr">
-        <is>
-          <t>0.1640±0.0155 (3)</t>
-        </is>
-      </c>
-      <c r="K14" s="313" t="inlineStr">
-        <is>
-          <t>0.4122±0.0166 (3)</t>
-        </is>
-      </c>
+          <t>rotation + spatial 头</t>
+        </is>
+      </c>
+      <c r="C14" s="313" t="n"/>
+      <c r="D14" s="313" t="n"/>
+      <c r="E14" s="313" t="n"/>
+      <c r="F14" s="313" t="n"/>
+      <c r="G14" s="313" t="n"/>
+      <c r="H14" s="313" t="n"/>
+      <c r="I14" s="315" t="inlineStr">
+        <is>
+          <t>0.3299±0.0000 (1)</t>
+        </is>
+      </c>
+      <c r="J14" s="313" t="n"/>
+      <c r="K14" s="315" t="inlineStr">
+        <is>
+          <t>0.4344±0.0000 (1)</t>
+        </is>
+      </c>
+      <c r="L14" s="313" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="312" t="inlineStr"/>
+      <c r="A15" s="311" t="inlineStr">
+        <is>
+          <t>预训练</t>
+        </is>
+      </c>
       <c r="B15" s="312" t="inlineStr">
         <is>
-          <t>└ raw tokenizer 预训练 large(60k)</t>
-        </is>
-      </c>
-      <c r="C15" s="313" t="n"/>
-      <c r="D15" s="313" t="n"/>
-      <c r="E15" s="313" t="n"/>
-      <c r="F15" s="313" t="n"/>
-      <c r="G15" s="313" t="n"/>
-      <c r="H15" s="313" t="n"/>
+          <t>预训练 base(60k)</t>
+        </is>
+      </c>
+      <c r="C15" s="313" t="inlineStr">
+        <is>
+          <t>0.8841±0.0043 (3)</t>
+        </is>
+      </c>
+      <c r="D15" s="313" t="inlineStr">
+        <is>
+          <t>0.6730±0.0116 (3)</t>
+        </is>
+      </c>
+      <c r="E15" s="313" t="inlineStr">
+        <is>
+          <t>0.6398±0.0615 (3)</t>
+        </is>
+      </c>
+      <c r="F15" s="313" t="inlineStr">
+        <is>
+          <t>0.6830±0.0228 (3)</t>
+        </is>
+      </c>
+      <c r="G15" s="313" t="inlineStr">
+        <is>
+          <t>0.6651±0.0109 (3)</t>
+        </is>
+      </c>
+      <c r="H15" s="313" t="inlineStr">
+        <is>
+          <t>0.6934±0.0032 (3)</t>
+        </is>
+      </c>
       <c r="I15" s="313" t="inlineStr">
         <is>
-          <t>0.3633±0.0349 (3)</t>
-        </is>
-      </c>
-      <c r="J15" s="314" t="inlineStr">
-        <is>
-          <t>0.1690±0.0018 (2)</t>
+          <t>0.3059±0.0262 (3)</t>
+        </is>
+      </c>
+      <c r="J15" s="313" t="inlineStr">
+        <is>
+          <t>0.1540±0.0202 (3)</t>
         </is>
       </c>
       <c r="K15" s="313" t="inlineStr">
         <is>
-          <t>0.4483±0.0031 (3)</t>
-        </is>
-      </c>
+          <t>0.3652±0.0083 (3)</t>
+        </is>
+      </c>
+      <c r="L15" s="313" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="312" t="inlineStr"/>
       <c r="B16" s="312" t="inlineStr">
         <is>
-          <t>└ 预训练池剔除 TUSZ/CHB-MIT</t>
-        </is>
-      </c>
-      <c r="C16" s="313" t="n"/>
-      <c r="D16" s="313" t="n"/>
-      <c r="E16" s="314" t="inlineStr">
-        <is>
-          <t>0.6221±0.0000 (1)</t>
-        </is>
-      </c>
-      <c r="F16" s="314" t="inlineStr">
-        <is>
-          <t>0.6410±0.0000 (1)</t>
-        </is>
-      </c>
-      <c r="G16" s="313" t="n"/>
-      <c r="H16" s="313" t="n"/>
-      <c r="I16" s="313" t="n"/>
-      <c r="J16" s="313" t="n"/>
-      <c r="K16" s="313" t="n"/>
+          <t>预训练 large(60k)</t>
+        </is>
+      </c>
+      <c r="C16" s="313" t="inlineStr">
+        <is>
+          <t>0.8869±0.0069 (3)</t>
+        </is>
+      </c>
+      <c r="D16" s="313" t="inlineStr">
+        <is>
+          <t>0.6523±0.0302 (3)</t>
+        </is>
+      </c>
+      <c r="E16" s="313" t="inlineStr">
+        <is>
+          <t>0.6289±0.0297 (3)</t>
+        </is>
+      </c>
+      <c r="F16" s="313" t="inlineStr">
+        <is>
+          <t>0.6162±0.0467 (3)</t>
+        </is>
+      </c>
+      <c r="G16" s="313" t="inlineStr">
+        <is>
+          <t>0.6641±0.0044 (3)</t>
+        </is>
+      </c>
+      <c r="H16" s="313" t="inlineStr">
+        <is>
+          <t>0.6996±0.0153 (3)</t>
+        </is>
+      </c>
+      <c r="I16" s="313" t="inlineStr">
+        <is>
+          <t>0.3140±0.0094 (3)</t>
+        </is>
+      </c>
+      <c r="J16" s="313" t="inlineStr">
+        <is>
+          <t>0.1640±0.0155 (3)</t>
+        </is>
+      </c>
+      <c r="K16" s="313" t="inlineStr">
+        <is>
+          <t>0.4122±0.0166 (3)</t>
+        </is>
+      </c>
+      <c r="L16" s="313" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="311" t="inlineStr">
-        <is>
-          <t>已否决</t>
-        </is>
-      </c>
+      <c r="A17" s="312" t="inlineStr"/>
       <c r="B17" s="312" t="inlineStr">
         <is>
-          <t>spatial_pe: xyz(蒙太奇坐标)</t>
+          <t>raw tokenizer 预训练 large(60k)</t>
         </is>
       </c>
       <c r="C17" s="313" t="n"/>
@@ -11479,82 +11503,77 @@
       <c r="E17" s="313" t="n"/>
       <c r="F17" s="313" t="n"/>
       <c r="G17" s="313" t="n"/>
-      <c r="H17" s="313" t="inlineStr">
-        <is>
-          <t>0.6954±0.0167 (3)</t>
-        </is>
-      </c>
+      <c r="H17" s="313" t="n"/>
       <c r="I17" s="313" t="inlineStr">
         <is>
-          <t>0.2478±0.0053 (3)</t>
-        </is>
-      </c>
-      <c r="J17" s="313" t="n"/>
+          <t>0.3633±0.0349 (3)</t>
+        </is>
+      </c>
+      <c r="J17" s="315" t="inlineStr">
+        <is>
+          <t>0.1690±0.0018 (2)</t>
+        </is>
+      </c>
       <c r="K17" s="313" t="inlineStr">
         <is>
-          <t>0.3338±0.0027 (3)</t>
-        </is>
-      </c>
+          <t>0.4483±0.0031 (3)</t>
+        </is>
+      </c>
+      <c r="L17" s="313" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="312" t="inlineStr"/>
       <c r="B18" s="312" t="inlineStr">
         <is>
-          <t>每窗口归一化</t>
+          <t>预训练池剔除 TUSZ/CHB-MIT</t>
         </is>
       </c>
       <c r="C18" s="313" t="n"/>
       <c r="D18" s="313" t="n"/>
-      <c r="E18" s="313" t="n"/>
-      <c r="F18" s="313" t="n"/>
+      <c r="E18" s="315" t="inlineStr">
+        <is>
+          <t>0.6221±0.0000 (1)</t>
+        </is>
+      </c>
+      <c r="F18" s="315" t="inlineStr">
+        <is>
+          <t>0.6410±0.0000 (1)</t>
+        </is>
+      </c>
       <c r="G18" s="313" t="n"/>
       <c r="H18" s="313" t="n"/>
-      <c r="I18" s="313" t="inlineStr">
-        <is>
-          <t>0.2532±0.0155 (3)</t>
-        </is>
-      </c>
+      <c r="I18" s="313" t="n"/>
       <c r="J18" s="313" t="n"/>
-      <c r="K18" s="313" t="inlineStr">
-        <is>
-          <t>0.3050±0.0438 (3)</t>
-        </is>
-      </c>
+      <c r="K18" s="313" t="n"/>
+      <c r="L18" s="313" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="311" t="inlineStr">
-        <is>
-          <t>容量</t>
-        </is>
-      </c>
+      <c r="A19" s="312" t="inlineStr"/>
       <c r="B19" s="312" t="inlineStr">
         <is>
-          <t>raw + large 容量</t>
+          <t>预训练 base,微调 patch_len=200</t>
         </is>
       </c>
       <c r="C19" s="313" t="n"/>
-      <c r="D19" s="313" t="n"/>
+      <c r="D19" s="313" t="inlineStr">
+        <is>
+          <t>0.6793±0.0109 (3)</t>
+        </is>
+      </c>
       <c r="E19" s="313" t="n"/>
       <c r="F19" s="313" t="n"/>
       <c r="G19" s="313" t="n"/>
       <c r="H19" s="313" t="n"/>
-      <c r="I19" s="313" t="inlineStr">
-        <is>
-          <t>0.4159±0.0529 (3)</t>
-        </is>
-      </c>
+      <c r="I19" s="313" t="n"/>
       <c r="J19" s="313" t="n"/>
-      <c r="K19" s="313" t="inlineStr">
-        <is>
-          <t>0.4437±0.0192 (3)</t>
-        </is>
-      </c>
+      <c r="K19" s="313" t="n"/>
+      <c r="L19" s="313" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="312" t="inlineStr"/>
       <c r="B20" s="312" t="inlineStr">
         <is>
-          <t>raw + attn 头</t>
+          <t>早期微调配方(6k checkpoint)</t>
         </is>
       </c>
       <c r="C20" s="313" t="n"/>
@@ -11563,21 +11582,653 @@
       <c r="F20" s="313" t="n"/>
       <c r="G20" s="313" t="n"/>
       <c r="H20" s="313" t="n"/>
-      <c r="I20" s="313" t="inlineStr">
+      <c r="I20" s="315" t="inlineStr">
+        <is>
+          <t>0.2690±0.0000 (1)</t>
+        </is>
+      </c>
+      <c r="J20" s="315" t="inlineStr">
+        <is>
+          <t>0.1279±0.0000 (1)</t>
+        </is>
+      </c>
+      <c r="K20" s="313" t="n"/>
+      <c r="L20" s="313" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="312" t="inlineStr"/>
+      <c r="B21" s="312" t="inlineStr">
+        <is>
+          <t>早期微调配方 v2(6k checkpoint)</t>
+        </is>
+      </c>
+      <c r="C21" s="313" t="n"/>
+      <c r="D21" s="313" t="n"/>
+      <c r="E21" s="313" t="n"/>
+      <c r="F21" s="313" t="n"/>
+      <c r="G21" s="313" t="n"/>
+      <c r="H21" s="313" t="n"/>
+      <c r="I21" s="315" t="inlineStr">
+        <is>
+          <t>0.2622±0.0000 (1)</t>
+        </is>
+      </c>
+      <c r="J21" s="315" t="inlineStr">
+        <is>
+          <t>0.1408±0.0000 (1)</t>
+        </is>
+      </c>
+      <c r="K21" s="313" t="n"/>
+      <c r="L21" s="313" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="312" t="inlineStr"/>
+      <c r="B22" s="312" t="inlineStr">
+        <is>
+          <t>早期微调配方 large(6k checkpoint)</t>
+        </is>
+      </c>
+      <c r="C22" s="313" t="n"/>
+      <c r="D22" s="313" t="n"/>
+      <c r="E22" s="313" t="n"/>
+      <c r="F22" s="313" t="n"/>
+      <c r="G22" s="313" t="n"/>
+      <c r="H22" s="313" t="n"/>
+      <c r="I22" s="315" t="inlineStr">
+        <is>
+          <t>0.2716±0.0000 (1)</t>
+        </is>
+      </c>
+      <c r="J22" s="315" t="inlineStr">
+        <is>
+          <t>0.1381±0.0000 (1)</t>
+        </is>
+      </c>
+      <c r="K22" s="313" t="n"/>
+      <c r="L22" s="313" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="311" t="inlineStr">
+        <is>
+          <t>容量阶梯</t>
+        </is>
+      </c>
+      <c r="B23" s="312" t="inlineStr">
+        <is>
+          <t>raw,d_model 32</t>
+        </is>
+      </c>
+      <c r="C23" s="313" t="n"/>
+      <c r="D23" s="313" t="n"/>
+      <c r="E23" s="313" t="n"/>
+      <c r="F23" s="313" t="n"/>
+      <c r="G23" s="313" t="n"/>
+      <c r="H23" s="313" t="n"/>
+      <c r="I23" s="313" t="inlineStr">
+        <is>
+          <t>0.2613±0.0100 (3)</t>
+        </is>
+      </c>
+      <c r="J23" s="313" t="n"/>
+      <c r="K23" s="313" t="inlineStr">
+        <is>
+          <t>0.2617±0.0019 (3)</t>
+        </is>
+      </c>
+      <c r="L23" s="313" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="312" t="inlineStr"/>
+      <c r="B24" s="312" t="inlineStr">
+        <is>
+          <t>raw,d_model 64</t>
+        </is>
+      </c>
+      <c r="C24" s="313" t="n"/>
+      <c r="D24" s="313" t="n"/>
+      <c r="E24" s="313" t="n"/>
+      <c r="F24" s="313" t="n"/>
+      <c r="G24" s="313" t="n"/>
+      <c r="H24" s="313" t="n"/>
+      <c r="I24" s="313" t="inlineStr">
+        <is>
+          <t>0.3129±0.0121 (3)</t>
+        </is>
+      </c>
+      <c r="J24" s="313" t="n"/>
+      <c r="K24" s="313" t="inlineStr">
+        <is>
+          <t>0.2780±0.0100 (3)</t>
+        </is>
+      </c>
+      <c r="L24" s="313" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="312" t="inlineStr"/>
+      <c r="B25" s="312" t="inlineStr">
+        <is>
+          <t>raw,d_model 256</t>
+        </is>
+      </c>
+      <c r="C25" s="313" t="n"/>
+      <c r="D25" s="313" t="n"/>
+      <c r="E25" s="313" t="n"/>
+      <c r="F25" s="313" t="n"/>
+      <c r="G25" s="313" t="n"/>
+      <c r="H25" s="313" t="n"/>
+      <c r="I25" s="313" t="inlineStr">
+        <is>
+          <t>0.4159±0.0529 (3)</t>
+        </is>
+      </c>
+      <c r="J25" s="313" t="n"/>
+      <c r="K25" s="313" t="inlineStr">
+        <is>
+          <t>0.4437±0.0192 (3)</t>
+        </is>
+      </c>
+      <c r="L25" s="313" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="312" t="inlineStr"/>
+      <c r="B26" s="312" t="inlineStr">
+        <is>
+          <t>raw,加宽</t>
+        </is>
+      </c>
+      <c r="C26" s="313" t="n"/>
+      <c r="D26" s="313" t="n"/>
+      <c r="E26" s="313" t="n"/>
+      <c r="F26" s="313" t="n"/>
+      <c r="G26" s="313" t="n"/>
+      <c r="H26" s="313" t="n"/>
+      <c r="I26" s="313" t="inlineStr">
+        <is>
+          <t>0.4093±0.0425 (3)</t>
+        </is>
+      </c>
+      <c r="J26" s="313" t="n"/>
+      <c r="K26" s="315" t="inlineStr">
+        <is>
+          <t>0.4261±0.0085 (2)</t>
+        </is>
+      </c>
+      <c r="L26" s="313" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="312" t="inlineStr"/>
+      <c r="B27" s="312" t="inlineStr">
+        <is>
+          <t>raw,16 频带</t>
+        </is>
+      </c>
+      <c r="C27" s="313" t="n"/>
+      <c r="D27" s="313" t="n"/>
+      <c r="E27" s="313" t="n"/>
+      <c r="F27" s="313" t="n"/>
+      <c r="G27" s="313" t="n"/>
+      <c r="H27" s="313" t="n"/>
+      <c r="I27" s="313" t="inlineStr">
+        <is>
+          <t>0.3781±0.0467 (3)</t>
+        </is>
+      </c>
+      <c r="J27" s="313" t="n"/>
+      <c r="K27" s="313" t="inlineStr">
+        <is>
+          <t>0.4288±0.0090 (3)</t>
+        </is>
+      </c>
+      <c r="L27" s="313" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="312" t="inlineStr"/>
+      <c r="B28" s="312" t="inlineStr">
+        <is>
+          <t>raw,patch_len 100</t>
+        </is>
+      </c>
+      <c r="C28" s="313" t="n"/>
+      <c r="D28" s="313" t="n"/>
+      <c r="E28" s="313" t="n"/>
+      <c r="F28" s="313" t="n"/>
+      <c r="G28" s="313" t="n"/>
+      <c r="H28" s="313" t="n"/>
+      <c r="I28" s="313" t="inlineStr">
+        <is>
+          <t>0.3508±0.0251 (3)</t>
+        </is>
+      </c>
+      <c r="J28" s="313" t="n"/>
+      <c r="K28" s="313" t="inlineStr">
+        <is>
+          <t>0.4066±0.0221 (3)</t>
+        </is>
+      </c>
+      <c r="L28" s="313" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="312" t="inlineStr"/>
+      <c r="B29" s="312" t="inlineStr">
+        <is>
+          <t>raw,dropout 0.5</t>
+        </is>
+      </c>
+      <c r="C29" s="313" t="n"/>
+      <c r="D29" s="313" t="n"/>
+      <c r="E29" s="313" t="n"/>
+      <c r="F29" s="313" t="n"/>
+      <c r="G29" s="313" t="n"/>
+      <c r="H29" s="313" t="n"/>
+      <c r="I29" s="313" t="inlineStr">
+        <is>
+          <t>0.3409±0.0196 (3)</t>
+        </is>
+      </c>
+      <c r="J29" s="313" t="n"/>
+      <c r="K29" s="313" t="inlineStr">
+        <is>
+          <t>0.4308±0.0139 (3)</t>
+        </is>
+      </c>
+      <c r="L29" s="313" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="312" t="inlineStr"/>
+      <c r="B30" s="312" t="inlineStr">
+        <is>
+          <t>raw,attn 头</t>
+        </is>
+      </c>
+      <c r="C30" s="313" t="n"/>
+      <c r="D30" s="313" t="n"/>
+      <c r="E30" s="313" t="n"/>
+      <c r="F30" s="313" t="n"/>
+      <c r="G30" s="313" t="n"/>
+      <c r="H30" s="313" t="n"/>
+      <c r="I30" s="313" t="inlineStr">
         <is>
           <t>0.3524±0.0467 (3)</t>
         </is>
       </c>
-      <c r="J20" s="313" t="n"/>
-      <c r="K20" s="313" t="inlineStr">
+      <c r="J30" s="313" t="n"/>
+      <c r="K30" s="313" t="inlineStr">
         <is>
           <t>0.4545±0.0054 (3)</t>
+        </is>
+      </c>
+      <c r="L30" s="313" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="311" t="inlineStr">
+        <is>
+          <t>已否决</t>
+        </is>
+      </c>
+      <c r="B31" s="312" t="inlineStr">
+        <is>
+          <t>spatial_pe: xyz(蒙太奇坐标)</t>
+        </is>
+      </c>
+      <c r="C31" s="313" t="n"/>
+      <c r="D31" s="313" t="n"/>
+      <c r="E31" s="313" t="n"/>
+      <c r="F31" s="313" t="n"/>
+      <c r="G31" s="313" t="n"/>
+      <c r="H31" s="313" t="inlineStr">
+        <is>
+          <t>0.6954±0.0167 (3)</t>
+        </is>
+      </c>
+      <c r="I31" s="313" t="inlineStr">
+        <is>
+          <t>0.2478±0.0053 (3)</t>
+        </is>
+      </c>
+      <c r="J31" s="313" t="n"/>
+      <c r="K31" s="313" t="inlineStr">
+        <is>
+          <t>0.3338±0.0027 (3)</t>
+        </is>
+      </c>
+      <c r="L31" s="313" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="312" t="inlineStr"/>
+      <c r="B32" s="312" t="inlineStr">
+        <is>
+          <t>每窗口归一化</t>
+        </is>
+      </c>
+      <c r="C32" s="313" t="n"/>
+      <c r="D32" s="313" t="n"/>
+      <c r="E32" s="313" t="n"/>
+      <c r="F32" s="313" t="n"/>
+      <c r="G32" s="313" t="n"/>
+      <c r="H32" s="313" t="n"/>
+      <c r="I32" s="313" t="inlineStr">
+        <is>
+          <t>0.2532±0.0155 (3)</t>
+        </is>
+      </c>
+      <c r="J32" s="313" t="n"/>
+      <c r="K32" s="313" t="inlineStr">
+        <is>
+          <t>0.3050±0.0438 (3)</t>
+        </is>
+      </c>
+      <c r="L32" s="313" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="312" t="inlineStr"/>
+      <c r="B33" s="312" t="inlineStr">
+        <is>
+          <t>每窗口归一化 + raw</t>
+        </is>
+      </c>
+      <c r="C33" s="313" t="n"/>
+      <c r="D33" s="313" t="n"/>
+      <c r="E33" s="313" t="n"/>
+      <c r="F33" s="313" t="n"/>
+      <c r="G33" s="313" t="n"/>
+      <c r="H33" s="313" t="n"/>
+      <c r="I33" s="315" t="inlineStr">
+        <is>
+          <t>0.2896±0.0146 (2)</t>
+        </is>
+      </c>
+      <c r="J33" s="313" t="n"/>
+      <c r="K33" s="315" t="inlineStr">
+        <is>
+          <t>0.2992±0.0139 (2)</t>
+        </is>
+      </c>
+      <c r="L33" s="313" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="312" t="inlineStr"/>
+      <c r="B34" s="312" t="inlineStr">
+        <is>
+          <t>每受试者归一化</t>
+        </is>
+      </c>
+      <c r="C34" s="313" t="n"/>
+      <c r="D34" s="313" t="n"/>
+      <c r="E34" s="313" t="n"/>
+      <c r="F34" s="313" t="n"/>
+      <c r="G34" s="313" t="n"/>
+      <c r="H34" s="313" t="n"/>
+      <c r="I34" s="313" t="n"/>
+      <c r="J34" s="315" t="inlineStr">
+        <is>
+          <t>0.1328±0.0007 (2)</t>
+        </is>
+      </c>
+      <c r="K34" s="313" t="n"/>
+      <c r="L34" s="313" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="312" t="inlineStr"/>
+      <c r="B35" s="312" t="inlineStr">
+        <is>
+          <t>每受试者归一化 + raw</t>
+        </is>
+      </c>
+      <c r="C35" s="313" t="n"/>
+      <c r="D35" s="313" t="n"/>
+      <c r="E35" s="313" t="n"/>
+      <c r="F35" s="313" t="n"/>
+      <c r="G35" s="313" t="n"/>
+      <c r="H35" s="313" t="n"/>
+      <c r="I35" s="313" t="n"/>
+      <c r="J35" s="313" t="inlineStr">
+        <is>
+          <t>0.1579±0.0034 (3)</t>
+        </is>
+      </c>
+      <c r="K35" s="313" t="n"/>
+      <c r="L35" s="313" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="312" t="inlineStr"/>
+      <c r="B36" s="312" t="inlineStr">
+        <is>
+          <t>每受试者归一化 + raw + attn 头</t>
+        </is>
+      </c>
+      <c r="C36" s="313" t="n"/>
+      <c r="D36" s="313" t="n"/>
+      <c r="E36" s="313" t="n"/>
+      <c r="F36" s="313" t="n"/>
+      <c r="G36" s="313" t="n"/>
+      <c r="H36" s="313" t="n"/>
+      <c r="I36" s="313" t="n"/>
+      <c r="J36" s="313" t="inlineStr">
+        <is>
+          <t>0.1513±0.0012 (3)</t>
+        </is>
+      </c>
+      <c r="K36" s="313" t="n"/>
+      <c r="L36" s="313" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="312" t="inlineStr"/>
+      <c r="B37" s="312" t="inlineStr">
+        <is>
+          <t>FACED 伪迹清洗</t>
+        </is>
+      </c>
+      <c r="C37" s="313" t="n"/>
+      <c r="D37" s="313" t="n"/>
+      <c r="E37" s="313" t="n"/>
+      <c r="F37" s="313" t="n"/>
+      <c r="G37" s="313" t="n"/>
+      <c r="H37" s="313" t="n"/>
+      <c r="I37" s="313" t="n"/>
+      <c r="J37" s="313" t="inlineStr">
+        <is>
+          <t>0.1346±0.0157 (3)</t>
+        </is>
+      </c>
+      <c r="K37" s="313" t="n"/>
+      <c r="L37" s="313" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="312" t="inlineStr"/>
+      <c r="B38" s="312" t="inlineStr">
+        <is>
+          <t>lr 1e-3</t>
+        </is>
+      </c>
+      <c r="C38" s="313" t="n"/>
+      <c r="D38" s="313" t="n"/>
+      <c r="E38" s="313" t="n"/>
+      <c r="F38" s="313" t="n"/>
+      <c r="G38" s="313" t="n"/>
+      <c r="H38" s="313" t="n"/>
+      <c r="I38" s="313" t="inlineStr">
+        <is>
+          <t>0.2498±0.0077 (3)</t>
+        </is>
+      </c>
+      <c r="J38" s="313" t="n"/>
+      <c r="K38" s="313" t="inlineStr">
+        <is>
+          <t>0.3094±0.0345 (3)</t>
+        </is>
+      </c>
+      <c r="L38" s="313" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="312" t="inlineStr"/>
+      <c r="B39" s="312" t="inlineStr">
+        <is>
+          <t>lr 3e-4</t>
+        </is>
+      </c>
+      <c r="C39" s="313" t="n"/>
+      <c r="D39" s="313" t="n"/>
+      <c r="E39" s="313" t="n"/>
+      <c r="F39" s="313" t="n"/>
+      <c r="G39" s="313" t="n"/>
+      <c r="H39" s="313" t="n"/>
+      <c r="I39" s="313" t="inlineStr">
+        <is>
+          <t>0.2623±0.0042 (3)</t>
+        </is>
+      </c>
+      <c r="J39" s="313" t="n"/>
+      <c r="K39" s="313" t="inlineStr">
+        <is>
+          <t>0.3495±0.0039 (3)</t>
+        </is>
+      </c>
+      <c r="L39" s="313" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="311" t="inlineStr">
+        <is>
+          <t>早期 pilot</t>
+        </is>
+      </c>
+      <c r="B40" s="312" t="inlineStr">
+        <is>
+          <t>冻结前端 pilot</t>
+        </is>
+      </c>
+      <c r="C40" s="313" t="n"/>
+      <c r="D40" s="313" t="inlineStr">
+        <is>
+          <t>0.6272±0.0099 (3)</t>
+        </is>
+      </c>
+      <c r="E40" s="313" t="n"/>
+      <c r="F40" s="313" t="n"/>
+      <c r="G40" s="313" t="n"/>
+      <c r="H40" s="313" t="n"/>
+      <c r="I40" s="313" t="n"/>
+      <c r="J40" s="313" t="n"/>
+      <c r="K40" s="313" t="n"/>
+      <c r="L40" s="313" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="312" t="inlineStr"/>
+      <c r="B41" s="312" t="inlineStr">
+        <is>
+          <t>未滤波 pilot</t>
+        </is>
+      </c>
+      <c r="C41" s="313" t="n"/>
+      <c r="D41" s="313" t="inlineStr">
+        <is>
+          <t>0.6209±0.0503 (3)</t>
+        </is>
+      </c>
+      <c r="E41" s="313" t="n"/>
+      <c r="F41" s="313" t="n"/>
+      <c r="G41" s="313" t="n"/>
+      <c r="H41" s="313" t="n"/>
+      <c r="I41" s="313" t="n"/>
+      <c r="J41" s="313" t="n"/>
+      <c r="K41" s="313" t="n"/>
+      <c r="L41" s="313" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="316" t="inlineStr">
+        <is>
+          <t>样本量消融</t>
+        </is>
+      </c>
+      <c r="B43" s="317" t="inlineStr">
+        <is>
+          <t>TUEV 训练集降采样(kappa) —— 检验等级三是否只是样本量问题</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="B44" s="309" t="inlineStr">
+        <is>
+          <t>模型</t>
+        </is>
+      </c>
+      <c r="C44" s="310" t="inlineStr">
+        <is>
+          <t>n=2160</t>
+        </is>
+      </c>
+      <c r="D44" s="310" t="inlineStr">
+        <is>
+          <t>n=6720</t>
+        </is>
+      </c>
+      <c r="E44" s="310" t="inlineStr">
+        <is>
+          <t>n=20000</t>
+        </is>
+      </c>
+      <c r="F44" s="310" t="inlineStr">
+        <is>
+          <t>全量 68445</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="B45" s="312" t="inlineStr">
+        <is>
+          <t>PACLock v2</t>
+        </is>
+      </c>
+      <c r="C45" s="315" t="inlineStr">
+        <is>
+          <t>0.6523±0.0000 (1)</t>
+        </is>
+      </c>
+      <c r="D45" s="315" t="inlineStr">
+        <is>
+          <t>0.7098±0.0000 (1)</t>
+        </is>
+      </c>
+      <c r="E45" s="315" t="inlineStr">
+        <is>
+          <t>0.6767±0.0000 (1)</t>
+        </is>
+      </c>
+      <c r="F45" s="313" t="inlineStr">
+        <is>
+          <t>0.7076±0.0311 (3)</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="B46" s="312" t="inlineStr">
+        <is>
+          <t>SPaRCNet</t>
+        </is>
+      </c>
+      <c r="C46" s="315" t="inlineStr">
+        <is>
+          <t>0.4917±0.0000 (1)</t>
+        </is>
+      </c>
+      <c r="D46" s="315" t="inlineStr">
+        <is>
+          <t>0.5532±0.0000 (1)</t>
+        </is>
+      </c>
+      <c r="E46" s="315" t="inlineStr">
+        <is>
+          <t>0.3642±0.0000 (1)</t>
+        </is>
+      </c>
+      <c r="F46" s="313" t="inlineStr">
+        <is>
+          <t>0.4885±0.0279 (3)</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A2:K2"/>
+    <mergeCell ref="A2:L2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/results/PACLock_baseline_matrix_filled.xlsx
+++ b/results/PACLock_baseline_matrix_filled.xlsx
@@ -11275,7 +11275,11 @@
           <t>0.6449±0.0000 (1)</t>
         </is>
       </c>
-      <c r="H11" s="313" t="n"/>
+      <c r="H11" s="315" t="inlineStr">
+        <is>
+          <t>0.7104±0.0000 (1)</t>
+        </is>
+      </c>
       <c r="I11" s="315" t="inlineStr">
         <is>
           <t>0.2961±0.0000 (1)</t>
@@ -11331,7 +11335,11 @@
         </is>
       </c>
       <c r="C13" s="313" t="n"/>
-      <c r="D13" s="313" t="n"/>
+      <c r="D13" s="315" t="inlineStr">
+        <is>
+          <t>0.6520±0.0000 (1)</t>
+        </is>
+      </c>
       <c r="E13" s="313" t="n"/>
       <c r="F13" s="313" t="n"/>
       <c r="G13" s="313" t="n"/>

--- a/results/PACLock_baseline_matrix_filled.xlsx
+++ b/results/PACLock_baseline_matrix_filled.xlsx
@@ -11258,7 +11258,11 @@
           <t>rotation(耦合只旋转不缩放)</t>
         </is>
       </c>
-      <c r="C11" s="313" t="n"/>
+      <c r="C11" s="315" t="inlineStr">
+        <is>
+          <t>0.8806±0.0000 (1)</t>
+        </is>
+      </c>
       <c r="D11" s="313" t="inlineStr">
         <is>
           <t>0.7328±0.0161 (3)</t>
@@ -11269,7 +11273,11 @@
           <t>0.6884±0.0000 (1)</t>
         </is>
       </c>
-      <c r="F11" s="313" t="n"/>
+      <c r="F11" s="315" t="inlineStr">
+        <is>
+          <t>0.5100±0.0000 (1)</t>
+        </is>
+      </c>
       <c r="G11" s="315" t="inlineStr">
         <is>
           <t>0.6449±0.0000 (1)</t>

--- a/results/PACLock_baseline_matrix_filled.xlsx
+++ b/results/PACLock_baseline_matrix_filled.xlsx
@@ -28,7 +28,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0000"/>
   </numFmts>
-  <fonts count="44">
+  <fonts count="45">
     <font>
       <name val="Calibri"/>
       <color indexed="8"/>
@@ -259,6 +259,10 @@
     <font>
       <i val="1"/>
       <color rgb="00808080"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <sz val="10"/>
     </font>
   </fonts>
   <fills count="22">
@@ -1234,7 +1238,7 @@
       <alignment vertical="bottom"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="318">
+  <cellXfs count="322">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="bottom"/>
     </xf>
@@ -2141,6 +2145,18 @@
     </xf>
     <xf numFmtId="0" fontId="34" fillId="19" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="34" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="38" fillId="10" borderId="68" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="10" borderId="68" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="10" borderId="68" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="0" borderId="68" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3519,7 +3535,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I22"/>
+  <dimension ref="A1:I23"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.83333" defaultRowHeight="15" customHeight="1" outlineLevelRow="0"/>
   <cols>
     <col width="24" customWidth="1" style="219" min="1" max="4"/>
@@ -4258,15 +4274,55 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="32" customHeight="1" s="220"/>
-    <row r="22" ht="22" customHeight="1" s="220">
-      <c r="A22" s="300" t="inlineStr">
+    <row r="21" ht="32" customHeight="1" s="220">
+      <c r="A21" s="297" t="n"/>
+      <c r="B21" s="318" t="inlineStr">
+        <is>
+          <t>PACLock (hybrid)</t>
+        </is>
+      </c>
+      <c r="C21" s="319" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="D21" s="320" t="inlineStr">
+        <is>
+          <t>0.3912 (1 seed)</t>
+        </is>
+      </c>
+      <c r="E21" s="320" t="inlineStr">
+        <is>
+          <t>0.1883 (1 seed)</t>
+        </is>
+      </c>
+      <c r="F21" s="320" t="inlineStr">
+        <is>
+          <t>0.3796 (1 seed)</t>
+        </is>
+      </c>
+      <c r="G21" s="320" t="inlineStr">
+        <is>
+          <t>+0.0324</t>
+        </is>
+      </c>
+      <c r="H21" s="321" t="inlineStr">
+        <is>
+          <t>+0.0260</t>
+        </is>
+      </c>
+      <c r="I21" s="321" t="inlineStr">
+        <is>
+          <t>-0.0210</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="22" customHeight="1" s="220"/>
+    <row r="23" ht="38" customHeight="1" s="220">
+      <c r="A23" s="300" t="inlineStr">
         <is>
           <t>灰色行 = 该 baseline 的原论文未评测本数据集,不存在官方超参;所用配方由我们从该模型覆盖过的数据集迁移而来。这些数字反映的是「该架构在我们所选配方下的表现」,不是「该 baseline 已发表的能力」。</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="38" customHeight="1" s="220"/>
     <row r="24" ht="38" customHeight="1" s="220"/>
     <row r="25" ht="38" customHeight="1" s="220"/>
     <row r="26" ht="38" customHeight="1" s="220"/>
@@ -10910,7 +10966,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L46"/>
+  <dimension ref="A1:L49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" style="220" min="1" max="1"/>
@@ -11255,52 +11311,32 @@
       </c>
       <c r="B11" s="312" t="inlineStr">
         <is>
-          <t>rotation(耦合只旋转不缩放)</t>
-        </is>
-      </c>
-      <c r="C11" s="315" t="inlineStr">
-        <is>
-          <t>0.8806±0.0000 (1)</t>
-        </is>
-      </c>
-      <c r="D11" s="313" t="inlineStr">
-        <is>
-          <t>0.7328±0.0161 (3)</t>
+          <t>hybrid(raw 行 + 交互行并列)</t>
+        </is>
+      </c>
+      <c r="C11" s="313" t="n"/>
+      <c r="D11" s="315" t="inlineStr">
+        <is>
+          <t>0.6951±0.0000 (1)</t>
         </is>
       </c>
       <c r="E11" s="315" t="inlineStr">
         <is>
-          <t>0.6884±0.0000 (1)</t>
+          <t>0.6299±0.0000 (1)</t>
         </is>
       </c>
       <c r="F11" s="315" t="inlineStr">
         <is>
-          <t>0.5100±0.0000 (1)</t>
-        </is>
-      </c>
-      <c r="G11" s="315" t="inlineStr">
-        <is>
-          <t>0.6449±0.0000 (1)</t>
-        </is>
-      </c>
-      <c r="H11" s="315" t="inlineStr">
-        <is>
-          <t>0.7104±0.0000 (1)</t>
-        </is>
-      </c>
-      <c r="I11" s="315" t="inlineStr">
-        <is>
-          <t>0.2961±0.0000 (1)</t>
-        </is>
-      </c>
-      <c r="J11" s="315" t="inlineStr">
-        <is>
-          <t>0.1514±0.0000 (1)</t>
-        </is>
-      </c>
-      <c r="K11" s="313" t="inlineStr">
-        <is>
-          <t>0.3708±0.0092 (3)</t>
+          <t>0.7473±0.0000 (1)</t>
+        </is>
+      </c>
+      <c r="G11" s="313" t="n"/>
+      <c r="H11" s="313" t="n"/>
+      <c r="I11" s="313" t="n"/>
+      <c r="J11" s="313" t="n"/>
+      <c r="K11" s="315" t="inlineStr">
+        <is>
+          <t>0.3912±0.0000 (1)</t>
         </is>
       </c>
       <c r="L11" s="313" t="n"/>
@@ -11309,62 +11345,62 @@
       <c r="A12" s="312" t="inlineStr"/>
       <c r="B12" s="312" t="inlineStr">
         <is>
-          <t>rotation(跑在 PAC 协议数据上,与上行不可比)</t>
+          <t>hybrid + 逐频带可学门</t>
         </is>
       </c>
       <c r="C12" s="313" t="n"/>
-      <c r="D12" s="313" t="n"/>
-      <c r="E12" s="313" t="n"/>
+      <c r="D12" s="315" t="inlineStr">
+        <is>
+          <t>0.6929±0.0000 (1)</t>
+        </is>
+      </c>
+      <c r="E12" s="315" t="inlineStr">
+        <is>
+          <t>0.6455±0.0000 (1)</t>
+        </is>
+      </c>
       <c r="F12" s="313" t="n"/>
       <c r="G12" s="313" t="n"/>
       <c r="H12" s="313" t="n"/>
       <c r="I12" s="313" t="n"/>
-      <c r="J12" s="315" t="inlineStr">
-        <is>
-          <t>0.1098±0.0000 (1)</t>
-        </is>
-      </c>
+      <c r="J12" s="313" t="n"/>
       <c r="K12" s="315" t="inlineStr">
         <is>
-          <t>0.2724±0.0000 (1)</t>
-        </is>
-      </c>
-      <c r="L12" s="315" t="inlineStr">
-        <is>
-          <t>0.5568±0.0000 (1)</t>
-        </is>
-      </c>
+          <t>0.3970±0.0000 (1)</t>
+        </is>
+      </c>
+      <c r="L12" s="313" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="312" t="inlineStr"/>
       <c r="B13" s="312" t="inlineStr">
         <is>
-          <t>spatial 头(保留电极身份)</t>
+          <t>hybrid + attn 头</t>
         </is>
       </c>
       <c r="C13" s="313" t="n"/>
       <c r="D13" s="315" t="inlineStr">
         <is>
-          <t>0.6520±0.0000 (1)</t>
-        </is>
-      </c>
-      <c r="E13" s="313" t="n"/>
-      <c r="F13" s="313" t="n"/>
+          <t>0.6814±0.0000 (1)</t>
+        </is>
+      </c>
+      <c r="E13" s="315" t="inlineStr">
+        <is>
+          <t>0.6306±0.0000 (1)</t>
+        </is>
+      </c>
+      <c r="F13" s="315" t="inlineStr">
+        <is>
+          <t>0.7200±0.0000 (1)</t>
+        </is>
+      </c>
       <c r="G13" s="313" t="n"/>
       <c r="H13" s="313" t="n"/>
-      <c r="I13" s="315" t="inlineStr">
-        <is>
-          <t>0.3560±0.0000 (1)</t>
-        </is>
-      </c>
-      <c r="J13" s="315" t="inlineStr">
-        <is>
-          <t>0.1514±0.0000 (1)</t>
-        </is>
-      </c>
+      <c r="I13" s="313" t="n"/>
+      <c r="J13" s="313" t="n"/>
       <c r="K13" s="315" t="inlineStr">
         <is>
-          <t>0.4144±0.0000 (1)</t>
+          <t>0.3542±0.0000 (1)</t>
         </is>
       </c>
       <c r="L13" s="313" t="n"/>
@@ -11373,136 +11409,116 @@
       <c r="A14" s="312" t="inlineStr"/>
       <c r="B14" s="312" t="inlineStr">
         <is>
-          <t>rotation + spatial 头</t>
-        </is>
-      </c>
-      <c r="C14" s="313" t="n"/>
-      <c r="D14" s="313" t="n"/>
-      <c r="E14" s="313" t="n"/>
-      <c r="F14" s="313" t="n"/>
-      <c r="G14" s="313" t="n"/>
-      <c r="H14" s="313" t="n"/>
+          <t>rotation(耦合只旋转不缩放)</t>
+        </is>
+      </c>
+      <c r="C14" s="315" t="inlineStr">
+        <is>
+          <t>0.8806±0.0000 (1)</t>
+        </is>
+      </c>
+      <c r="D14" s="313" t="inlineStr">
+        <is>
+          <t>0.7328±0.0161 (3)</t>
+        </is>
+      </c>
+      <c r="E14" s="315" t="inlineStr">
+        <is>
+          <t>0.6884±0.0000 (1)</t>
+        </is>
+      </c>
+      <c r="F14" s="315" t="inlineStr">
+        <is>
+          <t>0.5100±0.0000 (1)</t>
+        </is>
+      </c>
+      <c r="G14" s="315" t="inlineStr">
+        <is>
+          <t>0.6449±0.0000 (1)</t>
+        </is>
+      </c>
+      <c r="H14" s="315" t="inlineStr">
+        <is>
+          <t>0.7104±0.0000 (1)</t>
+        </is>
+      </c>
       <c r="I14" s="315" t="inlineStr">
         <is>
-          <t>0.3299±0.0000 (1)</t>
-        </is>
-      </c>
-      <c r="J14" s="313" t="n"/>
-      <c r="K14" s="315" t="inlineStr">
-        <is>
-          <t>0.4344±0.0000 (1)</t>
+          <t>0.2916±0.0063 (2)</t>
+        </is>
+      </c>
+      <c r="J14" s="315" t="inlineStr">
+        <is>
+          <t>0.1514±0.0000 (1)</t>
+        </is>
+      </c>
+      <c r="K14" s="313" t="inlineStr">
+        <is>
+          <t>0.3708±0.0092 (3)</t>
         </is>
       </c>
       <c r="L14" s="313" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="311" t="inlineStr">
-        <is>
-          <t>预训练</t>
-        </is>
-      </c>
+      <c r="A15" s="312" t="inlineStr"/>
       <c r="B15" s="312" t="inlineStr">
         <is>
-          <t>预训练 base(60k)</t>
-        </is>
-      </c>
-      <c r="C15" s="313" t="inlineStr">
-        <is>
-          <t>0.8841±0.0043 (3)</t>
-        </is>
-      </c>
-      <c r="D15" s="313" t="inlineStr">
-        <is>
-          <t>0.6730±0.0116 (3)</t>
-        </is>
-      </c>
-      <c r="E15" s="313" t="inlineStr">
-        <is>
-          <t>0.6398±0.0615 (3)</t>
-        </is>
-      </c>
-      <c r="F15" s="313" t="inlineStr">
-        <is>
-          <t>0.6830±0.0228 (3)</t>
-        </is>
-      </c>
-      <c r="G15" s="313" t="inlineStr">
-        <is>
-          <t>0.6651±0.0109 (3)</t>
-        </is>
-      </c>
-      <c r="H15" s="313" t="inlineStr">
-        <is>
-          <t>0.6934±0.0032 (3)</t>
-        </is>
-      </c>
-      <c r="I15" s="313" t="inlineStr">
-        <is>
-          <t>0.3059±0.0262 (3)</t>
-        </is>
-      </c>
-      <c r="J15" s="313" t="inlineStr">
-        <is>
-          <t>0.1540±0.0202 (3)</t>
-        </is>
-      </c>
-      <c r="K15" s="313" t="inlineStr">
-        <is>
-          <t>0.3652±0.0083 (3)</t>
-        </is>
-      </c>
-      <c r="L15" s="313" t="n"/>
+          <t>rotation(跑在 PAC 协议数据上,与上行不可比)</t>
+        </is>
+      </c>
+      <c r="C15" s="313" t="n"/>
+      <c r="D15" s="313" t="n"/>
+      <c r="E15" s="313" t="n"/>
+      <c r="F15" s="313" t="n"/>
+      <c r="G15" s="313" t="n"/>
+      <c r="H15" s="313" t="n"/>
+      <c r="I15" s="313" t="n"/>
+      <c r="J15" s="315" t="inlineStr">
+        <is>
+          <t>0.1098±0.0000 (1)</t>
+        </is>
+      </c>
+      <c r="K15" s="315" t="inlineStr">
+        <is>
+          <t>0.2724±0.0000 (1)</t>
+        </is>
+      </c>
+      <c r="L15" s="315" t="inlineStr">
+        <is>
+          <t>0.5568±0.0000 (1)</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="312" t="inlineStr"/>
       <c r="B16" s="312" t="inlineStr">
         <is>
-          <t>预训练 large(60k)</t>
-        </is>
-      </c>
-      <c r="C16" s="313" t="inlineStr">
-        <is>
-          <t>0.8869±0.0069 (3)</t>
-        </is>
-      </c>
-      <c r="D16" s="313" t="inlineStr">
-        <is>
-          <t>0.6523±0.0302 (3)</t>
-        </is>
-      </c>
-      <c r="E16" s="313" t="inlineStr">
-        <is>
-          <t>0.6289±0.0297 (3)</t>
-        </is>
-      </c>
-      <c r="F16" s="313" t="inlineStr">
-        <is>
-          <t>0.6162±0.0467 (3)</t>
-        </is>
-      </c>
-      <c r="G16" s="313" t="inlineStr">
-        <is>
-          <t>0.6641±0.0044 (3)</t>
-        </is>
-      </c>
-      <c r="H16" s="313" t="inlineStr">
-        <is>
-          <t>0.6996±0.0153 (3)</t>
-        </is>
-      </c>
+          <t>spatial 头(保留电极身份)</t>
+        </is>
+      </c>
+      <c r="C16" s="313" t="n"/>
+      <c r="D16" s="315" t="inlineStr">
+        <is>
+          <t>0.6520±0.0000 (1)</t>
+        </is>
+      </c>
+      <c r="E16" s="313" t="n"/>
+      <c r="F16" s="313" t="n"/>
+      <c r="G16" s="313" t="n"/>
+      <c r="H16" s="313" t="n"/>
       <c r="I16" s="313" t="inlineStr">
         <is>
-          <t>0.3140±0.0094 (3)</t>
-        </is>
-      </c>
-      <c r="J16" s="313" t="inlineStr">
-        <is>
-          <t>0.1640±0.0155 (3)</t>
+          <t>0.3535±0.0047 (3)</t>
+        </is>
+      </c>
+      <c r="J16" s="315" t="inlineStr">
+        <is>
+          <t>0.1514±0.0000 (1)</t>
         </is>
       </c>
       <c r="K16" s="313" t="inlineStr">
         <is>
-          <t>0.4122±0.0166 (3)</t>
+          <t>0.4317±0.0153 (3)</t>
         </is>
       </c>
       <c r="L16" s="313" t="n"/>
@@ -11511,7 +11527,7 @@
       <c r="A17" s="312" t="inlineStr"/>
       <c r="B17" s="312" t="inlineStr">
         <is>
-          <t>raw tokenizer 预训练 large(60k)</t>
+          <t>rotation + spatial 头</t>
         </is>
       </c>
       <c r="C17" s="313" t="n"/>
@@ -11520,120 +11536,192 @@
       <c r="F17" s="313" t="n"/>
       <c r="G17" s="313" t="n"/>
       <c r="H17" s="313" t="n"/>
-      <c r="I17" s="313" t="inlineStr">
-        <is>
-          <t>0.3633±0.0349 (3)</t>
-        </is>
-      </c>
-      <c r="J17" s="315" t="inlineStr">
-        <is>
-          <t>0.1690±0.0018 (2)</t>
-        </is>
-      </c>
-      <c r="K17" s="313" t="inlineStr">
-        <is>
-          <t>0.4483±0.0031 (3)</t>
+      <c r="I17" s="315" t="inlineStr">
+        <is>
+          <t>0.3299±0.0000 (1)</t>
+        </is>
+      </c>
+      <c r="J17" s="313" t="n"/>
+      <c r="K17" s="315" t="inlineStr">
+        <is>
+          <t>0.4344±0.0000 (1)</t>
         </is>
       </c>
       <c r="L17" s="313" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="312" t="inlineStr"/>
+      <c r="A18" s="311" t="inlineStr">
+        <is>
+          <t>预训练</t>
+        </is>
+      </c>
       <c r="B18" s="312" t="inlineStr">
         <is>
-          <t>预训练池剔除 TUSZ/CHB-MIT</t>
-        </is>
-      </c>
-      <c r="C18" s="313" t="n"/>
-      <c r="D18" s="313" t="n"/>
-      <c r="E18" s="315" t="inlineStr">
-        <is>
-          <t>0.6221±0.0000 (1)</t>
-        </is>
-      </c>
-      <c r="F18" s="315" t="inlineStr">
-        <is>
-          <t>0.6410±0.0000 (1)</t>
-        </is>
-      </c>
-      <c r="G18" s="313" t="n"/>
-      <c r="H18" s="313" t="n"/>
-      <c r="I18" s="313" t="n"/>
-      <c r="J18" s="313" t="n"/>
-      <c r="K18" s="313" t="n"/>
+          <t>预训练 base(60k)</t>
+        </is>
+      </c>
+      <c r="C18" s="313" t="inlineStr">
+        <is>
+          <t>0.8841±0.0043 (3)</t>
+        </is>
+      </c>
+      <c r="D18" s="313" t="inlineStr">
+        <is>
+          <t>0.6730±0.0116 (3)</t>
+        </is>
+      </c>
+      <c r="E18" s="313" t="inlineStr">
+        <is>
+          <t>0.6398±0.0615 (3)</t>
+        </is>
+      </c>
+      <c r="F18" s="313" t="inlineStr">
+        <is>
+          <t>0.6830±0.0228 (3)</t>
+        </is>
+      </c>
+      <c r="G18" s="313" t="inlineStr">
+        <is>
+          <t>0.6651±0.0109 (3)</t>
+        </is>
+      </c>
+      <c r="H18" s="313" t="inlineStr">
+        <is>
+          <t>0.6934±0.0032 (3)</t>
+        </is>
+      </c>
+      <c r="I18" s="313" t="inlineStr">
+        <is>
+          <t>0.3059±0.0262 (3)</t>
+        </is>
+      </c>
+      <c r="J18" s="313" t="inlineStr">
+        <is>
+          <t>0.1540±0.0202 (3)</t>
+        </is>
+      </c>
+      <c r="K18" s="313" t="inlineStr">
+        <is>
+          <t>0.3652±0.0083 (3)</t>
+        </is>
+      </c>
       <c r="L18" s="313" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="312" t="inlineStr"/>
       <c r="B19" s="312" t="inlineStr">
         <is>
-          <t>预训练 base,微调 patch_len=200</t>
-        </is>
-      </c>
-      <c r="C19" s="313" t="n"/>
+          <t>预训练 large(60k)</t>
+        </is>
+      </c>
+      <c r="C19" s="313" t="inlineStr">
+        <is>
+          <t>0.8869±0.0069 (3)</t>
+        </is>
+      </c>
       <c r="D19" s="313" t="inlineStr">
         <is>
-          <t>0.6793±0.0109 (3)</t>
-        </is>
-      </c>
-      <c r="E19" s="313" t="n"/>
-      <c r="F19" s="313" t="n"/>
-      <c r="G19" s="313" t="n"/>
-      <c r="H19" s="313" t="n"/>
-      <c r="I19" s="313" t="n"/>
-      <c r="J19" s="313" t="n"/>
-      <c r="K19" s="313" t="n"/>
+          <t>0.6523±0.0302 (3)</t>
+        </is>
+      </c>
+      <c r="E19" s="313" t="inlineStr">
+        <is>
+          <t>0.6289±0.0297 (3)</t>
+        </is>
+      </c>
+      <c r="F19" s="313" t="inlineStr">
+        <is>
+          <t>0.6162±0.0467 (3)</t>
+        </is>
+      </c>
+      <c r="G19" s="313" t="inlineStr">
+        <is>
+          <t>0.6641±0.0044 (3)</t>
+        </is>
+      </c>
+      <c r="H19" s="313" t="inlineStr">
+        <is>
+          <t>0.6996±0.0153 (3)</t>
+        </is>
+      </c>
+      <c r="I19" s="313" t="inlineStr">
+        <is>
+          <t>0.3140±0.0094 (3)</t>
+        </is>
+      </c>
+      <c r="J19" s="313" t="inlineStr">
+        <is>
+          <t>0.1640±0.0155 (3)</t>
+        </is>
+      </c>
+      <c r="K19" s="313" t="inlineStr">
+        <is>
+          <t>0.4122±0.0166 (3)</t>
+        </is>
+      </c>
       <c r="L19" s="313" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="312" t="inlineStr"/>
       <c r="B20" s="312" t="inlineStr">
         <is>
-          <t>早期微调配方(6k checkpoint)</t>
+          <t>raw tokenizer 预训练 large(60k)</t>
         </is>
       </c>
       <c r="C20" s="313" t="n"/>
       <c r="D20" s="313" t="n"/>
-      <c r="E20" s="313" t="n"/>
-      <c r="F20" s="313" t="n"/>
+      <c r="E20" s="315" t="inlineStr">
+        <is>
+          <t>0.5460±0.0000 (1)</t>
+        </is>
+      </c>
+      <c r="F20" s="315" t="inlineStr">
+        <is>
+          <t>0.6279±0.0000 (1)</t>
+        </is>
+      </c>
       <c r="G20" s="313" t="n"/>
       <c r="H20" s="313" t="n"/>
-      <c r="I20" s="315" t="inlineStr">
-        <is>
-          <t>0.2690±0.0000 (1)</t>
+      <c r="I20" s="313" t="inlineStr">
+        <is>
+          <t>0.3633±0.0349 (3)</t>
         </is>
       </c>
       <c r="J20" s="315" t="inlineStr">
         <is>
-          <t>0.1279±0.0000 (1)</t>
-        </is>
-      </c>
-      <c r="K20" s="313" t="n"/>
+          <t>0.1690±0.0018 (2)</t>
+        </is>
+      </c>
+      <c r="K20" s="313" t="inlineStr">
+        <is>
+          <t>0.4483±0.0031 (3)</t>
+        </is>
+      </c>
       <c r="L20" s="313" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="312" t="inlineStr"/>
       <c r="B21" s="312" t="inlineStr">
         <is>
-          <t>早期微调配方 v2(6k checkpoint)</t>
+          <t>预训练池剔除 TUSZ/CHB-MIT</t>
         </is>
       </c>
       <c r="C21" s="313" t="n"/>
       <c r="D21" s="313" t="n"/>
-      <c r="E21" s="313" t="n"/>
-      <c r="F21" s="313" t="n"/>
+      <c r="E21" s="315" t="inlineStr">
+        <is>
+          <t>0.6221±0.0000 (1)</t>
+        </is>
+      </c>
+      <c r="F21" s="315" t="inlineStr">
+        <is>
+          <t>0.6410±0.0000 (1)</t>
+        </is>
+      </c>
       <c r="G21" s="313" t="n"/>
       <c r="H21" s="313" t="n"/>
-      <c r="I21" s="315" t="inlineStr">
-        <is>
-          <t>0.2622±0.0000 (1)</t>
-        </is>
-      </c>
-      <c r="J21" s="315" t="inlineStr">
-        <is>
-          <t>0.1408±0.0000 (1)</t>
-        </is>
-      </c>
+      <c r="I21" s="313" t="n"/>
+      <c r="J21" s="313" t="n"/>
       <c r="K21" s="313" t="n"/>
       <c r="L21" s="313" t="n"/>
     </row>
@@ -11641,37 +11729,29 @@
       <c r="A22" s="312" t="inlineStr"/>
       <c r="B22" s="312" t="inlineStr">
         <is>
-          <t>早期微调配方 large(6k checkpoint)</t>
+          <t>预训练 base,微调 patch_len=200</t>
         </is>
       </c>
       <c r="C22" s="313" t="n"/>
-      <c r="D22" s="313" t="n"/>
+      <c r="D22" s="313" t="inlineStr">
+        <is>
+          <t>0.6793±0.0109 (3)</t>
+        </is>
+      </c>
       <c r="E22" s="313" t="n"/>
       <c r="F22" s="313" t="n"/>
       <c r="G22" s="313" t="n"/>
       <c r="H22" s="313" t="n"/>
-      <c r="I22" s="315" t="inlineStr">
-        <is>
-          <t>0.2716±0.0000 (1)</t>
-        </is>
-      </c>
-      <c r="J22" s="315" t="inlineStr">
-        <is>
-          <t>0.1381±0.0000 (1)</t>
-        </is>
-      </c>
+      <c r="I22" s="313" t="n"/>
+      <c r="J22" s="313" t="n"/>
       <c r="K22" s="313" t="n"/>
       <c r="L22" s="313" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="311" t="inlineStr">
-        <is>
-          <t>容量阶梯</t>
-        </is>
-      </c>
+      <c r="A23" s="312" t="inlineStr"/>
       <c r="B23" s="312" t="inlineStr">
         <is>
-          <t>raw,d_model 32</t>
+          <t>早期微调配方(6k checkpoint)</t>
         </is>
       </c>
       <c r="C23" s="313" t="n"/>
@@ -11680,24 +11760,24 @@
       <c r="F23" s="313" t="n"/>
       <c r="G23" s="313" t="n"/>
       <c r="H23" s="313" t="n"/>
-      <c r="I23" s="313" t="inlineStr">
-        <is>
-          <t>0.2613±0.0100 (3)</t>
-        </is>
-      </c>
-      <c r="J23" s="313" t="n"/>
-      <c r="K23" s="313" t="inlineStr">
-        <is>
-          <t>0.2617±0.0019 (3)</t>
-        </is>
-      </c>
+      <c r="I23" s="315" t="inlineStr">
+        <is>
+          <t>0.2690±0.0000 (1)</t>
+        </is>
+      </c>
+      <c r="J23" s="315" t="inlineStr">
+        <is>
+          <t>0.1279±0.0000 (1)</t>
+        </is>
+      </c>
+      <c r="K23" s="313" t="n"/>
       <c r="L23" s="313" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="312" t="inlineStr"/>
       <c r="B24" s="312" t="inlineStr">
         <is>
-          <t>raw,d_model 64</t>
+          <t>早期微调配方 v2(6k checkpoint)</t>
         </is>
       </c>
       <c r="C24" s="313" t="n"/>
@@ -11706,24 +11786,24 @@
       <c r="F24" s="313" t="n"/>
       <c r="G24" s="313" t="n"/>
       <c r="H24" s="313" t="n"/>
-      <c r="I24" s="313" t="inlineStr">
-        <is>
-          <t>0.3129±0.0121 (3)</t>
-        </is>
-      </c>
-      <c r="J24" s="313" t="n"/>
-      <c r="K24" s="313" t="inlineStr">
-        <is>
-          <t>0.2780±0.0100 (3)</t>
-        </is>
-      </c>
+      <c r="I24" s="315" t="inlineStr">
+        <is>
+          <t>0.2622±0.0000 (1)</t>
+        </is>
+      </c>
+      <c r="J24" s="315" t="inlineStr">
+        <is>
+          <t>0.1408±0.0000 (1)</t>
+        </is>
+      </c>
+      <c r="K24" s="313" t="n"/>
       <c r="L24" s="313" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="312" t="inlineStr"/>
       <c r="B25" s="312" t="inlineStr">
         <is>
-          <t>raw,d_model 256</t>
+          <t>早期微调配方 large(6k checkpoint)</t>
         </is>
       </c>
       <c r="C25" s="313" t="n"/>
@@ -11732,24 +11812,28 @@
       <c r="F25" s="313" t="n"/>
       <c r="G25" s="313" t="n"/>
       <c r="H25" s="313" t="n"/>
-      <c r="I25" s="313" t="inlineStr">
-        <is>
-          <t>0.4159±0.0529 (3)</t>
-        </is>
-      </c>
-      <c r="J25" s="313" t="n"/>
-      <c r="K25" s="313" t="inlineStr">
-        <is>
-          <t>0.4437±0.0192 (3)</t>
-        </is>
-      </c>
+      <c r="I25" s="315" t="inlineStr">
+        <is>
+          <t>0.2716±0.0000 (1)</t>
+        </is>
+      </c>
+      <c r="J25" s="315" t="inlineStr">
+        <is>
+          <t>0.1381±0.0000 (1)</t>
+        </is>
+      </c>
+      <c r="K25" s="313" t="n"/>
       <c r="L25" s="313" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="312" t="inlineStr"/>
+      <c r="A26" s="311" t="inlineStr">
+        <is>
+          <t>容量阶梯</t>
+        </is>
+      </c>
       <c r="B26" s="312" t="inlineStr">
         <is>
-          <t>raw,加宽</t>
+          <t>raw,d_model 32</t>
         </is>
       </c>
       <c r="C26" s="313" t="n"/>
@@ -11760,13 +11844,13 @@
       <c r="H26" s="313" t="n"/>
       <c r="I26" s="313" t="inlineStr">
         <is>
-          <t>0.4093±0.0425 (3)</t>
+          <t>0.2613±0.0100 (3)</t>
         </is>
       </c>
       <c r="J26" s="313" t="n"/>
-      <c r="K26" s="315" t="inlineStr">
-        <is>
-          <t>0.4261±0.0085 (2)</t>
+      <c r="K26" s="313" t="inlineStr">
+        <is>
+          <t>0.2617±0.0019 (3)</t>
         </is>
       </c>
       <c r="L26" s="313" t="n"/>
@@ -11775,7 +11859,7 @@
       <c r="A27" s="312" t="inlineStr"/>
       <c r="B27" s="312" t="inlineStr">
         <is>
-          <t>raw,16 频带</t>
+          <t>raw,d_model 64</t>
         </is>
       </c>
       <c r="C27" s="313" t="n"/>
@@ -11786,13 +11870,13 @@
       <c r="H27" s="313" t="n"/>
       <c r="I27" s="313" t="inlineStr">
         <is>
-          <t>0.3781±0.0467 (3)</t>
+          <t>0.3129±0.0121 (3)</t>
         </is>
       </c>
       <c r="J27" s="313" t="n"/>
       <c r="K27" s="313" t="inlineStr">
         <is>
-          <t>0.4288±0.0090 (3)</t>
+          <t>0.2780±0.0100 (3)</t>
         </is>
       </c>
       <c r="L27" s="313" t="n"/>
@@ -11801,7 +11885,7 @@
       <c r="A28" s="312" t="inlineStr"/>
       <c r="B28" s="312" t="inlineStr">
         <is>
-          <t>raw,patch_len 100</t>
+          <t>raw,d_model 256</t>
         </is>
       </c>
       <c r="C28" s="313" t="n"/>
@@ -11812,13 +11896,13 @@
       <c r="H28" s="313" t="n"/>
       <c r="I28" s="313" t="inlineStr">
         <is>
-          <t>0.3508±0.0251 (3)</t>
+          <t>0.4159±0.0529 (3)</t>
         </is>
       </c>
       <c r="J28" s="313" t="n"/>
       <c r="K28" s="313" t="inlineStr">
         <is>
-          <t>0.4066±0.0221 (3)</t>
+          <t>0.4437±0.0192 (3)</t>
         </is>
       </c>
       <c r="L28" s="313" t="n"/>
@@ -11827,7 +11911,7 @@
       <c r="A29" s="312" t="inlineStr"/>
       <c r="B29" s="312" t="inlineStr">
         <is>
-          <t>raw,dropout 0.5</t>
+          <t>raw,加宽</t>
         </is>
       </c>
       <c r="C29" s="313" t="n"/>
@@ -11838,13 +11922,13 @@
       <c r="H29" s="313" t="n"/>
       <c r="I29" s="313" t="inlineStr">
         <is>
-          <t>0.3409±0.0196 (3)</t>
+          <t>0.4093±0.0425 (3)</t>
         </is>
       </c>
       <c r="J29" s="313" t="n"/>
-      <c r="K29" s="313" t="inlineStr">
-        <is>
-          <t>0.4308±0.0139 (3)</t>
+      <c r="K29" s="315" t="inlineStr">
+        <is>
+          <t>0.4261±0.0085 (2)</t>
         </is>
       </c>
       <c r="L29" s="313" t="n"/>
@@ -11853,7 +11937,7 @@
       <c r="A30" s="312" t="inlineStr"/>
       <c r="B30" s="312" t="inlineStr">
         <is>
-          <t>raw,attn 头</t>
+          <t>raw,16 频带</t>
         </is>
       </c>
       <c r="C30" s="313" t="n"/>
@@ -11864,26 +11948,22 @@
       <c r="H30" s="313" t="n"/>
       <c r="I30" s="313" t="inlineStr">
         <is>
-          <t>0.3524±0.0467 (3)</t>
+          <t>0.3781±0.0467 (3)</t>
         </is>
       </c>
       <c r="J30" s="313" t="n"/>
       <c r="K30" s="313" t="inlineStr">
         <is>
-          <t>0.4545±0.0054 (3)</t>
+          <t>0.4288±0.0090 (3)</t>
         </is>
       </c>
       <c r="L30" s="313" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="311" t="inlineStr">
-        <is>
-          <t>已否决</t>
-        </is>
-      </c>
+      <c r="A31" s="312" t="inlineStr"/>
       <c r="B31" s="312" t="inlineStr">
         <is>
-          <t>spatial_pe: xyz(蒙太奇坐标)</t>
+          <t>raw,patch_len 100</t>
         </is>
       </c>
       <c r="C31" s="313" t="n"/>
@@ -11891,20 +11971,16 @@
       <c r="E31" s="313" t="n"/>
       <c r="F31" s="313" t="n"/>
       <c r="G31" s="313" t="n"/>
-      <c r="H31" s="313" t="inlineStr">
-        <is>
-          <t>0.6954±0.0167 (3)</t>
-        </is>
-      </c>
+      <c r="H31" s="313" t="n"/>
       <c r="I31" s="313" t="inlineStr">
         <is>
-          <t>0.2478±0.0053 (3)</t>
+          <t>0.3508±0.0251 (3)</t>
         </is>
       </c>
       <c r="J31" s="313" t="n"/>
       <c r="K31" s="313" t="inlineStr">
         <is>
-          <t>0.3338±0.0027 (3)</t>
+          <t>0.4066±0.0221 (3)</t>
         </is>
       </c>
       <c r="L31" s="313" t="n"/>
@@ -11913,7 +11989,7 @@
       <c r="A32" s="312" t="inlineStr"/>
       <c r="B32" s="312" t="inlineStr">
         <is>
-          <t>每窗口归一化</t>
+          <t>raw,dropout 0.5</t>
         </is>
       </c>
       <c r="C32" s="313" t="n"/>
@@ -11924,13 +12000,13 @@
       <c r="H32" s="313" t="n"/>
       <c r="I32" s="313" t="inlineStr">
         <is>
-          <t>0.2532±0.0155 (3)</t>
+          <t>0.3409±0.0196 (3)</t>
         </is>
       </c>
       <c r="J32" s="313" t="n"/>
       <c r="K32" s="313" t="inlineStr">
         <is>
-          <t>0.3050±0.0438 (3)</t>
+          <t>0.4308±0.0139 (3)</t>
         </is>
       </c>
       <c r="L32" s="313" t="n"/>
@@ -11939,7 +12015,7 @@
       <c r="A33" s="312" t="inlineStr"/>
       <c r="B33" s="312" t="inlineStr">
         <is>
-          <t>每窗口归一化 + raw</t>
+          <t>raw,attn 头</t>
         </is>
       </c>
       <c r="C33" s="313" t="n"/>
@@ -11948,24 +12024,28 @@
       <c r="F33" s="313" t="n"/>
       <c r="G33" s="313" t="n"/>
       <c r="H33" s="313" t="n"/>
-      <c r="I33" s="315" t="inlineStr">
-        <is>
-          <t>0.2896±0.0146 (2)</t>
+      <c r="I33" s="313" t="inlineStr">
+        <is>
+          <t>0.3524±0.0467 (3)</t>
         </is>
       </c>
       <c r="J33" s="313" t="n"/>
-      <c r="K33" s="315" t="inlineStr">
-        <is>
-          <t>0.2992±0.0139 (2)</t>
+      <c r="K33" s="313" t="inlineStr">
+        <is>
+          <t>0.4545±0.0054 (3)</t>
         </is>
       </c>
       <c r="L33" s="313" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="312" t="inlineStr"/>
+      <c r="A34" s="311" t="inlineStr">
+        <is>
+          <t>已否决</t>
+        </is>
+      </c>
       <c r="B34" s="312" t="inlineStr">
         <is>
-          <t>每受试者归一化</t>
+          <t>spatial_pe: xyz(蒙太奇坐标)</t>
         </is>
       </c>
       <c r="C34" s="313" t="n"/>
@@ -11973,21 +12053,29 @@
       <c r="E34" s="313" t="n"/>
       <c r="F34" s="313" t="n"/>
       <c r="G34" s="313" t="n"/>
-      <c r="H34" s="313" t="n"/>
-      <c r="I34" s="313" t="n"/>
-      <c r="J34" s="315" t="inlineStr">
-        <is>
-          <t>0.1328±0.0007 (2)</t>
-        </is>
-      </c>
-      <c r="K34" s="313" t="n"/>
+      <c r="H34" s="313" t="inlineStr">
+        <is>
+          <t>0.6954±0.0167 (3)</t>
+        </is>
+      </c>
+      <c r="I34" s="313" t="inlineStr">
+        <is>
+          <t>0.2478±0.0053 (3)</t>
+        </is>
+      </c>
+      <c r="J34" s="313" t="n"/>
+      <c r="K34" s="313" t="inlineStr">
+        <is>
+          <t>0.3338±0.0027 (3)</t>
+        </is>
+      </c>
       <c r="L34" s="313" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="312" t="inlineStr"/>
       <c r="B35" s="312" t="inlineStr">
         <is>
-          <t>每受试者归一化 + raw</t>
+          <t>每窗口归一化</t>
         </is>
       </c>
       <c r="C35" s="313" t="n"/>
@@ -11996,20 +12084,24 @@
       <c r="F35" s="313" t="n"/>
       <c r="G35" s="313" t="n"/>
       <c r="H35" s="313" t="n"/>
-      <c r="I35" s="313" t="n"/>
-      <c r="J35" s="313" t="inlineStr">
-        <is>
-          <t>0.1579±0.0034 (3)</t>
-        </is>
-      </c>
-      <c r="K35" s="313" t="n"/>
+      <c r="I35" s="313" t="inlineStr">
+        <is>
+          <t>0.2532±0.0155 (3)</t>
+        </is>
+      </c>
+      <c r="J35" s="313" t="n"/>
+      <c r="K35" s="313" t="inlineStr">
+        <is>
+          <t>0.3050±0.0438 (3)</t>
+        </is>
+      </c>
       <c r="L35" s="313" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="312" t="inlineStr"/>
       <c r="B36" s="312" t="inlineStr">
         <is>
-          <t>每受试者归一化 + raw + attn 头</t>
+          <t>每窗口归一化 + raw</t>
         </is>
       </c>
       <c r="C36" s="313" t="n"/>
@@ -12018,20 +12110,24 @@
       <c r="F36" s="313" t="n"/>
       <c r="G36" s="313" t="n"/>
       <c r="H36" s="313" t="n"/>
-      <c r="I36" s="313" t="n"/>
-      <c r="J36" s="313" t="inlineStr">
-        <is>
-          <t>0.1513±0.0012 (3)</t>
-        </is>
-      </c>
-      <c r="K36" s="313" t="n"/>
+      <c r="I36" s="315" t="inlineStr">
+        <is>
+          <t>0.2896±0.0146 (2)</t>
+        </is>
+      </c>
+      <c r="J36" s="313" t="n"/>
+      <c r="K36" s="315" t="inlineStr">
+        <is>
+          <t>0.2992±0.0139 (2)</t>
+        </is>
+      </c>
       <c r="L36" s="313" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="312" t="inlineStr"/>
       <c r="B37" s="312" t="inlineStr">
         <is>
-          <t>FACED 伪迹清洗</t>
+          <t>每受试者归一化</t>
         </is>
       </c>
       <c r="C37" s="313" t="n"/>
@@ -12041,9 +12137,9 @@
       <c r="G37" s="313" t="n"/>
       <c r="H37" s="313" t="n"/>
       <c r="I37" s="313" t="n"/>
-      <c r="J37" s="313" t="inlineStr">
-        <is>
-          <t>0.1346±0.0157 (3)</t>
+      <c r="J37" s="315" t="inlineStr">
+        <is>
+          <t>0.1328±0.0007 (2)</t>
         </is>
       </c>
       <c r="K37" s="313" t="n"/>
@@ -12053,7 +12149,7 @@
       <c r="A38" s="312" t="inlineStr"/>
       <c r="B38" s="312" t="inlineStr">
         <is>
-          <t>lr 1e-3</t>
+          <t>每受试者归一化 + raw</t>
         </is>
       </c>
       <c r="C38" s="313" t="n"/>
@@ -12062,24 +12158,20 @@
       <c r="F38" s="313" t="n"/>
       <c r="G38" s="313" t="n"/>
       <c r="H38" s="313" t="n"/>
-      <c r="I38" s="313" t="inlineStr">
-        <is>
-          <t>0.2498±0.0077 (3)</t>
-        </is>
-      </c>
-      <c r="J38" s="313" t="n"/>
-      <c r="K38" s="313" t="inlineStr">
-        <is>
-          <t>0.3094±0.0345 (3)</t>
-        </is>
-      </c>
+      <c r="I38" s="313" t="n"/>
+      <c r="J38" s="313" t="inlineStr">
+        <is>
+          <t>0.1579±0.0034 (3)</t>
+        </is>
+      </c>
+      <c r="K38" s="313" t="n"/>
       <c r="L38" s="313" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="312" t="inlineStr"/>
       <c r="B39" s="312" t="inlineStr">
         <is>
-          <t>lr 3e-4</t>
+          <t>每受试者归一化 + raw + attn 头</t>
         </is>
       </c>
       <c r="C39" s="313" t="n"/>
@@ -12088,42 +12180,34 @@
       <c r="F39" s="313" t="n"/>
       <c r="G39" s="313" t="n"/>
       <c r="H39" s="313" t="n"/>
-      <c r="I39" s="313" t="inlineStr">
-        <is>
-          <t>0.2623±0.0042 (3)</t>
-        </is>
-      </c>
-      <c r="J39" s="313" t="n"/>
-      <c r="K39" s="313" t="inlineStr">
-        <is>
-          <t>0.3495±0.0039 (3)</t>
-        </is>
-      </c>
+      <c r="I39" s="313" t="n"/>
+      <c r="J39" s="313" t="inlineStr">
+        <is>
+          <t>0.1513±0.0012 (3)</t>
+        </is>
+      </c>
+      <c r="K39" s="313" t="n"/>
       <c r="L39" s="313" t="n"/>
     </row>
     <row r="40">
-      <c r="A40" s="311" t="inlineStr">
-        <is>
-          <t>早期 pilot</t>
-        </is>
-      </c>
+      <c r="A40" s="312" t="inlineStr"/>
       <c r="B40" s="312" t="inlineStr">
         <is>
-          <t>冻结前端 pilot</t>
+          <t>FACED 伪迹清洗</t>
         </is>
       </c>
       <c r="C40" s="313" t="n"/>
-      <c r="D40" s="313" t="inlineStr">
-        <is>
-          <t>0.6272±0.0099 (3)</t>
-        </is>
-      </c>
+      <c r="D40" s="313" t="n"/>
       <c r="E40" s="313" t="n"/>
       <c r="F40" s="313" t="n"/>
       <c r="G40" s="313" t="n"/>
       <c r="H40" s="313" t="n"/>
       <c r="I40" s="313" t="n"/>
-      <c r="J40" s="313" t="n"/>
+      <c r="J40" s="313" t="inlineStr">
+        <is>
+          <t>0.1346±0.0157 (3)</t>
+        </is>
+      </c>
       <c r="K40" s="313" t="n"/>
       <c r="L40" s="313" t="n"/>
     </row>
@@ -12131,112 +12215,190 @@
       <c r="A41" s="312" t="inlineStr"/>
       <c r="B41" s="312" t="inlineStr">
         <is>
-          <t>未滤波 pilot</t>
+          <t>lr 1e-3</t>
         </is>
       </c>
       <c r="C41" s="313" t="n"/>
-      <c r="D41" s="313" t="inlineStr">
-        <is>
-          <t>0.6209±0.0503 (3)</t>
-        </is>
-      </c>
+      <c r="D41" s="313" t="n"/>
       <c r="E41" s="313" t="n"/>
       <c r="F41" s="313" t="n"/>
       <c r="G41" s="313" t="n"/>
       <c r="H41" s="313" t="n"/>
-      <c r="I41" s="313" t="n"/>
+      <c r="I41" s="313" t="inlineStr">
+        <is>
+          <t>0.2498±0.0077 (3)</t>
+        </is>
+      </c>
       <c r="J41" s="313" t="n"/>
-      <c r="K41" s="313" t="n"/>
+      <c r="K41" s="313" t="inlineStr">
+        <is>
+          <t>0.3094±0.0345 (3)</t>
+        </is>
+      </c>
       <c r="L41" s="313" t="n"/>
     </row>
+    <row r="42">
+      <c r="A42" s="312" t="inlineStr"/>
+      <c r="B42" s="312" t="inlineStr">
+        <is>
+          <t>lr 3e-4</t>
+        </is>
+      </c>
+      <c r="C42" s="313" t="n"/>
+      <c r="D42" s="313" t="n"/>
+      <c r="E42" s="313" t="n"/>
+      <c r="F42" s="313" t="n"/>
+      <c r="G42" s="313" t="n"/>
+      <c r="H42" s="313" t="n"/>
+      <c r="I42" s="313" t="inlineStr">
+        <is>
+          <t>0.2623±0.0042 (3)</t>
+        </is>
+      </c>
+      <c r="J42" s="313" t="n"/>
+      <c r="K42" s="313" t="inlineStr">
+        <is>
+          <t>0.3495±0.0039 (3)</t>
+        </is>
+      </c>
+      <c r="L42" s="313" t="n"/>
+    </row>
     <row r="43">
-      <c r="A43" s="316" t="inlineStr">
+      <c r="A43" s="311" t="inlineStr">
+        <is>
+          <t>早期 pilot</t>
+        </is>
+      </c>
+      <c r="B43" s="312" t="inlineStr">
+        <is>
+          <t>冻结前端 pilot</t>
+        </is>
+      </c>
+      <c r="C43" s="313" t="n"/>
+      <c r="D43" s="313" t="inlineStr">
+        <is>
+          <t>0.6272±0.0099 (3)</t>
+        </is>
+      </c>
+      <c r="E43" s="313" t="n"/>
+      <c r="F43" s="313" t="n"/>
+      <c r="G43" s="313" t="n"/>
+      <c r="H43" s="313" t="n"/>
+      <c r="I43" s="313" t="n"/>
+      <c r="J43" s="313" t="n"/>
+      <c r="K43" s="313" t="n"/>
+      <c r="L43" s="313" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="312" t="inlineStr"/>
+      <c r="B44" s="312" t="inlineStr">
+        <is>
+          <t>未滤波 pilot</t>
+        </is>
+      </c>
+      <c r="C44" s="313" t="n"/>
+      <c r="D44" s="313" t="inlineStr">
+        <is>
+          <t>0.6209±0.0503 (3)</t>
+        </is>
+      </c>
+      <c r="E44" s="313" t="n"/>
+      <c r="F44" s="313" t="n"/>
+      <c r="G44" s="313" t="n"/>
+      <c r="H44" s="313" t="n"/>
+      <c r="I44" s="313" t="n"/>
+      <c r="J44" s="313" t="n"/>
+      <c r="K44" s="313" t="n"/>
+      <c r="L44" s="313" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="316" t="inlineStr">
         <is>
           <t>样本量消融</t>
         </is>
       </c>
-      <c r="B43" s="317" t="inlineStr">
+      <c r="B46" s="317" t="inlineStr">
         <is>
           <t>TUEV 训练集降采样(kappa) —— 检验等级三是否只是样本量问题</t>
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="B44" s="309" t="inlineStr">
+    <row r="47">
+      <c r="B47" s="309" t="inlineStr">
         <is>
           <t>模型</t>
         </is>
       </c>
-      <c r="C44" s="310" t="inlineStr">
+      <c r="C47" s="310" t="inlineStr">
         <is>
           <t>n=2160</t>
         </is>
       </c>
-      <c r="D44" s="310" t="inlineStr">
+      <c r="D47" s="310" t="inlineStr">
         <is>
           <t>n=6720</t>
         </is>
       </c>
-      <c r="E44" s="310" t="inlineStr">
+      <c r="E47" s="310" t="inlineStr">
         <is>
           <t>n=20000</t>
         </is>
       </c>
-      <c r="F44" s="310" t="inlineStr">
+      <c r="F47" s="310" t="inlineStr">
         <is>
           <t>全量 68445</t>
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="B45" s="312" t="inlineStr">
+    <row r="48">
+      <c r="B48" s="312" t="inlineStr">
         <is>
           <t>PACLock v2</t>
         </is>
       </c>
-      <c r="C45" s="315" t="inlineStr">
+      <c r="C48" s="315" t="inlineStr">
         <is>
           <t>0.6523±0.0000 (1)</t>
         </is>
       </c>
-      <c r="D45" s="315" t="inlineStr">
+      <c r="D48" s="315" t="inlineStr">
         <is>
           <t>0.7098±0.0000 (1)</t>
         </is>
       </c>
-      <c r="E45" s="315" t="inlineStr">
+      <c r="E48" s="315" t="inlineStr">
         <is>
           <t>0.6767±0.0000 (1)</t>
         </is>
       </c>
-      <c r="F45" s="313" t="inlineStr">
+      <c r="F48" s="313" t="inlineStr">
         <is>
           <t>0.7076±0.0311 (3)</t>
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="B46" s="312" t="inlineStr">
+    <row r="49">
+      <c r="B49" s="312" t="inlineStr">
         <is>
           <t>SPaRCNet</t>
         </is>
       </c>
-      <c r="C46" s="315" t="inlineStr">
+      <c r="C49" s="315" t="inlineStr">
         <is>
           <t>0.4917±0.0000 (1)</t>
         </is>
       </c>
-      <c r="D46" s="315" t="inlineStr">
+      <c r="D49" s="315" t="inlineStr">
         <is>
           <t>0.5532±0.0000 (1)</t>
         </is>
       </c>
-      <c r="E46" s="315" t="inlineStr">
+      <c r="E49" s="315" t="inlineStr">
         <is>
           <t>0.3642±0.0000 (1)</t>
         </is>
       </c>
-      <c r="F46" s="313" t="inlineStr">
+      <c r="F49" s="313" t="inlineStr">
         <is>
           <t>0.4885±0.0279 (3)</t>
         </is>
@@ -12256,7 +12418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I22"/>
+  <dimension ref="A1:I23"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.66667" defaultRowHeight="15" customHeight="1" outlineLevelRow="0"/>
   <cols>
     <col width="24" customWidth="1" style="219" min="1" max="4"/>
@@ -12995,15 +13157,41 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="15" customHeight="1" s="220"/>
-    <row r="22" ht="13.75" customHeight="1" s="220">
-      <c r="A22" s="300" t="inlineStr">
+    <row r="21" ht="15" customHeight="1" s="220">
+      <c r="A21" s="297" t="n"/>
+      <c r="B21" s="318" t="inlineStr">
+        <is>
+          <t>PACLock (hybrid)</t>
+        </is>
+      </c>
+      <c r="C21" s="319" t="n"/>
+      <c r="D21" s="319" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E21" s="319" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F21" s="319" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G21" s="319" t="n"/>
+      <c r="H21" s="299" t="n"/>
+      <c r="I21" s="299" t="n"/>
+    </row>
+    <row r="22" ht="13.75" customHeight="1" s="220"/>
+    <row r="23" ht="15" customHeight="1" s="220">
+      <c r="A23" s="300" t="inlineStr">
         <is>
           <t>灰色行 = 该 baseline 的原论文未评测本数据集,不存在官方超参;所用配方由我们从该模型覆盖过的数据集迁移而来。这些数字反映的是「该架构在我们所选配方下的表现」,不是「该 baseline 已发表的能力」。</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="15" customHeight="1" s="220"/>
     <row r="24" ht="15" customHeight="1" s="220"/>
     <row r="25" ht="15" customHeight="1" s="220"/>
     <row r="26" ht="15" customHeight="1" s="220"/>
@@ -13061,7 +13249,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I22"/>
+  <dimension ref="A1:I23"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.66667" defaultRowHeight="15" customHeight="1" outlineLevelRow="0"/>
   <cols>
     <col width="24" customWidth="1" style="219" min="1" max="4"/>
@@ -13824,15 +14012,55 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="15" customHeight="1" s="220"/>
-    <row r="22" ht="13.75" customHeight="1" s="220">
-      <c r="A22" s="300" t="inlineStr">
+    <row r="21" ht="15" customHeight="1" s="220">
+      <c r="A21" s="297" t="n"/>
+      <c r="B21" s="318" t="inlineStr">
+        <is>
+          <t>PACLock (hybrid)</t>
+        </is>
+      </c>
+      <c r="C21" s="319" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="D21" s="320" t="inlineStr">
+        <is>
+          <t>0.6410 (1 seed)</t>
+        </is>
+      </c>
+      <c r="E21" s="320" t="inlineStr">
+        <is>
+          <t>0.6951 (1 seed)</t>
+        </is>
+      </c>
+      <c r="F21" s="320" t="inlineStr">
+        <is>
+          <t>0.8365 (1 seed)</t>
+        </is>
+      </c>
+      <c r="G21" s="320" t="inlineStr">
+        <is>
+          <t>-0.0125</t>
+        </is>
+      </c>
+      <c r="H21" s="321" t="inlineStr">
+        <is>
+          <t>+0.0221</t>
+        </is>
+      </c>
+      <c r="I21" s="321" t="inlineStr">
+        <is>
+          <t>+0.0428</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="13.75" customHeight="1" s="220"/>
+    <row r="23" ht="15" customHeight="1" s="220">
+      <c r="A23" s="300" t="inlineStr">
         <is>
           <t>灰色行 = 该 baseline 的原论文未评测本数据集,不存在官方超参;所用配方由我们从该模型覆盖过的数据集迁移而来。这些数字反映的是「该架构在我们所选配方下的表现」,不是「该 baseline 已发表的能力」。</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="15" customHeight="1" s="220"/>
     <row r="24" ht="15" customHeight="1" s="220"/>
     <row r="25" ht="15" customHeight="1" s="220"/>
     <row r="26" ht="15" customHeight="1" s="220"/>
@@ -13891,7 +14119,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I22"/>
+  <dimension ref="A1:I23"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.66667" defaultRowHeight="15" customHeight="1" outlineLevelRow="0"/>
   <cols>
     <col width="24" customWidth="1" style="219" min="1" max="4"/>
@@ -14654,15 +14882,55 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="15" customHeight="1" s="220"/>
-    <row r="22" ht="13.55" customHeight="1" s="220">
-      <c r="A22" s="300" t="inlineStr">
+    <row r="21" ht="15" customHeight="1" s="220">
+      <c r="A21" s="297" t="n"/>
+      <c r="B21" s="318" t="inlineStr">
+        <is>
+          <t>PACLock (hybrid)</t>
+        </is>
+      </c>
+      <c r="C21" s="319" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="D21" s="320" t="inlineStr">
+        <is>
+          <t>0.5901 (1 seed)</t>
+        </is>
+      </c>
+      <c r="E21" s="320" t="inlineStr">
+        <is>
+          <t>0.6299 (1 seed)</t>
+        </is>
+      </c>
+      <c r="F21" s="320" t="inlineStr">
+        <is>
+          <t>0.9276 (1 seed)</t>
+        </is>
+      </c>
+      <c r="G21" s="320" t="inlineStr">
+        <is>
+          <t>+0.0417</t>
+        </is>
+      </c>
+      <c r="H21" s="321" t="inlineStr">
+        <is>
+          <t>-0.0099</t>
+        </is>
+      </c>
+      <c r="I21" s="321" t="inlineStr">
+        <is>
+          <t>+0.0010</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="13.55" customHeight="1" s="220"/>
+    <row r="23" ht="15" customHeight="1" s="220">
+      <c r="A23" s="300" t="inlineStr">
         <is>
           <t>灰色行 = 该 baseline 的原论文未评测本数据集,不存在官方超参;所用配方由我们从该模型覆盖过的数据集迁移而来。这些数字反映的是「该架构在我们所选配方下的表现」,不是「该 baseline 已发表的能力」。</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="15" customHeight="1" s="220"/>
     <row r="24" ht="15" customHeight="1" s="220"/>
     <row r="25" ht="13.55" customHeight="1" s="220"/>
     <row r="26" ht="13.55" customHeight="1" s="220"/>
@@ -14718,7 +14986,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I22"/>
+  <dimension ref="A1:I23"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.66667" defaultRowHeight="15" customHeight="1" outlineLevelRow="0"/>
   <cols>
     <col width="24" customWidth="1" style="219" min="1" max="4"/>
@@ -15481,15 +15749,55 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="15" customHeight="1" s="220"/>
-    <row r="22" ht="13.75" customHeight="1" s="220">
-      <c r="A22" s="300" t="inlineStr">
+    <row r="21" ht="15" customHeight="1" s="220">
+      <c r="A21" s="297" t="n"/>
+      <c r="B21" s="318" t="inlineStr">
+        <is>
+          <t>PACLock (hybrid)</t>
+        </is>
+      </c>
+      <c r="C21" s="319" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="D21" s="320" t="inlineStr">
+        <is>
+          <t>0.5290 (1 seed)</t>
+        </is>
+      </c>
+      <c r="E21" s="320" t="inlineStr">
+        <is>
+          <t>0.7473 (1 seed)</t>
+        </is>
+      </c>
+      <c r="F21" s="320" t="inlineStr">
+        <is>
+          <t>0.9368 (1 seed)</t>
+        </is>
+      </c>
+      <c r="G21" s="320" t="inlineStr">
+        <is>
+          <t>+0.2009</t>
+        </is>
+      </c>
+      <c r="H21" s="321" t="inlineStr">
+        <is>
+          <t>+0.0643</t>
+        </is>
+      </c>
+      <c r="I21" s="321" t="inlineStr">
+        <is>
+          <t>+0.1311</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="13.75" customHeight="1" s="220"/>
+    <row r="23" ht="15" customHeight="1" s="220">
+      <c r="A23" s="300" t="inlineStr">
         <is>
           <t>灰色行 = 该 baseline 的原论文未评测本数据集,不存在官方超参;所用配方由我们从该模型覆盖过的数据集迁移而来。这些数字反映的是「该架构在我们所选配方下的表现」,不是「该 baseline 已发表的能力」。</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="15" customHeight="1" s="220"/>
     <row r="24" ht="15" customHeight="1" s="220"/>
     <row r="25" ht="15" customHeight="1" s="220"/>
     <row r="26" ht="15" customHeight="1" s="220"/>
@@ -15546,7 +15854,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I22"/>
+  <dimension ref="A1:I23"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.66667" defaultRowHeight="15" customHeight="1" outlineLevelRow="0"/>
   <cols>
     <col width="24" customWidth="1" style="219" min="1" max="4"/>
@@ -16309,15 +16617,41 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="15" customHeight="1" s="220"/>
-    <row r="22" ht="13.55" customHeight="1" s="220">
-      <c r="A22" s="300" t="inlineStr">
+    <row r="21" ht="15" customHeight="1" s="220">
+      <c r="A21" s="297" t="n"/>
+      <c r="B21" s="318" t="inlineStr">
+        <is>
+          <t>PACLock (hybrid)</t>
+        </is>
+      </c>
+      <c r="C21" s="319" t="n"/>
+      <c r="D21" s="319" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E21" s="319" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F21" s="319" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G21" s="319" t="n"/>
+      <c r="H21" s="299" t="n"/>
+      <c r="I21" s="299" t="n"/>
+    </row>
+    <row r="22" ht="13.55" customHeight="1" s="220"/>
+    <row r="23" ht="15" customHeight="1" s="220">
+      <c r="A23" s="300" t="inlineStr">
         <is>
           <t>灰色行 = 该 baseline 的原论文未评测本数据集,不存在官方超参;所用配方由我们从该模型覆盖过的数据集迁移而来。这些数字反映的是「该架构在我们所选配方下的表现」,不是「该 baseline 已发表的能力」。</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="15" customHeight="1" s="220"/>
     <row r="24" ht="15" customHeight="1" s="220"/>
     <row r="25" ht="13.55" customHeight="1" s="220"/>
     <row r="26" ht="13.55" customHeight="1" s="220"/>
@@ -16377,7 +16711,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I22"/>
+  <dimension ref="A1:I23"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.66667" defaultRowHeight="15" customHeight="1" outlineLevelRow="0"/>
   <cols>
     <col width="24" customWidth="1" style="219" min="1" max="4"/>
@@ -17140,15 +17474,41 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="15" customHeight="1" s="220"/>
-    <row r="22" ht="13.55" customHeight="1" s="220">
-      <c r="A22" s="300" t="inlineStr">
+    <row r="21" ht="15" customHeight="1" s="220">
+      <c r="A21" s="297" t="n"/>
+      <c r="B21" s="318" t="inlineStr">
+        <is>
+          <t>PACLock (hybrid)</t>
+        </is>
+      </c>
+      <c r="C21" s="319" t="n"/>
+      <c r="D21" s="319" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E21" s="319" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F21" s="319" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G21" s="319" t="n"/>
+      <c r="H21" s="299" t="n"/>
+      <c r="I21" s="299" t="n"/>
+    </row>
+    <row r="22" ht="13.55" customHeight="1" s="220"/>
+    <row r="23" ht="15" customHeight="1" s="220">
+      <c r="A23" s="300" t="inlineStr">
         <is>
           <t>灰色行 = 该 baseline 的原论文未评测本数据集,不存在官方超参;所用配方由我们从该模型覆盖过的数据集迁移而来。这些数字反映的是「该架构在我们所选配方下的表现」,不是「该 baseline 已发表的能力」。</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="15" customHeight="1" s="220"/>
     <row r="24" ht="15" customHeight="1" s="220"/>
     <row r="25" ht="13.55" customHeight="1" s="220"/>
     <row r="26" ht="13.55" customHeight="1" s="220"/>
@@ -17203,7 +17563,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I22"/>
+  <dimension ref="A1:I23"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.83333" defaultRowHeight="15" customHeight="1" outlineLevelRow="0"/>
   <cols>
     <col width="24" customWidth="1" style="219" min="1" max="4"/>
@@ -17966,15 +18326,41 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="123.8" customHeight="1" s="220"/>
-    <row r="22" ht="13.55" customHeight="1" s="220">
-      <c r="A22" s="300" t="inlineStr">
+    <row r="21" ht="123.8" customHeight="1" s="220">
+      <c r="A21" s="297" t="n"/>
+      <c r="B21" s="318" t="inlineStr">
+        <is>
+          <t>PACLock (hybrid)</t>
+        </is>
+      </c>
+      <c r="C21" s="319" t="n"/>
+      <c r="D21" s="319" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E21" s="319" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F21" s="319" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G21" s="299" t="n"/>
+      <c r="H21" s="299" t="n"/>
+      <c r="I21" s="299" t="n"/>
+    </row>
+    <row r="22" ht="13.55" customHeight="1" s="220"/>
+    <row r="23" ht="13.55" customHeight="1" s="220">
+      <c r="A23" s="300" t="inlineStr">
         <is>
           <t>灰色行 = 该 baseline 的原论文未评测本数据集,不存在官方超参;所用配方由我们从该模型覆盖过的数据集迁移而来。这些数字反映的是「该架构在我们所选配方下的表现」,不是「该 baseline 已发表的能力」。</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="13.55" customHeight="1" s="220"/>
     <row r="24" ht="13.55" customHeight="1" s="220"/>
     <row r="25" ht="13.55" customHeight="1" s="220"/>
     <row r="26" ht="13.55" customHeight="1" s="220"/>
@@ -18032,7 +18418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I22"/>
+  <dimension ref="A1:I23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" style="220" min="1" max="1"/>
@@ -18762,8 +19148,35 @@
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="300" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="297" t="n"/>
+      <c r="B21" s="298" t="inlineStr">
+        <is>
+          <t>PACLock (hybrid)</t>
+        </is>
+      </c>
+      <c r="C21" s="299" t="n"/>
+      <c r="D21" s="299" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E21" s="299" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F21" s="299" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G21" s="299" t="n"/>
+      <c r="H21" s="299" t="n"/>
+      <c r="I21" s="299" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="300" t="inlineStr">
         <is>
           <t>灰色行 = 该 baseline 的原论文未评测本数据集,不存在官方超参;所用配方由我们从该模型覆盖过的数据集迁移而来。这些数字反映的是「该架构在我们所选配方下的表现」,不是「该 baseline 已发表的能力」。</t>
         </is>

--- a/results/PACLock_baseline_matrix_filled.xlsx
+++ b/results/PACLock_baseline_matrix_filled.xlsx
@@ -11359,7 +11359,11 @@
           <t>0.6455±0.0000 (1)</t>
         </is>
       </c>
-      <c r="F12" s="313" t="n"/>
+      <c r="F12" s="315" t="inlineStr">
+        <is>
+          <t>0.7513±0.0000 (1)</t>
+        </is>
+      </c>
       <c r="G12" s="313" t="n"/>
       <c r="H12" s="313" t="n"/>
       <c r="I12" s="313" t="n"/>

--- a/results/PACLock_baseline_matrix_filled.xlsx
+++ b/results/PACLock_baseline_matrix_filled.xlsx
@@ -10966,7 +10966,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L49"/>
+  <dimension ref="A1:L51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" style="220" min="1" max="1"/>
@@ -11413,52 +11413,24 @@
       <c r="A14" s="312" t="inlineStr"/>
       <c r="B14" s="312" t="inlineStr">
         <is>
-          <t>rotation(耦合只旋转不缩放)</t>
-        </is>
-      </c>
-      <c r="C14" s="315" t="inlineStr">
-        <is>
-          <t>0.8806±0.0000 (1)</t>
-        </is>
-      </c>
-      <c r="D14" s="313" t="inlineStr">
-        <is>
-          <t>0.7328±0.0161 (3)</t>
-        </is>
-      </c>
-      <c r="E14" s="315" t="inlineStr">
-        <is>
-          <t>0.6884±0.0000 (1)</t>
-        </is>
-      </c>
-      <c r="F14" s="315" t="inlineStr">
-        <is>
-          <t>0.5100±0.0000 (1)</t>
-        </is>
-      </c>
-      <c r="G14" s="315" t="inlineStr">
-        <is>
-          <t>0.6449±0.0000 (1)</t>
-        </is>
-      </c>
-      <c r="H14" s="315" t="inlineStr">
-        <is>
-          <t>0.7104±0.0000 (1)</t>
-        </is>
-      </c>
+          <t>hybrid + spatial 头</t>
+        </is>
+      </c>
+      <c r="C14" s="313" t="n"/>
+      <c r="D14" s="313" t="n"/>
+      <c r="E14" s="313" t="n"/>
+      <c r="F14" s="313" t="n"/>
+      <c r="G14" s="313" t="n"/>
+      <c r="H14" s="313" t="n"/>
       <c r="I14" s="315" t="inlineStr">
         <is>
-          <t>0.2916±0.0063 (2)</t>
-        </is>
-      </c>
-      <c r="J14" s="315" t="inlineStr">
-        <is>
-          <t>0.1514±0.0000 (1)</t>
-        </is>
-      </c>
-      <c r="K14" s="313" t="inlineStr">
-        <is>
-          <t>0.3708±0.0092 (3)</t>
+          <t>0.4284±0.0000 (1)</t>
+        </is>
+      </c>
+      <c r="J14" s="313" t="n"/>
+      <c r="K14" s="315" t="inlineStr">
+        <is>
+          <t>0.4888±0.0000 (1)</t>
         </is>
       </c>
       <c r="L14" s="313" t="n"/>
@@ -11467,7 +11439,7 @@
       <c r="A15" s="312" t="inlineStr"/>
       <c r="B15" s="312" t="inlineStr">
         <is>
-          <t>rotation(跑在 PAC 协议数据上,与上行不可比)</t>
+          <t>hybrid + spatial 头 + 门</t>
         </is>
       </c>
       <c r="C15" s="313" t="n"/>
@@ -11476,43 +11448,59 @@
       <c r="F15" s="313" t="n"/>
       <c r="G15" s="313" t="n"/>
       <c r="H15" s="313" t="n"/>
-      <c r="I15" s="313" t="n"/>
-      <c r="J15" s="315" t="inlineStr">
-        <is>
-          <t>0.1098±0.0000 (1)</t>
-        </is>
-      </c>
+      <c r="I15" s="315" t="inlineStr">
+        <is>
+          <t>0.4258±0.0000 (1)</t>
+        </is>
+      </c>
+      <c r="J15" s="313" t="n"/>
       <c r="K15" s="315" t="inlineStr">
         <is>
-          <t>0.2724±0.0000 (1)</t>
-        </is>
-      </c>
-      <c r="L15" s="315" t="inlineStr">
-        <is>
-          <t>0.5568±0.0000 (1)</t>
-        </is>
-      </c>
+          <t>0.4923±0.0000 (1)</t>
+        </is>
+      </c>
+      <c r="L15" s="313" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="312" t="inlineStr"/>
       <c r="B16" s="312" t="inlineStr">
         <is>
-          <t>spatial 头(保留电极身份)</t>
-        </is>
-      </c>
-      <c r="C16" s="313" t="n"/>
-      <c r="D16" s="315" t="inlineStr">
-        <is>
-          <t>0.6520±0.0000 (1)</t>
-        </is>
-      </c>
-      <c r="E16" s="313" t="n"/>
-      <c r="F16" s="313" t="n"/>
-      <c r="G16" s="313" t="n"/>
-      <c r="H16" s="313" t="n"/>
-      <c r="I16" s="313" t="inlineStr">
-        <is>
-          <t>0.3535±0.0047 (3)</t>
+          <t>rotation(耦合只旋转不缩放)</t>
+        </is>
+      </c>
+      <c r="C16" s="315" t="inlineStr">
+        <is>
+          <t>0.8806±0.0000 (1)</t>
+        </is>
+      </c>
+      <c r="D16" s="313" t="inlineStr">
+        <is>
+          <t>0.7328±0.0161 (3)</t>
+        </is>
+      </c>
+      <c r="E16" s="315" t="inlineStr">
+        <is>
+          <t>0.6884±0.0000 (1)</t>
+        </is>
+      </c>
+      <c r="F16" s="315" t="inlineStr">
+        <is>
+          <t>0.5100±0.0000 (1)</t>
+        </is>
+      </c>
+      <c r="G16" s="315" t="inlineStr">
+        <is>
+          <t>0.6449±0.0000 (1)</t>
+        </is>
+      </c>
+      <c r="H16" s="315" t="inlineStr">
+        <is>
+          <t>0.7104±0.0000 (1)</t>
+        </is>
+      </c>
+      <c r="I16" s="315" t="inlineStr">
+        <is>
+          <t>0.2916±0.0063 (2)</t>
         </is>
       </c>
       <c r="J16" s="315" t="inlineStr">
@@ -11522,7 +11510,7 @@
       </c>
       <c r="K16" s="313" t="inlineStr">
         <is>
-          <t>0.4317±0.0153 (3)</t>
+          <t>0.3708±0.0092 (3)</t>
         </is>
       </c>
       <c r="L16" s="313" t="n"/>
@@ -11531,7 +11519,7 @@
       <c r="A17" s="312" t="inlineStr"/>
       <c r="B17" s="312" t="inlineStr">
         <is>
-          <t>rotation + spatial 头</t>
+          <t>rotation(跑在 PAC 协议数据上,与上行不可比)</t>
         </is>
       </c>
       <c r="C17" s="313" t="n"/>
@@ -11540,73 +11528,53 @@
       <c r="F17" s="313" t="n"/>
       <c r="G17" s="313" t="n"/>
       <c r="H17" s="313" t="n"/>
-      <c r="I17" s="315" t="inlineStr">
-        <is>
-          <t>0.3299±0.0000 (1)</t>
-        </is>
-      </c>
-      <c r="J17" s="313" t="n"/>
+      <c r="I17" s="313" t="n"/>
+      <c r="J17" s="315" t="inlineStr">
+        <is>
+          <t>0.1098±0.0000 (1)</t>
+        </is>
+      </c>
       <c r="K17" s="315" t="inlineStr">
         <is>
-          <t>0.4344±0.0000 (1)</t>
-        </is>
-      </c>
-      <c r="L17" s="313" t="n"/>
+          <t>0.2724±0.0000 (1)</t>
+        </is>
+      </c>
+      <c r="L17" s="315" t="inlineStr">
+        <is>
+          <t>0.5568±0.0000 (1)</t>
+        </is>
+      </c>
     </row>
     <row r="18">
-      <c r="A18" s="311" t="inlineStr">
-        <is>
-          <t>预训练</t>
-        </is>
-      </c>
+      <c r="A18" s="312" t="inlineStr"/>
       <c r="B18" s="312" t="inlineStr">
         <is>
-          <t>预训练 base(60k)</t>
-        </is>
-      </c>
-      <c r="C18" s="313" t="inlineStr">
-        <is>
-          <t>0.8841±0.0043 (3)</t>
-        </is>
-      </c>
-      <c r="D18" s="313" t="inlineStr">
-        <is>
-          <t>0.6730±0.0116 (3)</t>
-        </is>
-      </c>
-      <c r="E18" s="313" t="inlineStr">
-        <is>
-          <t>0.6398±0.0615 (3)</t>
-        </is>
-      </c>
-      <c r="F18" s="313" t="inlineStr">
-        <is>
-          <t>0.6830±0.0228 (3)</t>
-        </is>
-      </c>
-      <c r="G18" s="313" t="inlineStr">
-        <is>
-          <t>0.6651±0.0109 (3)</t>
-        </is>
-      </c>
-      <c r="H18" s="313" t="inlineStr">
-        <is>
-          <t>0.6934±0.0032 (3)</t>
-        </is>
-      </c>
+          <t>spatial 头(保留电极身份)</t>
+        </is>
+      </c>
+      <c r="C18" s="313" t="n"/>
+      <c r="D18" s="315" t="inlineStr">
+        <is>
+          <t>0.6520±0.0000 (1)</t>
+        </is>
+      </c>
+      <c r="E18" s="313" t="n"/>
+      <c r="F18" s="313" t="n"/>
+      <c r="G18" s="313" t="n"/>
+      <c r="H18" s="313" t="n"/>
       <c r="I18" s="313" t="inlineStr">
         <is>
-          <t>0.3059±0.0262 (3)</t>
-        </is>
-      </c>
-      <c r="J18" s="313" t="inlineStr">
-        <is>
-          <t>0.1540±0.0202 (3)</t>
+          <t>0.3535±0.0047 (3)</t>
+        </is>
+      </c>
+      <c r="J18" s="315" t="inlineStr">
+        <is>
+          <t>0.1514±0.0000 (1)</t>
         </is>
       </c>
       <c r="K18" s="313" t="inlineStr">
         <is>
-          <t>0.3652±0.0083 (3)</t>
+          <t>0.4317±0.0153 (3)</t>
         </is>
       </c>
       <c r="L18" s="313" t="n"/>
@@ -11615,90 +11583,82 @@
       <c r="A19" s="312" t="inlineStr"/>
       <c r="B19" s="312" t="inlineStr">
         <is>
-          <t>预训练 large(60k)</t>
-        </is>
-      </c>
-      <c r="C19" s="313" t="inlineStr">
-        <is>
-          <t>0.8869±0.0069 (3)</t>
-        </is>
-      </c>
-      <c r="D19" s="313" t="inlineStr">
-        <is>
-          <t>0.6523±0.0302 (3)</t>
-        </is>
-      </c>
-      <c r="E19" s="313" t="inlineStr">
-        <is>
-          <t>0.6289±0.0297 (3)</t>
-        </is>
-      </c>
-      <c r="F19" s="313" t="inlineStr">
-        <is>
-          <t>0.6162±0.0467 (3)</t>
-        </is>
-      </c>
-      <c r="G19" s="313" t="inlineStr">
-        <is>
-          <t>0.6641±0.0044 (3)</t>
-        </is>
-      </c>
-      <c r="H19" s="313" t="inlineStr">
-        <is>
-          <t>0.6996±0.0153 (3)</t>
-        </is>
-      </c>
-      <c r="I19" s="313" t="inlineStr">
-        <is>
-          <t>0.3140±0.0094 (3)</t>
-        </is>
-      </c>
-      <c r="J19" s="313" t="inlineStr">
-        <is>
-          <t>0.1640±0.0155 (3)</t>
-        </is>
-      </c>
-      <c r="K19" s="313" t="inlineStr">
-        <is>
-          <t>0.4122±0.0166 (3)</t>
+          <t>rotation + spatial 头</t>
+        </is>
+      </c>
+      <c r="C19" s="313" t="n"/>
+      <c r="D19" s="313" t="n"/>
+      <c r="E19" s="313" t="n"/>
+      <c r="F19" s="313" t="n"/>
+      <c r="G19" s="313" t="n"/>
+      <c r="H19" s="313" t="n"/>
+      <c r="I19" s="315" t="inlineStr">
+        <is>
+          <t>0.3299±0.0000 (1)</t>
+        </is>
+      </c>
+      <c r="J19" s="313" t="n"/>
+      <c r="K19" s="315" t="inlineStr">
+        <is>
+          <t>0.4344±0.0000 (1)</t>
         </is>
       </c>
       <c r="L19" s="313" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="312" t="inlineStr"/>
+      <c r="A20" s="311" t="inlineStr">
+        <is>
+          <t>预训练</t>
+        </is>
+      </c>
       <c r="B20" s="312" t="inlineStr">
         <is>
-          <t>raw tokenizer 预训练 large(60k)</t>
-        </is>
-      </c>
-      <c r="C20" s="313" t="n"/>
-      <c r="D20" s="313" t="n"/>
-      <c r="E20" s="315" t="inlineStr">
-        <is>
-          <t>0.5460±0.0000 (1)</t>
-        </is>
-      </c>
-      <c r="F20" s="315" t="inlineStr">
-        <is>
-          <t>0.6279±0.0000 (1)</t>
-        </is>
-      </c>
-      <c r="G20" s="313" t="n"/>
-      <c r="H20" s="313" t="n"/>
+          <t>预训练 base(60k)</t>
+        </is>
+      </c>
+      <c r="C20" s="313" t="inlineStr">
+        <is>
+          <t>0.8841±0.0043 (3)</t>
+        </is>
+      </c>
+      <c r="D20" s="313" t="inlineStr">
+        <is>
+          <t>0.6730±0.0116 (3)</t>
+        </is>
+      </c>
+      <c r="E20" s="313" t="inlineStr">
+        <is>
+          <t>0.6398±0.0615 (3)</t>
+        </is>
+      </c>
+      <c r="F20" s="313" t="inlineStr">
+        <is>
+          <t>0.6830±0.0228 (3)</t>
+        </is>
+      </c>
+      <c r="G20" s="313" t="inlineStr">
+        <is>
+          <t>0.6651±0.0109 (3)</t>
+        </is>
+      </c>
+      <c r="H20" s="313" t="inlineStr">
+        <is>
+          <t>0.6934±0.0032 (3)</t>
+        </is>
+      </c>
       <c r="I20" s="313" t="inlineStr">
         <is>
-          <t>0.3633±0.0349 (3)</t>
-        </is>
-      </c>
-      <c r="J20" s="315" t="inlineStr">
-        <is>
-          <t>0.1690±0.0018 (2)</t>
+          <t>0.3059±0.0262 (3)</t>
+        </is>
+      </c>
+      <c r="J20" s="313" t="inlineStr">
+        <is>
+          <t>0.1540±0.0202 (3)</t>
         </is>
       </c>
       <c r="K20" s="313" t="inlineStr">
         <is>
-          <t>0.4483±0.0031 (3)</t>
+          <t>0.3652±0.0083 (3)</t>
         </is>
       </c>
       <c r="L20" s="313" t="n"/>
@@ -11707,73 +11667,117 @@
       <c r="A21" s="312" t="inlineStr"/>
       <c r="B21" s="312" t="inlineStr">
         <is>
-          <t>预训练池剔除 TUSZ/CHB-MIT</t>
-        </is>
-      </c>
-      <c r="C21" s="313" t="n"/>
-      <c r="D21" s="313" t="n"/>
-      <c r="E21" s="315" t="inlineStr">
-        <is>
-          <t>0.6221±0.0000 (1)</t>
-        </is>
-      </c>
-      <c r="F21" s="315" t="inlineStr">
-        <is>
-          <t>0.6410±0.0000 (1)</t>
-        </is>
-      </c>
-      <c r="G21" s="313" t="n"/>
-      <c r="H21" s="313" t="n"/>
-      <c r="I21" s="313" t="n"/>
-      <c r="J21" s="313" t="n"/>
-      <c r="K21" s="313" t="n"/>
+          <t>预训练 large(60k)</t>
+        </is>
+      </c>
+      <c r="C21" s="313" t="inlineStr">
+        <is>
+          <t>0.8869±0.0069 (3)</t>
+        </is>
+      </c>
+      <c r="D21" s="313" t="inlineStr">
+        <is>
+          <t>0.6523±0.0302 (3)</t>
+        </is>
+      </c>
+      <c r="E21" s="313" t="inlineStr">
+        <is>
+          <t>0.6289±0.0297 (3)</t>
+        </is>
+      </c>
+      <c r="F21" s="313" t="inlineStr">
+        <is>
+          <t>0.6162±0.0467 (3)</t>
+        </is>
+      </c>
+      <c r="G21" s="313" t="inlineStr">
+        <is>
+          <t>0.6641±0.0044 (3)</t>
+        </is>
+      </c>
+      <c r="H21" s="313" t="inlineStr">
+        <is>
+          <t>0.6996±0.0153 (3)</t>
+        </is>
+      </c>
+      <c r="I21" s="313" t="inlineStr">
+        <is>
+          <t>0.3140±0.0094 (3)</t>
+        </is>
+      </c>
+      <c r="J21" s="313" t="inlineStr">
+        <is>
+          <t>0.1640±0.0155 (3)</t>
+        </is>
+      </c>
+      <c r="K21" s="313" t="inlineStr">
+        <is>
+          <t>0.4122±0.0166 (3)</t>
+        </is>
+      </c>
       <c r="L21" s="313" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="312" t="inlineStr"/>
       <c r="B22" s="312" t="inlineStr">
         <is>
-          <t>预训练 base,微调 patch_len=200</t>
+          <t>raw tokenizer 预训练 large(60k)</t>
         </is>
       </c>
       <c r="C22" s="313" t="n"/>
-      <c r="D22" s="313" t="inlineStr">
-        <is>
-          <t>0.6793±0.0109 (3)</t>
-        </is>
-      </c>
-      <c r="E22" s="313" t="n"/>
-      <c r="F22" s="313" t="n"/>
+      <c r="D22" s="313" t="n"/>
+      <c r="E22" s="315" t="inlineStr">
+        <is>
+          <t>0.5460±0.0000 (1)</t>
+        </is>
+      </c>
+      <c r="F22" s="315" t="inlineStr">
+        <is>
+          <t>0.6279±0.0000 (1)</t>
+        </is>
+      </c>
       <c r="G22" s="313" t="n"/>
       <c r="H22" s="313" t="n"/>
-      <c r="I22" s="313" t="n"/>
-      <c r="J22" s="313" t="n"/>
-      <c r="K22" s="313" t="n"/>
+      <c r="I22" s="313" t="inlineStr">
+        <is>
+          <t>0.3633±0.0349 (3)</t>
+        </is>
+      </c>
+      <c r="J22" s="315" t="inlineStr">
+        <is>
+          <t>0.1690±0.0018 (2)</t>
+        </is>
+      </c>
+      <c r="K22" s="313" t="inlineStr">
+        <is>
+          <t>0.4483±0.0031 (3)</t>
+        </is>
+      </c>
       <c r="L22" s="313" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="312" t="inlineStr"/>
       <c r="B23" s="312" t="inlineStr">
         <is>
-          <t>早期微调配方(6k checkpoint)</t>
+          <t>预训练池剔除 TUSZ/CHB-MIT</t>
         </is>
       </c>
       <c r="C23" s="313" t="n"/>
       <c r="D23" s="313" t="n"/>
-      <c r="E23" s="313" t="n"/>
-      <c r="F23" s="313" t="n"/>
+      <c r="E23" s="315" t="inlineStr">
+        <is>
+          <t>0.6221±0.0000 (1)</t>
+        </is>
+      </c>
+      <c r="F23" s="315" t="inlineStr">
+        <is>
+          <t>0.6410±0.0000 (1)</t>
+        </is>
+      </c>
       <c r="G23" s="313" t="n"/>
       <c r="H23" s="313" t="n"/>
-      <c r="I23" s="315" t="inlineStr">
-        <is>
-          <t>0.2690±0.0000 (1)</t>
-        </is>
-      </c>
-      <c r="J23" s="315" t="inlineStr">
-        <is>
-          <t>0.1279±0.0000 (1)</t>
-        </is>
-      </c>
+      <c r="I23" s="313" t="n"/>
+      <c r="J23" s="313" t="n"/>
       <c r="K23" s="313" t="n"/>
       <c r="L23" s="313" t="n"/>
     </row>
@@ -11781,25 +11785,21 @@
       <c r="A24" s="312" t="inlineStr"/>
       <c r="B24" s="312" t="inlineStr">
         <is>
-          <t>早期微调配方 v2(6k checkpoint)</t>
+          <t>预训练 base,微调 patch_len=200</t>
         </is>
       </c>
       <c r="C24" s="313" t="n"/>
-      <c r="D24" s="313" t="n"/>
+      <c r="D24" s="313" t="inlineStr">
+        <is>
+          <t>0.6793±0.0109 (3)</t>
+        </is>
+      </c>
       <c r="E24" s="313" t="n"/>
       <c r="F24" s="313" t="n"/>
       <c r="G24" s="313" t="n"/>
       <c r="H24" s="313" t="n"/>
-      <c r="I24" s="315" t="inlineStr">
-        <is>
-          <t>0.2622±0.0000 (1)</t>
-        </is>
-      </c>
-      <c r="J24" s="315" t="inlineStr">
-        <is>
-          <t>0.1408±0.0000 (1)</t>
-        </is>
-      </c>
+      <c r="I24" s="313" t="n"/>
+      <c r="J24" s="313" t="n"/>
       <c r="K24" s="313" t="n"/>
       <c r="L24" s="313" t="n"/>
     </row>
@@ -11807,7 +11807,7 @@
       <c r="A25" s="312" t="inlineStr"/>
       <c r="B25" s="312" t="inlineStr">
         <is>
-          <t>早期微调配方 large(6k checkpoint)</t>
+          <t>早期微调配方(6k checkpoint)</t>
         </is>
       </c>
       <c r="C25" s="313" t="n"/>
@@ -11818,26 +11818,22 @@
       <c r="H25" s="313" t="n"/>
       <c r="I25" s="315" t="inlineStr">
         <is>
-          <t>0.2716±0.0000 (1)</t>
+          <t>0.2690±0.0000 (1)</t>
         </is>
       </c>
       <c r="J25" s="315" t="inlineStr">
         <is>
-          <t>0.1381±0.0000 (1)</t>
+          <t>0.1279±0.0000 (1)</t>
         </is>
       </c>
       <c r="K25" s="313" t="n"/>
       <c r="L25" s="313" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="311" t="inlineStr">
-        <is>
-          <t>容量阶梯</t>
-        </is>
-      </c>
+      <c r="A26" s="312" t="inlineStr"/>
       <c r="B26" s="312" t="inlineStr">
         <is>
-          <t>raw,d_model 32</t>
+          <t>早期微调配方 v2(6k checkpoint)</t>
         </is>
       </c>
       <c r="C26" s="313" t="n"/>
@@ -11846,24 +11842,24 @@
       <c r="F26" s="313" t="n"/>
       <c r="G26" s="313" t="n"/>
       <c r="H26" s="313" t="n"/>
-      <c r="I26" s="313" t="inlineStr">
-        <is>
-          <t>0.2613±0.0100 (3)</t>
-        </is>
-      </c>
-      <c r="J26" s="313" t="n"/>
-      <c r="K26" s="313" t="inlineStr">
-        <is>
-          <t>0.2617±0.0019 (3)</t>
-        </is>
-      </c>
+      <c r="I26" s="315" t="inlineStr">
+        <is>
+          <t>0.2622±0.0000 (1)</t>
+        </is>
+      </c>
+      <c r="J26" s="315" t="inlineStr">
+        <is>
+          <t>0.1408±0.0000 (1)</t>
+        </is>
+      </c>
+      <c r="K26" s="313" t="n"/>
       <c r="L26" s="313" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="312" t="inlineStr"/>
       <c r="B27" s="312" t="inlineStr">
         <is>
-          <t>raw,d_model 64</t>
+          <t>早期微调配方 large(6k checkpoint)</t>
         </is>
       </c>
       <c r="C27" s="313" t="n"/>
@@ -11872,24 +11868,28 @@
       <c r="F27" s="313" t="n"/>
       <c r="G27" s="313" t="n"/>
       <c r="H27" s="313" t="n"/>
-      <c r="I27" s="313" t="inlineStr">
-        <is>
-          <t>0.3129±0.0121 (3)</t>
-        </is>
-      </c>
-      <c r="J27" s="313" t="n"/>
-      <c r="K27" s="313" t="inlineStr">
-        <is>
-          <t>0.2780±0.0100 (3)</t>
-        </is>
-      </c>
+      <c r="I27" s="315" t="inlineStr">
+        <is>
+          <t>0.2716±0.0000 (1)</t>
+        </is>
+      </c>
+      <c r="J27" s="315" t="inlineStr">
+        <is>
+          <t>0.1381±0.0000 (1)</t>
+        </is>
+      </c>
+      <c r="K27" s="313" t="n"/>
       <c r="L27" s="313" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="312" t="inlineStr"/>
+      <c r="A28" s="311" t="inlineStr">
+        <is>
+          <t>容量阶梯</t>
+        </is>
+      </c>
       <c r="B28" s="312" t="inlineStr">
         <is>
-          <t>raw,d_model 256</t>
+          <t>raw,d_model 32</t>
         </is>
       </c>
       <c r="C28" s="313" t="n"/>
@@ -11900,13 +11900,13 @@
       <c r="H28" s="313" t="n"/>
       <c r="I28" s="313" t="inlineStr">
         <is>
-          <t>0.4159±0.0529 (3)</t>
+          <t>0.2613±0.0100 (3)</t>
         </is>
       </c>
       <c r="J28" s="313" t="n"/>
       <c r="K28" s="313" t="inlineStr">
         <is>
-          <t>0.4437±0.0192 (3)</t>
+          <t>0.2617±0.0019 (3)</t>
         </is>
       </c>
       <c r="L28" s="313" t="n"/>
@@ -11915,7 +11915,7 @@
       <c r="A29" s="312" t="inlineStr"/>
       <c r="B29" s="312" t="inlineStr">
         <is>
-          <t>raw,加宽</t>
+          <t>raw,d_model 64</t>
         </is>
       </c>
       <c r="C29" s="313" t="n"/>
@@ -11926,13 +11926,13 @@
       <c r="H29" s="313" t="n"/>
       <c r="I29" s="313" t="inlineStr">
         <is>
-          <t>0.4093±0.0425 (3)</t>
+          <t>0.3129±0.0121 (3)</t>
         </is>
       </c>
       <c r="J29" s="313" t="n"/>
-      <c r="K29" s="315" t="inlineStr">
-        <is>
-          <t>0.4261±0.0085 (2)</t>
+      <c r="K29" s="313" t="inlineStr">
+        <is>
+          <t>0.2780±0.0100 (3)</t>
         </is>
       </c>
       <c r="L29" s="313" t="n"/>
@@ -11941,7 +11941,7 @@
       <c r="A30" s="312" t="inlineStr"/>
       <c r="B30" s="312" t="inlineStr">
         <is>
-          <t>raw,16 频带</t>
+          <t>raw,d_model 256</t>
         </is>
       </c>
       <c r="C30" s="313" t="n"/>
@@ -11952,13 +11952,13 @@
       <c r="H30" s="313" t="n"/>
       <c r="I30" s="313" t="inlineStr">
         <is>
-          <t>0.3781±0.0467 (3)</t>
+          <t>0.4159±0.0529 (3)</t>
         </is>
       </c>
       <c r="J30" s="313" t="n"/>
       <c r="K30" s="313" t="inlineStr">
         <is>
-          <t>0.4288±0.0090 (3)</t>
+          <t>0.4437±0.0192 (3)</t>
         </is>
       </c>
       <c r="L30" s="313" t="n"/>
@@ -11967,7 +11967,7 @@
       <c r="A31" s="312" t="inlineStr"/>
       <c r="B31" s="312" t="inlineStr">
         <is>
-          <t>raw,patch_len 100</t>
+          <t>raw,加宽</t>
         </is>
       </c>
       <c r="C31" s="313" t="n"/>
@@ -11978,13 +11978,13 @@
       <c r="H31" s="313" t="n"/>
       <c r="I31" s="313" t="inlineStr">
         <is>
-          <t>0.3508±0.0251 (3)</t>
+          <t>0.4093±0.0425 (3)</t>
         </is>
       </c>
       <c r="J31" s="313" t="n"/>
-      <c r="K31" s="313" t="inlineStr">
-        <is>
-          <t>0.4066±0.0221 (3)</t>
+      <c r="K31" s="315" t="inlineStr">
+        <is>
+          <t>0.4261±0.0085 (2)</t>
         </is>
       </c>
       <c r="L31" s="313" t="n"/>
@@ -11993,7 +11993,7 @@
       <c r="A32" s="312" t="inlineStr"/>
       <c r="B32" s="312" t="inlineStr">
         <is>
-          <t>raw,dropout 0.5</t>
+          <t>raw,16 频带</t>
         </is>
       </c>
       <c r="C32" s="313" t="n"/>
@@ -12004,13 +12004,13 @@
       <c r="H32" s="313" t="n"/>
       <c r="I32" s="313" t="inlineStr">
         <is>
-          <t>0.3409±0.0196 (3)</t>
+          <t>0.3781±0.0467 (3)</t>
         </is>
       </c>
       <c r="J32" s="313" t="n"/>
       <c r="K32" s="313" t="inlineStr">
         <is>
-          <t>0.4308±0.0139 (3)</t>
+          <t>0.4288±0.0090 (3)</t>
         </is>
       </c>
       <c r="L32" s="313" t="n"/>
@@ -12019,7 +12019,7 @@
       <c r="A33" s="312" t="inlineStr"/>
       <c r="B33" s="312" t="inlineStr">
         <is>
-          <t>raw,attn 头</t>
+          <t>raw,patch_len 100</t>
         </is>
       </c>
       <c r="C33" s="313" t="n"/>
@@ -12030,26 +12030,22 @@
       <c r="H33" s="313" t="n"/>
       <c r="I33" s="313" t="inlineStr">
         <is>
-          <t>0.3524±0.0467 (3)</t>
+          <t>0.3508±0.0251 (3)</t>
         </is>
       </c>
       <c r="J33" s="313" t="n"/>
       <c r="K33" s="313" t="inlineStr">
         <is>
-          <t>0.4545±0.0054 (3)</t>
+          <t>0.4066±0.0221 (3)</t>
         </is>
       </c>
       <c r="L33" s="313" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="311" t="inlineStr">
-        <is>
-          <t>已否决</t>
-        </is>
-      </c>
+      <c r="A34" s="312" t="inlineStr"/>
       <c r="B34" s="312" t="inlineStr">
         <is>
-          <t>spatial_pe: xyz(蒙太奇坐标)</t>
+          <t>raw,dropout 0.5</t>
         </is>
       </c>
       <c r="C34" s="313" t="n"/>
@@ -12057,20 +12053,16 @@
       <c r="E34" s="313" t="n"/>
       <c r="F34" s="313" t="n"/>
       <c r="G34" s="313" t="n"/>
-      <c r="H34" s="313" t="inlineStr">
-        <is>
-          <t>0.6954±0.0167 (3)</t>
-        </is>
-      </c>
+      <c r="H34" s="313" t="n"/>
       <c r="I34" s="313" t="inlineStr">
         <is>
-          <t>0.2478±0.0053 (3)</t>
+          <t>0.3409±0.0196 (3)</t>
         </is>
       </c>
       <c r="J34" s="313" t="n"/>
       <c r="K34" s="313" t="inlineStr">
         <is>
-          <t>0.3338±0.0027 (3)</t>
+          <t>0.4308±0.0139 (3)</t>
         </is>
       </c>
       <c r="L34" s="313" t="n"/>
@@ -12079,7 +12071,7 @@
       <c r="A35" s="312" t="inlineStr"/>
       <c r="B35" s="312" t="inlineStr">
         <is>
-          <t>每窗口归一化</t>
+          <t>raw,attn 头</t>
         </is>
       </c>
       <c r="C35" s="313" t="n"/>
@@ -12090,22 +12082,26 @@
       <c r="H35" s="313" t="n"/>
       <c r="I35" s="313" t="inlineStr">
         <is>
-          <t>0.2532±0.0155 (3)</t>
+          <t>0.3524±0.0467 (3)</t>
         </is>
       </c>
       <c r="J35" s="313" t="n"/>
       <c r="K35" s="313" t="inlineStr">
         <is>
-          <t>0.3050±0.0438 (3)</t>
+          <t>0.4545±0.0054 (3)</t>
         </is>
       </c>
       <c r="L35" s="313" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="312" t="inlineStr"/>
+      <c r="A36" s="311" t="inlineStr">
+        <is>
+          <t>已否决</t>
+        </is>
+      </c>
       <c r="B36" s="312" t="inlineStr">
         <is>
-          <t>每窗口归一化 + raw</t>
+          <t>spatial_pe: xyz(蒙太奇坐标)</t>
         </is>
       </c>
       <c r="C36" s="313" t="n"/>
@@ -12113,16 +12109,20 @@
       <c r="E36" s="313" t="n"/>
       <c r="F36" s="313" t="n"/>
       <c r="G36" s="313" t="n"/>
-      <c r="H36" s="313" t="n"/>
-      <c r="I36" s="315" t="inlineStr">
-        <is>
-          <t>0.2896±0.0146 (2)</t>
+      <c r="H36" s="313" t="inlineStr">
+        <is>
+          <t>0.6954±0.0167 (3)</t>
+        </is>
+      </c>
+      <c r="I36" s="313" t="inlineStr">
+        <is>
+          <t>0.2478±0.0053 (3)</t>
         </is>
       </c>
       <c r="J36" s="313" t="n"/>
-      <c r="K36" s="315" t="inlineStr">
-        <is>
-          <t>0.2992±0.0139 (2)</t>
+      <c r="K36" s="313" t="inlineStr">
+        <is>
+          <t>0.3338±0.0027 (3)</t>
         </is>
       </c>
       <c r="L36" s="313" t="n"/>
@@ -12131,7 +12131,7 @@
       <c r="A37" s="312" t="inlineStr"/>
       <c r="B37" s="312" t="inlineStr">
         <is>
-          <t>每受试者归一化</t>
+          <t>每窗口归一化</t>
         </is>
       </c>
       <c r="C37" s="313" t="n"/>
@@ -12140,20 +12140,24 @@
       <c r="F37" s="313" t="n"/>
       <c r="G37" s="313" t="n"/>
       <c r="H37" s="313" t="n"/>
-      <c r="I37" s="313" t="n"/>
-      <c r="J37" s="315" t="inlineStr">
-        <is>
-          <t>0.1328±0.0007 (2)</t>
-        </is>
-      </c>
-      <c r="K37" s="313" t="n"/>
+      <c r="I37" s="313" t="inlineStr">
+        <is>
+          <t>0.2532±0.0155 (3)</t>
+        </is>
+      </c>
+      <c r="J37" s="313" t="n"/>
+      <c r="K37" s="313" t="inlineStr">
+        <is>
+          <t>0.3050±0.0438 (3)</t>
+        </is>
+      </c>
       <c r="L37" s="313" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="312" t="inlineStr"/>
       <c r="B38" s="312" t="inlineStr">
         <is>
-          <t>每受试者归一化 + raw</t>
+          <t>每窗口归一化 + raw</t>
         </is>
       </c>
       <c r="C38" s="313" t="n"/>
@@ -12162,20 +12166,24 @@
       <c r="F38" s="313" t="n"/>
       <c r="G38" s="313" t="n"/>
       <c r="H38" s="313" t="n"/>
-      <c r="I38" s="313" t="n"/>
-      <c r="J38" s="313" t="inlineStr">
-        <is>
-          <t>0.1579±0.0034 (3)</t>
-        </is>
-      </c>
-      <c r="K38" s="313" t="n"/>
+      <c r="I38" s="315" t="inlineStr">
+        <is>
+          <t>0.2896±0.0146 (2)</t>
+        </is>
+      </c>
+      <c r="J38" s="313" t="n"/>
+      <c r="K38" s="315" t="inlineStr">
+        <is>
+          <t>0.2992±0.0139 (2)</t>
+        </is>
+      </c>
       <c r="L38" s="313" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="312" t="inlineStr"/>
       <c r="B39" s="312" t="inlineStr">
         <is>
-          <t>每受试者归一化 + raw + attn 头</t>
+          <t>每受试者归一化</t>
         </is>
       </c>
       <c r="C39" s="313" t="n"/>
@@ -12185,9 +12193,9 @@
       <c r="G39" s="313" t="n"/>
       <c r="H39" s="313" t="n"/>
       <c r="I39" s="313" t="n"/>
-      <c r="J39" s="313" t="inlineStr">
-        <is>
-          <t>0.1513±0.0012 (3)</t>
+      <c r="J39" s="315" t="inlineStr">
+        <is>
+          <t>0.1328±0.0007 (2)</t>
         </is>
       </c>
       <c r="K39" s="313" t="n"/>
@@ -12197,7 +12205,7 @@
       <c r="A40" s="312" t="inlineStr"/>
       <c r="B40" s="312" t="inlineStr">
         <is>
-          <t>FACED 伪迹清洗</t>
+          <t>每受试者归一化 + raw</t>
         </is>
       </c>
       <c r="C40" s="313" t="n"/>
@@ -12209,7 +12217,7 @@
       <c r="I40" s="313" t="n"/>
       <c r="J40" s="313" t="inlineStr">
         <is>
-          <t>0.1346±0.0157 (3)</t>
+          <t>0.1579±0.0034 (3)</t>
         </is>
       </c>
       <c r="K40" s="313" t="n"/>
@@ -12219,7 +12227,7 @@
       <c r="A41" s="312" t="inlineStr"/>
       <c r="B41" s="312" t="inlineStr">
         <is>
-          <t>lr 1e-3</t>
+          <t>每受试者归一化 + raw + attn 头</t>
         </is>
       </c>
       <c r="C41" s="313" t="n"/>
@@ -12228,24 +12236,20 @@
       <c r="F41" s="313" t="n"/>
       <c r="G41" s="313" t="n"/>
       <c r="H41" s="313" t="n"/>
-      <c r="I41" s="313" t="inlineStr">
-        <is>
-          <t>0.2498±0.0077 (3)</t>
-        </is>
-      </c>
-      <c r="J41" s="313" t="n"/>
-      <c r="K41" s="313" t="inlineStr">
-        <is>
-          <t>0.3094±0.0345 (3)</t>
-        </is>
-      </c>
+      <c r="I41" s="313" t="n"/>
+      <c r="J41" s="313" t="inlineStr">
+        <is>
+          <t>0.1513±0.0012 (3)</t>
+        </is>
+      </c>
+      <c r="K41" s="313" t="n"/>
       <c r="L41" s="313" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="312" t="inlineStr"/>
       <c r="B42" s="312" t="inlineStr">
         <is>
-          <t>lr 3e-4</t>
+          <t>FACED 伪迹清洗</t>
         </is>
       </c>
       <c r="C42" s="313" t="n"/>
@@ -12254,155 +12258,203 @@
       <c r="F42" s="313" t="n"/>
       <c r="G42" s="313" t="n"/>
       <c r="H42" s="313" t="n"/>
-      <c r="I42" s="313" t="inlineStr">
-        <is>
-          <t>0.2623±0.0042 (3)</t>
-        </is>
-      </c>
-      <c r="J42" s="313" t="n"/>
-      <c r="K42" s="313" t="inlineStr">
-        <is>
-          <t>0.3495±0.0039 (3)</t>
-        </is>
-      </c>
+      <c r="I42" s="313" t="n"/>
+      <c r="J42" s="313" t="inlineStr">
+        <is>
+          <t>0.1346±0.0157 (3)</t>
+        </is>
+      </c>
+      <c r="K42" s="313" t="n"/>
       <c r="L42" s="313" t="n"/>
     </row>
     <row r="43">
-      <c r="A43" s="311" t="inlineStr">
-        <is>
-          <t>早期 pilot</t>
-        </is>
-      </c>
+      <c r="A43" s="312" t="inlineStr"/>
       <c r="B43" s="312" t="inlineStr">
         <is>
-          <t>冻结前端 pilot</t>
+          <t>lr 1e-3</t>
         </is>
       </c>
       <c r="C43" s="313" t="n"/>
-      <c r="D43" s="313" t="inlineStr">
-        <is>
-          <t>0.6272±0.0099 (3)</t>
-        </is>
-      </c>
+      <c r="D43" s="313" t="n"/>
       <c r="E43" s="313" t="n"/>
       <c r="F43" s="313" t="n"/>
       <c r="G43" s="313" t="n"/>
       <c r="H43" s="313" t="n"/>
-      <c r="I43" s="313" t="n"/>
+      <c r="I43" s="313" t="inlineStr">
+        <is>
+          <t>0.2498±0.0077 (3)</t>
+        </is>
+      </c>
       <c r="J43" s="313" t="n"/>
-      <c r="K43" s="313" t="n"/>
+      <c r="K43" s="313" t="inlineStr">
+        <is>
+          <t>0.3094±0.0345 (3)</t>
+        </is>
+      </c>
       <c r="L43" s="313" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="312" t="inlineStr"/>
       <c r="B44" s="312" t="inlineStr">
         <is>
-          <t>未滤波 pilot</t>
+          <t>lr 3e-4</t>
         </is>
       </c>
       <c r="C44" s="313" t="n"/>
-      <c r="D44" s="313" t="inlineStr">
-        <is>
-          <t>0.6209±0.0503 (3)</t>
-        </is>
-      </c>
+      <c r="D44" s="313" t="n"/>
       <c r="E44" s="313" t="n"/>
       <c r="F44" s="313" t="n"/>
       <c r="G44" s="313" t="n"/>
       <c r="H44" s="313" t="n"/>
-      <c r="I44" s="313" t="n"/>
+      <c r="I44" s="313" t="inlineStr">
+        <is>
+          <t>0.2623±0.0042 (3)</t>
+        </is>
+      </c>
       <c r="J44" s="313" t="n"/>
-      <c r="K44" s="313" t="n"/>
+      <c r="K44" s="313" t="inlineStr">
+        <is>
+          <t>0.3495±0.0039 (3)</t>
+        </is>
+      </c>
       <c r="L44" s="313" t="n"/>
     </row>
+    <row r="45">
+      <c r="A45" s="311" t="inlineStr">
+        <is>
+          <t>早期 pilot</t>
+        </is>
+      </c>
+      <c r="B45" s="312" t="inlineStr">
+        <is>
+          <t>冻结前端 pilot</t>
+        </is>
+      </c>
+      <c r="C45" s="313" t="n"/>
+      <c r="D45" s="313" t="inlineStr">
+        <is>
+          <t>0.6272±0.0099 (3)</t>
+        </is>
+      </c>
+      <c r="E45" s="313" t="n"/>
+      <c r="F45" s="313" t="n"/>
+      <c r="G45" s="313" t="n"/>
+      <c r="H45" s="313" t="n"/>
+      <c r="I45" s="313" t="n"/>
+      <c r="J45" s="313" t="n"/>
+      <c r="K45" s="313" t="n"/>
+      <c r="L45" s="313" t="n"/>
+    </row>
     <row r="46">
-      <c r="A46" s="316" t="inlineStr">
+      <c r="A46" s="312" t="inlineStr"/>
+      <c r="B46" s="312" t="inlineStr">
+        <is>
+          <t>未滤波 pilot</t>
+        </is>
+      </c>
+      <c r="C46" s="313" t="n"/>
+      <c r="D46" s="313" t="inlineStr">
+        <is>
+          <t>0.6209±0.0503 (3)</t>
+        </is>
+      </c>
+      <c r="E46" s="313" t="n"/>
+      <c r="F46" s="313" t="n"/>
+      <c r="G46" s="313" t="n"/>
+      <c r="H46" s="313" t="n"/>
+      <c r="I46" s="313" t="n"/>
+      <c r="J46" s="313" t="n"/>
+      <c r="K46" s="313" t="n"/>
+      <c r="L46" s="313" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="316" t="inlineStr">
         <is>
           <t>样本量消融</t>
         </is>
       </c>
-      <c r="B46" s="317" t="inlineStr">
+      <c r="B48" s="317" t="inlineStr">
         <is>
           <t>TUEV 训练集降采样(kappa) —— 检验等级三是否只是样本量问题</t>
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="B47" s="309" t="inlineStr">
+    <row r="49">
+      <c r="B49" s="309" t="inlineStr">
         <is>
           <t>模型</t>
         </is>
       </c>
-      <c r="C47" s="310" t="inlineStr">
+      <c r="C49" s="310" t="inlineStr">
         <is>
           <t>n=2160</t>
         </is>
       </c>
-      <c r="D47" s="310" t="inlineStr">
+      <c r="D49" s="310" t="inlineStr">
         <is>
           <t>n=6720</t>
         </is>
       </c>
-      <c r="E47" s="310" t="inlineStr">
+      <c r="E49" s="310" t="inlineStr">
         <is>
           <t>n=20000</t>
         </is>
       </c>
-      <c r="F47" s="310" t="inlineStr">
+      <c r="F49" s="310" t="inlineStr">
         <is>
           <t>全量 68445</t>
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="B48" s="312" t="inlineStr">
+    <row r="50">
+      <c r="B50" s="312" t="inlineStr">
         <is>
           <t>PACLock v2</t>
         </is>
       </c>
-      <c r="C48" s="315" t="inlineStr">
+      <c r="C50" s="315" t="inlineStr">
         <is>
           <t>0.6523±0.0000 (1)</t>
         </is>
       </c>
-      <c r="D48" s="315" t="inlineStr">
+      <c r="D50" s="315" t="inlineStr">
         <is>
           <t>0.7098±0.0000 (1)</t>
         </is>
       </c>
-      <c r="E48" s="315" t="inlineStr">
+      <c r="E50" s="315" t="inlineStr">
         <is>
           <t>0.6767±0.0000 (1)</t>
         </is>
       </c>
-      <c r="F48" s="313" t="inlineStr">
+      <c r="F50" s="313" t="inlineStr">
         <is>
           <t>0.7076±0.0311 (3)</t>
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="B49" s="312" t="inlineStr">
+    <row r="51">
+      <c r="B51" s="312" t="inlineStr">
         <is>
           <t>SPaRCNet</t>
         </is>
       </c>
-      <c r="C49" s="315" t="inlineStr">
+      <c r="C51" s="315" t="inlineStr">
         <is>
           <t>0.4917±0.0000 (1)</t>
         </is>
       </c>
-      <c r="D49" s="315" t="inlineStr">
+      <c r="D51" s="315" t="inlineStr">
         <is>
           <t>0.5532±0.0000 (1)</t>
         </is>
       </c>
-      <c r="E49" s="315" t="inlineStr">
+      <c r="E51" s="315" t="inlineStr">
         <is>
           <t>0.3642±0.0000 (1)</t>
         </is>
       </c>
-      <c r="F49" s="313" t="inlineStr">
+      <c r="F51" s="313" t="inlineStr">
         <is>
           <t>0.4885±0.0279 (3)</t>
         </is>

--- a/results/PACLock_baseline_matrix_filled.xlsx
+++ b/results/PACLock_baseline_matrix_filled.xlsx
@@ -10966,7 +10966,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L51"/>
+  <dimension ref="A1:L53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" style="220" min="1" max="1"/>
@@ -11465,52 +11465,32 @@
       <c r="A16" s="312" t="inlineStr"/>
       <c r="B16" s="312" t="inlineStr">
         <is>
-          <t>rotation(耦合只旋转不缩放)</t>
-        </is>
-      </c>
-      <c r="C16" s="315" t="inlineStr">
-        <is>
-          <t>0.8806±0.0000 (1)</t>
-        </is>
-      </c>
-      <c r="D16" s="313" t="inlineStr">
-        <is>
-          <t>0.7328±0.0161 (3)</t>
+          <t>fused:行内融合 blend(β 零初始化)</t>
+        </is>
+      </c>
+      <c r="C16" s="313" t="n"/>
+      <c r="D16" s="315" t="inlineStr">
+        <is>
+          <t>0.5493±0.0000 (1)</t>
         </is>
       </c>
       <c r="E16" s="315" t="inlineStr">
         <is>
-          <t>0.6884±0.0000 (1)</t>
+          <t>0.5643±0.0000 (1)</t>
         </is>
       </c>
       <c r="F16" s="315" t="inlineStr">
         <is>
-          <t>0.5100±0.0000 (1)</t>
-        </is>
-      </c>
-      <c r="G16" s="315" t="inlineStr">
-        <is>
-          <t>0.6449±0.0000 (1)</t>
-        </is>
-      </c>
-      <c r="H16" s="315" t="inlineStr">
-        <is>
-          <t>0.7104±0.0000 (1)</t>
-        </is>
-      </c>
-      <c r="I16" s="315" t="inlineStr">
-        <is>
-          <t>0.2916±0.0063 (2)</t>
-        </is>
-      </c>
-      <c r="J16" s="315" t="inlineStr">
-        <is>
-          <t>0.1514±0.0000 (1)</t>
-        </is>
-      </c>
-      <c r="K16" s="313" t="inlineStr">
-        <is>
-          <t>0.3708±0.0092 (3)</t>
+          <t>0.7194±0.0000 (1)</t>
+        </is>
+      </c>
+      <c r="G16" s="313" t="n"/>
+      <c r="H16" s="313" t="n"/>
+      <c r="I16" s="313" t="n"/>
+      <c r="J16" s="313" t="n"/>
+      <c r="K16" s="315" t="inlineStr">
+        <is>
+          <t>0.4483±0.0000 (1)</t>
         </is>
       </c>
       <c r="L16" s="313" t="n"/>
@@ -11519,52 +11499,76 @@
       <c r="A17" s="312" t="inlineStr"/>
       <c r="B17" s="312" t="inlineStr">
         <is>
-          <t>rotation(跑在 PAC 协议数据上,与上行不可比)</t>
+          <t>fused:行内融合 gated(内容门)</t>
         </is>
       </c>
       <c r="C17" s="313" t="n"/>
-      <c r="D17" s="313" t="n"/>
-      <c r="E17" s="313" t="n"/>
-      <c r="F17" s="313" t="n"/>
+      <c r="D17" s="315" t="inlineStr">
+        <is>
+          <t>0.5879±0.0000 (1)</t>
+        </is>
+      </c>
+      <c r="E17" s="315" t="inlineStr">
+        <is>
+          <t>0.6950±0.0000 (1)</t>
+        </is>
+      </c>
+      <c r="F17" s="315" t="inlineStr">
+        <is>
+          <t>0.7441±0.0000 (1)</t>
+        </is>
+      </c>
       <c r="G17" s="313" t="n"/>
       <c r="H17" s="313" t="n"/>
       <c r="I17" s="313" t="n"/>
-      <c r="J17" s="315" t="inlineStr">
-        <is>
-          <t>0.1098±0.0000 (1)</t>
-        </is>
-      </c>
+      <c r="J17" s="313" t="n"/>
       <c r="K17" s="315" t="inlineStr">
         <is>
-          <t>0.2724±0.0000 (1)</t>
-        </is>
-      </c>
-      <c r="L17" s="315" t="inlineStr">
-        <is>
-          <t>0.5568±0.0000 (1)</t>
-        </is>
-      </c>
+          <t>0.4082±0.0000 (1)</t>
+        </is>
+      </c>
+      <c r="L17" s="313" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="312" t="inlineStr"/>
       <c r="B18" s="312" t="inlineStr">
         <is>
-          <t>spatial 头(保留电极身份)</t>
-        </is>
-      </c>
-      <c r="C18" s="313" t="n"/>
-      <c r="D18" s="315" t="inlineStr">
-        <is>
-          <t>0.6520±0.0000 (1)</t>
-        </is>
-      </c>
-      <c r="E18" s="313" t="n"/>
-      <c r="F18" s="313" t="n"/>
-      <c r="G18" s="313" t="n"/>
-      <c r="H18" s="313" t="n"/>
-      <c r="I18" s="313" t="inlineStr">
-        <is>
-          <t>0.3535±0.0047 (3)</t>
+          <t>rotation(耦合只旋转不缩放)</t>
+        </is>
+      </c>
+      <c r="C18" s="315" t="inlineStr">
+        <is>
+          <t>0.8806±0.0000 (1)</t>
+        </is>
+      </c>
+      <c r="D18" s="313" t="inlineStr">
+        <is>
+          <t>0.7328±0.0161 (3)</t>
+        </is>
+      </c>
+      <c r="E18" s="315" t="inlineStr">
+        <is>
+          <t>0.6884±0.0000 (1)</t>
+        </is>
+      </c>
+      <c r="F18" s="315" t="inlineStr">
+        <is>
+          <t>0.5100±0.0000 (1)</t>
+        </is>
+      </c>
+      <c r="G18" s="315" t="inlineStr">
+        <is>
+          <t>0.6449±0.0000 (1)</t>
+        </is>
+      </c>
+      <c r="H18" s="315" t="inlineStr">
+        <is>
+          <t>0.7104±0.0000 (1)</t>
+        </is>
+      </c>
+      <c r="I18" s="315" t="inlineStr">
+        <is>
+          <t>0.2916±0.0063 (2)</t>
         </is>
       </c>
       <c r="J18" s="315" t="inlineStr">
@@ -11574,7 +11578,7 @@
       </c>
       <c r="K18" s="313" t="inlineStr">
         <is>
-          <t>0.4317±0.0153 (3)</t>
+          <t>0.3708±0.0092 (3)</t>
         </is>
       </c>
       <c r="L18" s="313" t="n"/>
@@ -11583,7 +11587,7 @@
       <c r="A19" s="312" t="inlineStr"/>
       <c r="B19" s="312" t="inlineStr">
         <is>
-          <t>rotation + spatial 头</t>
+          <t>rotation(跑在 PAC 协议数据上,与上行不可比)</t>
         </is>
       </c>
       <c r="C19" s="313" t="n"/>
@@ -11592,73 +11596,53 @@
       <c r="F19" s="313" t="n"/>
       <c r="G19" s="313" t="n"/>
       <c r="H19" s="313" t="n"/>
-      <c r="I19" s="315" t="inlineStr">
-        <is>
-          <t>0.3299±0.0000 (1)</t>
-        </is>
-      </c>
-      <c r="J19" s="313" t="n"/>
+      <c r="I19" s="313" t="n"/>
+      <c r="J19" s="315" t="inlineStr">
+        <is>
+          <t>0.1098±0.0000 (1)</t>
+        </is>
+      </c>
       <c r="K19" s="315" t="inlineStr">
         <is>
-          <t>0.4344±0.0000 (1)</t>
-        </is>
-      </c>
-      <c r="L19" s="313" t="n"/>
+          <t>0.2724±0.0000 (1)</t>
+        </is>
+      </c>
+      <c r="L19" s="315" t="inlineStr">
+        <is>
+          <t>0.5568±0.0000 (1)</t>
+        </is>
+      </c>
     </row>
     <row r="20">
-      <c r="A20" s="311" t="inlineStr">
-        <is>
-          <t>预训练</t>
-        </is>
-      </c>
+      <c r="A20" s="312" t="inlineStr"/>
       <c r="B20" s="312" t="inlineStr">
         <is>
-          <t>预训练 base(60k)</t>
-        </is>
-      </c>
-      <c r="C20" s="313" t="inlineStr">
-        <is>
-          <t>0.8841±0.0043 (3)</t>
-        </is>
-      </c>
-      <c r="D20" s="313" t="inlineStr">
-        <is>
-          <t>0.6730±0.0116 (3)</t>
-        </is>
-      </c>
-      <c r="E20" s="313" t="inlineStr">
-        <is>
-          <t>0.6398±0.0615 (3)</t>
-        </is>
-      </c>
-      <c r="F20" s="313" t="inlineStr">
-        <is>
-          <t>0.6830±0.0228 (3)</t>
-        </is>
-      </c>
-      <c r="G20" s="313" t="inlineStr">
-        <is>
-          <t>0.6651±0.0109 (3)</t>
-        </is>
-      </c>
-      <c r="H20" s="313" t="inlineStr">
-        <is>
-          <t>0.6934±0.0032 (3)</t>
-        </is>
-      </c>
+          <t>spatial 头(保留电极身份)</t>
+        </is>
+      </c>
+      <c r="C20" s="313" t="n"/>
+      <c r="D20" s="315" t="inlineStr">
+        <is>
+          <t>0.6520±0.0000 (1)</t>
+        </is>
+      </c>
+      <c r="E20" s="313" t="n"/>
+      <c r="F20" s="313" t="n"/>
+      <c r="G20" s="313" t="n"/>
+      <c r="H20" s="313" t="n"/>
       <c r="I20" s="313" t="inlineStr">
         <is>
-          <t>0.3059±0.0262 (3)</t>
-        </is>
-      </c>
-      <c r="J20" s="313" t="inlineStr">
-        <is>
-          <t>0.1540±0.0202 (3)</t>
+          <t>0.3535±0.0047 (3)</t>
+        </is>
+      </c>
+      <c r="J20" s="315" t="inlineStr">
+        <is>
+          <t>0.1514±0.0000 (1)</t>
         </is>
       </c>
       <c r="K20" s="313" t="inlineStr">
         <is>
-          <t>0.3652±0.0083 (3)</t>
+          <t>0.4317±0.0153 (3)</t>
         </is>
       </c>
       <c r="L20" s="313" t="n"/>
@@ -11667,90 +11651,82 @@
       <c r="A21" s="312" t="inlineStr"/>
       <c r="B21" s="312" t="inlineStr">
         <is>
-          <t>预训练 large(60k)</t>
-        </is>
-      </c>
-      <c r="C21" s="313" t="inlineStr">
-        <is>
-          <t>0.8869±0.0069 (3)</t>
-        </is>
-      </c>
-      <c r="D21" s="313" t="inlineStr">
-        <is>
-          <t>0.6523±0.0302 (3)</t>
-        </is>
-      </c>
-      <c r="E21" s="313" t="inlineStr">
-        <is>
-          <t>0.6289±0.0297 (3)</t>
-        </is>
-      </c>
-      <c r="F21" s="313" t="inlineStr">
-        <is>
-          <t>0.6162±0.0467 (3)</t>
-        </is>
-      </c>
-      <c r="G21" s="313" t="inlineStr">
-        <is>
-          <t>0.6641±0.0044 (3)</t>
-        </is>
-      </c>
-      <c r="H21" s="313" t="inlineStr">
-        <is>
-          <t>0.6996±0.0153 (3)</t>
-        </is>
-      </c>
-      <c r="I21" s="313" t="inlineStr">
-        <is>
-          <t>0.3140±0.0094 (3)</t>
-        </is>
-      </c>
-      <c r="J21" s="313" t="inlineStr">
-        <is>
-          <t>0.1640±0.0155 (3)</t>
-        </is>
-      </c>
-      <c r="K21" s="313" t="inlineStr">
-        <is>
-          <t>0.4122±0.0166 (3)</t>
+          <t>rotation + spatial 头</t>
+        </is>
+      </c>
+      <c r="C21" s="313" t="n"/>
+      <c r="D21" s="313" t="n"/>
+      <c r="E21" s="313" t="n"/>
+      <c r="F21" s="313" t="n"/>
+      <c r="G21" s="313" t="n"/>
+      <c r="H21" s="313" t="n"/>
+      <c r="I21" s="315" t="inlineStr">
+        <is>
+          <t>0.3299±0.0000 (1)</t>
+        </is>
+      </c>
+      <c r="J21" s="313" t="n"/>
+      <c r="K21" s="315" t="inlineStr">
+        <is>
+          <t>0.4344±0.0000 (1)</t>
         </is>
       </c>
       <c r="L21" s="313" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="312" t="inlineStr"/>
+      <c r="A22" s="311" t="inlineStr">
+        <is>
+          <t>预训练</t>
+        </is>
+      </c>
       <c r="B22" s="312" t="inlineStr">
         <is>
-          <t>raw tokenizer 预训练 large(60k)</t>
-        </is>
-      </c>
-      <c r="C22" s="313" t="n"/>
-      <c r="D22" s="313" t="n"/>
-      <c r="E22" s="315" t="inlineStr">
-        <is>
-          <t>0.5460±0.0000 (1)</t>
-        </is>
-      </c>
-      <c r="F22" s="315" t="inlineStr">
-        <is>
-          <t>0.6279±0.0000 (1)</t>
-        </is>
-      </c>
-      <c r="G22" s="313" t="n"/>
-      <c r="H22" s="313" t="n"/>
+          <t>预训练 base(60k)</t>
+        </is>
+      </c>
+      <c r="C22" s="313" t="inlineStr">
+        <is>
+          <t>0.8841±0.0043 (3)</t>
+        </is>
+      </c>
+      <c r="D22" s="313" t="inlineStr">
+        <is>
+          <t>0.6730±0.0116 (3)</t>
+        </is>
+      </c>
+      <c r="E22" s="313" t="inlineStr">
+        <is>
+          <t>0.6398±0.0615 (3)</t>
+        </is>
+      </c>
+      <c r="F22" s="313" t="inlineStr">
+        <is>
+          <t>0.6830±0.0228 (3)</t>
+        </is>
+      </c>
+      <c r="G22" s="313" t="inlineStr">
+        <is>
+          <t>0.6651±0.0109 (3)</t>
+        </is>
+      </c>
+      <c r="H22" s="313" t="inlineStr">
+        <is>
+          <t>0.6934±0.0032 (3)</t>
+        </is>
+      </c>
       <c r="I22" s="313" t="inlineStr">
         <is>
-          <t>0.3633±0.0349 (3)</t>
-        </is>
-      </c>
-      <c r="J22" s="315" t="inlineStr">
-        <is>
-          <t>0.1690±0.0018 (2)</t>
+          <t>0.3059±0.0262 (3)</t>
+        </is>
+      </c>
+      <c r="J22" s="313" t="inlineStr">
+        <is>
+          <t>0.1540±0.0202 (3)</t>
         </is>
       </c>
       <c r="K22" s="313" t="inlineStr">
         <is>
-          <t>0.4483±0.0031 (3)</t>
+          <t>0.3652±0.0083 (3)</t>
         </is>
       </c>
       <c r="L22" s="313" t="n"/>
@@ -11759,73 +11735,117 @@
       <c r="A23" s="312" t="inlineStr"/>
       <c r="B23" s="312" t="inlineStr">
         <is>
-          <t>预训练池剔除 TUSZ/CHB-MIT</t>
-        </is>
-      </c>
-      <c r="C23" s="313" t="n"/>
-      <c r="D23" s="313" t="n"/>
-      <c r="E23" s="315" t="inlineStr">
-        <is>
-          <t>0.6221±0.0000 (1)</t>
-        </is>
-      </c>
-      <c r="F23" s="315" t="inlineStr">
-        <is>
-          <t>0.6410±0.0000 (1)</t>
-        </is>
-      </c>
-      <c r="G23" s="313" t="n"/>
-      <c r="H23" s="313" t="n"/>
-      <c r="I23" s="313" t="n"/>
-      <c r="J23" s="313" t="n"/>
-      <c r="K23" s="313" t="n"/>
+          <t>预训练 large(60k)</t>
+        </is>
+      </c>
+      <c r="C23" s="313" t="inlineStr">
+        <is>
+          <t>0.8869±0.0069 (3)</t>
+        </is>
+      </c>
+      <c r="D23" s="313" t="inlineStr">
+        <is>
+          <t>0.6523±0.0302 (3)</t>
+        </is>
+      </c>
+      <c r="E23" s="313" t="inlineStr">
+        <is>
+          <t>0.6289±0.0297 (3)</t>
+        </is>
+      </c>
+      <c r="F23" s="313" t="inlineStr">
+        <is>
+          <t>0.6162±0.0467 (3)</t>
+        </is>
+      </c>
+      <c r="G23" s="313" t="inlineStr">
+        <is>
+          <t>0.6641±0.0044 (3)</t>
+        </is>
+      </c>
+      <c r="H23" s="313" t="inlineStr">
+        <is>
+          <t>0.6996±0.0153 (3)</t>
+        </is>
+      </c>
+      <c r="I23" s="313" t="inlineStr">
+        <is>
+          <t>0.3140±0.0094 (3)</t>
+        </is>
+      </c>
+      <c r="J23" s="313" t="inlineStr">
+        <is>
+          <t>0.1640±0.0155 (3)</t>
+        </is>
+      </c>
+      <c r="K23" s="313" t="inlineStr">
+        <is>
+          <t>0.4122±0.0166 (3)</t>
+        </is>
+      </c>
       <c r="L23" s="313" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="312" t="inlineStr"/>
       <c r="B24" s="312" t="inlineStr">
         <is>
-          <t>预训练 base,微调 patch_len=200</t>
+          <t>raw tokenizer 预训练 large(60k)</t>
         </is>
       </c>
       <c r="C24" s="313" t="n"/>
-      <c r="D24" s="313" t="inlineStr">
-        <is>
-          <t>0.6793±0.0109 (3)</t>
-        </is>
-      </c>
-      <c r="E24" s="313" t="n"/>
-      <c r="F24" s="313" t="n"/>
+      <c r="D24" s="313" t="n"/>
+      <c r="E24" s="315" t="inlineStr">
+        <is>
+          <t>0.5460±0.0000 (1)</t>
+        </is>
+      </c>
+      <c r="F24" s="315" t="inlineStr">
+        <is>
+          <t>0.6279±0.0000 (1)</t>
+        </is>
+      </c>
       <c r="G24" s="313" t="n"/>
       <c r="H24" s="313" t="n"/>
-      <c r="I24" s="313" t="n"/>
-      <c r="J24" s="313" t="n"/>
-      <c r="K24" s="313" t="n"/>
+      <c r="I24" s="313" t="inlineStr">
+        <is>
+          <t>0.3633±0.0349 (3)</t>
+        </is>
+      </c>
+      <c r="J24" s="315" t="inlineStr">
+        <is>
+          <t>0.1690±0.0018 (2)</t>
+        </is>
+      </c>
+      <c r="K24" s="313" t="inlineStr">
+        <is>
+          <t>0.4483±0.0031 (3)</t>
+        </is>
+      </c>
       <c r="L24" s="313" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="312" t="inlineStr"/>
       <c r="B25" s="312" t="inlineStr">
         <is>
-          <t>早期微调配方(6k checkpoint)</t>
+          <t>预训练池剔除 TUSZ/CHB-MIT</t>
         </is>
       </c>
       <c r="C25" s="313" t="n"/>
       <c r="D25" s="313" t="n"/>
-      <c r="E25" s="313" t="n"/>
-      <c r="F25" s="313" t="n"/>
+      <c r="E25" s="315" t="inlineStr">
+        <is>
+          <t>0.6221±0.0000 (1)</t>
+        </is>
+      </c>
+      <c r="F25" s="315" t="inlineStr">
+        <is>
+          <t>0.6410±0.0000 (1)</t>
+        </is>
+      </c>
       <c r="G25" s="313" t="n"/>
       <c r="H25" s="313" t="n"/>
-      <c r="I25" s="315" t="inlineStr">
-        <is>
-          <t>0.2690±0.0000 (1)</t>
-        </is>
-      </c>
-      <c r="J25" s="315" t="inlineStr">
-        <is>
-          <t>0.1279±0.0000 (1)</t>
-        </is>
-      </c>
+      <c r="I25" s="313" t="n"/>
+      <c r="J25" s="313" t="n"/>
       <c r="K25" s="313" t="n"/>
       <c r="L25" s="313" t="n"/>
     </row>
@@ -11833,25 +11853,21 @@
       <c r="A26" s="312" t="inlineStr"/>
       <c r="B26" s="312" t="inlineStr">
         <is>
-          <t>早期微调配方 v2(6k checkpoint)</t>
+          <t>预训练 base,微调 patch_len=200</t>
         </is>
       </c>
       <c r="C26" s="313" t="n"/>
-      <c r="D26" s="313" t="n"/>
+      <c r="D26" s="313" t="inlineStr">
+        <is>
+          <t>0.6793±0.0109 (3)</t>
+        </is>
+      </c>
       <c r="E26" s="313" t="n"/>
       <c r="F26" s="313" t="n"/>
       <c r="G26" s="313" t="n"/>
       <c r="H26" s="313" t="n"/>
-      <c r="I26" s="315" t="inlineStr">
-        <is>
-          <t>0.2622±0.0000 (1)</t>
-        </is>
-      </c>
-      <c r="J26" s="315" t="inlineStr">
-        <is>
-          <t>0.1408±0.0000 (1)</t>
-        </is>
-      </c>
+      <c r="I26" s="313" t="n"/>
+      <c r="J26" s="313" t="n"/>
       <c r="K26" s="313" t="n"/>
       <c r="L26" s="313" t="n"/>
     </row>
@@ -11859,7 +11875,7 @@
       <c r="A27" s="312" t="inlineStr"/>
       <c r="B27" s="312" t="inlineStr">
         <is>
-          <t>早期微调配方 large(6k checkpoint)</t>
+          <t>早期微调配方(6k checkpoint)</t>
         </is>
       </c>
       <c r="C27" s="313" t="n"/>
@@ -11870,26 +11886,22 @@
       <c r="H27" s="313" t="n"/>
       <c r="I27" s="315" t="inlineStr">
         <is>
-          <t>0.2716±0.0000 (1)</t>
+          <t>0.2690±0.0000 (1)</t>
         </is>
       </c>
       <c r="J27" s="315" t="inlineStr">
         <is>
-          <t>0.1381±0.0000 (1)</t>
+          <t>0.1279±0.0000 (1)</t>
         </is>
       </c>
       <c r="K27" s="313" t="n"/>
       <c r="L27" s="313" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="311" t="inlineStr">
-        <is>
-          <t>容量阶梯</t>
-        </is>
-      </c>
+      <c r="A28" s="312" t="inlineStr"/>
       <c r="B28" s="312" t="inlineStr">
         <is>
-          <t>raw,d_model 32</t>
+          <t>早期微调配方 v2(6k checkpoint)</t>
         </is>
       </c>
       <c r="C28" s="313" t="n"/>
@@ -11898,24 +11910,24 @@
       <c r="F28" s="313" t="n"/>
       <c r="G28" s="313" t="n"/>
       <c r="H28" s="313" t="n"/>
-      <c r="I28" s="313" t="inlineStr">
-        <is>
-          <t>0.2613±0.0100 (3)</t>
-        </is>
-      </c>
-      <c r="J28" s="313" t="n"/>
-      <c r="K28" s="313" t="inlineStr">
-        <is>
-          <t>0.2617±0.0019 (3)</t>
-        </is>
-      </c>
+      <c r="I28" s="315" t="inlineStr">
+        <is>
+          <t>0.2622±0.0000 (1)</t>
+        </is>
+      </c>
+      <c r="J28" s="315" t="inlineStr">
+        <is>
+          <t>0.1408±0.0000 (1)</t>
+        </is>
+      </c>
+      <c r="K28" s="313" t="n"/>
       <c r="L28" s="313" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="312" t="inlineStr"/>
       <c r="B29" s="312" t="inlineStr">
         <is>
-          <t>raw,d_model 64</t>
+          <t>早期微调配方 large(6k checkpoint)</t>
         </is>
       </c>
       <c r="C29" s="313" t="n"/>
@@ -11924,24 +11936,28 @@
       <c r="F29" s="313" t="n"/>
       <c r="G29" s="313" t="n"/>
       <c r="H29" s="313" t="n"/>
-      <c r="I29" s="313" t="inlineStr">
-        <is>
-          <t>0.3129±0.0121 (3)</t>
-        </is>
-      </c>
-      <c r="J29" s="313" t="n"/>
-      <c r="K29" s="313" t="inlineStr">
-        <is>
-          <t>0.2780±0.0100 (3)</t>
-        </is>
-      </c>
+      <c r="I29" s="315" t="inlineStr">
+        <is>
+          <t>0.2716±0.0000 (1)</t>
+        </is>
+      </c>
+      <c r="J29" s="315" t="inlineStr">
+        <is>
+          <t>0.1381±0.0000 (1)</t>
+        </is>
+      </c>
+      <c r="K29" s="313" t="n"/>
       <c r="L29" s="313" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="312" t="inlineStr"/>
+      <c r="A30" s="311" t="inlineStr">
+        <is>
+          <t>容量阶梯</t>
+        </is>
+      </c>
       <c r="B30" s="312" t="inlineStr">
         <is>
-          <t>raw,d_model 256</t>
+          <t>raw,d_model 32</t>
         </is>
       </c>
       <c r="C30" s="313" t="n"/>
@@ -11952,13 +11968,13 @@
       <c r="H30" s="313" t="n"/>
       <c r="I30" s="313" t="inlineStr">
         <is>
-          <t>0.4159±0.0529 (3)</t>
+          <t>0.2613±0.0100 (3)</t>
         </is>
       </c>
       <c r="J30" s="313" t="n"/>
       <c r="K30" s="313" t="inlineStr">
         <is>
-          <t>0.4437±0.0192 (3)</t>
+          <t>0.2617±0.0019 (3)</t>
         </is>
       </c>
       <c r="L30" s="313" t="n"/>
@@ -11967,7 +11983,7 @@
       <c r="A31" s="312" t="inlineStr"/>
       <c r="B31" s="312" t="inlineStr">
         <is>
-          <t>raw,加宽</t>
+          <t>raw,d_model 64</t>
         </is>
       </c>
       <c r="C31" s="313" t="n"/>
@@ -11978,13 +11994,13 @@
       <c r="H31" s="313" t="n"/>
       <c r="I31" s="313" t="inlineStr">
         <is>
-          <t>0.4093±0.0425 (3)</t>
+          <t>0.3129±0.0121 (3)</t>
         </is>
       </c>
       <c r="J31" s="313" t="n"/>
-      <c r="K31" s="315" t="inlineStr">
-        <is>
-          <t>0.4261±0.0085 (2)</t>
+      <c r="K31" s="313" t="inlineStr">
+        <is>
+          <t>0.2780±0.0100 (3)</t>
         </is>
       </c>
       <c r="L31" s="313" t="n"/>
@@ -11993,7 +12009,7 @@
       <c r="A32" s="312" t="inlineStr"/>
       <c r="B32" s="312" t="inlineStr">
         <is>
-          <t>raw,16 频带</t>
+          <t>raw,d_model 256</t>
         </is>
       </c>
       <c r="C32" s="313" t="n"/>
@@ -12004,13 +12020,13 @@
       <c r="H32" s="313" t="n"/>
       <c r="I32" s="313" t="inlineStr">
         <is>
-          <t>0.3781±0.0467 (3)</t>
+          <t>0.4159±0.0529 (3)</t>
         </is>
       </c>
       <c r="J32" s="313" t="n"/>
       <c r="K32" s="313" t="inlineStr">
         <is>
-          <t>0.4288±0.0090 (3)</t>
+          <t>0.4437±0.0192 (3)</t>
         </is>
       </c>
       <c r="L32" s="313" t="n"/>
@@ -12019,7 +12035,7 @@
       <c r="A33" s="312" t="inlineStr"/>
       <c r="B33" s="312" t="inlineStr">
         <is>
-          <t>raw,patch_len 100</t>
+          <t>raw,加宽</t>
         </is>
       </c>
       <c r="C33" s="313" t="n"/>
@@ -12030,13 +12046,13 @@
       <c r="H33" s="313" t="n"/>
       <c r="I33" s="313" t="inlineStr">
         <is>
-          <t>0.3508±0.0251 (3)</t>
+          <t>0.4093±0.0425 (3)</t>
         </is>
       </c>
       <c r="J33" s="313" t="n"/>
-      <c r="K33" s="313" t="inlineStr">
-        <is>
-          <t>0.4066±0.0221 (3)</t>
+      <c r="K33" s="315" t="inlineStr">
+        <is>
+          <t>0.4261±0.0085 (2)</t>
         </is>
       </c>
       <c r="L33" s="313" t="n"/>
@@ -12045,7 +12061,7 @@
       <c r="A34" s="312" t="inlineStr"/>
       <c r="B34" s="312" t="inlineStr">
         <is>
-          <t>raw,dropout 0.5</t>
+          <t>raw,16 频带</t>
         </is>
       </c>
       <c r="C34" s="313" t="n"/>
@@ -12056,13 +12072,13 @@
       <c r="H34" s="313" t="n"/>
       <c r="I34" s="313" t="inlineStr">
         <is>
-          <t>0.3409±0.0196 (3)</t>
+          <t>0.3781±0.0467 (3)</t>
         </is>
       </c>
       <c r="J34" s="313" t="n"/>
       <c r="K34" s="313" t="inlineStr">
         <is>
-          <t>0.4308±0.0139 (3)</t>
+          <t>0.4288±0.0090 (3)</t>
         </is>
       </c>
       <c r="L34" s="313" t="n"/>
@@ -12071,7 +12087,7 @@
       <c r="A35" s="312" t="inlineStr"/>
       <c r="B35" s="312" t="inlineStr">
         <is>
-          <t>raw,attn 头</t>
+          <t>raw,patch_len 100</t>
         </is>
       </c>
       <c r="C35" s="313" t="n"/>
@@ -12082,26 +12098,22 @@
       <c r="H35" s="313" t="n"/>
       <c r="I35" s="313" t="inlineStr">
         <is>
-          <t>0.3524±0.0467 (3)</t>
+          <t>0.3508±0.0251 (3)</t>
         </is>
       </c>
       <c r="J35" s="313" t="n"/>
       <c r="K35" s="313" t="inlineStr">
         <is>
-          <t>0.4545±0.0054 (3)</t>
+          <t>0.4066±0.0221 (3)</t>
         </is>
       </c>
       <c r="L35" s="313" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="311" t="inlineStr">
-        <is>
-          <t>已否决</t>
-        </is>
-      </c>
+      <c r="A36" s="312" t="inlineStr"/>
       <c r="B36" s="312" t="inlineStr">
         <is>
-          <t>spatial_pe: xyz(蒙太奇坐标)</t>
+          <t>raw,dropout 0.5</t>
         </is>
       </c>
       <c r="C36" s="313" t="n"/>
@@ -12109,20 +12121,16 @@
       <c r="E36" s="313" t="n"/>
       <c r="F36" s="313" t="n"/>
       <c r="G36" s="313" t="n"/>
-      <c r="H36" s="313" t="inlineStr">
-        <is>
-          <t>0.6954±0.0167 (3)</t>
-        </is>
-      </c>
+      <c r="H36" s="313" t="n"/>
       <c r="I36" s="313" t="inlineStr">
         <is>
-          <t>0.2478±0.0053 (3)</t>
+          <t>0.3409±0.0196 (3)</t>
         </is>
       </c>
       <c r="J36" s="313" t="n"/>
       <c r="K36" s="313" t="inlineStr">
         <is>
-          <t>0.3338±0.0027 (3)</t>
+          <t>0.4308±0.0139 (3)</t>
         </is>
       </c>
       <c r="L36" s="313" t="n"/>
@@ -12131,7 +12139,7 @@
       <c r="A37" s="312" t="inlineStr"/>
       <c r="B37" s="312" t="inlineStr">
         <is>
-          <t>每窗口归一化</t>
+          <t>raw,attn 头</t>
         </is>
       </c>
       <c r="C37" s="313" t="n"/>
@@ -12142,22 +12150,26 @@
       <c r="H37" s="313" t="n"/>
       <c r="I37" s="313" t="inlineStr">
         <is>
-          <t>0.2532±0.0155 (3)</t>
+          <t>0.3524±0.0467 (3)</t>
         </is>
       </c>
       <c r="J37" s="313" t="n"/>
       <c r="K37" s="313" t="inlineStr">
         <is>
-          <t>0.3050±0.0438 (3)</t>
+          <t>0.4545±0.0054 (3)</t>
         </is>
       </c>
       <c r="L37" s="313" t="n"/>
     </row>
     <row r="38">
-      <c r="A38" s="312" t="inlineStr"/>
+      <c r="A38" s="311" t="inlineStr">
+        <is>
+          <t>已否决</t>
+        </is>
+      </c>
       <c r="B38" s="312" t="inlineStr">
         <is>
-          <t>每窗口归一化 + raw</t>
+          <t>spatial_pe: xyz(蒙太奇坐标)</t>
         </is>
       </c>
       <c r="C38" s="313" t="n"/>
@@ -12165,16 +12177,20 @@
       <c r="E38" s="313" t="n"/>
       <c r="F38" s="313" t="n"/>
       <c r="G38" s="313" t="n"/>
-      <c r="H38" s="313" t="n"/>
-      <c r="I38" s="315" t="inlineStr">
-        <is>
-          <t>0.2896±0.0146 (2)</t>
+      <c r="H38" s="313" t="inlineStr">
+        <is>
+          <t>0.6954±0.0167 (3)</t>
+        </is>
+      </c>
+      <c r="I38" s="313" t="inlineStr">
+        <is>
+          <t>0.2478±0.0053 (3)</t>
         </is>
       </c>
       <c r="J38" s="313" t="n"/>
-      <c r="K38" s="315" t="inlineStr">
-        <is>
-          <t>0.2992±0.0139 (2)</t>
+      <c r="K38" s="313" t="inlineStr">
+        <is>
+          <t>0.3338±0.0027 (3)</t>
         </is>
       </c>
       <c r="L38" s="313" t="n"/>
@@ -12183,7 +12199,7 @@
       <c r="A39" s="312" t="inlineStr"/>
       <c r="B39" s="312" t="inlineStr">
         <is>
-          <t>每受试者归一化</t>
+          <t>每窗口归一化</t>
         </is>
       </c>
       <c r="C39" s="313" t="n"/>
@@ -12192,20 +12208,24 @@
       <c r="F39" s="313" t="n"/>
       <c r="G39" s="313" t="n"/>
       <c r="H39" s="313" t="n"/>
-      <c r="I39" s="313" t="n"/>
-      <c r="J39" s="315" t="inlineStr">
-        <is>
-          <t>0.1328±0.0007 (2)</t>
-        </is>
-      </c>
-      <c r="K39" s="313" t="n"/>
+      <c r="I39" s="313" t="inlineStr">
+        <is>
+          <t>0.2532±0.0155 (3)</t>
+        </is>
+      </c>
+      <c r="J39" s="313" t="n"/>
+      <c r="K39" s="313" t="inlineStr">
+        <is>
+          <t>0.3050±0.0438 (3)</t>
+        </is>
+      </c>
       <c r="L39" s="313" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="312" t="inlineStr"/>
       <c r="B40" s="312" t="inlineStr">
         <is>
-          <t>每受试者归一化 + raw</t>
+          <t>每窗口归一化 + raw</t>
         </is>
       </c>
       <c r="C40" s="313" t="n"/>
@@ -12214,20 +12234,24 @@
       <c r="F40" s="313" t="n"/>
       <c r="G40" s="313" t="n"/>
       <c r="H40" s="313" t="n"/>
-      <c r="I40" s="313" t="n"/>
-      <c r="J40" s="313" t="inlineStr">
-        <is>
-          <t>0.1579±0.0034 (3)</t>
-        </is>
-      </c>
-      <c r="K40" s="313" t="n"/>
+      <c r="I40" s="315" t="inlineStr">
+        <is>
+          <t>0.2896±0.0146 (2)</t>
+        </is>
+      </c>
+      <c r="J40" s="313" t="n"/>
+      <c r="K40" s="315" t="inlineStr">
+        <is>
+          <t>0.2992±0.0139 (2)</t>
+        </is>
+      </c>
       <c r="L40" s="313" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="312" t="inlineStr"/>
       <c r="B41" s="312" t="inlineStr">
         <is>
-          <t>每受试者归一化 + raw + attn 头</t>
+          <t>每受试者归一化</t>
         </is>
       </c>
       <c r="C41" s="313" t="n"/>
@@ -12237,9 +12261,9 @@
       <c r="G41" s="313" t="n"/>
       <c r="H41" s="313" t="n"/>
       <c r="I41" s="313" t="n"/>
-      <c r="J41" s="313" t="inlineStr">
-        <is>
-          <t>0.1513±0.0012 (3)</t>
+      <c r="J41" s="315" t="inlineStr">
+        <is>
+          <t>0.1328±0.0007 (2)</t>
         </is>
       </c>
       <c r="K41" s="313" t="n"/>
@@ -12249,7 +12273,7 @@
       <c r="A42" s="312" t="inlineStr"/>
       <c r="B42" s="312" t="inlineStr">
         <is>
-          <t>FACED 伪迹清洗</t>
+          <t>每受试者归一化 + raw</t>
         </is>
       </c>
       <c r="C42" s="313" t="n"/>
@@ -12261,7 +12285,7 @@
       <c r="I42" s="313" t="n"/>
       <c r="J42" s="313" t="inlineStr">
         <is>
-          <t>0.1346±0.0157 (3)</t>
+          <t>0.1579±0.0034 (3)</t>
         </is>
       </c>
       <c r="K42" s="313" t="n"/>
@@ -12271,7 +12295,7 @@
       <c r="A43" s="312" t="inlineStr"/>
       <c r="B43" s="312" t="inlineStr">
         <is>
-          <t>lr 1e-3</t>
+          <t>每受试者归一化 + raw + attn 头</t>
         </is>
       </c>
       <c r="C43" s="313" t="n"/>
@@ -12280,24 +12304,20 @@
       <c r="F43" s="313" t="n"/>
       <c r="G43" s="313" t="n"/>
       <c r="H43" s="313" t="n"/>
-      <c r="I43" s="313" t="inlineStr">
-        <is>
-          <t>0.2498±0.0077 (3)</t>
-        </is>
-      </c>
-      <c r="J43" s="313" t="n"/>
-      <c r="K43" s="313" t="inlineStr">
-        <is>
-          <t>0.3094±0.0345 (3)</t>
-        </is>
-      </c>
+      <c r="I43" s="313" t="n"/>
+      <c r="J43" s="313" t="inlineStr">
+        <is>
+          <t>0.1513±0.0012 (3)</t>
+        </is>
+      </c>
+      <c r="K43" s="313" t="n"/>
       <c r="L43" s="313" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="312" t="inlineStr"/>
       <c r="B44" s="312" t="inlineStr">
         <is>
-          <t>lr 3e-4</t>
+          <t>FACED 伪迹清洗</t>
         </is>
       </c>
       <c r="C44" s="313" t="n"/>
@@ -12306,155 +12326,203 @@
       <c r="F44" s="313" t="n"/>
       <c r="G44" s="313" t="n"/>
       <c r="H44" s="313" t="n"/>
-      <c r="I44" s="313" t="inlineStr">
-        <is>
-          <t>0.2623±0.0042 (3)</t>
-        </is>
-      </c>
-      <c r="J44" s="313" t="n"/>
-      <c r="K44" s="313" t="inlineStr">
-        <is>
-          <t>0.3495±0.0039 (3)</t>
-        </is>
-      </c>
+      <c r="I44" s="313" t="n"/>
+      <c r="J44" s="313" t="inlineStr">
+        <is>
+          <t>0.1346±0.0157 (3)</t>
+        </is>
+      </c>
+      <c r="K44" s="313" t="n"/>
       <c r="L44" s="313" t="n"/>
     </row>
     <row r="45">
-      <c r="A45" s="311" t="inlineStr">
-        <is>
-          <t>早期 pilot</t>
-        </is>
-      </c>
+      <c r="A45" s="312" t="inlineStr"/>
       <c r="B45" s="312" t="inlineStr">
         <is>
-          <t>冻结前端 pilot</t>
+          <t>lr 1e-3</t>
         </is>
       </c>
       <c r="C45" s="313" t="n"/>
-      <c r="D45" s="313" t="inlineStr">
-        <is>
-          <t>0.6272±0.0099 (3)</t>
-        </is>
-      </c>
+      <c r="D45" s="313" t="n"/>
       <c r="E45" s="313" t="n"/>
       <c r="F45" s="313" t="n"/>
       <c r="G45" s="313" t="n"/>
       <c r="H45" s="313" t="n"/>
-      <c r="I45" s="313" t="n"/>
+      <c r="I45" s="313" t="inlineStr">
+        <is>
+          <t>0.2498±0.0077 (3)</t>
+        </is>
+      </c>
       <c r="J45" s="313" t="n"/>
-      <c r="K45" s="313" t="n"/>
+      <c r="K45" s="313" t="inlineStr">
+        <is>
+          <t>0.3094±0.0345 (3)</t>
+        </is>
+      </c>
       <c r="L45" s="313" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="312" t="inlineStr"/>
       <c r="B46" s="312" t="inlineStr">
         <is>
-          <t>未滤波 pilot</t>
+          <t>lr 3e-4</t>
         </is>
       </c>
       <c r="C46" s="313" t="n"/>
-      <c r="D46" s="313" t="inlineStr">
-        <is>
-          <t>0.6209±0.0503 (3)</t>
-        </is>
-      </c>
+      <c r="D46" s="313" t="n"/>
       <c r="E46" s="313" t="n"/>
       <c r="F46" s="313" t="n"/>
       <c r="G46" s="313" t="n"/>
       <c r="H46" s="313" t="n"/>
-      <c r="I46" s="313" t="n"/>
+      <c r="I46" s="313" t="inlineStr">
+        <is>
+          <t>0.2623±0.0042 (3)</t>
+        </is>
+      </c>
       <c r="J46" s="313" t="n"/>
-      <c r="K46" s="313" t="n"/>
+      <c r="K46" s="313" t="inlineStr">
+        <is>
+          <t>0.3495±0.0039 (3)</t>
+        </is>
+      </c>
       <c r="L46" s="313" t="n"/>
     </row>
+    <row r="47">
+      <c r="A47" s="311" t="inlineStr">
+        <is>
+          <t>早期 pilot</t>
+        </is>
+      </c>
+      <c r="B47" s="312" t="inlineStr">
+        <is>
+          <t>冻结前端 pilot</t>
+        </is>
+      </c>
+      <c r="C47" s="313" t="n"/>
+      <c r="D47" s="313" t="inlineStr">
+        <is>
+          <t>0.6272±0.0099 (3)</t>
+        </is>
+      </c>
+      <c r="E47" s="313" t="n"/>
+      <c r="F47" s="313" t="n"/>
+      <c r="G47" s="313" t="n"/>
+      <c r="H47" s="313" t="n"/>
+      <c r="I47" s="313" t="n"/>
+      <c r="J47" s="313" t="n"/>
+      <c r="K47" s="313" t="n"/>
+      <c r="L47" s="313" t="n"/>
+    </row>
     <row r="48">
-      <c r="A48" s="316" t="inlineStr">
+      <c r="A48" s="312" t="inlineStr"/>
+      <c r="B48" s="312" t="inlineStr">
+        <is>
+          <t>未滤波 pilot</t>
+        </is>
+      </c>
+      <c r="C48" s="313" t="n"/>
+      <c r="D48" s="313" t="inlineStr">
+        <is>
+          <t>0.6209±0.0503 (3)</t>
+        </is>
+      </c>
+      <c r="E48" s="313" t="n"/>
+      <c r="F48" s="313" t="n"/>
+      <c r="G48" s="313" t="n"/>
+      <c r="H48" s="313" t="n"/>
+      <c r="I48" s="313" t="n"/>
+      <c r="J48" s="313" t="n"/>
+      <c r="K48" s="313" t="n"/>
+      <c r="L48" s="313" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="316" t="inlineStr">
         <is>
           <t>样本量消融</t>
         </is>
       </c>
-      <c r="B48" s="317" t="inlineStr">
+      <c r="B50" s="317" t="inlineStr">
         <is>
           <t>TUEV 训练集降采样(kappa) —— 检验等级三是否只是样本量问题</t>
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="B49" s="309" t="inlineStr">
+    <row r="51">
+      <c r="B51" s="309" t="inlineStr">
         <is>
           <t>模型</t>
         </is>
       </c>
-      <c r="C49" s="310" t="inlineStr">
+      <c r="C51" s="310" t="inlineStr">
         <is>
           <t>n=2160</t>
         </is>
       </c>
-      <c r="D49" s="310" t="inlineStr">
+      <c r="D51" s="310" t="inlineStr">
         <is>
           <t>n=6720</t>
         </is>
       </c>
-      <c r="E49" s="310" t="inlineStr">
+      <c r="E51" s="310" t="inlineStr">
         <is>
           <t>n=20000</t>
         </is>
       </c>
-      <c r="F49" s="310" t="inlineStr">
+      <c r="F51" s="310" t="inlineStr">
         <is>
           <t>全量 68445</t>
         </is>
       </c>
     </row>
-    <row r="50">
-      <c r="B50" s="312" t="inlineStr">
+    <row r="52">
+      <c r="B52" s="312" t="inlineStr">
         <is>
           <t>PACLock v2</t>
         </is>
       </c>
-      <c r="C50" s="315" t="inlineStr">
+      <c r="C52" s="315" t="inlineStr">
         <is>
           <t>0.6523±0.0000 (1)</t>
         </is>
       </c>
-      <c r="D50" s="315" t="inlineStr">
+      <c r="D52" s="315" t="inlineStr">
         <is>
           <t>0.7098±0.0000 (1)</t>
         </is>
       </c>
-      <c r="E50" s="315" t="inlineStr">
+      <c r="E52" s="315" t="inlineStr">
         <is>
           <t>0.6767±0.0000 (1)</t>
         </is>
       </c>
-      <c r="F50" s="313" t="inlineStr">
+      <c r="F52" s="313" t="inlineStr">
         <is>
           <t>0.7076±0.0311 (3)</t>
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="B51" s="312" t="inlineStr">
+    <row r="53">
+      <c r="B53" s="312" t="inlineStr">
         <is>
           <t>SPaRCNet</t>
         </is>
       </c>
-      <c r="C51" s="315" t="inlineStr">
+      <c r="C53" s="315" t="inlineStr">
         <is>
           <t>0.4917±0.0000 (1)</t>
         </is>
       </c>
-      <c r="D51" s="315" t="inlineStr">
+      <c r="D53" s="315" t="inlineStr">
         <is>
           <t>0.5532±0.0000 (1)</t>
         </is>
       </c>
-      <c r="E51" s="315" t="inlineStr">
+      <c r="E53" s="315" t="inlineStr">
         <is>
           <t>0.3642±0.0000 (1)</t>
         </is>
       </c>
-      <c r="F51" s="313" t="inlineStr">
+      <c r="F53" s="313" t="inlineStr">
         <is>
           <t>0.4885±0.0279 (3)</t>
         </is>

--- a/results/PACLock_baseline_matrix_filled.xlsx
+++ b/results/PACLock_baseline_matrix_filled.xlsx
@@ -599,21 +599,21 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>D  对照（通用时序 FM；随机初始化同架构 —— 四道归因门第 4 门）</t>
+          <t>缓议：MOMENT 等通用时序 FM 对照 —— 不承重于 tokenizer 主张，留作 rebuttal 期选项</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>E  PACLock（scratch / 预训练 v2 / 冻结探针）</t>
+          <t>D  PACLock（scratch / 预训练 v2 / 冻结探针 vs 随机初始化探针 —— 四道门第 4 门）</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>F  参考值（灰）：无公开权重或异管线论文自报数，只作上下文</t>
+          <t>E  参考值（灰）：无公开权重或异管线论文自报数，只作上下文</t>
         </is>
       </c>
     </row>
@@ -690,7 +690,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G33"/>
+  <dimension ref="A1:G32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -972,70 +972,53 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>D 对照</t>
+          <t>D PACLock</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>MOMENT (通用时序 FM)</t>
-        </is>
-      </c>
-      <c r="G27" s="6" t="inlineStr">
-        <is>
-          <t>EEG 特异性对照</t>
+          <t>PACLock (duplex, scratch)</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="B28" t="inlineStr">
         <is>
-          <t>PACLock (随机初始化)</t>
+          <t>PACLock (duplex, 预训练 v2)</t>
         </is>
       </c>
       <c r="G28" s="6" t="inlineStr">
         <is>
-          <t>四道门第 4 门</t>
+          <t>band_norm_pac 目标</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>E PACLock</t>
-        </is>
-      </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>PACLock (duplex, scratch)</t>
+          <t>PACLock (冻结探针, v2)</t>
+        </is>
+      </c>
+      <c r="G29" s="6" t="inlineStr">
+        <is>
+          <t>patch_len 200；表征质量协议</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="B30" t="inlineStr">
         <is>
-          <t>PACLock (duplex, 预训练 v2)</t>
+          <t>PACLock (冻结探针, 随机初始化)</t>
         </is>
       </c>
       <c r="G30" s="6" t="inlineStr">
         <is>
-          <t>band_norm_pac 目标</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>PACLock (冻结探针, v2)</t>
-        </is>
-      </c>
-      <c r="G31" s="6" t="inlineStr">
-        <is>
-          <t>patch_len 200；表征质量协议</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="6" t="inlineStr">
+          <t>四道门第 4 门对照</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="6" t="inlineStr">
         <is>
           <t>空单元格 = 尚未跑；单 seed 数字标注 (1 seed)、斜体灰 —— 进论文正表需 3 seed（硬规则 4）</t>
         </is>
@@ -1052,7 +1035,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G33"/>
+  <dimension ref="A1:G32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -1568,88 +1551,71 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>D 对照</t>
+          <t>D PACLock</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>MOMENT (通用时序 FM)</t>
-        </is>
-      </c>
-      <c r="G27" s="6" t="inlineStr">
-        <is>
-          <t>EEG 特异性对照</t>
+          <t>PACLock (duplex, scratch)</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="D27" s="8" t="inlineStr">
+        <is>
+          <t>0.7117 (1 seed)</t>
+        </is>
+      </c>
+      <c r="E27" s="8" t="inlineStr">
+        <is>
+          <t>0.7676 (1 seed)</t>
+        </is>
+      </c>
+      <c r="F27" s="8" t="inlineStr">
+        <is>
+          <t>0.7712 (1 seed)</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="B28" t="inlineStr">
         <is>
-          <t>PACLock (随机初始化)</t>
+          <t>PACLock (duplex, 预训练 v2)</t>
         </is>
       </c>
       <c r="G28" s="6" t="inlineStr">
         <is>
-          <t>四道门第 4 门</t>
+          <t>band_norm_pac 目标</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>E PACLock</t>
-        </is>
-      </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>PACLock (duplex, scratch)</t>
-        </is>
-      </c>
-      <c r="C29" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="D29" s="8" t="inlineStr">
-        <is>
-          <t>0.7117 (1 seed)</t>
-        </is>
-      </c>
-      <c r="E29" s="8" t="inlineStr">
-        <is>
-          <t>0.7676 (1 seed)</t>
-        </is>
-      </c>
-      <c r="F29" s="8" t="inlineStr">
-        <is>
-          <t>0.7712 (1 seed)</t>
+          <t>PACLock (冻结探针, v2)</t>
+        </is>
+      </c>
+      <c r="G29" s="6" t="inlineStr">
+        <is>
+          <t>patch_len 200；表征质量协议</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="B30" t="inlineStr">
         <is>
-          <t>PACLock (duplex, 预训练 v2)</t>
+          <t>PACLock (冻结探针, 随机初始化)</t>
         </is>
       </c>
       <c r="G30" s="6" t="inlineStr">
         <is>
-          <t>band_norm_pac 目标</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>PACLock (冻结探针, v2)</t>
-        </is>
-      </c>
-      <c r="G31" s="6" t="inlineStr">
-        <is>
-          <t>patch_len 200；表征质量协议</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="6" t="inlineStr">
+          <t>四道门第 4 门对照</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="6" t="inlineStr">
         <is>
           <t>空单元格 = 尚未跑；单 seed 数字标注 (1 seed)、斜体灰 —— 进论文正表需 3 seed（硬规则 4）</t>
         </is>
@@ -1666,7 +1632,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G33"/>
+  <dimension ref="A1:G32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -2182,88 +2148,71 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>D 对照</t>
+          <t>D PACLock</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>MOMENT (通用时序 FM)</t>
-        </is>
-      </c>
-      <c r="G27" s="6" t="inlineStr">
-        <is>
-          <t>EEG 特异性对照</t>
+          <t>PACLock (duplex, scratch)</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="D27" s="8" t="inlineStr">
+        <is>
+          <t>0.3920 (1 seed)</t>
+        </is>
+      </c>
+      <c r="E27" s="8" t="inlineStr">
+        <is>
+          <t>0.1893 (1 seed)</t>
+        </is>
+      </c>
+      <c r="F27" s="8" t="inlineStr">
+        <is>
+          <t>0.3852 (1 seed)</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="B28" t="inlineStr">
         <is>
-          <t>PACLock (随机初始化)</t>
+          <t>PACLock (duplex, 预训练 v2)</t>
         </is>
       </c>
       <c r="G28" s="6" t="inlineStr">
         <is>
-          <t>四道门第 4 门</t>
+          <t>band_norm_pac 目标</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>E PACLock</t>
-        </is>
-      </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>PACLock (duplex, scratch)</t>
-        </is>
-      </c>
-      <c r="C29" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="D29" s="8" t="inlineStr">
-        <is>
-          <t>0.3920 (1 seed)</t>
-        </is>
-      </c>
-      <c r="E29" s="8" t="inlineStr">
-        <is>
-          <t>0.1893 (1 seed)</t>
-        </is>
-      </c>
-      <c r="F29" s="8" t="inlineStr">
-        <is>
-          <t>0.3852 (1 seed)</t>
+          <t>PACLock (冻结探针, v2)</t>
+        </is>
+      </c>
+      <c r="G29" s="6" t="inlineStr">
+        <is>
+          <t>patch_len 200；表征质量协议</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="B30" t="inlineStr">
         <is>
-          <t>PACLock (duplex, 预训练 v2)</t>
+          <t>PACLock (冻结探针, 随机初始化)</t>
         </is>
       </c>
       <c r="G30" s="6" t="inlineStr">
         <is>
-          <t>band_norm_pac 目标</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>PACLock (冻结探针, v2)</t>
-        </is>
-      </c>
-      <c r="G31" s="6" t="inlineStr">
-        <is>
-          <t>patch_len 200；表征质量协议</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="6" t="inlineStr">
+          <t>四道门第 4 门对照</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="6" t="inlineStr">
         <is>
           <t>空单元格 = 尚未跑；单 seed 数字标注 (1 seed)、斜体灰 —— 进论文正表需 3 seed（硬规则 4）</t>
         </is>
@@ -2280,7 +2229,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G33"/>
+  <dimension ref="A1:G32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -2796,88 +2745,71 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>D 对照</t>
+          <t>D PACLock</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>MOMENT (通用时序 FM)</t>
-        </is>
-      </c>
-      <c r="G27" s="6" t="inlineStr">
-        <is>
-          <t>EEG 特异性对照</t>
+          <t>PACLock (duplex, scratch)</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="D27" s="8" t="inlineStr">
+        <is>
+          <t>0.6533 (1 seed)</t>
+        </is>
+      </c>
+      <c r="E27" s="8" t="inlineStr">
+        <is>
+          <t>0.6276 (1 seed)</t>
+        </is>
+      </c>
+      <c r="F27" s="8" t="inlineStr">
+        <is>
+          <t>0.7597 (1 seed)</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="B28" t="inlineStr">
         <is>
-          <t>PACLock (随机初始化)</t>
+          <t>PACLock (duplex, 预训练 v2)</t>
         </is>
       </c>
       <c r="G28" s="6" t="inlineStr">
         <is>
-          <t>四道门第 4 门</t>
+          <t>band_norm_pac 目标</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>E PACLock</t>
-        </is>
-      </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>PACLock (duplex, scratch)</t>
-        </is>
-      </c>
-      <c r="C29" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="D29" s="8" t="inlineStr">
-        <is>
-          <t>0.6533 (1 seed)</t>
-        </is>
-      </c>
-      <c r="E29" s="8" t="inlineStr">
-        <is>
-          <t>0.6276 (1 seed)</t>
-        </is>
-      </c>
-      <c r="F29" s="8" t="inlineStr">
-        <is>
-          <t>0.7597 (1 seed)</t>
+          <t>PACLock (冻结探针, v2)</t>
+        </is>
+      </c>
+      <c r="G29" s="6" t="inlineStr">
+        <is>
+          <t>patch_len 200；表征质量协议</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="B30" t="inlineStr">
         <is>
-          <t>PACLock (duplex, 预训练 v2)</t>
+          <t>PACLock (冻结探针, 随机初始化)</t>
         </is>
       </c>
       <c r="G30" s="6" t="inlineStr">
         <is>
-          <t>band_norm_pac 目标</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>PACLock (冻结探针, v2)</t>
-        </is>
-      </c>
-      <c r="G31" s="6" t="inlineStr">
-        <is>
-          <t>patch_len 200；表征质量协议</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="6" t="inlineStr">
+          <t>四道门第 4 门对照</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="6" t="inlineStr">
         <is>
           <t>空单元格 = 尚未跑；单 seed 数字标注 (1 seed)、斜体灰 —— 进论文正表需 3 seed（硬规则 4）</t>
         </is>
@@ -2894,7 +2826,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G33"/>
+  <dimension ref="A1:G32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -3410,70 +3342,53 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>D 对照</t>
+          <t>D PACLock</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>MOMENT (通用时序 FM)</t>
-        </is>
-      </c>
-      <c r="G27" s="6" t="inlineStr">
-        <is>
-          <t>EEG 特异性对照</t>
+          <t>PACLock (duplex, scratch)</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="B28" t="inlineStr">
         <is>
-          <t>PACLock (随机初始化)</t>
+          <t>PACLock (duplex, 预训练 v2)</t>
         </is>
       </c>
       <c r="G28" s="6" t="inlineStr">
         <is>
-          <t>四道门第 4 门</t>
+          <t>band_norm_pac 目标</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>E PACLock</t>
-        </is>
-      </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>PACLock (duplex, scratch)</t>
+          <t>PACLock (冻结探针, v2)</t>
+        </is>
+      </c>
+      <c r="G29" s="6" t="inlineStr">
+        <is>
+          <t>patch_len 200；表征质量协议</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="B30" t="inlineStr">
         <is>
-          <t>PACLock (duplex, 预训练 v2)</t>
+          <t>PACLock (冻结探针, 随机初始化)</t>
         </is>
       </c>
       <c r="G30" s="6" t="inlineStr">
         <is>
-          <t>band_norm_pac 目标</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>PACLock (冻结探针, v2)</t>
-        </is>
-      </c>
-      <c r="G31" s="6" t="inlineStr">
-        <is>
-          <t>patch_len 200；表征质量协议</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="6" t="inlineStr">
+          <t>四道门第 4 门对照</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="6" t="inlineStr">
         <is>
           <t>空单元格 = 尚未跑；单 seed 数字标注 (1 seed)、斜体灰 —— 进论文正表需 3 seed（硬规则 4）</t>
         </is>
@@ -3490,7 +3405,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G33"/>
+  <dimension ref="A1:G32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -3988,70 +3903,53 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>D 对照</t>
+          <t>D PACLock</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>MOMENT (通用时序 FM)</t>
-        </is>
-      </c>
-      <c r="G27" s="6" t="inlineStr">
-        <is>
-          <t>EEG 特异性对照</t>
+          <t>PACLock (duplex, scratch)</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="B28" t="inlineStr">
         <is>
-          <t>PACLock (随机初始化)</t>
+          <t>PACLock (duplex, 预训练 v2)</t>
         </is>
       </c>
       <c r="G28" s="6" t="inlineStr">
         <is>
-          <t>四道门第 4 门</t>
+          <t>band_norm_pac 目标</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>E PACLock</t>
-        </is>
-      </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>PACLock (duplex, scratch)</t>
+          <t>PACLock (冻结探针, v2)</t>
+        </is>
+      </c>
+      <c r="G29" s="6" t="inlineStr">
+        <is>
+          <t>patch_len 200；表征质量协议</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="B30" t="inlineStr">
         <is>
-          <t>PACLock (duplex, 预训练 v2)</t>
+          <t>PACLock (冻结探针, 随机初始化)</t>
         </is>
       </c>
       <c r="G30" s="6" t="inlineStr">
         <is>
-          <t>band_norm_pac 目标</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>PACLock (冻结探针, v2)</t>
-        </is>
-      </c>
-      <c r="G31" s="6" t="inlineStr">
-        <is>
-          <t>patch_len 200；表征质量协议</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="6" t="inlineStr">
+          <t>四道门第 4 门对照</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="6" t="inlineStr">
         <is>
           <t>空单元格 = 尚未跑；单 seed 数字标注 (1 seed)、斜体灰 —— 进论文正表需 3 seed（硬规则 4）</t>
         </is>
@@ -4068,7 +3966,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G33"/>
+  <dimension ref="A1:G32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -4620,88 +4518,71 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>D 对照</t>
+          <t>D PACLock</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>MOMENT (通用时序 FM)</t>
-        </is>
-      </c>
-      <c r="G27" s="6" t="inlineStr">
-        <is>
-          <t>EEG 特异性对照</t>
+          <t>PACLock (duplex, scratch)</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="D27" s="8" t="inlineStr">
+        <is>
+          <t>0.6289 (1 seed)</t>
+        </is>
+      </c>
+      <c r="E27" s="8" t="inlineStr">
+        <is>
+          <t>0.7644 (1 seed)</t>
+        </is>
+      </c>
+      <c r="F27" s="8" t="inlineStr">
+        <is>
+          <t>0.7462 (1 seed)</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="B28" t="inlineStr">
         <is>
-          <t>PACLock (随机初始化)</t>
+          <t>PACLock (duplex, 预训练 v2)</t>
         </is>
       </c>
       <c r="G28" s="6" t="inlineStr">
         <is>
-          <t>四道门第 4 门</t>
+          <t>band_norm_pac 目标</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>E PACLock</t>
-        </is>
-      </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>PACLock (duplex, scratch)</t>
-        </is>
-      </c>
-      <c r="C29" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="D29" s="8" t="inlineStr">
-        <is>
-          <t>0.6289 (1 seed)</t>
-        </is>
-      </c>
-      <c r="E29" s="8" t="inlineStr">
-        <is>
-          <t>0.7644 (1 seed)</t>
-        </is>
-      </c>
-      <c r="F29" s="8" t="inlineStr">
-        <is>
-          <t>0.7462 (1 seed)</t>
+          <t>PACLock (冻结探针, v2)</t>
+        </is>
+      </c>
+      <c r="G29" s="6" t="inlineStr">
+        <is>
+          <t>patch_len 200；表征质量协议</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="B30" t="inlineStr">
         <is>
-          <t>PACLock (duplex, 预训练 v2)</t>
+          <t>PACLock (冻结探针, 随机初始化)</t>
         </is>
       </c>
       <c r="G30" s="6" t="inlineStr">
         <is>
-          <t>band_norm_pac 目标</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>PACLock (冻结探针, v2)</t>
-        </is>
-      </c>
-      <c r="G31" s="6" t="inlineStr">
-        <is>
-          <t>patch_len 200；表征质量协议</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="6" t="inlineStr">
+          <t>四道门第 4 门对照</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="6" t="inlineStr">
         <is>
           <t>空单元格 = 尚未跑；单 seed 数字标注 (1 seed)、斜体灰 —— 进论文正表需 3 seed（硬规则 4）</t>
         </is>
@@ -4718,7 +4599,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G33"/>
+  <dimension ref="A1:G32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -5270,88 +5151,71 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>D 对照</t>
+          <t>D PACLock</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>MOMENT (通用时序 FM)</t>
-        </is>
-      </c>
-      <c r="G27" s="6" t="inlineStr">
-        <is>
-          <t>EEG 特异性对照</t>
+          <t>PACLock (duplex, scratch)</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="D27" s="8" t="inlineStr">
+        <is>
+          <t>0.9775 (1 seed)</t>
+        </is>
+      </c>
+      <c r="E27" s="8" t="inlineStr">
+        <is>
+          <t>0.8735 (1 seed)</t>
+        </is>
+      </c>
+      <c r="F27" s="8" t="inlineStr">
+        <is>
+          <t>0.9810 (1 seed)</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="B28" t="inlineStr">
         <is>
-          <t>PACLock (随机初始化)</t>
+          <t>PACLock (duplex, 预训练 v2)</t>
         </is>
       </c>
       <c r="G28" s="6" t="inlineStr">
         <is>
-          <t>四道门第 4 门</t>
+          <t>band_norm_pac 目标</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>E PACLock</t>
-        </is>
-      </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>PACLock (duplex, scratch)</t>
-        </is>
-      </c>
-      <c r="C29" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="D29" s="8" t="inlineStr">
-        <is>
-          <t>0.9775 (1 seed)</t>
-        </is>
-      </c>
-      <c r="E29" s="8" t="inlineStr">
-        <is>
-          <t>0.8735 (1 seed)</t>
-        </is>
-      </c>
-      <c r="F29" s="8" t="inlineStr">
-        <is>
-          <t>0.9810 (1 seed)</t>
+          <t>PACLock (冻结探针, v2)</t>
+        </is>
+      </c>
+      <c r="G29" s="6" t="inlineStr">
+        <is>
+          <t>patch_len 200；表征质量协议</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="B30" t="inlineStr">
         <is>
-          <t>PACLock (duplex, 预训练 v2)</t>
+          <t>PACLock (冻结探针, 随机初始化)</t>
         </is>
       </c>
       <c r="G30" s="6" t="inlineStr">
         <is>
-          <t>band_norm_pac 目标</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>PACLock (冻结探针, v2)</t>
-        </is>
-      </c>
-      <c r="G31" s="6" t="inlineStr">
-        <is>
-          <t>patch_len 200；表征质量协议</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="6" t="inlineStr">
+          <t>四道门第 4 门对照</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="6" t="inlineStr">
         <is>
           <t>空单元格 = 尚未跑；单 seed 数字标注 (1 seed)、斜体灰 —— 进论文正表需 3 seed（硬规则 4）</t>
         </is>
@@ -5368,7 +5232,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G33"/>
+  <dimension ref="A1:G32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -5920,88 +5784,71 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>D 对照</t>
+          <t>D PACLock</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>MOMENT (通用时序 FM)</t>
-        </is>
-      </c>
-      <c r="G27" s="6" t="inlineStr">
-        <is>
-          <t>EEG 特异性对照</t>
+          <t>PACLock (duplex, scratch)</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="D27" s="8" t="inlineStr">
+        <is>
+          <t>0.7263 (1 seed)</t>
+        </is>
+      </c>
+      <c r="E27" s="8" t="inlineStr">
+        <is>
+          <t>0.5590 (1 seed)</t>
+        </is>
+      </c>
+      <c r="F27" s="8" t="inlineStr">
+        <is>
+          <t>0.4691 (1 seed)</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="B28" t="inlineStr">
         <is>
-          <t>PACLock (随机初始化)</t>
+          <t>PACLock (duplex, 预训练 v2)</t>
         </is>
       </c>
       <c r="G28" s="6" t="inlineStr">
         <is>
-          <t>四道门第 4 门</t>
+          <t>band_norm_pac 目标</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>E PACLock</t>
-        </is>
-      </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>PACLock (duplex, scratch)</t>
-        </is>
-      </c>
-      <c r="C29" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="D29" s="8" t="inlineStr">
-        <is>
-          <t>0.7263 (1 seed)</t>
-        </is>
-      </c>
-      <c r="E29" s="8" t="inlineStr">
-        <is>
-          <t>0.5590 (1 seed)</t>
-        </is>
-      </c>
-      <c r="F29" s="8" t="inlineStr">
-        <is>
-          <t>0.4691 (1 seed)</t>
+          <t>PACLock (冻结探针, v2)</t>
+        </is>
+      </c>
+      <c r="G29" s="6" t="inlineStr">
+        <is>
+          <t>patch_len 200；表征质量协议</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="B30" t="inlineStr">
         <is>
-          <t>PACLock (duplex, 预训练 v2)</t>
+          <t>PACLock (冻结探针, 随机初始化)</t>
         </is>
       </c>
       <c r="G30" s="6" t="inlineStr">
         <is>
-          <t>band_norm_pac 目标</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>PACLock (冻结探针, v2)</t>
-        </is>
-      </c>
-      <c r="G31" s="6" t="inlineStr">
-        <is>
-          <t>patch_len 200；表征质量协议</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="6" t="inlineStr">
+          <t>四道门第 4 门对照</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="6" t="inlineStr">
         <is>
           <t>空单元格 = 尚未跑；单 seed 数字标注 (1 seed)、斜体灰 —— 进论文正表需 3 seed（硬规则 4）</t>
         </is>
@@ -19982,7 +19829,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G37"/>
+  <dimension ref="A1:G36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -20491,129 +20338,112 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>D 对照</t>
+          <t>D PACLock</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>MOMENT (通用时序 FM)</t>
-        </is>
-      </c>
-      <c r="G27" s="6" t="inlineStr">
-        <is>
-          <t>EEG 特异性对照</t>
+          <t>PACLock (duplex, scratch)</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="D27" s="8" t="inlineStr">
+        <is>
+          <t>0.7094 (1 seed)</t>
+        </is>
+      </c>
+      <c r="E27" s="8" t="inlineStr">
+        <is>
+          <t>0.6464 (1 seed)</t>
+        </is>
+      </c>
+      <c r="F27" s="8" t="inlineStr">
+        <is>
+          <t>0.8428 (1 seed)</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="B28" t="inlineStr">
         <is>
-          <t>PACLock (随机初始化)</t>
+          <t>PACLock (duplex, 预训练 v2)</t>
         </is>
       </c>
       <c r="G28" s="6" t="inlineStr">
         <is>
-          <t>四道门第 4 门</t>
+          <t>band_norm_pac 目标</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>E PACLock</t>
-        </is>
-      </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>PACLock (duplex, scratch)</t>
-        </is>
-      </c>
-      <c r="C29" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="D29" s="8" t="inlineStr">
-        <is>
-          <t>0.7094 (1 seed)</t>
-        </is>
-      </c>
-      <c r="E29" s="8" t="inlineStr">
-        <is>
-          <t>0.6464 (1 seed)</t>
-        </is>
-      </c>
-      <c r="F29" s="8" t="inlineStr">
-        <is>
-          <t>0.8428 (1 seed)</t>
+          <t>PACLock (冻结探针, v2)</t>
+        </is>
+      </c>
+      <c r="G29" s="6" t="inlineStr">
+        <is>
+          <t>patch_len 200；表征质量协议</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="B30" t="inlineStr">
         <is>
-          <t>PACLock (duplex, 预训练 v2)</t>
+          <t>PACLock (冻结探针, 随机初始化)</t>
         </is>
       </c>
       <c r="G30" s="6" t="inlineStr">
         <is>
-          <t>band_norm_pac 目标</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>PACLock (冻结探针, v2)</t>
-        </is>
-      </c>
-      <c r="G31" s="6" t="inlineStr">
-        <is>
-          <t>patch_len 200；表征质量协议</t>
+          <t>四道门第 4 门对照</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="6" t="inlineStr">
+        <is>
+          <t>E 参考值（论文自报，不同管线，不可直接比）</t>
+        </is>
+      </c>
+      <c r="B32" s="6" t="inlineStr">
+        <is>
+          <t>CodeBrain (ICLR'26, 自报)</t>
+        </is>
+      </c>
+      <c r="D32" s="6" t="inlineStr">
+        <is>
+          <t>0.6912</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="6" t="inlineStr">
-        <is>
-          <t>F 参考值（论文自报，不同管线，不可直接比）</t>
-        </is>
-      </c>
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t>CodeBrain (ICLR'26, 自报)</t>
+          <t>Uni-NTFM-large (ICLR'26, 自报)</t>
         </is>
       </c>
       <c r="D33" s="6" t="inlineStr">
         <is>
-          <t>0.6912</t>
+          <t>0.7030</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="B34" s="6" t="inlineStr">
         <is>
-          <t>Uni-NTFM-large (ICLR'26, 自报)</t>
+          <t>CBraMod (原论文自报)</t>
         </is>
       </c>
       <c r="D34" s="6" t="inlineStr">
         <is>
-          <t>0.7030</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="B35" s="6" t="inlineStr">
-        <is>
-          <t>CBraMod (原论文自报)</t>
-        </is>
-      </c>
-      <c r="D35" s="6" t="inlineStr">
-        <is>
           <t>0.6512</t>
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="6" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="6" t="inlineStr">
         <is>
           <t>空单元格 = 尚未跑；单 seed 数字标注 (1 seed)、斜体灰 —— 进论文正表需 3 seed（硬规则 4）</t>
         </is>
@@ -22206,7 +22036,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G33"/>
+  <dimension ref="A1:G32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -22715,88 +22545,71 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>D 对照</t>
+          <t>D PACLock</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>MOMENT (通用时序 FM)</t>
-        </is>
-      </c>
-      <c r="G27" s="6" t="inlineStr">
-        <is>
-          <t>EEG 特异性对照</t>
+          <t>PACLock (duplex, scratch)</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="D27" s="8" t="inlineStr">
+        <is>
+          <t>0.6328 (1 seed)</t>
+        </is>
+      </c>
+      <c r="E27" s="8" t="inlineStr">
+        <is>
+          <t>0.9217 (1 seed)</t>
+        </is>
+      </c>
+      <c r="F27" s="8" t="inlineStr">
+        <is>
+          <t>0.6298 (1 seed)</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="B28" t="inlineStr">
         <is>
-          <t>PACLock (随机初始化)</t>
+          <t>PACLock (duplex, 预训练 v2)</t>
         </is>
       </c>
       <c r="G28" s="6" t="inlineStr">
         <is>
-          <t>四道门第 4 门</t>
+          <t>band_norm_pac 目标</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>E PACLock</t>
-        </is>
-      </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>PACLock (duplex, scratch)</t>
-        </is>
-      </c>
-      <c r="C29" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="D29" s="8" t="inlineStr">
-        <is>
-          <t>0.6328 (1 seed)</t>
-        </is>
-      </c>
-      <c r="E29" s="8" t="inlineStr">
-        <is>
-          <t>0.9217 (1 seed)</t>
-        </is>
-      </c>
-      <c r="F29" s="8" t="inlineStr">
-        <is>
-          <t>0.6298 (1 seed)</t>
+          <t>PACLock (冻结探针, v2)</t>
+        </is>
+      </c>
+      <c r="G29" s="6" t="inlineStr">
+        <is>
+          <t>patch_len 200；表征质量协议</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="B30" t="inlineStr">
         <is>
-          <t>PACLock (duplex, 预训练 v2)</t>
+          <t>PACLock (冻结探针, 随机初始化)</t>
         </is>
       </c>
       <c r="G30" s="6" t="inlineStr">
         <is>
-          <t>band_norm_pac 目标</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>PACLock (冻结探针, v2)</t>
-        </is>
-      </c>
-      <c r="G31" s="6" t="inlineStr">
-        <is>
-          <t>patch_len 200；表征质量协议</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="6" t="inlineStr">
+          <t>四道门第 4 门对照</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="6" t="inlineStr">
         <is>
           <t>空单元格 = 尚未跑；单 seed 数字标注 (1 seed)、斜体灰 —— 进论文正表需 3 seed（硬规则 4）</t>
         </is>
@@ -22813,7 +22626,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G33"/>
+  <dimension ref="A1:G32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -23327,88 +23140,71 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>D 对照</t>
+          <t>D PACLock</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>MOMENT (通用时序 FM)</t>
-        </is>
-      </c>
-      <c r="G27" s="6" t="inlineStr">
-        <is>
-          <t>EEG 特异性对照</t>
+          <t>PACLock (duplex, scratch)</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="D27" s="8" t="inlineStr">
+        <is>
+          <t>0.7130 (1 seed)</t>
+        </is>
+      </c>
+      <c r="E27" s="8" t="inlineStr">
+        <is>
+          <t>0.9256 (1 seed)</t>
+        </is>
+      </c>
+      <c r="F27" s="8" t="inlineStr">
+        <is>
+          <t>0.5163 (1 seed)</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="B28" t="inlineStr">
         <is>
-          <t>PACLock (随机初始化)</t>
+          <t>PACLock (duplex, 预训练 v2)</t>
         </is>
       </c>
       <c r="G28" s="6" t="inlineStr">
         <is>
-          <t>四道门第 4 门</t>
+          <t>band_norm_pac 目标</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>E PACLock</t>
-        </is>
-      </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>PACLock (duplex, scratch)</t>
-        </is>
-      </c>
-      <c r="C29" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="D29" s="8" t="inlineStr">
-        <is>
-          <t>0.7130 (1 seed)</t>
-        </is>
-      </c>
-      <c r="E29" s="8" t="inlineStr">
-        <is>
-          <t>0.9256 (1 seed)</t>
-        </is>
-      </c>
-      <c r="F29" s="8" t="inlineStr">
-        <is>
-          <t>0.5163 (1 seed)</t>
+          <t>PACLock (冻结探针, v2)</t>
+        </is>
+      </c>
+      <c r="G29" s="6" t="inlineStr">
+        <is>
+          <t>patch_len 200；表征质量协议</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="B30" t="inlineStr">
         <is>
-          <t>PACLock (duplex, 预训练 v2)</t>
+          <t>PACLock (冻结探针, 随机初始化)</t>
         </is>
       </c>
       <c r="G30" s="6" t="inlineStr">
         <is>
-          <t>band_norm_pac 目标</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>PACLock (冻结探针, v2)</t>
-        </is>
-      </c>
-      <c r="G31" s="6" t="inlineStr">
-        <is>
-          <t>patch_len 200；表征质量协议</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="6" t="inlineStr">
+          <t>四道门第 4 门对照</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="6" t="inlineStr">
         <is>
           <t>空单元格 = 尚未跑；单 seed 数字标注 (1 seed)、斜体灰 —— 进论文正表需 3 seed（硬规则 4）</t>
         </is>
@@ -23425,7 +23221,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G33"/>
+  <dimension ref="A1:G32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -23707,70 +23503,53 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>D 对照</t>
+          <t>D PACLock</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>MOMENT (通用时序 FM)</t>
-        </is>
-      </c>
-      <c r="G27" s="6" t="inlineStr">
-        <is>
-          <t>EEG 特异性对照</t>
+          <t>PACLock (duplex, scratch)</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="B28" t="inlineStr">
         <is>
-          <t>PACLock (随机初始化)</t>
+          <t>PACLock (duplex, 预训练 v2)</t>
         </is>
       </c>
       <c r="G28" s="6" t="inlineStr">
         <is>
-          <t>四道门第 4 门</t>
+          <t>band_norm_pac 目标</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>E PACLock</t>
-        </is>
-      </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>PACLock (duplex, scratch)</t>
+          <t>PACLock (冻结探针, v2)</t>
+        </is>
+      </c>
+      <c r="G29" s="6" t="inlineStr">
+        <is>
+          <t>patch_len 200；表征质量协议</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="B30" t="inlineStr">
         <is>
-          <t>PACLock (duplex, 预训练 v2)</t>
+          <t>PACLock (冻结探针, 随机初始化)</t>
         </is>
       </c>
       <c r="G30" s="6" t="inlineStr">
         <is>
-          <t>band_norm_pac 目标</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>PACLock (冻结探针, v2)</t>
-        </is>
-      </c>
-      <c r="G31" s="6" t="inlineStr">
-        <is>
-          <t>patch_len 200；表征质量协议</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="6" t="inlineStr">
+          <t>四道门第 4 门对照</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="6" t="inlineStr">
         <is>
           <t>空单元格 = 尚未跑；单 seed 数字标注 (1 seed)、斜体灰 —— 进论文正表需 3 seed（硬规则 4）</t>
         </is>
@@ -23787,7 +23566,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G33"/>
+  <dimension ref="A1:G32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -24332,88 +24111,71 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>D 对照</t>
+          <t>D PACLock</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>MOMENT (通用时序 FM)</t>
-        </is>
-      </c>
-      <c r="G27" s="6" t="inlineStr">
-        <is>
-          <t>EEG 特异性对照</t>
+          <t>PACLock (duplex, scratch)</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="D27" s="8" t="inlineStr">
+        <is>
+          <t>0.8052 (1 seed)</t>
+        </is>
+      </c>
+      <c r="E27" s="8" t="inlineStr">
+        <is>
+          <t>0.5000 (1 seed)</t>
+        </is>
+      </c>
+      <c r="F27" s="8" t="inlineStr">
+        <is>
+          <t>0.8493 (1 seed)</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="B28" t="inlineStr">
         <is>
-          <t>PACLock (随机初始化)</t>
+          <t>PACLock (duplex, 预训练 v2)</t>
         </is>
       </c>
       <c r="G28" s="6" t="inlineStr">
         <is>
-          <t>四道门第 4 门</t>
+          <t>band_norm_pac 目标</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>E PACLock</t>
-        </is>
-      </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>PACLock (duplex, scratch)</t>
-        </is>
-      </c>
-      <c r="C29" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="D29" s="8" t="inlineStr">
-        <is>
-          <t>0.8052 (1 seed)</t>
-        </is>
-      </c>
-      <c r="E29" s="8" t="inlineStr">
-        <is>
-          <t>0.5000 (1 seed)</t>
-        </is>
-      </c>
-      <c r="F29" s="8" t="inlineStr">
-        <is>
-          <t>0.8493 (1 seed)</t>
+          <t>PACLock (冻结探针, v2)</t>
+        </is>
+      </c>
+      <c r="G29" s="6" t="inlineStr">
+        <is>
+          <t>patch_len 200；表征质量协议</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="B30" t="inlineStr">
         <is>
-          <t>PACLock (duplex, 预训练 v2)</t>
+          <t>PACLock (冻结探针, 随机初始化)</t>
         </is>
       </c>
       <c r="G30" s="6" t="inlineStr">
         <is>
-          <t>band_norm_pac 目标</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>PACLock (冻结探针, v2)</t>
-        </is>
-      </c>
-      <c r="G31" s="6" t="inlineStr">
-        <is>
-          <t>patch_len 200；表征质量协议</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="6" t="inlineStr">
+          <t>四道门第 4 门对照</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="6" t="inlineStr">
         <is>
           <t>空单元格 = 尚未跑；单 seed 数字标注 (1 seed)、斜体灰 —— 进论文正表需 3 seed（硬规则 4）</t>
         </is>
@@ -24430,7 +24192,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G37"/>
+  <dimension ref="A1:G36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -24944,129 +24706,112 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>D 对照</t>
+          <t>D PACLock</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>MOMENT (通用时序 FM)</t>
-        </is>
-      </c>
-      <c r="G27" s="6" t="inlineStr">
-        <is>
-          <t>EEG 特异性对照</t>
+          <t>PACLock (duplex, scratch)</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="D27" s="8" t="inlineStr">
+        <is>
+          <t>0.8157 (1 seed)</t>
+        </is>
+      </c>
+      <c r="E27" s="8" t="inlineStr">
+        <is>
+          <t>0.8923 (1 seed)</t>
+        </is>
+      </c>
+      <c r="F27" s="8" t="inlineStr">
+        <is>
+          <t>0.8829 (1 seed)</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="B28" t="inlineStr">
         <is>
-          <t>PACLock (随机初始化)</t>
+          <t>PACLock (duplex, 预训练 v2)</t>
         </is>
       </c>
       <c r="G28" s="6" t="inlineStr">
         <is>
-          <t>四道门第 4 门</t>
+          <t>band_norm_pac 目标</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>E PACLock</t>
-        </is>
-      </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>PACLock (duplex, scratch)</t>
-        </is>
-      </c>
-      <c r="C29" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="D29" s="8" t="inlineStr">
-        <is>
-          <t>0.8157 (1 seed)</t>
-        </is>
-      </c>
-      <c r="E29" s="8" t="inlineStr">
-        <is>
-          <t>0.8923 (1 seed)</t>
-        </is>
-      </c>
-      <c r="F29" s="8" t="inlineStr">
-        <is>
-          <t>0.8829 (1 seed)</t>
+          <t>PACLock (冻结探针, v2)</t>
+        </is>
+      </c>
+      <c r="G29" s="6" t="inlineStr">
+        <is>
+          <t>patch_len 200；表征质量协议</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="B30" t="inlineStr">
         <is>
-          <t>PACLock (duplex, 预训练 v2)</t>
+          <t>PACLock (冻结探针, 随机初始化)</t>
         </is>
       </c>
       <c r="G30" s="6" t="inlineStr">
         <is>
-          <t>band_norm_pac 目标</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>PACLock (冻结探针, v2)</t>
-        </is>
-      </c>
-      <c r="G31" s="6" t="inlineStr">
-        <is>
-          <t>patch_len 200；表征质量协议</t>
+          <t>四道门第 4 门对照</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="6" t="inlineStr">
+        <is>
+          <t>E 参考值（论文自报，不同管线，不可直接比）</t>
+        </is>
+      </c>
+      <c r="B32" s="6" t="inlineStr">
+        <is>
+          <t>CodeBrain (ICLR'26, 自报)</t>
+        </is>
+      </c>
+      <c r="D32" s="6" t="inlineStr">
+        <is>
+          <t>0.8294</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="6" t="inlineStr">
-        <is>
-          <t>F 参考值（论文自报，不同管线，不可直接比）</t>
-        </is>
-      </c>
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t>CodeBrain (ICLR'26, 自报)</t>
+          <t>Uni-NTFM-large (ICLR'26, 自报)</t>
         </is>
       </c>
       <c r="D33" s="6" t="inlineStr">
         <is>
-          <t>0.8294</t>
+          <t>0.8197</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="B34" s="6" t="inlineStr">
         <is>
-          <t>Uni-NTFM-large (ICLR'26, 自报)</t>
+          <t>REVE-Base (原论文自报)</t>
         </is>
       </c>
       <c r="D34" s="6" t="inlineStr">
         <is>
-          <t>0.8197</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="B35" s="6" t="inlineStr">
-        <is>
-          <t>REVE-Base (原论文自报)</t>
-        </is>
-      </c>
-      <c r="D35" s="6" t="inlineStr">
-        <is>
           <t>0.8315</t>
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="6" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="6" t="inlineStr">
         <is>
           <t>空单元格 = 尚未跑；单 seed 数字标注 (1 seed)、斜体灰 —— 进论文正表需 3 seed（硬规则 4）</t>
         </is>
@@ -25083,7 +24828,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G33"/>
+  <dimension ref="A1:G32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -25628,88 +25373,71 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>D 对照</t>
+          <t>D PACLock</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>MOMENT (通用时序 FM)</t>
-        </is>
-      </c>
-      <c r="G27" s="6" t="inlineStr">
-        <is>
-          <t>EEG 特异性对照</t>
+          <t>PACLock (duplex, scratch)</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="D27" s="8" t="inlineStr">
+        <is>
+          <t>0.5617 (1 seed)</t>
+        </is>
+      </c>
+      <c r="E27" s="8" t="inlineStr">
+        <is>
+          <t>0.3613 (1 seed)</t>
+        </is>
+      </c>
+      <c r="F27" s="8" t="inlineStr">
+        <is>
+          <t>0.5814 (1 seed)</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="B28" t="inlineStr">
         <is>
-          <t>PACLock (随机初始化)</t>
+          <t>PACLock (duplex, 预训练 v2)</t>
         </is>
       </c>
       <c r="G28" s="6" t="inlineStr">
         <is>
-          <t>四道门第 4 门</t>
+          <t>band_norm_pac 目标</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>E PACLock</t>
-        </is>
-      </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>PACLock (duplex, scratch)</t>
-        </is>
-      </c>
-      <c r="C29" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="D29" s="8" t="inlineStr">
-        <is>
-          <t>0.5617 (1 seed)</t>
-        </is>
-      </c>
-      <c r="E29" s="8" t="inlineStr">
-        <is>
-          <t>0.3613 (1 seed)</t>
-        </is>
-      </c>
-      <c r="F29" s="8" t="inlineStr">
-        <is>
-          <t>0.5814 (1 seed)</t>
+          <t>PACLock (冻结探针, v2)</t>
+        </is>
+      </c>
+      <c r="G29" s="6" t="inlineStr">
+        <is>
+          <t>patch_len 200；表征质量协议</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="B30" t="inlineStr">
         <is>
-          <t>PACLock (duplex, 预训练 v2)</t>
+          <t>PACLock (冻结探针, 随机初始化)</t>
         </is>
       </c>
       <c r="G30" s="6" t="inlineStr">
         <is>
-          <t>band_norm_pac 目标</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>PACLock (冻结探针, v2)</t>
-        </is>
-      </c>
-      <c r="G31" s="6" t="inlineStr">
-        <is>
-          <t>patch_len 200；表征质量协议</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="6" t="inlineStr">
+          <t>四道门第 4 门对照</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="6" t="inlineStr">
         <is>
           <t>空单元格 = 尚未跑；单 seed 数字标注 (1 seed)、斜体灰 —— 进论文正表需 3 seed（硬规则 4）</t>
         </is>
@@ -25726,7 +25454,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G35"/>
+  <dimension ref="A1:G34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -26008,82 +25736,65 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>D 对照</t>
+          <t>D PACLock</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>MOMENT (通用时序 FM)</t>
-        </is>
-      </c>
-      <c r="G27" s="6" t="inlineStr">
-        <is>
-          <t>EEG 特异性对照</t>
+          <t>PACLock (duplex, scratch)</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="B28" t="inlineStr">
         <is>
-          <t>PACLock (随机初始化)</t>
+          <t>PACLock (duplex, 预训练 v2)</t>
         </is>
       </c>
       <c r="G28" s="6" t="inlineStr">
         <is>
-          <t>四道门第 4 门</t>
+          <t>band_norm_pac 目标</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>E PACLock</t>
-        </is>
-      </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>PACLock (duplex, scratch)</t>
+          <t>PACLock (冻结探针, v2)</t>
+        </is>
+      </c>
+      <c r="G29" s="6" t="inlineStr">
+        <is>
+          <t>patch_len 200；表征质量协议</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="B30" t="inlineStr">
         <is>
-          <t>PACLock (duplex, 预训练 v2)</t>
+          <t>PACLock (冻结探针, 随机初始化)</t>
         </is>
       </c>
       <c r="G30" s="6" t="inlineStr">
         <is>
-          <t>band_norm_pac 目标</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>PACLock (冻结探针, v2)</t>
-        </is>
-      </c>
-      <c r="G31" s="6" t="inlineStr">
-        <is>
-          <t>patch_len 200；表征质量协议</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="6" t="inlineStr">
-        <is>
-          <t>F 参考值（论文自报，不同管线，不可直接比）</t>
-        </is>
-      </c>
-      <c r="B33" s="6" t="inlineStr">
+          <t>四道门第 4 门对照</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="6" t="inlineStr">
+        <is>
+          <t>E 参考值（论文自报，不同管线，不可直接比）</t>
+        </is>
+      </c>
+      <c r="B32" s="6" t="inlineStr">
         <is>
           <t>CEEDNet (数据集作者, NeuroImage'23)</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="6" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="6" t="inlineStr">
         <is>
           <t>空单元格 = 尚未跑；单 seed 数字标注 (1 seed)、斜体灰 —— 进论文正表需 3 seed（硬规则 4）</t>
         </is>

--- a/results/PACLock_baseline_matrix_filled.xlsx
+++ b/results/PACLock_baseline_matrix_filled.xlsx
@@ -36,7 +36,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="8">
+  <fonts count="11">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -66,8 +66,18 @@
       <i val="1"/>
       <color rgb="00808080"/>
     </font>
+    <font>
+      <color rgb="008C8C8C"/>
+    </font>
+    <font>
+      <color rgb="00000000"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="008C8C8C"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -92,6 +102,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFF7E6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
   </fills>
@@ -121,7 +136,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -149,6 +164,13 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -514,7 +536,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A26"/>
+  <dimension ref="A1:A32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" min="1" max="1"/>
@@ -683,6 +705,41 @@
       <c r="A26" s="2" t="inlineStr">
         <is>
           <t>负对照套件（身份探针/LEACE/标签置换/配对 CI）另见 _消融 与论文附录，不入本表</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>单元格读法（2026-08-26 起）</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>灰色数字 = 该 baseline 的原论文没有跑过这个语料，超参是我们移植的（硬规则 2 的可见化）</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>黄色底 = 不足 3 seed，探索级而非进表级（硬规则 4）；我们自己的行按 seed 纪律恒为单 seed</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>加粗 = 该列最好成绩；E 组参考值（他人论文自报、异管线）不参与加粗比较</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>空格 = 尚未跑或有意不排（见 README 上方缓议清单）</t>
         </is>
       </c>
     </row>
@@ -697,15 +754,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G30"/>
+  <dimension ref="A1:F30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
     <col width="11" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
     <col width="46" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
@@ -761,11 +818,6 @@
           <t>Balanced Acc</t>
         </is>
       </c>
-      <c r="G4" s="5" t="inlineStr">
-        <is>
-          <t>备注</t>
-        </is>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -781,24 +833,19 @@
       <c r="C5" t="n">
         <v>0</v>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D5" s="17" t="inlineStr">
         <is>
           <t>0.0404±0.0000</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E5" s="17" t="inlineStr">
         <is>
           <t>0.7227±0.0000</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F5" s="17" t="inlineStr">
         <is>
           <t>0.7096±0.0000</t>
-        </is>
-      </c>
-      <c r="G5" s="6" t="inlineStr">
-        <is>
-          <t>bandpower+Hjorth+谱熵；四道门第 1 门</t>
         </is>
       </c>
     </row>
@@ -816,17 +863,17 @@
       <c r="C6" t="n">
         <v>1.14</v>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D6" s="17" t="inlineStr">
         <is>
           <t>0.3571±0.0345</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E6" s="17" t="inlineStr">
         <is>
           <t>0.8006±0.0337</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="F6" s="17" t="inlineStr">
         <is>
           <t>0.6390±0.0176</t>
         </is>
@@ -841,17 +888,17 @@
       <c r="C7" t="n">
         <v>1.57</v>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D7" s="17" t="inlineStr">
         <is>
           <t>0.4513±0.0505</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E7" s="17" t="inlineStr">
         <is>
           <t>0.8116±0.0173</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F7" s="17" t="inlineStr">
         <is>
           <t>0.6816±0.0463</t>
         </is>
@@ -866,17 +913,17 @@
       <c r="C8" t="n">
         <v>3.16</v>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D8" s="17" t="inlineStr">
         <is>
           <t>0.4227±0.0816</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E8" s="17" t="inlineStr">
         <is>
           <t>0.8583±0.0178</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F8" s="17" t="inlineStr">
         <is>
           <t>0.7015±0.0222</t>
         </is>
@@ -891,17 +938,17 @@
       <c r="C9" t="n">
         <v>2.47</v>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D9" s="17" t="inlineStr">
         <is>
           <t>0.4214±0.0833</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E9" s="17" t="inlineStr">
         <is>
           <t>0.8184±0.0111</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F9" s="17" t="inlineStr">
         <is>
           <t>0.6719±0.0409</t>
         </is>
@@ -920,11 +967,6 @@
           <t>EEGNet (调参)</t>
         </is>
       </c>
-      <c r="G11" s="6" t="inlineStr">
-        <is>
-          <t>公开搜索预算调参</t>
-        </is>
-      </c>
     </row>
     <row r="12">
       <c r="B12" t="inlineStr">
@@ -932,11 +974,6 @@
           <t>EEGConformer (调参)</t>
         </is>
       </c>
-      <c r="G12" s="6" t="inlineStr">
-        <is>
-          <t>benchmark 文献最强单体</t>
-        </is>
-      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -952,17 +989,17 @@
       <c r="C13" t="n">
         <v>3.19</v>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="D13" s="17" t="inlineStr">
         <is>
           <t>0.0905±0.0154</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="E13" s="17" t="inlineStr">
         <is>
           <t>0.7954±0.0222</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="F13" s="17" t="inlineStr">
         <is>
           <t>0.5135±0.0137</t>
         </is>
@@ -977,17 +1014,17 @@
       <c r="C14" t="n">
         <v>5.82</v>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="D14" s="17" t="inlineStr">
         <is>
           <t>0.3027±0.0156</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="E14" s="17" t="inlineStr">
         <is>
           <t>0.7677±0.0208</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="F14" s="17" t="inlineStr">
         <is>
           <t>0.6247±0.0362</t>
         </is>
@@ -1002,17 +1039,17 @@
       <c r="C15" t="n">
         <v>35.45</v>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="D15" s="17" t="inlineStr">
         <is>
           <t>0.4243±0.0520</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="E15" s="17" t="inlineStr">
         <is>
           <t>0.8316±0.0162</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="F15" s="17" t="inlineStr">
         <is>
           <t>0.6582±0.0659</t>
         </is>
@@ -1027,17 +1064,17 @@
       <c r="C16" t="n">
         <v>25.69</v>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="D16" s="17" t="inlineStr">
         <is>
           <t>0.3317±0.0665</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="E16" s="17" t="inlineStr">
         <is>
           <t>0.8462±0.0079</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="F16" s="17" t="inlineStr">
         <is>
           <t>0.5191±0.0270</t>
         </is>
@@ -1052,24 +1089,19 @@
       <c r="C17" t="n">
         <v>1.89</v>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="D17" s="17" t="inlineStr">
         <is>
           <t>0.0603±0.0095</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="E17" s="17" t="inlineStr">
         <is>
           <t>0.7707±0.0369</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="F17" s="17" t="inlineStr">
         <is>
           <t>0.5053±0.0076</t>
-        </is>
-      </c>
-      <c r="G17" s="6" t="inlineStr">
-        <is>
-          <t>tokenizer 直接对手</t>
         </is>
       </c>
     </row>
@@ -1082,24 +1114,19 @@
       <c r="C18" t="n">
         <v>69.51000000000001</v>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="D18" s="21" t="inlineStr">
         <is>
           <t>0.5181±0.0958</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="E18" s="17" t="inlineStr">
         <is>
           <t>0.8565±0.0007</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
+      <c r="F18" s="21" t="inlineStr">
         <is>
           <t>0.7552±0.0207</t>
-        </is>
-      </c>
-      <c r="G18" s="6" t="inlineStr">
-        <is>
-          <t>新增；HF 权重</t>
         </is>
       </c>
     </row>
@@ -1112,24 +1139,19 @@
       <c r="C19" t="n">
         <v>47.06</v>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="D19" s="18" t="inlineStr">
         <is>
           <t>0.2330±0.0890</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="E19" s="18" t="inlineStr">
         <is>
           <t>0.7295±0.0887</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
+      <c r="F19" s="18" t="inlineStr">
         <is>
           <t>0.5705±0.0202</t>
-        </is>
-      </c>
-      <c r="G19" s="6" t="inlineStr">
-        <is>
-          <t>新增；GDrive 权重</t>
         </is>
       </c>
     </row>
@@ -1147,17 +1169,17 @@
       <c r="C20" t="n">
         <v>3.19</v>
       </c>
-      <c r="D20" t="inlineStr">
+      <c r="D20" s="17" t="inlineStr">
         <is>
           <t>0.1666±0.0366</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="E20" s="17" t="inlineStr">
         <is>
           <t>0.7824±0.0215</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
+      <c r="F20" s="17" t="inlineStr">
         <is>
           <t>0.5490±0.0115</t>
         </is>
@@ -1172,17 +1194,17 @@
       <c r="C21" t="n">
         <v>5.82</v>
       </c>
-      <c r="D21" t="inlineStr">
+      <c r="D21" s="17" t="inlineStr">
         <is>
           <t>0.4913±0.0096</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="E21" s="17" t="inlineStr">
         <is>
           <t>0.8366±0.0100</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
+      <c r="F21" s="17" t="inlineStr">
         <is>
           <t>0.5000±0.0000</t>
         </is>
@@ -1197,17 +1219,17 @@
       <c r="C22" t="n">
         <v>35.45</v>
       </c>
-      <c r="D22" t="inlineStr">
+      <c r="D22" s="17" t="inlineStr">
         <is>
           <t>0.1993±0.0496</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="E22" s="17" t="inlineStr">
         <is>
           <t>0.8105±0.0419</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
+      <c r="F22" s="17" t="inlineStr">
         <is>
           <t>0.5787±0.0441</t>
         </is>
@@ -1222,24 +1244,19 @@
       <c r="C23" t="n">
         <v>25.69</v>
       </c>
-      <c r="D23" t="inlineStr">
+      <c r="D23" s="17" t="inlineStr">
         <is>
           <t>0.1283±0.0252</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="E23" s="17" t="inlineStr">
         <is>
           <t>0.8645±0.0139</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
+      <c r="F23" s="17" t="inlineStr">
         <is>
           <t>0.5027±0.0039</t>
-        </is>
-      </c>
-      <c r="G23" s="6" t="inlineStr">
-        <is>
-          <t>不新排；仅新语料已有数字</t>
         </is>
       </c>
     </row>
@@ -1252,24 +1269,19 @@
       <c r="C24" t="n">
         <v>1.89</v>
       </c>
-      <c r="D24" t="inlineStr">
+      <c r="D24" s="17" t="inlineStr">
         <is>
           <t>0.0120±0.0073</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
+      <c r="E24" s="17" t="inlineStr">
         <is>
           <t>0.5482±0.0297</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
+      <c r="F24" s="17" t="inlineStr">
         <is>
           <t>0.5000±0.0000</t>
-        </is>
-      </c>
-      <c r="G24" s="6" t="inlineStr">
-        <is>
-          <t>不新排；仅新语料已有数字</t>
         </is>
       </c>
     </row>
@@ -1287,17 +1299,17 @@
       <c r="C25" t="n">
         <v>1.62</v>
       </c>
-      <c r="D25" s="8" t="inlineStr">
+      <c r="D25" s="20" t="inlineStr">
         <is>
           <t>0.1329 (1 seed)</t>
         </is>
       </c>
-      <c r="E25" s="8" t="inlineStr">
+      <c r="E25" s="19" t="inlineStr">
         <is>
           <t>0.8683 (1 seed)</t>
         </is>
       </c>
-      <c r="F25" s="8" t="inlineStr">
+      <c r="F25" s="20" t="inlineStr">
         <is>
           <t>0.5000 (1 seed)</t>
         </is>
@@ -1309,11 +1321,6 @@
           <t>PACLock (duplex, 预训练 v2)</t>
         </is>
       </c>
-      <c r="G26" s="6" t="inlineStr">
-        <is>
-          <t>band_norm_pac 目标</t>
-        </is>
-      </c>
     </row>
     <row r="27">
       <c r="B27" t="inlineStr">
@@ -1321,11 +1328,6 @@
           <t>PACLock (冻结探针, v2)</t>
         </is>
       </c>
-      <c r="G27" s="6" t="inlineStr">
-        <is>
-          <t>patch_len 200；表征质量协议</t>
-        </is>
-      </c>
     </row>
     <row r="28">
       <c r="B28" t="inlineStr">
@@ -1333,12 +1335,8 @@
           <t>PACLock (冻结探针, 随机初始化)</t>
         </is>
       </c>
-      <c r="G28" s="6" t="inlineStr">
-        <is>
-          <t>四道门第 4 门对照</t>
-        </is>
-      </c>
-    </row>
+    </row>
+    <row r="29"/>
     <row r="30">
       <c r="A30" s="6" t="inlineStr">
         <is>
@@ -1357,15 +1355,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G30"/>
+  <dimension ref="A1:F30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
     <col width="11" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
     <col width="46" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
@@ -1421,11 +1419,6 @@
           <t>Weighted F1</t>
         </is>
       </c>
-      <c r="G4" s="5" t="inlineStr">
-        <is>
-          <t>备注</t>
-        </is>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1438,11 +1431,6 @@
           <t>手工特征 (LR/LDA 取优)</t>
         </is>
       </c>
-      <c r="G5" s="6" t="inlineStr">
-        <is>
-          <t>bandpower+Hjorth+谱熵；四道门第 1 门</t>
-        </is>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1458,17 +1446,17 @@
       <c r="C6" t="n">
         <v>1.38</v>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D6" s="17" t="inlineStr">
         <is>
           <t>0.7345±0.0161</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E6" s="17" t="inlineStr">
         <is>
           <t>0.7790±0.0090</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="F6" s="17" t="inlineStr">
         <is>
           <t>0.7905±0.0113</t>
         </is>
@@ -1483,17 +1471,17 @@
       <c r="C7" t="n">
         <v>1.57</v>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D7" s="17" t="inlineStr">
         <is>
           <t>0.7520±0.0045</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E7" s="21" t="inlineStr">
         <is>
           <t>0.7947±0.0008</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F7" s="17" t="inlineStr">
         <is>
           <t>0.8063±0.0051</t>
         </is>
@@ -1508,17 +1496,17 @@
       <c r="C8" t="n">
         <v>3.15</v>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D8" s="17" t="inlineStr">
         <is>
           <t>0.7532±0.0058</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E8" s="17" t="inlineStr">
         <is>
           <t>0.7918±0.0018</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F8" s="17" t="inlineStr">
         <is>
           <t>0.8058±0.0032</t>
         </is>
@@ -1533,17 +1521,17 @@
       <c r="C9" t="n">
         <v>2.67</v>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D9" s="17" t="inlineStr">
         <is>
           <t>0.7337±0.0126</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E9" s="17" t="inlineStr">
         <is>
           <t>0.7723±0.0082</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F9" s="17" t="inlineStr">
         <is>
           <t>0.7890±0.0088</t>
         </is>
@@ -1558,17 +1546,17 @@
       <c r="C10" t="n">
         <v>3.42</v>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D10" s="17" t="inlineStr">
         <is>
           <t>0.3927±0.1105</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E10" s="17" t="inlineStr">
         <is>
           <t>0.5237±0.0668</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="F10" s="17" t="inlineStr">
         <is>
           <t>0.4926±0.1033</t>
         </is>
@@ -1580,11 +1568,6 @@
           <t>EEGNet (调参)</t>
         </is>
       </c>
-      <c r="G11" s="6" t="inlineStr">
-        <is>
-          <t>公开搜索预算调参</t>
-        </is>
-      </c>
     </row>
     <row r="12">
       <c r="B12" t="inlineStr">
@@ -1592,11 +1575,6 @@
           <t>EEGConformer (调参)</t>
         </is>
       </c>
-      <c r="G12" s="6" t="inlineStr">
-        <is>
-          <t>benchmark 文献最强单体</t>
-        </is>
-      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1612,17 +1590,17 @@
       <c r="C13" t="n">
         <v>3.19</v>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="D13" s="17" t="inlineStr">
         <is>
           <t>0.7364±0.0046</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="E13" s="17" t="inlineStr">
         <is>
           <t>0.7711±0.0040</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="F13" s="17" t="inlineStr">
         <is>
           <t>0.7866±0.0019</t>
         </is>
@@ -1637,17 +1615,17 @@
       <c r="C14" t="n">
         <v>5.82</v>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="D14" s="17" t="inlineStr">
         <is>
           <t>0.7366±0.0145</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="E14" s="17" t="inlineStr">
         <is>
           <t>0.7683±0.0119</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="F14" s="17" t="inlineStr">
         <is>
           <t>0.7927±0.0111</t>
         </is>
@@ -1662,17 +1640,17 @@
       <c r="C15" t="n">
         <v>26.47</v>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="D15" s="21" t="inlineStr">
         <is>
           <t>0.7540±0.0063</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="E15" s="17" t="inlineStr">
         <is>
           <t>0.7842±0.0059</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="F15" s="21" t="inlineStr">
         <is>
           <t>0.8105±0.0046</t>
         </is>
@@ -1687,17 +1665,17 @@
       <c r="C16" t="n">
         <v>25.69</v>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="D16" s="17" t="inlineStr">
         <is>
           <t>0.7001±0.0167</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="E16" s="17" t="inlineStr">
         <is>
           <t>0.7387±0.0205</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="F16" s="17" t="inlineStr">
         <is>
           <t>0.7589±0.0179</t>
         </is>
@@ -1712,24 +1690,19 @@
       <c r="C17" t="n">
         <v>1.89</v>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="D17" s="17" t="inlineStr">
         <is>
           <t>0.7102±0.0030</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="E17" s="17" t="inlineStr">
         <is>
           <t>0.7400±0.0067</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="F17" s="17" t="inlineStr">
         <is>
           <t>0.7736±0.0043</t>
-        </is>
-      </c>
-      <c r="G17" s="6" t="inlineStr">
-        <is>
-          <t>tokenizer 直接对手</t>
         </is>
       </c>
     </row>
@@ -1739,11 +1712,6 @@
           <t>REVE-Base (pretrained)</t>
         </is>
       </c>
-      <c r="G18" s="6" t="inlineStr">
-        <is>
-          <t>新增；HF 权重</t>
-        </is>
-      </c>
     </row>
     <row r="19">
       <c r="B19" t="inlineStr">
@@ -1751,11 +1719,6 @@
           <t>CSBrain (pretrained)</t>
         </is>
       </c>
-      <c r="G19" s="6" t="inlineStr">
-        <is>
-          <t>新增；GDrive 权重</t>
-        </is>
-      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1771,17 +1734,17 @@
       <c r="C20" t="n">
         <v>3.18</v>
       </c>
-      <c r="D20" t="inlineStr">
+      <c r="D20" s="17" t="inlineStr">
         <is>
           <t>0.7378±0.0031</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="E20" s="17" t="inlineStr">
         <is>
           <t>0.7642±0.0071</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
+      <c r="F20" s="17" t="inlineStr">
         <is>
           <t>0.7943±0.0027</t>
         </is>
@@ -1796,17 +1759,17 @@
       <c r="C21" t="n">
         <v>5.82</v>
       </c>
-      <c r="D21" t="inlineStr">
+      <c r="D21" s="17" t="inlineStr">
         <is>
           <t>0.6236±0.0107</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="E21" s="17" t="inlineStr">
         <is>
           <t>0.6660±0.0144</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
+      <c r="F21" s="17" t="inlineStr">
         <is>
           <t>0.6979±0.0115</t>
         </is>
@@ -1821,17 +1784,17 @@
       <c r="C22" t="n">
         <v>26.47</v>
       </c>
-      <c r="D22" t="inlineStr">
+      <c r="D22" s="17" t="inlineStr">
         <is>
           <t>0.6976±0.0052</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="E22" s="17" t="inlineStr">
         <is>
           <t>0.7428±0.0021</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
+      <c r="F22" s="17" t="inlineStr">
         <is>
           <t>0.7614±0.0067</t>
         </is>
@@ -1843,11 +1806,6 @@
           <t>EEGPT (scratch)</t>
         </is>
       </c>
-      <c r="G23" s="6" t="inlineStr">
-        <is>
-          <t>不新排；仅新语料已有数字</t>
-        </is>
-      </c>
     </row>
     <row r="24">
       <c r="B24" t="inlineStr">
@@ -1855,11 +1813,6 @@
           <t>TFM-Tokenizer (scratch)</t>
         </is>
       </c>
-      <c r="G24" s="6" t="inlineStr">
-        <is>
-          <t>不新排；仅新语料已有数字</t>
-        </is>
-      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1875,17 +1828,17 @@
       <c r="C25" t="n">
         <v>1.61</v>
       </c>
-      <c r="D25" s="8" t="inlineStr">
+      <c r="D25" s="20" t="inlineStr">
         <is>
           <t>0.7117 (1 seed)</t>
         </is>
       </c>
-      <c r="E25" s="8" t="inlineStr">
+      <c r="E25" s="20" t="inlineStr">
         <is>
           <t>0.7676 (1 seed)</t>
         </is>
       </c>
-      <c r="F25" s="8" t="inlineStr">
+      <c r="F25" s="20" t="inlineStr">
         <is>
           <t>0.7712 (1 seed)</t>
         </is>
@@ -1900,24 +1853,19 @@
       <c r="C26" t="n">
         <v>1.61</v>
       </c>
-      <c r="D26" s="8" t="inlineStr">
+      <c r="D26" s="20" t="inlineStr">
         <is>
           <t>0.7000 (1 seed)</t>
         </is>
       </c>
-      <c r="E26" s="8" t="inlineStr">
+      <c r="E26" s="20" t="inlineStr">
         <is>
           <t>0.7575 (1 seed)</t>
         </is>
       </c>
-      <c r="F26" s="8" t="inlineStr">
+      <c r="F26" s="20" t="inlineStr">
         <is>
           <t>0.7640 (1 seed)</t>
-        </is>
-      </c>
-      <c r="G26" s="6" t="inlineStr">
-        <is>
-          <t>band_norm_pac 目标</t>
         </is>
       </c>
     </row>
@@ -1927,11 +1875,6 @@
           <t>PACLock (冻结探针, v2)</t>
         </is>
       </c>
-      <c r="G27" s="6" t="inlineStr">
-        <is>
-          <t>patch_len 200；表征质量协议</t>
-        </is>
-      </c>
     </row>
     <row r="28">
       <c r="B28" t="inlineStr">
@@ -1939,12 +1882,8 @@
           <t>PACLock (冻结探针, 随机初始化)</t>
         </is>
       </c>
-      <c r="G28" s="6" t="inlineStr">
-        <is>
-          <t>四道门第 4 门对照</t>
-        </is>
-      </c>
-    </row>
+    </row>
+    <row r="29"/>
     <row r="30">
       <c r="A30" s="6" t="inlineStr">
         <is>
@@ -1963,15 +1902,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G30"/>
+  <dimension ref="A1:F30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
     <col width="11" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
     <col width="46" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
@@ -2027,11 +1966,6 @@
           <t>Weighted F1</t>
         </is>
       </c>
-      <c r="G4" s="5" t="inlineStr">
-        <is>
-          <t>备注</t>
-        </is>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -2044,11 +1978,6 @@
           <t>手工特征 (LR/LDA 取优)</t>
         </is>
       </c>
-      <c r="G5" s="6" t="inlineStr">
-        <is>
-          <t>bandpower+Hjorth+谱熵；四道门第 1 门</t>
-        </is>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -2064,17 +1993,17 @@
       <c r="C6" t="n">
         <v>0.99</v>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D6" s="21" t="inlineStr">
         <is>
           <t>0.6440±0.0070</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E6" s="21" t="inlineStr">
         <is>
           <t>0.5254±0.0094</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="F6" s="21" t="inlineStr">
         <is>
           <t>0.6428±0.0068</t>
         </is>
@@ -2089,17 +2018,17 @@
       <c r="C7" t="n">
         <v>1.58</v>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D7" s="17" t="inlineStr">
         <is>
           <t>0.4922±0.0111</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E7" s="17" t="inlineStr">
         <is>
           <t>0.3229±0.0148</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F7" s="17" t="inlineStr">
         <is>
           <t>0.4861±0.0153</t>
         </is>
@@ -2114,17 +2043,17 @@
       <c r="C8" t="n">
         <v>3.16</v>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D8" s="17" t="inlineStr">
         <is>
           <t>0.4291±0.0203</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E8" s="17" t="inlineStr">
         <is>
           <t>0.2389±0.0271</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F8" s="17" t="inlineStr">
         <is>
           <t>0.4119±0.0435</t>
         </is>
@@ -2139,17 +2068,17 @@
       <c r="C9" t="n">
         <v>2.41</v>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D9" s="17" t="inlineStr">
         <is>
           <t>0.4891±0.0097</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E9" s="17" t="inlineStr">
         <is>
           <t>0.3188±0.0130</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F9" s="17" t="inlineStr">
         <is>
           <t>0.4858±0.0093</t>
         </is>
@@ -2164,17 +2093,17 @@
       <c r="C10" t="n">
         <v>3.43</v>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D10" s="17" t="inlineStr">
         <is>
           <t>0.5471±0.0223</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E10" s="17" t="inlineStr">
         <is>
           <t>0.3961±0.0297</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="F10" s="17" t="inlineStr">
         <is>
           <t>0.5461±0.0228</t>
         </is>
@@ -2186,11 +2115,6 @@
           <t>EEGNet (调参)</t>
         </is>
       </c>
-      <c r="G11" s="6" t="inlineStr">
-        <is>
-          <t>公开搜索预算调参</t>
-        </is>
-      </c>
     </row>
     <row r="12">
       <c r="B12" t="inlineStr">
@@ -2198,11 +2122,6 @@
           <t>EEGConformer (调参)</t>
         </is>
       </c>
-      <c r="G12" s="6" t="inlineStr">
-        <is>
-          <t>benchmark 文献最强单体</t>
-        </is>
-      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -2218,17 +2137,17 @@
       <c r="C13" t="n">
         <v>3.19</v>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="D13" s="17" t="inlineStr">
         <is>
           <t>0.4662±0.0066</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="E13" s="17" t="inlineStr">
         <is>
           <t>0.2882±0.0088</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="F13" s="17" t="inlineStr">
         <is>
           <t>0.4557±0.0139</t>
         </is>
@@ -2243,17 +2162,17 @@
       <c r="C14" t="n">
         <v>5.82</v>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="D14" s="17" t="inlineStr">
         <is>
           <t>0.4227±0.0246</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="E14" s="17" t="inlineStr">
         <is>
           <t>0.2303±0.0329</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="F14" s="17" t="inlineStr">
         <is>
           <t>0.4224±0.0240</t>
         </is>
@@ -2268,17 +2187,17 @@
       <c r="C15" t="n">
         <v>19.13</v>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="D15" s="17" t="inlineStr">
         <is>
           <t>0.5293±0.0036</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="E15" s="17" t="inlineStr">
         <is>
           <t>0.3724±0.0048</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="F15" s="17" t="inlineStr">
         <is>
           <t>0.5300±0.0036</t>
         </is>
@@ -2293,17 +2212,17 @@
       <c r="C16" t="n">
         <v>25.69</v>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="D16" s="17" t="inlineStr">
         <is>
           <t>0.3773±0.0197</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="E16" s="17" t="inlineStr">
         <is>
           <t>0.1698±0.0263</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="F16" s="17" t="inlineStr">
         <is>
           <t>0.3639±0.0144</t>
         </is>
@@ -2318,24 +2237,19 @@
       <c r="C17" t="n">
         <v>1.89</v>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="D17" s="17" t="inlineStr">
         <is>
           <t>0.3405±0.0214</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="E17" s="17" t="inlineStr">
         <is>
           <t>0.1207±0.0285</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="F17" s="17" t="inlineStr">
         <is>
           <t>0.3364±0.0185</t>
-        </is>
-      </c>
-      <c r="G17" s="6" t="inlineStr">
-        <is>
-          <t>tokenizer 直接对手</t>
         </is>
       </c>
     </row>
@@ -2345,11 +2259,6 @@
           <t>REVE-Base (pretrained)</t>
         </is>
       </c>
-      <c r="G18" s="6" t="inlineStr">
-        <is>
-          <t>新增；HF 权重</t>
-        </is>
-      </c>
     </row>
     <row r="19">
       <c r="B19" t="inlineStr">
@@ -2357,11 +2266,6 @@
           <t>CSBrain (pretrained)</t>
         </is>
       </c>
-      <c r="G19" s="6" t="inlineStr">
-        <is>
-          <t>新增；GDrive 权重</t>
-        </is>
-      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2377,17 +2281,17 @@
       <c r="C20" t="n">
         <v>3.19</v>
       </c>
-      <c r="D20" t="inlineStr">
+      <c r="D20" s="17" t="inlineStr">
         <is>
           <t>0.3281±0.0013</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="E20" s="17" t="inlineStr">
         <is>
           <t>0.1041±0.0017</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
+      <c r="F20" s="17" t="inlineStr">
         <is>
           <t>0.3219±0.0057</t>
         </is>
@@ -2402,17 +2306,17 @@
       <c r="C21" t="n">
         <v>5.82</v>
       </c>
-      <c r="D21" t="inlineStr">
+      <c r="D21" s="17" t="inlineStr">
         <is>
           <t>0.3147±0.0124</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="E21" s="17" t="inlineStr">
         <is>
           <t>0.0862±0.0165</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
+      <c r="F21" s="17" t="inlineStr">
         <is>
           <t>0.2972±0.0130</t>
         </is>
@@ -2427,17 +2331,17 @@
       <c r="C22" t="n">
         <v>19.13</v>
       </c>
-      <c r="D22" t="inlineStr">
+      <c r="D22" s="17" t="inlineStr">
         <is>
           <t>0.3043±0.0083</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="E22" s="17" t="inlineStr">
         <is>
           <t>0.0724±0.0111</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
+      <c r="F22" s="17" t="inlineStr">
         <is>
           <t>0.3013±0.0114</t>
         </is>
@@ -2449,11 +2353,6 @@
           <t>EEGPT (scratch)</t>
         </is>
       </c>
-      <c r="G23" s="6" t="inlineStr">
-        <is>
-          <t>不新排；仅新语料已有数字</t>
-        </is>
-      </c>
     </row>
     <row r="24">
       <c r="B24" t="inlineStr">
@@ -2461,11 +2360,6 @@
           <t>TFM-Tokenizer (scratch)</t>
         </is>
       </c>
-      <c r="G24" s="6" t="inlineStr">
-        <is>
-          <t>不新排；仅新语料已有数字</t>
-        </is>
-      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2481,17 +2375,17 @@
       <c r="C25" t="n">
         <v>1.61</v>
       </c>
-      <c r="D25" s="8" t="inlineStr">
+      <c r="D25" s="20" t="inlineStr">
         <is>
           <t>0.3920 (1 seed)</t>
         </is>
       </c>
-      <c r="E25" s="8" t="inlineStr">
+      <c r="E25" s="20" t="inlineStr">
         <is>
           <t>0.1893 (1 seed)</t>
         </is>
       </c>
-      <c r="F25" s="8" t="inlineStr">
+      <c r="F25" s="20" t="inlineStr">
         <is>
           <t>0.3852 (1 seed)</t>
         </is>
@@ -2503,11 +2397,6 @@
           <t>PACLock (duplex, 预训练 v2)</t>
         </is>
       </c>
-      <c r="G26" s="6" t="inlineStr">
-        <is>
-          <t>band_norm_pac 目标</t>
-        </is>
-      </c>
     </row>
     <row r="27">
       <c r="B27" t="inlineStr">
@@ -2515,11 +2404,6 @@
           <t>PACLock (冻结探针, v2)</t>
         </is>
       </c>
-      <c r="G27" s="6" t="inlineStr">
-        <is>
-          <t>patch_len 200；表征质量协议</t>
-        </is>
-      </c>
     </row>
     <row r="28">
       <c r="B28" t="inlineStr">
@@ -2527,12 +2411,8 @@
           <t>PACLock (冻结探针, 随机初始化)</t>
         </is>
       </c>
-      <c r="G28" s="6" t="inlineStr">
-        <is>
-          <t>四道门第 4 门对照</t>
-        </is>
-      </c>
-    </row>
+    </row>
+    <row r="29"/>
     <row r="30">
       <c r="A30" s="6" t="inlineStr">
         <is>
@@ -2551,15 +2431,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G30"/>
+  <dimension ref="A1:F30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
     <col width="11" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
     <col width="46" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
@@ -2615,11 +2495,6 @@
           <t>Weighted F1</t>
         </is>
       </c>
-      <c r="G4" s="5" t="inlineStr">
-        <is>
-          <t>备注</t>
-        </is>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -2632,11 +2507,6 @@
           <t>手工特征 (LR/LDA 取优)</t>
         </is>
       </c>
-      <c r="G5" s="6" t="inlineStr">
-        <is>
-          <t>bandpower+Hjorth+谱熵；四道门第 1 门</t>
-        </is>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -2652,17 +2522,17 @@
       <c r="C6" t="n">
         <v>1.23</v>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D6" s="17" t="inlineStr">
         <is>
           <t>0.6714±0.0095</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E6" s="17" t="inlineStr">
         <is>
           <t>0.6855±0.0018</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="F6" s="17" t="inlineStr">
         <is>
           <t>0.7718±0.0058</t>
         </is>
@@ -2677,17 +2547,17 @@
       <c r="C7" t="n">
         <v>1.56</v>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D7" s="21" t="inlineStr">
         <is>
           <t>0.6916±0.0119</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E7" s="21" t="inlineStr">
         <is>
           <t>0.7059±0.0080</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F7" s="21" t="inlineStr">
         <is>
           <t>0.7866±0.0098</t>
         </is>
@@ -2702,17 +2572,17 @@
       <c r="C8" t="n">
         <v>3.15</v>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D8" s="17" t="inlineStr">
         <is>
           <t>0.6778±0.0116</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E8" s="17" t="inlineStr">
         <is>
           <t>0.6989±0.0105</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F8" s="17" t="inlineStr">
         <is>
           <t>0.7771±0.0075</t>
         </is>
@@ -2727,17 +2597,17 @@
       <c r="C9" t="n">
         <v>2.51</v>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D9" s="17" t="inlineStr">
         <is>
           <t>0.6780±0.0039</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E9" s="17" t="inlineStr">
         <is>
           <t>0.6963±0.0082</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F9" s="17" t="inlineStr">
         <is>
           <t>0.7716±0.0066</t>
         </is>
@@ -2752,17 +2622,17 @@
       <c r="C10" t="n">
         <v>3.41</v>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D10" s="17" t="inlineStr">
         <is>
           <t>0.6553±0.0032</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E10" s="17" t="inlineStr">
         <is>
           <t>0.6576±0.0062</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="F10" s="17" t="inlineStr">
         <is>
           <t>0.7607±0.0033</t>
         </is>
@@ -2774,11 +2644,6 @@
           <t>EEGNet (调参)</t>
         </is>
       </c>
-      <c r="G11" s="6" t="inlineStr">
-        <is>
-          <t>公开搜索预算调参</t>
-        </is>
-      </c>
     </row>
     <row r="12">
       <c r="B12" t="inlineStr">
@@ -2786,11 +2651,6 @@
           <t>EEGConformer (调参)</t>
         </is>
       </c>
-      <c r="G12" s="6" t="inlineStr">
-        <is>
-          <t>benchmark 文献最强单体</t>
-        </is>
-      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -2806,17 +2666,17 @@
       <c r="C13" t="n">
         <v>3.19</v>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="D13" s="17" t="inlineStr">
         <is>
           <t>0.5940±0.0154</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="E13" s="17" t="inlineStr">
         <is>
           <t>0.5625±0.0302</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="F13" s="17" t="inlineStr">
         <is>
           <t>0.7172±0.0128</t>
         </is>
@@ -2831,17 +2691,17 @@
       <c r="C14" t="n">
         <v>5.82</v>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="D14" s="17" t="inlineStr">
         <is>
           <t>0.6100±0.0065</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="E14" s="17" t="inlineStr">
         <is>
           <t>0.6399±0.0144</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="F14" s="17" t="inlineStr">
         <is>
           <t>0.7321±0.0069</t>
         </is>
@@ -2856,17 +2716,17 @@
       <c r="C15" t="n">
         <v>9.85</v>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="D15" s="17" t="inlineStr">
         <is>
           <t>0.6715±0.0040</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="E15" s="17" t="inlineStr">
         <is>
           <t>0.6848±0.0135</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="F15" s="17" t="inlineStr">
         <is>
           <t>0.7665±0.0031</t>
         </is>
@@ -2881,17 +2741,17 @@
       <c r="C16" t="n">
         <v>25.69</v>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="D16" s="17" t="inlineStr">
         <is>
           <t>0.5978±0.0105</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="E16" s="17" t="inlineStr">
         <is>
           <t>0.6385±0.0099</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="F16" s="17" t="inlineStr">
         <is>
           <t>0.7253±0.0063</t>
         </is>
@@ -2906,24 +2766,19 @@
       <c r="C17" t="n">
         <v>1.89</v>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="D17" s="17" t="inlineStr">
         <is>
           <t>0.6138±0.0020</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="E17" s="17" t="inlineStr">
         <is>
           <t>0.5574±0.0075</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="F17" s="17" t="inlineStr">
         <is>
           <t>0.7266±0.0014</t>
-        </is>
-      </c>
-      <c r="G17" s="6" t="inlineStr">
-        <is>
-          <t>tokenizer 直接对手</t>
         </is>
       </c>
     </row>
@@ -2933,11 +2788,6 @@
           <t>REVE-Base (pretrained)</t>
         </is>
       </c>
-      <c r="G18" s="6" t="inlineStr">
-        <is>
-          <t>新增；HF 权重</t>
-        </is>
-      </c>
     </row>
     <row r="19">
       <c r="B19" t="inlineStr">
@@ -2945,11 +2795,6 @@
           <t>CSBrain (pretrained)</t>
         </is>
       </c>
-      <c r="G19" s="6" t="inlineStr">
-        <is>
-          <t>新增；GDrive 权重</t>
-        </is>
-      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2965,17 +2810,17 @@
       <c r="C20" t="n">
         <v>3.18</v>
       </c>
-      <c r="D20" t="inlineStr">
+      <c r="D20" s="17" t="inlineStr">
         <is>
           <t>0.6547±0.0157</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="E20" s="17" t="inlineStr">
         <is>
           <t>0.6372±0.0118</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
+      <c r="F20" s="17" t="inlineStr">
         <is>
           <t>0.7655±0.0068</t>
         </is>
@@ -2990,17 +2835,17 @@
       <c r="C21" t="n">
         <v>5.82</v>
       </c>
-      <c r="D21" t="inlineStr">
+      <c r="D21" s="17" t="inlineStr">
         <is>
           <t>0.5980±0.0081</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="E21" s="17" t="inlineStr">
         <is>
           <t>0.6138±0.0065</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
+      <c r="F21" s="17" t="inlineStr">
         <is>
           <t>0.7150±0.0076</t>
         </is>
@@ -3015,17 +2860,17 @@
       <c r="C22" t="n">
         <v>9.85</v>
       </c>
-      <c r="D22" t="inlineStr">
+      <c r="D22" s="17" t="inlineStr">
         <is>
           <t>0.6545±0.0029</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="E22" s="17" t="inlineStr">
         <is>
           <t>0.6588±0.0028</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
+      <c r="F22" s="17" t="inlineStr">
         <is>
           <t>0.7614±0.0033</t>
         </is>
@@ -3037,11 +2882,6 @@
           <t>EEGPT (scratch)</t>
         </is>
       </c>
-      <c r="G23" s="6" t="inlineStr">
-        <is>
-          <t>不新排；仅新语料已有数字</t>
-        </is>
-      </c>
     </row>
     <row r="24">
       <c r="B24" t="inlineStr">
@@ -3049,11 +2889,6 @@
           <t>TFM-Tokenizer (scratch)</t>
         </is>
       </c>
-      <c r="G24" s="6" t="inlineStr">
-        <is>
-          <t>不新排；仅新语料已有数字</t>
-        </is>
-      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -3069,17 +2904,17 @@
       <c r="C25" t="n">
         <v>1.62</v>
       </c>
-      <c r="D25" s="8" t="inlineStr">
+      <c r="D25" s="20" t="inlineStr">
         <is>
           <t>0.6533 (1 seed)</t>
         </is>
       </c>
-      <c r="E25" s="8" t="inlineStr">
+      <c r="E25" s="20" t="inlineStr">
         <is>
           <t>0.6276 (1 seed)</t>
         </is>
       </c>
-      <c r="F25" s="8" t="inlineStr">
+      <c r="F25" s="20" t="inlineStr">
         <is>
           <t>0.7597 (1 seed)</t>
         </is>
@@ -3094,24 +2929,19 @@
       <c r="C26" t="n">
         <v>1.62</v>
       </c>
-      <c r="D26" s="8" t="inlineStr">
+      <c r="D26" s="20" t="inlineStr">
         <is>
           <t>0.6775 (1 seed)</t>
         </is>
       </c>
-      <c r="E26" s="8" t="inlineStr">
+      <c r="E26" s="20" t="inlineStr">
         <is>
           <t>0.6578 (1 seed)</t>
         </is>
       </c>
-      <c r="F26" s="8" t="inlineStr">
+      <c r="F26" s="20" t="inlineStr">
         <is>
           <t>0.7769 (1 seed)</t>
-        </is>
-      </c>
-      <c r="G26" s="6" t="inlineStr">
-        <is>
-          <t>band_norm_pac 目标</t>
         </is>
       </c>
     </row>
@@ -3121,11 +2951,6 @@
           <t>PACLock (冻结探针, v2)</t>
         </is>
       </c>
-      <c r="G27" s="6" t="inlineStr">
-        <is>
-          <t>patch_len 200；表征质量协议</t>
-        </is>
-      </c>
     </row>
     <row r="28">
       <c r="B28" t="inlineStr">
@@ -3133,12 +2958,8 @@
           <t>PACLock (冻结探针, 随机初始化)</t>
         </is>
       </c>
-      <c r="G28" s="6" t="inlineStr">
-        <is>
-          <t>四道门第 4 门对照</t>
-        </is>
-      </c>
-    </row>
+    </row>
+    <row r="29"/>
     <row r="30">
       <c r="A30" s="6" t="inlineStr">
         <is>
@@ -3157,15 +2978,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G30"/>
+  <dimension ref="A1:F30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
     <col width="11" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
     <col width="46" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
@@ -3221,11 +3042,6 @@
           <t>Weighted F1</t>
         </is>
       </c>
-      <c r="G4" s="5" t="inlineStr">
-        <is>
-          <t>备注</t>
-        </is>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -3238,11 +3054,6 @@
           <t>手工特征 (LR/LDA 取优)</t>
         </is>
       </c>
-      <c r="G5" s="6" t="inlineStr">
-        <is>
-          <t>bandpower+Hjorth+谱熵；四道门第 1 门</t>
-        </is>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -3258,17 +3069,17 @@
       <c r="C6" t="n">
         <v>1.27</v>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D6" s="17" t="inlineStr">
         <is>
           <t>0.5905±0.0036</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E6" s="17" t="inlineStr">
         <is>
           <t>0.4540±0.0048</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="F6" s="17" t="inlineStr">
         <is>
           <t>0.5916±0.0057</t>
         </is>
@@ -3283,17 +3094,17 @@
       <c r="C7" t="n">
         <v>1.6</v>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D7" s="17" t="inlineStr">
         <is>
           <t>0.4891±0.0063</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E7" s="17" t="inlineStr">
         <is>
           <t>0.3188±0.0085</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F7" s="17" t="inlineStr">
         <is>
           <t>0.4848±0.0026</t>
         </is>
@@ -3308,17 +3119,17 @@
       <c r="C8" t="n">
         <v>3.18</v>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D8" s="17" t="inlineStr">
         <is>
           <t>0.4610±0.0089</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E8" s="17" t="inlineStr">
         <is>
           <t>0.2815±0.0118</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F8" s="17" t="inlineStr">
         <is>
           <t>0.4505±0.0099</t>
         </is>
@@ -3333,17 +3144,17 @@
       <c r="C9" t="n">
         <v>2.43</v>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D9" s="17" t="inlineStr">
         <is>
           <t>0.4935±0.0125</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E9" s="17" t="inlineStr">
         <is>
           <t>0.3246±0.0166</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F9" s="17" t="inlineStr">
         <is>
           <t>0.4903±0.0157</t>
         </is>
@@ -3358,17 +3169,17 @@
       <c r="C10" t="n">
         <v>3.48</v>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D10" s="17" t="inlineStr">
         <is>
           <t>0.5938±0.0136</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E10" s="17" t="inlineStr">
         <is>
           <t>0.4584±0.0181</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="F10" s="17" t="inlineStr">
         <is>
           <t>0.5940±0.0128</t>
         </is>
@@ -3380,11 +3191,6 @@
           <t>EEGNet (调参)</t>
         </is>
       </c>
-      <c r="G11" s="6" t="inlineStr">
-        <is>
-          <t>公开搜索预算调参</t>
-        </is>
-      </c>
     </row>
     <row r="12">
       <c r="B12" t="inlineStr">
@@ -3392,11 +3198,6 @@
           <t>EEGConformer (调参)</t>
         </is>
       </c>
-      <c r="G12" s="6" t="inlineStr">
-        <is>
-          <t>benchmark 文献最强单体</t>
-        </is>
-      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -3412,17 +3213,17 @@
       <c r="C13" t="n">
         <v>3.19</v>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="D13" s="17" t="inlineStr">
         <is>
           <t>0.5037±0.0072</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="E13" s="17" t="inlineStr">
         <is>
           <t>0.3380±0.0096</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="F13" s="17" t="inlineStr">
         <is>
           <t>0.5046±0.0049</t>
         </is>
@@ -3437,17 +3238,17 @@
       <c r="C14" t="n">
         <v>5.82</v>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="D14" s="17" t="inlineStr">
         <is>
           <t>0.5573±0.0159</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="E14" s="17" t="inlineStr">
         <is>
           <t>0.4096±0.0211</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="F14" s="17" t="inlineStr">
         <is>
           <t>0.5594±0.0157</t>
         </is>
@@ -3462,17 +3263,17 @@
       <c r="C15" t="n">
         <v>46.01</v>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="D15" s="21" t="inlineStr">
         <is>
           <t>0.6129±0.0094</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="E15" s="21" t="inlineStr">
         <is>
           <t>0.4838±0.0125</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="F15" s="21" t="inlineStr">
         <is>
           <t>0.6122±0.0094</t>
         </is>
@@ -3487,17 +3288,17 @@
       <c r="C16" t="n">
         <v>25.69</v>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="D16" s="17" t="inlineStr">
         <is>
           <t>0.4046±0.0397</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="E16" s="17" t="inlineStr">
         <is>
           <t>0.2060±0.0528</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="F16" s="17" t="inlineStr">
         <is>
           <t>0.4045±0.0409</t>
         </is>
@@ -3512,24 +3313,19 @@
       <c r="C17" t="n">
         <v>1.89</v>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="D17" s="17" t="inlineStr">
         <is>
           <t>0.4322±0.0143</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="E17" s="17" t="inlineStr">
         <is>
           <t>0.2429±0.0191</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="F17" s="17" t="inlineStr">
         <is>
           <t>0.4324±0.0147</t>
-        </is>
-      </c>
-      <c r="G17" s="6" t="inlineStr">
-        <is>
-          <t>tokenizer 直接对手</t>
         </is>
       </c>
     </row>
@@ -3539,11 +3335,6 @@
           <t>REVE-Base (pretrained)</t>
         </is>
       </c>
-      <c r="G18" s="6" t="inlineStr">
-        <is>
-          <t>新增；HF 权重</t>
-        </is>
-      </c>
     </row>
     <row r="19">
       <c r="B19" t="inlineStr">
@@ -3551,11 +3342,6 @@
           <t>CSBrain (pretrained)</t>
         </is>
       </c>
-      <c r="G19" s="6" t="inlineStr">
-        <is>
-          <t>新增；GDrive 权重</t>
-        </is>
-      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -3571,17 +3357,17 @@
       <c r="C20" t="n">
         <v>3.2</v>
       </c>
-      <c r="D20" t="inlineStr">
+      <c r="D20" s="17" t="inlineStr">
         <is>
           <t>0.3099±0.0292</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="E20" s="17" t="inlineStr">
         <is>
           <t>0.0800±0.0390</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
+      <c r="F20" s="17" t="inlineStr">
         <is>
           <t>0.2901±0.0544</t>
         </is>
@@ -3596,17 +3382,17 @@
       <c r="C21" t="n">
         <v>5.82</v>
       </c>
-      <c r="D21" t="inlineStr">
+      <c r="D21" s="17" t="inlineStr">
         <is>
           <t>0.3667±0.0142</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="E21" s="17" t="inlineStr">
         <is>
           <t>0.1555±0.0190</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
+      <c r="F21" s="17" t="inlineStr">
         <is>
           <t>0.3644±0.0163</t>
         </is>
@@ -3621,17 +3407,17 @@
       <c r="C22" t="n">
         <v>46.01</v>
       </c>
-      <c r="D22" t="inlineStr">
+      <c r="D22" s="17" t="inlineStr">
         <is>
           <t>0.5537±0.0033</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="E22" s="17" t="inlineStr">
         <is>
           <t>0.4049±0.0044</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
+      <c r="F22" s="17" t="inlineStr">
         <is>
           <t>0.5546±0.0044</t>
         </is>
@@ -3643,11 +3429,6 @@
           <t>EEGPT (scratch)</t>
         </is>
       </c>
-      <c r="G23" s="6" t="inlineStr">
-        <is>
-          <t>不新排；仅新语料已有数字</t>
-        </is>
-      </c>
     </row>
     <row r="24">
       <c r="B24" t="inlineStr">
@@ -3655,11 +3436,6 @@
           <t>TFM-Tokenizer (scratch)</t>
         </is>
       </c>
-      <c r="G24" s="6" t="inlineStr">
-        <is>
-          <t>不新排；仅新语料已有数字</t>
-        </is>
-      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -3679,11 +3455,6 @@
           <t>PACLock (duplex, 预训练 v2)</t>
         </is>
       </c>
-      <c r="G26" s="6" t="inlineStr">
-        <is>
-          <t>band_norm_pac 目标</t>
-        </is>
-      </c>
     </row>
     <row r="27">
       <c r="B27" t="inlineStr">
@@ -3691,11 +3462,6 @@
           <t>PACLock (冻结探针, v2)</t>
         </is>
       </c>
-      <c r="G27" s="6" t="inlineStr">
-        <is>
-          <t>patch_len 200；表征质量协议</t>
-        </is>
-      </c>
     </row>
     <row r="28">
       <c r="B28" t="inlineStr">
@@ -3703,12 +3469,8 @@
           <t>PACLock (冻结探针, 随机初始化)</t>
         </is>
       </c>
-      <c r="G28" s="6" t="inlineStr">
-        <is>
-          <t>四道门第 4 门对照</t>
-        </is>
-      </c>
-    </row>
+    </row>
+    <row r="29"/>
     <row r="30">
       <c r="A30" s="6" t="inlineStr">
         <is>
@@ -3727,15 +3489,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G30"/>
+  <dimension ref="A1:F30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
     <col width="11" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
     <col width="46" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
@@ -3791,11 +3553,6 @@
           <t>Weighted F1</t>
         </is>
       </c>
-      <c r="G4" s="5" t="inlineStr">
-        <is>
-          <t>备注</t>
-        </is>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -3808,11 +3565,6 @@
           <t>手工特征 (LR/LDA 取优)</t>
         </is>
       </c>
-      <c r="G5" s="6" t="inlineStr">
-        <is>
-          <t>bandpower+Hjorth+谱熵；四道门第 1 门</t>
-        </is>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -3828,17 +3580,17 @@
       <c r="C6" t="n">
         <v>1.23</v>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D6" s="17" t="inlineStr">
         <is>
           <t>0.2637±0.0137</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E6" s="17" t="inlineStr">
         <is>
           <t>0.1685±0.0153</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="F6" s="17" t="inlineStr">
         <is>
           <t>0.2451±0.0131</t>
         </is>
@@ -3853,17 +3605,17 @@
       <c r="C7" t="n">
         <v>1.58</v>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D7" s="17" t="inlineStr">
         <is>
           <t>0.2014±0.0210</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E7" s="17" t="inlineStr">
         <is>
           <t>0.0994±0.0232</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F7" s="17" t="inlineStr">
         <is>
           <t>0.1638±0.0352</t>
         </is>
@@ -3878,17 +3630,17 @@
       <c r="C8" t="n">
         <v>3.17</v>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D8" s="17" t="inlineStr">
         <is>
           <t>0.2116±0.0425</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E8" s="17" t="inlineStr">
         <is>
           <t>0.1117±0.0473</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F8" s="17" t="inlineStr">
         <is>
           <t>0.1903±0.0492</t>
         </is>
@@ -3903,17 +3655,17 @@
       <c r="C9" t="n">
         <v>2.48</v>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D9" s="17" t="inlineStr">
         <is>
           <t>0.2392±0.0141</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E9" s="17" t="inlineStr">
         <is>
           <t>0.1406±0.0154</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F9" s="17" t="inlineStr">
         <is>
           <t>0.2266±0.0103</t>
         </is>
@@ -3928,17 +3680,17 @@
       <c r="C10" t="n">
         <v>3.45</v>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D10" s="17" t="inlineStr">
         <is>
           <t>0.3197±0.0177</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E10" s="17" t="inlineStr">
         <is>
           <t>0.2330±0.0190</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="F10" s="17" t="inlineStr">
         <is>
           <t>0.3195±0.0195</t>
         </is>
@@ -3950,11 +3702,6 @@
           <t>EEGNet (调参)</t>
         </is>
       </c>
-      <c r="G11" s="6" t="inlineStr">
-        <is>
-          <t>公开搜索预算调参</t>
-        </is>
-      </c>
     </row>
     <row r="12">
       <c r="B12" t="inlineStr">
@@ -3962,11 +3709,6 @@
           <t>EEGConformer (调参)</t>
         </is>
       </c>
-      <c r="G12" s="6" t="inlineStr">
-        <is>
-          <t>benchmark 文献最强单体</t>
-        </is>
-      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -3982,17 +3724,17 @@
       <c r="C13" t="n">
         <v>3.19</v>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="D13" s="17" t="inlineStr">
         <is>
           <t>0.2195±0.0175</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="E13" s="17" t="inlineStr">
         <is>
           <t>0.1208±0.0182</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="F13" s="17" t="inlineStr">
         <is>
           <t>0.2088±0.0238</t>
         </is>
@@ -4007,17 +3749,17 @@
       <c r="C14" t="n">
         <v>5.82</v>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="D14" s="17" t="inlineStr">
         <is>
           <t>0.3272±0.0015</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="E14" s="17" t="inlineStr">
         <is>
           <t>0.2409±0.0009</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="F14" s="17" t="inlineStr">
         <is>
           <t>0.3240±0.0003</t>
         </is>
@@ -4032,17 +3774,17 @@
       <c r="C15" t="n">
         <v>56.25</v>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="D15" s="21" t="inlineStr">
         <is>
           <t>0.5509±0.0034</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="E15" s="21" t="inlineStr">
         <is>
           <t>0.4923±0.0034</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="F15" s="21" t="inlineStr">
         <is>
           <t>0.5557±0.0027</t>
         </is>
@@ -4057,17 +3799,17 @@
       <c r="C16" t="n">
         <v>25.69</v>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="D16" s="17" t="inlineStr">
         <is>
           <t>0.1718±0.0091</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="E16" s="17" t="inlineStr">
         <is>
           <t>0.0703±0.0095</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="F16" s="17" t="inlineStr">
         <is>
           <t>0.1590±0.0089</t>
         </is>
@@ -4082,24 +3824,19 @@
       <c r="C17" t="n">
         <v>1.89</v>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="D17" s="17" t="inlineStr">
         <is>
           <t>0.2359±0.0108</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="E17" s="17" t="inlineStr">
         <is>
           <t>0.1391±0.0124</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="F17" s="17" t="inlineStr">
         <is>
           <t>0.2312±0.0102</t>
-        </is>
-      </c>
-      <c r="G17" s="6" t="inlineStr">
-        <is>
-          <t>tokenizer 直接对手</t>
         </is>
       </c>
     </row>
@@ -4109,11 +3846,6 @@
           <t>REVE-Base (pretrained)</t>
         </is>
       </c>
-      <c r="G18" s="6" t="inlineStr">
-        <is>
-          <t>新增；HF 权重</t>
-        </is>
-      </c>
     </row>
     <row r="19">
       <c r="B19" t="inlineStr">
@@ -4121,11 +3853,6 @@
           <t>CSBrain (pretrained)</t>
         </is>
       </c>
-      <c r="G19" s="6" t="inlineStr">
-        <is>
-          <t>新增；GDrive 权重</t>
-        </is>
-      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -4141,17 +3868,17 @@
       <c r="C20" t="n">
         <v>3.19</v>
       </c>
-      <c r="D20" t="inlineStr">
+      <c r="D20" s="17" t="inlineStr">
         <is>
           <t>0.1854±0.0074</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="E20" s="17" t="inlineStr">
         <is>
           <t>0.0828±0.0083</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
+      <c r="F20" s="17" t="inlineStr">
         <is>
           <t>0.1748±0.0098</t>
         </is>
@@ -4166,17 +3893,17 @@
       <c r="C21" t="n">
         <v>5.82</v>
       </c>
-      <c r="D21" t="inlineStr">
+      <c r="D21" s="17" t="inlineStr">
         <is>
           <t>0.1583±0.0094</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="E21" s="17" t="inlineStr">
         <is>
           <t>0.0536±0.0112</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
+      <c r="F21" s="17" t="inlineStr">
         <is>
           <t>0.1548±0.0103</t>
         </is>
@@ -4195,11 +3922,6 @@
           <t>EEGPT (scratch)</t>
         </is>
       </c>
-      <c r="G23" s="6" t="inlineStr">
-        <is>
-          <t>不新排；仅新语料已有数字</t>
-        </is>
-      </c>
     </row>
     <row r="24">
       <c r="B24" t="inlineStr">
@@ -4207,11 +3929,6 @@
           <t>TFM-Tokenizer (scratch)</t>
         </is>
       </c>
-      <c r="G24" s="6" t="inlineStr">
-        <is>
-          <t>不新排；仅新语料已有数字</t>
-        </is>
-      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -4231,11 +3948,6 @@
           <t>PACLock (duplex, 预训练 v2)</t>
         </is>
       </c>
-      <c r="G26" s="6" t="inlineStr">
-        <is>
-          <t>band_norm_pac 目标</t>
-        </is>
-      </c>
     </row>
     <row r="27">
       <c r="B27" t="inlineStr">
@@ -4243,11 +3955,6 @@
           <t>PACLock (冻结探针, v2)</t>
         </is>
       </c>
-      <c r="G27" s="6" t="inlineStr">
-        <is>
-          <t>patch_len 200；表征质量协议</t>
-        </is>
-      </c>
     </row>
     <row r="28">
       <c r="B28" t="inlineStr">
@@ -4255,12 +3962,8 @@
           <t>PACLock (冻结探针, 随机初始化)</t>
         </is>
       </c>
-      <c r="G28" s="6" t="inlineStr">
-        <is>
-          <t>四道门第 4 门对照</t>
-        </is>
-      </c>
-    </row>
+    </row>
+    <row r="29"/>
     <row r="30">
       <c r="A30" s="6" t="inlineStr">
         <is>
@@ -4279,15 +3982,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G30"/>
+  <dimension ref="A1:F30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
     <col width="11" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
     <col width="46" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
@@ -4343,11 +4046,6 @@
           <t>Weighted F1</t>
         </is>
       </c>
-      <c r="G4" s="5" t="inlineStr">
-        <is>
-          <t>备注</t>
-        </is>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -4360,11 +4058,6 @@
           <t>手工特征 (LR/LDA 取优)</t>
         </is>
       </c>
-      <c r="G5" s="6" t="inlineStr">
-        <is>
-          <t>bandpower+Hjorth+谱熵；四道门第 1 门</t>
-        </is>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -4380,17 +4073,17 @@
       <c r="C6" t="n">
         <v>0.99</v>
       </c>
-      <c r="D6" s="8" t="inlineStr">
+      <c r="D6" s="22" t="inlineStr">
         <is>
           <t>0.6010 (1 seed)</t>
         </is>
       </c>
-      <c r="E6" s="8" t="inlineStr">
+      <c r="E6" s="22" t="inlineStr">
         <is>
           <t>0.7484 (1 seed)</t>
         </is>
       </c>
-      <c r="F6" s="8" t="inlineStr">
+      <c r="F6" s="22" t="inlineStr">
         <is>
           <t>0.7162 (1 seed)</t>
         </is>
@@ -4405,17 +4098,17 @@
       <c r="C7" t="n">
         <v>1.57</v>
       </c>
-      <c r="D7" s="8" t="inlineStr">
+      <c r="D7" s="22" t="inlineStr">
         <is>
           <t>0.6630 (1 seed)</t>
         </is>
       </c>
-      <c r="E7" s="8" t="inlineStr">
+      <c r="E7" s="22" t="inlineStr">
         <is>
           <t>0.7842 (1 seed)</t>
         </is>
       </c>
-      <c r="F7" s="8" t="inlineStr">
+      <c r="F7" s="22" t="inlineStr">
         <is>
           <t>0.7686 (1 seed)</t>
         </is>
@@ -4430,17 +4123,17 @@
       <c r="C8" t="n">
         <v>3.15</v>
       </c>
-      <c r="D8" s="8" t="inlineStr">
+      <c r="D8" s="22" t="inlineStr">
         <is>
           <t>0.7120 (1 seed)</t>
         </is>
       </c>
-      <c r="E8" s="8" t="inlineStr">
+      <c r="E8" s="22" t="inlineStr">
         <is>
           <t>0.8139 (1 seed)</t>
         </is>
       </c>
-      <c r="F8" s="8" t="inlineStr">
+      <c r="F8" s="22" t="inlineStr">
         <is>
           <t>0.8059 (1 seed)</t>
         </is>
@@ -4455,17 +4148,17 @@
       <c r="C9" t="n">
         <v>2.41</v>
       </c>
-      <c r="D9" s="8" t="inlineStr">
+      <c r="D9" s="22" t="inlineStr">
         <is>
           <t>0.6959 (1 seed)</t>
         </is>
       </c>
-      <c r="E9" s="8" t="inlineStr">
+      <c r="E9" s="22" t="inlineStr">
         <is>
           <t>0.8000 (1 seed)</t>
         </is>
       </c>
-      <c r="F9" s="8" t="inlineStr">
+      <c r="F9" s="22" t="inlineStr">
         <is>
           <t>0.7958 (1 seed)</t>
         </is>
@@ -4480,17 +4173,17 @@
       <c r="C10" t="n">
         <v>3.42</v>
       </c>
-      <c r="D10" s="8" t="inlineStr">
+      <c r="D10" s="22" t="inlineStr">
         <is>
           <t>0.5213 (1 seed)</t>
         </is>
       </c>
-      <c r="E10" s="8" t="inlineStr">
+      <c r="E10" s="22" t="inlineStr">
         <is>
           <t>0.6825 (1 seed)</t>
         </is>
       </c>
-      <c r="F10" s="8" t="inlineStr">
+      <c r="F10" s="22" t="inlineStr">
         <is>
           <t>0.6725 (1 seed)</t>
         </is>
@@ -4502,11 +4195,6 @@
           <t>EEGNet (调参)</t>
         </is>
       </c>
-      <c r="G11" s="6" t="inlineStr">
-        <is>
-          <t>公开搜索预算调参</t>
-        </is>
-      </c>
     </row>
     <row r="12">
       <c r="B12" t="inlineStr">
@@ -4514,11 +4202,6 @@
           <t>EEGConformer (调参)</t>
         </is>
       </c>
-      <c r="G12" s="6" t="inlineStr">
-        <is>
-          <t>benchmark 文献最强单体</t>
-        </is>
-      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -4534,17 +4217,17 @@
       <c r="C13" t="n">
         <v>3.19</v>
       </c>
-      <c r="D13" s="8" t="inlineStr">
+      <c r="D13" s="22" t="inlineStr">
         <is>
           <t>0.5750 (1 seed)</t>
         </is>
       </c>
-      <c r="E13" s="8" t="inlineStr">
+      <c r="E13" s="22" t="inlineStr">
         <is>
           <t>0.7282 (1 seed)</t>
         </is>
       </c>
-      <c r="F13" s="8" t="inlineStr">
+      <c r="F13" s="22" t="inlineStr">
         <is>
           <t>0.7047 (1 seed)</t>
         </is>
@@ -4559,17 +4242,17 @@
       <c r="C14" t="n">
         <v>5.82</v>
       </c>
-      <c r="D14" s="8" t="inlineStr">
+      <c r="D14" s="22" t="inlineStr">
         <is>
           <t>0.5931 (1 seed)</t>
         </is>
       </c>
-      <c r="E14" s="8" t="inlineStr">
+      <c r="E14" s="22" t="inlineStr">
         <is>
           <t>0.7433 (1 seed)</t>
         </is>
       </c>
-      <c r="F14" s="8" t="inlineStr">
+      <c r="F14" s="22" t="inlineStr">
         <is>
           <t>0.7150 (1 seed)</t>
         </is>
@@ -4584,17 +4267,17 @@
       <c r="C15" t="n">
         <v>17.85</v>
       </c>
-      <c r="D15" s="8" t="inlineStr">
+      <c r="D15" s="23" t="inlineStr">
         <is>
           <t>0.7147 (1 seed)</t>
         </is>
       </c>
-      <c r="E15" s="8" t="inlineStr">
+      <c r="E15" s="23" t="inlineStr">
         <is>
           <t>0.8153 (1 seed)</t>
         </is>
       </c>
-      <c r="F15" s="8" t="inlineStr">
+      <c r="F15" s="23" t="inlineStr">
         <is>
           <t>0.8078 (1 seed)</t>
         </is>
@@ -4609,17 +4292,17 @@
       <c r="C16" t="n">
         <v>25.69</v>
       </c>
-      <c r="D16" s="8" t="inlineStr">
+      <c r="D16" s="22" t="inlineStr">
         <is>
           <t>0.5235 (1 seed)</t>
         </is>
       </c>
-      <c r="E16" s="8" t="inlineStr">
+      <c r="E16" s="22" t="inlineStr">
         <is>
           <t>0.6982 (1 seed)</t>
         </is>
       </c>
-      <c r="F16" s="8" t="inlineStr">
+      <c r="F16" s="22" t="inlineStr">
         <is>
           <t>0.6652 (1 seed)</t>
         </is>
@@ -4634,24 +4317,19 @@
       <c r="C17" t="n">
         <v>1.89</v>
       </c>
-      <c r="D17" s="8" t="inlineStr">
+      <c r="D17" s="22" t="inlineStr">
         <is>
           <t>0.6480 (1 seed)</t>
         </is>
       </c>
-      <c r="E17" s="8" t="inlineStr">
+      <c r="E17" s="22" t="inlineStr">
         <is>
           <t>0.7756 (1 seed)</t>
         </is>
       </c>
-      <c r="F17" s="8" t="inlineStr">
+      <c r="F17" s="22" t="inlineStr">
         <is>
           <t>0.7584 (1 seed)</t>
-        </is>
-      </c>
-      <c r="G17" s="6" t="inlineStr">
-        <is>
-          <t>tokenizer 直接对手</t>
         </is>
       </c>
     </row>
@@ -4661,11 +4339,6 @@
           <t>REVE-Base (pretrained)</t>
         </is>
       </c>
-      <c r="G18" s="6" t="inlineStr">
-        <is>
-          <t>新增；HF 权重</t>
-        </is>
-      </c>
     </row>
     <row r="19">
       <c r="B19" t="inlineStr">
@@ -4673,11 +4346,6 @@
           <t>CSBrain (pretrained)</t>
         </is>
       </c>
-      <c r="G19" s="6" t="inlineStr">
-        <is>
-          <t>新增；GDrive 权重</t>
-        </is>
-      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -4693,17 +4361,17 @@
       <c r="C20" t="n">
         <v>3.19</v>
       </c>
-      <c r="D20" s="8" t="inlineStr">
+      <c r="D20" s="22" t="inlineStr">
         <is>
           <t>0.4985 (1 seed)</t>
         </is>
       </c>
-      <c r="E20" s="8" t="inlineStr">
+      <c r="E20" s="22" t="inlineStr">
         <is>
           <t>0.6849 (1 seed)</t>
         </is>
       </c>
-      <c r="F20" s="8" t="inlineStr">
+      <c r="F20" s="22" t="inlineStr">
         <is>
           <t>0.6280 (1 seed)</t>
         </is>
@@ -4718,17 +4386,17 @@
       <c r="C21" t="n">
         <v>5.82</v>
       </c>
-      <c r="D21" s="8" t="inlineStr">
+      <c r="D21" s="22" t="inlineStr">
         <is>
           <t>0.5265 (1 seed)</t>
         </is>
       </c>
-      <c r="E21" s="8" t="inlineStr">
+      <c r="E21" s="22" t="inlineStr">
         <is>
           <t>0.6991 (1 seed)</t>
         </is>
       </c>
-      <c r="F21" s="8" t="inlineStr">
+      <c r="F21" s="22" t="inlineStr">
         <is>
           <t>0.6641 (1 seed)</t>
         </is>
@@ -4743,17 +4411,17 @@
       <c r="C22" t="n">
         <v>17.85</v>
       </c>
-      <c r="D22" s="8" t="inlineStr">
+      <c r="D22" s="22" t="inlineStr">
         <is>
           <t>0.6503 (1 seed)</t>
         </is>
       </c>
-      <c r="E22" s="8" t="inlineStr">
+      <c r="E22" s="22" t="inlineStr">
         <is>
           <t>0.7729 (1 seed)</t>
         </is>
       </c>
-      <c r="F22" s="8" t="inlineStr">
+      <c r="F22" s="22" t="inlineStr">
         <is>
           <t>0.7614 (1 seed)</t>
         </is>
@@ -4768,24 +4436,19 @@
       <c r="C23" t="n">
         <v>25.69</v>
       </c>
-      <c r="D23" s="8" t="inlineStr">
+      <c r="D23" s="22" t="inlineStr">
         <is>
           <t>0.5820 (1 seed)</t>
         </is>
       </c>
-      <c r="E23" s="8" t="inlineStr">
+      <c r="E23" s="22" t="inlineStr">
         <is>
           <t>0.7279 (1 seed)</t>
         </is>
       </c>
-      <c r="F23" s="8" t="inlineStr">
+      <c r="F23" s="22" t="inlineStr">
         <is>
           <t>0.7200 (1 seed)</t>
-        </is>
-      </c>
-      <c r="G23" s="6" t="inlineStr">
-        <is>
-          <t>不新排；仅新语料已有数字</t>
         </is>
       </c>
     </row>
@@ -4798,24 +4461,19 @@
       <c r="C24" t="n">
         <v>1.89</v>
       </c>
-      <c r="D24" s="8" t="inlineStr">
+      <c r="D24" s="22" t="inlineStr">
         <is>
           <t>0.3644 (1 seed)</t>
         </is>
       </c>
-      <c r="E24" s="8" t="inlineStr">
+      <c r="E24" s="22" t="inlineStr">
         <is>
           <t>0.5853 (1 seed)</t>
         </is>
       </c>
-      <c r="F24" s="8" t="inlineStr">
+      <c r="F24" s="22" t="inlineStr">
         <is>
           <t>0.5575 (1 seed)</t>
-        </is>
-      </c>
-      <c r="G24" s="6" t="inlineStr">
-        <is>
-          <t>不新排；仅新语料已有数字</t>
         </is>
       </c>
     </row>
@@ -4833,17 +4491,17 @@
       <c r="C25" t="n">
         <v>1.61</v>
       </c>
-      <c r="D25" s="8" t="inlineStr">
+      <c r="D25" s="20" t="inlineStr">
         <is>
           <t>0.6289 (1 seed)</t>
         </is>
       </c>
-      <c r="E25" s="8" t="inlineStr">
+      <c r="E25" s="20" t="inlineStr">
         <is>
           <t>0.7644 (1 seed)</t>
         </is>
       </c>
-      <c r="F25" s="8" t="inlineStr">
+      <c r="F25" s="20" t="inlineStr">
         <is>
           <t>0.7462 (1 seed)</t>
         </is>
@@ -4855,11 +4513,6 @@
           <t>PACLock (duplex, 预训练 v2)</t>
         </is>
       </c>
-      <c r="G26" s="6" t="inlineStr">
-        <is>
-          <t>band_norm_pac 目标</t>
-        </is>
-      </c>
     </row>
     <row r="27">
       <c r="B27" t="inlineStr">
@@ -4867,11 +4520,6 @@
           <t>PACLock (冻结探针, v2)</t>
         </is>
       </c>
-      <c r="G27" s="6" t="inlineStr">
-        <is>
-          <t>patch_len 200；表征质量协议</t>
-        </is>
-      </c>
     </row>
     <row r="28">
       <c r="B28" t="inlineStr">
@@ -4879,12 +4527,8 @@
           <t>PACLock (冻结探针, 随机初始化)</t>
         </is>
       </c>
-      <c r="G28" s="6" t="inlineStr">
-        <is>
-          <t>四道门第 4 门对照</t>
-        </is>
-      </c>
-    </row>
+    </row>
+    <row r="29"/>
     <row r="30">
       <c r="A30" s="6" t="inlineStr">
         <is>
@@ -4903,15 +4547,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G30"/>
+  <dimension ref="A1:F30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
     <col width="11" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
     <col width="46" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
@@ -4967,11 +4611,6 @@
           <t>AUC-PR</t>
         </is>
       </c>
-      <c r="G4" s="5" t="inlineStr">
-        <is>
-          <t>备注</t>
-        </is>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -4984,11 +4623,6 @@
           <t>手工特征 (LR/LDA 取优)</t>
         </is>
       </c>
-      <c r="G5" s="6" t="inlineStr">
-        <is>
-          <t>bandpower+Hjorth+谱熵；四道门第 1 门</t>
-        </is>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -5004,17 +4638,17 @@
       <c r="C6" t="n">
         <v>0.99</v>
       </c>
-      <c r="D6" s="8" t="inlineStr">
+      <c r="D6" s="22" t="inlineStr">
         <is>
           <t>0.9757 (1 seed)</t>
         </is>
       </c>
-      <c r="E6" s="8" t="inlineStr">
+      <c r="E6" s="22" t="inlineStr">
         <is>
           <t>0.6242 (1 seed)</t>
         </is>
       </c>
-      <c r="F6" s="8" t="inlineStr">
+      <c r="F6" s="22" t="inlineStr">
         <is>
           <t>0.9772 (1 seed)</t>
         </is>
@@ -5029,17 +4663,17 @@
       <c r="C7" t="n">
         <v>1.57</v>
       </c>
-      <c r="D7" s="8" t="inlineStr">
+      <c r="D7" s="22" t="inlineStr">
         <is>
           <t>0.9659 (1 seed)</t>
         </is>
       </c>
-      <c r="E7" s="8" t="inlineStr">
+      <c r="E7" s="22" t="inlineStr">
         <is>
           <t>0.7985 (1 seed)</t>
         </is>
       </c>
-      <c r="F7" s="8" t="inlineStr">
+      <c r="F7" s="22" t="inlineStr">
         <is>
           <t>0.9735 (1 seed)</t>
         </is>
@@ -5054,17 +4688,17 @@
       <c r="C8" t="n">
         <v>3.16</v>
       </c>
-      <c r="D8" s="8" t="inlineStr">
+      <c r="D8" s="22" t="inlineStr">
         <is>
           <t>0.8850 (1 seed)</t>
         </is>
       </c>
-      <c r="E8" s="8" t="inlineStr">
+      <c r="E8" s="22" t="inlineStr">
         <is>
           <t>0.8236 (1 seed)</t>
         </is>
       </c>
-      <c r="F8" s="8" t="inlineStr">
+      <c r="F8" s="22" t="inlineStr">
         <is>
           <t>0.8775 (1 seed)</t>
         </is>
@@ -5079,17 +4713,17 @@
       <c r="C9" t="n">
         <v>2.42</v>
       </c>
-      <c r="D9" s="8" t="inlineStr">
+      <c r="D9" s="22" t="inlineStr">
         <is>
           <t>0.9581 (1 seed)</t>
         </is>
       </c>
-      <c r="E9" s="8" t="inlineStr">
+      <c r="E9" s="22" t="inlineStr">
         <is>
           <t>0.7620 (1 seed)</t>
         </is>
       </c>
-      <c r="F9" s="8" t="inlineStr">
+      <c r="F9" s="22" t="inlineStr">
         <is>
           <t>0.9669 (1 seed)</t>
         </is>
@@ -5104,17 +4738,17 @@
       <c r="C10" t="n">
         <v>3.43</v>
       </c>
-      <c r="D10" s="8" t="inlineStr">
+      <c r="D10" s="22" t="inlineStr">
         <is>
           <t>0.9933 (1 seed)</t>
         </is>
       </c>
-      <c r="E10" s="8" t="inlineStr">
+      <c r="E10" s="23" t="inlineStr">
         <is>
           <t>0.9577 (1 seed)</t>
         </is>
       </c>
-      <c r="F10" s="8" t="inlineStr">
+      <c r="F10" s="22" t="inlineStr">
         <is>
           <t>0.9941 (1 seed)</t>
         </is>
@@ -5126,11 +4760,6 @@
           <t>EEGNet (调参)</t>
         </is>
       </c>
-      <c r="G11" s="6" t="inlineStr">
-        <is>
-          <t>公开搜索预算调参</t>
-        </is>
-      </c>
     </row>
     <row r="12">
       <c r="B12" t="inlineStr">
@@ -5138,11 +4767,6 @@
           <t>EEGConformer (调参)</t>
         </is>
       </c>
-      <c r="G12" s="6" t="inlineStr">
-        <is>
-          <t>benchmark 文献最强单体</t>
-        </is>
-      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -5158,17 +4782,17 @@
       <c r="C13" t="n">
         <v>3.19</v>
       </c>
-      <c r="D13" s="8" t="inlineStr">
+      <c r="D13" s="23" t="inlineStr">
         <is>
           <t>0.9999 (1 seed)</t>
         </is>
       </c>
-      <c r="E13" s="8" t="inlineStr">
+      <c r="E13" s="22" t="inlineStr">
         <is>
           <t>0.8900 (1 seed)</t>
         </is>
       </c>
-      <c r="F13" s="8" t="inlineStr">
+      <c r="F13" s="23" t="inlineStr">
         <is>
           <t>0.9999 (1 seed)</t>
         </is>
@@ -5183,17 +4807,17 @@
       <c r="C14" t="n">
         <v>5.82</v>
       </c>
-      <c r="D14" s="8" t="inlineStr">
+      <c r="D14" s="22" t="inlineStr">
         <is>
           <t>0.9858 (1 seed)</t>
         </is>
       </c>
-      <c r="E14" s="8" t="inlineStr">
+      <c r="E14" s="22" t="inlineStr">
         <is>
           <t>0.8010 (1 seed)</t>
         </is>
       </c>
-      <c r="F14" s="8" t="inlineStr">
+      <c r="F14" s="22" t="inlineStr">
         <is>
           <t>0.9891 (1 seed)</t>
         </is>
@@ -5208,17 +4832,17 @@
       <c r="C15" t="n">
         <v>20.25</v>
       </c>
-      <c r="D15" s="8" t="inlineStr">
+      <c r="D15" s="22" t="inlineStr">
         <is>
           <t>0.9690 (1 seed)</t>
         </is>
       </c>
-      <c r="E15" s="8" t="inlineStr">
+      <c r="E15" s="22" t="inlineStr">
         <is>
           <t>0.8333 (1 seed)</t>
         </is>
       </c>
-      <c r="F15" s="8" t="inlineStr">
+      <c r="F15" s="22" t="inlineStr">
         <is>
           <t>0.9741 (1 seed)</t>
         </is>
@@ -5233,17 +4857,17 @@
       <c r="C16" t="n">
         <v>25.69</v>
       </c>
-      <c r="D16" s="8" t="inlineStr">
+      <c r="D16" s="22" t="inlineStr">
         <is>
           <t>0.9379 (1 seed)</t>
         </is>
       </c>
-      <c r="E16" s="8" t="inlineStr">
+      <c r="E16" s="22" t="inlineStr">
         <is>
           <t>0.8576 (1 seed)</t>
         </is>
       </c>
-      <c r="F16" s="8" t="inlineStr">
+      <c r="F16" s="22" t="inlineStr">
         <is>
           <t>0.9390 (1 seed)</t>
         </is>
@@ -5258,24 +4882,19 @@
       <c r="C17" t="n">
         <v>1.89</v>
       </c>
-      <c r="D17" s="8" t="inlineStr">
+      <c r="D17" s="22" t="inlineStr">
         <is>
           <t>0.9491 (1 seed)</t>
         </is>
       </c>
-      <c r="E17" s="8" t="inlineStr">
+      <c r="E17" s="22" t="inlineStr">
         <is>
           <t>0.8631 (1 seed)</t>
         </is>
       </c>
-      <c r="F17" s="8" t="inlineStr">
+      <c r="F17" s="22" t="inlineStr">
         <is>
           <t>0.9543 (1 seed)</t>
-        </is>
-      </c>
-      <c r="G17" s="6" t="inlineStr">
-        <is>
-          <t>tokenizer 直接对手</t>
         </is>
       </c>
     </row>
@@ -5285,11 +4904,6 @@
           <t>REVE-Base (pretrained)</t>
         </is>
       </c>
-      <c r="G18" s="6" t="inlineStr">
-        <is>
-          <t>新增；HF 权重</t>
-        </is>
-      </c>
     </row>
     <row r="19">
       <c r="B19" t="inlineStr">
@@ -5297,11 +4911,6 @@
           <t>CSBrain (pretrained)</t>
         </is>
       </c>
-      <c r="G19" s="6" t="inlineStr">
-        <is>
-          <t>新增；GDrive 权重</t>
-        </is>
-      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -5317,17 +4926,17 @@
       <c r="C20" t="n">
         <v>3.19</v>
       </c>
-      <c r="D20" s="8" t="inlineStr">
+      <c r="D20" s="22" t="inlineStr">
         <is>
           <t>0.9422 (1 seed)</t>
         </is>
       </c>
-      <c r="E20" s="8" t="inlineStr">
+      <c r="E20" s="22" t="inlineStr">
         <is>
           <t>0.7979 (1 seed)</t>
         </is>
       </c>
-      <c r="F20" s="8" t="inlineStr">
+      <c r="F20" s="22" t="inlineStr">
         <is>
           <t>0.9573 (1 seed)</t>
         </is>
@@ -5342,17 +4951,17 @@
       <c r="C21" t="n">
         <v>5.82</v>
       </c>
-      <c r="D21" s="8" t="inlineStr">
+      <c r="D21" s="22" t="inlineStr">
         <is>
           <t>0.9848 (1 seed)</t>
         </is>
       </c>
-      <c r="E21" s="8" t="inlineStr">
+      <c r="E21" s="22" t="inlineStr">
         <is>
           <t>0.8033 (1 seed)</t>
         </is>
       </c>
-      <c r="F21" s="8" t="inlineStr">
+      <c r="F21" s="22" t="inlineStr">
         <is>
           <t>0.9876 (1 seed)</t>
         </is>
@@ -5367,17 +4976,17 @@
       <c r="C22" t="n">
         <v>20.25</v>
       </c>
-      <c r="D22" s="8" t="inlineStr">
+      <c r="D22" s="22" t="inlineStr">
         <is>
           <t>0.9240 (1 seed)</t>
         </is>
       </c>
-      <c r="E22" s="8" t="inlineStr">
+      <c r="E22" s="22" t="inlineStr">
         <is>
           <t>0.8013 (1 seed)</t>
         </is>
       </c>
-      <c r="F22" s="8" t="inlineStr">
+      <c r="F22" s="22" t="inlineStr">
         <is>
           <t>0.9040 (1 seed)</t>
         </is>
@@ -5392,24 +5001,19 @@
       <c r="C23" t="n">
         <v>25.69</v>
       </c>
-      <c r="D23" s="8" t="inlineStr">
+      <c r="D23" s="22" t="inlineStr">
         <is>
           <t>0.8932 (1 seed)</t>
         </is>
       </c>
-      <c r="E23" s="8" t="inlineStr">
+      <c r="E23" s="22" t="inlineStr">
         <is>
           <t>0.8045 (1 seed)</t>
         </is>
       </c>
-      <c r="F23" s="8" t="inlineStr">
+      <c r="F23" s="22" t="inlineStr">
         <is>
           <t>0.8809 (1 seed)</t>
-        </is>
-      </c>
-      <c r="G23" s="6" t="inlineStr">
-        <is>
-          <t>不新排；仅新语料已有数字</t>
         </is>
       </c>
     </row>
@@ -5422,24 +5026,19 @@
       <c r="C24" t="n">
         <v>1.89</v>
       </c>
-      <c r="D24" s="8" t="inlineStr">
+      <c r="D24" s="22" t="inlineStr">
         <is>
           <t>0.8317 (1 seed)</t>
         </is>
       </c>
-      <c r="E24" s="8" t="inlineStr">
+      <c r="E24" s="22" t="inlineStr">
         <is>
           <t>0.7481 (1 seed)</t>
         </is>
       </c>
-      <c r="F24" s="8" t="inlineStr">
+      <c r="F24" s="22" t="inlineStr">
         <is>
           <t>0.8046 (1 seed)</t>
-        </is>
-      </c>
-      <c r="G24" s="6" t="inlineStr">
-        <is>
-          <t>不新排；仅新语料已有数字</t>
         </is>
       </c>
     </row>
@@ -5457,17 +5056,17 @@
       <c r="C25" t="n">
         <v>1.62</v>
       </c>
-      <c r="D25" s="8" t="inlineStr">
+      <c r="D25" s="20" t="inlineStr">
         <is>
           <t>0.9775 (1 seed)</t>
         </is>
       </c>
-      <c r="E25" s="8" t="inlineStr">
+      <c r="E25" s="20" t="inlineStr">
         <is>
           <t>0.8735 (1 seed)</t>
         </is>
       </c>
-      <c r="F25" s="8" t="inlineStr">
+      <c r="F25" s="20" t="inlineStr">
         <is>
           <t>0.9810 (1 seed)</t>
         </is>
@@ -5479,11 +5078,6 @@
           <t>PACLock (duplex, 预训练 v2)</t>
         </is>
       </c>
-      <c r="G26" s="6" t="inlineStr">
-        <is>
-          <t>band_norm_pac 目标</t>
-        </is>
-      </c>
     </row>
     <row r="27">
       <c r="B27" t="inlineStr">
@@ -5491,11 +5085,6 @@
           <t>PACLock (冻结探针, v2)</t>
         </is>
       </c>
-      <c r="G27" s="6" t="inlineStr">
-        <is>
-          <t>patch_len 200；表征质量协议</t>
-        </is>
-      </c>
     </row>
     <row r="28">
       <c r="B28" t="inlineStr">
@@ -5503,12 +5092,8 @@
           <t>PACLock (冻结探针, 随机初始化)</t>
         </is>
       </c>
-      <c r="G28" s="6" t="inlineStr">
-        <is>
-          <t>四道门第 4 门对照</t>
-        </is>
-      </c>
-    </row>
+    </row>
+    <row r="29"/>
     <row r="30">
       <c r="A30" s="6" t="inlineStr">
         <is>
@@ -5527,15 +5112,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G30"/>
+  <dimension ref="A1:F30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
     <col width="11" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
     <col width="46" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
@@ -5591,11 +5176,6 @@
           <t>AUC-PR</t>
         </is>
       </c>
-      <c r="G4" s="5" t="inlineStr">
-        <is>
-          <t>备注</t>
-        </is>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -5608,11 +5188,6 @@
           <t>手工特征 (LR/LDA 取优)</t>
         </is>
       </c>
-      <c r="G5" s="6" t="inlineStr">
-        <is>
-          <t>bandpower+Hjorth+谱熵；四道门第 1 门</t>
-        </is>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -5628,17 +5203,17 @@
       <c r="C6" t="n">
         <v>0.99</v>
       </c>
-      <c r="D6" s="8" t="inlineStr">
+      <c r="D6" s="22" t="inlineStr">
         <is>
           <t>0.7691 (1 seed)</t>
         </is>
       </c>
-      <c r="E6" s="8" t="inlineStr">
+      <c r="E6" s="22" t="inlineStr">
         <is>
           <t>0.5948 (1 seed)</t>
         </is>
       </c>
-      <c r="F6" s="8" t="inlineStr">
+      <c r="F6" s="22" t="inlineStr">
         <is>
           <t>0.5053 (1 seed)</t>
         </is>
@@ -5653,17 +5228,17 @@
       <c r="C7" t="n">
         <v>1.57</v>
       </c>
-      <c r="D7" s="8" t="inlineStr">
+      <c r="D7" s="22" t="inlineStr">
         <is>
           <t>0.7722 (1 seed)</t>
         </is>
       </c>
-      <c r="E7" s="8" t="inlineStr">
+      <c r="E7" s="22" t="inlineStr">
         <is>
           <t>0.5805 (1 seed)</t>
         </is>
       </c>
-      <c r="F7" s="8" t="inlineStr">
+      <c r="F7" s="22" t="inlineStr">
         <is>
           <t>0.5438 (1 seed)</t>
         </is>
@@ -5678,17 +5253,17 @@
       <c r="C8" t="n">
         <v>3.16</v>
       </c>
-      <c r="D8" s="8" t="inlineStr">
+      <c r="D8" s="22" t="inlineStr">
         <is>
           <t>0.8050 (1 seed)</t>
         </is>
       </c>
-      <c r="E8" s="8" t="inlineStr">
+      <c r="E8" s="22" t="inlineStr">
         <is>
           <t>0.5000 (1 seed)</t>
         </is>
       </c>
-      <c r="F8" s="8" t="inlineStr">
+      <c r="F8" s="22" t="inlineStr">
         <is>
           <t>0.6376 (1 seed)</t>
         </is>
@@ -5703,17 +5278,17 @@
       <c r="C9" t="n">
         <v>2.42</v>
       </c>
-      <c r="D9" s="8" t="inlineStr">
+      <c r="D9" s="22" t="inlineStr">
         <is>
           <t>0.7153 (1 seed)</t>
         </is>
       </c>
-      <c r="E9" s="8" t="inlineStr">
+      <c r="E9" s="22" t="inlineStr">
         <is>
           <t>0.6543 (1 seed)</t>
         </is>
       </c>
-      <c r="F9" s="8" t="inlineStr">
+      <c r="F9" s="22" t="inlineStr">
         <is>
           <t>0.4156 (1 seed)</t>
         </is>
@@ -5728,17 +5303,17 @@
       <c r="C10" t="n">
         <v>3.43</v>
       </c>
-      <c r="D10" s="8" t="inlineStr">
+      <c r="D10" s="22" t="inlineStr">
         <is>
           <t>0.5516 (1 seed)</t>
         </is>
       </c>
-      <c r="E10" s="8" t="inlineStr">
+      <c r="E10" s="22" t="inlineStr">
         <is>
           <t>0.5000 (1 seed)</t>
         </is>
       </c>
-      <c r="F10" s="8" t="inlineStr">
+      <c r="F10" s="22" t="inlineStr">
         <is>
           <t>0.2894 (1 seed)</t>
         </is>
@@ -5750,11 +5325,6 @@
           <t>EEGNet (调参)</t>
         </is>
       </c>
-      <c r="G11" s="6" t="inlineStr">
-        <is>
-          <t>公开搜索预算调参</t>
-        </is>
-      </c>
     </row>
     <row r="12">
       <c r="B12" t="inlineStr">
@@ -5762,11 +5332,6 @@
           <t>EEGConformer (调参)</t>
         </is>
       </c>
-      <c r="G12" s="6" t="inlineStr">
-        <is>
-          <t>benchmark 文献最强单体</t>
-        </is>
-      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -5782,17 +5347,17 @@
       <c r="C13" t="n">
         <v>3.19</v>
       </c>
-      <c r="D13" s="8" t="inlineStr">
+      <c r="D13" s="22" t="inlineStr">
         <is>
           <t>0.6604 (1 seed)</t>
         </is>
       </c>
-      <c r="E13" s="8" t="inlineStr">
+      <c r="E13" s="22" t="inlineStr">
         <is>
           <t>0.5173 (1 seed)</t>
         </is>
       </c>
-      <c r="F13" s="8" t="inlineStr">
+      <c r="F13" s="22" t="inlineStr">
         <is>
           <t>0.3818 (1 seed)</t>
         </is>
@@ -5807,17 +5372,17 @@
       <c r="C14" t="n">
         <v>5.82</v>
       </c>
-      <c r="D14" s="8" t="inlineStr">
+      <c r="D14" s="22" t="inlineStr">
         <is>
           <t>0.8214 (1 seed)</t>
         </is>
       </c>
-      <c r="E14" s="8" t="inlineStr">
+      <c r="E14" s="22" t="inlineStr">
         <is>
           <t>0.6937 (1 seed)</t>
         </is>
       </c>
-      <c r="F14" s="8" t="inlineStr">
+      <c r="F14" s="22" t="inlineStr">
         <is>
           <t>0.7152 (1 seed)</t>
         </is>
@@ -5832,17 +5397,17 @@
       <c r="C15" t="n">
         <v>20.25</v>
       </c>
-      <c r="D15" s="8" t="inlineStr">
+      <c r="D15" s="23" t="inlineStr">
         <is>
           <t>0.8557 (1 seed)</t>
         </is>
       </c>
-      <c r="E15" s="8" t="inlineStr">
+      <c r="E15" s="23" t="inlineStr">
         <is>
           <t>0.7178 (1 seed)</t>
         </is>
       </c>
-      <c r="F15" s="8" t="inlineStr">
+      <c r="F15" s="23" t="inlineStr">
         <is>
           <t>0.7323 (1 seed)</t>
         </is>
@@ -5857,17 +5422,17 @@
       <c r="C16" t="n">
         <v>25.69</v>
       </c>
-      <c r="D16" s="8" t="inlineStr">
+      <c r="D16" s="22" t="inlineStr">
         <is>
           <t>0.6816 (1 seed)</t>
         </is>
       </c>
-      <c r="E16" s="8" t="inlineStr">
+      <c r="E16" s="22" t="inlineStr">
         <is>
           <t>0.5768 (1 seed)</t>
         </is>
       </c>
-      <c r="F16" s="8" t="inlineStr">
+      <c r="F16" s="22" t="inlineStr">
         <is>
           <t>0.4864 (1 seed)</t>
         </is>
@@ -5882,24 +5447,19 @@
       <c r="C17" t="n">
         <v>1.89</v>
       </c>
-      <c r="D17" s="8" t="inlineStr">
+      <c r="D17" s="22" t="inlineStr">
         <is>
           <t>0.6927 (1 seed)</t>
         </is>
       </c>
-      <c r="E17" s="8" t="inlineStr">
+      <c r="E17" s="22" t="inlineStr">
         <is>
           <t>0.5099 (1 seed)</t>
         </is>
       </c>
-      <c r="F17" s="8" t="inlineStr">
+      <c r="F17" s="22" t="inlineStr">
         <is>
           <t>0.3817 (1 seed)</t>
-        </is>
-      </c>
-      <c r="G17" s="6" t="inlineStr">
-        <is>
-          <t>tokenizer 直接对手</t>
         </is>
       </c>
     </row>
@@ -5909,11 +5469,6 @@
           <t>REVE-Base (pretrained)</t>
         </is>
       </c>
-      <c r="G18" s="6" t="inlineStr">
-        <is>
-          <t>新增；HF 权重</t>
-        </is>
-      </c>
     </row>
     <row r="19">
       <c r="B19" t="inlineStr">
@@ -5921,11 +5476,6 @@
           <t>CSBrain (pretrained)</t>
         </is>
       </c>
-      <c r="G19" s="6" t="inlineStr">
-        <is>
-          <t>新增；GDrive 权重</t>
-        </is>
-      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -5941,17 +5491,17 @@
       <c r="C20" t="n">
         <v>3.19</v>
       </c>
-      <c r="D20" s="8" t="inlineStr">
+      <c r="D20" s="22" t="inlineStr">
         <is>
           <t>0.6491 (1 seed)</t>
         </is>
       </c>
-      <c r="E20" s="8" t="inlineStr">
+      <c r="E20" s="22" t="inlineStr">
         <is>
           <t>0.5717 (1 seed)</t>
         </is>
       </c>
-      <c r="F20" s="8" t="inlineStr">
+      <c r="F20" s="22" t="inlineStr">
         <is>
           <t>0.3365 (1 seed)</t>
         </is>
@@ -5966,17 +5516,17 @@
       <c r="C21" t="n">
         <v>5.82</v>
       </c>
-      <c r="D21" s="8" t="inlineStr">
+      <c r="D21" s="22" t="inlineStr">
         <is>
           <t>0.6580 (1 seed)</t>
         </is>
       </c>
-      <c r="E21" s="8" t="inlineStr">
+      <c r="E21" s="22" t="inlineStr">
         <is>
           <t>0.4974 (1 seed)</t>
         </is>
       </c>
-      <c r="F21" s="8" t="inlineStr">
+      <c r="F21" s="22" t="inlineStr">
         <is>
           <t>0.3446 (1 seed)</t>
         </is>
@@ -5991,17 +5541,17 @@
       <c r="C22" t="n">
         <v>20.25</v>
       </c>
-      <c r="D22" s="8" t="inlineStr">
+      <c r="D22" s="22" t="inlineStr">
         <is>
           <t>0.7072 (1 seed)</t>
         </is>
       </c>
-      <c r="E22" s="8" t="inlineStr">
+      <c r="E22" s="22" t="inlineStr">
         <is>
           <t>0.5865 (1 seed)</t>
         </is>
       </c>
-      <c r="F22" s="8" t="inlineStr">
+      <c r="F22" s="22" t="inlineStr">
         <is>
           <t>0.4466 (1 seed)</t>
         </is>
@@ -6016,24 +5566,19 @@
       <c r="C23" t="n">
         <v>25.69</v>
       </c>
-      <c r="D23" s="8" t="inlineStr">
+      <c r="D23" s="22" t="inlineStr">
         <is>
           <t>0.6902 (1 seed)</t>
         </is>
       </c>
-      <c r="E23" s="8" t="inlineStr">
+      <c r="E23" s="22" t="inlineStr">
         <is>
           <t>0.5000 (1 seed)</t>
         </is>
       </c>
-      <c r="F23" s="8" t="inlineStr">
+      <c r="F23" s="22" t="inlineStr">
         <is>
           <t>0.3862 (1 seed)</t>
-        </is>
-      </c>
-      <c r="G23" s="6" t="inlineStr">
-        <is>
-          <t>不新排；仅新语料已有数字</t>
         </is>
       </c>
     </row>
@@ -6046,24 +5591,19 @@
       <c r="C24" t="n">
         <v>1.89</v>
       </c>
-      <c r="D24" s="8" t="inlineStr">
+      <c r="D24" s="22" t="inlineStr">
         <is>
           <t>0.4633 (1 seed)</t>
         </is>
       </c>
-      <c r="E24" s="8" t="inlineStr">
+      <c r="E24" s="22" t="inlineStr">
         <is>
           <t>0.5000 (1 seed)</t>
         </is>
       </c>
-      <c r="F24" s="8" t="inlineStr">
+      <c r="F24" s="22" t="inlineStr">
         <is>
           <t>0.2402 (1 seed)</t>
-        </is>
-      </c>
-      <c r="G24" s="6" t="inlineStr">
-        <is>
-          <t>不新排；仅新语料已有数字</t>
         </is>
       </c>
     </row>
@@ -6081,17 +5621,17 @@
       <c r="C25" t="n">
         <v>1.62</v>
       </c>
-      <c r="D25" s="8" t="inlineStr">
+      <c r="D25" s="20" t="inlineStr">
         <is>
           <t>0.7263 (1 seed)</t>
         </is>
       </c>
-      <c r="E25" s="8" t="inlineStr">
+      <c r="E25" s="20" t="inlineStr">
         <is>
           <t>0.5590 (1 seed)</t>
         </is>
       </c>
-      <c r="F25" s="8" t="inlineStr">
+      <c r="F25" s="20" t="inlineStr">
         <is>
           <t>0.4691 (1 seed)</t>
         </is>
@@ -6103,11 +5643,6 @@
           <t>PACLock (duplex, 预训练 v2)</t>
         </is>
       </c>
-      <c r="G26" s="6" t="inlineStr">
-        <is>
-          <t>band_norm_pac 目标</t>
-        </is>
-      </c>
     </row>
     <row r="27">
       <c r="B27" t="inlineStr">
@@ -6115,11 +5650,6 @@
           <t>PACLock (冻结探针, v2)</t>
         </is>
       </c>
-      <c r="G27" s="6" t="inlineStr">
-        <is>
-          <t>patch_len 200；表征质量协议</t>
-        </is>
-      </c>
     </row>
     <row r="28">
       <c r="B28" t="inlineStr">
@@ -6127,12 +5657,8 @@
           <t>PACLock (冻结探针, 随机初始化)</t>
         </is>
       </c>
-      <c r="G28" s="6" t="inlineStr">
-        <is>
-          <t>四道门第 4 门对照</t>
-        </is>
-      </c>
-    </row>
+    </row>
+    <row r="29"/>
     <row r="30">
       <c r="A30" s="6" t="inlineStr">
         <is>
@@ -25385,15 +24911,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G34"/>
+  <dimension ref="A1:F34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
     <col width="11" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
     <col width="46" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
@@ -25442,11 +24968,6 @@
           <t>Weighted F1</t>
         </is>
       </c>
-      <c r="G4" s="5" t="inlineStr">
-        <is>
-          <t>备注</t>
-        </is>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -25462,24 +24983,19 @@
       <c r="C5" t="n">
         <v>0</v>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D5" s="17" t="inlineStr">
         <is>
           <t>0.5049±0.0000</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E5" s="17" t="inlineStr">
         <is>
           <t>0.4481±0.0000</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F5" s="17" t="inlineStr">
         <is>
           <t>0.7445±0.0000</t>
-        </is>
-      </c>
-      <c r="G5" s="6" t="inlineStr">
-        <is>
-          <t>bandpower+Hjorth+谱熵；四道门第 1 门</t>
         </is>
       </c>
     </row>
@@ -25497,17 +25013,17 @@
       <c r="C6" t="n">
         <v>0.99</v>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D6" s="18" t="inlineStr">
         <is>
           <t>0.4885±0.0228</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E6" s="18" t="inlineStr">
         <is>
           <t>0.4654±0.0283</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="F6" s="18" t="inlineStr">
         <is>
           <t>0.7354±0.0119</t>
         </is>
@@ -25522,17 +25038,17 @@
       <c r="C7" t="n">
         <v>1.57</v>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D7" s="18" t="inlineStr">
         <is>
           <t>0.4076±0.0803</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E7" s="18" t="inlineStr">
         <is>
           <t>0.4195±0.1027</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F7" s="18" t="inlineStr">
         <is>
           <t>0.6962±0.0371</t>
         </is>
@@ -25547,17 +25063,17 @@
       <c r="C8" t="n">
         <v>3.16</v>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D8" s="18" t="inlineStr">
         <is>
           <t>0.4098±0.0951</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E8" s="18" t="inlineStr">
         <is>
           <t>0.3679±0.0838</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F8" s="18" t="inlineStr">
         <is>
           <t>0.6916±0.0607</t>
         </is>
@@ -25572,17 +25088,17 @@
       <c r="C9" t="n">
         <v>2.42</v>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D9" s="18" t="inlineStr">
         <is>
           <t>0.4776±0.0263</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E9" s="18" t="inlineStr">
         <is>
           <t>0.4376±0.0561</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F9" s="18" t="inlineStr">
         <is>
           <t>0.7366±0.0138</t>
         </is>
@@ -25597,17 +25113,17 @@
       <c r="C10" t="n">
         <v>3.43</v>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D10" s="18" t="inlineStr">
         <is>
           <t>0.5006±0.0096</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E10" s="18" t="inlineStr">
         <is>
           <t>0.4731±0.0162</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="F10" s="18" t="inlineStr">
         <is>
           <t>0.7411±0.0071</t>
         </is>
@@ -25622,24 +25138,19 @@
       <c r="C11" t="n">
         <v>0</v>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D11" s="17" t="inlineStr">
         <is>
           <t>0.4788±0.0741</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E11" s="17" t="inlineStr">
         <is>
           <t>0.4152±0.0469</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="F11" s="17" t="inlineStr">
         <is>
           <t>0.7389±0.0299</t>
-        </is>
-      </c>
-      <c r="G11" s="6" t="inlineStr">
-        <is>
-          <t>公开搜索预算调参</t>
         </is>
       </c>
     </row>
@@ -25652,24 +25163,19 @@
       <c r="C12" t="n">
         <v>0.78</v>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D12" s="17" t="inlineStr">
         <is>
           <t>0.4548±0.0034</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E12" s="17" t="inlineStr">
         <is>
           <t>0.4212±0.0371</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="F12" s="17" t="inlineStr">
         <is>
           <t>0.7166±0.0048</t>
-        </is>
-      </c>
-      <c r="G12" s="6" t="inlineStr">
-        <is>
-          <t>benchmark 文献最强单体</t>
         </is>
       </c>
     </row>
@@ -25687,17 +25193,17 @@
       <c r="C13" t="n">
         <v>3.19</v>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="D13" s="18" t="inlineStr">
         <is>
           <t>0.5304±0.0227</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="E13" s="18" t="inlineStr">
         <is>
           <t>0.4894±0.0247</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="F13" s="18" t="inlineStr">
         <is>
           <t>0.7532±0.0129</t>
         </is>
@@ -25712,17 +25218,17 @@
       <c r="C14" t="n">
         <v>5.82</v>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="D14" s="18" t="inlineStr">
         <is>
           <t>0.5984±0.0025</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="E14" s="18" t="inlineStr">
         <is>
           <t>0.6305±0.0250</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="F14" s="18" t="inlineStr">
         <is>
           <t>0.8086±0.0039</t>
         </is>
@@ -25737,17 +25243,17 @@
       <c r="C15" t="n">
         <v>17.85</v>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="D15" s="18" t="inlineStr">
         <is>
           <t>0.6449±0.0177</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="E15" s="18" t="inlineStr">
         <is>
           <t>0.6029±0.0088</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="F15" s="18" t="inlineStr">
         <is>
           <t>0.8130±0.0095</t>
         </is>
@@ -25762,17 +25268,17 @@
       <c r="C16" t="n">
         <v>25.69</v>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="D16" s="18" t="inlineStr">
         <is>
           <t>0.5736±0.0323</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="E16" s="18" t="inlineStr">
         <is>
           <t>0.5131±0.0613</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="F16" s="18" t="inlineStr">
         <is>
           <t>0.7766±0.0163</t>
         </is>
@@ -25787,24 +25293,19 @@
       <c r="C17" t="n">
         <v>1.89</v>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="D17" s="18" t="inlineStr">
         <is>
           <t>0.6519±0.0170</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="E17" s="18" t="inlineStr">
         <is>
           <t>0.5959±0.0294</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="F17" s="18" t="inlineStr">
         <is>
           <t>0.8171±0.0085</t>
-        </is>
-      </c>
-      <c r="G17" s="6" t="inlineStr">
-        <is>
-          <t>tokenizer 直接对手</t>
         </is>
       </c>
     </row>
@@ -25817,24 +25318,19 @@
       <c r="C18" t="n">
         <v>69.48</v>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="D18" s="18" t="inlineStr">
         <is>
           <t>0.6846±0.0318</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="E18" s="1" t="inlineStr">
         <is>
           <t>0.6477±0.0149</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
+      <c r="F18" s="18" t="inlineStr">
         <is>
           <t>0.8378±0.0152</t>
-        </is>
-      </c>
-      <c r="G18" s="6" t="inlineStr">
-        <is>
-          <t>新增；HF 权重</t>
         </is>
       </c>
     </row>
@@ -25847,24 +25343,19 @@
       <c r="C19" t="n">
         <v>25.06</v>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="D19" s="18" t="inlineStr">
         <is>
           <t>0.6360±0.0399</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="E19" s="18" t="inlineStr">
         <is>
           <t>0.6270±0.0217</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
+      <c r="F19" s="18" t="inlineStr">
         <is>
           <t>0.8124±0.0199</t>
-        </is>
-      </c>
-      <c r="G19" s="6" t="inlineStr">
-        <is>
-          <t>新增；GDrive 权重</t>
         </is>
       </c>
     </row>
@@ -25882,17 +25373,17 @@
       <c r="C20" t="n">
         <v>3.19</v>
       </c>
-      <c r="D20" t="inlineStr">
+      <c r="D20" s="18" t="inlineStr">
         <is>
           <t>0.5324±0.0204</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="E20" s="18" t="inlineStr">
         <is>
           <t>0.5351±0.0510</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
+      <c r="F20" s="18" t="inlineStr">
         <is>
           <t>0.7612±0.0103</t>
         </is>
@@ -25907,17 +25398,17 @@
       <c r="C21" t="n">
         <v>5.82</v>
       </c>
-      <c r="D21" t="inlineStr">
+      <c r="D21" s="18" t="inlineStr">
         <is>
           <t>0.3717±0.0073</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="E21" s="18" t="inlineStr">
         <is>
           <t>0.3724±0.0697</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
+      <c r="F21" s="18" t="inlineStr">
         <is>
           <t>0.6928±0.0108</t>
         </is>
@@ -25932,17 +25423,17 @@
       <c r="C22" t="n">
         <v>17.85</v>
       </c>
-      <c r="D22" t="inlineStr">
+      <c r="D22" s="18" t="inlineStr">
         <is>
           <t>0.5638±0.0193</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="E22" s="18" t="inlineStr">
         <is>
           <t>0.5744±0.0086</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
+      <c r="F22" s="18" t="inlineStr">
         <is>
           <t>0.7671±0.0034</t>
         </is>
@@ -25954,11 +25445,6 @@
           <t>EEGPT (scratch)</t>
         </is>
       </c>
-      <c r="G23" s="6" t="inlineStr">
-        <is>
-          <t>不新排；仅新语料已有数字</t>
-        </is>
-      </c>
     </row>
     <row r="24">
       <c r="B24" t="inlineStr">
@@ -25966,11 +25452,6 @@
           <t>TFM-Tokenizer (scratch)</t>
         </is>
       </c>
-      <c r="G24" s="6" t="inlineStr">
-        <is>
-          <t>不新排；仅新语料已有数字</t>
-        </is>
-      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -25986,17 +25467,17 @@
       <c r="C25" t="n">
         <v>1.63</v>
       </c>
-      <c r="D25" s="8" t="inlineStr">
+      <c r="D25" s="19" t="inlineStr">
         <is>
           <t>0.7094 (1 seed)</t>
         </is>
       </c>
-      <c r="E25" s="8" t="inlineStr">
+      <c r="E25" s="20" t="inlineStr">
         <is>
           <t>0.6464 (1 seed)</t>
         </is>
       </c>
-      <c r="F25" s="8" t="inlineStr">
+      <c r="F25" s="19" t="inlineStr">
         <is>
           <t>0.8428 (1 seed)</t>
         </is>
@@ -26011,24 +25492,19 @@
       <c r="C26" t="n">
         <v>1.63</v>
       </c>
-      <c r="D26" s="8" t="inlineStr">
+      <c r="D26" s="20" t="inlineStr">
         <is>
           <t>0.6533 (1 seed)</t>
         </is>
       </c>
-      <c r="E26" s="8" t="inlineStr">
+      <c r="E26" s="20" t="inlineStr">
         <is>
           <t>0.5432 (1 seed)</t>
         </is>
       </c>
-      <c r="F26" s="8" t="inlineStr">
+      <c r="F26" s="20" t="inlineStr">
         <is>
           <t>0.8131 (1 seed)</t>
-        </is>
-      </c>
-      <c r="G26" s="6" t="inlineStr">
-        <is>
-          <t>band_norm_pac 目标</t>
         </is>
       </c>
     </row>
@@ -26041,24 +25517,19 @@
       <c r="C27" t="n">
         <v>1.66</v>
       </c>
-      <c r="D27" s="8" t="inlineStr">
+      <c r="D27" s="20" t="inlineStr">
         <is>
           <t>0.5184 (1 seed)</t>
         </is>
       </c>
-      <c r="E27" s="8" t="inlineStr">
+      <c r="E27" s="20" t="inlineStr">
         <is>
           <t>0.3993 (1 seed)</t>
         </is>
       </c>
-      <c r="F27" s="8" t="inlineStr">
+      <c r="F27" s="20" t="inlineStr">
         <is>
           <t>0.7488 (1 seed)</t>
-        </is>
-      </c>
-      <c r="G27" s="6" t="inlineStr">
-        <is>
-          <t>patch_len 200；表征质量协议</t>
         </is>
       </c>
     </row>
@@ -26071,27 +25542,23 @@
       <c r="C28" t="n">
         <v>1.66</v>
       </c>
-      <c r="D28" s="8" t="inlineStr">
+      <c r="D28" s="20" t="inlineStr">
         <is>
           <t>0.3859 (1 seed)</t>
         </is>
       </c>
-      <c r="E28" s="8" t="inlineStr">
+      <c r="E28" s="20" t="inlineStr">
         <is>
           <t>0.2695 (1 seed)</t>
         </is>
       </c>
-      <c r="F28" s="8" t="inlineStr">
+      <c r="F28" s="20" t="inlineStr">
         <is>
           <t>0.6760 (1 seed)</t>
         </is>
       </c>
-      <c r="G28" s="6" t="inlineStr">
-        <is>
-          <t>四道门第 4 门对照</t>
-        </is>
-      </c>
-    </row>
+    </row>
+    <row r="29"/>
     <row r="30">
       <c r="A30" s="6" t="inlineStr">
         <is>
@@ -26103,7 +25570,7 @@
           <t>CodeBrain (ICLR'26, 自报)</t>
         </is>
       </c>
-      <c r="D30" s="6" t="inlineStr">
+      <c r="D30" s="17" t="inlineStr">
         <is>
           <t>0.6912</t>
         </is>
@@ -26115,7 +25582,7 @@
           <t>Uni-NTFM-large (ICLR'26, 自报)</t>
         </is>
       </c>
-      <c r="D31" s="6" t="inlineStr">
+      <c r="D31" s="17" t="inlineStr">
         <is>
           <t>0.7030</t>
         </is>
@@ -26127,12 +25594,13 @@
           <t>CBraMod (原论文自报)</t>
         </is>
       </c>
-      <c r="D32" s="6" t="inlineStr">
+      <c r="D32" s="17" t="inlineStr">
         <is>
           <t>0.6512</t>
         </is>
       </c>
     </row>
+    <row r="33"/>
     <row r="34">
       <c r="A34" s="6" t="inlineStr">
         <is>
@@ -27727,15 +27195,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G30"/>
+  <dimension ref="A1:F30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
     <col width="11" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
     <col width="46" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
@@ -27784,11 +27252,6 @@
           <t>Balanced Acc</t>
         </is>
       </c>
-      <c r="G4" s="5" t="inlineStr">
-        <is>
-          <t>备注</t>
-        </is>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -27804,24 +27267,19 @@
       <c r="C5" t="n">
         <v>0</v>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D5" s="17" t="inlineStr">
         <is>
           <t>0.2384±0.0000</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E5" s="17" t="inlineStr">
         <is>
           <t>0.8035±0.0000</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F5" s="21" t="inlineStr">
         <is>
           <t>0.7412±0.0000</t>
-        </is>
-      </c>
-      <c r="G5" s="6" t="inlineStr">
-        <is>
-          <t>bandpower+Hjorth+谱熵；四道门第 1 门</t>
         </is>
       </c>
     </row>
@@ -27839,17 +27297,17 @@
       <c r="C6" t="n">
         <v>1.14</v>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D6" s="17" t="inlineStr">
         <is>
           <t>0.5020±0.0174</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E6" s="17" t="inlineStr">
         <is>
           <t>0.8888±0.0015</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="F6" s="17" t="inlineStr">
         <is>
           <t>0.5609±0.0310</t>
         </is>
@@ -27864,17 +27322,17 @@
       <c r="C7" t="n">
         <v>1.57</v>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D7" s="17" t="inlineStr">
         <is>
           <t>0.5043±0.0143</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E7" s="17" t="inlineStr">
         <is>
           <t>0.8871±0.0028</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F7" s="17" t="inlineStr">
         <is>
           <t>0.5601±0.0144</t>
         </is>
@@ -27889,17 +27347,17 @@
       <c r="C8" t="n">
         <v>3.15</v>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D8" s="17" t="inlineStr">
         <is>
           <t>0.3707±0.1579</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E8" s="17" t="inlineStr">
         <is>
           <t>0.8455±0.0343</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F8" s="17" t="inlineStr">
         <is>
           <t>0.5389±0.0447</t>
         </is>
@@ -27914,17 +27372,17 @@
       <c r="C9" t="n">
         <v>2.46</v>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D9" s="17" t="inlineStr">
         <is>
           <t>0.5449±0.0242</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E9" s="17" t="inlineStr">
         <is>
           <t>0.8924±0.0091</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F9" s="17" t="inlineStr">
         <is>
           <t>0.5953±0.0273</t>
         </is>
@@ -27939,17 +27397,17 @@
       <c r="C10" t="n">
         <v>3.43</v>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D10" s="17" t="inlineStr">
         <is>
           <t>0.3589±0.0256</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E10" s="17" t="inlineStr">
         <is>
           <t>0.8148±0.0162</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="F10" s="17" t="inlineStr">
         <is>
           <t>0.5514±0.0346</t>
         </is>
@@ -27964,24 +27422,19 @@
       <c r="C11" t="n">
         <v>0</v>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D11" s="17" t="inlineStr">
         <is>
           <t>0.4921±0.0247</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E11" s="17" t="inlineStr">
         <is>
           <t>0.8727±0.0032</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="F11" s="17" t="inlineStr">
         <is>
           <t>0.5215±0.0090</t>
-        </is>
-      </c>
-      <c r="G11" s="6" t="inlineStr">
-        <is>
-          <t>公开搜索预算调参</t>
         </is>
       </c>
     </row>
@@ -27994,24 +27447,19 @@
       <c r="C12" t="n">
         <v>1.46</v>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D12" s="17" t="inlineStr">
         <is>
           <t>0.3190±0.0307</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E12" s="17" t="inlineStr">
         <is>
           <t>0.8186±0.0231</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="F12" s="17" t="inlineStr">
         <is>
           <t>0.5216±0.0305</t>
-        </is>
-      </c>
-      <c r="G12" s="6" t="inlineStr">
-        <is>
-          <t>benchmark 文献最强单体</t>
         </is>
       </c>
     </row>
@@ -28029,17 +27477,17 @@
       <c r="C13" t="n">
         <v>3.19</v>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="D13" s="17" t="inlineStr">
         <is>
           <t>0.3379±0.0310</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="E13" s="17" t="inlineStr">
         <is>
           <t>0.8382±0.0110</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="F13" s="17" t="inlineStr">
         <is>
           <t>0.5634±0.0267</t>
         </is>
@@ -28054,17 +27502,17 @@
       <c r="C14" t="n">
         <v>5.82</v>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="D14" s="17" t="inlineStr">
         <is>
           <t>0.4754±0.0386</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="E14" s="17" t="inlineStr">
         <is>
           <t>0.8687±0.0206</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="F14" s="17" t="inlineStr">
         <is>
           <t>0.6139±0.0309</t>
         </is>
@@ -28079,17 +27527,17 @@
       <c r="C15" t="n">
         <v>30.65</v>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="D15" s="17" t="inlineStr">
         <is>
           <t>0.4344±0.0346</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="E15" s="17" t="inlineStr">
         <is>
           <t>0.8520±0.0041</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="F15" s="17" t="inlineStr">
         <is>
           <t>0.6347±0.0279</t>
         </is>
@@ -28104,17 +27552,17 @@
       <c r="C16" t="n">
         <v>25.69</v>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="D16" s="17" t="inlineStr">
         <is>
           <t>0.5446±0.0575</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="E16" s="17" t="inlineStr">
         <is>
           <t>0.8821±0.0099</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="F16" s="17" t="inlineStr">
         <is>
           <t>0.6587±0.0505</t>
         </is>
@@ -28129,24 +27577,19 @@
       <c r="C17" t="n">
         <v>1.89</v>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="D17" s="17" t="inlineStr">
         <is>
           <t>0.3474±0.0151</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="E17" s="17" t="inlineStr">
         <is>
           <t>0.8286±0.0048</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="F17" s="17" t="inlineStr">
         <is>
           <t>0.5645±0.0224</t>
-        </is>
-      </c>
-      <c r="G17" s="6" t="inlineStr">
-        <is>
-          <t>tokenizer 直接对手</t>
         </is>
       </c>
     </row>
@@ -28159,24 +27602,19 @@
       <c r="C18" t="n">
         <v>69.45999999999999</v>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="D18" s="17" t="inlineStr">
         <is>
           <t>0.5026±0.0609</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="E18" s="17" t="inlineStr">
         <is>
           <t>0.8885±0.0129</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
+      <c r="F18" s="17" t="inlineStr">
         <is>
           <t>0.5523±0.0304</t>
-        </is>
-      </c>
-      <c r="G18" s="6" t="inlineStr">
-        <is>
-          <t>新增；HF 权重</t>
         </is>
       </c>
     </row>
@@ -28189,24 +27627,19 @@
       <c r="C19" t="n">
         <v>41.06</v>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="D19" s="17" t="inlineStr">
         <is>
           <t>0.5170±0.0962</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="E19" s="17" t="inlineStr">
         <is>
           <t>0.8876±0.0221</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
+      <c r="F19" s="17" t="inlineStr">
         <is>
           <t>0.6207±0.0462</t>
-        </is>
-      </c>
-      <c r="G19" s="6" t="inlineStr">
-        <is>
-          <t>新增；GDrive 权重</t>
         </is>
       </c>
     </row>
@@ -28224,17 +27657,17 @@
       <c r="C20" t="n">
         <v>3.19</v>
       </c>
-      <c r="D20" t="inlineStr">
+      <c r="D20" s="17" t="inlineStr">
         <is>
           <t>0.3475±0.0210</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="E20" s="17" t="inlineStr">
         <is>
           <t>0.8256±0.0136</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
+      <c r="F20" s="17" t="inlineStr">
         <is>
           <t>0.6156±0.0527</t>
         </is>
@@ -28249,17 +27682,17 @@
       <c r="C21" t="n">
         <v>5.82</v>
       </c>
-      <c r="D21" t="inlineStr">
+      <c r="D21" s="17" t="inlineStr">
         <is>
           <t>0.4752±0.0390</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="E21" s="17" t="inlineStr">
         <is>
           <t>0.8575±0.0156</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
+      <c r="F21" s="17" t="inlineStr">
         <is>
           <t>0.5814±0.0290</t>
         </is>
@@ -28274,17 +27707,17 @@
       <c r="C22" t="n">
         <v>30.65</v>
       </c>
-      <c r="D22" t="inlineStr">
+      <c r="D22" s="17" t="inlineStr">
         <is>
           <t>0.4818±0.0426</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="E22" s="17" t="inlineStr">
         <is>
           <t>0.8753±0.0273</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
+      <c r="F22" s="17" t="inlineStr">
         <is>
           <t>0.5761±0.0403</t>
         </is>
@@ -28296,11 +27729,6 @@
           <t>EEGPT (scratch)</t>
         </is>
       </c>
-      <c r="G23" s="6" t="inlineStr">
-        <is>
-          <t>不新排；仅新语料已有数字</t>
-        </is>
-      </c>
     </row>
     <row r="24">
       <c r="B24" t="inlineStr">
@@ -28308,11 +27736,6 @@
           <t>TFM-Tokenizer (scratch)</t>
         </is>
       </c>
-      <c r="G24" s="6" t="inlineStr">
-        <is>
-          <t>不新排；仅新语料已有数字</t>
-        </is>
-      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -28328,17 +27751,17 @@
       <c r="C25" t="n">
         <v>1.62</v>
       </c>
-      <c r="D25" s="8" t="inlineStr">
+      <c r="D25" s="20" t="inlineStr">
         <is>
           <t>0.6328 (1 seed)</t>
         </is>
       </c>
-      <c r="E25" s="8" t="inlineStr">
+      <c r="E25" s="20" t="inlineStr">
         <is>
           <t>0.9217 (1 seed)</t>
         </is>
       </c>
-      <c r="F25" s="8" t="inlineStr">
+      <c r="F25" s="20" t="inlineStr">
         <is>
           <t>0.6298 (1 seed)</t>
         </is>
@@ -28353,24 +27776,19 @@
       <c r="C26" t="n">
         <v>1.62</v>
       </c>
-      <c r="D26" s="8" t="inlineStr">
+      <c r="D26" s="19" t="inlineStr">
         <is>
           <t>0.7143 (1 seed)</t>
         </is>
       </c>
-      <c r="E26" s="8" t="inlineStr">
+      <c r="E26" s="19" t="inlineStr">
         <is>
           <t>0.9386 (1 seed)</t>
         </is>
       </c>
-      <c r="F26" s="8" t="inlineStr">
+      <c r="F26" s="20" t="inlineStr">
         <is>
           <t>0.6832 (1 seed)</t>
-        </is>
-      </c>
-      <c r="G26" s="6" t="inlineStr">
-        <is>
-          <t>band_norm_pac 目标</t>
         </is>
       </c>
     </row>
@@ -28383,24 +27801,19 @@
       <c r="C27" t="n">
         <v>1.66</v>
       </c>
-      <c r="D27" s="8" t="inlineStr">
+      <c r="D27" s="20" t="inlineStr">
         <is>
           <t>0.5417 (1 seed)</t>
         </is>
       </c>
-      <c r="E27" s="8" t="inlineStr">
+      <c r="E27" s="20" t="inlineStr">
         <is>
           <t>0.9022 (1 seed)</t>
         </is>
       </c>
-      <c r="F27" s="8" t="inlineStr">
+      <c r="F27" s="20" t="inlineStr">
         <is>
           <t>0.5712 (1 seed)</t>
-        </is>
-      </c>
-      <c r="G27" s="6" t="inlineStr">
-        <is>
-          <t>patch_len 200；表征质量协议</t>
         </is>
       </c>
     </row>
@@ -28413,27 +27826,23 @@
       <c r="C28" t="n">
         <v>1.66</v>
       </c>
-      <c r="D28" s="8" t="inlineStr">
+      <c r="D28" s="20" t="inlineStr">
         <is>
           <t>0.4076 (1 seed)</t>
         </is>
       </c>
-      <c r="E28" s="8" t="inlineStr">
+      <c r="E28" s="20" t="inlineStr">
         <is>
           <t>0.8671 (1 seed)</t>
         </is>
       </c>
-      <c r="F28" s="8" t="inlineStr">
+      <c r="F28" s="20" t="inlineStr">
         <is>
           <t>0.5000 (1 seed)</t>
         </is>
       </c>
-      <c r="G28" s="6" t="inlineStr">
-        <is>
-          <t>四道门第 4 门对照</t>
-        </is>
-      </c>
-    </row>
+    </row>
+    <row r="29"/>
     <row r="30">
       <c r="A30" s="6" t="inlineStr">
         <is>
@@ -28452,15 +27861,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G30"/>
+  <dimension ref="A1:F30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
     <col width="11" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
     <col width="46" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
@@ -28509,11 +27918,6 @@
           <t>Balanced Acc</t>
         </is>
       </c>
-      <c r="G4" s="5" t="inlineStr">
-        <is>
-          <t>备注</t>
-        </is>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -28529,24 +27933,19 @@
       <c r="C5" t="n">
         <v>0</v>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D5" s="17" t="inlineStr">
         <is>
           <t>0.0468±0.0000</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E5" s="17" t="inlineStr">
         <is>
           <t>0.7117±0.0000</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F5" s="17" t="inlineStr">
         <is>
           <t>0.4998±0.0000</t>
-        </is>
-      </c>
-      <c r="G5" s="6" t="inlineStr">
-        <is>
-          <t>bandpower+Hjorth+谱熵；四道门第 1 门</t>
         </is>
       </c>
     </row>
@@ -28564,17 +27963,17 @@
       <c r="C6" t="n">
         <v>1.14</v>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D6" s="18" t="inlineStr">
         <is>
           <t>0.1976±0.0584</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E6" s="18" t="inlineStr">
         <is>
           <t>0.7995±0.0305</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="F6" s="18" t="inlineStr">
         <is>
           <t>0.5127±0.0064</t>
         </is>
@@ -28589,17 +27988,17 @@
       <c r="C7" t="n">
         <v>1.57</v>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D7" s="18" t="inlineStr">
         <is>
           <t>0.5072±0.0294</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E7" s="18" t="inlineStr">
         <is>
           <t>0.8905±0.0195</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F7" s="18" t="inlineStr">
         <is>
           <t>0.6362±0.0137</t>
         </is>
@@ -28614,17 +28013,17 @@
       <c r="C8" t="n">
         <v>3.15</v>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D8" s="18" t="inlineStr">
         <is>
           <t>0.5057±0.0605</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E8" s="18" t="inlineStr">
         <is>
           <t>0.9106±0.0068</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F8" s="1" t="inlineStr">
         <is>
           <t>0.6420±0.0476</t>
         </is>
@@ -28639,17 +28038,17 @@
       <c r="C9" t="n">
         <v>2.46</v>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D9" s="18" t="inlineStr">
         <is>
           <t>0.5341±0.0441</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E9" s="18" t="inlineStr">
         <is>
           <t>0.9124±0.0087</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F9" s="18" t="inlineStr">
         <is>
           <t>0.6163±0.0119</t>
         </is>
@@ -28664,17 +28063,17 @@
       <c r="C10" t="n">
         <v>3.43</v>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D10" s="18" t="inlineStr">
         <is>
           <t>0.2407±0.0926</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E10" s="18" t="inlineStr">
         <is>
           <t>0.7208±0.0847</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="F10" s="18" t="inlineStr">
         <is>
           <t>0.5551±0.0849</t>
         </is>
@@ -28689,24 +28088,19 @@
       <c r="C11" t="n">
         <v>0</v>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D11" s="17" t="inlineStr">
         <is>
           <t>0.1406±0.1098</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E11" s="17" t="inlineStr">
         <is>
           <t>0.7442±0.0898</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="F11" s="17" t="inlineStr">
         <is>
           <t>0.6016±0.1188</t>
-        </is>
-      </c>
-      <c r="G11" s="6" t="inlineStr">
-        <is>
-          <t>公开搜索预算调参</t>
         </is>
       </c>
     </row>
@@ -28716,11 +28110,6 @@
           <t>EEGConformer (调参)</t>
         </is>
       </c>
-      <c r="G12" s="6" t="inlineStr">
-        <is>
-          <t>benchmark 文献最强单体</t>
-        </is>
-      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -28736,24 +28125,19 @@
       <c r="C13" t="n">
         <v>3.19</v>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="D13" s="18" t="inlineStr">
         <is>
           <t>0.5601±0.0630</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="E13" s="18" t="inlineStr">
         <is>
           <t>0.8738±0.0030</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="F13" s="18" t="inlineStr">
         <is>
           <t>0.6190±0.0365</t>
-        </is>
-      </c>
-      <c r="G13" s="7" t="inlineStr">
-        <is>
-          <t>⚠ 自我重叠：BIOT 预训练集含 CHB-MIT，本行不作对比依据</t>
         </is>
       </c>
     </row>
@@ -28766,17 +28150,17 @@
       <c r="C14" t="n">
         <v>5.82</v>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="D14" s="17" t="inlineStr">
         <is>
           <t>0.4519±0.0791</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="E14" s="17" t="inlineStr">
         <is>
           <t>0.8709±0.0507</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="F14" s="17" t="inlineStr">
         <is>
           <t>0.5855±0.0387</t>
         </is>
@@ -28791,17 +28175,17 @@
       <c r="C15" t="n">
         <v>30.65</v>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="D15" s="18" t="inlineStr">
         <is>
           <t>0.2332±0.0798</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="E15" s="18" t="inlineStr">
         <is>
           <t>0.7828±0.0387</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="F15" s="18" t="inlineStr">
         <is>
           <t>0.5446±0.0162</t>
         </is>
@@ -28816,17 +28200,17 @@
       <c r="C16" t="n">
         <v>25.69</v>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="D16" s="17" t="inlineStr">
         <is>
           <t>0.2811±0.1082</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="E16" s="17" t="inlineStr">
         <is>
           <t>0.8574±0.0308</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="F16" s="17" t="inlineStr">
         <is>
           <t>0.5468±0.0516</t>
         </is>
@@ -28841,24 +28225,19 @@
       <c r="C17" t="n">
         <v>1.89</v>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="D17" s="18" t="inlineStr">
         <is>
           <t>0.6269±0.0205</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="E17" s="18" t="inlineStr">
         <is>
           <t>0.9291±0.0045</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="F17" s="18" t="inlineStr">
         <is>
           <t>0.6344±0.0133</t>
-        </is>
-      </c>
-      <c r="G17" s="6" t="inlineStr">
-        <is>
-          <t>tokenizer 直接对手</t>
         </is>
       </c>
     </row>
@@ -28871,24 +28250,19 @@
       <c r="C18" t="n">
         <v>69.45999999999999</v>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="D18" s="17" t="inlineStr">
         <is>
           <t>0.5802±0.1597</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="E18" s="17" t="inlineStr">
         <is>
           <t>0.8977±0.0523</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
+      <c r="F18" s="17" t="inlineStr">
         <is>
           <t>0.6320±0.0551</t>
-        </is>
-      </c>
-      <c r="G18" s="6" t="inlineStr">
-        <is>
-          <t>新增；HF 权重</t>
         </is>
       </c>
     </row>
@@ -28901,24 +28275,19 @@
       <c r="C19" t="n">
         <v>41.06</v>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="D19" s="18" t="inlineStr">
         <is>
           <t>0.3574±0.0782</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="E19" s="18" t="inlineStr">
         <is>
           <t>0.8521±0.0508</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
+      <c r="F19" s="18" t="inlineStr">
         <is>
           <t>0.5457±0.0178</t>
-        </is>
-      </c>
-      <c r="G19" s="6" t="inlineStr">
-        <is>
-          <t>新增；GDrive 权重</t>
         </is>
       </c>
     </row>
@@ -28936,17 +28305,17 @@
       <c r="C20" t="n">
         <v>3.19</v>
       </c>
-      <c r="D20" t="inlineStr">
+      <c r="D20" s="18" t="inlineStr">
         <is>
           <t>0.5661±0.0589</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="E20" s="18" t="inlineStr">
         <is>
           <t>0.8748±0.0151</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
+      <c r="F20" s="18" t="inlineStr">
         <is>
           <t>0.6240±0.0580</t>
         </is>
@@ -28961,17 +28330,17 @@
       <c r="C21" t="n">
         <v>5.82</v>
       </c>
-      <c r="D21" t="inlineStr">
+      <c r="D21" s="17" t="inlineStr">
         <is>
           <t>0.3596±0.0407</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="E21" s="17" t="inlineStr">
         <is>
           <t>0.8226±0.0243</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
+      <c r="F21" s="17" t="inlineStr">
         <is>
           <t>0.5854±0.0530</t>
         </is>
@@ -28986,17 +28355,17 @@
       <c r="C22" t="n">
         <v>30.65</v>
       </c>
-      <c r="D22" t="inlineStr">
+      <c r="D22" s="18" t="inlineStr">
         <is>
           <t>0.3169±0.1674</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="E22" s="18" t="inlineStr">
         <is>
           <t>0.7802±0.1088</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
+      <c r="F22" s="18" t="inlineStr">
         <is>
           <t>0.6018±0.0721</t>
         </is>
@@ -29008,11 +28377,6 @@
           <t>EEGPT (scratch)</t>
         </is>
       </c>
-      <c r="G23" s="6" t="inlineStr">
-        <is>
-          <t>不新排；仅新语料已有数字</t>
-        </is>
-      </c>
     </row>
     <row r="24">
       <c r="B24" t="inlineStr">
@@ -29020,11 +28384,6 @@
           <t>TFM-Tokenizer (scratch)</t>
         </is>
       </c>
-      <c r="G24" s="6" t="inlineStr">
-        <is>
-          <t>不新排；仅新语料已有数字</t>
-        </is>
-      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -29040,17 +28399,17 @@
       <c r="C25" t="n">
         <v>1.62</v>
       </c>
-      <c r="D25" s="8" t="inlineStr">
+      <c r="D25" s="20" t="inlineStr">
         <is>
           <t>0.7130 (1 seed)</t>
         </is>
       </c>
-      <c r="E25" s="8" t="inlineStr">
+      <c r="E25" s="20" t="inlineStr">
         <is>
           <t>0.9256 (1 seed)</t>
         </is>
       </c>
-      <c r="F25" s="8" t="inlineStr">
+      <c r="F25" s="20" t="inlineStr">
         <is>
           <t>0.5163 (1 seed)</t>
         </is>
@@ -29065,24 +28424,19 @@
       <c r="C26" t="n">
         <v>1.62</v>
       </c>
-      <c r="D26" s="8" t="inlineStr">
+      <c r="D26" s="19" t="inlineStr">
         <is>
           <t>0.7134 (1 seed)</t>
         </is>
       </c>
-      <c r="E26" s="8" t="inlineStr">
+      <c r="E26" s="19" t="inlineStr">
         <is>
           <t>0.9294 (1 seed)</t>
         </is>
       </c>
-      <c r="F26" s="8" t="inlineStr">
+      <c r="F26" s="20" t="inlineStr">
         <is>
           <t>0.5471 (1 seed)</t>
-        </is>
-      </c>
-      <c r="G26" s="6" t="inlineStr">
-        <is>
-          <t>band_norm_pac 目标</t>
         </is>
       </c>
     </row>
@@ -29095,24 +28449,19 @@
       <c r="C27" t="n">
         <v>1.66</v>
       </c>
-      <c r="D27" s="8" t="inlineStr">
+      <c r="D27" s="20" t="inlineStr">
         <is>
           <t>0.0499 (1 seed)</t>
         </is>
       </c>
-      <c r="E27" s="8" t="inlineStr">
+      <c r="E27" s="20" t="inlineStr">
         <is>
           <t>0.6917 (1 seed)</t>
         </is>
       </c>
-      <c r="F27" s="8" t="inlineStr">
+      <c r="F27" s="20" t="inlineStr">
         <is>
           <t>0.5000 (1 seed)</t>
-        </is>
-      </c>
-      <c r="G27" s="6" t="inlineStr">
-        <is>
-          <t>patch_len 200；表征质量协议</t>
         </is>
       </c>
     </row>
@@ -29125,27 +28474,23 @@
       <c r="C28" t="n">
         <v>1.66</v>
       </c>
-      <c r="D28" s="8" t="inlineStr">
+      <c r="D28" s="20" t="inlineStr">
         <is>
           <t>0.0147 (1 seed)</t>
         </is>
       </c>
-      <c r="E28" s="8" t="inlineStr">
+      <c r="E28" s="20" t="inlineStr">
         <is>
           <t>0.4725 (1 seed)</t>
         </is>
       </c>
-      <c r="F28" s="8" t="inlineStr">
+      <c r="F28" s="20" t="inlineStr">
         <is>
           <t>0.5000 (1 seed)</t>
         </is>
       </c>
-      <c r="G28" s="6" t="inlineStr">
-        <is>
-          <t>四道门第 4 门对照</t>
-        </is>
-      </c>
-    </row>
+    </row>
+    <row r="29"/>
     <row r="30">
       <c r="A30" s="6" t="inlineStr">
         <is>
@@ -29164,15 +28509,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G30"/>
+  <dimension ref="A1:F30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
     <col width="11" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
     <col width="46" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
@@ -29228,11 +28573,6 @@
           <t>Weighted F1</t>
         </is>
       </c>
-      <c r="G4" s="5" t="inlineStr">
-        <is>
-          <t>备注</t>
-        </is>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -29248,24 +28588,19 @@
       <c r="C5" t="n">
         <v>0</v>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D5" s="17" t="inlineStr">
         <is>
           <t>0.1864±0.0000</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E5" s="17" t="inlineStr">
         <is>
           <t>0.3437±0.0000</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F5" s="17" t="inlineStr">
         <is>
           <t>0.3016±0.0000</t>
-        </is>
-      </c>
-      <c r="G5" s="6" t="inlineStr">
-        <is>
-          <t>bandpower+Hjorth+谱熵；四道门第 1 门</t>
         </is>
       </c>
     </row>
@@ -29283,17 +28618,17 @@
       <c r="C6" t="n">
         <v>1.14</v>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D6" s="18" t="inlineStr">
         <is>
           <t>0.2196±0.0237</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E6" s="18" t="inlineStr">
         <is>
           <t>0.3734±0.0190</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="F6" s="18" t="inlineStr">
         <is>
           <t>0.2967±0.0227</t>
         </is>
@@ -29308,17 +28643,17 @@
       <c r="C7" t="n">
         <v>1.57</v>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D7" s="18" t="inlineStr">
         <is>
           <t>0.2034±0.0152</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E7" s="18" t="inlineStr">
         <is>
           <t>0.3789±0.0089</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F7" s="18" t="inlineStr">
         <is>
           <t>0.2515±0.0340</t>
         </is>
@@ -29333,17 +28668,17 @@
       <c r="C8" t="n">
         <v>3.16</v>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D8" s="18" t="inlineStr">
         <is>
           <t>0.2021±0.0096</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E8" s="18" t="inlineStr">
         <is>
           <t>0.3807±0.0085</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F8" s="18" t="inlineStr">
         <is>
           <t>0.2389±0.0175</t>
         </is>
@@ -29358,17 +28693,17 @@
       <c r="C9" t="n">
         <v>2.47</v>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D9" s="18" t="inlineStr">
         <is>
           <t>0.1832±0.0036</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E9" s="18" t="inlineStr">
         <is>
           <t>0.3676±0.0051</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F9" s="18" t="inlineStr">
         <is>
           <t>0.2049±0.0090</t>
         </is>
@@ -29383,17 +28718,17 @@
       <c r="C10" t="n">
         <v>3.43</v>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D10" s="18" t="inlineStr">
         <is>
           <t>0.1571±0.0142</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E10" s="18" t="inlineStr">
         <is>
           <t>0.3275±0.0122</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="F10" s="18" t="inlineStr">
         <is>
           <t>0.2226±0.0223</t>
         </is>
@@ -29405,11 +28740,6 @@
           <t>EEGNet (调参)</t>
         </is>
       </c>
-      <c r="G11" s="6" t="inlineStr">
-        <is>
-          <t>公开搜索预算调参</t>
-        </is>
-      </c>
     </row>
     <row r="12">
       <c r="B12" t="inlineStr">
@@ -29417,11 +28747,6 @@
           <t>EEGConformer (调参)</t>
         </is>
       </c>
-      <c r="G12" s="6" t="inlineStr">
-        <is>
-          <t>benchmark 文献最强单体</t>
-        </is>
-      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -29437,17 +28762,17 @@
       <c r="C13" t="n">
         <v>3.19</v>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="D13" s="18" t="inlineStr">
         <is>
           <t>0.1579±0.0086</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="E13" s="18" t="inlineStr">
         <is>
           <t>0.3330±0.0048</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="F13" s="18" t="inlineStr">
         <is>
           <t>0.2247±0.0181</t>
         </is>
@@ -29462,17 +28787,17 @@
       <c r="C14" t="n">
         <v>5.82</v>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="D14" s="17" t="inlineStr">
         <is>
           <t>0.1499±0.0040</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="E14" s="17" t="inlineStr">
         <is>
           <t>0.3387±0.0024</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="F14" s="17" t="inlineStr">
         <is>
           <t>0.1554±0.0066</t>
         </is>
@@ -29487,17 +28812,17 @@
       <c r="C15" t="n">
         <v>30.65</v>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="D15" s="17" t="inlineStr">
         <is>
           <t>0.1732±0.0058</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="E15" s="17" t="inlineStr">
         <is>
           <t>0.3596±0.0049</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="F15" s="17" t="inlineStr">
         <is>
           <t>0.2005±0.0069</t>
         </is>
@@ -29512,17 +28837,17 @@
       <c r="C16" t="n">
         <v>25.69</v>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="D16" s="17" t="inlineStr">
         <is>
           <t>0.1524±0.0105</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="E16" s="17" t="inlineStr">
         <is>
           <t>0.3355±0.0109</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="F16" s="17" t="inlineStr">
         <is>
           <t>0.1917±0.0252</t>
         </is>
@@ -29537,24 +28862,19 @@
       <c r="C17" t="n">
         <v>1.89</v>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="D17" s="18" t="inlineStr">
         <is>
           <t>0.1683±0.0041</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="E17" s="18" t="inlineStr">
         <is>
           <t>0.3492±0.0037</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="F17" s="18" t="inlineStr">
         <is>
           <t>0.2093±0.0178</t>
-        </is>
-      </c>
-      <c r="G17" s="6" t="inlineStr">
-        <is>
-          <t>tokenizer 直接对手</t>
         </is>
       </c>
     </row>
@@ -29567,24 +28887,19 @@
       <c r="C18" t="n">
         <v>69.81999999999999</v>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="D18" s="21" t="inlineStr">
         <is>
           <t>0.2301±0.0159</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="E18" s="21" t="inlineStr">
         <is>
           <t>0.4000±0.0090</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
+      <c r="F18" s="21" t="inlineStr">
         <is>
           <t>0.3048±0.0202</t>
-        </is>
-      </c>
-      <c r="G18" s="6" t="inlineStr">
-        <is>
-          <t>新增；HF 权重</t>
         </is>
       </c>
     </row>
@@ -29597,24 +28912,19 @@
       <c r="C19" t="n">
         <v>41.06</v>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="D19" s="17" t="inlineStr">
         <is>
           <t>0.1710±0.0053</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="E19" s="17" t="inlineStr">
         <is>
           <t>0.3547±0.0044</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
+      <c r="F19" s="17" t="inlineStr">
         <is>
           <t>0.2030±0.0090</t>
-        </is>
-      </c>
-      <c r="G19" s="6" t="inlineStr">
-        <is>
-          <t>新增；GDrive 权重</t>
         </is>
       </c>
     </row>
@@ -29632,17 +28942,17 @@
       <c r="C20" t="n">
         <v>3.19</v>
       </c>
-      <c r="D20" t="inlineStr">
+      <c r="D20" s="18" t="inlineStr">
         <is>
           <t>0.1672±0.0069</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="E20" s="18" t="inlineStr">
         <is>
           <t>0.3422±0.0026</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
+      <c r="F20" s="18" t="inlineStr">
         <is>
           <t>0.2318±0.0144</t>
         </is>
@@ -29657,17 +28967,17 @@
       <c r="C21" t="n">
         <v>5.82</v>
       </c>
-      <c r="D21" t="inlineStr">
+      <c r="D21" s="17" t="inlineStr">
         <is>
           <t>0.1581±0.0060</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="E21" s="17" t="inlineStr">
         <is>
           <t>0.3352±0.0026</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
+      <c r="F21" s="17" t="inlineStr">
         <is>
           <t>0.2078±0.0287</t>
         </is>
@@ -29682,17 +28992,17 @@
       <c r="C22" t="n">
         <v>30.65</v>
       </c>
-      <c r="D22" t="inlineStr">
+      <c r="D22" s="17" t="inlineStr">
         <is>
           <t>0.1726±0.0023</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="E22" s="17" t="inlineStr">
         <is>
           <t>0.3574±0.0014</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
+      <c r="F22" s="17" t="inlineStr">
         <is>
           <t>0.1982±0.0019</t>
         </is>
@@ -29707,24 +29017,19 @@
       <c r="C23" t="n">
         <v>25.69</v>
       </c>
-      <c r="D23" t="inlineStr">
+      <c r="D23" s="17" t="inlineStr">
         <is>
           <t>0.1274±0.0041</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="E23" s="17" t="inlineStr">
         <is>
           <t>0.3098±0.0034</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
+      <c r="F23" s="17" t="inlineStr">
         <is>
           <t>0.1427±0.0012</t>
-        </is>
-      </c>
-      <c r="G23" s="6" t="inlineStr">
-        <is>
-          <t>不新排；仅新语料已有数字</t>
         </is>
       </c>
     </row>
@@ -29737,24 +29042,19 @@
       <c r="C24" t="n">
         <v>1.89</v>
       </c>
-      <c r="D24" t="inlineStr">
+      <c r="D24" s="18" t="inlineStr">
         <is>
           <t>0.0809±0.0012</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
+      <c r="E24" s="18" t="inlineStr">
         <is>
           <t>0.2620±0.0017</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
+      <c r="F24" s="18" t="inlineStr">
         <is>
           <t>0.1313±0.0051</t>
-        </is>
-      </c>
-      <c r="G24" s="6" t="inlineStr">
-        <is>
-          <t>不新排；仅新语料已有数字</t>
         </is>
       </c>
     </row>
@@ -29772,17 +29072,17 @@
       <c r="C25" t="n">
         <v>1.63</v>
       </c>
-      <c r="D25" t="inlineStr">
+      <c r="D25" s="18" t="inlineStr">
         <is>
           <t>0.2047±0.0090</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
+      <c r="E25" s="18" t="inlineStr">
         <is>
           <t>0.3861±0.0085</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
+      <c r="F25" s="18" t="inlineStr">
         <is>
           <t>0.2451±0.0076</t>
         </is>
@@ -29794,11 +29094,6 @@
           <t>PACLock (duplex, 预训练 v2)</t>
         </is>
       </c>
-      <c r="G26" s="6" t="inlineStr">
-        <is>
-          <t>band_norm_pac 目标</t>
-        </is>
-      </c>
     </row>
     <row r="27">
       <c r="B27" t="inlineStr">
@@ -29806,11 +29101,6 @@
           <t>PACLock (冻结探针, v2)</t>
         </is>
       </c>
-      <c r="G27" s="6" t="inlineStr">
-        <is>
-          <t>patch_len 200；表征质量协议</t>
-        </is>
-      </c>
     </row>
     <row r="28">
       <c r="B28" t="inlineStr">
@@ -29818,12 +29108,8 @@
           <t>PACLock (冻结探针, 随机初始化)</t>
         </is>
       </c>
-      <c r="G28" s="6" t="inlineStr">
-        <is>
-          <t>四道门第 4 门对照</t>
-        </is>
-      </c>
-    </row>
+    </row>
+    <row r="29"/>
     <row r="30">
       <c r="A30" s="6" t="inlineStr">
         <is>
@@ -29842,15 +29128,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G30"/>
+  <dimension ref="A1:F30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
     <col width="11" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
     <col width="46" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
@@ -29899,11 +29185,6 @@
           <t>AUC-PR</t>
         </is>
       </c>
-      <c r="G4" s="5" t="inlineStr">
-        <is>
-          <t>备注</t>
-        </is>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -29919,24 +29200,19 @@
       <c r="C5" t="n">
         <v>0</v>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D5" s="17" t="inlineStr">
         <is>
           <t>0.5919±0.0000</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E5" s="17" t="inlineStr">
         <is>
           <t>0.6421±0.0000</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F5" s="17" t="inlineStr">
         <is>
           <t>0.6660±0.0000</t>
-        </is>
-      </c>
-      <c r="G5" s="6" t="inlineStr">
-        <is>
-          <t>bandpower+Hjorth+谱熵；四道门第 1 门</t>
         </is>
       </c>
     </row>
@@ -29954,17 +29230,17 @@
       <c r="C6" t="n">
         <v>1.14</v>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D6" s="17" t="inlineStr">
         <is>
           <t>0.7311±0.0084</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E6" s="17" t="inlineStr">
         <is>
           <t>0.5917±0.0403</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="F6" s="17" t="inlineStr">
         <is>
           <t>0.8155±0.0104</t>
         </is>
@@ -29979,17 +29255,17 @@
       <c r="C7" t="n">
         <v>1.57</v>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D7" s="17" t="inlineStr">
         <is>
           <t>0.6464±0.0510</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E7" s="17" t="inlineStr">
         <is>
           <t>0.6060±0.0468</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F7" s="17" t="inlineStr">
         <is>
           <t>0.7393±0.0230</t>
         </is>
@@ -30004,17 +29280,17 @@
       <c r="C8" t="n">
         <v>3.15</v>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D8" s="17" t="inlineStr">
         <is>
           <t>0.6630±0.0116</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E8" s="17" t="inlineStr">
         <is>
           <t>0.6388±0.0056</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F8" s="17" t="inlineStr">
         <is>
           <t>0.7569±0.0170</t>
         </is>
@@ -30029,17 +29305,17 @@
       <c r="C9" t="n">
         <v>2.46</v>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D9" s="17" t="inlineStr">
         <is>
           <t>0.6407±0.0430</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E9" s="17" t="inlineStr">
         <is>
           <t>0.6254±0.0143</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F9" s="17" t="inlineStr">
         <is>
           <t>0.7363±0.0276</t>
         </is>
@@ -30054,17 +29330,17 @@
       <c r="C10" t="n">
         <v>3.43</v>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D10" s="17" t="inlineStr">
         <is>
           <t>0.6177±0.0377</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E10" s="17" t="inlineStr">
         <is>
           <t>0.5620±0.0356</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="F10" s="17" t="inlineStr">
         <is>
           <t>0.7730±0.0301</t>
         </is>
@@ -30079,24 +29355,19 @@
       <c r="C11" t="n">
         <v>0</v>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D11" s="17" t="inlineStr">
         <is>
           <t>0.7848±0.0060</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E11" s="17" t="inlineStr">
         <is>
           <t>0.5938±0.0694</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="F11" s="17" t="inlineStr">
         <is>
           <t>0.8550±0.0090</t>
-        </is>
-      </c>
-      <c r="G11" s="6" t="inlineStr">
-        <is>
-          <t>公开搜索预算调参</t>
         </is>
       </c>
     </row>
@@ -30109,24 +29380,19 @@
       <c r="C12" t="n">
         <v>1.46</v>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D12" s="17" t="inlineStr">
         <is>
           <t>0.7215±0.0352</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E12" s="17" t="inlineStr">
         <is>
           <t>0.6361±0.0840</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="F12" s="17" t="inlineStr">
         <is>
           <t>0.8242±0.0149</t>
-        </is>
-      </c>
-      <c r="G12" s="6" t="inlineStr">
-        <is>
-          <t>benchmark 文献最强单体</t>
         </is>
       </c>
     </row>
@@ -30144,17 +29410,17 @@
       <c r="C13" t="n">
         <v>3.19</v>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="D13" s="17" t="inlineStr">
         <is>
           <t>0.7596±0.0163</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="E13" s="17" t="inlineStr">
         <is>
           <t>0.6347±0.0452</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="F13" s="17" t="inlineStr">
         <is>
           <t>0.8534±0.0126</t>
         </is>
@@ -30169,17 +29435,17 @@
       <c r="C14" t="n">
         <v>5.82</v>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="D14" s="17" t="inlineStr">
         <is>
           <t>0.7777±0.0153</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="E14" s="21" t="inlineStr">
         <is>
           <t>0.6601±0.0308</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="F14" s="21" t="inlineStr">
         <is>
           <t>0.8641±0.0075</t>
         </is>
@@ -30194,17 +29460,17 @@
       <c r="C15" t="n">
         <v>30.65</v>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="D15" s="17" t="inlineStr">
         <is>
           <t>0.6647±0.0173</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="E15" s="17" t="inlineStr">
         <is>
           <t>0.5967±0.0165</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="F15" s="17" t="inlineStr">
         <is>
           <t>0.8317±0.0177</t>
         </is>
@@ -30219,17 +29485,17 @@
       <c r="C16" t="n">
         <v>25.69</v>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="D16" s="17" t="inlineStr">
         <is>
           <t>0.7442±0.0223</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="E16" s="17" t="inlineStr">
         <is>
           <t>0.6564±0.0383</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="F16" s="17" t="inlineStr">
         <is>
           <t>0.8291±0.0169</t>
         </is>
@@ -30244,24 +29510,19 @@
       <c r="C17" t="n">
         <v>1.89</v>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="D17" s="17" t="inlineStr">
         <is>
           <t>0.6255±0.0132</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="E17" s="17" t="inlineStr">
         <is>
           <t>0.5386±0.0165</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="F17" s="17" t="inlineStr">
         <is>
           <t>0.7474±0.0061</t>
-        </is>
-      </c>
-      <c r="G17" s="6" t="inlineStr">
-        <is>
-          <t>tokenizer 直接对手</t>
         </is>
       </c>
     </row>
@@ -30271,11 +29532,6 @@
           <t>REVE-Base (pretrained)</t>
         </is>
       </c>
-      <c r="G18" s="6" t="inlineStr">
-        <is>
-          <t>新增；HF 权重</t>
-        </is>
-      </c>
     </row>
     <row r="19">
       <c r="B19" t="inlineStr">
@@ -30286,24 +29542,19 @@
       <c r="C19" t="n">
         <v>41.06</v>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="D19" s="17" t="inlineStr">
         <is>
           <t>0.5997±0.0351</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="E19" s="17" t="inlineStr">
         <is>
           <t>0.5633±0.0217</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
+      <c r="F19" s="17" t="inlineStr">
         <is>
           <t>0.7594±0.0065</t>
-        </is>
-      </c>
-      <c r="G19" s="6" t="inlineStr">
-        <is>
-          <t>新增；GDrive 权重</t>
         </is>
       </c>
     </row>
@@ -30321,17 +29572,17 @@
       <c r="C20" t="n">
         <v>3.19</v>
       </c>
-      <c r="D20" t="inlineStr">
+      <c r="D20" s="17" t="inlineStr">
         <is>
           <t>0.7522±0.0105</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="E20" s="17" t="inlineStr">
         <is>
           <t>0.6151±0.0324</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
+      <c r="F20" s="17" t="inlineStr">
         <is>
           <t>0.8542±0.0074</t>
         </is>
@@ -30346,17 +29597,17 @@
       <c r="C21" t="n">
         <v>5.82</v>
       </c>
-      <c r="D21" t="inlineStr">
+      <c r="D21" s="17" t="inlineStr">
         <is>
           <t>0.7186±0.0427</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="E21" s="17" t="inlineStr">
         <is>
           <t>0.6277±0.0327</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
+      <c r="F21" s="17" t="inlineStr">
         <is>
           <t>0.8204±0.0409</t>
         </is>
@@ -30371,17 +29622,17 @@
       <c r="C22" t="n">
         <v>30.65</v>
       </c>
-      <c r="D22" t="inlineStr">
+      <c r="D22" s="17" t="inlineStr">
         <is>
           <t>0.6422±0.0276</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="E22" s="17" t="inlineStr">
         <is>
           <t>0.6093±0.0229</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
+      <c r="F22" s="17" t="inlineStr">
         <is>
           <t>0.7790±0.0183</t>
         </is>
@@ -30396,24 +29647,19 @@
       <c r="C23" t="n">
         <v>25.69</v>
       </c>
-      <c r="D23" t="inlineStr">
+      <c r="D23" s="17" t="inlineStr">
         <is>
           <t>0.7859±0.0175</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="E23" s="17" t="inlineStr">
         <is>
           <t>0.5000±0.0000</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
+      <c r="F23" s="17" t="inlineStr">
         <is>
           <t>0.8421±0.0172</t>
-        </is>
-      </c>
-      <c r="G23" s="6" t="inlineStr">
-        <is>
-          <t>不新排；仅新语料已有数字</t>
         </is>
       </c>
     </row>
@@ -30426,24 +29672,19 @@
       <c r="C24" t="n">
         <v>1.89</v>
       </c>
-      <c r="D24" t="inlineStr">
+      <c r="D24" s="17" t="inlineStr">
         <is>
           <t>0.6070±0.0164</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
+      <c r="E24" s="17" t="inlineStr">
         <is>
           <t>0.5208±0.0170</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
+      <c r="F24" s="17" t="inlineStr">
         <is>
           <t>0.7500±0.0156</t>
-        </is>
-      </c>
-      <c r="G24" s="6" t="inlineStr">
-        <is>
-          <t>不新排；仅新语料已有数字</t>
         </is>
       </c>
     </row>
@@ -30461,17 +29702,17 @@
       <c r="C25" t="n">
         <v>1.62</v>
       </c>
-      <c r="D25" s="8" t="inlineStr">
+      <c r="D25" s="19" t="inlineStr">
         <is>
           <t>0.8052 (1 seed)</t>
         </is>
       </c>
-      <c r="E25" s="8" t="inlineStr">
+      <c r="E25" s="20" t="inlineStr">
         <is>
           <t>0.5000 (1 seed)</t>
         </is>
       </c>
-      <c r="F25" s="8" t="inlineStr">
+      <c r="F25" s="20" t="inlineStr">
         <is>
           <t>0.8493 (1 seed)</t>
         </is>
@@ -30483,11 +29724,6 @@
           <t>PACLock (duplex, 预训练 v2)</t>
         </is>
       </c>
-      <c r="G26" s="6" t="inlineStr">
-        <is>
-          <t>band_norm_pac 目标</t>
-        </is>
-      </c>
     </row>
     <row r="27">
       <c r="B27" t="inlineStr">
@@ -30495,11 +29731,6 @@
           <t>PACLock (冻结探针, v2)</t>
         </is>
       </c>
-      <c r="G27" s="6" t="inlineStr">
-        <is>
-          <t>patch_len 200；表征质量协议</t>
-        </is>
-      </c>
     </row>
     <row r="28">
       <c r="B28" t="inlineStr">
@@ -30507,12 +29738,8 @@
           <t>PACLock (冻结探针, 随机初始化)</t>
         </is>
       </c>
-      <c r="G28" s="6" t="inlineStr">
-        <is>
-          <t>四道门第 4 门对照</t>
-        </is>
-      </c>
-    </row>
+    </row>
+    <row r="29"/>
     <row r="30">
       <c r="A30" s="6" t="inlineStr">
         <is>
@@ -30531,15 +29758,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G34"/>
+  <dimension ref="A1:F34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
     <col width="11" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
     <col width="46" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
@@ -30588,11 +29815,6 @@
           <t>AUROC</t>
         </is>
       </c>
-      <c r="G4" s="5" t="inlineStr">
-        <is>
-          <t>备注</t>
-        </is>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -30608,24 +29830,19 @@
       <c r="C5" t="n">
         <v>0</v>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D5" s="17" t="inlineStr">
         <is>
           <t>0.7445±0.0000</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E5" s="17" t="inlineStr">
         <is>
           <t>0.8155±0.0000</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F5" s="17" t="inlineStr">
         <is>
           <t>0.8248±0.0000</t>
-        </is>
-      </c>
-      <c r="G5" s="6" t="inlineStr">
-        <is>
-          <t>bandpower+Hjorth+谱熵；四道门第 1 门</t>
         </is>
       </c>
     </row>
@@ -30643,17 +29860,17 @@
       <c r="C6" t="n">
         <v>1.14</v>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D6" s="18" t="inlineStr">
         <is>
           <t>0.7923±0.0093</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E6" s="18" t="inlineStr">
         <is>
           <t>0.8874±0.0025</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="F6" s="18" t="inlineStr">
         <is>
           <t>0.8877±0.0029</t>
         </is>
@@ -30668,17 +29885,17 @@
       <c r="C7" t="n">
         <v>1.57</v>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D7" s="18" t="inlineStr">
         <is>
           <t>0.7895±0.0012</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E7" s="18" t="inlineStr">
         <is>
           <t>0.8893±0.0062</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F7" s="18" t="inlineStr">
         <is>
           <t>0.8886±0.0059</t>
         </is>
@@ -30693,17 +29910,17 @@
       <c r="C8" t="n">
         <v>3.15</v>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D8" s="18" t="inlineStr">
         <is>
           <t>0.7816±0.0320</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E8" s="18" t="inlineStr">
         <is>
           <t>0.8876±0.0104</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F8" s="18" t="inlineStr">
         <is>
           <t>0.8913±0.0047</t>
         </is>
@@ -30718,17 +29935,17 @@
       <c r="C9" t="n">
         <v>2.46</v>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D9" s="18" t="inlineStr">
         <is>
           <t>0.7648±0.0330</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E9" s="18" t="inlineStr">
         <is>
           <t>0.8868±0.0050</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F9" s="18" t="inlineStr">
         <is>
           <t>0.8865±0.0069</t>
         </is>
@@ -30743,17 +29960,17 @@
       <c r="C10" t="n">
         <v>3.43</v>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D10" s="1" t="inlineStr">
         <is>
           <t>0.8198±0.0036</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E10" s="18" t="inlineStr">
         <is>
           <t>0.9022±0.0029</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="F10" s="18" t="inlineStr">
         <is>
           <t>0.8972±0.0046</t>
         </is>
@@ -30768,24 +29985,19 @@
       <c r="C11" t="n">
         <v>0</v>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D11" s="17" t="inlineStr">
         <is>
           <t>0.7681±0.0034</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E11" s="17" t="inlineStr">
         <is>
           <t>0.8511±0.0031</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="F11" s="17" t="inlineStr">
         <is>
           <t>0.8519±0.0034</t>
-        </is>
-      </c>
-      <c r="G11" s="6" t="inlineStr">
-        <is>
-          <t>公开搜索预算调参</t>
         </is>
       </c>
     </row>
@@ -30798,24 +30010,19 @@
       <c r="C12" t="n">
         <v>1.46</v>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D12" s="17" t="inlineStr">
         <is>
           <t>0.7892±0.0159</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E12" s="17" t="inlineStr">
         <is>
           <t>0.8834±0.0041</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="F12" s="17" t="inlineStr">
         <is>
           <t>0.8828±0.0012</t>
-        </is>
-      </c>
-      <c r="G12" s="6" t="inlineStr">
-        <is>
-          <t>benchmark 文献最强单体</t>
         </is>
       </c>
     </row>
@@ -30833,24 +30040,19 @@
       <c r="C13" t="n">
         <v>3.19</v>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="D13" s="18" t="inlineStr">
         <is>
           <t>0.7950±0.0026</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="E13" s="18" t="inlineStr">
         <is>
           <t>0.8704±0.0044</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="F13" s="18" t="inlineStr">
         <is>
           <t>0.8730±0.0026</t>
-        </is>
-      </c>
-      <c r="G13" s="7" t="inlineStr">
-        <is>
-          <t>⚠ 自我重叠：BIOT 预训练集含 TUAB，本行不作对比依据</t>
         </is>
       </c>
     </row>
@@ -30863,17 +30065,17 @@
       <c r="C14" t="n">
         <v>5.82</v>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="D14" s="18" t="inlineStr">
         <is>
           <t>0.7959±0.0016</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="E14" s="18" t="inlineStr">
         <is>
           <t>0.8586±0.0126</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="F14" s="18" t="inlineStr">
         <is>
           <t>0.8770±0.0029</t>
         </is>
@@ -30888,17 +30090,17 @@
       <c r="C15" t="n">
         <v>30.65</v>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="D15" s="18" t="inlineStr">
         <is>
           <t>0.7869±0.0104</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="E15" s="18" t="inlineStr">
         <is>
           <t>0.8662±0.0049</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="F15" s="18" t="inlineStr">
         <is>
           <t>0.8638±0.0075</t>
         </is>
@@ -30913,17 +30115,17 @@
       <c r="C16" t="n">
         <v>25.69</v>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="D16" s="18" t="inlineStr">
         <is>
           <t>0.8137±0.0052</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="E16" s="1" t="inlineStr">
         <is>
           <t>0.9054±0.0029</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="F16" s="1" t="inlineStr">
         <is>
           <t>0.9028±0.0033</t>
         </is>
@@ -30938,24 +30140,19 @@
       <c r="C17" t="n">
         <v>1.89</v>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="D17" s="18" t="inlineStr">
         <is>
           <t>0.7961±0.0056</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="E17" s="18" t="inlineStr">
         <is>
           <t>0.8840±0.0027</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="F17" s="18" t="inlineStr">
         <is>
           <t>0.8793±0.0021</t>
-        </is>
-      </c>
-      <c r="G17" s="6" t="inlineStr">
-        <is>
-          <t>tokenizer 直接对手</t>
         </is>
       </c>
     </row>
@@ -30968,24 +30165,19 @@
       <c r="C18" t="n">
         <v>69.45999999999999</v>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="D18" s="18" t="inlineStr">
         <is>
           <t>0.8055±0.0118</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="E18" s="18" t="inlineStr">
         <is>
           <t>0.8990±0.0088</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
+      <c r="F18" s="18" t="inlineStr">
         <is>
           <t>0.8945±0.0077</t>
-        </is>
-      </c>
-      <c r="G18" s="6" t="inlineStr">
-        <is>
-          <t>新增；HF 权重</t>
         </is>
       </c>
     </row>
@@ -30998,24 +30190,19 @@
       <c r="C19" t="n">
         <v>41.06</v>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="D19" s="18" t="inlineStr">
         <is>
           <t>0.8093±0.0074</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="E19" s="18" t="inlineStr">
         <is>
           <t>0.8996±0.0036</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
+      <c r="F19" s="18" t="inlineStr">
         <is>
           <t>0.8943±0.0047</t>
-        </is>
-      </c>
-      <c r="G19" s="6" t="inlineStr">
-        <is>
-          <t>新增；GDrive 权重</t>
         </is>
       </c>
     </row>
@@ -31033,17 +30220,17 @@
       <c r="C20" t="n">
         <v>3.19</v>
       </c>
-      <c r="D20" t="inlineStr">
+      <c r="D20" s="18" t="inlineStr">
         <is>
           <t>0.7909±0.0035</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="E20" s="18" t="inlineStr">
         <is>
           <t>0.8683±0.0024</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
+      <c r="F20" s="18" t="inlineStr">
         <is>
           <t>0.8694±0.0047</t>
         </is>
@@ -31058,17 +30245,17 @@
       <c r="C21" t="n">
         <v>5.82</v>
       </c>
-      <c r="D21" t="inlineStr">
+      <c r="D21" s="18" t="inlineStr">
         <is>
           <t>0.7769±0.0041</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="E21" s="18" t="inlineStr">
         <is>
           <t>0.8534±0.0053</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
+      <c r="F21" s="18" t="inlineStr">
         <is>
           <t>0.8614±0.0057</t>
         </is>
@@ -31083,17 +30270,17 @@
       <c r="C22" t="n">
         <v>30.65</v>
       </c>
-      <c r="D22" t="inlineStr">
+      <c r="D22" s="18" t="inlineStr">
         <is>
           <t>0.7920±0.0064</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="E22" s="18" t="inlineStr">
         <is>
           <t>0.8831±0.0030</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
+      <c r="F22" s="18" t="inlineStr">
         <is>
           <t>0.8763±0.0026</t>
         </is>
@@ -31105,11 +30292,6 @@
           <t>EEGPT (scratch)</t>
         </is>
       </c>
-      <c r="G23" s="6" t="inlineStr">
-        <is>
-          <t>不新排；仅新语料已有数字</t>
-        </is>
-      </c>
     </row>
     <row r="24">
       <c r="B24" t="inlineStr">
@@ -31117,11 +30299,6 @@
           <t>TFM-Tokenizer (scratch)</t>
         </is>
       </c>
-      <c r="G24" s="6" t="inlineStr">
-        <is>
-          <t>不新排；仅新语料已有数字</t>
-        </is>
-      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -31137,17 +30314,17 @@
       <c r="C25" t="n">
         <v>1.62</v>
       </c>
-      <c r="D25" s="8" t="inlineStr">
+      <c r="D25" s="20" t="inlineStr">
         <is>
           <t>0.8157 (1 seed)</t>
         </is>
       </c>
-      <c r="E25" s="8" t="inlineStr">
+      <c r="E25" s="20" t="inlineStr">
         <is>
           <t>0.8923 (1 seed)</t>
         </is>
       </c>
-      <c r="F25" s="8" t="inlineStr">
+      <c r="F25" s="20" t="inlineStr">
         <is>
           <t>0.8829 (1 seed)</t>
         </is>
@@ -31162,24 +30339,19 @@
       <c r="C26" t="n">
         <v>1.62</v>
       </c>
-      <c r="D26" s="8" t="inlineStr">
+      <c r="D26" s="20" t="inlineStr">
         <is>
           <t>0.8150 (1 seed)</t>
         </is>
       </c>
-      <c r="E26" s="8" t="inlineStr">
+      <c r="E26" s="20" t="inlineStr">
         <is>
           <t>0.8989 (1 seed)</t>
         </is>
       </c>
-      <c r="F26" s="8" t="inlineStr">
+      <c r="F26" s="20" t="inlineStr">
         <is>
           <t>0.8938 (1 seed)</t>
-        </is>
-      </c>
-      <c r="G26" s="6" t="inlineStr">
-        <is>
-          <t>band_norm_pac 目标</t>
         </is>
       </c>
     </row>
@@ -31189,11 +30361,6 @@
           <t>PACLock (冻结探针, v2)</t>
         </is>
       </c>
-      <c r="G27" s="6" t="inlineStr">
-        <is>
-          <t>patch_len 200；表征质量协议</t>
-        </is>
-      </c>
     </row>
     <row r="28">
       <c r="B28" t="inlineStr">
@@ -31201,12 +30368,8 @@
           <t>PACLock (冻结探针, 随机初始化)</t>
         </is>
       </c>
-      <c r="G28" s="6" t="inlineStr">
-        <is>
-          <t>四道门第 4 门对照</t>
-        </is>
-      </c>
-    </row>
+    </row>
+    <row r="29"/>
     <row r="30">
       <c r="A30" s="6" t="inlineStr">
         <is>
@@ -31218,7 +30381,7 @@
           <t>CodeBrain (ICLR'26, 自报)</t>
         </is>
       </c>
-      <c r="D30" s="6" t="inlineStr">
+      <c r="D30" s="17" t="inlineStr">
         <is>
           <t>0.8294</t>
         </is>
@@ -31230,7 +30393,7 @@
           <t>Uni-NTFM-large (ICLR'26, 自报)</t>
         </is>
       </c>
-      <c r="D31" s="6" t="inlineStr">
+      <c r="D31" s="17" t="inlineStr">
         <is>
           <t>0.8197</t>
         </is>
@@ -31242,12 +30405,13 @@
           <t>REVE-Base (原论文自报)</t>
         </is>
       </c>
-      <c r="D32" s="6" t="inlineStr">
+      <c r="D32" s="17" t="inlineStr">
         <is>
           <t>0.8315</t>
         </is>
       </c>
     </row>
+    <row r="33"/>
     <row r="34">
       <c r="A34" s="6" t="inlineStr">
         <is>
@@ -31266,15 +30430,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G30"/>
+  <dimension ref="A1:F30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
     <col width="11" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
     <col width="46" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
@@ -31323,11 +30487,6 @@
           <t>Weighted F1</t>
         </is>
       </c>
-      <c r="G4" s="5" t="inlineStr">
-        <is>
-          <t>备注</t>
-        </is>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -31343,24 +30502,19 @@
       <c r="C5" t="n">
         <v>0</v>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D5" s="17" t="inlineStr">
         <is>
           <t>0.4007±0.0000</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E5" s="17" t="inlineStr">
         <is>
           <t>0.1300±0.0000</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F5" s="17" t="inlineStr">
         <is>
           <t>0.4296±0.0000</t>
-        </is>
-      </c>
-      <c r="G5" s="6" t="inlineStr">
-        <is>
-          <t>bandpower+Hjorth+谱熵；四道门第 1 门</t>
         </is>
       </c>
     </row>
@@ -31378,17 +30532,17 @@
       <c r="C6" t="n">
         <v>1.14</v>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D6" s="17" t="inlineStr">
         <is>
           <t>0.3833±0.0062</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E6" s="17" t="inlineStr">
         <is>
           <t>0.0944±0.0248</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="F6" s="17" t="inlineStr">
         <is>
           <t>0.3744±0.0363</t>
         </is>
@@ -31403,17 +30557,17 @@
       <c r="C7" t="n">
         <v>1.57</v>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D7" s="17" t="inlineStr">
         <is>
           <t>0.4495±0.0192</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E7" s="17" t="inlineStr">
         <is>
           <t>0.1791±0.0321</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F7" s="17" t="inlineStr">
         <is>
           <t>0.4494±0.0329</t>
         </is>
@@ -31428,17 +30582,17 @@
       <c r="C8" t="n">
         <v>3.16</v>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D8" s="17" t="inlineStr">
         <is>
           <t>0.4804±0.0134</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E8" s="17" t="inlineStr">
         <is>
           <t>0.2588±0.0312</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F8" s="17" t="inlineStr">
         <is>
           <t>0.5004±0.0096</t>
         </is>
@@ -31453,17 +30607,17 @@
       <c r="C9" t="n">
         <v>2.47</v>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D9" s="17" t="inlineStr">
         <is>
           <t>0.3818±0.0270</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E9" s="17" t="inlineStr">
         <is>
           <t>0.0875±0.0375</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F9" s="17" t="inlineStr">
         <is>
           <t>0.3496±0.0394</t>
         </is>
@@ -31478,17 +30632,17 @@
       <c r="C10" t="n">
         <v>3.43</v>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D10" s="17" t="inlineStr">
         <is>
           <t>0.4904±0.0416</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E10" s="17" t="inlineStr">
         <is>
           <t>0.2906±0.0704</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="F10" s="17" t="inlineStr">
         <is>
           <t>0.5013±0.0494</t>
         </is>
@@ -31500,11 +30654,6 @@
           <t>EEGNet (调参)</t>
         </is>
       </c>
-      <c r="G11" s="6" t="inlineStr">
-        <is>
-          <t>公开搜索预算调参</t>
-        </is>
-      </c>
     </row>
     <row r="12">
       <c r="B12" t="inlineStr">
@@ -31515,24 +30664,19 @@
       <c r="C12" t="n">
         <v>1.46</v>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D12" s="17" t="inlineStr">
         <is>
           <t>0.4057±0.0619</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E12" s="17" t="inlineStr">
         <is>
           <t>0.1545±0.0914</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="F12" s="17" t="inlineStr">
         <is>
           <t>0.4430±0.0462</t>
-        </is>
-      </c>
-      <c r="G12" s="6" t="inlineStr">
-        <is>
-          <t>benchmark 文献最强单体</t>
         </is>
       </c>
     </row>
@@ -31550,17 +30694,17 @@
       <c r="C13" t="n">
         <v>3.19</v>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="D13" s="17" t="inlineStr">
         <is>
           <t>0.4829±0.0196</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="E13" s="17" t="inlineStr">
         <is>
           <t>0.2764±0.0347</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="F13" s="17" t="inlineStr">
         <is>
           <t>0.5070±0.0228</t>
         </is>
@@ -31582,17 +30726,17 @@
       <c r="C15" t="n">
         <v>35.45</v>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="D15" s="17" t="inlineStr">
         <is>
           <t>0.4411±0.0135</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="E15" s="17" t="inlineStr">
         <is>
           <t>0.1847±0.0306</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="F15" s="17" t="inlineStr">
         <is>
           <t>0.4663±0.0175</t>
         </is>
@@ -31607,17 +30751,17 @@
       <c r="C16" t="n">
         <v>25.69</v>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="D16" s="17" t="inlineStr">
         <is>
           <t>0.4964±0.0166</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="E16" s="17" t="inlineStr">
         <is>
           <t>0.2980±0.0450</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="F16" s="17" t="inlineStr">
         <is>
           <t>0.5216±0.0230</t>
         </is>
@@ -31632,24 +30776,19 @@
       <c r="C17" t="n">
         <v>1.89</v>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="D17" s="17" t="inlineStr">
         <is>
           <t>0.4464±0.0162</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="E17" s="17" t="inlineStr">
         <is>
           <t>0.1959±0.0216</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="F17" s="17" t="inlineStr">
         <is>
           <t>0.4692±0.0161</t>
-        </is>
-      </c>
-      <c r="G17" s="6" t="inlineStr">
-        <is>
-          <t>tokenizer 直接对手</t>
         </is>
       </c>
     </row>
@@ -31662,24 +30801,19 @@
       <c r="C18" t="n">
         <v>69.62</v>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="D18" s="17" t="inlineStr">
         <is>
           <t>0.5006±0.0398</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="E18" s="17" t="inlineStr">
         <is>
           <t>0.2970±0.0483</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
+      <c r="F18" s="17" t="inlineStr">
         <is>
           <t>0.5263±0.0393</t>
-        </is>
-      </c>
-      <c r="G18" s="6" t="inlineStr">
-        <is>
-          <t>新增；HF 权重</t>
         </is>
       </c>
     </row>
@@ -31692,24 +30826,19 @@
       <c r="C19" t="n">
         <v>47.06</v>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="D19" s="17" t="inlineStr">
         <is>
           <t>0.4426±0.0133</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="E19" s="17" t="inlineStr">
         <is>
           <t>0.2001±0.0204</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
+      <c r="F19" s="17" t="inlineStr">
         <is>
           <t>0.4807±0.0126</t>
-        </is>
-      </c>
-      <c r="G19" s="6" t="inlineStr">
-        <is>
-          <t>新增；GDrive 权重</t>
         </is>
       </c>
     </row>
@@ -31727,17 +30856,17 @@
       <c r="C20" t="n">
         <v>3.19</v>
       </c>
-      <c r="D20" t="inlineStr">
+      <c r="D20" s="17" t="inlineStr">
         <is>
           <t>0.5254±0.0171</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="E20" s="17" t="inlineStr">
         <is>
           <t>0.3108±0.0344</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
+      <c r="F20" s="17" t="inlineStr">
         <is>
           <t>0.5425±0.0298</t>
         </is>
@@ -31752,17 +30881,17 @@
       <c r="C21" t="n">
         <v>5.82</v>
       </c>
-      <c r="D21" t="inlineStr">
+      <c r="D21" s="17" t="inlineStr">
         <is>
           <t>0.4992±0.0162</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="E21" s="17" t="inlineStr">
         <is>
           <t>0.2953±0.0197</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
+      <c r="F21" s="17" t="inlineStr">
         <is>
           <t>0.5154±0.0062</t>
         </is>
@@ -31777,17 +30906,17 @@
       <c r="C22" t="n">
         <v>35.45</v>
       </c>
-      <c r="D22" t="inlineStr">
+      <c r="D22" s="17" t="inlineStr">
         <is>
           <t>0.4810±0.0152</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="E22" s="17" t="inlineStr">
         <is>
           <t>0.2736±0.0251</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
+      <c r="F22" s="17" t="inlineStr">
         <is>
           <t>0.5143±0.0173</t>
         </is>
@@ -31802,24 +30931,19 @@
       <c r="C23" t="n">
         <v>25.69</v>
       </c>
-      <c r="D23" t="inlineStr">
+      <c r="D23" s="17" t="inlineStr">
         <is>
           <t>0.4539±0.0461</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="E23" s="17" t="inlineStr">
         <is>
           <t>0.2224±0.0820</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
+      <c r="F23" s="17" t="inlineStr">
         <is>
           <t>0.4785±0.0635</t>
-        </is>
-      </c>
-      <c r="G23" s="6" t="inlineStr">
-        <is>
-          <t>不新排；仅新语料已有数字</t>
         </is>
       </c>
     </row>
@@ -31832,24 +30956,19 @@
       <c r="C24" t="n">
         <v>1.89</v>
       </c>
-      <c r="D24" t="inlineStr">
+      <c r="D24" s="17" t="inlineStr">
         <is>
           <t>0.4544±0.0180</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
+      <c r="E24" s="17" t="inlineStr">
         <is>
           <t>0.2230±0.0305</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
+      <c r="F24" s="17" t="inlineStr">
         <is>
           <t>0.4697±0.0254</t>
-        </is>
-      </c>
-      <c r="G24" s="6" t="inlineStr">
-        <is>
-          <t>不新排；仅新语料已有数字</t>
         </is>
       </c>
     </row>
@@ -31867,17 +30986,17 @@
       <c r="C25" t="n">
         <v>1.61</v>
       </c>
-      <c r="D25" s="8" t="inlineStr">
+      <c r="D25" s="19" t="inlineStr">
         <is>
           <t>0.5617 (1 seed)</t>
         </is>
       </c>
-      <c r="E25" s="8" t="inlineStr">
+      <c r="E25" s="19" t="inlineStr">
         <is>
           <t>0.3613 (1 seed)</t>
         </is>
       </c>
-      <c r="F25" s="8" t="inlineStr">
+      <c r="F25" s="19" t="inlineStr">
         <is>
           <t>0.5814 (1 seed)</t>
         </is>
@@ -31889,11 +31008,6 @@
           <t>PACLock (duplex, 预训练 v2)</t>
         </is>
       </c>
-      <c r="G26" s="6" t="inlineStr">
-        <is>
-          <t>band_norm_pac 目标</t>
-        </is>
-      </c>
     </row>
     <row r="27">
       <c r="B27" t="inlineStr">
@@ -31901,11 +31015,6 @@
           <t>PACLock (冻结探针, v2)</t>
         </is>
       </c>
-      <c r="G27" s="6" t="inlineStr">
-        <is>
-          <t>patch_len 200；表征质量协议</t>
-        </is>
-      </c>
     </row>
     <row r="28">
       <c r="B28" t="inlineStr">
@@ -31913,12 +31022,8 @@
           <t>PACLock (冻结探针, 随机初始化)</t>
         </is>
       </c>
-      <c r="G28" s="6" t="inlineStr">
-        <is>
-          <t>四道门第 4 门对照</t>
-        </is>
-      </c>
-    </row>
+    </row>
+    <row r="29"/>
     <row r="30">
       <c r="A30" s="6" t="inlineStr">
         <is>
@@ -31937,15 +31042,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G32"/>
+  <dimension ref="A1:F32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
     <col width="11" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
     <col width="46" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
@@ -32001,11 +31106,6 @@
           <t>Weighted F1</t>
         </is>
       </c>
-      <c r="G4" s="5" t="inlineStr">
-        <is>
-          <t>备注</t>
-        </is>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -32021,24 +31121,19 @@
       <c r="C5" t="n">
         <v>0</v>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D5" s="17" t="inlineStr">
         <is>
           <t>0.4987±0.0000</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E5" s="17" t="inlineStr">
         <is>
           <t>0.2458±0.0000</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F5" s="17" t="inlineStr">
         <is>
           <t>0.4892±0.0000</t>
-        </is>
-      </c>
-      <c r="G5" s="6" t="inlineStr">
-        <is>
-          <t>bandpower+Hjorth+谱熵；四道门第 1 门</t>
         </is>
       </c>
     </row>
@@ -32056,17 +31151,17 @@
       <c r="C6" t="n">
         <v>1.14</v>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D6" s="17" t="inlineStr">
         <is>
           <t>0.4414±0.0378</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E6" s="17" t="inlineStr">
         <is>
           <t>0.1613±0.0572</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="F6" s="17" t="inlineStr">
         <is>
           <t>0.4444±0.0385</t>
         </is>
@@ -32081,17 +31176,17 @@
       <c r="C7" t="n">
         <v>1.57</v>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D7" s="17" t="inlineStr">
         <is>
           <t>0.5322±0.0319</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E7" s="17" t="inlineStr">
         <is>
           <t>0.2990±0.0488</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F7" s="17" t="inlineStr">
         <is>
           <t>0.5166±0.0179</t>
         </is>
@@ -32106,17 +31201,17 @@
       <c r="C8" t="n">
         <v>3.16</v>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D8" s="17" t="inlineStr">
         <is>
           <t>0.5119±0.0188</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E8" s="17" t="inlineStr">
         <is>
           <t>0.2671±0.0292</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F8" s="17" t="inlineStr">
         <is>
           <t>0.5103±0.0193</t>
         </is>
@@ -32131,17 +31226,17 @@
       <c r="C9" t="n">
         <v>2.47</v>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D9" s="17" t="inlineStr">
         <is>
           <t>0.5569±0.0045</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E9" s="17" t="inlineStr">
         <is>
           <t>0.3335±0.0055</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F9" s="17" t="inlineStr">
         <is>
           <t>0.5483±0.0104</t>
         </is>
@@ -32156,17 +31251,17 @@
       <c r="C10" t="n">
         <v>3.43</v>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D10" s="17" t="inlineStr">
         <is>
           <t>0.5046±0.0250</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E10" s="17" t="inlineStr">
         <is>
           <t>0.2568±0.0365</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="F10" s="17" t="inlineStr">
         <is>
           <t>0.5056±0.0221</t>
         </is>
@@ -32178,11 +31273,6 @@
           <t>EEGNet (调参)</t>
         </is>
       </c>
-      <c r="G11" s="6" t="inlineStr">
-        <is>
-          <t>公开搜索预算调参</t>
-        </is>
-      </c>
     </row>
     <row r="12">
       <c r="B12" t="inlineStr">
@@ -32190,11 +31280,6 @@
           <t>EEGConformer (调参)</t>
         </is>
       </c>
-      <c r="G12" s="6" t="inlineStr">
-        <is>
-          <t>benchmark 文献最强单体</t>
-        </is>
-      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -32210,17 +31295,17 @@
       <c r="C13" t="n">
         <v>3.19</v>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="D13" s="17" t="inlineStr">
         <is>
           <t>0.5267±0.0169</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="E13" s="17" t="inlineStr">
         <is>
           <t>0.2887±0.0251</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="F13" s="17" t="inlineStr">
         <is>
           <t>0.5285±0.0166</t>
         </is>
@@ -32242,17 +31327,17 @@
       <c r="C15" t="n">
         <v>35.45</v>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="D15" s="17" t="inlineStr">
         <is>
           <t>0.5145±0.0252</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="E15" s="17" t="inlineStr">
         <is>
           <t>0.2716±0.0384</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="F15" s="17" t="inlineStr">
         <is>
           <t>0.5204±0.0249</t>
         </is>
@@ -32267,17 +31352,17 @@
       <c r="C16" t="n">
         <v>25.69</v>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="D16" s="17" t="inlineStr">
         <is>
           <t>0.5471±0.0174</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="E16" s="17" t="inlineStr">
         <is>
           <t>0.3187±0.0273</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="F16" s="17" t="inlineStr">
         <is>
           <t>0.5513±0.0197</t>
         </is>
@@ -32292,24 +31377,19 @@
       <c r="C17" t="n">
         <v>1.89</v>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="D17" s="17" t="inlineStr">
         <is>
           <t>0.5276±0.0268</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="E17" s="17" t="inlineStr">
         <is>
           <t>0.2906±0.0411</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="F17" s="17" t="inlineStr">
         <is>
           <t>0.5322±0.0264</t>
-        </is>
-      </c>
-      <c r="G17" s="6" t="inlineStr">
-        <is>
-          <t>tokenizer 直接对手</t>
         </is>
       </c>
     </row>
@@ -32322,24 +31402,19 @@
       <c r="C18" t="n">
         <v>69.62</v>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="D18" s="17" t="inlineStr">
         <is>
           <t>0.4298±0.0213</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="E18" s="17" t="inlineStr">
         <is>
           <t>0.1441±0.0324</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
+      <c r="F18" s="17" t="inlineStr">
         <is>
           <t>0.4315±0.0213</t>
-        </is>
-      </c>
-      <c r="G18" s="6" t="inlineStr">
-        <is>
-          <t>新增；HF 权重</t>
         </is>
       </c>
     </row>
@@ -32352,24 +31427,19 @@
       <c r="C19" t="n">
         <v>47.06</v>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="D19" s="17" t="inlineStr">
         <is>
           <t>0.4957±0.0240</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="E19" s="17" t="inlineStr">
         <is>
           <t>0.2433±0.0362</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
+      <c r="F19" s="17" t="inlineStr">
         <is>
           <t>0.4994±0.0235</t>
-        </is>
-      </c>
-      <c r="G19" s="6" t="inlineStr">
-        <is>
-          <t>新增；GDrive 权重</t>
         </is>
       </c>
     </row>
@@ -32387,17 +31457,17 @@
       <c r="C20" t="n">
         <v>3.19</v>
       </c>
-      <c r="D20" t="inlineStr">
+      <c r="D20" s="21" t="inlineStr">
         <is>
           <t>0.5609±0.0094</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="E20" s="21" t="inlineStr">
         <is>
           <t>0.3413±0.0134</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
+      <c r="F20" s="21" t="inlineStr">
         <is>
           <t>0.5567±0.0088</t>
         </is>
@@ -32412,17 +31482,17 @@
       <c r="C21" t="n">
         <v>5.82</v>
       </c>
-      <c r="D21" t="inlineStr">
+      <c r="D21" s="17" t="inlineStr">
         <is>
           <t>0.5068±0.0083</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="E21" s="17" t="inlineStr">
         <is>
           <t>0.2583±0.0130</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
+      <c r="F21" s="17" t="inlineStr">
         <is>
           <t>0.5086±0.0112</t>
         </is>
@@ -32444,24 +31514,19 @@
       <c r="C23" t="n">
         <v>25.69</v>
       </c>
-      <c r="D23" t="inlineStr">
+      <c r="D23" s="17" t="inlineStr">
         <is>
           <t>0.4269±0.0595</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="E23" s="17" t="inlineStr">
         <is>
           <t>0.1364±0.0878</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
+      <c r="F23" s="17" t="inlineStr">
         <is>
           <t>0.3499±0.1027</t>
-        </is>
-      </c>
-      <c r="G23" s="6" t="inlineStr">
-        <is>
-          <t>不新排；仅新语料已有数字</t>
         </is>
       </c>
     </row>
@@ -32474,24 +31539,19 @@
       <c r="C24" t="n">
         <v>1.89</v>
       </c>
-      <c r="D24" t="inlineStr">
+      <c r="D24" s="17" t="inlineStr">
         <is>
           <t>0.5020±0.0180</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
+      <c r="E24" s="17" t="inlineStr">
         <is>
           <t>0.2523±0.0276</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
+      <c r="F24" s="17" t="inlineStr">
         <is>
           <t>0.5024±0.0213</t>
-        </is>
-      </c>
-      <c r="G24" s="6" t="inlineStr">
-        <is>
-          <t>不新排；仅新语料已有数字</t>
         </is>
       </c>
     </row>
@@ -32509,17 +31569,17 @@
       <c r="C25" t="n">
         <v>1.62</v>
       </c>
-      <c r="D25" t="inlineStr">
+      <c r="D25" s="18" t="inlineStr">
         <is>
           <t>0.5254±0.0122</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
+      <c r="E25" s="18" t="inlineStr">
         <is>
           <t>0.2876±0.0192</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
+      <c r="F25" s="18" t="inlineStr">
         <is>
           <t>0.5294±0.0129</t>
         </is>
@@ -32531,11 +31591,6 @@
           <t>PACLock (duplex, 预训练 v2)</t>
         </is>
       </c>
-      <c r="G26" s="6" t="inlineStr">
-        <is>
-          <t>band_norm_pac 目标</t>
-        </is>
-      </c>
     </row>
     <row r="27">
       <c r="B27" t="inlineStr">
@@ -32543,11 +31598,6 @@
           <t>PACLock (冻结探针, v2)</t>
         </is>
       </c>
-      <c r="G27" s="6" t="inlineStr">
-        <is>
-          <t>patch_len 200；表征质量协议</t>
-        </is>
-      </c>
     </row>
     <row r="28">
       <c r="B28" t="inlineStr">
@@ -32555,12 +31605,8 @@
           <t>PACLock (冻结探针, 随机初始化)</t>
         </is>
       </c>
-      <c r="G28" s="6" t="inlineStr">
-        <is>
-          <t>四道门第 4 门对照</t>
-        </is>
-      </c>
-    </row>
+    </row>
+    <row r="29"/>
     <row r="30">
       <c r="A30" s="6" t="inlineStr">
         <is>
@@ -32573,6 +31619,7 @@
         </is>
       </c>
     </row>
+    <row r="31"/>
     <row r="32">
       <c r="A32" s="6" t="inlineStr">
         <is>

--- a/results/PACLock_baseline_matrix_filled.xlsx
+++ b/results/PACLock_baseline_matrix_filled.xlsx
@@ -4708,6 +4708,24 @@
           <t>手工特征 (LR/LDA 取优)</t>
         </is>
       </c>
+      <c r="C5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" s="17" t="inlineStr">
+        <is>
+          <t>0.9163±0.0000</t>
+        </is>
+      </c>
+      <c r="E5" s="17" t="inlineStr">
+        <is>
+          <t>0.8005±0.0000</t>
+        </is>
+      </c>
+      <c r="F5" s="17" t="inlineStr">
+        <is>
+          <t>0.9326±0.0000</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -4723,19 +4741,19 @@
       <c r="C6" t="n">
         <v>0.99</v>
       </c>
-      <c r="D6" s="22" t="inlineStr">
-        <is>
-          <t>0.9757 (1 seed)</t>
-        </is>
-      </c>
-      <c r="E6" s="22" t="inlineStr">
-        <is>
-          <t>0.6242 (1 seed)</t>
-        </is>
-      </c>
-      <c r="F6" s="22" t="inlineStr">
-        <is>
-          <t>0.9772 (1 seed)</t>
+      <c r="D6" s="17" t="inlineStr">
+        <is>
+          <t>0.9900±0.0103</t>
+        </is>
+      </c>
+      <c r="E6" s="17" t="inlineStr">
+        <is>
+          <t>0.7792±0.1098</t>
+        </is>
+      </c>
+      <c r="F6" s="17" t="inlineStr">
+        <is>
+          <t>0.9910±0.0099</t>
         </is>
       </c>
     </row>
@@ -4748,19 +4766,19 @@
       <c r="C7" t="n">
         <v>1.57</v>
       </c>
-      <c r="D7" s="22" t="inlineStr">
-        <is>
-          <t>0.9659 (1 seed)</t>
-        </is>
-      </c>
-      <c r="E7" s="22" t="inlineStr">
-        <is>
-          <t>0.7985 (1 seed)</t>
-        </is>
-      </c>
-      <c r="F7" s="22" t="inlineStr">
-        <is>
-          <t>0.9735 (1 seed)</t>
+      <c r="D7" s="17" t="inlineStr">
+        <is>
+          <t>0.9501±0.0209</t>
+        </is>
+      </c>
+      <c r="E7" s="17" t="inlineStr">
+        <is>
+          <t>0.7720±0.0339</t>
+        </is>
+      </c>
+      <c r="F7" s="17" t="inlineStr">
+        <is>
+          <t>0.9592±0.0179</t>
         </is>
       </c>
     </row>
@@ -4773,19 +4791,19 @@
       <c r="C8" t="n">
         <v>3.16</v>
       </c>
-      <c r="D8" s="22" t="inlineStr">
-        <is>
-          <t>0.8850 (1 seed)</t>
-        </is>
-      </c>
-      <c r="E8" s="22" t="inlineStr">
-        <is>
-          <t>0.8236 (1 seed)</t>
-        </is>
-      </c>
-      <c r="F8" s="22" t="inlineStr">
-        <is>
-          <t>0.8775 (1 seed)</t>
+      <c r="D8" s="17" t="inlineStr">
+        <is>
+          <t>0.8694±0.0470</t>
+        </is>
+      </c>
+      <c r="E8" s="17" t="inlineStr">
+        <is>
+          <t>0.7746±0.0516</t>
+        </is>
+      </c>
+      <c r="F8" s="17" t="inlineStr">
+        <is>
+          <t>0.8494±0.0853</t>
         </is>
       </c>
     </row>
@@ -4798,19 +4816,19 @@
       <c r="C9" t="n">
         <v>2.42</v>
       </c>
-      <c r="D9" s="22" t="inlineStr">
-        <is>
-          <t>0.9581 (1 seed)</t>
-        </is>
-      </c>
-      <c r="E9" s="22" t="inlineStr">
-        <is>
-          <t>0.7620 (1 seed)</t>
-        </is>
-      </c>
-      <c r="F9" s="22" t="inlineStr">
-        <is>
-          <t>0.9669 (1 seed)</t>
+      <c r="D9" s="17" t="inlineStr">
+        <is>
+          <t>0.9620±0.0049</t>
+        </is>
+      </c>
+      <c r="E9" s="17" t="inlineStr">
+        <is>
+          <t>0.7906±0.0202</t>
+        </is>
+      </c>
+      <c r="F9" s="17" t="inlineStr">
+        <is>
+          <t>0.9693±0.0034</t>
         </is>
       </c>
     </row>
@@ -4823,19 +4841,19 @@
       <c r="C10" t="n">
         <v>3.43</v>
       </c>
-      <c r="D10" s="22" t="inlineStr">
-        <is>
-          <t>0.9933 (1 seed)</t>
-        </is>
-      </c>
-      <c r="E10" s="23" t="inlineStr">
-        <is>
-          <t>0.9577 (1 seed)</t>
-        </is>
-      </c>
-      <c r="F10" s="22" t="inlineStr">
-        <is>
-          <t>0.9941 (1 seed)</t>
+      <c r="D10" s="21" t="inlineStr">
+        <is>
+          <t>0.9910±0.0066</t>
+        </is>
+      </c>
+      <c r="E10" s="17" t="inlineStr">
+        <is>
+          <t>0.8296±0.1052</t>
+        </is>
+      </c>
+      <c r="F10" s="21" t="inlineStr">
+        <is>
+          <t>0.9930±0.0049</t>
         </is>
       </c>
     </row>
@@ -4867,19 +4885,19 @@
       <c r="C13" t="n">
         <v>3.19</v>
       </c>
-      <c r="D13" s="23" t="inlineStr">
-        <is>
-          <t>0.9999 (1 seed)</t>
-        </is>
-      </c>
-      <c r="E13" s="22" t="inlineStr">
-        <is>
-          <t>0.8900 (1 seed)</t>
-        </is>
-      </c>
-      <c r="F13" s="23" t="inlineStr">
-        <is>
-          <t>0.9999 (1 seed)</t>
+      <c r="D13" s="17" t="inlineStr">
+        <is>
+          <t>0.9895±0.0075</t>
+        </is>
+      </c>
+      <c r="E13" s="17" t="inlineStr">
+        <is>
+          <t>0.8417±0.0370</t>
+        </is>
+      </c>
+      <c r="F13" s="17" t="inlineStr">
+        <is>
+          <t>0.9896±0.0073</t>
         </is>
       </c>
     </row>
@@ -4892,19 +4910,19 @@
       <c r="C14" t="n">
         <v>5.82</v>
       </c>
-      <c r="D14" s="22" t="inlineStr">
-        <is>
-          <t>0.9858 (1 seed)</t>
-        </is>
-      </c>
-      <c r="E14" s="22" t="inlineStr">
-        <is>
-          <t>0.8010 (1 seed)</t>
-        </is>
-      </c>
-      <c r="F14" s="22" t="inlineStr">
-        <is>
-          <t>0.9891 (1 seed)</t>
+      <c r="D14" s="17" t="inlineStr">
+        <is>
+          <t>0.9635±0.0190</t>
+        </is>
+      </c>
+      <c r="E14" s="17" t="inlineStr">
+        <is>
+          <t>0.8003±0.0005</t>
+        </is>
+      </c>
+      <c r="F14" s="17" t="inlineStr">
+        <is>
+          <t>0.9605±0.0245</t>
         </is>
       </c>
     </row>
@@ -4917,19 +4935,19 @@
       <c r="C15" t="n">
         <v>20.25</v>
       </c>
-      <c r="D15" s="22" t="inlineStr">
-        <is>
-          <t>0.9690 (1 seed)</t>
-        </is>
-      </c>
-      <c r="E15" s="22" t="inlineStr">
-        <is>
-          <t>0.8333 (1 seed)</t>
-        </is>
-      </c>
-      <c r="F15" s="22" t="inlineStr">
-        <is>
-          <t>0.9741 (1 seed)</t>
+      <c r="D15" s="17" t="inlineStr">
+        <is>
+          <t>0.9610±0.0200</t>
+        </is>
+      </c>
+      <c r="E15" s="17" t="inlineStr">
+        <is>
+          <t>0.8111±0.0157</t>
+        </is>
+      </c>
+      <c r="F15" s="17" t="inlineStr">
+        <is>
+          <t>0.9645±0.0202</t>
         </is>
       </c>
     </row>
@@ -4942,19 +4960,19 @@
       <c r="C16" t="n">
         <v>25.69</v>
       </c>
-      <c r="D16" s="22" t="inlineStr">
-        <is>
-          <t>0.9379 (1 seed)</t>
-        </is>
-      </c>
-      <c r="E16" s="22" t="inlineStr">
-        <is>
-          <t>0.8576 (1 seed)</t>
-        </is>
-      </c>
-      <c r="F16" s="22" t="inlineStr">
-        <is>
-          <t>0.9390 (1 seed)</t>
+      <c r="D16" s="17" t="inlineStr">
+        <is>
+          <t>0.9605±0.0212</t>
+        </is>
+      </c>
+      <c r="E16" s="21" t="inlineStr">
+        <is>
+          <t>0.8848±0.0431</t>
+        </is>
+      </c>
+      <c r="F16" s="17" t="inlineStr">
+        <is>
+          <t>0.9621±0.0212</t>
         </is>
       </c>
     </row>
@@ -4967,19 +4985,19 @@
       <c r="C17" t="n">
         <v>1.89</v>
       </c>
-      <c r="D17" s="22" t="inlineStr">
-        <is>
-          <t>0.9491 (1 seed)</t>
-        </is>
-      </c>
-      <c r="E17" s="22" t="inlineStr">
-        <is>
-          <t>0.8631 (1 seed)</t>
-        </is>
-      </c>
-      <c r="F17" s="22" t="inlineStr">
-        <is>
-          <t>0.9543 (1 seed)</t>
+      <c r="D17" s="17" t="inlineStr">
+        <is>
+          <t>0.8998±0.0351</t>
+        </is>
+      </c>
+      <c r="E17" s="17" t="inlineStr">
+        <is>
+          <t>0.8332±0.0278</t>
+        </is>
+      </c>
+      <c r="F17" s="17" t="inlineStr">
+        <is>
+          <t>0.8741±0.0569</t>
         </is>
       </c>
     </row>
@@ -5011,19 +5029,19 @@
       <c r="C20" t="n">
         <v>3.19</v>
       </c>
-      <c r="D20" s="22" t="inlineStr">
-        <is>
-          <t>0.9422 (1 seed)</t>
-        </is>
-      </c>
-      <c r="E20" s="22" t="inlineStr">
-        <is>
-          <t>0.7979 (1 seed)</t>
-        </is>
-      </c>
-      <c r="F20" s="22" t="inlineStr">
-        <is>
-          <t>0.9573 (1 seed)</t>
+      <c r="D20" s="17" t="inlineStr">
+        <is>
+          <t>0.9454±0.0143</t>
+        </is>
+      </c>
+      <c r="E20" s="17" t="inlineStr">
+        <is>
+          <t>0.7983±0.0007</t>
+        </is>
+      </c>
+      <c r="F20" s="17" t="inlineStr">
+        <is>
+          <t>0.9593±0.0103</t>
         </is>
       </c>
     </row>
@@ -5036,19 +5054,19 @@
       <c r="C21" t="n">
         <v>5.82</v>
       </c>
-      <c r="D21" s="22" t="inlineStr">
-        <is>
-          <t>0.9848 (1 seed)</t>
-        </is>
-      </c>
-      <c r="E21" s="22" t="inlineStr">
-        <is>
-          <t>0.8033 (1 seed)</t>
-        </is>
-      </c>
-      <c r="F21" s="22" t="inlineStr">
-        <is>
-          <t>0.9876 (1 seed)</t>
+      <c r="D21" s="17" t="inlineStr">
+        <is>
+          <t>0.8969±0.0660</t>
+        </is>
+      </c>
+      <c r="E21" s="17" t="inlineStr">
+        <is>
+          <t>0.8014±0.0017</t>
+        </is>
+      </c>
+      <c r="F21" s="17" t="inlineStr">
+        <is>
+          <t>0.8898±0.0727</t>
         </is>
       </c>
     </row>
@@ -5061,19 +5079,19 @@
       <c r="C22" t="n">
         <v>20.25</v>
       </c>
-      <c r="D22" s="22" t="inlineStr">
-        <is>
-          <t>0.9240 (1 seed)</t>
-        </is>
-      </c>
-      <c r="E22" s="22" t="inlineStr">
-        <is>
-          <t>0.8013 (1 seed)</t>
-        </is>
-      </c>
-      <c r="F22" s="22" t="inlineStr">
-        <is>
-          <t>0.9040 (1 seed)</t>
+      <c r="D22" s="17" t="inlineStr">
+        <is>
+          <t>0.9206±0.0373</t>
+        </is>
+      </c>
+      <c r="E22" s="17" t="inlineStr">
+        <is>
+          <t>0.8394±0.0470</t>
+        </is>
+      </c>
+      <c r="F22" s="17" t="inlineStr">
+        <is>
+          <t>0.9177±0.0365</t>
         </is>
       </c>
     </row>
@@ -5086,19 +5104,19 @@
       <c r="C23" t="n">
         <v>25.69</v>
       </c>
-      <c r="D23" s="22" t="inlineStr">
-        <is>
-          <t>0.8932 (1 seed)</t>
-        </is>
-      </c>
-      <c r="E23" s="22" t="inlineStr">
-        <is>
-          <t>0.8045 (1 seed)</t>
-        </is>
-      </c>
-      <c r="F23" s="22" t="inlineStr">
-        <is>
-          <t>0.8809 (1 seed)</t>
+      <c r="D23" s="17" t="inlineStr">
+        <is>
+          <t>0.8072±0.0935</t>
+        </is>
+      </c>
+      <c r="E23" s="17" t="inlineStr">
+        <is>
+          <t>0.6954±0.1385</t>
+        </is>
+      </c>
+      <c r="F23" s="17" t="inlineStr">
+        <is>
+          <t>0.7841±0.1009</t>
         </is>
       </c>
     </row>
@@ -5111,19 +5129,19 @@
       <c r="C24" t="n">
         <v>1.89</v>
       </c>
-      <c r="D24" s="22" t="inlineStr">
-        <is>
-          <t>0.8317 (1 seed)</t>
-        </is>
-      </c>
-      <c r="E24" s="22" t="inlineStr">
-        <is>
-          <t>0.7481 (1 seed)</t>
-        </is>
-      </c>
-      <c r="F24" s="22" t="inlineStr">
-        <is>
-          <t>0.8046 (1 seed)</t>
+      <c r="D24" s="17" t="inlineStr">
+        <is>
+          <t>0.7440±0.0687</t>
+        </is>
+      </c>
+      <c r="E24" s="17" t="inlineStr">
+        <is>
+          <t>0.5827±0.1170</t>
+        </is>
+      </c>
+      <c r="F24" s="17" t="inlineStr">
+        <is>
+          <t>0.7247±0.0659</t>
         </is>
       </c>
     </row>
@@ -5776,7 +5794,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F690"/>
+  <dimension ref="A1:F691"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15166,17 +15184,22 @@
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>[0]</t>
+          <t>[0, 1, 2]</t>
         </is>
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>filled (single-seed, grey)</t>
+          <t>filled</t>
         </is>
       </c>
       <c r="E328" t="inlineStr">
         <is>
-          <t>auroc 0.9999</t>
+          <t>[实测 3.19M] auroc per-seed 0:0.9999, 1:0.9864, 2:0.9823</t>
+        </is>
+      </c>
+      <c r="F328" t="inlineStr">
+        <is>
+          <t>stopped_by=patience lr=0.001 batch_size=512 epochs=100 patience=5 eval_every_steps=0 loss=bce_with_logits</t>
         </is>
       </c>
     </row>
@@ -15193,17 +15216,22 @@
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>[0]</t>
+          <t>[0, 1, 2]</t>
         </is>
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>filled (single-seed, grey)</t>
+          <t>filled</t>
         </is>
       </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t>auroc 0.9422</t>
+          <t>[实测 3.19M] auroc per-seed 0:0.9422, 1:0.9643, 2:0.9296</t>
+        </is>
+      </c>
+      <c r="F329" t="inlineStr">
+        <is>
+          <t>stopped_by=patience lr=0.001 batch_size=512 epochs=100 patience=5 eval_every_steps=0 loss=bce_with_logits</t>
         </is>
       </c>
     </row>
@@ -15220,17 +15248,22 @@
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>[0]</t>
+          <t>[0, 1, 2]</t>
         </is>
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>filled (single-seed, grey)</t>
+          <t>filled</t>
         </is>
       </c>
       <c r="E330" t="inlineStr">
         <is>
-          <t>auroc 0.9690</t>
+          <t>[实测 20.25M] auroc per-seed 0:0.9690, 1:0.9804, 2:0.9335</t>
+        </is>
+      </c>
+      <c r="F330" t="inlineStr">
+        <is>
+          <t>lr=0.0001 batch_size=64 epochs=50 patience=0 eval_every_steps=0 loss=bce_with_logits grad_clip=1.0 select_metric=auroc multi_lr=True</t>
         </is>
       </c>
     </row>
@@ -15247,17 +15280,22 @@
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>[0]</t>
+          <t>[0, 1, 2]</t>
         </is>
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>filled (single-seed, grey)</t>
+          <t>filled</t>
         </is>
       </c>
       <c r="E331" t="inlineStr">
         <is>
-          <t>auroc 0.9240</t>
+          <t>[实测 20.25M] auroc per-seed 0:0.9240, 1:0.8733, 2:0.9645</t>
+        </is>
+      </c>
+      <c r="F331" t="inlineStr">
+        <is>
+          <t>lr=0.0001 batch_size=64 epochs=50 patience=0 eval_every_steps=0 loss=bce_with_logits grad_clip=1.0 select_metric=auroc multi_lr=True</t>
         </is>
       </c>
     </row>
@@ -15274,17 +15312,22 @@
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>[0]</t>
+          <t>[0, 1, 2]</t>
         </is>
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>filled (single-seed, grey)</t>
+          <t>filled</t>
         </is>
       </c>
       <c r="E332" t="inlineStr">
         <is>
-          <t>auroc 0.8850</t>
+          <t>[实测 3.16M] auroc per-seed 0:0.8850, 1:0.8056, 2:0.9175</t>
+        </is>
+      </c>
+      <c r="F332" t="inlineStr">
+        <is>
+          <t>stopped_by=patience lr=0.001 batch_size=512 epochs=20 patience=8 eval_every_steps=200 loss=bce_with_logits</t>
         </is>
       </c>
     </row>
@@ -15301,17 +15344,22 @@
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>[0]</t>
+          <t>[0, 1, 2]</t>
         </is>
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>filled (single-seed, grey)</t>
+          <t>filled</t>
         </is>
       </c>
       <c r="E333" t="inlineStr">
         <is>
-          <t>auroc 0.9659</t>
+          <t>[实测 1.57M] auroc per-seed 0:0.9659, 1:0.9206, 2:0.9639</t>
+        </is>
+      </c>
+      <c r="F333" t="inlineStr">
+        <is>
+          <t>stopped_by=patience lr=0.001 batch_size=512 epochs=20 patience=8 eval_every_steps=200 loss=bce_with_logits</t>
         </is>
       </c>
     </row>
@@ -15328,17 +15376,22 @@
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>[0]</t>
+          <t>[0, 1, 2]</t>
         </is>
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>filled (single-seed, grey)</t>
+          <t>filled</t>
         </is>
       </c>
       <c r="E334" t="inlineStr">
         <is>
-          <t>auroc 0.9379</t>
+          <t>[实测 25.69M] auroc per-seed 0:0.9379, 1:0.9889, 2:0.9548</t>
+        </is>
+      </c>
+      <c r="F334" t="inlineStr">
+        <is>
+          <t>stopped_by=patience lr=0.0004 batch_size=32 epochs=40 patience=10 eval_every_steps=500 loss=bce_with_logits</t>
         </is>
       </c>
     </row>
@@ -15355,17 +15408,22 @@
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>[0]</t>
+          <t>[0, 1, 2]</t>
         </is>
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>filled (single-seed, grey)</t>
+          <t>filled</t>
         </is>
       </c>
       <c r="E335" t="inlineStr">
         <is>
-          <t>auroc 0.8932</t>
+          <t>[实测 25.69M] auroc per-seed 0:0.8932, 1:0.6772, 2:0.8513</t>
+        </is>
+      </c>
+      <c r="F335" t="inlineStr">
+        <is>
+          <t>lr=0.0004 batch_size=32 epochs=40 patience=10 eval_every_steps=500 loss=bce_with_logits</t>
         </is>
       </c>
     </row>
@@ -15377,22 +15435,27 @@
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>ffcl</t>
+          <t>feat_best</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>[0]</t>
+          <t>[0, 1, 2]</t>
         </is>
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>filled (single-seed, grey)</t>
+          <t>filled</t>
         </is>
       </c>
       <c r="E336" t="inlineStr">
         <is>
-          <t>auroc 0.9581</t>
+          <t>[实测 0.00M] auroc per-seed 0:0.9163, 1:0.9163, 2:0.9163</t>
+        </is>
+      </c>
+      <c r="F336" t="inlineStr">
+        <is>
+          <t>stopped_by=closed-form epochs=1 loss=closed-form</t>
         </is>
       </c>
     </row>
@@ -15404,22 +15467,27 @@
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>labram_pretrained</t>
+          <t>ffcl</t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>[0]</t>
+          <t>[0, 1, 2]</t>
         </is>
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t>filled (single-seed, grey)</t>
+          <t>filled</t>
         </is>
       </c>
       <c r="E337" t="inlineStr">
         <is>
-          <t>auroc 0.9858</t>
+          <t>[实测 2.42M] auroc per-seed 0:0.9581, 1:0.9589, 2:0.9689</t>
+        </is>
+      </c>
+      <c r="F337" t="inlineStr">
+        <is>
+          <t>lr=0.001 batch_size=512 epochs=20 patience=8 eval_every_steps=200 loss=bce_with_logits</t>
         </is>
       </c>
     </row>
@@ -15431,22 +15499,27 @@
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>labram_scratch</t>
+          <t>labram_pretrained</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>[0]</t>
+          <t>[0, 1, 2]</t>
         </is>
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t>filled (single-seed, grey)</t>
+          <t>filled</t>
         </is>
       </c>
       <c r="E338" t="inlineStr">
         <is>
-          <t>auroc 0.9848</t>
+          <t>[实测 5.82M] auroc per-seed 0:0.9858, 1:0.9394, 2:0.9654</t>
+        </is>
+      </c>
+      <c r="F338" t="inlineStr">
+        <is>
+          <t>stopped_by=patience lr=0.0005 batch_size=64 epochs=50 patience=10 eval_every_steps=0 loss=bce_with_logits loader_divisor=1.0</t>
         </is>
       </c>
     </row>
@@ -15458,22 +15531,27 @@
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>paclock_duplex</t>
+          <t>labram_scratch</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>[0]</t>
+          <t>[0, 1, 2]</t>
         </is>
       </c>
       <c r="D339" t="inlineStr">
         <is>
-          <t>filled (single-seed, grey)</t>
+          <t>filled</t>
         </is>
       </c>
       <c r="E339" t="inlineStr">
         <is>
-          <t>auroc 0.9775</t>
+          <t>[实测 5.82M] auroc per-seed 0:0.9848, 1:0.8806, 2:0.8255</t>
+        </is>
+      </c>
+      <c r="F339" t="inlineStr">
+        <is>
+          <t>stopped_by=patience lr=0.0005 batch_size=64 epochs=50 patience=10 eval_every_steps=0 loss=bce_with_logits loader_divisor=1.0</t>
         </is>
       </c>
     </row>
@@ -15485,7 +15563,7 @@
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>sparcnet</t>
+          <t>paclock_duplex</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
@@ -15500,7 +15578,7 @@
       </c>
       <c r="E340" t="inlineStr">
         <is>
-          <t>auroc 0.9757</t>
+          <t>auroc 0.9775</t>
         </is>
       </c>
     </row>
@@ -15512,22 +15590,27 @@
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>st_transformer</t>
+          <t>sparcnet</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>[0]</t>
+          <t>[0, 1, 2]</t>
         </is>
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t>filled (single-seed, grey)</t>
+          <t>filled</t>
         </is>
       </c>
       <c r="E341" t="inlineStr">
         <is>
-          <t>auroc 0.9933</t>
+          <t>[实测 0.99M] auroc per-seed 0:0.9757, 1:0.9948, 2:0.9994</t>
+        </is>
+      </c>
+      <c r="F341" t="inlineStr">
+        <is>
+          <t>stopped_by=patience lr=0.001 batch_size=512 epochs=20 patience=8 eval_every_steps=200 loss=bce_with_logits</t>
         </is>
       </c>
     </row>
@@ -15539,22 +15622,27 @@
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>tfm_pretrained</t>
+          <t>st_transformer</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>[0]</t>
+          <t>[0, 1, 2]</t>
         </is>
       </c>
       <c r="D342" t="inlineStr">
         <is>
-          <t>filled (single-seed, grey)</t>
+          <t>filled</t>
         </is>
       </c>
       <c r="E342" t="inlineStr">
         <is>
-          <t>auroc 0.9491</t>
+          <t>[实测 3.43M] auroc per-seed 0:0.9933, 1:0.9977, 2:0.9821</t>
+        </is>
+      </c>
+      <c r="F342" t="inlineStr">
+        <is>
+          <t>lr=0.001 batch_size=512 epochs=20 patience=8 eval_every_steps=200 loss=bce_with_logits</t>
         </is>
       </c>
     </row>
@@ -15566,34 +15654,39 @@
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>tfm_scratch</t>
+          <t>tfm_pretrained</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>[0]</t>
+          <t>[0, 1, 2]</t>
         </is>
       </c>
       <c r="D343" t="inlineStr">
         <is>
-          <t>filled (single-seed, grey)</t>
+          <t>filled</t>
         </is>
       </c>
       <c r="E343" t="inlineStr">
         <is>
-          <t>auroc 0.8317</t>
+          <t>[实测 1.89M] auroc per-seed 0:0.9491, 1:0.8701, 2:0.8803</t>
+        </is>
+      </c>
+      <c r="F343" t="inlineStr">
+        <is>
+          <t>lr=0.001 batch_size=512 epochs=7 patience=10 eval_every_steps=100 loss=bce_with_logits</t>
         </is>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>physionet_mi</t>
+          <t>mumtaz</t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>biot_prest16</t>
+          <t>tfm_scratch</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
@@ -15608,12 +15701,12 @@
       </c>
       <c r="E344" t="inlineStr">
         <is>
-          <t>[实测 3.19M] balanced_acc per-seed 0:0.4950, 1:0.5034, 2:0.5126</t>
+          <t>[实测 1.89M] auroc per-seed 0:0.8317, 1:0.6641, 2:0.7362</t>
         </is>
       </c>
       <c r="F344" t="inlineStr">
         <is>
-          <t>lr=0.0004 batch_size=64 epochs=100 patience=10 eval_every_steps=0 loss=cross_entropy</t>
+          <t>lr=0.001 batch_size=512 epochs=7 patience=10 eval_every_steps=100 loss=bce_with_logits</t>
         </is>
       </c>
     </row>
@@ -15625,7 +15718,7 @@
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>biot_scratch</t>
+          <t>biot_prest16</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
@@ -15640,7 +15733,7 @@
       </c>
       <c r="E345" t="inlineStr">
         <is>
-          <t>[实测 3.20M] balanced_acc per-seed 0:0.3337, 1:0.3273, 2:0.2687</t>
+          <t>[实测 3.19M] balanced_acc per-seed 0:0.4950, 1:0.5034, 2:0.5126</t>
         </is>
       </c>
       <c r="F345" t="inlineStr">
@@ -15657,22 +15750,27 @@
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>cbramod_pac</t>
+          <t>biot_scratch</t>
         </is>
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>[0, 1, 2]</t>
         </is>
       </c>
       <c r="D346" t="inlineStr">
         <is>
-          <t>skipped</t>
+          <t>filled</t>
         </is>
       </c>
       <c r="E346" t="inlineStr">
         <is>
-          <t>the workbook has no row for this variant</t>
+          <t>[实测 3.20M] balanced_acc per-seed 0:0.3337, 1:0.3273, 2:0.2687</t>
+        </is>
+      </c>
+      <c r="F346" t="inlineStr">
+        <is>
+          <t>lr=0.0004 batch_size=64 epochs=100 patience=10 eval_every_steps=0 loss=cross_entropy</t>
         </is>
       </c>
     </row>
@@ -15684,27 +15782,22 @@
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>cbramod_pretrained</t>
+          <t>cbramod_pac</t>
         </is>
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>[0, 1, 2]</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D347" t="inlineStr">
         <is>
-          <t>filled</t>
+          <t>skipped</t>
         </is>
       </c>
       <c r="E347" t="inlineStr">
         <is>
-          <t>[实测 46.01M] balanced_acc per-seed 0:0.6035, 1:0.6257, 2:0.6096</t>
-        </is>
-      </c>
-      <c r="F347" t="inlineStr">
-        <is>
-          <t>lr=0.0001 batch_size=64 epochs=50 patience=0 eval_every_steps=0 loss=cross_entropy label_smoothing=0.1 grad_clip=1.0 multi_lr=True</t>
+          <t>the workbook has no row for this variant</t>
         </is>
       </c>
     </row>
@@ -15716,7 +15809,7 @@
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>cbramod_scratch</t>
+          <t>cbramod_pretrained</t>
         </is>
       </c>
       <c r="C348" t="inlineStr">
@@ -15731,7 +15824,7 @@
       </c>
       <c r="E348" t="inlineStr">
         <is>
-          <t>[实测 46.01M] balanced_acc per-seed 0:0.5491, 1:0.5562, 2:0.5558</t>
+          <t>[实测 46.01M] balanced_acc per-seed 0:0.6035, 1:0.6257, 2:0.6096</t>
         </is>
       </c>
       <c r="F348" t="inlineStr">
@@ -15748,7 +15841,7 @@
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>cnn_transformer</t>
+          <t>cbramod_scratch</t>
         </is>
       </c>
       <c r="C349" t="inlineStr">
@@ -15763,12 +15856,12 @@
       </c>
       <c r="E349" t="inlineStr">
         <is>
-          <t>[实测 3.18M] balanced_acc per-seed 0:0.4501, 1:0.4718, 2:0.4612</t>
+          <t>[实测 46.01M] balanced_acc per-seed 0:0.5491, 1:0.5562, 2:0.5558</t>
         </is>
       </c>
       <c r="F349" t="inlineStr">
         <is>
-          <t>stopped_by=patience lr=0.0001 batch_size=64 epochs=100 patience=20 eval_every_steps=0 loss=cross_entropy label_smoothing=0.1</t>
+          <t>lr=0.0001 batch_size=64 epochs=50 patience=0 eval_every_steps=0 loss=cross_entropy label_smoothing=0.1 grad_clip=1.0 multi_lr=True</t>
         </is>
       </c>
     </row>
@@ -15780,22 +15873,27 @@
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>cnn_transformer_lr1e4</t>
+          <t>cnn_transformer</t>
         </is>
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>[0, 1, 2]</t>
         </is>
       </c>
       <c r="D350" t="inlineStr">
         <is>
-          <t>skipped</t>
+          <t>filled</t>
         </is>
       </c>
       <c r="E350" t="inlineStr">
         <is>
-          <t>no row label for 'cnn_transformer_lr1e4'</t>
+          <t>[实测 3.18M] balanced_acc per-seed 0:0.4501, 1:0.4718, 2:0.4612</t>
+        </is>
+      </c>
+      <c r="F350" t="inlineStr">
+        <is>
+          <t>stopped_by=patience lr=0.0001 batch_size=64 epochs=100 patience=20 eval_every_steps=0 loss=cross_entropy label_smoothing=0.1</t>
         </is>
       </c>
     </row>
@@ -15807,7 +15905,7 @@
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>cnn_transformer_lr3e4</t>
+          <t>cnn_transformer_lr1e4</t>
         </is>
       </c>
       <c r="C351" t="inlineStr">
@@ -15822,7 +15920,7 @@
       </c>
       <c r="E351" t="inlineStr">
         <is>
-          <t>no row label for 'cnn_transformer_lr3e4'</t>
+          <t>no row label for 'cnn_transformer_lr1e4'</t>
         </is>
       </c>
     </row>
@@ -15834,27 +15932,22 @@
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>contrawr</t>
+          <t>cnn_transformer_lr3e4</t>
         </is>
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>[0, 1, 2]</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D352" t="inlineStr">
         <is>
-          <t>filled</t>
+          <t>skipped</t>
         </is>
       </c>
       <c r="E352" t="inlineStr">
         <is>
-          <t>[实测 1.60M] balanced_acc per-seed 0:0.4898, 1:0.4965, 2:0.4810</t>
-        </is>
-      </c>
-      <c r="F352" t="inlineStr">
-        <is>
-          <t>lr=0.001 batch_size=64 epochs=100 patience=20 eval_every_steps=0 loss=cross_entropy label_smoothing=0.1</t>
+          <t>no row label for 'cnn_transformer_lr3e4'</t>
         </is>
       </c>
     </row>
@@ -15866,22 +15959,27 @@
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>diag_lr3e5</t>
+          <t>contrawr</t>
         </is>
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>[0, 1, 2]</t>
         </is>
       </c>
       <c r="D353" t="inlineStr">
         <is>
-          <t>skipped</t>
+          <t>filled</t>
         </is>
       </c>
       <c r="E353" t="inlineStr">
         <is>
-          <t>no row label for 'diag_lr3e5'</t>
+          <t>[实测 1.60M] balanced_acc per-seed 0:0.4898, 1:0.4965, 2:0.4810</t>
+        </is>
+      </c>
+      <c r="F353" t="inlineStr">
+        <is>
+          <t>lr=0.001 batch_size=64 epochs=100 patience=20 eval_every_steps=0 loss=cross_entropy label_smoothing=0.1</t>
         </is>
       </c>
     </row>
@@ -15893,7 +15991,7 @@
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>diag_patch200</t>
+          <t>diag_lr3e5</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
@@ -15908,7 +16006,7 @@
       </c>
       <c r="E354" t="inlineStr">
         <is>
-          <t>no row label for 'diag_patch200'</t>
+          <t>no row label for 'diag_lr3e5'</t>
         </is>
       </c>
     </row>
@@ -15920,7 +16018,7 @@
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>diag_patch200_lr3e5</t>
+          <t>diag_patch200</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
@@ -15935,7 +16033,7 @@
       </c>
       <c r="E355" t="inlineStr">
         <is>
-          <t>no row label for 'diag_patch200_lr3e5'</t>
+          <t>no row label for 'diag_patch200'</t>
         </is>
       </c>
     </row>
@@ -15947,27 +16045,22 @@
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>eegpt_pretrained</t>
+          <t>diag_patch200_lr3e5</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>[0, 1, 2]</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D356" t="inlineStr">
         <is>
-          <t>filled</t>
+          <t>skipped</t>
         </is>
       </c>
       <c r="E356" t="inlineStr">
         <is>
-          <t>[实测 25.69M] balanced_acc per-seed 0:0.4233, 1:0.4411, 2:0.3494</t>
-        </is>
-      </c>
-      <c r="F356" t="inlineStr">
-        <is>
-          <t>lr=0.0004 batch_size=32 epochs=100 patience=10 eval_every_steps=0 loss=cross_entropy</t>
+          <t>no row label for 'diag_patch200_lr3e5'</t>
         </is>
       </c>
     </row>
@@ -15979,7 +16072,7 @@
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>ffcl</t>
+          <t>eegpt_pretrained</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
@@ -15994,12 +16087,12 @@
       </c>
       <c r="E357" t="inlineStr">
         <is>
-          <t>[实测 2.43M] balanced_acc per-seed 0:0.4760, 1:0.5004, 2:0.5041</t>
+          <t>[实测 25.69M] balanced_acc per-seed 0:0.4233, 1:0.4411, 2:0.3494</t>
         </is>
       </c>
       <c r="F357" t="inlineStr">
         <is>
-          <t>lr=0.001 batch_size=64 epochs=100 patience=20 eval_every_steps=0 loss=cross_entropy label_smoothing=0.1</t>
+          <t>lr=0.0004 batch_size=32 epochs=100 patience=10 eval_every_steps=0 loss=cross_entropy</t>
         </is>
       </c>
     </row>
@@ -16011,7 +16104,7 @@
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>labram_pretrained</t>
+          <t>ffcl</t>
         </is>
       </c>
       <c r="C358" t="inlineStr">
@@ -16026,12 +16119,12 @@
       </c>
       <c r="E358" t="inlineStr">
         <is>
-          <t>[实测 5.82M] balanced_acc per-seed 0:0.5352, 1:0.5647, 2:0.5720</t>
+          <t>[实测 2.43M] balanced_acc per-seed 0:0.4760, 1:0.5004, 2:0.5041</t>
         </is>
       </c>
       <c r="F358" t="inlineStr">
         <is>
-          <t>stopped_by=patience lr=0.0005 batch_size=64 epochs=50 patience=10 eval_every_steps=0 loss=cross_entropy label_smoothing=0.1 loader_divisor=1.0</t>
+          <t>lr=0.001 batch_size=64 epochs=100 patience=20 eval_every_steps=0 loss=cross_entropy label_smoothing=0.1</t>
         </is>
       </c>
     </row>
@@ -16043,7 +16136,7 @@
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>labram_scratch</t>
+          <t>labram_pretrained</t>
         </is>
       </c>
       <c r="C359" t="inlineStr">
@@ -16058,7 +16151,7 @@
       </c>
       <c r="E359" t="inlineStr">
         <is>
-          <t>[实测 5.82M] balanced_acc per-seed 0:0.3854, 1:0.3635, 2:0.3510</t>
+          <t>[实测 5.82M] balanced_acc per-seed 0:0.5352, 1:0.5647, 2:0.5720</t>
         </is>
       </c>
       <c r="F359" t="inlineStr">
@@ -16075,22 +16168,27 @@
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>paclock_c_nm</t>
+          <t>labram_scratch</t>
         </is>
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>[0, 1, 2]</t>
         </is>
       </c>
       <c r="D360" t="inlineStr">
         <is>
-          <t>skipped</t>
+          <t>filled</t>
         </is>
       </c>
       <c r="E360" t="inlineStr">
         <is>
-          <t>no row label for 'paclock_c_nm'</t>
+          <t>[实测 5.82M] balanced_acc per-seed 0:0.3854, 1:0.3635, 2:0.3510</t>
+        </is>
+      </c>
+      <c r="F360" t="inlineStr">
+        <is>
+          <t>stopped_by=patience lr=0.0005 batch_size=64 epochs=50 patience=10 eval_every_steps=0 loss=cross_entropy label_smoothing=0.1 loader_divisor=1.0</t>
         </is>
       </c>
     </row>
@@ -16102,7 +16200,7 @@
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>paclock_concat</t>
+          <t>paclock_c_nm</t>
         </is>
       </c>
       <c r="C361" t="inlineStr">
@@ -16117,7 +16215,7 @@
       </c>
       <c r="E361" t="inlineStr">
         <is>
-          <t>no row label for 'paclock_concat'</t>
+          <t>no row label for 'paclock_c_nm'</t>
         </is>
       </c>
     </row>
@@ -16129,7 +16227,7 @@
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>paclock_duplex_ms</t>
+          <t>paclock_concat</t>
         </is>
       </c>
       <c r="C362" t="inlineStr">
@@ -16144,7 +16242,7 @@
       </c>
       <c r="E362" t="inlineStr">
         <is>
-          <t>no row label for 'paclock_duplex_ms'</t>
+          <t>no row label for 'paclock_concat'</t>
         </is>
       </c>
     </row>
@@ -16156,7 +16254,7 @@
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>paclock_flagship</t>
+          <t>paclock_duplex_ms</t>
         </is>
       </c>
       <c r="C363" t="inlineStr">
@@ -16171,7 +16269,7 @@
       </c>
       <c r="E363" t="inlineStr">
         <is>
-          <t>no row label for 'paclock_flagship'</t>
+          <t>no row label for 'paclock_duplex_ms'</t>
         </is>
       </c>
     </row>
@@ -16183,7 +16281,7 @@
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>paclock_ft_base</t>
+          <t>paclock_flagship</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
@@ -16198,7 +16296,7 @@
       </c>
       <c r="E364" t="inlineStr">
         <is>
-          <t>no row label for 'paclock_ft_base'</t>
+          <t>no row label for 'paclock_flagship'</t>
         </is>
       </c>
     </row>
@@ -16210,7 +16308,7 @@
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>paclock_ft_base_v2</t>
+          <t>paclock_ft_base</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
@@ -16225,7 +16323,7 @@
       </c>
       <c r="E365" t="inlineStr">
         <is>
-          <t>no row label for 'paclock_ft_base_v2'</t>
+          <t>no row label for 'paclock_ft_base'</t>
         </is>
       </c>
     </row>
@@ -16237,7 +16335,7 @@
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>paclock_ft_large</t>
+          <t>paclock_ft_base_v2</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
@@ -16252,7 +16350,7 @@
       </c>
       <c r="E366" t="inlineStr">
         <is>
-          <t>no row label for 'paclock_ft_large'</t>
+          <t>no row label for 'paclock_ft_base_v2'</t>
         </is>
       </c>
     </row>
@@ -16264,7 +16362,7 @@
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>paclock_fuse_ms</t>
+          <t>paclock_ft_large</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
@@ -16279,7 +16377,7 @@
       </c>
       <c r="E367" t="inlineStr">
         <is>
-          <t>no row label for 'paclock_fuse_ms'</t>
+          <t>no row label for 'paclock_ft_large'</t>
         </is>
       </c>
     </row>
@@ -16291,7 +16389,7 @@
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>paclock_fuse_sp</t>
+          <t>paclock_fuse_ms</t>
         </is>
       </c>
       <c r="C368" t="inlineStr">
@@ -16306,7 +16404,7 @@
       </c>
       <c r="E368" t="inlineStr">
         <is>
-          <t>no row label for 'paclock_fuse_sp'</t>
+          <t>no row label for 'paclock_fuse_ms'</t>
         </is>
       </c>
     </row>
@@ -16318,7 +16416,7 @@
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>paclock_h12</t>
+          <t>paclock_fuse_sp</t>
         </is>
       </c>
       <c r="C369" t="inlineStr">
@@ -16333,7 +16431,7 @@
       </c>
       <c r="E369" t="inlineStr">
         <is>
-          <t>no row label for 'paclock_h12'</t>
+          <t>no row label for 'paclock_fuse_sp'</t>
         </is>
       </c>
     </row>
@@ -16345,7 +16443,7 @@
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>paclock_h1stem</t>
+          <t>paclock_h12</t>
         </is>
       </c>
       <c r="C370" t="inlineStr">
@@ -16360,7 +16458,7 @@
       </c>
       <c r="E370" t="inlineStr">
         <is>
-          <t>no row label for 'paclock_h1stem'</t>
+          <t>no row label for 'paclock_h12'</t>
         </is>
       </c>
     </row>
@@ -16372,7 +16470,7 @@
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>paclock_h2mont</t>
+          <t>paclock_h1stem</t>
         </is>
       </c>
       <c r="C371" t="inlineStr">
@@ -16387,7 +16485,7 @@
       </c>
       <c r="E371" t="inlineStr">
         <is>
-          <t>no row label for 'paclock_h2mont'</t>
+          <t>no row label for 'paclock_h1stem'</t>
         </is>
       </c>
     </row>
@@ -16399,7 +16497,7 @@
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>paclock_h4flat</t>
+          <t>paclock_h2mont</t>
         </is>
       </c>
       <c r="C372" t="inlineStr">
@@ -16414,7 +16512,7 @@
       </c>
       <c r="E372" t="inlineStr">
         <is>
-          <t>no row label for 'paclock_h4flat'</t>
+          <t>no row label for 'paclock_h2mont'</t>
         </is>
       </c>
     </row>
@@ -16426,7 +16524,7 @@
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>paclock_hybrid_sp</t>
+          <t>paclock_h4flat</t>
         </is>
       </c>
       <c r="C373" t="inlineStr">
@@ -16441,7 +16539,7 @@
       </c>
       <c r="E373" t="inlineStr">
         <is>
-          <t>no row label for 'paclock_hybrid_sp'</t>
+          <t>no row label for 'paclock_h4flat'</t>
         </is>
       </c>
     </row>
@@ -16453,7 +16551,7 @@
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>paclock_hybrid_sp_gate</t>
+          <t>paclock_hybrid_sp</t>
         </is>
       </c>
       <c r="C374" t="inlineStr">
@@ -16468,7 +16566,7 @@
       </c>
       <c r="E374" t="inlineStr">
         <is>
-          <t>no row label for 'paclock_hybrid_sp_gate'</t>
+          <t>no row label for 'paclock_hybrid_sp'</t>
         </is>
       </c>
     </row>
@@ -16480,7 +16578,7 @@
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>paclock_lr1e3</t>
+          <t>paclock_hybrid_sp_gate</t>
         </is>
       </c>
       <c r="C375" t="inlineStr">
@@ -16495,7 +16593,7 @@
       </c>
       <c r="E375" t="inlineStr">
         <is>
-          <t>no row label for 'paclock_lr1e3'</t>
+          <t>no row label for 'paclock_hybrid_sp_gate'</t>
         </is>
       </c>
     </row>
@@ -16507,7 +16605,7 @@
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>paclock_lr3e4</t>
+          <t>paclock_lr1e3</t>
         </is>
       </c>
       <c r="C376" t="inlineStr">
@@ -16522,7 +16620,7 @@
       </c>
       <c r="E376" t="inlineStr">
         <is>
-          <t>no row label for 'paclock_lr3e4'</t>
+          <t>no row label for 'paclock_lr1e3'</t>
         </is>
       </c>
     </row>
@@ -16534,7 +16632,7 @@
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>paclock_pac</t>
+          <t>paclock_lr3e4</t>
         </is>
       </c>
       <c r="C377" t="inlineStr">
@@ -16549,7 +16647,7 @@
       </c>
       <c r="E377" t="inlineStr">
         <is>
-          <t>the workbook has no row for this variant</t>
+          <t>no row label for 'paclock_lr3e4'</t>
         </is>
       </c>
     </row>
@@ -16561,7 +16659,7 @@
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>paclock_pt_base</t>
+          <t>paclock_pac</t>
         </is>
       </c>
       <c r="C378" t="inlineStr">
@@ -16576,7 +16674,7 @@
       </c>
       <c r="E378" t="inlineStr">
         <is>
-          <t>row 'PACLock (pretrained, base)' not found</t>
+          <t>the workbook has no row for this variant</t>
         </is>
       </c>
     </row>
@@ -16588,7 +16686,7 @@
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>paclock_pt_large</t>
+          <t>paclock_pt_base</t>
         </is>
       </c>
       <c r="C379" t="inlineStr">
@@ -16603,7 +16701,7 @@
       </c>
       <c r="E379" t="inlineStr">
         <is>
-          <t>row 'PACLock (pretrained, large)' not found</t>
+          <t>row 'PACLock (pretrained, base)' not found</t>
         </is>
       </c>
     </row>
@@ -16615,7 +16713,7 @@
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>paclock_raw_drop5</t>
+          <t>paclock_pt_large</t>
         </is>
       </c>
       <c r="C380" t="inlineStr">
@@ -16630,7 +16728,7 @@
       </c>
       <c r="E380" t="inlineStr">
         <is>
-          <t>no row label for 'paclock_raw_drop5'</t>
+          <t>row 'PACLock (pretrained, large)' not found</t>
         </is>
       </c>
     </row>
@@ -16642,7 +16740,7 @@
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>paclock_raw_headattn</t>
+          <t>paclock_raw_drop5</t>
         </is>
       </c>
       <c r="C381" t="inlineStr">
@@ -16657,7 +16755,7 @@
       </c>
       <c r="E381" t="inlineStr">
         <is>
-          <t>no row label for 'paclock_raw_headattn'</t>
+          <t>no row label for 'paclock_raw_drop5'</t>
         </is>
       </c>
     </row>
@@ -16669,7 +16767,7 @@
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>paclock_raw_large</t>
+          <t>paclock_raw_headattn</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
@@ -16684,7 +16782,7 @@
       </c>
       <c r="E382" t="inlineStr">
         <is>
-          <t>no row label for 'paclock_raw_large'</t>
+          <t>no row label for 'paclock_raw_headattn'</t>
         </is>
       </c>
     </row>
@@ -16696,7 +16794,7 @@
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>paclock_raw_nb16</t>
+          <t>paclock_raw_large</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
@@ -16711,7 +16809,7 @@
       </c>
       <c r="E383" t="inlineStr">
         <is>
-          <t>no row label for 'paclock_raw_nb16'</t>
+          <t>no row label for 'paclock_raw_large'</t>
         </is>
       </c>
     </row>
@@ -16723,7 +16821,7 @@
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>paclock_raw_p100</t>
+          <t>paclock_raw_nb16</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
@@ -16738,7 +16836,7 @@
       </c>
       <c r="E384" t="inlineStr">
         <is>
-          <t>no row label for 'paclock_raw_p100'</t>
+          <t>no row label for 'paclock_raw_nb16'</t>
         </is>
       </c>
     </row>
@@ -16750,7 +16848,7 @@
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>paclock_raw_small</t>
+          <t>paclock_raw_p100</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
@@ -16765,7 +16863,7 @@
       </c>
       <c r="E385" t="inlineStr">
         <is>
-          <t>no row label for 'paclock_raw_small'</t>
+          <t>no row label for 'paclock_raw_p100'</t>
         </is>
       </c>
     </row>
@@ -16777,7 +16875,7 @@
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>paclock_raw_sphead</t>
+          <t>paclock_raw_small</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
@@ -16792,7 +16890,7 @@
       </c>
       <c r="E386" t="inlineStr">
         <is>
-          <t>no row label for 'paclock_raw_sphead'</t>
+          <t>no row label for 'paclock_raw_small'</t>
         </is>
       </c>
     </row>
@@ -16804,7 +16902,7 @@
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>paclock_raw_tiny</t>
+          <t>paclock_raw_sphead</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
@@ -16819,7 +16917,7 @@
       </c>
       <c r="E387" t="inlineStr">
         <is>
-          <t>no row label for 'paclock_raw_tiny'</t>
+          <t>no row label for 'paclock_raw_sphead'</t>
         </is>
       </c>
     </row>
@@ -16831,7 +16929,7 @@
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>paclock_raw_wide</t>
+          <t>paclock_raw_tiny</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
@@ -16846,7 +16944,7 @@
       </c>
       <c r="E388" t="inlineStr">
         <is>
-          <t>no row label for 'paclock_raw_wide'</t>
+          <t>no row label for 'paclock_raw_tiny'</t>
         </is>
       </c>
     </row>
@@ -16858,7 +16956,7 @@
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>paclock_rawpt_large</t>
+          <t>paclock_raw_wide</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
@@ -16873,7 +16971,7 @@
       </c>
       <c r="E389" t="inlineStr">
         <is>
-          <t>no row label for 'paclock_rawpt_large'</t>
+          <t>no row label for 'paclock_raw_wide'</t>
         </is>
       </c>
     </row>
@@ -16885,7 +16983,7 @@
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>paclock_rawtok</t>
+          <t>paclock_rawpt_large</t>
         </is>
       </c>
       <c r="C390" t="inlineStr">
@@ -16900,7 +16998,7 @@
       </c>
       <c r="E390" t="inlineStr">
         <is>
-          <t>no row label for 'paclock_rawtok'</t>
+          <t>no row label for 'paclock_rawpt_large'</t>
         </is>
       </c>
     </row>
@@ -16912,7 +17010,7 @@
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>paclock_rot2</t>
+          <t>paclock_rawtok</t>
         </is>
       </c>
       <c r="C391" t="inlineStr">
@@ -16927,7 +17025,7 @@
       </c>
       <c r="E391" t="inlineStr">
         <is>
-          <t>no row label for 'paclock_rot2'</t>
+          <t>no row label for 'paclock_rawtok'</t>
         </is>
       </c>
     </row>
@@ -16939,7 +17037,7 @@
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>paclock_rot_sphead</t>
+          <t>paclock_rot2</t>
         </is>
       </c>
       <c r="C392" t="inlineStr">
@@ -16954,7 +17052,7 @@
       </c>
       <c r="E392" t="inlineStr">
         <is>
-          <t>no row label for 'paclock_rot_sphead'</t>
+          <t>no row label for 'paclock_rot2'</t>
         </is>
       </c>
     </row>
@@ -16966,7 +17064,7 @@
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>paclock_rsp_t1_drop04</t>
+          <t>paclock_rot_sphead</t>
         </is>
       </c>
       <c r="C393" t="inlineStr">
@@ -16981,7 +17079,7 @@
       </c>
       <c r="E393" t="inlineStr">
         <is>
-          <t>no row label for 'paclock_rsp_t1_drop04'</t>
+          <t>no row label for 'paclock_rot_sphead'</t>
         </is>
       </c>
     </row>
@@ -16993,7 +17091,7 @@
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>paclock_rsp_t2_wd1e3</t>
+          <t>paclock_rsp_t1_drop04</t>
         </is>
       </c>
       <c r="C394" t="inlineStr">
@@ -17008,7 +17106,7 @@
       </c>
       <c r="E394" t="inlineStr">
         <is>
-          <t>no row label for 'paclock_rsp_t2_wd1e3'</t>
+          <t>no row label for 'paclock_rsp_t1_drop04'</t>
         </is>
       </c>
     </row>
@@ -17020,7 +17118,7 @@
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>paclock_rsp_t3_aug</t>
+          <t>paclock_rsp_t2_wd1e3</t>
         </is>
       </c>
       <c r="C395" t="inlineStr">
@@ -17035,7 +17133,7 @@
       </c>
       <c r="E395" t="inlineStr">
         <is>
-          <t>no row label for 'paclock_rsp_t3_aug'</t>
+          <t>no row label for 'paclock_rsp_t2_wd1e3'</t>
         </is>
       </c>
     </row>
@@ -17047,7 +17145,7 @@
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>paclock_rsp_t4_combo</t>
+          <t>paclock_rsp_t3_aug</t>
         </is>
       </c>
       <c r="C396" t="inlineStr">
@@ -17062,7 +17160,7 @@
       </c>
       <c r="E396" t="inlineStr">
         <is>
-          <t>no row label for 'paclock_rsp_t4_combo'</t>
+          <t>no row label for 'paclock_rsp_t3_aug'</t>
         </is>
       </c>
     </row>
@@ -17074,7 +17172,7 @@
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>paclock_rsp_t5_aug_wd</t>
+          <t>paclock_rsp_t4_combo</t>
         </is>
       </c>
       <c r="C397" t="inlineStr">
@@ -17089,7 +17187,7 @@
       </c>
       <c r="E397" t="inlineStr">
         <is>
-          <t>no row label for 'paclock_rsp_t5_aug_wd'</t>
+          <t>no row label for 'paclock_rsp_t4_combo'</t>
         </is>
       </c>
     </row>
@@ -17101,7 +17199,7 @@
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>paclock_rsp_t6_aug_strong</t>
+          <t>paclock_rsp_t5_aug_wd</t>
         </is>
       </c>
       <c r="C398" t="inlineStr">
@@ -17116,7 +17214,7 @@
       </c>
       <c r="E398" t="inlineStr">
         <is>
-          <t>no row label for 'paclock_rsp_t6_aug_strong'</t>
+          <t>no row label for 'paclock_rsp_t5_aug_wd'</t>
         </is>
       </c>
     </row>
@@ -17128,7 +17226,7 @@
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>paclock_sphead</t>
+          <t>paclock_rsp_t6_aug_strong</t>
         </is>
       </c>
       <c r="C399" t="inlineStr">
@@ -17143,7 +17241,7 @@
       </c>
       <c r="E399" t="inlineStr">
         <is>
-          <t>no row label for 'paclock_sphead'</t>
+          <t>no row label for 'paclock_rsp_t6_aug_strong'</t>
         </is>
       </c>
     </row>
@@ -17155,7 +17253,7 @@
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>paclock_v2</t>
+          <t>paclock_sphead</t>
         </is>
       </c>
       <c r="C400" t="inlineStr">
@@ -17170,7 +17268,7 @@
       </c>
       <c r="E400" t="inlineStr">
         <is>
-          <t>row 'PACLock (from scratch, full)' not found</t>
+          <t>no row label for 'paclock_sphead'</t>
         </is>
       </c>
     </row>
@@ -17182,7 +17280,7 @@
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>paclock_wn</t>
+          <t>paclock_v2</t>
         </is>
       </c>
       <c r="C401" t="inlineStr">
@@ -17197,7 +17295,7 @@
       </c>
       <c r="E401" t="inlineStr">
         <is>
-          <t>no row label for 'paclock_wn'</t>
+          <t>row 'PACLock (from scratch, full)' not found</t>
         </is>
       </c>
     </row>
@@ -17209,7 +17307,7 @@
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>paclock_wn_raw</t>
+          <t>paclock_wn</t>
         </is>
       </c>
       <c r="C402" t="inlineStr">
@@ -17224,7 +17322,7 @@
       </c>
       <c r="E402" t="inlineStr">
         <is>
-          <t>no row label for 'paclock_wn_raw'</t>
+          <t>no row label for 'paclock_wn'</t>
         </is>
       </c>
     </row>
@@ -17236,7 +17334,7 @@
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>paclock_xyz</t>
+          <t>paclock_wn_raw</t>
         </is>
       </c>
       <c r="C403" t="inlineStr">
@@ -17251,7 +17349,7 @@
       </c>
       <c r="E403" t="inlineStr">
         <is>
-          <t>no row label for 'paclock_xyz'</t>
+          <t>no row label for 'paclock_wn_raw'</t>
         </is>
       </c>
     </row>
@@ -17263,27 +17361,22 @@
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>sparcnet</t>
+          <t>paclock_xyz</t>
         </is>
       </c>
       <c r="C404" t="inlineStr">
         <is>
-          <t>[0, 1, 2]</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D404" t="inlineStr">
         <is>
-          <t>filled</t>
+          <t>skipped</t>
         </is>
       </c>
       <c r="E404" t="inlineStr">
         <is>
-          <t>[实测 1.27M] balanced_acc per-seed 0:0.5951, 1:0.5863, 2:0.5901</t>
-        </is>
-      </c>
-      <c r="F404" t="inlineStr">
-        <is>
-          <t>lr=0.001 batch_size=64 epochs=100 patience=20 eval_every_steps=0 loss=cross_entropy label_smoothing=0.1</t>
+          <t>no row label for 'paclock_xyz'</t>
         </is>
       </c>
     </row>
@@ -17295,7 +17388,7 @@
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>st_transformer</t>
+          <t>sparcnet</t>
         </is>
       </c>
       <c r="C405" t="inlineStr">
@@ -17310,7 +17403,7 @@
       </c>
       <c r="E405" t="inlineStr">
         <is>
-          <t>[实测 3.48M] balanced_acc per-seed 0:0.5757, 1:0.5973, 2:0.6085</t>
+          <t>[实测 1.27M] balanced_acc per-seed 0:0.5951, 1:0.5863, 2:0.5901</t>
         </is>
       </c>
       <c r="F405" t="inlineStr">
@@ -17327,7 +17420,7 @@
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>tfm_pretrained</t>
+          <t>st_transformer</t>
         </is>
       </c>
       <c r="C406" t="inlineStr">
@@ -17342,24 +17435,24 @@
       </c>
       <c r="E406" t="inlineStr">
         <is>
-          <t>[实测 1.89M] balanced_acc per-seed 0:0.4524, 1:0.4217, 2:0.4226</t>
+          <t>[实测 3.48M] balanced_acc per-seed 0:0.5757, 1:0.5973, 2:0.6085</t>
         </is>
       </c>
       <c r="F406" t="inlineStr">
         <is>
-          <t>lr=0.001 batch_size=32 epochs=50 patience=10 eval_every_steps=0 loss=cross_entropy label_smoothing=0.1</t>
+          <t>lr=0.001 batch_size=64 epochs=100 patience=20 eval_every_steps=0 loss=cross_entropy label_smoothing=0.1</t>
         </is>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>siena</t>
+          <t>physionet_mi</t>
         </is>
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>biot_prest16</t>
+          <t>tfm_pretrained</t>
         </is>
       </c>
       <c r="C407" t="inlineStr">
@@ -17374,12 +17467,12 @@
       </c>
       <c r="E407" t="inlineStr">
         <is>
-          <t>[实测 3.19M] pr_auc per-seed 0:0.0688, 1:0.1026, 2:0.1000  [seed spread 17% -- mean is a weak summary]</t>
+          <t>[实测 1.89M] balanced_acc per-seed 0:0.4524, 1:0.4217, 2:0.4226</t>
         </is>
       </c>
       <c r="F407" t="inlineStr">
         <is>
-          <t>stopped_by=patience lr=0.001 batch_size=512 epochs=100 patience=5 eval_every_steps=0 loss=bce_with_logits</t>
+          <t>lr=0.001 batch_size=32 epochs=50 patience=10 eval_every_steps=0 loss=cross_entropy label_smoothing=0.1</t>
         </is>
       </c>
     </row>
@@ -17391,7 +17484,7 @@
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>biot_scratch</t>
+          <t>biot_prest16</t>
         </is>
       </c>
       <c r="C408" t="inlineStr">
@@ -17406,7 +17499,7 @@
       </c>
       <c r="E408" t="inlineStr">
         <is>
-          <t>[实测 3.19M] pr_auc per-seed 0:0.1584, 1:0.2150, 2:0.1265  [seed spread 22% -- mean is a weak summary]</t>
+          <t>[实测 3.19M] pr_auc per-seed 0:0.0688, 1:0.1026, 2:0.1000  [seed spread 17% -- mean is a weak summary]</t>
         </is>
       </c>
       <c r="F408" t="inlineStr">
@@ -17423,7 +17516,7 @@
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>cbramod_pretrained</t>
+          <t>biot_scratch</t>
         </is>
       </c>
       <c r="C409" t="inlineStr">
@@ -17438,12 +17531,12 @@
       </c>
       <c r="E409" t="inlineStr">
         <is>
-          <t>[实测 35.45M] pr_auc per-seed 0:0.3530, 1:0.4441, 2:0.4758</t>
+          <t>[实测 3.19M] pr_auc per-seed 0:0.1584, 1:0.2150, 2:0.1265  [seed spread 22% -- mean is a weak summary]</t>
         </is>
       </c>
       <c r="F409" t="inlineStr">
         <is>
-          <t>lr=0.0001 batch_size=64 epochs=50 patience=0 eval_every_steps=0 loss=bce_with_logits grad_clip=1.0 select_metric=auroc multi_lr=True</t>
+          <t>stopped_by=patience lr=0.001 batch_size=512 epochs=100 patience=5 eval_every_steps=0 loss=bce_with_logits</t>
         </is>
       </c>
     </row>
@@ -17455,7 +17548,7 @@
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>cbramod_scratch</t>
+          <t>cbramod_pretrained</t>
         </is>
       </c>
       <c r="C410" t="inlineStr">
@@ -17470,7 +17563,7 @@
       </c>
       <c r="E410" t="inlineStr">
         <is>
-          <t>[实测 35.45M] pr_auc per-seed 0:0.2693, 1:0.1607, 2:0.1679  [seed spread 25% -- mean is a weak summary]</t>
+          <t>[实测 35.45M] pr_auc per-seed 0:0.3530, 1:0.4441, 2:0.4758</t>
         </is>
       </c>
       <c r="F410" t="inlineStr">
@@ -17487,7 +17580,7 @@
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>cnn_transformer</t>
+          <t>cbramod_scratch</t>
         </is>
       </c>
       <c r="C411" t="inlineStr">
@@ -17502,12 +17595,12 @@
       </c>
       <c r="E411" t="inlineStr">
         <is>
-          <t>[实测 3.16M] pr_auc per-seed 0:0.4808, 1:0.3073, 2:0.4801  [seed spread 19% -- mean is a weak summary]</t>
+          <t>[实测 35.45M] pr_auc per-seed 0:0.2693, 1:0.1607, 2:0.1679  [seed spread 25% -- mean is a weak summary]</t>
         </is>
       </c>
       <c r="F411" t="inlineStr">
         <is>
-          <t>lr=0.001 batch_size=512 epochs=20 patience=8 eval_every_steps=200 loss=bce_with_logits</t>
+          <t>lr=0.0001 batch_size=64 epochs=50 patience=0 eval_every_steps=0 loss=bce_with_logits grad_clip=1.0 select_metric=auroc multi_lr=True</t>
         </is>
       </c>
     </row>
@@ -17519,7 +17612,7 @@
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>contrawr</t>
+          <t>cnn_transformer</t>
         </is>
       </c>
       <c r="C412" t="inlineStr">
@@ -17534,7 +17627,7 @@
       </c>
       <c r="E412" t="inlineStr">
         <is>
-          <t>[实测 1.57M] pr_auc per-seed 0:0.3800, 1:0.4873, 2:0.4868</t>
+          <t>[实测 3.16M] pr_auc per-seed 0:0.4808, 1:0.3073, 2:0.4801  [seed spread 19% -- mean is a weak summary]</t>
         </is>
       </c>
       <c r="F412" t="inlineStr">
@@ -17551,7 +17644,7 @@
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>csbrain_pretrained</t>
+          <t>contrawr</t>
         </is>
       </c>
       <c r="C413" t="inlineStr">
@@ -17566,12 +17659,12 @@
       </c>
       <c r="E413" t="inlineStr">
         <is>
-          <t>[实测 47.06M] pr_auc per-seed 0:0.1402, 1:0.3531, 2:0.2057  [seed spread 38% -- mean is a weak summary]</t>
+          <t>[实测 1.57M] pr_auc per-seed 0:0.3800, 1:0.4873, 2:0.4868</t>
         </is>
       </c>
       <c r="F413" t="inlineStr">
         <is>
-          <t>stopped_by=patience lr=0.0001 batch_size=64 epochs=25 patience=10 eval_every_steps=500 loss=bce_with_logits grad_clip=1.0</t>
+          <t>lr=0.001 batch_size=512 epochs=20 patience=8 eval_every_steps=200 loss=bce_with_logits</t>
         </is>
       </c>
     </row>
@@ -17583,22 +17676,27 @@
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>eegconformer_t1</t>
+          <t>csbrain_pretrained</t>
         </is>
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>[0, 1, 2]</t>
         </is>
       </c>
       <c r="D414" t="inlineStr">
         <is>
-          <t>skipped</t>
+          <t>filled</t>
         </is>
       </c>
       <c r="E414" t="inlineStr">
         <is>
-          <t>no row label for 'eegconformer_t1'</t>
+          <t>[实测 47.06M] pr_auc per-seed 0:0.1402, 1:0.3531, 2:0.2057  [seed spread 38% -- mean is a weak summary]</t>
+        </is>
+      </c>
+      <c r="F414" t="inlineStr">
+        <is>
+          <t>stopped_by=patience lr=0.0001 batch_size=64 epochs=25 patience=10 eval_every_steps=500 loss=bce_with_logits grad_clip=1.0</t>
         </is>
       </c>
     </row>
@@ -17610,7 +17708,7 @@
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>eegconformer_t2</t>
+          <t>eegconformer_t1</t>
         </is>
       </c>
       <c r="C415" t="inlineStr">
@@ -17625,7 +17723,7 @@
       </c>
       <c r="E415" t="inlineStr">
         <is>
-          <t>no row label for 'eegconformer_t2'</t>
+          <t>no row label for 'eegconformer_t1'</t>
         </is>
       </c>
     </row>
@@ -17637,7 +17735,7 @@
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>eegconformer_t3</t>
+          <t>eegconformer_t2</t>
         </is>
       </c>
       <c r="C416" t="inlineStr">
@@ -17652,7 +17750,7 @@
       </c>
       <c r="E416" t="inlineStr">
         <is>
-          <t>no row label for 'eegconformer_t3'</t>
+          <t>no row label for 'eegconformer_t2'</t>
         </is>
       </c>
     </row>
@@ -17664,7 +17762,7 @@
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>eegconformer_t4</t>
+          <t>eegconformer_t3</t>
         </is>
       </c>
       <c r="C417" t="inlineStr">
@@ -17679,7 +17777,7 @@
       </c>
       <c r="E417" t="inlineStr">
         <is>
-          <t>no row label for 'eegconformer_t4'</t>
+          <t>no row label for 'eegconformer_t3'</t>
         </is>
       </c>
     </row>
@@ -17691,7 +17789,7 @@
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>eegnet_t1</t>
+          <t>eegconformer_t4</t>
         </is>
       </c>
       <c r="C418" t="inlineStr">
@@ -17706,7 +17804,7 @@
       </c>
       <c r="E418" t="inlineStr">
         <is>
-          <t>no row label for 'eegnet_t1'</t>
+          <t>no row label for 'eegconformer_t4'</t>
         </is>
       </c>
     </row>
@@ -17718,7 +17816,7 @@
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>eegnet_t2</t>
+          <t>eegnet_t1</t>
         </is>
       </c>
       <c r="C419" t="inlineStr">
@@ -17733,7 +17831,7 @@
       </c>
       <c r="E419" t="inlineStr">
         <is>
-          <t>no row label for 'eegnet_t2'</t>
+          <t>no row label for 'eegnet_t1'</t>
         </is>
       </c>
     </row>
@@ -17745,7 +17843,7 @@
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>eegnet_t3</t>
+          <t>eegnet_t2</t>
         </is>
       </c>
       <c r="C420" t="inlineStr">
@@ -17760,7 +17858,7 @@
       </c>
       <c r="E420" t="inlineStr">
         <is>
-          <t>no row label for 'eegnet_t3'</t>
+          <t>no row label for 'eegnet_t2'</t>
         </is>
       </c>
     </row>
@@ -17772,7 +17870,7 @@
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>eegnet_t4</t>
+          <t>eegnet_t3</t>
         </is>
       </c>
       <c r="C421" t="inlineStr">
@@ -17787,7 +17885,7 @@
       </c>
       <c r="E421" t="inlineStr">
         <is>
-          <t>no row label for 'eegnet_t4'</t>
+          <t>no row label for 'eegnet_t3'</t>
         </is>
       </c>
     </row>
@@ -17799,27 +17897,22 @@
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>eegpt_pretrained</t>
+          <t>eegnet_t4</t>
         </is>
       </c>
       <c r="C422" t="inlineStr">
         <is>
-          <t>[0, 1, 2]</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D422" t="inlineStr">
         <is>
-          <t>filled</t>
+          <t>skipped</t>
         </is>
       </c>
       <c r="E422" t="inlineStr">
         <is>
-          <t>[实测 25.69M] pr_auc per-seed 0:0.2390, 1:0.3648, 2:0.3914  [seed spread 20% -- mean is a weak summary]</t>
-        </is>
-      </c>
-      <c r="F422" t="inlineStr">
-        <is>
-          <t>stopped_by=patience lr=0.0004 batch_size=32 epochs=40 patience=10 eval_every_steps=500 loss=bce_with_logits</t>
+          <t>no row label for 'eegnet_t4'</t>
         </is>
       </c>
     </row>
@@ -17831,7 +17924,7 @@
       </c>
       <c r="B423" t="inlineStr">
         <is>
-          <t>eegpt_scratch</t>
+          <t>eegpt_pretrained</t>
         </is>
       </c>
       <c r="C423" t="inlineStr">
@@ -17846,7 +17939,7 @@
       </c>
       <c r="E423" t="inlineStr">
         <is>
-          <t>[实测 25.69M] pr_auc per-seed 0:0.1107, 1:0.1103, 2:0.1640  [seed spread 20% -- mean is a weak summary]</t>
+          <t>[实测 25.69M] pr_auc per-seed 0:0.2390, 1:0.3648, 2:0.3914  [seed spread 20% -- mean is a weak summary]</t>
         </is>
       </c>
       <c r="F423" t="inlineStr">
@@ -17863,7 +17956,7 @@
       </c>
       <c r="B424" t="inlineStr">
         <is>
-          <t>feat_best</t>
+          <t>eegpt_scratch</t>
         </is>
       </c>
       <c r="C424" t="inlineStr">
@@ -17878,12 +17971,12 @@
       </c>
       <c r="E424" t="inlineStr">
         <is>
-          <t>[实测 0.00M] pr_auc per-seed 0:0.0404, 1:0.0404, 2:0.0404</t>
+          <t>[实测 25.69M] pr_auc per-seed 0:0.1107, 1:0.1103, 2:0.1640  [seed spread 20% -- mean is a weak summary]</t>
         </is>
       </c>
       <c r="F424" t="inlineStr">
         <is>
-          <t>stopped_by=closed-form epochs=1 loss=closed-form</t>
+          <t>stopped_by=patience lr=0.0004 batch_size=32 epochs=40 patience=10 eval_every_steps=500 loss=bce_with_logits</t>
         </is>
       </c>
     </row>
@@ -17895,7 +17988,7 @@
       </c>
       <c r="B425" t="inlineStr">
         <is>
-          <t>ffcl</t>
+          <t>feat_best</t>
         </is>
       </c>
       <c r="C425" t="inlineStr">
@@ -17910,12 +18003,12 @@
       </c>
       <c r="E425" t="inlineStr">
         <is>
-          <t>[实测 2.47M] pr_auc per-seed 0:0.3084, 1:0.4492, 2:0.5066  [seed spread 20% -- mean is a weak summary]</t>
+          <t>[实测 0.00M] pr_auc per-seed 0:0.0404, 1:0.0404, 2:0.0404</t>
         </is>
       </c>
       <c r="F425" t="inlineStr">
         <is>
-          <t>lr=0.001 batch_size=512 epochs=20 patience=8 eval_every_steps=200 loss=bce_with_logits</t>
+          <t>stopped_by=closed-form epochs=1 loss=closed-form</t>
         </is>
       </c>
     </row>
@@ -17927,7 +18020,7 @@
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>labram_pretrained</t>
+          <t>ffcl</t>
         </is>
       </c>
       <c r="C426" t="inlineStr">
@@ -17942,12 +18035,12 @@
       </c>
       <c r="E426" t="inlineStr">
         <is>
-          <t>[实测 5.82M] pr_auc per-seed 0:0.3124, 1:0.2807, 2:0.3149</t>
+          <t>[实测 2.47M] pr_auc per-seed 0:0.3084, 1:0.4492, 2:0.5066  [seed spread 20% -- mean is a weak summary]</t>
         </is>
       </c>
       <c r="F426" t="inlineStr">
         <is>
-          <t>stopped_by=patience lr=0.0005 batch_size=64 epochs=50 patience=10 eval_every_steps=0 loss=bce_with_logits loader_divisor=1.0</t>
+          <t>lr=0.001 batch_size=512 epochs=20 patience=8 eval_every_steps=200 loss=bce_with_logits</t>
         </is>
       </c>
     </row>
@@ -17959,7 +18052,7 @@
       </c>
       <c r="B427" t="inlineStr">
         <is>
-          <t>labram_scratch</t>
+          <t>labram_pretrained</t>
         </is>
       </c>
       <c r="C427" t="inlineStr">
@@ -17974,7 +18067,7 @@
       </c>
       <c r="E427" t="inlineStr">
         <is>
-          <t>[实测 5.82M] pr_auc per-seed 0:0.4995, 1:0.4966, 2:0.4779</t>
+          <t>[实测 5.82M] pr_auc per-seed 0:0.3124, 1:0.2807, 2:0.3149</t>
         </is>
       </c>
       <c r="F427" t="inlineStr">
@@ -17991,22 +18084,27 @@
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>paclock</t>
+          <t>labram_scratch</t>
         </is>
       </c>
       <c r="C428" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>[0, 1, 2]</t>
         </is>
       </c>
       <c r="D428" t="inlineStr">
         <is>
-          <t>skipped</t>
+          <t>filled</t>
         </is>
       </c>
       <c r="E428" t="inlineStr">
         <is>
-          <t>no row label for 'paclock'</t>
+          <t>[实测 5.82M] pr_auc per-seed 0:0.4995, 1:0.4966, 2:0.4779</t>
+        </is>
+      </c>
+      <c r="F428" t="inlineStr">
+        <is>
+          <t>stopped_by=patience lr=0.0005 batch_size=64 epochs=50 patience=10 eval_every_steps=0 loss=bce_with_logits loader_divisor=1.0</t>
         </is>
       </c>
     </row>
@@ -18018,22 +18116,22 @@
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>paclock_duplex</t>
+          <t>paclock</t>
         </is>
       </c>
       <c r="C429" t="inlineStr">
         <is>
-          <t>[0]</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D429" t="inlineStr">
         <is>
-          <t>filled (single-seed, grey)</t>
+          <t>skipped</t>
         </is>
       </c>
       <c r="E429" t="inlineStr">
         <is>
-          <t>pr_auc 0.1098</t>
+          <t>no row label for 'paclock'</t>
         </is>
       </c>
     </row>
@@ -18045,22 +18143,22 @@
       </c>
       <c r="B430" t="inlineStr">
         <is>
-          <t>paclock_duplex_b32x4</t>
+          <t>paclock_duplex</t>
         </is>
       </c>
       <c r="C430" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>[0]</t>
         </is>
       </c>
       <c r="D430" t="inlineStr">
         <is>
-          <t>skipped</t>
+          <t>filled (single-seed, grey)</t>
         </is>
       </c>
       <c r="E430" t="inlineStr">
         <is>
-          <t>no row label for 'paclock_duplex_b32x4'</t>
+          <t>pr_auc 0.1098</t>
         </is>
       </c>
     </row>
@@ -18072,7 +18170,7 @@
       </c>
       <c r="B431" t="inlineStr">
         <is>
-          <t>paclock_duplex_ptF</t>
+          <t>paclock_duplex_b32x4</t>
         </is>
       </c>
       <c r="C431" t="inlineStr">
@@ -18087,7 +18185,7 @@
       </c>
       <c r="E431" t="inlineStr">
         <is>
-          <t>row 'CroFreMo (预训练 v2-full)' not found</t>
+          <t>no row label for 'paclock_duplex_b32x4'</t>
         </is>
       </c>
     </row>
@@ -18099,27 +18197,22 @@
       </c>
       <c r="B432" t="inlineStr">
         <is>
-          <t>reve_pretrained</t>
+          <t>paclock_duplex_ptF</t>
         </is>
       </c>
       <c r="C432" t="inlineStr">
         <is>
-          <t>[0, 1, 2]</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D432" t="inlineStr">
         <is>
-          <t>filled</t>
+          <t>skipped</t>
         </is>
       </c>
       <c r="E432" t="inlineStr">
         <is>
-          <t>[实测 69.51M] pr_auc per-seed 0:0.3828, 1:0.5912, 2:0.5804  [seed spread 18% -- mean is a weak summary]</t>
-        </is>
-      </c>
-      <c r="F432" t="inlineStr">
-        <is>
-          <t>stopped_by=patience lr=0.0001 batch_size=128 epochs=15 patience=10 eval_every_steps=500 loss=bce_with_logits grad_clip=1.0</t>
+          <t>row 'CroFreMo (预训练 v2-full)' not found</t>
         </is>
       </c>
     </row>
@@ -18131,7 +18224,7 @@
       </c>
       <c r="B433" t="inlineStr">
         <is>
-          <t>sparcnet</t>
+          <t>reve_pretrained</t>
         </is>
       </c>
       <c r="C433" t="inlineStr">
@@ -18146,12 +18239,12 @@
       </c>
       <c r="E433" t="inlineStr">
         <is>
-          <t>[实测 1.14M] pr_auc per-seed 0:0.4057, 1:0.3291, 2:0.3365</t>
+          <t>[实测 69.51M] pr_auc per-seed 0:0.3828, 1:0.5912, 2:0.5804  [seed spread 18% -- mean is a weak summary]</t>
         </is>
       </c>
       <c r="F433" t="inlineStr">
         <is>
-          <t>stopped_by=patience lr=0.001 batch_size=512 epochs=20 patience=8 eval_every_steps=200 loss=bce_with_logits</t>
+          <t>stopped_by=patience lr=0.0001 batch_size=128 epochs=15 patience=10 eval_every_steps=500 loss=bce_with_logits grad_clip=1.0</t>
         </is>
       </c>
     </row>
@@ -18163,7 +18256,7 @@
       </c>
       <c r="B434" t="inlineStr">
         <is>
-          <t>st_transformer</t>
+          <t>sparcnet</t>
         </is>
       </c>
       <c r="C434" t="inlineStr">
@@ -18173,12 +18266,17 @@
       </c>
       <c r="D434" t="inlineStr">
         <is>
-          <t>withheld (rule 3)</t>
+          <t>filled</t>
         </is>
       </c>
       <c r="E434" t="inlineStr">
         <is>
-          <t>mis-configured seeds [0]: {0: 'val peak at first evaluation and never cleared chance (0.0074 vs 0.0100)'}; measured pr_auc 0.2178±0.1511</t>
+          <t>[实测 1.14M] pr_auc per-seed 0:0.4057, 1:0.3291, 2:0.3365</t>
+        </is>
+      </c>
+      <c r="F434" t="inlineStr">
+        <is>
+          <t>stopped_by=patience lr=0.001 batch_size=512 epochs=20 patience=8 eval_every_steps=200 loss=bce_with_logits</t>
         </is>
       </c>
     </row>
@@ -18190,7 +18288,7 @@
       </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t>tfm_pretrained</t>
+          <t>st_transformer</t>
         </is>
       </c>
       <c r="C435" t="inlineStr">
@@ -18200,17 +18298,12 @@
       </c>
       <c r="D435" t="inlineStr">
         <is>
-          <t>filled</t>
+          <t>withheld (rule 3)</t>
         </is>
       </c>
       <c r="E435" t="inlineStr">
         <is>
-          <t>[实测 1.89M] pr_auc per-seed 0:0.0693, 1:0.0471, 2:0.0645  [seed spread 16% -- mean is a weak summary]</t>
-        </is>
-      </c>
-      <c r="F435" t="inlineStr">
-        <is>
-          <t>lr=0.001 batch_size=512 epochs=7 patience=10 eval_every_steps=100 loss=bce_with_logits</t>
+          <t>mis-configured seeds [0]: {0: 'val peak at first evaluation and never cleared chance (0.0074 vs 0.0100)'}; measured pr_auc 0.2178±0.1511</t>
         </is>
       </c>
     </row>
@@ -18222,7 +18315,7 @@
       </c>
       <c r="B436" t="inlineStr">
         <is>
-          <t>tfm_scratch</t>
+          <t>tfm_pretrained</t>
         </is>
       </c>
       <c r="C436" t="inlineStr">
@@ -18237,7 +18330,7 @@
       </c>
       <c r="E436" t="inlineStr">
         <is>
-          <t>[实测 1.89M] pr_auc per-seed 0:0.0078, 1:0.0222, 2:0.0059  [seed spread 61% -- mean is a weak summary]</t>
+          <t>[实测 1.89M] pr_auc per-seed 0:0.0693, 1:0.0471, 2:0.0645  [seed spread 16% -- mean is a weak summary]</t>
         </is>
       </c>
       <c r="F436" t="inlineStr">
@@ -18249,12 +18342,12 @@
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
-          <t>sleepedf</t>
+          <t>siena</t>
         </is>
       </c>
       <c r="B437" t="inlineStr">
         <is>
-          <t>biot_prest16</t>
+          <t>tfm_scratch</t>
         </is>
       </c>
       <c r="C437" t="inlineStr">
@@ -18269,12 +18362,12 @@
       </c>
       <c r="E437" t="inlineStr">
         <is>
-          <t>[实测 3.19M] cohen_kappa per-seed 0:0.5804, 1:0.5861, 2:0.6156</t>
+          <t>[实测 1.89M] pr_auc per-seed 0:0.0078, 1:0.0222, 2:0.0059  [seed spread 61% -- mean is a weak summary]</t>
         </is>
       </c>
       <c r="F437" t="inlineStr">
         <is>
-          <t>lr=0.0004 batch_size=64 epochs=40 patience=10 eval_every_steps=0 loss=cross_entropy</t>
+          <t>lr=0.001 batch_size=512 epochs=7 patience=10 eval_every_steps=100 loss=bce_with_logits</t>
         </is>
       </c>
     </row>
@@ -18286,7 +18379,7 @@
       </c>
       <c r="B438" t="inlineStr">
         <is>
-          <t>biot_scratch</t>
+          <t>biot_prest16</t>
         </is>
       </c>
       <c r="C438" t="inlineStr">
@@ -18301,7 +18394,7 @@
       </c>
       <c r="E438" t="inlineStr">
         <is>
-          <t>[实测 3.18M] cohen_kappa per-seed 0:0.6579, 1:0.6341, 2:0.6722</t>
+          <t>[实测 3.19M] cohen_kappa per-seed 0:0.5804, 1:0.5861, 2:0.6156</t>
         </is>
       </c>
       <c r="F438" t="inlineStr">
@@ -18318,22 +18411,27 @@
       </c>
       <c r="B439" t="inlineStr">
         <is>
-          <t>cbramod_pac</t>
+          <t>biot_scratch</t>
         </is>
       </c>
       <c r="C439" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>[0, 1, 2]</t>
         </is>
       </c>
       <c r="D439" t="inlineStr">
         <is>
-          <t>skipped</t>
+          <t>filled</t>
         </is>
       </c>
       <c r="E439" t="inlineStr">
         <is>
-          <t>the workbook has no row for this variant</t>
+          <t>[实测 3.18M] cohen_kappa per-seed 0:0.6579, 1:0.6341, 2:0.6722</t>
+        </is>
+      </c>
+      <c r="F439" t="inlineStr">
+        <is>
+          <t>lr=0.0004 batch_size=64 epochs=40 patience=10 eval_every_steps=0 loss=cross_entropy</t>
         </is>
       </c>
     </row>
@@ -18345,27 +18443,22 @@
       </c>
       <c r="B440" t="inlineStr">
         <is>
-          <t>cbramod_pretrained</t>
+          <t>cbramod_pac</t>
         </is>
       </c>
       <c r="C440" t="inlineStr">
         <is>
-          <t>[0, 1, 2]</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D440" t="inlineStr">
         <is>
-          <t>filled</t>
+          <t>skipped</t>
         </is>
       </c>
       <c r="E440" t="inlineStr">
         <is>
-          <t>[实测 9.85M] cohen_kappa per-seed 0:0.6658, 1:0.6743, 2:0.6742</t>
-        </is>
-      </c>
-      <c r="F440" t="inlineStr">
-        <is>
-          <t>lr=0.0001 batch_size=64 epochs=50 patience=0 eval_every_steps=0 loss=cross_entropy label_smoothing=0.1 grad_clip=1.0 multi_lr=True</t>
+          <t>the workbook has no row for this variant</t>
         </is>
       </c>
     </row>
@@ -18377,7 +18470,7 @@
       </c>
       <c r="B441" t="inlineStr">
         <is>
-          <t>cbramod_scratch</t>
+          <t>cbramod_pretrained</t>
         </is>
       </c>
       <c r="C441" t="inlineStr">
@@ -18392,7 +18485,7 @@
       </c>
       <c r="E441" t="inlineStr">
         <is>
-          <t>[实测 9.85M] cohen_kappa per-seed 0:0.6504, 1:0.6561, 2:0.6569</t>
+          <t>[实测 9.85M] cohen_kappa per-seed 0:0.6658, 1:0.6743, 2:0.6742</t>
         </is>
       </c>
       <c r="F441" t="inlineStr">
@@ -18409,7 +18502,7 @@
       </c>
       <c r="B442" t="inlineStr">
         <is>
-          <t>cnn_transformer</t>
+          <t>cbramod_scratch</t>
         </is>
       </c>
       <c r="C442" t="inlineStr">
@@ -18424,12 +18517,12 @@
       </c>
       <c r="E442" t="inlineStr">
         <is>
-          <t>[实测 3.15M] cohen_kappa per-seed 0:0.6871, 1:0.6614, 2:0.6850</t>
+          <t>[实测 9.85M] cohen_kappa per-seed 0:0.6504, 1:0.6561, 2:0.6569</t>
         </is>
       </c>
       <c r="F442" t="inlineStr">
         <is>
-          <t>lr=0.001 batch_size=512 epochs=60 patience=15 eval_every_steps=0 loss=cross_entropy label_smoothing=0.1</t>
+          <t>lr=0.0001 batch_size=64 epochs=50 patience=0 eval_every_steps=0 loss=cross_entropy label_smoothing=0.1 grad_clip=1.0 multi_lr=True</t>
         </is>
       </c>
     </row>
@@ -18441,7 +18534,7 @@
       </c>
       <c r="B443" t="inlineStr">
         <is>
-          <t>contrawr</t>
+          <t>cnn_transformer</t>
         </is>
       </c>
       <c r="C443" t="inlineStr">
@@ -18456,7 +18549,7 @@
       </c>
       <c r="E443" t="inlineStr">
         <is>
-          <t>[实测 1.56M] cohen_kappa per-seed 0:0.6752, 1:0.6964, 2:0.7031</t>
+          <t>[实测 3.15M] cohen_kappa per-seed 0:0.6871, 1:0.6614, 2:0.6850</t>
         </is>
       </c>
       <c r="F443" t="inlineStr">
@@ -18473,7 +18566,7 @@
       </c>
       <c r="B444" t="inlineStr">
         <is>
-          <t>eegpt_pretrained</t>
+          <t>contrawr</t>
         </is>
       </c>
       <c r="C444" t="inlineStr">
@@ -18488,12 +18581,12 @@
       </c>
       <c r="E444" t="inlineStr">
         <is>
-          <t>[实测 25.69M] cohen_kappa per-seed 0:0.6071, 1:0.5831, 2:0.6031</t>
+          <t>[实测 1.56M] cohen_kappa per-seed 0:0.6752, 1:0.6964, 2:0.7031</t>
         </is>
       </c>
       <c r="F444" t="inlineStr">
         <is>
-          <t>lr=0.0004 batch_size=32 epochs=40 patience=10 eval_every_steps=200 loss=cross_entropy</t>
+          <t>lr=0.001 batch_size=512 epochs=60 patience=15 eval_every_steps=0 loss=cross_entropy label_smoothing=0.1</t>
         </is>
       </c>
     </row>
@@ -18505,7 +18598,7 @@
       </c>
       <c r="B445" t="inlineStr">
         <is>
-          <t>ffcl</t>
+          <t>eegpt_pretrained</t>
         </is>
       </c>
       <c r="C445" t="inlineStr">
@@ -18520,12 +18613,12 @@
       </c>
       <c r="E445" t="inlineStr">
         <is>
-          <t>[实测 2.51M] cohen_kappa per-seed 0:0.6785, 1:0.6730, 2:0.6824</t>
+          <t>[实测 25.69M] cohen_kappa per-seed 0:0.6071, 1:0.5831, 2:0.6031</t>
         </is>
       </c>
       <c r="F445" t="inlineStr">
         <is>
-          <t>lr=0.001 batch_size=512 epochs=60 patience=15 eval_every_steps=0 loss=cross_entropy label_smoothing=0.1</t>
+          <t>lr=0.0004 batch_size=32 epochs=40 patience=10 eval_every_steps=200 loss=cross_entropy</t>
         </is>
       </c>
     </row>
@@ -18537,7 +18630,7 @@
       </c>
       <c r="B446" t="inlineStr">
         <is>
-          <t>labram_pretrained</t>
+          <t>ffcl</t>
         </is>
       </c>
       <c r="C446" t="inlineStr">
@@ -18552,12 +18645,12 @@
       </c>
       <c r="E446" t="inlineStr">
         <is>
-          <t>[实测 5.82M] cohen_kappa per-seed 0:0.6082, 1:0.6032, 2:0.6188</t>
+          <t>[实测 2.51M] cohen_kappa per-seed 0:0.6785, 1:0.6730, 2:0.6824</t>
         </is>
       </c>
       <c r="F446" t="inlineStr">
         <is>
-          <t>stopped_by=patience lr=0.0005 batch_size=64 epochs=50 patience=10 eval_every_steps=0 loss=cross_entropy label_smoothing=0.1 loader_divisor=1.0</t>
+          <t>lr=0.001 batch_size=512 epochs=60 patience=15 eval_every_steps=0 loss=cross_entropy label_smoothing=0.1</t>
         </is>
       </c>
     </row>
@@ -18569,7 +18662,7 @@
       </c>
       <c r="B447" t="inlineStr">
         <is>
-          <t>labram_scratch</t>
+          <t>labram_pretrained</t>
         </is>
       </c>
       <c r="C447" t="inlineStr">
@@ -18584,7 +18677,7 @@
       </c>
       <c r="E447" t="inlineStr">
         <is>
-          <t>[实测 5.82M] cohen_kappa per-seed 0:0.6094, 1:0.5932, 2:0.5915</t>
+          <t>[实测 5.82M] cohen_kappa per-seed 0:0.6082, 1:0.6032, 2:0.6188</t>
         </is>
       </c>
       <c r="F447" t="inlineStr">
@@ -18601,22 +18694,27 @@
       </c>
       <c r="B448" t="inlineStr">
         <is>
-          <t>paclock_duplex</t>
+          <t>labram_scratch</t>
         </is>
       </c>
       <c r="C448" t="inlineStr">
         <is>
-          <t>[0]</t>
+          <t>[0, 1, 2]</t>
         </is>
       </c>
       <c r="D448" t="inlineStr">
         <is>
-          <t>filled (single-seed, grey)</t>
+          <t>filled</t>
         </is>
       </c>
       <c r="E448" t="inlineStr">
         <is>
-          <t>cohen_kappa 0.6533</t>
+          <t>[实测 5.82M] cohen_kappa per-seed 0:0.6094, 1:0.5932, 2:0.5915</t>
+        </is>
+      </c>
+      <c r="F448" t="inlineStr">
+        <is>
+          <t>stopped_by=patience lr=0.0005 batch_size=64 epochs=50 patience=10 eval_every_steps=0 loss=cross_entropy label_smoothing=0.1 loader_divisor=1.0</t>
         </is>
       </c>
     </row>
@@ -18628,22 +18726,22 @@
       </c>
       <c r="B449" t="inlineStr">
         <is>
-          <t>paclock_duplex_pt</t>
+          <t>paclock_duplex</t>
         </is>
       </c>
       <c r="C449" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>[0]</t>
         </is>
       </c>
       <c r="D449" t="inlineStr">
         <is>
-          <t>skipped</t>
+          <t>filled (single-seed, grey)</t>
         </is>
       </c>
       <c r="E449" t="inlineStr">
         <is>
-          <t>row 'PACLock (duplex, pretrained)' not found</t>
+          <t>cohen_kappa 0.6533</t>
         </is>
       </c>
     </row>
@@ -18655,22 +18753,22 @@
       </c>
       <c r="B450" t="inlineStr">
         <is>
-          <t>paclock_duplex_pt2</t>
+          <t>paclock_duplex_pt</t>
         </is>
       </c>
       <c r="C450" t="inlineStr">
         <is>
-          <t>[0]</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D450" t="inlineStr">
         <is>
-          <t>filled (single-seed, grey)</t>
+          <t>skipped</t>
         </is>
       </c>
       <c r="E450" t="inlineStr">
         <is>
-          <t>cohen_kappa 0.6775</t>
+          <t>row 'PACLock (duplex, pretrained)' not found</t>
         </is>
       </c>
     </row>
@@ -18682,7 +18780,7 @@
       </c>
       <c r="B451" t="inlineStr">
         <is>
-          <t>paclock_duplex_pt3</t>
+          <t>paclock_duplex_pt2</t>
         </is>
       </c>
       <c r="C451" t="inlineStr">
@@ -18697,7 +18795,7 @@
       </c>
       <c r="E451" t="inlineStr">
         <is>
-          <t>cohen_kappa 0.6664</t>
+          <t>cohen_kappa 0.6775</t>
         </is>
       </c>
     </row>
@@ -18709,22 +18807,22 @@
       </c>
       <c r="B452" t="inlineStr">
         <is>
-          <t>paclock_duplex_ptF</t>
+          <t>paclock_duplex_pt3</t>
         </is>
       </c>
       <c r="C452" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>[0]</t>
         </is>
       </c>
       <c r="D452" t="inlineStr">
         <is>
-          <t>skipped</t>
+          <t>filled (single-seed, grey)</t>
         </is>
       </c>
       <c r="E452" t="inlineStr">
         <is>
-          <t>row 'CroFreMo (预训练 v2-full)' not found</t>
+          <t>cohen_kappa 0.6664</t>
         </is>
       </c>
     </row>
@@ -18736,7 +18834,7 @@
       </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t>paclock_pac</t>
+          <t>paclock_duplex_ptF</t>
         </is>
       </c>
       <c r="C453" t="inlineStr">
@@ -18751,7 +18849,7 @@
       </c>
       <c r="E453" t="inlineStr">
         <is>
-          <t>the workbook has no row for this variant</t>
+          <t>row 'CroFreMo (预训练 v2-full)' not found</t>
         </is>
       </c>
     </row>
@@ -18763,7 +18861,7 @@
       </c>
       <c r="B454" t="inlineStr">
         <is>
-          <t>paclock_pt_base</t>
+          <t>paclock_pac</t>
         </is>
       </c>
       <c r="C454" t="inlineStr">
@@ -18778,7 +18876,7 @@
       </c>
       <c r="E454" t="inlineStr">
         <is>
-          <t>row 'PACLock (pretrained, base)' not found</t>
+          <t>the workbook has no row for this variant</t>
         </is>
       </c>
     </row>
@@ -18790,7 +18888,7 @@
       </c>
       <c r="B455" t="inlineStr">
         <is>
-          <t>paclock_pt_large</t>
+          <t>paclock_pt_base</t>
         </is>
       </c>
       <c r="C455" t="inlineStr">
@@ -18805,7 +18903,7 @@
       </c>
       <c r="E455" t="inlineStr">
         <is>
-          <t>row 'PACLock (pretrained, large)' not found</t>
+          <t>row 'PACLock (pretrained, base)' not found</t>
         </is>
       </c>
     </row>
@@ -18817,7 +18915,7 @@
       </c>
       <c r="B456" t="inlineStr">
         <is>
-          <t>paclock_rawtok</t>
+          <t>paclock_pt_large</t>
         </is>
       </c>
       <c r="C456" t="inlineStr">
@@ -18832,7 +18930,7 @@
       </c>
       <c r="E456" t="inlineStr">
         <is>
-          <t>no row label for 'paclock_rawtok'</t>
+          <t>row 'PACLock (pretrained, large)' not found</t>
         </is>
       </c>
     </row>
@@ -18844,7 +18942,7 @@
       </c>
       <c r="B457" t="inlineStr">
         <is>
-          <t>paclock_rot2</t>
+          <t>paclock_rawtok</t>
         </is>
       </c>
       <c r="C457" t="inlineStr">
@@ -18859,7 +18957,7 @@
       </c>
       <c r="E457" t="inlineStr">
         <is>
-          <t>no row label for 'paclock_rot2'</t>
+          <t>no row label for 'paclock_rawtok'</t>
         </is>
       </c>
     </row>
@@ -18871,7 +18969,7 @@
       </c>
       <c r="B458" t="inlineStr">
         <is>
-          <t>paclock_v2</t>
+          <t>paclock_rot2</t>
         </is>
       </c>
       <c r="C458" t="inlineStr">
@@ -18886,7 +18984,7 @@
       </c>
       <c r="E458" t="inlineStr">
         <is>
-          <t>row 'PACLock (from scratch, full)' not found</t>
+          <t>no row label for 'paclock_rot2'</t>
         </is>
       </c>
     </row>
@@ -18898,27 +18996,22 @@
       </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t>sparcnet</t>
+          <t>paclock_v2</t>
         </is>
       </c>
       <c r="C459" t="inlineStr">
         <is>
-          <t>[0, 1, 2]</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D459" t="inlineStr">
         <is>
-          <t>filled</t>
+          <t>skipped</t>
         </is>
       </c>
       <c r="E459" t="inlineStr">
         <is>
-          <t>[实测 1.23M] cohen_kappa per-seed 0:0.6662, 1:0.6848, 2:0.6632</t>
-        </is>
-      </c>
-      <c r="F459" t="inlineStr">
-        <is>
-          <t>lr=0.001 batch_size=512 epochs=60 patience=15 eval_every_steps=0 loss=cross_entropy label_smoothing=0.1</t>
+          <t>row 'PACLock (from scratch, full)' not found</t>
         </is>
       </c>
     </row>
@@ -18930,7 +19023,7 @@
       </c>
       <c r="B460" t="inlineStr">
         <is>
-          <t>st_transformer</t>
+          <t>sparcnet</t>
         </is>
       </c>
       <c r="C460" t="inlineStr">
@@ -18945,7 +19038,7 @@
       </c>
       <c r="E460" t="inlineStr">
         <is>
-          <t>[实测 3.41M] cohen_kappa per-seed 0:0.6508, 1:0.6570, 2:0.6581</t>
+          <t>[实测 1.23M] cohen_kappa per-seed 0:0.6662, 1:0.6848, 2:0.6632</t>
         </is>
       </c>
       <c r="F460" t="inlineStr">
@@ -18962,7 +19055,7 @@
       </c>
       <c r="B461" t="inlineStr">
         <is>
-          <t>tfm_pretrained</t>
+          <t>st_transformer</t>
         </is>
       </c>
       <c r="C461" t="inlineStr">
@@ -18977,24 +19070,24 @@
       </c>
       <c r="E461" t="inlineStr">
         <is>
-          <t>[实测 1.89M] cohen_kappa per-seed 0:0.6165, 1:0.6126, 2:0.6122</t>
+          <t>[实测 3.41M] cohen_kappa per-seed 0:0.6508, 1:0.6570, 2:0.6581</t>
         </is>
       </c>
       <c r="F461" t="inlineStr">
         <is>
-          <t>lr=0.001 batch_size=512 epochs=50 patience=10 eval_every_steps=0 loss=cross_entropy label_smoothing=0.1</t>
+          <t>lr=0.001 batch_size=512 epochs=60 patience=15 eval_every_steps=0 loss=cross_entropy label_smoothing=0.1</t>
         </is>
       </c>
     </row>
     <row r="462">
       <c r="A462" t="inlineStr">
         <is>
-          <t>tuab</t>
+          <t>sleepedf</t>
         </is>
       </c>
       <c r="B462" t="inlineStr">
         <is>
-          <t>biot_prest16</t>
+          <t>tfm_pretrained</t>
         </is>
       </c>
       <c r="C462" t="inlineStr">
@@ -19009,12 +19102,12 @@
       </c>
       <c r="E462" t="inlineStr">
         <is>
-          <t>[实测 3.19M] auroc per-seed 0:0.8750, 1:0.8692, 2:0.8747</t>
+          <t>[实测 1.89M] cohen_kappa per-seed 0:0.6165, 1:0.6126, 2:0.6122</t>
         </is>
       </c>
       <c r="F462" t="inlineStr">
         <is>
-          <t>lr=0.001 batch_size=512 epochs=100 patience=5 eval_every_steps=0 loss=bce_with_logits</t>
+          <t>lr=0.001 batch_size=512 epochs=50 patience=10 eval_every_steps=0 loss=cross_entropy label_smoothing=0.1</t>
         </is>
       </c>
     </row>
@@ -19026,7 +19119,7 @@
       </c>
       <c r="B463" t="inlineStr">
         <is>
-          <t>biot_scratch</t>
+          <t>biot_prest16</t>
         </is>
       </c>
       <c r="C463" t="inlineStr">
@@ -19041,7 +19134,7 @@
       </c>
       <c r="E463" t="inlineStr">
         <is>
-          <t>[实测 3.19M] auroc per-seed 0:0.8658, 1:0.8761, 2:0.8665</t>
+          <t>[实测 3.19M] auroc per-seed 0:0.8750, 1:0.8692, 2:0.8747</t>
         </is>
       </c>
       <c r="F463" t="inlineStr">
@@ -19058,22 +19151,27 @@
       </c>
       <c r="B464" t="inlineStr">
         <is>
-          <t>cbramod_pac</t>
+          <t>biot_scratch</t>
         </is>
       </c>
       <c r="C464" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>[0, 1, 2]</t>
         </is>
       </c>
       <c r="D464" t="inlineStr">
         <is>
-          <t>skipped</t>
+          <t>filled</t>
         </is>
       </c>
       <c r="E464" t="inlineStr">
         <is>
-          <t>the workbook has no row for this variant</t>
+          <t>[实测 3.19M] auroc per-seed 0:0.8658, 1:0.8761, 2:0.8665</t>
+        </is>
+      </c>
+      <c r="F464" t="inlineStr">
+        <is>
+          <t>lr=0.001 batch_size=512 epochs=100 patience=5 eval_every_steps=0 loss=bce_with_logits</t>
         </is>
       </c>
     </row>
@@ -19085,27 +19183,22 @@
       </c>
       <c r="B465" t="inlineStr">
         <is>
-          <t>cbramod_pretrained</t>
+          <t>cbramod_pac</t>
         </is>
       </c>
       <c r="C465" t="inlineStr">
         <is>
-          <t>[0, 1, 2]</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D465" t="inlineStr">
         <is>
-          <t>filled</t>
+          <t>skipped</t>
         </is>
       </c>
       <c r="E465" t="inlineStr">
         <is>
-          <t>[实测 30.65M] auroc per-seed 0:0.8586, 1:0.8584, 2:0.8744</t>
-        </is>
-      </c>
-      <c r="F465" t="inlineStr">
-        <is>
-          <t>lr=0.0001 batch_size=64 epochs=50 patience=0 eval_every_steps=0 loss=bce_with_logits grad_clip=1.0 select_metric=auroc multi_lr=True</t>
+          <t>the workbook has no row for this variant</t>
         </is>
       </c>
     </row>
@@ -19117,7 +19210,7 @@
       </c>
       <c r="B466" t="inlineStr">
         <is>
-          <t>cbramod_scratch</t>
+          <t>cbramod_pretrained</t>
         </is>
       </c>
       <c r="C466" t="inlineStr">
@@ -19132,7 +19225,7 @@
       </c>
       <c r="E466" t="inlineStr">
         <is>
-          <t>[实测 30.65M] auroc per-seed 0:0.8727, 1:0.8789, 2:0.8771</t>
+          <t>[实测 30.65M] auroc per-seed 0:0.8586, 1:0.8584, 2:0.8744</t>
         </is>
       </c>
       <c r="F466" t="inlineStr">
@@ -19149,7 +19242,7 @@
       </c>
       <c r="B467" t="inlineStr">
         <is>
-          <t>cnn_transformer</t>
+          <t>cbramod_scratch</t>
         </is>
       </c>
       <c r="C467" t="inlineStr">
@@ -19164,12 +19257,12 @@
       </c>
       <c r="E467" t="inlineStr">
         <is>
-          <t>[实测 3.15M] auroc per-seed 0:0.8910, 1:0.8972, 2:0.8858</t>
+          <t>[实测 30.65M] auroc per-seed 0:0.8727, 1:0.8789, 2:0.8771</t>
         </is>
       </c>
       <c r="F467" t="inlineStr">
         <is>
-          <t>lr=0.001 batch_size=512 epochs=20 patience=8 eval_every_steps=200 loss=bce_with_logits</t>
+          <t>lr=0.0001 batch_size=64 epochs=50 patience=0 eval_every_steps=0 loss=bce_with_logits grad_clip=1.0 select_metric=auroc multi_lr=True</t>
         </is>
       </c>
     </row>
@@ -19181,7 +19274,7 @@
       </c>
       <c r="B468" t="inlineStr">
         <is>
-          <t>contrawr</t>
+          <t>cnn_transformer</t>
         </is>
       </c>
       <c r="C468" t="inlineStr">
@@ -19196,7 +19289,7 @@
       </c>
       <c r="E468" t="inlineStr">
         <is>
-          <t>[实测 1.57M] auroc per-seed 0:0.8849, 1:0.8839, 2:0.8969</t>
+          <t>[实测 3.15M] auroc per-seed 0:0.8910, 1:0.8972, 2:0.8858</t>
         </is>
       </c>
       <c r="F468" t="inlineStr">
@@ -19213,7 +19306,7 @@
       </c>
       <c r="B469" t="inlineStr">
         <is>
-          <t>csbrain_pretrained</t>
+          <t>contrawr</t>
         </is>
       </c>
       <c r="C469" t="inlineStr">
@@ -19228,12 +19321,12 @@
       </c>
       <c r="E469" t="inlineStr">
         <is>
-          <t>[实测 41.06M] auroc per-seed 0:0.8890, 1:0.8935, 2:0.9005</t>
+          <t>[实测 1.57M] auroc per-seed 0:0.8849, 1:0.8839, 2:0.8969</t>
         </is>
       </c>
       <c r="F469" t="inlineStr">
         <is>
-          <t>stopped_by=patience lr=0.0001 batch_size=64 epochs=25 patience=10 eval_every_steps=500 loss=bce_with_logits grad_clip=1.0</t>
+          <t>lr=0.001 batch_size=512 epochs=20 patience=8 eval_every_steps=200 loss=bce_with_logits</t>
         </is>
       </c>
     </row>
@@ -19245,7 +19338,7 @@
       </c>
       <c r="B470" t="inlineStr">
         <is>
-          <t>eegconformer</t>
+          <t>csbrain_pretrained</t>
         </is>
       </c>
       <c r="C470" t="inlineStr">
@@ -19260,12 +19353,12 @@
       </c>
       <c r="E470" t="inlineStr">
         <is>
-          <t>[实测 1.46M] auroc per-seed 0:0.8843, 1:0.8828, 2:0.8813</t>
+          <t>[实测 41.06M] auroc per-seed 0:0.8890, 1:0.8935, 2:0.9005</t>
         </is>
       </c>
       <c r="F470" t="inlineStr">
         <is>
-          <t>stopped_by=patience lr=0.0003 batch_size=128 epochs=20 patience=8 eval_every_steps=200 loss=bce_with_logits grad_clip=1.0</t>
+          <t>stopped_by=patience lr=0.0001 batch_size=64 epochs=25 patience=10 eval_every_steps=500 loss=bce_with_logits grad_clip=1.0</t>
         </is>
       </c>
     </row>
@@ -19277,22 +19370,27 @@
       </c>
       <c r="B471" t="inlineStr">
         <is>
-          <t>eegconformer_t1</t>
+          <t>eegconformer</t>
         </is>
       </c>
       <c r="C471" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>[0, 1, 2]</t>
         </is>
       </c>
       <c r="D471" t="inlineStr">
         <is>
-          <t>skipped</t>
+          <t>filled</t>
         </is>
       </c>
       <c r="E471" t="inlineStr">
         <is>
-          <t>no row label for 'eegconformer_t1'</t>
+          <t>[实测 1.46M] auroc per-seed 0:0.8843, 1:0.8828, 2:0.8813</t>
+        </is>
+      </c>
+      <c r="F471" t="inlineStr">
+        <is>
+          <t>stopped_by=patience lr=0.0003 batch_size=128 epochs=20 patience=8 eval_every_steps=200 loss=bce_with_logits grad_clip=1.0</t>
         </is>
       </c>
     </row>
@@ -19304,7 +19402,7 @@
       </c>
       <c r="B472" t="inlineStr">
         <is>
-          <t>eegconformer_t2</t>
+          <t>eegconformer_t1</t>
         </is>
       </c>
       <c r="C472" t="inlineStr">
@@ -19319,7 +19417,7 @@
       </c>
       <c r="E472" t="inlineStr">
         <is>
-          <t>no row label for 'eegconformer_t2'</t>
+          <t>no row label for 'eegconformer_t1'</t>
         </is>
       </c>
     </row>
@@ -19331,7 +19429,7 @@
       </c>
       <c r="B473" t="inlineStr">
         <is>
-          <t>eegconformer_t3</t>
+          <t>eegconformer_t2</t>
         </is>
       </c>
       <c r="C473" t="inlineStr">
@@ -19346,7 +19444,7 @@
       </c>
       <c r="E473" t="inlineStr">
         <is>
-          <t>no row label for 'eegconformer_t3'</t>
+          <t>no row label for 'eegconformer_t2'</t>
         </is>
       </c>
     </row>
@@ -19358,7 +19456,7 @@
       </c>
       <c r="B474" t="inlineStr">
         <is>
-          <t>eegconformer_t4</t>
+          <t>eegconformer_t3</t>
         </is>
       </c>
       <c r="C474" t="inlineStr">
@@ -19373,7 +19471,7 @@
       </c>
       <c r="E474" t="inlineStr">
         <is>
-          <t>no row label for 'eegconformer_t4'</t>
+          <t>no row label for 'eegconformer_t3'</t>
         </is>
       </c>
     </row>
@@ -19385,27 +19483,22 @@
       </c>
       <c r="B475" t="inlineStr">
         <is>
-          <t>eegnet</t>
+          <t>eegconformer_t4</t>
         </is>
       </c>
       <c r="C475" t="inlineStr">
         <is>
-          <t>[0, 1, 2]</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D475" t="inlineStr">
         <is>
-          <t>filled</t>
+          <t>skipped</t>
         </is>
       </c>
       <c r="E475" t="inlineStr">
         <is>
-          <t>[实测 0.00M] auroc per-seed 0:0.8551, 1:0.8535, 2:0.8471</t>
-        </is>
-      </c>
-      <c r="F475" t="inlineStr">
-        <is>
-          <t>stopped_by=patience lr=0.001 batch_size=512 epochs=20 patience=8 eval_every_steps=200 loss=bce_with_logits grad_clip=1.0</t>
+          <t>no row label for 'eegconformer_t4'</t>
         </is>
       </c>
     </row>
@@ -19417,22 +19510,27 @@
       </c>
       <c r="B476" t="inlineStr">
         <is>
-          <t>eegnet_t1</t>
+          <t>eegnet</t>
         </is>
       </c>
       <c r="C476" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>[0, 1, 2]</t>
         </is>
       </c>
       <c r="D476" t="inlineStr">
         <is>
-          <t>skipped</t>
+          <t>filled</t>
         </is>
       </c>
       <c r="E476" t="inlineStr">
         <is>
-          <t>no row label for 'eegnet_t1'</t>
+          <t>[实测 0.00M] auroc per-seed 0:0.8551, 1:0.8535, 2:0.8471</t>
+        </is>
+      </c>
+      <c r="F476" t="inlineStr">
+        <is>
+          <t>stopped_by=patience lr=0.001 batch_size=512 epochs=20 patience=8 eval_every_steps=200 loss=bce_with_logits grad_clip=1.0</t>
         </is>
       </c>
     </row>
@@ -19444,7 +19542,7 @@
       </c>
       <c r="B477" t="inlineStr">
         <is>
-          <t>eegnet_t2</t>
+          <t>eegnet_t1</t>
         </is>
       </c>
       <c r="C477" t="inlineStr">
@@ -19459,7 +19557,7 @@
       </c>
       <c r="E477" t="inlineStr">
         <is>
-          <t>no row label for 'eegnet_t2'</t>
+          <t>no row label for 'eegnet_t1'</t>
         </is>
       </c>
     </row>
@@ -19471,7 +19569,7 @@
       </c>
       <c r="B478" t="inlineStr">
         <is>
-          <t>eegnet_t3</t>
+          <t>eegnet_t2</t>
         </is>
       </c>
       <c r="C478" t="inlineStr">
@@ -19486,7 +19584,7 @@
       </c>
       <c r="E478" t="inlineStr">
         <is>
-          <t>no row label for 'eegnet_t3'</t>
+          <t>no row label for 'eegnet_t2'</t>
         </is>
       </c>
     </row>
@@ -19498,7 +19596,7 @@
       </c>
       <c r="B479" t="inlineStr">
         <is>
-          <t>eegnet_t4</t>
+          <t>eegnet_t3</t>
         </is>
       </c>
       <c r="C479" t="inlineStr">
@@ -19513,7 +19611,7 @@
       </c>
       <c r="E479" t="inlineStr">
         <is>
-          <t>no row label for 'eegnet_t4'</t>
+          <t>no row label for 'eegnet_t3'</t>
         </is>
       </c>
     </row>
@@ -19525,27 +19623,22 @@
       </c>
       <c r="B480" t="inlineStr">
         <is>
-          <t>eegpt_pretrained</t>
+          <t>eegnet_t4</t>
         </is>
       </c>
       <c r="C480" t="inlineStr">
         <is>
-          <t>[0, 1, 2]</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D480" t="inlineStr">
         <is>
-          <t>filled</t>
+          <t>skipped</t>
         </is>
       </c>
       <c r="E480" t="inlineStr">
         <is>
-          <t>[实测 25.69M] auroc per-seed 0:0.9046, 1:0.8981, 2:0.9057</t>
-        </is>
-      </c>
-      <c r="F480" t="inlineStr">
-        <is>
-          <t>lr=0.0004 batch_size=32 epochs=40 patience=10 eval_every_steps=200 loss=bce_with_logits</t>
+          <t>no row label for 'eegnet_t4'</t>
         </is>
       </c>
     </row>
@@ -19557,7 +19650,7 @@
       </c>
       <c r="B481" t="inlineStr">
         <is>
-          <t>feat_best</t>
+          <t>eegpt_pretrained</t>
         </is>
       </c>
       <c r="C481" t="inlineStr">
@@ -19572,12 +19665,12 @@
       </c>
       <c r="E481" t="inlineStr">
         <is>
-          <t>[实测 0.00M] auroc per-seed 0:0.8248, 1:0.8248, 2:0.8248</t>
+          <t>[实测 25.69M] auroc per-seed 0:0.9046, 1:0.8981, 2:0.9057</t>
         </is>
       </c>
       <c r="F481" t="inlineStr">
         <is>
-          <t>stopped_by=closed-form epochs=1 loss=closed-form</t>
+          <t>lr=0.0004 batch_size=32 epochs=40 patience=10 eval_every_steps=200 loss=bce_with_logits</t>
         </is>
       </c>
     </row>
@@ -19589,7 +19682,7 @@
       </c>
       <c r="B482" t="inlineStr">
         <is>
-          <t>ffcl</t>
+          <t>feat_best</t>
         </is>
       </c>
       <c r="C482" t="inlineStr">
@@ -19604,12 +19697,12 @@
       </c>
       <c r="E482" t="inlineStr">
         <is>
-          <t>[实测 2.46M] auroc per-seed 0:0.8896, 1:0.8929, 2:0.8769</t>
+          <t>[实测 0.00M] auroc per-seed 0:0.8248, 1:0.8248, 2:0.8248</t>
         </is>
       </c>
       <c r="F482" t="inlineStr">
         <is>
-          <t>lr=0.001 batch_size=512 epochs=20 patience=8 eval_every_steps=200 loss=bce_with_logits</t>
+          <t>stopped_by=closed-form epochs=1 loss=closed-form</t>
         </is>
       </c>
     </row>
@@ -19621,7 +19714,7 @@
       </c>
       <c r="B483" t="inlineStr">
         <is>
-          <t>labram_pretrained</t>
+          <t>ffcl</t>
         </is>
       </c>
       <c r="C483" t="inlineStr">
@@ -19636,12 +19729,12 @@
       </c>
       <c r="E483" t="inlineStr">
         <is>
-          <t>[实测 5.82M] auroc per-seed 0:0.8750, 1:0.8748, 2:0.8811</t>
+          <t>[实测 2.46M] auroc per-seed 0:0.8896, 1:0.8929, 2:0.8769</t>
         </is>
       </c>
       <c r="F483" t="inlineStr">
         <is>
-          <t>lr=0.0005 batch_size=64 epochs=50 patience=10 eval_every_steps=0 loss=bce_with_logits</t>
+          <t>lr=0.001 batch_size=512 epochs=20 patience=8 eval_every_steps=200 loss=bce_with_logits</t>
         </is>
       </c>
     </row>
@@ -19653,7 +19746,7 @@
       </c>
       <c r="B484" t="inlineStr">
         <is>
-          <t>labram_scratch</t>
+          <t>labram_pretrained</t>
         </is>
       </c>
       <c r="C484" t="inlineStr">
@@ -19668,12 +19761,12 @@
       </c>
       <c r="E484" t="inlineStr">
         <is>
-          <t>[实测 5.82M] auroc per-seed 0:0.8617, 1:0.8682, 2:0.8543</t>
+          <t>[实测 5.82M] auroc per-seed 0:0.8750, 1:0.8748, 2:0.8811</t>
         </is>
       </c>
       <c r="F484" t="inlineStr">
         <is>
-          <t>stopped_by=patience lr=0.0005 batch_size=64 epochs=50 patience=10 eval_every_steps=0 loss=bce_with_logits</t>
+          <t>lr=0.0005 batch_size=64 epochs=50 patience=10 eval_every_steps=0 loss=bce_with_logits</t>
         </is>
       </c>
     </row>
@@ -19685,22 +19778,27 @@
       </c>
       <c r="B485" t="inlineStr">
         <is>
-          <t>paclock_duplex</t>
+          <t>labram_scratch</t>
         </is>
       </c>
       <c r="C485" t="inlineStr">
         <is>
-          <t>[0]</t>
+          <t>[0, 1, 2]</t>
         </is>
       </c>
       <c r="D485" t="inlineStr">
         <is>
-          <t>filled (single-seed, grey)</t>
+          <t>filled</t>
         </is>
       </c>
       <c r="E485" t="inlineStr">
         <is>
-          <t>auroc 0.8829</t>
+          <t>[实测 5.82M] auroc per-seed 0:0.8617, 1:0.8682, 2:0.8543</t>
+        </is>
+      </c>
+      <c r="F485" t="inlineStr">
+        <is>
+          <t>stopped_by=patience lr=0.0005 batch_size=64 epochs=50 patience=10 eval_every_steps=0 loss=bce_with_logits</t>
         </is>
       </c>
     </row>
@@ -19712,22 +19810,22 @@
       </c>
       <c r="B486" t="inlineStr">
         <is>
-          <t>paclock_duplex_pt</t>
+          <t>paclock_duplex</t>
         </is>
       </c>
       <c r="C486" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>[0]</t>
         </is>
       </c>
       <c r="D486" t="inlineStr">
         <is>
-          <t>skipped</t>
+          <t>filled (single-seed, grey)</t>
         </is>
       </c>
       <c r="E486" t="inlineStr">
         <is>
-          <t>row 'PACLock (duplex, pretrained)' not found</t>
+          <t>auroc 0.8829</t>
         </is>
       </c>
     </row>
@@ -19739,22 +19837,22 @@
       </c>
       <c r="B487" t="inlineStr">
         <is>
-          <t>paclock_duplex_pt2</t>
+          <t>paclock_duplex_pt</t>
         </is>
       </c>
       <c r="C487" t="inlineStr">
         <is>
-          <t>[0]</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D487" t="inlineStr">
         <is>
-          <t>filled (single-seed, grey)</t>
+          <t>skipped</t>
         </is>
       </c>
       <c r="E487" t="inlineStr">
         <is>
-          <t>auroc 0.8938</t>
+          <t>row 'PACLock (duplex, pretrained)' not found</t>
         </is>
       </c>
     </row>
@@ -19766,22 +19864,22 @@
       </c>
       <c r="B488" t="inlineStr">
         <is>
-          <t>paclock_duplex_ptF</t>
+          <t>paclock_duplex_pt2</t>
         </is>
       </c>
       <c r="C488" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>[0]</t>
         </is>
       </c>
       <c r="D488" t="inlineStr">
         <is>
-          <t>skipped</t>
+          <t>filled (single-seed, grey)</t>
         </is>
       </c>
       <c r="E488" t="inlineStr">
         <is>
-          <t>row 'CroFreMo (预训练 v2-full)' not found</t>
+          <t>auroc 0.8938</t>
         </is>
       </c>
     </row>
@@ -19793,7 +19891,7 @@
       </c>
       <c r="B489" t="inlineStr">
         <is>
-          <t>paclock_pt_base</t>
+          <t>paclock_duplex_ptF</t>
         </is>
       </c>
       <c r="C489" t="inlineStr">
@@ -19808,7 +19906,7 @@
       </c>
       <c r="E489" t="inlineStr">
         <is>
-          <t>row 'PACLock (pretrained, base)' not found</t>
+          <t>row 'CroFreMo (预训练 v2-full)' not found</t>
         </is>
       </c>
     </row>
@@ -19820,7 +19918,7 @@
       </c>
       <c r="B490" t="inlineStr">
         <is>
-          <t>paclock_pt_large</t>
+          <t>paclock_pt_base</t>
         </is>
       </c>
       <c r="C490" t="inlineStr">
@@ -19835,7 +19933,7 @@
       </c>
       <c r="E490" t="inlineStr">
         <is>
-          <t>row 'PACLock (pretrained, large)' not found</t>
+          <t>row 'PACLock (pretrained, base)' not found</t>
         </is>
       </c>
     </row>
@@ -19847,7 +19945,7 @@
       </c>
       <c r="B491" t="inlineStr">
         <is>
-          <t>paclock_rawtok</t>
+          <t>paclock_pt_large</t>
         </is>
       </c>
       <c r="C491" t="inlineStr">
@@ -19862,7 +19960,7 @@
       </c>
       <c r="E491" t="inlineStr">
         <is>
-          <t>no row label for 'paclock_rawtok'</t>
+          <t>row 'PACLock (pretrained, large)' not found</t>
         </is>
       </c>
     </row>
@@ -19874,7 +19972,7 @@
       </c>
       <c r="B492" t="inlineStr">
         <is>
-          <t>paclock_rot2</t>
+          <t>paclock_rawtok</t>
         </is>
       </c>
       <c r="C492" t="inlineStr">
@@ -19889,7 +19987,7 @@
       </c>
       <c r="E492" t="inlineStr">
         <is>
-          <t>no row label for 'paclock_rot2'</t>
+          <t>no row label for 'paclock_rawtok'</t>
         </is>
       </c>
     </row>
@@ -19901,7 +19999,7 @@
       </c>
       <c r="B493" t="inlineStr">
         <is>
-          <t>paclock_v2</t>
+          <t>paclock_rot2</t>
         </is>
       </c>
       <c r="C493" t="inlineStr">
@@ -19916,7 +20014,7 @@
       </c>
       <c r="E493" t="inlineStr">
         <is>
-          <t>row 'PACLock (from scratch, full)' not found</t>
+          <t>no row label for 'paclock_rot2'</t>
         </is>
       </c>
     </row>
@@ -19928,27 +20026,22 @@
       </c>
       <c r="B494" t="inlineStr">
         <is>
-          <t>reve_pretrained</t>
+          <t>paclock_v2</t>
         </is>
       </c>
       <c r="C494" t="inlineStr">
         <is>
-          <t>[0, 1, 2]</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D494" t="inlineStr">
         <is>
-          <t>filled</t>
+          <t>skipped</t>
         </is>
       </c>
       <c r="E494" t="inlineStr">
         <is>
-          <t>[实测 69.46M] auroc per-seed 0:0.9037, 1:0.8950, 2:0.8848</t>
-        </is>
-      </c>
-      <c r="F494" t="inlineStr">
-        <is>
-          <t>stopped_by=patience lr=0.0001 batch_size=128 epochs=15 patience=10 eval_every_steps=500 loss=bce_with_logits grad_clip=1.0</t>
+          <t>row 'PACLock (from scratch, full)' not found</t>
         </is>
       </c>
     </row>
@@ -19960,7 +20053,7 @@
       </c>
       <c r="B495" t="inlineStr">
         <is>
-          <t>sparcnet</t>
+          <t>reve_pretrained</t>
         </is>
       </c>
       <c r="C495" t="inlineStr">
@@ -19975,12 +20068,12 @@
       </c>
       <c r="E495" t="inlineStr">
         <is>
-          <t>[实测 1.14M] auroc per-seed 0:0.8836, 1:0.8896, 2:0.8898</t>
+          <t>[实测 69.46M] auroc per-seed 0:0.9037, 1:0.8950, 2:0.8848</t>
         </is>
       </c>
       <c r="F495" t="inlineStr">
         <is>
-          <t>lr=0.001 batch_size=512 epochs=20 patience=8 eval_every_steps=200 loss=bce_with_logits</t>
+          <t>stopped_by=patience lr=0.0001 batch_size=128 epochs=15 patience=10 eval_every_steps=500 loss=bce_with_logits grad_clip=1.0</t>
         </is>
       </c>
     </row>
@@ -19992,7 +20085,7 @@
       </c>
       <c r="B496" t="inlineStr">
         <is>
-          <t>st_transformer</t>
+          <t>sparcnet</t>
         </is>
       </c>
       <c r="C496" t="inlineStr">
@@ -20007,7 +20100,7 @@
       </c>
       <c r="E496" t="inlineStr">
         <is>
-          <t>[实测 3.43M] auroc per-seed 0:0.9017, 1:0.8992, 2:0.8908</t>
+          <t>[实测 1.14M] auroc per-seed 0:0.8836, 1:0.8896, 2:0.8898</t>
         </is>
       </c>
       <c r="F496" t="inlineStr">
@@ -20024,7 +20117,7 @@
       </c>
       <c r="B497" t="inlineStr">
         <is>
-          <t>tfm_pretrained</t>
+          <t>st_transformer</t>
         </is>
       </c>
       <c r="C497" t="inlineStr">
@@ -20039,39 +20132,44 @@
       </c>
       <c r="E497" t="inlineStr">
         <is>
-          <t>[实测 1.89M] auroc per-seed 0:0.8785, 1:0.8821, 2:0.8772</t>
+          <t>[实测 3.43M] auroc per-seed 0:0.9017, 1:0.8992, 2:0.8908</t>
         </is>
       </c>
       <c r="F497" t="inlineStr">
         <is>
-          <t>lr=0.001 batch_size=512 epochs=10 patience=10 eval_every_steps=100 loss=bce_with_logits label_smoothing=0.1</t>
+          <t>lr=0.001 batch_size=512 epochs=20 patience=8 eval_every_steps=200 loss=bce_with_logits</t>
         </is>
       </c>
     </row>
     <row r="498">
       <c r="A498" t="inlineStr">
         <is>
-          <t>tuar</t>
+          <t>tuab</t>
         </is>
       </c>
       <c r="B498" t="inlineStr">
         <is>
-          <t>biot_prest16</t>
+          <t>tfm_pretrained</t>
         </is>
       </c>
       <c r="C498" t="inlineStr">
         <is>
-          <t>[0]</t>
+          <t>[0, 1, 2]</t>
         </is>
       </c>
       <c r="D498" t="inlineStr">
         <is>
-          <t>filled (single-seed, grey)</t>
+          <t>filled</t>
         </is>
       </c>
       <c r="E498" t="inlineStr">
         <is>
-          <t>cohen_kappa 0.5750</t>
+          <t>[实测 1.89M] auroc per-seed 0:0.8785, 1:0.8821, 2:0.8772</t>
+        </is>
+      </c>
+      <c r="F498" t="inlineStr">
+        <is>
+          <t>lr=0.001 batch_size=512 epochs=10 patience=10 eval_every_steps=100 loss=bce_with_logits label_smoothing=0.1</t>
         </is>
       </c>
     </row>
@@ -20083,7 +20181,7 @@
       </c>
       <c r="B499" t="inlineStr">
         <is>
-          <t>biot_scratch</t>
+          <t>biot_prest16</t>
         </is>
       </c>
       <c r="C499" t="inlineStr">
@@ -20098,7 +20196,7 @@
       </c>
       <c r="E499" t="inlineStr">
         <is>
-          <t>cohen_kappa 0.4985</t>
+          <t>cohen_kappa 0.5750</t>
         </is>
       </c>
     </row>
@@ -20110,7 +20208,7 @@
       </c>
       <c r="B500" t="inlineStr">
         <is>
-          <t>cbramod_pretrained</t>
+          <t>biot_scratch</t>
         </is>
       </c>
       <c r="C500" t="inlineStr">
@@ -20125,7 +20223,7 @@
       </c>
       <c r="E500" t="inlineStr">
         <is>
-          <t>cohen_kappa 0.7147</t>
+          <t>cohen_kappa 0.4985</t>
         </is>
       </c>
     </row>
@@ -20137,7 +20235,7 @@
       </c>
       <c r="B501" t="inlineStr">
         <is>
-          <t>cbramod_scratch</t>
+          <t>cbramod_pretrained</t>
         </is>
       </c>
       <c r="C501" t="inlineStr">
@@ -20152,7 +20250,7 @@
       </c>
       <c r="E501" t="inlineStr">
         <is>
-          <t>cohen_kappa 0.6503</t>
+          <t>cohen_kappa 0.7147</t>
         </is>
       </c>
     </row>
@@ -20164,7 +20262,7 @@
       </c>
       <c r="B502" t="inlineStr">
         <is>
-          <t>cnn_transformer</t>
+          <t>cbramod_scratch</t>
         </is>
       </c>
       <c r="C502" t="inlineStr">
@@ -20179,7 +20277,7 @@
       </c>
       <c r="E502" t="inlineStr">
         <is>
-          <t>cohen_kappa 0.7120</t>
+          <t>cohen_kappa 0.6503</t>
         </is>
       </c>
     </row>
@@ -20191,7 +20289,7 @@
       </c>
       <c r="B503" t="inlineStr">
         <is>
-          <t>contrawr</t>
+          <t>cnn_transformer</t>
         </is>
       </c>
       <c r="C503" t="inlineStr">
@@ -20206,7 +20304,7 @@
       </c>
       <c r="E503" t="inlineStr">
         <is>
-          <t>cohen_kappa 0.6630</t>
+          <t>cohen_kappa 0.7120</t>
         </is>
       </c>
     </row>
@@ -20218,7 +20316,7 @@
       </c>
       <c r="B504" t="inlineStr">
         <is>
-          <t>eegpt_pretrained</t>
+          <t>contrawr</t>
         </is>
       </c>
       <c r="C504" t="inlineStr">
@@ -20233,7 +20331,7 @@
       </c>
       <c r="E504" t="inlineStr">
         <is>
-          <t>cohen_kappa 0.5235</t>
+          <t>cohen_kappa 0.6630</t>
         </is>
       </c>
     </row>
@@ -20245,7 +20343,7 @@
       </c>
       <c r="B505" t="inlineStr">
         <is>
-          <t>eegpt_scratch</t>
+          <t>eegpt_pretrained</t>
         </is>
       </c>
       <c r="C505" t="inlineStr">
@@ -20260,7 +20358,7 @@
       </c>
       <c r="E505" t="inlineStr">
         <is>
-          <t>cohen_kappa 0.5820</t>
+          <t>cohen_kappa 0.5235</t>
         </is>
       </c>
     </row>
@@ -20272,7 +20370,7 @@
       </c>
       <c r="B506" t="inlineStr">
         <is>
-          <t>ffcl</t>
+          <t>eegpt_scratch</t>
         </is>
       </c>
       <c r="C506" t="inlineStr">
@@ -20287,7 +20385,7 @@
       </c>
       <c r="E506" t="inlineStr">
         <is>
-          <t>cohen_kappa 0.6959</t>
+          <t>cohen_kappa 0.5820</t>
         </is>
       </c>
     </row>
@@ -20299,7 +20397,7 @@
       </c>
       <c r="B507" t="inlineStr">
         <is>
-          <t>labram_pretrained</t>
+          <t>ffcl</t>
         </is>
       </c>
       <c r="C507" t="inlineStr">
@@ -20314,7 +20412,7 @@
       </c>
       <c r="E507" t="inlineStr">
         <is>
-          <t>cohen_kappa 0.5931</t>
+          <t>cohen_kappa 0.6959</t>
         </is>
       </c>
     </row>
@@ -20326,7 +20424,7 @@
       </c>
       <c r="B508" t="inlineStr">
         <is>
-          <t>labram_scratch</t>
+          <t>labram_pretrained</t>
         </is>
       </c>
       <c r="C508" t="inlineStr">
@@ -20341,7 +20439,7 @@
       </c>
       <c r="E508" t="inlineStr">
         <is>
-          <t>cohen_kappa 0.5265</t>
+          <t>cohen_kappa 0.5931</t>
         </is>
       </c>
     </row>
@@ -20353,7 +20451,7 @@
       </c>
       <c r="B509" t="inlineStr">
         <is>
-          <t>paclock_duplex</t>
+          <t>labram_scratch</t>
         </is>
       </c>
       <c r="C509" t="inlineStr">
@@ -20368,7 +20466,7 @@
       </c>
       <c r="E509" t="inlineStr">
         <is>
-          <t>cohen_kappa 0.6289</t>
+          <t>cohen_kappa 0.5265</t>
         </is>
       </c>
     </row>
@@ -20380,22 +20478,22 @@
       </c>
       <c r="B510" t="inlineStr">
         <is>
-          <t>paclock_pac</t>
+          <t>paclock_duplex</t>
         </is>
       </c>
       <c r="C510" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>[0]</t>
         </is>
       </c>
       <c r="D510" t="inlineStr">
         <is>
-          <t>skipped</t>
+          <t>filled (single-seed, grey)</t>
         </is>
       </c>
       <c r="E510" t="inlineStr">
         <is>
-          <t>the workbook has no row for this variant</t>
+          <t>cohen_kappa 0.6289</t>
         </is>
       </c>
     </row>
@@ -20407,7 +20505,7 @@
       </c>
       <c r="B511" t="inlineStr">
         <is>
-          <t>paclock_raw</t>
+          <t>paclock_pac</t>
         </is>
       </c>
       <c r="C511" t="inlineStr">
@@ -20422,7 +20520,7 @@
       </c>
       <c r="E511" t="inlineStr">
         <is>
-          <t>no row label for 'paclock_raw'</t>
+          <t>the workbook has no row for this variant</t>
         </is>
       </c>
     </row>
@@ -20434,7 +20532,7 @@
       </c>
       <c r="B512" t="inlineStr">
         <is>
-          <t>paclock_rot</t>
+          <t>paclock_raw</t>
         </is>
       </c>
       <c r="C512" t="inlineStr">
@@ -20449,7 +20547,7 @@
       </c>
       <c r="E512" t="inlineStr">
         <is>
-          <t>no row label for 'paclock_rot'</t>
+          <t>no row label for 'paclock_raw'</t>
         </is>
       </c>
     </row>
@@ -20461,22 +20559,22 @@
       </c>
       <c r="B513" t="inlineStr">
         <is>
-          <t>sparcnet</t>
+          <t>paclock_rot</t>
         </is>
       </c>
       <c r="C513" t="inlineStr">
         <is>
-          <t>[0]</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D513" t="inlineStr">
         <is>
-          <t>filled (single-seed, grey)</t>
+          <t>skipped</t>
         </is>
       </c>
       <c r="E513" t="inlineStr">
         <is>
-          <t>cohen_kappa 0.6010</t>
+          <t>no row label for 'paclock_rot'</t>
         </is>
       </c>
     </row>
@@ -20488,7 +20586,7 @@
       </c>
       <c r="B514" t="inlineStr">
         <is>
-          <t>st_transformer</t>
+          <t>sparcnet</t>
         </is>
       </c>
       <c r="C514" t="inlineStr">
@@ -20503,7 +20601,7 @@
       </c>
       <c r="E514" t="inlineStr">
         <is>
-          <t>cohen_kappa 0.5213</t>
+          <t>cohen_kappa 0.6010</t>
         </is>
       </c>
     </row>
@@ -20515,7 +20613,7 @@
       </c>
       <c r="B515" t="inlineStr">
         <is>
-          <t>tfm_pretrained</t>
+          <t>st_transformer</t>
         </is>
       </c>
       <c r="C515" t="inlineStr">
@@ -20530,7 +20628,7 @@
       </c>
       <c r="E515" t="inlineStr">
         <is>
-          <t>cohen_kappa 0.6480</t>
+          <t>cohen_kappa 0.5213</t>
         </is>
       </c>
     </row>
@@ -20542,7 +20640,7 @@
       </c>
       <c r="B516" t="inlineStr">
         <is>
-          <t>tfm_scratch</t>
+          <t>tfm_pretrained</t>
         </is>
       </c>
       <c r="C516" t="inlineStr">
@@ -20557,39 +20655,34 @@
       </c>
       <c r="E516" t="inlineStr">
         <is>
-          <t>cohen_kappa 0.3644</t>
+          <t>cohen_kappa 0.6480</t>
         </is>
       </c>
     </row>
     <row r="517">
       <c r="A517" t="inlineStr">
         <is>
-          <t>tuep</t>
+          <t>tuar</t>
         </is>
       </c>
       <c r="B517" t="inlineStr">
         <is>
-          <t>biot_prest16</t>
+          <t>tfm_scratch</t>
         </is>
       </c>
       <c r="C517" t="inlineStr">
         <is>
-          <t>[0, 1, 2]</t>
+          <t>[0]</t>
         </is>
       </c>
       <c r="D517" t="inlineStr">
         <is>
-          <t>filled</t>
+          <t>filled (single-seed, grey)</t>
         </is>
       </c>
       <c r="E517" t="inlineStr">
         <is>
-          <t>[实测 3.19M] auroc per-seed 0:0.7513, 1:0.7452, 2:0.7823</t>
-        </is>
-      </c>
-      <c r="F517" t="inlineStr">
-        <is>
-          <t>stopped_by=patience lr=0.001 batch_size=512 epochs=100 patience=5 eval_every_steps=0 loss=bce_with_logits</t>
+          <t>cohen_kappa 0.3644</t>
         </is>
       </c>
     </row>
@@ -20601,7 +20694,7 @@
       </c>
       <c r="B518" t="inlineStr">
         <is>
-          <t>biot_scratch</t>
+          <t>biot_prest16</t>
         </is>
       </c>
       <c r="C518" t="inlineStr">
@@ -20616,7 +20709,7 @@
       </c>
       <c r="E518" t="inlineStr">
         <is>
-          <t>[实测 3.19M] auroc per-seed 0:0.7593, 1:0.7374, 2:0.7599</t>
+          <t>[实测 3.19M] auroc per-seed 0:0.7513, 1:0.7452, 2:0.7823</t>
         </is>
       </c>
       <c r="F518" t="inlineStr">
@@ -20633,7 +20726,7 @@
       </c>
       <c r="B519" t="inlineStr">
         <is>
-          <t>cbramod_pretrained</t>
+          <t>biot_scratch</t>
         </is>
       </c>
       <c r="C519" t="inlineStr">
@@ -20648,12 +20741,12 @@
       </c>
       <c r="E519" t="inlineStr">
         <is>
-          <t>[实测 30.65M] auroc per-seed 0:0.6891, 1:0.6516, 2:0.6533</t>
+          <t>[实测 3.19M] auroc per-seed 0:0.7593, 1:0.7374, 2:0.7599</t>
         </is>
       </c>
       <c r="F519" t="inlineStr">
         <is>
-          <t>lr=0.0001 batch_size=64 epochs=50 patience=0 eval_every_steps=0 loss=bce_with_logits grad_clip=1.0 select_metric=auroc multi_lr=True</t>
+          <t>stopped_by=patience lr=0.001 batch_size=512 epochs=100 patience=5 eval_every_steps=0 loss=bce_with_logits</t>
         </is>
       </c>
     </row>
@@ -20665,7 +20758,7 @@
       </c>
       <c r="B520" t="inlineStr">
         <is>
-          <t>cbramod_scratch</t>
+          <t>cbramod_pretrained</t>
         </is>
       </c>
       <c r="C520" t="inlineStr">
@@ -20680,7 +20773,7 @@
       </c>
       <c r="E520" t="inlineStr">
         <is>
-          <t>[实测 30.65M] auroc per-seed 0:0.6043, 1:0.6529, 2:0.6695</t>
+          <t>[实测 30.65M] auroc per-seed 0:0.6891, 1:0.6516, 2:0.6533</t>
         </is>
       </c>
       <c r="F520" t="inlineStr">
@@ -20697,7 +20790,7 @@
       </c>
       <c r="B521" t="inlineStr">
         <is>
-          <t>cnn_transformer</t>
+          <t>cbramod_scratch</t>
         </is>
       </c>
       <c r="C521" t="inlineStr">
@@ -20712,12 +20805,12 @@
       </c>
       <c r="E521" t="inlineStr">
         <is>
-          <t>[实测 3.15M] auroc per-seed 0:0.6580, 1:0.6790, 2:0.6519</t>
+          <t>[实测 30.65M] auroc per-seed 0:0.6043, 1:0.6529, 2:0.6695</t>
         </is>
       </c>
       <c r="F521" t="inlineStr">
         <is>
-          <t>stopped_by=patience lr=0.001 batch_size=512 epochs=20 patience=8 eval_every_steps=200 loss=bce_with_logits</t>
+          <t>lr=0.0001 batch_size=64 epochs=50 patience=0 eval_every_steps=0 loss=bce_with_logits grad_clip=1.0 select_metric=auroc multi_lr=True</t>
         </is>
       </c>
     </row>
@@ -20729,7 +20822,7 @@
       </c>
       <c r="B522" t="inlineStr">
         <is>
-          <t>contrawr</t>
+          <t>cnn_transformer</t>
         </is>
       </c>
       <c r="C522" t="inlineStr">
@@ -20744,7 +20837,7 @@
       </c>
       <c r="E522" t="inlineStr">
         <is>
-          <t>[实测 1.57M] auroc per-seed 0:0.6938, 1:0.5756, 2:0.6699</t>
+          <t>[实测 3.15M] auroc per-seed 0:0.6580, 1:0.6790, 2:0.6519</t>
         </is>
       </c>
       <c r="F522" t="inlineStr">
@@ -20761,7 +20854,7 @@
       </c>
       <c r="B523" t="inlineStr">
         <is>
-          <t>csbrain_pretrained</t>
+          <t>contrawr</t>
         </is>
       </c>
       <c r="C523" t="inlineStr">
@@ -20776,12 +20869,12 @@
       </c>
       <c r="E523" t="inlineStr">
         <is>
-          <t>[实测 41.06M] auroc per-seed 0:0.5971, 1:0.6439, 2:0.5581</t>
+          <t>[实测 1.57M] auroc per-seed 0:0.6938, 1:0.5756, 2:0.6699</t>
         </is>
       </c>
       <c r="F523" t="inlineStr">
         <is>
-          <t>stopped_by=patience lr=0.0001 batch_size=64 epochs=50 patience=10 eval_every_steps=0 loss=bce_with_logits grad_clip=1.0</t>
+          <t>stopped_by=patience lr=0.001 batch_size=512 epochs=20 patience=8 eval_every_steps=200 loss=bce_with_logits</t>
         </is>
       </c>
     </row>
@@ -20793,7 +20886,7 @@
       </c>
       <c r="B524" t="inlineStr">
         <is>
-          <t>eegconformer</t>
+          <t>csbrain_pretrained</t>
         </is>
       </c>
       <c r="C524" t="inlineStr">
@@ -20808,12 +20901,12 @@
       </c>
       <c r="E524" t="inlineStr">
         <is>
-          <t>[实测 1.46M] auroc per-seed 0:0.7562, 1:0.7349, 2:0.6733</t>
+          <t>[实测 41.06M] auroc per-seed 0:0.5971, 1:0.6439, 2:0.5581</t>
         </is>
       </c>
       <c r="F524" t="inlineStr">
         <is>
-          <t>stopped_by=patience lr=0.0003 batch_size=128 epochs=20 patience=8 eval_every_steps=200 loss=bce_with_logits grad_clip=1.0</t>
+          <t>stopped_by=patience lr=0.0001 batch_size=64 epochs=50 patience=10 eval_every_steps=0 loss=bce_with_logits grad_clip=1.0</t>
         </is>
       </c>
     </row>
@@ -20825,22 +20918,27 @@
       </c>
       <c r="B525" t="inlineStr">
         <is>
-          <t>eegconformer_t1</t>
+          <t>eegconformer</t>
         </is>
       </c>
       <c r="C525" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>[0, 1, 2]</t>
         </is>
       </c>
       <c r="D525" t="inlineStr">
         <is>
-          <t>skipped</t>
+          <t>filled</t>
         </is>
       </c>
       <c r="E525" t="inlineStr">
         <is>
-          <t>no row label for 'eegconformer_t1'</t>
+          <t>[实测 1.46M] auroc per-seed 0:0.7562, 1:0.7349, 2:0.6733</t>
+        </is>
+      </c>
+      <c r="F525" t="inlineStr">
+        <is>
+          <t>stopped_by=patience lr=0.0003 batch_size=128 epochs=20 patience=8 eval_every_steps=200 loss=bce_with_logits grad_clip=1.0</t>
         </is>
       </c>
     </row>
@@ -20852,7 +20950,7 @@
       </c>
       <c r="B526" t="inlineStr">
         <is>
-          <t>eegconformer_t2</t>
+          <t>eegconformer_t1</t>
         </is>
       </c>
       <c r="C526" t="inlineStr">
@@ -20867,7 +20965,7 @@
       </c>
       <c r="E526" t="inlineStr">
         <is>
-          <t>no row label for 'eegconformer_t2'</t>
+          <t>no row label for 'eegconformer_t1'</t>
         </is>
       </c>
     </row>
@@ -20879,7 +20977,7 @@
       </c>
       <c r="B527" t="inlineStr">
         <is>
-          <t>eegconformer_t3</t>
+          <t>eegconformer_t2</t>
         </is>
       </c>
       <c r="C527" t="inlineStr">
@@ -20894,7 +20992,7 @@
       </c>
       <c r="E527" t="inlineStr">
         <is>
-          <t>no row label for 'eegconformer_t3'</t>
+          <t>no row label for 'eegconformer_t2'</t>
         </is>
       </c>
     </row>
@@ -20906,7 +21004,7 @@
       </c>
       <c r="B528" t="inlineStr">
         <is>
-          <t>eegconformer_t4</t>
+          <t>eegconformer_t3</t>
         </is>
       </c>
       <c r="C528" t="inlineStr">
@@ -20921,7 +21019,7 @@
       </c>
       <c r="E528" t="inlineStr">
         <is>
-          <t>no row label for 'eegconformer_t4'</t>
+          <t>no row label for 'eegconformer_t3'</t>
         </is>
       </c>
     </row>
@@ -20933,27 +21031,22 @@
       </c>
       <c r="B529" t="inlineStr">
         <is>
-          <t>eegnet</t>
+          <t>eegconformer_t4</t>
         </is>
       </c>
       <c r="C529" t="inlineStr">
         <is>
-          <t>[0, 1, 2]</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D529" t="inlineStr">
         <is>
-          <t>filled</t>
+          <t>skipped</t>
         </is>
       </c>
       <c r="E529" t="inlineStr">
         <is>
-          <t>[实测 0.00M] auroc per-seed 0:0.7773, 1:0.7919, 2:0.7852</t>
-        </is>
-      </c>
-      <c r="F529" t="inlineStr">
-        <is>
-          <t>stopped_by=patience lr=0.001 batch_size=512 epochs=20 patience=8 eval_every_steps=200 loss=bce_with_logits grad_clip=1.0</t>
+          <t>no row label for 'eegconformer_t4'</t>
         </is>
       </c>
     </row>
@@ -20965,22 +21058,27 @@
       </c>
       <c r="B530" t="inlineStr">
         <is>
-          <t>eegnet_t1</t>
+          <t>eegnet</t>
         </is>
       </c>
       <c r="C530" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>[0, 1, 2]</t>
         </is>
       </c>
       <c r="D530" t="inlineStr">
         <is>
-          <t>skipped</t>
+          <t>filled</t>
         </is>
       </c>
       <c r="E530" t="inlineStr">
         <is>
-          <t>no row label for 'eegnet_t1'</t>
+          <t>[实测 0.00M] auroc per-seed 0:0.7773, 1:0.7919, 2:0.7852</t>
+        </is>
+      </c>
+      <c r="F530" t="inlineStr">
+        <is>
+          <t>stopped_by=patience lr=0.001 batch_size=512 epochs=20 patience=8 eval_every_steps=200 loss=bce_with_logits grad_clip=1.0</t>
         </is>
       </c>
     </row>
@@ -20992,7 +21090,7 @@
       </c>
       <c r="B531" t="inlineStr">
         <is>
-          <t>eegnet_t2</t>
+          <t>eegnet_t1</t>
         </is>
       </c>
       <c r="C531" t="inlineStr">
@@ -21007,7 +21105,7 @@
       </c>
       <c r="E531" t="inlineStr">
         <is>
-          <t>no row label for 'eegnet_t2'</t>
+          <t>no row label for 'eegnet_t1'</t>
         </is>
       </c>
     </row>
@@ -21019,7 +21117,7 @@
       </c>
       <c r="B532" t="inlineStr">
         <is>
-          <t>eegnet_t3</t>
+          <t>eegnet_t2</t>
         </is>
       </c>
       <c r="C532" t="inlineStr">
@@ -21034,7 +21132,7 @@
       </c>
       <c r="E532" t="inlineStr">
         <is>
-          <t>no row label for 'eegnet_t3'</t>
+          <t>no row label for 'eegnet_t2'</t>
         </is>
       </c>
     </row>
@@ -21046,7 +21144,7 @@
       </c>
       <c r="B533" t="inlineStr">
         <is>
-          <t>eegnet_t4</t>
+          <t>eegnet_t3</t>
         </is>
       </c>
       <c r="C533" t="inlineStr">
@@ -21061,7 +21159,7 @@
       </c>
       <c r="E533" t="inlineStr">
         <is>
-          <t>no row label for 'eegnet_t4'</t>
+          <t>no row label for 'eegnet_t3'</t>
         </is>
       </c>
     </row>
@@ -21073,27 +21171,22 @@
       </c>
       <c r="B534" t="inlineStr">
         <is>
-          <t>eegpt_pretrained</t>
+          <t>eegnet_t4</t>
         </is>
       </c>
       <c r="C534" t="inlineStr">
         <is>
-          <t>[0, 1, 2]</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D534" t="inlineStr">
         <is>
-          <t>filled</t>
+          <t>skipped</t>
         </is>
       </c>
       <c r="E534" t="inlineStr">
         <is>
-          <t>[实测 25.69M] auroc per-seed 0:0.7150, 1:0.7690, 2:0.7486</t>
-        </is>
-      </c>
-      <c r="F534" t="inlineStr">
-        <is>
-          <t>stopped_by=patience lr=0.0004 batch_size=32 epochs=40 patience=10 eval_every_steps=500 loss=bce_with_logits</t>
+          <t>no row label for 'eegnet_t4'</t>
         </is>
       </c>
     </row>
@@ -21105,7 +21198,7 @@
       </c>
       <c r="B535" t="inlineStr">
         <is>
-          <t>eegpt_scratch</t>
+          <t>eegpt_pretrained</t>
         </is>
       </c>
       <c r="C535" t="inlineStr">
@@ -21120,7 +21213,7 @@
       </c>
       <c r="E535" t="inlineStr">
         <is>
-          <t>[实测 25.69M] auroc per-seed 0:0.7626, 1:0.8048, 2:0.7904</t>
+          <t>[实测 25.69M] auroc per-seed 0:0.7150, 1:0.7690, 2:0.7486</t>
         </is>
       </c>
       <c r="F535" t="inlineStr">
@@ -21137,7 +21230,7 @@
       </c>
       <c r="B536" t="inlineStr">
         <is>
-          <t>feat_best</t>
+          <t>eegpt_scratch</t>
         </is>
       </c>
       <c r="C536" t="inlineStr">
@@ -21152,12 +21245,12 @@
       </c>
       <c r="E536" t="inlineStr">
         <is>
-          <t>[实测 0.00M] auroc per-seed 0:0.5919, 1:0.5919, 2:0.5919</t>
+          <t>[实测 25.69M] auroc per-seed 0:0.7626, 1:0.8048, 2:0.7904</t>
         </is>
       </c>
       <c r="F536" t="inlineStr">
         <is>
-          <t>stopped_by=closed-form epochs=1 loss=closed-form</t>
+          <t>stopped_by=patience lr=0.0004 batch_size=32 epochs=40 patience=10 eval_every_steps=500 loss=bce_with_logits</t>
         </is>
       </c>
     </row>
@@ -21169,7 +21262,7 @@
       </c>
       <c r="B537" t="inlineStr">
         <is>
-          <t>ffcl</t>
+          <t>feat_best</t>
         </is>
       </c>
       <c r="C537" t="inlineStr">
@@ -21184,12 +21277,12 @@
       </c>
       <c r="E537" t="inlineStr">
         <is>
-          <t>[实测 2.46M] auroc per-seed 0:0.6875, 1:0.6509, 2:0.5837</t>
+          <t>[实测 0.00M] auroc per-seed 0:0.5919, 1:0.5919, 2:0.5919</t>
         </is>
       </c>
       <c r="F537" t="inlineStr">
         <is>
-          <t>stopped_by=patience lr=0.001 batch_size=512 epochs=20 patience=8 eval_every_steps=200 loss=bce_with_logits</t>
+          <t>stopped_by=closed-form epochs=1 loss=closed-form</t>
         </is>
       </c>
     </row>
@@ -21201,7 +21294,7 @@
       </c>
       <c r="B538" t="inlineStr">
         <is>
-          <t>labram_pretrained</t>
+          <t>ffcl</t>
         </is>
       </c>
       <c r="C538" t="inlineStr">
@@ -21216,12 +21309,12 @@
       </c>
       <c r="E538" t="inlineStr">
         <is>
-          <t>[实测 5.82M] auroc per-seed 0:0.7884, 1:0.7561, 2:0.7885</t>
+          <t>[实测 2.46M] auroc per-seed 0:0.6875, 1:0.6509, 2:0.5837</t>
         </is>
       </c>
       <c r="F538" t="inlineStr">
         <is>
-          <t>stopped_by=patience lr=0.0005 batch_size=64 epochs=50 patience=10 eval_every_steps=0 loss=bce_with_logits loader_divisor=1.0</t>
+          <t>stopped_by=patience lr=0.001 batch_size=512 epochs=20 patience=8 eval_every_steps=200 loss=bce_with_logits</t>
         </is>
       </c>
     </row>
@@ -21233,7 +21326,7 @@
       </c>
       <c r="B539" t="inlineStr">
         <is>
-          <t>labram_scratch</t>
+          <t>labram_pretrained</t>
         </is>
       </c>
       <c r="C539" t="inlineStr">
@@ -21248,7 +21341,7 @@
       </c>
       <c r="E539" t="inlineStr">
         <is>
-          <t>[实测 5.82M] auroc per-seed 0:0.6618, 1:0.7646, 2:0.7295</t>
+          <t>[实测 5.82M] auroc per-seed 0:0.7884, 1:0.7561, 2:0.7885</t>
         </is>
       </c>
       <c r="F539" t="inlineStr">
@@ -21265,22 +21358,27 @@
       </c>
       <c r="B540" t="inlineStr">
         <is>
-          <t>paclock_duplex</t>
+          <t>labram_scratch</t>
         </is>
       </c>
       <c r="C540" t="inlineStr">
         <is>
-          <t>[0]</t>
+          <t>[0, 1, 2]</t>
         </is>
       </c>
       <c r="D540" t="inlineStr">
         <is>
-          <t>filled (single-seed, grey)</t>
+          <t>filled</t>
         </is>
       </c>
       <c r="E540" t="inlineStr">
         <is>
-          <t>auroc 0.8052</t>
+          <t>[实测 5.82M] auroc per-seed 0:0.6618, 1:0.7646, 2:0.7295</t>
+        </is>
+      </c>
+      <c r="F540" t="inlineStr">
+        <is>
+          <t>stopped_by=patience lr=0.0005 batch_size=64 epochs=50 patience=10 eval_every_steps=0 loss=bce_with_logits loader_divisor=1.0</t>
         </is>
       </c>
     </row>
@@ -21292,22 +21390,22 @@
       </c>
       <c r="B541" t="inlineStr">
         <is>
-          <t>paclock_duplex_ptF</t>
+          <t>paclock_duplex</t>
         </is>
       </c>
       <c r="C541" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>[0]</t>
         </is>
       </c>
       <c r="D541" t="inlineStr">
         <is>
-          <t>skipped</t>
+          <t>filled (single-seed, grey)</t>
         </is>
       </c>
       <c r="E541" t="inlineStr">
         <is>
-          <t>row 'CroFreMo (预训练 v2-full)' not found</t>
+          <t>auroc 0.8052</t>
         </is>
       </c>
     </row>
@@ -21319,27 +21417,22 @@
       </c>
       <c r="B542" t="inlineStr">
         <is>
-          <t>reve_pretrained</t>
+          <t>paclock_duplex_ptF</t>
         </is>
       </c>
       <c r="C542" t="inlineStr">
         <is>
-          <t>[0, 1, 2]</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D542" t="inlineStr">
         <is>
-          <t>filled</t>
+          <t>skipped</t>
         </is>
       </c>
       <c r="E542" t="inlineStr">
         <is>
-          <t>[实测 69.46M] auroc per-seed 0:0.6801, 1:0.6785, 2:0.6342</t>
-        </is>
-      </c>
-      <c r="F542" t="inlineStr">
-        <is>
-          <t>stopped_by=patience lr=5e-05 batch_size=128 epochs=30 patience=10 eval_every_steps=0 loss=bce_with_logits grad_clip=1.0</t>
+          <t>row 'CroFreMo (预训练 v2-full)' not found</t>
         </is>
       </c>
     </row>
@@ -21351,22 +21444,27 @@
       </c>
       <c r="B543" t="inlineStr">
         <is>
-          <t>reve_pt_lrhalf</t>
+          <t>reve_pretrained</t>
         </is>
       </c>
       <c r="C543" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>[0, 1, 2]</t>
         </is>
       </c>
       <c r="D543" t="inlineStr">
         <is>
-          <t>skipped</t>
+          <t>filled</t>
         </is>
       </c>
       <c r="E543" t="inlineStr">
         <is>
-          <t>no row label for 'reve_pt_lrhalf'</t>
+          <t>[实测 69.46M] auroc per-seed 0:0.6801, 1:0.6785, 2:0.6342</t>
+        </is>
+      </c>
+      <c r="F543" t="inlineStr">
+        <is>
+          <t>stopped_by=patience lr=5e-05 batch_size=128 epochs=30 patience=10 eval_every_steps=0 loss=bce_with_logits grad_clip=1.0</t>
         </is>
       </c>
     </row>
@@ -21378,27 +21476,22 @@
       </c>
       <c r="B544" t="inlineStr">
         <is>
-          <t>sparcnet</t>
+          <t>reve_pt_lrhalf</t>
         </is>
       </c>
       <c r="C544" t="inlineStr">
         <is>
-          <t>[0, 1, 2]</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D544" t="inlineStr">
         <is>
-          <t>filled</t>
+          <t>skipped</t>
         </is>
       </c>
       <c r="E544" t="inlineStr">
         <is>
-          <t>[实测 1.14M] auroc per-seed 0:0.7312, 1:0.7414, 2:0.7209</t>
-        </is>
-      </c>
-      <c r="F544" t="inlineStr">
-        <is>
-          <t>stopped_by=patience lr=0.001 batch_size=512 epochs=20 patience=8 eval_every_steps=200 loss=bce_with_logits</t>
+          <t>no row label for 'reve_pt_lrhalf'</t>
         </is>
       </c>
     </row>
@@ -21410,7 +21503,7 @@
       </c>
       <c r="B545" t="inlineStr">
         <is>
-          <t>st_transformer</t>
+          <t>sparcnet</t>
         </is>
       </c>
       <c r="C545" t="inlineStr">
@@ -21425,7 +21518,7 @@
       </c>
       <c r="E545" t="inlineStr">
         <is>
-          <t>[实测 3.43M] auroc per-seed 0:0.5898, 1:0.5923, 2:0.6710</t>
+          <t>[实测 1.14M] auroc per-seed 0:0.7312, 1:0.7414, 2:0.7209</t>
         </is>
       </c>
       <c r="F545" t="inlineStr">
@@ -21442,7 +21535,7 @@
       </c>
       <c r="B546" t="inlineStr">
         <is>
-          <t>tfm_pretrained</t>
+          <t>st_transformer</t>
         </is>
       </c>
       <c r="C546" t="inlineStr">
@@ -21457,12 +21550,12 @@
       </c>
       <c r="E546" t="inlineStr">
         <is>
-          <t>[实测 1.89M] auroc per-seed 0:0.6440, 1:0.6183, 2:0.6142</t>
+          <t>[实测 3.43M] auroc per-seed 0:0.5898, 1:0.5923, 2:0.6710</t>
         </is>
       </c>
       <c r="F546" t="inlineStr">
         <is>
-          <t>stopped_by=patience lr=0.001 batch_size=512 epochs=7 patience=10 eval_every_steps=100 loss=bce_with_logits</t>
+          <t>stopped_by=patience lr=0.001 batch_size=512 epochs=20 patience=8 eval_every_steps=200 loss=bce_with_logits</t>
         </is>
       </c>
     </row>
@@ -21474,7 +21567,7 @@
       </c>
       <c r="B547" t="inlineStr">
         <is>
-          <t>tfm_scratch</t>
+          <t>tfm_pretrained</t>
         </is>
       </c>
       <c r="C547" t="inlineStr">
@@ -21489,7 +21582,7 @@
       </c>
       <c r="E547" t="inlineStr">
         <is>
-          <t>[实测 1.89M] auroc per-seed 0:0.5838, 1:0.6180, 2:0.6193</t>
+          <t>[实测 1.89M] auroc per-seed 0:0.6440, 1:0.6183, 2:0.6142</t>
         </is>
       </c>
       <c r="F547" t="inlineStr">
@@ -21501,27 +21594,32 @@
     <row r="548">
       <c r="A548" t="inlineStr">
         <is>
-          <t>tuev</t>
+          <t>tuep</t>
         </is>
       </c>
       <c r="B548" t="inlineStr">
         <is>
-          <t>biot_hop50</t>
+          <t>tfm_scratch</t>
         </is>
       </c>
       <c r="C548" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>[0, 1, 2]</t>
         </is>
       </c>
       <c r="D548" t="inlineStr">
         <is>
-          <t>skipped</t>
+          <t>filled</t>
         </is>
       </c>
       <c r="E548" t="inlineStr">
         <is>
-          <t>the workbook has no row for this variant</t>
+          <t>[实测 1.89M] auroc per-seed 0:0.5838, 1:0.6180, 2:0.6193</t>
+        </is>
+      </c>
+      <c r="F548" t="inlineStr">
+        <is>
+          <t>stopped_by=patience lr=0.001 batch_size=512 epochs=7 patience=10 eval_every_steps=100 loss=bce_with_logits</t>
         </is>
       </c>
     </row>
@@ -21533,27 +21631,22 @@
       </c>
       <c r="B549" t="inlineStr">
         <is>
-          <t>biot_prest16</t>
+          <t>biot_hop50</t>
         </is>
       </c>
       <c r="C549" t="inlineStr">
         <is>
-          <t>[0, 1, 2]</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D549" t="inlineStr">
         <is>
-          <t>filled</t>
+          <t>skipped</t>
         </is>
       </c>
       <c r="E549" t="inlineStr">
         <is>
-          <t>[实测 3.19M] cohen_kappa per-seed 0:0.5005, 1:0.5354, 2:0.5554</t>
-        </is>
-      </c>
-      <c r="F549" t="inlineStr">
-        <is>
-          <t>lr=0.001 batch_size=128 epochs=100 patience=5 eval_every_steps=0 loss=cross_entropy label_smoothing=0.0</t>
+          <t>the workbook has no row for this variant</t>
         </is>
       </c>
     </row>
@@ -21565,7 +21658,7 @@
       </c>
       <c r="B550" t="inlineStr">
         <is>
-          <t>biot_scratch</t>
+          <t>biot_prest16</t>
         </is>
       </c>
       <c r="C550" t="inlineStr">
@@ -21580,7 +21673,7 @@
       </c>
       <c r="E550" t="inlineStr">
         <is>
-          <t>[实测 3.19M] cohen_kappa per-seed 0:0.5039, 1:0.5425, 2:0.5508</t>
+          <t>[实测 3.19M] cohen_kappa per-seed 0:0.5005, 1:0.5354, 2:0.5554</t>
         </is>
       </c>
       <c r="F550" t="inlineStr">
@@ -21597,22 +21690,27 @@
       </c>
       <c r="B551" t="inlineStr">
         <is>
-          <t>biot_tok100</t>
+          <t>biot_scratch</t>
         </is>
       </c>
       <c r="C551" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>[0, 1, 2]</t>
         </is>
       </c>
       <c r="D551" t="inlineStr">
         <is>
-          <t>skipped</t>
+          <t>filled</t>
         </is>
       </c>
       <c r="E551" t="inlineStr">
         <is>
-          <t>the workbook has no row for this variant</t>
+          <t>[实测 3.19M] cohen_kappa per-seed 0:0.5039, 1:0.5425, 2:0.5508</t>
+        </is>
+      </c>
+      <c r="F551" t="inlineStr">
+        <is>
+          <t>lr=0.001 batch_size=128 epochs=100 patience=5 eval_every_steps=0 loss=cross_entropy label_smoothing=0.0</t>
         </is>
       </c>
     </row>
@@ -21624,7 +21722,7 @@
       </c>
       <c r="B552" t="inlineStr">
         <is>
-          <t>cand_base</t>
+          <t>biot_tok100</t>
         </is>
       </c>
       <c r="C552" t="inlineStr">
@@ -21651,7 +21749,7 @@
       </c>
       <c r="B553" t="inlineStr">
         <is>
-          <t>cand_dense</t>
+          <t>cand_base</t>
         </is>
       </c>
       <c r="C553" t="inlineStr">
@@ -21678,7 +21776,7 @@
       </c>
       <c r="B554" t="inlineStr">
         <is>
-          <t>cand_dense_lr1e5</t>
+          <t>cand_dense</t>
         </is>
       </c>
       <c r="C554" t="inlineStr">
@@ -21705,7 +21803,7 @@
       </c>
       <c r="B555" t="inlineStr">
         <is>
-          <t>cand_dense_lr3e5</t>
+          <t>cand_dense_lr1e5</t>
         </is>
       </c>
       <c r="C555" t="inlineStr">
@@ -21732,7 +21830,7 @@
       </c>
       <c r="B556" t="inlineStr">
         <is>
-          <t>cand_dense_patch100</t>
+          <t>cand_dense_lr3e5</t>
         </is>
       </c>
       <c r="C556" t="inlineStr">
@@ -21759,7 +21857,7 @@
       </c>
       <c r="B557" t="inlineStr">
         <is>
-          <t>cand_e60_base</t>
+          <t>cand_dense_patch100</t>
         </is>
       </c>
       <c r="C557" t="inlineStr">
@@ -21786,7 +21884,7 @@
       </c>
       <c r="B558" t="inlineStr">
         <is>
-          <t>cand_e60_patch100</t>
+          <t>cand_e60_base</t>
         </is>
       </c>
       <c r="C558" t="inlineStr">
@@ -21813,7 +21911,7 @@
       </c>
       <c r="B559" t="inlineStr">
         <is>
-          <t>cand_e60_size_base</t>
+          <t>cand_e60_patch100</t>
         </is>
       </c>
       <c r="C559" t="inlineStr">
@@ -21840,7 +21938,7 @@
       </c>
       <c r="B560" t="inlineStr">
         <is>
-          <t>cand_e60_size_large</t>
+          <t>cand_e60_size_base</t>
         </is>
       </c>
       <c r="C560" t="inlineStr">
@@ -21867,7 +21965,7 @@
       </c>
       <c r="B561" t="inlineStr">
         <is>
-          <t>cand_ms</t>
+          <t>cand_e60_size_large</t>
         </is>
       </c>
       <c r="C561" t="inlineStr">
@@ -21894,7 +21992,7 @@
       </c>
       <c r="B562" t="inlineStr">
         <is>
-          <t>cand_p100_large</t>
+          <t>cand_ms</t>
         </is>
       </c>
       <c r="C562" t="inlineStr">
@@ -21921,7 +22019,7 @@
       </c>
       <c r="B563" t="inlineStr">
         <is>
-          <t>cand_p50_win100</t>
+          <t>cand_p100_large</t>
         </is>
       </c>
       <c r="C563" t="inlineStr">
@@ -21948,7 +22046,7 @@
       </c>
       <c r="B564" t="inlineStr">
         <is>
-          <t>cand_p50_win200</t>
+          <t>cand_p50_win100</t>
         </is>
       </c>
       <c r="C564" t="inlineStr">
@@ -21975,7 +22073,7 @@
       </c>
       <c r="B565" t="inlineStr">
         <is>
-          <t>cand_pacwin200</t>
+          <t>cand_p50_win200</t>
         </is>
       </c>
       <c r="C565" t="inlineStr">
@@ -22002,7 +22100,7 @@
       </c>
       <c r="B566" t="inlineStr">
         <is>
-          <t>cand_patch100</t>
+          <t>cand_pacwin200</t>
         </is>
       </c>
       <c r="C566" t="inlineStr">
@@ -22029,7 +22127,7 @@
       </c>
       <c r="B567" t="inlineStr">
         <is>
-          <t>cand_patch50</t>
+          <t>cand_patch100</t>
         </is>
       </c>
       <c r="C567" t="inlineStr">
@@ -22056,7 +22154,7 @@
       </c>
       <c r="B568" t="inlineStr">
         <is>
-          <t>cbramod_pac</t>
+          <t>cand_patch50</t>
         </is>
       </c>
       <c r="C568" t="inlineStr">
@@ -22083,7 +22181,7 @@
       </c>
       <c r="B569" t="inlineStr">
         <is>
-          <t>cbramod_pacfe_pac</t>
+          <t>cbramod_pac</t>
         </is>
       </c>
       <c r="C569" t="inlineStr">
@@ -22098,7 +22196,7 @@
       </c>
       <c r="E569" t="inlineStr">
         <is>
-          <t>no row label for 'cbramod_pacfe_pac'</t>
+          <t>the workbook has no row for this variant</t>
         </is>
       </c>
     </row>
@@ -22110,7 +22208,7 @@
       </c>
       <c r="B570" t="inlineStr">
         <is>
-          <t>cbramod_pacfe_raw</t>
+          <t>cbramod_pacfe_pac</t>
         </is>
       </c>
       <c r="C570" t="inlineStr">
@@ -22125,7 +22223,7 @@
       </c>
       <c r="E570" t="inlineStr">
         <is>
-          <t>no row label for 'cbramod_pacfe_raw'</t>
+          <t>no row label for 'cbramod_pacfe_pac'</t>
         </is>
       </c>
     </row>
@@ -22137,7 +22235,7 @@
       </c>
       <c r="B571" t="inlineStr">
         <is>
-          <t>cbramod_paclockfe</t>
+          <t>cbramod_pacfe_raw</t>
         </is>
       </c>
       <c r="C571" t="inlineStr">
@@ -22152,7 +22250,7 @@
       </c>
       <c r="E571" t="inlineStr">
         <is>
-          <t>no row label for 'cbramod_paclockfe'</t>
+          <t>no row label for 'cbramod_pacfe_raw'</t>
         </is>
       </c>
     </row>
@@ -22164,27 +22262,22 @@
       </c>
       <c r="B572" t="inlineStr">
         <is>
-          <t>cbramod_pretrained</t>
+          <t>cbramod_paclockfe</t>
         </is>
       </c>
       <c r="C572" t="inlineStr">
         <is>
-          <t>[0, 1, 2]</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D572" t="inlineStr">
         <is>
-          <t>filled</t>
+          <t>skipped</t>
         </is>
       </c>
       <c r="E572" t="inlineStr">
         <is>
-          <t>[实测 17.85M] cohen_kappa per-seed 0:0.6199, 1:0.6566, 2:0.6582</t>
-        </is>
-      </c>
-      <c r="F572" t="inlineStr">
-        <is>
-          <t>lr=0.0001 batch_size=64 epochs=50 patience=0 eval_every_steps=0 loss=cross_entropy label_smoothing=0.1 grad_clip=1.0 multi_lr=True</t>
+          <t>no row label for 'cbramod_paclockfe'</t>
         </is>
       </c>
     </row>
@@ -22196,7 +22289,7 @@
       </c>
       <c r="B573" t="inlineStr">
         <is>
-          <t>cbramod_scratch</t>
+          <t>cbramod_pretrained</t>
         </is>
       </c>
       <c r="C573" t="inlineStr">
@@ -22211,7 +22304,7 @@
       </c>
       <c r="E573" t="inlineStr">
         <is>
-          <t>[实测 17.85M] cohen_kappa per-seed 0:0.5755, 1:0.5366, 2:0.5794</t>
+          <t>[实测 17.85M] cohen_kappa per-seed 0:0.6199, 1:0.6566, 2:0.6582</t>
         </is>
       </c>
       <c r="F573" t="inlineStr">
@@ -22228,7 +22321,7 @@
       </c>
       <c r="B574" t="inlineStr">
         <is>
-          <t>cnn_transformer</t>
+          <t>cbramod_scratch</t>
         </is>
       </c>
       <c r="C574" t="inlineStr">
@@ -22243,12 +22336,12 @@
       </c>
       <c r="E574" t="inlineStr">
         <is>
-          <t>[实测 3.16M] cohen_kappa per-seed 0:0.4987, 1:0.2779, 2:0.4527  [seed spread 23% -- mean is a weak summary]</t>
+          <t>[实测 17.85M] cohen_kappa per-seed 0:0.5755, 1:0.5366, 2:0.5794</t>
         </is>
       </c>
       <c r="F574" t="inlineStr">
         <is>
-          <t>lr=0.001 batch_size=512 epochs=100 patience=15 eval_every_steps=0 loss=cross_entropy label_smoothing=0.1</t>
+          <t>lr=0.0001 batch_size=64 epochs=50 patience=0 eval_every_steps=0 loss=cross_entropy label_smoothing=0.1 grad_clip=1.0 multi_lr=True</t>
         </is>
       </c>
     </row>
@@ -22260,7 +22353,7 @@
       </c>
       <c r="B575" t="inlineStr">
         <is>
-          <t>contrawr</t>
+          <t>cnn_transformer</t>
         </is>
       </c>
       <c r="C575" t="inlineStr">
@@ -22275,7 +22368,7 @@
       </c>
       <c r="E575" t="inlineStr">
         <is>
-          <t>[实测 1.57M] cohen_kappa per-seed 0:0.4410, 1:0.4849, 2:0.2969  [seed spread 20% -- mean is a weak summary]</t>
+          <t>[实测 3.16M] cohen_kappa per-seed 0:0.4987, 1:0.2779, 2:0.4527  [seed spread 23% -- mean is a weak summary]</t>
         </is>
       </c>
       <c r="F575" t="inlineStr">
@@ -22292,7 +22385,7 @@
       </c>
       <c r="B576" t="inlineStr">
         <is>
-          <t>csbrain_pretrained</t>
+          <t>contrawr</t>
         </is>
       </c>
       <c r="C576" t="inlineStr">
@@ -22307,12 +22400,12 @@
       </c>
       <c r="E576" t="inlineStr">
         <is>
-          <t>[实测 25.06M] cohen_kappa per-seed 0:0.6132, 1:0.6922, 2:0.6027</t>
+          <t>[实测 1.57M] cohen_kappa per-seed 0:0.4410, 1:0.4849, 2:0.2969  [seed spread 20% -- mean is a weak summary]</t>
         </is>
       </c>
       <c r="F576" t="inlineStr">
         <is>
-          <t>stopped_by=patience lr=0.0001 batch_size=64 epochs=50 patience=10 eval_every_steps=0 loss=cross_entropy label_smoothing=0.1 grad_clip=1.0</t>
+          <t>lr=0.001 batch_size=512 epochs=100 patience=15 eval_every_steps=0 loss=cross_entropy label_smoothing=0.1</t>
         </is>
       </c>
     </row>
@@ -22324,22 +22417,27 @@
       </c>
       <c r="B577" t="inlineStr">
         <is>
-          <t>csbrain_pretrained_ls0</t>
+          <t>csbrain_pretrained</t>
         </is>
       </c>
       <c r="C577" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>[0, 1, 2]</t>
         </is>
       </c>
       <c r="D577" t="inlineStr">
         <is>
-          <t>skipped</t>
+          <t>filled</t>
         </is>
       </c>
       <c r="E577" t="inlineStr">
         <is>
-          <t>no row label for 'csbrain_pretrained_ls0'</t>
+          <t>[实测 25.06M] cohen_kappa per-seed 0:0.6132, 1:0.6922, 2:0.6027</t>
+        </is>
+      </c>
+      <c r="F577" t="inlineStr">
+        <is>
+          <t>stopped_by=patience lr=0.0001 batch_size=64 epochs=50 patience=10 eval_every_steps=0 loss=cross_entropy label_smoothing=0.1 grad_clip=1.0</t>
         </is>
       </c>
     </row>
@@ -22351,27 +22449,22 @@
       </c>
       <c r="B578" t="inlineStr">
         <is>
-          <t>eegconformer</t>
+          <t>csbrain_pretrained_ls0</t>
         </is>
       </c>
       <c r="C578" t="inlineStr">
         <is>
-          <t>[0, 1, 2]</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D578" t="inlineStr">
         <is>
-          <t>filled</t>
+          <t>skipped</t>
         </is>
       </c>
       <c r="E578" t="inlineStr">
         <is>
-          <t>[实测 0.78M] cohen_kappa per-seed 0:0.4524, 1:0.4596, 2:0.4525</t>
-        </is>
-      </c>
-      <c r="F578" t="inlineStr">
-        <is>
-          <t>stopped_by=patience lr=0.001 batch_size=128 epochs=100 patience=15 eval_every_steps=0 loss=cross_entropy label_smoothing=0.1 grad_clip=1.0</t>
+          <t>no row label for 'csbrain_pretrained_ls0'</t>
         </is>
       </c>
     </row>
@@ -22383,22 +22476,27 @@
       </c>
       <c r="B579" t="inlineStr">
         <is>
-          <t>eegconformer_t1</t>
+          <t>eegconformer</t>
         </is>
       </c>
       <c r="C579" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>[0, 1, 2]</t>
         </is>
       </c>
       <c r="D579" t="inlineStr">
         <is>
-          <t>skipped</t>
+          <t>filled</t>
         </is>
       </c>
       <c r="E579" t="inlineStr">
         <is>
-          <t>no row label for 'eegconformer_t1'</t>
+          <t>[实测 0.78M] cohen_kappa per-seed 0:0.4524, 1:0.4596, 2:0.4525</t>
+        </is>
+      </c>
+      <c r="F579" t="inlineStr">
+        <is>
+          <t>stopped_by=patience lr=0.001 batch_size=128 epochs=100 patience=15 eval_every_steps=0 loss=cross_entropy label_smoothing=0.1 grad_clip=1.0</t>
         </is>
       </c>
     </row>
@@ -22410,7 +22508,7 @@
       </c>
       <c r="B580" t="inlineStr">
         <is>
-          <t>eegconformer_t2</t>
+          <t>eegconformer_t1</t>
         </is>
       </c>
       <c r="C580" t="inlineStr">
@@ -22425,7 +22523,7 @@
       </c>
       <c r="E580" t="inlineStr">
         <is>
-          <t>no row label for 'eegconformer_t2'</t>
+          <t>no row label for 'eegconformer_t1'</t>
         </is>
       </c>
     </row>
@@ -22437,7 +22535,7 @@
       </c>
       <c r="B581" t="inlineStr">
         <is>
-          <t>eegconformer_t3</t>
+          <t>eegconformer_t2</t>
         </is>
       </c>
       <c r="C581" t="inlineStr">
@@ -22452,7 +22550,7 @@
       </c>
       <c r="E581" t="inlineStr">
         <is>
-          <t>no row label for 'eegconformer_t3'</t>
+          <t>no row label for 'eegconformer_t2'</t>
         </is>
       </c>
     </row>
@@ -22464,7 +22562,7 @@
       </c>
       <c r="B582" t="inlineStr">
         <is>
-          <t>eegconformer_t4</t>
+          <t>eegconformer_t3</t>
         </is>
       </c>
       <c r="C582" t="inlineStr">
@@ -22479,7 +22577,7 @@
       </c>
       <c r="E582" t="inlineStr">
         <is>
-          <t>no row label for 'eegconformer_t4'</t>
+          <t>no row label for 'eegconformer_t3'</t>
         </is>
       </c>
     </row>
@@ -22491,27 +22589,22 @@
       </c>
       <c r="B583" t="inlineStr">
         <is>
-          <t>eegnet</t>
+          <t>eegconformer_t4</t>
         </is>
       </c>
       <c r="C583" t="inlineStr">
         <is>
-          <t>[0, 1, 2]</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D583" t="inlineStr">
         <is>
-          <t>filled</t>
+          <t>skipped</t>
         </is>
       </c>
       <c r="E583" t="inlineStr">
         <is>
-          <t>[实测 0.00M] cohen_kappa per-seed 0:0.5836, 1:0.4223, 2:0.4306  [seed spread 15% -- mean is a weak summary]</t>
-        </is>
-      </c>
-      <c r="F583" t="inlineStr">
-        <is>
-          <t>stopped_by=patience lr=0.001 batch_size=512 epochs=100 patience=15 eval_every_steps=0 loss=cross_entropy label_smoothing=0.1 grad_clip=1.0</t>
+          <t>no row label for 'eegconformer_t4'</t>
         </is>
       </c>
     </row>
@@ -22523,22 +22616,27 @@
       </c>
       <c r="B584" t="inlineStr">
         <is>
-          <t>eegnet_t1</t>
+          <t>eegnet</t>
         </is>
       </c>
       <c r="C584" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>[0, 1, 2]</t>
         </is>
       </c>
       <c r="D584" t="inlineStr">
         <is>
-          <t>skipped</t>
+          <t>filled</t>
         </is>
       </c>
       <c r="E584" t="inlineStr">
         <is>
-          <t>no row label for 'eegnet_t1'</t>
+          <t>[实测 0.00M] cohen_kappa per-seed 0:0.5836, 1:0.4223, 2:0.4306  [seed spread 15% -- mean is a weak summary]</t>
+        </is>
+      </c>
+      <c r="F584" t="inlineStr">
+        <is>
+          <t>stopped_by=patience lr=0.001 batch_size=512 epochs=100 patience=15 eval_every_steps=0 loss=cross_entropy label_smoothing=0.1 grad_clip=1.0</t>
         </is>
       </c>
     </row>
@@ -22550,7 +22648,7 @@
       </c>
       <c r="B585" t="inlineStr">
         <is>
-          <t>eegnet_t2</t>
+          <t>eegnet_t1</t>
         </is>
       </c>
       <c r="C585" t="inlineStr">
@@ -22565,7 +22663,7 @@
       </c>
       <c r="E585" t="inlineStr">
         <is>
-          <t>no row label for 'eegnet_t2'</t>
+          <t>no row label for 'eegnet_t1'</t>
         </is>
       </c>
     </row>
@@ -22577,7 +22675,7 @@
       </c>
       <c r="B586" t="inlineStr">
         <is>
-          <t>eegnet_t3</t>
+          <t>eegnet_t2</t>
         </is>
       </c>
       <c r="C586" t="inlineStr">
@@ -22592,7 +22690,7 @@
       </c>
       <c r="E586" t="inlineStr">
         <is>
-          <t>no row label for 'eegnet_t3'</t>
+          <t>no row label for 'eegnet_t2'</t>
         </is>
       </c>
     </row>
@@ -22604,7 +22702,7 @@
       </c>
       <c r="B587" t="inlineStr">
         <is>
-          <t>eegnet_t4</t>
+          <t>eegnet_t3</t>
         </is>
       </c>
       <c r="C587" t="inlineStr">
@@ -22619,7 +22717,7 @@
       </c>
       <c r="E587" t="inlineStr">
         <is>
-          <t>no row label for 'eegnet_t4'</t>
+          <t>no row label for 'eegnet_t3'</t>
         </is>
       </c>
     </row>
@@ -22631,27 +22729,22 @@
       </c>
       <c r="B588" t="inlineStr">
         <is>
-          <t>eegpt_pretrained</t>
+          <t>eegnet_t4</t>
         </is>
       </c>
       <c r="C588" t="inlineStr">
         <is>
-          <t>[0, 1, 2]</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D588" t="inlineStr">
         <is>
-          <t>filled</t>
+          <t>skipped</t>
         </is>
       </c>
       <c r="E588" t="inlineStr">
         <is>
-          <t>[实测 25.69M] cohen_kappa per-seed 0:0.5311, 1:0.6095, 2:0.5803</t>
-        </is>
-      </c>
-      <c r="F588" t="inlineStr">
-        <is>
-          <t>lr=0.0004 batch_size=32 epochs=40 patience=10 eval_every_steps=0 loss=cross_entropy</t>
+          <t>no row label for 'eegnet_t4'</t>
         </is>
       </c>
     </row>
@@ -22663,7 +22756,7 @@
       </c>
       <c r="B589" t="inlineStr">
         <is>
-          <t>feat_best</t>
+          <t>eegpt_pretrained</t>
         </is>
       </c>
       <c r="C589" t="inlineStr">
@@ -22678,12 +22771,12 @@
       </c>
       <c r="E589" t="inlineStr">
         <is>
-          <t>[实测 0.00M] cohen_kappa per-seed 0:0.5049, 1:0.5049, 2:0.5049</t>
+          <t>[实测 25.69M] cohen_kappa per-seed 0:0.5311, 1:0.6095, 2:0.5803</t>
         </is>
       </c>
       <c r="F589" t="inlineStr">
         <is>
-          <t>stopped_by=closed-form epochs=1 loss=closed-form</t>
+          <t>lr=0.0004 batch_size=32 epochs=40 patience=10 eval_every_steps=0 loss=cross_entropy</t>
         </is>
       </c>
     </row>
@@ -22695,7 +22788,7 @@
       </c>
       <c r="B590" t="inlineStr">
         <is>
-          <t>ffcl</t>
+          <t>feat_best</t>
         </is>
       </c>
       <c r="C590" t="inlineStr">
@@ -22710,12 +22803,12 @@
       </c>
       <c r="E590" t="inlineStr">
         <is>
-          <t>[实测 2.42M] cohen_kappa per-seed 0:0.5069, 1:0.4432, 2:0.4827</t>
+          <t>[实测 0.00M] cohen_kappa per-seed 0:0.5049, 1:0.5049, 2:0.5049</t>
         </is>
       </c>
       <c r="F590" t="inlineStr">
         <is>
-          <t>lr=0.001 batch_size=512 epochs=100 patience=15 eval_every_steps=0 loss=cross_entropy label_smoothing=0.1</t>
+          <t>stopped_by=closed-form epochs=1 loss=closed-form</t>
         </is>
       </c>
     </row>
@@ -22727,7 +22820,7 @@
       </c>
       <c r="B591" t="inlineStr">
         <is>
-          <t>labram_pretrained</t>
+          <t>ffcl</t>
         </is>
       </c>
       <c r="C591" t="inlineStr">
@@ -22742,12 +22835,12 @@
       </c>
       <c r="E591" t="inlineStr">
         <is>
-          <t>[实测 5.82M] cohen_kappa per-seed 0:0.6012, 1:0.5989, 2:0.5951</t>
+          <t>[实测 2.42M] cohen_kappa per-seed 0:0.5069, 1:0.4432, 2:0.4827</t>
         </is>
       </c>
       <c r="F591" t="inlineStr">
         <is>
-          <t>stopped_by=patience lr=0.0005 batch_size=64 epochs=50 patience=10 eval_every_steps=100 loss=cross_entropy label_smoothing=0.1</t>
+          <t>lr=0.001 batch_size=512 epochs=100 patience=15 eval_every_steps=0 loss=cross_entropy label_smoothing=0.1</t>
         </is>
       </c>
     </row>
@@ -22759,7 +22852,7 @@
       </c>
       <c r="B592" t="inlineStr">
         <is>
-          <t>labram_scratch</t>
+          <t>labram_pretrained</t>
         </is>
       </c>
       <c r="C592" t="inlineStr">
@@ -22774,12 +22867,12 @@
       </c>
       <c r="E592" t="inlineStr">
         <is>
-          <t>[实测 5.82M] cohen_kappa per-seed 0:0.3624, 1:0.3727, 2:0.3801</t>
+          <t>[实测 5.82M] cohen_kappa per-seed 0:0.6012, 1:0.5989, 2:0.5951</t>
         </is>
       </c>
       <c r="F592" t="inlineStr">
         <is>
-          <t>lr=0.0005 batch_size=64 epochs=50 patience=10 eval_every_steps=0 loss=cross_entropy label_smoothing=0.1</t>
+          <t>stopped_by=patience lr=0.0005 batch_size=64 epochs=50 patience=10 eval_every_steps=100 loss=cross_entropy label_smoothing=0.1</t>
         </is>
       </c>
     </row>
@@ -22791,22 +22884,27 @@
       </c>
       <c r="B593" t="inlineStr">
         <is>
-          <t>paclock</t>
+          <t>labram_scratch</t>
         </is>
       </c>
       <c r="C593" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>[0, 1, 2]</t>
         </is>
       </c>
       <c r="D593" t="inlineStr">
         <is>
-          <t>skipped</t>
+          <t>filled</t>
         </is>
       </c>
       <c r="E593" t="inlineStr">
         <is>
-          <t>no row label for 'paclock'</t>
+          <t>[实测 5.82M] cohen_kappa per-seed 0:0.3624, 1:0.3727, 2:0.3801</t>
+        </is>
+      </c>
+      <c r="F593" t="inlineStr">
+        <is>
+          <t>lr=0.0005 batch_size=64 epochs=50 patience=10 eval_every_steps=0 loss=cross_entropy label_smoothing=0.1</t>
         </is>
       </c>
     </row>
@@ -22818,22 +22916,22 @@
       </c>
       <c r="B594" t="inlineStr">
         <is>
-          <t>paclock_duplex</t>
+          <t>paclock</t>
         </is>
       </c>
       <c r="C594" t="inlineStr">
         <is>
-          <t>[0]</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D594" t="inlineStr">
         <is>
-          <t>filled (single-seed, grey)</t>
+          <t>skipped</t>
         </is>
       </c>
       <c r="E594" t="inlineStr">
         <is>
-          <t>cohen_kappa 0.7094</t>
+          <t>no row label for 'paclock'</t>
         </is>
       </c>
     </row>
@@ -22845,22 +22943,22 @@
       </c>
       <c r="B595" t="inlineStr">
         <is>
-          <t>paclock_duplex_ms</t>
+          <t>paclock_duplex</t>
         </is>
       </c>
       <c r="C595" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>[0]</t>
         </is>
       </c>
       <c r="D595" t="inlineStr">
         <is>
-          <t>skipped</t>
+          <t>filled (single-seed, grey)</t>
         </is>
       </c>
       <c r="E595" t="inlineStr">
         <is>
-          <t>no row label for 'paclock_duplex_ms'</t>
+          <t>cohen_kappa 0.7094</t>
         </is>
       </c>
     </row>
@@ -22872,7 +22970,7 @@
       </c>
       <c r="B596" t="inlineStr">
         <is>
-          <t>paclock_duplex_pt</t>
+          <t>paclock_duplex_ms</t>
         </is>
       </c>
       <c r="C596" t="inlineStr">
@@ -22887,7 +22985,7 @@
       </c>
       <c r="E596" t="inlineStr">
         <is>
-          <t>row 'PACLock (duplex, pretrained)' not found</t>
+          <t>no row label for 'paclock_duplex_ms'</t>
         </is>
       </c>
     </row>
@@ -22899,22 +22997,22 @@
       </c>
       <c r="B597" t="inlineStr">
         <is>
-          <t>paclock_duplex_pt2</t>
+          <t>paclock_duplex_pt</t>
         </is>
       </c>
       <c r="C597" t="inlineStr">
         <is>
-          <t>[0]</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D597" t="inlineStr">
         <is>
-          <t>filled (single-seed, grey)</t>
+          <t>skipped</t>
         </is>
       </c>
       <c r="E597" t="inlineStr">
         <is>
-          <t>cohen_kappa 0.6533</t>
+          <t>row 'PACLock (duplex, pretrained)' not found</t>
         </is>
       </c>
     </row>
@@ -22926,7 +23024,7 @@
       </c>
       <c r="B598" t="inlineStr">
         <is>
-          <t>paclock_duplex_pt3</t>
+          <t>paclock_duplex_pt2</t>
         </is>
       </c>
       <c r="C598" t="inlineStr">
@@ -22941,7 +23039,7 @@
       </c>
       <c r="E598" t="inlineStr">
         <is>
-          <t>cohen_kappa 0.6753</t>
+          <t>cohen_kappa 0.6533</t>
         </is>
       </c>
     </row>
@@ -22953,22 +23051,22 @@
       </c>
       <c r="B599" t="inlineStr">
         <is>
-          <t>paclock_duplex_ptF</t>
+          <t>paclock_duplex_pt3</t>
         </is>
       </c>
       <c r="C599" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>[0]</t>
         </is>
       </c>
       <c r="D599" t="inlineStr">
         <is>
-          <t>skipped</t>
+          <t>filled (single-seed, grey)</t>
         </is>
       </c>
       <c r="E599" t="inlineStr">
         <is>
-          <t>row 'CroFreMo (预训练 v2-full)' not found</t>
+          <t>cohen_kappa 0.6753</t>
         </is>
       </c>
     </row>
@@ -22980,7 +23078,7 @@
       </c>
       <c r="B600" t="inlineStr">
         <is>
-          <t>paclock_flagship</t>
+          <t>paclock_duplex_ptF</t>
         </is>
       </c>
       <c r="C600" t="inlineStr">
@@ -22995,7 +23093,7 @@
       </c>
       <c r="E600" t="inlineStr">
         <is>
-          <t>no row label for 'paclock_flagship'</t>
+          <t>row 'CroFreMo (预训练 v2-full)' not found</t>
         </is>
       </c>
     </row>
@@ -23007,7 +23105,7 @@
       </c>
       <c r="B601" t="inlineStr">
         <is>
-          <t>paclock_ft_base_partial</t>
+          <t>paclock_flagship</t>
         </is>
       </c>
       <c r="C601" t="inlineStr">
@@ -23022,7 +23120,7 @@
       </c>
       <c r="E601" t="inlineStr">
         <is>
-          <t>no row label for 'paclock_ft_base_partial'</t>
+          <t>no row label for 'paclock_flagship'</t>
         </is>
       </c>
     </row>
@@ -23034,7 +23132,7 @@
       </c>
       <c r="B602" t="inlineStr">
         <is>
-          <t>paclock_ft_base_v2_v2</t>
+          <t>paclock_ft_base_partial</t>
         </is>
       </c>
       <c r="C602" t="inlineStr">
@@ -23049,7 +23147,7 @@
       </c>
       <c r="E602" t="inlineStr">
         <is>
-          <t>no row label for 'paclock_ft_base_v2_v2'</t>
+          <t>no row label for 'paclock_ft_base_partial'</t>
         </is>
       </c>
     </row>
@@ -23061,7 +23159,7 @@
       </c>
       <c r="B603" t="inlineStr">
         <is>
-          <t>paclock_fuse</t>
+          <t>paclock_ft_base_v2_v2</t>
         </is>
       </c>
       <c r="C603" t="inlineStr">
@@ -23076,7 +23174,7 @@
       </c>
       <c r="E603" t="inlineStr">
         <is>
-          <t>no row label for 'paclock_fuse'</t>
+          <t>no row label for 'paclock_ft_base_v2_v2'</t>
         </is>
       </c>
     </row>
@@ -23088,7 +23186,7 @@
       </c>
       <c r="B604" t="inlineStr">
         <is>
-          <t>paclock_fusegate</t>
+          <t>paclock_fuse</t>
         </is>
       </c>
       <c r="C604" t="inlineStr">
@@ -23103,7 +23201,7 @@
       </c>
       <c r="E604" t="inlineStr">
         <is>
-          <t>no row label for 'paclock_fusegate'</t>
+          <t>no row label for 'paclock_fuse'</t>
         </is>
       </c>
     </row>
@@ -23115,7 +23213,7 @@
       </c>
       <c r="B605" t="inlineStr">
         <is>
-          <t>paclock_h12</t>
+          <t>paclock_fusegate</t>
         </is>
       </c>
       <c r="C605" t="inlineStr">
@@ -23130,7 +23228,7 @@
       </c>
       <c r="E605" t="inlineStr">
         <is>
-          <t>no row label for 'paclock_h12'</t>
+          <t>no row label for 'paclock_fusegate'</t>
         </is>
       </c>
     </row>
@@ -23142,7 +23240,7 @@
       </c>
       <c r="B606" t="inlineStr">
         <is>
-          <t>paclock_h1stem</t>
+          <t>paclock_h12</t>
         </is>
       </c>
       <c r="C606" t="inlineStr">
@@ -23157,7 +23255,7 @@
       </c>
       <c r="E606" t="inlineStr">
         <is>
-          <t>no row label for 'paclock_h1stem'</t>
+          <t>no row label for 'paclock_h12'</t>
         </is>
       </c>
     </row>
@@ -23169,7 +23267,7 @@
       </c>
       <c r="B607" t="inlineStr">
         <is>
-          <t>paclock_h2mont</t>
+          <t>paclock_h1stem</t>
         </is>
       </c>
       <c r="C607" t="inlineStr">
@@ -23184,7 +23282,7 @@
       </c>
       <c r="E607" t="inlineStr">
         <is>
-          <t>no row label for 'paclock_h2mont'</t>
+          <t>no row label for 'paclock_h1stem'</t>
         </is>
       </c>
     </row>
@@ -23196,7 +23294,7 @@
       </c>
       <c r="B608" t="inlineStr">
         <is>
-          <t>paclock_hybrid</t>
+          <t>paclock_h2mont</t>
         </is>
       </c>
       <c r="C608" t="inlineStr">
@@ -23211,7 +23309,7 @@
       </c>
       <c r="E608" t="inlineStr">
         <is>
-          <t>no row label for 'paclock_hybrid'</t>
+          <t>no row label for 'paclock_h2mont'</t>
         </is>
       </c>
     </row>
@@ -23223,7 +23321,7 @@
       </c>
       <c r="B609" t="inlineStr">
         <is>
-          <t>paclock_hybrid_attn</t>
+          <t>paclock_hybrid</t>
         </is>
       </c>
       <c r="C609" t="inlineStr">
@@ -23238,7 +23336,7 @@
       </c>
       <c r="E609" t="inlineStr">
         <is>
-          <t>no row label for 'paclock_hybrid_attn'</t>
+          <t>no row label for 'paclock_hybrid'</t>
         </is>
       </c>
     </row>
@@ -23250,7 +23348,7 @@
       </c>
       <c r="B610" t="inlineStr">
         <is>
-          <t>paclock_hybrid_gate</t>
+          <t>paclock_hybrid_attn</t>
         </is>
       </c>
       <c r="C610" t="inlineStr">
@@ -23265,7 +23363,7 @@
       </c>
       <c r="E610" t="inlineStr">
         <is>
-          <t>no row label for 'paclock_hybrid_gate'</t>
+          <t>no row label for 'paclock_hybrid_attn'</t>
         </is>
       </c>
     </row>
@@ -23277,7 +23375,7 @@
       </c>
       <c r="B611" t="inlineStr">
         <is>
-          <t>paclock_nb16</t>
+          <t>paclock_hybrid_gate</t>
         </is>
       </c>
       <c r="C611" t="inlineStr">
@@ -23292,7 +23390,7 @@
       </c>
       <c r="E611" t="inlineStr">
         <is>
-          <t>no row label for 'paclock_nb16'</t>
+          <t>no row label for 'paclock_hybrid_gate'</t>
         </is>
       </c>
     </row>
@@ -23304,7 +23402,7 @@
       </c>
       <c r="B612" t="inlineStr">
         <is>
-          <t>paclock_pac</t>
+          <t>paclock_nb16</t>
         </is>
       </c>
       <c r="C612" t="inlineStr">
@@ -23319,7 +23417,7 @@
       </c>
       <c r="E612" t="inlineStr">
         <is>
-          <t>the workbook has no row for this variant</t>
+          <t>no row label for 'paclock_nb16'</t>
         </is>
       </c>
     </row>
@@ -23331,7 +23429,7 @@
       </c>
       <c r="B613" t="inlineStr">
         <is>
-          <t>paclock_pilot_frozen</t>
+          <t>paclock_pac</t>
         </is>
       </c>
       <c r="C613" t="inlineStr">
@@ -23358,7 +23456,7 @@
       </c>
       <c r="B614" t="inlineStr">
         <is>
-          <t>paclock_pilot_unfiltered</t>
+          <t>paclock_pilot_frozen</t>
         </is>
       </c>
       <c r="C614" t="inlineStr">
@@ -23385,22 +23483,22 @@
       </c>
       <c r="B615" t="inlineStr">
         <is>
-          <t>paclock_probe_rand</t>
+          <t>paclock_pilot_unfiltered</t>
         </is>
       </c>
       <c r="C615" t="inlineStr">
         <is>
-          <t>[0]</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D615" t="inlineStr">
         <is>
-          <t>filled (single-seed, grey)</t>
+          <t>skipped</t>
         </is>
       </c>
       <c r="E615" t="inlineStr">
         <is>
-          <t>cohen_kappa 0.3859</t>
+          <t>the workbook has no row for this variant</t>
         </is>
       </c>
     </row>
@@ -23412,22 +23510,22 @@
       </c>
       <c r="B616" t="inlineStr">
         <is>
-          <t>paclock_probe_v1</t>
+          <t>paclock_probe_rand</t>
         </is>
       </c>
       <c r="C616" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>[0]</t>
         </is>
       </c>
       <c r="D616" t="inlineStr">
         <is>
-          <t>skipped</t>
+          <t>filled (single-seed, grey)</t>
         </is>
       </c>
       <c r="E616" t="inlineStr">
         <is>
-          <t>no row label for 'paclock_probe_v1'</t>
+          <t>cohen_kappa 0.3859</t>
         </is>
       </c>
     </row>
@@ -23439,22 +23537,22 @@
       </c>
       <c r="B617" t="inlineStr">
         <is>
-          <t>paclock_probe_v2</t>
+          <t>paclock_probe_v1</t>
         </is>
       </c>
       <c r="C617" t="inlineStr">
         <is>
-          <t>[0]</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D617" t="inlineStr">
         <is>
-          <t>filled (single-seed, grey)</t>
+          <t>skipped</t>
         </is>
       </c>
       <c r="E617" t="inlineStr">
         <is>
-          <t>cohen_kappa 0.5184</t>
+          <t>no row label for 'paclock_probe_v1'</t>
         </is>
       </c>
     </row>
@@ -23466,22 +23564,22 @@
       </c>
       <c r="B618" t="inlineStr">
         <is>
-          <t>paclock_pt_base</t>
+          <t>paclock_probe_v2</t>
         </is>
       </c>
       <c r="C618" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>[0]</t>
         </is>
       </c>
       <c r="D618" t="inlineStr">
         <is>
-          <t>skipped</t>
+          <t>filled (single-seed, grey)</t>
         </is>
       </c>
       <c r="E618" t="inlineStr">
         <is>
-          <t>row 'PACLock (pretrained, base)' not found</t>
+          <t>cohen_kappa 0.5184</t>
         </is>
       </c>
     </row>
@@ -23493,7 +23591,7 @@
       </c>
       <c r="B619" t="inlineStr">
         <is>
-          <t>paclock_pt_base_p200</t>
+          <t>paclock_pt_base</t>
         </is>
       </c>
       <c r="C619" t="inlineStr">
@@ -23508,7 +23606,7 @@
       </c>
       <c r="E619" t="inlineStr">
         <is>
-          <t>no row label for 'paclock_pt_base_p200'</t>
+          <t>row 'PACLock (pretrained, base)' not found</t>
         </is>
       </c>
     </row>
@@ -23520,7 +23618,7 @@
       </c>
       <c r="B620" t="inlineStr">
         <is>
-          <t>paclock_pt_large</t>
+          <t>paclock_pt_base_p200</t>
         </is>
       </c>
       <c r="C620" t="inlineStr">
@@ -23535,7 +23633,7 @@
       </c>
       <c r="E620" t="inlineStr">
         <is>
-          <t>row 'PACLock (pretrained, large)' not found</t>
+          <t>no row label for 'paclock_pt_base_p200'</t>
         </is>
       </c>
     </row>
@@ -23547,7 +23645,7 @@
       </c>
       <c r="B621" t="inlineStr">
         <is>
-          <t>paclock_rawtok</t>
+          <t>paclock_pt_large</t>
         </is>
       </c>
       <c r="C621" t="inlineStr">
@@ -23562,7 +23660,7 @@
       </c>
       <c r="E621" t="inlineStr">
         <is>
-          <t>no row label for 'paclock_rawtok'</t>
+          <t>row 'PACLock (pretrained, large)' not found</t>
         </is>
       </c>
     </row>
@@ -23574,7 +23672,7 @@
       </c>
       <c r="B622" t="inlineStr">
         <is>
-          <t>paclock_rot2</t>
+          <t>paclock_rawtok</t>
         </is>
       </c>
       <c r="C622" t="inlineStr">
@@ -23589,7 +23687,7 @@
       </c>
       <c r="E622" t="inlineStr">
         <is>
-          <t>no row label for 'paclock_rot2'</t>
+          <t>no row label for 'paclock_rawtok'</t>
         </is>
       </c>
     </row>
@@ -23601,7 +23699,7 @@
       </c>
       <c r="B623" t="inlineStr">
         <is>
-          <t>paclock_rot_ms</t>
+          <t>paclock_rot2</t>
         </is>
       </c>
       <c r="C623" t="inlineStr">
@@ -23616,7 +23714,7 @@
       </c>
       <c r="E623" t="inlineStr">
         <is>
-          <t>no row label for 'paclock_rot_ms'</t>
+          <t>no row label for 'paclock_rot2'</t>
         </is>
       </c>
     </row>
@@ -23628,7 +23726,7 @@
       </c>
       <c r="B624" t="inlineStr">
         <is>
-          <t>paclock_sphead</t>
+          <t>paclock_rot_ms</t>
         </is>
       </c>
       <c r="C624" t="inlineStr">
@@ -23643,7 +23741,7 @@
       </c>
       <c r="E624" t="inlineStr">
         <is>
-          <t>no row label for 'paclock_sphead'</t>
+          <t>no row label for 'paclock_rot_ms'</t>
         </is>
       </c>
     </row>
@@ -23655,7 +23753,7 @@
       </c>
       <c r="B625" t="inlineStr">
         <is>
-          <t>paclock_v2</t>
+          <t>paclock_sphead</t>
         </is>
       </c>
       <c r="C625" t="inlineStr">
@@ -23670,7 +23768,7 @@
       </c>
       <c r="E625" t="inlineStr">
         <is>
-          <t>row 'PACLock (from scratch, full)' not found</t>
+          <t>no row label for 'paclock_sphead'</t>
         </is>
       </c>
     </row>
@@ -23682,7 +23780,7 @@
       </c>
       <c r="B626" t="inlineStr">
         <is>
-          <t>paclock_v2_n20000</t>
+          <t>paclock_v2</t>
         </is>
       </c>
       <c r="C626" t="inlineStr">
@@ -23697,7 +23795,7 @@
       </c>
       <c r="E626" t="inlineStr">
         <is>
-          <t>no row label for 'paclock_v2_n20000'</t>
+          <t>row 'PACLock (from scratch, full)' not found</t>
         </is>
       </c>
     </row>
@@ -23709,7 +23807,7 @@
       </c>
       <c r="B627" t="inlineStr">
         <is>
-          <t>paclock_v2_n2160</t>
+          <t>paclock_v2_n20000</t>
         </is>
       </c>
       <c r="C627" t="inlineStr">
@@ -23724,7 +23822,7 @@
       </c>
       <c r="E627" t="inlineStr">
         <is>
-          <t>no row label for 'paclock_v2_n2160'</t>
+          <t>no row label for 'paclock_v2_n20000'</t>
         </is>
       </c>
     </row>
@@ -23736,7 +23834,7 @@
       </c>
       <c r="B628" t="inlineStr">
         <is>
-          <t>paclock_v2_n6720</t>
+          <t>paclock_v2_n2160</t>
         </is>
       </c>
       <c r="C628" t="inlineStr">
@@ -23751,7 +23849,7 @@
       </c>
       <c r="E628" t="inlineStr">
         <is>
-          <t>no row label for 'paclock_v2_n6720'</t>
+          <t>no row label for 'paclock_v2_n2160'</t>
         </is>
       </c>
     </row>
@@ -23763,27 +23861,22 @@
       </c>
       <c r="B629" t="inlineStr">
         <is>
-          <t>reve_pretrained</t>
+          <t>paclock_v2_n6720</t>
         </is>
       </c>
       <c r="C629" t="inlineStr">
         <is>
-          <t>[0, 1, 2]</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D629" t="inlineStr">
         <is>
-          <t>filled</t>
+          <t>skipped</t>
         </is>
       </c>
       <c r="E629" t="inlineStr">
         <is>
-          <t>[实测 69.48M] cohen_kappa per-seed 0:0.7188, 1:0.6423, 2:0.6927</t>
-        </is>
-      </c>
-      <c r="F629" t="inlineStr">
-        <is>
-          <t>stopped_by=patience lr=0.0001 batch_size=128 epochs=30 patience=10 eval_every_steps=0 loss=cross_entropy label_smoothing=0.0 grad_clip=1.0</t>
+          <t>no row label for 'paclock_v2_n6720'</t>
         </is>
       </c>
     </row>
@@ -23795,7 +23888,7 @@
       </c>
       <c r="B630" t="inlineStr">
         <is>
-          <t>sparcnet</t>
+          <t>reve_pretrained</t>
         </is>
       </c>
       <c r="C630" t="inlineStr">
@@ -23810,12 +23903,12 @@
       </c>
       <c r="E630" t="inlineStr">
         <is>
-          <t>[实测 0.99M] cohen_kappa per-seed 0:0.4665, 1:0.5199, 2:0.4791</t>
+          <t>[实测 69.48M] cohen_kappa per-seed 0:0.7188, 1:0.6423, 2:0.6927</t>
         </is>
       </c>
       <c r="F630" t="inlineStr">
         <is>
-          <t>lr=0.001 batch_size=512 epochs=100 patience=15 eval_every_steps=0 loss=cross_entropy label_smoothing=0.1</t>
+          <t>stopped_by=patience lr=0.0001 batch_size=128 epochs=30 patience=10 eval_every_steps=0 loss=cross_entropy label_smoothing=0.0 grad_clip=1.0</t>
         </is>
       </c>
     </row>
@@ -23827,22 +23920,27 @@
       </c>
       <c r="B631" t="inlineStr">
         <is>
-          <t>sparcnet_n20000</t>
+          <t>sparcnet</t>
         </is>
       </c>
       <c r="C631" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>[0, 1, 2]</t>
         </is>
       </c>
       <c r="D631" t="inlineStr">
         <is>
-          <t>skipped</t>
+          <t>filled</t>
         </is>
       </c>
       <c r="E631" t="inlineStr">
         <is>
-          <t>no row label for 'sparcnet_n20000'</t>
+          <t>[实测 0.99M] cohen_kappa per-seed 0:0.4665, 1:0.5199, 2:0.4791</t>
+        </is>
+      </c>
+      <c r="F631" t="inlineStr">
+        <is>
+          <t>lr=0.001 batch_size=512 epochs=100 patience=15 eval_every_steps=0 loss=cross_entropy label_smoothing=0.1</t>
         </is>
       </c>
     </row>
@@ -23854,7 +23952,7 @@
       </c>
       <c r="B632" t="inlineStr">
         <is>
-          <t>sparcnet_n2160</t>
+          <t>sparcnet_n20000</t>
         </is>
       </c>
       <c r="C632" t="inlineStr">
@@ -23869,7 +23967,7 @@
       </c>
       <c r="E632" t="inlineStr">
         <is>
-          <t>no row label for 'sparcnet_n2160'</t>
+          <t>no row label for 'sparcnet_n20000'</t>
         </is>
       </c>
     </row>
@@ -23881,7 +23979,7 @@
       </c>
       <c r="B633" t="inlineStr">
         <is>
-          <t>sparcnet_n6720</t>
+          <t>sparcnet_n2160</t>
         </is>
       </c>
       <c r="C633" t="inlineStr">
@@ -23896,7 +23994,7 @@
       </c>
       <c r="E633" t="inlineStr">
         <is>
-          <t>no row label for 'sparcnet_n6720'</t>
+          <t>no row label for 'sparcnet_n2160'</t>
         </is>
       </c>
     </row>
@@ -23908,27 +24006,22 @@
       </c>
       <c r="B634" t="inlineStr">
         <is>
-          <t>st_transformer</t>
+          <t>sparcnet_n6720</t>
         </is>
       </c>
       <c r="C634" t="inlineStr">
         <is>
-          <t>[0, 1, 2]</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D634" t="inlineStr">
         <is>
-          <t>filled</t>
+          <t>skipped</t>
         </is>
       </c>
       <c r="E634" t="inlineStr">
         <is>
-          <t>[实测 3.43M] cohen_kappa per-seed 0:0.5139, 1:0.4916, 2:0.4962</t>
-        </is>
-      </c>
-      <c r="F634" t="inlineStr">
-        <is>
-          <t>lr=0.001 batch_size=512 epochs=100 patience=15 eval_every_steps=0 loss=cross_entropy label_smoothing=0.1</t>
+          <t>no row label for 'sparcnet_n6720'</t>
         </is>
       </c>
     </row>
@@ -23940,7 +24033,7 @@
       </c>
       <c r="B635" t="inlineStr">
         <is>
-          <t>tfm_pretrained</t>
+          <t>st_transformer</t>
         </is>
       </c>
       <c r="C635" t="inlineStr">
@@ -23955,24 +24048,24 @@
       </c>
       <c r="E635" t="inlineStr">
         <is>
-          <t>[实测 1.89M] cohen_kappa per-seed 0:0.6543, 1:0.6299, 2:0.6715</t>
+          <t>[实测 3.43M] cohen_kappa per-seed 0:0.5139, 1:0.4916, 2:0.4962</t>
         </is>
       </c>
       <c r="F635" t="inlineStr">
         <is>
-          <t>lr=0.001 batch_size=512 epochs=50 patience=10 eval_every_steps=100 loss=cross_entropy label_smoothing=0.1</t>
+          <t>lr=0.001 batch_size=512 epochs=100 patience=15 eval_every_steps=0 loss=cross_entropy label_smoothing=0.1</t>
         </is>
       </c>
     </row>
     <row r="636">
       <c r="A636" t="inlineStr">
         <is>
-          <t>tusz</t>
+          <t>tuev</t>
         </is>
       </c>
       <c r="B636" t="inlineStr">
         <is>
-          <t>biot_prest16</t>
+          <t>tfm_pretrained</t>
         </is>
       </c>
       <c r="C636" t="inlineStr">
@@ -23987,12 +24080,12 @@
       </c>
       <c r="E636" t="inlineStr">
         <is>
-          <t>[实测 3.19M] pr_auc per-seed 0:0.3673, 1:0.3513, 2:0.2951</t>
+          <t>[实测 1.89M] cohen_kappa per-seed 0:0.6543, 1:0.6299, 2:0.6715</t>
         </is>
       </c>
       <c r="F636" t="inlineStr">
         <is>
-          <t>lr=0.001 batch_size=512 epochs=100 patience=5 eval_every_steps=0 loss=bce_with_logits</t>
+          <t>lr=0.001 batch_size=512 epochs=50 patience=10 eval_every_steps=100 loss=cross_entropy label_smoothing=0.1</t>
         </is>
       </c>
     </row>
@@ -24004,7 +24097,7 @@
       </c>
       <c r="B637" t="inlineStr">
         <is>
-          <t>biot_scratch</t>
+          <t>biot_prest16</t>
         </is>
       </c>
       <c r="C637" t="inlineStr">
@@ -24019,7 +24112,7 @@
       </c>
       <c r="E637" t="inlineStr">
         <is>
-          <t>[实测 3.19M] pr_auc per-seed 0:0.3186, 1:0.3682, 2:0.3556</t>
+          <t>[实测 3.19M] pr_auc per-seed 0:0.3673, 1:0.3513, 2:0.2951</t>
         </is>
       </c>
       <c r="F637" t="inlineStr">
@@ -24036,22 +24129,27 @@
       </c>
       <c r="B638" t="inlineStr">
         <is>
-          <t>cbramod_pac</t>
+          <t>biot_scratch</t>
         </is>
       </c>
       <c r="C638" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>[0, 1, 2]</t>
         </is>
       </c>
       <c r="D638" t="inlineStr">
         <is>
-          <t>skipped</t>
+          <t>filled</t>
         </is>
       </c>
       <c r="E638" t="inlineStr">
         <is>
-          <t>the workbook has no row for this variant</t>
+          <t>[实测 3.19M] pr_auc per-seed 0:0.3186, 1:0.3682, 2:0.3556</t>
+        </is>
+      </c>
+      <c r="F638" t="inlineStr">
+        <is>
+          <t>lr=0.001 batch_size=512 epochs=100 patience=5 eval_every_steps=0 loss=bce_with_logits</t>
         </is>
       </c>
     </row>
@@ -24063,27 +24161,22 @@
       </c>
       <c r="B639" t="inlineStr">
         <is>
-          <t>cbramod_pretrained</t>
+          <t>cbramod_pac</t>
         </is>
       </c>
       <c r="C639" t="inlineStr">
         <is>
-          <t>[0, 1, 2]</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D639" t="inlineStr">
         <is>
-          <t>filled</t>
+          <t>skipped</t>
         </is>
       </c>
       <c r="E639" t="inlineStr">
         <is>
-          <t>[实测 30.65M] pr_auc per-seed 0:0.4139, 1:0.4061, 2:0.4831</t>
-        </is>
-      </c>
-      <c r="F639" t="inlineStr">
-        <is>
-          <t>lr=0.0001 batch_size=64 epochs=50 patience=0 eval_every_steps=0 loss=bce_with_logits grad_clip=1.0 select_metric=auroc multi_lr=True</t>
+          <t>the workbook has no row for this variant</t>
         </is>
       </c>
     </row>
@@ -24095,7 +24188,7 @@
       </c>
       <c r="B640" t="inlineStr">
         <is>
-          <t>cbramod_scratch</t>
+          <t>cbramod_pretrained</t>
         </is>
       </c>
       <c r="C640" t="inlineStr">
@@ -24110,7 +24203,7 @@
       </c>
       <c r="E640" t="inlineStr">
         <is>
-          <t>[实测 30.65M] pr_auc per-seed 0:0.4662, 1:0.5401, 2:0.4392</t>
+          <t>[实测 30.65M] pr_auc per-seed 0:0.4139, 1:0.4061, 2:0.4831</t>
         </is>
       </c>
       <c r="F640" t="inlineStr">
@@ -24127,7 +24220,7 @@
       </c>
       <c r="B641" t="inlineStr">
         <is>
-          <t>cnn_transformer</t>
+          <t>cbramod_scratch</t>
         </is>
       </c>
       <c r="C641" t="inlineStr">
@@ -24142,12 +24235,12 @@
       </c>
       <c r="E641" t="inlineStr">
         <is>
-          <t>[实测 3.15M] pr_auc per-seed 0:0.1493, 1:0.4554, 2:0.5073  [seed spread 43% -- mean is a weak summary]</t>
+          <t>[实测 30.65M] pr_auc per-seed 0:0.4662, 1:0.5401, 2:0.4392</t>
         </is>
       </c>
       <c r="F641" t="inlineStr">
         <is>
-          <t>lr=0.001 batch_size=512 epochs=20 patience=8 eval_every_steps=200 loss=bce_with_logits</t>
+          <t>lr=0.0001 batch_size=64 epochs=50 patience=0 eval_every_steps=0 loss=bce_with_logits grad_clip=1.0 select_metric=auroc multi_lr=True</t>
         </is>
       </c>
     </row>
@@ -24159,7 +24252,7 @@
       </c>
       <c r="B642" t="inlineStr">
         <is>
-          <t>contrawr</t>
+          <t>cnn_transformer</t>
         </is>
       </c>
       <c r="C642" t="inlineStr">
@@ -24174,7 +24267,7 @@
       </c>
       <c r="E642" t="inlineStr">
         <is>
-          <t>[实测 1.57M] pr_auc per-seed 0:0.5188, 1:0.4849, 2:0.5092</t>
+          <t>[实测 3.15M] pr_auc per-seed 0:0.1493, 1:0.4554, 2:0.5073  [seed spread 43% -- mean is a weak summary]</t>
         </is>
       </c>
       <c r="F642" t="inlineStr">
@@ -24191,7 +24284,7 @@
       </c>
       <c r="B643" t="inlineStr">
         <is>
-          <t>csbrain_pretrained</t>
+          <t>contrawr</t>
         </is>
       </c>
       <c r="C643" t="inlineStr">
@@ -24206,12 +24299,12 @@
       </c>
       <c r="E643" t="inlineStr">
         <is>
-          <t>[实测 41.06M] pr_auc per-seed 0:0.6207, 1:0.3889, 2:0.5414  [seed spread 19% -- mean is a weak summary]</t>
+          <t>[实测 1.57M] pr_auc per-seed 0:0.5188, 1:0.4849, 2:0.5092</t>
         </is>
       </c>
       <c r="F643" t="inlineStr">
         <is>
-          <t>stopped_by=patience lr=0.0001 batch_size=64 epochs=25 patience=10 eval_every_steps=500 loss=bce_with_logits grad_clip=1.0</t>
+          <t>lr=0.001 batch_size=512 epochs=20 patience=8 eval_every_steps=200 loss=bce_with_logits</t>
         </is>
       </c>
     </row>
@@ -24223,7 +24316,7 @@
       </c>
       <c r="B644" t="inlineStr">
         <is>
-          <t>eegconformer</t>
+          <t>csbrain_pretrained</t>
         </is>
       </c>
       <c r="C644" t="inlineStr">
@@ -24238,12 +24331,12 @@
       </c>
       <c r="E644" t="inlineStr">
         <is>
-          <t>[实测 1.46M] pr_auc per-seed 0:0.3624, 1:0.2985, 2:0.2961</t>
+          <t>[实测 41.06M] pr_auc per-seed 0:0.6207, 1:0.3889, 2:0.5414  [seed spread 19% -- mean is a weak summary]</t>
         </is>
       </c>
       <c r="F644" t="inlineStr">
         <is>
-          <t>stopped_by=patience lr=0.001 batch_size=128 epochs=20 patience=8 eval_every_steps=200 loss=bce_with_logits grad_clip=1.0</t>
+          <t>stopped_by=patience lr=0.0001 batch_size=64 epochs=25 patience=10 eval_every_steps=500 loss=bce_with_logits grad_clip=1.0</t>
         </is>
       </c>
     </row>
@@ -24255,22 +24348,27 @@
       </c>
       <c r="B645" t="inlineStr">
         <is>
-          <t>eegconformer_t1</t>
+          <t>eegconformer</t>
         </is>
       </c>
       <c r="C645" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>[0, 1, 2]</t>
         </is>
       </c>
       <c r="D645" t="inlineStr">
         <is>
-          <t>skipped</t>
+          <t>filled</t>
         </is>
       </c>
       <c r="E645" t="inlineStr">
         <is>
-          <t>no row label for 'eegconformer_t1'</t>
+          <t>[实测 1.46M] pr_auc per-seed 0:0.3624, 1:0.2985, 2:0.2961</t>
+        </is>
+      </c>
+      <c r="F645" t="inlineStr">
+        <is>
+          <t>stopped_by=patience lr=0.001 batch_size=128 epochs=20 patience=8 eval_every_steps=200 loss=bce_with_logits grad_clip=1.0</t>
         </is>
       </c>
     </row>
@@ -24282,7 +24380,7 @@
       </c>
       <c r="B646" t="inlineStr">
         <is>
-          <t>eegconformer_t2</t>
+          <t>eegconformer_t1</t>
         </is>
       </c>
       <c r="C646" t="inlineStr">
@@ -24297,7 +24395,7 @@
       </c>
       <c r="E646" t="inlineStr">
         <is>
-          <t>no row label for 'eegconformer_t2'</t>
+          <t>no row label for 'eegconformer_t1'</t>
         </is>
       </c>
     </row>
@@ -24309,7 +24407,7 @@
       </c>
       <c r="B647" t="inlineStr">
         <is>
-          <t>eegconformer_t3</t>
+          <t>eegconformer_t2</t>
         </is>
       </c>
       <c r="C647" t="inlineStr">
@@ -24324,7 +24422,7 @@
       </c>
       <c r="E647" t="inlineStr">
         <is>
-          <t>no row label for 'eegconformer_t3'</t>
+          <t>no row label for 'eegconformer_t2'</t>
         </is>
       </c>
     </row>
@@ -24336,7 +24434,7 @@
       </c>
       <c r="B648" t="inlineStr">
         <is>
-          <t>eegconformer_t4</t>
+          <t>eegconformer_t3</t>
         </is>
       </c>
       <c r="C648" t="inlineStr">
@@ -24351,7 +24449,7 @@
       </c>
       <c r="E648" t="inlineStr">
         <is>
-          <t>no row label for 'eegconformer_t4'</t>
+          <t>no row label for 'eegconformer_t3'</t>
         </is>
       </c>
     </row>
@@ -24363,27 +24461,22 @@
       </c>
       <c r="B649" t="inlineStr">
         <is>
-          <t>eegnet</t>
+          <t>eegconformer_t4</t>
         </is>
       </c>
       <c r="C649" t="inlineStr">
         <is>
-          <t>[0, 1, 2]</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D649" t="inlineStr">
         <is>
-          <t>filled</t>
+          <t>skipped</t>
         </is>
       </c>
       <c r="E649" t="inlineStr">
         <is>
-          <t>[实测 0.00M] pr_auc per-seed 0:0.4598, 1:0.4970, 2:0.5196</t>
-        </is>
-      </c>
-      <c r="F649" t="inlineStr">
-        <is>
-          <t>stopped_by=patience lr=0.001 batch_size=512 epochs=20 patience=8 eval_every_steps=200 loss=bce_with_logits grad_clip=1.0</t>
+          <t>no row label for 'eegconformer_t4'</t>
         </is>
       </c>
     </row>
@@ -24395,22 +24488,27 @@
       </c>
       <c r="B650" t="inlineStr">
         <is>
-          <t>eegnet_t1</t>
+          <t>eegnet</t>
         </is>
       </c>
       <c r="C650" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>[0, 1, 2]</t>
         </is>
       </c>
       <c r="D650" t="inlineStr">
         <is>
-          <t>skipped</t>
+          <t>filled</t>
         </is>
       </c>
       <c r="E650" t="inlineStr">
         <is>
-          <t>no row label for 'eegnet_t1'</t>
+          <t>[实测 0.00M] pr_auc per-seed 0:0.4598, 1:0.4970, 2:0.5196</t>
+        </is>
+      </c>
+      <c r="F650" t="inlineStr">
+        <is>
+          <t>stopped_by=patience lr=0.001 batch_size=512 epochs=20 patience=8 eval_every_steps=200 loss=bce_with_logits grad_clip=1.0</t>
         </is>
       </c>
     </row>
@@ -24422,7 +24520,7 @@
       </c>
       <c r="B651" t="inlineStr">
         <is>
-          <t>eegnet_t2</t>
+          <t>eegnet_t1</t>
         </is>
       </c>
       <c r="C651" t="inlineStr">
@@ -24437,7 +24535,7 @@
       </c>
       <c r="E651" t="inlineStr">
         <is>
-          <t>no row label for 'eegnet_t2'</t>
+          <t>no row label for 'eegnet_t1'</t>
         </is>
       </c>
     </row>
@@ -24449,7 +24547,7 @@
       </c>
       <c r="B652" t="inlineStr">
         <is>
-          <t>eegnet_t3</t>
+          <t>eegnet_t2</t>
         </is>
       </c>
       <c r="C652" t="inlineStr">
@@ -24464,7 +24562,7 @@
       </c>
       <c r="E652" t="inlineStr">
         <is>
-          <t>no row label for 'eegnet_t3'</t>
+          <t>no row label for 'eegnet_t2'</t>
         </is>
       </c>
     </row>
@@ -24476,7 +24574,7 @@
       </c>
       <c r="B653" t="inlineStr">
         <is>
-          <t>eegnet_t4</t>
+          <t>eegnet_t3</t>
         </is>
       </c>
       <c r="C653" t="inlineStr">
@@ -24491,7 +24589,7 @@
       </c>
       <c r="E653" t="inlineStr">
         <is>
-          <t>no row label for 'eegnet_t4'</t>
+          <t>no row label for 'eegnet_t3'</t>
         </is>
       </c>
     </row>
@@ -24503,27 +24601,22 @@
       </c>
       <c r="B654" t="inlineStr">
         <is>
-          <t>eegpt_pretrained</t>
+          <t>eegnet_t4</t>
         </is>
       </c>
       <c r="C654" t="inlineStr">
         <is>
-          <t>[0, 1, 2]</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D654" t="inlineStr">
         <is>
-          <t>filled</t>
+          <t>skipped</t>
         </is>
       </c>
       <c r="E654" t="inlineStr">
         <is>
-          <t>[实测 25.69M] pr_auc per-seed 0:0.6257, 1:0.5102, 2:0.4980</t>
-        </is>
-      </c>
-      <c r="F654" t="inlineStr">
-        <is>
-          <t>lr=0.0004 batch_size=32 epochs=40 patience=10 eval_every_steps=500 loss=bce_with_logits</t>
+          <t>no row label for 'eegnet_t4'</t>
         </is>
       </c>
     </row>
@@ -24535,7 +24628,7 @@
       </c>
       <c r="B655" t="inlineStr">
         <is>
-          <t>feat_best</t>
+          <t>eegpt_pretrained</t>
         </is>
       </c>
       <c r="C655" t="inlineStr">
@@ -24550,12 +24643,12 @@
       </c>
       <c r="E655" t="inlineStr">
         <is>
-          <t>[实测 0.00M] pr_auc per-seed 0:0.2384, 1:0.2384, 2:0.2384</t>
+          <t>[实测 25.69M] pr_auc per-seed 0:0.6257, 1:0.5102, 2:0.4980</t>
         </is>
       </c>
       <c r="F655" t="inlineStr">
         <is>
-          <t>stopped_by=closed-form epochs=1 loss=closed-form</t>
+          <t>lr=0.0004 batch_size=32 epochs=40 patience=10 eval_every_steps=500 loss=bce_with_logits</t>
         </is>
       </c>
     </row>
@@ -24567,7 +24660,7 @@
       </c>
       <c r="B656" t="inlineStr">
         <is>
-          <t>ffcl</t>
+          <t>feat_best</t>
         </is>
       </c>
       <c r="C656" t="inlineStr">
@@ -24582,12 +24675,12 @@
       </c>
       <c r="E656" t="inlineStr">
         <is>
-          <t>[实测 2.46M] pr_auc per-seed 0:0.5511, 1:0.5126, 2:0.5709</t>
+          <t>[实测 0.00M] pr_auc per-seed 0:0.2384, 1:0.2384, 2:0.2384</t>
         </is>
       </c>
       <c r="F656" t="inlineStr">
         <is>
-          <t>lr=0.001 batch_size=512 epochs=20 patience=8 eval_every_steps=200 loss=bce_with_logits</t>
+          <t>stopped_by=closed-form epochs=1 loss=closed-form</t>
         </is>
       </c>
     </row>
@@ -24599,7 +24692,7 @@
       </c>
       <c r="B657" t="inlineStr">
         <is>
-          <t>labram_pretrained</t>
+          <t>ffcl</t>
         </is>
       </c>
       <c r="C657" t="inlineStr">
@@ -24614,12 +24707,12 @@
       </c>
       <c r="E657" t="inlineStr">
         <is>
-          <t>[实测 5.82M] pr_auc per-seed 0:0.4828, 1:0.5186, 2:0.4249</t>
+          <t>[实测 2.46M] pr_auc per-seed 0:0.5511, 1:0.5126, 2:0.5709</t>
         </is>
       </c>
       <c r="F657" t="inlineStr">
         <is>
-          <t>lr=0.0005 batch_size=64 epochs=50 patience=10 eval_every_steps=100 loss=bce_with_logits</t>
+          <t>lr=0.001 batch_size=512 epochs=20 patience=8 eval_every_steps=200 loss=bce_with_logits</t>
         </is>
       </c>
     </row>
@@ -24631,7 +24724,7 @@
       </c>
       <c r="B658" t="inlineStr">
         <is>
-          <t>labram_scratch</t>
+          <t>labram_pretrained</t>
         </is>
       </c>
       <c r="C658" t="inlineStr">
@@ -24646,12 +24739,12 @@
       </c>
       <c r="E658" t="inlineStr">
         <is>
-          <t>[实测 5.82M] pr_auc per-seed 0:0.4201, 1:0.5036, 2:0.5020</t>
+          <t>[实测 5.82M] pr_auc per-seed 0:0.4828, 1:0.5186, 2:0.4249</t>
         </is>
       </c>
       <c r="F658" t="inlineStr">
         <is>
-          <t>stopped_by=patience lr=0.0005 batch_size=64 epochs=50 patience=10 eval_every_steps=0 loss=bce_with_logits</t>
+          <t>lr=0.0005 batch_size=64 epochs=50 patience=10 eval_every_steps=100 loss=bce_with_logits</t>
         </is>
       </c>
     </row>
@@ -24663,22 +24756,27 @@
       </c>
       <c r="B659" t="inlineStr">
         <is>
-          <t>paclock_duplex</t>
+          <t>labram_scratch</t>
         </is>
       </c>
       <c r="C659" t="inlineStr">
         <is>
-          <t>[0]</t>
+          <t>[0, 1, 2]</t>
         </is>
       </c>
       <c r="D659" t="inlineStr">
         <is>
-          <t>filled (single-seed, grey)</t>
+          <t>filled</t>
         </is>
       </c>
       <c r="E659" t="inlineStr">
         <is>
-          <t>pr_auc 0.6328</t>
+          <t>[实测 5.82M] pr_auc per-seed 0:0.4201, 1:0.5036, 2:0.5020</t>
+        </is>
+      </c>
+      <c r="F659" t="inlineStr">
+        <is>
+          <t>stopped_by=patience lr=0.0005 batch_size=64 epochs=50 patience=10 eval_every_steps=0 loss=bce_with_logits</t>
         </is>
       </c>
     </row>
@@ -24690,22 +24788,22 @@
       </c>
       <c r="B660" t="inlineStr">
         <is>
-          <t>paclock_duplex_ms</t>
+          <t>paclock_duplex</t>
         </is>
       </c>
       <c r="C660" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>[0]</t>
         </is>
       </c>
       <c r="D660" t="inlineStr">
         <is>
-          <t>skipped</t>
+          <t>filled (single-seed, grey)</t>
         </is>
       </c>
       <c r="E660" t="inlineStr">
         <is>
-          <t>no row label for 'paclock_duplex_ms'</t>
+          <t>pr_auc 0.6328</t>
         </is>
       </c>
     </row>
@@ -24717,7 +24815,7 @@
       </c>
       <c r="B661" t="inlineStr">
         <is>
-          <t>paclock_duplex_pt</t>
+          <t>paclock_duplex_ms</t>
         </is>
       </c>
       <c r="C661" t="inlineStr">
@@ -24732,7 +24830,7 @@
       </c>
       <c r="E661" t="inlineStr">
         <is>
-          <t>row 'PACLock (duplex, pretrained)' not found</t>
+          <t>no row label for 'paclock_duplex_ms'</t>
         </is>
       </c>
     </row>
@@ -24744,22 +24842,22 @@
       </c>
       <c r="B662" t="inlineStr">
         <is>
-          <t>paclock_duplex_pt2</t>
+          <t>paclock_duplex_pt</t>
         </is>
       </c>
       <c r="C662" t="inlineStr">
         <is>
-          <t>[0]</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D662" t="inlineStr">
         <is>
-          <t>filled (single-seed, grey)</t>
+          <t>skipped</t>
         </is>
       </c>
       <c r="E662" t="inlineStr">
         <is>
-          <t>pr_auc 0.7143</t>
+          <t>row 'PACLock (duplex, pretrained)' not found</t>
         </is>
       </c>
     </row>
@@ -24771,22 +24869,22 @@
       </c>
       <c r="B663" t="inlineStr">
         <is>
-          <t>paclock_duplex_ptF</t>
+          <t>paclock_duplex_pt2</t>
         </is>
       </c>
       <c r="C663" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>[0]</t>
         </is>
       </c>
       <c r="D663" t="inlineStr">
         <is>
-          <t>skipped</t>
+          <t>filled (single-seed, grey)</t>
         </is>
       </c>
       <c r="E663" t="inlineStr">
         <is>
-          <t>row 'CroFreMo (预训练 v2-full)' not found</t>
+          <t>pr_auc 0.7143</t>
         </is>
       </c>
     </row>
@@ -24798,7 +24896,7 @@
       </c>
       <c r="B664" t="inlineStr">
         <is>
-          <t>paclock_fg_gms</t>
+          <t>paclock_duplex_ptF</t>
         </is>
       </c>
       <c r="C664" t="inlineStr">
@@ -24813,7 +24911,7 @@
       </c>
       <c r="E664" t="inlineStr">
         <is>
-          <t>no row label for 'paclock_fg_gms'</t>
+          <t>row 'CroFreMo (预训练 v2-full)' not found</t>
         </is>
       </c>
     </row>
@@ -24825,7 +24923,7 @@
       </c>
       <c r="B665" t="inlineStr">
         <is>
-          <t>paclock_fg_stem</t>
+          <t>paclock_fg_gms</t>
         </is>
       </c>
       <c r="C665" t="inlineStr">
@@ -24840,7 +24938,7 @@
       </c>
       <c r="E665" t="inlineStr">
         <is>
-          <t>no row label for 'paclock_fg_stem'</t>
+          <t>no row label for 'paclock_fg_gms'</t>
         </is>
       </c>
     </row>
@@ -24852,7 +24950,7 @@
       </c>
       <c r="B666" t="inlineStr">
         <is>
-          <t>paclock_flagship</t>
+          <t>paclock_fg_stem</t>
         </is>
       </c>
       <c r="C666" t="inlineStr">
@@ -24867,7 +24965,7 @@
       </c>
       <c r="E666" t="inlineStr">
         <is>
-          <t>no row label for 'paclock_flagship'</t>
+          <t>no row label for 'paclock_fg_stem'</t>
         </is>
       </c>
     </row>
@@ -24879,7 +24977,7 @@
       </c>
       <c r="B667" t="inlineStr">
         <is>
-          <t>paclock_fuse</t>
+          <t>paclock_flagship</t>
         </is>
       </c>
       <c r="C667" t="inlineStr">
@@ -24894,7 +24992,7 @@
       </c>
       <c r="E667" t="inlineStr">
         <is>
-          <t>no row label for 'paclock_fuse'</t>
+          <t>no row label for 'paclock_flagship'</t>
         </is>
       </c>
     </row>
@@ -24906,7 +25004,7 @@
       </c>
       <c r="B668" t="inlineStr">
         <is>
-          <t>paclock_fusegate</t>
+          <t>paclock_fuse</t>
         </is>
       </c>
       <c r="C668" t="inlineStr">
@@ -24921,7 +25019,7 @@
       </c>
       <c r="E668" t="inlineStr">
         <is>
-          <t>no row label for 'paclock_fusegate'</t>
+          <t>no row label for 'paclock_fuse'</t>
         </is>
       </c>
     </row>
@@ -24933,7 +25031,7 @@
       </c>
       <c r="B669" t="inlineStr">
         <is>
-          <t>paclock_fusegate_ms</t>
+          <t>paclock_fusegate</t>
         </is>
       </c>
       <c r="C669" t="inlineStr">
@@ -24948,7 +25046,7 @@
       </c>
       <c r="E669" t="inlineStr">
         <is>
-          <t>no row label for 'paclock_fusegate_ms'</t>
+          <t>no row label for 'paclock_fusegate'</t>
         </is>
       </c>
     </row>
@@ -24960,7 +25058,7 @@
       </c>
       <c r="B670" t="inlineStr">
         <is>
-          <t>paclock_hybrid</t>
+          <t>paclock_fusegate_ms</t>
         </is>
       </c>
       <c r="C670" t="inlineStr">
@@ -24975,7 +25073,7 @@
       </c>
       <c r="E670" t="inlineStr">
         <is>
-          <t>no row label for 'paclock_hybrid'</t>
+          <t>no row label for 'paclock_fusegate_ms'</t>
         </is>
       </c>
     </row>
@@ -24987,7 +25085,7 @@
       </c>
       <c r="B671" t="inlineStr">
         <is>
-          <t>paclock_hybrid_attn</t>
+          <t>paclock_hybrid</t>
         </is>
       </c>
       <c r="C671" t="inlineStr">
@@ -25002,7 +25100,7 @@
       </c>
       <c r="E671" t="inlineStr">
         <is>
-          <t>no row label for 'paclock_hybrid_attn'</t>
+          <t>no row label for 'paclock_hybrid'</t>
         </is>
       </c>
     </row>
@@ -25014,7 +25112,7 @@
       </c>
       <c r="B672" t="inlineStr">
         <is>
-          <t>paclock_hybrid_gate</t>
+          <t>paclock_hybrid_attn</t>
         </is>
       </c>
       <c r="C672" t="inlineStr">
@@ -25029,7 +25127,7 @@
       </c>
       <c r="E672" t="inlineStr">
         <is>
-          <t>no row label for 'paclock_hybrid_gate'</t>
+          <t>no row label for 'paclock_hybrid_attn'</t>
         </is>
       </c>
     </row>
@@ -25041,7 +25139,7 @@
       </c>
       <c r="B673" t="inlineStr">
         <is>
-          <t>paclock_p200_pt</t>
+          <t>paclock_hybrid_gate</t>
         </is>
       </c>
       <c r="C673" t="inlineStr">
@@ -25056,7 +25154,7 @@
       </c>
       <c r="E673" t="inlineStr">
         <is>
-          <t>no row label for 'paclock_p200_pt'</t>
+          <t>no row label for 'paclock_hybrid_gate'</t>
         </is>
       </c>
     </row>
@@ -25068,7 +25166,7 @@
       </c>
       <c r="B674" t="inlineStr">
         <is>
-          <t>paclock_p200_pt_notok</t>
+          <t>paclock_p200_pt</t>
         </is>
       </c>
       <c r="C674" t="inlineStr">
@@ -25083,7 +25181,7 @@
       </c>
       <c r="E674" t="inlineStr">
         <is>
-          <t>no row label for 'paclock_p200_pt_notok'</t>
+          <t>no row label for 'paclock_p200_pt'</t>
         </is>
       </c>
     </row>
@@ -25095,7 +25193,7 @@
       </c>
       <c r="B675" t="inlineStr">
         <is>
-          <t>paclock_p200_scratch</t>
+          <t>paclock_p200_pt_notok</t>
         </is>
       </c>
       <c r="C675" t="inlineStr">
@@ -25110,7 +25208,7 @@
       </c>
       <c r="E675" t="inlineStr">
         <is>
-          <t>no row label for 'paclock_p200_scratch'</t>
+          <t>no row label for 'paclock_p200_pt_notok'</t>
         </is>
       </c>
     </row>
@@ -25122,7 +25220,7 @@
       </c>
       <c r="B676" t="inlineStr">
         <is>
-          <t>paclock_pac</t>
+          <t>paclock_p200_scratch</t>
         </is>
       </c>
       <c r="C676" t="inlineStr">
@@ -25137,7 +25235,7 @@
       </c>
       <c r="E676" t="inlineStr">
         <is>
-          <t>the workbook has no row for this variant</t>
+          <t>no row label for 'paclock_p200_scratch'</t>
         </is>
       </c>
     </row>
@@ -25149,22 +25247,22 @@
       </c>
       <c r="B677" t="inlineStr">
         <is>
-          <t>paclock_probe_rand</t>
+          <t>paclock_pac</t>
         </is>
       </c>
       <c r="C677" t="inlineStr">
         <is>
-          <t>[0]</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D677" t="inlineStr">
         <is>
-          <t>filled (single-seed, grey)</t>
+          <t>skipped</t>
         </is>
       </c>
       <c r="E677" t="inlineStr">
         <is>
-          <t>pr_auc 0.4076</t>
+          <t>the workbook has no row for this variant</t>
         </is>
       </c>
     </row>
@@ -25176,22 +25274,22 @@
       </c>
       <c r="B678" t="inlineStr">
         <is>
-          <t>paclock_probe_v1</t>
+          <t>paclock_probe_rand</t>
         </is>
       </c>
       <c r="C678" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>[0]</t>
         </is>
       </c>
       <c r="D678" t="inlineStr">
         <is>
-          <t>skipped</t>
+          <t>filled (single-seed, grey)</t>
         </is>
       </c>
       <c r="E678" t="inlineStr">
         <is>
-          <t>no row label for 'paclock_probe_v1'</t>
+          <t>pr_auc 0.4076</t>
         </is>
       </c>
     </row>
@@ -25203,22 +25301,22 @@
       </c>
       <c r="B679" t="inlineStr">
         <is>
-          <t>paclock_probe_v2</t>
+          <t>paclock_probe_v1</t>
         </is>
       </c>
       <c r="C679" t="inlineStr">
         <is>
-          <t>[0]</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D679" t="inlineStr">
         <is>
-          <t>filled (single-seed, grey)</t>
+          <t>skipped</t>
         </is>
       </c>
       <c r="E679" t="inlineStr">
         <is>
-          <t>pr_auc 0.5417</t>
+          <t>no row label for 'paclock_probe_v1'</t>
         </is>
       </c>
     </row>
@@ -25230,22 +25328,22 @@
       </c>
       <c r="B680" t="inlineStr">
         <is>
-          <t>paclock_pt_base</t>
+          <t>paclock_probe_v2</t>
         </is>
       </c>
       <c r="C680" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>[0]</t>
         </is>
       </c>
       <c r="D680" t="inlineStr">
         <is>
-          <t>skipped</t>
+          <t>filled (single-seed, grey)</t>
         </is>
       </c>
       <c r="E680" t="inlineStr">
         <is>
-          <t>row 'PACLock (pretrained, base)' not found</t>
+          <t>pr_auc 0.5417</t>
         </is>
       </c>
     </row>
@@ -25257,7 +25355,7 @@
       </c>
       <c r="B681" t="inlineStr">
         <is>
-          <t>paclock_pt_excl</t>
+          <t>paclock_pt_base</t>
         </is>
       </c>
       <c r="C681" t="inlineStr">
@@ -25272,7 +25370,7 @@
       </c>
       <c r="E681" t="inlineStr">
         <is>
-          <t>no row label for 'paclock_pt_excl'</t>
+          <t>row 'PACLock (pretrained, base)' not found</t>
         </is>
       </c>
     </row>
@@ -25284,7 +25382,7 @@
       </c>
       <c r="B682" t="inlineStr">
         <is>
-          <t>paclock_pt_large</t>
+          <t>paclock_pt_excl</t>
         </is>
       </c>
       <c r="C682" t="inlineStr">
@@ -25299,7 +25397,7 @@
       </c>
       <c r="E682" t="inlineStr">
         <is>
-          <t>row 'PACLock (pretrained, large)' not found</t>
+          <t>no row label for 'paclock_pt_excl'</t>
         </is>
       </c>
     </row>
@@ -25311,7 +25409,7 @@
       </c>
       <c r="B683" t="inlineStr">
         <is>
-          <t>paclock_rawpt_large</t>
+          <t>paclock_pt_large</t>
         </is>
       </c>
       <c r="C683" t="inlineStr">
@@ -25326,7 +25424,7 @@
       </c>
       <c r="E683" t="inlineStr">
         <is>
-          <t>no row label for 'paclock_rawpt_large'</t>
+          <t>row 'PACLock (pretrained, large)' not found</t>
         </is>
       </c>
     </row>
@@ -25338,7 +25436,7 @@
       </c>
       <c r="B684" t="inlineStr">
         <is>
-          <t>paclock_rawtok</t>
+          <t>paclock_rawpt_large</t>
         </is>
       </c>
       <c r="C684" t="inlineStr">
@@ -25353,7 +25451,7 @@
       </c>
       <c r="E684" t="inlineStr">
         <is>
-          <t>no row label for 'paclock_rawtok'</t>
+          <t>no row label for 'paclock_rawpt_large'</t>
         </is>
       </c>
     </row>
@@ -25365,7 +25463,7 @@
       </c>
       <c r="B685" t="inlineStr">
         <is>
-          <t>paclock_rot2</t>
+          <t>paclock_rawtok</t>
         </is>
       </c>
       <c r="C685" t="inlineStr">
@@ -25380,7 +25478,7 @@
       </c>
       <c r="E685" t="inlineStr">
         <is>
-          <t>no row label for 'paclock_rot2'</t>
+          <t>no row label for 'paclock_rawtok'</t>
         </is>
       </c>
     </row>
@@ -25392,7 +25490,7 @@
       </c>
       <c r="B686" t="inlineStr">
         <is>
-          <t>paclock_v2</t>
+          <t>paclock_rot2</t>
         </is>
       </c>
       <c r="C686" t="inlineStr">
@@ -25407,7 +25505,7 @@
       </c>
       <c r="E686" t="inlineStr">
         <is>
-          <t>row 'PACLock (from scratch, full)' not found</t>
+          <t>no row label for 'paclock_rot2'</t>
         </is>
       </c>
     </row>
@@ -25419,27 +25517,22 @@
       </c>
       <c r="B687" t="inlineStr">
         <is>
-          <t>reve_pretrained</t>
+          <t>paclock_v2</t>
         </is>
       </c>
       <c r="C687" t="inlineStr">
         <is>
-          <t>[0, 1, 2]</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D687" t="inlineStr">
         <is>
-          <t>filled</t>
+          <t>skipped</t>
         </is>
       </c>
       <c r="E687" t="inlineStr">
         <is>
-          <t>[实测 69.46M] pr_auc per-seed 0:0.4370, 1:0.5838, 2:0.4869</t>
-        </is>
-      </c>
-      <c r="F687" t="inlineStr">
-        <is>
-          <t>stopped_by=patience lr=0.0001 batch_size=128 epochs=15 patience=10 eval_every_steps=500 loss=bce_with_logits grad_clip=1.0</t>
+          <t>row 'PACLock (from scratch, full)' not found</t>
         </is>
       </c>
     </row>
@@ -25451,7 +25544,7 @@
       </c>
       <c r="B688" t="inlineStr">
         <is>
-          <t>sparcnet</t>
+          <t>reve_pretrained</t>
         </is>
       </c>
       <c r="C688" t="inlineStr">
@@ -25466,12 +25559,12 @@
       </c>
       <c r="E688" t="inlineStr">
         <is>
-          <t>[实测 1.14M] pr_auc per-seed 0:0.4795, 1:0.5046, 2:0.5218</t>
+          <t>[实测 69.46M] pr_auc per-seed 0:0.4370, 1:0.5838, 2:0.4869</t>
         </is>
       </c>
       <c r="F688" t="inlineStr">
         <is>
-          <t>lr=0.001 batch_size=512 epochs=20 patience=8 eval_every_steps=200 loss=bce_with_logits</t>
+          <t>stopped_by=patience lr=0.0001 batch_size=128 epochs=15 patience=10 eval_every_steps=500 loss=bce_with_logits grad_clip=1.0</t>
         </is>
       </c>
     </row>
@@ -25483,7 +25576,7 @@
       </c>
       <c r="B689" t="inlineStr">
         <is>
-          <t>st_transformer</t>
+          <t>sparcnet</t>
         </is>
       </c>
       <c r="C689" t="inlineStr">
@@ -25498,7 +25591,7 @@
       </c>
       <c r="E689" t="inlineStr">
         <is>
-          <t>[实测 3.43M] pr_auc per-seed 0:0.3318, 1:0.3515, 2:0.3933</t>
+          <t>[实测 1.14M] pr_auc per-seed 0:0.4795, 1:0.5046, 2:0.5218</t>
         </is>
       </c>
       <c r="F689" t="inlineStr">
@@ -25515,25 +25608,57 @@
       </c>
       <c r="B690" t="inlineStr">
         <is>
+          <t>st_transformer</t>
+        </is>
+      </c>
+      <c r="C690" t="inlineStr">
+        <is>
+          <t>[0, 1, 2]</t>
+        </is>
+      </c>
+      <c r="D690" t="inlineStr">
+        <is>
+          <t>filled</t>
+        </is>
+      </c>
+      <c r="E690" t="inlineStr">
+        <is>
+          <t>[实测 3.43M] pr_auc per-seed 0:0.3318, 1:0.3515, 2:0.3933</t>
+        </is>
+      </c>
+      <c r="F690" t="inlineStr">
+        <is>
+          <t>lr=0.001 batch_size=512 epochs=20 patience=8 eval_every_steps=200 loss=bce_with_logits</t>
+        </is>
+      </c>
+    </row>
+    <row r="691">
+      <c r="A691" t="inlineStr">
+        <is>
+          <t>tusz</t>
+        </is>
+      </c>
+      <c r="B691" t="inlineStr">
+        <is>
           <t>tfm_pretrained</t>
         </is>
       </c>
-      <c r="C690" t="inlineStr">
+      <c r="C691" t="inlineStr">
         <is>
           <t>[0, 1, 2]</t>
         </is>
       </c>
-      <c r="D690" t="inlineStr">
+      <c r="D691" t="inlineStr">
         <is>
           <t>filled</t>
         </is>
       </c>
-      <c r="E690" t="inlineStr">
+      <c r="E691" t="inlineStr">
         <is>
           <t>[实测 1.89M] pr_auc per-seed 0:0.3348, 1:0.3686, 2:0.3389</t>
         </is>
       </c>
-      <c r="F690" t="inlineStr">
+      <c r="F691" t="inlineStr">
         <is>
           <t>lr=0.001 batch_size=512 epochs=5 patience=10 eval_every_steps=100 loss=bce_with_logits label_smoothing=0.1</t>
         </is>

--- a/results/PACLock_baseline_matrix_filled.xlsx
+++ b/results/PACLock_baseline_matrix_filled.xlsx
@@ -27,6 +27,7 @@
     <sheet name="EEGMat" sheetId="18" state="visible" r:id="rId18"/>
     <sheet name="_填写记录" sheetId="19" state="visible" r:id="rId19"/>
     <sheet name="_消融" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet name="_预训练诊断" sheetId="21" state="visible" r:id="rId21"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1343,7 +1344,6 @@
         </is>
       </c>
     </row>
-    <row r="30"/>
     <row r="31">
       <c r="A31" s="6" t="inlineStr">
         <is>
@@ -1915,7 +1915,6 @@
         </is>
       </c>
     </row>
-    <row r="30"/>
     <row r="31">
       <c r="A31" s="6" t="inlineStr">
         <is>
@@ -2451,7 +2450,6 @@
         </is>
       </c>
     </row>
-    <row r="30"/>
     <row r="31">
       <c r="A31" s="6" t="inlineStr">
         <is>
@@ -3023,7 +3021,6 @@
         </is>
       </c>
     </row>
-    <row r="30"/>
     <row r="31">
       <c r="A31" s="6" t="inlineStr">
         <is>
@@ -3541,7 +3538,6 @@
         </is>
       </c>
     </row>
-    <row r="30"/>
     <row r="31">
       <c r="A31" s="6" t="inlineStr">
         <is>
@@ -4041,7 +4037,6 @@
         </is>
       </c>
     </row>
-    <row r="30"/>
     <row r="31">
       <c r="A31" s="6" t="inlineStr">
         <is>
@@ -4613,7 +4608,6 @@
         </is>
       </c>
     </row>
-    <row r="30"/>
     <row r="31">
       <c r="A31" s="6" t="inlineStr">
         <is>
@@ -5203,7 +5197,6 @@
         </is>
       </c>
     </row>
-    <row r="30"/>
     <row r="31">
       <c r="A31" s="6" t="inlineStr">
         <is>
@@ -5775,7 +5768,6 @@
         </is>
       </c>
     </row>
-    <row r="30"/>
     <row r="31">
       <c r="A31" s="6" t="inlineStr">
         <is>
@@ -27670,7 +27662,6 @@
         </is>
       </c>
     </row>
-    <row r="30"/>
     <row r="31">
       <c r="A31" s="6" t="inlineStr">
         <is>
@@ -27712,7 +27703,6 @@
         </is>
       </c>
     </row>
-    <row r="34"/>
     <row r="35">
       <c r="A35" s="6" t="inlineStr">
         <is>
@@ -29301,6 +29291,632 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E46"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>预训练诊断(2026-09-02 定稿;结论见 docs/FINDINGS.md 5.6)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>A. 冻结探针,lr=1e-3(与参考线匹配)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>checkpoint</t>
+        </is>
+      </c>
+      <c r="B4" s="1" t="inlineStr">
+        <is>
+          <t>TUSZ pr_auc</t>
+        </is>
+      </c>
+      <c r="C4" s="1" t="inlineStr">
+        <is>
+          <t>TUEV kappa</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>随机初始化</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>0.4076</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.3859</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>v1 欠训 1.6ep</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>0.4842</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.6351</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>v2 欠训 1.6ep</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>0.5417</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.5184</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>v2 收敛 15.4ep (ptF)</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>0.4445275840076715</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0.6509876244558666</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>v3(FAME) 20k</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0.3328237539130039</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.5391831434368992</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>v3(FAME) 40k</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0.4112430646733859</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.5496358730083497</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>v3(FAME) 60k</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>0.3836310517716551</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0.4708963361620297</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>v3(FAME) 80k</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>0.4718484877398866</v>
+      </c>
+      <c r="C12" t="n">
+        <v>0.5319707988149562</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>v3(FAME) 100k</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>0.5047550940108541</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.5639229466028473</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>A2. 同上,lr=1e-4(内部对照组,不与参考线比)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>v2 收敛 (ptF)</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>0.486</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0.5813</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>v3(FAME) 20k</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>0.397958610027846</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0.4715749021437604</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>v3(FAME) 40k</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>0.4911939914046341</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0.3708686448909037</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>v3(FAME) 60k</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>0.2777385287081304</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0.4875331791018003</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>v3(FAME) 80k</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>0.4883372136553454</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0.5155547316871869</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>v3(FAME) 100k</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>0.4924195988451215</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0.5144236053003975</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>B. 标注量消融(scratch vs ptF,单 seed)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>语料</t>
+        </is>
+      </c>
+      <c r="B24" s="1" t="inlineStr">
+        <is>
+          <t>训练量</t>
+        </is>
+      </c>
+      <c r="C24" s="1" t="inlineStr">
+        <is>
+          <t>scratch</t>
+        </is>
+      </c>
+      <c r="D24" s="1" t="inlineStr">
+        <is>
+          <t>ptF</t>
+        </is>
+      </c>
+      <c r="E24" s="1" t="inlineStr">
+        <is>
+          <t>delta</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>tusz</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>05%</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>0.6409847213931373</v>
+      </c>
+      <c r="D25" t="n">
+        <v>0.5777148438818177</v>
+      </c>
+      <c r="E25" t="n">
+        <v>-0.06326987751131963</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>tusz</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>0.5306988364843777</v>
+      </c>
+      <c r="D26" t="n">
+        <v>0.5821092683396684</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0.05141043185529071</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>tusz</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>0.5688782571777783</v>
+      </c>
+      <c r="D27" t="n">
+        <v>0.5916386242776533</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0.02276036709987506</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>tusz</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>0.6328</v>
+      </c>
+      <c r="D28" t="n">
+        <v>0.4968</v>
+      </c>
+      <c r="E28" t="n">
+        <v>-0.136</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>tuev</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>05%</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>0.5411598657522759</v>
+      </c>
+      <c r="D29" t="n">
+        <v>0.5205810950586779</v>
+      </c>
+      <c r="E29" t="n">
+        <v>-0.02057877069359804</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>tuev</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>0.6936138339658515</v>
+      </c>
+      <c r="D30" t="n">
+        <v>0.5747054109455207</v>
+      </c>
+      <c r="E30" t="n">
+        <v>-0.1189084230203308</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>tuev</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>0.7304827265373887</v>
+      </c>
+      <c r="D31" t="n">
+        <v>0.598865761794396</v>
+      </c>
+      <c r="E31" t="n">
+        <v>-0.1316169647429927</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>tuev</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>0.7094</v>
+      </c>
+      <c r="D32" t="n">
+        <v>0.5662</v>
+      </c>
+      <c r="E32" t="n">
+        <v>-0.1432</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="inlineStr">
+        <is>
+          <t>C. Siena 逐被试 AP(配方匹配对:32x4/60ep)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="inlineStr">
+        <is>
+          <t>被试</t>
+        </is>
+      </c>
+      <c r="B35" s="1" t="inlineStr">
+        <is>
+          <t>scratch</t>
+        </is>
+      </c>
+      <c r="C35" s="1" t="inlineStr">
+        <is>
+          <t>ptF</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>PN14</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>0.0159</v>
+      </c>
+      <c r="C36" t="n">
+        <v>0.1276</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>PN16</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>0.0304</v>
+      </c>
+      <c r="C37" t="n">
+        <v>0.5852000000000001</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>PN17</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>0.3515</v>
+      </c>
+      <c r="C38" t="n">
+        <v>0.7725</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>全局</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>0.0654</v>
+      </c>
+      <c r="C39" t="n">
+        <v>0.4682</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="inlineStr">
+        <is>
+          <t>D. 调参探针赢家(val 选优;赢家将于定稿波升为格子配方)</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="1" t="inlineStr">
+        <is>
+          <t>语料</t>
+        </is>
+      </c>
+      <c r="B42" s="1" t="inlineStr">
+        <is>
+          <t>arm</t>
+        </is>
+      </c>
+      <c r="C42" s="1" t="inlineStr">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+      <c r="D42" s="1" t="inlineStr">
+        <is>
+          <t>旧格子值</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>caueeg</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>paclock_tune_t3</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>0.5577902721924565</v>
+      </c>
+      <c r="D43" t="n">
+        <v>0.5254</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>mumtaz</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>paclock_tune_t1</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>0.9804125177809389</v>
+      </c>
+      <c r="D44" t="n">
+        <v>0.9775</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>tuar</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>paclock_tune_t1</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>0.6575608887426647</v>
+      </c>
+      <c r="D45" t="n">
+        <v>0.6289</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>adfd</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>paclock_ptF_lr3rd</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>0.4824716290965309</v>
+      </c>
+      <c r="D46" t="n">
+        <v>0.3786</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -29961,7 +30577,6 @@
         </is>
       </c>
     </row>
-    <row r="30"/>
     <row r="31">
       <c r="A31" s="6" t="inlineStr">
         <is>
@@ -30616,7 +31231,6 @@
         </is>
       </c>
     </row>
-    <row r="30"/>
     <row r="31">
       <c r="A31" s="6" t="inlineStr">
         <is>
@@ -31224,7 +31838,6 @@
         </is>
       </c>
     </row>
-    <row r="30"/>
     <row r="31">
       <c r="A31" s="6" t="inlineStr">
         <is>
@@ -31879,7 +32492,6 @@
         </is>
       </c>
     </row>
-    <row r="30"/>
     <row r="31">
       <c r="A31" s="6" t="inlineStr">
         <is>
@@ -32516,7 +33128,6 @@
         </is>
       </c>
     </row>
-    <row r="30"/>
     <row r="31">
       <c r="A31" s="6" t="inlineStr">
         <is>
@@ -32558,7 +33169,6 @@
         </is>
       </c>
     </row>
-    <row r="34"/>
     <row r="35">
       <c r="A35" s="6" t="inlineStr">
         <is>
@@ -33195,7 +33805,6 @@
         </is>
       </c>
     </row>
-    <row r="30"/>
     <row r="31">
       <c r="A31" s="6" t="inlineStr">
         <is>
@@ -33785,7 +34394,6 @@
         </is>
       </c>
     </row>
-    <row r="30"/>
     <row r="31">
       <c r="A31" s="6" t="inlineStr">
         <is>
@@ -33798,7 +34406,6 @@
         </is>
       </c>
     </row>
-    <row r="32"/>
     <row r="33">
       <c r="A33" s="6" t="inlineStr">
         <is>

--- a/results/PACLock_baseline_matrix_filled.xlsx
+++ b/results/PACLock_baseline_matrix_filled.xlsx
@@ -5923,7 +5923,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F767"/>
+  <dimension ref="A1:F769"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20754,22 +20754,22 @@
       </c>
       <c r="B516" t="inlineStr">
         <is>
-          <t>paclock_pt_base</t>
+          <t>paclock_duplex_ptS</t>
         </is>
       </c>
       <c r="C516" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>[0]</t>
         </is>
       </c>
       <c r="D516" t="inlineStr">
         <is>
-          <t>skipped</t>
+          <t>filled (single-seed, grey)</t>
         </is>
       </c>
       <c r="E516" t="inlineStr">
         <is>
-          <t>row 'PACLock (pretrained, base)' not found</t>
+          <t>auroc 0.8892</t>
         </is>
       </c>
     </row>
@@ -20781,7 +20781,7 @@
       </c>
       <c r="B517" t="inlineStr">
         <is>
-          <t>paclock_pt_large</t>
+          <t>paclock_pt_base</t>
         </is>
       </c>
       <c r="C517" t="inlineStr">
@@ -20796,7 +20796,7 @@
       </c>
       <c r="E517" t="inlineStr">
         <is>
-          <t>row 'PACLock (pretrained, large)' not found</t>
+          <t>row 'PACLock (pretrained, base)' not found</t>
         </is>
       </c>
     </row>
@@ -20808,7 +20808,7 @@
       </c>
       <c r="B518" t="inlineStr">
         <is>
-          <t>paclock_rawtok</t>
+          <t>paclock_pt_large</t>
         </is>
       </c>
       <c r="C518" t="inlineStr">
@@ -20823,7 +20823,7 @@
       </c>
       <c r="E518" t="inlineStr">
         <is>
-          <t>no row label for 'paclock_rawtok'</t>
+          <t>row 'PACLock (pretrained, large)' not found</t>
         </is>
       </c>
     </row>
@@ -20835,7 +20835,7 @@
       </c>
       <c r="B519" t="inlineStr">
         <is>
-          <t>paclock_rot2</t>
+          <t>paclock_rawtok</t>
         </is>
       </c>
       <c r="C519" t="inlineStr">
@@ -20850,7 +20850,7 @@
       </c>
       <c r="E519" t="inlineStr">
         <is>
-          <t>no row label for 'paclock_rot2'</t>
+          <t>no row label for 'paclock_rawtok'</t>
         </is>
       </c>
     </row>
@@ -20862,7 +20862,7 @@
       </c>
       <c r="B520" t="inlineStr">
         <is>
-          <t>paclock_v2</t>
+          <t>paclock_rot2</t>
         </is>
       </c>
       <c r="C520" t="inlineStr">
@@ -20877,7 +20877,7 @@
       </c>
       <c r="E520" t="inlineStr">
         <is>
-          <t>row 'PACLock (from scratch, full)' not found</t>
+          <t>no row label for 'paclock_rot2'</t>
         </is>
       </c>
     </row>
@@ -20889,27 +20889,22 @@
       </c>
       <c r="B521" t="inlineStr">
         <is>
-          <t>reve_pretrained</t>
+          <t>paclock_v2</t>
         </is>
       </c>
       <c r="C521" t="inlineStr">
         <is>
-          <t>[0, 1, 2]</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D521" t="inlineStr">
         <is>
-          <t>filled</t>
+          <t>skipped</t>
         </is>
       </c>
       <c r="E521" t="inlineStr">
         <is>
-          <t>[实测 69.46M] auroc per-seed 0:0.9037, 1:0.8950, 2:0.8848</t>
-        </is>
-      </c>
-      <c r="F521" t="inlineStr">
-        <is>
-          <t>stopped_by=patience lr=0.0001 batch_size=128 epochs=15 patience=10 eval_every_steps=500 loss=bce_with_logits grad_clip=1.0</t>
+          <t>row 'PACLock (from scratch, full)' not found</t>
         </is>
       </c>
     </row>
@@ -20921,7 +20916,7 @@
       </c>
       <c r="B522" t="inlineStr">
         <is>
-          <t>sparcnet</t>
+          <t>reve_pretrained</t>
         </is>
       </c>
       <c r="C522" t="inlineStr">
@@ -20936,12 +20931,12 @@
       </c>
       <c r="E522" t="inlineStr">
         <is>
-          <t>[实测 1.14M] auroc per-seed 0:0.8836, 1:0.8896, 2:0.8898</t>
+          <t>[实测 69.46M] auroc per-seed 0:0.9037, 1:0.8950, 2:0.8848</t>
         </is>
       </c>
       <c r="F522" t="inlineStr">
         <is>
-          <t>lr=0.001 batch_size=512 epochs=20 patience=8 eval_every_steps=200 loss=bce_with_logits</t>
+          <t>stopped_by=patience lr=0.0001 batch_size=128 epochs=15 patience=10 eval_every_steps=500 loss=bce_with_logits grad_clip=1.0</t>
         </is>
       </c>
     </row>
@@ -20953,7 +20948,7 @@
       </c>
       <c r="B523" t="inlineStr">
         <is>
-          <t>st_transformer</t>
+          <t>sparcnet</t>
         </is>
       </c>
       <c r="C523" t="inlineStr">
@@ -20968,7 +20963,7 @@
       </c>
       <c r="E523" t="inlineStr">
         <is>
-          <t>[实测 3.43M] auroc per-seed 0:0.9017, 1:0.8992, 2:0.8908</t>
+          <t>[实测 1.14M] auroc per-seed 0:0.8836, 1:0.8896, 2:0.8898</t>
         </is>
       </c>
       <c r="F523" t="inlineStr">
@@ -20985,7 +20980,7 @@
       </c>
       <c r="B524" t="inlineStr">
         <is>
-          <t>tfm_pretrained</t>
+          <t>st_transformer</t>
         </is>
       </c>
       <c r="C524" t="inlineStr">
@@ -21000,39 +20995,44 @@
       </c>
       <c r="E524" t="inlineStr">
         <is>
-          <t>[实测 1.89M] auroc per-seed 0:0.8785, 1:0.8821, 2:0.8772</t>
+          <t>[实测 3.43M] auroc per-seed 0:0.9017, 1:0.8992, 2:0.8908</t>
         </is>
       </c>
       <c r="F524" t="inlineStr">
         <is>
-          <t>lr=0.001 batch_size=512 epochs=10 patience=10 eval_every_steps=100 loss=bce_with_logits label_smoothing=0.1</t>
+          <t>lr=0.001 batch_size=512 epochs=20 patience=8 eval_every_steps=200 loss=bce_with_logits</t>
         </is>
       </c>
     </row>
     <row r="525">
       <c r="A525" t="inlineStr">
         <is>
-          <t>tuar</t>
+          <t>tuab</t>
         </is>
       </c>
       <c r="B525" t="inlineStr">
         <is>
-          <t>biot_prest16</t>
+          <t>tfm_pretrained</t>
         </is>
       </c>
       <c r="C525" t="inlineStr">
         <is>
-          <t>[0, 1]</t>
+          <t>[0, 1, 2]</t>
         </is>
       </c>
       <c r="D525" t="inlineStr">
         <is>
-          <t>filled (single-seed, grey)</t>
+          <t>filled</t>
         </is>
       </c>
       <c r="E525" t="inlineStr">
         <is>
-          <t>cohen_kappa 0.5750, 0.5053</t>
+          <t>[实测 1.89M] auroc per-seed 0:0.8785, 1:0.8821, 2:0.8772</t>
+        </is>
+      </c>
+      <c r="F525" t="inlineStr">
+        <is>
+          <t>lr=0.001 batch_size=512 epochs=10 patience=10 eval_every_steps=100 loss=bce_with_logits label_smoothing=0.1</t>
         </is>
       </c>
     </row>
@@ -21044,12 +21044,12 @@
       </c>
       <c r="B526" t="inlineStr">
         <is>
-          <t>biot_scratch</t>
+          <t>biot_prest16</t>
         </is>
       </c>
       <c r="C526" t="inlineStr">
         <is>
-          <t>[0]</t>
+          <t>[0, 1]</t>
         </is>
       </c>
       <c r="D526" t="inlineStr">
@@ -21059,7 +21059,7 @@
       </c>
       <c r="E526" t="inlineStr">
         <is>
-          <t>cohen_kappa 0.4985</t>
+          <t>cohen_kappa 0.5750, 0.5053</t>
         </is>
       </c>
     </row>
@@ -21071,7 +21071,7 @@
       </c>
       <c r="B527" t="inlineStr">
         <is>
-          <t>cbramod_pretrained</t>
+          <t>biot_scratch</t>
         </is>
       </c>
       <c r="C527" t="inlineStr">
@@ -21086,7 +21086,7 @@
       </c>
       <c r="E527" t="inlineStr">
         <is>
-          <t>cohen_kappa 0.7147</t>
+          <t>cohen_kappa 0.4985</t>
         </is>
       </c>
     </row>
@@ -21098,7 +21098,7 @@
       </c>
       <c r="B528" t="inlineStr">
         <is>
-          <t>cbramod_scratch</t>
+          <t>cbramod_pretrained</t>
         </is>
       </c>
       <c r="C528" t="inlineStr">
@@ -21113,7 +21113,7 @@
       </c>
       <c r="E528" t="inlineStr">
         <is>
-          <t>cohen_kappa 0.6503</t>
+          <t>cohen_kappa 0.7147</t>
         </is>
       </c>
     </row>
@@ -21125,7 +21125,7 @@
       </c>
       <c r="B529" t="inlineStr">
         <is>
-          <t>cnn_transformer</t>
+          <t>cbramod_scratch</t>
         </is>
       </c>
       <c r="C529" t="inlineStr">
@@ -21140,7 +21140,7 @@
       </c>
       <c r="E529" t="inlineStr">
         <is>
-          <t>cohen_kappa 0.7120</t>
+          <t>cohen_kappa 0.6503</t>
         </is>
       </c>
     </row>
@@ -21152,7 +21152,7 @@
       </c>
       <c r="B530" t="inlineStr">
         <is>
-          <t>contrawr</t>
+          <t>cnn_transformer</t>
         </is>
       </c>
       <c r="C530" t="inlineStr">
@@ -21167,7 +21167,7 @@
       </c>
       <c r="E530" t="inlineStr">
         <is>
-          <t>cohen_kappa 0.6630</t>
+          <t>cohen_kappa 0.7120</t>
         </is>
       </c>
     </row>
@@ -21179,7 +21179,7 @@
       </c>
       <c r="B531" t="inlineStr">
         <is>
-          <t>eegpt_pretrained</t>
+          <t>contrawr</t>
         </is>
       </c>
       <c r="C531" t="inlineStr">
@@ -21194,7 +21194,7 @@
       </c>
       <c r="E531" t="inlineStr">
         <is>
-          <t>cohen_kappa 0.5235</t>
+          <t>cohen_kappa 0.6630</t>
         </is>
       </c>
     </row>
@@ -21206,7 +21206,7 @@
       </c>
       <c r="B532" t="inlineStr">
         <is>
-          <t>eegpt_scratch</t>
+          <t>eegpt_pretrained</t>
         </is>
       </c>
       <c r="C532" t="inlineStr">
@@ -21221,7 +21221,7 @@
       </c>
       <c r="E532" t="inlineStr">
         <is>
-          <t>cohen_kappa 0.5820</t>
+          <t>cohen_kappa 0.5235</t>
         </is>
       </c>
     </row>
@@ -21233,7 +21233,7 @@
       </c>
       <c r="B533" t="inlineStr">
         <is>
-          <t>ffcl</t>
+          <t>eegpt_scratch</t>
         </is>
       </c>
       <c r="C533" t="inlineStr">
@@ -21248,7 +21248,7 @@
       </c>
       <c r="E533" t="inlineStr">
         <is>
-          <t>cohen_kappa 0.6959</t>
+          <t>cohen_kappa 0.5820</t>
         </is>
       </c>
     </row>
@@ -21260,7 +21260,7 @@
       </c>
       <c r="B534" t="inlineStr">
         <is>
-          <t>labram_pretrained</t>
+          <t>ffcl</t>
         </is>
       </c>
       <c r="C534" t="inlineStr">
@@ -21275,7 +21275,7 @@
       </c>
       <c r="E534" t="inlineStr">
         <is>
-          <t>cohen_kappa 0.5931</t>
+          <t>cohen_kappa 0.6959</t>
         </is>
       </c>
     </row>
@@ -21287,7 +21287,7 @@
       </c>
       <c r="B535" t="inlineStr">
         <is>
-          <t>labram_scratch</t>
+          <t>labram_pretrained</t>
         </is>
       </c>
       <c r="C535" t="inlineStr">
@@ -21302,7 +21302,7 @@
       </c>
       <c r="E535" t="inlineStr">
         <is>
-          <t>cohen_kappa 0.5265</t>
+          <t>cohen_kappa 0.5931</t>
         </is>
       </c>
     </row>
@@ -21314,7 +21314,7 @@
       </c>
       <c r="B536" t="inlineStr">
         <is>
-          <t>paclock_duplex</t>
+          <t>labram_scratch</t>
         </is>
       </c>
       <c r="C536" t="inlineStr">
@@ -21329,7 +21329,7 @@
       </c>
       <c r="E536" t="inlineStr">
         <is>
-          <t>cohen_kappa 0.6289</t>
+          <t>cohen_kappa 0.5265</t>
         </is>
       </c>
     </row>
@@ -21341,7 +21341,7 @@
       </c>
       <c r="B537" t="inlineStr">
         <is>
-          <t>paclock_duplex_ptS</t>
+          <t>paclock_duplex</t>
         </is>
       </c>
       <c r="C537" t="inlineStr">
@@ -21356,7 +21356,7 @@
       </c>
       <c r="E537" t="inlineStr">
         <is>
-          <t>cohen_kappa 0.5923</t>
+          <t>cohen_kappa 0.6289</t>
         </is>
       </c>
     </row>
@@ -21368,22 +21368,22 @@
       </c>
       <c r="B538" t="inlineStr">
         <is>
-          <t>paclock_pac</t>
+          <t>paclock_duplex_ptS</t>
         </is>
       </c>
       <c r="C538" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>[0]</t>
         </is>
       </c>
       <c r="D538" t="inlineStr">
         <is>
-          <t>skipped</t>
+          <t>filled (single-seed, grey)</t>
         </is>
       </c>
       <c r="E538" t="inlineStr">
         <is>
-          <t>the workbook has no row for this variant</t>
+          <t>cohen_kappa 0.5923</t>
         </is>
       </c>
     </row>
@@ -21395,7 +21395,7 @@
       </c>
       <c r="B539" t="inlineStr">
         <is>
-          <t>paclock_ptF_t1</t>
+          <t>paclock_pac</t>
         </is>
       </c>
       <c r="C539" t="inlineStr">
@@ -21410,7 +21410,7 @@
       </c>
       <c r="E539" t="inlineStr">
         <is>
-          <t>no row label for 'paclock_ptF_t1'</t>
+          <t>the workbook has no row for this variant</t>
         </is>
       </c>
     </row>
@@ -21422,7 +21422,7 @@
       </c>
       <c r="B540" t="inlineStr">
         <is>
-          <t>paclock_ptF_t2</t>
+          <t>paclock_ptF_t1</t>
         </is>
       </c>
       <c r="C540" t="inlineStr">
@@ -21437,7 +21437,7 @@
       </c>
       <c r="E540" t="inlineStr">
         <is>
-          <t>no row label for 'paclock_ptF_t2'</t>
+          <t>no row label for 'paclock_ptF_t1'</t>
         </is>
       </c>
     </row>
@@ -21449,7 +21449,7 @@
       </c>
       <c r="B541" t="inlineStr">
         <is>
-          <t>paclock_raw</t>
+          <t>paclock_ptF_t2</t>
         </is>
       </c>
       <c r="C541" t="inlineStr">
@@ -21464,7 +21464,7 @@
       </c>
       <c r="E541" t="inlineStr">
         <is>
-          <t>no row label for 'paclock_raw'</t>
+          <t>no row label for 'paclock_ptF_t2'</t>
         </is>
       </c>
     </row>
@@ -21476,7 +21476,7 @@
       </c>
       <c r="B542" t="inlineStr">
         <is>
-          <t>paclock_rot</t>
+          <t>paclock_raw</t>
         </is>
       </c>
       <c r="C542" t="inlineStr">
@@ -21491,7 +21491,7 @@
       </c>
       <c r="E542" t="inlineStr">
         <is>
-          <t>no row label for 'paclock_rot'</t>
+          <t>no row label for 'paclock_raw'</t>
         </is>
       </c>
     </row>
@@ -21503,7 +21503,7 @@
       </c>
       <c r="B543" t="inlineStr">
         <is>
-          <t>paclock_tune_t1</t>
+          <t>paclock_rot</t>
         </is>
       </c>
       <c r="C543" t="inlineStr">
@@ -21518,7 +21518,7 @@
       </c>
       <c r="E543" t="inlineStr">
         <is>
-          <t>no row label for 'paclock_tune_t1'</t>
+          <t>no row label for 'paclock_rot'</t>
         </is>
       </c>
     </row>
@@ -21530,7 +21530,7 @@
       </c>
       <c r="B544" t="inlineStr">
         <is>
-          <t>paclock_tune_t2</t>
+          <t>paclock_tune_t1</t>
         </is>
       </c>
       <c r="C544" t="inlineStr">
@@ -21545,7 +21545,7 @@
       </c>
       <c r="E544" t="inlineStr">
         <is>
-          <t>no row label for 'paclock_tune_t2'</t>
+          <t>no row label for 'paclock_tune_t1'</t>
         </is>
       </c>
     </row>
@@ -21557,22 +21557,22 @@
       </c>
       <c r="B545" t="inlineStr">
         <is>
-          <t>sparcnet</t>
+          <t>paclock_tune_t2</t>
         </is>
       </c>
       <c r="C545" t="inlineStr">
         <is>
-          <t>[0]</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D545" t="inlineStr">
         <is>
-          <t>filled (single-seed, grey)</t>
+          <t>skipped</t>
         </is>
       </c>
       <c r="E545" t="inlineStr">
         <is>
-          <t>cohen_kappa 0.6010</t>
+          <t>no row label for 'paclock_tune_t2'</t>
         </is>
       </c>
     </row>
@@ -21584,7 +21584,7 @@
       </c>
       <c r="B546" t="inlineStr">
         <is>
-          <t>st_transformer</t>
+          <t>sparcnet</t>
         </is>
       </c>
       <c r="C546" t="inlineStr">
@@ -21599,7 +21599,7 @@
       </c>
       <c r="E546" t="inlineStr">
         <is>
-          <t>cohen_kappa 0.5213</t>
+          <t>cohen_kappa 0.6010</t>
         </is>
       </c>
     </row>
@@ -21611,7 +21611,7 @@
       </c>
       <c r="B547" t="inlineStr">
         <is>
-          <t>tfm_pretrained</t>
+          <t>st_transformer</t>
         </is>
       </c>
       <c r="C547" t="inlineStr">
@@ -21626,7 +21626,7 @@
       </c>
       <c r="E547" t="inlineStr">
         <is>
-          <t>cohen_kappa 0.6480</t>
+          <t>cohen_kappa 0.5213</t>
         </is>
       </c>
     </row>
@@ -21638,7 +21638,7 @@
       </c>
       <c r="B548" t="inlineStr">
         <is>
-          <t>tfm_scratch</t>
+          <t>tfm_pretrained</t>
         </is>
       </c>
       <c r="C548" t="inlineStr">
@@ -21653,39 +21653,34 @@
       </c>
       <c r="E548" t="inlineStr">
         <is>
-          <t>cohen_kappa 0.3644</t>
+          <t>cohen_kappa 0.6480</t>
         </is>
       </c>
     </row>
     <row r="549">
       <c r="A549" t="inlineStr">
         <is>
-          <t>tuep</t>
+          <t>tuar</t>
         </is>
       </c>
       <c r="B549" t="inlineStr">
         <is>
-          <t>biot_prest16</t>
+          <t>tfm_scratch</t>
         </is>
       </c>
       <c r="C549" t="inlineStr">
         <is>
-          <t>[0, 1, 2]</t>
+          <t>[0]</t>
         </is>
       </c>
       <c r="D549" t="inlineStr">
         <is>
-          <t>filled</t>
+          <t>filled (single-seed, grey)</t>
         </is>
       </c>
       <c r="E549" t="inlineStr">
         <is>
-          <t>[实测 3.19M] auroc per-seed 0:0.7513, 1:0.7452, 2:0.7823</t>
-        </is>
-      </c>
-      <c r="F549" t="inlineStr">
-        <is>
-          <t>stopped_by=patience lr=0.001 batch_size=512 epochs=100 patience=5 eval_every_steps=0 loss=bce_with_logits</t>
+          <t>cohen_kappa 0.3644</t>
         </is>
       </c>
     </row>
@@ -21697,7 +21692,7 @@
       </c>
       <c r="B550" t="inlineStr">
         <is>
-          <t>biot_scratch</t>
+          <t>biot_prest16</t>
         </is>
       </c>
       <c r="C550" t="inlineStr">
@@ -21712,7 +21707,7 @@
       </c>
       <c r="E550" t="inlineStr">
         <is>
-          <t>[实测 3.19M] auroc per-seed 0:0.7593, 1:0.7374, 2:0.7599</t>
+          <t>[实测 3.19M] auroc per-seed 0:0.7513, 1:0.7452, 2:0.7823</t>
         </is>
       </c>
       <c r="F550" t="inlineStr">
@@ -21729,22 +21724,27 @@
       </c>
       <c r="B551" t="inlineStr">
         <is>
-          <t>cbramod_crofremo</t>
+          <t>biot_scratch</t>
         </is>
       </c>
       <c r="C551" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>[0, 1, 2]</t>
         </is>
       </c>
       <c r="D551" t="inlineStr">
         <is>
-          <t>skipped</t>
+          <t>filled</t>
         </is>
       </c>
       <c r="E551" t="inlineStr">
         <is>
-          <t>no row label for 'cbramod_crofremo'</t>
+          <t>[实测 3.19M] auroc per-seed 0:0.7593, 1:0.7374, 2:0.7599</t>
+        </is>
+      </c>
+      <c r="F551" t="inlineStr">
+        <is>
+          <t>stopped_by=patience lr=0.001 batch_size=512 epochs=100 patience=5 eval_every_steps=0 loss=bce_with_logits</t>
         </is>
       </c>
     </row>
@@ -21756,27 +21756,22 @@
       </c>
       <c r="B552" t="inlineStr">
         <is>
-          <t>cbramod_pretrained</t>
+          <t>cbramod_crofremo</t>
         </is>
       </c>
       <c r="C552" t="inlineStr">
         <is>
-          <t>[0, 1, 2]</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D552" t="inlineStr">
         <is>
-          <t>filled</t>
+          <t>skipped</t>
         </is>
       </c>
       <c r="E552" t="inlineStr">
         <is>
-          <t>[实测 30.65M] auroc per-seed 0:0.6891, 1:0.6516, 2:0.6533</t>
-        </is>
-      </c>
-      <c r="F552" t="inlineStr">
-        <is>
-          <t>lr=0.0001 batch_size=64 epochs=50 patience=0 eval_every_steps=0 loss=bce_with_logits grad_clip=1.0 select_metric=auroc multi_lr=True</t>
+          <t>no row label for 'cbramod_crofremo'</t>
         </is>
       </c>
     </row>
@@ -21788,7 +21783,7 @@
       </c>
       <c r="B553" t="inlineStr">
         <is>
-          <t>cbramod_scratch</t>
+          <t>cbramod_pretrained</t>
         </is>
       </c>
       <c r="C553" t="inlineStr">
@@ -21803,7 +21798,7 @@
       </c>
       <c r="E553" t="inlineStr">
         <is>
-          <t>[实测 30.65M] auroc per-seed 0:0.6043, 1:0.6529, 2:0.6695</t>
+          <t>[实测 30.65M] auroc per-seed 0:0.6891, 1:0.6516, 2:0.6533</t>
         </is>
       </c>
       <c r="F553" t="inlineStr">
@@ -21820,7 +21815,7 @@
       </c>
       <c r="B554" t="inlineStr">
         <is>
-          <t>cnn_transformer</t>
+          <t>cbramod_scratch</t>
         </is>
       </c>
       <c r="C554" t="inlineStr">
@@ -21835,12 +21830,12 @@
       </c>
       <c r="E554" t="inlineStr">
         <is>
-          <t>[实测 3.15M] auroc per-seed 0:0.6580, 1:0.6790, 2:0.6519</t>
+          <t>[实测 30.65M] auroc per-seed 0:0.6043, 1:0.6529, 2:0.6695</t>
         </is>
       </c>
       <c r="F554" t="inlineStr">
         <is>
-          <t>stopped_by=patience lr=0.001 batch_size=512 epochs=20 patience=8 eval_every_steps=200 loss=bce_with_logits</t>
+          <t>lr=0.0001 batch_size=64 epochs=50 patience=0 eval_every_steps=0 loss=bce_with_logits grad_clip=1.0 select_metric=auroc multi_lr=True</t>
         </is>
       </c>
     </row>
@@ -21852,7 +21847,7 @@
       </c>
       <c r="B555" t="inlineStr">
         <is>
-          <t>contrawr</t>
+          <t>cnn_transformer</t>
         </is>
       </c>
       <c r="C555" t="inlineStr">
@@ -21867,7 +21862,7 @@
       </c>
       <c r="E555" t="inlineStr">
         <is>
-          <t>[实测 1.57M] auroc per-seed 0:0.6938, 1:0.5756, 2:0.6699</t>
+          <t>[实测 3.15M] auroc per-seed 0:0.6580, 1:0.6790, 2:0.6519</t>
         </is>
       </c>
       <c r="F555" t="inlineStr">
@@ -21884,7 +21879,7 @@
       </c>
       <c r="B556" t="inlineStr">
         <is>
-          <t>csbrain_pretrained</t>
+          <t>contrawr</t>
         </is>
       </c>
       <c r="C556" t="inlineStr">
@@ -21899,12 +21894,12 @@
       </c>
       <c r="E556" t="inlineStr">
         <is>
-          <t>[实测 41.06M] auroc per-seed 0:0.5971, 1:0.6439, 2:0.5581</t>
+          <t>[实测 1.57M] auroc per-seed 0:0.6938, 1:0.5756, 2:0.6699</t>
         </is>
       </c>
       <c r="F556" t="inlineStr">
         <is>
-          <t>stopped_by=patience lr=0.0001 batch_size=64 epochs=50 patience=10 eval_every_steps=0 loss=bce_with_logits grad_clip=1.0</t>
+          <t>stopped_by=patience lr=0.001 batch_size=512 epochs=20 patience=8 eval_every_steps=200 loss=bce_with_logits</t>
         </is>
       </c>
     </row>
@@ -21916,7 +21911,7 @@
       </c>
       <c r="B557" t="inlineStr">
         <is>
-          <t>eegconformer</t>
+          <t>csbrain_pretrained</t>
         </is>
       </c>
       <c r="C557" t="inlineStr">
@@ -21931,12 +21926,12 @@
       </c>
       <c r="E557" t="inlineStr">
         <is>
-          <t>[实测 1.46M] auroc per-seed 0:0.7562, 1:0.7349, 2:0.6733</t>
+          <t>[实测 41.06M] auroc per-seed 0:0.5971, 1:0.6439, 2:0.5581</t>
         </is>
       </c>
       <c r="F557" t="inlineStr">
         <is>
-          <t>stopped_by=patience lr=0.0003 batch_size=128 epochs=20 patience=8 eval_every_steps=200 loss=bce_with_logits grad_clip=1.0</t>
+          <t>stopped_by=patience lr=0.0001 batch_size=64 epochs=50 patience=10 eval_every_steps=0 loss=bce_with_logits grad_clip=1.0</t>
         </is>
       </c>
     </row>
@@ -21948,22 +21943,27 @@
       </c>
       <c r="B558" t="inlineStr">
         <is>
-          <t>eegconformer_t1</t>
+          <t>eegconformer</t>
         </is>
       </c>
       <c r="C558" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>[0, 1, 2]</t>
         </is>
       </c>
       <c r="D558" t="inlineStr">
         <is>
-          <t>skipped</t>
+          <t>filled</t>
         </is>
       </c>
       <c r="E558" t="inlineStr">
         <is>
-          <t>no row label for 'eegconformer_t1'</t>
+          <t>[实测 1.46M] auroc per-seed 0:0.7562, 1:0.7349, 2:0.6733</t>
+        </is>
+      </c>
+      <c r="F558" t="inlineStr">
+        <is>
+          <t>stopped_by=patience lr=0.0003 batch_size=128 epochs=20 patience=8 eval_every_steps=200 loss=bce_with_logits grad_clip=1.0</t>
         </is>
       </c>
     </row>
@@ -21975,7 +21975,7 @@
       </c>
       <c r="B559" t="inlineStr">
         <is>
-          <t>eegconformer_t2</t>
+          <t>eegconformer_t1</t>
         </is>
       </c>
       <c r="C559" t="inlineStr">
@@ -21990,7 +21990,7 @@
       </c>
       <c r="E559" t="inlineStr">
         <is>
-          <t>no row label for 'eegconformer_t2'</t>
+          <t>no row label for 'eegconformer_t1'</t>
         </is>
       </c>
     </row>
@@ -22002,7 +22002,7 @@
       </c>
       <c r="B560" t="inlineStr">
         <is>
-          <t>eegconformer_t3</t>
+          <t>eegconformer_t2</t>
         </is>
       </c>
       <c r="C560" t="inlineStr">
@@ -22017,7 +22017,7 @@
       </c>
       <c r="E560" t="inlineStr">
         <is>
-          <t>no row label for 'eegconformer_t3'</t>
+          <t>no row label for 'eegconformer_t2'</t>
         </is>
       </c>
     </row>
@@ -22029,7 +22029,7 @@
       </c>
       <c r="B561" t="inlineStr">
         <is>
-          <t>eegconformer_t4</t>
+          <t>eegconformer_t3</t>
         </is>
       </c>
       <c r="C561" t="inlineStr">
@@ -22044,7 +22044,7 @@
       </c>
       <c r="E561" t="inlineStr">
         <is>
-          <t>no row label for 'eegconformer_t4'</t>
+          <t>no row label for 'eegconformer_t3'</t>
         </is>
       </c>
     </row>
@@ -22056,27 +22056,22 @@
       </c>
       <c r="B562" t="inlineStr">
         <is>
-          <t>eegnet</t>
+          <t>eegconformer_t4</t>
         </is>
       </c>
       <c r="C562" t="inlineStr">
         <is>
-          <t>[0, 1, 2]</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D562" t="inlineStr">
         <is>
-          <t>filled</t>
+          <t>skipped</t>
         </is>
       </c>
       <c r="E562" t="inlineStr">
         <is>
-          <t>[实测 0.00M] auroc per-seed 0:0.7773, 1:0.7919, 2:0.7852</t>
-        </is>
-      </c>
-      <c r="F562" t="inlineStr">
-        <is>
-          <t>stopped_by=patience lr=0.001 batch_size=512 epochs=20 patience=8 eval_every_steps=200 loss=bce_with_logits grad_clip=1.0</t>
+          <t>no row label for 'eegconformer_t4'</t>
         </is>
       </c>
     </row>
@@ -22088,22 +22083,27 @@
       </c>
       <c r="B563" t="inlineStr">
         <is>
-          <t>eegnet_t1</t>
+          <t>eegnet</t>
         </is>
       </c>
       <c r="C563" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>[0, 1, 2]</t>
         </is>
       </c>
       <c r="D563" t="inlineStr">
         <is>
-          <t>skipped</t>
+          <t>filled</t>
         </is>
       </c>
       <c r="E563" t="inlineStr">
         <is>
-          <t>no row label for 'eegnet_t1'</t>
+          <t>[实测 0.00M] auroc per-seed 0:0.7773, 1:0.7919, 2:0.7852</t>
+        </is>
+      </c>
+      <c r="F563" t="inlineStr">
+        <is>
+          <t>stopped_by=patience lr=0.001 batch_size=512 epochs=20 patience=8 eval_every_steps=200 loss=bce_with_logits grad_clip=1.0</t>
         </is>
       </c>
     </row>
@@ -22115,7 +22115,7 @@
       </c>
       <c r="B564" t="inlineStr">
         <is>
-          <t>eegnet_t2</t>
+          <t>eegnet_t1</t>
         </is>
       </c>
       <c r="C564" t="inlineStr">
@@ -22130,7 +22130,7 @@
       </c>
       <c r="E564" t="inlineStr">
         <is>
-          <t>no row label for 'eegnet_t2'</t>
+          <t>no row label for 'eegnet_t1'</t>
         </is>
       </c>
     </row>
@@ -22142,7 +22142,7 @@
       </c>
       <c r="B565" t="inlineStr">
         <is>
-          <t>eegnet_t3</t>
+          <t>eegnet_t2</t>
         </is>
       </c>
       <c r="C565" t="inlineStr">
@@ -22157,7 +22157,7 @@
       </c>
       <c r="E565" t="inlineStr">
         <is>
-          <t>no row label for 'eegnet_t3'</t>
+          <t>no row label for 'eegnet_t2'</t>
         </is>
       </c>
     </row>
@@ -22169,7 +22169,7 @@
       </c>
       <c r="B566" t="inlineStr">
         <is>
-          <t>eegnet_t4</t>
+          <t>eegnet_t3</t>
         </is>
       </c>
       <c r="C566" t="inlineStr">
@@ -22184,7 +22184,7 @@
       </c>
       <c r="E566" t="inlineStr">
         <is>
-          <t>no row label for 'eegnet_t4'</t>
+          <t>no row label for 'eegnet_t3'</t>
         </is>
       </c>
     </row>
@@ -22196,27 +22196,22 @@
       </c>
       <c r="B567" t="inlineStr">
         <is>
-          <t>eegpt_pretrained</t>
+          <t>eegnet_t4</t>
         </is>
       </c>
       <c r="C567" t="inlineStr">
         <is>
-          <t>[0, 1, 2]</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D567" t="inlineStr">
         <is>
-          <t>filled</t>
+          <t>skipped</t>
         </is>
       </c>
       <c r="E567" t="inlineStr">
         <is>
-          <t>[实测 25.69M] auroc per-seed 0:0.7150, 1:0.7690, 2:0.7486</t>
-        </is>
-      </c>
-      <c r="F567" t="inlineStr">
-        <is>
-          <t>stopped_by=patience lr=0.0004 batch_size=32 epochs=40 patience=10 eval_every_steps=500 loss=bce_with_logits</t>
+          <t>no row label for 'eegnet_t4'</t>
         </is>
       </c>
     </row>
@@ -22228,7 +22223,7 @@
       </c>
       <c r="B568" t="inlineStr">
         <is>
-          <t>eegpt_scratch</t>
+          <t>eegpt_pretrained</t>
         </is>
       </c>
       <c r="C568" t="inlineStr">
@@ -22243,7 +22238,7 @@
       </c>
       <c r="E568" t="inlineStr">
         <is>
-          <t>[实测 25.69M] auroc per-seed 0:0.7626, 1:0.8048, 2:0.7904</t>
+          <t>[实测 25.69M] auroc per-seed 0:0.7150, 1:0.7690, 2:0.7486</t>
         </is>
       </c>
       <c r="F568" t="inlineStr">
@@ -22260,7 +22255,7 @@
       </c>
       <c r="B569" t="inlineStr">
         <is>
-          <t>feat_best</t>
+          <t>eegpt_scratch</t>
         </is>
       </c>
       <c r="C569" t="inlineStr">
@@ -22275,12 +22270,12 @@
       </c>
       <c r="E569" t="inlineStr">
         <is>
-          <t>[实测 0.00M] auroc per-seed 0:0.5919, 1:0.5919, 2:0.5919</t>
+          <t>[实测 25.69M] auroc per-seed 0:0.7626, 1:0.8048, 2:0.7904</t>
         </is>
       </c>
       <c r="F569" t="inlineStr">
         <is>
-          <t>stopped_by=closed-form epochs=1 loss=closed-form</t>
+          <t>stopped_by=patience lr=0.0004 batch_size=32 epochs=40 patience=10 eval_every_steps=500 loss=bce_with_logits</t>
         </is>
       </c>
     </row>
@@ -22292,7 +22287,7 @@
       </c>
       <c r="B570" t="inlineStr">
         <is>
-          <t>ffcl</t>
+          <t>feat_best</t>
         </is>
       </c>
       <c r="C570" t="inlineStr">
@@ -22307,12 +22302,12 @@
       </c>
       <c r="E570" t="inlineStr">
         <is>
-          <t>[实测 2.46M] auroc per-seed 0:0.6875, 1:0.6509, 2:0.5837</t>
+          <t>[实测 0.00M] auroc per-seed 0:0.5919, 1:0.5919, 2:0.5919</t>
         </is>
       </c>
       <c r="F570" t="inlineStr">
         <is>
-          <t>stopped_by=patience lr=0.001 batch_size=512 epochs=20 patience=8 eval_every_steps=200 loss=bce_with_logits</t>
+          <t>stopped_by=closed-form epochs=1 loss=closed-form</t>
         </is>
       </c>
     </row>
@@ -22324,7 +22319,7 @@
       </c>
       <c r="B571" t="inlineStr">
         <is>
-          <t>labram_pretrained</t>
+          <t>ffcl</t>
         </is>
       </c>
       <c r="C571" t="inlineStr">
@@ -22339,12 +22334,12 @@
       </c>
       <c r="E571" t="inlineStr">
         <is>
-          <t>[实测 5.82M] auroc per-seed 0:0.7884, 1:0.7561, 2:0.7885</t>
+          <t>[实测 2.46M] auroc per-seed 0:0.6875, 1:0.6509, 2:0.5837</t>
         </is>
       </c>
       <c r="F571" t="inlineStr">
         <is>
-          <t>stopped_by=patience lr=0.0005 batch_size=64 epochs=50 patience=10 eval_every_steps=0 loss=bce_with_logits loader_divisor=1.0</t>
+          <t>stopped_by=patience lr=0.001 batch_size=512 epochs=20 patience=8 eval_every_steps=200 loss=bce_with_logits</t>
         </is>
       </c>
     </row>
@@ -22356,7 +22351,7 @@
       </c>
       <c r="B572" t="inlineStr">
         <is>
-          <t>labram_scratch</t>
+          <t>labram_pretrained</t>
         </is>
       </c>
       <c r="C572" t="inlineStr">
@@ -22371,7 +22366,7 @@
       </c>
       <c r="E572" t="inlineStr">
         <is>
-          <t>[实测 5.82M] auroc per-seed 0:0.6618, 1:0.7646, 2:0.7295</t>
+          <t>[实测 5.82M] auroc per-seed 0:0.7884, 1:0.7561, 2:0.7885</t>
         </is>
       </c>
       <c r="F572" t="inlineStr">
@@ -22388,22 +22383,27 @@
       </c>
       <c r="B573" t="inlineStr">
         <is>
-          <t>paclock_duplex</t>
+          <t>labram_scratch</t>
         </is>
       </c>
       <c r="C573" t="inlineStr">
         <is>
-          <t>[0]</t>
+          <t>[0, 1, 2]</t>
         </is>
       </c>
       <c r="D573" t="inlineStr">
         <is>
-          <t>filled (single-seed, grey)</t>
+          <t>filled</t>
         </is>
       </c>
       <c r="E573" t="inlineStr">
         <is>
-          <t>auroc 0.8052</t>
+          <t>[实测 5.82M] auroc per-seed 0:0.6618, 1:0.7646, 2:0.7295</t>
+        </is>
+      </c>
+      <c r="F573" t="inlineStr">
+        <is>
+          <t>stopped_by=patience lr=0.0005 batch_size=64 epochs=50 patience=10 eval_every_steps=0 loss=bce_with_logits loader_divisor=1.0</t>
         </is>
       </c>
     </row>
@@ -22415,22 +22415,22 @@
       </c>
       <c r="B574" t="inlineStr">
         <is>
-          <t>paclock_duplex_ptF</t>
+          <t>paclock_duplex</t>
         </is>
       </c>
       <c r="C574" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>[0]</t>
         </is>
       </c>
       <c r="D574" t="inlineStr">
         <is>
-          <t>skipped</t>
+          <t>filled (single-seed, grey)</t>
         </is>
       </c>
       <c r="E574" t="inlineStr">
         <is>
-          <t>row 'CroFreMo (预训练 v2-full)' not found</t>
+          <t>auroc 0.8052</t>
         </is>
       </c>
     </row>
@@ -22442,22 +22442,22 @@
       </c>
       <c r="B575" t="inlineStr">
         <is>
-          <t>paclock_duplex_ptS</t>
+          <t>paclock_duplex_ptF</t>
         </is>
       </c>
       <c r="C575" t="inlineStr">
         <is>
-          <t>[0]</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D575" t="inlineStr">
         <is>
-          <t>filled (single-seed, grey)</t>
+          <t>skipped</t>
         </is>
       </c>
       <c r="E575" t="inlineStr">
         <is>
-          <t>auroc 0.7686</t>
+          <t>row 'CroFreMo (预训练 v2-full)' not found</t>
         </is>
       </c>
     </row>
@@ -22469,27 +22469,22 @@
       </c>
       <c r="B576" t="inlineStr">
         <is>
-          <t>reve_pretrained</t>
+          <t>paclock_duplex_ptS</t>
         </is>
       </c>
       <c r="C576" t="inlineStr">
         <is>
-          <t>[0, 1, 2]</t>
+          <t>[0]</t>
         </is>
       </c>
       <c r="D576" t="inlineStr">
         <is>
-          <t>filled</t>
+          <t>filled (single-seed, grey)</t>
         </is>
       </c>
       <c r="E576" t="inlineStr">
         <is>
-          <t>[实测 69.46M] auroc per-seed 0:0.6801, 1:0.6785, 2:0.6342</t>
-        </is>
-      </c>
-      <c r="F576" t="inlineStr">
-        <is>
-          <t>stopped_by=patience lr=5e-05 batch_size=128 epochs=30 patience=10 eval_every_steps=0 loss=bce_with_logits grad_clip=1.0</t>
+          <t>auroc 0.7686</t>
         </is>
       </c>
     </row>
@@ -22501,22 +22496,27 @@
       </c>
       <c r="B577" t="inlineStr">
         <is>
-          <t>reve_pt_lrhalf</t>
+          <t>reve_pretrained</t>
         </is>
       </c>
       <c r="C577" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>[0, 1, 2]</t>
         </is>
       </c>
       <c r="D577" t="inlineStr">
         <is>
-          <t>skipped</t>
+          <t>filled</t>
         </is>
       </c>
       <c r="E577" t="inlineStr">
         <is>
-          <t>no row label for 'reve_pt_lrhalf'</t>
+          <t>[实测 69.46M] auroc per-seed 0:0.6801, 1:0.6785, 2:0.6342</t>
+        </is>
+      </c>
+      <c r="F577" t="inlineStr">
+        <is>
+          <t>stopped_by=patience lr=5e-05 batch_size=128 epochs=30 patience=10 eval_every_steps=0 loss=bce_with_logits grad_clip=1.0</t>
         </is>
       </c>
     </row>
@@ -22528,27 +22528,22 @@
       </c>
       <c r="B578" t="inlineStr">
         <is>
-          <t>sparcnet</t>
+          <t>reve_pt_lrhalf</t>
         </is>
       </c>
       <c r="C578" t="inlineStr">
         <is>
-          <t>[0, 1, 2]</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D578" t="inlineStr">
         <is>
-          <t>filled</t>
+          <t>skipped</t>
         </is>
       </c>
       <c r="E578" t="inlineStr">
         <is>
-          <t>[实测 1.14M] auroc per-seed 0:0.7312, 1:0.7414, 2:0.7209</t>
-        </is>
-      </c>
-      <c r="F578" t="inlineStr">
-        <is>
-          <t>stopped_by=patience lr=0.001 batch_size=512 epochs=20 patience=8 eval_every_steps=200 loss=bce_with_logits</t>
+          <t>no row label for 'reve_pt_lrhalf'</t>
         </is>
       </c>
     </row>
@@ -22560,7 +22555,7 @@
       </c>
       <c r="B579" t="inlineStr">
         <is>
-          <t>st_transformer</t>
+          <t>sparcnet</t>
         </is>
       </c>
       <c r="C579" t="inlineStr">
@@ -22575,7 +22570,7 @@
       </c>
       <c r="E579" t="inlineStr">
         <is>
-          <t>[实测 3.43M] auroc per-seed 0:0.5898, 1:0.5923, 2:0.6710</t>
+          <t>[实测 1.14M] auroc per-seed 0:0.7312, 1:0.7414, 2:0.7209</t>
         </is>
       </c>
       <c r="F579" t="inlineStr">
@@ -22592,7 +22587,7 @@
       </c>
       <c r="B580" t="inlineStr">
         <is>
-          <t>tfm_pretrained</t>
+          <t>st_transformer</t>
         </is>
       </c>
       <c r="C580" t="inlineStr">
@@ -22607,12 +22602,12 @@
       </c>
       <c r="E580" t="inlineStr">
         <is>
-          <t>[实测 1.89M] auroc per-seed 0:0.6440, 1:0.6183, 2:0.6142</t>
+          <t>[实测 3.43M] auroc per-seed 0:0.5898, 1:0.5923, 2:0.6710</t>
         </is>
       </c>
       <c r="F580" t="inlineStr">
         <is>
-          <t>stopped_by=patience lr=0.001 batch_size=512 epochs=7 patience=10 eval_every_steps=100 loss=bce_with_logits</t>
+          <t>stopped_by=patience lr=0.001 batch_size=512 epochs=20 patience=8 eval_every_steps=200 loss=bce_with_logits</t>
         </is>
       </c>
     </row>
@@ -22624,7 +22619,7 @@
       </c>
       <c r="B581" t="inlineStr">
         <is>
-          <t>tfm_scratch</t>
+          <t>tfm_pretrained</t>
         </is>
       </c>
       <c r="C581" t="inlineStr">
@@ -22639,7 +22634,7 @@
       </c>
       <c r="E581" t="inlineStr">
         <is>
-          <t>[实测 1.89M] auroc per-seed 0:0.5838, 1:0.6180, 2:0.6193</t>
+          <t>[实测 1.89M] auroc per-seed 0:0.6440, 1:0.6183, 2:0.6142</t>
         </is>
       </c>
       <c r="F581" t="inlineStr">
@@ -22651,27 +22646,32 @@
     <row r="582">
       <c r="A582" t="inlineStr">
         <is>
-          <t>tuev</t>
+          <t>tuep</t>
         </is>
       </c>
       <c r="B582" t="inlineStr">
         <is>
-          <t>biot_hop50</t>
+          <t>tfm_scratch</t>
         </is>
       </c>
       <c r="C582" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>[0, 1, 2]</t>
         </is>
       </c>
       <c r="D582" t="inlineStr">
         <is>
-          <t>skipped</t>
+          <t>filled</t>
         </is>
       </c>
       <c r="E582" t="inlineStr">
         <is>
-          <t>the workbook has no row for this variant</t>
+          <t>[实测 1.89M] auroc per-seed 0:0.5838, 1:0.6180, 2:0.6193</t>
+        </is>
+      </c>
+      <c r="F582" t="inlineStr">
+        <is>
+          <t>stopped_by=patience lr=0.001 batch_size=512 epochs=7 patience=10 eval_every_steps=100 loss=bce_with_logits</t>
         </is>
       </c>
     </row>
@@ -22683,27 +22683,22 @@
       </c>
       <c r="B583" t="inlineStr">
         <is>
-          <t>biot_prest16</t>
+          <t>biot_hop50</t>
         </is>
       </c>
       <c r="C583" t="inlineStr">
         <is>
-          <t>[0, 1, 2]</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D583" t="inlineStr">
         <is>
-          <t>filled</t>
+          <t>skipped</t>
         </is>
       </c>
       <c r="E583" t="inlineStr">
         <is>
-          <t>[实测 3.19M] cohen_kappa per-seed 0:0.5005, 1:0.5354, 2:0.5554</t>
-        </is>
-      </c>
-      <c r="F583" t="inlineStr">
-        <is>
-          <t>lr=0.001 batch_size=128 epochs=100 patience=5 eval_every_steps=0 loss=cross_entropy label_smoothing=0.0</t>
+          <t>the workbook has no row for this variant</t>
         </is>
       </c>
     </row>
@@ -22715,7 +22710,7 @@
       </c>
       <c r="B584" t="inlineStr">
         <is>
-          <t>biot_scratch</t>
+          <t>biot_prest16</t>
         </is>
       </c>
       <c r="C584" t="inlineStr">
@@ -22730,7 +22725,7 @@
       </c>
       <c r="E584" t="inlineStr">
         <is>
-          <t>[实测 3.19M] cohen_kappa per-seed 0:0.5039, 1:0.5425, 2:0.5508</t>
+          <t>[实测 3.19M] cohen_kappa per-seed 0:0.5005, 1:0.5354, 2:0.5554</t>
         </is>
       </c>
       <c r="F584" t="inlineStr">
@@ -22747,22 +22742,27 @@
       </c>
       <c r="B585" t="inlineStr">
         <is>
-          <t>biot_tok100</t>
+          <t>biot_scratch</t>
         </is>
       </c>
       <c r="C585" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>[0, 1, 2]</t>
         </is>
       </c>
       <c r="D585" t="inlineStr">
         <is>
-          <t>skipped</t>
+          <t>filled</t>
         </is>
       </c>
       <c r="E585" t="inlineStr">
         <is>
-          <t>the workbook has no row for this variant</t>
+          <t>[实测 3.19M] cohen_kappa per-seed 0:0.5039, 1:0.5425, 2:0.5508</t>
+        </is>
+      </c>
+      <c r="F585" t="inlineStr">
+        <is>
+          <t>lr=0.001 batch_size=128 epochs=100 patience=5 eval_every_steps=0 loss=cross_entropy label_smoothing=0.0</t>
         </is>
       </c>
     </row>
@@ -22774,7 +22774,7 @@
       </c>
       <c r="B586" t="inlineStr">
         <is>
-          <t>cand_base</t>
+          <t>biot_tok100</t>
         </is>
       </c>
       <c r="C586" t="inlineStr">
@@ -22801,7 +22801,7 @@
       </c>
       <c r="B587" t="inlineStr">
         <is>
-          <t>cand_dense</t>
+          <t>cand_base</t>
         </is>
       </c>
       <c r="C587" t="inlineStr">
@@ -22828,7 +22828,7 @@
       </c>
       <c r="B588" t="inlineStr">
         <is>
-          <t>cand_dense_lr1e5</t>
+          <t>cand_dense</t>
         </is>
       </c>
       <c r="C588" t="inlineStr">
@@ -22855,7 +22855,7 @@
       </c>
       <c r="B589" t="inlineStr">
         <is>
-          <t>cand_dense_lr3e5</t>
+          <t>cand_dense_lr1e5</t>
         </is>
       </c>
       <c r="C589" t="inlineStr">
@@ -22882,7 +22882,7 @@
       </c>
       <c r="B590" t="inlineStr">
         <is>
-          <t>cand_dense_patch100</t>
+          <t>cand_dense_lr3e5</t>
         </is>
       </c>
       <c r="C590" t="inlineStr">
@@ -22909,7 +22909,7 @@
       </c>
       <c r="B591" t="inlineStr">
         <is>
-          <t>cand_e60_base</t>
+          <t>cand_dense_patch100</t>
         </is>
       </c>
       <c r="C591" t="inlineStr">
@@ -22936,7 +22936,7 @@
       </c>
       <c r="B592" t="inlineStr">
         <is>
-          <t>cand_e60_patch100</t>
+          <t>cand_e60_base</t>
         </is>
       </c>
       <c r="C592" t="inlineStr">
@@ -22963,7 +22963,7 @@
       </c>
       <c r="B593" t="inlineStr">
         <is>
-          <t>cand_e60_size_base</t>
+          <t>cand_e60_patch100</t>
         </is>
       </c>
       <c r="C593" t="inlineStr">
@@ -22990,7 +22990,7 @@
       </c>
       <c r="B594" t="inlineStr">
         <is>
-          <t>cand_e60_size_large</t>
+          <t>cand_e60_size_base</t>
         </is>
       </c>
       <c r="C594" t="inlineStr">
@@ -23017,7 +23017,7 @@
       </c>
       <c r="B595" t="inlineStr">
         <is>
-          <t>cand_ms</t>
+          <t>cand_e60_size_large</t>
         </is>
       </c>
       <c r="C595" t="inlineStr">
@@ -23044,7 +23044,7 @@
       </c>
       <c r="B596" t="inlineStr">
         <is>
-          <t>cand_p100_large</t>
+          <t>cand_ms</t>
         </is>
       </c>
       <c r="C596" t="inlineStr">
@@ -23071,7 +23071,7 @@
       </c>
       <c r="B597" t="inlineStr">
         <is>
-          <t>cand_p50_win100</t>
+          <t>cand_p100_large</t>
         </is>
       </c>
       <c r="C597" t="inlineStr">
@@ -23098,7 +23098,7 @@
       </c>
       <c r="B598" t="inlineStr">
         <is>
-          <t>cand_p50_win200</t>
+          <t>cand_p50_win100</t>
         </is>
       </c>
       <c r="C598" t="inlineStr">
@@ -23125,7 +23125,7 @@
       </c>
       <c r="B599" t="inlineStr">
         <is>
-          <t>cand_pacwin200</t>
+          <t>cand_p50_win200</t>
         </is>
       </c>
       <c r="C599" t="inlineStr">
@@ -23152,7 +23152,7 @@
       </c>
       <c r="B600" t="inlineStr">
         <is>
-          <t>cand_patch100</t>
+          <t>cand_pacwin200</t>
         </is>
       </c>
       <c r="C600" t="inlineStr">
@@ -23179,7 +23179,7 @@
       </c>
       <c r="B601" t="inlineStr">
         <is>
-          <t>cand_patch50</t>
+          <t>cand_patch100</t>
         </is>
       </c>
       <c r="C601" t="inlineStr">
@@ -23206,7 +23206,7 @@
       </c>
       <c r="B602" t="inlineStr">
         <is>
-          <t>cbramod_crofremo</t>
+          <t>cand_patch50</t>
         </is>
       </c>
       <c r="C602" t="inlineStr">
@@ -23221,7 +23221,7 @@
       </c>
       <c r="E602" t="inlineStr">
         <is>
-          <t>no row label for 'cbramod_crofremo'</t>
+          <t>the workbook has no row for this variant</t>
         </is>
       </c>
     </row>
@@ -23233,7 +23233,7 @@
       </c>
       <c r="B603" t="inlineStr">
         <is>
-          <t>cbramod_crofremo_bands</t>
+          <t>cbramod_crofremo</t>
         </is>
       </c>
       <c r="C603" t="inlineStr">
@@ -23248,7 +23248,7 @@
       </c>
       <c r="E603" t="inlineStr">
         <is>
-          <t>no row label for 'cbramod_crofremo_bands'</t>
+          <t>no row label for 'cbramod_crofremo'</t>
         </is>
       </c>
     </row>
@@ -23260,7 +23260,7 @@
       </c>
       <c r="B604" t="inlineStr">
         <is>
-          <t>cbramod_pac</t>
+          <t>cbramod_crofremo_bands</t>
         </is>
       </c>
       <c r="C604" t="inlineStr">
@@ -23275,7 +23275,7 @@
       </c>
       <c r="E604" t="inlineStr">
         <is>
-          <t>the workbook has no row for this variant</t>
+          <t>no row label for 'cbramod_crofremo_bands'</t>
         </is>
       </c>
     </row>
@@ -23287,7 +23287,7 @@
       </c>
       <c r="B605" t="inlineStr">
         <is>
-          <t>cbramod_pacfe_pac</t>
+          <t>cbramod_pac</t>
         </is>
       </c>
       <c r="C605" t="inlineStr">
@@ -23302,7 +23302,7 @@
       </c>
       <c r="E605" t="inlineStr">
         <is>
-          <t>no row label for 'cbramod_pacfe_pac'</t>
+          <t>the workbook has no row for this variant</t>
         </is>
       </c>
     </row>
@@ -23314,7 +23314,7 @@
       </c>
       <c r="B606" t="inlineStr">
         <is>
-          <t>cbramod_pacfe_raw</t>
+          <t>cbramod_pacfe_pac</t>
         </is>
       </c>
       <c r="C606" t="inlineStr">
@@ -23329,7 +23329,7 @@
       </c>
       <c r="E606" t="inlineStr">
         <is>
-          <t>no row label for 'cbramod_pacfe_raw'</t>
+          <t>no row label for 'cbramod_pacfe_pac'</t>
         </is>
       </c>
     </row>
@@ -23341,7 +23341,7 @@
       </c>
       <c r="B607" t="inlineStr">
         <is>
-          <t>cbramod_paclockfe</t>
+          <t>cbramod_pacfe_raw</t>
         </is>
       </c>
       <c r="C607" t="inlineStr">
@@ -23356,7 +23356,7 @@
       </c>
       <c r="E607" t="inlineStr">
         <is>
-          <t>no row label for 'cbramod_paclockfe'</t>
+          <t>no row label for 'cbramod_pacfe_raw'</t>
         </is>
       </c>
     </row>
@@ -23368,27 +23368,22 @@
       </c>
       <c r="B608" t="inlineStr">
         <is>
-          <t>cbramod_pretrained</t>
+          <t>cbramod_paclockfe</t>
         </is>
       </c>
       <c r="C608" t="inlineStr">
         <is>
-          <t>[0, 1, 2]</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D608" t="inlineStr">
         <is>
-          <t>filled</t>
+          <t>skipped</t>
         </is>
       </c>
       <c r="E608" t="inlineStr">
         <is>
-          <t>[实测 17.85M] cohen_kappa per-seed 0:0.6199, 1:0.6566, 2:0.6582</t>
-        </is>
-      </c>
-      <c r="F608" t="inlineStr">
-        <is>
-          <t>lr=0.0001 batch_size=64 epochs=50 patience=0 eval_every_steps=0 loss=cross_entropy label_smoothing=0.1 grad_clip=1.0 multi_lr=True</t>
+          <t>no row label for 'cbramod_paclockfe'</t>
         </is>
       </c>
     </row>
@@ -23400,22 +23395,27 @@
       </c>
       <c r="B609" t="inlineStr">
         <is>
-          <t>cbramod_rawfe_bands</t>
+          <t>cbramod_pretrained</t>
         </is>
       </c>
       <c r="C609" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>[0, 1, 2]</t>
         </is>
       </c>
       <c r="D609" t="inlineStr">
         <is>
-          <t>skipped</t>
+          <t>filled</t>
         </is>
       </c>
       <c r="E609" t="inlineStr">
         <is>
-          <t>no row label for 'cbramod_rawfe_bands'</t>
+          <t>[实测 17.85M] cohen_kappa per-seed 0:0.6199, 1:0.6566, 2:0.6582</t>
+        </is>
+      </c>
+      <c r="F609" t="inlineStr">
+        <is>
+          <t>lr=0.0001 batch_size=64 epochs=50 patience=0 eval_every_steps=0 loss=cross_entropy label_smoothing=0.1 grad_clip=1.0 multi_lr=True</t>
         </is>
       </c>
     </row>
@@ -23427,27 +23427,22 @@
       </c>
       <c r="B610" t="inlineStr">
         <is>
-          <t>cbramod_scratch</t>
+          <t>cbramod_rawfe_bands</t>
         </is>
       </c>
       <c r="C610" t="inlineStr">
         <is>
-          <t>[0, 1, 2]</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D610" t="inlineStr">
         <is>
-          <t>filled</t>
+          <t>skipped</t>
         </is>
       </c>
       <c r="E610" t="inlineStr">
         <is>
-          <t>[实测 17.85M] cohen_kappa per-seed 0:0.5755, 1:0.5366, 2:0.5794</t>
-        </is>
-      </c>
-      <c r="F610" t="inlineStr">
-        <is>
-          <t>lr=0.0001 batch_size=64 epochs=50 patience=0 eval_every_steps=0 loss=cross_entropy label_smoothing=0.1 grad_clip=1.0 multi_lr=True</t>
+          <t>no row label for 'cbramod_rawfe_bands'</t>
         </is>
       </c>
     </row>
@@ -23459,7 +23454,7 @@
       </c>
       <c r="B611" t="inlineStr">
         <is>
-          <t>cnn_transformer</t>
+          <t>cbramod_scratch</t>
         </is>
       </c>
       <c r="C611" t="inlineStr">
@@ -23474,12 +23469,12 @@
       </c>
       <c r="E611" t="inlineStr">
         <is>
-          <t>[实测 3.16M] cohen_kappa per-seed 0:0.4987, 1:0.2779, 2:0.4527  [seed spread 23% -- mean is a weak summary]</t>
+          <t>[实测 17.85M] cohen_kappa per-seed 0:0.5755, 1:0.5366, 2:0.5794</t>
         </is>
       </c>
       <c r="F611" t="inlineStr">
         <is>
-          <t>lr=0.001 batch_size=512 epochs=100 patience=15 eval_every_steps=0 loss=cross_entropy label_smoothing=0.1</t>
+          <t>lr=0.0001 batch_size=64 epochs=50 patience=0 eval_every_steps=0 loss=cross_entropy label_smoothing=0.1 grad_clip=1.0 multi_lr=True</t>
         </is>
       </c>
     </row>
@@ -23491,7 +23486,7 @@
       </c>
       <c r="B612" t="inlineStr">
         <is>
-          <t>contrawr</t>
+          <t>cnn_transformer</t>
         </is>
       </c>
       <c r="C612" t="inlineStr">
@@ -23506,7 +23501,7 @@
       </c>
       <c r="E612" t="inlineStr">
         <is>
-          <t>[实测 1.57M] cohen_kappa per-seed 0:0.4410, 1:0.4849, 2:0.2969  [seed spread 20% -- mean is a weak summary]</t>
+          <t>[实测 3.16M] cohen_kappa per-seed 0:0.4987, 1:0.2779, 2:0.4527  [seed spread 23% -- mean is a weak summary]</t>
         </is>
       </c>
       <c r="F612" t="inlineStr">
@@ -23523,7 +23518,7 @@
       </c>
       <c r="B613" t="inlineStr">
         <is>
-          <t>csbrain_pretrained</t>
+          <t>contrawr</t>
         </is>
       </c>
       <c r="C613" t="inlineStr">
@@ -23538,12 +23533,12 @@
       </c>
       <c r="E613" t="inlineStr">
         <is>
-          <t>[实测 25.06M] cohen_kappa per-seed 0:0.6132, 1:0.6922, 2:0.6027</t>
+          <t>[实测 1.57M] cohen_kappa per-seed 0:0.4410, 1:0.4849, 2:0.2969  [seed spread 20% -- mean is a weak summary]</t>
         </is>
       </c>
       <c r="F613" t="inlineStr">
         <is>
-          <t>stopped_by=patience lr=0.0001 batch_size=64 epochs=50 patience=10 eval_every_steps=0 loss=cross_entropy label_smoothing=0.1 grad_clip=1.0</t>
+          <t>lr=0.001 batch_size=512 epochs=100 patience=15 eval_every_steps=0 loss=cross_entropy label_smoothing=0.1</t>
         </is>
       </c>
     </row>
@@ -23555,22 +23550,27 @@
       </c>
       <c r="B614" t="inlineStr">
         <is>
-          <t>csbrain_pretrained_ls0</t>
+          <t>csbrain_pretrained</t>
         </is>
       </c>
       <c r="C614" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>[0, 1, 2]</t>
         </is>
       </c>
       <c r="D614" t="inlineStr">
         <is>
-          <t>skipped</t>
+          <t>filled</t>
         </is>
       </c>
       <c r="E614" t="inlineStr">
         <is>
-          <t>no row label for 'csbrain_pretrained_ls0'</t>
+          <t>[实测 25.06M] cohen_kappa per-seed 0:0.6132, 1:0.6922, 2:0.6027</t>
+        </is>
+      </c>
+      <c r="F614" t="inlineStr">
+        <is>
+          <t>stopped_by=patience lr=0.0001 batch_size=64 epochs=50 patience=10 eval_every_steps=0 loss=cross_entropy label_smoothing=0.1 grad_clip=1.0</t>
         </is>
       </c>
     </row>
@@ -23582,27 +23582,22 @@
       </c>
       <c r="B615" t="inlineStr">
         <is>
-          <t>eegconformer</t>
+          <t>csbrain_pretrained_ls0</t>
         </is>
       </c>
       <c r="C615" t="inlineStr">
         <is>
-          <t>[0, 1, 2]</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D615" t="inlineStr">
         <is>
-          <t>filled</t>
+          <t>skipped</t>
         </is>
       </c>
       <c r="E615" t="inlineStr">
         <is>
-          <t>[实测 0.78M] cohen_kappa per-seed 0:0.4524, 1:0.4596, 2:0.4525</t>
-        </is>
-      </c>
-      <c r="F615" t="inlineStr">
-        <is>
-          <t>stopped_by=patience lr=0.001 batch_size=128 epochs=100 patience=15 eval_every_steps=0 loss=cross_entropy label_smoothing=0.1 grad_clip=1.0</t>
+          <t>no row label for 'csbrain_pretrained_ls0'</t>
         </is>
       </c>
     </row>
@@ -23614,22 +23609,27 @@
       </c>
       <c r="B616" t="inlineStr">
         <is>
-          <t>eegconformer_t1</t>
+          <t>eegconformer</t>
         </is>
       </c>
       <c r="C616" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>[0, 1, 2]</t>
         </is>
       </c>
       <c r="D616" t="inlineStr">
         <is>
-          <t>skipped</t>
+          <t>filled</t>
         </is>
       </c>
       <c r="E616" t="inlineStr">
         <is>
-          <t>no row label for 'eegconformer_t1'</t>
+          <t>[实测 0.78M] cohen_kappa per-seed 0:0.4524, 1:0.4596, 2:0.4525</t>
+        </is>
+      </c>
+      <c r="F616" t="inlineStr">
+        <is>
+          <t>stopped_by=patience lr=0.001 batch_size=128 epochs=100 patience=15 eval_every_steps=0 loss=cross_entropy label_smoothing=0.1 grad_clip=1.0</t>
         </is>
       </c>
     </row>
@@ -23641,7 +23641,7 @@
       </c>
       <c r="B617" t="inlineStr">
         <is>
-          <t>eegconformer_t2</t>
+          <t>eegconformer_t1</t>
         </is>
       </c>
       <c r="C617" t="inlineStr">
@@ -23656,7 +23656,7 @@
       </c>
       <c r="E617" t="inlineStr">
         <is>
-          <t>no row label for 'eegconformer_t2'</t>
+          <t>no row label for 'eegconformer_t1'</t>
         </is>
       </c>
     </row>
@@ -23668,7 +23668,7 @@
       </c>
       <c r="B618" t="inlineStr">
         <is>
-          <t>eegconformer_t3</t>
+          <t>eegconformer_t2</t>
         </is>
       </c>
       <c r="C618" t="inlineStr">
@@ -23683,7 +23683,7 @@
       </c>
       <c r="E618" t="inlineStr">
         <is>
-          <t>no row label for 'eegconformer_t3'</t>
+          <t>no row label for 'eegconformer_t2'</t>
         </is>
       </c>
     </row>
@@ -23695,7 +23695,7 @@
       </c>
       <c r="B619" t="inlineStr">
         <is>
-          <t>eegconformer_t4</t>
+          <t>eegconformer_t3</t>
         </is>
       </c>
       <c r="C619" t="inlineStr">
@@ -23710,7 +23710,7 @@
       </c>
       <c r="E619" t="inlineStr">
         <is>
-          <t>no row label for 'eegconformer_t4'</t>
+          <t>no row label for 'eegconformer_t3'</t>
         </is>
       </c>
     </row>
@@ -23722,27 +23722,22 @@
       </c>
       <c r="B620" t="inlineStr">
         <is>
-          <t>eegnet</t>
+          <t>eegconformer_t4</t>
         </is>
       </c>
       <c r="C620" t="inlineStr">
         <is>
-          <t>[0, 1, 2]</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D620" t="inlineStr">
         <is>
-          <t>filled</t>
+          <t>skipped</t>
         </is>
       </c>
       <c r="E620" t="inlineStr">
         <is>
-          <t>[实测 0.00M] cohen_kappa per-seed 0:0.5836, 1:0.4223, 2:0.4306  [seed spread 15% -- mean is a weak summary]</t>
-        </is>
-      </c>
-      <c r="F620" t="inlineStr">
-        <is>
-          <t>stopped_by=patience lr=0.001 batch_size=512 epochs=100 patience=15 eval_every_steps=0 loss=cross_entropy label_smoothing=0.1 grad_clip=1.0</t>
+          <t>no row label for 'eegconformer_t4'</t>
         </is>
       </c>
     </row>
@@ -23754,22 +23749,27 @@
       </c>
       <c r="B621" t="inlineStr">
         <is>
-          <t>eegnet_t1</t>
+          <t>eegnet</t>
         </is>
       </c>
       <c r="C621" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>[0, 1, 2]</t>
         </is>
       </c>
       <c r="D621" t="inlineStr">
         <is>
-          <t>skipped</t>
+          <t>filled</t>
         </is>
       </c>
       <c r="E621" t="inlineStr">
         <is>
-          <t>no row label for 'eegnet_t1'</t>
+          <t>[实测 0.00M] cohen_kappa per-seed 0:0.5836, 1:0.4223, 2:0.4306  [seed spread 15% -- mean is a weak summary]</t>
+        </is>
+      </c>
+      <c r="F621" t="inlineStr">
+        <is>
+          <t>stopped_by=patience lr=0.001 batch_size=512 epochs=100 patience=15 eval_every_steps=0 loss=cross_entropy label_smoothing=0.1 grad_clip=1.0</t>
         </is>
       </c>
     </row>
@@ -23781,7 +23781,7 @@
       </c>
       <c r="B622" t="inlineStr">
         <is>
-          <t>eegnet_t2</t>
+          <t>eegnet_t1</t>
         </is>
       </c>
       <c r="C622" t="inlineStr">
@@ -23796,7 +23796,7 @@
       </c>
       <c r="E622" t="inlineStr">
         <is>
-          <t>no row label for 'eegnet_t2'</t>
+          <t>no row label for 'eegnet_t1'</t>
         </is>
       </c>
     </row>
@@ -23808,7 +23808,7 @@
       </c>
       <c r="B623" t="inlineStr">
         <is>
-          <t>eegnet_t3</t>
+          <t>eegnet_t2</t>
         </is>
       </c>
       <c r="C623" t="inlineStr">
@@ -23823,7 +23823,7 @@
       </c>
       <c r="E623" t="inlineStr">
         <is>
-          <t>no row label for 'eegnet_t3'</t>
+          <t>no row label for 'eegnet_t2'</t>
         </is>
       </c>
     </row>
@@ -23835,7 +23835,7 @@
       </c>
       <c r="B624" t="inlineStr">
         <is>
-          <t>eegnet_t4</t>
+          <t>eegnet_t3</t>
         </is>
       </c>
       <c r="C624" t="inlineStr">
@@ -23850,7 +23850,7 @@
       </c>
       <c r="E624" t="inlineStr">
         <is>
-          <t>no row label for 'eegnet_t4'</t>
+          <t>no row label for 'eegnet_t3'</t>
         </is>
       </c>
     </row>
@@ -23862,27 +23862,22 @@
       </c>
       <c r="B625" t="inlineStr">
         <is>
-          <t>eegpt_pretrained</t>
+          <t>eegnet_t4</t>
         </is>
       </c>
       <c r="C625" t="inlineStr">
         <is>
-          <t>[0, 1, 2]</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D625" t="inlineStr">
         <is>
-          <t>filled</t>
+          <t>skipped</t>
         </is>
       </c>
       <c r="E625" t="inlineStr">
         <is>
-          <t>[实测 25.69M] cohen_kappa per-seed 0:0.5311, 1:0.6095, 2:0.5803</t>
-        </is>
-      </c>
-      <c r="F625" t="inlineStr">
-        <is>
-          <t>lr=0.0004 batch_size=32 epochs=40 patience=10 eval_every_steps=0 loss=cross_entropy</t>
+          <t>no row label for 'eegnet_t4'</t>
         </is>
       </c>
     </row>
@@ -23894,7 +23889,7 @@
       </c>
       <c r="B626" t="inlineStr">
         <is>
-          <t>feat_best</t>
+          <t>eegpt_pretrained</t>
         </is>
       </c>
       <c r="C626" t="inlineStr">
@@ -23909,12 +23904,12 @@
       </c>
       <c r="E626" t="inlineStr">
         <is>
-          <t>[实测 0.00M] cohen_kappa per-seed 0:0.5049, 1:0.5049, 2:0.5049</t>
+          <t>[实测 25.69M] cohen_kappa per-seed 0:0.5311, 1:0.6095, 2:0.5803</t>
         </is>
       </c>
       <c r="F626" t="inlineStr">
         <is>
-          <t>stopped_by=closed-form epochs=1 loss=closed-form</t>
+          <t>lr=0.0004 batch_size=32 epochs=40 patience=10 eval_every_steps=0 loss=cross_entropy</t>
         </is>
       </c>
     </row>
@@ -23926,7 +23921,7 @@
       </c>
       <c r="B627" t="inlineStr">
         <is>
-          <t>ffcl</t>
+          <t>feat_best</t>
         </is>
       </c>
       <c r="C627" t="inlineStr">
@@ -23941,12 +23936,12 @@
       </c>
       <c r="E627" t="inlineStr">
         <is>
-          <t>[实测 2.42M] cohen_kappa per-seed 0:0.5069, 1:0.4432, 2:0.4827</t>
+          <t>[实测 0.00M] cohen_kappa per-seed 0:0.5049, 1:0.5049, 2:0.5049</t>
         </is>
       </c>
       <c r="F627" t="inlineStr">
         <is>
-          <t>lr=0.001 batch_size=512 epochs=100 patience=15 eval_every_steps=0 loss=cross_entropy label_smoothing=0.1</t>
+          <t>stopped_by=closed-form epochs=1 loss=closed-form</t>
         </is>
       </c>
     </row>
@@ -23958,7 +23953,7 @@
       </c>
       <c r="B628" t="inlineStr">
         <is>
-          <t>labram_pretrained</t>
+          <t>ffcl</t>
         </is>
       </c>
       <c r="C628" t="inlineStr">
@@ -23973,12 +23968,12 @@
       </c>
       <c r="E628" t="inlineStr">
         <is>
-          <t>[实测 5.82M] cohen_kappa per-seed 0:0.6012, 1:0.5989, 2:0.5951</t>
+          <t>[实测 2.42M] cohen_kappa per-seed 0:0.5069, 1:0.4432, 2:0.4827</t>
         </is>
       </c>
       <c r="F628" t="inlineStr">
         <is>
-          <t>stopped_by=patience lr=0.0005 batch_size=64 epochs=50 patience=10 eval_every_steps=100 loss=cross_entropy label_smoothing=0.1</t>
+          <t>lr=0.001 batch_size=512 epochs=100 patience=15 eval_every_steps=0 loss=cross_entropy label_smoothing=0.1</t>
         </is>
       </c>
     </row>
@@ -23990,7 +23985,7 @@
       </c>
       <c r="B629" t="inlineStr">
         <is>
-          <t>labram_scratch</t>
+          <t>labram_pretrained</t>
         </is>
       </c>
       <c r="C629" t="inlineStr">
@@ -24005,12 +24000,12 @@
       </c>
       <c r="E629" t="inlineStr">
         <is>
-          <t>[实测 5.82M] cohen_kappa per-seed 0:0.3624, 1:0.3727, 2:0.3801</t>
+          <t>[实测 5.82M] cohen_kappa per-seed 0:0.6012, 1:0.5989, 2:0.5951</t>
         </is>
       </c>
       <c r="F629" t="inlineStr">
         <is>
-          <t>lr=0.0005 batch_size=64 epochs=50 patience=10 eval_every_steps=0 loss=cross_entropy label_smoothing=0.1</t>
+          <t>stopped_by=patience lr=0.0005 batch_size=64 epochs=50 patience=10 eval_every_steps=100 loss=cross_entropy label_smoothing=0.1</t>
         </is>
       </c>
     </row>
@@ -24022,22 +24017,27 @@
       </c>
       <c r="B630" t="inlineStr">
         <is>
-          <t>paclock</t>
+          <t>labram_scratch</t>
         </is>
       </c>
       <c r="C630" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>[0, 1, 2]</t>
         </is>
       </c>
       <c r="D630" t="inlineStr">
         <is>
-          <t>skipped</t>
+          <t>filled</t>
         </is>
       </c>
       <c r="E630" t="inlineStr">
         <is>
-          <t>no row label for 'paclock'</t>
+          <t>[实测 5.82M] cohen_kappa per-seed 0:0.3624, 1:0.3727, 2:0.3801</t>
+        </is>
+      </c>
+      <c r="F630" t="inlineStr">
+        <is>
+          <t>lr=0.0005 batch_size=64 epochs=50 patience=10 eval_every_steps=0 loss=cross_entropy label_smoothing=0.1</t>
         </is>
       </c>
     </row>
@@ -24049,22 +24049,22 @@
       </c>
       <c r="B631" t="inlineStr">
         <is>
-          <t>paclock_duplex</t>
+          <t>paclock</t>
         </is>
       </c>
       <c r="C631" t="inlineStr">
         <is>
-          <t>[0]</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D631" t="inlineStr">
         <is>
-          <t>filled (single-seed, grey)</t>
+          <t>skipped</t>
         </is>
       </c>
       <c r="E631" t="inlineStr">
         <is>
-          <t>cohen_kappa 0.7094</t>
+          <t>no row label for 'paclock'</t>
         </is>
       </c>
     </row>
@@ -24076,22 +24076,22 @@
       </c>
       <c r="B632" t="inlineStr">
         <is>
-          <t>paclock_duplex_ms</t>
+          <t>paclock_duplex</t>
         </is>
       </c>
       <c r="C632" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>[0]</t>
         </is>
       </c>
       <c r="D632" t="inlineStr">
         <is>
-          <t>skipped</t>
+          <t>filled (single-seed, grey)</t>
         </is>
       </c>
       <c r="E632" t="inlineStr">
         <is>
-          <t>no row label for 'paclock_duplex_ms'</t>
+          <t>cohen_kappa 0.7094</t>
         </is>
       </c>
     </row>
@@ -24103,7 +24103,7 @@
       </c>
       <c r="B633" t="inlineStr">
         <is>
-          <t>paclock_duplex_p200</t>
+          <t>paclock_duplex_ms</t>
         </is>
       </c>
       <c r="C633" t="inlineStr">
@@ -24118,7 +24118,7 @@
       </c>
       <c r="E633" t="inlineStr">
         <is>
-          <t>no row label for 'paclock_duplex_p200'</t>
+          <t>no row label for 'paclock_duplex_ms'</t>
         </is>
       </c>
     </row>
@@ -24130,7 +24130,7 @@
       </c>
       <c r="B634" t="inlineStr">
         <is>
-          <t>paclock_duplex_p200ptF</t>
+          <t>paclock_duplex_p200</t>
         </is>
       </c>
       <c r="C634" t="inlineStr">
@@ -24145,7 +24145,7 @@
       </c>
       <c r="E634" t="inlineStr">
         <is>
-          <t>no row label for 'paclock_duplex_p200ptF'</t>
+          <t>no row label for 'paclock_duplex_p200'</t>
         </is>
       </c>
     </row>
@@ -24157,7 +24157,7 @@
       </c>
       <c r="B635" t="inlineStr">
         <is>
-          <t>paclock_duplex_pt</t>
+          <t>paclock_duplex_p200ptF</t>
         </is>
       </c>
       <c r="C635" t="inlineStr">
@@ -24172,7 +24172,7 @@
       </c>
       <c r="E635" t="inlineStr">
         <is>
-          <t>row 'PACLock (duplex, pretrained)' not found</t>
+          <t>no row label for 'paclock_duplex_p200ptF'</t>
         </is>
       </c>
     </row>
@@ -24184,22 +24184,22 @@
       </c>
       <c r="B636" t="inlineStr">
         <is>
-          <t>paclock_duplex_pt2</t>
+          <t>paclock_duplex_pt</t>
         </is>
       </c>
       <c r="C636" t="inlineStr">
         <is>
-          <t>[0]</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D636" t="inlineStr">
         <is>
-          <t>filled (single-seed, grey)</t>
+          <t>skipped</t>
         </is>
       </c>
       <c r="E636" t="inlineStr">
         <is>
-          <t>cohen_kappa 0.6533</t>
+          <t>row 'PACLock (duplex, pretrained)' not found</t>
         </is>
       </c>
     </row>
@@ -24211,7 +24211,7 @@
       </c>
       <c r="B637" t="inlineStr">
         <is>
-          <t>paclock_duplex_pt3</t>
+          <t>paclock_duplex_pt2</t>
         </is>
       </c>
       <c r="C637" t="inlineStr">
@@ -24226,7 +24226,7 @@
       </c>
       <c r="E637" t="inlineStr">
         <is>
-          <t>cohen_kappa 0.6753</t>
+          <t>cohen_kappa 0.6533</t>
         </is>
       </c>
     </row>
@@ -24238,22 +24238,22 @@
       </c>
       <c r="B638" t="inlineStr">
         <is>
-          <t>paclock_duplex_ptF</t>
+          <t>paclock_duplex_pt3</t>
         </is>
       </c>
       <c r="C638" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>[0]</t>
         </is>
       </c>
       <c r="D638" t="inlineStr">
         <is>
-          <t>skipped</t>
+          <t>filled (single-seed, grey)</t>
         </is>
       </c>
       <c r="E638" t="inlineStr">
         <is>
-          <t>row 'CroFreMo (预训练 v2-full)' not found</t>
+          <t>cohen_kappa 0.6753</t>
         </is>
       </c>
     </row>
@@ -24265,22 +24265,22 @@
       </c>
       <c r="B639" t="inlineStr">
         <is>
-          <t>paclock_duplex_ptS</t>
+          <t>paclock_duplex_ptF</t>
         </is>
       </c>
       <c r="C639" t="inlineStr">
         <is>
-          <t>[0]</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D639" t="inlineStr">
         <is>
-          <t>filled (single-seed, grey)</t>
+          <t>skipped</t>
         </is>
       </c>
       <c r="E639" t="inlineStr">
         <is>
-          <t>cohen_kappa 0.6417</t>
+          <t>row 'CroFreMo (预训练 v2-full)' not found</t>
         </is>
       </c>
     </row>
@@ -24292,22 +24292,22 @@
       </c>
       <c r="B640" t="inlineStr">
         <is>
-          <t>paclock_flagship</t>
+          <t>paclock_duplex_ptS</t>
         </is>
       </c>
       <c r="C640" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>[0]</t>
         </is>
       </c>
       <c r="D640" t="inlineStr">
         <is>
-          <t>skipped</t>
+          <t>filled (single-seed, grey)</t>
         </is>
       </c>
       <c r="E640" t="inlineStr">
         <is>
-          <t>no row label for 'paclock_flagship'</t>
+          <t>cohen_kappa 0.6417</t>
         </is>
       </c>
     </row>
@@ -24319,7 +24319,7 @@
       </c>
       <c r="B641" t="inlineStr">
         <is>
-          <t>paclock_ft_base_partial</t>
+          <t>paclock_flagship</t>
         </is>
       </c>
       <c r="C641" t="inlineStr">
@@ -24334,7 +24334,7 @@
       </c>
       <c r="E641" t="inlineStr">
         <is>
-          <t>no row label for 'paclock_ft_base_partial'</t>
+          <t>no row label for 'paclock_flagship'</t>
         </is>
       </c>
     </row>
@@ -24346,7 +24346,7 @@
       </c>
       <c r="B642" t="inlineStr">
         <is>
-          <t>paclock_ft_base_v2_v2</t>
+          <t>paclock_ft_base_partial</t>
         </is>
       </c>
       <c r="C642" t="inlineStr">
@@ -24361,7 +24361,7 @@
       </c>
       <c r="E642" t="inlineStr">
         <is>
-          <t>no row label for 'paclock_ft_base_v2_v2'</t>
+          <t>no row label for 'paclock_ft_base_partial'</t>
         </is>
       </c>
     </row>
@@ -24373,7 +24373,7 @@
       </c>
       <c r="B643" t="inlineStr">
         <is>
-          <t>paclock_fuse</t>
+          <t>paclock_ft_base_v2_v2</t>
         </is>
       </c>
       <c r="C643" t="inlineStr">
@@ -24388,7 +24388,7 @@
       </c>
       <c r="E643" t="inlineStr">
         <is>
-          <t>no row label for 'paclock_fuse'</t>
+          <t>no row label for 'paclock_ft_base_v2_v2'</t>
         </is>
       </c>
     </row>
@@ -24400,7 +24400,7 @@
       </c>
       <c r="B644" t="inlineStr">
         <is>
-          <t>paclock_fusegate</t>
+          <t>paclock_fuse</t>
         </is>
       </c>
       <c r="C644" t="inlineStr">
@@ -24415,7 +24415,7 @@
       </c>
       <c r="E644" t="inlineStr">
         <is>
-          <t>no row label for 'paclock_fusegate'</t>
+          <t>no row label for 'paclock_fuse'</t>
         </is>
       </c>
     </row>
@@ -24427,7 +24427,7 @@
       </c>
       <c r="B645" t="inlineStr">
         <is>
-          <t>paclock_h12</t>
+          <t>paclock_fusegate</t>
         </is>
       </c>
       <c r="C645" t="inlineStr">
@@ -24442,7 +24442,7 @@
       </c>
       <c r="E645" t="inlineStr">
         <is>
-          <t>no row label for 'paclock_h12'</t>
+          <t>no row label for 'paclock_fusegate'</t>
         </is>
       </c>
     </row>
@@ -24454,7 +24454,7 @@
       </c>
       <c r="B646" t="inlineStr">
         <is>
-          <t>paclock_h1stem</t>
+          <t>paclock_h12</t>
         </is>
       </c>
       <c r="C646" t="inlineStr">
@@ -24469,7 +24469,7 @@
       </c>
       <c r="E646" t="inlineStr">
         <is>
-          <t>no row label for 'paclock_h1stem'</t>
+          <t>no row label for 'paclock_h12'</t>
         </is>
       </c>
     </row>
@@ -24481,7 +24481,7 @@
       </c>
       <c r="B647" t="inlineStr">
         <is>
-          <t>paclock_h2mont</t>
+          <t>paclock_h1stem</t>
         </is>
       </c>
       <c r="C647" t="inlineStr">
@@ -24496,7 +24496,7 @@
       </c>
       <c r="E647" t="inlineStr">
         <is>
-          <t>no row label for 'paclock_h2mont'</t>
+          <t>no row label for 'paclock_h1stem'</t>
         </is>
       </c>
     </row>
@@ -24508,7 +24508,7 @@
       </c>
       <c r="B648" t="inlineStr">
         <is>
-          <t>paclock_hybrid</t>
+          <t>paclock_h2mont</t>
         </is>
       </c>
       <c r="C648" t="inlineStr">
@@ -24523,7 +24523,7 @@
       </c>
       <c r="E648" t="inlineStr">
         <is>
-          <t>no row label for 'paclock_hybrid'</t>
+          <t>no row label for 'paclock_h2mont'</t>
         </is>
       </c>
     </row>
@@ -24535,7 +24535,7 @@
       </c>
       <c r="B649" t="inlineStr">
         <is>
-          <t>paclock_hybrid_attn</t>
+          <t>paclock_hybrid</t>
         </is>
       </c>
       <c r="C649" t="inlineStr">
@@ -24550,7 +24550,7 @@
       </c>
       <c r="E649" t="inlineStr">
         <is>
-          <t>no row label for 'paclock_hybrid_attn'</t>
+          <t>no row label for 'paclock_hybrid'</t>
         </is>
       </c>
     </row>
@@ -24562,7 +24562,7 @@
       </c>
       <c r="B650" t="inlineStr">
         <is>
-          <t>paclock_hybrid_gate</t>
+          <t>paclock_hybrid_attn</t>
         </is>
       </c>
       <c r="C650" t="inlineStr">
@@ -24577,7 +24577,7 @@
       </c>
       <c r="E650" t="inlineStr">
         <is>
-          <t>no row label for 'paclock_hybrid_gate'</t>
+          <t>no row label for 'paclock_hybrid_attn'</t>
         </is>
       </c>
     </row>
@@ -24589,7 +24589,7 @@
       </c>
       <c r="B651" t="inlineStr">
         <is>
-          <t>paclock_lf05_ptF</t>
+          <t>paclock_hybrid_gate</t>
         </is>
       </c>
       <c r="C651" t="inlineStr">
@@ -24604,7 +24604,7 @@
       </c>
       <c r="E651" t="inlineStr">
         <is>
-          <t>no row label for 'paclock_lf05_ptF'</t>
+          <t>no row label for 'paclock_hybrid_gate'</t>
         </is>
       </c>
     </row>
@@ -24616,7 +24616,7 @@
       </c>
       <c r="B652" t="inlineStr">
         <is>
-          <t>paclock_lf05_scratch</t>
+          <t>paclock_lf05_ptF</t>
         </is>
       </c>
       <c r="C652" t="inlineStr">
@@ -24631,7 +24631,7 @@
       </c>
       <c r="E652" t="inlineStr">
         <is>
-          <t>no row label for 'paclock_lf05_scratch'</t>
+          <t>no row label for 'paclock_lf05_ptF'</t>
         </is>
       </c>
     </row>
@@ -24643,7 +24643,7 @@
       </c>
       <c r="B653" t="inlineStr">
         <is>
-          <t>paclock_lf10_ptF</t>
+          <t>paclock_lf05_scratch</t>
         </is>
       </c>
       <c r="C653" t="inlineStr">
@@ -24658,7 +24658,7 @@
       </c>
       <c r="E653" t="inlineStr">
         <is>
-          <t>no row label for 'paclock_lf10_ptF'</t>
+          <t>no row label for 'paclock_lf05_scratch'</t>
         </is>
       </c>
     </row>
@@ -24670,7 +24670,7 @@
       </c>
       <c r="B654" t="inlineStr">
         <is>
-          <t>paclock_lf10_scratch</t>
+          <t>paclock_lf10_ptF</t>
         </is>
       </c>
       <c r="C654" t="inlineStr">
@@ -24685,7 +24685,7 @@
       </c>
       <c r="E654" t="inlineStr">
         <is>
-          <t>no row label for 'paclock_lf10_scratch'</t>
+          <t>no row label for 'paclock_lf10_ptF'</t>
         </is>
       </c>
     </row>
@@ -24697,7 +24697,7 @@
       </c>
       <c r="B655" t="inlineStr">
         <is>
-          <t>paclock_lf25_ptF</t>
+          <t>paclock_lf10_scratch</t>
         </is>
       </c>
       <c r="C655" t="inlineStr">
@@ -24712,7 +24712,7 @@
       </c>
       <c r="E655" t="inlineStr">
         <is>
-          <t>no row label for 'paclock_lf25_ptF'</t>
+          <t>no row label for 'paclock_lf10_scratch'</t>
         </is>
       </c>
     </row>
@@ -24724,7 +24724,7 @@
       </c>
       <c r="B656" t="inlineStr">
         <is>
-          <t>paclock_lf25_scratch</t>
+          <t>paclock_lf25_ptF</t>
         </is>
       </c>
       <c r="C656" t="inlineStr">
@@ -24739,7 +24739,7 @@
       </c>
       <c r="E656" t="inlineStr">
         <is>
-          <t>no row label for 'paclock_lf25_scratch'</t>
+          <t>no row label for 'paclock_lf25_ptF'</t>
         </is>
       </c>
     </row>
@@ -24751,7 +24751,7 @@
       </c>
       <c r="B657" t="inlineStr">
         <is>
-          <t>paclock_nb16</t>
+          <t>paclock_lf25_scratch</t>
         </is>
       </c>
       <c r="C657" t="inlineStr">
@@ -24766,7 +24766,7 @@
       </c>
       <c r="E657" t="inlineStr">
         <is>
-          <t>no row label for 'paclock_nb16'</t>
+          <t>no row label for 'paclock_lf25_scratch'</t>
         </is>
       </c>
     </row>
@@ -24778,7 +24778,7 @@
       </c>
       <c r="B658" t="inlineStr">
         <is>
-          <t>paclock_pac</t>
+          <t>paclock_nb16</t>
         </is>
       </c>
       <c r="C658" t="inlineStr">
@@ -24793,7 +24793,7 @@
       </c>
       <c r="E658" t="inlineStr">
         <is>
-          <t>the workbook has no row for this variant</t>
+          <t>no row label for 'paclock_nb16'</t>
         </is>
       </c>
     </row>
@@ -24805,7 +24805,7 @@
       </c>
       <c r="B659" t="inlineStr">
         <is>
-          <t>paclock_pilot_frozen</t>
+          <t>paclock_pac</t>
         </is>
       </c>
       <c r="C659" t="inlineStr">
@@ -24832,7 +24832,7 @@
       </c>
       <c r="B660" t="inlineStr">
         <is>
-          <t>paclock_pilot_unfiltered</t>
+          <t>paclock_pilot_frozen</t>
         </is>
       </c>
       <c r="C660" t="inlineStr">
@@ -24859,22 +24859,22 @@
       </c>
       <c r="B661" t="inlineStr">
         <is>
-          <t>paclock_probe_rand</t>
+          <t>paclock_pilot_unfiltered</t>
         </is>
       </c>
       <c r="C661" t="inlineStr">
         <is>
-          <t>[0]</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D661" t="inlineStr">
         <is>
-          <t>filled (single-seed, grey)</t>
+          <t>skipped</t>
         </is>
       </c>
       <c r="E661" t="inlineStr">
         <is>
-          <t>cohen_kappa 0.3859</t>
+          <t>the workbook has no row for this variant</t>
         </is>
       </c>
     </row>
@@ -24886,22 +24886,22 @@
       </c>
       <c r="B662" t="inlineStr">
         <is>
-          <t>paclock_probe_v1</t>
+          <t>paclock_probe_rand</t>
         </is>
       </c>
       <c r="C662" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>[0]</t>
         </is>
       </c>
       <c r="D662" t="inlineStr">
         <is>
-          <t>skipped</t>
+          <t>filled (single-seed, grey)</t>
         </is>
       </c>
       <c r="E662" t="inlineStr">
         <is>
-          <t>no row label for 'paclock_probe_v1'</t>
+          <t>cohen_kappa 0.3859</t>
         </is>
       </c>
     </row>
@@ -24913,22 +24913,22 @@
       </c>
       <c r="B663" t="inlineStr">
         <is>
-          <t>paclock_probe_v2</t>
+          <t>paclock_probe_v1</t>
         </is>
       </c>
       <c r="C663" t="inlineStr">
         <is>
-          <t>[0]</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D663" t="inlineStr">
         <is>
-          <t>filled (single-seed, grey)</t>
+          <t>skipped</t>
         </is>
       </c>
       <c r="E663" t="inlineStr">
         <is>
-          <t>cohen_kappa 0.5184</t>
+          <t>no row label for 'paclock_probe_v1'</t>
         </is>
       </c>
     </row>
@@ -24940,22 +24940,22 @@
       </c>
       <c r="B664" t="inlineStr">
         <is>
-          <t>paclock_ptF_frozenL3</t>
+          <t>paclock_probe_v2</t>
         </is>
       </c>
       <c r="C664" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>[0]</t>
         </is>
       </c>
       <c r="D664" t="inlineStr">
         <is>
-          <t>skipped</t>
+          <t>filled (single-seed, grey)</t>
         </is>
       </c>
       <c r="E664" t="inlineStr">
         <is>
-          <t>no row label for 'paclock_ptF_frozenL3'</t>
+          <t>cohen_kappa 0.5184</t>
         </is>
       </c>
     </row>
@@ -24967,7 +24967,7 @@
       </c>
       <c r="B665" t="inlineStr">
         <is>
-          <t>paclock_pt_base</t>
+          <t>paclock_ptF_frozenL3</t>
         </is>
       </c>
       <c r="C665" t="inlineStr">
@@ -24982,7 +24982,7 @@
       </c>
       <c r="E665" t="inlineStr">
         <is>
-          <t>row 'PACLock (pretrained, base)' not found</t>
+          <t>no row label for 'paclock_ptF_frozenL3'</t>
         </is>
       </c>
     </row>
@@ -24994,7 +24994,7 @@
       </c>
       <c r="B666" t="inlineStr">
         <is>
-          <t>paclock_pt_base_p200</t>
+          <t>paclock_pt_base</t>
         </is>
       </c>
       <c r="C666" t="inlineStr">
@@ -25009,7 +25009,7 @@
       </c>
       <c r="E666" t="inlineStr">
         <is>
-          <t>no row label for 'paclock_pt_base_p200'</t>
+          <t>row 'PACLock (pretrained, base)' not found</t>
         </is>
       </c>
     </row>
@@ -25021,7 +25021,7 @@
       </c>
       <c r="B667" t="inlineStr">
         <is>
-          <t>paclock_pt_large</t>
+          <t>paclock_pt_base_p200</t>
         </is>
       </c>
       <c r="C667" t="inlineStr">
@@ -25036,7 +25036,7 @@
       </c>
       <c r="E667" t="inlineStr">
         <is>
-          <t>row 'PACLock (pretrained, large)' not found</t>
+          <t>no row label for 'paclock_pt_base_p200'</t>
         </is>
       </c>
     </row>
@@ -25048,7 +25048,7 @@
       </c>
       <c r="B668" t="inlineStr">
         <is>
-          <t>paclock_rawtok</t>
+          <t>paclock_pt_large</t>
         </is>
       </c>
       <c r="C668" t="inlineStr">
@@ -25063,7 +25063,7 @@
       </c>
       <c r="E668" t="inlineStr">
         <is>
-          <t>no row label for 'paclock_rawtok'</t>
+          <t>row 'PACLock (pretrained, large)' not found</t>
         </is>
       </c>
     </row>
@@ -25075,7 +25075,7 @@
       </c>
       <c r="B669" t="inlineStr">
         <is>
-          <t>paclock_rot2</t>
+          <t>paclock_rawtok</t>
         </is>
       </c>
       <c r="C669" t="inlineStr">
@@ -25090,7 +25090,7 @@
       </c>
       <c r="E669" t="inlineStr">
         <is>
-          <t>no row label for 'paclock_rot2'</t>
+          <t>no row label for 'paclock_rawtok'</t>
         </is>
       </c>
     </row>
@@ -25102,7 +25102,7 @@
       </c>
       <c r="B670" t="inlineStr">
         <is>
-          <t>paclock_rot_ms</t>
+          <t>paclock_rot2</t>
         </is>
       </c>
       <c r="C670" t="inlineStr">
@@ -25117,7 +25117,7 @@
       </c>
       <c r="E670" t="inlineStr">
         <is>
-          <t>no row label for 'paclock_rot_ms'</t>
+          <t>no row label for 'paclock_rot2'</t>
         </is>
       </c>
     </row>
@@ -25129,7 +25129,7 @@
       </c>
       <c r="B671" t="inlineStr">
         <is>
-          <t>paclock_sphead</t>
+          <t>paclock_rot_ms</t>
         </is>
       </c>
       <c r="C671" t="inlineStr">
@@ -25144,7 +25144,7 @@
       </c>
       <c r="E671" t="inlineStr">
         <is>
-          <t>no row label for 'paclock_sphead'</t>
+          <t>no row label for 'paclock_rot_ms'</t>
         </is>
       </c>
     </row>
@@ -25156,7 +25156,7 @@
       </c>
       <c r="B672" t="inlineStr">
         <is>
-          <t>paclock_v2</t>
+          <t>paclock_sphead</t>
         </is>
       </c>
       <c r="C672" t="inlineStr">
@@ -25171,7 +25171,7 @@
       </c>
       <c r="E672" t="inlineStr">
         <is>
-          <t>row 'PACLock (from scratch, full)' not found</t>
+          <t>no row label for 'paclock_sphead'</t>
         </is>
       </c>
     </row>
@@ -25183,7 +25183,7 @@
       </c>
       <c r="B673" t="inlineStr">
         <is>
-          <t>paclock_v2_n20000</t>
+          <t>paclock_v2</t>
         </is>
       </c>
       <c r="C673" t="inlineStr">
@@ -25198,7 +25198,7 @@
       </c>
       <c r="E673" t="inlineStr">
         <is>
-          <t>no row label for 'paclock_v2_n20000'</t>
+          <t>row 'PACLock (from scratch, full)' not found</t>
         </is>
       </c>
     </row>
@@ -25210,7 +25210,7 @@
       </c>
       <c r="B674" t="inlineStr">
         <is>
-          <t>paclock_v2_n2160</t>
+          <t>paclock_v2_n20000</t>
         </is>
       </c>
       <c r="C674" t="inlineStr">
@@ -25225,7 +25225,7 @@
       </c>
       <c r="E674" t="inlineStr">
         <is>
-          <t>no row label for 'paclock_v2_n2160'</t>
+          <t>no row label for 'paclock_v2_n20000'</t>
         </is>
       </c>
     </row>
@@ -25237,7 +25237,7 @@
       </c>
       <c r="B675" t="inlineStr">
         <is>
-          <t>paclock_v2_n6720</t>
+          <t>paclock_v2_n2160</t>
         </is>
       </c>
       <c r="C675" t="inlineStr">
@@ -25252,7 +25252,7 @@
       </c>
       <c r="E675" t="inlineStr">
         <is>
-          <t>no row label for 'paclock_v2_n6720'</t>
+          <t>no row label for 'paclock_v2_n2160'</t>
         </is>
       </c>
     </row>
@@ -25264,7 +25264,7 @@
       </c>
       <c r="B676" t="inlineStr">
         <is>
-          <t>paclock_v3traj_100000frozen</t>
+          <t>paclock_v2_n6720</t>
         </is>
       </c>
       <c r="C676" t="inlineStr">
@@ -25279,7 +25279,7 @@
       </c>
       <c r="E676" t="inlineStr">
         <is>
-          <t>no row label for 'paclock_v3traj_100000frozen'</t>
+          <t>no row label for 'paclock_v2_n6720'</t>
         </is>
       </c>
     </row>
@@ -25291,7 +25291,7 @@
       </c>
       <c r="B677" t="inlineStr">
         <is>
-          <t>paclock_v3traj_100000frozenL3</t>
+          <t>paclock_v3traj_100000frozen</t>
         </is>
       </c>
       <c r="C677" t="inlineStr">
@@ -25306,7 +25306,7 @@
       </c>
       <c r="E677" t="inlineStr">
         <is>
-          <t>no row label for 'paclock_v3traj_100000frozenL3'</t>
+          <t>no row label for 'paclock_v3traj_100000frozen'</t>
         </is>
       </c>
     </row>
@@ -25318,7 +25318,7 @@
       </c>
       <c r="B678" t="inlineStr">
         <is>
-          <t>paclock_v3traj_20000frozen</t>
+          <t>paclock_v3traj_100000frozenL3</t>
         </is>
       </c>
       <c r="C678" t="inlineStr">
@@ -25333,7 +25333,7 @@
       </c>
       <c r="E678" t="inlineStr">
         <is>
-          <t>no row label for 'paclock_v3traj_20000frozen'</t>
+          <t>no row label for 'paclock_v3traj_100000frozenL3'</t>
         </is>
       </c>
     </row>
@@ -25345,7 +25345,7 @@
       </c>
       <c r="B679" t="inlineStr">
         <is>
-          <t>paclock_v3traj_20000frozenL3</t>
+          <t>paclock_v3traj_20000frozen</t>
         </is>
       </c>
       <c r="C679" t="inlineStr">
@@ -25360,7 +25360,7 @@
       </c>
       <c r="E679" t="inlineStr">
         <is>
-          <t>no row label for 'paclock_v3traj_20000frozenL3'</t>
+          <t>no row label for 'paclock_v3traj_20000frozen'</t>
         </is>
       </c>
     </row>
@@ -25372,7 +25372,7 @@
       </c>
       <c r="B680" t="inlineStr">
         <is>
-          <t>paclock_v3traj_40000frozen</t>
+          <t>paclock_v3traj_20000frozenL3</t>
         </is>
       </c>
       <c r="C680" t="inlineStr">
@@ -25387,7 +25387,7 @@
       </c>
       <c r="E680" t="inlineStr">
         <is>
-          <t>no row label for 'paclock_v3traj_40000frozen'</t>
+          <t>no row label for 'paclock_v3traj_20000frozenL3'</t>
         </is>
       </c>
     </row>
@@ -25399,7 +25399,7 @@
       </c>
       <c r="B681" t="inlineStr">
         <is>
-          <t>paclock_v3traj_40000frozenL3</t>
+          <t>paclock_v3traj_40000frozen</t>
         </is>
       </c>
       <c r="C681" t="inlineStr">
@@ -25414,7 +25414,7 @@
       </c>
       <c r="E681" t="inlineStr">
         <is>
-          <t>no row label for 'paclock_v3traj_40000frozenL3'</t>
+          <t>no row label for 'paclock_v3traj_40000frozen'</t>
         </is>
       </c>
     </row>
@@ -25426,7 +25426,7 @@
       </c>
       <c r="B682" t="inlineStr">
         <is>
-          <t>paclock_v3traj_60000frozen</t>
+          <t>paclock_v3traj_40000frozenL3</t>
         </is>
       </c>
       <c r="C682" t="inlineStr">
@@ -25441,7 +25441,7 @@
       </c>
       <c r="E682" t="inlineStr">
         <is>
-          <t>no row label for 'paclock_v3traj_60000frozen'</t>
+          <t>no row label for 'paclock_v3traj_40000frozenL3'</t>
         </is>
       </c>
     </row>
@@ -25453,7 +25453,7 @@
       </c>
       <c r="B683" t="inlineStr">
         <is>
-          <t>paclock_v3traj_60000frozenL3</t>
+          <t>paclock_v3traj_60000frozen</t>
         </is>
       </c>
       <c r="C683" t="inlineStr">
@@ -25468,7 +25468,7 @@
       </c>
       <c r="E683" t="inlineStr">
         <is>
-          <t>no row label for 'paclock_v3traj_60000frozenL3'</t>
+          <t>no row label for 'paclock_v3traj_60000frozen'</t>
         </is>
       </c>
     </row>
@@ -25480,7 +25480,7 @@
       </c>
       <c r="B684" t="inlineStr">
         <is>
-          <t>paclock_v3traj_80000frozen</t>
+          <t>paclock_v3traj_60000frozenL3</t>
         </is>
       </c>
       <c r="C684" t="inlineStr">
@@ -25495,7 +25495,7 @@
       </c>
       <c r="E684" t="inlineStr">
         <is>
-          <t>no row label for 'paclock_v3traj_80000frozen'</t>
+          <t>no row label for 'paclock_v3traj_60000frozenL3'</t>
         </is>
       </c>
     </row>
@@ -25507,7 +25507,7 @@
       </c>
       <c r="B685" t="inlineStr">
         <is>
-          <t>paclock_v3traj_80000frozenL3</t>
+          <t>paclock_v3traj_80000frozen</t>
         </is>
       </c>
       <c r="C685" t="inlineStr">
@@ -25522,7 +25522,7 @@
       </c>
       <c r="E685" t="inlineStr">
         <is>
-          <t>no row label for 'paclock_v3traj_80000frozenL3'</t>
+          <t>no row label for 'paclock_v3traj_80000frozen'</t>
         </is>
       </c>
     </row>
@@ -25534,27 +25534,22 @@
       </c>
       <c r="B686" t="inlineStr">
         <is>
-          <t>reve_pretrained</t>
+          <t>paclock_v3traj_80000frozenL3</t>
         </is>
       </c>
       <c r="C686" t="inlineStr">
         <is>
-          <t>[0, 1, 2]</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D686" t="inlineStr">
         <is>
-          <t>filled</t>
+          <t>skipped</t>
         </is>
       </c>
       <c r="E686" t="inlineStr">
         <is>
-          <t>[实测 69.48M] cohen_kappa per-seed 0:0.7188, 1:0.6423, 2:0.6927</t>
-        </is>
-      </c>
-      <c r="F686" t="inlineStr">
-        <is>
-          <t>stopped_by=patience lr=0.0001 batch_size=128 epochs=30 patience=10 eval_every_steps=0 loss=cross_entropy label_smoothing=0.0 grad_clip=1.0</t>
+          <t>no row label for 'paclock_v3traj_80000frozenL3'</t>
         </is>
       </c>
     </row>
@@ -25566,7 +25561,7 @@
       </c>
       <c r="B687" t="inlineStr">
         <is>
-          <t>sparcnet</t>
+          <t>reve_pretrained</t>
         </is>
       </c>
       <c r="C687" t="inlineStr">
@@ -25581,12 +25576,12 @@
       </c>
       <c r="E687" t="inlineStr">
         <is>
-          <t>[实测 0.99M] cohen_kappa per-seed 0:0.4665, 1:0.5199, 2:0.4791</t>
+          <t>[实测 69.48M] cohen_kappa per-seed 0:0.7188, 1:0.6423, 2:0.6927</t>
         </is>
       </c>
       <c r="F687" t="inlineStr">
         <is>
-          <t>lr=0.001 batch_size=512 epochs=100 patience=15 eval_every_steps=0 loss=cross_entropy label_smoothing=0.1</t>
+          <t>stopped_by=patience lr=0.0001 batch_size=128 epochs=30 patience=10 eval_every_steps=0 loss=cross_entropy label_smoothing=0.0 grad_clip=1.0</t>
         </is>
       </c>
     </row>
@@ -25598,22 +25593,27 @@
       </c>
       <c r="B688" t="inlineStr">
         <is>
-          <t>sparcnet_n20000</t>
+          <t>sparcnet</t>
         </is>
       </c>
       <c r="C688" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>[0, 1, 2]</t>
         </is>
       </c>
       <c r="D688" t="inlineStr">
         <is>
-          <t>skipped</t>
+          <t>filled</t>
         </is>
       </c>
       <c r="E688" t="inlineStr">
         <is>
-          <t>no row label for 'sparcnet_n20000'</t>
+          <t>[实测 0.99M] cohen_kappa per-seed 0:0.4665, 1:0.5199, 2:0.4791</t>
+        </is>
+      </c>
+      <c r="F688" t="inlineStr">
+        <is>
+          <t>lr=0.001 batch_size=512 epochs=100 patience=15 eval_every_steps=0 loss=cross_entropy label_smoothing=0.1</t>
         </is>
       </c>
     </row>
@@ -25625,7 +25625,7 @@
       </c>
       <c r="B689" t="inlineStr">
         <is>
-          <t>sparcnet_n2160</t>
+          <t>sparcnet_n20000</t>
         </is>
       </c>
       <c r="C689" t="inlineStr">
@@ -25640,7 +25640,7 @@
       </c>
       <c r="E689" t="inlineStr">
         <is>
-          <t>no row label for 'sparcnet_n2160'</t>
+          <t>no row label for 'sparcnet_n20000'</t>
         </is>
       </c>
     </row>
@@ -25652,7 +25652,7 @@
       </c>
       <c r="B690" t="inlineStr">
         <is>
-          <t>sparcnet_n6720</t>
+          <t>sparcnet_n2160</t>
         </is>
       </c>
       <c r="C690" t="inlineStr">
@@ -25667,7 +25667,7 @@
       </c>
       <c r="E690" t="inlineStr">
         <is>
-          <t>no row label for 'sparcnet_n6720'</t>
+          <t>no row label for 'sparcnet_n2160'</t>
         </is>
       </c>
     </row>
@@ -25679,27 +25679,22 @@
       </c>
       <c r="B691" t="inlineStr">
         <is>
-          <t>st_transformer</t>
+          <t>sparcnet_n6720</t>
         </is>
       </c>
       <c r="C691" t="inlineStr">
         <is>
-          <t>[0, 1, 2]</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D691" t="inlineStr">
         <is>
-          <t>filled</t>
+          <t>skipped</t>
         </is>
       </c>
       <c r="E691" t="inlineStr">
         <is>
-          <t>[实测 3.43M] cohen_kappa per-seed 0:0.5139, 1:0.4916, 2:0.4962</t>
-        </is>
-      </c>
-      <c r="F691" t="inlineStr">
-        <is>
-          <t>lr=0.001 batch_size=512 epochs=100 patience=15 eval_every_steps=0 loss=cross_entropy label_smoothing=0.1</t>
+          <t>no row label for 'sparcnet_n6720'</t>
         </is>
       </c>
     </row>
@@ -25711,7 +25706,7 @@
       </c>
       <c r="B692" t="inlineStr">
         <is>
-          <t>tfm_pretrained</t>
+          <t>st_transformer</t>
         </is>
       </c>
       <c r="C692" t="inlineStr">
@@ -25726,24 +25721,24 @@
       </c>
       <c r="E692" t="inlineStr">
         <is>
-          <t>[实测 1.89M] cohen_kappa per-seed 0:0.6543, 1:0.6299, 2:0.6715</t>
+          <t>[实测 3.43M] cohen_kappa per-seed 0:0.5139, 1:0.4916, 2:0.4962</t>
         </is>
       </c>
       <c r="F692" t="inlineStr">
         <is>
-          <t>lr=0.001 batch_size=512 epochs=50 patience=10 eval_every_steps=100 loss=cross_entropy label_smoothing=0.1</t>
+          <t>lr=0.001 batch_size=512 epochs=100 patience=15 eval_every_steps=0 loss=cross_entropy label_smoothing=0.1</t>
         </is>
       </c>
     </row>
     <row r="693">
       <c r="A693" t="inlineStr">
         <is>
-          <t>tusz</t>
+          <t>tuev</t>
         </is>
       </c>
       <c r="B693" t="inlineStr">
         <is>
-          <t>biot_prest16</t>
+          <t>tfm_pretrained</t>
         </is>
       </c>
       <c r="C693" t="inlineStr">
@@ -25758,12 +25753,12 @@
       </c>
       <c r="E693" t="inlineStr">
         <is>
-          <t>[实测 3.19M] pr_auc per-seed 0:0.3673, 1:0.3513, 2:0.2951</t>
+          <t>[实测 1.89M] cohen_kappa per-seed 0:0.6543, 1:0.6299, 2:0.6715</t>
         </is>
       </c>
       <c r="F693" t="inlineStr">
         <is>
-          <t>lr=0.001 batch_size=512 epochs=100 patience=5 eval_every_steps=0 loss=bce_with_logits</t>
+          <t>lr=0.001 batch_size=512 epochs=50 patience=10 eval_every_steps=100 loss=cross_entropy label_smoothing=0.1</t>
         </is>
       </c>
     </row>
@@ -25775,7 +25770,7 @@
       </c>
       <c r="B694" t="inlineStr">
         <is>
-          <t>biot_scratch</t>
+          <t>biot_prest16</t>
         </is>
       </c>
       <c r="C694" t="inlineStr">
@@ -25790,7 +25785,7 @@
       </c>
       <c r="E694" t="inlineStr">
         <is>
-          <t>[实测 3.19M] pr_auc per-seed 0:0.3186, 1:0.3682, 2:0.3556</t>
+          <t>[实测 3.19M] pr_auc per-seed 0:0.3673, 1:0.3513, 2:0.2951</t>
         </is>
       </c>
       <c r="F694" t="inlineStr">
@@ -25807,22 +25802,27 @@
       </c>
       <c r="B695" t="inlineStr">
         <is>
-          <t>cbramod_pac</t>
+          <t>biot_scratch</t>
         </is>
       </c>
       <c r="C695" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>[0, 1, 2]</t>
         </is>
       </c>
       <c r="D695" t="inlineStr">
         <is>
-          <t>skipped</t>
+          <t>filled</t>
         </is>
       </c>
       <c r="E695" t="inlineStr">
         <is>
-          <t>the workbook has no row for this variant</t>
+          <t>[实测 3.19M] pr_auc per-seed 0:0.3186, 1:0.3682, 2:0.3556</t>
+        </is>
+      </c>
+      <c r="F695" t="inlineStr">
+        <is>
+          <t>lr=0.001 batch_size=512 epochs=100 patience=5 eval_every_steps=0 loss=bce_with_logits</t>
         </is>
       </c>
     </row>
@@ -25834,27 +25834,22 @@
       </c>
       <c r="B696" t="inlineStr">
         <is>
-          <t>cbramod_pretrained</t>
+          <t>cbramod_pac</t>
         </is>
       </c>
       <c r="C696" t="inlineStr">
         <is>
-          <t>[0, 1, 2]</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D696" t="inlineStr">
         <is>
-          <t>filled</t>
+          <t>skipped</t>
         </is>
       </c>
       <c r="E696" t="inlineStr">
         <is>
-          <t>[实测 30.65M] pr_auc per-seed 0:0.4139, 1:0.4061, 2:0.4831</t>
-        </is>
-      </c>
-      <c r="F696" t="inlineStr">
-        <is>
-          <t>lr=0.0001 batch_size=64 epochs=50 patience=0 eval_every_steps=0 loss=bce_with_logits grad_clip=1.0 select_metric=auroc multi_lr=True</t>
+          <t>the workbook has no row for this variant</t>
         </is>
       </c>
     </row>
@@ -25866,7 +25861,7 @@
       </c>
       <c r="B697" t="inlineStr">
         <is>
-          <t>cbramod_scratch</t>
+          <t>cbramod_pretrained</t>
         </is>
       </c>
       <c r="C697" t="inlineStr">
@@ -25881,7 +25876,7 @@
       </c>
       <c r="E697" t="inlineStr">
         <is>
-          <t>[实测 30.65M] pr_auc per-seed 0:0.4662, 1:0.5401, 2:0.4392</t>
+          <t>[实测 30.65M] pr_auc per-seed 0:0.4139, 1:0.4061, 2:0.4831</t>
         </is>
       </c>
       <c r="F697" t="inlineStr">
@@ -25898,27 +25893,22 @@
       </c>
       <c r="B698" t="inlineStr">
         <is>
-          <t>cnn_transformer</t>
+          <t>cbramod_rawfe_bands</t>
         </is>
       </c>
       <c r="C698" t="inlineStr">
         <is>
-          <t>[0, 1, 2]</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D698" t="inlineStr">
         <is>
-          <t>filled</t>
+          <t>skipped</t>
         </is>
       </c>
       <c r="E698" t="inlineStr">
         <is>
-          <t>[实测 3.15M] pr_auc per-seed 0:0.1493, 1:0.4554, 2:0.5073  [seed spread 43% -- mean is a weak summary]</t>
-        </is>
-      </c>
-      <c r="F698" t="inlineStr">
-        <is>
-          <t>lr=0.001 batch_size=512 epochs=20 patience=8 eval_every_steps=200 loss=bce_with_logits</t>
+          <t>no row label for 'cbramod_rawfe_bands'</t>
         </is>
       </c>
     </row>
@@ -25930,7 +25920,7 @@
       </c>
       <c r="B699" t="inlineStr">
         <is>
-          <t>contrawr</t>
+          <t>cbramod_scratch</t>
         </is>
       </c>
       <c r="C699" t="inlineStr">
@@ -25945,12 +25935,12 @@
       </c>
       <c r="E699" t="inlineStr">
         <is>
-          <t>[实测 1.57M] pr_auc per-seed 0:0.5188, 1:0.4849, 2:0.5092</t>
+          <t>[实测 30.65M] pr_auc per-seed 0:0.4662, 1:0.5401, 2:0.4392</t>
         </is>
       </c>
       <c r="F699" t="inlineStr">
         <is>
-          <t>lr=0.001 batch_size=512 epochs=20 patience=8 eval_every_steps=200 loss=bce_with_logits</t>
+          <t>lr=0.0001 batch_size=64 epochs=50 patience=0 eval_every_steps=0 loss=bce_with_logits grad_clip=1.0 select_metric=auroc multi_lr=True</t>
         </is>
       </c>
     </row>
@@ -25962,7 +25952,7 @@
       </c>
       <c r="B700" t="inlineStr">
         <is>
-          <t>csbrain_pretrained</t>
+          <t>cnn_transformer</t>
         </is>
       </c>
       <c r="C700" t="inlineStr">
@@ -25977,12 +25967,12 @@
       </c>
       <c r="E700" t="inlineStr">
         <is>
-          <t>[实测 41.06M] pr_auc per-seed 0:0.6207, 1:0.3889, 2:0.5414  [seed spread 19% -- mean is a weak summary]</t>
+          <t>[实测 3.15M] pr_auc per-seed 0:0.1493, 1:0.4554, 2:0.5073  [seed spread 43% -- mean is a weak summary]</t>
         </is>
       </c>
       <c r="F700" t="inlineStr">
         <is>
-          <t>stopped_by=patience lr=0.0001 batch_size=64 epochs=25 patience=10 eval_every_steps=500 loss=bce_with_logits grad_clip=1.0</t>
+          <t>lr=0.001 batch_size=512 epochs=20 patience=8 eval_every_steps=200 loss=bce_with_logits</t>
         </is>
       </c>
     </row>
@@ -25994,7 +25984,7 @@
       </c>
       <c r="B701" t="inlineStr">
         <is>
-          <t>eegconformer</t>
+          <t>contrawr</t>
         </is>
       </c>
       <c r="C701" t="inlineStr">
@@ -26009,12 +25999,12 @@
       </c>
       <c r="E701" t="inlineStr">
         <is>
-          <t>[实测 1.46M] pr_auc per-seed 0:0.3624, 1:0.2985, 2:0.2961</t>
+          <t>[实测 1.57M] pr_auc per-seed 0:0.5188, 1:0.4849, 2:0.5092</t>
         </is>
       </c>
       <c r="F701" t="inlineStr">
         <is>
-          <t>stopped_by=patience lr=0.001 batch_size=128 epochs=20 patience=8 eval_every_steps=200 loss=bce_with_logits grad_clip=1.0</t>
+          <t>lr=0.001 batch_size=512 epochs=20 patience=8 eval_every_steps=200 loss=bce_with_logits</t>
         </is>
       </c>
     </row>
@@ -26026,22 +26016,27 @@
       </c>
       <c r="B702" t="inlineStr">
         <is>
-          <t>eegconformer_t1</t>
+          <t>csbrain_pretrained</t>
         </is>
       </c>
       <c r="C702" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>[0, 1, 2]</t>
         </is>
       </c>
       <c r="D702" t="inlineStr">
         <is>
-          <t>skipped</t>
+          <t>filled</t>
         </is>
       </c>
       <c r="E702" t="inlineStr">
         <is>
-          <t>no row label for 'eegconformer_t1'</t>
+          <t>[实测 41.06M] pr_auc per-seed 0:0.6207, 1:0.3889, 2:0.5414  [seed spread 19% -- mean is a weak summary]</t>
+        </is>
+      </c>
+      <c r="F702" t="inlineStr">
+        <is>
+          <t>stopped_by=patience lr=0.0001 batch_size=64 epochs=25 patience=10 eval_every_steps=500 loss=bce_with_logits grad_clip=1.0</t>
         </is>
       </c>
     </row>
@@ -26053,22 +26048,27 @@
       </c>
       <c r="B703" t="inlineStr">
         <is>
-          <t>eegconformer_t2</t>
+          <t>eegconformer</t>
         </is>
       </c>
       <c r="C703" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>[0, 1, 2]</t>
         </is>
       </c>
       <c r="D703" t="inlineStr">
         <is>
-          <t>skipped</t>
+          <t>filled</t>
         </is>
       </c>
       <c r="E703" t="inlineStr">
         <is>
-          <t>no row label for 'eegconformer_t2'</t>
+          <t>[实测 1.46M] pr_auc per-seed 0:0.3624, 1:0.2985, 2:0.2961</t>
+        </is>
+      </c>
+      <c r="F703" t="inlineStr">
+        <is>
+          <t>stopped_by=patience lr=0.001 batch_size=128 epochs=20 patience=8 eval_every_steps=200 loss=bce_with_logits grad_clip=1.0</t>
         </is>
       </c>
     </row>
@@ -26080,7 +26080,7 @@
       </c>
       <c r="B704" t="inlineStr">
         <is>
-          <t>eegconformer_t3</t>
+          <t>eegconformer_t1</t>
         </is>
       </c>
       <c r="C704" t="inlineStr">
@@ -26095,7 +26095,7 @@
       </c>
       <c r="E704" t="inlineStr">
         <is>
-          <t>no row label for 'eegconformer_t3'</t>
+          <t>no row label for 'eegconformer_t1'</t>
         </is>
       </c>
     </row>
@@ -26107,7 +26107,7 @@
       </c>
       <c r="B705" t="inlineStr">
         <is>
-          <t>eegconformer_t4</t>
+          <t>eegconformer_t2</t>
         </is>
       </c>
       <c r="C705" t="inlineStr">
@@ -26122,7 +26122,7 @@
       </c>
       <c r="E705" t="inlineStr">
         <is>
-          <t>no row label for 'eegconformer_t4'</t>
+          <t>no row label for 'eegconformer_t2'</t>
         </is>
       </c>
     </row>
@@ -26134,27 +26134,22 @@
       </c>
       <c r="B706" t="inlineStr">
         <is>
-          <t>eegnet</t>
+          <t>eegconformer_t3</t>
         </is>
       </c>
       <c r="C706" t="inlineStr">
         <is>
-          <t>[0, 1, 2]</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D706" t="inlineStr">
         <is>
-          <t>filled</t>
+          <t>skipped</t>
         </is>
       </c>
       <c r="E706" t="inlineStr">
         <is>
-          <t>[实测 0.00M] pr_auc per-seed 0:0.4598, 1:0.4970, 2:0.5196</t>
-        </is>
-      </c>
-      <c r="F706" t="inlineStr">
-        <is>
-          <t>stopped_by=patience lr=0.001 batch_size=512 epochs=20 patience=8 eval_every_steps=200 loss=bce_with_logits grad_clip=1.0</t>
+          <t>no row label for 'eegconformer_t3'</t>
         </is>
       </c>
     </row>
@@ -26166,7 +26161,7 @@
       </c>
       <c r="B707" t="inlineStr">
         <is>
-          <t>eegnet_t1</t>
+          <t>eegconformer_t4</t>
         </is>
       </c>
       <c r="C707" t="inlineStr">
@@ -26181,7 +26176,7 @@
       </c>
       <c r="E707" t="inlineStr">
         <is>
-          <t>no row label for 'eegnet_t1'</t>
+          <t>no row label for 'eegconformer_t4'</t>
         </is>
       </c>
     </row>
@@ -26193,22 +26188,27 @@
       </c>
       <c r="B708" t="inlineStr">
         <is>
-          <t>eegnet_t2</t>
+          <t>eegnet</t>
         </is>
       </c>
       <c r="C708" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>[0, 1, 2]</t>
         </is>
       </c>
       <c r="D708" t="inlineStr">
         <is>
-          <t>skipped</t>
+          <t>filled</t>
         </is>
       </c>
       <c r="E708" t="inlineStr">
         <is>
-          <t>no row label for 'eegnet_t2'</t>
+          <t>[实测 0.00M] pr_auc per-seed 0:0.4598, 1:0.4970, 2:0.5196</t>
+        </is>
+      </c>
+      <c r="F708" t="inlineStr">
+        <is>
+          <t>stopped_by=patience lr=0.001 batch_size=512 epochs=20 patience=8 eval_every_steps=200 loss=bce_with_logits grad_clip=1.0</t>
         </is>
       </c>
     </row>
@@ -26220,7 +26220,7 @@
       </c>
       <c r="B709" t="inlineStr">
         <is>
-          <t>eegnet_t3</t>
+          <t>eegnet_t1</t>
         </is>
       </c>
       <c r="C709" t="inlineStr">
@@ -26235,7 +26235,7 @@
       </c>
       <c r="E709" t="inlineStr">
         <is>
-          <t>no row label for 'eegnet_t3'</t>
+          <t>no row label for 'eegnet_t1'</t>
         </is>
       </c>
     </row>
@@ -26247,7 +26247,7 @@
       </c>
       <c r="B710" t="inlineStr">
         <is>
-          <t>eegnet_t4</t>
+          <t>eegnet_t2</t>
         </is>
       </c>
       <c r="C710" t="inlineStr">
@@ -26262,7 +26262,7 @@
       </c>
       <c r="E710" t="inlineStr">
         <is>
-          <t>no row label for 'eegnet_t4'</t>
+          <t>no row label for 'eegnet_t2'</t>
         </is>
       </c>
     </row>
@@ -26274,27 +26274,22 @@
       </c>
       <c r="B711" t="inlineStr">
         <is>
-          <t>eegpt_pretrained</t>
+          <t>eegnet_t3</t>
         </is>
       </c>
       <c r="C711" t="inlineStr">
         <is>
-          <t>[0, 1, 2]</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D711" t="inlineStr">
         <is>
-          <t>filled</t>
+          <t>skipped</t>
         </is>
       </c>
       <c r="E711" t="inlineStr">
         <is>
-          <t>[实测 25.69M] pr_auc per-seed 0:0.6257, 1:0.5102, 2:0.4980</t>
-        </is>
-      </c>
-      <c r="F711" t="inlineStr">
-        <is>
-          <t>lr=0.0004 batch_size=32 epochs=40 patience=10 eval_every_steps=500 loss=bce_with_logits</t>
+          <t>no row label for 'eegnet_t3'</t>
         </is>
       </c>
     </row>
@@ -26306,27 +26301,22 @@
       </c>
       <c r="B712" t="inlineStr">
         <is>
-          <t>feat_best</t>
+          <t>eegnet_t4</t>
         </is>
       </c>
       <c r="C712" t="inlineStr">
         <is>
-          <t>[0, 1, 2]</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D712" t="inlineStr">
         <is>
-          <t>filled</t>
+          <t>skipped</t>
         </is>
       </c>
       <c r="E712" t="inlineStr">
         <is>
-          <t>[实测 0.00M] pr_auc per-seed 0:0.2384, 1:0.2384, 2:0.2384</t>
-        </is>
-      </c>
-      <c r="F712" t="inlineStr">
-        <is>
-          <t>stopped_by=closed-form epochs=1 loss=closed-form</t>
+          <t>no row label for 'eegnet_t4'</t>
         </is>
       </c>
     </row>
@@ -26338,7 +26328,7 @@
       </c>
       <c r="B713" t="inlineStr">
         <is>
-          <t>ffcl</t>
+          <t>eegpt_pretrained</t>
         </is>
       </c>
       <c r="C713" t="inlineStr">
@@ -26353,12 +26343,12 @@
       </c>
       <c r="E713" t="inlineStr">
         <is>
-          <t>[实测 2.46M] pr_auc per-seed 0:0.5511, 1:0.5126, 2:0.5709</t>
+          <t>[实测 25.69M] pr_auc per-seed 0:0.6257, 1:0.5102, 2:0.4980</t>
         </is>
       </c>
       <c r="F713" t="inlineStr">
         <is>
-          <t>lr=0.001 batch_size=512 epochs=20 patience=8 eval_every_steps=200 loss=bce_with_logits</t>
+          <t>lr=0.0004 batch_size=32 epochs=40 patience=10 eval_every_steps=500 loss=bce_with_logits</t>
         </is>
       </c>
     </row>
@@ -26370,7 +26360,7 @@
       </c>
       <c r="B714" t="inlineStr">
         <is>
-          <t>labram_pretrained</t>
+          <t>feat_best</t>
         </is>
       </c>
       <c r="C714" t="inlineStr">
@@ -26385,12 +26375,12 @@
       </c>
       <c r="E714" t="inlineStr">
         <is>
-          <t>[实测 5.82M] pr_auc per-seed 0:0.4828, 1:0.5186, 2:0.4249</t>
+          <t>[实测 0.00M] pr_auc per-seed 0:0.2384, 1:0.2384, 2:0.2384</t>
         </is>
       </c>
       <c r="F714" t="inlineStr">
         <is>
-          <t>lr=0.0005 batch_size=64 epochs=50 patience=10 eval_every_steps=100 loss=bce_with_logits</t>
+          <t>stopped_by=closed-form epochs=1 loss=closed-form</t>
         </is>
       </c>
     </row>
@@ -26402,7 +26392,7 @@
       </c>
       <c r="B715" t="inlineStr">
         <is>
-          <t>labram_scratch</t>
+          <t>ffcl</t>
         </is>
       </c>
       <c r="C715" t="inlineStr">
@@ -26417,12 +26407,12 @@
       </c>
       <c r="E715" t="inlineStr">
         <is>
-          <t>[实测 5.82M] pr_auc per-seed 0:0.4201, 1:0.5036, 2:0.5020</t>
+          <t>[实测 2.46M] pr_auc per-seed 0:0.5511, 1:0.5126, 2:0.5709</t>
         </is>
       </c>
       <c r="F715" t="inlineStr">
         <is>
-          <t>stopped_by=patience lr=0.0005 batch_size=64 epochs=50 patience=10 eval_every_steps=0 loss=bce_with_logits</t>
+          <t>lr=0.001 batch_size=512 epochs=20 patience=8 eval_every_steps=200 loss=bce_with_logits</t>
         </is>
       </c>
     </row>
@@ -26434,22 +26424,27 @@
       </c>
       <c r="B716" t="inlineStr">
         <is>
-          <t>paclock_duplex</t>
+          <t>labram_pretrained</t>
         </is>
       </c>
       <c r="C716" t="inlineStr">
         <is>
-          <t>[0]</t>
+          <t>[0, 1, 2]</t>
         </is>
       </c>
       <c r="D716" t="inlineStr">
         <is>
-          <t>filled (single-seed, grey)</t>
+          <t>filled</t>
         </is>
       </c>
       <c r="E716" t="inlineStr">
         <is>
-          <t>pr_auc 0.6328</t>
+          <t>[实测 5.82M] pr_auc per-seed 0:0.4828, 1:0.5186, 2:0.4249</t>
+        </is>
+      </c>
+      <c r="F716" t="inlineStr">
+        <is>
+          <t>lr=0.0005 batch_size=64 epochs=50 patience=10 eval_every_steps=100 loss=bce_with_logits</t>
         </is>
       </c>
     </row>
@@ -26461,22 +26456,27 @@
       </c>
       <c r="B717" t="inlineStr">
         <is>
-          <t>paclock_duplex_ms</t>
+          <t>labram_scratch</t>
         </is>
       </c>
       <c r="C717" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>[0, 1, 2]</t>
         </is>
       </c>
       <c r="D717" t="inlineStr">
         <is>
-          <t>skipped</t>
+          <t>filled</t>
         </is>
       </c>
       <c r="E717" t="inlineStr">
         <is>
-          <t>no row label for 'paclock_duplex_ms'</t>
+          <t>[实测 5.82M] pr_auc per-seed 0:0.4201, 1:0.5036, 2:0.5020</t>
+        </is>
+      </c>
+      <c r="F717" t="inlineStr">
+        <is>
+          <t>stopped_by=patience lr=0.0005 batch_size=64 epochs=50 patience=10 eval_every_steps=0 loss=bce_with_logits</t>
         </is>
       </c>
     </row>
@@ -26488,22 +26488,22 @@
       </c>
       <c r="B718" t="inlineStr">
         <is>
-          <t>paclock_duplex_p200</t>
+          <t>paclock_duplex</t>
         </is>
       </c>
       <c r="C718" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>[0]</t>
         </is>
       </c>
       <c r="D718" t="inlineStr">
         <is>
-          <t>skipped</t>
+          <t>filled (single-seed, grey)</t>
         </is>
       </c>
       <c r="E718" t="inlineStr">
         <is>
-          <t>no row label for 'paclock_duplex_p200'</t>
+          <t>pr_auc 0.6328</t>
         </is>
       </c>
     </row>
@@ -26515,7 +26515,7 @@
       </c>
       <c r="B719" t="inlineStr">
         <is>
-          <t>paclock_duplex_p200ptF</t>
+          <t>paclock_duplex_ms</t>
         </is>
       </c>
       <c r="C719" t="inlineStr">
@@ -26530,7 +26530,7 @@
       </c>
       <c r="E719" t="inlineStr">
         <is>
-          <t>no row label for 'paclock_duplex_p200ptF'</t>
+          <t>no row label for 'paclock_duplex_ms'</t>
         </is>
       </c>
     </row>
@@ -26542,7 +26542,7 @@
       </c>
       <c r="B720" t="inlineStr">
         <is>
-          <t>paclock_duplex_pt</t>
+          <t>paclock_duplex_p200</t>
         </is>
       </c>
       <c r="C720" t="inlineStr">
@@ -26557,7 +26557,7 @@
       </c>
       <c r="E720" t="inlineStr">
         <is>
-          <t>row 'PACLock (duplex, pretrained)' not found</t>
+          <t>no row label for 'paclock_duplex_p200'</t>
         </is>
       </c>
     </row>
@@ -26569,22 +26569,22 @@
       </c>
       <c r="B721" t="inlineStr">
         <is>
-          <t>paclock_duplex_pt2</t>
+          <t>paclock_duplex_p200ptF</t>
         </is>
       </c>
       <c r="C721" t="inlineStr">
         <is>
-          <t>[0]</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D721" t="inlineStr">
         <is>
-          <t>filled (single-seed, grey)</t>
+          <t>skipped</t>
         </is>
       </c>
       <c r="E721" t="inlineStr">
         <is>
-          <t>pr_auc 0.7143</t>
+          <t>no row label for 'paclock_duplex_p200ptF'</t>
         </is>
       </c>
     </row>
@@ -26596,7 +26596,7 @@
       </c>
       <c r="B722" t="inlineStr">
         <is>
-          <t>paclock_duplex_ptF</t>
+          <t>paclock_duplex_pt</t>
         </is>
       </c>
       <c r="C722" t="inlineStr">
@@ -26611,7 +26611,7 @@
       </c>
       <c r="E722" t="inlineStr">
         <is>
-          <t>row 'CroFreMo (预训练 v2-full)' not found</t>
+          <t>row 'PACLock (duplex, pretrained)' not found</t>
         </is>
       </c>
     </row>
@@ -26623,7 +26623,7 @@
       </c>
       <c r="B723" t="inlineStr">
         <is>
-          <t>paclock_duplex_ptS</t>
+          <t>paclock_duplex_pt2</t>
         </is>
       </c>
       <c r="C723" t="inlineStr">
@@ -26638,7 +26638,7 @@
       </c>
       <c r="E723" t="inlineStr">
         <is>
-          <t>pr_auc 0.6525</t>
+          <t>pr_auc 0.7143</t>
         </is>
       </c>
     </row>
@@ -26650,7 +26650,7 @@
       </c>
       <c r="B724" t="inlineStr">
         <is>
-          <t>paclock_fg_gms</t>
+          <t>paclock_duplex_ptF</t>
         </is>
       </c>
       <c r="C724" t="inlineStr">
@@ -26665,7 +26665,7 @@
       </c>
       <c r="E724" t="inlineStr">
         <is>
-          <t>no row label for 'paclock_fg_gms'</t>
+          <t>row 'CroFreMo (预训练 v2-full)' not found</t>
         </is>
       </c>
     </row>
@@ -26677,22 +26677,22 @@
       </c>
       <c r="B725" t="inlineStr">
         <is>
-          <t>paclock_fg_stem</t>
+          <t>paclock_duplex_ptS</t>
         </is>
       </c>
       <c r="C725" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>[0]</t>
         </is>
       </c>
       <c r="D725" t="inlineStr">
         <is>
-          <t>skipped</t>
+          <t>filled (single-seed, grey)</t>
         </is>
       </c>
       <c r="E725" t="inlineStr">
         <is>
-          <t>no row label for 'paclock_fg_stem'</t>
+          <t>pr_auc 0.6525</t>
         </is>
       </c>
     </row>
@@ -26704,7 +26704,7 @@
       </c>
       <c r="B726" t="inlineStr">
         <is>
-          <t>paclock_flagship</t>
+          <t>paclock_fg_gms</t>
         </is>
       </c>
       <c r="C726" t="inlineStr">
@@ -26719,7 +26719,7 @@
       </c>
       <c r="E726" t="inlineStr">
         <is>
-          <t>no row label for 'paclock_flagship'</t>
+          <t>no row label for 'paclock_fg_gms'</t>
         </is>
       </c>
     </row>
@@ -26731,7 +26731,7 @@
       </c>
       <c r="B727" t="inlineStr">
         <is>
-          <t>paclock_fuse</t>
+          <t>paclock_fg_stem</t>
         </is>
       </c>
       <c r="C727" t="inlineStr">
@@ -26746,7 +26746,7 @@
       </c>
       <c r="E727" t="inlineStr">
         <is>
-          <t>no row label for 'paclock_fuse'</t>
+          <t>no row label for 'paclock_fg_stem'</t>
         </is>
       </c>
     </row>
@@ -26758,7 +26758,7 @@
       </c>
       <c r="B728" t="inlineStr">
         <is>
-          <t>paclock_fusegate</t>
+          <t>paclock_flagship</t>
         </is>
       </c>
       <c r="C728" t="inlineStr">
@@ -26773,7 +26773,7 @@
       </c>
       <c r="E728" t="inlineStr">
         <is>
-          <t>no row label for 'paclock_fusegate'</t>
+          <t>no row label for 'paclock_flagship'</t>
         </is>
       </c>
     </row>
@@ -26785,7 +26785,7 @@
       </c>
       <c r="B729" t="inlineStr">
         <is>
-          <t>paclock_fusegate_ms</t>
+          <t>paclock_fuse</t>
         </is>
       </c>
       <c r="C729" t="inlineStr">
@@ -26800,7 +26800,7 @@
       </c>
       <c r="E729" t="inlineStr">
         <is>
-          <t>no row label for 'paclock_fusegate_ms'</t>
+          <t>no row label for 'paclock_fuse'</t>
         </is>
       </c>
     </row>
@@ -26812,7 +26812,7 @@
       </c>
       <c r="B730" t="inlineStr">
         <is>
-          <t>paclock_hybrid</t>
+          <t>paclock_fusegate</t>
         </is>
       </c>
       <c r="C730" t="inlineStr">
@@ -26827,7 +26827,7 @@
       </c>
       <c r="E730" t="inlineStr">
         <is>
-          <t>no row label for 'paclock_hybrid'</t>
+          <t>no row label for 'paclock_fusegate'</t>
         </is>
       </c>
     </row>
@@ -26839,7 +26839,7 @@
       </c>
       <c r="B731" t="inlineStr">
         <is>
-          <t>paclock_hybrid_attn</t>
+          <t>paclock_fusegate_ms</t>
         </is>
       </c>
       <c r="C731" t="inlineStr">
@@ -26854,7 +26854,7 @@
       </c>
       <c r="E731" t="inlineStr">
         <is>
-          <t>no row label for 'paclock_hybrid_attn'</t>
+          <t>no row label for 'paclock_fusegate_ms'</t>
         </is>
       </c>
     </row>
@@ -26866,7 +26866,7 @@
       </c>
       <c r="B732" t="inlineStr">
         <is>
-          <t>paclock_hybrid_gate</t>
+          <t>paclock_hybrid</t>
         </is>
       </c>
       <c r="C732" t="inlineStr">
@@ -26881,7 +26881,7 @@
       </c>
       <c r="E732" t="inlineStr">
         <is>
-          <t>no row label for 'paclock_hybrid_gate'</t>
+          <t>no row label for 'paclock_hybrid'</t>
         </is>
       </c>
     </row>
@@ -26893,7 +26893,7 @@
       </c>
       <c r="B733" t="inlineStr">
         <is>
-          <t>paclock_lf05_ptF</t>
+          <t>paclock_hybrid_attn</t>
         </is>
       </c>
       <c r="C733" t="inlineStr">
@@ -26908,7 +26908,7 @@
       </c>
       <c r="E733" t="inlineStr">
         <is>
-          <t>no row label for 'paclock_lf05_ptF'</t>
+          <t>no row label for 'paclock_hybrid_attn'</t>
         </is>
       </c>
     </row>
@@ -26920,7 +26920,7 @@
       </c>
       <c r="B734" t="inlineStr">
         <is>
-          <t>paclock_lf05_scratch</t>
+          <t>paclock_hybrid_gate</t>
         </is>
       </c>
       <c r="C734" t="inlineStr">
@@ -26935,7 +26935,7 @@
       </c>
       <c r="E734" t="inlineStr">
         <is>
-          <t>no row label for 'paclock_lf05_scratch'</t>
+          <t>no row label for 'paclock_hybrid_gate'</t>
         </is>
       </c>
     </row>
@@ -26947,7 +26947,7 @@
       </c>
       <c r="B735" t="inlineStr">
         <is>
-          <t>paclock_lf10_ptF</t>
+          <t>paclock_lf05_ptF</t>
         </is>
       </c>
       <c r="C735" t="inlineStr">
@@ -26962,7 +26962,7 @@
       </c>
       <c r="E735" t="inlineStr">
         <is>
-          <t>no row label for 'paclock_lf10_ptF'</t>
+          <t>no row label for 'paclock_lf05_ptF'</t>
         </is>
       </c>
     </row>
@@ -26974,7 +26974,7 @@
       </c>
       <c r="B736" t="inlineStr">
         <is>
-          <t>paclock_lf10_scratch</t>
+          <t>paclock_lf05_scratch</t>
         </is>
       </c>
       <c r="C736" t="inlineStr">
@@ -26989,7 +26989,7 @@
       </c>
       <c r="E736" t="inlineStr">
         <is>
-          <t>no row label for 'paclock_lf10_scratch'</t>
+          <t>no row label for 'paclock_lf05_scratch'</t>
         </is>
       </c>
     </row>
@@ -27001,7 +27001,7 @@
       </c>
       <c r="B737" t="inlineStr">
         <is>
-          <t>paclock_lf25_ptF</t>
+          <t>paclock_lf10_ptF</t>
         </is>
       </c>
       <c r="C737" t="inlineStr">
@@ -27016,7 +27016,7 @@
       </c>
       <c r="E737" t="inlineStr">
         <is>
-          <t>no row label for 'paclock_lf25_ptF'</t>
+          <t>no row label for 'paclock_lf10_ptF'</t>
         </is>
       </c>
     </row>
@@ -27028,7 +27028,7 @@
       </c>
       <c r="B738" t="inlineStr">
         <is>
-          <t>paclock_lf25_scratch</t>
+          <t>paclock_lf10_scratch</t>
         </is>
       </c>
       <c r="C738" t="inlineStr">
@@ -27043,7 +27043,7 @@
       </c>
       <c r="E738" t="inlineStr">
         <is>
-          <t>no row label for 'paclock_lf25_scratch'</t>
+          <t>no row label for 'paclock_lf10_scratch'</t>
         </is>
       </c>
     </row>
@@ -27055,7 +27055,7 @@
       </c>
       <c r="B739" t="inlineStr">
         <is>
-          <t>paclock_p200_pt</t>
+          <t>paclock_lf25_ptF</t>
         </is>
       </c>
       <c r="C739" t="inlineStr">
@@ -27070,7 +27070,7 @@
       </c>
       <c r="E739" t="inlineStr">
         <is>
-          <t>no row label for 'paclock_p200_pt'</t>
+          <t>no row label for 'paclock_lf25_ptF'</t>
         </is>
       </c>
     </row>
@@ -27082,7 +27082,7 @@
       </c>
       <c r="B740" t="inlineStr">
         <is>
-          <t>paclock_p200_pt_notok</t>
+          <t>paclock_lf25_scratch</t>
         </is>
       </c>
       <c r="C740" t="inlineStr">
@@ -27097,7 +27097,7 @@
       </c>
       <c r="E740" t="inlineStr">
         <is>
-          <t>no row label for 'paclock_p200_pt_notok'</t>
+          <t>no row label for 'paclock_lf25_scratch'</t>
         </is>
       </c>
     </row>
@@ -27109,7 +27109,7 @@
       </c>
       <c r="B741" t="inlineStr">
         <is>
-          <t>paclock_p200_scratch</t>
+          <t>paclock_p200_pt</t>
         </is>
       </c>
       <c r="C741" t="inlineStr">
@@ -27124,7 +27124,7 @@
       </c>
       <c r="E741" t="inlineStr">
         <is>
-          <t>no row label for 'paclock_p200_scratch'</t>
+          <t>no row label for 'paclock_p200_pt'</t>
         </is>
       </c>
     </row>
@@ -27136,7 +27136,7 @@
       </c>
       <c r="B742" t="inlineStr">
         <is>
-          <t>paclock_pac</t>
+          <t>paclock_p200_pt_notok</t>
         </is>
       </c>
       <c r="C742" t="inlineStr">
@@ -27151,7 +27151,7 @@
       </c>
       <c r="E742" t="inlineStr">
         <is>
-          <t>the workbook has no row for this variant</t>
+          <t>no row label for 'paclock_p200_pt_notok'</t>
         </is>
       </c>
     </row>
@@ -27163,22 +27163,22 @@
       </c>
       <c r="B743" t="inlineStr">
         <is>
-          <t>paclock_probe_rand</t>
+          <t>paclock_p200_scratch</t>
         </is>
       </c>
       <c r="C743" t="inlineStr">
         <is>
-          <t>[0]</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D743" t="inlineStr">
         <is>
-          <t>filled (single-seed, grey)</t>
+          <t>skipped</t>
         </is>
       </c>
       <c r="E743" t="inlineStr">
         <is>
-          <t>pr_auc 0.4076</t>
+          <t>no row label for 'paclock_p200_scratch'</t>
         </is>
       </c>
     </row>
@@ -27190,7 +27190,7 @@
       </c>
       <c r="B744" t="inlineStr">
         <is>
-          <t>paclock_probe_v1</t>
+          <t>paclock_pac</t>
         </is>
       </c>
       <c r="C744" t="inlineStr">
@@ -27205,7 +27205,7 @@
       </c>
       <c r="E744" t="inlineStr">
         <is>
-          <t>no row label for 'paclock_probe_v1'</t>
+          <t>the workbook has no row for this variant</t>
         </is>
       </c>
     </row>
@@ -27217,7 +27217,7 @@
       </c>
       <c r="B745" t="inlineStr">
         <is>
-          <t>paclock_probe_v2</t>
+          <t>paclock_probe_rand</t>
         </is>
       </c>
       <c r="C745" t="inlineStr">
@@ -27232,7 +27232,7 @@
       </c>
       <c r="E745" t="inlineStr">
         <is>
-          <t>pr_auc 0.5417</t>
+          <t>pr_auc 0.4076</t>
         </is>
       </c>
     </row>
@@ -27244,7 +27244,7 @@
       </c>
       <c r="B746" t="inlineStr">
         <is>
-          <t>paclock_ptF_frozenL3</t>
+          <t>paclock_probe_v1</t>
         </is>
       </c>
       <c r="C746" t="inlineStr">
@@ -27259,7 +27259,7 @@
       </c>
       <c r="E746" t="inlineStr">
         <is>
-          <t>no row label for 'paclock_ptF_frozenL3'</t>
+          <t>no row label for 'paclock_probe_v1'</t>
         </is>
       </c>
     </row>
@@ -27271,22 +27271,22 @@
       </c>
       <c r="B747" t="inlineStr">
         <is>
-          <t>paclock_pt_base</t>
+          <t>paclock_probe_v2</t>
         </is>
       </c>
       <c r="C747" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>[0]</t>
         </is>
       </c>
       <c r="D747" t="inlineStr">
         <is>
-          <t>skipped</t>
+          <t>filled (single-seed, grey)</t>
         </is>
       </c>
       <c r="E747" t="inlineStr">
         <is>
-          <t>row 'PACLock (pretrained, base)' not found</t>
+          <t>pr_auc 0.5417</t>
         </is>
       </c>
     </row>
@@ -27298,7 +27298,7 @@
       </c>
       <c r="B748" t="inlineStr">
         <is>
-          <t>paclock_pt_excl</t>
+          <t>paclock_ptF_frozenL3</t>
         </is>
       </c>
       <c r="C748" t="inlineStr">
@@ -27313,7 +27313,7 @@
       </c>
       <c r="E748" t="inlineStr">
         <is>
-          <t>no row label for 'paclock_pt_excl'</t>
+          <t>no row label for 'paclock_ptF_frozenL3'</t>
         </is>
       </c>
     </row>
@@ -27325,7 +27325,7 @@
       </c>
       <c r="B749" t="inlineStr">
         <is>
-          <t>paclock_pt_large</t>
+          <t>paclock_pt_base</t>
         </is>
       </c>
       <c r="C749" t="inlineStr">
@@ -27340,7 +27340,7 @@
       </c>
       <c r="E749" t="inlineStr">
         <is>
-          <t>row 'PACLock (pretrained, large)' not found</t>
+          <t>row 'PACLock (pretrained, base)' not found</t>
         </is>
       </c>
     </row>
@@ -27352,7 +27352,7 @@
       </c>
       <c r="B750" t="inlineStr">
         <is>
-          <t>paclock_rawpt_large</t>
+          <t>paclock_pt_excl</t>
         </is>
       </c>
       <c r="C750" t="inlineStr">
@@ -27367,7 +27367,7 @@
       </c>
       <c r="E750" t="inlineStr">
         <is>
-          <t>no row label for 'paclock_rawpt_large'</t>
+          <t>no row label for 'paclock_pt_excl'</t>
         </is>
       </c>
     </row>
@@ -27379,7 +27379,7 @@
       </c>
       <c r="B751" t="inlineStr">
         <is>
-          <t>paclock_rawtok</t>
+          <t>paclock_pt_large</t>
         </is>
       </c>
       <c r="C751" t="inlineStr">
@@ -27394,7 +27394,7 @@
       </c>
       <c r="E751" t="inlineStr">
         <is>
-          <t>no row label for 'paclock_rawtok'</t>
+          <t>row 'PACLock (pretrained, large)' not found</t>
         </is>
       </c>
     </row>
@@ -27406,7 +27406,7 @@
       </c>
       <c r="B752" t="inlineStr">
         <is>
-          <t>paclock_rot2</t>
+          <t>paclock_rawpt_large</t>
         </is>
       </c>
       <c r="C752" t="inlineStr">
@@ -27421,7 +27421,7 @@
       </c>
       <c r="E752" t="inlineStr">
         <is>
-          <t>no row label for 'paclock_rot2'</t>
+          <t>no row label for 'paclock_rawpt_large'</t>
         </is>
       </c>
     </row>
@@ -27433,7 +27433,7 @@
       </c>
       <c r="B753" t="inlineStr">
         <is>
-          <t>paclock_v2</t>
+          <t>paclock_rawtok</t>
         </is>
       </c>
       <c r="C753" t="inlineStr">
@@ -27448,7 +27448,7 @@
       </c>
       <c r="E753" t="inlineStr">
         <is>
-          <t>row 'PACLock (from scratch, full)' not found</t>
+          <t>no row label for 'paclock_rawtok'</t>
         </is>
       </c>
     </row>
@@ -27460,7 +27460,7 @@
       </c>
       <c r="B754" t="inlineStr">
         <is>
-          <t>paclock_v3traj_100000frozen</t>
+          <t>paclock_rot2</t>
         </is>
       </c>
       <c r="C754" t="inlineStr">
@@ -27475,7 +27475,7 @@
       </c>
       <c r="E754" t="inlineStr">
         <is>
-          <t>no row label for 'paclock_v3traj_100000frozen'</t>
+          <t>no row label for 'paclock_rot2'</t>
         </is>
       </c>
     </row>
@@ -27487,7 +27487,7 @@
       </c>
       <c r="B755" t="inlineStr">
         <is>
-          <t>paclock_v3traj_100000frozenL3</t>
+          <t>paclock_v2</t>
         </is>
       </c>
       <c r="C755" t="inlineStr">
@@ -27502,7 +27502,7 @@
       </c>
       <c r="E755" t="inlineStr">
         <is>
-          <t>no row label for 'paclock_v3traj_100000frozenL3'</t>
+          <t>row 'PACLock (from scratch, full)' not found</t>
         </is>
       </c>
     </row>
@@ -27514,7 +27514,7 @@
       </c>
       <c r="B756" t="inlineStr">
         <is>
-          <t>paclock_v3traj_20000frozen</t>
+          <t>paclock_v3traj_100000frozen</t>
         </is>
       </c>
       <c r="C756" t="inlineStr">
@@ -27529,7 +27529,7 @@
       </c>
       <c r="E756" t="inlineStr">
         <is>
-          <t>no row label for 'paclock_v3traj_20000frozen'</t>
+          <t>no row label for 'paclock_v3traj_100000frozen'</t>
         </is>
       </c>
     </row>
@@ -27541,7 +27541,7 @@
       </c>
       <c r="B757" t="inlineStr">
         <is>
-          <t>paclock_v3traj_20000frozenL3</t>
+          <t>paclock_v3traj_100000frozenL3</t>
         </is>
       </c>
       <c r="C757" t="inlineStr">
@@ -27556,7 +27556,7 @@
       </c>
       <c r="E757" t="inlineStr">
         <is>
-          <t>no row label for 'paclock_v3traj_20000frozenL3'</t>
+          <t>no row label for 'paclock_v3traj_100000frozenL3'</t>
         </is>
       </c>
     </row>
@@ -27568,7 +27568,7 @@
       </c>
       <c r="B758" t="inlineStr">
         <is>
-          <t>paclock_v3traj_40000frozen</t>
+          <t>paclock_v3traj_20000frozen</t>
         </is>
       </c>
       <c r="C758" t="inlineStr">
@@ -27583,7 +27583,7 @@
       </c>
       <c r="E758" t="inlineStr">
         <is>
-          <t>no row label for 'paclock_v3traj_40000frozen'</t>
+          <t>no row label for 'paclock_v3traj_20000frozen'</t>
         </is>
       </c>
     </row>
@@ -27595,7 +27595,7 @@
       </c>
       <c r="B759" t="inlineStr">
         <is>
-          <t>paclock_v3traj_40000frozenL3</t>
+          <t>paclock_v3traj_20000frozenL3</t>
         </is>
       </c>
       <c r="C759" t="inlineStr">
@@ -27610,7 +27610,7 @@
       </c>
       <c r="E759" t="inlineStr">
         <is>
-          <t>no row label for 'paclock_v3traj_40000frozenL3'</t>
+          <t>no row label for 'paclock_v3traj_20000frozenL3'</t>
         </is>
       </c>
     </row>
@@ -27622,7 +27622,7 @@
       </c>
       <c r="B760" t="inlineStr">
         <is>
-          <t>paclock_v3traj_60000frozen</t>
+          <t>paclock_v3traj_40000frozen</t>
         </is>
       </c>
       <c r="C760" t="inlineStr">
@@ -27637,7 +27637,7 @@
       </c>
       <c r="E760" t="inlineStr">
         <is>
-          <t>no row label for 'paclock_v3traj_60000frozen'</t>
+          <t>no row label for 'paclock_v3traj_40000frozen'</t>
         </is>
       </c>
     </row>
@@ -27649,7 +27649,7 @@
       </c>
       <c r="B761" t="inlineStr">
         <is>
-          <t>paclock_v3traj_60000frozenL3</t>
+          <t>paclock_v3traj_40000frozenL3</t>
         </is>
       </c>
       <c r="C761" t="inlineStr">
@@ -27664,7 +27664,7 @@
       </c>
       <c r="E761" t="inlineStr">
         <is>
-          <t>no row label for 'paclock_v3traj_60000frozenL3'</t>
+          <t>no row label for 'paclock_v3traj_40000frozenL3'</t>
         </is>
       </c>
     </row>
@@ -27676,7 +27676,7 @@
       </c>
       <c r="B762" t="inlineStr">
         <is>
-          <t>paclock_v3traj_80000frozen</t>
+          <t>paclock_v3traj_60000frozen</t>
         </is>
       </c>
       <c r="C762" t="inlineStr">
@@ -27691,7 +27691,7 @@
       </c>
       <c r="E762" t="inlineStr">
         <is>
-          <t>no row label for 'paclock_v3traj_80000frozen'</t>
+          <t>no row label for 'paclock_v3traj_60000frozen'</t>
         </is>
       </c>
     </row>
@@ -27703,7 +27703,7 @@
       </c>
       <c r="B763" t="inlineStr">
         <is>
-          <t>paclock_v3traj_80000frozenL3</t>
+          <t>paclock_v3traj_60000frozenL3</t>
         </is>
       </c>
       <c r="C763" t="inlineStr">
@@ -27718,7 +27718,7 @@
       </c>
       <c r="E763" t="inlineStr">
         <is>
-          <t>no row label for 'paclock_v3traj_80000frozenL3'</t>
+          <t>no row label for 'paclock_v3traj_60000frozenL3'</t>
         </is>
       </c>
     </row>
@@ -27730,27 +27730,22 @@
       </c>
       <c r="B764" t="inlineStr">
         <is>
-          <t>reve_pretrained</t>
+          <t>paclock_v3traj_80000frozen</t>
         </is>
       </c>
       <c r="C764" t="inlineStr">
         <is>
-          <t>[0, 1, 2]</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D764" t="inlineStr">
         <is>
-          <t>filled</t>
+          <t>skipped</t>
         </is>
       </c>
       <c r="E764" t="inlineStr">
         <is>
-          <t>[实测 69.46M] pr_auc per-seed 0:0.4370, 1:0.5838, 2:0.4869</t>
-        </is>
-      </c>
-      <c r="F764" t="inlineStr">
-        <is>
-          <t>stopped_by=patience lr=0.0001 batch_size=128 epochs=15 patience=10 eval_every_steps=500 loss=bce_with_logits grad_clip=1.0</t>
+          <t>no row label for 'paclock_v3traj_80000frozen'</t>
         </is>
       </c>
     </row>
@@ -27762,27 +27757,22 @@
       </c>
       <c r="B765" t="inlineStr">
         <is>
-          <t>sparcnet</t>
+          <t>paclock_v3traj_80000frozenL3</t>
         </is>
       </c>
       <c r="C765" t="inlineStr">
         <is>
-          <t>[0, 1, 2]</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D765" t="inlineStr">
         <is>
-          <t>filled</t>
+          <t>skipped</t>
         </is>
       </c>
       <c r="E765" t="inlineStr">
         <is>
-          <t>[实测 1.14M] pr_auc per-seed 0:0.4795, 1:0.5046, 2:0.5218</t>
-        </is>
-      </c>
-      <c r="F765" t="inlineStr">
-        <is>
-          <t>lr=0.001 batch_size=512 epochs=20 patience=8 eval_every_steps=200 loss=bce_with_logits</t>
+          <t>no row label for 'paclock_v3traj_80000frozenL3'</t>
         </is>
       </c>
     </row>
@@ -27794,7 +27784,7 @@
       </c>
       <c r="B766" t="inlineStr">
         <is>
-          <t>st_transformer</t>
+          <t>reve_pretrained</t>
         </is>
       </c>
       <c r="C766" t="inlineStr">
@@ -27809,12 +27799,12 @@
       </c>
       <c r="E766" t="inlineStr">
         <is>
-          <t>[实测 3.43M] pr_auc per-seed 0:0.3318, 1:0.3515, 2:0.3933</t>
+          <t>[实测 69.46M] pr_auc per-seed 0:0.4370, 1:0.5838, 2:0.4869</t>
         </is>
       </c>
       <c r="F766" t="inlineStr">
         <is>
-          <t>lr=0.001 batch_size=512 epochs=20 patience=8 eval_every_steps=200 loss=bce_with_logits</t>
+          <t>stopped_by=patience lr=0.0001 batch_size=128 epochs=15 patience=10 eval_every_steps=500 loss=bce_with_logits grad_clip=1.0</t>
         </is>
       </c>
     </row>
@@ -27826,25 +27816,89 @@
       </c>
       <c r="B767" t="inlineStr">
         <is>
+          <t>sparcnet</t>
+        </is>
+      </c>
+      <c r="C767" t="inlineStr">
+        <is>
+          <t>[0, 1, 2]</t>
+        </is>
+      </c>
+      <c r="D767" t="inlineStr">
+        <is>
+          <t>filled</t>
+        </is>
+      </c>
+      <c r="E767" t="inlineStr">
+        <is>
+          <t>[实测 1.14M] pr_auc per-seed 0:0.4795, 1:0.5046, 2:0.5218</t>
+        </is>
+      </c>
+      <c r="F767" t="inlineStr">
+        <is>
+          <t>lr=0.001 batch_size=512 epochs=20 patience=8 eval_every_steps=200 loss=bce_with_logits</t>
+        </is>
+      </c>
+    </row>
+    <row r="768">
+      <c r="A768" t="inlineStr">
+        <is>
+          <t>tusz</t>
+        </is>
+      </c>
+      <c r="B768" t="inlineStr">
+        <is>
+          <t>st_transformer</t>
+        </is>
+      </c>
+      <c r="C768" t="inlineStr">
+        <is>
+          <t>[0, 1, 2]</t>
+        </is>
+      </c>
+      <c r="D768" t="inlineStr">
+        <is>
+          <t>filled</t>
+        </is>
+      </c>
+      <c r="E768" t="inlineStr">
+        <is>
+          <t>[实测 3.43M] pr_auc per-seed 0:0.3318, 1:0.3515, 2:0.3933</t>
+        </is>
+      </c>
+      <c r="F768" t="inlineStr">
+        <is>
+          <t>lr=0.001 batch_size=512 epochs=20 patience=8 eval_every_steps=200 loss=bce_with_logits</t>
+        </is>
+      </c>
+    </row>
+    <row r="769">
+      <c r="A769" t="inlineStr">
+        <is>
+          <t>tusz</t>
+        </is>
+      </c>
+      <c r="B769" t="inlineStr">
+        <is>
           <t>tfm_pretrained</t>
         </is>
       </c>
-      <c r="C767" t="inlineStr">
+      <c r="C769" t="inlineStr">
         <is>
           <t>[0, 1, 2]</t>
         </is>
       </c>
-      <c r="D767" t="inlineStr">
+      <c r="D769" t="inlineStr">
         <is>
           <t>filled</t>
         </is>
       </c>
-      <c r="E767" t="inlineStr">
+      <c r="E769" t="inlineStr">
         <is>
           <t>[实测 1.89M] pr_auc per-seed 0:0.3348, 1:0.3686, 2:0.3389</t>
         </is>
       </c>
-      <c r="F767" t="inlineStr">
+      <c r="F769" t="inlineStr">
         <is>
           <t>lr=0.001 batch_size=512 epochs=5 patience=10 eval_every_steps=100 loss=bce_with_logits label_smoothing=0.1</t>
         </is>
@@ -34127,9 +34181,24 @@
           <t>CroFreMo (预训练 ptS)</t>
         </is>
       </c>
-      <c r="D28" s="20" t="n"/>
-      <c r="E28" s="20" t="n"/>
-      <c r="F28" s="20" t="n"/>
+      <c r="C28" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="D28" s="24" t="inlineStr">
+        <is>
+          <t>0.8054 (1 seed)</t>
+        </is>
+      </c>
+      <c r="E28" s="24" t="inlineStr">
+        <is>
+          <t>0.8938 (1 seed)</t>
+        </is>
+      </c>
+      <c r="F28" s="24" t="inlineStr">
+        <is>
+          <t>0.8892 (1 seed)</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="B29" t="inlineStr">

--- a/results/PACLock_baseline_matrix_filled.xlsx
+++ b/results/PACLock_baseline_matrix_filled.xlsx
@@ -1934,9 +1934,24 @@
           <t>CroFreMo (预训练 ptS)</t>
         </is>
       </c>
-      <c r="D28" s="20" t="n"/>
-      <c r="E28" s="20" t="n"/>
-      <c r="F28" s="20" t="n"/>
+      <c r="C28" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="D28" s="24" t="inlineStr">
+        <is>
+          <t>0.6721 (1 seed)</t>
+        </is>
+      </c>
+      <c r="E28" s="24" t="inlineStr">
+        <is>
+          <t>0.7463 (1 seed)</t>
+        </is>
+      </c>
+      <c r="F28" s="24" t="inlineStr">
+        <is>
+          <t>0.7375 (1 seed)</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="B29" t="inlineStr">
@@ -5923,7 +5938,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F769"/>
+  <dimension ref="A1:F770"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15374,22 +15389,22 @@
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>paclock_pac</t>
+          <t>paclock_duplex_ptS</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>[0]</t>
         </is>
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>skipped</t>
+          <t>filled (single-seed, grey)</t>
         </is>
       </c>
       <c r="E331" t="inlineStr">
         <is>
-          <t>the workbook has no row for this variant</t>
+          <t>cohen_kappa 0.6721</t>
         </is>
       </c>
     </row>
@@ -15401,7 +15416,7 @@
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>paclock_pt_base</t>
+          <t>paclock_pac</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
@@ -15416,7 +15431,7 @@
       </c>
       <c r="E332" t="inlineStr">
         <is>
-          <t>row 'PACLock (pretrained, base)' not found</t>
+          <t>the workbook has no row for this variant</t>
         </is>
       </c>
     </row>
@@ -15428,7 +15443,7 @@
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>paclock_pt_large</t>
+          <t>paclock_pt_base</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
@@ -15443,7 +15458,7 @@
       </c>
       <c r="E333" t="inlineStr">
         <is>
-          <t>row 'PACLock (pretrained, large)' not found</t>
+          <t>row 'PACLock (pretrained, base)' not found</t>
         </is>
       </c>
     </row>
@@ -15455,7 +15470,7 @@
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>paclock_rawtok</t>
+          <t>paclock_pt_large</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
@@ -15470,7 +15485,7 @@
       </c>
       <c r="E334" t="inlineStr">
         <is>
-          <t>no row label for 'paclock_rawtok'</t>
+          <t>row 'PACLock (pretrained, large)' not found</t>
         </is>
       </c>
     </row>
@@ -15482,7 +15497,7 @@
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>paclock_rot2</t>
+          <t>paclock_rawtok</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
@@ -15497,7 +15512,7 @@
       </c>
       <c r="E335" t="inlineStr">
         <is>
-          <t>no row label for 'paclock_rot2'</t>
+          <t>no row label for 'paclock_rawtok'</t>
         </is>
       </c>
     </row>
@@ -15509,7 +15524,7 @@
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>paclock_tune_t2</t>
+          <t>paclock_rot2</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
@@ -15524,7 +15539,7 @@
       </c>
       <c r="E336" t="inlineStr">
         <is>
-          <t>no row label for 'paclock_tune_t2'</t>
+          <t>no row label for 'paclock_rot2'</t>
         </is>
       </c>
     </row>
@@ -15536,7 +15551,7 @@
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>paclock_v2</t>
+          <t>paclock_tune_t2</t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
@@ -15551,7 +15566,7 @@
       </c>
       <c r="E337" t="inlineStr">
         <is>
-          <t>row 'PACLock (from scratch, full)' not found</t>
+          <t>no row label for 'paclock_tune_t2'</t>
         </is>
       </c>
     </row>
@@ -15563,7 +15578,7 @@
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>paclock_xyz</t>
+          <t>paclock_v2</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
@@ -15578,7 +15593,7 @@
       </c>
       <c r="E338" t="inlineStr">
         <is>
-          <t>no row label for 'paclock_xyz'</t>
+          <t>row 'PACLock (from scratch, full)' not found</t>
         </is>
       </c>
     </row>
@@ -15590,27 +15605,22 @@
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>sparcnet</t>
+          <t>paclock_xyz</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>[0, 1, 2]</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D339" t="inlineStr">
         <is>
-          <t>filled</t>
+          <t>skipped</t>
         </is>
       </c>
       <c r="E339" t="inlineStr">
         <is>
-          <t>[实测 1.38M] cohen_kappa per-seed 0:0.7286, 1:0.7185, 2:0.7565</t>
-        </is>
-      </c>
-      <c r="F339" t="inlineStr">
-        <is>
-          <t>lr=0.001 batch_size=512 epochs=60 patience=15 eval_every_steps=0 loss=cross_entropy label_smoothing=0.1</t>
+          <t>no row label for 'paclock_xyz'</t>
         </is>
       </c>
     </row>
@@ -15622,7 +15632,7 @@
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>st_transformer</t>
+          <t>sparcnet</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
@@ -15637,7 +15647,7 @@
       </c>
       <c r="E340" t="inlineStr">
         <is>
-          <t>[实测 3.42M] cohen_kappa per-seed 0:0.5488, 1:0.3217, 2:0.3076  [seed spread 28% -- mean is a weak summary]</t>
+          <t>[实测 1.38M] cohen_kappa per-seed 0:0.7286, 1:0.7185, 2:0.7565</t>
         </is>
       </c>
       <c r="F340" t="inlineStr">
@@ -15654,7 +15664,7 @@
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>tfm_pretrained</t>
+          <t>st_transformer</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
@@ -15669,24 +15679,24 @@
       </c>
       <c r="E341" t="inlineStr">
         <is>
-          <t>[实测 1.89M] cohen_kappa per-seed 0:0.7144, 1:0.7084, 2:0.7077</t>
+          <t>[实测 3.42M] cohen_kappa per-seed 0:0.5488, 1:0.3217, 2:0.3076  [seed spread 28% -- mean is a weak summary]</t>
         </is>
       </c>
       <c r="F341" t="inlineStr">
         <is>
-          <t>lr=0.001 batch_size=512 epochs=50 patience=10 eval_every_steps=0 loss=cross_entropy label_smoothing=0.1</t>
+          <t>lr=0.001 batch_size=512 epochs=60 patience=15 eval_every_steps=0 loss=cross_entropy label_smoothing=0.1</t>
         </is>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>mumtaz</t>
+          <t>isruc</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>biot_prest16</t>
+          <t>tfm_pretrained</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
@@ -15701,12 +15711,12 @@
       </c>
       <c r="E342" t="inlineStr">
         <is>
-          <t>[实测 3.19M] auroc per-seed 0:0.9999, 1:0.9864, 2:0.9823</t>
+          <t>[实测 1.89M] cohen_kappa per-seed 0:0.7144, 1:0.7084, 2:0.7077</t>
         </is>
       </c>
       <c r="F342" t="inlineStr">
         <is>
-          <t>stopped_by=patience lr=0.001 batch_size=512 epochs=100 patience=5 eval_every_steps=0 loss=bce_with_logits</t>
+          <t>lr=0.001 batch_size=512 epochs=50 patience=10 eval_every_steps=0 loss=cross_entropy label_smoothing=0.1</t>
         </is>
       </c>
     </row>
@@ -15718,7 +15728,7 @@
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>biot_scratch</t>
+          <t>biot_prest16</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
@@ -15733,7 +15743,7 @@
       </c>
       <c r="E343" t="inlineStr">
         <is>
-          <t>[实测 3.19M] auroc per-seed 0:0.9422, 1:0.9643, 2:0.9296</t>
+          <t>[实测 3.19M] auroc per-seed 0:0.9999, 1:0.9864, 2:0.9823</t>
         </is>
       </c>
       <c r="F343" t="inlineStr">
@@ -15750,7 +15760,7 @@
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>cbramod_pretrained</t>
+          <t>biot_scratch</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
@@ -15765,12 +15775,12 @@
       </c>
       <c r="E344" t="inlineStr">
         <is>
-          <t>[实测 20.25M] auroc per-seed 0:0.9690, 1:0.9804, 2:0.9335</t>
+          <t>[实测 3.19M] auroc per-seed 0:0.9422, 1:0.9643, 2:0.9296</t>
         </is>
       </c>
       <c r="F344" t="inlineStr">
         <is>
-          <t>lr=0.0001 batch_size=64 epochs=50 patience=0 eval_every_steps=0 loss=bce_with_logits grad_clip=1.0 select_metric=auroc multi_lr=True</t>
+          <t>stopped_by=patience lr=0.001 batch_size=512 epochs=100 patience=5 eval_every_steps=0 loss=bce_with_logits</t>
         </is>
       </c>
     </row>
@@ -15782,7 +15792,7 @@
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>cbramod_scratch</t>
+          <t>cbramod_pretrained</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
@@ -15797,7 +15807,7 @@
       </c>
       <c r="E345" t="inlineStr">
         <is>
-          <t>[实测 20.25M] auroc per-seed 0:0.9240, 1:0.8733, 2:0.9645</t>
+          <t>[实测 20.25M] auroc per-seed 0:0.9690, 1:0.9804, 2:0.9335</t>
         </is>
       </c>
       <c r="F345" t="inlineStr">
@@ -15814,7 +15824,7 @@
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>cnn_transformer</t>
+          <t>cbramod_scratch</t>
         </is>
       </c>
       <c r="C346" t="inlineStr">
@@ -15829,12 +15839,12 @@
       </c>
       <c r="E346" t="inlineStr">
         <is>
-          <t>[实测 3.16M] auroc per-seed 0:0.8850, 1:0.8056, 2:0.9175</t>
+          <t>[实测 20.25M] auroc per-seed 0:0.9240, 1:0.8733, 2:0.9645</t>
         </is>
       </c>
       <c r="F346" t="inlineStr">
         <is>
-          <t>stopped_by=patience lr=0.001 batch_size=512 epochs=20 patience=8 eval_every_steps=200 loss=bce_with_logits</t>
+          <t>lr=0.0001 batch_size=64 epochs=50 patience=0 eval_every_steps=0 loss=bce_with_logits grad_clip=1.0 select_metric=auroc multi_lr=True</t>
         </is>
       </c>
     </row>
@@ -15846,7 +15856,7 @@
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>contrawr</t>
+          <t>cnn_transformer</t>
         </is>
       </c>
       <c r="C347" t="inlineStr">
@@ -15861,7 +15871,7 @@
       </c>
       <c r="E347" t="inlineStr">
         <is>
-          <t>[实测 1.57M] auroc per-seed 0:0.9659, 1:0.9206, 2:0.9639</t>
+          <t>[实测 3.16M] auroc per-seed 0:0.8850, 1:0.8056, 2:0.9175</t>
         </is>
       </c>
       <c r="F347" t="inlineStr">
@@ -15878,7 +15888,7 @@
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>eegpt_pretrained</t>
+          <t>contrawr</t>
         </is>
       </c>
       <c r="C348" t="inlineStr">
@@ -15893,12 +15903,12 @@
       </c>
       <c r="E348" t="inlineStr">
         <is>
-          <t>[实测 25.69M] auroc per-seed 0:0.9379, 1:0.9889, 2:0.9548</t>
+          <t>[实测 1.57M] auroc per-seed 0:0.9659, 1:0.9206, 2:0.9639</t>
         </is>
       </c>
       <c r="F348" t="inlineStr">
         <is>
-          <t>stopped_by=patience lr=0.0004 batch_size=32 epochs=40 patience=10 eval_every_steps=500 loss=bce_with_logits</t>
+          <t>stopped_by=patience lr=0.001 batch_size=512 epochs=20 patience=8 eval_every_steps=200 loss=bce_with_logits</t>
         </is>
       </c>
     </row>
@@ -15910,7 +15920,7 @@
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>eegpt_scratch</t>
+          <t>eegpt_pretrained</t>
         </is>
       </c>
       <c r="C349" t="inlineStr">
@@ -15925,12 +15935,12 @@
       </c>
       <c r="E349" t="inlineStr">
         <is>
-          <t>[实测 25.69M] auroc per-seed 0:0.8932, 1:0.6772, 2:0.8513</t>
+          <t>[实测 25.69M] auroc per-seed 0:0.9379, 1:0.9889, 2:0.9548</t>
         </is>
       </c>
       <c r="F349" t="inlineStr">
         <is>
-          <t>lr=0.0004 batch_size=32 epochs=40 patience=10 eval_every_steps=500 loss=bce_with_logits</t>
+          <t>stopped_by=patience lr=0.0004 batch_size=32 epochs=40 patience=10 eval_every_steps=500 loss=bce_with_logits</t>
         </is>
       </c>
     </row>
@@ -15942,7 +15952,7 @@
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>feat_best</t>
+          <t>eegpt_scratch</t>
         </is>
       </c>
       <c r="C350" t="inlineStr">
@@ -15957,12 +15967,12 @@
       </c>
       <c r="E350" t="inlineStr">
         <is>
-          <t>[实测 0.00M] auroc per-seed 0:0.9163, 1:0.9163, 2:0.9163</t>
+          <t>[实测 25.69M] auroc per-seed 0:0.8932, 1:0.6772, 2:0.8513</t>
         </is>
       </c>
       <c r="F350" t="inlineStr">
         <is>
-          <t>stopped_by=closed-form epochs=1 loss=closed-form</t>
+          <t>lr=0.0004 batch_size=32 epochs=40 patience=10 eval_every_steps=500 loss=bce_with_logits</t>
         </is>
       </c>
     </row>
@@ -15974,7 +15984,7 @@
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>ffcl</t>
+          <t>feat_best</t>
         </is>
       </c>
       <c r="C351" t="inlineStr">
@@ -15989,12 +15999,12 @@
       </c>
       <c r="E351" t="inlineStr">
         <is>
-          <t>[实测 2.42M] auroc per-seed 0:0.9581, 1:0.9589, 2:0.9689</t>
+          <t>[实测 0.00M] auroc per-seed 0:0.9163, 1:0.9163, 2:0.9163</t>
         </is>
       </c>
       <c r="F351" t="inlineStr">
         <is>
-          <t>lr=0.001 batch_size=512 epochs=20 patience=8 eval_every_steps=200 loss=bce_with_logits</t>
+          <t>stopped_by=closed-form epochs=1 loss=closed-form</t>
         </is>
       </c>
     </row>
@@ -16006,7 +16016,7 @@
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>labram_pretrained</t>
+          <t>ffcl</t>
         </is>
       </c>
       <c r="C352" t="inlineStr">
@@ -16021,12 +16031,12 @@
       </c>
       <c r="E352" t="inlineStr">
         <is>
-          <t>[实测 5.82M] auroc per-seed 0:0.9858, 1:0.9394, 2:0.9654</t>
+          <t>[实测 2.42M] auroc per-seed 0:0.9581, 1:0.9589, 2:0.9689</t>
         </is>
       </c>
       <c r="F352" t="inlineStr">
         <is>
-          <t>stopped_by=patience lr=0.0005 batch_size=64 epochs=50 patience=10 eval_every_steps=0 loss=bce_with_logits loader_divisor=1.0</t>
+          <t>lr=0.001 batch_size=512 epochs=20 patience=8 eval_every_steps=200 loss=bce_with_logits</t>
         </is>
       </c>
     </row>
@@ -16038,7 +16048,7 @@
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>labram_scratch</t>
+          <t>labram_pretrained</t>
         </is>
       </c>
       <c r="C353" t="inlineStr">
@@ -16053,7 +16063,7 @@
       </c>
       <c r="E353" t="inlineStr">
         <is>
-          <t>[实测 5.82M] auroc per-seed 0:0.9848, 1:0.8806, 2:0.8255</t>
+          <t>[实测 5.82M] auroc per-seed 0:0.9858, 1:0.9394, 2:0.9654</t>
         </is>
       </c>
       <c r="F353" t="inlineStr">
@@ -16070,22 +16080,27 @@
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>paclock_duplex</t>
+          <t>labram_scratch</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>[0]</t>
+          <t>[0, 1, 2]</t>
         </is>
       </c>
       <c r="D354" t="inlineStr">
         <is>
-          <t>filled (single-seed, grey)</t>
+          <t>filled</t>
         </is>
       </c>
       <c r="E354" t="inlineStr">
         <is>
-          <t>auroc 0.9775</t>
+          <t>[实测 5.82M] auroc per-seed 0:0.9848, 1:0.8806, 2:0.8255</t>
+        </is>
+      </c>
+      <c r="F354" t="inlineStr">
+        <is>
+          <t>stopped_by=patience lr=0.0005 batch_size=64 epochs=50 patience=10 eval_every_steps=0 loss=bce_with_logits loader_divisor=1.0</t>
         </is>
       </c>
     </row>
@@ -16097,22 +16112,22 @@
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>paclock_duplex_ptF</t>
+          <t>paclock_duplex</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>[0]</t>
         </is>
       </c>
       <c r="D355" t="inlineStr">
         <is>
-          <t>skipped</t>
+          <t>filled (single-seed, grey)</t>
         </is>
       </c>
       <c r="E355" t="inlineStr">
         <is>
-          <t>row 'CroFreMo (预训练 v2-full)' not found</t>
+          <t>auroc 0.9775</t>
         </is>
       </c>
     </row>
@@ -16124,7 +16139,7 @@
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>paclock_tune_t1</t>
+          <t>paclock_duplex_ptF</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
@@ -16139,7 +16154,7 @@
       </c>
       <c r="E356" t="inlineStr">
         <is>
-          <t>no row label for 'paclock_tune_t1'</t>
+          <t>row 'CroFreMo (预训练 v2-full)' not found</t>
         </is>
       </c>
     </row>
@@ -16151,7 +16166,7 @@
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>paclock_tune_t2</t>
+          <t>paclock_tune_t1</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
@@ -16166,7 +16181,7 @@
       </c>
       <c r="E357" t="inlineStr">
         <is>
-          <t>no row label for 'paclock_tune_t2'</t>
+          <t>no row label for 'paclock_tune_t1'</t>
         </is>
       </c>
     </row>
@@ -16178,27 +16193,22 @@
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>sparcnet</t>
+          <t>paclock_tune_t2</t>
         </is>
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>[0, 1, 2]</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D358" t="inlineStr">
         <is>
-          <t>filled</t>
+          <t>skipped</t>
         </is>
       </c>
       <c r="E358" t="inlineStr">
         <is>
-          <t>[实测 0.99M] auroc per-seed 0:0.9757, 1:0.9948, 2:0.9994</t>
-        </is>
-      </c>
-      <c r="F358" t="inlineStr">
-        <is>
-          <t>stopped_by=patience lr=0.001 batch_size=512 epochs=20 patience=8 eval_every_steps=200 loss=bce_with_logits</t>
+          <t>no row label for 'paclock_tune_t2'</t>
         </is>
       </c>
     </row>
@@ -16210,7 +16220,7 @@
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>st_transformer</t>
+          <t>sparcnet</t>
         </is>
       </c>
       <c r="C359" t="inlineStr">
@@ -16225,12 +16235,12 @@
       </c>
       <c r="E359" t="inlineStr">
         <is>
-          <t>[实测 3.43M] auroc per-seed 0:0.9933, 1:0.9977, 2:0.9821</t>
+          <t>[实测 0.99M] auroc per-seed 0:0.9757, 1:0.9948, 2:0.9994</t>
         </is>
       </c>
       <c r="F359" t="inlineStr">
         <is>
-          <t>lr=0.001 batch_size=512 epochs=20 patience=8 eval_every_steps=200 loss=bce_with_logits</t>
+          <t>stopped_by=patience lr=0.001 batch_size=512 epochs=20 patience=8 eval_every_steps=200 loss=bce_with_logits</t>
         </is>
       </c>
     </row>
@@ -16242,7 +16252,7 @@
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>tfm_pretrained</t>
+          <t>st_transformer</t>
         </is>
       </c>
       <c r="C360" t="inlineStr">
@@ -16257,12 +16267,12 @@
       </c>
       <c r="E360" t="inlineStr">
         <is>
-          <t>[实测 1.89M] auroc per-seed 0:0.9491, 1:0.8701, 2:0.8803</t>
+          <t>[实测 3.43M] auroc per-seed 0:0.9933, 1:0.9977, 2:0.9821</t>
         </is>
       </c>
       <c r="F360" t="inlineStr">
         <is>
-          <t>lr=0.001 batch_size=512 epochs=7 patience=10 eval_every_steps=100 loss=bce_with_logits</t>
+          <t>lr=0.001 batch_size=512 epochs=20 patience=8 eval_every_steps=200 loss=bce_with_logits</t>
         </is>
       </c>
     </row>
@@ -16274,7 +16284,7 @@
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>tfm_scratch</t>
+          <t>tfm_pretrained</t>
         </is>
       </c>
       <c r="C361" t="inlineStr">
@@ -16289,7 +16299,7 @@
       </c>
       <c r="E361" t="inlineStr">
         <is>
-          <t>[实测 1.89M] auroc per-seed 0:0.8317, 1:0.6641, 2:0.7362</t>
+          <t>[实测 1.89M] auroc per-seed 0:0.9491, 1:0.8701, 2:0.8803</t>
         </is>
       </c>
       <c r="F361" t="inlineStr">
@@ -16301,12 +16311,12 @@
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>physionet_mi</t>
+          <t>mumtaz</t>
         </is>
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>biot_prest16</t>
+          <t>tfm_scratch</t>
         </is>
       </c>
       <c r="C362" t="inlineStr">
@@ -16321,12 +16331,12 @@
       </c>
       <c r="E362" t="inlineStr">
         <is>
-          <t>[实测 3.19M] balanced_acc per-seed 0:0.4950, 1:0.5034, 2:0.5126</t>
+          <t>[实测 1.89M] auroc per-seed 0:0.8317, 1:0.6641, 2:0.7362</t>
         </is>
       </c>
       <c r="F362" t="inlineStr">
         <is>
-          <t>lr=0.0004 batch_size=64 epochs=100 patience=10 eval_every_steps=0 loss=cross_entropy</t>
+          <t>lr=0.001 batch_size=512 epochs=7 patience=10 eval_every_steps=100 loss=bce_with_logits</t>
         </is>
       </c>
     </row>
@@ -16338,7 +16348,7 @@
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>biot_scratch</t>
+          <t>biot_prest16</t>
         </is>
       </c>
       <c r="C363" t="inlineStr">
@@ -16353,7 +16363,7 @@
       </c>
       <c r="E363" t="inlineStr">
         <is>
-          <t>[实测 3.20M] balanced_acc per-seed 0:0.3337, 1:0.3273, 2:0.2687</t>
+          <t>[实测 3.19M] balanced_acc per-seed 0:0.4950, 1:0.5034, 2:0.5126</t>
         </is>
       </c>
       <c r="F363" t="inlineStr">
@@ -16370,22 +16380,27 @@
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>cbramod_pac</t>
+          <t>biot_scratch</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>[0, 1, 2]</t>
         </is>
       </c>
       <c r="D364" t="inlineStr">
         <is>
-          <t>skipped</t>
+          <t>filled</t>
         </is>
       </c>
       <c r="E364" t="inlineStr">
         <is>
-          <t>the workbook has no row for this variant</t>
+          <t>[实测 3.20M] balanced_acc per-seed 0:0.3337, 1:0.3273, 2:0.2687</t>
+        </is>
+      </c>
+      <c r="F364" t="inlineStr">
+        <is>
+          <t>lr=0.0004 batch_size=64 epochs=100 patience=10 eval_every_steps=0 loss=cross_entropy</t>
         </is>
       </c>
     </row>
@@ -16397,27 +16412,22 @@
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>cbramod_pretrained</t>
+          <t>cbramod_pac</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>[0, 1, 2]</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D365" t="inlineStr">
         <is>
-          <t>filled</t>
+          <t>skipped</t>
         </is>
       </c>
       <c r="E365" t="inlineStr">
         <is>
-          <t>[实测 46.01M] balanced_acc per-seed 0:0.6035, 1:0.6257, 2:0.6096</t>
-        </is>
-      </c>
-      <c r="F365" t="inlineStr">
-        <is>
-          <t>lr=0.0001 batch_size=64 epochs=50 patience=0 eval_every_steps=0 loss=cross_entropy label_smoothing=0.1 grad_clip=1.0 multi_lr=True</t>
+          <t>the workbook has no row for this variant</t>
         </is>
       </c>
     </row>
@@ -16429,7 +16439,7 @@
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>cbramod_scratch</t>
+          <t>cbramod_pretrained</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
@@ -16444,7 +16454,7 @@
       </c>
       <c r="E366" t="inlineStr">
         <is>
-          <t>[实测 46.01M] balanced_acc per-seed 0:0.5491, 1:0.5562, 2:0.5558</t>
+          <t>[实测 46.01M] balanced_acc per-seed 0:0.6035, 1:0.6257, 2:0.6096</t>
         </is>
       </c>
       <c r="F366" t="inlineStr">
@@ -16461,7 +16471,7 @@
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>cnn_transformer</t>
+          <t>cbramod_scratch</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
@@ -16476,12 +16486,12 @@
       </c>
       <c r="E367" t="inlineStr">
         <is>
-          <t>[实测 3.18M] balanced_acc per-seed 0:0.4501, 1:0.4718, 2:0.4612</t>
+          <t>[实测 46.01M] balanced_acc per-seed 0:0.5491, 1:0.5562, 2:0.5558</t>
         </is>
       </c>
       <c r="F367" t="inlineStr">
         <is>
-          <t>stopped_by=patience lr=0.0001 batch_size=64 epochs=100 patience=20 eval_every_steps=0 loss=cross_entropy label_smoothing=0.1</t>
+          <t>lr=0.0001 batch_size=64 epochs=50 patience=0 eval_every_steps=0 loss=cross_entropy label_smoothing=0.1 grad_clip=1.0 multi_lr=True</t>
         </is>
       </c>
     </row>
@@ -16493,22 +16503,27 @@
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>cnn_transformer_lr1e4</t>
+          <t>cnn_transformer</t>
         </is>
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>[0, 1, 2]</t>
         </is>
       </c>
       <c r="D368" t="inlineStr">
         <is>
-          <t>skipped</t>
+          <t>filled</t>
         </is>
       </c>
       <c r="E368" t="inlineStr">
         <is>
-          <t>no row label for 'cnn_transformer_lr1e4'</t>
+          <t>[实测 3.18M] balanced_acc per-seed 0:0.4501, 1:0.4718, 2:0.4612</t>
+        </is>
+      </c>
+      <c r="F368" t="inlineStr">
+        <is>
+          <t>stopped_by=patience lr=0.0001 batch_size=64 epochs=100 patience=20 eval_every_steps=0 loss=cross_entropy label_smoothing=0.1</t>
         </is>
       </c>
     </row>
@@ -16520,7 +16535,7 @@
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>cnn_transformer_lr3e4</t>
+          <t>cnn_transformer_lr1e4</t>
         </is>
       </c>
       <c r="C369" t="inlineStr">
@@ -16535,7 +16550,7 @@
       </c>
       <c r="E369" t="inlineStr">
         <is>
-          <t>no row label for 'cnn_transformer_lr3e4'</t>
+          <t>no row label for 'cnn_transformer_lr1e4'</t>
         </is>
       </c>
     </row>
@@ -16547,27 +16562,22 @@
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>contrawr</t>
+          <t>cnn_transformer_lr3e4</t>
         </is>
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>[0, 1, 2]</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D370" t="inlineStr">
         <is>
-          <t>filled</t>
+          <t>skipped</t>
         </is>
       </c>
       <c r="E370" t="inlineStr">
         <is>
-          <t>[实测 1.60M] balanced_acc per-seed 0:0.4898, 1:0.4965, 2:0.4810</t>
-        </is>
-      </c>
-      <c r="F370" t="inlineStr">
-        <is>
-          <t>lr=0.001 batch_size=64 epochs=100 patience=20 eval_every_steps=0 loss=cross_entropy label_smoothing=0.1</t>
+          <t>no row label for 'cnn_transformer_lr3e4'</t>
         </is>
       </c>
     </row>
@@ -16579,22 +16589,27 @@
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>diag_lr3e5</t>
+          <t>contrawr</t>
         </is>
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>[0, 1, 2]</t>
         </is>
       </c>
       <c r="D371" t="inlineStr">
         <is>
-          <t>skipped</t>
+          <t>filled</t>
         </is>
       </c>
       <c r="E371" t="inlineStr">
         <is>
-          <t>no row label for 'diag_lr3e5'</t>
+          <t>[实测 1.60M] balanced_acc per-seed 0:0.4898, 1:0.4965, 2:0.4810</t>
+        </is>
+      </c>
+      <c r="F371" t="inlineStr">
+        <is>
+          <t>lr=0.001 batch_size=64 epochs=100 patience=20 eval_every_steps=0 loss=cross_entropy label_smoothing=0.1</t>
         </is>
       </c>
     </row>
@@ -16606,7 +16621,7 @@
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>diag_patch200</t>
+          <t>diag_lr3e5</t>
         </is>
       </c>
       <c r="C372" t="inlineStr">
@@ -16621,7 +16636,7 @@
       </c>
       <c r="E372" t="inlineStr">
         <is>
-          <t>no row label for 'diag_patch200'</t>
+          <t>no row label for 'diag_lr3e5'</t>
         </is>
       </c>
     </row>
@@ -16633,7 +16648,7 @@
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>diag_patch200_lr3e5</t>
+          <t>diag_patch200</t>
         </is>
       </c>
       <c r="C373" t="inlineStr">
@@ -16648,7 +16663,7 @@
       </c>
       <c r="E373" t="inlineStr">
         <is>
-          <t>no row label for 'diag_patch200_lr3e5'</t>
+          <t>no row label for 'diag_patch200'</t>
         </is>
       </c>
     </row>
@@ -16660,27 +16675,22 @@
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>eegpt_pretrained</t>
+          <t>diag_patch200_lr3e5</t>
         </is>
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>[0, 1, 2]</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D374" t="inlineStr">
         <is>
-          <t>filled</t>
+          <t>skipped</t>
         </is>
       </c>
       <c r="E374" t="inlineStr">
         <is>
-          <t>[实测 25.69M] balanced_acc per-seed 0:0.4233, 1:0.4411, 2:0.3494</t>
-        </is>
-      </c>
-      <c r="F374" t="inlineStr">
-        <is>
-          <t>lr=0.0004 batch_size=32 epochs=100 patience=10 eval_every_steps=0 loss=cross_entropy</t>
+          <t>no row label for 'diag_patch200_lr3e5'</t>
         </is>
       </c>
     </row>
@@ -16692,7 +16702,7 @@
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>ffcl</t>
+          <t>eegpt_pretrained</t>
         </is>
       </c>
       <c r="C375" t="inlineStr">
@@ -16707,12 +16717,12 @@
       </c>
       <c r="E375" t="inlineStr">
         <is>
-          <t>[实测 2.43M] balanced_acc per-seed 0:0.4760, 1:0.5004, 2:0.5041</t>
+          <t>[实测 25.69M] balanced_acc per-seed 0:0.4233, 1:0.4411, 2:0.3494</t>
         </is>
       </c>
       <c r="F375" t="inlineStr">
         <is>
-          <t>lr=0.001 batch_size=64 epochs=100 patience=20 eval_every_steps=0 loss=cross_entropy label_smoothing=0.1</t>
+          <t>lr=0.0004 batch_size=32 epochs=100 patience=10 eval_every_steps=0 loss=cross_entropy</t>
         </is>
       </c>
     </row>
@@ -16724,7 +16734,7 @@
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>labram_pretrained</t>
+          <t>ffcl</t>
         </is>
       </c>
       <c r="C376" t="inlineStr">
@@ -16739,12 +16749,12 @@
       </c>
       <c r="E376" t="inlineStr">
         <is>
-          <t>[实测 5.82M] balanced_acc per-seed 0:0.5352, 1:0.5647, 2:0.5720</t>
+          <t>[实测 2.43M] balanced_acc per-seed 0:0.4760, 1:0.5004, 2:0.5041</t>
         </is>
       </c>
       <c r="F376" t="inlineStr">
         <is>
-          <t>stopped_by=patience lr=0.0005 batch_size=64 epochs=50 patience=10 eval_every_steps=0 loss=cross_entropy label_smoothing=0.1 loader_divisor=1.0</t>
+          <t>lr=0.001 batch_size=64 epochs=100 patience=20 eval_every_steps=0 loss=cross_entropy label_smoothing=0.1</t>
         </is>
       </c>
     </row>
@@ -16756,7 +16766,7 @@
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>labram_scratch</t>
+          <t>labram_pretrained</t>
         </is>
       </c>
       <c r="C377" t="inlineStr">
@@ -16771,7 +16781,7 @@
       </c>
       <c r="E377" t="inlineStr">
         <is>
-          <t>[实测 5.82M] balanced_acc per-seed 0:0.3854, 1:0.3635, 2:0.3510</t>
+          <t>[实测 5.82M] balanced_acc per-seed 0:0.5352, 1:0.5647, 2:0.5720</t>
         </is>
       </c>
       <c r="F377" t="inlineStr">
@@ -16788,22 +16798,27 @@
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>paclock_c_nm</t>
+          <t>labram_scratch</t>
         </is>
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>[0, 1, 2]</t>
         </is>
       </c>
       <c r="D378" t="inlineStr">
         <is>
-          <t>skipped</t>
+          <t>filled</t>
         </is>
       </c>
       <c r="E378" t="inlineStr">
         <is>
-          <t>no row label for 'paclock_c_nm'</t>
+          <t>[实测 5.82M] balanced_acc per-seed 0:0.3854, 1:0.3635, 2:0.3510</t>
+        </is>
+      </c>
+      <c r="F378" t="inlineStr">
+        <is>
+          <t>stopped_by=patience lr=0.0005 batch_size=64 epochs=50 patience=10 eval_every_steps=0 loss=cross_entropy label_smoothing=0.1 loader_divisor=1.0</t>
         </is>
       </c>
     </row>
@@ -16815,7 +16830,7 @@
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>paclock_concat</t>
+          <t>paclock_c_nm</t>
         </is>
       </c>
       <c r="C379" t="inlineStr">
@@ -16830,7 +16845,7 @@
       </c>
       <c r="E379" t="inlineStr">
         <is>
-          <t>no row label for 'paclock_concat'</t>
+          <t>no row label for 'paclock_c_nm'</t>
         </is>
       </c>
     </row>
@@ -16842,7 +16857,7 @@
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>paclock_duplex_ms</t>
+          <t>paclock_concat</t>
         </is>
       </c>
       <c r="C380" t="inlineStr">
@@ -16857,7 +16872,7 @@
       </c>
       <c r="E380" t="inlineStr">
         <is>
-          <t>no row label for 'paclock_duplex_ms'</t>
+          <t>no row label for 'paclock_concat'</t>
         </is>
       </c>
     </row>
@@ -16869,7 +16884,7 @@
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>paclock_flagship</t>
+          <t>paclock_duplex_ms</t>
         </is>
       </c>
       <c r="C381" t="inlineStr">
@@ -16884,7 +16899,7 @@
       </c>
       <c r="E381" t="inlineStr">
         <is>
-          <t>no row label for 'paclock_flagship'</t>
+          <t>no row label for 'paclock_duplex_ms'</t>
         </is>
       </c>
     </row>
@@ -16896,7 +16911,7 @@
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>paclock_ft_base</t>
+          <t>paclock_flagship</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
@@ -16911,7 +16926,7 @@
       </c>
       <c r="E382" t="inlineStr">
         <is>
-          <t>no row label for 'paclock_ft_base'</t>
+          <t>no row label for 'paclock_flagship'</t>
         </is>
       </c>
     </row>
@@ -16923,7 +16938,7 @@
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>paclock_ft_base_v2</t>
+          <t>paclock_ft_base</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
@@ -16938,7 +16953,7 @@
       </c>
       <c r="E383" t="inlineStr">
         <is>
-          <t>no row label for 'paclock_ft_base_v2'</t>
+          <t>no row label for 'paclock_ft_base'</t>
         </is>
       </c>
     </row>
@@ -16950,7 +16965,7 @@
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>paclock_ft_large</t>
+          <t>paclock_ft_base_v2</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
@@ -16965,7 +16980,7 @@
       </c>
       <c r="E384" t="inlineStr">
         <is>
-          <t>no row label for 'paclock_ft_large'</t>
+          <t>no row label for 'paclock_ft_base_v2'</t>
         </is>
       </c>
     </row>
@@ -16977,7 +16992,7 @@
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>paclock_fuse_ms</t>
+          <t>paclock_ft_large</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
@@ -16992,7 +17007,7 @@
       </c>
       <c r="E385" t="inlineStr">
         <is>
-          <t>no row label for 'paclock_fuse_ms'</t>
+          <t>no row label for 'paclock_ft_large'</t>
         </is>
       </c>
     </row>
@@ -17004,7 +17019,7 @@
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>paclock_fuse_sp</t>
+          <t>paclock_fuse_ms</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
@@ -17019,7 +17034,7 @@
       </c>
       <c r="E386" t="inlineStr">
         <is>
-          <t>no row label for 'paclock_fuse_sp'</t>
+          <t>no row label for 'paclock_fuse_ms'</t>
         </is>
       </c>
     </row>
@@ -17031,7 +17046,7 @@
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>paclock_h12</t>
+          <t>paclock_fuse_sp</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
@@ -17046,7 +17061,7 @@
       </c>
       <c r="E387" t="inlineStr">
         <is>
-          <t>no row label for 'paclock_h12'</t>
+          <t>no row label for 'paclock_fuse_sp'</t>
         </is>
       </c>
     </row>
@@ -17058,7 +17073,7 @@
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>paclock_h1stem</t>
+          <t>paclock_h12</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
@@ -17073,7 +17088,7 @@
       </c>
       <c r="E388" t="inlineStr">
         <is>
-          <t>no row label for 'paclock_h1stem'</t>
+          <t>no row label for 'paclock_h12'</t>
         </is>
       </c>
     </row>
@@ -17085,7 +17100,7 @@
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>paclock_h2mont</t>
+          <t>paclock_h1stem</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
@@ -17100,7 +17115,7 @@
       </c>
       <c r="E389" t="inlineStr">
         <is>
-          <t>no row label for 'paclock_h2mont'</t>
+          <t>no row label for 'paclock_h1stem'</t>
         </is>
       </c>
     </row>
@@ -17112,7 +17127,7 @@
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>paclock_h4flat</t>
+          <t>paclock_h2mont</t>
         </is>
       </c>
       <c r="C390" t="inlineStr">
@@ -17127,7 +17142,7 @@
       </c>
       <c r="E390" t="inlineStr">
         <is>
-          <t>no row label for 'paclock_h4flat'</t>
+          <t>no row label for 'paclock_h2mont'</t>
         </is>
       </c>
     </row>
@@ -17139,7 +17154,7 @@
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>paclock_hybrid_sp</t>
+          <t>paclock_h4flat</t>
         </is>
       </c>
       <c r="C391" t="inlineStr">
@@ -17154,7 +17169,7 @@
       </c>
       <c r="E391" t="inlineStr">
         <is>
-          <t>no row label for 'paclock_hybrid_sp'</t>
+          <t>no row label for 'paclock_h4flat'</t>
         </is>
       </c>
     </row>
@@ -17166,7 +17181,7 @@
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>paclock_hybrid_sp_gate</t>
+          <t>paclock_hybrid_sp</t>
         </is>
       </c>
       <c r="C392" t="inlineStr">
@@ -17181,7 +17196,7 @@
       </c>
       <c r="E392" t="inlineStr">
         <is>
-          <t>no row label for 'paclock_hybrid_sp_gate'</t>
+          <t>no row label for 'paclock_hybrid_sp'</t>
         </is>
       </c>
     </row>
@@ -17193,7 +17208,7 @@
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>paclock_lr1e3</t>
+          <t>paclock_hybrid_sp_gate</t>
         </is>
       </c>
       <c r="C393" t="inlineStr">
@@ -17208,7 +17223,7 @@
       </c>
       <c r="E393" t="inlineStr">
         <is>
-          <t>no row label for 'paclock_lr1e3'</t>
+          <t>no row label for 'paclock_hybrid_sp_gate'</t>
         </is>
       </c>
     </row>
@@ -17220,7 +17235,7 @@
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>paclock_lr3e4</t>
+          <t>paclock_lr1e3</t>
         </is>
       </c>
       <c r="C394" t="inlineStr">
@@ -17235,7 +17250,7 @@
       </c>
       <c r="E394" t="inlineStr">
         <is>
-          <t>no row label for 'paclock_lr3e4'</t>
+          <t>no row label for 'paclock_lr1e3'</t>
         </is>
       </c>
     </row>
@@ -17247,7 +17262,7 @@
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>paclock_pac</t>
+          <t>paclock_lr3e4</t>
         </is>
       </c>
       <c r="C395" t="inlineStr">
@@ -17262,7 +17277,7 @@
       </c>
       <c r="E395" t="inlineStr">
         <is>
-          <t>the workbook has no row for this variant</t>
+          <t>no row label for 'paclock_lr3e4'</t>
         </is>
       </c>
     </row>
@@ -17274,7 +17289,7 @@
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>paclock_pt_base</t>
+          <t>paclock_pac</t>
         </is>
       </c>
       <c r="C396" t="inlineStr">
@@ -17289,7 +17304,7 @@
       </c>
       <c r="E396" t="inlineStr">
         <is>
-          <t>row 'PACLock (pretrained, base)' not found</t>
+          <t>the workbook has no row for this variant</t>
         </is>
       </c>
     </row>
@@ -17301,7 +17316,7 @@
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>paclock_pt_large</t>
+          <t>paclock_pt_base</t>
         </is>
       </c>
       <c r="C397" t="inlineStr">
@@ -17316,7 +17331,7 @@
       </c>
       <c r="E397" t="inlineStr">
         <is>
-          <t>row 'PACLock (pretrained, large)' not found</t>
+          <t>row 'PACLock (pretrained, base)' not found</t>
         </is>
       </c>
     </row>
@@ -17328,7 +17343,7 @@
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>paclock_raw_drop5</t>
+          <t>paclock_pt_large</t>
         </is>
       </c>
       <c r="C398" t="inlineStr">
@@ -17343,7 +17358,7 @@
       </c>
       <c r="E398" t="inlineStr">
         <is>
-          <t>no row label for 'paclock_raw_drop5'</t>
+          <t>row 'PACLock (pretrained, large)' not found</t>
         </is>
       </c>
     </row>
@@ -17355,7 +17370,7 @@
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>paclock_raw_headattn</t>
+          <t>paclock_raw_drop5</t>
         </is>
       </c>
       <c r="C399" t="inlineStr">
@@ -17370,7 +17385,7 @@
       </c>
       <c r="E399" t="inlineStr">
         <is>
-          <t>no row label for 'paclock_raw_headattn'</t>
+          <t>no row label for 'paclock_raw_drop5'</t>
         </is>
       </c>
     </row>
@@ -17382,7 +17397,7 @@
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>paclock_raw_large</t>
+          <t>paclock_raw_headattn</t>
         </is>
       </c>
       <c r="C400" t="inlineStr">
@@ -17397,7 +17412,7 @@
       </c>
       <c r="E400" t="inlineStr">
         <is>
-          <t>no row label for 'paclock_raw_large'</t>
+          <t>no row label for 'paclock_raw_headattn'</t>
         </is>
       </c>
     </row>
@@ -17409,7 +17424,7 @@
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>paclock_raw_nb16</t>
+          <t>paclock_raw_large</t>
         </is>
       </c>
       <c r="C401" t="inlineStr">
@@ -17424,7 +17439,7 @@
       </c>
       <c r="E401" t="inlineStr">
         <is>
-          <t>no row label for 'paclock_raw_nb16'</t>
+          <t>no row label for 'paclock_raw_large'</t>
         </is>
       </c>
     </row>
@@ -17436,7 +17451,7 @@
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>paclock_raw_p100</t>
+          <t>paclock_raw_nb16</t>
         </is>
       </c>
       <c r="C402" t="inlineStr">
@@ -17451,7 +17466,7 @@
       </c>
       <c r="E402" t="inlineStr">
         <is>
-          <t>no row label for 'paclock_raw_p100'</t>
+          <t>no row label for 'paclock_raw_nb16'</t>
         </is>
       </c>
     </row>
@@ -17463,7 +17478,7 @@
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>paclock_raw_small</t>
+          <t>paclock_raw_p100</t>
         </is>
       </c>
       <c r="C403" t="inlineStr">
@@ -17478,7 +17493,7 @@
       </c>
       <c r="E403" t="inlineStr">
         <is>
-          <t>no row label for 'paclock_raw_small'</t>
+          <t>no row label for 'paclock_raw_p100'</t>
         </is>
       </c>
     </row>
@@ -17490,7 +17505,7 @@
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>paclock_raw_sphead</t>
+          <t>paclock_raw_small</t>
         </is>
       </c>
       <c r="C404" t="inlineStr">
@@ -17505,7 +17520,7 @@
       </c>
       <c r="E404" t="inlineStr">
         <is>
-          <t>no row label for 'paclock_raw_sphead'</t>
+          <t>no row label for 'paclock_raw_small'</t>
         </is>
       </c>
     </row>
@@ -17517,7 +17532,7 @@
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>paclock_raw_tiny</t>
+          <t>paclock_raw_sphead</t>
         </is>
       </c>
       <c r="C405" t="inlineStr">
@@ -17532,7 +17547,7 @@
       </c>
       <c r="E405" t="inlineStr">
         <is>
-          <t>no row label for 'paclock_raw_tiny'</t>
+          <t>no row label for 'paclock_raw_sphead'</t>
         </is>
       </c>
     </row>
@@ -17544,7 +17559,7 @@
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>paclock_raw_wide</t>
+          <t>paclock_raw_tiny</t>
         </is>
       </c>
       <c r="C406" t="inlineStr">
@@ -17559,7 +17574,7 @@
       </c>
       <c r="E406" t="inlineStr">
         <is>
-          <t>no row label for 'paclock_raw_wide'</t>
+          <t>no row label for 'paclock_raw_tiny'</t>
         </is>
       </c>
     </row>
@@ -17571,7 +17586,7 @@
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>paclock_rawpt_large</t>
+          <t>paclock_raw_wide</t>
         </is>
       </c>
       <c r="C407" t="inlineStr">
@@ -17586,7 +17601,7 @@
       </c>
       <c r="E407" t="inlineStr">
         <is>
-          <t>no row label for 'paclock_rawpt_large'</t>
+          <t>no row label for 'paclock_raw_wide'</t>
         </is>
       </c>
     </row>
@@ -17598,7 +17613,7 @@
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>paclock_rawtok</t>
+          <t>paclock_rawpt_large</t>
         </is>
       </c>
       <c r="C408" t="inlineStr">
@@ -17613,7 +17628,7 @@
       </c>
       <c r="E408" t="inlineStr">
         <is>
-          <t>no row label for 'paclock_rawtok'</t>
+          <t>no row label for 'paclock_rawpt_large'</t>
         </is>
       </c>
     </row>
@@ -17625,7 +17640,7 @@
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>paclock_rot2</t>
+          <t>paclock_rawtok</t>
         </is>
       </c>
       <c r="C409" t="inlineStr">
@@ -17640,7 +17655,7 @@
       </c>
       <c r="E409" t="inlineStr">
         <is>
-          <t>no row label for 'paclock_rot2'</t>
+          <t>no row label for 'paclock_rawtok'</t>
         </is>
       </c>
     </row>
@@ -17652,7 +17667,7 @@
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>paclock_rot_sphead</t>
+          <t>paclock_rot2</t>
         </is>
       </c>
       <c r="C410" t="inlineStr">
@@ -17667,7 +17682,7 @@
       </c>
       <c r="E410" t="inlineStr">
         <is>
-          <t>no row label for 'paclock_rot_sphead'</t>
+          <t>no row label for 'paclock_rot2'</t>
         </is>
       </c>
     </row>
@@ -17679,7 +17694,7 @@
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>paclock_rsp_t1_drop04</t>
+          <t>paclock_rot_sphead</t>
         </is>
       </c>
       <c r="C411" t="inlineStr">
@@ -17694,7 +17709,7 @@
       </c>
       <c r="E411" t="inlineStr">
         <is>
-          <t>no row label for 'paclock_rsp_t1_drop04'</t>
+          <t>no row label for 'paclock_rot_sphead'</t>
         </is>
       </c>
     </row>
@@ -17706,7 +17721,7 @@
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>paclock_rsp_t2_wd1e3</t>
+          <t>paclock_rsp_t1_drop04</t>
         </is>
       </c>
       <c r="C412" t="inlineStr">
@@ -17721,7 +17736,7 @@
       </c>
       <c r="E412" t="inlineStr">
         <is>
-          <t>no row label for 'paclock_rsp_t2_wd1e3'</t>
+          <t>no row label for 'paclock_rsp_t1_drop04'</t>
         </is>
       </c>
     </row>
@@ -17733,7 +17748,7 @@
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>paclock_rsp_t3_aug</t>
+          <t>paclock_rsp_t2_wd1e3</t>
         </is>
       </c>
       <c r="C413" t="inlineStr">
@@ -17748,7 +17763,7 @@
       </c>
       <c r="E413" t="inlineStr">
         <is>
-          <t>no row label for 'paclock_rsp_t3_aug'</t>
+          <t>no row label for 'paclock_rsp_t2_wd1e3'</t>
         </is>
       </c>
     </row>
@@ -17760,7 +17775,7 @@
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>paclock_rsp_t4_combo</t>
+          <t>paclock_rsp_t3_aug</t>
         </is>
       </c>
       <c r="C414" t="inlineStr">
@@ -17775,7 +17790,7 @@
       </c>
       <c r="E414" t="inlineStr">
         <is>
-          <t>no row label for 'paclock_rsp_t4_combo'</t>
+          <t>no row label for 'paclock_rsp_t3_aug'</t>
         </is>
       </c>
     </row>
@@ -17787,7 +17802,7 @@
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>paclock_rsp_t5_aug_wd</t>
+          <t>paclock_rsp_t4_combo</t>
         </is>
       </c>
       <c r="C415" t="inlineStr">
@@ -17802,7 +17817,7 @@
       </c>
       <c r="E415" t="inlineStr">
         <is>
-          <t>no row label for 'paclock_rsp_t5_aug_wd'</t>
+          <t>no row label for 'paclock_rsp_t4_combo'</t>
         </is>
       </c>
     </row>
@@ -17814,7 +17829,7 @@
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>paclock_rsp_t6_aug_strong</t>
+          <t>paclock_rsp_t5_aug_wd</t>
         </is>
       </c>
       <c r="C416" t="inlineStr">
@@ -17829,7 +17844,7 @@
       </c>
       <c r="E416" t="inlineStr">
         <is>
-          <t>no row label for 'paclock_rsp_t6_aug_strong'</t>
+          <t>no row label for 'paclock_rsp_t5_aug_wd'</t>
         </is>
       </c>
     </row>
@@ -17841,7 +17856,7 @@
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>paclock_sphead</t>
+          <t>paclock_rsp_t6_aug_strong</t>
         </is>
       </c>
       <c r="C417" t="inlineStr">
@@ -17856,7 +17871,7 @@
       </c>
       <c r="E417" t="inlineStr">
         <is>
-          <t>no row label for 'paclock_sphead'</t>
+          <t>no row label for 'paclock_rsp_t6_aug_strong'</t>
         </is>
       </c>
     </row>
@@ -17868,7 +17883,7 @@
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>paclock_v2</t>
+          <t>paclock_sphead</t>
         </is>
       </c>
       <c r="C418" t="inlineStr">
@@ -17883,7 +17898,7 @@
       </c>
       <c r="E418" t="inlineStr">
         <is>
-          <t>row 'PACLock (from scratch, full)' not found</t>
+          <t>no row label for 'paclock_sphead'</t>
         </is>
       </c>
     </row>
@@ -17895,7 +17910,7 @@
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>paclock_wn</t>
+          <t>paclock_v2</t>
         </is>
       </c>
       <c r="C419" t="inlineStr">
@@ -17910,7 +17925,7 @@
       </c>
       <c r="E419" t="inlineStr">
         <is>
-          <t>no row label for 'paclock_wn'</t>
+          <t>row 'PACLock (from scratch, full)' not found</t>
         </is>
       </c>
     </row>
@@ -17922,7 +17937,7 @@
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>paclock_wn_raw</t>
+          <t>paclock_wn</t>
         </is>
       </c>
       <c r="C420" t="inlineStr">
@@ -17937,7 +17952,7 @@
       </c>
       <c r="E420" t="inlineStr">
         <is>
-          <t>no row label for 'paclock_wn_raw'</t>
+          <t>no row label for 'paclock_wn'</t>
         </is>
       </c>
     </row>
@@ -17949,7 +17964,7 @@
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>paclock_xyz</t>
+          <t>paclock_wn_raw</t>
         </is>
       </c>
       <c r="C421" t="inlineStr">
@@ -17964,7 +17979,7 @@
       </c>
       <c r="E421" t="inlineStr">
         <is>
-          <t>no row label for 'paclock_xyz'</t>
+          <t>no row label for 'paclock_wn_raw'</t>
         </is>
       </c>
     </row>
@@ -17976,27 +17991,22 @@
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>sparcnet</t>
+          <t>paclock_xyz</t>
         </is>
       </c>
       <c r="C422" t="inlineStr">
         <is>
-          <t>[0, 1, 2]</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D422" t="inlineStr">
         <is>
-          <t>filled</t>
+          <t>skipped</t>
         </is>
       </c>
       <c r="E422" t="inlineStr">
         <is>
-          <t>[实测 1.27M] balanced_acc per-seed 0:0.5951, 1:0.5863, 2:0.5901</t>
-        </is>
-      </c>
-      <c r="F422" t="inlineStr">
-        <is>
-          <t>lr=0.001 batch_size=64 epochs=100 patience=20 eval_every_steps=0 loss=cross_entropy label_smoothing=0.1</t>
+          <t>no row label for 'paclock_xyz'</t>
         </is>
       </c>
     </row>
@@ -18008,7 +18018,7 @@
       </c>
       <c r="B423" t="inlineStr">
         <is>
-          <t>st_transformer</t>
+          <t>sparcnet</t>
         </is>
       </c>
       <c r="C423" t="inlineStr">
@@ -18023,7 +18033,7 @@
       </c>
       <c r="E423" t="inlineStr">
         <is>
-          <t>[实测 3.48M] balanced_acc per-seed 0:0.5757, 1:0.5973, 2:0.6085</t>
+          <t>[实测 1.27M] balanced_acc per-seed 0:0.5951, 1:0.5863, 2:0.5901</t>
         </is>
       </c>
       <c r="F423" t="inlineStr">
@@ -18040,7 +18050,7 @@
       </c>
       <c r="B424" t="inlineStr">
         <is>
-          <t>tfm_pretrained</t>
+          <t>st_transformer</t>
         </is>
       </c>
       <c r="C424" t="inlineStr">
@@ -18055,24 +18065,24 @@
       </c>
       <c r="E424" t="inlineStr">
         <is>
-          <t>[实测 1.89M] balanced_acc per-seed 0:0.4524, 1:0.4217, 2:0.4226</t>
+          <t>[实测 3.48M] balanced_acc per-seed 0:0.5757, 1:0.5973, 2:0.6085</t>
         </is>
       </c>
       <c r="F424" t="inlineStr">
         <is>
-          <t>lr=0.001 batch_size=32 epochs=50 patience=10 eval_every_steps=0 loss=cross_entropy label_smoothing=0.1</t>
+          <t>lr=0.001 batch_size=64 epochs=100 patience=20 eval_every_steps=0 loss=cross_entropy label_smoothing=0.1</t>
         </is>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>siena</t>
+          <t>physionet_mi</t>
         </is>
       </c>
       <c r="B425" t="inlineStr">
         <is>
-          <t>biot_prest16</t>
+          <t>tfm_pretrained</t>
         </is>
       </c>
       <c r="C425" t="inlineStr">
@@ -18087,12 +18097,12 @@
       </c>
       <c r="E425" t="inlineStr">
         <is>
-          <t>[实测 3.19M] pr_auc per-seed 0:0.0688, 1:0.1026, 2:0.1000  [seed spread 17% -- mean is a weak summary]</t>
+          <t>[实测 1.89M] balanced_acc per-seed 0:0.4524, 1:0.4217, 2:0.4226</t>
         </is>
       </c>
       <c r="F425" t="inlineStr">
         <is>
-          <t>stopped_by=patience lr=0.001 batch_size=512 epochs=100 patience=5 eval_every_steps=0 loss=bce_with_logits</t>
+          <t>lr=0.001 batch_size=32 epochs=50 patience=10 eval_every_steps=0 loss=cross_entropy label_smoothing=0.1</t>
         </is>
       </c>
     </row>
@@ -18104,7 +18114,7 @@
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>biot_scratch</t>
+          <t>biot_prest16</t>
         </is>
       </c>
       <c r="C426" t="inlineStr">
@@ -18119,7 +18129,7 @@
       </c>
       <c r="E426" t="inlineStr">
         <is>
-          <t>[实测 3.19M] pr_auc per-seed 0:0.1584, 1:0.2150, 2:0.1265  [seed spread 22% -- mean is a weak summary]</t>
+          <t>[实测 3.19M] pr_auc per-seed 0:0.0688, 1:0.1026, 2:0.1000  [seed spread 17% -- mean is a weak summary]</t>
         </is>
       </c>
       <c r="F426" t="inlineStr">
@@ -18136,22 +18146,27 @@
       </c>
       <c r="B427" t="inlineStr">
         <is>
-          <t>cbramod_crofremo</t>
+          <t>biot_scratch</t>
         </is>
       </c>
       <c r="C427" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>[0, 1, 2]</t>
         </is>
       </c>
       <c r="D427" t="inlineStr">
         <is>
-          <t>skipped</t>
+          <t>filled</t>
         </is>
       </c>
       <c r="E427" t="inlineStr">
         <is>
-          <t>no row label for 'cbramod_crofremo'</t>
+          <t>[实测 3.19M] pr_auc per-seed 0:0.1584, 1:0.2150, 2:0.1265  [seed spread 22% -- mean is a weak summary]</t>
+        </is>
+      </c>
+      <c r="F427" t="inlineStr">
+        <is>
+          <t>stopped_by=patience lr=0.001 batch_size=512 epochs=100 patience=5 eval_every_steps=0 loss=bce_with_logits</t>
         </is>
       </c>
     </row>
@@ -18163,27 +18178,22 @@
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>cbramod_pretrained</t>
+          <t>cbramod_crofremo</t>
         </is>
       </c>
       <c r="C428" t="inlineStr">
         <is>
-          <t>[0, 1, 2]</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D428" t="inlineStr">
         <is>
-          <t>filled</t>
+          <t>skipped</t>
         </is>
       </c>
       <c r="E428" t="inlineStr">
         <is>
-          <t>[实测 35.45M] pr_auc per-seed 0:0.3530, 1:0.4441, 2:0.4758</t>
-        </is>
-      </c>
-      <c r="F428" t="inlineStr">
-        <is>
-          <t>lr=0.0001 batch_size=64 epochs=50 patience=0 eval_every_steps=0 loss=bce_with_logits grad_clip=1.0 select_metric=auroc multi_lr=True</t>
+          <t>no row label for 'cbramod_crofremo'</t>
         </is>
       </c>
     </row>
@@ -18195,7 +18205,7 @@
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>cbramod_scratch</t>
+          <t>cbramod_pretrained</t>
         </is>
       </c>
       <c r="C429" t="inlineStr">
@@ -18210,7 +18220,7 @@
       </c>
       <c r="E429" t="inlineStr">
         <is>
-          <t>[实测 35.45M] pr_auc per-seed 0:0.2693, 1:0.1607, 2:0.1679  [seed spread 25% -- mean is a weak summary]</t>
+          <t>[实测 35.45M] pr_auc per-seed 0:0.3530, 1:0.4441, 2:0.4758</t>
         </is>
       </c>
       <c r="F429" t="inlineStr">
@@ -18227,7 +18237,7 @@
       </c>
       <c r="B430" t="inlineStr">
         <is>
-          <t>cnn_transformer</t>
+          <t>cbramod_scratch</t>
         </is>
       </c>
       <c r="C430" t="inlineStr">
@@ -18242,12 +18252,12 @@
       </c>
       <c r="E430" t="inlineStr">
         <is>
-          <t>[实测 3.16M] pr_auc per-seed 0:0.4808, 1:0.3073, 2:0.4801  [seed spread 19% -- mean is a weak summary]</t>
+          <t>[实测 35.45M] pr_auc per-seed 0:0.2693, 1:0.1607, 2:0.1679  [seed spread 25% -- mean is a weak summary]</t>
         </is>
       </c>
       <c r="F430" t="inlineStr">
         <is>
-          <t>lr=0.001 batch_size=512 epochs=20 patience=8 eval_every_steps=200 loss=bce_with_logits</t>
+          <t>lr=0.0001 batch_size=64 epochs=50 patience=0 eval_every_steps=0 loss=bce_with_logits grad_clip=1.0 select_metric=auroc multi_lr=True</t>
         </is>
       </c>
     </row>
@@ -18259,7 +18269,7 @@
       </c>
       <c r="B431" t="inlineStr">
         <is>
-          <t>contrawr</t>
+          <t>cnn_transformer</t>
         </is>
       </c>
       <c r="C431" t="inlineStr">
@@ -18274,7 +18284,7 @@
       </c>
       <c r="E431" t="inlineStr">
         <is>
-          <t>[实测 1.57M] pr_auc per-seed 0:0.3800, 1:0.4873, 2:0.4868</t>
+          <t>[实测 3.16M] pr_auc per-seed 0:0.4808, 1:0.3073, 2:0.4801  [seed spread 19% -- mean is a weak summary]</t>
         </is>
       </c>
       <c r="F431" t="inlineStr">
@@ -18291,7 +18301,7 @@
       </c>
       <c r="B432" t="inlineStr">
         <is>
-          <t>csbrain_pretrained</t>
+          <t>contrawr</t>
         </is>
       </c>
       <c r="C432" t="inlineStr">
@@ -18306,12 +18316,12 @@
       </c>
       <c r="E432" t="inlineStr">
         <is>
-          <t>[实测 47.06M] pr_auc per-seed 0:0.1402, 1:0.3531, 2:0.2057  [seed spread 38% -- mean is a weak summary]</t>
+          <t>[实测 1.57M] pr_auc per-seed 0:0.3800, 1:0.4873, 2:0.4868</t>
         </is>
       </c>
       <c r="F432" t="inlineStr">
         <is>
-          <t>stopped_by=patience lr=0.0001 batch_size=64 epochs=25 patience=10 eval_every_steps=500 loss=bce_with_logits grad_clip=1.0</t>
+          <t>lr=0.001 batch_size=512 epochs=20 patience=8 eval_every_steps=200 loss=bce_with_logits</t>
         </is>
       </c>
     </row>
@@ -18323,22 +18333,27 @@
       </c>
       <c r="B433" t="inlineStr">
         <is>
-          <t>eegconformer_t1</t>
+          <t>csbrain_pretrained</t>
         </is>
       </c>
       <c r="C433" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>[0, 1, 2]</t>
         </is>
       </c>
       <c r="D433" t="inlineStr">
         <is>
-          <t>skipped</t>
+          <t>filled</t>
         </is>
       </c>
       <c r="E433" t="inlineStr">
         <is>
-          <t>no row label for 'eegconformer_t1'</t>
+          <t>[实测 47.06M] pr_auc per-seed 0:0.1402, 1:0.3531, 2:0.2057  [seed spread 38% -- mean is a weak summary]</t>
+        </is>
+      </c>
+      <c r="F433" t="inlineStr">
+        <is>
+          <t>stopped_by=patience lr=0.0001 batch_size=64 epochs=25 patience=10 eval_every_steps=500 loss=bce_with_logits grad_clip=1.0</t>
         </is>
       </c>
     </row>
@@ -18350,7 +18365,7 @@
       </c>
       <c r="B434" t="inlineStr">
         <is>
-          <t>eegconformer_t2</t>
+          <t>eegconformer_t1</t>
         </is>
       </c>
       <c r="C434" t="inlineStr">
@@ -18365,7 +18380,7 @@
       </c>
       <c r="E434" t="inlineStr">
         <is>
-          <t>no row label for 'eegconformer_t2'</t>
+          <t>no row label for 'eegconformer_t1'</t>
         </is>
       </c>
     </row>
@@ -18377,7 +18392,7 @@
       </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t>eegconformer_t3</t>
+          <t>eegconformer_t2</t>
         </is>
       </c>
       <c r="C435" t="inlineStr">
@@ -18392,7 +18407,7 @@
       </c>
       <c r="E435" t="inlineStr">
         <is>
-          <t>no row label for 'eegconformer_t3'</t>
+          <t>no row label for 'eegconformer_t2'</t>
         </is>
       </c>
     </row>
@@ -18404,7 +18419,7 @@
       </c>
       <c r="B436" t="inlineStr">
         <is>
-          <t>eegconformer_t4</t>
+          <t>eegconformer_t3</t>
         </is>
       </c>
       <c r="C436" t="inlineStr">
@@ -18419,7 +18434,7 @@
       </c>
       <c r="E436" t="inlineStr">
         <is>
-          <t>no row label for 'eegconformer_t4'</t>
+          <t>no row label for 'eegconformer_t3'</t>
         </is>
       </c>
     </row>
@@ -18431,7 +18446,7 @@
       </c>
       <c r="B437" t="inlineStr">
         <is>
-          <t>eegnet_t1</t>
+          <t>eegconformer_t4</t>
         </is>
       </c>
       <c r="C437" t="inlineStr">
@@ -18446,7 +18461,7 @@
       </c>
       <c r="E437" t="inlineStr">
         <is>
-          <t>no row label for 'eegnet_t1'</t>
+          <t>no row label for 'eegconformer_t4'</t>
         </is>
       </c>
     </row>
@@ -18458,7 +18473,7 @@
       </c>
       <c r="B438" t="inlineStr">
         <is>
-          <t>eegnet_t2</t>
+          <t>eegnet_t1</t>
         </is>
       </c>
       <c r="C438" t="inlineStr">
@@ -18473,7 +18488,7 @@
       </c>
       <c r="E438" t="inlineStr">
         <is>
-          <t>no row label for 'eegnet_t2'</t>
+          <t>no row label for 'eegnet_t1'</t>
         </is>
       </c>
     </row>
@@ -18485,7 +18500,7 @@
       </c>
       <c r="B439" t="inlineStr">
         <is>
-          <t>eegnet_t3</t>
+          <t>eegnet_t2</t>
         </is>
       </c>
       <c r="C439" t="inlineStr">
@@ -18500,7 +18515,7 @@
       </c>
       <c r="E439" t="inlineStr">
         <is>
-          <t>no row label for 'eegnet_t3'</t>
+          <t>no row label for 'eegnet_t2'</t>
         </is>
       </c>
     </row>
@@ -18512,7 +18527,7 @@
       </c>
       <c r="B440" t="inlineStr">
         <is>
-          <t>eegnet_t4</t>
+          <t>eegnet_t3</t>
         </is>
       </c>
       <c r="C440" t="inlineStr">
@@ -18527,7 +18542,7 @@
       </c>
       <c r="E440" t="inlineStr">
         <is>
-          <t>no row label for 'eegnet_t4'</t>
+          <t>no row label for 'eegnet_t3'</t>
         </is>
       </c>
     </row>
@@ -18539,27 +18554,22 @@
       </c>
       <c r="B441" t="inlineStr">
         <is>
-          <t>eegpt_pretrained</t>
+          <t>eegnet_t4</t>
         </is>
       </c>
       <c r="C441" t="inlineStr">
         <is>
-          <t>[0, 1, 2]</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D441" t="inlineStr">
         <is>
-          <t>filled</t>
+          <t>skipped</t>
         </is>
       </c>
       <c r="E441" t="inlineStr">
         <is>
-          <t>[实测 25.69M] pr_auc per-seed 0:0.2390, 1:0.3648, 2:0.3914  [seed spread 20% -- mean is a weak summary]</t>
-        </is>
-      </c>
-      <c r="F441" t="inlineStr">
-        <is>
-          <t>stopped_by=patience lr=0.0004 batch_size=32 epochs=40 patience=10 eval_every_steps=500 loss=bce_with_logits</t>
+          <t>no row label for 'eegnet_t4'</t>
         </is>
       </c>
     </row>
@@ -18571,7 +18581,7 @@
       </c>
       <c r="B442" t="inlineStr">
         <is>
-          <t>eegpt_scratch</t>
+          <t>eegpt_pretrained</t>
         </is>
       </c>
       <c r="C442" t="inlineStr">
@@ -18586,7 +18596,7 @@
       </c>
       <c r="E442" t="inlineStr">
         <is>
-          <t>[实测 25.69M] pr_auc per-seed 0:0.1107, 1:0.1103, 2:0.1640  [seed spread 20% -- mean is a weak summary]</t>
+          <t>[实测 25.69M] pr_auc per-seed 0:0.2390, 1:0.3648, 2:0.3914  [seed spread 20% -- mean is a weak summary]</t>
         </is>
       </c>
       <c r="F442" t="inlineStr">
@@ -18603,7 +18613,7 @@
       </c>
       <c r="B443" t="inlineStr">
         <is>
-          <t>feat_best</t>
+          <t>eegpt_scratch</t>
         </is>
       </c>
       <c r="C443" t="inlineStr">
@@ -18618,12 +18628,12 @@
       </c>
       <c r="E443" t="inlineStr">
         <is>
-          <t>[实测 0.00M] pr_auc per-seed 0:0.0404, 1:0.0404, 2:0.0404</t>
+          <t>[实测 25.69M] pr_auc per-seed 0:0.1107, 1:0.1103, 2:0.1640  [seed spread 20% -- mean is a weak summary]</t>
         </is>
       </c>
       <c r="F443" t="inlineStr">
         <is>
-          <t>stopped_by=closed-form epochs=1 loss=closed-form</t>
+          <t>stopped_by=patience lr=0.0004 batch_size=32 epochs=40 patience=10 eval_every_steps=500 loss=bce_with_logits</t>
         </is>
       </c>
     </row>
@@ -18635,7 +18645,7 @@
       </c>
       <c r="B444" t="inlineStr">
         <is>
-          <t>ffcl</t>
+          <t>feat_best</t>
         </is>
       </c>
       <c r="C444" t="inlineStr">
@@ -18650,12 +18660,12 @@
       </c>
       <c r="E444" t="inlineStr">
         <is>
-          <t>[实测 2.47M] pr_auc per-seed 0:0.3084, 1:0.4492, 2:0.5066  [seed spread 20% -- mean is a weak summary]</t>
+          <t>[实测 0.00M] pr_auc per-seed 0:0.0404, 1:0.0404, 2:0.0404</t>
         </is>
       </c>
       <c r="F444" t="inlineStr">
         <is>
-          <t>lr=0.001 batch_size=512 epochs=20 patience=8 eval_every_steps=200 loss=bce_with_logits</t>
+          <t>stopped_by=closed-form epochs=1 loss=closed-form</t>
         </is>
       </c>
     </row>
@@ -18667,7 +18677,7 @@
       </c>
       <c r="B445" t="inlineStr">
         <is>
-          <t>labram_pretrained</t>
+          <t>ffcl</t>
         </is>
       </c>
       <c r="C445" t="inlineStr">
@@ -18682,12 +18692,12 @@
       </c>
       <c r="E445" t="inlineStr">
         <is>
-          <t>[实测 5.82M] pr_auc per-seed 0:0.3124, 1:0.2807, 2:0.3149</t>
+          <t>[实测 2.47M] pr_auc per-seed 0:0.3084, 1:0.4492, 2:0.5066  [seed spread 20% -- mean is a weak summary]</t>
         </is>
       </c>
       <c r="F445" t="inlineStr">
         <is>
-          <t>stopped_by=patience lr=0.0005 batch_size=64 epochs=50 patience=10 eval_every_steps=0 loss=bce_with_logits loader_divisor=1.0</t>
+          <t>lr=0.001 batch_size=512 epochs=20 patience=8 eval_every_steps=200 loss=bce_with_logits</t>
         </is>
       </c>
     </row>
@@ -18699,7 +18709,7 @@
       </c>
       <c r="B446" t="inlineStr">
         <is>
-          <t>labram_scratch</t>
+          <t>labram_pretrained</t>
         </is>
       </c>
       <c r="C446" t="inlineStr">
@@ -18714,7 +18724,7 @@
       </c>
       <c r="E446" t="inlineStr">
         <is>
-          <t>[实测 5.82M] pr_auc per-seed 0:0.4995, 1:0.4966, 2:0.4779</t>
+          <t>[实测 5.82M] pr_auc per-seed 0:0.3124, 1:0.2807, 2:0.3149</t>
         </is>
       </c>
       <c r="F446" t="inlineStr">
@@ -18731,22 +18741,27 @@
       </c>
       <c r="B447" t="inlineStr">
         <is>
-          <t>paclock</t>
+          <t>labram_scratch</t>
         </is>
       </c>
       <c r="C447" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>[0, 1, 2]</t>
         </is>
       </c>
       <c r="D447" t="inlineStr">
         <is>
-          <t>skipped</t>
+          <t>filled</t>
         </is>
       </c>
       <c r="E447" t="inlineStr">
         <is>
-          <t>no row label for 'paclock'</t>
+          <t>[实测 5.82M] pr_auc per-seed 0:0.4995, 1:0.4966, 2:0.4779</t>
+        </is>
+      </c>
+      <c r="F447" t="inlineStr">
+        <is>
+          <t>stopped_by=patience lr=0.0005 batch_size=64 epochs=50 patience=10 eval_every_steps=0 loss=bce_with_logits loader_divisor=1.0</t>
         </is>
       </c>
     </row>
@@ -18758,22 +18773,22 @@
       </c>
       <c r="B448" t="inlineStr">
         <is>
-          <t>paclock_duplex</t>
+          <t>paclock</t>
         </is>
       </c>
       <c r="C448" t="inlineStr">
         <is>
-          <t>[0]</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D448" t="inlineStr">
         <is>
-          <t>filled (single-seed, grey)</t>
+          <t>skipped</t>
         </is>
       </c>
       <c r="E448" t="inlineStr">
         <is>
-          <t>pr_auc 0.1098</t>
+          <t>no row label for 'paclock'</t>
         </is>
       </c>
     </row>
@@ -18785,22 +18800,22 @@
       </c>
       <c r="B449" t="inlineStr">
         <is>
-          <t>paclock_duplex_b32x4</t>
+          <t>paclock_duplex</t>
         </is>
       </c>
       <c r="C449" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>[0]</t>
         </is>
       </c>
       <c r="D449" t="inlineStr">
         <is>
-          <t>skipped</t>
+          <t>filled (single-seed, grey)</t>
         </is>
       </c>
       <c r="E449" t="inlineStr">
         <is>
-          <t>no row label for 'paclock_duplex_b32x4'</t>
+          <t>pr_auc 0.1098</t>
         </is>
       </c>
     </row>
@@ -18812,7 +18827,7 @@
       </c>
       <c r="B450" t="inlineStr">
         <is>
-          <t>paclock_duplex_ptF</t>
+          <t>paclock_duplex_b32x4</t>
         </is>
       </c>
       <c r="C450" t="inlineStr">
@@ -18827,7 +18842,7 @@
       </c>
       <c r="E450" t="inlineStr">
         <is>
-          <t>row 'CroFreMo (预训练 v2-full)' not found</t>
+          <t>no row label for 'paclock_duplex_b32x4'</t>
         </is>
       </c>
     </row>
@@ -18839,27 +18854,22 @@
       </c>
       <c r="B451" t="inlineStr">
         <is>
-          <t>paclock_duplex_ptS</t>
+          <t>paclock_duplex_ptF</t>
         </is>
       </c>
       <c r="C451" t="inlineStr">
         <is>
-          <t>[0, 1, 2]</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D451" t="inlineStr">
         <is>
-          <t>filled</t>
+          <t>skipped</t>
         </is>
       </c>
       <c r="E451" t="inlineStr">
         <is>
-          <t>[实测 1.62M] pr_auc per-seed 0:0.4912, 1:0.4112, 2:0.4669</t>
-        </is>
-      </c>
-      <c r="F451" t="inlineStr">
-        <is>
-          <t>stopped_by=patience lr=0.0005 batch_size=32 epochs=60 patience=20 eval_every_steps=200 loss=bce_with_logits grad_clip=1.0 tokenizer_mode=duplex pac_token_mode=measured interaction_mode=rotation band_pe=index spatial_pe=xyz</t>
+          <t>row 'CroFreMo (预训练 v2-full)' not found</t>
         </is>
       </c>
     </row>
@@ -18871,22 +18881,27 @@
       </c>
       <c r="B452" t="inlineStr">
         <is>
-          <t>paclock_ptFtune_t1</t>
+          <t>paclock_duplex_ptS</t>
         </is>
       </c>
       <c r="C452" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>[0, 1, 2]</t>
         </is>
       </c>
       <c r="D452" t="inlineStr">
         <is>
-          <t>skipped</t>
+          <t>filled</t>
         </is>
       </c>
       <c r="E452" t="inlineStr">
         <is>
-          <t>no row label for 'paclock_ptFtune_t1'</t>
+          <t>[实测 1.62M] pr_auc per-seed 0:0.4912, 1:0.4112, 2:0.4669</t>
+        </is>
+      </c>
+      <c r="F452" t="inlineStr">
+        <is>
+          <t>stopped_by=patience lr=0.0005 batch_size=32 epochs=60 patience=20 eval_every_steps=200 loss=bce_with_logits grad_clip=1.0 tokenizer_mode=duplex pac_token_mode=measured interaction_mode=rotation band_pe=index spatial_pe=xyz</t>
         </is>
       </c>
     </row>
@@ -18898,7 +18913,7 @@
       </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t>paclock_ptFtune_t2</t>
+          <t>paclock_ptFtune_t1</t>
         </is>
       </c>
       <c r="C453" t="inlineStr">
@@ -18913,7 +18928,7 @@
       </c>
       <c r="E453" t="inlineStr">
         <is>
-          <t>no row label for 'paclock_ptFtune_t2'</t>
+          <t>no row label for 'paclock_ptFtune_t1'</t>
         </is>
       </c>
     </row>
@@ -18925,27 +18940,22 @@
       </c>
       <c r="B454" t="inlineStr">
         <is>
-          <t>reve_pretrained</t>
+          <t>paclock_ptFtune_t2</t>
         </is>
       </c>
       <c r="C454" t="inlineStr">
         <is>
-          <t>[0, 1, 2]</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D454" t="inlineStr">
         <is>
-          <t>filled</t>
+          <t>skipped</t>
         </is>
       </c>
       <c r="E454" t="inlineStr">
         <is>
-          <t>[实测 69.51M] pr_auc per-seed 0:0.3828, 1:0.5912, 2:0.5804  [seed spread 18% -- mean is a weak summary]</t>
-        </is>
-      </c>
-      <c r="F454" t="inlineStr">
-        <is>
-          <t>stopped_by=patience lr=0.0001 batch_size=128 epochs=15 patience=10 eval_every_steps=500 loss=bce_with_logits grad_clip=1.0</t>
+          <t>no row label for 'paclock_ptFtune_t2'</t>
         </is>
       </c>
     </row>
@@ -18957,7 +18967,7 @@
       </c>
       <c r="B455" t="inlineStr">
         <is>
-          <t>sparcnet</t>
+          <t>reve_pretrained</t>
         </is>
       </c>
       <c r="C455" t="inlineStr">
@@ -18972,12 +18982,12 @@
       </c>
       <c r="E455" t="inlineStr">
         <is>
-          <t>[实测 1.14M] pr_auc per-seed 0:0.4057, 1:0.3291, 2:0.3365</t>
+          <t>[实测 69.51M] pr_auc per-seed 0:0.3828, 1:0.5912, 2:0.5804  [seed spread 18% -- mean is a weak summary]</t>
         </is>
       </c>
       <c r="F455" t="inlineStr">
         <is>
-          <t>stopped_by=patience lr=0.001 batch_size=512 epochs=20 patience=8 eval_every_steps=200 loss=bce_with_logits</t>
+          <t>stopped_by=patience lr=0.0001 batch_size=128 epochs=15 patience=10 eval_every_steps=500 loss=bce_with_logits grad_clip=1.0</t>
         </is>
       </c>
     </row>
@@ -18989,7 +18999,7 @@
       </c>
       <c r="B456" t="inlineStr">
         <is>
-          <t>st_transformer</t>
+          <t>sparcnet</t>
         </is>
       </c>
       <c r="C456" t="inlineStr">
@@ -18999,12 +19009,17 @@
       </c>
       <c r="D456" t="inlineStr">
         <is>
-          <t>withheld (rule 3)</t>
+          <t>filled</t>
         </is>
       </c>
       <c r="E456" t="inlineStr">
         <is>
-          <t>mis-configured seeds [0]: {0: 'val peak at first evaluation and never cleared chance (0.0074 vs 0.0100)'}; measured pr_auc 0.2178±0.1511</t>
+          <t>[实测 1.14M] pr_auc per-seed 0:0.4057, 1:0.3291, 2:0.3365</t>
+        </is>
+      </c>
+      <c r="F456" t="inlineStr">
+        <is>
+          <t>stopped_by=patience lr=0.001 batch_size=512 epochs=20 patience=8 eval_every_steps=200 loss=bce_with_logits</t>
         </is>
       </c>
     </row>
@@ -19016,7 +19031,7 @@
       </c>
       <c r="B457" t="inlineStr">
         <is>
-          <t>tfm_pretrained</t>
+          <t>st_transformer</t>
         </is>
       </c>
       <c r="C457" t="inlineStr">
@@ -19026,17 +19041,12 @@
       </c>
       <c r="D457" t="inlineStr">
         <is>
-          <t>filled</t>
+          <t>withheld (rule 3)</t>
         </is>
       </c>
       <c r="E457" t="inlineStr">
         <is>
-          <t>[实测 1.89M] pr_auc per-seed 0:0.0693, 1:0.0471, 2:0.0645  [seed spread 16% -- mean is a weak summary]</t>
-        </is>
-      </c>
-      <c r="F457" t="inlineStr">
-        <is>
-          <t>lr=0.001 batch_size=512 epochs=7 patience=10 eval_every_steps=100 loss=bce_with_logits</t>
+          <t>mis-configured seeds [0]: {0: 'val peak at first evaluation and never cleared chance (0.0074 vs 0.0100)'}; measured pr_auc 0.2178±0.1511</t>
         </is>
       </c>
     </row>
@@ -19048,7 +19058,7 @@
       </c>
       <c r="B458" t="inlineStr">
         <is>
-          <t>tfm_scratch</t>
+          <t>tfm_pretrained</t>
         </is>
       </c>
       <c r="C458" t="inlineStr">
@@ -19063,7 +19073,7 @@
       </c>
       <c r="E458" t="inlineStr">
         <is>
-          <t>[实测 1.89M] pr_auc per-seed 0:0.0078, 1:0.0222, 2:0.0059  [seed spread 61% -- mean is a weak summary]</t>
+          <t>[实测 1.89M] pr_auc per-seed 0:0.0693, 1:0.0471, 2:0.0645  [seed spread 16% -- mean is a weak summary]</t>
         </is>
       </c>
       <c r="F458" t="inlineStr">
@@ -19075,12 +19085,12 @@
     <row r="459">
       <c r="A459" t="inlineStr">
         <is>
-          <t>sleepedf</t>
+          <t>siena</t>
         </is>
       </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t>biot_prest16</t>
+          <t>tfm_scratch</t>
         </is>
       </c>
       <c r="C459" t="inlineStr">
@@ -19095,12 +19105,12 @@
       </c>
       <c r="E459" t="inlineStr">
         <is>
-          <t>[实测 3.19M] cohen_kappa per-seed 0:0.5804, 1:0.5861, 2:0.6156</t>
+          <t>[实测 1.89M] pr_auc per-seed 0:0.0078, 1:0.0222, 2:0.0059  [seed spread 61% -- mean is a weak summary]</t>
         </is>
       </c>
       <c r="F459" t="inlineStr">
         <is>
-          <t>lr=0.0004 batch_size=64 epochs=40 patience=10 eval_every_steps=0 loss=cross_entropy</t>
+          <t>lr=0.001 batch_size=512 epochs=7 patience=10 eval_every_steps=100 loss=bce_with_logits</t>
         </is>
       </c>
     </row>
@@ -19112,7 +19122,7 @@
       </c>
       <c r="B460" t="inlineStr">
         <is>
-          <t>biot_scratch</t>
+          <t>biot_prest16</t>
         </is>
       </c>
       <c r="C460" t="inlineStr">
@@ -19127,7 +19137,7 @@
       </c>
       <c r="E460" t="inlineStr">
         <is>
-          <t>[实测 3.18M] cohen_kappa per-seed 0:0.6579, 1:0.6341, 2:0.6722</t>
+          <t>[实测 3.19M] cohen_kappa per-seed 0:0.5804, 1:0.5861, 2:0.6156</t>
         </is>
       </c>
       <c r="F460" t="inlineStr">
@@ -19144,22 +19154,27 @@
       </c>
       <c r="B461" t="inlineStr">
         <is>
-          <t>cbramod_crofremo</t>
+          <t>biot_scratch</t>
         </is>
       </c>
       <c r="C461" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>[0, 1, 2]</t>
         </is>
       </c>
       <c r="D461" t="inlineStr">
         <is>
-          <t>skipped</t>
+          <t>filled</t>
         </is>
       </c>
       <c r="E461" t="inlineStr">
         <is>
-          <t>no row label for 'cbramod_crofremo'</t>
+          <t>[实测 3.18M] cohen_kappa per-seed 0:0.6579, 1:0.6341, 2:0.6722</t>
+        </is>
+      </c>
+      <c r="F461" t="inlineStr">
+        <is>
+          <t>lr=0.0004 batch_size=64 epochs=40 patience=10 eval_every_steps=0 loss=cross_entropy</t>
         </is>
       </c>
     </row>
@@ -19171,7 +19186,7 @@
       </c>
       <c r="B462" t="inlineStr">
         <is>
-          <t>cbramod_pac</t>
+          <t>cbramod_crofremo</t>
         </is>
       </c>
       <c r="C462" t="inlineStr">
@@ -19186,7 +19201,7 @@
       </c>
       <c r="E462" t="inlineStr">
         <is>
-          <t>the workbook has no row for this variant</t>
+          <t>no row label for 'cbramod_crofremo'</t>
         </is>
       </c>
     </row>
@@ -19198,27 +19213,22 @@
       </c>
       <c r="B463" t="inlineStr">
         <is>
-          <t>cbramod_pretrained</t>
+          <t>cbramod_pac</t>
         </is>
       </c>
       <c r="C463" t="inlineStr">
         <is>
-          <t>[0, 1, 2]</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D463" t="inlineStr">
         <is>
-          <t>filled</t>
+          <t>skipped</t>
         </is>
       </c>
       <c r="E463" t="inlineStr">
         <is>
-          <t>[实测 9.85M] cohen_kappa per-seed 0:0.6658, 1:0.6743, 2:0.6742</t>
-        </is>
-      </c>
-      <c r="F463" t="inlineStr">
-        <is>
-          <t>lr=0.0001 batch_size=64 epochs=50 patience=0 eval_every_steps=0 loss=cross_entropy label_smoothing=0.1 grad_clip=1.0 multi_lr=True</t>
+          <t>the workbook has no row for this variant</t>
         </is>
       </c>
     </row>
@@ -19230,7 +19240,7 @@
       </c>
       <c r="B464" t="inlineStr">
         <is>
-          <t>cbramod_scratch</t>
+          <t>cbramod_pretrained</t>
         </is>
       </c>
       <c r="C464" t="inlineStr">
@@ -19245,7 +19255,7 @@
       </c>
       <c r="E464" t="inlineStr">
         <is>
-          <t>[实测 9.85M] cohen_kappa per-seed 0:0.6504, 1:0.6561, 2:0.6569</t>
+          <t>[实测 9.85M] cohen_kappa per-seed 0:0.6658, 1:0.6743, 2:0.6742</t>
         </is>
       </c>
       <c r="F464" t="inlineStr">
@@ -19262,7 +19272,7 @@
       </c>
       <c r="B465" t="inlineStr">
         <is>
-          <t>cnn_transformer</t>
+          <t>cbramod_scratch</t>
         </is>
       </c>
       <c r="C465" t="inlineStr">
@@ -19277,12 +19287,12 @@
       </c>
       <c r="E465" t="inlineStr">
         <is>
-          <t>[实测 3.15M] cohen_kappa per-seed 0:0.6871, 1:0.6614, 2:0.6850</t>
+          <t>[实测 9.85M] cohen_kappa per-seed 0:0.6504, 1:0.6561, 2:0.6569</t>
         </is>
       </c>
       <c r="F465" t="inlineStr">
         <is>
-          <t>lr=0.001 batch_size=512 epochs=60 patience=15 eval_every_steps=0 loss=cross_entropy label_smoothing=0.1</t>
+          <t>lr=0.0001 batch_size=64 epochs=50 patience=0 eval_every_steps=0 loss=cross_entropy label_smoothing=0.1 grad_clip=1.0 multi_lr=True</t>
         </is>
       </c>
     </row>
@@ -19294,7 +19304,7 @@
       </c>
       <c r="B466" t="inlineStr">
         <is>
-          <t>contrawr</t>
+          <t>cnn_transformer</t>
         </is>
       </c>
       <c r="C466" t="inlineStr">
@@ -19309,7 +19319,7 @@
       </c>
       <c r="E466" t="inlineStr">
         <is>
-          <t>[实测 1.56M] cohen_kappa per-seed 0:0.6752, 1:0.6964, 2:0.7031</t>
+          <t>[实测 3.15M] cohen_kappa per-seed 0:0.6871, 1:0.6614, 2:0.6850</t>
         </is>
       </c>
       <c r="F466" t="inlineStr">
@@ -19326,7 +19336,7 @@
       </c>
       <c r="B467" t="inlineStr">
         <is>
-          <t>eegpt_pretrained</t>
+          <t>contrawr</t>
         </is>
       </c>
       <c r="C467" t="inlineStr">
@@ -19341,12 +19351,12 @@
       </c>
       <c r="E467" t="inlineStr">
         <is>
-          <t>[实测 25.69M] cohen_kappa per-seed 0:0.6071, 1:0.5831, 2:0.6031</t>
+          <t>[实测 1.56M] cohen_kappa per-seed 0:0.6752, 1:0.6964, 2:0.7031</t>
         </is>
       </c>
       <c r="F467" t="inlineStr">
         <is>
-          <t>lr=0.0004 batch_size=32 epochs=40 patience=10 eval_every_steps=200 loss=cross_entropy</t>
+          <t>lr=0.001 batch_size=512 epochs=60 patience=15 eval_every_steps=0 loss=cross_entropy label_smoothing=0.1</t>
         </is>
       </c>
     </row>
@@ -19358,7 +19368,7 @@
       </c>
       <c r="B468" t="inlineStr">
         <is>
-          <t>ffcl</t>
+          <t>eegpt_pretrained</t>
         </is>
       </c>
       <c r="C468" t="inlineStr">
@@ -19373,12 +19383,12 @@
       </c>
       <c r="E468" t="inlineStr">
         <is>
-          <t>[实测 2.51M] cohen_kappa per-seed 0:0.6785, 1:0.6730, 2:0.6824</t>
+          <t>[实测 25.69M] cohen_kappa per-seed 0:0.6071, 1:0.5831, 2:0.6031</t>
         </is>
       </c>
       <c r="F468" t="inlineStr">
         <is>
-          <t>lr=0.001 batch_size=512 epochs=60 patience=15 eval_every_steps=0 loss=cross_entropy label_smoothing=0.1</t>
+          <t>lr=0.0004 batch_size=32 epochs=40 patience=10 eval_every_steps=200 loss=cross_entropy</t>
         </is>
       </c>
     </row>
@@ -19390,7 +19400,7 @@
       </c>
       <c r="B469" t="inlineStr">
         <is>
-          <t>labram_pretrained</t>
+          <t>ffcl</t>
         </is>
       </c>
       <c r="C469" t="inlineStr">
@@ -19405,12 +19415,12 @@
       </c>
       <c r="E469" t="inlineStr">
         <is>
-          <t>[实测 5.82M] cohen_kappa per-seed 0:0.6082, 1:0.6032, 2:0.6188</t>
+          <t>[实测 2.51M] cohen_kappa per-seed 0:0.6785, 1:0.6730, 2:0.6824</t>
         </is>
       </c>
       <c r="F469" t="inlineStr">
         <is>
-          <t>stopped_by=patience lr=0.0005 batch_size=64 epochs=50 patience=10 eval_every_steps=0 loss=cross_entropy label_smoothing=0.1 loader_divisor=1.0</t>
+          <t>lr=0.001 batch_size=512 epochs=60 patience=15 eval_every_steps=0 loss=cross_entropy label_smoothing=0.1</t>
         </is>
       </c>
     </row>
@@ -19422,7 +19432,7 @@
       </c>
       <c r="B470" t="inlineStr">
         <is>
-          <t>labram_scratch</t>
+          <t>labram_pretrained</t>
         </is>
       </c>
       <c r="C470" t="inlineStr">
@@ -19437,7 +19447,7 @@
       </c>
       <c r="E470" t="inlineStr">
         <is>
-          <t>[实测 5.82M] cohen_kappa per-seed 0:0.6094, 1:0.5932, 2:0.5915</t>
+          <t>[实测 5.82M] cohen_kappa per-seed 0:0.6082, 1:0.6032, 2:0.6188</t>
         </is>
       </c>
       <c r="F470" t="inlineStr">
@@ -19454,22 +19464,27 @@
       </c>
       <c r="B471" t="inlineStr">
         <is>
-          <t>paclock_duplex</t>
+          <t>labram_scratch</t>
         </is>
       </c>
       <c r="C471" t="inlineStr">
         <is>
-          <t>[0]</t>
+          <t>[0, 1, 2]</t>
         </is>
       </c>
       <c r="D471" t="inlineStr">
         <is>
-          <t>filled (single-seed, grey)</t>
+          <t>filled</t>
         </is>
       </c>
       <c r="E471" t="inlineStr">
         <is>
-          <t>cohen_kappa 0.6533</t>
+          <t>[实测 5.82M] cohen_kappa per-seed 0:0.6094, 1:0.5932, 2:0.5915</t>
+        </is>
+      </c>
+      <c r="F471" t="inlineStr">
+        <is>
+          <t>stopped_by=patience lr=0.0005 batch_size=64 epochs=50 patience=10 eval_every_steps=0 loss=cross_entropy label_smoothing=0.1 loader_divisor=1.0</t>
         </is>
       </c>
     </row>
@@ -19481,22 +19496,22 @@
       </c>
       <c r="B472" t="inlineStr">
         <is>
-          <t>paclock_duplex_pt</t>
+          <t>paclock_duplex</t>
         </is>
       </c>
       <c r="C472" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>[0]</t>
         </is>
       </c>
       <c r="D472" t="inlineStr">
         <is>
-          <t>skipped</t>
+          <t>filled (single-seed, grey)</t>
         </is>
       </c>
       <c r="E472" t="inlineStr">
         <is>
-          <t>row 'PACLock (duplex, pretrained)' not found</t>
+          <t>cohen_kappa 0.6533</t>
         </is>
       </c>
     </row>
@@ -19508,22 +19523,22 @@
       </c>
       <c r="B473" t="inlineStr">
         <is>
-          <t>paclock_duplex_pt2</t>
+          <t>paclock_duplex_pt</t>
         </is>
       </c>
       <c r="C473" t="inlineStr">
         <is>
-          <t>[0]</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D473" t="inlineStr">
         <is>
-          <t>filled (single-seed, grey)</t>
+          <t>skipped</t>
         </is>
       </c>
       <c r="E473" t="inlineStr">
         <is>
-          <t>cohen_kappa 0.6775</t>
+          <t>row 'PACLock (duplex, pretrained)' not found</t>
         </is>
       </c>
     </row>
@@ -19535,7 +19550,7 @@
       </c>
       <c r="B474" t="inlineStr">
         <is>
-          <t>paclock_duplex_pt3</t>
+          <t>paclock_duplex_pt2</t>
         </is>
       </c>
       <c r="C474" t="inlineStr">
@@ -19550,7 +19565,7 @@
       </c>
       <c r="E474" t="inlineStr">
         <is>
-          <t>cohen_kappa 0.6664</t>
+          <t>cohen_kappa 0.6775</t>
         </is>
       </c>
     </row>
@@ -19562,22 +19577,22 @@
       </c>
       <c r="B475" t="inlineStr">
         <is>
-          <t>paclock_duplex_ptF</t>
+          <t>paclock_duplex_pt3</t>
         </is>
       </c>
       <c r="C475" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>[0]</t>
         </is>
       </c>
       <c r="D475" t="inlineStr">
         <is>
-          <t>skipped</t>
+          <t>filled (single-seed, grey)</t>
         </is>
       </c>
       <c r="E475" t="inlineStr">
         <is>
-          <t>row 'CroFreMo (预训练 v2-full)' not found</t>
+          <t>cohen_kappa 0.6664</t>
         </is>
       </c>
     </row>
@@ -19589,22 +19604,22 @@
       </c>
       <c r="B476" t="inlineStr">
         <is>
-          <t>paclock_duplex_ptS</t>
+          <t>paclock_duplex_ptF</t>
         </is>
       </c>
       <c r="C476" t="inlineStr">
         <is>
-          <t>[0]</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D476" t="inlineStr">
         <is>
-          <t>filled (single-seed, grey)</t>
+          <t>skipped</t>
         </is>
       </c>
       <c r="E476" t="inlineStr">
         <is>
-          <t>cohen_kappa 0.6747</t>
+          <t>row 'CroFreMo (预训练 v2-full)' not found</t>
         </is>
       </c>
     </row>
@@ -19616,22 +19631,22 @@
       </c>
       <c r="B477" t="inlineStr">
         <is>
-          <t>paclock_pac</t>
+          <t>paclock_duplex_ptS</t>
         </is>
       </c>
       <c r="C477" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>[0]</t>
         </is>
       </c>
       <c r="D477" t="inlineStr">
         <is>
-          <t>skipped</t>
+          <t>filled (single-seed, grey)</t>
         </is>
       </c>
       <c r="E477" t="inlineStr">
         <is>
-          <t>the workbook has no row for this variant</t>
+          <t>cohen_kappa 0.6747</t>
         </is>
       </c>
     </row>
@@ -19643,7 +19658,7 @@
       </c>
       <c r="B478" t="inlineStr">
         <is>
-          <t>paclock_pt_base</t>
+          <t>paclock_pac</t>
         </is>
       </c>
       <c r="C478" t="inlineStr">
@@ -19658,7 +19673,7 @@
       </c>
       <c r="E478" t="inlineStr">
         <is>
-          <t>row 'PACLock (pretrained, base)' not found</t>
+          <t>the workbook has no row for this variant</t>
         </is>
       </c>
     </row>
@@ -19670,7 +19685,7 @@
       </c>
       <c r="B479" t="inlineStr">
         <is>
-          <t>paclock_pt_large</t>
+          <t>paclock_pt_base</t>
         </is>
       </c>
       <c r="C479" t="inlineStr">
@@ -19685,7 +19700,7 @@
       </c>
       <c r="E479" t="inlineStr">
         <is>
-          <t>row 'PACLock (pretrained, large)' not found</t>
+          <t>row 'PACLock (pretrained, base)' not found</t>
         </is>
       </c>
     </row>
@@ -19697,7 +19712,7 @@
       </c>
       <c r="B480" t="inlineStr">
         <is>
-          <t>paclock_rawtok</t>
+          <t>paclock_pt_large</t>
         </is>
       </c>
       <c r="C480" t="inlineStr">
@@ -19712,7 +19727,7 @@
       </c>
       <c r="E480" t="inlineStr">
         <is>
-          <t>no row label for 'paclock_rawtok'</t>
+          <t>row 'PACLock (pretrained, large)' not found</t>
         </is>
       </c>
     </row>
@@ -19724,7 +19739,7 @@
       </c>
       <c r="B481" t="inlineStr">
         <is>
-          <t>paclock_rot2</t>
+          <t>paclock_rawtok</t>
         </is>
       </c>
       <c r="C481" t="inlineStr">
@@ -19739,7 +19754,7 @@
       </c>
       <c r="E481" t="inlineStr">
         <is>
-          <t>no row label for 'paclock_rot2'</t>
+          <t>no row label for 'paclock_rawtok'</t>
         </is>
       </c>
     </row>
@@ -19751,7 +19766,7 @@
       </c>
       <c r="B482" t="inlineStr">
         <is>
-          <t>paclock_tune_t1</t>
+          <t>paclock_rot2</t>
         </is>
       </c>
       <c r="C482" t="inlineStr">
@@ -19766,7 +19781,7 @@
       </c>
       <c r="E482" t="inlineStr">
         <is>
-          <t>no row label for 'paclock_tune_t1'</t>
+          <t>no row label for 'paclock_rot2'</t>
         </is>
       </c>
     </row>
@@ -19778,7 +19793,7 @@
       </c>
       <c r="B483" t="inlineStr">
         <is>
-          <t>paclock_tune_t2</t>
+          <t>paclock_tune_t1</t>
         </is>
       </c>
       <c r="C483" t="inlineStr">
@@ -19793,7 +19808,7 @@
       </c>
       <c r="E483" t="inlineStr">
         <is>
-          <t>no row label for 'paclock_tune_t2'</t>
+          <t>no row label for 'paclock_tune_t1'</t>
         </is>
       </c>
     </row>
@@ -19805,7 +19820,7 @@
       </c>
       <c r="B484" t="inlineStr">
         <is>
-          <t>paclock_v2</t>
+          <t>paclock_tune_t2</t>
         </is>
       </c>
       <c r="C484" t="inlineStr">
@@ -19820,7 +19835,7 @@
       </c>
       <c r="E484" t="inlineStr">
         <is>
-          <t>row 'PACLock (from scratch, full)' not found</t>
+          <t>no row label for 'paclock_tune_t2'</t>
         </is>
       </c>
     </row>
@@ -19832,27 +19847,22 @@
       </c>
       <c r="B485" t="inlineStr">
         <is>
-          <t>sparcnet</t>
+          <t>paclock_v2</t>
         </is>
       </c>
       <c r="C485" t="inlineStr">
         <is>
-          <t>[0, 1, 2]</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D485" t="inlineStr">
         <is>
-          <t>filled</t>
+          <t>skipped</t>
         </is>
       </c>
       <c r="E485" t="inlineStr">
         <is>
-          <t>[实测 1.23M] cohen_kappa per-seed 0:0.6662, 1:0.6848, 2:0.6632</t>
-        </is>
-      </c>
-      <c r="F485" t="inlineStr">
-        <is>
-          <t>lr=0.001 batch_size=512 epochs=60 patience=15 eval_every_steps=0 loss=cross_entropy label_smoothing=0.1</t>
+          <t>row 'PACLock (from scratch, full)' not found</t>
         </is>
       </c>
     </row>
@@ -19864,7 +19874,7 @@
       </c>
       <c r="B486" t="inlineStr">
         <is>
-          <t>st_transformer</t>
+          <t>sparcnet</t>
         </is>
       </c>
       <c r="C486" t="inlineStr">
@@ -19879,7 +19889,7 @@
       </c>
       <c r="E486" t="inlineStr">
         <is>
-          <t>[实测 3.41M] cohen_kappa per-seed 0:0.6508, 1:0.6570, 2:0.6581</t>
+          <t>[实测 1.23M] cohen_kappa per-seed 0:0.6662, 1:0.6848, 2:0.6632</t>
         </is>
       </c>
       <c r="F486" t="inlineStr">
@@ -19896,7 +19906,7 @@
       </c>
       <c r="B487" t="inlineStr">
         <is>
-          <t>tfm_pretrained</t>
+          <t>st_transformer</t>
         </is>
       </c>
       <c r="C487" t="inlineStr">
@@ -19911,24 +19921,24 @@
       </c>
       <c r="E487" t="inlineStr">
         <is>
-          <t>[实测 1.89M] cohen_kappa per-seed 0:0.6165, 1:0.6126, 2:0.6122</t>
+          <t>[实测 3.41M] cohen_kappa per-seed 0:0.6508, 1:0.6570, 2:0.6581</t>
         </is>
       </c>
       <c r="F487" t="inlineStr">
         <is>
-          <t>lr=0.001 batch_size=512 epochs=50 patience=10 eval_every_steps=0 loss=cross_entropy label_smoothing=0.1</t>
+          <t>lr=0.001 batch_size=512 epochs=60 patience=15 eval_every_steps=0 loss=cross_entropy label_smoothing=0.1</t>
         </is>
       </c>
     </row>
     <row r="488">
       <c r="A488" t="inlineStr">
         <is>
-          <t>tuab</t>
+          <t>sleepedf</t>
         </is>
       </c>
       <c r="B488" t="inlineStr">
         <is>
-          <t>biot_prest16</t>
+          <t>tfm_pretrained</t>
         </is>
       </c>
       <c r="C488" t="inlineStr">
@@ -19943,12 +19953,12 @@
       </c>
       <c r="E488" t="inlineStr">
         <is>
-          <t>[实测 3.19M] auroc per-seed 0:0.8750, 1:0.8692, 2:0.8747</t>
+          <t>[实测 1.89M] cohen_kappa per-seed 0:0.6165, 1:0.6126, 2:0.6122</t>
         </is>
       </c>
       <c r="F488" t="inlineStr">
         <is>
-          <t>lr=0.001 batch_size=512 epochs=100 patience=5 eval_every_steps=0 loss=bce_with_logits</t>
+          <t>lr=0.001 batch_size=512 epochs=50 patience=10 eval_every_steps=0 loss=cross_entropy label_smoothing=0.1</t>
         </is>
       </c>
     </row>
@@ -19960,7 +19970,7 @@
       </c>
       <c r="B489" t="inlineStr">
         <is>
-          <t>biot_scratch</t>
+          <t>biot_prest16</t>
         </is>
       </c>
       <c r="C489" t="inlineStr">
@@ -19975,7 +19985,7 @@
       </c>
       <c r="E489" t="inlineStr">
         <is>
-          <t>[实测 3.19M] auroc per-seed 0:0.8658, 1:0.8761, 2:0.8665</t>
+          <t>[实测 3.19M] auroc per-seed 0:0.8750, 1:0.8692, 2:0.8747</t>
         </is>
       </c>
       <c r="F489" t="inlineStr">
@@ -19992,22 +20002,27 @@
       </c>
       <c r="B490" t="inlineStr">
         <is>
-          <t>cbramod_crofremo</t>
+          <t>biot_scratch</t>
         </is>
       </c>
       <c r="C490" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>[0, 1, 2]</t>
         </is>
       </c>
       <c r="D490" t="inlineStr">
         <is>
-          <t>skipped</t>
+          <t>filled</t>
         </is>
       </c>
       <c r="E490" t="inlineStr">
         <is>
-          <t>no row label for 'cbramod_crofremo'</t>
+          <t>[实测 3.19M] auroc per-seed 0:0.8658, 1:0.8761, 2:0.8665</t>
+        </is>
+      </c>
+      <c r="F490" t="inlineStr">
+        <is>
+          <t>lr=0.001 batch_size=512 epochs=100 patience=5 eval_every_steps=0 loss=bce_with_logits</t>
         </is>
       </c>
     </row>
@@ -20019,7 +20034,7 @@
       </c>
       <c r="B491" t="inlineStr">
         <is>
-          <t>cbramod_pac</t>
+          <t>cbramod_crofremo</t>
         </is>
       </c>
       <c r="C491" t="inlineStr">
@@ -20034,7 +20049,7 @@
       </c>
       <c r="E491" t="inlineStr">
         <is>
-          <t>the workbook has no row for this variant</t>
+          <t>no row label for 'cbramod_crofremo'</t>
         </is>
       </c>
     </row>
@@ -20046,27 +20061,22 @@
       </c>
       <c r="B492" t="inlineStr">
         <is>
-          <t>cbramod_pretrained</t>
+          <t>cbramod_pac</t>
         </is>
       </c>
       <c r="C492" t="inlineStr">
         <is>
-          <t>[0, 1, 2]</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D492" t="inlineStr">
         <is>
-          <t>filled</t>
+          <t>skipped</t>
         </is>
       </c>
       <c r="E492" t="inlineStr">
         <is>
-          <t>[实测 30.65M] auroc per-seed 0:0.8586, 1:0.8584, 2:0.8744</t>
-        </is>
-      </c>
-      <c r="F492" t="inlineStr">
-        <is>
-          <t>lr=0.0001 batch_size=64 epochs=50 patience=0 eval_every_steps=0 loss=bce_with_logits grad_clip=1.0 select_metric=auroc multi_lr=True</t>
+          <t>the workbook has no row for this variant</t>
         </is>
       </c>
     </row>
@@ -20078,7 +20088,7 @@
       </c>
       <c r="B493" t="inlineStr">
         <is>
-          <t>cbramod_scratch</t>
+          <t>cbramod_pretrained</t>
         </is>
       </c>
       <c r="C493" t="inlineStr">
@@ -20093,7 +20103,7 @@
       </c>
       <c r="E493" t="inlineStr">
         <is>
-          <t>[实测 30.65M] auroc per-seed 0:0.8727, 1:0.8789, 2:0.8771</t>
+          <t>[实测 30.65M] auroc per-seed 0:0.8586, 1:0.8584, 2:0.8744</t>
         </is>
       </c>
       <c r="F493" t="inlineStr">
@@ -20110,7 +20120,7 @@
       </c>
       <c r="B494" t="inlineStr">
         <is>
-          <t>cnn_transformer</t>
+          <t>cbramod_scratch</t>
         </is>
       </c>
       <c r="C494" t="inlineStr">
@@ -20125,12 +20135,12 @@
       </c>
       <c r="E494" t="inlineStr">
         <is>
-          <t>[实测 3.15M] auroc per-seed 0:0.8910, 1:0.8972, 2:0.8858</t>
+          <t>[实测 30.65M] auroc per-seed 0:0.8727, 1:0.8789, 2:0.8771</t>
         </is>
       </c>
       <c r="F494" t="inlineStr">
         <is>
-          <t>lr=0.001 batch_size=512 epochs=20 patience=8 eval_every_steps=200 loss=bce_with_logits</t>
+          <t>lr=0.0001 batch_size=64 epochs=50 patience=0 eval_every_steps=0 loss=bce_with_logits grad_clip=1.0 select_metric=auroc multi_lr=True</t>
         </is>
       </c>
     </row>
@@ -20142,7 +20152,7 @@
       </c>
       <c r="B495" t="inlineStr">
         <is>
-          <t>contrawr</t>
+          <t>cnn_transformer</t>
         </is>
       </c>
       <c r="C495" t="inlineStr">
@@ -20157,7 +20167,7 @@
       </c>
       <c r="E495" t="inlineStr">
         <is>
-          <t>[实测 1.57M] auroc per-seed 0:0.8849, 1:0.8839, 2:0.8969</t>
+          <t>[实测 3.15M] auroc per-seed 0:0.8910, 1:0.8972, 2:0.8858</t>
         </is>
       </c>
       <c r="F495" t="inlineStr">
@@ -20174,7 +20184,7 @@
       </c>
       <c r="B496" t="inlineStr">
         <is>
-          <t>csbrain_pretrained</t>
+          <t>contrawr</t>
         </is>
       </c>
       <c r="C496" t="inlineStr">
@@ -20189,12 +20199,12 @@
       </c>
       <c r="E496" t="inlineStr">
         <is>
-          <t>[实测 41.06M] auroc per-seed 0:0.8890, 1:0.8935, 2:0.9005</t>
+          <t>[实测 1.57M] auroc per-seed 0:0.8849, 1:0.8839, 2:0.8969</t>
         </is>
       </c>
       <c r="F496" t="inlineStr">
         <is>
-          <t>stopped_by=patience lr=0.0001 batch_size=64 epochs=25 patience=10 eval_every_steps=500 loss=bce_with_logits grad_clip=1.0</t>
+          <t>lr=0.001 batch_size=512 epochs=20 patience=8 eval_every_steps=200 loss=bce_with_logits</t>
         </is>
       </c>
     </row>
@@ -20206,7 +20216,7 @@
       </c>
       <c r="B497" t="inlineStr">
         <is>
-          <t>eegconformer</t>
+          <t>csbrain_pretrained</t>
         </is>
       </c>
       <c r="C497" t="inlineStr">
@@ -20221,12 +20231,12 @@
       </c>
       <c r="E497" t="inlineStr">
         <is>
-          <t>[实测 1.46M] auroc per-seed 0:0.8843, 1:0.8828, 2:0.8813</t>
+          <t>[实测 41.06M] auroc per-seed 0:0.8890, 1:0.8935, 2:0.9005</t>
         </is>
       </c>
       <c r="F497" t="inlineStr">
         <is>
-          <t>stopped_by=patience lr=0.0003 batch_size=128 epochs=20 patience=8 eval_every_steps=200 loss=bce_with_logits grad_clip=1.0</t>
+          <t>stopped_by=patience lr=0.0001 batch_size=64 epochs=25 patience=10 eval_every_steps=500 loss=bce_with_logits grad_clip=1.0</t>
         </is>
       </c>
     </row>
@@ -20238,22 +20248,27 @@
       </c>
       <c r="B498" t="inlineStr">
         <is>
-          <t>eegconformer_t1</t>
+          <t>eegconformer</t>
         </is>
       </c>
       <c r="C498" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>[0, 1, 2]</t>
         </is>
       </c>
       <c r="D498" t="inlineStr">
         <is>
-          <t>skipped</t>
+          <t>filled</t>
         </is>
       </c>
       <c r="E498" t="inlineStr">
         <is>
-          <t>no row label for 'eegconformer_t1'</t>
+          <t>[实测 1.46M] auroc per-seed 0:0.8843, 1:0.8828, 2:0.8813</t>
+        </is>
+      </c>
+      <c r="F498" t="inlineStr">
+        <is>
+          <t>stopped_by=patience lr=0.0003 batch_size=128 epochs=20 patience=8 eval_every_steps=200 loss=bce_with_logits grad_clip=1.0</t>
         </is>
       </c>
     </row>
@@ -20265,7 +20280,7 @@
       </c>
       <c r="B499" t="inlineStr">
         <is>
-          <t>eegconformer_t2</t>
+          <t>eegconformer_t1</t>
         </is>
       </c>
       <c r="C499" t="inlineStr">
@@ -20280,7 +20295,7 @@
       </c>
       <c r="E499" t="inlineStr">
         <is>
-          <t>no row label for 'eegconformer_t2'</t>
+          <t>no row label for 'eegconformer_t1'</t>
         </is>
       </c>
     </row>
@@ -20292,7 +20307,7 @@
       </c>
       <c r="B500" t="inlineStr">
         <is>
-          <t>eegconformer_t3</t>
+          <t>eegconformer_t2</t>
         </is>
       </c>
       <c r="C500" t="inlineStr">
@@ -20307,7 +20322,7 @@
       </c>
       <c r="E500" t="inlineStr">
         <is>
-          <t>no row label for 'eegconformer_t3'</t>
+          <t>no row label for 'eegconformer_t2'</t>
         </is>
       </c>
     </row>
@@ -20319,7 +20334,7 @@
       </c>
       <c r="B501" t="inlineStr">
         <is>
-          <t>eegconformer_t4</t>
+          <t>eegconformer_t3</t>
         </is>
       </c>
       <c r="C501" t="inlineStr">
@@ -20334,7 +20349,7 @@
       </c>
       <c r="E501" t="inlineStr">
         <is>
-          <t>no row label for 'eegconformer_t4'</t>
+          <t>no row label for 'eegconformer_t3'</t>
         </is>
       </c>
     </row>
@@ -20346,27 +20361,22 @@
       </c>
       <c r="B502" t="inlineStr">
         <is>
-          <t>eegnet</t>
+          <t>eegconformer_t4</t>
         </is>
       </c>
       <c r="C502" t="inlineStr">
         <is>
-          <t>[0, 1, 2]</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D502" t="inlineStr">
         <is>
-          <t>filled</t>
+          <t>skipped</t>
         </is>
       </c>
       <c r="E502" t="inlineStr">
         <is>
-          <t>[实测 0.00M] auroc per-seed 0:0.8551, 1:0.8535, 2:0.8471</t>
-        </is>
-      </c>
-      <c r="F502" t="inlineStr">
-        <is>
-          <t>stopped_by=patience lr=0.001 batch_size=512 epochs=20 patience=8 eval_every_steps=200 loss=bce_with_logits grad_clip=1.0</t>
+          <t>no row label for 'eegconformer_t4'</t>
         </is>
       </c>
     </row>
@@ -20378,22 +20388,27 @@
       </c>
       <c r="B503" t="inlineStr">
         <is>
-          <t>eegnet_t1</t>
+          <t>eegnet</t>
         </is>
       </c>
       <c r="C503" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>[0, 1, 2]</t>
         </is>
       </c>
       <c r="D503" t="inlineStr">
         <is>
-          <t>skipped</t>
+          <t>filled</t>
         </is>
       </c>
       <c r="E503" t="inlineStr">
         <is>
-          <t>no row label for 'eegnet_t1'</t>
+          <t>[实测 0.00M] auroc per-seed 0:0.8551, 1:0.8535, 2:0.8471</t>
+        </is>
+      </c>
+      <c r="F503" t="inlineStr">
+        <is>
+          <t>stopped_by=patience lr=0.001 batch_size=512 epochs=20 patience=8 eval_every_steps=200 loss=bce_with_logits grad_clip=1.0</t>
         </is>
       </c>
     </row>
@@ -20405,7 +20420,7 @@
       </c>
       <c r="B504" t="inlineStr">
         <is>
-          <t>eegnet_t2</t>
+          <t>eegnet_t1</t>
         </is>
       </c>
       <c r="C504" t="inlineStr">
@@ -20420,7 +20435,7 @@
       </c>
       <c r="E504" t="inlineStr">
         <is>
-          <t>no row label for 'eegnet_t2'</t>
+          <t>no row label for 'eegnet_t1'</t>
         </is>
       </c>
     </row>
@@ -20432,7 +20447,7 @@
       </c>
       <c r="B505" t="inlineStr">
         <is>
-          <t>eegnet_t3</t>
+          <t>eegnet_t2</t>
         </is>
       </c>
       <c r="C505" t="inlineStr">
@@ -20447,7 +20462,7 @@
       </c>
       <c r="E505" t="inlineStr">
         <is>
-          <t>no row label for 'eegnet_t3'</t>
+          <t>no row label for 'eegnet_t2'</t>
         </is>
       </c>
     </row>
@@ -20459,7 +20474,7 @@
       </c>
       <c r="B506" t="inlineStr">
         <is>
-          <t>eegnet_t4</t>
+          <t>eegnet_t3</t>
         </is>
       </c>
       <c r="C506" t="inlineStr">
@@ -20474,7 +20489,7 @@
       </c>
       <c r="E506" t="inlineStr">
         <is>
-          <t>no row label for 'eegnet_t4'</t>
+          <t>no row label for 'eegnet_t3'</t>
         </is>
       </c>
     </row>
@@ -20486,27 +20501,22 @@
       </c>
       <c r="B507" t="inlineStr">
         <is>
-          <t>eegpt_pretrained</t>
+          <t>eegnet_t4</t>
         </is>
       </c>
       <c r="C507" t="inlineStr">
         <is>
-          <t>[0, 1, 2]</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D507" t="inlineStr">
         <is>
-          <t>filled</t>
+          <t>skipped</t>
         </is>
       </c>
       <c r="E507" t="inlineStr">
         <is>
-          <t>[实测 25.69M] auroc per-seed 0:0.9046, 1:0.8981, 2:0.9057</t>
-        </is>
-      </c>
-      <c r="F507" t="inlineStr">
-        <is>
-          <t>lr=0.0004 batch_size=32 epochs=40 patience=10 eval_every_steps=200 loss=bce_with_logits</t>
+          <t>no row label for 'eegnet_t4'</t>
         </is>
       </c>
     </row>
@@ -20518,7 +20528,7 @@
       </c>
       <c r="B508" t="inlineStr">
         <is>
-          <t>feat_best</t>
+          <t>eegpt_pretrained</t>
         </is>
       </c>
       <c r="C508" t="inlineStr">
@@ -20533,12 +20543,12 @@
       </c>
       <c r="E508" t="inlineStr">
         <is>
-          <t>[实测 0.00M] auroc per-seed 0:0.8248, 1:0.8248, 2:0.8248</t>
+          <t>[实测 25.69M] auroc per-seed 0:0.9046, 1:0.8981, 2:0.9057</t>
         </is>
       </c>
       <c r="F508" t="inlineStr">
         <is>
-          <t>stopped_by=closed-form epochs=1 loss=closed-form</t>
+          <t>lr=0.0004 batch_size=32 epochs=40 patience=10 eval_every_steps=200 loss=bce_with_logits</t>
         </is>
       </c>
     </row>
@@ -20550,7 +20560,7 @@
       </c>
       <c r="B509" t="inlineStr">
         <is>
-          <t>ffcl</t>
+          <t>feat_best</t>
         </is>
       </c>
       <c r="C509" t="inlineStr">
@@ -20565,12 +20575,12 @@
       </c>
       <c r="E509" t="inlineStr">
         <is>
-          <t>[实测 2.46M] auroc per-seed 0:0.8896, 1:0.8929, 2:0.8769</t>
+          <t>[实测 0.00M] auroc per-seed 0:0.8248, 1:0.8248, 2:0.8248</t>
         </is>
       </c>
       <c r="F509" t="inlineStr">
         <is>
-          <t>lr=0.001 batch_size=512 epochs=20 patience=8 eval_every_steps=200 loss=bce_with_logits</t>
+          <t>stopped_by=closed-form epochs=1 loss=closed-form</t>
         </is>
       </c>
     </row>
@@ -20582,7 +20592,7 @@
       </c>
       <c r="B510" t="inlineStr">
         <is>
-          <t>labram_pretrained</t>
+          <t>ffcl</t>
         </is>
       </c>
       <c r="C510" t="inlineStr">
@@ -20597,12 +20607,12 @@
       </c>
       <c r="E510" t="inlineStr">
         <is>
-          <t>[实测 5.82M] auroc per-seed 0:0.8750, 1:0.8748, 2:0.8811</t>
+          <t>[实测 2.46M] auroc per-seed 0:0.8896, 1:0.8929, 2:0.8769</t>
         </is>
       </c>
       <c r="F510" t="inlineStr">
         <is>
-          <t>lr=0.0005 batch_size=64 epochs=50 patience=10 eval_every_steps=0 loss=bce_with_logits</t>
+          <t>lr=0.001 batch_size=512 epochs=20 patience=8 eval_every_steps=200 loss=bce_with_logits</t>
         </is>
       </c>
     </row>
@@ -20614,7 +20624,7 @@
       </c>
       <c r="B511" t="inlineStr">
         <is>
-          <t>labram_scratch</t>
+          <t>labram_pretrained</t>
         </is>
       </c>
       <c r="C511" t="inlineStr">
@@ -20629,12 +20639,12 @@
       </c>
       <c r="E511" t="inlineStr">
         <is>
-          <t>[实测 5.82M] auroc per-seed 0:0.8617, 1:0.8682, 2:0.8543</t>
+          <t>[实测 5.82M] auroc per-seed 0:0.8750, 1:0.8748, 2:0.8811</t>
         </is>
       </c>
       <c r="F511" t="inlineStr">
         <is>
-          <t>stopped_by=patience lr=0.0005 batch_size=64 epochs=50 patience=10 eval_every_steps=0 loss=bce_with_logits</t>
+          <t>lr=0.0005 batch_size=64 epochs=50 patience=10 eval_every_steps=0 loss=bce_with_logits</t>
         </is>
       </c>
     </row>
@@ -20646,22 +20656,27 @@
       </c>
       <c r="B512" t="inlineStr">
         <is>
-          <t>paclock_duplex</t>
+          <t>labram_scratch</t>
         </is>
       </c>
       <c r="C512" t="inlineStr">
         <is>
-          <t>[0]</t>
+          <t>[0, 1, 2]</t>
         </is>
       </c>
       <c r="D512" t="inlineStr">
         <is>
-          <t>filled (single-seed, grey)</t>
+          <t>filled</t>
         </is>
       </c>
       <c r="E512" t="inlineStr">
         <is>
-          <t>auroc 0.8829</t>
+          <t>[实测 5.82M] auroc per-seed 0:0.8617, 1:0.8682, 2:0.8543</t>
+        </is>
+      </c>
+      <c r="F512" t="inlineStr">
+        <is>
+          <t>stopped_by=patience lr=0.0005 batch_size=64 epochs=50 patience=10 eval_every_steps=0 loss=bce_with_logits</t>
         </is>
       </c>
     </row>
@@ -20673,22 +20688,22 @@
       </c>
       <c r="B513" t="inlineStr">
         <is>
-          <t>paclock_duplex_pt</t>
+          <t>paclock_duplex</t>
         </is>
       </c>
       <c r="C513" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>[0]</t>
         </is>
       </c>
       <c r="D513" t="inlineStr">
         <is>
-          <t>skipped</t>
+          <t>filled (single-seed, grey)</t>
         </is>
       </c>
       <c r="E513" t="inlineStr">
         <is>
-          <t>row 'PACLock (duplex, pretrained)' not found</t>
+          <t>auroc 0.8829</t>
         </is>
       </c>
     </row>
@@ -20700,22 +20715,22 @@
       </c>
       <c r="B514" t="inlineStr">
         <is>
-          <t>paclock_duplex_pt2</t>
+          <t>paclock_duplex_pt</t>
         </is>
       </c>
       <c r="C514" t="inlineStr">
         <is>
-          <t>[0]</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D514" t="inlineStr">
         <is>
-          <t>filled (single-seed, grey)</t>
+          <t>skipped</t>
         </is>
       </c>
       <c r="E514" t="inlineStr">
         <is>
-          <t>auroc 0.8938</t>
+          <t>row 'PACLock (duplex, pretrained)' not found</t>
         </is>
       </c>
     </row>
@@ -20727,22 +20742,22 @@
       </c>
       <c r="B515" t="inlineStr">
         <is>
-          <t>paclock_duplex_ptF</t>
+          <t>paclock_duplex_pt2</t>
         </is>
       </c>
       <c r="C515" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>[0]</t>
         </is>
       </c>
       <c r="D515" t="inlineStr">
         <is>
-          <t>skipped</t>
+          <t>filled (single-seed, grey)</t>
         </is>
       </c>
       <c r="E515" t="inlineStr">
         <is>
-          <t>row 'CroFreMo (预训练 v2-full)' not found</t>
+          <t>auroc 0.8938</t>
         </is>
       </c>
     </row>
@@ -20754,22 +20769,22 @@
       </c>
       <c r="B516" t="inlineStr">
         <is>
-          <t>paclock_duplex_ptS</t>
+          <t>paclock_duplex_ptF</t>
         </is>
       </c>
       <c r="C516" t="inlineStr">
         <is>
-          <t>[0]</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D516" t="inlineStr">
         <is>
-          <t>filled (single-seed, grey)</t>
+          <t>skipped</t>
         </is>
       </c>
       <c r="E516" t="inlineStr">
         <is>
-          <t>auroc 0.8892</t>
+          <t>row 'CroFreMo (预训练 v2-full)' not found</t>
         </is>
       </c>
     </row>
@@ -20781,22 +20796,22 @@
       </c>
       <c r="B517" t="inlineStr">
         <is>
-          <t>paclock_pt_base</t>
+          <t>paclock_duplex_ptS</t>
         </is>
       </c>
       <c r="C517" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>[0]</t>
         </is>
       </c>
       <c r="D517" t="inlineStr">
         <is>
-          <t>skipped</t>
+          <t>filled (single-seed, grey)</t>
         </is>
       </c>
       <c r="E517" t="inlineStr">
         <is>
-          <t>row 'PACLock (pretrained, base)' not found</t>
+          <t>auroc 0.8892</t>
         </is>
       </c>
     </row>
@@ -20808,7 +20823,7 @@
       </c>
       <c r="B518" t="inlineStr">
         <is>
-          <t>paclock_pt_large</t>
+          <t>paclock_pt_base</t>
         </is>
       </c>
       <c r="C518" t="inlineStr">
@@ -20823,7 +20838,7 @@
       </c>
       <c r="E518" t="inlineStr">
         <is>
-          <t>row 'PACLock (pretrained, large)' not found</t>
+          <t>row 'PACLock (pretrained, base)' not found</t>
         </is>
       </c>
     </row>
@@ -20835,7 +20850,7 @@
       </c>
       <c r="B519" t="inlineStr">
         <is>
-          <t>paclock_rawtok</t>
+          <t>paclock_pt_large</t>
         </is>
       </c>
       <c r="C519" t="inlineStr">
@@ -20850,7 +20865,7 @@
       </c>
       <c r="E519" t="inlineStr">
         <is>
-          <t>no row label for 'paclock_rawtok'</t>
+          <t>row 'PACLock (pretrained, large)' not found</t>
         </is>
       </c>
     </row>
@@ -20862,7 +20877,7 @@
       </c>
       <c r="B520" t="inlineStr">
         <is>
-          <t>paclock_rot2</t>
+          <t>paclock_rawtok</t>
         </is>
       </c>
       <c r="C520" t="inlineStr">
@@ -20877,7 +20892,7 @@
       </c>
       <c r="E520" t="inlineStr">
         <is>
-          <t>no row label for 'paclock_rot2'</t>
+          <t>no row label for 'paclock_rawtok'</t>
         </is>
       </c>
     </row>
@@ -20889,7 +20904,7 @@
       </c>
       <c r="B521" t="inlineStr">
         <is>
-          <t>paclock_v2</t>
+          <t>paclock_rot2</t>
         </is>
       </c>
       <c r="C521" t="inlineStr">
@@ -20904,7 +20919,7 @@
       </c>
       <c r="E521" t="inlineStr">
         <is>
-          <t>row 'PACLock (from scratch, full)' not found</t>
+          <t>no row label for 'paclock_rot2'</t>
         </is>
       </c>
     </row>
@@ -20916,27 +20931,22 @@
       </c>
       <c r="B522" t="inlineStr">
         <is>
-          <t>reve_pretrained</t>
+          <t>paclock_v2</t>
         </is>
       </c>
       <c r="C522" t="inlineStr">
         <is>
-          <t>[0, 1, 2]</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D522" t="inlineStr">
         <is>
-          <t>filled</t>
+          <t>skipped</t>
         </is>
       </c>
       <c r="E522" t="inlineStr">
         <is>
-          <t>[实测 69.46M] auroc per-seed 0:0.9037, 1:0.8950, 2:0.8848</t>
-        </is>
-      </c>
-      <c r="F522" t="inlineStr">
-        <is>
-          <t>stopped_by=patience lr=0.0001 batch_size=128 epochs=15 patience=10 eval_every_steps=500 loss=bce_with_logits grad_clip=1.0</t>
+          <t>row 'PACLock (from scratch, full)' not found</t>
         </is>
       </c>
     </row>
@@ -20948,7 +20958,7 @@
       </c>
       <c r="B523" t="inlineStr">
         <is>
-          <t>sparcnet</t>
+          <t>reve_pretrained</t>
         </is>
       </c>
       <c r="C523" t="inlineStr">
@@ -20963,12 +20973,12 @@
       </c>
       <c r="E523" t="inlineStr">
         <is>
-          <t>[实测 1.14M] auroc per-seed 0:0.8836, 1:0.8896, 2:0.8898</t>
+          <t>[实测 69.46M] auroc per-seed 0:0.9037, 1:0.8950, 2:0.8848</t>
         </is>
       </c>
       <c r="F523" t="inlineStr">
         <is>
-          <t>lr=0.001 batch_size=512 epochs=20 patience=8 eval_every_steps=200 loss=bce_with_logits</t>
+          <t>stopped_by=patience lr=0.0001 batch_size=128 epochs=15 patience=10 eval_every_steps=500 loss=bce_with_logits grad_clip=1.0</t>
         </is>
       </c>
     </row>
@@ -20980,7 +20990,7 @@
       </c>
       <c r="B524" t="inlineStr">
         <is>
-          <t>st_transformer</t>
+          <t>sparcnet</t>
         </is>
       </c>
       <c r="C524" t="inlineStr">
@@ -20995,7 +21005,7 @@
       </c>
       <c r="E524" t="inlineStr">
         <is>
-          <t>[实测 3.43M] auroc per-seed 0:0.9017, 1:0.8992, 2:0.8908</t>
+          <t>[实测 1.14M] auroc per-seed 0:0.8836, 1:0.8896, 2:0.8898</t>
         </is>
       </c>
       <c r="F524" t="inlineStr">
@@ -21012,7 +21022,7 @@
       </c>
       <c r="B525" t="inlineStr">
         <is>
-          <t>tfm_pretrained</t>
+          <t>st_transformer</t>
         </is>
       </c>
       <c r="C525" t="inlineStr">
@@ -21027,39 +21037,44 @@
       </c>
       <c r="E525" t="inlineStr">
         <is>
-          <t>[实测 1.89M] auroc per-seed 0:0.8785, 1:0.8821, 2:0.8772</t>
+          <t>[实测 3.43M] auroc per-seed 0:0.9017, 1:0.8992, 2:0.8908</t>
         </is>
       </c>
       <c r="F525" t="inlineStr">
         <is>
-          <t>lr=0.001 batch_size=512 epochs=10 patience=10 eval_every_steps=100 loss=bce_with_logits label_smoothing=0.1</t>
+          <t>lr=0.001 batch_size=512 epochs=20 patience=8 eval_every_steps=200 loss=bce_with_logits</t>
         </is>
       </c>
     </row>
     <row r="526">
       <c r="A526" t="inlineStr">
         <is>
-          <t>tuar</t>
+          <t>tuab</t>
         </is>
       </c>
       <c r="B526" t="inlineStr">
         <is>
-          <t>biot_prest16</t>
+          <t>tfm_pretrained</t>
         </is>
       </c>
       <c r="C526" t="inlineStr">
         <is>
-          <t>[0, 1]</t>
+          <t>[0, 1, 2]</t>
         </is>
       </c>
       <c r="D526" t="inlineStr">
         <is>
-          <t>filled (single-seed, grey)</t>
+          <t>filled</t>
         </is>
       </c>
       <c r="E526" t="inlineStr">
         <is>
-          <t>cohen_kappa 0.5750, 0.5053</t>
+          <t>[实测 1.89M] auroc per-seed 0:0.8785, 1:0.8821, 2:0.8772</t>
+        </is>
+      </c>
+      <c r="F526" t="inlineStr">
+        <is>
+          <t>lr=0.001 batch_size=512 epochs=10 patience=10 eval_every_steps=100 loss=bce_with_logits label_smoothing=0.1</t>
         </is>
       </c>
     </row>
@@ -21071,12 +21086,12 @@
       </c>
       <c r="B527" t="inlineStr">
         <is>
-          <t>biot_scratch</t>
+          <t>biot_prest16</t>
         </is>
       </c>
       <c r="C527" t="inlineStr">
         <is>
-          <t>[0]</t>
+          <t>[0, 1]</t>
         </is>
       </c>
       <c r="D527" t="inlineStr">
@@ -21086,7 +21101,7 @@
       </c>
       <c r="E527" t="inlineStr">
         <is>
-          <t>cohen_kappa 0.4985</t>
+          <t>cohen_kappa 0.5750, 0.5053</t>
         </is>
       </c>
     </row>
@@ -21098,7 +21113,7 @@
       </c>
       <c r="B528" t="inlineStr">
         <is>
-          <t>cbramod_pretrained</t>
+          <t>biot_scratch</t>
         </is>
       </c>
       <c r="C528" t="inlineStr">
@@ -21113,7 +21128,7 @@
       </c>
       <c r="E528" t="inlineStr">
         <is>
-          <t>cohen_kappa 0.7147</t>
+          <t>cohen_kappa 0.4985</t>
         </is>
       </c>
     </row>
@@ -21125,7 +21140,7 @@
       </c>
       <c r="B529" t="inlineStr">
         <is>
-          <t>cbramod_scratch</t>
+          <t>cbramod_pretrained</t>
         </is>
       </c>
       <c r="C529" t="inlineStr">
@@ -21140,7 +21155,7 @@
       </c>
       <c r="E529" t="inlineStr">
         <is>
-          <t>cohen_kappa 0.6503</t>
+          <t>cohen_kappa 0.7147</t>
         </is>
       </c>
     </row>
@@ -21152,7 +21167,7 @@
       </c>
       <c r="B530" t="inlineStr">
         <is>
-          <t>cnn_transformer</t>
+          <t>cbramod_scratch</t>
         </is>
       </c>
       <c r="C530" t="inlineStr">
@@ -21167,7 +21182,7 @@
       </c>
       <c r="E530" t="inlineStr">
         <is>
-          <t>cohen_kappa 0.7120</t>
+          <t>cohen_kappa 0.6503</t>
         </is>
       </c>
     </row>
@@ -21179,7 +21194,7 @@
       </c>
       <c r="B531" t="inlineStr">
         <is>
-          <t>contrawr</t>
+          <t>cnn_transformer</t>
         </is>
       </c>
       <c r="C531" t="inlineStr">
@@ -21194,7 +21209,7 @@
       </c>
       <c r="E531" t="inlineStr">
         <is>
-          <t>cohen_kappa 0.6630</t>
+          <t>cohen_kappa 0.7120</t>
         </is>
       </c>
     </row>
@@ -21206,7 +21221,7 @@
       </c>
       <c r="B532" t="inlineStr">
         <is>
-          <t>eegpt_pretrained</t>
+          <t>contrawr</t>
         </is>
       </c>
       <c r="C532" t="inlineStr">
@@ -21221,7 +21236,7 @@
       </c>
       <c r="E532" t="inlineStr">
         <is>
-          <t>cohen_kappa 0.5235</t>
+          <t>cohen_kappa 0.6630</t>
         </is>
       </c>
     </row>
@@ -21233,7 +21248,7 @@
       </c>
       <c r="B533" t="inlineStr">
         <is>
-          <t>eegpt_scratch</t>
+          <t>eegpt_pretrained</t>
         </is>
       </c>
       <c r="C533" t="inlineStr">
@@ -21248,7 +21263,7 @@
       </c>
       <c r="E533" t="inlineStr">
         <is>
-          <t>cohen_kappa 0.5820</t>
+          <t>cohen_kappa 0.5235</t>
         </is>
       </c>
     </row>
@@ -21260,7 +21275,7 @@
       </c>
       <c r="B534" t="inlineStr">
         <is>
-          <t>ffcl</t>
+          <t>eegpt_scratch</t>
         </is>
       </c>
       <c r="C534" t="inlineStr">
@@ -21275,7 +21290,7 @@
       </c>
       <c r="E534" t="inlineStr">
         <is>
-          <t>cohen_kappa 0.6959</t>
+          <t>cohen_kappa 0.5820</t>
         </is>
       </c>
     </row>
@@ -21287,7 +21302,7 @@
       </c>
       <c r="B535" t="inlineStr">
         <is>
-          <t>labram_pretrained</t>
+          <t>ffcl</t>
         </is>
       </c>
       <c r="C535" t="inlineStr">
@@ -21302,7 +21317,7 @@
       </c>
       <c r="E535" t="inlineStr">
         <is>
-          <t>cohen_kappa 0.5931</t>
+          <t>cohen_kappa 0.6959</t>
         </is>
       </c>
     </row>
@@ -21314,7 +21329,7 @@
       </c>
       <c r="B536" t="inlineStr">
         <is>
-          <t>labram_scratch</t>
+          <t>labram_pretrained</t>
         </is>
       </c>
       <c r="C536" t="inlineStr">
@@ -21329,7 +21344,7 @@
       </c>
       <c r="E536" t="inlineStr">
         <is>
-          <t>cohen_kappa 0.5265</t>
+          <t>cohen_kappa 0.5931</t>
         </is>
       </c>
     </row>
@@ -21341,7 +21356,7 @@
       </c>
       <c r="B537" t="inlineStr">
         <is>
-          <t>paclock_duplex</t>
+          <t>labram_scratch</t>
         </is>
       </c>
       <c r="C537" t="inlineStr">
@@ -21356,7 +21371,7 @@
       </c>
       <c r="E537" t="inlineStr">
         <is>
-          <t>cohen_kappa 0.6289</t>
+          <t>cohen_kappa 0.5265</t>
         </is>
       </c>
     </row>
@@ -21368,7 +21383,7 @@
       </c>
       <c r="B538" t="inlineStr">
         <is>
-          <t>paclock_duplex_ptS</t>
+          <t>paclock_duplex</t>
         </is>
       </c>
       <c r="C538" t="inlineStr">
@@ -21383,7 +21398,7 @@
       </c>
       <c r="E538" t="inlineStr">
         <is>
-          <t>cohen_kappa 0.5923</t>
+          <t>cohen_kappa 0.6289</t>
         </is>
       </c>
     </row>
@@ -21395,22 +21410,22 @@
       </c>
       <c r="B539" t="inlineStr">
         <is>
-          <t>paclock_pac</t>
+          <t>paclock_duplex_ptS</t>
         </is>
       </c>
       <c r="C539" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>[0]</t>
         </is>
       </c>
       <c r="D539" t="inlineStr">
         <is>
-          <t>skipped</t>
+          <t>filled (single-seed, grey)</t>
         </is>
       </c>
       <c r="E539" t="inlineStr">
         <is>
-          <t>the workbook has no row for this variant</t>
+          <t>cohen_kappa 0.5923</t>
         </is>
       </c>
     </row>
@@ -21422,7 +21437,7 @@
       </c>
       <c r="B540" t="inlineStr">
         <is>
-          <t>paclock_ptF_t1</t>
+          <t>paclock_pac</t>
         </is>
       </c>
       <c r="C540" t="inlineStr">
@@ -21437,7 +21452,7 @@
       </c>
       <c r="E540" t="inlineStr">
         <is>
-          <t>no row label for 'paclock_ptF_t1'</t>
+          <t>the workbook has no row for this variant</t>
         </is>
       </c>
     </row>
@@ -21449,7 +21464,7 @@
       </c>
       <c r="B541" t="inlineStr">
         <is>
-          <t>paclock_ptF_t2</t>
+          <t>paclock_ptF_t1</t>
         </is>
       </c>
       <c r="C541" t="inlineStr">
@@ -21464,7 +21479,7 @@
       </c>
       <c r="E541" t="inlineStr">
         <is>
-          <t>no row label for 'paclock_ptF_t2'</t>
+          <t>no row label for 'paclock_ptF_t1'</t>
         </is>
       </c>
     </row>
@@ -21476,7 +21491,7 @@
       </c>
       <c r="B542" t="inlineStr">
         <is>
-          <t>paclock_raw</t>
+          <t>paclock_ptF_t2</t>
         </is>
       </c>
       <c r="C542" t="inlineStr">
@@ -21491,7 +21506,7 @@
       </c>
       <c r="E542" t="inlineStr">
         <is>
-          <t>no row label for 'paclock_raw'</t>
+          <t>no row label for 'paclock_ptF_t2'</t>
         </is>
       </c>
     </row>
@@ -21503,7 +21518,7 @@
       </c>
       <c r="B543" t="inlineStr">
         <is>
-          <t>paclock_rot</t>
+          <t>paclock_raw</t>
         </is>
       </c>
       <c r="C543" t="inlineStr">
@@ -21518,7 +21533,7 @@
       </c>
       <c r="E543" t="inlineStr">
         <is>
-          <t>no row label for 'paclock_rot'</t>
+          <t>no row label for 'paclock_raw'</t>
         </is>
       </c>
     </row>
@@ -21530,7 +21545,7 @@
       </c>
       <c r="B544" t="inlineStr">
         <is>
-          <t>paclock_tune_t1</t>
+          <t>paclock_rot</t>
         </is>
       </c>
       <c r="C544" t="inlineStr">
@@ -21545,7 +21560,7 @@
       </c>
       <c r="E544" t="inlineStr">
         <is>
-          <t>no row label for 'paclock_tune_t1'</t>
+          <t>no row label for 'paclock_rot'</t>
         </is>
       </c>
     </row>
@@ -21557,7 +21572,7 @@
       </c>
       <c r="B545" t="inlineStr">
         <is>
-          <t>paclock_tune_t2</t>
+          <t>paclock_tune_t1</t>
         </is>
       </c>
       <c r="C545" t="inlineStr">
@@ -21572,7 +21587,7 @@
       </c>
       <c r="E545" t="inlineStr">
         <is>
-          <t>no row label for 'paclock_tune_t2'</t>
+          <t>no row label for 'paclock_tune_t1'</t>
         </is>
       </c>
     </row>
@@ -21584,22 +21599,22 @@
       </c>
       <c r="B546" t="inlineStr">
         <is>
-          <t>sparcnet</t>
+          <t>paclock_tune_t2</t>
         </is>
       </c>
       <c r="C546" t="inlineStr">
         <is>
-          <t>[0]</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D546" t="inlineStr">
         <is>
-          <t>filled (single-seed, grey)</t>
+          <t>skipped</t>
         </is>
       </c>
       <c r="E546" t="inlineStr">
         <is>
-          <t>cohen_kappa 0.6010</t>
+          <t>no row label for 'paclock_tune_t2'</t>
         </is>
       </c>
     </row>
@@ -21611,7 +21626,7 @@
       </c>
       <c r="B547" t="inlineStr">
         <is>
-          <t>st_transformer</t>
+          <t>sparcnet</t>
         </is>
       </c>
       <c r="C547" t="inlineStr">
@@ -21626,7 +21641,7 @@
       </c>
       <c r="E547" t="inlineStr">
         <is>
-          <t>cohen_kappa 0.5213</t>
+          <t>cohen_kappa 0.6010</t>
         </is>
       </c>
     </row>
@@ -21638,7 +21653,7 @@
       </c>
       <c r="B548" t="inlineStr">
         <is>
-          <t>tfm_pretrained</t>
+          <t>st_transformer</t>
         </is>
       </c>
       <c r="C548" t="inlineStr">
@@ -21653,7 +21668,7 @@
       </c>
       <c r="E548" t="inlineStr">
         <is>
-          <t>cohen_kappa 0.6480</t>
+          <t>cohen_kappa 0.5213</t>
         </is>
       </c>
     </row>
@@ -21665,7 +21680,7 @@
       </c>
       <c r="B549" t="inlineStr">
         <is>
-          <t>tfm_scratch</t>
+          <t>tfm_pretrained</t>
         </is>
       </c>
       <c r="C549" t="inlineStr">
@@ -21680,39 +21695,34 @@
       </c>
       <c r="E549" t="inlineStr">
         <is>
-          <t>cohen_kappa 0.3644</t>
+          <t>cohen_kappa 0.6480</t>
         </is>
       </c>
     </row>
     <row r="550">
       <c r="A550" t="inlineStr">
         <is>
-          <t>tuep</t>
+          <t>tuar</t>
         </is>
       </c>
       <c r="B550" t="inlineStr">
         <is>
-          <t>biot_prest16</t>
+          <t>tfm_scratch</t>
         </is>
       </c>
       <c r="C550" t="inlineStr">
         <is>
-          <t>[0, 1, 2]</t>
+          <t>[0]</t>
         </is>
       </c>
       <c r="D550" t="inlineStr">
         <is>
-          <t>filled</t>
+          <t>filled (single-seed, grey)</t>
         </is>
       </c>
       <c r="E550" t="inlineStr">
         <is>
-          <t>[实测 3.19M] auroc per-seed 0:0.7513, 1:0.7452, 2:0.7823</t>
-        </is>
-      </c>
-      <c r="F550" t="inlineStr">
-        <is>
-          <t>stopped_by=patience lr=0.001 batch_size=512 epochs=100 patience=5 eval_every_steps=0 loss=bce_with_logits</t>
+          <t>cohen_kappa 0.3644</t>
         </is>
       </c>
     </row>
@@ -21724,7 +21734,7 @@
       </c>
       <c r="B551" t="inlineStr">
         <is>
-          <t>biot_scratch</t>
+          <t>biot_prest16</t>
         </is>
       </c>
       <c r="C551" t="inlineStr">
@@ -21739,7 +21749,7 @@
       </c>
       <c r="E551" t="inlineStr">
         <is>
-          <t>[实测 3.19M] auroc per-seed 0:0.7593, 1:0.7374, 2:0.7599</t>
+          <t>[实测 3.19M] auroc per-seed 0:0.7513, 1:0.7452, 2:0.7823</t>
         </is>
       </c>
       <c r="F551" t="inlineStr">
@@ -21756,22 +21766,27 @@
       </c>
       <c r="B552" t="inlineStr">
         <is>
-          <t>cbramod_crofremo</t>
+          <t>biot_scratch</t>
         </is>
       </c>
       <c r="C552" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>[0, 1, 2]</t>
         </is>
       </c>
       <c r="D552" t="inlineStr">
         <is>
-          <t>skipped</t>
+          <t>filled</t>
         </is>
       </c>
       <c r="E552" t="inlineStr">
         <is>
-          <t>no row label for 'cbramod_crofremo'</t>
+          <t>[实测 3.19M] auroc per-seed 0:0.7593, 1:0.7374, 2:0.7599</t>
+        </is>
+      </c>
+      <c r="F552" t="inlineStr">
+        <is>
+          <t>stopped_by=patience lr=0.001 batch_size=512 epochs=100 patience=5 eval_every_steps=0 loss=bce_with_logits</t>
         </is>
       </c>
     </row>
@@ -21783,27 +21798,22 @@
       </c>
       <c r="B553" t="inlineStr">
         <is>
-          <t>cbramod_pretrained</t>
+          <t>cbramod_crofremo</t>
         </is>
       </c>
       <c r="C553" t="inlineStr">
         <is>
-          <t>[0, 1, 2]</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D553" t="inlineStr">
         <is>
-          <t>filled</t>
+          <t>skipped</t>
         </is>
       </c>
       <c r="E553" t="inlineStr">
         <is>
-          <t>[实测 30.65M] auroc per-seed 0:0.6891, 1:0.6516, 2:0.6533</t>
-        </is>
-      </c>
-      <c r="F553" t="inlineStr">
-        <is>
-          <t>lr=0.0001 batch_size=64 epochs=50 patience=0 eval_every_steps=0 loss=bce_with_logits grad_clip=1.0 select_metric=auroc multi_lr=True</t>
+          <t>no row label for 'cbramod_crofremo'</t>
         </is>
       </c>
     </row>
@@ -21815,7 +21825,7 @@
       </c>
       <c r="B554" t="inlineStr">
         <is>
-          <t>cbramod_scratch</t>
+          <t>cbramod_pretrained</t>
         </is>
       </c>
       <c r="C554" t="inlineStr">
@@ -21830,7 +21840,7 @@
       </c>
       <c r="E554" t="inlineStr">
         <is>
-          <t>[实测 30.65M] auroc per-seed 0:0.6043, 1:0.6529, 2:0.6695</t>
+          <t>[实测 30.65M] auroc per-seed 0:0.6891, 1:0.6516, 2:0.6533</t>
         </is>
       </c>
       <c r="F554" t="inlineStr">
@@ -21847,7 +21857,7 @@
       </c>
       <c r="B555" t="inlineStr">
         <is>
-          <t>cnn_transformer</t>
+          <t>cbramod_scratch</t>
         </is>
       </c>
       <c r="C555" t="inlineStr">
@@ -21862,12 +21872,12 @@
       </c>
       <c r="E555" t="inlineStr">
         <is>
-          <t>[实测 3.15M] auroc per-seed 0:0.6580, 1:0.6790, 2:0.6519</t>
+          <t>[实测 30.65M] auroc per-seed 0:0.6043, 1:0.6529, 2:0.6695</t>
         </is>
       </c>
       <c r="F555" t="inlineStr">
         <is>
-          <t>stopped_by=patience lr=0.001 batch_size=512 epochs=20 patience=8 eval_every_steps=200 loss=bce_with_logits</t>
+          <t>lr=0.0001 batch_size=64 epochs=50 patience=0 eval_every_steps=0 loss=bce_with_logits grad_clip=1.0 select_metric=auroc multi_lr=True</t>
         </is>
       </c>
     </row>
@@ -21879,7 +21889,7 @@
       </c>
       <c r="B556" t="inlineStr">
         <is>
-          <t>contrawr</t>
+          <t>cnn_transformer</t>
         </is>
       </c>
       <c r="C556" t="inlineStr">
@@ -21894,7 +21904,7 @@
       </c>
       <c r="E556" t="inlineStr">
         <is>
-          <t>[实测 1.57M] auroc per-seed 0:0.6938, 1:0.5756, 2:0.6699</t>
+          <t>[实测 3.15M] auroc per-seed 0:0.6580, 1:0.6790, 2:0.6519</t>
         </is>
       </c>
       <c r="F556" t="inlineStr">
@@ -21911,7 +21921,7 @@
       </c>
       <c r="B557" t="inlineStr">
         <is>
-          <t>csbrain_pretrained</t>
+          <t>contrawr</t>
         </is>
       </c>
       <c r="C557" t="inlineStr">
@@ -21926,12 +21936,12 @@
       </c>
       <c r="E557" t="inlineStr">
         <is>
-          <t>[实测 41.06M] auroc per-seed 0:0.5971, 1:0.6439, 2:0.5581</t>
+          <t>[实测 1.57M] auroc per-seed 0:0.6938, 1:0.5756, 2:0.6699</t>
         </is>
       </c>
       <c r="F557" t="inlineStr">
         <is>
-          <t>stopped_by=patience lr=0.0001 batch_size=64 epochs=50 patience=10 eval_every_steps=0 loss=bce_with_logits grad_clip=1.0</t>
+          <t>stopped_by=patience lr=0.001 batch_size=512 epochs=20 patience=8 eval_every_steps=200 loss=bce_with_logits</t>
         </is>
       </c>
     </row>
@@ -21943,7 +21953,7 @@
       </c>
       <c r="B558" t="inlineStr">
         <is>
-          <t>eegconformer</t>
+          <t>csbrain_pretrained</t>
         </is>
       </c>
       <c r="C558" t="inlineStr">
@@ -21958,12 +21968,12 @@
       </c>
       <c r="E558" t="inlineStr">
         <is>
-          <t>[实测 1.46M] auroc per-seed 0:0.7562, 1:0.7349, 2:0.6733</t>
+          <t>[实测 41.06M] auroc per-seed 0:0.5971, 1:0.6439, 2:0.5581</t>
         </is>
       </c>
       <c r="F558" t="inlineStr">
         <is>
-          <t>stopped_by=patience lr=0.0003 batch_size=128 epochs=20 patience=8 eval_every_steps=200 loss=bce_with_logits grad_clip=1.0</t>
+          <t>stopped_by=patience lr=0.0001 batch_size=64 epochs=50 patience=10 eval_every_steps=0 loss=bce_with_logits grad_clip=1.0</t>
         </is>
       </c>
     </row>
@@ -21975,22 +21985,27 @@
       </c>
       <c r="B559" t="inlineStr">
         <is>
-          <t>eegconformer_t1</t>
+          <t>eegconformer</t>
         </is>
       </c>
       <c r="C559" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>[0, 1, 2]</t>
         </is>
       </c>
       <c r="D559" t="inlineStr">
         <is>
-          <t>skipped</t>
+          <t>filled</t>
         </is>
       </c>
       <c r="E559" t="inlineStr">
         <is>
-          <t>no row label for 'eegconformer_t1'</t>
+          <t>[实测 1.46M] auroc per-seed 0:0.7562, 1:0.7349, 2:0.6733</t>
+        </is>
+      </c>
+      <c r="F559" t="inlineStr">
+        <is>
+          <t>stopped_by=patience lr=0.0003 batch_size=128 epochs=20 patience=8 eval_every_steps=200 loss=bce_with_logits grad_clip=1.0</t>
         </is>
       </c>
     </row>
@@ -22002,7 +22017,7 @@
       </c>
       <c r="B560" t="inlineStr">
         <is>
-          <t>eegconformer_t2</t>
+          <t>eegconformer_t1</t>
         </is>
       </c>
       <c r="C560" t="inlineStr">
@@ -22017,7 +22032,7 @@
       </c>
       <c r="E560" t="inlineStr">
         <is>
-          <t>no row label for 'eegconformer_t2'</t>
+          <t>no row label for 'eegconformer_t1'</t>
         </is>
       </c>
     </row>
@@ -22029,7 +22044,7 @@
       </c>
       <c r="B561" t="inlineStr">
         <is>
-          <t>eegconformer_t3</t>
+          <t>eegconformer_t2</t>
         </is>
       </c>
       <c r="C561" t="inlineStr">
@@ -22044,7 +22059,7 @@
       </c>
       <c r="E561" t="inlineStr">
         <is>
-          <t>no row label for 'eegconformer_t3'</t>
+          <t>no row label for 'eegconformer_t2'</t>
         </is>
       </c>
     </row>
@@ -22056,7 +22071,7 @@
       </c>
       <c r="B562" t="inlineStr">
         <is>
-          <t>eegconformer_t4</t>
+          <t>eegconformer_t3</t>
         </is>
       </c>
       <c r="C562" t="inlineStr">
@@ -22071,7 +22086,7 @@
       </c>
       <c r="E562" t="inlineStr">
         <is>
-          <t>no row label for 'eegconformer_t4'</t>
+          <t>no row label for 'eegconformer_t3'</t>
         </is>
       </c>
     </row>
@@ -22083,27 +22098,22 @@
       </c>
       <c r="B563" t="inlineStr">
         <is>
-          <t>eegnet</t>
+          <t>eegconformer_t4</t>
         </is>
       </c>
       <c r="C563" t="inlineStr">
         <is>
-          <t>[0, 1, 2]</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D563" t="inlineStr">
         <is>
-          <t>filled</t>
+          <t>skipped</t>
         </is>
       </c>
       <c r="E563" t="inlineStr">
         <is>
-          <t>[实测 0.00M] auroc per-seed 0:0.7773, 1:0.7919, 2:0.7852</t>
-        </is>
-      </c>
-      <c r="F563" t="inlineStr">
-        <is>
-          <t>stopped_by=patience lr=0.001 batch_size=512 epochs=20 patience=8 eval_every_steps=200 loss=bce_with_logits grad_clip=1.0</t>
+          <t>no row label for 'eegconformer_t4'</t>
         </is>
       </c>
     </row>
@@ -22115,22 +22125,27 @@
       </c>
       <c r="B564" t="inlineStr">
         <is>
-          <t>eegnet_t1</t>
+          <t>eegnet</t>
         </is>
       </c>
       <c r="C564" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>[0, 1, 2]</t>
         </is>
       </c>
       <c r="D564" t="inlineStr">
         <is>
-          <t>skipped</t>
+          <t>filled</t>
         </is>
       </c>
       <c r="E564" t="inlineStr">
         <is>
-          <t>no row label for 'eegnet_t1'</t>
+          <t>[实测 0.00M] auroc per-seed 0:0.7773, 1:0.7919, 2:0.7852</t>
+        </is>
+      </c>
+      <c r="F564" t="inlineStr">
+        <is>
+          <t>stopped_by=patience lr=0.001 batch_size=512 epochs=20 patience=8 eval_every_steps=200 loss=bce_with_logits grad_clip=1.0</t>
         </is>
       </c>
     </row>
@@ -22142,7 +22157,7 @@
       </c>
       <c r="B565" t="inlineStr">
         <is>
-          <t>eegnet_t2</t>
+          <t>eegnet_t1</t>
         </is>
       </c>
       <c r="C565" t="inlineStr">
@@ -22157,7 +22172,7 @@
       </c>
       <c r="E565" t="inlineStr">
         <is>
-          <t>no row label for 'eegnet_t2'</t>
+          <t>no row label for 'eegnet_t1'</t>
         </is>
       </c>
     </row>
@@ -22169,7 +22184,7 @@
       </c>
       <c r="B566" t="inlineStr">
         <is>
-          <t>eegnet_t3</t>
+          <t>eegnet_t2</t>
         </is>
       </c>
       <c r="C566" t="inlineStr">
@@ -22184,7 +22199,7 @@
       </c>
       <c r="E566" t="inlineStr">
         <is>
-          <t>no row label for 'eegnet_t3'</t>
+          <t>no row label for 'eegnet_t2'</t>
         </is>
       </c>
     </row>
@@ -22196,7 +22211,7 @@
       </c>
       <c r="B567" t="inlineStr">
         <is>
-          <t>eegnet_t4</t>
+          <t>eegnet_t3</t>
         </is>
       </c>
       <c r="C567" t="inlineStr">
@@ -22211,7 +22226,7 @@
       </c>
       <c r="E567" t="inlineStr">
         <is>
-          <t>no row label for 'eegnet_t4'</t>
+          <t>no row label for 'eegnet_t3'</t>
         </is>
       </c>
     </row>
@@ -22223,27 +22238,22 @@
       </c>
       <c r="B568" t="inlineStr">
         <is>
-          <t>eegpt_pretrained</t>
+          <t>eegnet_t4</t>
         </is>
       </c>
       <c r="C568" t="inlineStr">
         <is>
-          <t>[0, 1, 2]</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D568" t="inlineStr">
         <is>
-          <t>filled</t>
+          <t>skipped</t>
         </is>
       </c>
       <c r="E568" t="inlineStr">
         <is>
-          <t>[实测 25.69M] auroc per-seed 0:0.7150, 1:0.7690, 2:0.7486</t>
-        </is>
-      </c>
-      <c r="F568" t="inlineStr">
-        <is>
-          <t>stopped_by=patience lr=0.0004 batch_size=32 epochs=40 patience=10 eval_every_steps=500 loss=bce_with_logits</t>
+          <t>no row label for 'eegnet_t4'</t>
         </is>
       </c>
     </row>
@@ -22255,7 +22265,7 @@
       </c>
       <c r="B569" t="inlineStr">
         <is>
-          <t>eegpt_scratch</t>
+          <t>eegpt_pretrained</t>
         </is>
       </c>
       <c r="C569" t="inlineStr">
@@ -22270,7 +22280,7 @@
       </c>
       <c r="E569" t="inlineStr">
         <is>
-          <t>[实测 25.69M] auroc per-seed 0:0.7626, 1:0.8048, 2:0.7904</t>
+          <t>[实测 25.69M] auroc per-seed 0:0.7150, 1:0.7690, 2:0.7486</t>
         </is>
       </c>
       <c r="F569" t="inlineStr">
@@ -22287,7 +22297,7 @@
       </c>
       <c r="B570" t="inlineStr">
         <is>
-          <t>feat_best</t>
+          <t>eegpt_scratch</t>
         </is>
       </c>
       <c r="C570" t="inlineStr">
@@ -22302,12 +22312,12 @@
       </c>
       <c r="E570" t="inlineStr">
         <is>
-          <t>[实测 0.00M] auroc per-seed 0:0.5919, 1:0.5919, 2:0.5919</t>
+          <t>[实测 25.69M] auroc per-seed 0:0.7626, 1:0.8048, 2:0.7904</t>
         </is>
       </c>
       <c r="F570" t="inlineStr">
         <is>
-          <t>stopped_by=closed-form epochs=1 loss=closed-form</t>
+          <t>stopped_by=patience lr=0.0004 batch_size=32 epochs=40 patience=10 eval_every_steps=500 loss=bce_with_logits</t>
         </is>
       </c>
     </row>
@@ -22319,7 +22329,7 @@
       </c>
       <c r="B571" t="inlineStr">
         <is>
-          <t>ffcl</t>
+          <t>feat_best</t>
         </is>
       </c>
       <c r="C571" t="inlineStr">
@@ -22334,12 +22344,12 @@
       </c>
       <c r="E571" t="inlineStr">
         <is>
-          <t>[实测 2.46M] auroc per-seed 0:0.6875, 1:0.6509, 2:0.5837</t>
+          <t>[实测 0.00M] auroc per-seed 0:0.5919, 1:0.5919, 2:0.5919</t>
         </is>
       </c>
       <c r="F571" t="inlineStr">
         <is>
-          <t>stopped_by=patience lr=0.001 batch_size=512 epochs=20 patience=8 eval_every_steps=200 loss=bce_with_logits</t>
+          <t>stopped_by=closed-form epochs=1 loss=closed-form</t>
         </is>
       </c>
     </row>
@@ -22351,7 +22361,7 @@
       </c>
       <c r="B572" t="inlineStr">
         <is>
-          <t>labram_pretrained</t>
+          <t>ffcl</t>
         </is>
       </c>
       <c r="C572" t="inlineStr">
@@ -22366,12 +22376,12 @@
       </c>
       <c r="E572" t="inlineStr">
         <is>
-          <t>[实测 5.82M] auroc per-seed 0:0.7884, 1:0.7561, 2:0.7885</t>
+          <t>[实测 2.46M] auroc per-seed 0:0.6875, 1:0.6509, 2:0.5837</t>
         </is>
       </c>
       <c r="F572" t="inlineStr">
         <is>
-          <t>stopped_by=patience lr=0.0005 batch_size=64 epochs=50 patience=10 eval_every_steps=0 loss=bce_with_logits loader_divisor=1.0</t>
+          <t>stopped_by=patience lr=0.001 batch_size=512 epochs=20 patience=8 eval_every_steps=200 loss=bce_with_logits</t>
         </is>
       </c>
     </row>
@@ -22383,7 +22393,7 @@
       </c>
       <c r="B573" t="inlineStr">
         <is>
-          <t>labram_scratch</t>
+          <t>labram_pretrained</t>
         </is>
       </c>
       <c r="C573" t="inlineStr">
@@ -22398,7 +22408,7 @@
       </c>
       <c r="E573" t="inlineStr">
         <is>
-          <t>[实测 5.82M] auroc per-seed 0:0.6618, 1:0.7646, 2:0.7295</t>
+          <t>[实测 5.82M] auroc per-seed 0:0.7884, 1:0.7561, 2:0.7885</t>
         </is>
       </c>
       <c r="F573" t="inlineStr">
@@ -22415,22 +22425,27 @@
       </c>
       <c r="B574" t="inlineStr">
         <is>
-          <t>paclock_duplex</t>
+          <t>labram_scratch</t>
         </is>
       </c>
       <c r="C574" t="inlineStr">
         <is>
-          <t>[0]</t>
+          <t>[0, 1, 2]</t>
         </is>
       </c>
       <c r="D574" t="inlineStr">
         <is>
-          <t>filled (single-seed, grey)</t>
+          <t>filled</t>
         </is>
       </c>
       <c r="E574" t="inlineStr">
         <is>
-          <t>auroc 0.8052</t>
+          <t>[实测 5.82M] auroc per-seed 0:0.6618, 1:0.7646, 2:0.7295</t>
+        </is>
+      </c>
+      <c r="F574" t="inlineStr">
+        <is>
+          <t>stopped_by=patience lr=0.0005 batch_size=64 epochs=50 patience=10 eval_every_steps=0 loss=bce_with_logits loader_divisor=1.0</t>
         </is>
       </c>
     </row>
@@ -22442,22 +22457,22 @@
       </c>
       <c r="B575" t="inlineStr">
         <is>
-          <t>paclock_duplex_ptF</t>
+          <t>paclock_duplex</t>
         </is>
       </c>
       <c r="C575" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>[0]</t>
         </is>
       </c>
       <c r="D575" t="inlineStr">
         <is>
-          <t>skipped</t>
+          <t>filled (single-seed, grey)</t>
         </is>
       </c>
       <c r="E575" t="inlineStr">
         <is>
-          <t>row 'CroFreMo (预训练 v2-full)' not found</t>
+          <t>auroc 0.8052</t>
         </is>
       </c>
     </row>
@@ -22469,22 +22484,22 @@
       </c>
       <c r="B576" t="inlineStr">
         <is>
-          <t>paclock_duplex_ptS</t>
+          <t>paclock_duplex_ptF</t>
         </is>
       </c>
       <c r="C576" t="inlineStr">
         <is>
-          <t>[0]</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D576" t="inlineStr">
         <is>
-          <t>filled (single-seed, grey)</t>
+          <t>skipped</t>
         </is>
       </c>
       <c r="E576" t="inlineStr">
         <is>
-          <t>auroc 0.7686</t>
+          <t>row 'CroFreMo (预训练 v2-full)' not found</t>
         </is>
       </c>
     </row>
@@ -22496,27 +22511,22 @@
       </c>
       <c r="B577" t="inlineStr">
         <is>
-          <t>reve_pretrained</t>
+          <t>paclock_duplex_ptS</t>
         </is>
       </c>
       <c r="C577" t="inlineStr">
         <is>
-          <t>[0, 1, 2]</t>
+          <t>[0]</t>
         </is>
       </c>
       <c r="D577" t="inlineStr">
         <is>
-          <t>filled</t>
+          <t>filled (single-seed, grey)</t>
         </is>
       </c>
       <c r="E577" t="inlineStr">
         <is>
-          <t>[实测 69.46M] auroc per-seed 0:0.6801, 1:0.6785, 2:0.6342</t>
-        </is>
-      </c>
-      <c r="F577" t="inlineStr">
-        <is>
-          <t>stopped_by=patience lr=5e-05 batch_size=128 epochs=30 patience=10 eval_every_steps=0 loss=bce_with_logits grad_clip=1.0</t>
+          <t>auroc 0.7686</t>
         </is>
       </c>
     </row>
@@ -22528,22 +22538,27 @@
       </c>
       <c r="B578" t="inlineStr">
         <is>
-          <t>reve_pt_lrhalf</t>
+          <t>reve_pretrained</t>
         </is>
       </c>
       <c r="C578" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>[0, 1, 2]</t>
         </is>
       </c>
       <c r="D578" t="inlineStr">
         <is>
-          <t>skipped</t>
+          <t>filled</t>
         </is>
       </c>
       <c r="E578" t="inlineStr">
         <is>
-          <t>no row label for 'reve_pt_lrhalf'</t>
+          <t>[实测 69.46M] auroc per-seed 0:0.6801, 1:0.6785, 2:0.6342</t>
+        </is>
+      </c>
+      <c r="F578" t="inlineStr">
+        <is>
+          <t>stopped_by=patience lr=5e-05 batch_size=128 epochs=30 patience=10 eval_every_steps=0 loss=bce_with_logits grad_clip=1.0</t>
         </is>
       </c>
     </row>
@@ -22555,27 +22570,22 @@
       </c>
       <c r="B579" t="inlineStr">
         <is>
-          <t>sparcnet</t>
+          <t>reve_pt_lrhalf</t>
         </is>
       </c>
       <c r="C579" t="inlineStr">
         <is>
-          <t>[0, 1, 2]</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D579" t="inlineStr">
         <is>
-          <t>filled</t>
+          <t>skipped</t>
         </is>
       </c>
       <c r="E579" t="inlineStr">
         <is>
-          <t>[实测 1.14M] auroc per-seed 0:0.7312, 1:0.7414, 2:0.7209</t>
-        </is>
-      </c>
-      <c r="F579" t="inlineStr">
-        <is>
-          <t>stopped_by=patience lr=0.001 batch_size=512 epochs=20 patience=8 eval_every_steps=200 loss=bce_with_logits</t>
+          <t>no row label for 'reve_pt_lrhalf'</t>
         </is>
       </c>
     </row>
@@ -22587,7 +22597,7 @@
       </c>
       <c r="B580" t="inlineStr">
         <is>
-          <t>st_transformer</t>
+          <t>sparcnet</t>
         </is>
       </c>
       <c r="C580" t="inlineStr">
@@ -22602,7 +22612,7 @@
       </c>
       <c r="E580" t="inlineStr">
         <is>
-          <t>[实测 3.43M] auroc per-seed 0:0.5898, 1:0.5923, 2:0.6710</t>
+          <t>[实测 1.14M] auroc per-seed 0:0.7312, 1:0.7414, 2:0.7209</t>
         </is>
       </c>
       <c r="F580" t="inlineStr">
@@ -22619,7 +22629,7 @@
       </c>
       <c r="B581" t="inlineStr">
         <is>
-          <t>tfm_pretrained</t>
+          <t>st_transformer</t>
         </is>
       </c>
       <c r="C581" t="inlineStr">
@@ -22634,12 +22644,12 @@
       </c>
       <c r="E581" t="inlineStr">
         <is>
-          <t>[实测 1.89M] auroc per-seed 0:0.6440, 1:0.6183, 2:0.6142</t>
+          <t>[实测 3.43M] auroc per-seed 0:0.5898, 1:0.5923, 2:0.6710</t>
         </is>
       </c>
       <c r="F581" t="inlineStr">
         <is>
-          <t>stopped_by=patience lr=0.001 batch_size=512 epochs=7 patience=10 eval_every_steps=100 loss=bce_with_logits</t>
+          <t>stopped_by=patience lr=0.001 batch_size=512 epochs=20 patience=8 eval_every_steps=200 loss=bce_with_logits</t>
         </is>
       </c>
     </row>
@@ -22651,7 +22661,7 @@
       </c>
       <c r="B582" t="inlineStr">
         <is>
-          <t>tfm_scratch</t>
+          <t>tfm_pretrained</t>
         </is>
       </c>
       <c r="C582" t="inlineStr">
@@ -22666,7 +22676,7 @@
       </c>
       <c r="E582" t="inlineStr">
         <is>
-          <t>[实测 1.89M] auroc per-seed 0:0.5838, 1:0.6180, 2:0.6193</t>
+          <t>[实测 1.89M] auroc per-seed 0:0.6440, 1:0.6183, 2:0.6142</t>
         </is>
       </c>
       <c r="F582" t="inlineStr">
@@ -22678,27 +22688,32 @@
     <row r="583">
       <c r="A583" t="inlineStr">
         <is>
-          <t>tuev</t>
+          <t>tuep</t>
         </is>
       </c>
       <c r="B583" t="inlineStr">
         <is>
-          <t>biot_hop50</t>
+          <t>tfm_scratch</t>
         </is>
       </c>
       <c r="C583" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>[0, 1, 2]</t>
         </is>
       </c>
       <c r="D583" t="inlineStr">
         <is>
-          <t>skipped</t>
+          <t>filled</t>
         </is>
       </c>
       <c r="E583" t="inlineStr">
         <is>
-          <t>the workbook has no row for this variant</t>
+          <t>[实测 1.89M] auroc per-seed 0:0.5838, 1:0.6180, 2:0.6193</t>
+        </is>
+      </c>
+      <c r="F583" t="inlineStr">
+        <is>
+          <t>stopped_by=patience lr=0.001 batch_size=512 epochs=7 patience=10 eval_every_steps=100 loss=bce_with_logits</t>
         </is>
       </c>
     </row>
@@ -22710,27 +22725,22 @@
       </c>
       <c r="B584" t="inlineStr">
         <is>
-          <t>biot_prest16</t>
+          <t>biot_hop50</t>
         </is>
       </c>
       <c r="C584" t="inlineStr">
         <is>
-          <t>[0, 1, 2]</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D584" t="inlineStr">
         <is>
-          <t>filled</t>
+          <t>skipped</t>
         </is>
       </c>
       <c r="E584" t="inlineStr">
         <is>
-          <t>[实测 3.19M] cohen_kappa per-seed 0:0.5005, 1:0.5354, 2:0.5554</t>
-        </is>
-      </c>
-      <c r="F584" t="inlineStr">
-        <is>
-          <t>lr=0.001 batch_size=128 epochs=100 patience=5 eval_every_steps=0 loss=cross_entropy label_smoothing=0.0</t>
+          <t>the workbook has no row for this variant</t>
         </is>
       </c>
     </row>
@@ -22742,7 +22752,7 @@
       </c>
       <c r="B585" t="inlineStr">
         <is>
-          <t>biot_scratch</t>
+          <t>biot_prest16</t>
         </is>
       </c>
       <c r="C585" t="inlineStr">
@@ -22757,7 +22767,7 @@
       </c>
       <c r="E585" t="inlineStr">
         <is>
-          <t>[实测 3.19M] cohen_kappa per-seed 0:0.5039, 1:0.5425, 2:0.5508</t>
+          <t>[实测 3.19M] cohen_kappa per-seed 0:0.5005, 1:0.5354, 2:0.5554</t>
         </is>
       </c>
       <c r="F585" t="inlineStr">
@@ -22774,22 +22784,27 @@
       </c>
       <c r="B586" t="inlineStr">
         <is>
-          <t>biot_tok100</t>
+          <t>biot_scratch</t>
         </is>
       </c>
       <c r="C586" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>[0, 1, 2]</t>
         </is>
       </c>
       <c r="D586" t="inlineStr">
         <is>
-          <t>skipped</t>
+          <t>filled</t>
         </is>
       </c>
       <c r="E586" t="inlineStr">
         <is>
-          <t>the workbook has no row for this variant</t>
+          <t>[实测 3.19M] cohen_kappa per-seed 0:0.5039, 1:0.5425, 2:0.5508</t>
+        </is>
+      </c>
+      <c r="F586" t="inlineStr">
+        <is>
+          <t>lr=0.001 batch_size=128 epochs=100 patience=5 eval_every_steps=0 loss=cross_entropy label_smoothing=0.0</t>
         </is>
       </c>
     </row>
@@ -22801,7 +22816,7 @@
       </c>
       <c r="B587" t="inlineStr">
         <is>
-          <t>cand_base</t>
+          <t>biot_tok100</t>
         </is>
       </c>
       <c r="C587" t="inlineStr">
@@ -22828,7 +22843,7 @@
       </c>
       <c r="B588" t="inlineStr">
         <is>
-          <t>cand_dense</t>
+          <t>cand_base</t>
         </is>
       </c>
       <c r="C588" t="inlineStr">
@@ -22855,7 +22870,7 @@
       </c>
       <c r="B589" t="inlineStr">
         <is>
-          <t>cand_dense_lr1e5</t>
+          <t>cand_dense</t>
         </is>
       </c>
       <c r="C589" t="inlineStr">
@@ -22882,7 +22897,7 @@
       </c>
       <c r="B590" t="inlineStr">
         <is>
-          <t>cand_dense_lr3e5</t>
+          <t>cand_dense_lr1e5</t>
         </is>
       </c>
       <c r="C590" t="inlineStr">
@@ -22909,7 +22924,7 @@
       </c>
       <c r="B591" t="inlineStr">
         <is>
-          <t>cand_dense_patch100</t>
+          <t>cand_dense_lr3e5</t>
         </is>
       </c>
       <c r="C591" t="inlineStr">
@@ -22936,7 +22951,7 @@
       </c>
       <c r="B592" t="inlineStr">
         <is>
-          <t>cand_e60_base</t>
+          <t>cand_dense_patch100</t>
         </is>
       </c>
       <c r="C592" t="inlineStr">
@@ -22963,7 +22978,7 @@
       </c>
       <c r="B593" t="inlineStr">
         <is>
-          <t>cand_e60_patch100</t>
+          <t>cand_e60_base</t>
         </is>
       </c>
       <c r="C593" t="inlineStr">
@@ -22990,7 +23005,7 @@
       </c>
       <c r="B594" t="inlineStr">
         <is>
-          <t>cand_e60_size_base</t>
+          <t>cand_e60_patch100</t>
         </is>
       </c>
       <c r="C594" t="inlineStr">
@@ -23017,7 +23032,7 @@
       </c>
       <c r="B595" t="inlineStr">
         <is>
-          <t>cand_e60_size_large</t>
+          <t>cand_e60_size_base</t>
         </is>
       </c>
       <c r="C595" t="inlineStr">
@@ -23044,7 +23059,7 @@
       </c>
       <c r="B596" t="inlineStr">
         <is>
-          <t>cand_ms</t>
+          <t>cand_e60_size_large</t>
         </is>
       </c>
       <c r="C596" t="inlineStr">
@@ -23071,7 +23086,7 @@
       </c>
       <c r="B597" t="inlineStr">
         <is>
-          <t>cand_p100_large</t>
+          <t>cand_ms</t>
         </is>
       </c>
       <c r="C597" t="inlineStr">
@@ -23098,7 +23113,7 @@
       </c>
       <c r="B598" t="inlineStr">
         <is>
-          <t>cand_p50_win100</t>
+          <t>cand_p100_large</t>
         </is>
       </c>
       <c r="C598" t="inlineStr">
@@ -23125,7 +23140,7 @@
       </c>
       <c r="B599" t="inlineStr">
         <is>
-          <t>cand_p50_win200</t>
+          <t>cand_p50_win100</t>
         </is>
       </c>
       <c r="C599" t="inlineStr">
@@ -23152,7 +23167,7 @@
       </c>
       <c r="B600" t="inlineStr">
         <is>
-          <t>cand_pacwin200</t>
+          <t>cand_p50_win200</t>
         </is>
       </c>
       <c r="C600" t="inlineStr">
@@ -23179,7 +23194,7 @@
       </c>
       <c r="B601" t="inlineStr">
         <is>
-          <t>cand_patch100</t>
+          <t>cand_pacwin200</t>
         </is>
       </c>
       <c r="C601" t="inlineStr">
@@ -23206,7 +23221,7 @@
       </c>
       <c r="B602" t="inlineStr">
         <is>
-          <t>cand_patch50</t>
+          <t>cand_patch100</t>
         </is>
       </c>
       <c r="C602" t="inlineStr">
@@ -23233,7 +23248,7 @@
       </c>
       <c r="B603" t="inlineStr">
         <is>
-          <t>cbramod_crofremo</t>
+          <t>cand_patch50</t>
         </is>
       </c>
       <c r="C603" t="inlineStr">
@@ -23248,7 +23263,7 @@
       </c>
       <c r="E603" t="inlineStr">
         <is>
-          <t>no row label for 'cbramod_crofremo'</t>
+          <t>the workbook has no row for this variant</t>
         </is>
       </c>
     </row>
@@ -23260,7 +23275,7 @@
       </c>
       <c r="B604" t="inlineStr">
         <is>
-          <t>cbramod_crofremo_bands</t>
+          <t>cbramod_crofremo</t>
         </is>
       </c>
       <c r="C604" t="inlineStr">
@@ -23275,7 +23290,7 @@
       </c>
       <c r="E604" t="inlineStr">
         <is>
-          <t>no row label for 'cbramod_crofremo_bands'</t>
+          <t>no row label for 'cbramod_crofremo'</t>
         </is>
       </c>
     </row>
@@ -23287,7 +23302,7 @@
       </c>
       <c r="B605" t="inlineStr">
         <is>
-          <t>cbramod_pac</t>
+          <t>cbramod_crofremo_bands</t>
         </is>
       </c>
       <c r="C605" t="inlineStr">
@@ -23302,7 +23317,7 @@
       </c>
       <c r="E605" t="inlineStr">
         <is>
-          <t>the workbook has no row for this variant</t>
+          <t>no row label for 'cbramod_crofremo_bands'</t>
         </is>
       </c>
     </row>
@@ -23314,7 +23329,7 @@
       </c>
       <c r="B606" t="inlineStr">
         <is>
-          <t>cbramod_pacfe_pac</t>
+          <t>cbramod_pac</t>
         </is>
       </c>
       <c r="C606" t="inlineStr">
@@ -23329,7 +23344,7 @@
       </c>
       <c r="E606" t="inlineStr">
         <is>
-          <t>no row label for 'cbramod_pacfe_pac'</t>
+          <t>the workbook has no row for this variant</t>
         </is>
       </c>
     </row>
@@ -23341,7 +23356,7 @@
       </c>
       <c r="B607" t="inlineStr">
         <is>
-          <t>cbramod_pacfe_raw</t>
+          <t>cbramod_pacfe_pac</t>
         </is>
       </c>
       <c r="C607" t="inlineStr">
@@ -23356,7 +23371,7 @@
       </c>
       <c r="E607" t="inlineStr">
         <is>
-          <t>no row label for 'cbramod_pacfe_raw'</t>
+          <t>no row label for 'cbramod_pacfe_pac'</t>
         </is>
       </c>
     </row>
@@ -23368,7 +23383,7 @@
       </c>
       <c r="B608" t="inlineStr">
         <is>
-          <t>cbramod_paclockfe</t>
+          <t>cbramod_pacfe_raw</t>
         </is>
       </c>
       <c r="C608" t="inlineStr">
@@ -23383,7 +23398,7 @@
       </c>
       <c r="E608" t="inlineStr">
         <is>
-          <t>no row label for 'cbramod_paclockfe'</t>
+          <t>no row label for 'cbramod_pacfe_raw'</t>
         </is>
       </c>
     </row>
@@ -23395,27 +23410,22 @@
       </c>
       <c r="B609" t="inlineStr">
         <is>
-          <t>cbramod_pretrained</t>
+          <t>cbramod_paclockfe</t>
         </is>
       </c>
       <c r="C609" t="inlineStr">
         <is>
-          <t>[0, 1, 2]</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D609" t="inlineStr">
         <is>
-          <t>filled</t>
+          <t>skipped</t>
         </is>
       </c>
       <c r="E609" t="inlineStr">
         <is>
-          <t>[实测 17.85M] cohen_kappa per-seed 0:0.6199, 1:0.6566, 2:0.6582</t>
-        </is>
-      </c>
-      <c r="F609" t="inlineStr">
-        <is>
-          <t>lr=0.0001 batch_size=64 epochs=50 patience=0 eval_every_steps=0 loss=cross_entropy label_smoothing=0.1 grad_clip=1.0 multi_lr=True</t>
+          <t>no row label for 'cbramod_paclockfe'</t>
         </is>
       </c>
     </row>
@@ -23427,22 +23437,27 @@
       </c>
       <c r="B610" t="inlineStr">
         <is>
-          <t>cbramod_rawfe_bands</t>
+          <t>cbramod_pretrained</t>
         </is>
       </c>
       <c r="C610" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>[0, 1, 2]</t>
         </is>
       </c>
       <c r="D610" t="inlineStr">
         <is>
-          <t>skipped</t>
+          <t>filled</t>
         </is>
       </c>
       <c r="E610" t="inlineStr">
         <is>
-          <t>no row label for 'cbramod_rawfe_bands'</t>
+          <t>[实测 17.85M] cohen_kappa per-seed 0:0.6199, 1:0.6566, 2:0.6582</t>
+        </is>
+      </c>
+      <c r="F610" t="inlineStr">
+        <is>
+          <t>lr=0.0001 batch_size=64 epochs=50 patience=0 eval_every_steps=0 loss=cross_entropy label_smoothing=0.1 grad_clip=1.0 multi_lr=True</t>
         </is>
       </c>
     </row>
@@ -23454,27 +23469,22 @@
       </c>
       <c r="B611" t="inlineStr">
         <is>
-          <t>cbramod_scratch</t>
+          <t>cbramod_rawfe_bands</t>
         </is>
       </c>
       <c r="C611" t="inlineStr">
         <is>
-          <t>[0, 1, 2]</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D611" t="inlineStr">
         <is>
-          <t>filled</t>
+          <t>skipped</t>
         </is>
       </c>
       <c r="E611" t="inlineStr">
         <is>
-          <t>[实测 17.85M] cohen_kappa per-seed 0:0.5755, 1:0.5366, 2:0.5794</t>
-        </is>
-      </c>
-      <c r="F611" t="inlineStr">
-        <is>
-          <t>lr=0.0001 batch_size=64 epochs=50 patience=0 eval_every_steps=0 loss=cross_entropy label_smoothing=0.1 grad_clip=1.0 multi_lr=True</t>
+          <t>no row label for 'cbramod_rawfe_bands'</t>
         </is>
       </c>
     </row>
@@ -23486,7 +23496,7 @@
       </c>
       <c r="B612" t="inlineStr">
         <is>
-          <t>cnn_transformer</t>
+          <t>cbramod_scratch</t>
         </is>
       </c>
       <c r="C612" t="inlineStr">
@@ -23501,12 +23511,12 @@
       </c>
       <c r="E612" t="inlineStr">
         <is>
-          <t>[实测 3.16M] cohen_kappa per-seed 0:0.4987, 1:0.2779, 2:0.4527  [seed spread 23% -- mean is a weak summary]</t>
+          <t>[实测 17.85M] cohen_kappa per-seed 0:0.5755, 1:0.5366, 2:0.5794</t>
         </is>
       </c>
       <c r="F612" t="inlineStr">
         <is>
-          <t>lr=0.001 batch_size=512 epochs=100 patience=15 eval_every_steps=0 loss=cross_entropy label_smoothing=0.1</t>
+          <t>lr=0.0001 batch_size=64 epochs=50 patience=0 eval_every_steps=0 loss=cross_entropy label_smoothing=0.1 grad_clip=1.0 multi_lr=True</t>
         </is>
       </c>
     </row>
@@ -23518,7 +23528,7 @@
       </c>
       <c r="B613" t="inlineStr">
         <is>
-          <t>contrawr</t>
+          <t>cnn_transformer</t>
         </is>
       </c>
       <c r="C613" t="inlineStr">
@@ -23533,7 +23543,7 @@
       </c>
       <c r="E613" t="inlineStr">
         <is>
-          <t>[实测 1.57M] cohen_kappa per-seed 0:0.4410, 1:0.4849, 2:0.2969  [seed spread 20% -- mean is a weak summary]</t>
+          <t>[实测 3.16M] cohen_kappa per-seed 0:0.4987, 1:0.2779, 2:0.4527  [seed spread 23% -- mean is a weak summary]</t>
         </is>
       </c>
       <c r="F613" t="inlineStr">
@@ -23550,7 +23560,7 @@
       </c>
       <c r="B614" t="inlineStr">
         <is>
-          <t>csbrain_pretrained</t>
+          <t>contrawr</t>
         </is>
       </c>
       <c r="C614" t="inlineStr">
@@ -23565,12 +23575,12 @@
       </c>
       <c r="E614" t="inlineStr">
         <is>
-          <t>[实测 25.06M] cohen_kappa per-seed 0:0.6132, 1:0.6922, 2:0.6027</t>
+          <t>[实测 1.57M] cohen_kappa per-seed 0:0.4410, 1:0.4849, 2:0.2969  [seed spread 20% -- mean is a weak summary]</t>
         </is>
       </c>
       <c r="F614" t="inlineStr">
         <is>
-          <t>stopped_by=patience lr=0.0001 batch_size=64 epochs=50 patience=10 eval_every_steps=0 loss=cross_entropy label_smoothing=0.1 grad_clip=1.0</t>
+          <t>lr=0.001 batch_size=512 epochs=100 patience=15 eval_every_steps=0 loss=cross_entropy label_smoothing=0.1</t>
         </is>
       </c>
     </row>
@@ -23582,22 +23592,27 @@
       </c>
       <c r="B615" t="inlineStr">
         <is>
-          <t>csbrain_pretrained_ls0</t>
+          <t>csbrain_pretrained</t>
         </is>
       </c>
       <c r="C615" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>[0, 1, 2]</t>
         </is>
       </c>
       <c r="D615" t="inlineStr">
         <is>
-          <t>skipped</t>
+          <t>filled</t>
         </is>
       </c>
       <c r="E615" t="inlineStr">
         <is>
-          <t>no row label for 'csbrain_pretrained_ls0'</t>
+          <t>[实测 25.06M] cohen_kappa per-seed 0:0.6132, 1:0.6922, 2:0.6027</t>
+        </is>
+      </c>
+      <c r="F615" t="inlineStr">
+        <is>
+          <t>stopped_by=patience lr=0.0001 batch_size=64 epochs=50 patience=10 eval_every_steps=0 loss=cross_entropy label_smoothing=0.1 grad_clip=1.0</t>
         </is>
       </c>
     </row>
@@ -23609,27 +23624,22 @@
       </c>
       <c r="B616" t="inlineStr">
         <is>
-          <t>eegconformer</t>
+          <t>csbrain_pretrained_ls0</t>
         </is>
       </c>
       <c r="C616" t="inlineStr">
         <is>
-          <t>[0, 1, 2]</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D616" t="inlineStr">
         <is>
-          <t>filled</t>
+          <t>skipped</t>
         </is>
       </c>
       <c r="E616" t="inlineStr">
         <is>
-          <t>[实测 0.78M] cohen_kappa per-seed 0:0.4524, 1:0.4596, 2:0.4525</t>
-        </is>
-      </c>
-      <c r="F616" t="inlineStr">
-        <is>
-          <t>stopped_by=patience lr=0.001 batch_size=128 epochs=100 patience=15 eval_every_steps=0 loss=cross_entropy label_smoothing=0.1 grad_clip=1.0</t>
+          <t>no row label for 'csbrain_pretrained_ls0'</t>
         </is>
       </c>
     </row>
@@ -23641,22 +23651,27 @@
       </c>
       <c r="B617" t="inlineStr">
         <is>
-          <t>eegconformer_t1</t>
+          <t>eegconformer</t>
         </is>
       </c>
       <c r="C617" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>[0, 1, 2]</t>
         </is>
       </c>
       <c r="D617" t="inlineStr">
         <is>
-          <t>skipped</t>
+          <t>filled</t>
         </is>
       </c>
       <c r="E617" t="inlineStr">
         <is>
-          <t>no row label for 'eegconformer_t1'</t>
+          <t>[实测 0.78M] cohen_kappa per-seed 0:0.4524, 1:0.4596, 2:0.4525</t>
+        </is>
+      </c>
+      <c r="F617" t="inlineStr">
+        <is>
+          <t>stopped_by=patience lr=0.001 batch_size=128 epochs=100 patience=15 eval_every_steps=0 loss=cross_entropy label_smoothing=0.1 grad_clip=1.0</t>
         </is>
       </c>
     </row>
@@ -23668,7 +23683,7 @@
       </c>
       <c r="B618" t="inlineStr">
         <is>
-          <t>eegconformer_t2</t>
+          <t>eegconformer_t1</t>
         </is>
       </c>
       <c r="C618" t="inlineStr">
@@ -23683,7 +23698,7 @@
       </c>
       <c r="E618" t="inlineStr">
         <is>
-          <t>no row label for 'eegconformer_t2'</t>
+          <t>no row label for 'eegconformer_t1'</t>
         </is>
       </c>
     </row>
@@ -23695,7 +23710,7 @@
       </c>
       <c r="B619" t="inlineStr">
         <is>
-          <t>eegconformer_t3</t>
+          <t>eegconformer_t2</t>
         </is>
       </c>
       <c r="C619" t="inlineStr">
@@ -23710,7 +23725,7 @@
       </c>
       <c r="E619" t="inlineStr">
         <is>
-          <t>no row label for 'eegconformer_t3'</t>
+          <t>no row label for 'eegconformer_t2'</t>
         </is>
       </c>
     </row>
@@ -23722,7 +23737,7 @@
       </c>
       <c r="B620" t="inlineStr">
         <is>
-          <t>eegconformer_t4</t>
+          <t>eegconformer_t3</t>
         </is>
       </c>
       <c r="C620" t="inlineStr">
@@ -23737,7 +23752,7 @@
       </c>
       <c r="E620" t="inlineStr">
         <is>
-          <t>no row label for 'eegconformer_t4'</t>
+          <t>no row label for 'eegconformer_t3'</t>
         </is>
       </c>
     </row>
@@ -23749,27 +23764,22 @@
       </c>
       <c r="B621" t="inlineStr">
         <is>
-          <t>eegnet</t>
+          <t>eegconformer_t4</t>
         </is>
       </c>
       <c r="C621" t="inlineStr">
         <is>
-          <t>[0, 1, 2]</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D621" t="inlineStr">
         <is>
-          <t>filled</t>
+          <t>skipped</t>
         </is>
       </c>
       <c r="E621" t="inlineStr">
         <is>
-          <t>[实测 0.00M] cohen_kappa per-seed 0:0.5836, 1:0.4223, 2:0.4306  [seed spread 15% -- mean is a weak summary]</t>
-        </is>
-      </c>
-      <c r="F621" t="inlineStr">
-        <is>
-          <t>stopped_by=patience lr=0.001 batch_size=512 epochs=100 patience=15 eval_every_steps=0 loss=cross_entropy label_smoothing=0.1 grad_clip=1.0</t>
+          <t>no row label for 'eegconformer_t4'</t>
         </is>
       </c>
     </row>
@@ -23781,22 +23791,27 @@
       </c>
       <c r="B622" t="inlineStr">
         <is>
-          <t>eegnet_t1</t>
+          <t>eegnet</t>
         </is>
       </c>
       <c r="C622" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>[0, 1, 2]</t>
         </is>
       </c>
       <c r="D622" t="inlineStr">
         <is>
-          <t>skipped</t>
+          <t>filled</t>
         </is>
       </c>
       <c r="E622" t="inlineStr">
         <is>
-          <t>no row label for 'eegnet_t1'</t>
+          <t>[实测 0.00M] cohen_kappa per-seed 0:0.5836, 1:0.4223, 2:0.4306  [seed spread 15% -- mean is a weak summary]</t>
+        </is>
+      </c>
+      <c r="F622" t="inlineStr">
+        <is>
+          <t>stopped_by=patience lr=0.001 batch_size=512 epochs=100 patience=15 eval_every_steps=0 loss=cross_entropy label_smoothing=0.1 grad_clip=1.0</t>
         </is>
       </c>
     </row>
@@ -23808,7 +23823,7 @@
       </c>
       <c r="B623" t="inlineStr">
         <is>
-          <t>eegnet_t2</t>
+          <t>eegnet_t1</t>
         </is>
       </c>
       <c r="C623" t="inlineStr">
@@ -23823,7 +23838,7 @@
       </c>
       <c r="E623" t="inlineStr">
         <is>
-          <t>no row label for 'eegnet_t2'</t>
+          <t>no row label for 'eegnet_t1'</t>
         </is>
       </c>
     </row>
@@ -23835,7 +23850,7 @@
       </c>
       <c r="B624" t="inlineStr">
         <is>
-          <t>eegnet_t3</t>
+          <t>eegnet_t2</t>
         </is>
       </c>
       <c r="C624" t="inlineStr">
@@ -23850,7 +23865,7 @@
       </c>
       <c r="E624" t="inlineStr">
         <is>
-          <t>no row label for 'eegnet_t3'</t>
+          <t>no row label for 'eegnet_t2'</t>
         </is>
       </c>
     </row>
@@ -23862,7 +23877,7 @@
       </c>
       <c r="B625" t="inlineStr">
         <is>
-          <t>eegnet_t4</t>
+          <t>eegnet_t3</t>
         </is>
       </c>
       <c r="C625" t="inlineStr">
@@ -23877,7 +23892,7 @@
       </c>
       <c r="E625" t="inlineStr">
         <is>
-          <t>no row label for 'eegnet_t4'</t>
+          <t>no row label for 'eegnet_t3'</t>
         </is>
       </c>
     </row>
@@ -23889,27 +23904,22 @@
       </c>
       <c r="B626" t="inlineStr">
         <is>
-          <t>eegpt_pretrained</t>
+          <t>eegnet_t4</t>
         </is>
       </c>
       <c r="C626" t="inlineStr">
         <is>
-          <t>[0, 1, 2]</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D626" t="inlineStr">
         <is>
-          <t>filled</t>
+          <t>skipped</t>
         </is>
       </c>
       <c r="E626" t="inlineStr">
         <is>
-          <t>[实测 25.69M] cohen_kappa per-seed 0:0.5311, 1:0.6095, 2:0.5803</t>
-        </is>
-      </c>
-      <c r="F626" t="inlineStr">
-        <is>
-          <t>lr=0.0004 batch_size=32 epochs=40 patience=10 eval_every_steps=0 loss=cross_entropy</t>
+          <t>no row label for 'eegnet_t4'</t>
         </is>
       </c>
     </row>
@@ -23921,7 +23931,7 @@
       </c>
       <c r="B627" t="inlineStr">
         <is>
-          <t>feat_best</t>
+          <t>eegpt_pretrained</t>
         </is>
       </c>
       <c r="C627" t="inlineStr">
@@ -23936,12 +23946,12 @@
       </c>
       <c r="E627" t="inlineStr">
         <is>
-          <t>[实测 0.00M] cohen_kappa per-seed 0:0.5049, 1:0.5049, 2:0.5049</t>
+          <t>[实测 25.69M] cohen_kappa per-seed 0:0.5311, 1:0.6095, 2:0.5803</t>
         </is>
       </c>
       <c r="F627" t="inlineStr">
         <is>
-          <t>stopped_by=closed-form epochs=1 loss=closed-form</t>
+          <t>lr=0.0004 batch_size=32 epochs=40 patience=10 eval_every_steps=0 loss=cross_entropy</t>
         </is>
       </c>
     </row>
@@ -23953,7 +23963,7 @@
       </c>
       <c r="B628" t="inlineStr">
         <is>
-          <t>ffcl</t>
+          <t>feat_best</t>
         </is>
       </c>
       <c r="C628" t="inlineStr">
@@ -23968,12 +23978,12 @@
       </c>
       <c r="E628" t="inlineStr">
         <is>
-          <t>[实测 2.42M] cohen_kappa per-seed 0:0.5069, 1:0.4432, 2:0.4827</t>
+          <t>[实测 0.00M] cohen_kappa per-seed 0:0.5049, 1:0.5049, 2:0.5049</t>
         </is>
       </c>
       <c r="F628" t="inlineStr">
         <is>
-          <t>lr=0.001 batch_size=512 epochs=100 patience=15 eval_every_steps=0 loss=cross_entropy label_smoothing=0.1</t>
+          <t>stopped_by=closed-form epochs=1 loss=closed-form</t>
         </is>
       </c>
     </row>
@@ -23985,7 +23995,7 @@
       </c>
       <c r="B629" t="inlineStr">
         <is>
-          <t>labram_pretrained</t>
+          <t>ffcl</t>
         </is>
       </c>
       <c r="C629" t="inlineStr">
@@ -24000,12 +24010,12 @@
       </c>
       <c r="E629" t="inlineStr">
         <is>
-          <t>[实测 5.82M] cohen_kappa per-seed 0:0.6012, 1:0.5989, 2:0.5951</t>
+          <t>[实测 2.42M] cohen_kappa per-seed 0:0.5069, 1:0.4432, 2:0.4827</t>
         </is>
       </c>
       <c r="F629" t="inlineStr">
         <is>
-          <t>stopped_by=patience lr=0.0005 batch_size=64 epochs=50 patience=10 eval_every_steps=100 loss=cross_entropy label_smoothing=0.1</t>
+          <t>lr=0.001 batch_size=512 epochs=100 patience=15 eval_every_steps=0 loss=cross_entropy label_smoothing=0.1</t>
         </is>
       </c>
     </row>
@@ -24017,7 +24027,7 @@
       </c>
       <c r="B630" t="inlineStr">
         <is>
-          <t>labram_scratch</t>
+          <t>labram_pretrained</t>
         </is>
       </c>
       <c r="C630" t="inlineStr">
@@ -24032,12 +24042,12 @@
       </c>
       <c r="E630" t="inlineStr">
         <is>
-          <t>[实测 5.82M] cohen_kappa per-seed 0:0.3624, 1:0.3727, 2:0.3801</t>
+          <t>[实测 5.82M] cohen_kappa per-seed 0:0.6012, 1:0.5989, 2:0.5951</t>
         </is>
       </c>
       <c r="F630" t="inlineStr">
         <is>
-          <t>lr=0.0005 batch_size=64 epochs=50 patience=10 eval_every_steps=0 loss=cross_entropy label_smoothing=0.1</t>
+          <t>stopped_by=patience lr=0.0005 batch_size=64 epochs=50 patience=10 eval_every_steps=100 loss=cross_entropy label_smoothing=0.1</t>
         </is>
       </c>
     </row>
@@ -24049,22 +24059,27 @@
       </c>
       <c r="B631" t="inlineStr">
         <is>
-          <t>paclock</t>
+          <t>labram_scratch</t>
         </is>
       </c>
       <c r="C631" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>[0, 1, 2]</t>
         </is>
       </c>
       <c r="D631" t="inlineStr">
         <is>
-          <t>skipped</t>
+          <t>filled</t>
         </is>
       </c>
       <c r="E631" t="inlineStr">
         <is>
-          <t>no row label for 'paclock'</t>
+          <t>[实测 5.82M] cohen_kappa per-seed 0:0.3624, 1:0.3727, 2:0.3801</t>
+        </is>
+      </c>
+      <c r="F631" t="inlineStr">
+        <is>
+          <t>lr=0.0005 batch_size=64 epochs=50 patience=10 eval_every_steps=0 loss=cross_entropy label_smoothing=0.1</t>
         </is>
       </c>
     </row>
@@ -24076,22 +24091,22 @@
       </c>
       <c r="B632" t="inlineStr">
         <is>
-          <t>paclock_duplex</t>
+          <t>paclock</t>
         </is>
       </c>
       <c r="C632" t="inlineStr">
         <is>
-          <t>[0]</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D632" t="inlineStr">
         <is>
-          <t>filled (single-seed, grey)</t>
+          <t>skipped</t>
         </is>
       </c>
       <c r="E632" t="inlineStr">
         <is>
-          <t>cohen_kappa 0.7094</t>
+          <t>no row label for 'paclock'</t>
         </is>
       </c>
     </row>
@@ -24103,22 +24118,22 @@
       </c>
       <c r="B633" t="inlineStr">
         <is>
-          <t>paclock_duplex_ms</t>
+          <t>paclock_duplex</t>
         </is>
       </c>
       <c r="C633" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>[0]</t>
         </is>
       </c>
       <c r="D633" t="inlineStr">
         <is>
-          <t>skipped</t>
+          <t>filled (single-seed, grey)</t>
         </is>
       </c>
       <c r="E633" t="inlineStr">
         <is>
-          <t>no row label for 'paclock_duplex_ms'</t>
+          <t>cohen_kappa 0.7094</t>
         </is>
       </c>
     </row>
@@ -24130,7 +24145,7 @@
       </c>
       <c r="B634" t="inlineStr">
         <is>
-          <t>paclock_duplex_p200</t>
+          <t>paclock_duplex_ms</t>
         </is>
       </c>
       <c r="C634" t="inlineStr">
@@ -24145,7 +24160,7 @@
       </c>
       <c r="E634" t="inlineStr">
         <is>
-          <t>no row label for 'paclock_duplex_p200'</t>
+          <t>no row label for 'paclock_duplex_ms'</t>
         </is>
       </c>
     </row>
@@ -24157,7 +24172,7 @@
       </c>
       <c r="B635" t="inlineStr">
         <is>
-          <t>paclock_duplex_p200ptF</t>
+          <t>paclock_duplex_p200</t>
         </is>
       </c>
       <c r="C635" t="inlineStr">
@@ -24172,7 +24187,7 @@
       </c>
       <c r="E635" t="inlineStr">
         <is>
-          <t>no row label for 'paclock_duplex_p200ptF'</t>
+          <t>no row label for 'paclock_duplex_p200'</t>
         </is>
       </c>
     </row>
@@ -24184,7 +24199,7 @@
       </c>
       <c r="B636" t="inlineStr">
         <is>
-          <t>paclock_duplex_pt</t>
+          <t>paclock_duplex_p200ptF</t>
         </is>
       </c>
       <c r="C636" t="inlineStr">
@@ -24199,7 +24214,7 @@
       </c>
       <c r="E636" t="inlineStr">
         <is>
-          <t>row 'PACLock (duplex, pretrained)' not found</t>
+          <t>no row label for 'paclock_duplex_p200ptF'</t>
         </is>
       </c>
     </row>
@@ -24211,22 +24226,22 @@
       </c>
       <c r="B637" t="inlineStr">
         <is>
-          <t>paclock_duplex_pt2</t>
+          <t>paclock_duplex_pt</t>
         </is>
       </c>
       <c r="C637" t="inlineStr">
         <is>
-          <t>[0]</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D637" t="inlineStr">
         <is>
-          <t>filled (single-seed, grey)</t>
+          <t>skipped</t>
         </is>
       </c>
       <c r="E637" t="inlineStr">
         <is>
-          <t>cohen_kappa 0.6533</t>
+          <t>row 'PACLock (duplex, pretrained)' not found</t>
         </is>
       </c>
     </row>
@@ -24238,7 +24253,7 @@
       </c>
       <c r="B638" t="inlineStr">
         <is>
-          <t>paclock_duplex_pt3</t>
+          <t>paclock_duplex_pt2</t>
         </is>
       </c>
       <c r="C638" t="inlineStr">
@@ -24253,7 +24268,7 @@
       </c>
       <c r="E638" t="inlineStr">
         <is>
-          <t>cohen_kappa 0.6753</t>
+          <t>cohen_kappa 0.6533</t>
         </is>
       </c>
     </row>
@@ -24265,22 +24280,22 @@
       </c>
       <c r="B639" t="inlineStr">
         <is>
-          <t>paclock_duplex_ptF</t>
+          <t>paclock_duplex_pt3</t>
         </is>
       </c>
       <c r="C639" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>[0]</t>
         </is>
       </c>
       <c r="D639" t="inlineStr">
         <is>
-          <t>skipped</t>
+          <t>filled (single-seed, grey)</t>
         </is>
       </c>
       <c r="E639" t="inlineStr">
         <is>
-          <t>row 'CroFreMo (预训练 v2-full)' not found</t>
+          <t>cohen_kappa 0.6753</t>
         </is>
       </c>
     </row>
@@ -24292,22 +24307,22 @@
       </c>
       <c r="B640" t="inlineStr">
         <is>
-          <t>paclock_duplex_ptS</t>
+          <t>paclock_duplex_ptF</t>
         </is>
       </c>
       <c r="C640" t="inlineStr">
         <is>
-          <t>[0]</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D640" t="inlineStr">
         <is>
-          <t>filled (single-seed, grey)</t>
+          <t>skipped</t>
         </is>
       </c>
       <c r="E640" t="inlineStr">
         <is>
-          <t>cohen_kappa 0.6417</t>
+          <t>row 'CroFreMo (预训练 v2-full)' not found</t>
         </is>
       </c>
     </row>
@@ -24319,22 +24334,22 @@
       </c>
       <c r="B641" t="inlineStr">
         <is>
-          <t>paclock_flagship</t>
+          <t>paclock_duplex_ptS</t>
         </is>
       </c>
       <c r="C641" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>[0]</t>
         </is>
       </c>
       <c r="D641" t="inlineStr">
         <is>
-          <t>skipped</t>
+          <t>filled (single-seed, grey)</t>
         </is>
       </c>
       <c r="E641" t="inlineStr">
         <is>
-          <t>no row label for 'paclock_flagship'</t>
+          <t>cohen_kappa 0.6417</t>
         </is>
       </c>
     </row>
@@ -24346,7 +24361,7 @@
       </c>
       <c r="B642" t="inlineStr">
         <is>
-          <t>paclock_ft_base_partial</t>
+          <t>paclock_flagship</t>
         </is>
       </c>
       <c r="C642" t="inlineStr">
@@ -24361,7 +24376,7 @@
       </c>
       <c r="E642" t="inlineStr">
         <is>
-          <t>no row label for 'paclock_ft_base_partial'</t>
+          <t>no row label for 'paclock_flagship'</t>
         </is>
       </c>
     </row>
@@ -24373,7 +24388,7 @@
       </c>
       <c r="B643" t="inlineStr">
         <is>
-          <t>paclock_ft_base_v2_v2</t>
+          <t>paclock_ft_base_partial</t>
         </is>
       </c>
       <c r="C643" t="inlineStr">
@@ -24388,7 +24403,7 @@
       </c>
       <c r="E643" t="inlineStr">
         <is>
-          <t>no row label for 'paclock_ft_base_v2_v2'</t>
+          <t>no row label for 'paclock_ft_base_partial'</t>
         </is>
       </c>
     </row>
@@ -24400,7 +24415,7 @@
       </c>
       <c r="B644" t="inlineStr">
         <is>
-          <t>paclock_fuse</t>
+          <t>paclock_ft_base_v2_v2</t>
         </is>
       </c>
       <c r="C644" t="inlineStr">
@@ -24415,7 +24430,7 @@
       </c>
       <c r="E644" t="inlineStr">
         <is>
-          <t>no row label for 'paclock_fuse'</t>
+          <t>no row label for 'paclock_ft_base_v2_v2'</t>
         </is>
       </c>
     </row>
@@ -24427,7 +24442,7 @@
       </c>
       <c r="B645" t="inlineStr">
         <is>
-          <t>paclock_fusegate</t>
+          <t>paclock_fuse</t>
         </is>
       </c>
       <c r="C645" t="inlineStr">
@@ -24442,7 +24457,7 @@
       </c>
       <c r="E645" t="inlineStr">
         <is>
-          <t>no row label for 'paclock_fusegate'</t>
+          <t>no row label for 'paclock_fuse'</t>
         </is>
       </c>
     </row>
@@ -24454,7 +24469,7 @@
       </c>
       <c r="B646" t="inlineStr">
         <is>
-          <t>paclock_h12</t>
+          <t>paclock_fusegate</t>
         </is>
       </c>
       <c r="C646" t="inlineStr">
@@ -24469,7 +24484,7 @@
       </c>
       <c r="E646" t="inlineStr">
         <is>
-          <t>no row label for 'paclock_h12'</t>
+          <t>no row label for 'paclock_fusegate'</t>
         </is>
       </c>
     </row>
@@ -24481,7 +24496,7 @@
       </c>
       <c r="B647" t="inlineStr">
         <is>
-          <t>paclock_h1stem</t>
+          <t>paclock_h12</t>
         </is>
       </c>
       <c r="C647" t="inlineStr">
@@ -24496,7 +24511,7 @@
       </c>
       <c r="E647" t="inlineStr">
         <is>
-          <t>no row label for 'paclock_h1stem'</t>
+          <t>no row label for 'paclock_h12'</t>
         </is>
       </c>
     </row>
@@ -24508,7 +24523,7 @@
       </c>
       <c r="B648" t="inlineStr">
         <is>
-          <t>paclock_h2mont</t>
+          <t>paclock_h1stem</t>
         </is>
       </c>
       <c r="C648" t="inlineStr">
@@ -24523,7 +24538,7 @@
       </c>
       <c r="E648" t="inlineStr">
         <is>
-          <t>no row label for 'paclock_h2mont'</t>
+          <t>no row label for 'paclock_h1stem'</t>
         </is>
       </c>
     </row>
@@ -24535,7 +24550,7 @@
       </c>
       <c r="B649" t="inlineStr">
         <is>
-          <t>paclock_hybrid</t>
+          <t>paclock_h2mont</t>
         </is>
       </c>
       <c r="C649" t="inlineStr">
@@ -24550,7 +24565,7 @@
       </c>
       <c r="E649" t="inlineStr">
         <is>
-          <t>no row label for 'paclock_hybrid'</t>
+          <t>no row label for 'paclock_h2mont'</t>
         </is>
       </c>
     </row>
@@ -24562,7 +24577,7 @@
       </c>
       <c r="B650" t="inlineStr">
         <is>
-          <t>paclock_hybrid_attn</t>
+          <t>paclock_hybrid</t>
         </is>
       </c>
       <c r="C650" t="inlineStr">
@@ -24577,7 +24592,7 @@
       </c>
       <c r="E650" t="inlineStr">
         <is>
-          <t>no row label for 'paclock_hybrid_attn'</t>
+          <t>no row label for 'paclock_hybrid'</t>
         </is>
       </c>
     </row>
@@ -24589,7 +24604,7 @@
       </c>
       <c r="B651" t="inlineStr">
         <is>
-          <t>paclock_hybrid_gate</t>
+          <t>paclock_hybrid_attn</t>
         </is>
       </c>
       <c r="C651" t="inlineStr">
@@ -24604,7 +24619,7 @@
       </c>
       <c r="E651" t="inlineStr">
         <is>
-          <t>no row label for 'paclock_hybrid_gate'</t>
+          <t>no row label for 'paclock_hybrid_attn'</t>
         </is>
       </c>
     </row>
@@ -24616,7 +24631,7 @@
       </c>
       <c r="B652" t="inlineStr">
         <is>
-          <t>paclock_lf05_ptF</t>
+          <t>paclock_hybrid_gate</t>
         </is>
       </c>
       <c r="C652" t="inlineStr">
@@ -24631,7 +24646,7 @@
       </c>
       <c r="E652" t="inlineStr">
         <is>
-          <t>no row label for 'paclock_lf05_ptF'</t>
+          <t>no row label for 'paclock_hybrid_gate'</t>
         </is>
       </c>
     </row>
@@ -24643,7 +24658,7 @@
       </c>
       <c r="B653" t="inlineStr">
         <is>
-          <t>paclock_lf05_scratch</t>
+          <t>paclock_lf05_ptF</t>
         </is>
       </c>
       <c r="C653" t="inlineStr">
@@ -24658,7 +24673,7 @@
       </c>
       <c r="E653" t="inlineStr">
         <is>
-          <t>no row label for 'paclock_lf05_scratch'</t>
+          <t>no row label for 'paclock_lf05_ptF'</t>
         </is>
       </c>
     </row>
@@ -24670,7 +24685,7 @@
       </c>
       <c r="B654" t="inlineStr">
         <is>
-          <t>paclock_lf10_ptF</t>
+          <t>paclock_lf05_scratch</t>
         </is>
       </c>
       <c r="C654" t="inlineStr">
@@ -24685,7 +24700,7 @@
       </c>
       <c r="E654" t="inlineStr">
         <is>
-          <t>no row label for 'paclock_lf10_ptF'</t>
+          <t>no row label for 'paclock_lf05_scratch'</t>
         </is>
       </c>
     </row>
@@ -24697,7 +24712,7 @@
       </c>
       <c r="B655" t="inlineStr">
         <is>
-          <t>paclock_lf10_scratch</t>
+          <t>paclock_lf10_ptF</t>
         </is>
       </c>
       <c r="C655" t="inlineStr">
@@ -24712,7 +24727,7 @@
       </c>
       <c r="E655" t="inlineStr">
         <is>
-          <t>no row label for 'paclock_lf10_scratch'</t>
+          <t>no row label for 'paclock_lf10_ptF'</t>
         </is>
       </c>
     </row>
@@ -24724,7 +24739,7 @@
       </c>
       <c r="B656" t="inlineStr">
         <is>
-          <t>paclock_lf25_ptF</t>
+          <t>paclock_lf10_scratch</t>
         </is>
       </c>
       <c r="C656" t="inlineStr">
@@ -24739,7 +24754,7 @@
       </c>
       <c r="E656" t="inlineStr">
         <is>
-          <t>no row label for 'paclock_lf25_ptF'</t>
+          <t>no row label for 'paclock_lf10_scratch'</t>
         </is>
       </c>
     </row>
@@ -24751,7 +24766,7 @@
       </c>
       <c r="B657" t="inlineStr">
         <is>
-          <t>paclock_lf25_scratch</t>
+          <t>paclock_lf25_ptF</t>
         </is>
       </c>
       <c r="C657" t="inlineStr">
@@ -24766,7 +24781,7 @@
       </c>
       <c r="E657" t="inlineStr">
         <is>
-          <t>no row label for 'paclock_lf25_scratch'</t>
+          <t>no row label for 'paclock_lf25_ptF'</t>
         </is>
       </c>
     </row>
@@ -24778,7 +24793,7 @@
       </c>
       <c r="B658" t="inlineStr">
         <is>
-          <t>paclock_nb16</t>
+          <t>paclock_lf25_scratch</t>
         </is>
       </c>
       <c r="C658" t="inlineStr">
@@ -24793,7 +24808,7 @@
       </c>
       <c r="E658" t="inlineStr">
         <is>
-          <t>no row label for 'paclock_nb16'</t>
+          <t>no row label for 'paclock_lf25_scratch'</t>
         </is>
       </c>
     </row>
@@ -24805,7 +24820,7 @@
       </c>
       <c r="B659" t="inlineStr">
         <is>
-          <t>paclock_pac</t>
+          <t>paclock_nb16</t>
         </is>
       </c>
       <c r="C659" t="inlineStr">
@@ -24820,7 +24835,7 @@
       </c>
       <c r="E659" t="inlineStr">
         <is>
-          <t>the workbook has no row for this variant</t>
+          <t>no row label for 'paclock_nb16'</t>
         </is>
       </c>
     </row>
@@ -24832,7 +24847,7 @@
       </c>
       <c r="B660" t="inlineStr">
         <is>
-          <t>paclock_pilot_frozen</t>
+          <t>paclock_pac</t>
         </is>
       </c>
       <c r="C660" t="inlineStr">
@@ -24859,7 +24874,7 @@
       </c>
       <c r="B661" t="inlineStr">
         <is>
-          <t>paclock_pilot_unfiltered</t>
+          <t>paclock_pilot_frozen</t>
         </is>
       </c>
       <c r="C661" t="inlineStr">
@@ -24886,22 +24901,22 @@
       </c>
       <c r="B662" t="inlineStr">
         <is>
-          <t>paclock_probe_rand</t>
+          <t>paclock_pilot_unfiltered</t>
         </is>
       </c>
       <c r="C662" t="inlineStr">
         <is>
-          <t>[0]</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D662" t="inlineStr">
         <is>
-          <t>filled (single-seed, grey)</t>
+          <t>skipped</t>
         </is>
       </c>
       <c r="E662" t="inlineStr">
         <is>
-          <t>cohen_kappa 0.3859</t>
+          <t>the workbook has no row for this variant</t>
         </is>
       </c>
     </row>
@@ -24913,22 +24928,22 @@
       </c>
       <c r="B663" t="inlineStr">
         <is>
-          <t>paclock_probe_v1</t>
+          <t>paclock_probe_rand</t>
         </is>
       </c>
       <c r="C663" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>[0]</t>
         </is>
       </c>
       <c r="D663" t="inlineStr">
         <is>
-          <t>skipped</t>
+          <t>filled (single-seed, grey)</t>
         </is>
       </c>
       <c r="E663" t="inlineStr">
         <is>
-          <t>no row label for 'paclock_probe_v1'</t>
+          <t>cohen_kappa 0.3859</t>
         </is>
       </c>
     </row>
@@ -24940,22 +24955,22 @@
       </c>
       <c r="B664" t="inlineStr">
         <is>
-          <t>paclock_probe_v2</t>
+          <t>paclock_probe_v1</t>
         </is>
       </c>
       <c r="C664" t="inlineStr">
         <is>
-          <t>[0]</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D664" t="inlineStr">
         <is>
-          <t>filled (single-seed, grey)</t>
+          <t>skipped</t>
         </is>
       </c>
       <c r="E664" t="inlineStr">
         <is>
-          <t>cohen_kappa 0.5184</t>
+          <t>no row label for 'paclock_probe_v1'</t>
         </is>
       </c>
     </row>
@@ -24967,22 +24982,22 @@
       </c>
       <c r="B665" t="inlineStr">
         <is>
-          <t>paclock_ptF_frozenL3</t>
+          <t>paclock_probe_v2</t>
         </is>
       </c>
       <c r="C665" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>[0]</t>
         </is>
       </c>
       <c r="D665" t="inlineStr">
         <is>
-          <t>skipped</t>
+          <t>filled (single-seed, grey)</t>
         </is>
       </c>
       <c r="E665" t="inlineStr">
         <is>
-          <t>no row label for 'paclock_ptF_frozenL3'</t>
+          <t>cohen_kappa 0.5184</t>
         </is>
       </c>
     </row>
@@ -24994,7 +25009,7 @@
       </c>
       <c r="B666" t="inlineStr">
         <is>
-          <t>paclock_pt_base</t>
+          <t>paclock_ptF_frozenL3</t>
         </is>
       </c>
       <c r="C666" t="inlineStr">
@@ -25009,7 +25024,7 @@
       </c>
       <c r="E666" t="inlineStr">
         <is>
-          <t>row 'PACLock (pretrained, base)' not found</t>
+          <t>no row label for 'paclock_ptF_frozenL3'</t>
         </is>
       </c>
     </row>
@@ -25021,7 +25036,7 @@
       </c>
       <c r="B667" t="inlineStr">
         <is>
-          <t>paclock_pt_base_p200</t>
+          <t>paclock_pt_base</t>
         </is>
       </c>
       <c r="C667" t="inlineStr">
@@ -25036,7 +25051,7 @@
       </c>
       <c r="E667" t="inlineStr">
         <is>
-          <t>no row label for 'paclock_pt_base_p200'</t>
+          <t>row 'PACLock (pretrained, base)' not found</t>
         </is>
       </c>
     </row>
@@ -25048,7 +25063,7 @@
       </c>
       <c r="B668" t="inlineStr">
         <is>
-          <t>paclock_pt_large</t>
+          <t>paclock_pt_base_p200</t>
         </is>
       </c>
       <c r="C668" t="inlineStr">
@@ -25063,7 +25078,7 @@
       </c>
       <c r="E668" t="inlineStr">
         <is>
-          <t>row 'PACLock (pretrained, large)' not found</t>
+          <t>no row label for 'paclock_pt_base_p200'</t>
         </is>
       </c>
     </row>
@@ -25075,7 +25090,7 @@
       </c>
       <c r="B669" t="inlineStr">
         <is>
-          <t>paclock_rawtok</t>
+          <t>paclock_pt_large</t>
         </is>
       </c>
       <c r="C669" t="inlineStr">
@@ -25090,7 +25105,7 @@
       </c>
       <c r="E669" t="inlineStr">
         <is>
-          <t>no row label for 'paclock_rawtok'</t>
+          <t>row 'PACLock (pretrained, large)' not found</t>
         </is>
       </c>
     </row>
@@ -25102,7 +25117,7 @@
       </c>
       <c r="B670" t="inlineStr">
         <is>
-          <t>paclock_rot2</t>
+          <t>paclock_rawtok</t>
         </is>
       </c>
       <c r="C670" t="inlineStr">
@@ -25117,7 +25132,7 @@
       </c>
       <c r="E670" t="inlineStr">
         <is>
-          <t>no row label for 'paclock_rot2'</t>
+          <t>no row label for 'paclock_rawtok'</t>
         </is>
       </c>
     </row>
@@ -25129,7 +25144,7 @@
       </c>
       <c r="B671" t="inlineStr">
         <is>
-          <t>paclock_rot_ms</t>
+          <t>paclock_rot2</t>
         </is>
       </c>
       <c r="C671" t="inlineStr">
@@ -25144,7 +25159,7 @@
       </c>
       <c r="E671" t="inlineStr">
         <is>
-          <t>no row label for 'paclock_rot_ms'</t>
+          <t>no row label for 'paclock_rot2'</t>
         </is>
       </c>
     </row>
@@ -25156,7 +25171,7 @@
       </c>
       <c r="B672" t="inlineStr">
         <is>
-          <t>paclock_sphead</t>
+          <t>paclock_rot_ms</t>
         </is>
       </c>
       <c r="C672" t="inlineStr">
@@ -25171,7 +25186,7 @@
       </c>
       <c r="E672" t="inlineStr">
         <is>
-          <t>no row label for 'paclock_sphead'</t>
+          <t>no row label for 'paclock_rot_ms'</t>
         </is>
       </c>
     </row>
@@ -25183,7 +25198,7 @@
       </c>
       <c r="B673" t="inlineStr">
         <is>
-          <t>paclock_v2</t>
+          <t>paclock_sphead</t>
         </is>
       </c>
       <c r="C673" t="inlineStr">
@@ -25198,7 +25213,7 @@
       </c>
       <c r="E673" t="inlineStr">
         <is>
-          <t>row 'PACLock (from scratch, full)' not found</t>
+          <t>no row label for 'paclock_sphead'</t>
         </is>
       </c>
     </row>
@@ -25210,7 +25225,7 @@
       </c>
       <c r="B674" t="inlineStr">
         <is>
-          <t>paclock_v2_n20000</t>
+          <t>paclock_v2</t>
         </is>
       </c>
       <c r="C674" t="inlineStr">
@@ -25225,7 +25240,7 @@
       </c>
       <c r="E674" t="inlineStr">
         <is>
-          <t>no row label for 'paclock_v2_n20000'</t>
+          <t>row 'PACLock (from scratch, full)' not found</t>
         </is>
       </c>
     </row>
@@ -25237,7 +25252,7 @@
       </c>
       <c r="B675" t="inlineStr">
         <is>
-          <t>paclock_v2_n2160</t>
+          <t>paclock_v2_n20000</t>
         </is>
       </c>
       <c r="C675" t="inlineStr">
@@ -25252,7 +25267,7 @@
       </c>
       <c r="E675" t="inlineStr">
         <is>
-          <t>no row label for 'paclock_v2_n2160'</t>
+          <t>no row label for 'paclock_v2_n20000'</t>
         </is>
       </c>
     </row>
@@ -25264,7 +25279,7 @@
       </c>
       <c r="B676" t="inlineStr">
         <is>
-          <t>paclock_v2_n6720</t>
+          <t>paclock_v2_n2160</t>
         </is>
       </c>
       <c r="C676" t="inlineStr">
@@ -25279,7 +25294,7 @@
       </c>
       <c r="E676" t="inlineStr">
         <is>
-          <t>no row label for 'paclock_v2_n6720'</t>
+          <t>no row label for 'paclock_v2_n2160'</t>
         </is>
       </c>
     </row>
@@ -25291,7 +25306,7 @@
       </c>
       <c r="B677" t="inlineStr">
         <is>
-          <t>paclock_v3traj_100000frozen</t>
+          <t>paclock_v2_n6720</t>
         </is>
       </c>
       <c r="C677" t="inlineStr">
@@ -25306,7 +25321,7 @@
       </c>
       <c r="E677" t="inlineStr">
         <is>
-          <t>no row label for 'paclock_v3traj_100000frozen'</t>
+          <t>no row label for 'paclock_v2_n6720'</t>
         </is>
       </c>
     </row>
@@ -25318,7 +25333,7 @@
       </c>
       <c r="B678" t="inlineStr">
         <is>
-          <t>paclock_v3traj_100000frozenL3</t>
+          <t>paclock_v3traj_100000frozen</t>
         </is>
       </c>
       <c r="C678" t="inlineStr">
@@ -25333,7 +25348,7 @@
       </c>
       <c r="E678" t="inlineStr">
         <is>
-          <t>no row label for 'paclock_v3traj_100000frozenL3'</t>
+          <t>no row label for 'paclock_v3traj_100000frozen'</t>
         </is>
       </c>
     </row>
@@ -25345,7 +25360,7 @@
       </c>
       <c r="B679" t="inlineStr">
         <is>
-          <t>paclock_v3traj_20000frozen</t>
+          <t>paclock_v3traj_100000frozenL3</t>
         </is>
       </c>
       <c r="C679" t="inlineStr">
@@ -25360,7 +25375,7 @@
       </c>
       <c r="E679" t="inlineStr">
         <is>
-          <t>no row label for 'paclock_v3traj_20000frozen'</t>
+          <t>no row label for 'paclock_v3traj_100000frozenL3'</t>
         </is>
       </c>
     </row>
@@ -25372,7 +25387,7 @@
       </c>
       <c r="B680" t="inlineStr">
         <is>
-          <t>paclock_v3traj_20000frozenL3</t>
+          <t>paclock_v3traj_20000frozen</t>
         </is>
       </c>
       <c r="C680" t="inlineStr">
@@ -25387,7 +25402,7 @@
       </c>
       <c r="E680" t="inlineStr">
         <is>
-          <t>no row label for 'paclock_v3traj_20000frozenL3'</t>
+          <t>no row label for 'paclock_v3traj_20000frozen'</t>
         </is>
       </c>
     </row>
@@ -25399,7 +25414,7 @@
       </c>
       <c r="B681" t="inlineStr">
         <is>
-          <t>paclock_v3traj_40000frozen</t>
+          <t>paclock_v3traj_20000frozenL3</t>
         </is>
       </c>
       <c r="C681" t="inlineStr">
@@ -25414,7 +25429,7 @@
       </c>
       <c r="E681" t="inlineStr">
         <is>
-          <t>no row label for 'paclock_v3traj_40000frozen'</t>
+          <t>no row label for 'paclock_v3traj_20000frozenL3'</t>
         </is>
       </c>
     </row>
@@ -25426,7 +25441,7 @@
       </c>
       <c r="B682" t="inlineStr">
         <is>
-          <t>paclock_v3traj_40000frozenL3</t>
+          <t>paclock_v3traj_40000frozen</t>
         </is>
       </c>
       <c r="C682" t="inlineStr">
@@ -25441,7 +25456,7 @@
       </c>
       <c r="E682" t="inlineStr">
         <is>
-          <t>no row label for 'paclock_v3traj_40000frozenL3'</t>
+          <t>no row label for 'paclock_v3traj_40000frozen'</t>
         </is>
       </c>
     </row>
@@ -25453,7 +25468,7 @@
       </c>
       <c r="B683" t="inlineStr">
         <is>
-          <t>paclock_v3traj_60000frozen</t>
+          <t>paclock_v3traj_40000frozenL3</t>
         </is>
       </c>
       <c r="C683" t="inlineStr">
@@ -25468,7 +25483,7 @@
       </c>
       <c r="E683" t="inlineStr">
         <is>
-          <t>no row label for 'paclock_v3traj_60000frozen'</t>
+          <t>no row label for 'paclock_v3traj_40000frozenL3'</t>
         </is>
       </c>
     </row>
@@ -25480,7 +25495,7 @@
       </c>
       <c r="B684" t="inlineStr">
         <is>
-          <t>paclock_v3traj_60000frozenL3</t>
+          <t>paclock_v3traj_60000frozen</t>
         </is>
       </c>
       <c r="C684" t="inlineStr">
@@ -25495,7 +25510,7 @@
       </c>
       <c r="E684" t="inlineStr">
         <is>
-          <t>no row label for 'paclock_v3traj_60000frozenL3'</t>
+          <t>no row label for 'paclock_v3traj_60000frozen'</t>
         </is>
       </c>
     </row>
@@ -25507,7 +25522,7 @@
       </c>
       <c r="B685" t="inlineStr">
         <is>
-          <t>paclock_v3traj_80000frozen</t>
+          <t>paclock_v3traj_60000frozenL3</t>
         </is>
       </c>
       <c r="C685" t="inlineStr">
@@ -25522,7 +25537,7 @@
       </c>
       <c r="E685" t="inlineStr">
         <is>
-          <t>no row label for 'paclock_v3traj_80000frozen'</t>
+          <t>no row label for 'paclock_v3traj_60000frozenL3'</t>
         </is>
       </c>
     </row>
@@ -25534,7 +25549,7 @@
       </c>
       <c r="B686" t="inlineStr">
         <is>
-          <t>paclock_v3traj_80000frozenL3</t>
+          <t>paclock_v3traj_80000frozen</t>
         </is>
       </c>
       <c r="C686" t="inlineStr">
@@ -25549,7 +25564,7 @@
       </c>
       <c r="E686" t="inlineStr">
         <is>
-          <t>no row label for 'paclock_v3traj_80000frozenL3'</t>
+          <t>no row label for 'paclock_v3traj_80000frozen'</t>
         </is>
       </c>
     </row>
@@ -25561,27 +25576,22 @@
       </c>
       <c r="B687" t="inlineStr">
         <is>
-          <t>reve_pretrained</t>
+          <t>paclock_v3traj_80000frozenL3</t>
         </is>
       </c>
       <c r="C687" t="inlineStr">
         <is>
-          <t>[0, 1, 2]</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D687" t="inlineStr">
         <is>
-          <t>filled</t>
+          <t>skipped</t>
         </is>
       </c>
       <c r="E687" t="inlineStr">
         <is>
-          <t>[实测 69.48M] cohen_kappa per-seed 0:0.7188, 1:0.6423, 2:0.6927</t>
-        </is>
-      </c>
-      <c r="F687" t="inlineStr">
-        <is>
-          <t>stopped_by=patience lr=0.0001 batch_size=128 epochs=30 patience=10 eval_every_steps=0 loss=cross_entropy label_smoothing=0.0 grad_clip=1.0</t>
+          <t>no row label for 'paclock_v3traj_80000frozenL3'</t>
         </is>
       </c>
     </row>
@@ -25593,7 +25603,7 @@
       </c>
       <c r="B688" t="inlineStr">
         <is>
-          <t>sparcnet</t>
+          <t>reve_pretrained</t>
         </is>
       </c>
       <c r="C688" t="inlineStr">
@@ -25608,12 +25618,12 @@
       </c>
       <c r="E688" t="inlineStr">
         <is>
-          <t>[实测 0.99M] cohen_kappa per-seed 0:0.4665, 1:0.5199, 2:0.4791</t>
+          <t>[实测 69.48M] cohen_kappa per-seed 0:0.7188, 1:0.6423, 2:0.6927</t>
         </is>
       </c>
       <c r="F688" t="inlineStr">
         <is>
-          <t>lr=0.001 batch_size=512 epochs=100 patience=15 eval_every_steps=0 loss=cross_entropy label_smoothing=0.1</t>
+          <t>stopped_by=patience lr=0.0001 batch_size=128 epochs=30 patience=10 eval_every_steps=0 loss=cross_entropy label_smoothing=0.0 grad_clip=1.0</t>
         </is>
       </c>
     </row>
@@ -25625,22 +25635,27 @@
       </c>
       <c r="B689" t="inlineStr">
         <is>
-          <t>sparcnet_n20000</t>
+          <t>sparcnet</t>
         </is>
       </c>
       <c r="C689" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>[0, 1, 2]</t>
         </is>
       </c>
       <c r="D689" t="inlineStr">
         <is>
-          <t>skipped</t>
+          <t>filled</t>
         </is>
       </c>
       <c r="E689" t="inlineStr">
         <is>
-          <t>no row label for 'sparcnet_n20000'</t>
+          <t>[实测 0.99M] cohen_kappa per-seed 0:0.4665, 1:0.5199, 2:0.4791</t>
+        </is>
+      </c>
+      <c r="F689" t="inlineStr">
+        <is>
+          <t>lr=0.001 batch_size=512 epochs=100 patience=15 eval_every_steps=0 loss=cross_entropy label_smoothing=0.1</t>
         </is>
       </c>
     </row>
@@ -25652,7 +25667,7 @@
       </c>
       <c r="B690" t="inlineStr">
         <is>
-          <t>sparcnet_n2160</t>
+          <t>sparcnet_n20000</t>
         </is>
       </c>
       <c r="C690" t="inlineStr">
@@ -25667,7 +25682,7 @@
       </c>
       <c r="E690" t="inlineStr">
         <is>
-          <t>no row label for 'sparcnet_n2160'</t>
+          <t>no row label for 'sparcnet_n20000'</t>
         </is>
       </c>
     </row>
@@ -25679,7 +25694,7 @@
       </c>
       <c r="B691" t="inlineStr">
         <is>
-          <t>sparcnet_n6720</t>
+          <t>sparcnet_n2160</t>
         </is>
       </c>
       <c r="C691" t="inlineStr">
@@ -25694,7 +25709,7 @@
       </c>
       <c r="E691" t="inlineStr">
         <is>
-          <t>no row label for 'sparcnet_n6720'</t>
+          <t>no row label for 'sparcnet_n2160'</t>
         </is>
       </c>
     </row>
@@ -25706,27 +25721,22 @@
       </c>
       <c r="B692" t="inlineStr">
         <is>
-          <t>st_transformer</t>
+          <t>sparcnet_n6720</t>
         </is>
       </c>
       <c r="C692" t="inlineStr">
         <is>
-          <t>[0, 1, 2]</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D692" t="inlineStr">
         <is>
-          <t>filled</t>
+          <t>skipped</t>
         </is>
       </c>
       <c r="E692" t="inlineStr">
         <is>
-          <t>[实测 3.43M] cohen_kappa per-seed 0:0.5139, 1:0.4916, 2:0.4962</t>
-        </is>
-      </c>
-      <c r="F692" t="inlineStr">
-        <is>
-          <t>lr=0.001 batch_size=512 epochs=100 patience=15 eval_every_steps=0 loss=cross_entropy label_smoothing=0.1</t>
+          <t>no row label for 'sparcnet_n6720'</t>
         </is>
       </c>
     </row>
@@ -25738,7 +25748,7 @@
       </c>
       <c r="B693" t="inlineStr">
         <is>
-          <t>tfm_pretrained</t>
+          <t>st_transformer</t>
         </is>
       </c>
       <c r="C693" t="inlineStr">
@@ -25753,24 +25763,24 @@
       </c>
       <c r="E693" t="inlineStr">
         <is>
-          <t>[实测 1.89M] cohen_kappa per-seed 0:0.6543, 1:0.6299, 2:0.6715</t>
+          <t>[实测 3.43M] cohen_kappa per-seed 0:0.5139, 1:0.4916, 2:0.4962</t>
         </is>
       </c>
       <c r="F693" t="inlineStr">
         <is>
-          <t>lr=0.001 batch_size=512 epochs=50 patience=10 eval_every_steps=100 loss=cross_entropy label_smoothing=0.1</t>
+          <t>lr=0.001 batch_size=512 epochs=100 patience=15 eval_every_steps=0 loss=cross_entropy label_smoothing=0.1</t>
         </is>
       </c>
     </row>
     <row r="694">
       <c r="A694" t="inlineStr">
         <is>
-          <t>tusz</t>
+          <t>tuev</t>
         </is>
       </c>
       <c r="B694" t="inlineStr">
         <is>
-          <t>biot_prest16</t>
+          <t>tfm_pretrained</t>
         </is>
       </c>
       <c r="C694" t="inlineStr">
@@ -25785,12 +25795,12 @@
       </c>
       <c r="E694" t="inlineStr">
         <is>
-          <t>[实测 3.19M] pr_auc per-seed 0:0.3673, 1:0.3513, 2:0.2951</t>
+          <t>[实测 1.89M] cohen_kappa per-seed 0:0.6543, 1:0.6299, 2:0.6715</t>
         </is>
       </c>
       <c r="F694" t="inlineStr">
         <is>
-          <t>lr=0.001 batch_size=512 epochs=100 patience=5 eval_every_steps=0 loss=bce_with_logits</t>
+          <t>lr=0.001 batch_size=512 epochs=50 patience=10 eval_every_steps=100 loss=cross_entropy label_smoothing=0.1</t>
         </is>
       </c>
     </row>
@@ -25802,7 +25812,7 @@
       </c>
       <c r="B695" t="inlineStr">
         <is>
-          <t>biot_scratch</t>
+          <t>biot_prest16</t>
         </is>
       </c>
       <c r="C695" t="inlineStr">
@@ -25817,7 +25827,7 @@
       </c>
       <c r="E695" t="inlineStr">
         <is>
-          <t>[实测 3.19M] pr_auc per-seed 0:0.3186, 1:0.3682, 2:0.3556</t>
+          <t>[实测 3.19M] pr_auc per-seed 0:0.3673, 1:0.3513, 2:0.2951</t>
         </is>
       </c>
       <c r="F695" t="inlineStr">
@@ -25834,22 +25844,27 @@
       </c>
       <c r="B696" t="inlineStr">
         <is>
-          <t>cbramod_pac</t>
+          <t>biot_scratch</t>
         </is>
       </c>
       <c r="C696" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>[0, 1, 2]</t>
         </is>
       </c>
       <c r="D696" t="inlineStr">
         <is>
-          <t>skipped</t>
+          <t>filled</t>
         </is>
       </c>
       <c r="E696" t="inlineStr">
         <is>
-          <t>the workbook has no row for this variant</t>
+          <t>[实测 3.19M] pr_auc per-seed 0:0.3186, 1:0.3682, 2:0.3556</t>
+        </is>
+      </c>
+      <c r="F696" t="inlineStr">
+        <is>
+          <t>lr=0.001 batch_size=512 epochs=100 patience=5 eval_every_steps=0 loss=bce_with_logits</t>
         </is>
       </c>
     </row>
@@ -25861,27 +25876,22 @@
       </c>
       <c r="B697" t="inlineStr">
         <is>
-          <t>cbramod_pretrained</t>
+          <t>cbramod_pac</t>
         </is>
       </c>
       <c r="C697" t="inlineStr">
         <is>
-          <t>[0, 1, 2]</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D697" t="inlineStr">
         <is>
-          <t>filled</t>
+          <t>skipped</t>
         </is>
       </c>
       <c r="E697" t="inlineStr">
         <is>
-          <t>[实测 30.65M] pr_auc per-seed 0:0.4139, 1:0.4061, 2:0.4831</t>
-        </is>
-      </c>
-      <c r="F697" t="inlineStr">
-        <is>
-          <t>lr=0.0001 batch_size=64 epochs=50 patience=0 eval_every_steps=0 loss=bce_with_logits grad_clip=1.0 select_metric=auroc multi_lr=True</t>
+          <t>the workbook has no row for this variant</t>
         </is>
       </c>
     </row>
@@ -25893,22 +25903,27 @@
       </c>
       <c r="B698" t="inlineStr">
         <is>
-          <t>cbramod_rawfe_bands</t>
+          <t>cbramod_pretrained</t>
         </is>
       </c>
       <c r="C698" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>[0, 1, 2]</t>
         </is>
       </c>
       <c r="D698" t="inlineStr">
         <is>
-          <t>skipped</t>
+          <t>filled</t>
         </is>
       </c>
       <c r="E698" t="inlineStr">
         <is>
-          <t>no row label for 'cbramod_rawfe_bands'</t>
+          <t>[实测 30.65M] pr_auc per-seed 0:0.4139, 1:0.4061, 2:0.4831</t>
+        </is>
+      </c>
+      <c r="F698" t="inlineStr">
+        <is>
+          <t>lr=0.0001 batch_size=64 epochs=50 patience=0 eval_every_steps=0 loss=bce_with_logits grad_clip=1.0 select_metric=auroc multi_lr=True</t>
         </is>
       </c>
     </row>
@@ -25920,27 +25935,22 @@
       </c>
       <c r="B699" t="inlineStr">
         <is>
-          <t>cbramod_scratch</t>
+          <t>cbramod_rawfe_bands</t>
         </is>
       </c>
       <c r="C699" t="inlineStr">
         <is>
-          <t>[0, 1, 2]</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D699" t="inlineStr">
         <is>
-          <t>filled</t>
+          <t>skipped</t>
         </is>
       </c>
       <c r="E699" t="inlineStr">
         <is>
-          <t>[实测 30.65M] pr_auc per-seed 0:0.4662, 1:0.5401, 2:0.4392</t>
-        </is>
-      </c>
-      <c r="F699" t="inlineStr">
-        <is>
-          <t>lr=0.0001 batch_size=64 epochs=50 patience=0 eval_every_steps=0 loss=bce_with_logits grad_clip=1.0 select_metric=auroc multi_lr=True</t>
+          <t>no row label for 'cbramod_rawfe_bands'</t>
         </is>
       </c>
     </row>
@@ -25952,7 +25962,7 @@
       </c>
       <c r="B700" t="inlineStr">
         <is>
-          <t>cnn_transformer</t>
+          <t>cbramod_scratch</t>
         </is>
       </c>
       <c r="C700" t="inlineStr">
@@ -25967,12 +25977,12 @@
       </c>
       <c r="E700" t="inlineStr">
         <is>
-          <t>[实测 3.15M] pr_auc per-seed 0:0.1493, 1:0.4554, 2:0.5073  [seed spread 43% -- mean is a weak summary]</t>
+          <t>[实测 30.65M] pr_auc per-seed 0:0.4662, 1:0.5401, 2:0.4392</t>
         </is>
       </c>
       <c r="F700" t="inlineStr">
         <is>
-          <t>lr=0.001 batch_size=512 epochs=20 patience=8 eval_every_steps=200 loss=bce_with_logits</t>
+          <t>lr=0.0001 batch_size=64 epochs=50 patience=0 eval_every_steps=0 loss=bce_with_logits grad_clip=1.0 select_metric=auroc multi_lr=True</t>
         </is>
       </c>
     </row>
@@ -25984,7 +25994,7 @@
       </c>
       <c r="B701" t="inlineStr">
         <is>
-          <t>contrawr</t>
+          <t>cnn_transformer</t>
         </is>
       </c>
       <c r="C701" t="inlineStr">
@@ -25999,7 +26009,7 @@
       </c>
       <c r="E701" t="inlineStr">
         <is>
-          <t>[实测 1.57M] pr_auc per-seed 0:0.5188, 1:0.4849, 2:0.5092</t>
+          <t>[实测 3.15M] pr_auc per-seed 0:0.1493, 1:0.4554, 2:0.5073  [seed spread 43% -- mean is a weak summary]</t>
         </is>
       </c>
       <c r="F701" t="inlineStr">
@@ -26016,7 +26026,7 @@
       </c>
       <c r="B702" t="inlineStr">
         <is>
-          <t>csbrain_pretrained</t>
+          <t>contrawr</t>
         </is>
       </c>
       <c r="C702" t="inlineStr">
@@ -26031,12 +26041,12 @@
       </c>
       <c r="E702" t="inlineStr">
         <is>
-          <t>[实测 41.06M] pr_auc per-seed 0:0.6207, 1:0.3889, 2:0.5414  [seed spread 19% -- mean is a weak summary]</t>
+          <t>[实测 1.57M] pr_auc per-seed 0:0.5188, 1:0.4849, 2:0.5092</t>
         </is>
       </c>
       <c r="F702" t="inlineStr">
         <is>
-          <t>stopped_by=patience lr=0.0001 batch_size=64 epochs=25 patience=10 eval_every_steps=500 loss=bce_with_logits grad_clip=1.0</t>
+          <t>lr=0.001 batch_size=512 epochs=20 patience=8 eval_every_steps=200 loss=bce_with_logits</t>
         </is>
       </c>
     </row>
@@ -26048,7 +26058,7 @@
       </c>
       <c r="B703" t="inlineStr">
         <is>
-          <t>eegconformer</t>
+          <t>csbrain_pretrained</t>
         </is>
       </c>
       <c r="C703" t="inlineStr">
@@ -26063,12 +26073,12 @@
       </c>
       <c r="E703" t="inlineStr">
         <is>
-          <t>[实测 1.46M] pr_auc per-seed 0:0.3624, 1:0.2985, 2:0.2961</t>
+          <t>[实测 41.06M] pr_auc per-seed 0:0.6207, 1:0.3889, 2:0.5414  [seed spread 19% -- mean is a weak summary]</t>
         </is>
       </c>
       <c r="F703" t="inlineStr">
         <is>
-          <t>stopped_by=patience lr=0.001 batch_size=128 epochs=20 patience=8 eval_every_steps=200 loss=bce_with_logits grad_clip=1.0</t>
+          <t>stopped_by=patience lr=0.0001 batch_size=64 epochs=25 patience=10 eval_every_steps=500 loss=bce_with_logits grad_clip=1.0</t>
         </is>
       </c>
     </row>
@@ -26080,22 +26090,27 @@
       </c>
       <c r="B704" t="inlineStr">
         <is>
-          <t>eegconformer_t1</t>
+          <t>eegconformer</t>
         </is>
       </c>
       <c r="C704" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>[0, 1, 2]</t>
         </is>
       </c>
       <c r="D704" t="inlineStr">
         <is>
-          <t>skipped</t>
+          <t>filled</t>
         </is>
       </c>
       <c r="E704" t="inlineStr">
         <is>
-          <t>no row label for 'eegconformer_t1'</t>
+          <t>[实测 1.46M] pr_auc per-seed 0:0.3624, 1:0.2985, 2:0.2961</t>
+        </is>
+      </c>
+      <c r="F704" t="inlineStr">
+        <is>
+          <t>stopped_by=patience lr=0.001 batch_size=128 epochs=20 patience=8 eval_every_steps=200 loss=bce_with_logits grad_clip=1.0</t>
         </is>
       </c>
     </row>
@@ -26107,7 +26122,7 @@
       </c>
       <c r="B705" t="inlineStr">
         <is>
-          <t>eegconformer_t2</t>
+          <t>eegconformer_t1</t>
         </is>
       </c>
       <c r="C705" t="inlineStr">
@@ -26122,7 +26137,7 @@
       </c>
       <c r="E705" t="inlineStr">
         <is>
-          <t>no row label for 'eegconformer_t2'</t>
+          <t>no row label for 'eegconformer_t1'</t>
         </is>
       </c>
     </row>
@@ -26134,7 +26149,7 @@
       </c>
       <c r="B706" t="inlineStr">
         <is>
-          <t>eegconformer_t3</t>
+          <t>eegconformer_t2</t>
         </is>
       </c>
       <c r="C706" t="inlineStr">
@@ -26149,7 +26164,7 @@
       </c>
       <c r="E706" t="inlineStr">
         <is>
-          <t>no row label for 'eegconformer_t3'</t>
+          <t>no row label for 'eegconformer_t2'</t>
         </is>
       </c>
     </row>
@@ -26161,7 +26176,7 @@
       </c>
       <c r="B707" t="inlineStr">
         <is>
-          <t>eegconformer_t4</t>
+          <t>eegconformer_t3</t>
         </is>
       </c>
       <c r="C707" t="inlineStr">
@@ -26176,7 +26191,7 @@
       </c>
       <c r="E707" t="inlineStr">
         <is>
-          <t>no row label for 'eegconformer_t4'</t>
+          <t>no row label for 'eegconformer_t3'</t>
         </is>
       </c>
     </row>
@@ -26188,27 +26203,22 @@
       </c>
       <c r="B708" t="inlineStr">
         <is>
-          <t>eegnet</t>
+          <t>eegconformer_t4</t>
         </is>
       </c>
       <c r="C708" t="inlineStr">
         <is>
-          <t>[0, 1, 2]</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D708" t="inlineStr">
         <is>
-          <t>filled</t>
+          <t>skipped</t>
         </is>
       </c>
       <c r="E708" t="inlineStr">
         <is>
-          <t>[实测 0.00M] pr_auc per-seed 0:0.4598, 1:0.4970, 2:0.5196</t>
-        </is>
-      </c>
-      <c r="F708" t="inlineStr">
-        <is>
-          <t>stopped_by=patience lr=0.001 batch_size=512 epochs=20 patience=8 eval_every_steps=200 loss=bce_with_logits grad_clip=1.0</t>
+          <t>no row label for 'eegconformer_t4'</t>
         </is>
       </c>
     </row>
@@ -26220,22 +26230,27 @@
       </c>
       <c r="B709" t="inlineStr">
         <is>
-          <t>eegnet_t1</t>
+          <t>eegnet</t>
         </is>
       </c>
       <c r="C709" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>[0, 1, 2]</t>
         </is>
       </c>
       <c r="D709" t="inlineStr">
         <is>
-          <t>skipped</t>
+          <t>filled</t>
         </is>
       </c>
       <c r="E709" t="inlineStr">
         <is>
-          <t>no row label for 'eegnet_t1'</t>
+          <t>[实测 0.00M] pr_auc per-seed 0:0.4598, 1:0.4970, 2:0.5196</t>
+        </is>
+      </c>
+      <c r="F709" t="inlineStr">
+        <is>
+          <t>stopped_by=patience lr=0.001 batch_size=512 epochs=20 patience=8 eval_every_steps=200 loss=bce_with_logits grad_clip=1.0</t>
         </is>
       </c>
     </row>
@@ -26247,7 +26262,7 @@
       </c>
       <c r="B710" t="inlineStr">
         <is>
-          <t>eegnet_t2</t>
+          <t>eegnet_t1</t>
         </is>
       </c>
       <c r="C710" t="inlineStr">
@@ -26262,7 +26277,7 @@
       </c>
       <c r="E710" t="inlineStr">
         <is>
-          <t>no row label for 'eegnet_t2'</t>
+          <t>no row label for 'eegnet_t1'</t>
         </is>
       </c>
     </row>
@@ -26274,7 +26289,7 @@
       </c>
       <c r="B711" t="inlineStr">
         <is>
-          <t>eegnet_t3</t>
+          <t>eegnet_t2</t>
         </is>
       </c>
       <c r="C711" t="inlineStr">
@@ -26289,7 +26304,7 @@
       </c>
       <c r="E711" t="inlineStr">
         <is>
-          <t>no row label for 'eegnet_t3'</t>
+          <t>no row label for 'eegnet_t2'</t>
         </is>
       </c>
     </row>
@@ -26301,7 +26316,7 @@
       </c>
       <c r="B712" t="inlineStr">
         <is>
-          <t>eegnet_t4</t>
+          <t>eegnet_t3</t>
         </is>
       </c>
       <c r="C712" t="inlineStr">
@@ -26316,7 +26331,7 @@
       </c>
       <c r="E712" t="inlineStr">
         <is>
-          <t>no row label for 'eegnet_t4'</t>
+          <t>no row label for 'eegnet_t3'</t>
         </is>
       </c>
     </row>
@@ -26328,27 +26343,22 @@
       </c>
       <c r="B713" t="inlineStr">
         <is>
-          <t>eegpt_pretrained</t>
+          <t>eegnet_t4</t>
         </is>
       </c>
       <c r="C713" t="inlineStr">
         <is>
-          <t>[0, 1, 2]</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D713" t="inlineStr">
         <is>
-          <t>filled</t>
+          <t>skipped</t>
         </is>
       </c>
       <c r="E713" t="inlineStr">
         <is>
-          <t>[实测 25.69M] pr_auc per-seed 0:0.6257, 1:0.5102, 2:0.4980</t>
-        </is>
-      </c>
-      <c r="F713" t="inlineStr">
-        <is>
-          <t>lr=0.0004 batch_size=32 epochs=40 patience=10 eval_every_steps=500 loss=bce_with_logits</t>
+          <t>no row label for 'eegnet_t4'</t>
         </is>
       </c>
     </row>
@@ -26360,7 +26370,7 @@
       </c>
       <c r="B714" t="inlineStr">
         <is>
-          <t>feat_best</t>
+          <t>eegpt_pretrained</t>
         </is>
       </c>
       <c r="C714" t="inlineStr">
@@ -26375,12 +26385,12 @@
       </c>
       <c r="E714" t="inlineStr">
         <is>
-          <t>[实测 0.00M] pr_auc per-seed 0:0.2384, 1:0.2384, 2:0.2384</t>
+          <t>[实测 25.69M] pr_auc per-seed 0:0.6257, 1:0.5102, 2:0.4980</t>
         </is>
       </c>
       <c r="F714" t="inlineStr">
         <is>
-          <t>stopped_by=closed-form epochs=1 loss=closed-form</t>
+          <t>lr=0.0004 batch_size=32 epochs=40 patience=10 eval_every_steps=500 loss=bce_with_logits</t>
         </is>
       </c>
     </row>
@@ -26392,7 +26402,7 @@
       </c>
       <c r="B715" t="inlineStr">
         <is>
-          <t>ffcl</t>
+          <t>feat_best</t>
         </is>
       </c>
       <c r="C715" t="inlineStr">
@@ -26407,12 +26417,12 @@
       </c>
       <c r="E715" t="inlineStr">
         <is>
-          <t>[实测 2.46M] pr_auc per-seed 0:0.5511, 1:0.5126, 2:0.5709</t>
+          <t>[实测 0.00M] pr_auc per-seed 0:0.2384, 1:0.2384, 2:0.2384</t>
         </is>
       </c>
       <c r="F715" t="inlineStr">
         <is>
-          <t>lr=0.001 batch_size=512 epochs=20 patience=8 eval_every_steps=200 loss=bce_with_logits</t>
+          <t>stopped_by=closed-form epochs=1 loss=closed-form</t>
         </is>
       </c>
     </row>
@@ -26424,7 +26434,7 @@
       </c>
       <c r="B716" t="inlineStr">
         <is>
-          <t>labram_pretrained</t>
+          <t>ffcl</t>
         </is>
       </c>
       <c r="C716" t="inlineStr">
@@ -26439,12 +26449,12 @@
       </c>
       <c r="E716" t="inlineStr">
         <is>
-          <t>[实测 5.82M] pr_auc per-seed 0:0.4828, 1:0.5186, 2:0.4249</t>
+          <t>[实测 2.46M] pr_auc per-seed 0:0.5511, 1:0.5126, 2:0.5709</t>
         </is>
       </c>
       <c r="F716" t="inlineStr">
         <is>
-          <t>lr=0.0005 batch_size=64 epochs=50 patience=10 eval_every_steps=100 loss=bce_with_logits</t>
+          <t>lr=0.001 batch_size=512 epochs=20 patience=8 eval_every_steps=200 loss=bce_with_logits</t>
         </is>
       </c>
     </row>
@@ -26456,7 +26466,7 @@
       </c>
       <c r="B717" t="inlineStr">
         <is>
-          <t>labram_scratch</t>
+          <t>labram_pretrained</t>
         </is>
       </c>
       <c r="C717" t="inlineStr">
@@ -26471,12 +26481,12 @@
       </c>
       <c r="E717" t="inlineStr">
         <is>
-          <t>[实测 5.82M] pr_auc per-seed 0:0.4201, 1:0.5036, 2:0.5020</t>
+          <t>[实测 5.82M] pr_auc per-seed 0:0.4828, 1:0.5186, 2:0.4249</t>
         </is>
       </c>
       <c r="F717" t="inlineStr">
         <is>
-          <t>stopped_by=patience lr=0.0005 batch_size=64 epochs=50 patience=10 eval_every_steps=0 loss=bce_with_logits</t>
+          <t>lr=0.0005 batch_size=64 epochs=50 patience=10 eval_every_steps=100 loss=bce_with_logits</t>
         </is>
       </c>
     </row>
@@ -26488,22 +26498,27 @@
       </c>
       <c r="B718" t="inlineStr">
         <is>
-          <t>paclock_duplex</t>
+          <t>labram_scratch</t>
         </is>
       </c>
       <c r="C718" t="inlineStr">
         <is>
-          <t>[0]</t>
+          <t>[0, 1, 2]</t>
         </is>
       </c>
       <c r="D718" t="inlineStr">
         <is>
-          <t>filled (single-seed, grey)</t>
+          <t>filled</t>
         </is>
       </c>
       <c r="E718" t="inlineStr">
         <is>
-          <t>pr_auc 0.6328</t>
+          <t>[实测 5.82M] pr_auc per-seed 0:0.4201, 1:0.5036, 2:0.5020</t>
+        </is>
+      </c>
+      <c r="F718" t="inlineStr">
+        <is>
+          <t>stopped_by=patience lr=0.0005 batch_size=64 epochs=50 patience=10 eval_every_steps=0 loss=bce_with_logits</t>
         </is>
       </c>
     </row>
@@ -26515,22 +26530,22 @@
       </c>
       <c r="B719" t="inlineStr">
         <is>
-          <t>paclock_duplex_ms</t>
+          <t>paclock_duplex</t>
         </is>
       </c>
       <c r="C719" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>[0]</t>
         </is>
       </c>
       <c r="D719" t="inlineStr">
         <is>
-          <t>skipped</t>
+          <t>filled (single-seed, grey)</t>
         </is>
       </c>
       <c r="E719" t="inlineStr">
         <is>
-          <t>no row label for 'paclock_duplex_ms'</t>
+          <t>pr_auc 0.6328</t>
         </is>
       </c>
     </row>
@@ -26542,7 +26557,7 @@
       </c>
       <c r="B720" t="inlineStr">
         <is>
-          <t>paclock_duplex_p200</t>
+          <t>paclock_duplex_ms</t>
         </is>
       </c>
       <c r="C720" t="inlineStr">
@@ -26557,7 +26572,7 @@
       </c>
       <c r="E720" t="inlineStr">
         <is>
-          <t>no row label for 'paclock_duplex_p200'</t>
+          <t>no row label for 'paclock_duplex_ms'</t>
         </is>
       </c>
     </row>
@@ -26569,7 +26584,7 @@
       </c>
       <c r="B721" t="inlineStr">
         <is>
-          <t>paclock_duplex_p200ptF</t>
+          <t>paclock_duplex_p200</t>
         </is>
       </c>
       <c r="C721" t="inlineStr">
@@ -26584,7 +26599,7 @@
       </c>
       <c r="E721" t="inlineStr">
         <is>
-          <t>no row label for 'paclock_duplex_p200ptF'</t>
+          <t>no row label for 'paclock_duplex_p200'</t>
         </is>
       </c>
     </row>
@@ -26596,7 +26611,7 @@
       </c>
       <c r="B722" t="inlineStr">
         <is>
-          <t>paclock_duplex_pt</t>
+          <t>paclock_duplex_p200ptF</t>
         </is>
       </c>
       <c r="C722" t="inlineStr">
@@ -26611,7 +26626,7 @@
       </c>
       <c r="E722" t="inlineStr">
         <is>
-          <t>row 'PACLock (duplex, pretrained)' not found</t>
+          <t>no row label for 'paclock_duplex_p200ptF'</t>
         </is>
       </c>
     </row>
@@ -26623,22 +26638,22 @@
       </c>
       <c r="B723" t="inlineStr">
         <is>
-          <t>paclock_duplex_pt2</t>
+          <t>paclock_duplex_pt</t>
         </is>
       </c>
       <c r="C723" t="inlineStr">
         <is>
-          <t>[0]</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D723" t="inlineStr">
         <is>
-          <t>filled (single-seed, grey)</t>
+          <t>skipped</t>
         </is>
       </c>
       <c r="E723" t="inlineStr">
         <is>
-          <t>pr_auc 0.7143</t>
+          <t>row 'PACLock (duplex, pretrained)' not found</t>
         </is>
       </c>
     </row>
@@ -26650,22 +26665,22 @@
       </c>
       <c r="B724" t="inlineStr">
         <is>
-          <t>paclock_duplex_ptF</t>
+          <t>paclock_duplex_pt2</t>
         </is>
       </c>
       <c r="C724" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>[0]</t>
         </is>
       </c>
       <c r="D724" t="inlineStr">
         <is>
-          <t>skipped</t>
+          <t>filled (single-seed, grey)</t>
         </is>
       </c>
       <c r="E724" t="inlineStr">
         <is>
-          <t>row 'CroFreMo (预训练 v2-full)' not found</t>
+          <t>pr_auc 0.7143</t>
         </is>
       </c>
     </row>
@@ -26677,22 +26692,22 @@
       </c>
       <c r="B725" t="inlineStr">
         <is>
-          <t>paclock_duplex_ptS</t>
+          <t>paclock_duplex_ptF</t>
         </is>
       </c>
       <c r="C725" t="inlineStr">
         <is>
-          <t>[0]</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D725" t="inlineStr">
         <is>
-          <t>filled (single-seed, grey)</t>
+          <t>skipped</t>
         </is>
       </c>
       <c r="E725" t="inlineStr">
         <is>
-          <t>pr_auc 0.6525</t>
+          <t>row 'CroFreMo (预训练 v2-full)' not found</t>
         </is>
       </c>
     </row>
@@ -26704,22 +26719,22 @@
       </c>
       <c r="B726" t="inlineStr">
         <is>
-          <t>paclock_fg_gms</t>
+          <t>paclock_duplex_ptS</t>
         </is>
       </c>
       <c r="C726" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>[0]</t>
         </is>
       </c>
       <c r="D726" t="inlineStr">
         <is>
-          <t>skipped</t>
+          <t>filled (single-seed, grey)</t>
         </is>
       </c>
       <c r="E726" t="inlineStr">
         <is>
-          <t>no row label for 'paclock_fg_gms'</t>
+          <t>pr_auc 0.6525</t>
         </is>
       </c>
     </row>
@@ -26731,7 +26746,7 @@
       </c>
       <c r="B727" t="inlineStr">
         <is>
-          <t>paclock_fg_stem</t>
+          <t>paclock_fg_gms</t>
         </is>
       </c>
       <c r="C727" t="inlineStr">
@@ -26746,7 +26761,7 @@
       </c>
       <c r="E727" t="inlineStr">
         <is>
-          <t>no row label for 'paclock_fg_stem'</t>
+          <t>no row label for 'paclock_fg_gms'</t>
         </is>
       </c>
     </row>
@@ -26758,7 +26773,7 @@
       </c>
       <c r="B728" t="inlineStr">
         <is>
-          <t>paclock_flagship</t>
+          <t>paclock_fg_stem</t>
         </is>
       </c>
       <c r="C728" t="inlineStr">
@@ -26773,7 +26788,7 @@
       </c>
       <c r="E728" t="inlineStr">
         <is>
-          <t>no row label for 'paclock_flagship'</t>
+          <t>no row label for 'paclock_fg_stem'</t>
         </is>
       </c>
     </row>
@@ -26785,7 +26800,7 @@
       </c>
       <c r="B729" t="inlineStr">
         <is>
-          <t>paclock_fuse</t>
+          <t>paclock_flagship</t>
         </is>
       </c>
       <c r="C729" t="inlineStr">
@@ -26800,7 +26815,7 @@
       </c>
       <c r="E729" t="inlineStr">
         <is>
-          <t>no row label for 'paclock_fuse'</t>
+          <t>no row label for 'paclock_flagship'</t>
         </is>
       </c>
     </row>
@@ -26812,7 +26827,7 @@
       </c>
       <c r="B730" t="inlineStr">
         <is>
-          <t>paclock_fusegate</t>
+          <t>paclock_fuse</t>
         </is>
       </c>
       <c r="C730" t="inlineStr">
@@ -26827,7 +26842,7 @@
       </c>
       <c r="E730" t="inlineStr">
         <is>
-          <t>no row label for 'paclock_fusegate'</t>
+          <t>no row label for 'paclock_fuse'</t>
         </is>
       </c>
     </row>
@@ -26839,7 +26854,7 @@
       </c>
       <c r="B731" t="inlineStr">
         <is>
-          <t>paclock_fusegate_ms</t>
+          <t>paclock_fusegate</t>
         </is>
       </c>
       <c r="C731" t="inlineStr">
@@ -26854,7 +26869,7 @@
       </c>
       <c r="E731" t="inlineStr">
         <is>
-          <t>no row label for 'paclock_fusegate_ms'</t>
+          <t>no row label for 'paclock_fusegate'</t>
         </is>
       </c>
     </row>
@@ -26866,7 +26881,7 @@
       </c>
       <c r="B732" t="inlineStr">
         <is>
-          <t>paclock_hybrid</t>
+          <t>paclock_fusegate_ms</t>
         </is>
       </c>
       <c r="C732" t="inlineStr">
@@ -26881,7 +26896,7 @@
       </c>
       <c r="E732" t="inlineStr">
         <is>
-          <t>no row label for 'paclock_hybrid'</t>
+          <t>no row label for 'paclock_fusegate_ms'</t>
         </is>
       </c>
     </row>
@@ -26893,7 +26908,7 @@
       </c>
       <c r="B733" t="inlineStr">
         <is>
-          <t>paclock_hybrid_attn</t>
+          <t>paclock_hybrid</t>
         </is>
       </c>
       <c r="C733" t="inlineStr">
@@ -26908,7 +26923,7 @@
       </c>
       <c r="E733" t="inlineStr">
         <is>
-          <t>no row label for 'paclock_hybrid_attn'</t>
+          <t>no row label for 'paclock_hybrid'</t>
         </is>
       </c>
     </row>
@@ -26920,7 +26935,7 @@
       </c>
       <c r="B734" t="inlineStr">
         <is>
-          <t>paclock_hybrid_gate</t>
+          <t>paclock_hybrid_attn</t>
         </is>
       </c>
       <c r="C734" t="inlineStr">
@@ -26935,7 +26950,7 @@
       </c>
       <c r="E734" t="inlineStr">
         <is>
-          <t>no row label for 'paclock_hybrid_gate'</t>
+          <t>no row label for 'paclock_hybrid_attn'</t>
         </is>
       </c>
     </row>
@@ -26947,7 +26962,7 @@
       </c>
       <c r="B735" t="inlineStr">
         <is>
-          <t>paclock_lf05_ptF</t>
+          <t>paclock_hybrid_gate</t>
         </is>
       </c>
       <c r="C735" t="inlineStr">
@@ -26962,7 +26977,7 @@
       </c>
       <c r="E735" t="inlineStr">
         <is>
-          <t>no row label for 'paclock_lf05_ptF'</t>
+          <t>no row label for 'paclock_hybrid_gate'</t>
         </is>
       </c>
     </row>
@@ -26974,7 +26989,7 @@
       </c>
       <c r="B736" t="inlineStr">
         <is>
-          <t>paclock_lf05_scratch</t>
+          <t>paclock_lf05_ptF</t>
         </is>
       </c>
       <c r="C736" t="inlineStr">
@@ -26989,7 +27004,7 @@
       </c>
       <c r="E736" t="inlineStr">
         <is>
-          <t>no row label for 'paclock_lf05_scratch'</t>
+          <t>no row label for 'paclock_lf05_ptF'</t>
         </is>
       </c>
     </row>
@@ -27001,7 +27016,7 @@
       </c>
       <c r="B737" t="inlineStr">
         <is>
-          <t>paclock_lf10_ptF</t>
+          <t>paclock_lf05_scratch</t>
         </is>
       </c>
       <c r="C737" t="inlineStr">
@@ -27016,7 +27031,7 @@
       </c>
       <c r="E737" t="inlineStr">
         <is>
-          <t>no row label for 'paclock_lf10_ptF'</t>
+          <t>no row label for 'paclock_lf05_scratch'</t>
         </is>
       </c>
     </row>
@@ -27028,7 +27043,7 @@
       </c>
       <c r="B738" t="inlineStr">
         <is>
-          <t>paclock_lf10_scratch</t>
+          <t>paclock_lf10_ptF</t>
         </is>
       </c>
       <c r="C738" t="inlineStr">
@@ -27043,7 +27058,7 @@
       </c>
       <c r="E738" t="inlineStr">
         <is>
-          <t>no row label for 'paclock_lf10_scratch'</t>
+          <t>no row label for 'paclock_lf10_ptF'</t>
         </is>
       </c>
     </row>
@@ -27055,7 +27070,7 @@
       </c>
       <c r="B739" t="inlineStr">
         <is>
-          <t>paclock_lf25_ptF</t>
+          <t>paclock_lf10_scratch</t>
         </is>
       </c>
       <c r="C739" t="inlineStr">
@@ -27070,7 +27085,7 @@
       </c>
       <c r="E739" t="inlineStr">
         <is>
-          <t>no row label for 'paclock_lf25_ptF'</t>
+          <t>no row label for 'paclock_lf10_scratch'</t>
         </is>
       </c>
     </row>
@@ -27082,7 +27097,7 @@
       </c>
       <c r="B740" t="inlineStr">
         <is>
-          <t>paclock_lf25_scratch</t>
+          <t>paclock_lf25_ptF</t>
         </is>
       </c>
       <c r="C740" t="inlineStr">
@@ -27097,7 +27112,7 @@
       </c>
       <c r="E740" t="inlineStr">
         <is>
-          <t>no row label for 'paclock_lf25_scratch'</t>
+          <t>no row label for 'paclock_lf25_ptF'</t>
         </is>
       </c>
     </row>
@@ -27109,7 +27124,7 @@
       </c>
       <c r="B741" t="inlineStr">
         <is>
-          <t>paclock_p200_pt</t>
+          <t>paclock_lf25_scratch</t>
         </is>
       </c>
       <c r="C741" t="inlineStr">
@@ -27124,7 +27139,7 @@
       </c>
       <c r="E741" t="inlineStr">
         <is>
-          <t>no row label for 'paclock_p200_pt'</t>
+          <t>no row label for 'paclock_lf25_scratch'</t>
         </is>
       </c>
     </row>
@@ -27136,7 +27151,7 @@
       </c>
       <c r="B742" t="inlineStr">
         <is>
-          <t>paclock_p200_pt_notok</t>
+          <t>paclock_p200_pt</t>
         </is>
       </c>
       <c r="C742" t="inlineStr">
@@ -27151,7 +27166,7 @@
       </c>
       <c r="E742" t="inlineStr">
         <is>
-          <t>no row label for 'paclock_p200_pt_notok'</t>
+          <t>no row label for 'paclock_p200_pt'</t>
         </is>
       </c>
     </row>
@@ -27163,7 +27178,7 @@
       </c>
       <c r="B743" t="inlineStr">
         <is>
-          <t>paclock_p200_scratch</t>
+          <t>paclock_p200_pt_notok</t>
         </is>
       </c>
       <c r="C743" t="inlineStr">
@@ -27178,7 +27193,7 @@
       </c>
       <c r="E743" t="inlineStr">
         <is>
-          <t>no row label for 'paclock_p200_scratch'</t>
+          <t>no row label for 'paclock_p200_pt_notok'</t>
         </is>
       </c>
     </row>
@@ -27190,7 +27205,7 @@
       </c>
       <c r="B744" t="inlineStr">
         <is>
-          <t>paclock_pac</t>
+          <t>paclock_p200_scratch</t>
         </is>
       </c>
       <c r="C744" t="inlineStr">
@@ -27205,7 +27220,7 @@
       </c>
       <c r="E744" t="inlineStr">
         <is>
-          <t>the workbook has no row for this variant</t>
+          <t>no row label for 'paclock_p200_scratch'</t>
         </is>
       </c>
     </row>
@@ -27217,22 +27232,22 @@
       </c>
       <c r="B745" t="inlineStr">
         <is>
-          <t>paclock_probe_rand</t>
+          <t>paclock_pac</t>
         </is>
       </c>
       <c r="C745" t="inlineStr">
         <is>
-          <t>[0]</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D745" t="inlineStr">
         <is>
-          <t>filled (single-seed, grey)</t>
+          <t>skipped</t>
         </is>
       </c>
       <c r="E745" t="inlineStr">
         <is>
-          <t>pr_auc 0.4076</t>
+          <t>the workbook has no row for this variant</t>
         </is>
       </c>
     </row>
@@ -27244,22 +27259,22 @@
       </c>
       <c r="B746" t="inlineStr">
         <is>
-          <t>paclock_probe_v1</t>
+          <t>paclock_probe_rand</t>
         </is>
       </c>
       <c r="C746" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>[0]</t>
         </is>
       </c>
       <c r="D746" t="inlineStr">
         <is>
-          <t>skipped</t>
+          <t>filled (single-seed, grey)</t>
         </is>
       </c>
       <c r="E746" t="inlineStr">
         <is>
-          <t>no row label for 'paclock_probe_v1'</t>
+          <t>pr_auc 0.4076</t>
         </is>
       </c>
     </row>
@@ -27271,22 +27286,22 @@
       </c>
       <c r="B747" t="inlineStr">
         <is>
-          <t>paclock_probe_v2</t>
+          <t>paclock_probe_v1</t>
         </is>
       </c>
       <c r="C747" t="inlineStr">
         <is>
-          <t>[0]</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D747" t="inlineStr">
         <is>
-          <t>filled (single-seed, grey)</t>
+          <t>skipped</t>
         </is>
       </c>
       <c r="E747" t="inlineStr">
         <is>
-          <t>pr_auc 0.5417</t>
+          <t>no row label for 'paclock_probe_v1'</t>
         </is>
       </c>
     </row>
@@ -27298,22 +27313,22 @@
       </c>
       <c r="B748" t="inlineStr">
         <is>
-          <t>paclock_ptF_frozenL3</t>
+          <t>paclock_probe_v2</t>
         </is>
       </c>
       <c r="C748" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>[0]</t>
         </is>
       </c>
       <c r="D748" t="inlineStr">
         <is>
-          <t>skipped</t>
+          <t>filled (single-seed, grey)</t>
         </is>
       </c>
       <c r="E748" t="inlineStr">
         <is>
-          <t>no row label for 'paclock_ptF_frozenL3'</t>
+          <t>pr_auc 0.5417</t>
         </is>
       </c>
     </row>
@@ -27325,7 +27340,7 @@
       </c>
       <c r="B749" t="inlineStr">
         <is>
-          <t>paclock_pt_base</t>
+          <t>paclock_ptF_frozenL3</t>
         </is>
       </c>
       <c r="C749" t="inlineStr">
@@ -27340,7 +27355,7 @@
       </c>
       <c r="E749" t="inlineStr">
         <is>
-          <t>row 'PACLock (pretrained, base)' not found</t>
+          <t>no row label for 'paclock_ptF_frozenL3'</t>
         </is>
       </c>
     </row>
@@ -27352,7 +27367,7 @@
       </c>
       <c r="B750" t="inlineStr">
         <is>
-          <t>paclock_pt_excl</t>
+          <t>paclock_pt_base</t>
         </is>
       </c>
       <c r="C750" t="inlineStr">
@@ -27367,7 +27382,7 @@
       </c>
       <c r="E750" t="inlineStr">
         <is>
-          <t>no row label for 'paclock_pt_excl'</t>
+          <t>row 'PACLock (pretrained, base)' not found</t>
         </is>
       </c>
     </row>
@@ -27379,7 +27394,7 @@
       </c>
       <c r="B751" t="inlineStr">
         <is>
-          <t>paclock_pt_large</t>
+          <t>paclock_pt_excl</t>
         </is>
       </c>
       <c r="C751" t="inlineStr">
@@ -27394,7 +27409,7 @@
       </c>
       <c r="E751" t="inlineStr">
         <is>
-          <t>row 'PACLock (pretrained, large)' not found</t>
+          <t>no row label for 'paclock_pt_excl'</t>
         </is>
       </c>
     </row>
@@ -27406,7 +27421,7 @@
       </c>
       <c r="B752" t="inlineStr">
         <is>
-          <t>paclock_rawpt_large</t>
+          <t>paclock_pt_large</t>
         </is>
       </c>
       <c r="C752" t="inlineStr">
@@ -27421,7 +27436,7 @@
       </c>
       <c r="E752" t="inlineStr">
         <is>
-          <t>no row label for 'paclock_rawpt_large'</t>
+          <t>row 'PACLock (pretrained, large)' not found</t>
         </is>
       </c>
     </row>
@@ -27433,7 +27448,7 @@
       </c>
       <c r="B753" t="inlineStr">
         <is>
-          <t>paclock_rawtok</t>
+          <t>paclock_rawpt_large</t>
         </is>
       </c>
       <c r="C753" t="inlineStr">
@@ -27448,7 +27463,7 @@
       </c>
       <c r="E753" t="inlineStr">
         <is>
-          <t>no row label for 'paclock_rawtok'</t>
+          <t>no row label for 'paclock_rawpt_large'</t>
         </is>
       </c>
     </row>
@@ -27460,7 +27475,7 @@
       </c>
       <c r="B754" t="inlineStr">
         <is>
-          <t>paclock_rot2</t>
+          <t>paclock_rawtok</t>
         </is>
       </c>
       <c r="C754" t="inlineStr">
@@ -27475,7 +27490,7 @@
       </c>
       <c r="E754" t="inlineStr">
         <is>
-          <t>no row label for 'paclock_rot2'</t>
+          <t>no row label for 'paclock_rawtok'</t>
         </is>
       </c>
     </row>
@@ -27487,7 +27502,7 @@
       </c>
       <c r="B755" t="inlineStr">
         <is>
-          <t>paclock_v2</t>
+          <t>paclock_rot2</t>
         </is>
       </c>
       <c r="C755" t="inlineStr">
@@ -27502,7 +27517,7 @@
       </c>
       <c r="E755" t="inlineStr">
         <is>
-          <t>row 'PACLock (from scratch, full)' not found</t>
+          <t>no row label for 'paclock_rot2'</t>
         </is>
       </c>
     </row>
@@ -27514,7 +27529,7 @@
       </c>
       <c r="B756" t="inlineStr">
         <is>
-          <t>paclock_v3traj_100000frozen</t>
+          <t>paclock_v2</t>
         </is>
       </c>
       <c r="C756" t="inlineStr">
@@ -27529,7 +27544,7 @@
       </c>
       <c r="E756" t="inlineStr">
         <is>
-          <t>no row label for 'paclock_v3traj_100000frozen'</t>
+          <t>row 'PACLock (from scratch, full)' not found</t>
         </is>
       </c>
     </row>
@@ -27541,7 +27556,7 @@
       </c>
       <c r="B757" t="inlineStr">
         <is>
-          <t>paclock_v3traj_100000frozenL3</t>
+          <t>paclock_v3traj_100000frozen</t>
         </is>
       </c>
       <c r="C757" t="inlineStr">
@@ -27556,7 +27571,7 @@
       </c>
       <c r="E757" t="inlineStr">
         <is>
-          <t>no row label for 'paclock_v3traj_100000frozenL3'</t>
+          <t>no row label for 'paclock_v3traj_100000frozen'</t>
         </is>
       </c>
     </row>
@@ -27568,7 +27583,7 @@
       </c>
       <c r="B758" t="inlineStr">
         <is>
-          <t>paclock_v3traj_20000frozen</t>
+          <t>paclock_v3traj_100000frozenL3</t>
         </is>
       </c>
       <c r="C758" t="inlineStr">
@@ -27583,7 +27598,7 @@
       </c>
       <c r="E758" t="inlineStr">
         <is>
-          <t>no row label for 'paclock_v3traj_20000frozen'</t>
+          <t>no row label for 'paclock_v3traj_100000frozenL3'</t>
         </is>
       </c>
     </row>
@@ -27595,7 +27610,7 @@
       </c>
       <c r="B759" t="inlineStr">
         <is>
-          <t>paclock_v3traj_20000frozenL3</t>
+          <t>paclock_v3traj_20000frozen</t>
         </is>
       </c>
       <c r="C759" t="inlineStr">
@@ -27610,7 +27625,7 @@
       </c>
       <c r="E759" t="inlineStr">
         <is>
-          <t>no row label for 'paclock_v3traj_20000frozenL3'</t>
+          <t>no row label for 'paclock_v3traj_20000frozen'</t>
         </is>
       </c>
     </row>
@@ -27622,7 +27637,7 @@
       </c>
       <c r="B760" t="inlineStr">
         <is>
-          <t>paclock_v3traj_40000frozen</t>
+          <t>paclock_v3traj_20000frozenL3</t>
         </is>
       </c>
       <c r="C760" t="inlineStr">
@@ -27637,7 +27652,7 @@
       </c>
       <c r="E760" t="inlineStr">
         <is>
-          <t>no row label for 'paclock_v3traj_40000frozen'</t>
+          <t>no row label for 'paclock_v3traj_20000frozenL3'</t>
         </is>
       </c>
     </row>
@@ -27649,7 +27664,7 @@
       </c>
       <c r="B761" t="inlineStr">
         <is>
-          <t>paclock_v3traj_40000frozenL3</t>
+          <t>paclock_v3traj_40000frozen</t>
         </is>
       </c>
       <c r="C761" t="inlineStr">
@@ -27664,7 +27679,7 @@
       </c>
       <c r="E761" t="inlineStr">
         <is>
-          <t>no row label for 'paclock_v3traj_40000frozenL3'</t>
+          <t>no row label for 'paclock_v3traj_40000frozen'</t>
         </is>
       </c>
     </row>
@@ -27676,7 +27691,7 @@
       </c>
       <c r="B762" t="inlineStr">
         <is>
-          <t>paclock_v3traj_60000frozen</t>
+          <t>paclock_v3traj_40000frozenL3</t>
         </is>
       </c>
       <c r="C762" t="inlineStr">
@@ -27691,7 +27706,7 @@
       </c>
       <c r="E762" t="inlineStr">
         <is>
-          <t>no row label for 'paclock_v3traj_60000frozen'</t>
+          <t>no row label for 'paclock_v3traj_40000frozenL3'</t>
         </is>
       </c>
     </row>
@@ -27703,7 +27718,7 @@
       </c>
       <c r="B763" t="inlineStr">
         <is>
-          <t>paclock_v3traj_60000frozenL3</t>
+          <t>paclock_v3traj_60000frozen</t>
         </is>
       </c>
       <c r="C763" t="inlineStr">
@@ -27718,7 +27733,7 @@
       </c>
       <c r="E763" t="inlineStr">
         <is>
-          <t>no row label for 'paclock_v3traj_60000frozenL3'</t>
+          <t>no row label for 'paclock_v3traj_60000frozen'</t>
         </is>
       </c>
     </row>
@@ -27730,7 +27745,7 @@
       </c>
       <c r="B764" t="inlineStr">
         <is>
-          <t>paclock_v3traj_80000frozen</t>
+          <t>paclock_v3traj_60000frozenL3</t>
         </is>
       </c>
       <c r="C764" t="inlineStr">
@@ -27745,7 +27760,7 @@
       </c>
       <c r="E764" t="inlineStr">
         <is>
-          <t>no row label for 'paclock_v3traj_80000frozen'</t>
+          <t>no row label for 'paclock_v3traj_60000frozenL3'</t>
         </is>
       </c>
     </row>
@@ -27757,7 +27772,7 @@
       </c>
       <c r="B765" t="inlineStr">
         <is>
-          <t>paclock_v3traj_80000frozenL3</t>
+          <t>paclock_v3traj_80000frozen</t>
         </is>
       </c>
       <c r="C765" t="inlineStr">
@@ -27772,7 +27787,7 @@
       </c>
       <c r="E765" t="inlineStr">
         <is>
-          <t>no row label for 'paclock_v3traj_80000frozenL3'</t>
+          <t>no row label for 'paclock_v3traj_80000frozen'</t>
         </is>
       </c>
     </row>
@@ -27784,27 +27799,22 @@
       </c>
       <c r="B766" t="inlineStr">
         <is>
-          <t>reve_pretrained</t>
+          <t>paclock_v3traj_80000frozenL3</t>
         </is>
       </c>
       <c r="C766" t="inlineStr">
         <is>
-          <t>[0, 1, 2]</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D766" t="inlineStr">
         <is>
-          <t>filled</t>
+          <t>skipped</t>
         </is>
       </c>
       <c r="E766" t="inlineStr">
         <is>
-          <t>[实测 69.46M] pr_auc per-seed 0:0.4370, 1:0.5838, 2:0.4869</t>
-        </is>
-      </c>
-      <c r="F766" t="inlineStr">
-        <is>
-          <t>stopped_by=patience lr=0.0001 batch_size=128 epochs=15 patience=10 eval_every_steps=500 loss=bce_with_logits grad_clip=1.0</t>
+          <t>no row label for 'paclock_v3traj_80000frozenL3'</t>
         </is>
       </c>
     </row>
@@ -27816,7 +27826,7 @@
       </c>
       <c r="B767" t="inlineStr">
         <is>
-          <t>sparcnet</t>
+          <t>reve_pretrained</t>
         </is>
       </c>
       <c r="C767" t="inlineStr">
@@ -27831,12 +27841,12 @@
       </c>
       <c r="E767" t="inlineStr">
         <is>
-          <t>[实测 1.14M] pr_auc per-seed 0:0.4795, 1:0.5046, 2:0.5218</t>
+          <t>[实测 69.46M] pr_auc per-seed 0:0.4370, 1:0.5838, 2:0.4869</t>
         </is>
       </c>
       <c r="F767" t="inlineStr">
         <is>
-          <t>lr=0.001 batch_size=512 epochs=20 patience=8 eval_every_steps=200 loss=bce_with_logits</t>
+          <t>stopped_by=patience lr=0.0001 batch_size=128 epochs=15 patience=10 eval_every_steps=500 loss=bce_with_logits grad_clip=1.0</t>
         </is>
       </c>
     </row>
@@ -27848,7 +27858,7 @@
       </c>
       <c r="B768" t="inlineStr">
         <is>
-          <t>st_transformer</t>
+          <t>sparcnet</t>
         </is>
       </c>
       <c r="C768" t="inlineStr">
@@ -27863,7 +27873,7 @@
       </c>
       <c r="E768" t="inlineStr">
         <is>
-          <t>[实测 3.43M] pr_auc per-seed 0:0.3318, 1:0.3515, 2:0.3933</t>
+          <t>[实测 1.14M] pr_auc per-seed 0:0.4795, 1:0.5046, 2:0.5218</t>
         </is>
       </c>
       <c r="F768" t="inlineStr">
@@ -27880,25 +27890,57 @@
       </c>
       <c r="B769" t="inlineStr">
         <is>
+          <t>st_transformer</t>
+        </is>
+      </c>
+      <c r="C769" t="inlineStr">
+        <is>
+          <t>[0, 1, 2]</t>
+        </is>
+      </c>
+      <c r="D769" t="inlineStr">
+        <is>
+          <t>filled</t>
+        </is>
+      </c>
+      <c r="E769" t="inlineStr">
+        <is>
+          <t>[实测 3.43M] pr_auc per-seed 0:0.3318, 1:0.3515, 2:0.3933</t>
+        </is>
+      </c>
+      <c r="F769" t="inlineStr">
+        <is>
+          <t>lr=0.001 batch_size=512 epochs=20 patience=8 eval_every_steps=200 loss=bce_with_logits</t>
+        </is>
+      </c>
+    </row>
+    <row r="770">
+      <c r="A770" t="inlineStr">
+        <is>
+          <t>tusz</t>
+        </is>
+      </c>
+      <c r="B770" t="inlineStr">
+        <is>
           <t>tfm_pretrained</t>
         </is>
       </c>
-      <c r="C769" t="inlineStr">
+      <c r="C770" t="inlineStr">
         <is>
           <t>[0, 1, 2]</t>
         </is>
       </c>
-      <c r="D769" t="inlineStr">
+      <c r="D770" t="inlineStr">
         <is>
           <t>filled</t>
         </is>
       </c>
-      <c r="E769" t="inlineStr">
+      <c r="E770" t="inlineStr">
         <is>
           <t>[实测 1.89M] pr_auc per-seed 0:0.3348, 1:0.3686, 2:0.3389</t>
         </is>
       </c>
-      <c r="F769" t="inlineStr">
+      <c r="F770" t="inlineStr">
         <is>
           <t>lr=0.001 batch_size=512 epochs=5 patience=10 eval_every_steps=100 loss=bce_with_logits label_smoothing=0.1</t>
         </is>
